--- a/live_mlb_hitter_fantasy_scores_2026_07_11.xlsx
+++ b/live_mlb_hitter_fantasy_scores_2026_07_11.xlsx
@@ -487,7 +487,7 @@
     <col width="27" customWidth="1" min="2" max="2"/>
     <col width="10" customWidth="1" min="3" max="3"/>
     <col width="14" customWidth="1" min="4" max="4"/>
-    <col width="15" customWidth="1" min="5" max="5"/>
+    <col width="18" customWidth="1" min="5" max="5"/>
     <col width="10" customWidth="1" min="6" max="6"/>
     <col width="13" customWidth="1" min="7" max="7"/>
     <col width="10" customWidth="1" min="8" max="8"/>
@@ -693,7 +693,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-07-11 08:11:16 PM PT</t>
+          <t>2026-07-11 08:13:16 PM PT</t>
         </is>
       </c>
       <c r="C2" t="n">
@@ -807,7 +807,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>2026-07-11 08:11:17 PM PT</t>
+          <t>2026-07-11 08:13:18 PM PT</t>
         </is>
       </c>
       <c r="C3" t="n">
@@ -921,7 +921,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-07-11 08:11:18 PM PT</t>
+          <t>2026-07-11 08:13:19 PM PT</t>
         </is>
       </c>
       <c r="C4" t="n">
@@ -934,7 +934,7 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Top 7 | 3 out</t>
+          <t>Bottom 7 | 0 out</t>
         </is>
       </c>
       <c r="F4" t="n">
@@ -942,17 +942,17 @@
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Top</t>
+          <t>Bottom</t>
         </is>
       </c>
       <c r="H4" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="I4" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="J4" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K4" t="inlineStr">
         <is>
@@ -1044,7 +1044,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>2026-07-11 08:11:17 PM PT</t>
+          <t>2026-07-11 08:13:18 PM PT</t>
         </is>
       </c>
       <c r="C5" t="n">
@@ -1158,7 +1158,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>2026-07-11 08:11:18 PM PT</t>
+          <t>2026-07-11 08:13:18 PM PT</t>
         </is>
       </c>
       <c r="C6" t="n">
@@ -1272,7 +1272,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>2026-07-11 08:11:17 PM PT</t>
+          <t>2026-07-11 08:13:17 PM PT</t>
         </is>
       </c>
       <c r="C7" t="n">
@@ -1386,7 +1386,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>2026-07-11 08:11:17 PM PT</t>
+          <t>2026-07-11 08:13:18 PM PT</t>
         </is>
       </c>
       <c r="C8" t="n">
@@ -1500,7 +1500,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>2026-07-11 08:11:16 PM PT</t>
+          <t>2026-07-11 08:13:17 PM PT</t>
         </is>
       </c>
       <c r="C9" t="n">
@@ -1614,7 +1614,7 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>2026-07-11 08:11:18 PM PT</t>
+          <t>2026-07-11 08:13:19 PM PT</t>
         </is>
       </c>
       <c r="C10" t="n">
@@ -1627,7 +1627,7 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Top 7 | 3 out</t>
+          <t>Bottom 7 | 0 out</t>
         </is>
       </c>
       <c r="F10" t="n">
@@ -1635,17 +1635,17 @@
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Top</t>
+          <t>Bottom</t>
         </is>
       </c>
       <c r="H10" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="I10" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="J10" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K10" t="inlineStr">
         <is>
@@ -1737,7 +1737,7 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>2026-07-11 08:11:17 PM PT</t>
+          <t>2026-07-11 08:13:18 PM PT</t>
         </is>
       </c>
       <c r="C11" t="n">
@@ -1851,7 +1851,7 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>2026-07-11 08:11:17 PM PT</t>
+          <t>2026-07-11 08:13:18 PM PT</t>
         </is>
       </c>
       <c r="C12" t="n">
@@ -1965,7 +1965,7 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>2026-07-11 08:11:18 PM PT</t>
+          <t>2026-07-11 08:13:19 PM PT</t>
         </is>
       </c>
       <c r="C13" t="n">
@@ -1978,7 +1978,7 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Top 7 | 3 out</t>
+          <t>Bottom 7 | 0 out</t>
         </is>
       </c>
       <c r="F13" t="n">
@@ -1986,17 +1986,17 @@
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Top</t>
+          <t>Bottom</t>
         </is>
       </c>
       <c r="H13" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="I13" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="J13" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K13" t="inlineStr">
         <is>
@@ -2088,7 +2088,7 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>2026-07-11 08:11:17 PM PT</t>
+          <t>2026-07-11 08:13:18 PM PT</t>
         </is>
       </c>
       <c r="C14" t="n">
@@ -2202,7 +2202,7 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>2026-07-11 08:11:17 PM PT</t>
+          <t>2026-07-11 08:13:17 PM PT</t>
         </is>
       </c>
       <c r="C15" t="n">
@@ -2316,7 +2316,7 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>2026-07-11 08:11:17 PM PT</t>
+          <t>2026-07-11 08:13:18 PM PT</t>
         </is>
       </c>
       <c r="C16" t="n">
@@ -2430,7 +2430,7 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>2026-07-11 08:11:18 PM PT</t>
+          <t>2026-07-11 08:13:19 PM PT</t>
         </is>
       </c>
       <c r="C17" t="n">
@@ -2443,7 +2443,7 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Top 7 | 3 out</t>
+          <t>Bottom 7 | 0 out</t>
         </is>
       </c>
       <c r="F17" t="n">
@@ -2451,17 +2451,17 @@
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Top</t>
+          <t>Bottom</t>
         </is>
       </c>
       <c r="H17" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="I17" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="J17" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K17" t="inlineStr">
         <is>
@@ -2553,7 +2553,7 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>2026-07-11 08:11:17 PM PT</t>
+          <t>2026-07-11 08:13:17 PM PT</t>
         </is>
       </c>
       <c r="C18" t="n">
@@ -2667,7 +2667,7 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>2026-07-11 08:11:18 PM PT</t>
+          <t>2026-07-11 08:13:18 PM PT</t>
         </is>
       </c>
       <c r="C19" t="n">
@@ -2781,7 +2781,7 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>2026-07-11 08:11:17 PM PT</t>
+          <t>2026-07-11 08:13:17 PM PT</t>
         </is>
       </c>
       <c r="C20" t="n">
@@ -2895,7 +2895,7 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>2026-07-11 08:11:17 PM PT</t>
+          <t>2026-07-11 08:13:17 PM PT</t>
         </is>
       </c>
       <c r="C21" t="n">
@@ -3009,7 +3009,7 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>2026-07-11 08:11:18 PM PT</t>
+          <t>2026-07-11 08:13:19 PM PT</t>
         </is>
       </c>
       <c r="C22" t="n">
@@ -3037,10 +3037,10 @@
         <v>1</v>
       </c>
       <c r="I22" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J22" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="K22" t="inlineStr">
         <is>
@@ -3132,7 +3132,7 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>2026-07-11 08:11:17 PM PT</t>
+          <t>2026-07-11 08:13:18 PM PT</t>
         </is>
       </c>
       <c r="C23" t="n">
@@ -3246,7 +3246,7 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>2026-07-11 08:11:17 PM PT</t>
+          <t>2026-07-11 08:13:17 PM PT</t>
         </is>
       </c>
       <c r="C24" t="n">
@@ -3360,7 +3360,7 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>2026-07-11 08:11:18 PM PT</t>
+          <t>2026-07-11 08:13:18 PM PT</t>
         </is>
       </c>
       <c r="C25" t="n">
@@ -3474,7 +3474,7 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>2026-07-11 08:11:16 PM PT</t>
+          <t>2026-07-11 08:13:16 PM PT</t>
         </is>
       </c>
       <c r="C26" t="n">
@@ -3588,7 +3588,7 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>2026-07-11 08:11:17 PM PT</t>
+          <t>2026-07-11 08:13:17 PM PT</t>
         </is>
       </c>
       <c r="C27" t="n">
@@ -3702,7 +3702,7 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>2026-07-11 08:11:17 PM PT</t>
+          <t>2026-07-11 08:13:18 PM PT</t>
         </is>
       </c>
       <c r="C28" t="n">
@@ -3816,7 +3816,7 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>2026-07-11 08:11:18 PM PT</t>
+          <t>2026-07-11 08:13:18 PM PT</t>
         </is>
       </c>
       <c r="C29" t="n">
@@ -3930,7 +3930,7 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>2026-07-11 08:11:18 PM PT</t>
+          <t>2026-07-11 08:13:18 PM PT</t>
         </is>
       </c>
       <c r="C30" t="n">
@@ -4044,7 +4044,7 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>2026-07-11 08:11:17 PM PT</t>
+          <t>2026-07-11 08:13:18 PM PT</t>
         </is>
       </c>
       <c r="C31" t="n">
@@ -4158,7 +4158,7 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>2026-07-11 08:11:17 PM PT</t>
+          <t>2026-07-11 08:13:18 PM PT</t>
         </is>
       </c>
       <c r="C32" t="n">
@@ -4272,7 +4272,7 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>2026-07-11 08:11:17 PM PT</t>
+          <t>2026-07-11 08:13:18 PM PT</t>
         </is>
       </c>
       <c r="C33" t="n">
@@ -4386,7 +4386,7 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>2026-07-11 08:11:16 PM PT</t>
+          <t>2026-07-11 08:13:16 PM PT</t>
         </is>
       </c>
       <c r="C34" t="n">
@@ -4500,7 +4500,7 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>2026-07-11 08:11:16 PM PT</t>
+          <t>2026-07-11 08:13:16 PM PT</t>
         </is>
       </c>
       <c r="C35" t="n">
@@ -4614,7 +4614,7 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>2026-07-11 08:11:18 PM PT</t>
+          <t>2026-07-11 08:13:19 PM PT</t>
         </is>
       </c>
       <c r="C36" t="n">
@@ -4627,7 +4627,7 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Top 7 | 3 out</t>
+          <t>Bottom 7 | 0 out</t>
         </is>
       </c>
       <c r="F36" t="n">
@@ -4635,17 +4635,17 @@
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Top</t>
+          <t>Bottom</t>
         </is>
       </c>
       <c r="H36" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="I36" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="J36" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K36" t="inlineStr">
         <is>
@@ -4737,7 +4737,7 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>2026-07-11 08:11:17 PM PT</t>
+          <t>2026-07-11 08:13:18 PM PT</t>
         </is>
       </c>
       <c r="C37" t="n">
@@ -4851,7 +4851,7 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>2026-07-11 08:11:16 PM PT</t>
+          <t>2026-07-11 08:13:17 PM PT</t>
         </is>
       </c>
       <c r="C38" t="n">
@@ -4965,7 +4965,7 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>2026-07-11 08:11:17 PM PT</t>
+          <t>2026-07-11 08:13:18 PM PT</t>
         </is>
       </c>
       <c r="C39" t="n">
@@ -5079,7 +5079,7 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>2026-07-11 08:11:16 PM PT</t>
+          <t>2026-07-11 08:13:16 PM PT</t>
         </is>
       </c>
       <c r="C40" t="n">
@@ -5193,7 +5193,7 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>2026-07-11 08:11:18 PM PT</t>
+          <t>2026-07-11 08:13:19 PM PT</t>
         </is>
       </c>
       <c r="C41" t="n">
@@ -5221,10 +5221,10 @@
         <v>1</v>
       </c>
       <c r="I41" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J41" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="K41" t="inlineStr">
         <is>
@@ -5316,7 +5316,7 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>2026-07-11 08:11:18 PM PT</t>
+          <t>2026-07-11 08:13:18 PM PT</t>
         </is>
       </c>
       <c r="C42" t="n">
@@ -5430,7 +5430,7 @@
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>2026-07-11 08:11:17 PM PT</t>
+          <t>2026-07-11 08:13:18 PM PT</t>
         </is>
       </c>
       <c r="C43" t="n">
@@ -5544,7 +5544,7 @@
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>2026-07-11 08:11:17 PM PT</t>
+          <t>2026-07-11 08:13:18 PM PT</t>
         </is>
       </c>
       <c r="C44" t="n">
@@ -5658,7 +5658,7 @@
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>2026-07-11 08:11:18 PM PT</t>
+          <t>2026-07-11 08:13:18 PM PT</t>
         </is>
       </c>
       <c r="C45" t="n">
@@ -5772,7 +5772,7 @@
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>2026-07-11 08:11:17 PM PT</t>
+          <t>2026-07-11 08:13:18 PM PT</t>
         </is>
       </c>
       <c r="C46" t="n">
@@ -5886,7 +5886,7 @@
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>2026-07-11 08:11:17 PM PT</t>
+          <t>2026-07-11 08:13:17 PM PT</t>
         </is>
       </c>
       <c r="C47" t="n">
@@ -6000,7 +6000,7 @@
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>2026-07-11 08:11:17 PM PT</t>
+          <t>2026-07-11 08:13:18 PM PT</t>
         </is>
       </c>
       <c r="C48" t="n">
@@ -6114,7 +6114,7 @@
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>2026-07-11 08:11:17 PM PT</t>
+          <t>2026-07-11 08:13:17 PM PT</t>
         </is>
       </c>
       <c r="C49" t="n">
@@ -6228,7 +6228,7 @@
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>2026-07-11 08:11:16 PM PT</t>
+          <t>2026-07-11 08:13:16 PM PT</t>
         </is>
       </c>
       <c r="C50" t="n">
@@ -6342,7 +6342,7 @@
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>2026-07-11 08:11:18 PM PT</t>
+          <t>2026-07-11 08:13:18 PM PT</t>
         </is>
       </c>
       <c r="C51" t="n">
@@ -6456,7 +6456,7 @@
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>2026-07-11 08:11:18 PM PT</t>
+          <t>2026-07-11 08:13:18 PM PT</t>
         </is>
       </c>
       <c r="C52" t="n">
@@ -6570,7 +6570,7 @@
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>2026-07-11 08:11:17 PM PT</t>
+          <t>2026-07-11 08:13:18 PM PT</t>
         </is>
       </c>
       <c r="C53" t="n">
@@ -6684,7 +6684,7 @@
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>2026-07-11 08:11:16 PM PT</t>
+          <t>2026-07-11 08:13:17 PM PT</t>
         </is>
       </c>
       <c r="C54" t="n">
@@ -6798,7 +6798,7 @@
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>2026-07-11 08:11:16 PM PT</t>
+          <t>2026-07-11 08:13:17 PM PT</t>
         </is>
       </c>
       <c r="C55" t="n">
@@ -6912,7 +6912,7 @@
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>2026-07-11 08:11:16 PM PT</t>
+          <t>2026-07-11 08:13:17 PM PT</t>
         </is>
       </c>
       <c r="C56" t="n">
@@ -7026,7 +7026,7 @@
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>2026-07-11 08:11:17 PM PT</t>
+          <t>2026-07-11 08:13:18 PM PT</t>
         </is>
       </c>
       <c r="C57" t="n">
@@ -7140,7 +7140,7 @@
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>2026-07-11 08:11:17 PM PT</t>
+          <t>2026-07-11 08:13:17 PM PT</t>
         </is>
       </c>
       <c r="C58" t="n">
@@ -7254,7 +7254,7 @@
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>2026-07-11 08:11:16 PM PT</t>
+          <t>2026-07-11 08:13:17 PM PT</t>
         </is>
       </c>
       <c r="C59" t="n">
@@ -7368,7 +7368,7 @@
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>2026-07-11 08:11:16 PM PT</t>
+          <t>2026-07-11 08:13:16 PM PT</t>
         </is>
       </c>
       <c r="C60" t="n">
@@ -7482,7 +7482,7 @@
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>2026-07-11 08:11:16 PM PT</t>
+          <t>2026-07-11 08:13:16 PM PT</t>
         </is>
       </c>
       <c r="C61" t="n">
@@ -7596,7 +7596,7 @@
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>2026-07-11 08:11:18 PM PT</t>
+          <t>2026-07-11 08:13:19 PM PT</t>
         </is>
       </c>
       <c r="C62" t="n">
@@ -7609,7 +7609,7 @@
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>Top 7 | 3 out</t>
+          <t>Bottom 7 | 0 out</t>
         </is>
       </c>
       <c r="F62" t="n">
@@ -7617,17 +7617,17 @@
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Top</t>
+          <t>Bottom</t>
         </is>
       </c>
       <c r="H62" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="I62" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="J62" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K62" t="inlineStr">
         <is>
@@ -7719,7 +7719,7 @@
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>2026-07-11 08:11:17 PM PT</t>
+          <t>2026-07-11 08:13:17 PM PT</t>
         </is>
       </c>
       <c r="C63" t="n">
@@ -7833,7 +7833,7 @@
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>2026-07-11 08:11:17 PM PT</t>
+          <t>2026-07-11 08:13:18 PM PT</t>
         </is>
       </c>
       <c r="C64" t="n">
@@ -7947,7 +7947,7 @@
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>2026-07-11 08:11:18 PM PT</t>
+          <t>2026-07-11 08:13:19 PM PT</t>
         </is>
       </c>
       <c r="C65" t="n">
@@ -7960,7 +7960,7 @@
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>Top 7 | 3 out</t>
+          <t>Bottom 7 | 0 out</t>
         </is>
       </c>
       <c r="F65" t="n">
@@ -7968,17 +7968,17 @@
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>Top</t>
+          <t>Bottom</t>
         </is>
       </c>
       <c r="H65" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="I65" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="J65" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K65" t="inlineStr">
         <is>
@@ -8070,7 +8070,7 @@
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>2026-07-11 08:11:17 PM PT</t>
+          <t>2026-07-11 08:13:18 PM PT</t>
         </is>
       </c>
       <c r="C66" t="n">
@@ -8184,7 +8184,7 @@
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>2026-07-11 08:11:17 PM PT</t>
+          <t>2026-07-11 08:13:17 PM PT</t>
         </is>
       </c>
       <c r="C67" t="n">
@@ -8298,7 +8298,7 @@
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>2026-07-11 08:11:16 PM PT</t>
+          <t>2026-07-11 08:13:17 PM PT</t>
         </is>
       </c>
       <c r="C68" t="n">
@@ -8412,7 +8412,7 @@
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>2026-07-11 08:11:18 PM PT</t>
+          <t>2026-07-11 08:13:19 PM PT</t>
         </is>
       </c>
       <c r="C69" t="n">
@@ -8440,10 +8440,10 @@
         <v>1</v>
       </c>
       <c r="I69" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J69" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="K69" t="inlineStr">
         <is>
@@ -8535,7 +8535,7 @@
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>2026-07-11 08:11:16 PM PT</t>
+          <t>2026-07-11 08:13:16 PM PT</t>
         </is>
       </c>
       <c r="C70" t="n">
@@ -8649,7 +8649,7 @@
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>2026-07-11 08:11:17 PM PT</t>
+          <t>2026-07-11 08:13:17 PM PT</t>
         </is>
       </c>
       <c r="C71" t="n">
@@ -8763,7 +8763,7 @@
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>2026-07-11 08:11:16 PM PT</t>
+          <t>2026-07-11 08:13:16 PM PT</t>
         </is>
       </c>
       <c r="C72" t="n">
@@ -8877,7 +8877,7 @@
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>2026-07-11 08:11:18 PM PT</t>
+          <t>2026-07-11 08:13:19 PM PT</t>
         </is>
       </c>
       <c r="C73" t="n">
@@ -8890,7 +8890,7 @@
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>Top 7 | 3 out</t>
+          <t>Bottom 7 | 0 out</t>
         </is>
       </c>
       <c r="F73" t="n">
@@ -8898,17 +8898,17 @@
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>Top</t>
+          <t>Bottom</t>
         </is>
       </c>
       <c r="H73" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="I73" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="J73" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K73" t="inlineStr">
         <is>
@@ -9000,7 +9000,7 @@
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>2026-07-11 08:11:18 PM PT</t>
+          <t>2026-07-11 08:13:19 PM PT</t>
         </is>
       </c>
       <c r="C74" t="n">
@@ -9028,10 +9028,10 @@
         <v>1</v>
       </c>
       <c r="I74" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J74" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="K74" t="inlineStr">
         <is>
@@ -9123,7 +9123,7 @@
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>2026-07-11 08:11:18 PM PT</t>
+          <t>2026-07-11 08:13:18 PM PT</t>
         </is>
       </c>
       <c r="C75" t="n">
@@ -9237,7 +9237,7 @@
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>2026-07-11 08:11:18 PM PT</t>
+          <t>2026-07-11 08:13:18 PM PT</t>
         </is>
       </c>
       <c r="C76" t="n">
@@ -9351,7 +9351,7 @@
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>2026-07-11 08:11:17 PM PT</t>
+          <t>2026-07-11 08:13:18 PM PT</t>
         </is>
       </c>
       <c r="C77" t="n">
@@ -9465,7 +9465,7 @@
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>2026-07-11 08:11:16 PM PT</t>
+          <t>2026-07-11 08:13:16 PM PT</t>
         </is>
       </c>
       <c r="C78" t="n">
@@ -9579,7 +9579,7 @@
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>2026-07-11 08:11:16 PM PT</t>
+          <t>2026-07-11 08:13:16 PM PT</t>
         </is>
       </c>
       <c r="C79" t="n">
@@ -9693,7 +9693,7 @@
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>2026-07-11 08:11:16 PM PT</t>
+          <t>2026-07-11 08:13:16 PM PT</t>
         </is>
       </c>
       <c r="C80" t="n">
@@ -9807,7 +9807,7 @@
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>2026-07-11 08:11:16 PM PT</t>
+          <t>2026-07-11 08:13:16 PM PT</t>
         </is>
       </c>
       <c r="C81" t="n">
@@ -9921,7 +9921,7 @@
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>2026-07-11 08:11:16 PM PT</t>
+          <t>2026-07-11 08:13:16 PM PT</t>
         </is>
       </c>
       <c r="C82" t="n">
@@ -10035,7 +10035,7 @@
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>2026-07-11 08:11:16 PM PT</t>
+          <t>2026-07-11 08:13:16 PM PT</t>
         </is>
       </c>
       <c r="C83" t="n">
@@ -10149,7 +10149,7 @@
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>2026-07-11 08:11:17 PM PT</t>
+          <t>2026-07-11 08:13:17 PM PT</t>
         </is>
       </c>
       <c r="C84" t="n">
@@ -10263,7 +10263,7 @@
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>2026-07-11 08:11:17 PM PT</t>
+          <t>2026-07-11 08:13:17 PM PT</t>
         </is>
       </c>
       <c r="C85" t="n">
@@ -10377,7 +10377,7 @@
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>2026-07-11 08:11:17 PM PT</t>
+          <t>2026-07-11 08:13:17 PM PT</t>
         </is>
       </c>
       <c r="C86" t="n">
@@ -10491,7 +10491,7 @@
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>2026-07-11 08:11:17 PM PT</t>
+          <t>2026-07-11 08:13:18 PM PT</t>
         </is>
       </c>
       <c r="C87" t="n">
@@ -10605,7 +10605,7 @@
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>2026-07-11 08:11:18 PM PT</t>
+          <t>2026-07-11 08:13:19 PM PT</t>
         </is>
       </c>
       <c r="C88" t="n">
@@ -10618,7 +10618,7 @@
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>Top 7 | 3 out</t>
+          <t>Bottom 7 | 0 out</t>
         </is>
       </c>
       <c r="F88" t="n">
@@ -10626,17 +10626,17 @@
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>Top</t>
+          <t>Bottom</t>
         </is>
       </c>
       <c r="H88" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="I88" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="J88" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K88" t="inlineStr">
         <is>
@@ -10728,7 +10728,7 @@
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>2026-07-11 08:11:17 PM PT</t>
+          <t>2026-07-11 08:13:17 PM PT</t>
         </is>
       </c>
       <c r="C89" t="n">
@@ -10842,7 +10842,7 @@
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>2026-07-11 08:11:18 PM PT</t>
+          <t>2026-07-11 08:13:18 PM PT</t>
         </is>
       </c>
       <c r="C90" t="n">
@@ -10956,7 +10956,7 @@
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>2026-07-11 08:11:17 PM PT</t>
+          <t>2026-07-11 08:13:18 PM PT</t>
         </is>
       </c>
       <c r="C91" t="n">
@@ -11070,7 +11070,7 @@
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>2026-07-11 08:11:17 PM PT</t>
+          <t>2026-07-11 08:13:18 PM PT</t>
         </is>
       </c>
       <c r="C92" t="n">
@@ -11184,7 +11184,7 @@
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>2026-07-11 08:11:17 PM PT</t>
+          <t>2026-07-11 08:13:17 PM PT</t>
         </is>
       </c>
       <c r="C93" t="n">
@@ -11298,7 +11298,7 @@
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>2026-07-11 08:11:17 PM PT</t>
+          <t>2026-07-11 08:13:18 PM PT</t>
         </is>
       </c>
       <c r="C94" t="n">
@@ -11412,7 +11412,7 @@
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>2026-07-11 08:11:17 PM PT</t>
+          <t>2026-07-11 08:13:18 PM PT</t>
         </is>
       </c>
       <c r="C95" t="n">
@@ -11526,7 +11526,7 @@
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>2026-07-11 08:11:18 PM PT</t>
+          <t>2026-07-11 08:13:19 PM PT</t>
         </is>
       </c>
       <c r="C96" t="n">
@@ -11554,10 +11554,10 @@
         <v>1</v>
       </c>
       <c r="I96" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J96" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="K96" t="inlineStr">
         <is>
@@ -11649,7 +11649,7 @@
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>2026-07-11 08:11:17 PM PT</t>
+          <t>2026-07-11 08:13:18 PM PT</t>
         </is>
       </c>
       <c r="C97" t="n">
@@ -11763,7 +11763,7 @@
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>2026-07-11 08:11:16 PM PT</t>
+          <t>2026-07-11 08:13:16 PM PT</t>
         </is>
       </c>
       <c r="C98" t="n">
@@ -11877,7 +11877,7 @@
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>2026-07-11 08:11:16 PM PT</t>
+          <t>2026-07-11 08:13:17 PM PT</t>
         </is>
       </c>
       <c r="C99" t="n">
@@ -11991,7 +11991,7 @@
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>2026-07-11 08:11:17 PM PT</t>
+          <t>2026-07-11 08:13:17 PM PT</t>
         </is>
       </c>
       <c r="C100" t="n">
@@ -12105,7 +12105,7 @@
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>2026-07-11 08:11:18 PM PT</t>
+          <t>2026-07-11 08:13:19 PM PT</t>
         </is>
       </c>
       <c r="C101" t="n">
@@ -12118,7 +12118,7 @@
       </c>
       <c r="E101" t="inlineStr">
         <is>
-          <t>Top 7 | 3 out</t>
+          <t>Bottom 7 | 0 out</t>
         </is>
       </c>
       <c r="F101" t="n">
@@ -12126,17 +12126,17 @@
       </c>
       <c r="G101" t="inlineStr">
         <is>
-          <t>Top</t>
+          <t>Bottom</t>
         </is>
       </c>
       <c r="H101" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="I101" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="J101" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K101" t="inlineStr">
         <is>
@@ -12228,7 +12228,7 @@
       </c>
       <c r="B102" t="inlineStr">
         <is>
-          <t>2026-07-11 08:11:17 PM PT</t>
+          <t>2026-07-11 08:13:18 PM PT</t>
         </is>
       </c>
       <c r="C102" t="n">
@@ -12342,7 +12342,7 @@
       </c>
       <c r="B103" t="inlineStr">
         <is>
-          <t>2026-07-11 08:11:17 PM PT</t>
+          <t>2026-07-11 08:13:18 PM PT</t>
         </is>
       </c>
       <c r="C103" t="n">
@@ -12456,7 +12456,7 @@
       </c>
       <c r="B104" t="inlineStr">
         <is>
-          <t>2026-07-11 08:11:17 PM PT</t>
+          <t>2026-07-11 08:13:18 PM PT</t>
         </is>
       </c>
       <c r="C104" t="n">
@@ -12570,7 +12570,7 @@
       </c>
       <c r="B105" t="inlineStr">
         <is>
-          <t>2026-07-11 08:11:17 PM PT</t>
+          <t>2026-07-11 08:13:17 PM PT</t>
         </is>
       </c>
       <c r="C105" t="n">
@@ -12684,7 +12684,7 @@
       </c>
       <c r="B106" t="inlineStr">
         <is>
-          <t>2026-07-11 08:11:17 PM PT</t>
+          <t>2026-07-11 08:13:17 PM PT</t>
         </is>
       </c>
       <c r="C106" t="n">
@@ -12798,7 +12798,7 @@
       </c>
       <c r="B107" t="inlineStr">
         <is>
-          <t>2026-07-11 08:11:17 PM PT</t>
+          <t>2026-07-11 08:13:18 PM PT</t>
         </is>
       </c>
       <c r="C107" t="n">
@@ -12912,30 +12912,39 @@
       </c>
       <c r="B108" t="inlineStr">
         <is>
-          <t>2026-07-11 08:11:17 PM PT</t>
+          <t>2026-07-11 08:13:19 PM PT</t>
         </is>
       </c>
       <c r="C108" t="n">
-        <v>824576</v>
+        <v>823926</v>
       </c>
       <c r="D108" t="inlineStr">
         <is>
-          <t>11:10 AM PT</t>
+          <t>6:10 PM PT</t>
         </is>
       </c>
       <c r="E108" t="inlineStr">
         <is>
-          <t>Final</t>
+          <t>Top 7 | 1 out</t>
         </is>
       </c>
       <c r="F108" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="G108" t="inlineStr">
         <is>
           <t>Top</t>
         </is>
       </c>
+      <c r="H108" t="n">
+        <v>1</v>
+      </c>
+      <c r="I108" t="n">
+        <v>0</v>
+      </c>
+      <c r="J108" t="n">
+        <v>0</v>
+      </c>
       <c r="K108" t="inlineStr">
         <is>
           <t>Away</t>
@@ -12943,37 +12952,37 @@
       </c>
       <c r="L108" t="inlineStr">
         <is>
-          <t>ATH</t>
+          <t>ARI</t>
         </is>
       </c>
       <c r="M108" t="inlineStr">
         <is>
-          <t>CWS</t>
+          <t>LAD</t>
         </is>
       </c>
       <c r="N108" t="inlineStr">
         <is>
-          <t>Lawrence Butler</t>
+          <t>Geraldo Perdomo</t>
         </is>
       </c>
       <c r="O108" t="n">
-        <v>671732</v>
+        <v>672695</v>
       </c>
       <c r="P108" t="inlineStr">
         <is>
-          <t>RF</t>
+          <t>SS</t>
         </is>
       </c>
       <c r="Q108" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>2</t>
         </is>
       </c>
       <c r="R108" t="n">
         <v>4</v>
       </c>
       <c r="S108" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="T108" t="n">
         <v>0</v>
@@ -12991,16 +13000,16 @@
         <v>0</v>
       </c>
       <c r="Y108" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Z108" t="n">
         <v>0</v>
       </c>
       <c r="AA108" s="5" t="n">
-        <v>3</v>
-      </c>
-      <c r="AB108" t="n">
-        <v>0</v>
+        <v>1</v>
+      </c>
+      <c r="AB108" s="9" t="n">
+        <v>1</v>
       </c>
       <c r="AC108" t="n">
         <v>0</v>
@@ -13012,10 +13021,10 @@
         <v>6</v>
       </c>
       <c r="AF108" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="AG108" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
     </row>
     <row r="109">
@@ -13026,15 +13035,15 @@
       </c>
       <c r="B109" t="inlineStr">
         <is>
-          <t>2026-07-11 08:11:18 PM PT</t>
+          <t>2026-07-11 08:13:17 PM PT</t>
         </is>
       </c>
       <c r="C109" t="n">
-        <v>824492</v>
+        <v>824576</v>
       </c>
       <c r="D109" t="inlineStr">
         <is>
-          <t>4:10 PM PT</t>
+          <t>11:10 AM PT</t>
         </is>
       </c>
       <c r="E109" t="inlineStr">
@@ -13047,71 +13056,71 @@
       </c>
       <c r="G109" t="inlineStr">
         <is>
-          <t>Bottom</t>
+          <t>Top</t>
         </is>
       </c>
       <c r="K109" t="inlineStr">
         <is>
-          <t>Home</t>
+          <t>Away</t>
         </is>
       </c>
       <c r="L109" t="inlineStr">
         <is>
-          <t>CIN</t>
+          <t>ATH</t>
         </is>
       </c>
       <c r="M109" t="inlineStr">
         <is>
-          <t>CHC</t>
+          <t>CWS</t>
         </is>
       </c>
       <c r="N109" t="inlineStr">
         <is>
-          <t>TJ Friedl</t>
+          <t>Lawrence Butler</t>
         </is>
       </c>
       <c r="O109" t="n">
-        <v>670770</v>
+        <v>671732</v>
       </c>
       <c r="P109" t="inlineStr">
         <is>
-          <t>CF</t>
+          <t>RF</t>
         </is>
       </c>
       <c r="Q109" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>6</t>
         </is>
       </c>
       <c r="R109" t="n">
+        <v>4</v>
+      </c>
+      <c r="S109" t="n">
+        <v>1</v>
+      </c>
+      <c r="T109" t="n">
+        <v>0</v>
+      </c>
+      <c r="U109" t="n">
+        <v>0</v>
+      </c>
+      <c r="V109" t="n">
+        <v>0</v>
+      </c>
+      <c r="W109" t="n">
+        <v>0</v>
+      </c>
+      <c r="X109" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y109" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z109" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA109" s="5" t="n">
         <v>3</v>
-      </c>
-      <c r="S109" t="n">
-        <v>3</v>
-      </c>
-      <c r="T109" t="n">
-        <v>2</v>
-      </c>
-      <c r="U109" t="n">
-        <v>2</v>
-      </c>
-      <c r="V109" t="n">
-        <v>0</v>
-      </c>
-      <c r="W109" t="n">
-        <v>0</v>
-      </c>
-      <c r="X109" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y109" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z109" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA109" t="n">
-        <v>0</v>
       </c>
       <c r="AB109" t="n">
         <v>0</v>
@@ -13126,10 +13135,10 @@
         <v>6</v>
       </c>
       <c r="AF109" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="AG109" t="n">
-        <v>11</v>
+        <v>4</v>
       </c>
     </row>
     <row r="110">
@@ -13140,15 +13149,15 @@
       </c>
       <c r="B110" t="inlineStr">
         <is>
-          <t>2026-07-11 08:11:17 PM PT</t>
+          <t>2026-07-11 08:13:18 PM PT</t>
         </is>
       </c>
       <c r="C110" t="n">
-        <v>823844</v>
+        <v>824492</v>
       </c>
       <c r="D110" t="inlineStr">
         <is>
-          <t>1:10 PM PT</t>
+          <t>4:10 PM PT</t>
         </is>
       </c>
       <c r="E110" t="inlineStr">
@@ -13166,42 +13175,42 @@
       </c>
       <c r="K110" t="inlineStr">
         <is>
-          <t>Away</t>
+          <t>Home</t>
         </is>
       </c>
       <c r="L110" t="inlineStr">
         <is>
-          <t>CLE</t>
+          <t>CIN</t>
         </is>
       </c>
       <c r="M110" t="inlineStr">
         <is>
-          <t>MIA</t>
+          <t>CHC</t>
         </is>
       </c>
       <c r="N110" t="inlineStr">
         <is>
-          <t>Brayan Rocchio</t>
+          <t>TJ Friedl</t>
         </is>
       </c>
       <c r="O110" t="n">
-        <v>677587</v>
+        <v>670770</v>
       </c>
       <c r="P110" t="inlineStr">
         <is>
-          <t>SS</t>
+          <t>CF</t>
         </is>
       </c>
       <c r="Q110" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>9</t>
         </is>
       </c>
       <c r="R110" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="S110" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="T110" t="n">
         <v>2</v>
@@ -13240,7 +13249,7 @@
         <v>6</v>
       </c>
       <c r="AF110" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="AG110" t="n">
         <v>11</v>
@@ -13254,15 +13263,15 @@
       </c>
       <c r="B111" t="inlineStr">
         <is>
-          <t>2026-07-11 08:11:17 PM PT</t>
+          <t>2026-07-11 08:13:18 PM PT</t>
         </is>
       </c>
       <c r="C111" t="n">
-        <v>823198</v>
+        <v>823844</v>
       </c>
       <c r="D111" t="inlineStr">
         <is>
-          <t>1:05 PM PT</t>
+          <t>1:10 PM PT</t>
         </is>
       </c>
       <c r="E111" t="inlineStr">
@@ -13275,7 +13284,7 @@
       </c>
       <c r="G111" t="inlineStr">
         <is>
-          <t>Top</t>
+          <t>Bottom</t>
         </is>
       </c>
       <c r="K111" t="inlineStr">
@@ -13285,25 +13294,25 @@
       </c>
       <c r="L111" t="inlineStr">
         <is>
-          <t>COL</t>
+          <t>CLE</t>
         </is>
       </c>
       <c r="M111" t="inlineStr">
         <is>
-          <t>SF</t>
+          <t>MIA</t>
         </is>
       </c>
       <c r="N111" t="inlineStr">
         <is>
-          <t>Mickey Moniak</t>
+          <t>Brayan Rocchio</t>
         </is>
       </c>
       <c r="O111" t="n">
-        <v>666160</v>
+        <v>677587</v>
       </c>
       <c r="P111" t="inlineStr">
         <is>
-          <t>LF</t>
+          <t>SS</t>
         </is>
       </c>
       <c r="Q111" t="inlineStr">
@@ -13312,10 +13321,10 @@
         </is>
       </c>
       <c r="R111" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="S111" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="T111" t="n">
         <v>2</v>
@@ -13348,16 +13357,16 @@
         <v>0</v>
       </c>
       <c r="AD111" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AE111" s="4" t="n">
         <v>6</v>
       </c>
       <c r="AF111" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="AG111" t="n">
-        <v>6</v>
+        <v>11</v>
       </c>
     </row>
     <row r="112">
@@ -13368,15 +13377,15 @@
       </c>
       <c r="B112" t="inlineStr">
         <is>
-          <t>2026-07-11 08:11:17 PM PT</t>
+          <t>2026-07-11 08:13:17 PM PT</t>
         </is>
       </c>
       <c r="C112" t="n">
-        <v>824249</v>
+        <v>823198</v>
       </c>
       <c r="D112" t="inlineStr">
         <is>
-          <t>3:10 PM PT</t>
+          <t>1:05 PM PT</t>
         </is>
       </c>
       <c r="E112" t="inlineStr">
@@ -13389,47 +13398,47 @@
       </c>
       <c r="G112" t="inlineStr">
         <is>
-          <t>Bottom</t>
+          <t>Top</t>
         </is>
       </c>
       <c r="K112" t="inlineStr">
         <is>
-          <t>Home</t>
+          <t>Away</t>
         </is>
       </c>
       <c r="L112" t="inlineStr">
         <is>
-          <t>DET</t>
+          <t>COL</t>
         </is>
       </c>
       <c r="M112" t="inlineStr">
         <is>
-          <t>PHI</t>
+          <t>SF</t>
         </is>
       </c>
       <c r="N112" t="inlineStr">
         <is>
-          <t>Hao-Yu Lee</t>
+          <t>Mickey Moniak</t>
         </is>
       </c>
       <c r="O112" t="n">
-        <v>701678</v>
+        <v>666160</v>
       </c>
       <c r="P112" t="inlineStr">
         <is>
-          <t>2B</t>
+          <t>LF</t>
         </is>
       </c>
       <c r="Q112" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>2</t>
         </is>
       </c>
       <c r="R112" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="S112" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="T112" t="n">
         <v>2</v>
@@ -13462,7 +13471,7 @@
         <v>0</v>
       </c>
       <c r="AD112" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AE112" s="4" t="n">
         <v>6</v>
@@ -13471,7 +13480,7 @@
         <v>2</v>
       </c>
       <c r="AG112" t="n">
-        <v>10</v>
+        <v>6</v>
       </c>
     </row>
     <row r="113">
@@ -13482,84 +13491,75 @@
       </c>
       <c r="B113" t="inlineStr">
         <is>
-          <t>2026-07-11 08:11:18 PM PT</t>
+          <t>2026-07-11 08:13:18 PM PT</t>
         </is>
       </c>
       <c r="C113" t="n">
-        <v>823276</v>
+        <v>824249</v>
       </c>
       <c r="D113" t="inlineStr">
         <is>
-          <t>5:40 PM PT</t>
+          <t>3:10 PM PT</t>
         </is>
       </c>
       <c r="E113" t="inlineStr">
         <is>
-          <t>Top 7 | 3 out</t>
+          <t>Final</t>
         </is>
       </c>
       <c r="F113" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="G113" t="inlineStr">
         <is>
-          <t>Top</t>
-        </is>
-      </c>
-      <c r="H113" t="n">
+          <t>Bottom</t>
+        </is>
+      </c>
+      <c r="K113" t="inlineStr">
+        <is>
+          <t>Home</t>
+        </is>
+      </c>
+      <c r="L113" t="inlineStr">
+        <is>
+          <t>DET</t>
+        </is>
+      </c>
+      <c r="M113" t="inlineStr">
+        <is>
+          <t>PHI</t>
+        </is>
+      </c>
+      <c r="N113" t="inlineStr">
+        <is>
+          <t>Hao-Yu Lee</t>
+        </is>
+      </c>
+      <c r="O113" t="n">
+        <v>701678</v>
+      </c>
+      <c r="P113" t="inlineStr">
+        <is>
+          <t>2B</t>
+        </is>
+      </c>
+      <c r="Q113" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="R113" t="n">
         <v>3</v>
       </c>
-      <c r="I113" t="n">
+      <c r="S113" t="n">
+        <v>3</v>
+      </c>
+      <c r="T113" t="n">
         <v>2</v>
       </c>
-      <c r="J113" t="n">
-        <v>1</v>
-      </c>
-      <c r="K113" t="inlineStr">
-        <is>
-          <t>Home</t>
-        </is>
-      </c>
-      <c r="L113" t="inlineStr">
-        <is>
-          <t>SD</t>
-        </is>
-      </c>
-      <c r="M113" t="inlineStr">
-        <is>
-          <t>TOR</t>
-        </is>
-      </c>
-      <c r="N113" t="inlineStr">
-        <is>
-          <t>Fernando Tatis Jr.</t>
-        </is>
-      </c>
-      <c r="O113" t="n">
-        <v>665487</v>
-      </c>
-      <c r="P113" t="inlineStr">
-        <is>
-          <t>RF</t>
-        </is>
-      </c>
-      <c r="Q113" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="R113" t="n">
-        <v>4</v>
-      </c>
-      <c r="S113" t="n">
+      <c r="U113" t="n">
         <v>2</v>
       </c>
-      <c r="T113" t="n">
-        <v>0</v>
-      </c>
-      <c r="U113" t="n">
-        <v>0</v>
-      </c>
       <c r="V113" t="n">
         <v>0</v>
       </c>
@@ -13570,13 +13570,13 @@
         <v>0</v>
       </c>
       <c r="Y113" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Z113" t="n">
         <v>0</v>
       </c>
-      <c r="AA113" s="5" t="n">
-        <v>2</v>
+      <c r="AA113" t="n">
+        <v>0</v>
       </c>
       <c r="AB113" t="n">
         <v>0</v>
@@ -13591,10 +13591,10 @@
         <v>6</v>
       </c>
       <c r="AF113" t="n">
-        <v>8</v>
+        <v>2</v>
       </c>
       <c r="AG113" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
     </row>
     <row r="114">
@@ -13605,30 +13605,39 @@
       </c>
       <c r="B114" t="inlineStr">
         <is>
-          <t>2026-07-11 08:11:17 PM PT</t>
+          <t>2026-07-11 08:13:19 PM PT</t>
         </is>
       </c>
       <c r="C114" t="n">
-        <v>822875</v>
+        <v>823276</v>
       </c>
       <c r="D114" t="inlineStr">
         <is>
-          <t>4:05 PM PT</t>
+          <t>5:40 PM PT</t>
         </is>
       </c>
       <c r="E114" t="inlineStr">
         <is>
-          <t>Final</t>
+          <t>Bottom 7 | 0 out</t>
         </is>
       </c>
       <c r="F114" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="G114" t="inlineStr">
         <is>
           <t>Bottom</t>
         </is>
       </c>
+      <c r="H114" t="n">
+        <v>0</v>
+      </c>
+      <c r="I114" t="n">
+        <v>0</v>
+      </c>
+      <c r="J114" t="n">
+        <v>0</v>
+      </c>
       <c r="K114" t="inlineStr">
         <is>
           <t>Home</t>
@@ -13636,62 +13645,62 @@
       </c>
       <c r="L114" t="inlineStr">
         <is>
-          <t>TEX</t>
+          <t>SD</t>
         </is>
       </c>
       <c r="M114" t="inlineStr">
         <is>
-          <t>HOU</t>
+          <t>TOR</t>
         </is>
       </c>
       <c r="N114" t="inlineStr">
         <is>
-          <t>Evan Carter</t>
+          <t>Fernando Tatis Jr.</t>
         </is>
       </c>
       <c r="O114" t="n">
-        <v>694497</v>
+        <v>665487</v>
       </c>
       <c r="P114" t="inlineStr">
         <is>
-          <t>CF</t>
+          <t>RF</t>
         </is>
       </c>
       <c r="Q114" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>1</t>
         </is>
       </c>
       <c r="R114" t="n">
         <v>4</v>
       </c>
       <c r="S114" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="T114" t="n">
+        <v>0</v>
+      </c>
+      <c r="U114" t="n">
+        <v>0</v>
+      </c>
+      <c r="V114" t="n">
+        <v>0</v>
+      </c>
+      <c r="W114" t="n">
+        <v>0</v>
+      </c>
+      <c r="X114" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y114" t="n">
+        <v>1</v>
+      </c>
+      <c r="Z114" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA114" s="5" t="n">
         <v>2</v>
       </c>
-      <c r="U114" t="n">
-        <v>2</v>
-      </c>
-      <c r="V114" t="n">
-        <v>0</v>
-      </c>
-      <c r="W114" t="n">
-        <v>0</v>
-      </c>
-      <c r="X114" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y114" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z114" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA114" t="n">
-        <v>0</v>
-      </c>
       <c r="AB114" t="n">
         <v>0</v>
       </c>
@@ -13699,13 +13708,13 @@
         <v>0</v>
       </c>
       <c r="AD114" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AE114" s="4" t="n">
         <v>6</v>
       </c>
       <c r="AF114" t="n">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="AG114" t="n">
         <v>7</v>
@@ -13719,119 +13728,110 @@
       </c>
       <c r="B115" t="inlineStr">
         <is>
-          <t>2026-07-11 08:11:18 PM PT</t>
+          <t>2026-07-11 08:13:18 PM PT</t>
         </is>
       </c>
       <c r="C115" t="n">
-        <v>823926</v>
+        <v>822875</v>
       </c>
       <c r="D115" t="inlineStr">
         <is>
-          <t>6:10 PM PT</t>
+          <t>4:05 PM PT</t>
         </is>
       </c>
       <c r="E115" t="inlineStr">
         <is>
-          <t>Top 7 | 1 out</t>
+          <t>Final</t>
         </is>
       </c>
       <c r="F115" t="n">
+        <v>9</v>
+      </c>
+      <c r="G115" t="inlineStr">
+        <is>
+          <t>Bottom</t>
+        </is>
+      </c>
+      <c r="K115" t="inlineStr">
+        <is>
+          <t>Home</t>
+        </is>
+      </c>
+      <c r="L115" t="inlineStr">
+        <is>
+          <t>TEX</t>
+        </is>
+      </c>
+      <c r="M115" t="inlineStr">
+        <is>
+          <t>HOU</t>
+        </is>
+      </c>
+      <c r="N115" t="inlineStr">
+        <is>
+          <t>Evan Carter</t>
+        </is>
+      </c>
+      <c r="O115" t="n">
+        <v>694497</v>
+      </c>
+      <c r="P115" t="inlineStr">
+        <is>
+          <t>CF</t>
+        </is>
+      </c>
+      <c r="Q115" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="R115" t="n">
+        <v>4</v>
+      </c>
+      <c r="S115" t="n">
+        <v>4</v>
+      </c>
+      <c r="T115" t="n">
+        <v>2</v>
+      </c>
+      <c r="U115" t="n">
+        <v>2</v>
+      </c>
+      <c r="V115" t="n">
+        <v>0</v>
+      </c>
+      <c r="W115" t="n">
+        <v>0</v>
+      </c>
+      <c r="X115" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y115" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z115" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA115" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB115" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC115" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD115" t="n">
+        <v>1</v>
+      </c>
+      <c r="AE115" s="4" t="n">
+        <v>6</v>
+      </c>
+      <c r="AF115" t="n">
+        <v>3</v>
+      </c>
+      <c r="AG115" t="n">
         <v>7</v>
-      </c>
-      <c r="G115" t="inlineStr">
-        <is>
-          <t>Top</t>
-        </is>
-      </c>
-      <c r="H115" t="n">
-        <v>1</v>
-      </c>
-      <c r="I115" t="n">
-        <v>1</v>
-      </c>
-      <c r="J115" t="n">
-        <v>3</v>
-      </c>
-      <c r="K115" t="inlineStr">
-        <is>
-          <t>Away</t>
-        </is>
-      </c>
-      <c r="L115" t="inlineStr">
-        <is>
-          <t>ARI</t>
-        </is>
-      </c>
-      <c r="M115" t="inlineStr">
-        <is>
-          <t>LAD</t>
-        </is>
-      </c>
-      <c r="N115" t="inlineStr">
-        <is>
-          <t>Max Kepler</t>
-        </is>
-      </c>
-      <c r="O115" t="n">
-        <v>596146</v>
-      </c>
-      <c r="P115" t="inlineStr">
-        <is>
-          <t>LF</t>
-        </is>
-      </c>
-      <c r="Q115" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="R115" t="n">
-        <v>3</v>
-      </c>
-      <c r="S115" t="n">
-        <v>2</v>
-      </c>
-      <c r="T115" t="n">
-        <v>1</v>
-      </c>
-      <c r="U115" t="n">
-        <v>1</v>
-      </c>
-      <c r="V115" t="n">
-        <v>0</v>
-      </c>
-      <c r="W115" t="n">
-        <v>0</v>
-      </c>
-      <c r="X115" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y115" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z115" t="n">
-        <v>1</v>
-      </c>
-      <c r="AA115" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB115" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC115" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD115" t="n">
-        <v>1</v>
-      </c>
-      <c r="AE115" s="4" t="n">
-        <v>5</v>
-      </c>
-      <c r="AF115" t="n">
-        <v>6</v>
-      </c>
-      <c r="AG115" t="n">
-        <v>5</v>
       </c>
     </row>
     <row r="116">
@@ -13842,30 +13842,39 @@
       </c>
       <c r="B116" t="inlineStr">
         <is>
-          <t>2026-07-11 08:11:18 PM PT</t>
+          <t>2026-07-11 08:13:19 PM PT</t>
         </is>
       </c>
       <c r="C116" t="n">
-        <v>823030</v>
+        <v>823926</v>
       </c>
       <c r="D116" t="inlineStr">
         <is>
-          <t>4:15 PM PT</t>
+          <t>6:10 PM PT</t>
         </is>
       </c>
       <c r="E116" t="inlineStr">
         <is>
-          <t>Final</t>
+          <t>Top 7 | 1 out</t>
         </is>
       </c>
       <c r="F116" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="G116" t="inlineStr">
         <is>
           <t>Top</t>
         </is>
       </c>
+      <c r="H116" t="n">
+        <v>1</v>
+      </c>
+      <c r="I116" t="n">
+        <v>0</v>
+      </c>
+      <c r="J116" t="n">
+        <v>0</v>
+      </c>
       <c r="K116" t="inlineStr">
         <is>
           <t>Away</t>
@@ -13873,37 +13882,37 @@
       </c>
       <c r="L116" t="inlineStr">
         <is>
-          <t>ATL</t>
+          <t>ARI</t>
         </is>
       </c>
       <c r="M116" t="inlineStr">
         <is>
-          <t>STL</t>
+          <t>LAD</t>
         </is>
       </c>
       <c r="N116" t="inlineStr">
         <is>
-          <t>Drake Baldwin</t>
+          <t>Max Kepler</t>
         </is>
       </c>
       <c r="O116" t="n">
-        <v>686948</v>
+        <v>596146</v>
       </c>
       <c r="P116" t="inlineStr">
         <is>
-          <t>DH</t>
+          <t>LF</t>
         </is>
       </c>
       <c r="Q116" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="R116" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="S116" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="T116" t="n">
         <v>1</v>
@@ -13924,10 +13933,10 @@
         <v>0</v>
       </c>
       <c r="Z116" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA116" s="5" t="n">
-        <v>1</v>
+        <v>1</v>
+      </c>
+      <c r="AA116" t="n">
+        <v>0</v>
       </c>
       <c r="AB116" t="n">
         <v>0</v>
@@ -13936,16 +13945,16 @@
         <v>0</v>
       </c>
       <c r="AD116" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AE116" s="4" t="n">
         <v>5</v>
       </c>
       <c r="AF116" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="AG116" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="117">
@@ -13956,7 +13965,7 @@
       </c>
       <c r="B117" t="inlineStr">
         <is>
-          <t>2026-07-11 08:11:18 PM PT</t>
+          <t>2026-07-11 08:13:18 PM PT</t>
         </is>
       </c>
       <c r="C117" t="n">
@@ -13997,24 +14006,24 @@
       </c>
       <c r="N117" t="inlineStr">
         <is>
-          <t>Eli White</t>
+          <t>Drake Baldwin</t>
         </is>
       </c>
       <c r="O117" t="n">
-        <v>642201</v>
+        <v>686948</v>
       </c>
       <c r="P117" t="inlineStr">
         <is>
-          <t>RF</t>
+          <t>DH</t>
         </is>
       </c>
       <c r="Q117" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>4</t>
         </is>
       </c>
       <c r="R117" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="S117" t="n">
         <v>3</v>
@@ -14023,10 +14032,10 @@
         <v>1</v>
       </c>
       <c r="U117" t="n">
-        <v>0</v>
-      </c>
-      <c r="V117" s="7" t="n">
-        <v>1</v>
+        <v>1</v>
+      </c>
+      <c r="V117" t="n">
+        <v>0</v>
       </c>
       <c r="W117" t="n">
         <v>0</v>
@@ -14040,8 +14049,8 @@
       <c r="Z117" t="n">
         <v>0</v>
       </c>
-      <c r="AA117" t="n">
-        <v>0</v>
+      <c r="AA117" s="5" t="n">
+        <v>1</v>
       </c>
       <c r="AB117" t="n">
         <v>0</v>
@@ -14070,15 +14079,15 @@
       </c>
       <c r="B118" t="inlineStr">
         <is>
-          <t>2026-07-11 08:11:17 PM PT</t>
+          <t>2026-07-11 08:13:18 PM PT</t>
         </is>
       </c>
       <c r="C118" t="n">
-        <v>824813</v>
+        <v>823030</v>
       </c>
       <c r="D118" t="inlineStr">
         <is>
-          <t>4:05 PM PT</t>
+          <t>4:15 PM PT</t>
         </is>
       </c>
       <c r="E118" t="inlineStr">
@@ -14096,35 +14105,35 @@
       </c>
       <c r="K118" t="inlineStr">
         <is>
-          <t>Home</t>
+          <t>Away</t>
         </is>
       </c>
       <c r="L118" t="inlineStr">
         <is>
-          <t>BAL</t>
+          <t>ATL</t>
         </is>
       </c>
       <c r="M118" t="inlineStr">
         <is>
-          <t>KC</t>
+          <t>STL</t>
         </is>
       </c>
       <c r="N118" t="inlineStr">
         <is>
-          <t>Samuel Basallo</t>
+          <t>Eli White</t>
         </is>
       </c>
       <c r="O118" t="n">
-        <v>694212</v>
+        <v>642201</v>
       </c>
       <c r="P118" t="inlineStr">
         <is>
-          <t>DH</t>
+          <t>RF</t>
         </is>
       </c>
       <c r="Q118" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>7</t>
         </is>
       </c>
       <c r="R118" t="n">
@@ -14137,10 +14146,10 @@
         <v>1</v>
       </c>
       <c r="U118" t="n">
-        <v>1</v>
-      </c>
-      <c r="V118" t="n">
-        <v>0</v>
+        <v>0</v>
+      </c>
+      <c r="V118" s="7" t="n">
+        <v>1</v>
       </c>
       <c r="W118" t="n">
         <v>0</v>
@@ -14152,7 +14161,7 @@
         <v>0</v>
       </c>
       <c r="Z118" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AA118" t="n">
         <v>0</v>
@@ -14164,13 +14173,13 @@
         <v>0</v>
       </c>
       <c r="AD118" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AE118" s="4" t="n">
         <v>5</v>
       </c>
       <c r="AF118" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="AG118" t="n">
         <v>6</v>
@@ -14184,15 +14193,15 @@
       </c>
       <c r="B119" t="inlineStr">
         <is>
-          <t>2026-07-11 08:11:17 PM PT</t>
+          <t>2026-07-11 08:13:18 PM PT</t>
         </is>
       </c>
       <c r="C119" t="n">
-        <v>823603</v>
+        <v>824813</v>
       </c>
       <c r="D119" t="inlineStr">
         <is>
-          <t>1:10 PM PT</t>
+          <t>4:05 PM PT</t>
         </is>
       </c>
       <c r="E119" t="inlineStr">
@@ -14205,56 +14214,56 @@
       </c>
       <c r="G119" t="inlineStr">
         <is>
-          <t>Bottom</t>
+          <t>Top</t>
         </is>
       </c>
       <c r="K119" t="inlineStr">
         <is>
-          <t>Away</t>
+          <t>Home</t>
         </is>
       </c>
       <c r="L119" t="inlineStr">
         <is>
-          <t>BOS</t>
+          <t>BAL</t>
         </is>
       </c>
       <c r="M119" t="inlineStr">
         <is>
-          <t>NYM</t>
+          <t>KC</t>
         </is>
       </c>
       <c r="N119" t="inlineStr">
         <is>
-          <t>Ceddanne Rafaela</t>
+          <t>Samuel Basallo</t>
         </is>
       </c>
       <c r="O119" t="n">
-        <v>678882</v>
+        <v>694212</v>
       </c>
       <c r="P119" t="inlineStr">
         <is>
-          <t>CF</t>
+          <t>DH</t>
         </is>
       </c>
       <c r="Q119" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>5</t>
         </is>
       </c>
       <c r="R119" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="S119" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="T119" t="n">
         <v>1</v>
       </c>
       <c r="U119" t="n">
-        <v>0</v>
-      </c>
-      <c r="V119" s="7" t="n">
-        <v>1</v>
+        <v>1</v>
+      </c>
+      <c r="V119" t="n">
+        <v>0</v>
       </c>
       <c r="W119" t="n">
         <v>0</v>
@@ -14266,7 +14275,7 @@
         <v>0</v>
       </c>
       <c r="Z119" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AA119" t="n">
         <v>0</v>
@@ -14278,13 +14287,13 @@
         <v>0</v>
       </c>
       <c r="AD119" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AE119" s="4" t="n">
         <v>5</v>
       </c>
       <c r="AF119" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="AG119" t="n">
         <v>6</v>
@@ -14298,15 +14307,15 @@
       </c>
       <c r="B120" t="inlineStr">
         <is>
-          <t>2026-07-11 08:11:18 PM PT</t>
+          <t>2026-07-11 08:13:17 PM PT</t>
         </is>
       </c>
       <c r="C120" t="n">
-        <v>824492</v>
+        <v>823603</v>
       </c>
       <c r="D120" t="inlineStr">
         <is>
-          <t>4:10 PM PT</t>
+          <t>1:10 PM PT</t>
         </is>
       </c>
       <c r="E120" t="inlineStr">
@@ -14329,46 +14338,46 @@
       </c>
       <c r="L120" t="inlineStr">
         <is>
-          <t>CHC</t>
+          <t>BOS</t>
         </is>
       </c>
       <c r="M120" t="inlineStr">
         <is>
-          <t>CIN</t>
+          <t>NYM</t>
         </is>
       </c>
       <c r="N120" t="inlineStr">
         <is>
-          <t>Miguel Amaya</t>
+          <t>Ceddanne Rafaela</t>
         </is>
       </c>
       <c r="O120" t="n">
-        <v>665804</v>
+        <v>678882</v>
       </c>
       <c r="P120" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>CF</t>
         </is>
       </c>
       <c r="Q120" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>2</t>
         </is>
       </c>
       <c r="R120" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="S120" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="T120" t="n">
         <v>1</v>
       </c>
       <c r="U120" t="n">
-        <v>1</v>
-      </c>
-      <c r="V120" t="n">
-        <v>0</v>
+        <v>0</v>
+      </c>
+      <c r="V120" s="7" t="n">
+        <v>1</v>
       </c>
       <c r="W120" t="n">
         <v>0</v>
@@ -14377,7 +14386,7 @@
         <v>0</v>
       </c>
       <c r="Y120" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Z120" t="n">
         <v>0</v>
@@ -14392,16 +14401,16 @@
         <v>0</v>
       </c>
       <c r="AD120" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AE120" s="4" t="n">
         <v>5</v>
       </c>
       <c r="AF120" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="AG120" t="n">
-        <v>9</v>
+        <v>6</v>
       </c>
     </row>
     <row r="121">
@@ -14412,15 +14421,15 @@
       </c>
       <c r="B121" t="inlineStr">
         <is>
-          <t>2026-07-11 08:11:17 PM PT</t>
+          <t>2026-07-11 08:13:18 PM PT</t>
         </is>
       </c>
       <c r="C121" t="n">
-        <v>823198</v>
+        <v>824492</v>
       </c>
       <c r="D121" t="inlineStr">
         <is>
-          <t>1:05 PM PT</t>
+          <t>4:10 PM PT</t>
         </is>
       </c>
       <c r="E121" t="inlineStr">
@@ -14433,7 +14442,7 @@
       </c>
       <c r="G121" t="inlineStr">
         <is>
-          <t>Top</t>
+          <t>Bottom</t>
         </is>
       </c>
       <c r="K121" t="inlineStr">
@@ -14443,30 +14452,30 @@
       </c>
       <c r="L121" t="inlineStr">
         <is>
-          <t>COL</t>
+          <t>CHC</t>
         </is>
       </c>
       <c r="M121" t="inlineStr">
         <is>
-          <t>SF</t>
+          <t>CIN</t>
         </is>
       </c>
       <c r="N121" t="inlineStr">
         <is>
-          <t>Hunter Goodman</t>
+          <t>Miguel Amaya</t>
         </is>
       </c>
       <c r="O121" t="n">
-        <v>696100</v>
+        <v>665804</v>
       </c>
       <c r="P121" t="inlineStr">
         <is>
-          <t>DH</t>
+          <t>C</t>
         </is>
       </c>
       <c r="Q121" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>9</t>
         </is>
       </c>
       <c r="R121" t="n">
@@ -14479,10 +14488,10 @@
         <v>1</v>
       </c>
       <c r="U121" t="n">
-        <v>0</v>
-      </c>
-      <c r="V121" s="7" t="n">
-        <v>1</v>
+        <v>1</v>
+      </c>
+      <c r="V121" t="n">
+        <v>0</v>
       </c>
       <c r="W121" t="n">
         <v>0</v>
@@ -14491,7 +14500,7 @@
         <v>0</v>
       </c>
       <c r="Y121" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Z121" t="n">
         <v>0</v>
@@ -14512,10 +14521,10 @@
         <v>5</v>
       </c>
       <c r="AF121" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="AG121" t="n">
-        <v>6</v>
+        <v>9</v>
       </c>
     </row>
     <row r="122">
@@ -14526,15 +14535,15 @@
       </c>
       <c r="B122" t="inlineStr">
         <is>
-          <t>2026-07-11 08:11:17 PM PT</t>
+          <t>2026-07-11 08:13:17 PM PT</t>
         </is>
       </c>
       <c r="C122" t="n">
-        <v>824576</v>
+        <v>823198</v>
       </c>
       <c r="D122" t="inlineStr">
         <is>
-          <t>11:10 AM PT</t>
+          <t>1:05 PM PT</t>
         </is>
       </c>
       <c r="E122" t="inlineStr">
@@ -14552,35 +14561,35 @@
       </c>
       <c r="K122" t="inlineStr">
         <is>
-          <t>Home</t>
+          <t>Away</t>
         </is>
       </c>
       <c r="L122" t="inlineStr">
         <is>
-          <t>CWS</t>
+          <t>COL</t>
         </is>
       </c>
       <c r="M122" t="inlineStr">
         <is>
-          <t>ATH</t>
+          <t>SF</t>
         </is>
       </c>
       <c r="N122" t="inlineStr">
         <is>
-          <t>Randal Grichuk</t>
+          <t>Hunter Goodman</t>
         </is>
       </c>
       <c r="O122" t="n">
-        <v>545341</v>
+        <v>696100</v>
       </c>
       <c r="P122" t="inlineStr">
         <is>
-          <t>LF</t>
+          <t>DH</t>
         </is>
       </c>
       <c r="Q122" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>3</t>
         </is>
       </c>
       <c r="R122" t="n">
@@ -14626,10 +14635,10 @@
         <v>5</v>
       </c>
       <c r="AF122" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AG122" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="123">
@@ -14640,15 +14649,15 @@
       </c>
       <c r="B123" t="inlineStr">
         <is>
-          <t>2026-07-11 08:11:17 PM PT</t>
+          <t>2026-07-11 08:13:17 PM PT</t>
         </is>
       </c>
       <c r="C123" t="n">
-        <v>824249</v>
+        <v>824576</v>
       </c>
       <c r="D123" t="inlineStr">
         <is>
-          <t>3:10 PM PT</t>
+          <t>11:10 AM PT</t>
         </is>
       </c>
       <c r="E123" t="inlineStr">
@@ -14661,7 +14670,7 @@
       </c>
       <c r="G123" t="inlineStr">
         <is>
-          <t>Bottom</t>
+          <t>Top</t>
         </is>
       </c>
       <c r="K123" t="inlineStr">
@@ -14671,46 +14680,46 @@
       </c>
       <c r="L123" t="inlineStr">
         <is>
-          <t>DET</t>
+          <t>CWS</t>
         </is>
       </c>
       <c r="M123" t="inlineStr">
         <is>
-          <t>PHI</t>
+          <t>ATH</t>
         </is>
       </c>
       <c r="N123" t="inlineStr">
         <is>
-          <t>Dillon Dingler</t>
+          <t>Randal Grichuk</t>
         </is>
       </c>
       <c r="O123" t="n">
-        <v>693307</v>
+        <v>545341</v>
       </c>
       <c r="P123" t="inlineStr">
         <is>
-          <t>DH</t>
+          <t>LF</t>
         </is>
       </c>
       <c r="Q123" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>1</t>
         </is>
       </c>
       <c r="R123" t="n">
         <v>4</v>
       </c>
       <c r="S123" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="T123" t="n">
         <v>1</v>
       </c>
       <c r="U123" t="n">
-        <v>1</v>
-      </c>
-      <c r="V123" t="n">
-        <v>0</v>
+        <v>0</v>
+      </c>
+      <c r="V123" s="7" t="n">
+        <v>1</v>
       </c>
       <c r="W123" t="n">
         <v>0</v>
@@ -14727,8 +14736,8 @@
       <c r="AA123" t="n">
         <v>0</v>
       </c>
-      <c r="AB123" s="9" t="n">
-        <v>1</v>
+      <c r="AB123" t="n">
+        <v>0</v>
       </c>
       <c r="AC123" t="n">
         <v>0</v>
@@ -14740,10 +14749,10 @@
         <v>5</v>
       </c>
       <c r="AF123" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AG123" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
     </row>
     <row r="124">
@@ -14754,15 +14763,15 @@
       </c>
       <c r="B124" t="inlineStr">
         <is>
-          <t>2026-07-11 08:11:17 PM PT</t>
+          <t>2026-07-11 08:13:18 PM PT</t>
         </is>
       </c>
       <c r="C124" t="n">
-        <v>822875</v>
+        <v>824249</v>
       </c>
       <c r="D124" t="inlineStr">
         <is>
-          <t>4:05 PM PT</t>
+          <t>3:10 PM PT</t>
         </is>
       </c>
       <c r="E124" t="inlineStr">
@@ -14780,42 +14789,42 @@
       </c>
       <c r="K124" t="inlineStr">
         <is>
-          <t>Away</t>
+          <t>Home</t>
         </is>
       </c>
       <c r="L124" t="inlineStr">
         <is>
-          <t>HOU</t>
+          <t>DET</t>
         </is>
       </c>
       <c r="M124" t="inlineStr">
         <is>
-          <t>TEX</t>
+          <t>PHI</t>
         </is>
       </c>
       <c r="N124" t="inlineStr">
         <is>
-          <t>Jose Altuve</t>
+          <t>Dillon Dingler</t>
         </is>
       </c>
       <c r="O124" t="n">
-        <v>514888</v>
+        <v>693307</v>
       </c>
       <c r="P124" t="inlineStr">
         <is>
-          <t>2B</t>
+          <t>DH</t>
         </is>
       </c>
       <c r="Q124" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>3</t>
         </is>
       </c>
       <c r="R124" t="n">
         <v>4</v>
       </c>
       <c r="S124" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="T124" t="n">
         <v>1</v>
@@ -14833,7 +14842,7 @@
         <v>0</v>
       </c>
       <c r="Y124" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Z124" t="n">
         <v>0</v>
@@ -14841,20 +14850,20 @@
       <c r="AA124" t="n">
         <v>0</v>
       </c>
-      <c r="AB124" t="n">
-        <v>0</v>
+      <c r="AB124" s="9" t="n">
+        <v>1</v>
       </c>
       <c r="AC124" t="n">
         <v>0</v>
       </c>
       <c r="AD124" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AE124" s="4" t="n">
         <v>5</v>
       </c>
       <c r="AF124" t="n">
-        <v>9</v>
+        <v>2</v>
       </c>
       <c r="AG124" t="n">
         <v>10</v>
@@ -14868,7 +14877,7 @@
       </c>
       <c r="B125" t="inlineStr">
         <is>
-          <t>2026-07-11 08:11:17 PM PT</t>
+          <t>2026-07-11 08:13:18 PM PT</t>
         </is>
       </c>
       <c r="C125" t="n">
@@ -14909,20 +14918,20 @@
       </c>
       <c r="N125" t="inlineStr">
         <is>
-          <t>Yainer Diaz</t>
+          <t>Jose Altuve</t>
         </is>
       </c>
       <c r="O125" t="n">
-        <v>673237</v>
+        <v>514888</v>
       </c>
       <c r="P125" t="inlineStr">
         <is>
-          <t>DH</t>
+          <t>2B</t>
         </is>
       </c>
       <c r="Q125" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>5</t>
         </is>
       </c>
       <c r="R125" t="n">
@@ -14935,10 +14944,10 @@
         <v>1</v>
       </c>
       <c r="U125" t="n">
-        <v>0</v>
-      </c>
-      <c r="V125" s="7" t="n">
-        <v>1</v>
+        <v>1</v>
+      </c>
+      <c r="V125" t="n">
+        <v>0</v>
       </c>
       <c r="W125" t="n">
         <v>0</v>
@@ -14947,7 +14956,7 @@
         <v>0</v>
       </c>
       <c r="Y125" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Z125" t="n">
         <v>0</v>
@@ -14982,11 +14991,11 @@
       </c>
       <c r="B126" t="inlineStr">
         <is>
-          <t>2026-07-11 08:11:17 PM PT</t>
+          <t>2026-07-11 08:13:18 PM PT</t>
         </is>
       </c>
       <c r="C126" t="n">
-        <v>824813</v>
+        <v>822875</v>
       </c>
       <c r="D126" t="inlineStr">
         <is>
@@ -15003,7 +15012,7 @@
       </c>
       <c r="G126" t="inlineStr">
         <is>
-          <t>Top</t>
+          <t>Bottom</t>
         </is>
       </c>
       <c r="K126" t="inlineStr">
@@ -15013,30 +15022,30 @@
       </c>
       <c r="L126" t="inlineStr">
         <is>
-          <t>KC</t>
+          <t>HOU</t>
         </is>
       </c>
       <c r="M126" t="inlineStr">
         <is>
-          <t>BAL</t>
+          <t>TEX</t>
         </is>
       </c>
       <c r="N126" t="inlineStr">
         <is>
-          <t>Jac Caglianone</t>
+          <t>Yainer Diaz</t>
         </is>
       </c>
       <c r="O126" t="n">
-        <v>695506</v>
+        <v>673237</v>
       </c>
       <c r="P126" t="inlineStr">
         <is>
-          <t>RF</t>
+          <t>DH</t>
         </is>
       </c>
       <c r="Q126" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>7</t>
         </is>
       </c>
       <c r="R126" t="n">
@@ -15049,10 +15058,10 @@
         <v>1</v>
       </c>
       <c r="U126" t="n">
-        <v>1</v>
-      </c>
-      <c r="V126" t="n">
-        <v>0</v>
+        <v>0</v>
+      </c>
+      <c r="V126" s="7" t="n">
+        <v>1</v>
       </c>
       <c r="W126" t="n">
         <v>0</v>
@@ -15061,7 +15070,7 @@
         <v>0</v>
       </c>
       <c r="Y126" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Z126" t="n">
         <v>0</v>
@@ -15082,10 +15091,10 @@
         <v>5</v>
       </c>
       <c r="AF126" t="n">
-        <v>1</v>
+        <v>9</v>
       </c>
       <c r="AG126" t="n">
-        <v>2</v>
+        <v>10</v>
       </c>
     </row>
     <row r="127">
@@ -15096,77 +15105,68 @@
       </c>
       <c r="B127" t="inlineStr">
         <is>
-          <t>2026-07-11 08:11:18 PM PT</t>
+          <t>2026-07-11 08:13:18 PM PT</t>
         </is>
       </c>
       <c r="C127" t="n">
-        <v>823926</v>
+        <v>824813</v>
       </c>
       <c r="D127" t="inlineStr">
         <is>
-          <t>6:10 PM PT</t>
+          <t>4:05 PM PT</t>
         </is>
       </c>
       <c r="E127" t="inlineStr">
         <is>
-          <t>Top 7 | 1 out</t>
+          <t>Final</t>
         </is>
       </c>
       <c r="F127" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="G127" t="inlineStr">
         <is>
           <t>Top</t>
         </is>
       </c>
-      <c r="H127" t="n">
-        <v>1</v>
-      </c>
-      <c r="I127" t="n">
-        <v>1</v>
-      </c>
-      <c r="J127" t="n">
-        <v>3</v>
-      </c>
       <c r="K127" t="inlineStr">
         <is>
-          <t>Home</t>
+          <t>Away</t>
         </is>
       </c>
       <c r="L127" t="inlineStr">
         <is>
-          <t>LAD</t>
+          <t>KC</t>
         </is>
       </c>
       <c r="M127" t="inlineStr">
         <is>
-          <t>ARI</t>
+          <t>BAL</t>
         </is>
       </c>
       <c r="N127" t="inlineStr">
         <is>
-          <t>Mookie Betts</t>
+          <t>Jac Caglianone</t>
         </is>
       </c>
       <c r="O127" t="n">
-        <v>605141</v>
+        <v>695506</v>
       </c>
       <c r="P127" t="inlineStr">
         <is>
-          <t>SS</t>
+          <t>RF</t>
         </is>
       </c>
       <c r="Q127" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>3</t>
         </is>
       </c>
       <c r="R127" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="S127" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="T127" t="n">
         <v>1</v>
@@ -15184,10 +15184,10 @@
         <v>0</v>
       </c>
       <c r="Y127" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Z127" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AA127" t="n">
         <v>0</v>
@@ -15205,10 +15205,10 @@
         <v>5</v>
       </c>
       <c r="AF127" t="n">
+        <v>1</v>
+      </c>
+      <c r="AG127" t="n">
         <v>2</v>
-      </c>
-      <c r="AG127" t="n">
-        <v>6</v>
       </c>
     </row>
     <row r="128">
@@ -15219,29 +15219,38 @@
       </c>
       <c r="B128" t="inlineStr">
         <is>
-          <t>2026-07-11 08:11:17 PM PT</t>
+          <t>2026-07-11 08:13:19 PM PT</t>
         </is>
       </c>
       <c r="C128" t="n">
-        <v>823844</v>
+        <v>823926</v>
       </c>
       <c r="D128" t="inlineStr">
         <is>
-          <t>1:10 PM PT</t>
+          <t>6:10 PM PT</t>
         </is>
       </c>
       <c r="E128" t="inlineStr">
         <is>
-          <t>Final</t>
+          <t>Top 7 | 1 out</t>
         </is>
       </c>
       <c r="F128" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="G128" t="inlineStr">
         <is>
-          <t>Bottom</t>
-        </is>
+          <t>Top</t>
+        </is>
+      </c>
+      <c r="H128" t="n">
+        <v>1</v>
+      </c>
+      <c r="I128" t="n">
+        <v>0</v>
+      </c>
+      <c r="J128" t="n">
+        <v>0</v>
       </c>
       <c r="K128" t="inlineStr">
         <is>
@@ -15250,34 +15259,34 @@
       </c>
       <c r="L128" t="inlineStr">
         <is>
-          <t>MIA</t>
+          <t>LAD</t>
         </is>
       </c>
       <c r="M128" t="inlineStr">
         <is>
-          <t>CLE</t>
+          <t>ARI</t>
         </is>
       </c>
       <c r="N128" t="inlineStr">
         <is>
-          <t>Kyle Stowers</t>
+          <t>Mookie Betts</t>
         </is>
       </c>
       <c r="O128" t="n">
-        <v>669065</v>
+        <v>605141</v>
       </c>
       <c r="P128" t="inlineStr">
         <is>
-          <t>1B</t>
+          <t>SS</t>
         </is>
       </c>
       <c r="Q128" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="R128" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="S128" t="n">
         <v>3</v>
@@ -15301,10 +15310,10 @@
         <v>0</v>
       </c>
       <c r="Z128" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA128" s="5" t="n">
-        <v>1</v>
+        <v>1</v>
+      </c>
+      <c r="AA128" t="n">
+        <v>0</v>
       </c>
       <c r="AB128" t="n">
         <v>0</v>
@@ -15319,10 +15328,10 @@
         <v>5</v>
       </c>
       <c r="AF128" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AG128" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
     </row>
     <row r="129">
@@ -15333,7 +15342,7 @@
       </c>
       <c r="B129" t="inlineStr">
         <is>
-          <t>2026-07-11 08:11:17 PM PT</t>
+          <t>2026-07-11 08:13:18 PM PT</t>
         </is>
       </c>
       <c r="C129" t="n">
@@ -15374,36 +15383,36 @@
       </c>
       <c r="N129" t="inlineStr">
         <is>
-          <t>Heriberto Hernández</t>
+          <t>Kyle Stowers</t>
         </is>
       </c>
       <c r="O129" t="n">
-        <v>681715</v>
+        <v>669065</v>
       </c>
       <c r="P129" t="inlineStr">
         <is>
-          <t>LF</t>
+          <t>1B</t>
         </is>
       </c>
       <c r="Q129" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>3</t>
         </is>
       </c>
       <c r="R129" t="n">
         <v>4</v>
       </c>
       <c r="S129" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="T129" t="n">
         <v>1</v>
       </c>
       <c r="U129" t="n">
-        <v>0</v>
-      </c>
-      <c r="V129" s="7" t="n">
-        <v>1</v>
+        <v>1</v>
+      </c>
+      <c r="V129" t="n">
+        <v>0</v>
       </c>
       <c r="W129" t="n">
         <v>0</v>
@@ -15417,8 +15426,8 @@
       <c r="Z129" t="n">
         <v>0</v>
       </c>
-      <c r="AA129" t="n">
-        <v>0</v>
+      <c r="AA129" s="5" t="n">
+        <v>1</v>
       </c>
       <c r="AB129" t="n">
         <v>0</v>
@@ -15427,7 +15436,7 @@
         <v>0</v>
       </c>
       <c r="AD129" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AE129" s="4" t="n">
         <v>5</v>
@@ -15447,15 +15456,15 @@
       </c>
       <c r="B130" t="inlineStr">
         <is>
-          <t>2026-07-11 08:11:16 PM PT</t>
+          <t>2026-07-11 08:13:18 PM PT</t>
         </is>
       </c>
       <c r="C130" t="n">
-        <v>823356</v>
+        <v>823844</v>
       </c>
       <c r="D130" t="inlineStr">
         <is>
-          <t>1:05 PM PT</t>
+          <t>1:10 PM PT</t>
         </is>
       </c>
       <c r="E130" t="inlineStr">
@@ -15468,56 +15477,56 @@
       </c>
       <c r="G130" t="inlineStr">
         <is>
-          <t>Top</t>
+          <t>Bottom</t>
         </is>
       </c>
       <c r="K130" t="inlineStr">
         <is>
-          <t>Away</t>
+          <t>Home</t>
         </is>
       </c>
       <c r="L130" t="inlineStr">
         <is>
-          <t>MIL</t>
+          <t>MIA</t>
         </is>
       </c>
       <c r="M130" t="inlineStr">
         <is>
-          <t>PIT</t>
+          <t>CLE</t>
         </is>
       </c>
       <c r="N130" t="inlineStr">
         <is>
-          <t>Luis Lara</t>
+          <t>Heriberto Hernández</t>
         </is>
       </c>
       <c r="O130" t="n">
-        <v>800325</v>
+        <v>681715</v>
       </c>
       <c r="P130" t="inlineStr">
         <is>
-          <t>RF</t>
+          <t>LF</t>
         </is>
       </c>
       <c r="Q130" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>5</t>
         </is>
       </c>
       <c r="R130" t="n">
         <v>4</v>
       </c>
       <c r="S130" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="T130" t="n">
         <v>1</v>
       </c>
       <c r="U130" t="n">
-        <v>1</v>
-      </c>
-      <c r="V130" t="n">
-        <v>0</v>
+        <v>0</v>
+      </c>
+      <c r="V130" s="7" t="n">
+        <v>1</v>
       </c>
       <c r="W130" t="n">
         <v>0</v>
@@ -15531,8 +15540,8 @@
       <c r="Z130" t="n">
         <v>0</v>
       </c>
-      <c r="AA130" s="5" t="n">
-        <v>1</v>
+      <c r="AA130" t="n">
+        <v>0</v>
       </c>
       <c r="AB130" t="n">
         <v>0</v>
@@ -15547,7 +15556,7 @@
         <v>5</v>
       </c>
       <c r="AF130" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AG130" t="n">
         <v>7</v>
@@ -15561,15 +15570,15 @@
       </c>
       <c r="B131" t="inlineStr">
         <is>
-          <t>2026-07-11 08:11:16 PM PT</t>
+          <t>2026-07-11 08:13:16 PM PT</t>
         </is>
       </c>
       <c r="C131" t="n">
-        <v>823682</v>
+        <v>823356</v>
       </c>
       <c r="D131" t="inlineStr">
         <is>
-          <t>11:10 AM PT</t>
+          <t>1:05 PM PT</t>
         </is>
       </c>
       <c r="E131" t="inlineStr">
@@ -15587,51 +15596,51 @@
       </c>
       <c r="K131" t="inlineStr">
         <is>
-          <t>Home</t>
+          <t>Away</t>
         </is>
       </c>
       <c r="L131" t="inlineStr">
         <is>
-          <t>MIN</t>
+          <t>MIL</t>
         </is>
       </c>
       <c r="M131" t="inlineStr">
         <is>
-          <t>LAA</t>
+          <t>PIT</t>
         </is>
       </c>
       <c r="N131" t="inlineStr">
         <is>
-          <t>Josh Bell</t>
+          <t>Luis Lara</t>
         </is>
       </c>
       <c r="O131" t="n">
-        <v>605137</v>
+        <v>800325</v>
       </c>
       <c r="P131" t="inlineStr">
         <is>
-          <t>DH</t>
+          <t>RF</t>
         </is>
       </c>
       <c r="Q131" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>7</t>
         </is>
       </c>
       <c r="R131" t="n">
         <v>4</v>
       </c>
       <c r="S131" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="T131" t="n">
         <v>1</v>
       </c>
       <c r="U131" t="n">
-        <v>0</v>
-      </c>
-      <c r="V131" s="7" t="n">
-        <v>1</v>
+        <v>1</v>
+      </c>
+      <c r="V131" t="n">
+        <v>0</v>
       </c>
       <c r="W131" t="n">
         <v>0</v>
@@ -15645,8 +15654,8 @@
       <c r="Z131" t="n">
         <v>0</v>
       </c>
-      <c r="AA131" t="n">
-        <v>0</v>
+      <c r="AA131" s="5" t="n">
+        <v>1</v>
       </c>
       <c r="AB131" t="n">
         <v>0</v>
@@ -15655,16 +15664,16 @@
         <v>0</v>
       </c>
       <c r="AD131" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AE131" s="4" t="n">
         <v>5</v>
       </c>
       <c r="AF131" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="AG131" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
     </row>
     <row r="132">
@@ -15675,7 +15684,7 @@
       </c>
       <c r="B132" t="inlineStr">
         <is>
-          <t>2026-07-11 08:11:16 PM PT</t>
+          <t>2026-07-11 08:13:17 PM PT</t>
         </is>
       </c>
       <c r="C132" t="n">
@@ -15716,36 +15725,36 @@
       </c>
       <c r="N132" t="inlineStr">
         <is>
-          <t>Luke Keaschall</t>
+          <t>Josh Bell</t>
         </is>
       </c>
       <c r="O132" t="n">
-        <v>807712</v>
+        <v>605137</v>
       </c>
       <c r="P132" t="inlineStr">
         <is>
-          <t>CF</t>
+          <t>DH</t>
         </is>
       </c>
       <c r="Q132" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>3</t>
         </is>
       </c>
       <c r="R132" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="S132" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="T132" t="n">
         <v>1</v>
       </c>
       <c r="U132" t="n">
-        <v>1</v>
-      </c>
-      <c r="V132" t="n">
-        <v>0</v>
+        <v>0</v>
+      </c>
+      <c r="V132" s="7" t="n">
+        <v>1</v>
       </c>
       <c r="W132" t="n">
         <v>0</v>
@@ -15757,7 +15766,7 @@
         <v>0</v>
       </c>
       <c r="Z132" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AA132" t="n">
         <v>0</v>
@@ -15789,15 +15798,15 @@
       </c>
       <c r="B133" t="inlineStr">
         <is>
-          <t>2026-07-11 08:11:17 PM PT</t>
+          <t>2026-07-11 08:13:17 PM PT</t>
         </is>
       </c>
       <c r="C133" t="n">
-        <v>822711</v>
+        <v>823682</v>
       </c>
       <c r="D133" t="inlineStr">
         <is>
-          <t>1:05 PM PT</t>
+          <t>11:10 AM PT</t>
         </is>
       </c>
       <c r="E133" t="inlineStr">
@@ -15810,56 +15819,56 @@
       </c>
       <c r="G133" t="inlineStr">
         <is>
-          <t>Bottom</t>
+          <t>Top</t>
         </is>
       </c>
       <c r="K133" t="inlineStr">
         <is>
-          <t>Away</t>
+          <t>Home</t>
         </is>
       </c>
       <c r="L133" t="inlineStr">
         <is>
-          <t>NYY</t>
+          <t>MIN</t>
         </is>
       </c>
       <c r="M133" t="inlineStr">
         <is>
-          <t>WSH</t>
+          <t>LAA</t>
         </is>
       </c>
       <c r="N133" t="inlineStr">
         <is>
-          <t>Cody Bellinger</t>
+          <t>Luke Keaschall</t>
         </is>
       </c>
       <c r="O133" t="n">
-        <v>641355</v>
+        <v>807712</v>
       </c>
       <c r="P133" t="inlineStr">
         <is>
-          <t>LF</t>
+          <t>CF</t>
         </is>
       </c>
       <c r="Q133" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>9</t>
         </is>
       </c>
       <c r="R133" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="S133" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="T133" t="n">
         <v>1</v>
       </c>
       <c r="U133" t="n">
-        <v>0</v>
-      </c>
-      <c r="V133" s="7" t="n">
-        <v>1</v>
+        <v>1</v>
+      </c>
+      <c r="V133" t="n">
+        <v>0</v>
       </c>
       <c r="W133" t="n">
         <v>0</v>
@@ -15871,7 +15880,7 @@
         <v>0</v>
       </c>
       <c r="Z133" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AA133" t="n">
         <v>0</v>
@@ -15889,7 +15898,7 @@
         <v>5</v>
       </c>
       <c r="AF133" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="AG133" t="n">
         <v>9</v>
@@ -15903,15 +15912,15 @@
       </c>
       <c r="B134" t="inlineStr">
         <is>
-          <t>2026-07-11 08:11:16 PM PT</t>
+          <t>2026-07-11 08:13:17 PM PT</t>
         </is>
       </c>
       <c r="C134" t="n">
-        <v>823357</v>
+        <v>822711</v>
       </c>
       <c r="D134" t="inlineStr">
         <is>
-          <t>9:05 AM PT</t>
+          <t>1:05 PM PT</t>
         </is>
       </c>
       <c r="E134" t="inlineStr">
@@ -15924,40 +15933,40 @@
       </c>
       <c r="G134" t="inlineStr">
         <is>
-          <t>Top</t>
+          <t>Bottom</t>
         </is>
       </c>
       <c r="K134" t="inlineStr">
         <is>
-          <t>Home</t>
+          <t>Away</t>
         </is>
       </c>
       <c r="L134" t="inlineStr">
         <is>
-          <t>PIT</t>
+          <t>NYY</t>
         </is>
       </c>
       <c r="M134" t="inlineStr">
         <is>
-          <t>MIL</t>
+          <t>WSH</t>
         </is>
       </c>
       <c r="N134" t="inlineStr">
         <is>
-          <t>Brandon Lowe</t>
+          <t>Cody Bellinger</t>
         </is>
       </c>
       <c r="O134" t="n">
-        <v>664040</v>
+        <v>641355</v>
       </c>
       <c r="P134" t="inlineStr">
         <is>
-          <t>2B</t>
+          <t>LF</t>
         </is>
       </c>
       <c r="Q134" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>5</t>
         </is>
       </c>
       <c r="R134" t="n">
@@ -15970,10 +15979,10 @@
         <v>1</v>
       </c>
       <c r="U134" t="n">
-        <v>1</v>
-      </c>
-      <c r="V134" t="n">
-        <v>0</v>
+        <v>0</v>
+      </c>
+      <c r="V134" s="7" t="n">
+        <v>1</v>
       </c>
       <c r="W134" t="n">
         <v>0</v>
@@ -15982,7 +15991,7 @@
         <v>0</v>
       </c>
       <c r="Y134" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Z134" t="n">
         <v>0</v>
@@ -15997,16 +16006,16 @@
         <v>0</v>
       </c>
       <c r="AD134" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AE134" s="4" t="n">
         <v>5</v>
       </c>
       <c r="AF134" t="n">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="AG134" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
     </row>
     <row r="135">
@@ -16017,7 +16026,7 @@
       </c>
       <c r="B135" t="inlineStr">
         <is>
-          <t>2026-07-11 08:11:16 PM PT</t>
+          <t>2026-07-11 08:13:16 PM PT</t>
         </is>
       </c>
       <c r="C135" t="n">
@@ -16058,27 +16067,27 @@
       </c>
       <c r="N135" t="inlineStr">
         <is>
-          <t>Nick Gonzales</t>
+          <t>Brandon Lowe</t>
         </is>
       </c>
       <c r="O135" t="n">
-        <v>693304</v>
+        <v>664040</v>
       </c>
       <c r="P135" t="inlineStr">
         <is>
-          <t>3B</t>
+          <t>2B</t>
         </is>
       </c>
       <c r="Q135" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>2</t>
         </is>
       </c>
       <c r="R135" t="n">
         <v>4</v>
       </c>
       <c r="S135" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="T135" t="n">
         <v>1</v>
@@ -16096,13 +16105,13 @@
         <v>0</v>
       </c>
       <c r="Y135" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Z135" t="n">
         <v>0</v>
       </c>
-      <c r="AA135" s="5" t="n">
-        <v>1</v>
+      <c r="AA135" t="n">
+        <v>0</v>
       </c>
       <c r="AB135" t="n">
         <v>0</v>
@@ -16131,15 +16140,15 @@
       </c>
       <c r="B136" t="inlineStr">
         <is>
-          <t>2026-07-11 08:11:17 PM PT</t>
+          <t>2026-07-11 08:13:16 PM PT</t>
         </is>
       </c>
       <c r="C136" t="n">
-        <v>822953</v>
+        <v>823357</v>
       </c>
       <c r="D136" t="inlineStr">
         <is>
-          <t>1:10 PM PT</t>
+          <t>9:05 AM PT</t>
         </is>
       </c>
       <c r="E136" t="inlineStr">
@@ -16157,51 +16166,51 @@
       </c>
       <c r="K136" t="inlineStr">
         <is>
-          <t>Away</t>
+          <t>Home</t>
         </is>
       </c>
       <c r="L136" t="inlineStr">
         <is>
-          <t>SEA</t>
+          <t>PIT</t>
         </is>
       </c>
       <c r="M136" t="inlineStr">
         <is>
-          <t>TB</t>
+          <t>MIL</t>
         </is>
       </c>
       <c r="N136" t="inlineStr">
         <is>
-          <t>Josh Naylor</t>
+          <t>Nick Gonzales</t>
         </is>
       </c>
       <c r="O136" t="n">
-        <v>647304</v>
+        <v>693304</v>
       </c>
       <c r="P136" t="inlineStr">
         <is>
-          <t>1B</t>
+          <t>3B</t>
         </is>
       </c>
       <c r="Q136" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="R136" t="n">
         <v>4</v>
       </c>
       <c r="S136" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="T136" t="n">
         <v>1</v>
       </c>
       <c r="U136" t="n">
-        <v>0</v>
-      </c>
-      <c r="V136" s="7" t="n">
-        <v>1</v>
+        <v>1</v>
+      </c>
+      <c r="V136" t="n">
+        <v>0</v>
       </c>
       <c r="W136" t="n">
         <v>0</v>
@@ -16215,8 +16224,8 @@
       <c r="Z136" t="n">
         <v>0</v>
       </c>
-      <c r="AA136" t="n">
-        <v>0</v>
+      <c r="AA136" s="5" t="n">
+        <v>1</v>
       </c>
       <c r="AB136" t="n">
         <v>0</v>
@@ -16225,16 +16234,16 @@
         <v>0</v>
       </c>
       <c r="AD136" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AE136" s="4" t="n">
         <v>5</v>
       </c>
       <c r="AF136" t="n">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="AG136" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
     </row>
     <row r="137">
@@ -16245,7 +16254,7 @@
       </c>
       <c r="B137" t="inlineStr">
         <is>
-          <t>2026-07-11 08:11:17 PM PT</t>
+          <t>2026-07-11 08:13:18 PM PT</t>
         </is>
       </c>
       <c r="C137" t="n">
@@ -16286,60 +16295,60 @@
       </c>
       <c r="N137" t="inlineStr">
         <is>
-          <t>Victor Robles</t>
+          <t>Josh Naylor</t>
         </is>
       </c>
       <c r="O137" t="n">
-        <v>645302</v>
+        <v>647304</v>
       </c>
       <c r="P137" t="inlineStr">
         <is>
-          <t>CF</t>
+          <t>1B</t>
         </is>
       </c>
       <c r="Q137" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>5</t>
         </is>
       </c>
       <c r="R137" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="S137" t="n">
+        <v>4</v>
+      </c>
+      <c r="T137" t="n">
+        <v>1</v>
+      </c>
+      <c r="U137" t="n">
+        <v>0</v>
+      </c>
+      <c r="V137" s="7" t="n">
+        <v>1</v>
+      </c>
+      <c r="W137" t="n">
+        <v>0</v>
+      </c>
+      <c r="X137" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y137" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z137" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA137" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB137" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC137" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD137" t="n">
         <v>2</v>
-      </c>
-      <c r="T137" t="n">
-        <v>1</v>
-      </c>
-      <c r="U137" t="n">
-        <v>0</v>
-      </c>
-      <c r="V137" s="7" t="n">
-        <v>1</v>
-      </c>
-      <c r="W137" t="n">
-        <v>0</v>
-      </c>
-      <c r="X137" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y137" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z137" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA137" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB137" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC137" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD137" t="n">
-        <v>0</v>
       </c>
       <c r="AE137" s="4" t="n">
         <v>5</v>
@@ -16359,15 +16368,15 @@
       </c>
       <c r="B138" t="inlineStr">
         <is>
-          <t>2026-07-11 08:11:17 PM PT</t>
+          <t>2026-07-11 08:13:18 PM PT</t>
         </is>
       </c>
       <c r="C138" t="n">
-        <v>823198</v>
+        <v>822953</v>
       </c>
       <c r="D138" t="inlineStr">
         <is>
-          <t>1:05 PM PT</t>
+          <t>1:10 PM PT</t>
         </is>
       </c>
       <c r="E138" t="inlineStr">
@@ -16385,51 +16394,51 @@
       </c>
       <c r="K138" t="inlineStr">
         <is>
-          <t>Home</t>
+          <t>Away</t>
         </is>
       </c>
       <c r="L138" t="inlineStr">
         <is>
-          <t>SF</t>
+          <t>SEA</t>
         </is>
       </c>
       <c r="M138" t="inlineStr">
         <is>
-          <t>COL</t>
+          <t>TB</t>
         </is>
       </c>
       <c r="N138" t="inlineStr">
         <is>
-          <t>Heliot Ramos</t>
+          <t>Victor Robles</t>
         </is>
       </c>
       <c r="O138" t="n">
-        <v>671218</v>
+        <v>645302</v>
       </c>
       <c r="P138" t="inlineStr">
         <is>
-          <t>LF</t>
+          <t>CF</t>
         </is>
       </c>
       <c r="Q138" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>8</t>
         </is>
       </c>
       <c r="R138" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="S138" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="T138" t="n">
         <v>1</v>
       </c>
       <c r="U138" t="n">
-        <v>1</v>
-      </c>
-      <c r="V138" t="n">
-        <v>0</v>
+        <v>0</v>
+      </c>
+      <c r="V138" s="7" t="n">
+        <v>1</v>
       </c>
       <c r="W138" t="n">
         <v>0</v>
@@ -16438,7 +16447,7 @@
         <v>0</v>
       </c>
       <c r="Y138" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Z138" t="n">
         <v>0</v>
@@ -16459,10 +16468,10 @@
         <v>5</v>
       </c>
       <c r="AF138" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="AG138" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
     </row>
     <row r="139">
@@ -16473,15 +16482,15 @@
       </c>
       <c r="B139" t="inlineStr">
         <is>
-          <t>2026-07-11 08:11:18 PM PT</t>
+          <t>2026-07-11 08:13:17 PM PT</t>
         </is>
       </c>
       <c r="C139" t="n">
-        <v>823030</v>
+        <v>823198</v>
       </c>
       <c r="D139" t="inlineStr">
         <is>
-          <t>4:15 PM PT</t>
+          <t>1:05 PM PT</t>
         </is>
       </c>
       <c r="E139" t="inlineStr">
@@ -16504,30 +16513,30 @@
       </c>
       <c r="L139" t="inlineStr">
         <is>
-          <t>STL</t>
+          <t>SF</t>
         </is>
       </c>
       <c r="M139" t="inlineStr">
         <is>
-          <t>ATL</t>
+          <t>COL</t>
         </is>
       </c>
       <c r="N139" t="inlineStr">
         <is>
-          <t>Iván Herrera</t>
+          <t>Heliot Ramos</t>
         </is>
       </c>
       <c r="O139" t="n">
-        <v>671056</v>
+        <v>671218</v>
       </c>
       <c r="P139" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>LF</t>
         </is>
       </c>
       <c r="Q139" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="R139" t="n">
@@ -16576,7 +16585,7 @@
         <v>4</v>
       </c>
       <c r="AG139" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
     </row>
     <row r="140">
@@ -16587,7 +16596,7 @@
       </c>
       <c r="B140" t="inlineStr">
         <is>
-          <t>2026-07-11 08:11:18 PM PT</t>
+          <t>2026-07-11 08:13:18 PM PT</t>
         </is>
       </c>
       <c r="C140" t="n">
@@ -16628,27 +16637,27 @@
       </c>
       <c r="N140" t="inlineStr">
         <is>
-          <t>Jordan Walker</t>
+          <t>Iván Herrera</t>
         </is>
       </c>
       <c r="O140" t="n">
-        <v>691023</v>
+        <v>671056</v>
       </c>
       <c r="P140" t="inlineStr">
         <is>
-          <t>RF</t>
+          <t>C</t>
         </is>
       </c>
       <c r="Q140" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>2</t>
         </is>
       </c>
       <c r="R140" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="S140" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="T140" t="n">
         <v>1</v>
@@ -16701,7 +16710,7 @@
       </c>
       <c r="B141" t="inlineStr">
         <is>
-          <t>2026-07-11 08:11:18 PM PT</t>
+          <t>2026-07-11 08:13:18 PM PT</t>
         </is>
       </c>
       <c r="C141" t="n">
@@ -16742,20 +16751,20 @@
       </c>
       <c r="N141" t="inlineStr">
         <is>
-          <t>Blaze Jordan</t>
+          <t>Jordan Walker</t>
         </is>
       </c>
       <c r="O141" t="n">
-        <v>691458</v>
+        <v>691023</v>
       </c>
       <c r="P141" t="inlineStr">
         <is>
-          <t>3B</t>
+          <t>RF</t>
         </is>
       </c>
       <c r="Q141" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>4</t>
         </is>
       </c>
       <c r="R141" t="n">
@@ -16780,10 +16789,10 @@
         <v>0</v>
       </c>
       <c r="Y141" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Z141" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AA141" t="n">
         <v>0</v>
@@ -16795,7 +16804,7 @@
         <v>0</v>
       </c>
       <c r="AD141" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AE141" s="4" t="n">
         <v>5</v>
@@ -16815,15 +16824,15 @@
       </c>
       <c r="B142" t="inlineStr">
         <is>
-          <t>2026-07-11 08:11:17 PM PT</t>
+          <t>2026-07-11 08:13:18 PM PT</t>
         </is>
       </c>
       <c r="C142" t="n">
-        <v>822953</v>
+        <v>823030</v>
       </c>
       <c r="D142" t="inlineStr">
         <is>
-          <t>1:10 PM PT</t>
+          <t>4:15 PM PT</t>
         </is>
       </c>
       <c r="E142" t="inlineStr">
@@ -16846,37 +16855,37 @@
       </c>
       <c r="L142" t="inlineStr">
         <is>
-          <t>TB</t>
+          <t>STL</t>
         </is>
       </c>
       <c r="M142" t="inlineStr">
         <is>
-          <t>SEA</t>
+          <t>ATL</t>
         </is>
       </c>
       <c r="N142" t="inlineStr">
         <is>
-          <t>Chandler Simpson</t>
+          <t>Blaze Jordan</t>
         </is>
       </c>
       <c r="O142" t="n">
-        <v>802415</v>
+        <v>691458</v>
       </c>
       <c r="P142" t="inlineStr">
         <is>
-          <t>LF</t>
+          <t>3B</t>
         </is>
       </c>
       <c r="Q142" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>8</t>
         </is>
       </c>
       <c r="R142" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="S142" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="T142" t="n">
         <v>1</v>
@@ -16894,10 +16903,10 @@
         <v>0</v>
       </c>
       <c r="Y142" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Z142" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AA142" t="n">
         <v>0</v>
@@ -16909,16 +16918,16 @@
         <v>0</v>
       </c>
       <c r="AD142" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AE142" s="4" t="n">
         <v>5</v>
       </c>
       <c r="AF142" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="AG142" t="n">
-        <v>12</v>
+        <v>5</v>
       </c>
     </row>
     <row r="143">
@@ -16929,15 +16938,15 @@
       </c>
       <c r="B143" t="inlineStr">
         <is>
-          <t>2026-07-11 08:11:17 PM PT</t>
+          <t>2026-07-11 08:13:18 PM PT</t>
         </is>
       </c>
       <c r="C143" t="n">
-        <v>822875</v>
+        <v>822953</v>
       </c>
       <c r="D143" t="inlineStr">
         <is>
-          <t>4:05 PM PT</t>
+          <t>1:10 PM PT</t>
         </is>
       </c>
       <c r="E143" t="inlineStr">
@@ -16950,7 +16959,7 @@
       </c>
       <c r="G143" t="inlineStr">
         <is>
-          <t>Bottom</t>
+          <t>Top</t>
         </is>
       </c>
       <c r="K143" t="inlineStr">
@@ -16960,21 +16969,21 @@
       </c>
       <c r="L143" t="inlineStr">
         <is>
-          <t>TEX</t>
+          <t>TB</t>
         </is>
       </c>
       <c r="M143" t="inlineStr">
         <is>
-          <t>HOU</t>
+          <t>SEA</t>
         </is>
       </c>
       <c r="N143" t="inlineStr">
         <is>
-          <t>Wyatt Langford</t>
+          <t>Chandler Simpson</t>
         </is>
       </c>
       <c r="O143" t="n">
-        <v>694671</v>
+        <v>802415</v>
       </c>
       <c r="P143" t="inlineStr">
         <is>
@@ -16983,14 +16992,14 @@
       </c>
       <c r="Q143" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>6</t>
         </is>
       </c>
       <c r="R143" t="n">
         <v>4</v>
       </c>
       <c r="S143" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="T143" t="n">
         <v>1</v>
@@ -17008,13 +17017,13 @@
         <v>0</v>
       </c>
       <c r="Y143" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Z143" t="n">
         <v>0</v>
       </c>
-      <c r="AA143" s="5" t="n">
-        <v>1</v>
+      <c r="AA143" t="n">
+        <v>0</v>
       </c>
       <c r="AB143" t="n">
         <v>0</v>
@@ -17029,10 +17038,10 @@
         <v>5</v>
       </c>
       <c r="AF143" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="AG143" t="n">
-        <v>7</v>
+        <v>12</v>
       </c>
     </row>
     <row r="144">
@@ -17043,7 +17052,7 @@
       </c>
       <c r="B144" t="inlineStr">
         <is>
-          <t>2026-07-11 08:11:17 PM PT</t>
+          <t>2026-07-11 08:13:18 PM PT</t>
         </is>
       </c>
       <c r="C144" t="n">
@@ -17084,27 +17093,27 @@
       </c>
       <c r="N144" t="inlineStr">
         <is>
-          <t>Cam Cauley</t>
+          <t>Wyatt Langford</t>
         </is>
       </c>
       <c r="O144" t="n">
-        <v>695508</v>
+        <v>694671</v>
       </c>
       <c r="P144" t="inlineStr">
         <is>
-          <t>PH</t>
+          <t>LF</t>
         </is>
       </c>
       <c r="Q144" t="inlineStr">
         <is>
-          <t>4 (Sub)</t>
+          <t>2</t>
         </is>
       </c>
       <c r="R144" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="S144" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="T144" t="n">
         <v>1</v>
@@ -17122,13 +17131,13 @@
         <v>0</v>
       </c>
       <c r="Y144" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Z144" t="n">
         <v>0</v>
       </c>
-      <c r="AA144" t="n">
-        <v>0</v>
+      <c r="AA144" s="5" t="n">
+        <v>1</v>
       </c>
       <c r="AB144" t="n">
         <v>0</v>
@@ -17157,119 +17166,110 @@
       </c>
       <c r="B145" t="inlineStr">
         <is>
-          <t>2026-07-11 08:11:18 PM PT</t>
+          <t>2026-07-11 08:13:18 PM PT</t>
         </is>
       </c>
       <c r="C145" t="n">
-        <v>823926</v>
+        <v>822875</v>
       </c>
       <c r="D145" t="inlineStr">
         <is>
-          <t>6:10 PM PT</t>
+          <t>4:05 PM PT</t>
         </is>
       </c>
       <c r="E145" t="inlineStr">
         <is>
-          <t>Top 7 | 1 out</t>
+          <t>Final</t>
         </is>
       </c>
       <c r="F145" t="n">
+        <v>9</v>
+      </c>
+      <c r="G145" t="inlineStr">
+        <is>
+          <t>Bottom</t>
+        </is>
+      </c>
+      <c r="K145" t="inlineStr">
+        <is>
+          <t>Home</t>
+        </is>
+      </c>
+      <c r="L145" t="inlineStr">
+        <is>
+          <t>TEX</t>
+        </is>
+      </c>
+      <c r="M145" t="inlineStr">
+        <is>
+          <t>HOU</t>
+        </is>
+      </c>
+      <c r="N145" t="inlineStr">
+        <is>
+          <t>Cam Cauley</t>
+        </is>
+      </c>
+      <c r="O145" t="n">
+        <v>695508</v>
+      </c>
+      <c r="P145" t="inlineStr">
+        <is>
+          <t>PH</t>
+        </is>
+      </c>
+      <c r="Q145" t="inlineStr">
+        <is>
+          <t>4 (Sub)</t>
+        </is>
+      </c>
+      <c r="R145" t="n">
+        <v>1</v>
+      </c>
+      <c r="S145" t="n">
+        <v>1</v>
+      </c>
+      <c r="T145" t="n">
+        <v>1</v>
+      </c>
+      <c r="U145" t="n">
+        <v>1</v>
+      </c>
+      <c r="V145" t="n">
+        <v>0</v>
+      </c>
+      <c r="W145" t="n">
+        <v>0</v>
+      </c>
+      <c r="X145" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y145" t="n">
+        <v>1</v>
+      </c>
+      <c r="Z145" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA145" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB145" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC145" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD145" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE145" s="4" t="n">
+        <v>5</v>
+      </c>
+      <c r="AF145" t="n">
+        <v>3</v>
+      </c>
+      <c r="AG145" t="n">
         <v>7</v>
-      </c>
-      <c r="G145" t="inlineStr">
-        <is>
-          <t>Top</t>
-        </is>
-      </c>
-      <c r="H145" t="n">
-        <v>1</v>
-      </c>
-      <c r="I145" t="n">
-        <v>1</v>
-      </c>
-      <c r="J145" t="n">
-        <v>3</v>
-      </c>
-      <c r="K145" t="inlineStr">
-        <is>
-          <t>Away</t>
-        </is>
-      </c>
-      <c r="L145" t="inlineStr">
-        <is>
-          <t>ARI</t>
-        </is>
-      </c>
-      <c r="M145" t="inlineStr">
-        <is>
-          <t>LAD</t>
-        </is>
-      </c>
-      <c r="N145" t="inlineStr">
-        <is>
-          <t>Geraldo Perdomo</t>
-        </is>
-      </c>
-      <c r="O145" t="n">
-        <v>672695</v>
-      </c>
-      <c r="P145" t="inlineStr">
-        <is>
-          <t>SS</t>
-        </is>
-      </c>
-      <c r="Q145" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="R145" t="n">
-        <v>3</v>
-      </c>
-      <c r="S145" t="n">
-        <v>2</v>
-      </c>
-      <c r="T145" t="n">
-        <v>0</v>
-      </c>
-      <c r="U145" t="n">
-        <v>0</v>
-      </c>
-      <c r="V145" t="n">
-        <v>0</v>
-      </c>
-      <c r="W145" t="n">
-        <v>0</v>
-      </c>
-      <c r="X145" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y145" t="n">
-        <v>1</v>
-      </c>
-      <c r="Z145" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA145" s="5" t="n">
-        <v>1</v>
-      </c>
-      <c r="AB145" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC145" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD145" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE145" s="4" t="n">
-        <v>4</v>
-      </c>
-      <c r="AF145" t="n">
-        <v>6</v>
-      </c>
-      <c r="AG145" t="n">
-        <v>5</v>
       </c>
     </row>
     <row r="146">
@@ -17280,7 +17280,7 @@
       </c>
       <c r="B146" t="inlineStr">
         <is>
-          <t>2026-07-11 08:11:18 PM PT</t>
+          <t>2026-07-11 08:13:19 PM PT</t>
         </is>
       </c>
       <c r="C146" t="n">
@@ -17308,10 +17308,10 @@
         <v>1</v>
       </c>
       <c r="I146" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J146" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="K146" t="inlineStr">
         <is>
@@ -17403,7 +17403,7 @@
       </c>
       <c r="B147" t="inlineStr">
         <is>
-          <t>2026-07-11 08:11:18 PM PT</t>
+          <t>2026-07-11 08:13:18 PM PT</t>
         </is>
       </c>
       <c r="C147" t="n">
@@ -17517,7 +17517,7 @@
       </c>
       <c r="B148" t="inlineStr">
         <is>
-          <t>2026-07-11 08:11:17 PM PT</t>
+          <t>2026-07-11 08:13:18 PM PT</t>
         </is>
       </c>
       <c r="C148" t="n">
@@ -17631,7 +17631,7 @@
       </c>
       <c r="B149" t="inlineStr">
         <is>
-          <t>2026-07-11 08:11:17 PM PT</t>
+          <t>2026-07-11 08:13:17 PM PT</t>
         </is>
       </c>
       <c r="C149" t="n">
@@ -17745,7 +17745,7 @@
       </c>
       <c r="B150" t="inlineStr">
         <is>
-          <t>2026-07-11 08:11:16 PM PT</t>
+          <t>2026-07-11 08:13:16 PM PT</t>
         </is>
       </c>
       <c r="C150" t="n">
@@ -17859,7 +17859,7 @@
       </c>
       <c r="B151" t="inlineStr">
         <is>
-          <t>2026-07-11 08:11:16 PM PT</t>
+          <t>2026-07-11 08:13:16 PM PT</t>
         </is>
       </c>
       <c r="C151" t="n">
@@ -17973,7 +17973,7 @@
       </c>
       <c r="B152" t="inlineStr">
         <is>
-          <t>2026-07-11 08:11:16 PM PT</t>
+          <t>2026-07-11 08:13:17 PM PT</t>
         </is>
       </c>
       <c r="C152" t="n">
@@ -18087,7 +18087,7 @@
       </c>
       <c r="B153" t="inlineStr">
         <is>
-          <t>2026-07-11 08:11:17 PM PT</t>
+          <t>2026-07-11 08:13:18 PM PT</t>
         </is>
       </c>
       <c r="C153" t="n">
@@ -18201,7 +18201,7 @@
       </c>
       <c r="B154" t="inlineStr">
         <is>
-          <t>2026-07-11 08:11:17 PM PT</t>
+          <t>2026-07-11 08:13:18 PM PT</t>
         </is>
       </c>
       <c r="C154" t="n">
@@ -18315,7 +18315,7 @@
       </c>
       <c r="B155" t="inlineStr">
         <is>
-          <t>2026-07-11 08:11:16 PM PT</t>
+          <t>2026-07-11 08:13:16 PM PT</t>
         </is>
       </c>
       <c r="C155" t="n">
@@ -18429,7 +18429,7 @@
       </c>
       <c r="B156" t="inlineStr">
         <is>
-          <t>2026-07-11 08:11:18 PM PT</t>
+          <t>2026-07-11 08:13:19 PM PT</t>
         </is>
       </c>
       <c r="C156" t="n">
@@ -18442,7 +18442,7 @@
       </c>
       <c r="E156" t="inlineStr">
         <is>
-          <t>Top 7 | 3 out</t>
+          <t>Bottom 7 | 0 out</t>
         </is>
       </c>
       <c r="F156" t="n">
@@ -18450,17 +18450,17 @@
       </c>
       <c r="G156" t="inlineStr">
         <is>
-          <t>Top</t>
+          <t>Bottom</t>
         </is>
       </c>
       <c r="H156" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="I156" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="J156" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K156" t="inlineStr">
         <is>
@@ -18552,7 +18552,7 @@
       </c>
       <c r="B157" t="inlineStr">
         <is>
-          <t>2026-07-11 08:11:18 PM PT</t>
+          <t>2026-07-11 08:13:19 PM PT</t>
         </is>
       </c>
       <c r="C157" t="n">
@@ -18565,7 +18565,7 @@
       </c>
       <c r="E157" t="inlineStr">
         <is>
-          <t>Top 7 | 3 out</t>
+          <t>Bottom 7 | 0 out</t>
         </is>
       </c>
       <c r="F157" t="n">
@@ -18573,17 +18573,17 @@
       </c>
       <c r="G157" t="inlineStr">
         <is>
-          <t>Top</t>
+          <t>Bottom</t>
         </is>
       </c>
       <c r="H157" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="I157" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="J157" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K157" t="inlineStr">
         <is>
@@ -18675,7 +18675,7 @@
       </c>
       <c r="B158" t="inlineStr">
         <is>
-          <t>2026-07-11 08:11:18 PM PT</t>
+          <t>2026-07-11 08:13:19 PM PT</t>
         </is>
       </c>
       <c r="C158" t="n">
@@ -18688,7 +18688,7 @@
       </c>
       <c r="E158" t="inlineStr">
         <is>
-          <t>Top 7 | 3 out</t>
+          <t>Bottom 7 | 0 out</t>
         </is>
       </c>
       <c r="F158" t="n">
@@ -18696,17 +18696,17 @@
       </c>
       <c r="G158" t="inlineStr">
         <is>
-          <t>Top</t>
+          <t>Bottom</t>
         </is>
       </c>
       <c r="H158" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="I158" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="J158" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K158" t="inlineStr">
         <is>
@@ -18798,7 +18798,7 @@
       </c>
       <c r="B159" t="inlineStr">
         <is>
-          <t>2026-07-11 08:11:18 PM PT</t>
+          <t>2026-07-11 08:13:19 PM PT</t>
         </is>
       </c>
       <c r="C159" t="n">
@@ -18811,7 +18811,7 @@
       </c>
       <c r="E159" t="inlineStr">
         <is>
-          <t>Top 7 | 3 out</t>
+          <t>Bottom 7 | 0 out</t>
         </is>
       </c>
       <c r="F159" t="n">
@@ -18819,17 +18819,17 @@
       </c>
       <c r="G159" t="inlineStr">
         <is>
-          <t>Top</t>
+          <t>Bottom</t>
         </is>
       </c>
       <c r="H159" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="I159" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="J159" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K159" t="inlineStr">
         <is>
@@ -18921,7 +18921,7 @@
       </c>
       <c r="B160" t="inlineStr">
         <is>
-          <t>2026-07-11 08:11:18 PM PT</t>
+          <t>2026-07-11 08:13:18 PM PT</t>
         </is>
       </c>
       <c r="C160" t="n">
@@ -19035,7 +19035,7 @@
       </c>
       <c r="B161" t="inlineStr">
         <is>
-          <t>2026-07-11 08:11:18 PM PT</t>
+          <t>2026-07-11 08:13:18 PM PT</t>
         </is>
       </c>
       <c r="C161" t="n">
@@ -19149,7 +19149,7 @@
       </c>
       <c r="B162" t="inlineStr">
         <is>
-          <t>2026-07-11 08:11:18 PM PT</t>
+          <t>2026-07-11 08:13:18 PM PT</t>
         </is>
       </c>
       <c r="C162" t="n">
@@ -19263,7 +19263,7 @@
       </c>
       <c r="B163" t="inlineStr">
         <is>
-          <t>2026-07-11 08:11:18 PM PT</t>
+          <t>2026-07-11 08:13:18 PM PT</t>
         </is>
       </c>
       <c r="C163" t="n">
@@ -19377,7 +19377,7 @@
       </c>
       <c r="B164" t="inlineStr">
         <is>
-          <t>2026-07-11 08:11:18 PM PT</t>
+          <t>2026-07-11 08:13:18 PM PT</t>
         </is>
       </c>
       <c r="C164" t="n">
@@ -19491,7 +19491,7 @@
       </c>
       <c r="B165" t="inlineStr">
         <is>
-          <t>2026-07-11 08:11:17 PM PT</t>
+          <t>2026-07-11 08:13:18 PM PT</t>
         </is>
       </c>
       <c r="C165" t="n">
@@ -19605,7 +19605,7 @@
       </c>
       <c r="B166" t="inlineStr">
         <is>
-          <t>2026-07-11 08:11:17 PM PT</t>
+          <t>2026-07-11 08:13:17 PM PT</t>
         </is>
       </c>
       <c r="C166" t="n">
@@ -19719,7 +19719,7 @@
       </c>
       <c r="B167" t="inlineStr">
         <is>
-          <t>2026-07-11 08:11:17 PM PT</t>
+          <t>2026-07-11 08:13:18 PM PT</t>
         </is>
       </c>
       <c r="C167" t="n">
@@ -19833,7 +19833,7 @@
       </c>
       <c r="B168" t="inlineStr">
         <is>
-          <t>2026-07-11 08:11:17 PM PT</t>
+          <t>2026-07-11 08:13:18 PM PT</t>
         </is>
       </c>
       <c r="C168" t="n">
@@ -19947,7 +19947,7 @@
       </c>
       <c r="B169" t="inlineStr">
         <is>
-          <t>2026-07-11 08:11:17 PM PT</t>
+          <t>2026-07-11 08:13:18 PM PT</t>
         </is>
       </c>
       <c r="C169" t="n">
@@ -20061,7 +20061,7 @@
       </c>
       <c r="B170" t="inlineStr">
         <is>
-          <t>2026-07-11 08:11:16 PM PT</t>
+          <t>2026-07-11 08:13:17 PM PT</t>
         </is>
       </c>
       <c r="C170" t="n">
@@ -20175,7 +20175,7 @@
       </c>
       <c r="B171" t="inlineStr">
         <is>
-          <t>2026-07-11 08:11:18 PM PT</t>
+          <t>2026-07-11 08:13:19 PM PT</t>
         </is>
       </c>
       <c r="C171" t="n">
@@ -20203,10 +20203,10 @@
         <v>1</v>
       </c>
       <c r="I171" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J171" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="K171" t="inlineStr">
         <is>
@@ -20298,7 +20298,7 @@
       </c>
       <c r="B172" t="inlineStr">
         <is>
-          <t>2026-07-11 08:11:18 PM PT</t>
+          <t>2026-07-11 08:13:19 PM PT</t>
         </is>
       </c>
       <c r="C172" t="n">
@@ -20326,10 +20326,10 @@
         <v>1</v>
       </c>
       <c r="I172" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J172" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="K172" t="inlineStr">
         <is>
@@ -20421,7 +20421,7 @@
       </c>
       <c r="B173" t="inlineStr">
         <is>
-          <t>2026-07-11 08:11:17 PM PT</t>
+          <t>2026-07-11 08:13:18 PM PT</t>
         </is>
       </c>
       <c r="C173" t="n">
@@ -20535,7 +20535,7 @@
       </c>
       <c r="B174" t="inlineStr">
         <is>
-          <t>2026-07-11 08:11:17 PM PT</t>
+          <t>2026-07-11 08:13:18 PM PT</t>
         </is>
       </c>
       <c r="C174" t="n">
@@ -20649,7 +20649,7 @@
       </c>
       <c r="B175" t="inlineStr">
         <is>
-          <t>2026-07-11 08:11:16 PM PT</t>
+          <t>2026-07-11 08:13:16 PM PT</t>
         </is>
       </c>
       <c r="C175" t="n">
@@ -20763,7 +20763,7 @@
       </c>
       <c r="B176" t="inlineStr">
         <is>
-          <t>2026-07-11 08:11:16 PM PT</t>
+          <t>2026-07-11 08:13:16 PM PT</t>
         </is>
       </c>
       <c r="C176" t="n">
@@ -20877,7 +20877,7 @@
       </c>
       <c r="B177" t="inlineStr">
         <is>
-          <t>2026-07-11 08:11:16 PM PT</t>
+          <t>2026-07-11 08:13:17 PM PT</t>
         </is>
       </c>
       <c r="C177" t="n">
@@ -20991,7 +20991,7 @@
       </c>
       <c r="B178" t="inlineStr">
         <is>
-          <t>2026-07-11 08:11:16 PM PT</t>
+          <t>2026-07-11 08:13:17 PM PT</t>
         </is>
       </c>
       <c r="C178" t="n">
@@ -21105,7 +21105,7 @@
       </c>
       <c r="B179" t="inlineStr">
         <is>
-          <t>2026-07-11 08:11:16 PM PT</t>
+          <t>2026-07-11 08:13:17 PM PT</t>
         </is>
       </c>
       <c r="C179" t="n">
@@ -21219,7 +21219,7 @@
       </c>
       <c r="B180" t="inlineStr">
         <is>
-          <t>2026-07-11 08:11:17 PM PT</t>
+          <t>2026-07-11 08:13:17 PM PT</t>
         </is>
       </c>
       <c r="C180" t="n">
@@ -21333,7 +21333,7 @@
       </c>
       <c r="B181" t="inlineStr">
         <is>
-          <t>2026-07-11 08:11:17 PM PT</t>
+          <t>2026-07-11 08:13:17 PM PT</t>
         </is>
       </c>
       <c r="C181" t="n">
@@ -21447,7 +21447,7 @@
       </c>
       <c r="B182" t="inlineStr">
         <is>
-          <t>2026-07-11 08:11:17 PM PT</t>
+          <t>2026-07-11 08:13:17 PM PT</t>
         </is>
       </c>
       <c r="C182" t="n">
@@ -21561,7 +21561,7 @@
       </c>
       <c r="B183" t="inlineStr">
         <is>
-          <t>2026-07-11 08:11:17 PM PT</t>
+          <t>2026-07-11 08:13:18 PM PT</t>
         </is>
       </c>
       <c r="C183" t="n">
@@ -21675,7 +21675,7 @@
       </c>
       <c r="B184" t="inlineStr">
         <is>
-          <t>2026-07-11 08:11:16 PM PT</t>
+          <t>2026-07-11 08:13:16 PM PT</t>
         </is>
       </c>
       <c r="C184" t="n">
@@ -21789,7 +21789,7 @@
       </c>
       <c r="B185" t="inlineStr">
         <is>
-          <t>2026-07-11 08:11:16 PM PT</t>
+          <t>2026-07-11 08:13:16 PM PT</t>
         </is>
       </c>
       <c r="C185" t="n">
@@ -21903,7 +21903,7 @@
       </c>
       <c r="B186" t="inlineStr">
         <is>
-          <t>2026-07-11 08:11:17 PM PT</t>
+          <t>2026-07-11 08:13:18 PM PT</t>
         </is>
       </c>
       <c r="C186" t="n">
@@ -22017,7 +22017,7 @@
       </c>
       <c r="B187" t="inlineStr">
         <is>
-          <t>2026-07-11 08:11:17 PM PT</t>
+          <t>2026-07-11 08:13:17 PM PT</t>
         </is>
       </c>
       <c r="C187" t="n">
@@ -22131,7 +22131,7 @@
       </c>
       <c r="B188" t="inlineStr">
         <is>
-          <t>2026-07-11 08:11:17 PM PT</t>
+          <t>2026-07-11 08:13:18 PM PT</t>
         </is>
       </c>
       <c r="C188" t="n">
@@ -22245,7 +22245,7 @@
       </c>
       <c r="B189" t="inlineStr">
         <is>
-          <t>2026-07-11 08:11:17 PM PT</t>
+          <t>2026-07-11 08:13:18 PM PT</t>
         </is>
       </c>
       <c r="C189" t="n">
@@ -22359,7 +22359,7 @@
       </c>
       <c r="B190" t="inlineStr">
         <is>
-          <t>2026-07-11 08:11:17 PM PT</t>
+          <t>2026-07-11 08:13:17 PM PT</t>
         </is>
       </c>
       <c r="C190" t="n">
@@ -22473,7 +22473,7 @@
       </c>
       <c r="B191" t="inlineStr">
         <is>
-          <t>2026-07-11 08:11:17 PM PT</t>
+          <t>2026-07-11 08:13:17 PM PT</t>
         </is>
       </c>
       <c r="C191" t="n">
@@ -22587,7 +22587,7 @@
       </c>
       <c r="B192" t="inlineStr">
         <is>
-          <t>2026-07-11 08:11:18 PM PT</t>
+          <t>2026-07-11 08:13:19 PM PT</t>
         </is>
       </c>
       <c r="C192" t="n">
@@ -22615,10 +22615,10 @@
         <v>1</v>
       </c>
       <c r="I192" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J192" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="K192" t="inlineStr">
         <is>
@@ -22710,7 +22710,7 @@
       </c>
       <c r="B193" t="inlineStr">
         <is>
-          <t>2026-07-11 08:11:17 PM PT</t>
+          <t>2026-07-11 08:13:17 PM PT</t>
         </is>
       </c>
       <c r="C193" t="n">
@@ -22824,7 +22824,7 @@
       </c>
       <c r="B194" t="inlineStr">
         <is>
-          <t>2026-07-11 08:11:18 PM PT</t>
+          <t>2026-07-11 08:13:18 PM PT</t>
         </is>
       </c>
       <c r="C194" t="n">
@@ -22938,7 +22938,7 @@
       </c>
       <c r="B195" t="inlineStr">
         <is>
-          <t>2026-07-11 08:11:18 PM PT</t>
+          <t>2026-07-11 08:13:18 PM PT</t>
         </is>
       </c>
       <c r="C195" t="n">
@@ -23052,7 +23052,7 @@
       </c>
       <c r="B196" t="inlineStr">
         <is>
-          <t>2026-07-11 08:11:17 PM PT</t>
+          <t>2026-07-11 08:13:18 PM PT</t>
         </is>
       </c>
       <c r="C196" t="n">
@@ -23166,7 +23166,7 @@
       </c>
       <c r="B197" t="inlineStr">
         <is>
-          <t>2026-07-11 08:11:17 PM PT</t>
+          <t>2026-07-11 08:13:17 PM PT</t>
         </is>
       </c>
       <c r="C197" t="n">
@@ -23280,7 +23280,7 @@
       </c>
       <c r="B198" t="inlineStr">
         <is>
-          <t>2026-07-11 08:11:17 PM PT</t>
+          <t>2026-07-11 08:13:17 PM PT</t>
         </is>
       </c>
       <c r="C198" t="n">
@@ -23394,7 +23394,7 @@
       </c>
       <c r="B199" t="inlineStr">
         <is>
-          <t>2026-07-11 08:11:17 PM PT</t>
+          <t>2026-07-11 08:13:17 PM PT</t>
         </is>
       </c>
       <c r="C199" t="n">
@@ -23508,7 +23508,7 @@
       </c>
       <c r="B200" t="inlineStr">
         <is>
-          <t>2026-07-11 08:11:18 PM PT</t>
+          <t>2026-07-11 08:13:18 PM PT</t>
         </is>
       </c>
       <c r="C200" t="n">
@@ -23622,7 +23622,7 @@
       </c>
       <c r="B201" t="inlineStr">
         <is>
-          <t>2026-07-11 08:11:17 PM PT</t>
+          <t>2026-07-11 08:13:17 PM PT</t>
         </is>
       </c>
       <c r="C201" t="n">
@@ -23736,7 +23736,7 @@
       </c>
       <c r="B202" t="inlineStr">
         <is>
-          <t>2026-07-11 08:11:17 PM PT</t>
+          <t>2026-07-11 08:13:17 PM PT</t>
         </is>
       </c>
       <c r="C202" t="n">
@@ -23850,7 +23850,7 @@
       </c>
       <c r="B203" t="inlineStr">
         <is>
-          <t>2026-07-11 08:11:17 PM PT</t>
+          <t>2026-07-11 08:13:17 PM PT</t>
         </is>
       </c>
       <c r="C203" t="n">
@@ -23964,7 +23964,7 @@
       </c>
       <c r="B204" t="inlineStr">
         <is>
-          <t>2026-07-11 08:11:17 PM PT</t>
+          <t>2026-07-11 08:13:17 PM PT</t>
         </is>
       </c>
       <c r="C204" t="n">
@@ -24078,7 +24078,7 @@
       </c>
       <c r="B205" t="inlineStr">
         <is>
-          <t>2026-07-11 08:11:17 PM PT</t>
+          <t>2026-07-11 08:13:17 PM PT</t>
         </is>
       </c>
       <c r="C205" t="n">
@@ -24192,7 +24192,7 @@
       </c>
       <c r="B206" t="inlineStr">
         <is>
-          <t>2026-07-11 08:11:17 PM PT</t>
+          <t>2026-07-11 08:13:18 PM PT</t>
         </is>
       </c>
       <c r="C206" t="n">
@@ -24306,7 +24306,7 @@
       </c>
       <c r="B207" t="inlineStr">
         <is>
-          <t>2026-07-11 08:11:17 PM PT</t>
+          <t>2026-07-11 08:13:18 PM PT</t>
         </is>
       </c>
       <c r="C207" t="n">
@@ -24420,7 +24420,7 @@
       </c>
       <c r="B208" t="inlineStr">
         <is>
-          <t>2026-07-11 08:11:17 PM PT</t>
+          <t>2026-07-11 08:13:18 PM PT</t>
         </is>
       </c>
       <c r="C208" t="n">
@@ -24534,7 +24534,7 @@
       </c>
       <c r="B209" t="inlineStr">
         <is>
-          <t>2026-07-11 08:11:17 PM PT</t>
+          <t>2026-07-11 08:13:18 PM PT</t>
         </is>
       </c>
       <c r="C209" t="n">
@@ -24648,7 +24648,7 @@
       </c>
       <c r="B210" t="inlineStr">
         <is>
-          <t>2026-07-11 08:11:17 PM PT</t>
+          <t>2026-07-11 08:13:18 PM PT</t>
         </is>
       </c>
       <c r="C210" t="n">
@@ -24762,7 +24762,7 @@
       </c>
       <c r="B211" t="inlineStr">
         <is>
-          <t>2026-07-11 08:11:16 PM PT</t>
+          <t>2026-07-11 08:13:17 PM PT</t>
         </is>
       </c>
       <c r="C211" t="n">
@@ -24876,7 +24876,7 @@
       </c>
       <c r="B212" t="inlineStr">
         <is>
-          <t>2026-07-11 08:11:17 PM PT</t>
+          <t>2026-07-11 08:13:18 PM PT</t>
         </is>
       </c>
       <c r="C212" t="n">
@@ -24990,7 +24990,7 @@
       </c>
       <c r="B213" t="inlineStr">
         <is>
-          <t>2026-07-11 08:11:17 PM PT</t>
+          <t>2026-07-11 08:13:18 PM PT</t>
         </is>
       </c>
       <c r="C213" t="n">
@@ -25104,7 +25104,7 @@
       </c>
       <c r="B214" t="inlineStr">
         <is>
-          <t>2026-07-11 08:11:16 PM PT</t>
+          <t>2026-07-11 08:13:17 PM PT</t>
         </is>
       </c>
       <c r="C214" t="n">
@@ -25218,7 +25218,7 @@
       </c>
       <c r="B215" t="inlineStr">
         <is>
-          <t>2026-07-11 08:11:17 PM PT</t>
+          <t>2026-07-11 08:13:17 PM PT</t>
         </is>
       </c>
       <c r="C215" t="n">
@@ -25332,7 +25332,7 @@
       </c>
       <c r="B216" t="inlineStr">
         <is>
-          <t>2026-07-11 08:11:17 PM PT</t>
+          <t>2026-07-11 08:13:17 PM PT</t>
         </is>
       </c>
       <c r="C216" t="n">
@@ -25446,7 +25446,7 @@
       </c>
       <c r="B217" t="inlineStr">
         <is>
-          <t>2026-07-11 08:11:17 PM PT</t>
+          <t>2026-07-11 08:13:17 PM PT</t>
         </is>
       </c>
       <c r="C217" t="n">
@@ -25560,7 +25560,7 @@
       </c>
       <c r="B218" t="inlineStr">
         <is>
-          <t>2026-07-11 08:11:17 PM PT</t>
+          <t>2026-07-11 08:13:17 PM PT</t>
         </is>
       </c>
       <c r="C218" t="n">
@@ -25674,7 +25674,7 @@
       </c>
       <c r="B219" t="inlineStr">
         <is>
-          <t>2026-07-11 08:11:17 PM PT</t>
+          <t>2026-07-11 08:13:17 PM PT</t>
         </is>
       </c>
       <c r="C219" t="n">
@@ -25788,7 +25788,7 @@
       </c>
       <c r="B220" t="inlineStr">
         <is>
-          <t>2026-07-11 08:11:17 PM PT</t>
+          <t>2026-07-11 08:13:17 PM PT</t>
         </is>
       </c>
       <c r="C220" t="n">
@@ -25902,7 +25902,7 @@
       </c>
       <c r="B221" t="inlineStr">
         <is>
-          <t>2026-07-11 08:11:17 PM PT</t>
+          <t>2026-07-11 08:13:17 PM PT</t>
         </is>
       </c>
       <c r="C221" t="n">
@@ -26016,7 +26016,7 @@
       </c>
       <c r="B222" t="inlineStr">
         <is>
-          <t>2026-07-11 08:11:16 PM PT</t>
+          <t>2026-07-11 08:13:16 PM PT</t>
         </is>
       </c>
       <c r="C222" t="n">
@@ -26130,7 +26130,7 @@
       </c>
       <c r="B223" t="inlineStr">
         <is>
-          <t>2026-07-11 08:11:16 PM PT</t>
+          <t>2026-07-11 08:13:16 PM PT</t>
         </is>
       </c>
       <c r="C223" t="n">
@@ -26244,7 +26244,7 @@
       </c>
       <c r="B224" t="inlineStr">
         <is>
-          <t>2026-07-11 08:11:17 PM PT</t>
+          <t>2026-07-11 08:13:18 PM PT</t>
         </is>
       </c>
       <c r="C224" t="n">
@@ -26358,7 +26358,7 @@
       </c>
       <c r="B225" t="inlineStr">
         <is>
-          <t>2026-07-11 08:11:17 PM PT</t>
+          <t>2026-07-11 08:13:17 PM PT</t>
         </is>
       </c>
       <c r="C225" t="n">
@@ -26472,7 +26472,7 @@
       </c>
       <c r="B226" t="inlineStr">
         <is>
-          <t>2026-07-11 08:11:17 PM PT</t>
+          <t>2026-07-11 08:13:18 PM PT</t>
         </is>
       </c>
       <c r="C226" t="n">
@@ -26586,7 +26586,7 @@
       </c>
       <c r="B227" t="inlineStr">
         <is>
-          <t>2026-07-11 08:11:17 PM PT</t>
+          <t>2026-07-11 08:13:18 PM PT</t>
         </is>
       </c>
       <c r="C227" t="n">
@@ -26700,7 +26700,7 @@
       </c>
       <c r="B228" t="inlineStr">
         <is>
-          <t>2026-07-11 08:11:18 PM PT</t>
+          <t>2026-07-11 08:13:19 PM PT</t>
         </is>
       </c>
       <c r="C228" t="n">
@@ -26713,7 +26713,7 @@
       </c>
       <c r="E228" t="inlineStr">
         <is>
-          <t>Top 7 | 3 out</t>
+          <t>Bottom 7 | 0 out</t>
         </is>
       </c>
       <c r="F228" t="n">
@@ -26721,17 +26721,17 @@
       </c>
       <c r="G228" t="inlineStr">
         <is>
-          <t>Top</t>
+          <t>Bottom</t>
         </is>
       </c>
       <c r="H228" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="I228" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="J228" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K228" t="inlineStr">
         <is>
@@ -26823,7 +26823,7 @@
       </c>
       <c r="B229" t="inlineStr">
         <is>
-          <t>2026-07-11 08:11:17 PM PT</t>
+          <t>2026-07-11 08:13:17 PM PT</t>
         </is>
       </c>
       <c r="C229" t="n">
@@ -26937,7 +26937,7 @@
       </c>
       <c r="B230" t="inlineStr">
         <is>
-          <t>2026-07-11 08:11:17 PM PT</t>
+          <t>2026-07-11 08:13:17 PM PT</t>
         </is>
       </c>
       <c r="C230" t="n">
@@ -27051,7 +27051,7 @@
       </c>
       <c r="B231" t="inlineStr">
         <is>
-          <t>2026-07-11 08:11:17 PM PT</t>
+          <t>2026-07-11 08:13:17 PM PT</t>
         </is>
       </c>
       <c r="C231" t="n">
@@ -27165,7 +27165,7 @@
       </c>
       <c r="B232" t="inlineStr">
         <is>
-          <t>2026-07-11 08:11:17 PM PT</t>
+          <t>2026-07-11 08:13:17 PM PT</t>
         </is>
       </c>
       <c r="C232" t="n">
@@ -27279,7 +27279,7 @@
       </c>
       <c r="B233" t="inlineStr">
         <is>
-          <t>2026-07-11 08:11:18 PM PT</t>
+          <t>2026-07-11 08:13:19 PM PT</t>
         </is>
       </c>
       <c r="C233" t="n">
@@ -27307,10 +27307,10 @@
         <v>1</v>
       </c>
       <c r="I233" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J233" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="K233" t="inlineStr">
         <is>
@@ -27402,7 +27402,7 @@
       </c>
       <c r="B234" t="inlineStr">
         <is>
-          <t>2026-07-11 08:11:18 PM PT</t>
+          <t>2026-07-11 08:13:19 PM PT</t>
         </is>
       </c>
       <c r="C234" t="n">
@@ -27430,10 +27430,10 @@
         <v>1</v>
       </c>
       <c r="I234" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J234" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="K234" t="inlineStr">
         <is>
@@ -27525,7 +27525,7 @@
       </c>
       <c r="B235" t="inlineStr">
         <is>
-          <t>2026-07-11 08:11:18 PM PT</t>
+          <t>2026-07-11 08:13:19 PM PT</t>
         </is>
       </c>
       <c r="C235" t="n">
@@ -27553,10 +27553,10 @@
         <v>1</v>
       </c>
       <c r="I235" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J235" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="K235" t="inlineStr">
         <is>
@@ -27648,7 +27648,7 @@
       </c>
       <c r="B236" t="inlineStr">
         <is>
-          <t>2026-07-11 08:11:17 PM PT</t>
+          <t>2026-07-11 08:13:17 PM PT</t>
         </is>
       </c>
       <c r="C236" t="n">
@@ -27762,7 +27762,7 @@
       </c>
       <c r="B237" t="inlineStr">
         <is>
-          <t>2026-07-11 08:11:17 PM PT</t>
+          <t>2026-07-11 08:13:17 PM PT</t>
         </is>
       </c>
       <c r="C237" t="n">
@@ -27876,7 +27876,7 @@
       </c>
       <c r="B238" t="inlineStr">
         <is>
-          <t>2026-07-11 08:11:17 PM PT</t>
+          <t>2026-07-11 08:13:17 PM PT</t>
         </is>
       </c>
       <c r="C238" t="n">
@@ -27990,7 +27990,7 @@
       </c>
       <c r="B239" t="inlineStr">
         <is>
-          <t>2026-07-11 08:11:17 PM PT</t>
+          <t>2026-07-11 08:13:17 PM PT</t>
         </is>
       </c>
       <c r="C239" t="n">
@@ -28104,7 +28104,7 @@
       </c>
       <c r="B240" t="inlineStr">
         <is>
-          <t>2026-07-11 08:11:17 PM PT</t>
+          <t>2026-07-11 08:13:17 PM PT</t>
         </is>
       </c>
       <c r="C240" t="n">
@@ -28218,7 +28218,7 @@
       </c>
       <c r="B241" t="inlineStr">
         <is>
-          <t>2026-07-11 08:11:17 PM PT</t>
+          <t>2026-07-11 08:13:17 PM PT</t>
         </is>
       </c>
       <c r="C241" t="n">
@@ -28332,7 +28332,7 @@
       </c>
       <c r="B242" t="inlineStr">
         <is>
-          <t>2026-07-11 08:11:17 PM PT</t>
+          <t>2026-07-11 08:13:17 PM PT</t>
         </is>
       </c>
       <c r="C242" t="n">
@@ -28446,7 +28446,7 @@
       </c>
       <c r="B243" t="inlineStr">
         <is>
-          <t>2026-07-11 08:11:18 PM PT</t>
+          <t>2026-07-11 08:13:18 PM PT</t>
         </is>
       </c>
       <c r="C243" t="n">
@@ -28560,7 +28560,7 @@
       </c>
       <c r="B244" t="inlineStr">
         <is>
-          <t>2026-07-11 08:11:18 PM PT</t>
+          <t>2026-07-11 08:13:18 PM PT</t>
         </is>
       </c>
       <c r="C244" t="n">
@@ -28674,7 +28674,7 @@
       </c>
       <c r="B245" t="inlineStr">
         <is>
-          <t>2026-07-11 08:11:18 PM PT</t>
+          <t>2026-07-11 08:13:18 PM PT</t>
         </is>
       </c>
       <c r="C245" t="n">
@@ -28788,7 +28788,7 @@
       </c>
       <c r="B246" t="inlineStr">
         <is>
-          <t>2026-07-11 08:11:17 PM PT</t>
+          <t>2026-07-11 08:13:18 PM PT</t>
         </is>
       </c>
       <c r="C246" t="n">
@@ -28902,7 +28902,7 @@
       </c>
       <c r="B247" t="inlineStr">
         <is>
-          <t>2026-07-11 08:11:17 PM PT</t>
+          <t>2026-07-11 08:13:18 PM PT</t>
         </is>
       </c>
       <c r="C247" t="n">
@@ -29016,7 +29016,7 @@
       </c>
       <c r="B248" t="inlineStr">
         <is>
-          <t>2026-07-11 08:11:17 PM PT</t>
+          <t>2026-07-11 08:13:18 PM PT</t>
         </is>
       </c>
       <c r="C248" t="n">
@@ -29130,7 +29130,7 @@
       </c>
       <c r="B249" t="inlineStr">
         <is>
-          <t>2026-07-11 08:11:17 PM PT</t>
+          <t>2026-07-11 08:13:17 PM PT</t>
         </is>
       </c>
       <c r="C249" t="n">
@@ -29244,7 +29244,7 @@
       </c>
       <c r="B250" t="inlineStr">
         <is>
-          <t>2026-07-11 08:11:17 PM PT</t>
+          <t>2026-07-11 08:13:17 PM PT</t>
         </is>
       </c>
       <c r="C250" t="n">
@@ -29358,7 +29358,7 @@
       </c>
       <c r="B251" t="inlineStr">
         <is>
-          <t>2026-07-11 08:11:17 PM PT</t>
+          <t>2026-07-11 08:13:17 PM PT</t>
         </is>
       </c>
       <c r="C251" t="n">
@@ -29472,7 +29472,7 @@
       </c>
       <c r="B252" t="inlineStr">
         <is>
-          <t>2026-07-11 08:11:18 PM PT</t>
+          <t>2026-07-11 08:13:18 PM PT</t>
         </is>
       </c>
       <c r="C252" t="n">
@@ -29586,7 +29586,7 @@
       </c>
       <c r="B253" t="inlineStr">
         <is>
-          <t>2026-07-11 08:11:18 PM PT</t>
+          <t>2026-07-11 08:13:18 PM PT</t>
         </is>
       </c>
       <c r="C253" t="n">
@@ -29700,7 +29700,7 @@
       </c>
       <c r="B254" t="inlineStr">
         <is>
-          <t>2026-07-11 08:11:18 PM PT</t>
+          <t>2026-07-11 08:13:18 PM PT</t>
         </is>
       </c>
       <c r="C254" t="n">
@@ -29814,7 +29814,7 @@
       </c>
       <c r="B255" t="inlineStr">
         <is>
-          <t>2026-07-11 08:11:18 PM PT</t>
+          <t>2026-07-11 08:13:18 PM PT</t>
         </is>
       </c>
       <c r="C255" t="n">
@@ -29928,7 +29928,7 @@
       </c>
       <c r="B256" t="inlineStr">
         <is>
-          <t>2026-07-11 08:11:18 PM PT</t>
+          <t>2026-07-11 08:13:18 PM PT</t>
         </is>
       </c>
       <c r="C256" t="n">
@@ -30042,7 +30042,7 @@
       </c>
       <c r="B257" t="inlineStr">
         <is>
-          <t>2026-07-11 08:11:17 PM PT</t>
+          <t>2026-07-11 08:13:17 PM PT</t>
         </is>
       </c>
       <c r="C257" t="n">
@@ -30156,7 +30156,7 @@
       </c>
       <c r="B258" t="inlineStr">
         <is>
-          <t>2026-07-11 08:11:17 PM PT</t>
+          <t>2026-07-11 08:13:17 PM PT</t>
         </is>
       </c>
       <c r="C258" t="n">
@@ -30270,7 +30270,7 @@
       </c>
       <c r="B259" t="inlineStr">
         <is>
-          <t>2026-07-11 08:11:17 PM PT</t>
+          <t>2026-07-11 08:13:17 PM PT</t>
         </is>
       </c>
       <c r="C259" t="n">
@@ -30384,7 +30384,7 @@
       </c>
       <c r="B260" t="inlineStr">
         <is>
-          <t>2026-07-11 08:11:17 PM PT</t>
+          <t>2026-07-11 08:13:17 PM PT</t>
         </is>
       </c>
       <c r="C260" t="n">
@@ -30498,7 +30498,7 @@
       </c>
       <c r="B261" t="inlineStr">
         <is>
-          <t>2026-07-11 08:11:17 PM PT</t>
+          <t>2026-07-11 08:13:17 PM PT</t>
         </is>
       </c>
       <c r="C261" t="n">
@@ -30612,7 +30612,7 @@
       </c>
       <c r="B262" t="inlineStr">
         <is>
-          <t>2026-07-11 08:11:17 PM PT</t>
+          <t>2026-07-11 08:13:17 PM PT</t>
         </is>
       </c>
       <c r="C262" t="n">
@@ -30726,7 +30726,7 @@
       </c>
       <c r="B263" t="inlineStr">
         <is>
-          <t>2026-07-11 08:11:17 PM PT</t>
+          <t>2026-07-11 08:13:17 PM PT</t>
         </is>
       </c>
       <c r="C263" t="n">
@@ -30840,7 +30840,7 @@
       </c>
       <c r="B264" t="inlineStr">
         <is>
-          <t>2026-07-11 08:11:17 PM PT</t>
+          <t>2026-07-11 08:13:18 PM PT</t>
         </is>
       </c>
       <c r="C264" t="n">
@@ -30954,7 +30954,7 @@
       </c>
       <c r="B265" t="inlineStr">
         <is>
-          <t>2026-07-11 08:11:17 PM PT</t>
+          <t>2026-07-11 08:13:18 PM PT</t>
         </is>
       </c>
       <c r="C265" t="n">
@@ -31068,7 +31068,7 @@
       </c>
       <c r="B266" t="inlineStr">
         <is>
-          <t>2026-07-11 08:11:17 PM PT</t>
+          <t>2026-07-11 08:13:18 PM PT</t>
         </is>
       </c>
       <c r="C266" t="n">
@@ -31182,7 +31182,7 @@
       </c>
       <c r="B267" t="inlineStr">
         <is>
-          <t>2026-07-11 08:11:17 PM PT</t>
+          <t>2026-07-11 08:13:18 PM PT</t>
         </is>
       </c>
       <c r="C267" t="n">
@@ -31296,7 +31296,7 @@
       </c>
       <c r="B268" t="inlineStr">
         <is>
-          <t>2026-07-11 08:11:17 PM PT</t>
+          <t>2026-07-11 08:13:18 PM PT</t>
         </is>
       </c>
       <c r="C268" t="n">
@@ -31410,7 +31410,7 @@
       </c>
       <c r="B269" t="inlineStr">
         <is>
-          <t>2026-07-11 08:11:17 PM PT</t>
+          <t>2026-07-11 08:13:18 PM PT</t>
         </is>
       </c>
       <c r="C269" t="n">
@@ -31524,7 +31524,7 @@
       </c>
       <c r="B270" t="inlineStr">
         <is>
-          <t>2026-07-11 08:11:17 PM PT</t>
+          <t>2026-07-11 08:13:18 PM PT</t>
         </is>
       </c>
       <c r="C270" t="n">
@@ -31638,7 +31638,7 @@
       </c>
       <c r="B271" t="inlineStr">
         <is>
-          <t>2026-07-11 08:11:17 PM PT</t>
+          <t>2026-07-11 08:13:18 PM PT</t>
         </is>
       </c>
       <c r="C271" t="n">
@@ -31752,7 +31752,7 @@
       </c>
       <c r="B272" t="inlineStr">
         <is>
-          <t>2026-07-11 08:11:17 PM PT</t>
+          <t>2026-07-11 08:13:18 PM PT</t>
         </is>
       </c>
       <c r="C272" t="n">
@@ -31866,7 +31866,7 @@
       </c>
       <c r="B273" t="inlineStr">
         <is>
-          <t>2026-07-11 08:11:17 PM PT</t>
+          <t>2026-07-11 08:13:18 PM PT</t>
         </is>
       </c>
       <c r="C273" t="n">
@@ -31980,7 +31980,7 @@
       </c>
       <c r="B274" t="inlineStr">
         <is>
-          <t>2026-07-11 08:11:17 PM PT</t>
+          <t>2026-07-11 08:13:18 PM PT</t>
         </is>
       </c>
       <c r="C274" t="n">
@@ -32094,7 +32094,7 @@
       </c>
       <c r="B275" t="inlineStr">
         <is>
-          <t>2026-07-11 08:11:16 PM PT</t>
+          <t>2026-07-11 08:13:17 PM PT</t>
         </is>
       </c>
       <c r="C275" t="n">
@@ -32208,7 +32208,7 @@
       </c>
       <c r="B276" t="inlineStr">
         <is>
-          <t>2026-07-11 08:11:16 PM PT</t>
+          <t>2026-07-11 08:13:17 PM PT</t>
         </is>
       </c>
       <c r="C276" t="n">
@@ -32322,7 +32322,7 @@
       </c>
       <c r="B277" t="inlineStr">
         <is>
-          <t>2026-07-11 08:11:16 PM PT</t>
+          <t>2026-07-11 08:13:17 PM PT</t>
         </is>
       </c>
       <c r="C277" t="n">
@@ -32436,7 +32436,7 @@
       </c>
       <c r="B278" t="inlineStr">
         <is>
-          <t>2026-07-11 08:11:18 PM PT</t>
+          <t>2026-07-11 08:13:19 PM PT</t>
         </is>
       </c>
       <c r="C278" t="n">
@@ -32464,10 +32464,10 @@
         <v>1</v>
       </c>
       <c r="I278" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J278" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="K278" t="inlineStr">
         <is>
@@ -32559,7 +32559,7 @@
       </c>
       <c r="B279" t="inlineStr">
         <is>
-          <t>2026-07-11 08:11:18 PM PT</t>
+          <t>2026-07-11 08:13:19 PM PT</t>
         </is>
       </c>
       <c r="C279" t="n">
@@ -32587,10 +32587,10 @@
         <v>1</v>
       </c>
       <c r="I279" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J279" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="K279" t="inlineStr">
         <is>
@@ -32682,7 +32682,7 @@
       </c>
       <c r="B280" t="inlineStr">
         <is>
-          <t>2026-07-11 08:11:18 PM PT</t>
+          <t>2026-07-11 08:13:19 PM PT</t>
         </is>
       </c>
       <c r="C280" t="n">
@@ -32710,10 +32710,10 @@
         <v>1</v>
       </c>
       <c r="I280" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J280" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="K280" t="inlineStr">
         <is>
@@ -32805,7 +32805,7 @@
       </c>
       <c r="B281" t="inlineStr">
         <is>
-          <t>2026-07-11 08:11:18 PM PT</t>
+          <t>2026-07-11 08:13:19 PM PT</t>
         </is>
       </c>
       <c r="C281" t="n">
@@ -32833,10 +32833,10 @@
         <v>1</v>
       </c>
       <c r="I281" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J281" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="K281" t="inlineStr">
         <is>
@@ -32928,7 +32928,7 @@
       </c>
       <c r="B282" t="inlineStr">
         <is>
-          <t>2026-07-11 08:11:17 PM PT</t>
+          <t>2026-07-11 08:13:18 PM PT</t>
         </is>
       </c>
       <c r="C282" t="n">
@@ -33042,7 +33042,7 @@
       </c>
       <c r="B283" t="inlineStr">
         <is>
-          <t>2026-07-11 08:11:16 PM PT</t>
+          <t>2026-07-11 08:13:16 PM PT</t>
         </is>
       </c>
       <c r="C283" t="n">
@@ -33156,7 +33156,7 @@
       </c>
       <c r="B284" t="inlineStr">
         <is>
-          <t>2026-07-11 08:11:16 PM PT</t>
+          <t>2026-07-11 08:13:16 PM PT</t>
         </is>
       </c>
       <c r="C284" t="n">
@@ -33270,7 +33270,7 @@
       </c>
       <c r="B285" t="inlineStr">
         <is>
-          <t>2026-07-11 08:11:16 PM PT</t>
+          <t>2026-07-11 08:13:16 PM PT</t>
         </is>
       </c>
       <c r="C285" t="n">
@@ -33384,7 +33384,7 @@
       </c>
       <c r="B286" t="inlineStr">
         <is>
-          <t>2026-07-11 08:11:16 PM PT</t>
+          <t>2026-07-11 08:13:16 PM PT</t>
         </is>
       </c>
       <c r="C286" t="n">
@@ -33498,7 +33498,7 @@
       </c>
       <c r="B287" t="inlineStr">
         <is>
-          <t>2026-07-11 08:11:16 PM PT</t>
+          <t>2026-07-11 08:13:16 PM PT</t>
         </is>
       </c>
       <c r="C287" t="n">
@@ -33612,7 +33612,7 @@
       </c>
       <c r="B288" t="inlineStr">
         <is>
-          <t>2026-07-11 08:11:16 PM PT</t>
+          <t>2026-07-11 08:13:16 PM PT</t>
         </is>
       </c>
       <c r="C288" t="n">
@@ -33726,7 +33726,7 @@
       </c>
       <c r="B289" t="inlineStr">
         <is>
-          <t>2026-07-11 08:11:16 PM PT</t>
+          <t>2026-07-11 08:13:17 PM PT</t>
         </is>
       </c>
       <c r="C289" t="n">
@@ -33840,7 +33840,7 @@
       </c>
       <c r="B290" t="inlineStr">
         <is>
-          <t>2026-07-11 08:11:17 PM PT</t>
+          <t>2026-07-11 08:13:17 PM PT</t>
         </is>
       </c>
       <c r="C290" t="n">
@@ -33954,7 +33954,7 @@
       </c>
       <c r="B291" t="inlineStr">
         <is>
-          <t>2026-07-11 08:11:17 PM PT</t>
+          <t>2026-07-11 08:13:17 PM PT</t>
         </is>
       </c>
       <c r="C291" t="n">
@@ -34068,7 +34068,7 @@
       </c>
       <c r="B292" t="inlineStr">
         <is>
-          <t>2026-07-11 08:11:17 PM PT</t>
+          <t>2026-07-11 08:13:17 PM PT</t>
         </is>
       </c>
       <c r="C292" t="n">
@@ -34182,7 +34182,7 @@
       </c>
       <c r="B293" t="inlineStr">
         <is>
-          <t>2026-07-11 08:11:17 PM PT</t>
+          <t>2026-07-11 08:13:17 PM PT</t>
         </is>
       </c>
       <c r="C293" t="n">
@@ -34296,7 +34296,7 @@
       </c>
       <c r="B294" t="inlineStr">
         <is>
-          <t>2026-07-11 08:11:17 PM PT</t>
+          <t>2026-07-11 08:13:17 PM PT</t>
         </is>
       </c>
       <c r="C294" t="n">
@@ -34410,7 +34410,7 @@
       </c>
       <c r="B295" t="inlineStr">
         <is>
-          <t>2026-07-11 08:11:17 PM PT</t>
+          <t>2026-07-11 08:13:17 PM PT</t>
         </is>
       </c>
       <c r="C295" t="n">
@@ -34524,7 +34524,7 @@
       </c>
       <c r="B296" t="inlineStr">
         <is>
-          <t>2026-07-11 08:11:17 PM PT</t>
+          <t>2026-07-11 08:13:18 PM PT</t>
         </is>
       </c>
       <c r="C296" t="n">
@@ -34638,7 +34638,7 @@
       </c>
       <c r="B297" t="inlineStr">
         <is>
-          <t>2026-07-11 08:11:17 PM PT</t>
+          <t>2026-07-11 08:13:18 PM PT</t>
         </is>
       </c>
       <c r="C297" t="n">
@@ -34752,7 +34752,7 @@
       </c>
       <c r="B298" t="inlineStr">
         <is>
-          <t>2026-07-11 08:11:16 PM PT</t>
+          <t>2026-07-11 08:13:16 PM PT</t>
         </is>
       </c>
       <c r="C298" t="n">
@@ -34866,7 +34866,7 @@
       </c>
       <c r="B299" t="inlineStr">
         <is>
-          <t>2026-07-11 08:11:16 PM PT</t>
+          <t>2026-07-11 08:13:16 PM PT</t>
         </is>
       </c>
       <c r="C299" t="n">
@@ -34980,7 +34980,7 @@
       </c>
       <c r="B300" t="inlineStr">
         <is>
-          <t>2026-07-11 08:11:16 PM PT</t>
+          <t>2026-07-11 08:13:16 PM PT</t>
         </is>
       </c>
       <c r="C300" t="n">
@@ -35094,7 +35094,7 @@
       </c>
       <c r="B301" t="inlineStr">
         <is>
-          <t>2026-07-11 08:11:16 PM PT</t>
+          <t>2026-07-11 08:13:16 PM PT</t>
         </is>
       </c>
       <c r="C301" t="n">
@@ -35208,7 +35208,7 @@
       </c>
       <c r="B302" t="inlineStr">
         <is>
-          <t>2026-07-11 08:11:16 PM PT</t>
+          <t>2026-07-11 08:13:16 PM PT</t>
         </is>
       </c>
       <c r="C302" t="n">
@@ -35322,7 +35322,7 @@
       </c>
       <c r="B303" t="inlineStr">
         <is>
-          <t>2026-07-11 08:11:16 PM PT</t>
+          <t>2026-07-11 08:13:16 PM PT</t>
         </is>
       </c>
       <c r="C303" t="n">
@@ -35436,7 +35436,7 @@
       </c>
       <c r="B304" t="inlineStr">
         <is>
-          <t>2026-07-11 08:11:16 PM PT</t>
+          <t>2026-07-11 08:13:16 PM PT</t>
         </is>
       </c>
       <c r="C304" t="n">
@@ -35550,7 +35550,7 @@
       </c>
       <c r="B305" t="inlineStr">
         <is>
-          <t>2026-07-11 08:11:16 PM PT</t>
+          <t>2026-07-11 08:13:16 PM PT</t>
         </is>
       </c>
       <c r="C305" t="n">
@@ -35664,7 +35664,7 @@
       </c>
       <c r="B306" t="inlineStr">
         <is>
-          <t>2026-07-11 08:11:18 PM PT</t>
+          <t>2026-07-11 08:13:19 PM PT</t>
         </is>
       </c>
       <c r="C306" t="n">
@@ -35677,7 +35677,7 @@
       </c>
       <c r="E306" t="inlineStr">
         <is>
-          <t>Top 7 | 3 out</t>
+          <t>Bottom 7 | 0 out</t>
         </is>
       </c>
       <c r="F306" t="n">
@@ -35685,17 +35685,17 @@
       </c>
       <c r="G306" t="inlineStr">
         <is>
-          <t>Top</t>
+          <t>Bottom</t>
         </is>
       </c>
       <c r="H306" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="I306" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="J306" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K306" t="inlineStr">
         <is>
@@ -35787,7 +35787,7 @@
       </c>
       <c r="B307" t="inlineStr">
         <is>
-          <t>2026-07-11 08:11:17 PM PT</t>
+          <t>2026-07-11 08:13:18 PM PT</t>
         </is>
       </c>
       <c r="C307" t="n">
@@ -35901,7 +35901,7 @@
       </c>
       <c r="B308" t="inlineStr">
         <is>
-          <t>2026-07-11 08:11:17 PM PT</t>
+          <t>2026-07-11 08:13:18 PM PT</t>
         </is>
       </c>
       <c r="C308" t="n">
@@ -36015,7 +36015,7 @@
       </c>
       <c r="B309" t="inlineStr">
         <is>
-          <t>2026-07-11 08:11:17 PM PT</t>
+          <t>2026-07-11 08:13:18 PM PT</t>
         </is>
       </c>
       <c r="C309" t="n">
@@ -36129,7 +36129,7 @@
       </c>
       <c r="B310" t="inlineStr">
         <is>
-          <t>2026-07-11 08:11:17 PM PT</t>
+          <t>2026-07-11 08:13:18 PM PT</t>
         </is>
       </c>
       <c r="C310" t="n">
@@ -36243,7 +36243,7 @@
       </c>
       <c r="B311" t="inlineStr">
         <is>
-          <t>2026-07-11 08:11:17 PM PT</t>
+          <t>2026-07-11 08:13:18 PM PT</t>
         </is>
       </c>
       <c r="C311" t="n">
@@ -36357,7 +36357,7 @@
       </c>
       <c r="B312" t="inlineStr">
         <is>
-          <t>2026-07-11 08:11:17 PM PT</t>
+          <t>2026-07-11 08:13:17 PM PT</t>
         </is>
       </c>
       <c r="C312" t="n">
@@ -36471,7 +36471,7 @@
       </c>
       <c r="B313" t="inlineStr">
         <is>
-          <t>2026-07-11 08:11:17 PM PT</t>
+          <t>2026-07-11 08:13:17 PM PT</t>
         </is>
       </c>
       <c r="C313" t="n">
@@ -36585,7 +36585,7 @@
       </c>
       <c r="B314" t="inlineStr">
         <is>
-          <t>2026-07-11 08:11:18 PM PT</t>
+          <t>2026-07-11 08:13:18 PM PT</t>
         </is>
       </c>
       <c r="C314" t="n">
@@ -36699,7 +36699,7 @@
       </c>
       <c r="B315" t="inlineStr">
         <is>
-          <t>2026-07-11 08:11:18 PM PT</t>
+          <t>2026-07-11 08:13:18 PM PT</t>
         </is>
       </c>
       <c r="C315" t="n">
@@ -36813,7 +36813,7 @@
       </c>
       <c r="B316" t="inlineStr">
         <is>
-          <t>2026-07-11 08:11:18 PM PT</t>
+          <t>2026-07-11 08:13:18 PM PT</t>
         </is>
       </c>
       <c r="C316" t="n">
@@ -36927,7 +36927,7 @@
       </c>
       <c r="B317" t="inlineStr">
         <is>
-          <t>2026-07-11 08:11:18 PM PT</t>
+          <t>2026-07-11 08:13:18 PM PT</t>
         </is>
       </c>
       <c r="C317" t="n">
@@ -37041,7 +37041,7 @@
       </c>
       <c r="B318" t="inlineStr">
         <is>
-          <t>2026-07-11 08:11:17 PM PT</t>
+          <t>2026-07-11 08:13:18 PM PT</t>
         </is>
       </c>
       <c r="C318" t="n">
@@ -37155,7 +37155,7 @@
       </c>
       <c r="B319" t="inlineStr">
         <is>
-          <t>2026-07-11 08:11:17 PM PT</t>
+          <t>2026-07-11 08:13:18 PM PT</t>
         </is>
       </c>
       <c r="C319" t="n">
@@ -37269,7 +37269,7 @@
       </c>
       <c r="B320" t="inlineStr">
         <is>
-          <t>2026-07-11 08:11:17 PM PT</t>
+          <t>2026-07-11 08:13:18 PM PT</t>
         </is>
       </c>
       <c r="C320" t="n">
@@ -37383,7 +37383,7 @@
       </c>
       <c r="B321" t="inlineStr">
         <is>
-          <t>2026-07-11 08:11:17 PM PT</t>
+          <t>2026-07-11 08:13:18 PM PT</t>
         </is>
       </c>
       <c r="C321" t="n">
@@ -37497,7 +37497,7 @@
       </c>
       <c r="B322" t="inlineStr">
         <is>
-          <t>2026-07-11 08:11:17 PM PT</t>
+          <t>2026-07-11 08:13:18 PM PT</t>
         </is>
       </c>
       <c r="C322" t="n">
@@ -37611,7 +37611,7 @@
       </c>
       <c r="B323" t="inlineStr">
         <is>
-          <t>2026-07-11 08:11:17 PM PT</t>
+          <t>2026-07-11 08:13:18 PM PT</t>
         </is>
       </c>
       <c r="C323" t="n">
@@ -37725,7 +37725,7 @@
       </c>
       <c r="B324" t="inlineStr">
         <is>
-          <t>2026-07-11 08:11:17 PM PT</t>
+          <t>2026-07-11 08:13:18 PM PT</t>
         </is>
       </c>
       <c r="C324" t="n">
@@ -37839,7 +37839,7 @@
       </c>
       <c r="B325" t="inlineStr">
         <is>
-          <t>2026-07-11 08:11:17 PM PT</t>
+          <t>2026-07-11 08:13:18 PM PT</t>
         </is>
       </c>
       <c r="C325" t="n">
@@ -37953,7 +37953,7 @@
       </c>
       <c r="B326" t="inlineStr">
         <is>
-          <t>2026-07-11 08:11:17 PM PT</t>
+          <t>2026-07-11 08:13:18 PM PT</t>
         </is>
       </c>
       <c r="C326" t="n">
@@ -38067,7 +38067,7 @@
       </c>
       <c r="B327" t="inlineStr">
         <is>
-          <t>2026-07-11 08:11:18 PM PT</t>
+          <t>2026-07-11 08:13:19 PM PT</t>
         </is>
       </c>
       <c r="C327" t="n">
@@ -38080,7 +38080,7 @@
       </c>
       <c r="E327" t="inlineStr">
         <is>
-          <t>Top 7 | 3 out</t>
+          <t>Bottom 7 | 0 out</t>
         </is>
       </c>
       <c r="F327" t="n">
@@ -38088,17 +38088,17 @@
       </c>
       <c r="G327" t="inlineStr">
         <is>
-          <t>Top</t>
+          <t>Bottom</t>
         </is>
       </c>
       <c r="H327" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="I327" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="J327" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K327" t="inlineStr">
         <is>
@@ -38190,7 +38190,7 @@
       </c>
       <c r="B328" t="inlineStr">
         <is>
-          <t>2026-07-11 08:11:17 PM PT</t>
+          <t>2026-07-11 08:13:17 PM PT</t>
         </is>
       </c>
       <c r="C328" t="n">
@@ -38304,7 +38304,7 @@
       </c>
       <c r="B329" t="inlineStr">
         <is>
-          <t>2026-07-11 08:11:17 PM PT</t>
+          <t>2026-07-11 08:13:17 PM PT</t>
         </is>
       </c>
       <c r="C329" t="n">

--- a/live_mlb_hitter_fantasy_scores_2026_07_11.xlsx
+++ b/live_mlb_hitter_fantasy_scores_2026_07_11.xlsx
@@ -693,7 +693,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-07-11 08:13:16 PM PT</t>
+          <t>2026-07-11 08:15:16 PM PT</t>
         </is>
       </c>
       <c r="C2" t="n">
@@ -807,7 +807,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>2026-07-11 08:13:18 PM PT</t>
+          <t>2026-07-11 08:15:18 PM PT</t>
         </is>
       </c>
       <c r="C3" t="n">
@@ -921,7 +921,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-07-11 08:13:19 PM PT</t>
+          <t>2026-07-11 08:15:19 PM PT</t>
         </is>
       </c>
       <c r="C4" t="n">
@@ -949,10 +949,10 @@
         <v>0</v>
       </c>
       <c r="I4" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="J4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K4" t="inlineStr">
         <is>
@@ -1044,7 +1044,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>2026-07-11 08:13:18 PM PT</t>
+          <t>2026-07-11 08:15:18 PM PT</t>
         </is>
       </c>
       <c r="C5" t="n">
@@ -1158,7 +1158,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>2026-07-11 08:13:18 PM PT</t>
+          <t>2026-07-11 08:15:18 PM PT</t>
         </is>
       </c>
       <c r="C6" t="n">
@@ -1272,7 +1272,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>2026-07-11 08:13:17 PM PT</t>
+          <t>2026-07-11 08:15:17 PM PT</t>
         </is>
       </c>
       <c r="C7" t="n">
@@ -1386,7 +1386,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>2026-07-11 08:13:18 PM PT</t>
+          <t>2026-07-11 08:15:18 PM PT</t>
         </is>
       </c>
       <c r="C8" t="n">
@@ -1500,7 +1500,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>2026-07-11 08:13:17 PM PT</t>
+          <t>2026-07-11 08:15:17 PM PT</t>
         </is>
       </c>
       <c r="C9" t="n">
@@ -1614,7 +1614,7 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>2026-07-11 08:13:19 PM PT</t>
+          <t>2026-07-11 08:15:19 PM PT</t>
         </is>
       </c>
       <c r="C10" t="n">
@@ -1642,10 +1642,10 @@
         <v>0</v>
       </c>
       <c r="I10" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="J10" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K10" t="inlineStr">
         <is>
@@ -1737,7 +1737,7 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>2026-07-11 08:13:18 PM PT</t>
+          <t>2026-07-11 08:15:18 PM PT</t>
         </is>
       </c>
       <c r="C11" t="n">
@@ -1851,7 +1851,7 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>2026-07-11 08:13:18 PM PT</t>
+          <t>2026-07-11 08:15:18 PM PT</t>
         </is>
       </c>
       <c r="C12" t="n">
@@ -1965,7 +1965,7 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>2026-07-11 08:13:19 PM PT</t>
+          <t>2026-07-11 08:15:19 PM PT</t>
         </is>
       </c>
       <c r="C13" t="n">
@@ -1993,10 +1993,10 @@
         <v>0</v>
       </c>
       <c r="I13" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="J13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K13" t="inlineStr">
         <is>
@@ -2088,7 +2088,7 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>2026-07-11 08:13:18 PM PT</t>
+          <t>2026-07-11 08:15:18 PM PT</t>
         </is>
       </c>
       <c r="C14" t="n">
@@ -2202,7 +2202,7 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>2026-07-11 08:13:17 PM PT</t>
+          <t>2026-07-11 08:15:17 PM PT</t>
         </is>
       </c>
       <c r="C15" t="n">
@@ -2316,7 +2316,7 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>2026-07-11 08:13:18 PM PT</t>
+          <t>2026-07-11 08:15:18 PM PT</t>
         </is>
       </c>
       <c r="C16" t="n">
@@ -2430,7 +2430,7 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>2026-07-11 08:13:19 PM PT</t>
+          <t>2026-07-11 08:15:19 PM PT</t>
         </is>
       </c>
       <c r="C17" t="n">
@@ -2458,10 +2458,10 @@
         <v>0</v>
       </c>
       <c r="I17" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="J17" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K17" t="inlineStr">
         <is>
@@ -2553,7 +2553,7 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>2026-07-11 08:13:17 PM PT</t>
+          <t>2026-07-11 08:15:17 PM PT</t>
         </is>
       </c>
       <c r="C18" t="n">
@@ -2667,7 +2667,7 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>2026-07-11 08:13:18 PM PT</t>
+          <t>2026-07-11 08:15:18 PM PT</t>
         </is>
       </c>
       <c r="C19" t="n">
@@ -2781,7 +2781,7 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>2026-07-11 08:13:17 PM PT</t>
+          <t>2026-07-11 08:15:17 PM PT</t>
         </is>
       </c>
       <c r="C20" t="n">
@@ -2895,7 +2895,7 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>2026-07-11 08:13:17 PM PT</t>
+          <t>2026-07-11 08:15:17 PM PT</t>
         </is>
       </c>
       <c r="C21" t="n">
@@ -3009,7 +3009,7 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>2026-07-11 08:13:19 PM PT</t>
+          <t>2026-07-11 08:15:19 PM PT</t>
         </is>
       </c>
       <c r="C22" t="n">
@@ -3037,10 +3037,10 @@
         <v>1</v>
       </c>
       <c r="I22" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J22" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K22" t="inlineStr">
         <is>
@@ -3132,7 +3132,7 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>2026-07-11 08:13:18 PM PT</t>
+          <t>2026-07-11 08:15:18 PM PT</t>
         </is>
       </c>
       <c r="C23" t="n">
@@ -3246,7 +3246,7 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>2026-07-11 08:13:17 PM PT</t>
+          <t>2026-07-11 08:15:17 PM PT</t>
         </is>
       </c>
       <c r="C24" t="n">
@@ -3360,7 +3360,7 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>2026-07-11 08:13:18 PM PT</t>
+          <t>2026-07-11 08:15:18 PM PT</t>
         </is>
       </c>
       <c r="C25" t="n">
@@ -3474,7 +3474,7 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>2026-07-11 08:13:16 PM PT</t>
+          <t>2026-07-11 08:15:16 PM PT</t>
         </is>
       </c>
       <c r="C26" t="n">
@@ -3588,7 +3588,7 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>2026-07-11 08:13:17 PM PT</t>
+          <t>2026-07-11 08:15:17 PM PT</t>
         </is>
       </c>
       <c r="C27" t="n">
@@ -3702,7 +3702,7 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>2026-07-11 08:13:18 PM PT</t>
+          <t>2026-07-11 08:15:18 PM PT</t>
         </is>
       </c>
       <c r="C28" t="n">
@@ -3816,7 +3816,7 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>2026-07-11 08:13:18 PM PT</t>
+          <t>2026-07-11 08:15:18 PM PT</t>
         </is>
       </c>
       <c r="C29" t="n">
@@ -3930,7 +3930,7 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>2026-07-11 08:13:18 PM PT</t>
+          <t>2026-07-11 08:15:18 PM PT</t>
         </is>
       </c>
       <c r="C30" t="n">
@@ -4044,7 +4044,7 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>2026-07-11 08:13:18 PM PT</t>
+          <t>2026-07-11 08:15:18 PM PT</t>
         </is>
       </c>
       <c r="C31" t="n">
@@ -4158,7 +4158,7 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>2026-07-11 08:13:18 PM PT</t>
+          <t>2026-07-11 08:15:18 PM PT</t>
         </is>
       </c>
       <c r="C32" t="n">
@@ -4272,7 +4272,7 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>2026-07-11 08:13:18 PM PT</t>
+          <t>2026-07-11 08:15:18 PM PT</t>
         </is>
       </c>
       <c r="C33" t="n">
@@ -4386,7 +4386,7 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>2026-07-11 08:13:16 PM PT</t>
+          <t>2026-07-11 08:15:16 PM PT</t>
         </is>
       </c>
       <c r="C34" t="n">
@@ -4500,7 +4500,7 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>2026-07-11 08:13:16 PM PT</t>
+          <t>2026-07-11 08:15:17 PM PT</t>
         </is>
       </c>
       <c r="C35" t="n">
@@ -4614,7 +4614,7 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>2026-07-11 08:13:19 PM PT</t>
+          <t>2026-07-11 08:15:19 PM PT</t>
         </is>
       </c>
       <c r="C36" t="n">
@@ -4642,10 +4642,10 @@
         <v>0</v>
       </c>
       <c r="I36" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="J36" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K36" t="inlineStr">
         <is>
@@ -4737,7 +4737,7 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>2026-07-11 08:13:18 PM PT</t>
+          <t>2026-07-11 08:15:18 PM PT</t>
         </is>
       </c>
       <c r="C37" t="n">
@@ -4851,7 +4851,7 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>2026-07-11 08:13:17 PM PT</t>
+          <t>2026-07-11 08:15:17 PM PT</t>
         </is>
       </c>
       <c r="C38" t="n">
@@ -4965,7 +4965,7 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>2026-07-11 08:13:18 PM PT</t>
+          <t>2026-07-11 08:15:18 PM PT</t>
         </is>
       </c>
       <c r="C39" t="n">
@@ -5079,7 +5079,7 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>2026-07-11 08:13:16 PM PT</t>
+          <t>2026-07-11 08:15:17 PM PT</t>
         </is>
       </c>
       <c r="C40" t="n">
@@ -5193,7 +5193,7 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>2026-07-11 08:13:19 PM PT</t>
+          <t>2026-07-11 08:15:19 PM PT</t>
         </is>
       </c>
       <c r="C41" t="n">
@@ -5221,10 +5221,10 @@
         <v>1</v>
       </c>
       <c r="I41" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J41" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K41" t="inlineStr">
         <is>
@@ -5316,7 +5316,7 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>2026-07-11 08:13:18 PM PT</t>
+          <t>2026-07-11 08:15:18 PM PT</t>
         </is>
       </c>
       <c r="C42" t="n">
@@ -5430,7 +5430,7 @@
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>2026-07-11 08:13:18 PM PT</t>
+          <t>2026-07-11 08:15:18 PM PT</t>
         </is>
       </c>
       <c r="C43" t="n">
@@ -5544,7 +5544,7 @@
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>2026-07-11 08:13:18 PM PT</t>
+          <t>2026-07-11 08:15:18 PM PT</t>
         </is>
       </c>
       <c r="C44" t="n">
@@ -5658,7 +5658,7 @@
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>2026-07-11 08:13:18 PM PT</t>
+          <t>2026-07-11 08:15:18 PM PT</t>
         </is>
       </c>
       <c r="C45" t="n">
@@ -5772,7 +5772,7 @@
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>2026-07-11 08:13:18 PM PT</t>
+          <t>2026-07-11 08:15:18 PM PT</t>
         </is>
       </c>
       <c r="C46" t="n">
@@ -5886,7 +5886,7 @@
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>2026-07-11 08:13:17 PM PT</t>
+          <t>2026-07-11 08:15:17 PM PT</t>
         </is>
       </c>
       <c r="C47" t="n">
@@ -6000,7 +6000,7 @@
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>2026-07-11 08:13:18 PM PT</t>
+          <t>2026-07-11 08:15:18 PM PT</t>
         </is>
       </c>
       <c r="C48" t="n">
@@ -6114,7 +6114,7 @@
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>2026-07-11 08:13:17 PM PT</t>
+          <t>2026-07-11 08:15:17 PM PT</t>
         </is>
       </c>
       <c r="C49" t="n">
@@ -6228,7 +6228,7 @@
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>2026-07-11 08:13:16 PM PT</t>
+          <t>2026-07-11 08:15:17 PM PT</t>
         </is>
       </c>
       <c r="C50" t="n">
@@ -6342,7 +6342,7 @@
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>2026-07-11 08:13:18 PM PT</t>
+          <t>2026-07-11 08:15:18 PM PT</t>
         </is>
       </c>
       <c r="C51" t="n">
@@ -6456,7 +6456,7 @@
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>2026-07-11 08:13:18 PM PT</t>
+          <t>2026-07-11 08:15:18 PM PT</t>
         </is>
       </c>
       <c r="C52" t="n">
@@ -6570,7 +6570,7 @@
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>2026-07-11 08:13:18 PM PT</t>
+          <t>2026-07-11 08:15:18 PM PT</t>
         </is>
       </c>
       <c r="C53" t="n">
@@ -6684,7 +6684,7 @@
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>2026-07-11 08:13:17 PM PT</t>
+          <t>2026-07-11 08:15:17 PM PT</t>
         </is>
       </c>
       <c r="C54" t="n">
@@ -6798,7 +6798,7 @@
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>2026-07-11 08:13:17 PM PT</t>
+          <t>2026-07-11 08:15:17 PM PT</t>
         </is>
       </c>
       <c r="C55" t="n">
@@ -6912,7 +6912,7 @@
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>2026-07-11 08:13:17 PM PT</t>
+          <t>2026-07-11 08:15:17 PM PT</t>
         </is>
       </c>
       <c r="C56" t="n">
@@ -7026,7 +7026,7 @@
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>2026-07-11 08:13:18 PM PT</t>
+          <t>2026-07-11 08:15:18 PM PT</t>
         </is>
       </c>
       <c r="C57" t="n">
@@ -7140,7 +7140,7 @@
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>2026-07-11 08:13:17 PM PT</t>
+          <t>2026-07-11 08:15:17 PM PT</t>
         </is>
       </c>
       <c r="C58" t="n">
@@ -7254,7 +7254,7 @@
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>2026-07-11 08:13:17 PM PT</t>
+          <t>2026-07-11 08:15:17 PM PT</t>
         </is>
       </c>
       <c r="C59" t="n">
@@ -7368,7 +7368,7 @@
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>2026-07-11 08:13:16 PM PT</t>
+          <t>2026-07-11 08:15:16 PM PT</t>
         </is>
       </c>
       <c r="C60" t="n">
@@ -7482,7 +7482,7 @@
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>2026-07-11 08:13:16 PM PT</t>
+          <t>2026-07-11 08:15:16 PM PT</t>
         </is>
       </c>
       <c r="C61" t="n">
@@ -7596,7 +7596,7 @@
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>2026-07-11 08:13:19 PM PT</t>
+          <t>2026-07-11 08:15:19 PM PT</t>
         </is>
       </c>
       <c r="C62" t="n">
@@ -7624,10 +7624,10 @@
         <v>0</v>
       </c>
       <c r="I62" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="J62" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K62" t="inlineStr">
         <is>
@@ -7719,7 +7719,7 @@
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>2026-07-11 08:13:17 PM PT</t>
+          <t>2026-07-11 08:15:17 PM PT</t>
         </is>
       </c>
       <c r="C63" t="n">
@@ -7833,7 +7833,7 @@
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>2026-07-11 08:13:18 PM PT</t>
+          <t>2026-07-11 08:15:18 PM PT</t>
         </is>
       </c>
       <c r="C64" t="n">
@@ -7947,7 +7947,7 @@
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>2026-07-11 08:13:19 PM PT</t>
+          <t>2026-07-11 08:15:19 PM PT</t>
         </is>
       </c>
       <c r="C65" t="n">
@@ -7975,10 +7975,10 @@
         <v>0</v>
       </c>
       <c r="I65" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="J65" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K65" t="inlineStr">
         <is>
@@ -8070,7 +8070,7 @@
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>2026-07-11 08:13:18 PM PT</t>
+          <t>2026-07-11 08:15:18 PM PT</t>
         </is>
       </c>
       <c r="C66" t="n">
@@ -8184,7 +8184,7 @@
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>2026-07-11 08:13:17 PM PT</t>
+          <t>2026-07-11 08:15:17 PM PT</t>
         </is>
       </c>
       <c r="C67" t="n">
@@ -8298,7 +8298,7 @@
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>2026-07-11 08:13:17 PM PT</t>
+          <t>2026-07-11 08:15:17 PM PT</t>
         </is>
       </c>
       <c r="C68" t="n">
@@ -8412,7 +8412,7 @@
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>2026-07-11 08:13:19 PM PT</t>
+          <t>2026-07-11 08:15:19 PM PT</t>
         </is>
       </c>
       <c r="C69" t="n">
@@ -8440,10 +8440,10 @@
         <v>1</v>
       </c>
       <c r="I69" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J69" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K69" t="inlineStr">
         <is>
@@ -8535,7 +8535,7 @@
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>2026-07-11 08:13:16 PM PT</t>
+          <t>2026-07-11 08:15:17 PM PT</t>
         </is>
       </c>
       <c r="C70" t="n">
@@ -8649,7 +8649,7 @@
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>2026-07-11 08:13:17 PM PT</t>
+          <t>2026-07-11 08:15:17 PM PT</t>
         </is>
       </c>
       <c r="C71" t="n">
@@ -8763,7 +8763,7 @@
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>2026-07-11 08:13:16 PM PT</t>
+          <t>2026-07-11 08:15:17 PM PT</t>
         </is>
       </c>
       <c r="C72" t="n">
@@ -8877,7 +8877,7 @@
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>2026-07-11 08:13:19 PM PT</t>
+          <t>2026-07-11 08:15:19 PM PT</t>
         </is>
       </c>
       <c r="C73" t="n">
@@ -8905,10 +8905,10 @@
         <v>0</v>
       </c>
       <c r="I73" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="J73" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K73" t="inlineStr">
         <is>
@@ -9000,7 +9000,7 @@
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>2026-07-11 08:13:19 PM PT</t>
+          <t>2026-07-11 08:15:19 PM PT</t>
         </is>
       </c>
       <c r="C74" t="n">
@@ -9028,10 +9028,10 @@
         <v>1</v>
       </c>
       <c r="I74" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J74" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K74" t="inlineStr">
         <is>
@@ -9123,7 +9123,7 @@
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>2026-07-11 08:13:18 PM PT</t>
+          <t>2026-07-11 08:15:18 PM PT</t>
         </is>
       </c>
       <c r="C75" t="n">
@@ -9237,7 +9237,7 @@
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>2026-07-11 08:13:18 PM PT</t>
+          <t>2026-07-11 08:15:18 PM PT</t>
         </is>
       </c>
       <c r="C76" t="n">
@@ -9351,7 +9351,7 @@
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>2026-07-11 08:13:18 PM PT</t>
+          <t>2026-07-11 08:15:18 PM PT</t>
         </is>
       </c>
       <c r="C77" t="n">
@@ -9465,7 +9465,7 @@
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>2026-07-11 08:13:16 PM PT</t>
+          <t>2026-07-11 08:15:16 PM PT</t>
         </is>
       </c>
       <c r="C78" t="n">
@@ -9579,7 +9579,7 @@
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>2026-07-11 08:13:16 PM PT</t>
+          <t>2026-07-11 08:15:17 PM PT</t>
         </is>
       </c>
       <c r="C79" t="n">
@@ -9693,7 +9693,7 @@
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>2026-07-11 08:13:16 PM PT</t>
+          <t>2026-07-11 08:15:17 PM PT</t>
         </is>
       </c>
       <c r="C80" t="n">
@@ -9807,7 +9807,7 @@
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>2026-07-11 08:13:16 PM PT</t>
+          <t>2026-07-11 08:15:16 PM PT</t>
         </is>
       </c>
       <c r="C81" t="n">
@@ -9921,7 +9921,7 @@
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>2026-07-11 08:13:16 PM PT</t>
+          <t>2026-07-11 08:15:16 PM PT</t>
         </is>
       </c>
       <c r="C82" t="n">
@@ -10035,7 +10035,7 @@
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>2026-07-11 08:13:16 PM PT</t>
+          <t>2026-07-11 08:15:16 PM PT</t>
         </is>
       </c>
       <c r="C83" t="n">
@@ -10149,7 +10149,7 @@
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>2026-07-11 08:13:17 PM PT</t>
+          <t>2026-07-11 08:15:17 PM PT</t>
         </is>
       </c>
       <c r="C84" t="n">
@@ -10263,7 +10263,7 @@
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>2026-07-11 08:13:17 PM PT</t>
+          <t>2026-07-11 08:15:17 PM PT</t>
         </is>
       </c>
       <c r="C85" t="n">
@@ -10377,7 +10377,7 @@
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>2026-07-11 08:13:17 PM PT</t>
+          <t>2026-07-11 08:15:17 PM PT</t>
         </is>
       </c>
       <c r="C86" t="n">
@@ -10491,7 +10491,7 @@
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>2026-07-11 08:13:18 PM PT</t>
+          <t>2026-07-11 08:15:18 PM PT</t>
         </is>
       </c>
       <c r="C87" t="n">
@@ -10605,7 +10605,7 @@
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>2026-07-11 08:13:19 PM PT</t>
+          <t>2026-07-11 08:15:19 PM PT</t>
         </is>
       </c>
       <c r="C88" t="n">
@@ -10633,10 +10633,10 @@
         <v>0</v>
       </c>
       <c r="I88" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="J88" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K88" t="inlineStr">
         <is>
@@ -10728,7 +10728,7 @@
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>2026-07-11 08:13:17 PM PT</t>
+          <t>2026-07-11 08:15:17 PM PT</t>
         </is>
       </c>
       <c r="C89" t="n">
@@ -10842,7 +10842,7 @@
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>2026-07-11 08:13:18 PM PT</t>
+          <t>2026-07-11 08:15:18 PM PT</t>
         </is>
       </c>
       <c r="C90" t="n">
@@ -10956,7 +10956,7 @@
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>2026-07-11 08:13:18 PM PT</t>
+          <t>2026-07-11 08:15:18 PM PT</t>
         </is>
       </c>
       <c r="C91" t="n">
@@ -11070,7 +11070,7 @@
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>2026-07-11 08:13:18 PM PT</t>
+          <t>2026-07-11 08:15:18 PM PT</t>
         </is>
       </c>
       <c r="C92" t="n">
@@ -11184,7 +11184,7 @@
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>2026-07-11 08:13:17 PM PT</t>
+          <t>2026-07-11 08:15:17 PM PT</t>
         </is>
       </c>
       <c r="C93" t="n">
@@ -11298,7 +11298,7 @@
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>2026-07-11 08:13:18 PM PT</t>
+          <t>2026-07-11 08:15:18 PM PT</t>
         </is>
       </c>
       <c r="C94" t="n">
@@ -11412,7 +11412,7 @@
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>2026-07-11 08:13:18 PM PT</t>
+          <t>2026-07-11 08:15:18 PM PT</t>
         </is>
       </c>
       <c r="C95" t="n">
@@ -11526,7 +11526,7 @@
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>2026-07-11 08:13:19 PM PT</t>
+          <t>2026-07-11 08:15:19 PM PT</t>
         </is>
       </c>
       <c r="C96" t="n">
@@ -11554,10 +11554,10 @@
         <v>1</v>
       </c>
       <c r="I96" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J96" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K96" t="inlineStr">
         <is>
@@ -11649,7 +11649,7 @@
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>2026-07-11 08:13:18 PM PT</t>
+          <t>2026-07-11 08:15:18 PM PT</t>
         </is>
       </c>
       <c r="C97" t="n">
@@ -11763,7 +11763,7 @@
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>2026-07-11 08:13:16 PM PT</t>
+          <t>2026-07-11 08:15:17 PM PT</t>
         </is>
       </c>
       <c r="C98" t="n">
@@ -11877,7 +11877,7 @@
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>2026-07-11 08:13:17 PM PT</t>
+          <t>2026-07-11 08:15:17 PM PT</t>
         </is>
       </c>
       <c r="C99" t="n">
@@ -11991,7 +11991,7 @@
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>2026-07-11 08:13:17 PM PT</t>
+          <t>2026-07-11 08:15:17 PM PT</t>
         </is>
       </c>
       <c r="C100" t="n">
@@ -12105,7 +12105,7 @@
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>2026-07-11 08:13:19 PM PT</t>
+          <t>2026-07-11 08:15:19 PM PT</t>
         </is>
       </c>
       <c r="C101" t="n">
@@ -12133,10 +12133,10 @@
         <v>0</v>
       </c>
       <c r="I101" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="J101" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K101" t="inlineStr">
         <is>
@@ -12228,7 +12228,7 @@
       </c>
       <c r="B102" t="inlineStr">
         <is>
-          <t>2026-07-11 08:13:18 PM PT</t>
+          <t>2026-07-11 08:15:18 PM PT</t>
         </is>
       </c>
       <c r="C102" t="n">
@@ -12342,7 +12342,7 @@
       </c>
       <c r="B103" t="inlineStr">
         <is>
-          <t>2026-07-11 08:13:18 PM PT</t>
+          <t>2026-07-11 08:15:18 PM PT</t>
         </is>
       </c>
       <c r="C103" t="n">
@@ -12456,7 +12456,7 @@
       </c>
       <c r="B104" t="inlineStr">
         <is>
-          <t>2026-07-11 08:13:18 PM PT</t>
+          <t>2026-07-11 08:15:18 PM PT</t>
         </is>
       </c>
       <c r="C104" t="n">
@@ -12570,7 +12570,7 @@
       </c>
       <c r="B105" t="inlineStr">
         <is>
-          <t>2026-07-11 08:13:17 PM PT</t>
+          <t>2026-07-11 08:15:17 PM PT</t>
         </is>
       </c>
       <c r="C105" t="n">
@@ -12684,7 +12684,7 @@
       </c>
       <c r="B106" t="inlineStr">
         <is>
-          <t>2026-07-11 08:13:17 PM PT</t>
+          <t>2026-07-11 08:15:17 PM PT</t>
         </is>
       </c>
       <c r="C106" t="n">
@@ -12798,7 +12798,7 @@
       </c>
       <c r="B107" t="inlineStr">
         <is>
-          <t>2026-07-11 08:13:18 PM PT</t>
+          <t>2026-07-11 08:15:18 PM PT</t>
         </is>
       </c>
       <c r="C107" t="n">
@@ -12912,7 +12912,7 @@
       </c>
       <c r="B108" t="inlineStr">
         <is>
-          <t>2026-07-11 08:13:19 PM PT</t>
+          <t>2026-07-11 08:15:19 PM PT</t>
         </is>
       </c>
       <c r="C108" t="n">
@@ -12940,10 +12940,10 @@
         <v>1</v>
       </c>
       <c r="I108" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J108" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K108" t="inlineStr">
         <is>
@@ -13035,7 +13035,7 @@
       </c>
       <c r="B109" t="inlineStr">
         <is>
-          <t>2026-07-11 08:13:17 PM PT</t>
+          <t>2026-07-11 08:15:17 PM PT</t>
         </is>
       </c>
       <c r="C109" t="n">
@@ -13149,7 +13149,7 @@
       </c>
       <c r="B110" t="inlineStr">
         <is>
-          <t>2026-07-11 08:13:18 PM PT</t>
+          <t>2026-07-11 08:15:18 PM PT</t>
         </is>
       </c>
       <c r="C110" t="n">
@@ -13263,7 +13263,7 @@
       </c>
       <c r="B111" t="inlineStr">
         <is>
-          <t>2026-07-11 08:13:18 PM PT</t>
+          <t>2026-07-11 08:15:18 PM PT</t>
         </is>
       </c>
       <c r="C111" t="n">
@@ -13377,7 +13377,7 @@
       </c>
       <c r="B112" t="inlineStr">
         <is>
-          <t>2026-07-11 08:13:17 PM PT</t>
+          <t>2026-07-11 08:15:17 PM PT</t>
         </is>
       </c>
       <c r="C112" t="n">
@@ -13491,7 +13491,7 @@
       </c>
       <c r="B113" t="inlineStr">
         <is>
-          <t>2026-07-11 08:13:18 PM PT</t>
+          <t>2026-07-11 08:15:18 PM PT</t>
         </is>
       </c>
       <c r="C113" t="n">
@@ -13605,7 +13605,7 @@
       </c>
       <c r="B114" t="inlineStr">
         <is>
-          <t>2026-07-11 08:13:19 PM PT</t>
+          <t>2026-07-11 08:15:19 PM PT</t>
         </is>
       </c>
       <c r="C114" t="n">
@@ -13633,10 +13633,10 @@
         <v>0</v>
       </c>
       <c r="I114" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="J114" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K114" t="inlineStr">
         <is>
@@ -13728,7 +13728,7 @@
       </c>
       <c r="B115" t="inlineStr">
         <is>
-          <t>2026-07-11 08:13:18 PM PT</t>
+          <t>2026-07-11 08:15:18 PM PT</t>
         </is>
       </c>
       <c r="C115" t="n">
@@ -13842,7 +13842,7 @@
       </c>
       <c r="B116" t="inlineStr">
         <is>
-          <t>2026-07-11 08:13:19 PM PT</t>
+          <t>2026-07-11 08:15:19 PM PT</t>
         </is>
       </c>
       <c r="C116" t="n">
@@ -13870,10 +13870,10 @@
         <v>1</v>
       </c>
       <c r="I116" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J116" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K116" t="inlineStr">
         <is>
@@ -13965,7 +13965,7 @@
       </c>
       <c r="B117" t="inlineStr">
         <is>
-          <t>2026-07-11 08:13:18 PM PT</t>
+          <t>2026-07-11 08:15:18 PM PT</t>
         </is>
       </c>
       <c r="C117" t="n">
@@ -14079,7 +14079,7 @@
       </c>
       <c r="B118" t="inlineStr">
         <is>
-          <t>2026-07-11 08:13:18 PM PT</t>
+          <t>2026-07-11 08:15:18 PM PT</t>
         </is>
       </c>
       <c r="C118" t="n">
@@ -14193,7 +14193,7 @@
       </c>
       <c r="B119" t="inlineStr">
         <is>
-          <t>2026-07-11 08:13:18 PM PT</t>
+          <t>2026-07-11 08:15:18 PM PT</t>
         </is>
       </c>
       <c r="C119" t="n">
@@ -14307,7 +14307,7 @@
       </c>
       <c r="B120" t="inlineStr">
         <is>
-          <t>2026-07-11 08:13:17 PM PT</t>
+          <t>2026-07-11 08:15:17 PM PT</t>
         </is>
       </c>
       <c r="C120" t="n">
@@ -14421,7 +14421,7 @@
       </c>
       <c r="B121" t="inlineStr">
         <is>
-          <t>2026-07-11 08:13:18 PM PT</t>
+          <t>2026-07-11 08:15:18 PM PT</t>
         </is>
       </c>
       <c r="C121" t="n">
@@ -14535,7 +14535,7 @@
       </c>
       <c r="B122" t="inlineStr">
         <is>
-          <t>2026-07-11 08:13:17 PM PT</t>
+          <t>2026-07-11 08:15:17 PM PT</t>
         </is>
       </c>
       <c r="C122" t="n">
@@ -14649,7 +14649,7 @@
       </c>
       <c r="B123" t="inlineStr">
         <is>
-          <t>2026-07-11 08:13:17 PM PT</t>
+          <t>2026-07-11 08:15:17 PM PT</t>
         </is>
       </c>
       <c r="C123" t="n">
@@ -14763,7 +14763,7 @@
       </c>
       <c r="B124" t="inlineStr">
         <is>
-          <t>2026-07-11 08:13:18 PM PT</t>
+          <t>2026-07-11 08:15:18 PM PT</t>
         </is>
       </c>
       <c r="C124" t="n">
@@ -14877,7 +14877,7 @@
       </c>
       <c r="B125" t="inlineStr">
         <is>
-          <t>2026-07-11 08:13:18 PM PT</t>
+          <t>2026-07-11 08:15:18 PM PT</t>
         </is>
       </c>
       <c r="C125" t="n">
@@ -14991,7 +14991,7 @@
       </c>
       <c r="B126" t="inlineStr">
         <is>
-          <t>2026-07-11 08:13:18 PM PT</t>
+          <t>2026-07-11 08:15:18 PM PT</t>
         </is>
       </c>
       <c r="C126" t="n">
@@ -15105,7 +15105,7 @@
       </c>
       <c r="B127" t="inlineStr">
         <is>
-          <t>2026-07-11 08:13:18 PM PT</t>
+          <t>2026-07-11 08:15:18 PM PT</t>
         </is>
       </c>
       <c r="C127" t="n">
@@ -15219,7 +15219,7 @@
       </c>
       <c r="B128" t="inlineStr">
         <is>
-          <t>2026-07-11 08:13:19 PM PT</t>
+          <t>2026-07-11 08:15:19 PM PT</t>
         </is>
       </c>
       <c r="C128" t="n">
@@ -15247,10 +15247,10 @@
         <v>1</v>
       </c>
       <c r="I128" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J128" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K128" t="inlineStr">
         <is>
@@ -15342,7 +15342,7 @@
       </c>
       <c r="B129" t="inlineStr">
         <is>
-          <t>2026-07-11 08:13:18 PM PT</t>
+          <t>2026-07-11 08:15:18 PM PT</t>
         </is>
       </c>
       <c r="C129" t="n">
@@ -15456,7 +15456,7 @@
       </c>
       <c r="B130" t="inlineStr">
         <is>
-          <t>2026-07-11 08:13:18 PM PT</t>
+          <t>2026-07-11 08:15:18 PM PT</t>
         </is>
       </c>
       <c r="C130" t="n">
@@ -15570,7 +15570,7 @@
       </c>
       <c r="B131" t="inlineStr">
         <is>
-          <t>2026-07-11 08:13:16 PM PT</t>
+          <t>2026-07-11 08:15:17 PM PT</t>
         </is>
       </c>
       <c r="C131" t="n">
@@ -15684,7 +15684,7 @@
       </c>
       <c r="B132" t="inlineStr">
         <is>
-          <t>2026-07-11 08:13:17 PM PT</t>
+          <t>2026-07-11 08:15:17 PM PT</t>
         </is>
       </c>
       <c r="C132" t="n">
@@ -15798,7 +15798,7 @@
       </c>
       <c r="B133" t="inlineStr">
         <is>
-          <t>2026-07-11 08:13:17 PM PT</t>
+          <t>2026-07-11 08:15:17 PM PT</t>
         </is>
       </c>
       <c r="C133" t="n">
@@ -15912,7 +15912,7 @@
       </c>
       <c r="B134" t="inlineStr">
         <is>
-          <t>2026-07-11 08:13:17 PM PT</t>
+          <t>2026-07-11 08:15:17 PM PT</t>
         </is>
       </c>
       <c r="C134" t="n">
@@ -16026,7 +16026,7 @@
       </c>
       <c r="B135" t="inlineStr">
         <is>
-          <t>2026-07-11 08:13:16 PM PT</t>
+          <t>2026-07-11 08:15:16 PM PT</t>
         </is>
       </c>
       <c r="C135" t="n">
@@ -16140,7 +16140,7 @@
       </c>
       <c r="B136" t="inlineStr">
         <is>
-          <t>2026-07-11 08:13:16 PM PT</t>
+          <t>2026-07-11 08:15:16 PM PT</t>
         </is>
       </c>
       <c r="C136" t="n">
@@ -16254,7 +16254,7 @@
       </c>
       <c r="B137" t="inlineStr">
         <is>
-          <t>2026-07-11 08:13:18 PM PT</t>
+          <t>2026-07-11 08:15:18 PM PT</t>
         </is>
       </c>
       <c r="C137" t="n">
@@ -16368,7 +16368,7 @@
       </c>
       <c r="B138" t="inlineStr">
         <is>
-          <t>2026-07-11 08:13:18 PM PT</t>
+          <t>2026-07-11 08:15:18 PM PT</t>
         </is>
       </c>
       <c r="C138" t="n">
@@ -16482,7 +16482,7 @@
       </c>
       <c r="B139" t="inlineStr">
         <is>
-          <t>2026-07-11 08:13:17 PM PT</t>
+          <t>2026-07-11 08:15:17 PM PT</t>
         </is>
       </c>
       <c r="C139" t="n">
@@ -16596,7 +16596,7 @@
       </c>
       <c r="B140" t="inlineStr">
         <is>
-          <t>2026-07-11 08:13:18 PM PT</t>
+          <t>2026-07-11 08:15:18 PM PT</t>
         </is>
       </c>
       <c r="C140" t="n">
@@ -16710,7 +16710,7 @@
       </c>
       <c r="B141" t="inlineStr">
         <is>
-          <t>2026-07-11 08:13:18 PM PT</t>
+          <t>2026-07-11 08:15:18 PM PT</t>
         </is>
       </c>
       <c r="C141" t="n">
@@ -16824,7 +16824,7 @@
       </c>
       <c r="B142" t="inlineStr">
         <is>
-          <t>2026-07-11 08:13:18 PM PT</t>
+          <t>2026-07-11 08:15:18 PM PT</t>
         </is>
       </c>
       <c r="C142" t="n">
@@ -16938,7 +16938,7 @@
       </c>
       <c r="B143" t="inlineStr">
         <is>
-          <t>2026-07-11 08:13:18 PM PT</t>
+          <t>2026-07-11 08:15:18 PM PT</t>
         </is>
       </c>
       <c r="C143" t="n">
@@ -17052,7 +17052,7 @@
       </c>
       <c r="B144" t="inlineStr">
         <is>
-          <t>2026-07-11 08:13:18 PM PT</t>
+          <t>2026-07-11 08:15:18 PM PT</t>
         </is>
       </c>
       <c r="C144" t="n">
@@ -17166,7 +17166,7 @@
       </c>
       <c r="B145" t="inlineStr">
         <is>
-          <t>2026-07-11 08:13:18 PM PT</t>
+          <t>2026-07-11 08:15:18 PM PT</t>
         </is>
       </c>
       <c r="C145" t="n">
@@ -17280,7 +17280,7 @@
       </c>
       <c r="B146" t="inlineStr">
         <is>
-          <t>2026-07-11 08:13:19 PM PT</t>
+          <t>2026-07-11 08:15:19 PM PT</t>
         </is>
       </c>
       <c r="C146" t="n">
@@ -17308,10 +17308,10 @@
         <v>1</v>
       </c>
       <c r="I146" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J146" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K146" t="inlineStr">
         <is>
@@ -17403,7 +17403,7 @@
       </c>
       <c r="B147" t="inlineStr">
         <is>
-          <t>2026-07-11 08:13:18 PM PT</t>
+          <t>2026-07-11 08:15:18 PM PT</t>
         </is>
       </c>
       <c r="C147" t="n">
@@ -17517,7 +17517,7 @@
       </c>
       <c r="B148" t="inlineStr">
         <is>
-          <t>2026-07-11 08:13:18 PM PT</t>
+          <t>2026-07-11 08:15:18 PM PT</t>
         </is>
       </c>
       <c r="C148" t="n">
@@ -17631,7 +17631,7 @@
       </c>
       <c r="B149" t="inlineStr">
         <is>
-          <t>2026-07-11 08:13:17 PM PT</t>
+          <t>2026-07-11 08:15:17 PM PT</t>
         </is>
       </c>
       <c r="C149" t="n">
@@ -17745,7 +17745,7 @@
       </c>
       <c r="B150" t="inlineStr">
         <is>
-          <t>2026-07-11 08:13:16 PM PT</t>
+          <t>2026-07-11 08:15:16 PM PT</t>
         </is>
       </c>
       <c r="C150" t="n">
@@ -17859,7 +17859,7 @@
       </c>
       <c r="B151" t="inlineStr">
         <is>
-          <t>2026-07-11 08:13:16 PM PT</t>
+          <t>2026-07-11 08:15:17 PM PT</t>
         </is>
       </c>
       <c r="C151" t="n">
@@ -17973,7 +17973,7 @@
       </c>
       <c r="B152" t="inlineStr">
         <is>
-          <t>2026-07-11 08:13:17 PM PT</t>
+          <t>2026-07-11 08:15:17 PM PT</t>
         </is>
       </c>
       <c r="C152" t="n">
@@ -18087,7 +18087,7 @@
       </c>
       <c r="B153" t="inlineStr">
         <is>
-          <t>2026-07-11 08:13:18 PM PT</t>
+          <t>2026-07-11 08:15:18 PM PT</t>
         </is>
       </c>
       <c r="C153" t="n">
@@ -18201,7 +18201,7 @@
       </c>
       <c r="B154" t="inlineStr">
         <is>
-          <t>2026-07-11 08:13:18 PM PT</t>
+          <t>2026-07-11 08:15:18 PM PT</t>
         </is>
       </c>
       <c r="C154" t="n">
@@ -18315,7 +18315,7 @@
       </c>
       <c r="B155" t="inlineStr">
         <is>
-          <t>2026-07-11 08:13:16 PM PT</t>
+          <t>2026-07-11 08:15:16 PM PT</t>
         </is>
       </c>
       <c r="C155" t="n">
@@ -18429,7 +18429,7 @@
       </c>
       <c r="B156" t="inlineStr">
         <is>
-          <t>2026-07-11 08:13:19 PM PT</t>
+          <t>2026-07-11 08:15:19 PM PT</t>
         </is>
       </c>
       <c r="C156" t="n">
@@ -18457,10 +18457,10 @@
         <v>0</v>
       </c>
       <c r="I156" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="J156" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K156" t="inlineStr">
         <is>
@@ -18552,7 +18552,7 @@
       </c>
       <c r="B157" t="inlineStr">
         <is>
-          <t>2026-07-11 08:13:19 PM PT</t>
+          <t>2026-07-11 08:15:19 PM PT</t>
         </is>
       </c>
       <c r="C157" t="n">
@@ -18580,10 +18580,10 @@
         <v>0</v>
       </c>
       <c r="I157" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="J157" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K157" t="inlineStr">
         <is>
@@ -18675,7 +18675,7 @@
       </c>
       <c r="B158" t="inlineStr">
         <is>
-          <t>2026-07-11 08:13:19 PM PT</t>
+          <t>2026-07-11 08:15:19 PM PT</t>
         </is>
       </c>
       <c r="C158" t="n">
@@ -18703,10 +18703,10 @@
         <v>0</v>
       </c>
       <c r="I158" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="J158" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K158" t="inlineStr">
         <is>
@@ -18798,7 +18798,7 @@
       </c>
       <c r="B159" t="inlineStr">
         <is>
-          <t>2026-07-11 08:13:19 PM PT</t>
+          <t>2026-07-11 08:15:19 PM PT</t>
         </is>
       </c>
       <c r="C159" t="n">
@@ -18826,10 +18826,10 @@
         <v>0</v>
       </c>
       <c r="I159" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="J159" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K159" t="inlineStr">
         <is>
@@ -18921,7 +18921,7 @@
       </c>
       <c r="B160" t="inlineStr">
         <is>
-          <t>2026-07-11 08:13:18 PM PT</t>
+          <t>2026-07-11 08:15:18 PM PT</t>
         </is>
       </c>
       <c r="C160" t="n">
@@ -19035,7 +19035,7 @@
       </c>
       <c r="B161" t="inlineStr">
         <is>
-          <t>2026-07-11 08:13:18 PM PT</t>
+          <t>2026-07-11 08:15:18 PM PT</t>
         </is>
       </c>
       <c r="C161" t="n">
@@ -19149,7 +19149,7 @@
       </c>
       <c r="B162" t="inlineStr">
         <is>
-          <t>2026-07-11 08:13:18 PM PT</t>
+          <t>2026-07-11 08:15:18 PM PT</t>
         </is>
       </c>
       <c r="C162" t="n">
@@ -19263,7 +19263,7 @@
       </c>
       <c r="B163" t="inlineStr">
         <is>
-          <t>2026-07-11 08:13:18 PM PT</t>
+          <t>2026-07-11 08:15:18 PM PT</t>
         </is>
       </c>
       <c r="C163" t="n">
@@ -19377,7 +19377,7 @@
       </c>
       <c r="B164" t="inlineStr">
         <is>
-          <t>2026-07-11 08:13:18 PM PT</t>
+          <t>2026-07-11 08:15:18 PM PT</t>
         </is>
       </c>
       <c r="C164" t="n">
@@ -19491,7 +19491,7 @@
       </c>
       <c r="B165" t="inlineStr">
         <is>
-          <t>2026-07-11 08:13:18 PM PT</t>
+          <t>2026-07-11 08:15:18 PM PT</t>
         </is>
       </c>
       <c r="C165" t="n">
@@ -19605,7 +19605,7 @@
       </c>
       <c r="B166" t="inlineStr">
         <is>
-          <t>2026-07-11 08:13:17 PM PT</t>
+          <t>2026-07-11 08:15:17 PM PT</t>
         </is>
       </c>
       <c r="C166" t="n">
@@ -19719,7 +19719,7 @@
       </c>
       <c r="B167" t="inlineStr">
         <is>
-          <t>2026-07-11 08:13:18 PM PT</t>
+          <t>2026-07-11 08:15:18 PM PT</t>
         </is>
       </c>
       <c r="C167" t="n">
@@ -19833,7 +19833,7 @@
       </c>
       <c r="B168" t="inlineStr">
         <is>
-          <t>2026-07-11 08:13:18 PM PT</t>
+          <t>2026-07-11 08:15:18 PM PT</t>
         </is>
       </c>
       <c r="C168" t="n">
@@ -19947,7 +19947,7 @@
       </c>
       <c r="B169" t="inlineStr">
         <is>
-          <t>2026-07-11 08:13:18 PM PT</t>
+          <t>2026-07-11 08:15:18 PM PT</t>
         </is>
       </c>
       <c r="C169" t="n">
@@ -20061,7 +20061,7 @@
       </c>
       <c r="B170" t="inlineStr">
         <is>
-          <t>2026-07-11 08:13:17 PM PT</t>
+          <t>2026-07-11 08:15:17 PM PT</t>
         </is>
       </c>
       <c r="C170" t="n">
@@ -20175,7 +20175,7 @@
       </c>
       <c r="B171" t="inlineStr">
         <is>
-          <t>2026-07-11 08:13:19 PM PT</t>
+          <t>2026-07-11 08:15:19 PM PT</t>
         </is>
       </c>
       <c r="C171" t="n">
@@ -20203,10 +20203,10 @@
         <v>1</v>
       </c>
       <c r="I171" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J171" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K171" t="inlineStr">
         <is>
@@ -20298,7 +20298,7 @@
       </c>
       <c r="B172" t="inlineStr">
         <is>
-          <t>2026-07-11 08:13:19 PM PT</t>
+          <t>2026-07-11 08:15:19 PM PT</t>
         </is>
       </c>
       <c r="C172" t="n">
@@ -20326,10 +20326,10 @@
         <v>1</v>
       </c>
       <c r="I172" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J172" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K172" t="inlineStr">
         <is>
@@ -20421,7 +20421,7 @@
       </c>
       <c r="B173" t="inlineStr">
         <is>
-          <t>2026-07-11 08:13:18 PM PT</t>
+          <t>2026-07-11 08:15:18 PM PT</t>
         </is>
       </c>
       <c r="C173" t="n">
@@ -20535,7 +20535,7 @@
       </c>
       <c r="B174" t="inlineStr">
         <is>
-          <t>2026-07-11 08:13:18 PM PT</t>
+          <t>2026-07-11 08:15:18 PM PT</t>
         </is>
       </c>
       <c r="C174" t="n">
@@ -20649,7 +20649,7 @@
       </c>
       <c r="B175" t="inlineStr">
         <is>
-          <t>2026-07-11 08:13:16 PM PT</t>
+          <t>2026-07-11 08:15:16 PM PT</t>
         </is>
       </c>
       <c r="C175" t="n">
@@ -20763,7 +20763,7 @@
       </c>
       <c r="B176" t="inlineStr">
         <is>
-          <t>2026-07-11 08:13:16 PM PT</t>
+          <t>2026-07-11 08:15:17 PM PT</t>
         </is>
       </c>
       <c r="C176" t="n">
@@ -20877,7 +20877,7 @@
       </c>
       <c r="B177" t="inlineStr">
         <is>
-          <t>2026-07-11 08:13:17 PM PT</t>
+          <t>2026-07-11 08:15:17 PM PT</t>
         </is>
       </c>
       <c r="C177" t="n">
@@ -20991,7 +20991,7 @@
       </c>
       <c r="B178" t="inlineStr">
         <is>
-          <t>2026-07-11 08:13:17 PM PT</t>
+          <t>2026-07-11 08:15:17 PM PT</t>
         </is>
       </c>
       <c r="C178" t="n">
@@ -21105,7 +21105,7 @@
       </c>
       <c r="B179" t="inlineStr">
         <is>
-          <t>2026-07-11 08:13:17 PM PT</t>
+          <t>2026-07-11 08:15:17 PM PT</t>
         </is>
       </c>
       <c r="C179" t="n">
@@ -21219,7 +21219,7 @@
       </c>
       <c r="B180" t="inlineStr">
         <is>
-          <t>2026-07-11 08:13:17 PM PT</t>
+          <t>2026-07-11 08:15:17 PM PT</t>
         </is>
       </c>
       <c r="C180" t="n">
@@ -21333,7 +21333,7 @@
       </c>
       <c r="B181" t="inlineStr">
         <is>
-          <t>2026-07-11 08:13:17 PM PT</t>
+          <t>2026-07-11 08:15:17 PM PT</t>
         </is>
       </c>
       <c r="C181" t="n">
@@ -21447,7 +21447,7 @@
       </c>
       <c r="B182" t="inlineStr">
         <is>
-          <t>2026-07-11 08:13:17 PM PT</t>
+          <t>2026-07-11 08:15:17 PM PT</t>
         </is>
       </c>
       <c r="C182" t="n">
@@ -21561,7 +21561,7 @@
       </c>
       <c r="B183" t="inlineStr">
         <is>
-          <t>2026-07-11 08:13:18 PM PT</t>
+          <t>2026-07-11 08:15:18 PM PT</t>
         </is>
       </c>
       <c r="C183" t="n">
@@ -21675,7 +21675,7 @@
       </c>
       <c r="B184" t="inlineStr">
         <is>
-          <t>2026-07-11 08:13:16 PM PT</t>
+          <t>2026-07-11 08:15:17 PM PT</t>
         </is>
       </c>
       <c r="C184" t="n">
@@ -21789,7 +21789,7 @@
       </c>
       <c r="B185" t="inlineStr">
         <is>
-          <t>2026-07-11 08:13:16 PM PT</t>
+          <t>2026-07-11 08:15:17 PM PT</t>
         </is>
       </c>
       <c r="C185" t="n">
@@ -21903,7 +21903,7 @@
       </c>
       <c r="B186" t="inlineStr">
         <is>
-          <t>2026-07-11 08:13:18 PM PT</t>
+          <t>2026-07-11 08:15:18 PM PT</t>
         </is>
       </c>
       <c r="C186" t="n">
@@ -22017,7 +22017,7 @@
       </c>
       <c r="B187" t="inlineStr">
         <is>
-          <t>2026-07-11 08:13:17 PM PT</t>
+          <t>2026-07-11 08:15:17 PM PT</t>
         </is>
       </c>
       <c r="C187" t="n">
@@ -22131,7 +22131,7 @@
       </c>
       <c r="B188" t="inlineStr">
         <is>
-          <t>2026-07-11 08:13:18 PM PT</t>
+          <t>2026-07-11 08:15:18 PM PT</t>
         </is>
       </c>
       <c r="C188" t="n">
@@ -22245,7 +22245,7 @@
       </c>
       <c r="B189" t="inlineStr">
         <is>
-          <t>2026-07-11 08:13:18 PM PT</t>
+          <t>2026-07-11 08:15:18 PM PT</t>
         </is>
       </c>
       <c r="C189" t="n">
@@ -22359,7 +22359,7 @@
       </c>
       <c r="B190" t="inlineStr">
         <is>
-          <t>2026-07-11 08:13:17 PM PT</t>
+          <t>2026-07-11 08:15:17 PM PT</t>
         </is>
       </c>
       <c r="C190" t="n">
@@ -22473,7 +22473,7 @@
       </c>
       <c r="B191" t="inlineStr">
         <is>
-          <t>2026-07-11 08:13:17 PM PT</t>
+          <t>2026-07-11 08:15:17 PM PT</t>
         </is>
       </c>
       <c r="C191" t="n">
@@ -22587,7 +22587,7 @@
       </c>
       <c r="B192" t="inlineStr">
         <is>
-          <t>2026-07-11 08:13:19 PM PT</t>
+          <t>2026-07-11 08:15:19 PM PT</t>
         </is>
       </c>
       <c r="C192" t="n">
@@ -22615,10 +22615,10 @@
         <v>1</v>
       </c>
       <c r="I192" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J192" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K192" t="inlineStr">
         <is>
@@ -22710,7 +22710,7 @@
       </c>
       <c r="B193" t="inlineStr">
         <is>
-          <t>2026-07-11 08:13:17 PM PT</t>
+          <t>2026-07-11 08:15:17 PM PT</t>
         </is>
       </c>
       <c r="C193" t="n">
@@ -22824,7 +22824,7 @@
       </c>
       <c r="B194" t="inlineStr">
         <is>
-          <t>2026-07-11 08:13:18 PM PT</t>
+          <t>2026-07-11 08:15:18 PM PT</t>
         </is>
       </c>
       <c r="C194" t="n">
@@ -22938,7 +22938,7 @@
       </c>
       <c r="B195" t="inlineStr">
         <is>
-          <t>2026-07-11 08:13:18 PM PT</t>
+          <t>2026-07-11 08:15:18 PM PT</t>
         </is>
       </c>
       <c r="C195" t="n">
@@ -23052,7 +23052,7 @@
       </c>
       <c r="B196" t="inlineStr">
         <is>
-          <t>2026-07-11 08:13:18 PM PT</t>
+          <t>2026-07-11 08:15:18 PM PT</t>
         </is>
       </c>
       <c r="C196" t="n">
@@ -23166,7 +23166,7 @@
       </c>
       <c r="B197" t="inlineStr">
         <is>
-          <t>2026-07-11 08:13:17 PM PT</t>
+          <t>2026-07-11 08:15:17 PM PT</t>
         </is>
       </c>
       <c r="C197" t="n">
@@ -23280,7 +23280,7 @@
       </c>
       <c r="B198" t="inlineStr">
         <is>
-          <t>2026-07-11 08:13:17 PM PT</t>
+          <t>2026-07-11 08:15:17 PM PT</t>
         </is>
       </c>
       <c r="C198" t="n">
@@ -23394,7 +23394,7 @@
       </c>
       <c r="B199" t="inlineStr">
         <is>
-          <t>2026-07-11 08:13:17 PM PT</t>
+          <t>2026-07-11 08:15:17 PM PT</t>
         </is>
       </c>
       <c r="C199" t="n">
@@ -23508,7 +23508,7 @@
       </c>
       <c r="B200" t="inlineStr">
         <is>
-          <t>2026-07-11 08:13:18 PM PT</t>
+          <t>2026-07-11 08:15:18 PM PT</t>
         </is>
       </c>
       <c r="C200" t="n">
@@ -23622,7 +23622,7 @@
       </c>
       <c r="B201" t="inlineStr">
         <is>
-          <t>2026-07-11 08:13:17 PM PT</t>
+          <t>2026-07-11 08:15:17 PM PT</t>
         </is>
       </c>
       <c r="C201" t="n">
@@ -23736,7 +23736,7 @@
       </c>
       <c r="B202" t="inlineStr">
         <is>
-          <t>2026-07-11 08:13:17 PM PT</t>
+          <t>2026-07-11 08:15:17 PM PT</t>
         </is>
       </c>
       <c r="C202" t="n">
@@ -23850,7 +23850,7 @@
       </c>
       <c r="B203" t="inlineStr">
         <is>
-          <t>2026-07-11 08:13:17 PM PT</t>
+          <t>2026-07-11 08:15:17 PM PT</t>
         </is>
       </c>
       <c r="C203" t="n">
@@ -23964,7 +23964,7 @@
       </c>
       <c r="B204" t="inlineStr">
         <is>
-          <t>2026-07-11 08:13:17 PM PT</t>
+          <t>2026-07-11 08:15:17 PM PT</t>
         </is>
       </c>
       <c r="C204" t="n">
@@ -24078,7 +24078,7 @@
       </c>
       <c r="B205" t="inlineStr">
         <is>
-          <t>2026-07-11 08:13:17 PM PT</t>
+          <t>2026-07-11 08:15:17 PM PT</t>
         </is>
       </c>
       <c r="C205" t="n">
@@ -24192,7 +24192,7 @@
       </c>
       <c r="B206" t="inlineStr">
         <is>
-          <t>2026-07-11 08:13:18 PM PT</t>
+          <t>2026-07-11 08:15:18 PM PT</t>
         </is>
       </c>
       <c r="C206" t="n">
@@ -24306,7 +24306,7 @@
       </c>
       <c r="B207" t="inlineStr">
         <is>
-          <t>2026-07-11 08:13:18 PM PT</t>
+          <t>2026-07-11 08:15:18 PM PT</t>
         </is>
       </c>
       <c r="C207" t="n">
@@ -24420,7 +24420,7 @@
       </c>
       <c r="B208" t="inlineStr">
         <is>
-          <t>2026-07-11 08:13:18 PM PT</t>
+          <t>2026-07-11 08:15:18 PM PT</t>
         </is>
       </c>
       <c r="C208" t="n">
@@ -24534,7 +24534,7 @@
       </c>
       <c r="B209" t="inlineStr">
         <is>
-          <t>2026-07-11 08:13:18 PM PT</t>
+          <t>2026-07-11 08:15:18 PM PT</t>
         </is>
       </c>
       <c r="C209" t="n">
@@ -24648,7 +24648,7 @@
       </c>
       <c r="B210" t="inlineStr">
         <is>
-          <t>2026-07-11 08:13:18 PM PT</t>
+          <t>2026-07-11 08:15:18 PM PT</t>
         </is>
       </c>
       <c r="C210" t="n">
@@ -24762,7 +24762,7 @@
       </c>
       <c r="B211" t="inlineStr">
         <is>
-          <t>2026-07-11 08:13:17 PM PT</t>
+          <t>2026-07-11 08:15:17 PM PT</t>
         </is>
       </c>
       <c r="C211" t="n">
@@ -24876,7 +24876,7 @@
       </c>
       <c r="B212" t="inlineStr">
         <is>
-          <t>2026-07-11 08:13:18 PM PT</t>
+          <t>2026-07-11 08:15:18 PM PT</t>
         </is>
       </c>
       <c r="C212" t="n">
@@ -24990,7 +24990,7 @@
       </c>
       <c r="B213" t="inlineStr">
         <is>
-          <t>2026-07-11 08:13:18 PM PT</t>
+          <t>2026-07-11 08:15:18 PM PT</t>
         </is>
       </c>
       <c r="C213" t="n">
@@ -25104,7 +25104,7 @@
       </c>
       <c r="B214" t="inlineStr">
         <is>
-          <t>2026-07-11 08:13:17 PM PT</t>
+          <t>2026-07-11 08:15:17 PM PT</t>
         </is>
       </c>
       <c r="C214" t="n">
@@ -25218,7 +25218,7 @@
       </c>
       <c r="B215" t="inlineStr">
         <is>
-          <t>2026-07-11 08:13:17 PM PT</t>
+          <t>2026-07-11 08:15:17 PM PT</t>
         </is>
       </c>
       <c r="C215" t="n">
@@ -25332,7 +25332,7 @@
       </c>
       <c r="B216" t="inlineStr">
         <is>
-          <t>2026-07-11 08:13:17 PM PT</t>
+          <t>2026-07-11 08:15:17 PM PT</t>
         </is>
       </c>
       <c r="C216" t="n">
@@ -25446,7 +25446,7 @@
       </c>
       <c r="B217" t="inlineStr">
         <is>
-          <t>2026-07-11 08:13:17 PM PT</t>
+          <t>2026-07-11 08:15:17 PM PT</t>
         </is>
       </c>
       <c r="C217" t="n">
@@ -25560,7 +25560,7 @@
       </c>
       <c r="B218" t="inlineStr">
         <is>
-          <t>2026-07-11 08:13:17 PM PT</t>
+          <t>2026-07-11 08:15:17 PM PT</t>
         </is>
       </c>
       <c r="C218" t="n">
@@ -25674,7 +25674,7 @@
       </c>
       <c r="B219" t="inlineStr">
         <is>
-          <t>2026-07-11 08:13:17 PM PT</t>
+          <t>2026-07-11 08:15:17 PM PT</t>
         </is>
       </c>
       <c r="C219" t="n">
@@ -25788,7 +25788,7 @@
       </c>
       <c r="B220" t="inlineStr">
         <is>
-          <t>2026-07-11 08:13:17 PM PT</t>
+          <t>2026-07-11 08:15:17 PM PT</t>
         </is>
       </c>
       <c r="C220" t="n">
@@ -25902,7 +25902,7 @@
       </c>
       <c r="B221" t="inlineStr">
         <is>
-          <t>2026-07-11 08:13:17 PM PT</t>
+          <t>2026-07-11 08:15:17 PM PT</t>
         </is>
       </c>
       <c r="C221" t="n">
@@ -26016,7 +26016,7 @@
       </c>
       <c r="B222" t="inlineStr">
         <is>
-          <t>2026-07-11 08:13:16 PM PT</t>
+          <t>2026-07-11 08:15:16 PM PT</t>
         </is>
       </c>
       <c r="C222" t="n">
@@ -26130,7 +26130,7 @@
       </c>
       <c r="B223" t="inlineStr">
         <is>
-          <t>2026-07-11 08:13:16 PM PT</t>
+          <t>2026-07-11 08:15:17 PM PT</t>
         </is>
       </c>
       <c r="C223" t="n">
@@ -26244,7 +26244,7 @@
       </c>
       <c r="B224" t="inlineStr">
         <is>
-          <t>2026-07-11 08:13:18 PM PT</t>
+          <t>2026-07-11 08:15:18 PM PT</t>
         </is>
       </c>
       <c r="C224" t="n">
@@ -26358,7 +26358,7 @@
       </c>
       <c r="B225" t="inlineStr">
         <is>
-          <t>2026-07-11 08:13:17 PM PT</t>
+          <t>2026-07-11 08:15:17 PM PT</t>
         </is>
       </c>
       <c r="C225" t="n">
@@ -26472,7 +26472,7 @@
       </c>
       <c r="B226" t="inlineStr">
         <is>
-          <t>2026-07-11 08:13:18 PM PT</t>
+          <t>2026-07-11 08:15:18 PM PT</t>
         </is>
       </c>
       <c r="C226" t="n">
@@ -26586,7 +26586,7 @@
       </c>
       <c r="B227" t="inlineStr">
         <is>
-          <t>2026-07-11 08:13:18 PM PT</t>
+          <t>2026-07-11 08:15:18 PM PT</t>
         </is>
       </c>
       <c r="C227" t="n">
@@ -26700,7 +26700,7 @@
       </c>
       <c r="B228" t="inlineStr">
         <is>
-          <t>2026-07-11 08:13:19 PM PT</t>
+          <t>2026-07-11 08:15:19 PM PT</t>
         </is>
       </c>
       <c r="C228" t="n">
@@ -26728,10 +26728,10 @@
         <v>0</v>
       </c>
       <c r="I228" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="J228" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K228" t="inlineStr">
         <is>
@@ -26823,7 +26823,7 @@
       </c>
       <c r="B229" t="inlineStr">
         <is>
-          <t>2026-07-11 08:13:17 PM PT</t>
+          <t>2026-07-11 08:15:17 PM PT</t>
         </is>
       </c>
       <c r="C229" t="n">
@@ -26937,7 +26937,7 @@
       </c>
       <c r="B230" t="inlineStr">
         <is>
-          <t>2026-07-11 08:13:17 PM PT</t>
+          <t>2026-07-11 08:15:17 PM PT</t>
         </is>
       </c>
       <c r="C230" t="n">
@@ -27051,7 +27051,7 @@
       </c>
       <c r="B231" t="inlineStr">
         <is>
-          <t>2026-07-11 08:13:17 PM PT</t>
+          <t>2026-07-11 08:15:17 PM PT</t>
         </is>
       </c>
       <c r="C231" t="n">
@@ -27165,7 +27165,7 @@
       </c>
       <c r="B232" t="inlineStr">
         <is>
-          <t>2026-07-11 08:13:17 PM PT</t>
+          <t>2026-07-11 08:15:17 PM PT</t>
         </is>
       </c>
       <c r="C232" t="n">
@@ -27279,7 +27279,7 @@
       </c>
       <c r="B233" t="inlineStr">
         <is>
-          <t>2026-07-11 08:13:19 PM PT</t>
+          <t>2026-07-11 08:15:19 PM PT</t>
         </is>
       </c>
       <c r="C233" t="n">
@@ -27307,10 +27307,10 @@
         <v>1</v>
       </c>
       <c r="I233" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J233" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K233" t="inlineStr">
         <is>
@@ -27402,7 +27402,7 @@
       </c>
       <c r="B234" t="inlineStr">
         <is>
-          <t>2026-07-11 08:13:19 PM PT</t>
+          <t>2026-07-11 08:15:19 PM PT</t>
         </is>
       </c>
       <c r="C234" t="n">
@@ -27430,10 +27430,10 @@
         <v>1</v>
       </c>
       <c r="I234" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J234" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K234" t="inlineStr">
         <is>
@@ -27525,7 +27525,7 @@
       </c>
       <c r="B235" t="inlineStr">
         <is>
-          <t>2026-07-11 08:13:19 PM PT</t>
+          <t>2026-07-11 08:15:19 PM PT</t>
         </is>
       </c>
       <c r="C235" t="n">
@@ -27553,10 +27553,10 @@
         <v>1</v>
       </c>
       <c r="I235" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J235" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K235" t="inlineStr">
         <is>
@@ -27648,7 +27648,7 @@
       </c>
       <c r="B236" t="inlineStr">
         <is>
-          <t>2026-07-11 08:13:17 PM PT</t>
+          <t>2026-07-11 08:15:17 PM PT</t>
         </is>
       </c>
       <c r="C236" t="n">
@@ -27762,7 +27762,7 @@
       </c>
       <c r="B237" t="inlineStr">
         <is>
-          <t>2026-07-11 08:13:17 PM PT</t>
+          <t>2026-07-11 08:15:17 PM PT</t>
         </is>
       </c>
       <c r="C237" t="n">
@@ -27876,7 +27876,7 @@
       </c>
       <c r="B238" t="inlineStr">
         <is>
-          <t>2026-07-11 08:13:17 PM PT</t>
+          <t>2026-07-11 08:15:17 PM PT</t>
         </is>
       </c>
       <c r="C238" t="n">
@@ -27990,7 +27990,7 @@
       </c>
       <c r="B239" t="inlineStr">
         <is>
-          <t>2026-07-11 08:13:17 PM PT</t>
+          <t>2026-07-11 08:15:17 PM PT</t>
         </is>
       </c>
       <c r="C239" t="n">
@@ -28104,7 +28104,7 @@
       </c>
       <c r="B240" t="inlineStr">
         <is>
-          <t>2026-07-11 08:13:17 PM PT</t>
+          <t>2026-07-11 08:15:17 PM PT</t>
         </is>
       </c>
       <c r="C240" t="n">
@@ -28218,7 +28218,7 @@
       </c>
       <c r="B241" t="inlineStr">
         <is>
-          <t>2026-07-11 08:13:17 PM PT</t>
+          <t>2026-07-11 08:15:17 PM PT</t>
         </is>
       </c>
       <c r="C241" t="n">
@@ -28332,7 +28332,7 @@
       </c>
       <c r="B242" t="inlineStr">
         <is>
-          <t>2026-07-11 08:13:17 PM PT</t>
+          <t>2026-07-11 08:15:17 PM PT</t>
         </is>
       </c>
       <c r="C242" t="n">
@@ -28446,7 +28446,7 @@
       </c>
       <c r="B243" t="inlineStr">
         <is>
-          <t>2026-07-11 08:13:18 PM PT</t>
+          <t>2026-07-11 08:15:18 PM PT</t>
         </is>
       </c>
       <c r="C243" t="n">
@@ -28560,7 +28560,7 @@
       </c>
       <c r="B244" t="inlineStr">
         <is>
-          <t>2026-07-11 08:13:18 PM PT</t>
+          <t>2026-07-11 08:15:18 PM PT</t>
         </is>
       </c>
       <c r="C244" t="n">
@@ -28674,7 +28674,7 @@
       </c>
       <c r="B245" t="inlineStr">
         <is>
-          <t>2026-07-11 08:13:18 PM PT</t>
+          <t>2026-07-11 08:15:18 PM PT</t>
         </is>
       </c>
       <c r="C245" t="n">
@@ -28788,7 +28788,7 @@
       </c>
       <c r="B246" t="inlineStr">
         <is>
-          <t>2026-07-11 08:13:18 PM PT</t>
+          <t>2026-07-11 08:15:18 PM PT</t>
         </is>
       </c>
       <c r="C246" t="n">
@@ -28902,7 +28902,7 @@
       </c>
       <c r="B247" t="inlineStr">
         <is>
-          <t>2026-07-11 08:13:18 PM PT</t>
+          <t>2026-07-11 08:15:18 PM PT</t>
         </is>
       </c>
       <c r="C247" t="n">
@@ -29016,7 +29016,7 @@
       </c>
       <c r="B248" t="inlineStr">
         <is>
-          <t>2026-07-11 08:13:18 PM PT</t>
+          <t>2026-07-11 08:15:18 PM PT</t>
         </is>
       </c>
       <c r="C248" t="n">
@@ -29130,7 +29130,7 @@
       </c>
       <c r="B249" t="inlineStr">
         <is>
-          <t>2026-07-11 08:13:17 PM PT</t>
+          <t>2026-07-11 08:15:17 PM PT</t>
         </is>
       </c>
       <c r="C249" t="n">
@@ -29244,7 +29244,7 @@
       </c>
       <c r="B250" t="inlineStr">
         <is>
-          <t>2026-07-11 08:13:17 PM PT</t>
+          <t>2026-07-11 08:15:17 PM PT</t>
         </is>
       </c>
       <c r="C250" t="n">
@@ -29358,7 +29358,7 @@
       </c>
       <c r="B251" t="inlineStr">
         <is>
-          <t>2026-07-11 08:13:17 PM PT</t>
+          <t>2026-07-11 08:15:17 PM PT</t>
         </is>
       </c>
       <c r="C251" t="n">
@@ -29472,7 +29472,7 @@
       </c>
       <c r="B252" t="inlineStr">
         <is>
-          <t>2026-07-11 08:13:18 PM PT</t>
+          <t>2026-07-11 08:15:18 PM PT</t>
         </is>
       </c>
       <c r="C252" t="n">
@@ -29586,7 +29586,7 @@
       </c>
       <c r="B253" t="inlineStr">
         <is>
-          <t>2026-07-11 08:13:18 PM PT</t>
+          <t>2026-07-11 08:15:18 PM PT</t>
         </is>
       </c>
       <c r="C253" t="n">
@@ -29700,7 +29700,7 @@
       </c>
       <c r="B254" t="inlineStr">
         <is>
-          <t>2026-07-11 08:13:18 PM PT</t>
+          <t>2026-07-11 08:15:18 PM PT</t>
         </is>
       </c>
       <c r="C254" t="n">
@@ -29814,7 +29814,7 @@
       </c>
       <c r="B255" t="inlineStr">
         <is>
-          <t>2026-07-11 08:13:18 PM PT</t>
+          <t>2026-07-11 08:15:18 PM PT</t>
         </is>
       </c>
       <c r="C255" t="n">
@@ -29928,7 +29928,7 @@
       </c>
       <c r="B256" t="inlineStr">
         <is>
-          <t>2026-07-11 08:13:18 PM PT</t>
+          <t>2026-07-11 08:15:18 PM PT</t>
         </is>
       </c>
       <c r="C256" t="n">
@@ -30042,7 +30042,7 @@
       </c>
       <c r="B257" t="inlineStr">
         <is>
-          <t>2026-07-11 08:13:17 PM PT</t>
+          <t>2026-07-11 08:15:17 PM PT</t>
         </is>
       </c>
       <c r="C257" t="n">
@@ -30156,7 +30156,7 @@
       </c>
       <c r="B258" t="inlineStr">
         <is>
-          <t>2026-07-11 08:13:17 PM PT</t>
+          <t>2026-07-11 08:15:17 PM PT</t>
         </is>
       </c>
       <c r="C258" t="n">
@@ -30270,7 +30270,7 @@
       </c>
       <c r="B259" t="inlineStr">
         <is>
-          <t>2026-07-11 08:13:17 PM PT</t>
+          <t>2026-07-11 08:15:17 PM PT</t>
         </is>
       </c>
       <c r="C259" t="n">
@@ -30384,7 +30384,7 @@
       </c>
       <c r="B260" t="inlineStr">
         <is>
-          <t>2026-07-11 08:13:17 PM PT</t>
+          <t>2026-07-11 08:15:17 PM PT</t>
         </is>
       </c>
       <c r="C260" t="n">
@@ -30498,7 +30498,7 @@
       </c>
       <c r="B261" t="inlineStr">
         <is>
-          <t>2026-07-11 08:13:17 PM PT</t>
+          <t>2026-07-11 08:15:17 PM PT</t>
         </is>
       </c>
       <c r="C261" t="n">
@@ -30612,7 +30612,7 @@
       </c>
       <c r="B262" t="inlineStr">
         <is>
-          <t>2026-07-11 08:13:17 PM PT</t>
+          <t>2026-07-11 08:15:17 PM PT</t>
         </is>
       </c>
       <c r="C262" t="n">
@@ -30726,7 +30726,7 @@
       </c>
       <c r="B263" t="inlineStr">
         <is>
-          <t>2026-07-11 08:13:17 PM PT</t>
+          <t>2026-07-11 08:15:17 PM PT</t>
         </is>
       </c>
       <c r="C263" t="n">
@@ -30840,7 +30840,7 @@
       </c>
       <c r="B264" t="inlineStr">
         <is>
-          <t>2026-07-11 08:13:18 PM PT</t>
+          <t>2026-07-11 08:15:18 PM PT</t>
         </is>
       </c>
       <c r="C264" t="n">
@@ -30954,7 +30954,7 @@
       </c>
       <c r="B265" t="inlineStr">
         <is>
-          <t>2026-07-11 08:13:18 PM PT</t>
+          <t>2026-07-11 08:15:18 PM PT</t>
         </is>
       </c>
       <c r="C265" t="n">
@@ -31068,7 +31068,7 @@
       </c>
       <c r="B266" t="inlineStr">
         <is>
-          <t>2026-07-11 08:13:18 PM PT</t>
+          <t>2026-07-11 08:15:18 PM PT</t>
         </is>
       </c>
       <c r="C266" t="n">
@@ -31182,7 +31182,7 @@
       </c>
       <c r="B267" t="inlineStr">
         <is>
-          <t>2026-07-11 08:13:18 PM PT</t>
+          <t>2026-07-11 08:15:18 PM PT</t>
         </is>
       </c>
       <c r="C267" t="n">
@@ -31296,7 +31296,7 @@
       </c>
       <c r="B268" t="inlineStr">
         <is>
-          <t>2026-07-11 08:13:18 PM PT</t>
+          <t>2026-07-11 08:15:18 PM PT</t>
         </is>
       </c>
       <c r="C268" t="n">
@@ -31410,7 +31410,7 @@
       </c>
       <c r="B269" t="inlineStr">
         <is>
-          <t>2026-07-11 08:13:18 PM PT</t>
+          <t>2026-07-11 08:15:18 PM PT</t>
         </is>
       </c>
       <c r="C269" t="n">
@@ -31524,7 +31524,7 @@
       </c>
       <c r="B270" t="inlineStr">
         <is>
-          <t>2026-07-11 08:13:18 PM PT</t>
+          <t>2026-07-11 08:15:18 PM PT</t>
         </is>
       </c>
       <c r="C270" t="n">
@@ -31638,7 +31638,7 @@
       </c>
       <c r="B271" t="inlineStr">
         <is>
-          <t>2026-07-11 08:13:18 PM PT</t>
+          <t>2026-07-11 08:15:18 PM PT</t>
         </is>
       </c>
       <c r="C271" t="n">
@@ -31752,7 +31752,7 @@
       </c>
       <c r="B272" t="inlineStr">
         <is>
-          <t>2026-07-11 08:13:18 PM PT</t>
+          <t>2026-07-11 08:15:18 PM PT</t>
         </is>
       </c>
       <c r="C272" t="n">
@@ -31866,7 +31866,7 @@
       </c>
       <c r="B273" t="inlineStr">
         <is>
-          <t>2026-07-11 08:13:18 PM PT</t>
+          <t>2026-07-11 08:15:18 PM PT</t>
         </is>
       </c>
       <c r="C273" t="n">
@@ -31980,7 +31980,7 @@
       </c>
       <c r="B274" t="inlineStr">
         <is>
-          <t>2026-07-11 08:13:18 PM PT</t>
+          <t>2026-07-11 08:15:18 PM PT</t>
         </is>
       </c>
       <c r="C274" t="n">
@@ -32094,7 +32094,7 @@
       </c>
       <c r="B275" t="inlineStr">
         <is>
-          <t>2026-07-11 08:13:17 PM PT</t>
+          <t>2026-07-11 08:15:17 PM PT</t>
         </is>
       </c>
       <c r="C275" t="n">
@@ -32208,7 +32208,7 @@
       </c>
       <c r="B276" t="inlineStr">
         <is>
-          <t>2026-07-11 08:13:17 PM PT</t>
+          <t>2026-07-11 08:15:17 PM PT</t>
         </is>
       </c>
       <c r="C276" t="n">
@@ -32322,7 +32322,7 @@
       </c>
       <c r="B277" t="inlineStr">
         <is>
-          <t>2026-07-11 08:13:17 PM PT</t>
+          <t>2026-07-11 08:15:17 PM PT</t>
         </is>
       </c>
       <c r="C277" t="n">
@@ -32436,7 +32436,7 @@
       </c>
       <c r="B278" t="inlineStr">
         <is>
-          <t>2026-07-11 08:13:19 PM PT</t>
+          <t>2026-07-11 08:15:19 PM PT</t>
         </is>
       </c>
       <c r="C278" t="n">
@@ -32464,10 +32464,10 @@
         <v>1</v>
       </c>
       <c r="I278" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J278" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K278" t="inlineStr">
         <is>
@@ -32559,7 +32559,7 @@
       </c>
       <c r="B279" t="inlineStr">
         <is>
-          <t>2026-07-11 08:13:19 PM PT</t>
+          <t>2026-07-11 08:15:19 PM PT</t>
         </is>
       </c>
       <c r="C279" t="n">
@@ -32587,10 +32587,10 @@
         <v>1</v>
       </c>
       <c r="I279" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J279" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K279" t="inlineStr">
         <is>
@@ -32682,7 +32682,7 @@
       </c>
       <c r="B280" t="inlineStr">
         <is>
-          <t>2026-07-11 08:13:19 PM PT</t>
+          <t>2026-07-11 08:15:19 PM PT</t>
         </is>
       </c>
       <c r="C280" t="n">
@@ -32710,10 +32710,10 @@
         <v>1</v>
       </c>
       <c r="I280" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J280" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K280" t="inlineStr">
         <is>
@@ -32805,7 +32805,7 @@
       </c>
       <c r="B281" t="inlineStr">
         <is>
-          <t>2026-07-11 08:13:19 PM PT</t>
+          <t>2026-07-11 08:15:19 PM PT</t>
         </is>
       </c>
       <c r="C281" t="n">
@@ -32833,10 +32833,10 @@
         <v>1</v>
       </c>
       <c r="I281" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J281" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K281" t="inlineStr">
         <is>
@@ -32928,7 +32928,7 @@
       </c>
       <c r="B282" t="inlineStr">
         <is>
-          <t>2026-07-11 08:13:18 PM PT</t>
+          <t>2026-07-11 08:15:18 PM PT</t>
         </is>
       </c>
       <c r="C282" t="n">
@@ -33042,7 +33042,7 @@
       </c>
       <c r="B283" t="inlineStr">
         <is>
-          <t>2026-07-11 08:13:16 PM PT</t>
+          <t>2026-07-11 08:15:16 PM PT</t>
         </is>
       </c>
       <c r="C283" t="n">
@@ -33156,7 +33156,7 @@
       </c>
       <c r="B284" t="inlineStr">
         <is>
-          <t>2026-07-11 08:13:16 PM PT</t>
+          <t>2026-07-11 08:15:17 PM PT</t>
         </is>
       </c>
       <c r="C284" t="n">
@@ -33270,7 +33270,7 @@
       </c>
       <c r="B285" t="inlineStr">
         <is>
-          <t>2026-07-11 08:13:16 PM PT</t>
+          <t>2026-07-11 08:15:16 PM PT</t>
         </is>
       </c>
       <c r="C285" t="n">
@@ -33384,7 +33384,7 @@
       </c>
       <c r="B286" t="inlineStr">
         <is>
-          <t>2026-07-11 08:13:16 PM PT</t>
+          <t>2026-07-11 08:15:17 PM PT</t>
         </is>
       </c>
       <c r="C286" t="n">
@@ -33498,7 +33498,7 @@
       </c>
       <c r="B287" t="inlineStr">
         <is>
-          <t>2026-07-11 08:13:16 PM PT</t>
+          <t>2026-07-11 08:15:17 PM PT</t>
         </is>
       </c>
       <c r="C287" t="n">
@@ -33612,7 +33612,7 @@
       </c>
       <c r="B288" t="inlineStr">
         <is>
-          <t>2026-07-11 08:13:16 PM PT</t>
+          <t>2026-07-11 08:15:16 PM PT</t>
         </is>
       </c>
       <c r="C288" t="n">
@@ -33726,7 +33726,7 @@
       </c>
       <c r="B289" t="inlineStr">
         <is>
-          <t>2026-07-11 08:13:17 PM PT</t>
+          <t>2026-07-11 08:15:17 PM PT</t>
         </is>
       </c>
       <c r="C289" t="n">
@@ -33840,7 +33840,7 @@
       </c>
       <c r="B290" t="inlineStr">
         <is>
-          <t>2026-07-11 08:13:17 PM PT</t>
+          <t>2026-07-11 08:15:17 PM PT</t>
         </is>
       </c>
       <c r="C290" t="n">
@@ -33954,7 +33954,7 @@
       </c>
       <c r="B291" t="inlineStr">
         <is>
-          <t>2026-07-11 08:13:17 PM PT</t>
+          <t>2026-07-11 08:15:17 PM PT</t>
         </is>
       </c>
       <c r="C291" t="n">
@@ -34068,7 +34068,7 @@
       </c>
       <c r="B292" t="inlineStr">
         <is>
-          <t>2026-07-11 08:13:17 PM PT</t>
+          <t>2026-07-11 08:15:17 PM PT</t>
         </is>
       </c>
       <c r="C292" t="n">
@@ -34182,7 +34182,7 @@
       </c>
       <c r="B293" t="inlineStr">
         <is>
-          <t>2026-07-11 08:13:17 PM PT</t>
+          <t>2026-07-11 08:15:17 PM PT</t>
         </is>
       </c>
       <c r="C293" t="n">
@@ -34296,7 +34296,7 @@
       </c>
       <c r="B294" t="inlineStr">
         <is>
-          <t>2026-07-11 08:13:17 PM PT</t>
+          <t>2026-07-11 08:15:17 PM PT</t>
         </is>
       </c>
       <c r="C294" t="n">
@@ -34410,7 +34410,7 @@
       </c>
       <c r="B295" t="inlineStr">
         <is>
-          <t>2026-07-11 08:13:17 PM PT</t>
+          <t>2026-07-11 08:15:17 PM PT</t>
         </is>
       </c>
       <c r="C295" t="n">
@@ -34524,7 +34524,7 @@
       </c>
       <c r="B296" t="inlineStr">
         <is>
-          <t>2026-07-11 08:13:18 PM PT</t>
+          <t>2026-07-11 08:15:18 PM PT</t>
         </is>
       </c>
       <c r="C296" t="n">
@@ -34638,7 +34638,7 @@
       </c>
       <c r="B297" t="inlineStr">
         <is>
-          <t>2026-07-11 08:13:18 PM PT</t>
+          <t>2026-07-11 08:15:18 PM PT</t>
         </is>
       </c>
       <c r="C297" t="n">
@@ -34752,7 +34752,7 @@
       </c>
       <c r="B298" t="inlineStr">
         <is>
-          <t>2026-07-11 08:13:16 PM PT</t>
+          <t>2026-07-11 08:15:17 PM PT</t>
         </is>
       </c>
       <c r="C298" t="n">
@@ -34866,7 +34866,7 @@
       </c>
       <c r="B299" t="inlineStr">
         <is>
-          <t>2026-07-11 08:13:16 PM PT</t>
+          <t>2026-07-11 08:15:17 PM PT</t>
         </is>
       </c>
       <c r="C299" t="n">
@@ -34980,7 +34980,7 @@
       </c>
       <c r="B300" t="inlineStr">
         <is>
-          <t>2026-07-11 08:13:16 PM PT</t>
+          <t>2026-07-11 08:15:17 PM PT</t>
         </is>
       </c>
       <c r="C300" t="n">
@@ -35094,7 +35094,7 @@
       </c>
       <c r="B301" t="inlineStr">
         <is>
-          <t>2026-07-11 08:13:16 PM PT</t>
+          <t>2026-07-11 08:15:16 PM PT</t>
         </is>
       </c>
       <c r="C301" t="n">
@@ -35208,7 +35208,7 @@
       </c>
       <c r="B302" t="inlineStr">
         <is>
-          <t>2026-07-11 08:13:16 PM PT</t>
+          <t>2026-07-11 08:15:17 PM PT</t>
         </is>
       </c>
       <c r="C302" t="n">
@@ -35322,7 +35322,7 @@
       </c>
       <c r="B303" t="inlineStr">
         <is>
-          <t>2026-07-11 08:13:16 PM PT</t>
+          <t>2026-07-11 08:15:16 PM PT</t>
         </is>
       </c>
       <c r="C303" t="n">
@@ -35436,7 +35436,7 @@
       </c>
       <c r="B304" t="inlineStr">
         <is>
-          <t>2026-07-11 08:13:16 PM PT</t>
+          <t>2026-07-11 08:15:16 PM PT</t>
         </is>
       </c>
       <c r="C304" t="n">
@@ -35550,7 +35550,7 @@
       </c>
       <c r="B305" t="inlineStr">
         <is>
-          <t>2026-07-11 08:13:16 PM PT</t>
+          <t>2026-07-11 08:15:17 PM PT</t>
         </is>
       </c>
       <c r="C305" t="n">
@@ -35664,7 +35664,7 @@
       </c>
       <c r="B306" t="inlineStr">
         <is>
-          <t>2026-07-11 08:13:19 PM PT</t>
+          <t>2026-07-11 08:15:19 PM PT</t>
         </is>
       </c>
       <c r="C306" t="n">
@@ -35692,10 +35692,10 @@
         <v>0</v>
       </c>
       <c r="I306" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="J306" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K306" t="inlineStr">
         <is>
@@ -35787,7 +35787,7 @@
       </c>
       <c r="B307" t="inlineStr">
         <is>
-          <t>2026-07-11 08:13:18 PM PT</t>
+          <t>2026-07-11 08:15:18 PM PT</t>
         </is>
       </c>
       <c r="C307" t="n">
@@ -35901,7 +35901,7 @@
       </c>
       <c r="B308" t="inlineStr">
         <is>
-          <t>2026-07-11 08:13:18 PM PT</t>
+          <t>2026-07-11 08:15:18 PM PT</t>
         </is>
       </c>
       <c r="C308" t="n">
@@ -36015,7 +36015,7 @@
       </c>
       <c r="B309" t="inlineStr">
         <is>
-          <t>2026-07-11 08:13:18 PM PT</t>
+          <t>2026-07-11 08:15:18 PM PT</t>
         </is>
       </c>
       <c r="C309" t="n">
@@ -36129,7 +36129,7 @@
       </c>
       <c r="B310" t="inlineStr">
         <is>
-          <t>2026-07-11 08:13:18 PM PT</t>
+          <t>2026-07-11 08:15:18 PM PT</t>
         </is>
       </c>
       <c r="C310" t="n">
@@ -36243,7 +36243,7 @@
       </c>
       <c r="B311" t="inlineStr">
         <is>
-          <t>2026-07-11 08:13:18 PM PT</t>
+          <t>2026-07-11 08:15:18 PM PT</t>
         </is>
       </c>
       <c r="C311" t="n">
@@ -36357,7 +36357,7 @@
       </c>
       <c r="B312" t="inlineStr">
         <is>
-          <t>2026-07-11 08:13:17 PM PT</t>
+          <t>2026-07-11 08:15:17 PM PT</t>
         </is>
       </c>
       <c r="C312" t="n">
@@ -36471,7 +36471,7 @@
       </c>
       <c r="B313" t="inlineStr">
         <is>
-          <t>2026-07-11 08:13:17 PM PT</t>
+          <t>2026-07-11 08:15:17 PM PT</t>
         </is>
       </c>
       <c r="C313" t="n">
@@ -36585,7 +36585,7 @@
       </c>
       <c r="B314" t="inlineStr">
         <is>
-          <t>2026-07-11 08:13:18 PM PT</t>
+          <t>2026-07-11 08:15:18 PM PT</t>
         </is>
       </c>
       <c r="C314" t="n">
@@ -36699,7 +36699,7 @@
       </c>
       <c r="B315" t="inlineStr">
         <is>
-          <t>2026-07-11 08:13:18 PM PT</t>
+          <t>2026-07-11 08:15:18 PM PT</t>
         </is>
       </c>
       <c r="C315" t="n">
@@ -36813,7 +36813,7 @@
       </c>
       <c r="B316" t="inlineStr">
         <is>
-          <t>2026-07-11 08:13:18 PM PT</t>
+          <t>2026-07-11 08:15:18 PM PT</t>
         </is>
       </c>
       <c r="C316" t="n">
@@ -36927,7 +36927,7 @@
       </c>
       <c r="B317" t="inlineStr">
         <is>
-          <t>2026-07-11 08:13:18 PM PT</t>
+          <t>2026-07-11 08:15:18 PM PT</t>
         </is>
       </c>
       <c r="C317" t="n">
@@ -37041,7 +37041,7 @@
       </c>
       <c r="B318" t="inlineStr">
         <is>
-          <t>2026-07-11 08:13:18 PM PT</t>
+          <t>2026-07-11 08:15:18 PM PT</t>
         </is>
       </c>
       <c r="C318" t="n">
@@ -37155,7 +37155,7 @@
       </c>
       <c r="B319" t="inlineStr">
         <is>
-          <t>2026-07-11 08:13:18 PM PT</t>
+          <t>2026-07-11 08:15:18 PM PT</t>
         </is>
       </c>
       <c r="C319" t="n">
@@ -37269,7 +37269,7 @@
       </c>
       <c r="B320" t="inlineStr">
         <is>
-          <t>2026-07-11 08:13:18 PM PT</t>
+          <t>2026-07-11 08:15:18 PM PT</t>
         </is>
       </c>
       <c r="C320" t="n">
@@ -37383,7 +37383,7 @@
       </c>
       <c r="B321" t="inlineStr">
         <is>
-          <t>2026-07-11 08:13:18 PM PT</t>
+          <t>2026-07-11 08:15:18 PM PT</t>
         </is>
       </c>
       <c r="C321" t="n">
@@ -37497,7 +37497,7 @@
       </c>
       <c r="B322" t="inlineStr">
         <is>
-          <t>2026-07-11 08:13:18 PM PT</t>
+          <t>2026-07-11 08:15:18 PM PT</t>
         </is>
       </c>
       <c r="C322" t="n">
@@ -37611,7 +37611,7 @@
       </c>
       <c r="B323" t="inlineStr">
         <is>
-          <t>2026-07-11 08:13:18 PM PT</t>
+          <t>2026-07-11 08:15:18 PM PT</t>
         </is>
       </c>
       <c r="C323" t="n">
@@ -37725,7 +37725,7 @@
       </c>
       <c r="B324" t="inlineStr">
         <is>
-          <t>2026-07-11 08:13:18 PM PT</t>
+          <t>2026-07-11 08:15:18 PM PT</t>
         </is>
       </c>
       <c r="C324" t="n">
@@ -37839,7 +37839,7 @@
       </c>
       <c r="B325" t="inlineStr">
         <is>
-          <t>2026-07-11 08:13:18 PM PT</t>
+          <t>2026-07-11 08:15:18 PM PT</t>
         </is>
       </c>
       <c r="C325" t="n">
@@ -37953,7 +37953,7 @@
       </c>
       <c r="B326" t="inlineStr">
         <is>
-          <t>2026-07-11 08:13:18 PM PT</t>
+          <t>2026-07-11 08:15:18 PM PT</t>
         </is>
       </c>
       <c r="C326" t="n">
@@ -38067,7 +38067,7 @@
       </c>
       <c r="B327" t="inlineStr">
         <is>
-          <t>2026-07-11 08:13:19 PM PT</t>
+          <t>2026-07-11 08:15:19 PM PT</t>
         </is>
       </c>
       <c r="C327" t="n">
@@ -38095,10 +38095,10 @@
         <v>0</v>
       </c>
       <c r="I327" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="J327" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K327" t="inlineStr">
         <is>
@@ -38190,7 +38190,7 @@
       </c>
       <c r="B328" t="inlineStr">
         <is>
-          <t>2026-07-11 08:13:17 PM PT</t>
+          <t>2026-07-11 08:15:17 PM PT</t>
         </is>
       </c>
       <c r="C328" t="n">
@@ -38304,7 +38304,7 @@
       </c>
       <c r="B329" t="inlineStr">
         <is>
-          <t>2026-07-11 08:13:17 PM PT</t>
+          <t>2026-07-11 08:15:17 PM PT</t>
         </is>
       </c>
       <c r="C329" t="n">

--- a/live_mlb_hitter_fantasy_scores_2026_07_11.xlsx
+++ b/live_mlb_hitter_fantasy_scores_2026_07_11.xlsx
@@ -693,7 +693,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-07-11 08:15:16 PM PT</t>
+          <t>2026-07-11 08:17:16 PM PT</t>
         </is>
       </c>
       <c r="C2" t="n">
@@ -807,7 +807,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>2026-07-11 08:15:18 PM PT</t>
+          <t>2026-07-11 08:17:18 PM PT</t>
         </is>
       </c>
       <c r="C3" t="n">
@@ -921,7 +921,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-07-11 08:15:19 PM PT</t>
+          <t>2026-07-11 08:17:18 PM PT</t>
         </is>
       </c>
       <c r="C4" t="n">
@@ -934,7 +934,7 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Bottom 7 | 0 out</t>
+          <t>Bottom 7 | 1 out</t>
         </is>
       </c>
       <c r="F4" t="n">
@@ -946,13 +946,13 @@
         </is>
       </c>
       <c r="H4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I4" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="J4" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K4" t="inlineStr">
         <is>
@@ -1044,7 +1044,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>2026-07-11 08:15:18 PM PT</t>
+          <t>2026-07-11 08:17:18 PM PT</t>
         </is>
       </c>
       <c r="C5" t="n">
@@ -1158,7 +1158,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>2026-07-11 08:15:18 PM PT</t>
+          <t>2026-07-11 08:17:18 PM PT</t>
         </is>
       </c>
       <c r="C6" t="n">
@@ -1272,7 +1272,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>2026-07-11 08:15:17 PM PT</t>
+          <t>2026-07-11 08:17:17 PM PT</t>
         </is>
       </c>
       <c r="C7" t="n">
@@ -1386,7 +1386,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>2026-07-11 08:15:18 PM PT</t>
+          <t>2026-07-11 08:17:18 PM PT</t>
         </is>
       </c>
       <c r="C8" t="n">
@@ -1500,7 +1500,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>2026-07-11 08:15:17 PM PT</t>
+          <t>2026-07-11 08:17:17 PM PT</t>
         </is>
       </c>
       <c r="C9" t="n">
@@ -1614,7 +1614,7 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>2026-07-11 08:15:19 PM PT</t>
+          <t>2026-07-11 08:17:18 PM PT</t>
         </is>
       </c>
       <c r="C10" t="n">
@@ -1627,7 +1627,7 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Bottom 7 | 0 out</t>
+          <t>Bottom 7 | 1 out</t>
         </is>
       </c>
       <c r="F10" t="n">
@@ -1639,13 +1639,13 @@
         </is>
       </c>
       <c r="H10" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I10" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="J10" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K10" t="inlineStr">
         <is>
@@ -1737,7 +1737,7 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>2026-07-11 08:15:18 PM PT</t>
+          <t>2026-07-11 08:17:17 PM PT</t>
         </is>
       </c>
       <c r="C11" t="n">
@@ -1851,7 +1851,7 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>2026-07-11 08:15:18 PM PT</t>
+          <t>2026-07-11 08:17:18 PM PT</t>
         </is>
       </c>
       <c r="C12" t="n">
@@ -1965,7 +1965,7 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>2026-07-11 08:15:19 PM PT</t>
+          <t>2026-07-11 08:17:18 PM PT</t>
         </is>
       </c>
       <c r="C13" t="n">
@@ -1978,7 +1978,7 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Bottom 7 | 0 out</t>
+          <t>Bottom 7 | 1 out</t>
         </is>
       </c>
       <c r="F13" t="n">
@@ -1990,13 +1990,13 @@
         </is>
       </c>
       <c r="H13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I13" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="J13" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K13" t="inlineStr">
         <is>
@@ -2088,7 +2088,7 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>2026-07-11 08:15:18 PM PT</t>
+          <t>2026-07-11 08:17:18 PM PT</t>
         </is>
       </c>
       <c r="C14" t="n">
@@ -2202,7 +2202,7 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>2026-07-11 08:15:17 PM PT</t>
+          <t>2026-07-11 08:17:17 PM PT</t>
         </is>
       </c>
       <c r="C15" t="n">
@@ -2316,7 +2316,7 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>2026-07-11 08:15:18 PM PT</t>
+          <t>2026-07-11 08:17:18 PM PT</t>
         </is>
       </c>
       <c r="C16" t="n">
@@ -2430,7 +2430,7 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>2026-07-11 08:15:19 PM PT</t>
+          <t>2026-07-11 08:17:18 PM PT</t>
         </is>
       </c>
       <c r="C17" t="n">
@@ -2443,7 +2443,7 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Bottom 7 | 0 out</t>
+          <t>Bottom 7 | 1 out</t>
         </is>
       </c>
       <c r="F17" t="n">
@@ -2455,13 +2455,13 @@
         </is>
       </c>
       <c r="H17" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I17" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="J17" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K17" t="inlineStr">
         <is>
@@ -2553,7 +2553,7 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>2026-07-11 08:15:17 PM PT</t>
+          <t>2026-07-11 08:17:17 PM PT</t>
         </is>
       </c>
       <c r="C18" t="n">
@@ -2667,7 +2667,7 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>2026-07-11 08:15:18 PM PT</t>
+          <t>2026-07-11 08:17:18 PM PT</t>
         </is>
       </c>
       <c r="C19" t="n">
@@ -2781,7 +2781,7 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>2026-07-11 08:15:17 PM PT</t>
+          <t>2026-07-11 08:17:17 PM PT</t>
         </is>
       </c>
       <c r="C20" t="n">
@@ -2895,7 +2895,7 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>2026-07-11 08:15:17 PM PT</t>
+          <t>2026-07-11 08:17:17 PM PT</t>
         </is>
       </c>
       <c r="C21" t="n">
@@ -3009,7 +3009,7 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>2026-07-11 08:15:19 PM PT</t>
+          <t>2026-07-11 08:17:18 PM PT</t>
         </is>
       </c>
       <c r="C22" t="n">
@@ -3037,10 +3037,10 @@
         <v>1</v>
       </c>
       <c r="I22" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="J22" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K22" t="inlineStr">
         <is>
@@ -3132,7 +3132,7 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>2026-07-11 08:15:18 PM PT</t>
+          <t>2026-07-11 08:17:18 PM PT</t>
         </is>
       </c>
       <c r="C23" t="n">
@@ -3246,7 +3246,7 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>2026-07-11 08:15:17 PM PT</t>
+          <t>2026-07-11 08:17:17 PM PT</t>
         </is>
       </c>
       <c r="C24" t="n">
@@ -3360,7 +3360,7 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>2026-07-11 08:15:18 PM PT</t>
+          <t>2026-07-11 08:17:18 PM PT</t>
         </is>
       </c>
       <c r="C25" t="n">
@@ -3474,7 +3474,7 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>2026-07-11 08:15:16 PM PT</t>
+          <t>2026-07-11 08:17:16 PM PT</t>
         </is>
       </c>
       <c r="C26" t="n">
@@ -3588,7 +3588,7 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>2026-07-11 08:15:17 PM PT</t>
+          <t>2026-07-11 08:17:17 PM PT</t>
         </is>
       </c>
       <c r="C27" t="n">
@@ -3702,7 +3702,7 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>2026-07-11 08:15:18 PM PT</t>
+          <t>2026-07-11 08:17:17 PM PT</t>
         </is>
       </c>
       <c r="C28" t="n">
@@ -3816,7 +3816,7 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>2026-07-11 08:15:18 PM PT</t>
+          <t>2026-07-11 08:17:18 PM PT</t>
         </is>
       </c>
       <c r="C29" t="n">
@@ -3930,7 +3930,7 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>2026-07-11 08:15:18 PM PT</t>
+          <t>2026-07-11 08:17:18 PM PT</t>
         </is>
       </c>
       <c r="C30" t="n">
@@ -4044,7 +4044,7 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>2026-07-11 08:15:18 PM PT</t>
+          <t>2026-07-11 08:17:18 PM PT</t>
         </is>
       </c>
       <c r="C31" t="n">
@@ -4158,7 +4158,7 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>2026-07-11 08:15:18 PM PT</t>
+          <t>2026-07-11 08:17:17 PM PT</t>
         </is>
       </c>
       <c r="C32" t="n">
@@ -4272,7 +4272,7 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>2026-07-11 08:15:18 PM PT</t>
+          <t>2026-07-11 08:17:18 PM PT</t>
         </is>
       </c>
       <c r="C33" t="n">
@@ -4386,7 +4386,7 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>2026-07-11 08:15:16 PM PT</t>
+          <t>2026-07-11 08:17:16 PM PT</t>
         </is>
       </c>
       <c r="C34" t="n">
@@ -4500,7 +4500,7 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>2026-07-11 08:15:17 PM PT</t>
+          <t>2026-07-11 08:17:16 PM PT</t>
         </is>
       </c>
       <c r="C35" t="n">
@@ -4614,7 +4614,7 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>2026-07-11 08:15:19 PM PT</t>
+          <t>2026-07-11 08:17:18 PM PT</t>
         </is>
       </c>
       <c r="C36" t="n">
@@ -4627,7 +4627,7 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Bottom 7 | 0 out</t>
+          <t>Bottom 7 | 1 out</t>
         </is>
       </c>
       <c r="F36" t="n">
@@ -4639,13 +4639,13 @@
         </is>
       </c>
       <c r="H36" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I36" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="J36" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K36" t="inlineStr">
         <is>
@@ -4737,7 +4737,7 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>2026-07-11 08:15:18 PM PT</t>
+          <t>2026-07-11 08:17:17 PM PT</t>
         </is>
       </c>
       <c r="C37" t="n">
@@ -4851,7 +4851,7 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>2026-07-11 08:15:17 PM PT</t>
+          <t>2026-07-11 08:17:17 PM PT</t>
         </is>
       </c>
       <c r="C38" t="n">
@@ -4965,7 +4965,7 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>2026-07-11 08:15:18 PM PT</t>
+          <t>2026-07-11 08:17:18 PM PT</t>
         </is>
       </c>
       <c r="C39" t="n">
@@ -5079,7 +5079,7 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>2026-07-11 08:15:17 PM PT</t>
+          <t>2026-07-11 08:17:16 PM PT</t>
         </is>
       </c>
       <c r="C40" t="n">
@@ -5193,7 +5193,7 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>2026-07-11 08:15:19 PM PT</t>
+          <t>2026-07-11 08:17:18 PM PT</t>
         </is>
       </c>
       <c r="C41" t="n">
@@ -5221,10 +5221,10 @@
         <v>1</v>
       </c>
       <c r="I41" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="J41" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K41" t="inlineStr">
         <is>
@@ -5316,7 +5316,7 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>2026-07-11 08:15:18 PM PT</t>
+          <t>2026-07-11 08:17:18 PM PT</t>
         </is>
       </c>
       <c r="C42" t="n">
@@ -5430,7 +5430,7 @@
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>2026-07-11 08:15:18 PM PT</t>
+          <t>2026-07-11 08:17:18 PM PT</t>
         </is>
       </c>
       <c r="C43" t="n">
@@ -5544,7 +5544,7 @@
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>2026-07-11 08:15:18 PM PT</t>
+          <t>2026-07-11 08:17:18 PM PT</t>
         </is>
       </c>
       <c r="C44" t="n">
@@ -5658,7 +5658,7 @@
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>2026-07-11 08:15:18 PM PT</t>
+          <t>2026-07-11 08:17:18 PM PT</t>
         </is>
       </c>
       <c r="C45" t="n">
@@ -5772,7 +5772,7 @@
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>2026-07-11 08:15:18 PM PT</t>
+          <t>2026-07-11 08:17:18 PM PT</t>
         </is>
       </c>
       <c r="C46" t="n">
@@ -5886,7 +5886,7 @@
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>2026-07-11 08:15:17 PM PT</t>
+          <t>2026-07-11 08:17:17 PM PT</t>
         </is>
       </c>
       <c r="C47" t="n">
@@ -6000,7 +6000,7 @@
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>2026-07-11 08:15:18 PM PT</t>
+          <t>2026-07-11 08:17:18 PM PT</t>
         </is>
       </c>
       <c r="C48" t="n">
@@ -6114,7 +6114,7 @@
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>2026-07-11 08:15:17 PM PT</t>
+          <t>2026-07-11 08:17:17 PM PT</t>
         </is>
       </c>
       <c r="C49" t="n">
@@ -6228,7 +6228,7 @@
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>2026-07-11 08:15:17 PM PT</t>
+          <t>2026-07-11 08:17:16 PM PT</t>
         </is>
       </c>
       <c r="C50" t="n">
@@ -6342,7 +6342,7 @@
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>2026-07-11 08:15:18 PM PT</t>
+          <t>2026-07-11 08:17:18 PM PT</t>
         </is>
       </c>
       <c r="C51" t="n">
@@ -6456,7 +6456,7 @@
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>2026-07-11 08:15:18 PM PT</t>
+          <t>2026-07-11 08:17:18 PM PT</t>
         </is>
       </c>
       <c r="C52" t="n">
@@ -6570,7 +6570,7 @@
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>2026-07-11 08:15:18 PM PT</t>
+          <t>2026-07-11 08:17:18 PM PT</t>
         </is>
       </c>
       <c r="C53" t="n">
@@ -6684,7 +6684,7 @@
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>2026-07-11 08:15:17 PM PT</t>
+          <t>2026-07-11 08:17:17 PM PT</t>
         </is>
       </c>
       <c r="C54" t="n">
@@ -6798,7 +6798,7 @@
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>2026-07-11 08:15:17 PM PT</t>
+          <t>2026-07-11 08:17:17 PM PT</t>
         </is>
       </c>
       <c r="C55" t="n">
@@ -6912,7 +6912,7 @@
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>2026-07-11 08:15:17 PM PT</t>
+          <t>2026-07-11 08:17:17 PM PT</t>
         </is>
       </c>
       <c r="C56" t="n">
@@ -7026,7 +7026,7 @@
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>2026-07-11 08:15:18 PM PT</t>
+          <t>2026-07-11 08:17:18 PM PT</t>
         </is>
       </c>
       <c r="C57" t="n">
@@ -7140,7 +7140,7 @@
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>2026-07-11 08:15:17 PM PT</t>
+          <t>2026-07-11 08:17:17 PM PT</t>
         </is>
       </c>
       <c r="C58" t="n">
@@ -7254,7 +7254,7 @@
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>2026-07-11 08:15:17 PM PT</t>
+          <t>2026-07-11 08:17:17 PM PT</t>
         </is>
       </c>
       <c r="C59" t="n">
@@ -7368,7 +7368,7 @@
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>2026-07-11 08:15:16 PM PT</t>
+          <t>2026-07-11 08:17:16 PM PT</t>
         </is>
       </c>
       <c r="C60" t="n">
@@ -7482,7 +7482,7 @@
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>2026-07-11 08:15:16 PM PT</t>
+          <t>2026-07-11 08:17:16 PM PT</t>
         </is>
       </c>
       <c r="C61" t="n">
@@ -7596,7 +7596,7 @@
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>2026-07-11 08:15:19 PM PT</t>
+          <t>2026-07-11 08:17:18 PM PT</t>
         </is>
       </c>
       <c r="C62" t="n">
@@ -7609,7 +7609,7 @@
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>Bottom 7 | 0 out</t>
+          <t>Bottom 7 | 1 out</t>
         </is>
       </c>
       <c r="F62" t="n">
@@ -7621,13 +7621,13 @@
         </is>
       </c>
       <c r="H62" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I62" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="J62" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K62" t="inlineStr">
         <is>
@@ -7719,30 +7719,39 @@
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>2026-07-11 08:15:17 PM PT</t>
+          <t>2026-07-11 08:17:18 PM PT</t>
         </is>
       </c>
       <c r="C63" t="n">
-        <v>824576</v>
+        <v>823926</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>11:10 AM PT</t>
+          <t>6:10 PM PT</t>
         </is>
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>Final</t>
+          <t>Top 7 | 1 out</t>
         </is>
       </c>
       <c r="F63" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="G63" t="inlineStr">
         <is>
           <t>Top</t>
         </is>
       </c>
+      <c r="H63" t="n">
+        <v>1</v>
+      </c>
+      <c r="I63" t="n">
+        <v>3</v>
+      </c>
+      <c r="J63" t="n">
+        <v>2</v>
+      </c>
       <c r="K63" t="inlineStr">
         <is>
           <t>Away</t>
@@ -7750,21 +7759,21 @@
       </c>
       <c r="L63" t="inlineStr">
         <is>
-          <t>ATH</t>
+          <t>ARI</t>
         </is>
       </c>
       <c r="M63" t="inlineStr">
         <is>
-          <t>CWS</t>
+          <t>LAD</t>
         </is>
       </c>
       <c r="N63" t="inlineStr">
         <is>
-          <t>Jacob Wilson</t>
+          <t>Geraldo Perdomo</t>
         </is>
       </c>
       <c r="O63" t="n">
-        <v>805779</v>
+        <v>672695</v>
       </c>
       <c r="P63" t="inlineStr">
         <is>
@@ -7773,44 +7782,44 @@
       </c>
       <c r="Q63" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="R63" t="n">
         <v>4</v>
       </c>
       <c r="S63" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="T63" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="U63" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="V63" t="n">
         <v>0</v>
       </c>
-      <c r="W63" s="8" t="n">
-        <v>1</v>
+      <c r="W63" t="n">
+        <v>0</v>
       </c>
       <c r="X63" t="n">
         <v>0</v>
       </c>
       <c r="Y63" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Z63" t="n">
         <v>0</v>
       </c>
-      <c r="AA63" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB63" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC63" t="n">
-        <v>0</v>
+      <c r="AA63" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="AB63" s="9" t="n">
+        <v>1</v>
+      </c>
+      <c r="AC63" s="6" t="n">
+        <v>1</v>
       </c>
       <c r="AD63" t="n">
         <v>0</v>
@@ -7819,10 +7828,10 @@
         <v>11</v>
       </c>
       <c r="AF63" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="AG63" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
     </row>
     <row r="64">
@@ -7833,15 +7842,15 @@
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>2026-07-11 08:15:18 PM PT</t>
+          <t>2026-07-11 08:17:17 PM PT</t>
         </is>
       </c>
       <c r="C64" t="n">
-        <v>824249</v>
+        <v>824576</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>3:10 PM PT</t>
+          <t>11:10 AM PT</t>
         </is>
       </c>
       <c r="E64" t="inlineStr">
@@ -7854,7 +7863,7 @@
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>Bottom</t>
+          <t>Top</t>
         </is>
       </c>
       <c r="K64" t="inlineStr">
@@ -7864,30 +7873,30 @@
       </c>
       <c r="L64" t="inlineStr">
         <is>
-          <t>PHI</t>
+          <t>ATH</t>
         </is>
       </c>
       <c r="M64" t="inlineStr">
         <is>
-          <t>DET</t>
+          <t>CWS</t>
         </is>
       </c>
       <c r="N64" t="inlineStr">
         <is>
-          <t>J.T. Realmuto</t>
+          <t>Jacob Wilson</t>
         </is>
       </c>
       <c r="O64" t="n">
-        <v>592663</v>
+        <v>805779</v>
       </c>
       <c r="P64" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>SS</t>
         </is>
       </c>
       <c r="Q64" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>1</t>
         </is>
       </c>
       <c r="R64" t="n">
@@ -7897,25 +7906,25 @@
         <v>4</v>
       </c>
       <c r="T64" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="U64" t="n">
-        <v>0</v>
-      </c>
-      <c r="V64" s="7" t="n">
-        <v>1</v>
-      </c>
-      <c r="W64" t="n">
-        <v>0</v>
+        <v>1</v>
+      </c>
+      <c r="V64" t="n">
+        <v>0</v>
+      </c>
+      <c r="W64" s="8" t="n">
+        <v>1</v>
       </c>
       <c r="X64" t="n">
         <v>0</v>
       </c>
       <c r="Y64" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Z64" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AA64" t="n">
         <v>0</v>
@@ -7927,16 +7936,16 @@
         <v>0</v>
       </c>
       <c r="AD64" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AE64" s="4" t="n">
         <v>11</v>
       </c>
       <c r="AF64" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="AG64" t="n">
-        <v>7</v>
+        <v>4</v>
       </c>
     </row>
     <row r="65">
@@ -7947,101 +7956,92 @@
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>2026-07-11 08:15:19 PM PT</t>
+          <t>2026-07-11 08:17:18 PM PT</t>
         </is>
       </c>
       <c r="C65" t="n">
-        <v>823276</v>
+        <v>824249</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>5:40 PM PT</t>
+          <t>3:10 PM PT</t>
         </is>
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>Bottom 7 | 0 out</t>
+          <t>Final</t>
         </is>
       </c>
       <c r="F65" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="G65" t="inlineStr">
         <is>
           <t>Bottom</t>
         </is>
       </c>
-      <c r="H65" t="n">
-        <v>0</v>
-      </c>
-      <c r="I65" t="n">
+      <c r="K65" t="inlineStr">
+        <is>
+          <t>Away</t>
+        </is>
+      </c>
+      <c r="L65" t="inlineStr">
+        <is>
+          <t>PHI</t>
+        </is>
+      </c>
+      <c r="M65" t="inlineStr">
+        <is>
+          <t>DET</t>
+        </is>
+      </c>
+      <c r="N65" t="inlineStr">
+        <is>
+          <t>J.T. Realmuto</t>
+        </is>
+      </c>
+      <c r="O65" t="n">
+        <v>592663</v>
+      </c>
+      <c r="P65" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="Q65" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="R65" t="n">
+        <v>4</v>
+      </c>
+      <c r="S65" t="n">
+        <v>4</v>
+      </c>
+      <c r="T65" t="n">
+        <v>1</v>
+      </c>
+      <c r="U65" t="n">
+        <v>0</v>
+      </c>
+      <c r="V65" s="7" t="n">
+        <v>1</v>
+      </c>
+      <c r="W65" t="n">
+        <v>0</v>
+      </c>
+      <c r="X65" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y65" t="n">
+        <v>1</v>
+      </c>
+      <c r="Z65" t="n">
         <v>2</v>
       </c>
-      <c r="J65" t="n">
-        <v>1</v>
-      </c>
-      <c r="K65" t="inlineStr">
-        <is>
-          <t>Home</t>
-        </is>
-      </c>
-      <c r="L65" t="inlineStr">
-        <is>
-          <t>SD</t>
-        </is>
-      </c>
-      <c r="M65" t="inlineStr">
-        <is>
-          <t>TOR</t>
-        </is>
-      </c>
-      <c r="N65" t="inlineStr">
-        <is>
-          <t>Jackson Merrill</t>
-        </is>
-      </c>
-      <c r="O65" t="n">
-        <v>701538</v>
-      </c>
-      <c r="P65" t="inlineStr">
-        <is>
-          <t>CF</t>
-        </is>
-      </c>
-      <c r="Q65" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="R65" t="n">
-        <v>4</v>
-      </c>
-      <c r="S65" t="n">
-        <v>2</v>
-      </c>
-      <c r="T65" t="n">
-        <v>1</v>
-      </c>
-      <c r="U65" t="n">
-        <v>1</v>
-      </c>
-      <c r="V65" t="n">
-        <v>0</v>
-      </c>
-      <c r="W65" t="n">
-        <v>0</v>
-      </c>
-      <c r="X65" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y65" t="n">
-        <v>2</v>
-      </c>
-      <c r="Z65" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA65" s="5" t="n">
-        <v>2</v>
+      <c r="AA65" t="n">
+        <v>0</v>
       </c>
       <c r="AB65" t="n">
         <v>0</v>
@@ -8050,13 +8050,13 @@
         <v>0</v>
       </c>
       <c r="AD65" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AE65" s="4" t="n">
         <v>11</v>
       </c>
       <c r="AF65" t="n">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="AG65" t="n">
         <v>7</v>
@@ -8070,52 +8070,61 @@
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>2026-07-11 08:15:18 PM PT</t>
+          <t>2026-07-11 08:17:18 PM PT</t>
         </is>
       </c>
       <c r="C66" t="n">
-        <v>823844</v>
+        <v>823276</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>1:10 PM PT</t>
+          <t>5:40 PM PT</t>
         </is>
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>Final</t>
+          <t>Bottom 7 | 1 out</t>
         </is>
       </c>
       <c r="F66" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="G66" t="inlineStr">
         <is>
           <t>Bottom</t>
         </is>
       </c>
+      <c r="H66" t="n">
+        <v>1</v>
+      </c>
+      <c r="I66" t="n">
+        <v>0</v>
+      </c>
+      <c r="J66" t="n">
+        <v>0</v>
+      </c>
       <c r="K66" t="inlineStr">
         <is>
-          <t>Away</t>
+          <t>Home</t>
         </is>
       </c>
       <c r="L66" t="inlineStr">
         <is>
-          <t>CLE</t>
+          <t>SD</t>
         </is>
       </c>
       <c r="M66" t="inlineStr">
         <is>
-          <t>MIA</t>
+          <t>TOR</t>
         </is>
       </c>
       <c r="N66" t="inlineStr">
         <is>
-          <t>Petey Halpin</t>
+          <t>Jackson Merrill</t>
         </is>
       </c>
       <c r="O66" t="n">
-        <v>690984</v>
+        <v>701538</v>
       </c>
       <c r="P66" t="inlineStr">
         <is>
@@ -8124,14 +8133,14 @@
       </c>
       <c r="Q66" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>2</t>
         </is>
       </c>
       <c r="R66" t="n">
         <v>4</v>
       </c>
       <c r="S66" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="T66" t="n">
         <v>1</v>
@@ -8149,31 +8158,31 @@
         <v>0</v>
       </c>
       <c r="Y66" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="Z66" t="n">
         <v>0</v>
       </c>
-      <c r="AA66" t="n">
-        <v>0</v>
+      <c r="AA66" s="5" t="n">
+        <v>2</v>
       </c>
       <c r="AB66" t="n">
         <v>0</v>
       </c>
-      <c r="AC66" s="6" t="n">
-        <v>1</v>
+      <c r="AC66" t="n">
+        <v>0</v>
       </c>
       <c r="AD66" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="AE66" s="4" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="AF66" t="n">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="AG66" t="n">
-        <v>11</v>
+        <v>7</v>
       </c>
     </row>
     <row r="67">
@@ -8184,15 +8193,15 @@
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>2026-07-11 08:15:17 PM PT</t>
+          <t>2026-07-11 08:17:18 PM PT</t>
         </is>
       </c>
       <c r="C67" t="n">
-        <v>824576</v>
+        <v>823844</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>11:10 AM PT</t>
+          <t>1:10 PM PT</t>
         </is>
       </c>
       <c r="E67" t="inlineStr">
@@ -8205,89 +8214,89 @@
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>Top</t>
+          <t>Bottom</t>
         </is>
       </c>
       <c r="K67" t="inlineStr">
         <is>
-          <t>Home</t>
+          <t>Away</t>
         </is>
       </c>
       <c r="L67" t="inlineStr">
         <is>
-          <t>CWS</t>
+          <t>CLE</t>
         </is>
       </c>
       <c r="M67" t="inlineStr">
         <is>
-          <t>ATH</t>
+          <t>MIA</t>
         </is>
       </c>
       <c r="N67" t="inlineStr">
         <is>
-          <t>Chase Meidroth</t>
+          <t>Petey Halpin</t>
         </is>
       </c>
       <c r="O67" t="n">
-        <v>805367</v>
+        <v>690984</v>
       </c>
       <c r="P67" t="inlineStr">
         <is>
-          <t>2B</t>
+          <t>CF</t>
         </is>
       </c>
       <c r="Q67" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>7</t>
         </is>
       </c>
       <c r="R67" t="n">
+        <v>4</v>
+      </c>
+      <c r="S67" t="n">
+        <v>4</v>
+      </c>
+      <c r="T67" t="n">
+        <v>1</v>
+      </c>
+      <c r="U67" t="n">
+        <v>1</v>
+      </c>
+      <c r="V67" t="n">
+        <v>0</v>
+      </c>
+      <c r="W67" t="n">
+        <v>0</v>
+      </c>
+      <c r="X67" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y67" t="n">
+        <v>1</v>
+      </c>
+      <c r="Z67" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA67" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB67" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC67" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="AD67" t="n">
         <v>3</v>
-      </c>
-      <c r="S67" t="n">
-        <v>3</v>
-      </c>
-      <c r="T67" t="n">
-        <v>2</v>
-      </c>
-      <c r="U67" t="n">
-        <v>1</v>
-      </c>
-      <c r="V67" s="7" t="n">
-        <v>1</v>
-      </c>
-      <c r="W67" t="n">
-        <v>0</v>
-      </c>
-      <c r="X67" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y67" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z67" t="n">
-        <v>1</v>
-      </c>
-      <c r="AA67" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB67" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC67" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD67" t="n">
-        <v>0</v>
       </c>
       <c r="AE67" s="4" t="n">
         <v>10</v>
       </c>
       <c r="AF67" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="AG67" t="n">
-        <v>5</v>
+        <v>11</v>
       </c>
     </row>
     <row r="68">
@@ -8298,11 +8307,11 @@
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>2026-07-11 08:15:17 PM PT</t>
+          <t>2026-07-11 08:17:17 PM PT</t>
         </is>
       </c>
       <c r="C68" t="n">
-        <v>823682</v>
+        <v>824576</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -8324,42 +8333,42 @@
       </c>
       <c r="K68" t="inlineStr">
         <is>
-          <t>Away</t>
+          <t>Home</t>
         </is>
       </c>
       <c r="L68" t="inlineStr">
         <is>
-          <t>LAA</t>
+          <t>CWS</t>
         </is>
       </c>
       <c r="M68" t="inlineStr">
         <is>
-          <t>MIN</t>
+          <t>ATH</t>
         </is>
       </c>
       <c r="N68" t="inlineStr">
         <is>
-          <t>Mike Trout</t>
+          <t>Chase Meidroth</t>
         </is>
       </c>
       <c r="O68" t="n">
-        <v>545361</v>
+        <v>805367</v>
       </c>
       <c r="P68" t="inlineStr">
         <is>
-          <t>CF</t>
+          <t>2B</t>
         </is>
       </c>
       <c r="Q68" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>5</t>
         </is>
       </c>
       <c r="R68" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="S68" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="T68" t="n">
         <v>2</v>
@@ -8377,10 +8386,10 @@
         <v>0</v>
       </c>
       <c r="Y68" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Z68" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AA68" t="n">
         <v>0</v>
@@ -8392,16 +8401,16 @@
         <v>0</v>
       </c>
       <c r="AD68" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AE68" s="4" t="n">
         <v>10</v>
       </c>
       <c r="AF68" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="AG68" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
     </row>
     <row r="69">
@@ -8412,61 +8421,52 @@
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>2026-07-11 08:15:19 PM PT</t>
+          <t>2026-07-11 08:17:17 PM PT</t>
         </is>
       </c>
       <c r="C69" t="n">
-        <v>823926</v>
+        <v>823682</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>6:10 PM PT</t>
+          <t>11:10 AM PT</t>
         </is>
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>Top 7 | 1 out</t>
+          <t>Final</t>
         </is>
       </c>
       <c r="F69" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="G69" t="inlineStr">
         <is>
           <t>Top</t>
         </is>
       </c>
-      <c r="H69" t="n">
-        <v>1</v>
-      </c>
-      <c r="I69" t="n">
-        <v>1</v>
-      </c>
-      <c r="J69" t="n">
-        <v>1</v>
-      </c>
       <c r="K69" t="inlineStr">
         <is>
-          <t>Home</t>
+          <t>Away</t>
         </is>
       </c>
       <c r="L69" t="inlineStr">
         <is>
-          <t>LAD</t>
+          <t>LAA</t>
         </is>
       </c>
       <c r="M69" t="inlineStr">
         <is>
-          <t>ARI</t>
+          <t>MIN</t>
         </is>
       </c>
       <c r="N69" t="inlineStr">
         <is>
-          <t>Andy Pages</t>
+          <t>Mike Trout</t>
         </is>
       </c>
       <c r="O69" t="n">
-        <v>681624</v>
+        <v>545361</v>
       </c>
       <c r="P69" t="inlineStr">
         <is>
@@ -8479,19 +8479,19 @@
         </is>
       </c>
       <c r="R69" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="S69" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="T69" t="n">
         <v>2</v>
       </c>
       <c r="U69" t="n">
-        <v>2</v>
-      </c>
-      <c r="V69" t="n">
-        <v>0</v>
+        <v>1</v>
+      </c>
+      <c r="V69" s="7" t="n">
+        <v>1</v>
       </c>
       <c r="W69" t="n">
         <v>0</v>
@@ -8503,7 +8503,7 @@
         <v>1</v>
       </c>
       <c r="Z69" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AA69" t="n">
         <v>0</v>
@@ -8515,16 +8515,16 @@
         <v>0</v>
       </c>
       <c r="AD69" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AE69" s="4" t="n">
         <v>10</v>
       </c>
       <c r="AF69" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AG69" t="n">
-        <v>6</v>
+        <v>10</v>
       </c>
     </row>
     <row r="70">
@@ -8535,61 +8535,70 @@
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>2026-07-11 08:15:17 PM PT</t>
+          <t>2026-07-11 08:17:18 PM PT</t>
         </is>
       </c>
       <c r="C70" t="n">
-        <v>823356</v>
+        <v>823926</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>1:05 PM PT</t>
+          <t>6:10 PM PT</t>
         </is>
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>Final</t>
+          <t>Top 7 | 1 out</t>
         </is>
       </c>
       <c r="F70" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="G70" t="inlineStr">
         <is>
           <t>Top</t>
         </is>
       </c>
+      <c r="H70" t="n">
+        <v>1</v>
+      </c>
+      <c r="I70" t="n">
+        <v>3</v>
+      </c>
+      <c r="J70" t="n">
+        <v>2</v>
+      </c>
       <c r="K70" t="inlineStr">
         <is>
-          <t>Away</t>
+          <t>Home</t>
         </is>
       </c>
       <c r="L70" t="inlineStr">
         <is>
-          <t>MIL</t>
+          <t>LAD</t>
         </is>
       </c>
       <c r="M70" t="inlineStr">
         <is>
-          <t>PIT</t>
+          <t>ARI</t>
         </is>
       </c>
       <c r="N70" t="inlineStr">
         <is>
-          <t>Joey Ortiz</t>
+          <t>Andy Pages</t>
         </is>
       </c>
       <c r="O70" t="n">
-        <v>687401</v>
+        <v>681624</v>
       </c>
       <c r="P70" t="inlineStr">
         <is>
-          <t>3B</t>
+          <t>CF</t>
         </is>
       </c>
       <c r="Q70" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>2</t>
         </is>
       </c>
       <c r="R70" t="n">
@@ -8602,10 +8611,10 @@
         <v>2</v>
       </c>
       <c r="U70" t="n">
-        <v>1</v>
-      </c>
-      <c r="V70" s="7" t="n">
-        <v>1</v>
+        <v>2</v>
+      </c>
+      <c r="V70" t="n">
+        <v>0</v>
       </c>
       <c r="W70" t="n">
         <v>0</v>
@@ -8617,7 +8626,7 @@
         <v>1</v>
       </c>
       <c r="Z70" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AA70" t="n">
         <v>0</v>
@@ -8638,7 +8647,7 @@
         <v>2</v>
       </c>
       <c r="AG70" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
     </row>
     <row r="71">
@@ -8649,11 +8658,11 @@
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>2026-07-11 08:15:17 PM PT</t>
+          <t>2026-07-11 08:17:16 PM PT</t>
         </is>
       </c>
       <c r="C71" t="n">
-        <v>822711</v>
+        <v>823356</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
@@ -8670,7 +8679,7 @@
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>Bottom</t>
+          <t>Top</t>
         </is>
       </c>
       <c r="K71" t="inlineStr">
@@ -8680,46 +8689,46 @@
       </c>
       <c r="L71" t="inlineStr">
         <is>
-          <t>NYY</t>
+          <t>MIL</t>
         </is>
       </c>
       <c r="M71" t="inlineStr">
         <is>
-          <t>WSH</t>
+          <t>PIT</t>
         </is>
       </c>
       <c r="N71" t="inlineStr">
         <is>
-          <t>Ben Rice</t>
+          <t>Joey Ortiz</t>
         </is>
       </c>
       <c r="O71" t="n">
-        <v>700250</v>
+        <v>687401</v>
       </c>
       <c r="P71" t="inlineStr">
         <is>
-          <t>DH</t>
+          <t>3B</t>
         </is>
       </c>
       <c r="Q71" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>9</t>
         </is>
       </c>
       <c r="R71" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="S71" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="T71" t="n">
         <v>2</v>
       </c>
       <c r="U71" t="n">
-        <v>2</v>
-      </c>
-      <c r="V71" t="n">
-        <v>0</v>
+        <v>1</v>
+      </c>
+      <c r="V71" s="7" t="n">
+        <v>1</v>
       </c>
       <c r="W71" t="n">
         <v>0</v>
@@ -8728,13 +8737,13 @@
         <v>0</v>
       </c>
       <c r="Y71" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Z71" t="n">
         <v>0</v>
       </c>
-      <c r="AA71" s="5" t="n">
-        <v>2</v>
+      <c r="AA71" t="n">
+        <v>0</v>
       </c>
       <c r="AB71" t="n">
         <v>0</v>
@@ -8749,10 +8758,10 @@
         <v>10</v>
       </c>
       <c r="AF71" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="AG71" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
     </row>
     <row r="72">
@@ -8763,11 +8772,11 @@
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>2026-07-11 08:15:17 PM PT</t>
+          <t>2026-07-11 08:17:17 PM PT</t>
         </is>
       </c>
       <c r="C72" t="n">
-        <v>823356</v>
+        <v>822711</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
@@ -8784,35 +8793,35 @@
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>Top</t>
+          <t>Bottom</t>
         </is>
       </c>
       <c r="K72" t="inlineStr">
         <is>
-          <t>Home</t>
+          <t>Away</t>
         </is>
       </c>
       <c r="L72" t="inlineStr">
         <is>
-          <t>PIT</t>
+          <t>NYY</t>
         </is>
       </c>
       <c r="M72" t="inlineStr">
         <is>
-          <t>MIL</t>
+          <t>WSH</t>
         </is>
       </c>
       <c r="N72" t="inlineStr">
         <is>
-          <t>Brandon Lowe</t>
+          <t>Ben Rice</t>
         </is>
       </c>
       <c r="O72" t="n">
-        <v>664040</v>
+        <v>700250</v>
       </c>
       <c r="P72" t="inlineStr">
         <is>
-          <t>2B</t>
+          <t>DH</t>
         </is>
       </c>
       <c r="Q72" t="inlineStr">
@@ -8824,16 +8833,16 @@
         <v>4</v>
       </c>
       <c r="S72" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="T72" t="n">
         <v>2</v>
       </c>
       <c r="U72" t="n">
-        <v>1</v>
-      </c>
-      <c r="V72" s="7" t="n">
-        <v>1</v>
+        <v>2</v>
+      </c>
+      <c r="V72" t="n">
+        <v>0</v>
       </c>
       <c r="W72" t="n">
         <v>0</v>
@@ -8842,13 +8851,13 @@
         <v>0</v>
       </c>
       <c r="Y72" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Z72" t="n">
         <v>0</v>
       </c>
-      <c r="AA72" t="n">
-        <v>0</v>
+      <c r="AA72" s="5" t="n">
+        <v>2</v>
       </c>
       <c r="AB72" t="n">
         <v>0</v>
@@ -8857,16 +8866,16 @@
         <v>0</v>
       </c>
       <c r="AD72" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AE72" s="4" t="n">
         <v>10</v>
       </c>
       <c r="AF72" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="AG72" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
     </row>
     <row r="73">
@@ -8877,86 +8886,77 @@
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>2026-07-11 08:15:19 PM PT</t>
+          <t>2026-07-11 08:17:16 PM PT</t>
         </is>
       </c>
       <c r="C73" t="n">
-        <v>823276</v>
+        <v>823356</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>5:40 PM PT</t>
+          <t>1:05 PM PT</t>
         </is>
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>Bottom 7 | 0 out</t>
+          <t>Final</t>
         </is>
       </c>
       <c r="F73" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>Bottom</t>
-        </is>
-      </c>
-      <c r="H73" t="n">
-        <v>0</v>
-      </c>
-      <c r="I73" t="n">
+          <t>Top</t>
+        </is>
+      </c>
+      <c r="K73" t="inlineStr">
+        <is>
+          <t>Home</t>
+        </is>
+      </c>
+      <c r="L73" t="inlineStr">
+        <is>
+          <t>PIT</t>
+        </is>
+      </c>
+      <c r="M73" t="inlineStr">
+        <is>
+          <t>MIL</t>
+        </is>
+      </c>
+      <c r="N73" t="inlineStr">
+        <is>
+          <t>Brandon Lowe</t>
+        </is>
+      </c>
+      <c r="O73" t="n">
+        <v>664040</v>
+      </c>
+      <c r="P73" t="inlineStr">
+        <is>
+          <t>2B</t>
+        </is>
+      </c>
+      <c r="Q73" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="R73" t="n">
+        <v>4</v>
+      </c>
+      <c r="S73" t="n">
+        <v>4</v>
+      </c>
+      <c r="T73" t="n">
         <v>2</v>
       </c>
-      <c r="J73" t="n">
-        <v>1</v>
-      </c>
-      <c r="K73" t="inlineStr">
-        <is>
-          <t>Away</t>
-        </is>
-      </c>
-      <c r="L73" t="inlineStr">
-        <is>
-          <t>TOR</t>
-        </is>
-      </c>
-      <c r="M73" t="inlineStr">
-        <is>
-          <t>SD</t>
-        </is>
-      </c>
-      <c r="N73" t="inlineStr">
-        <is>
-          <t>Ernie Clement</t>
-        </is>
-      </c>
-      <c r="O73" t="n">
-        <v>676391</v>
-      </c>
-      <c r="P73" t="inlineStr">
-        <is>
-          <t>2B</t>
-        </is>
-      </c>
-      <c r="Q73" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="R73" t="n">
-        <v>4</v>
-      </c>
-      <c r="S73" t="n">
-        <v>3</v>
-      </c>
-      <c r="T73" t="n">
-        <v>1</v>
-      </c>
       <c r="U73" t="n">
         <v>1</v>
       </c>
-      <c r="V73" t="n">
-        <v>0</v>
+      <c r="V73" s="7" t="n">
+        <v>1</v>
       </c>
       <c r="W73" t="n">
         <v>0</v>
@@ -8965,31 +8965,31 @@
         <v>0</v>
       </c>
       <c r="Y73" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Z73" t="n">
         <v>0</v>
       </c>
-      <c r="AA73" s="5" t="n">
-        <v>1</v>
+      <c r="AA73" t="n">
+        <v>0</v>
       </c>
       <c r="AB73" t="n">
         <v>0</v>
       </c>
-      <c r="AC73" s="6" t="n">
-        <v>1</v>
+      <c r="AC73" t="n">
+        <v>0</v>
       </c>
       <c r="AD73" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AE73" s="4" t="n">
         <v>10</v>
       </c>
       <c r="AF73" t="n">
+        <v>3</v>
+      </c>
+      <c r="AG73" t="n">
         <v>7</v>
-      </c>
-      <c r="AG73" t="n">
-        <v>6</v>
       </c>
     </row>
     <row r="74">
@@ -9000,20 +9000,20 @@
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>2026-07-11 08:15:19 PM PT</t>
+          <t>2026-07-11 08:17:18 PM PT</t>
         </is>
       </c>
       <c r="C74" t="n">
-        <v>823926</v>
+        <v>823276</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>6:10 PM PT</t>
+          <t>5:40 PM PT</t>
         </is>
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>Top 7 | 1 out</t>
+          <t>Bottom 7 | 1 out</t>
         </is>
       </c>
       <c r="F74" t="n">
@@ -9021,17 +9021,17 @@
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>Top</t>
+          <t>Bottom</t>
         </is>
       </c>
       <c r="H74" t="n">
         <v>1</v>
       </c>
       <c r="I74" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J74" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K74" t="inlineStr">
         <is>
@@ -9040,38 +9040,38 @@
       </c>
       <c r="L74" t="inlineStr">
         <is>
-          <t>ARI</t>
+          <t>TOR</t>
         </is>
       </c>
       <c r="M74" t="inlineStr">
         <is>
-          <t>LAD</t>
+          <t>SD</t>
         </is>
       </c>
       <c r="N74" t="inlineStr">
         <is>
-          <t>Gabriel Moreno</t>
+          <t>Ernie Clement</t>
         </is>
       </c>
       <c r="O74" t="n">
-        <v>672515</v>
+        <v>676391</v>
       </c>
       <c r="P74" t="inlineStr">
         <is>
-          <t>DH</t>
+          <t>2B</t>
         </is>
       </c>
       <c r="Q74" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>1</t>
         </is>
       </c>
       <c r="R74" t="n">
+        <v>4</v>
+      </c>
+      <c r="S74" t="n">
         <v>3</v>
       </c>
-      <c r="S74" t="n">
-        <v>2</v>
-      </c>
       <c r="T74" t="n">
         <v>1</v>
       </c>
@@ -9088,7 +9088,7 @@
         <v>0</v>
       </c>
       <c r="Y74" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="Z74" t="n">
         <v>0</v>
@@ -9099,20 +9099,20 @@
       <c r="AB74" t="n">
         <v>0</v>
       </c>
-      <c r="AC74" t="n">
-        <v>0</v>
+      <c r="AC74" s="6" t="n">
+        <v>1</v>
       </c>
       <c r="AD74" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AE74" s="4" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AF74" t="n">
+        <v>7</v>
+      </c>
+      <c r="AG74" t="n">
         <v>6</v>
-      </c>
-      <c r="AG74" t="n">
-        <v>5</v>
       </c>
     </row>
     <row r="75">
@@ -9123,29 +9123,38 @@
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>2026-07-11 08:15:18 PM PT</t>
+          <t>2026-07-11 08:17:18 PM PT</t>
         </is>
       </c>
       <c r="C75" t="n">
-        <v>824492</v>
+        <v>823926</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>4:10 PM PT</t>
+          <t>6:10 PM PT</t>
         </is>
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>Final</t>
+          <t>Top 7 | 1 out</t>
         </is>
       </c>
       <c r="F75" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>Bottom</t>
-        </is>
+          <t>Top</t>
+        </is>
+      </c>
+      <c r="H75" t="n">
+        <v>1</v>
+      </c>
+      <c r="I75" t="n">
+        <v>3</v>
+      </c>
+      <c r="J75" t="n">
+        <v>2</v>
       </c>
       <c r="K75" t="inlineStr">
         <is>
@@ -9154,37 +9163,37 @@
       </c>
       <c r="L75" t="inlineStr">
         <is>
-          <t>CHC</t>
+          <t>ARI</t>
         </is>
       </c>
       <c r="M75" t="inlineStr">
         <is>
-          <t>CIN</t>
+          <t>LAD</t>
         </is>
       </c>
       <c r="N75" t="inlineStr">
         <is>
-          <t>Seiya Suzuki</t>
+          <t>Gabriel Moreno</t>
         </is>
       </c>
       <c r="O75" t="n">
-        <v>673548</v>
+        <v>672515</v>
       </c>
       <c r="P75" t="inlineStr">
         <is>
-          <t>RF</t>
+          <t>DH</t>
         </is>
       </c>
       <c r="Q75" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>4</t>
         </is>
       </c>
       <c r="R75" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="S75" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="T75" t="n">
         <v>1</v>
@@ -9202,10 +9211,10 @@
         <v>0</v>
       </c>
       <c r="Y75" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="Z75" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AA75" s="5" t="n">
         <v>1</v>
@@ -9223,10 +9232,10 @@
         <v>9</v>
       </c>
       <c r="AF75" t="n">
+        <v>6</v>
+      </c>
+      <c r="AG75" t="n">
         <v>5</v>
-      </c>
-      <c r="AG75" t="n">
-        <v>9</v>
       </c>
     </row>
     <row r="76">
@@ -9237,7 +9246,7 @@
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>2026-07-11 08:15:18 PM PT</t>
+          <t>2026-07-11 08:17:18 PM PT</t>
         </is>
       </c>
       <c r="C76" t="n">
@@ -9278,36 +9287,36 @@
       </c>
       <c r="N76" t="inlineStr">
         <is>
-          <t>Ian Happ</t>
+          <t>Seiya Suzuki</t>
         </is>
       </c>
       <c r="O76" t="n">
-        <v>664023</v>
+        <v>673548</v>
       </c>
       <c r="P76" t="inlineStr">
         <is>
-          <t>LF</t>
+          <t>RF</t>
         </is>
       </c>
       <c r="Q76" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>2</t>
         </is>
       </c>
       <c r="R76" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="S76" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="T76" t="n">
         <v>1</v>
       </c>
       <c r="U76" t="n">
-        <v>0</v>
-      </c>
-      <c r="V76" s="7" t="n">
-        <v>1</v>
+        <v>1</v>
+      </c>
+      <c r="V76" t="n">
+        <v>0</v>
       </c>
       <c r="W76" t="n">
         <v>0</v>
@@ -9316,7 +9325,7 @@
         <v>0</v>
       </c>
       <c r="Y76" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Z76" t="n">
         <v>1</v>
@@ -9331,7 +9340,7 @@
         <v>0</v>
       </c>
       <c r="AD76" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AE76" s="4" t="n">
         <v>9</v>
@@ -9351,15 +9360,15 @@
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>2026-07-11 08:15:18 PM PT</t>
+          <t>2026-07-11 08:17:18 PM PT</t>
         </is>
       </c>
       <c r="C77" t="n">
-        <v>823844</v>
+        <v>824492</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>1:10 PM PT</t>
+          <t>4:10 PM PT</t>
         </is>
       </c>
       <c r="E77" t="inlineStr">
@@ -9382,37 +9391,37 @@
       </c>
       <c r="L77" t="inlineStr">
         <is>
-          <t>CLE</t>
+          <t>CHC</t>
         </is>
       </c>
       <c r="M77" t="inlineStr">
         <is>
-          <t>MIA</t>
+          <t>CIN</t>
         </is>
       </c>
       <c r="N77" t="inlineStr">
         <is>
-          <t>Patrick Bailey</t>
+          <t>Ian Happ</t>
         </is>
       </c>
       <c r="O77" t="n">
-        <v>672275</v>
+        <v>664023</v>
       </c>
       <c r="P77" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>LF</t>
         </is>
       </c>
       <c r="Q77" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>7</t>
         </is>
       </c>
       <c r="R77" t="n">
         <v>4</v>
       </c>
       <c r="S77" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="T77" t="n">
         <v>1</v>
@@ -9433,10 +9442,10 @@
         <v>0</v>
       </c>
       <c r="Z77" t="n">
-        <v>2</v>
-      </c>
-      <c r="AA77" t="n">
-        <v>0</v>
+        <v>1</v>
+      </c>
+      <c r="AA77" s="5" t="n">
+        <v>1</v>
       </c>
       <c r="AB77" t="n">
         <v>0</v>
@@ -9445,16 +9454,16 @@
         <v>0</v>
       </c>
       <c r="AD77" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AE77" s="4" t="n">
         <v>9</v>
       </c>
       <c r="AF77" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="AG77" t="n">
-        <v>11</v>
+        <v>9</v>
       </c>
     </row>
     <row r="78">
@@ -9465,15 +9474,15 @@
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>2026-07-11 08:15:16 PM PT</t>
+          <t>2026-07-11 08:17:18 PM PT</t>
         </is>
       </c>
       <c r="C78" t="n">
-        <v>823357</v>
+        <v>823844</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>9:05 AM PT</t>
+          <t>1:10 PM PT</t>
         </is>
       </c>
       <c r="E78" t="inlineStr">
@@ -9486,7 +9495,7 @@
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>Top</t>
+          <t>Bottom</t>
         </is>
       </c>
       <c r="K78" t="inlineStr">
@@ -9496,37 +9505,37 @@
       </c>
       <c r="L78" t="inlineStr">
         <is>
-          <t>MIL</t>
+          <t>CLE</t>
         </is>
       </c>
       <c r="M78" t="inlineStr">
         <is>
-          <t>PIT</t>
+          <t>MIA</t>
         </is>
       </c>
       <c r="N78" t="inlineStr">
         <is>
-          <t>Garrett Mitchell</t>
+          <t>Patrick Bailey</t>
         </is>
       </c>
       <c r="O78" t="n">
-        <v>669003</v>
+        <v>672275</v>
       </c>
       <c r="P78" t="inlineStr">
         <is>
-          <t>CF</t>
+          <t>C</t>
         </is>
       </c>
       <c r="Q78" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>8</t>
         </is>
       </c>
       <c r="R78" t="n">
         <v>4</v>
       </c>
       <c r="S78" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="T78" t="n">
         <v>1</v>
@@ -9544,13 +9553,13 @@
         <v>0</v>
       </c>
       <c r="Y78" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Z78" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA78" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
+      </c>
+      <c r="AA78" t="n">
+        <v>0</v>
       </c>
       <c r="AB78" t="n">
         <v>0</v>
@@ -9565,10 +9574,10 @@
         <v>9</v>
       </c>
       <c r="AF78" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="AG78" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
     </row>
     <row r="79">
@@ -9579,15 +9588,15 @@
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>2026-07-11 08:15:17 PM PT</t>
+          <t>2026-07-11 08:17:16 PM PT</t>
         </is>
       </c>
       <c r="C79" t="n">
-        <v>823356</v>
+        <v>823357</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>1:05 PM PT</t>
+          <t>9:05 AM PT</t>
         </is>
       </c>
       <c r="E79" t="inlineStr">
@@ -9620,27 +9629,27 @@
       </c>
       <c r="N79" t="inlineStr">
         <is>
-          <t>Brice Turang</t>
+          <t>Garrett Mitchell</t>
         </is>
       </c>
       <c r="O79" t="n">
-        <v>668930</v>
+        <v>669003</v>
       </c>
       <c r="P79" t="inlineStr">
         <is>
-          <t>2B</t>
+          <t>CF</t>
         </is>
       </c>
       <c r="Q79" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="R79" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="S79" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="T79" t="n">
         <v>1</v>
@@ -9658,31 +9667,31 @@
         <v>0</v>
       </c>
       <c r="Y79" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Z79" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA79" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="AB79" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC79" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD79" t="n">
         <v>2</v>
-      </c>
-      <c r="AA79" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB79" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC79" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD79" t="n">
-        <v>1</v>
       </c>
       <c r="AE79" s="4" t="n">
         <v>9</v>
       </c>
       <c r="AF79" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="AG79" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
     </row>
     <row r="80">
@@ -9693,7 +9702,7 @@
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>2026-07-11 08:15:17 PM PT</t>
+          <t>2026-07-11 08:17:16 PM PT</t>
         </is>
       </c>
       <c r="C80" t="n">
@@ -9734,60 +9743,60 @@
       </c>
       <c r="N80" t="inlineStr">
         <is>
-          <t>Jake Bauers</t>
+          <t>Brice Turang</t>
         </is>
       </c>
       <c r="O80" t="n">
-        <v>641343</v>
+        <v>668930</v>
       </c>
       <c r="P80" t="inlineStr">
         <is>
-          <t>1B</t>
+          <t>2B</t>
         </is>
       </c>
       <c r="Q80" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>3</t>
         </is>
       </c>
       <c r="R80" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="S80" t="n">
+        <v>5</v>
+      </c>
+      <c r="T80" t="n">
+        <v>1</v>
+      </c>
+      <c r="U80" t="n">
+        <v>0</v>
+      </c>
+      <c r="V80" s="7" t="n">
+        <v>1</v>
+      </c>
+      <c r="W80" t="n">
+        <v>0</v>
+      </c>
+      <c r="X80" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y80" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z80" t="n">
         <v>2</v>
       </c>
-      <c r="T80" t="n">
-        <v>0</v>
-      </c>
-      <c r="U80" t="n">
-        <v>0</v>
-      </c>
-      <c r="V80" t="n">
-        <v>0</v>
-      </c>
-      <c r="W80" t="n">
-        <v>0</v>
-      </c>
-      <c r="X80" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y80" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z80" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA80" s="5" t="n">
-        <v>2</v>
+      <c r="AA80" t="n">
+        <v>0</v>
       </c>
       <c r="AB80" t="n">
         <v>0</v>
       </c>
-      <c r="AC80" s="6" t="n">
-        <v>1</v>
+      <c r="AC80" t="n">
+        <v>0</v>
       </c>
       <c r="AD80" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AE80" s="4" t="n">
         <v>9</v>
@@ -9807,15 +9816,15 @@
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>2026-07-11 08:15:16 PM PT</t>
+          <t>2026-07-11 08:17:16 PM PT</t>
         </is>
       </c>
       <c r="C81" t="n">
-        <v>823357</v>
+        <v>823356</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>9:05 AM PT</t>
+          <t>1:05 PM PT</t>
         </is>
       </c>
       <c r="E81" t="inlineStr">
@@ -9848,36 +9857,36 @@
       </c>
       <c r="N81" t="inlineStr">
         <is>
-          <t>Luis Lara</t>
+          <t>Jake Bauers</t>
         </is>
       </c>
       <c r="O81" t="n">
-        <v>800325</v>
+        <v>641343</v>
       </c>
       <c r="P81" t="inlineStr">
         <is>
-          <t>LF</t>
+          <t>1B</t>
         </is>
       </c>
       <c r="Q81" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>4</t>
         </is>
       </c>
       <c r="R81" t="n">
         <v>4</v>
       </c>
       <c r="S81" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="T81" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="U81" t="n">
         <v>0</v>
       </c>
-      <c r="V81" s="7" t="n">
-        <v>1</v>
+      <c r="V81" t="n">
+        <v>0</v>
       </c>
       <c r="W81" t="n">
         <v>0</v>
@@ -9886,31 +9895,31 @@
         <v>0</v>
       </c>
       <c r="Y81" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Z81" t="n">
         <v>0</v>
       </c>
       <c r="AA81" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AB81" t="n">
         <v>0</v>
       </c>
-      <c r="AC81" t="n">
-        <v>0</v>
+      <c r="AC81" s="6" t="n">
+        <v>1</v>
       </c>
       <c r="AD81" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AE81" s="4" t="n">
         <v>9</v>
       </c>
       <c r="AF81" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="AG81" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
     </row>
     <row r="82">
@@ -9921,7 +9930,7 @@
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>2026-07-11 08:15:16 PM PT</t>
+          <t>2026-07-11 08:17:16 PM PT</t>
         </is>
       </c>
       <c r="C82" t="n">
@@ -9947,26 +9956,26 @@
       </c>
       <c r="K82" t="inlineStr">
         <is>
-          <t>Home</t>
+          <t>Away</t>
         </is>
       </c>
       <c r="L82" t="inlineStr">
         <is>
+          <t>MIL</t>
+        </is>
+      </c>
+      <c r="M82" t="inlineStr">
+        <is>
           <t>PIT</t>
         </is>
       </c>
-      <c r="M82" t="inlineStr">
-        <is>
-          <t>MIL</t>
-        </is>
-      </c>
       <c r="N82" t="inlineStr">
         <is>
-          <t>Jake Mangum</t>
+          <t>Luis Lara</t>
         </is>
       </c>
       <c r="O82" t="n">
-        <v>663968</v>
+        <v>800325</v>
       </c>
       <c r="P82" t="inlineStr">
         <is>
@@ -9975,7 +9984,7 @@
       </c>
       <c r="Q82" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>6</t>
         </is>
       </c>
       <c r="R82" t="n">
@@ -9988,10 +9997,10 @@
         <v>1</v>
       </c>
       <c r="U82" t="n">
-        <v>1</v>
-      </c>
-      <c r="V82" t="n">
-        <v>0</v>
+        <v>0</v>
+      </c>
+      <c r="V82" s="7" t="n">
+        <v>1</v>
       </c>
       <c r="W82" t="n">
         <v>0</v>
@@ -10000,16 +10009,16 @@
         <v>0</v>
       </c>
       <c r="Y82" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="Z82" t="n">
         <v>0</v>
       </c>
-      <c r="AA82" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB82" s="9" t="n">
-        <v>1</v>
+      <c r="AA82" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="AB82" t="n">
+        <v>0</v>
       </c>
       <c r="AC82" t="n">
         <v>0</v>
@@ -10021,10 +10030,10 @@
         <v>9</v>
       </c>
       <c r="AF82" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="AG82" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
     </row>
     <row r="83">
@@ -10035,7 +10044,7 @@
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>2026-07-11 08:15:16 PM PT</t>
+          <t>2026-07-11 08:17:16 PM PT</t>
         </is>
       </c>
       <c r="C83" t="n">
@@ -10076,54 +10085,54 @@
       </c>
       <c r="N83" t="inlineStr">
         <is>
-          <t>Henry Davis</t>
+          <t>Jake Mangum</t>
         </is>
       </c>
       <c r="O83" t="n">
-        <v>680779</v>
+        <v>663968</v>
       </c>
       <c r="P83" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>LF</t>
         </is>
       </c>
       <c r="Q83" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>1</t>
         </is>
       </c>
       <c r="R83" t="n">
         <v>4</v>
       </c>
       <c r="S83" t="n">
+        <v>3</v>
+      </c>
+      <c r="T83" t="n">
+        <v>1</v>
+      </c>
+      <c r="U83" t="n">
+        <v>1</v>
+      </c>
+      <c r="V83" t="n">
+        <v>0</v>
+      </c>
+      <c r="W83" t="n">
+        <v>0</v>
+      </c>
+      <c r="X83" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y83" t="n">
         <v>2</v>
       </c>
-      <c r="T83" t="n">
-        <v>1</v>
-      </c>
-      <c r="U83" t="n">
-        <v>1</v>
-      </c>
-      <c r="V83" t="n">
-        <v>0</v>
-      </c>
-      <c r="W83" t="n">
-        <v>0</v>
-      </c>
-      <c r="X83" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y83" t="n">
-        <v>1</v>
-      </c>
       <c r="Z83" t="n">
         <v>0</v>
       </c>
-      <c r="AA83" s="5" t="n">
-        <v>2</v>
-      </c>
-      <c r="AB83" t="n">
-        <v>0</v>
+      <c r="AA83" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB83" s="9" t="n">
+        <v>1</v>
       </c>
       <c r="AC83" t="n">
         <v>0</v>
@@ -10149,15 +10158,15 @@
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>2026-07-11 08:15:17 PM PT</t>
+          <t>2026-07-11 08:17:16 PM PT</t>
         </is>
       </c>
       <c r="C84" t="n">
-        <v>824576</v>
+        <v>823357</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t>11:10 AM PT</t>
+          <t>9:05 AM PT</t>
         </is>
       </c>
       <c r="E84" t="inlineStr">
@@ -10175,67 +10184,67 @@
       </c>
       <c r="K84" t="inlineStr">
         <is>
-          <t>Away</t>
+          <t>Home</t>
         </is>
       </c>
       <c r="L84" t="inlineStr">
         <is>
-          <t>ATH</t>
+          <t>PIT</t>
         </is>
       </c>
       <c r="M84" t="inlineStr">
         <is>
-          <t>CWS</t>
+          <t>MIL</t>
         </is>
       </c>
       <c r="N84" t="inlineStr">
         <is>
-          <t>Joshua Kuroda-Grauer</t>
+          <t>Henry Davis</t>
         </is>
       </c>
       <c r="O84" t="n">
-        <v>811965</v>
+        <v>680779</v>
       </c>
       <c r="P84" t="inlineStr">
         <is>
-          <t>3B</t>
+          <t>C</t>
         </is>
       </c>
       <c r="Q84" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>9</t>
         </is>
       </c>
       <c r="R84" t="n">
         <v>4</v>
       </c>
       <c r="S84" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="T84" t="n">
+        <v>1</v>
+      </c>
+      <c r="U84" t="n">
+        <v>1</v>
+      </c>
+      <c r="V84" t="n">
+        <v>0</v>
+      </c>
+      <c r="W84" t="n">
+        <v>0</v>
+      </c>
+      <c r="X84" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y84" t="n">
+        <v>1</v>
+      </c>
+      <c r="Z84" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA84" s="5" t="n">
         <v>2</v>
       </c>
-      <c r="U84" t="n">
-        <v>1</v>
-      </c>
-      <c r="V84" s="7" t="n">
-        <v>1</v>
-      </c>
-      <c r="W84" t="n">
-        <v>0</v>
-      </c>
-      <c r="X84" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y84" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z84" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA84" t="n">
-        <v>0</v>
-      </c>
       <c r="AB84" t="n">
         <v>0</v>
       </c>
@@ -10246,13 +10255,13 @@
         <v>0</v>
       </c>
       <c r="AE84" s="4" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="AF84" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="AG84" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
     </row>
     <row r="85">
@@ -10263,7 +10272,7 @@
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>2026-07-11 08:15:17 PM PT</t>
+          <t>2026-07-11 08:17:17 PM PT</t>
         </is>
       </c>
       <c r="C85" t="n">
@@ -10289,42 +10298,42 @@
       </c>
       <c r="K85" t="inlineStr">
         <is>
-          <t>Home</t>
+          <t>Away</t>
         </is>
       </c>
       <c r="L85" t="inlineStr">
         <is>
+          <t>ATH</t>
+        </is>
+      </c>
+      <c r="M85" t="inlineStr">
+        <is>
           <t>CWS</t>
         </is>
       </c>
-      <c r="M85" t="inlineStr">
-        <is>
-          <t>ATH</t>
-        </is>
-      </c>
       <c r="N85" t="inlineStr">
         <is>
-          <t>Luisangel Acuña</t>
+          <t>Joshua Kuroda-Grauer</t>
         </is>
       </c>
       <c r="O85" t="n">
-        <v>682668</v>
+        <v>811965</v>
       </c>
       <c r="P85" t="inlineStr">
         <is>
-          <t>SS</t>
+          <t>3B</t>
         </is>
       </c>
       <c r="Q85" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>5</t>
         </is>
       </c>
       <c r="R85" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="S85" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="T85" t="n">
         <v>2</v>
@@ -10357,16 +10366,16 @@
         <v>0</v>
       </c>
       <c r="AD85" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AE85" s="4" t="n">
         <v>8</v>
       </c>
       <c r="AF85" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AG85" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
     </row>
     <row r="86">
@@ -10377,15 +10386,15 @@
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>2026-07-11 08:15:17 PM PT</t>
+          <t>2026-07-11 08:17:17 PM PT</t>
         </is>
       </c>
       <c r="C86" t="n">
-        <v>823603</v>
+        <v>824576</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>
-          <t>1:10 PM PT</t>
+          <t>11:10 AM PT</t>
         </is>
       </c>
       <c r="E86" t="inlineStr">
@@ -10398,7 +10407,7 @@
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>Bottom</t>
+          <t>Top</t>
         </is>
       </c>
       <c r="K86" t="inlineStr">
@@ -10408,25 +10417,25 @@
       </c>
       <c r="L86" t="inlineStr">
         <is>
-          <t>NYM</t>
+          <t>CWS</t>
         </is>
       </c>
       <c r="M86" t="inlineStr">
         <is>
-          <t>BOS</t>
+          <t>ATH</t>
         </is>
       </c>
       <c r="N86" t="inlineStr">
         <is>
-          <t>Francisco Alvarez</t>
+          <t>Luisangel Acuña</t>
         </is>
       </c>
       <c r="O86" t="n">
-        <v>682626</v>
+        <v>682668</v>
       </c>
       <c r="P86" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>SS</t>
         </is>
       </c>
       <c r="Q86" t="inlineStr">
@@ -10435,7 +10444,7 @@
         </is>
       </c>
       <c r="R86" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="S86" t="n">
         <v>3</v>
@@ -10444,10 +10453,10 @@
         <v>2</v>
       </c>
       <c r="U86" t="n">
-        <v>2</v>
-      </c>
-      <c r="V86" t="n">
-        <v>0</v>
+        <v>1</v>
+      </c>
+      <c r="V86" s="7" t="n">
+        <v>1</v>
       </c>
       <c r="W86" t="n">
         <v>0</v>
@@ -10461,8 +10470,8 @@
       <c r="Z86" t="n">
         <v>0</v>
       </c>
-      <c r="AA86" s="5" t="n">
-        <v>1</v>
+      <c r="AA86" t="n">
+        <v>0</v>
       </c>
       <c r="AB86" t="n">
         <v>0</v>
@@ -10477,10 +10486,10 @@
         <v>8</v>
       </c>
       <c r="AF86" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AG86" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
     </row>
     <row r="87">
@@ -10491,15 +10500,15 @@
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>2026-07-11 08:15:18 PM PT</t>
+          <t>2026-07-11 08:17:17 PM PT</t>
         </is>
       </c>
       <c r="C87" t="n">
-        <v>824249</v>
+        <v>823603</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>
-          <t>3:10 PM PT</t>
+          <t>1:10 PM PT</t>
         </is>
       </c>
       <c r="E87" t="inlineStr">
@@ -10517,51 +10526,51 @@
       </c>
       <c r="K87" t="inlineStr">
         <is>
-          <t>Away</t>
+          <t>Home</t>
         </is>
       </c>
       <c r="L87" t="inlineStr">
         <is>
-          <t>PHI</t>
+          <t>NYM</t>
         </is>
       </c>
       <c r="M87" t="inlineStr">
         <is>
-          <t>DET</t>
+          <t>BOS</t>
         </is>
       </c>
       <c r="N87" t="inlineStr">
         <is>
-          <t>Bryce Harper</t>
+          <t>Francisco Alvarez</t>
         </is>
       </c>
       <c r="O87" t="n">
-        <v>547180</v>
+        <v>682626</v>
       </c>
       <c r="P87" t="inlineStr">
         <is>
-          <t>1B</t>
+          <t>C</t>
         </is>
       </c>
       <c r="Q87" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>7</t>
         </is>
       </c>
       <c r="R87" t="n">
         <v>4</v>
       </c>
       <c r="S87" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="T87" t="n">
         <v>2</v>
       </c>
       <c r="U87" t="n">
-        <v>1</v>
-      </c>
-      <c r="V87" s="7" t="n">
-        <v>1</v>
+        <v>2</v>
+      </c>
+      <c r="V87" t="n">
+        <v>0</v>
       </c>
       <c r="W87" t="n">
         <v>0</v>
@@ -10575,8 +10584,8 @@
       <c r="Z87" t="n">
         <v>0</v>
       </c>
-      <c r="AA87" t="n">
-        <v>0</v>
+      <c r="AA87" s="5" t="n">
+        <v>1</v>
       </c>
       <c r="AB87" t="n">
         <v>0</v>
@@ -10585,16 +10594,16 @@
         <v>0</v>
       </c>
       <c r="AD87" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AE87" s="4" t="n">
         <v>8</v>
       </c>
       <c r="AF87" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="AG87" t="n">
-        <v>7</v>
+        <v>3</v>
       </c>
     </row>
     <row r="88">
@@ -10605,86 +10614,77 @@
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>2026-07-11 08:15:19 PM PT</t>
+          <t>2026-07-11 08:17:18 PM PT</t>
         </is>
       </c>
       <c r="C88" t="n">
-        <v>823276</v>
+        <v>824249</v>
       </c>
       <c r="D88" t="inlineStr">
         <is>
-          <t>5:40 PM PT</t>
+          <t>3:10 PM PT</t>
         </is>
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>Bottom 7 | 0 out</t>
+          <t>Final</t>
         </is>
       </c>
       <c r="F88" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="G88" t="inlineStr">
         <is>
           <t>Bottom</t>
         </is>
       </c>
-      <c r="H88" t="n">
-        <v>0</v>
-      </c>
-      <c r="I88" t="n">
+      <c r="K88" t="inlineStr">
+        <is>
+          <t>Away</t>
+        </is>
+      </c>
+      <c r="L88" t="inlineStr">
+        <is>
+          <t>PHI</t>
+        </is>
+      </c>
+      <c r="M88" t="inlineStr">
+        <is>
+          <t>DET</t>
+        </is>
+      </c>
+      <c r="N88" t="inlineStr">
+        <is>
+          <t>Bryce Harper</t>
+        </is>
+      </c>
+      <c r="O88" t="n">
+        <v>547180</v>
+      </c>
+      <c r="P88" t="inlineStr">
+        <is>
+          <t>1B</t>
+        </is>
+      </c>
+      <c r="Q88" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="R88" t="n">
+        <v>4</v>
+      </c>
+      <c r="S88" t="n">
+        <v>4</v>
+      </c>
+      <c r="T88" t="n">
         <v>2</v>
       </c>
-      <c r="J88" t="n">
-        <v>1</v>
-      </c>
-      <c r="K88" t="inlineStr">
-        <is>
-          <t>Home</t>
-        </is>
-      </c>
-      <c r="L88" t="inlineStr">
-        <is>
-          <t>SD</t>
-        </is>
-      </c>
-      <c r="M88" t="inlineStr">
-        <is>
-          <t>TOR</t>
-        </is>
-      </c>
-      <c r="N88" t="inlineStr">
-        <is>
-          <t>Gavin Sheets</t>
-        </is>
-      </c>
-      <c r="O88" t="n">
-        <v>657757</v>
-      </c>
-      <c r="P88" t="inlineStr">
-        <is>
-          <t>LF</t>
-        </is>
-      </c>
-      <c r="Q88" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="R88" t="n">
-        <v>4</v>
-      </c>
-      <c r="S88" t="n">
-        <v>2</v>
-      </c>
-      <c r="T88" t="n">
-        <v>0</v>
-      </c>
       <c r="U88" t="n">
-        <v>0</v>
-      </c>
-      <c r="V88" t="n">
-        <v>0</v>
+        <v>1</v>
+      </c>
+      <c r="V88" s="7" t="n">
+        <v>1</v>
       </c>
       <c r="W88" t="n">
         <v>0</v>
@@ -10693,13 +10693,13 @@
         <v>0</v>
       </c>
       <c r="Y88" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Z88" t="n">
-        <v>1</v>
-      </c>
-      <c r="AA88" s="5" t="n">
-        <v>2</v>
+        <v>0</v>
+      </c>
+      <c r="AA88" t="n">
+        <v>0</v>
       </c>
       <c r="AB88" t="n">
         <v>0</v>
@@ -10708,13 +10708,13 @@
         <v>0</v>
       </c>
       <c r="AD88" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AE88" s="4" t="n">
         <v>8</v>
       </c>
       <c r="AF88" t="n">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="AG88" t="n">
         <v>7</v>
@@ -10728,29 +10728,38 @@
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>2026-07-11 08:15:17 PM PT</t>
+          <t>2026-07-11 08:17:18 PM PT</t>
         </is>
       </c>
       <c r="C89" t="n">
-        <v>823198</v>
+        <v>823276</v>
       </c>
       <c r="D89" t="inlineStr">
         <is>
-          <t>1:05 PM PT</t>
+          <t>5:40 PM PT</t>
         </is>
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>Final</t>
+          <t>Bottom 7 | 1 out</t>
         </is>
       </c>
       <c r="F89" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>Top</t>
-        </is>
+          <t>Bottom</t>
+        </is>
+      </c>
+      <c r="H89" t="n">
+        <v>1</v>
+      </c>
+      <c r="I89" t="n">
+        <v>0</v>
+      </c>
+      <c r="J89" t="n">
+        <v>0</v>
       </c>
       <c r="K89" t="inlineStr">
         <is>
@@ -10759,61 +10768,61 @@
       </c>
       <c r="L89" t="inlineStr">
         <is>
-          <t>SF</t>
+          <t>SD</t>
         </is>
       </c>
       <c r="M89" t="inlineStr">
         <is>
-          <t>COL</t>
+          <t>TOR</t>
         </is>
       </c>
       <c r="N89" t="inlineStr">
         <is>
-          <t>Luis Arraez</t>
+          <t>Gavin Sheets</t>
         </is>
       </c>
       <c r="O89" t="n">
-        <v>650333</v>
+        <v>657757</v>
       </c>
       <c r="P89" t="inlineStr">
         <is>
-          <t>2B</t>
+          <t>LF</t>
         </is>
       </c>
       <c r="Q89" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>5</t>
         </is>
       </c>
       <c r="R89" t="n">
         <v>4</v>
       </c>
       <c r="S89" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="T89" t="n">
+        <v>0</v>
+      </c>
+      <c r="U89" t="n">
+        <v>0</v>
+      </c>
+      <c r="V89" t="n">
+        <v>0</v>
+      </c>
+      <c r="W89" t="n">
+        <v>0</v>
+      </c>
+      <c r="X89" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y89" t="n">
+        <v>1</v>
+      </c>
+      <c r="Z89" t="n">
+        <v>1</v>
+      </c>
+      <c r="AA89" s="5" t="n">
         <v>2</v>
-      </c>
-      <c r="U89" t="n">
-        <v>2</v>
-      </c>
-      <c r="V89" t="n">
-        <v>0</v>
-      </c>
-      <c r="W89" t="n">
-        <v>0</v>
-      </c>
-      <c r="X89" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y89" t="n">
-        <v>1</v>
-      </c>
-      <c r="Z89" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA89" t="n">
-        <v>0</v>
       </c>
       <c r="AB89" t="n">
         <v>0</v>
@@ -10828,7 +10837,7 @@
         <v>8</v>
       </c>
       <c r="AF89" t="n">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="AG89" t="n">
         <v>7</v>
@@ -10842,15 +10851,15 @@
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>2026-07-11 08:15:18 PM PT</t>
+          <t>2026-07-11 08:17:17 PM PT</t>
         </is>
       </c>
       <c r="C90" t="n">
-        <v>823030</v>
+        <v>823198</v>
       </c>
       <c r="D90" t="inlineStr">
         <is>
-          <t>4:15 PM PT</t>
+          <t>1:05 PM PT</t>
         </is>
       </c>
       <c r="E90" t="inlineStr">
@@ -10873,55 +10882,55 @@
       </c>
       <c r="L90" t="inlineStr">
         <is>
-          <t>STL</t>
+          <t>SF</t>
         </is>
       </c>
       <c r="M90" t="inlineStr">
         <is>
-          <t>ATL</t>
+          <t>COL</t>
         </is>
       </c>
       <c r="N90" t="inlineStr">
         <is>
-          <t>Bryan Torres</t>
+          <t>Luis Arraez</t>
         </is>
       </c>
       <c r="O90" t="n">
-        <v>663494</v>
+        <v>650333</v>
       </c>
       <c r="P90" t="inlineStr">
         <is>
-          <t>DH</t>
+          <t>2B</t>
         </is>
       </c>
       <c r="Q90" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>2</t>
         </is>
       </c>
       <c r="R90" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="S90" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="T90" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="U90" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="V90" t="n">
         <v>0</v>
       </c>
-      <c r="W90" s="8" t="n">
-        <v>1</v>
+      <c r="W90" t="n">
+        <v>0</v>
       </c>
       <c r="X90" t="n">
         <v>0</v>
       </c>
       <c r="Y90" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Z90" t="n">
         <v>0</v>
@@ -10945,7 +10954,7 @@
         <v>4</v>
       </c>
       <c r="AG90" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
     </row>
     <row r="91">
@@ -10956,15 +10965,15 @@
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>2026-07-11 08:15:18 PM PT</t>
+          <t>2026-07-11 08:17:18 PM PT</t>
         </is>
       </c>
       <c r="C91" t="n">
-        <v>823844</v>
+        <v>823030</v>
       </c>
       <c r="D91" t="inlineStr">
         <is>
-          <t>1:10 PM PT</t>
+          <t>4:15 PM PT</t>
         </is>
       </c>
       <c r="E91" t="inlineStr">
@@ -10977,44 +10986,44 @@
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>Bottom</t>
+          <t>Top</t>
         </is>
       </c>
       <c r="K91" t="inlineStr">
         <is>
-          <t>Away</t>
+          <t>Home</t>
         </is>
       </c>
       <c r="L91" t="inlineStr">
         <is>
-          <t>CLE</t>
+          <t>STL</t>
         </is>
       </c>
       <c r="M91" t="inlineStr">
         <is>
-          <t>MIA</t>
+          <t>ATL</t>
         </is>
       </c>
       <c r="N91" t="inlineStr">
         <is>
-          <t>Kyle Manzardo</t>
+          <t>Bryan Torres</t>
         </is>
       </c>
       <c r="O91" t="n">
-        <v>700932</v>
+        <v>663494</v>
       </c>
       <c r="P91" t="inlineStr">
         <is>
-          <t>1B</t>
+          <t>DH</t>
         </is>
       </c>
       <c r="Q91" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>7</t>
         </is>
       </c>
       <c r="R91" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="S91" t="n">
         <v>3</v>
@@ -11023,19 +11032,19 @@
         <v>1</v>
       </c>
       <c r="U91" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="V91" t="n">
         <v>0</v>
       </c>
-      <c r="W91" t="n">
-        <v>0</v>
+      <c r="W91" s="8" t="n">
+        <v>1</v>
       </c>
       <c r="X91" t="n">
         <v>0</v>
       </c>
       <c r="Y91" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Z91" t="n">
         <v>0</v>
@@ -11043,8 +11052,8 @@
       <c r="AA91" t="n">
         <v>0</v>
       </c>
-      <c r="AB91" s="9" t="n">
-        <v>1</v>
+      <c r="AB91" t="n">
+        <v>0</v>
       </c>
       <c r="AC91" t="n">
         <v>0</v>
@@ -11053,13 +11062,13 @@
         <v>1</v>
       </c>
       <c r="AE91" s="4" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AF91" t="n">
         <v>4</v>
       </c>
       <c r="AG91" t="n">
-        <v>11</v>
+        <v>5</v>
       </c>
     </row>
     <row r="92">
@@ -11070,7 +11079,7 @@
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>2026-07-11 08:15:18 PM PT</t>
+          <t>2026-07-11 08:17:18 PM PT</t>
         </is>
       </c>
       <c r="C92" t="n">
@@ -11111,36 +11120,36 @@
       </c>
       <c r="N92" t="inlineStr">
         <is>
-          <t>Kahlil Watson</t>
+          <t>Kyle Manzardo</t>
         </is>
       </c>
       <c r="O92" t="n">
-        <v>696135</v>
+        <v>700932</v>
       </c>
       <c r="P92" t="inlineStr">
         <is>
-          <t>RF</t>
+          <t>1B</t>
         </is>
       </c>
       <c r="Q92" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>4</t>
         </is>
       </c>
       <c r="R92" t="n">
         <v>4</v>
       </c>
       <c r="S92" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="T92" t="n">
         <v>1</v>
       </c>
       <c r="U92" t="n">
-        <v>0</v>
-      </c>
-      <c r="V92" s="7" t="n">
-        <v>1</v>
+        <v>1</v>
+      </c>
+      <c r="V92" t="n">
+        <v>0</v>
       </c>
       <c r="W92" t="n">
         <v>0</v>
@@ -11157,8 +11166,8 @@
       <c r="AA92" t="n">
         <v>0</v>
       </c>
-      <c r="AB92" t="n">
-        <v>0</v>
+      <c r="AB92" s="9" t="n">
+        <v>1</v>
       </c>
       <c r="AC92" t="n">
         <v>0</v>
@@ -11184,15 +11193,15 @@
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>2026-07-11 08:15:17 PM PT</t>
+          <t>2026-07-11 08:17:18 PM PT</t>
         </is>
       </c>
       <c r="C93" t="n">
-        <v>823198</v>
+        <v>823844</v>
       </c>
       <c r="D93" t="inlineStr">
         <is>
-          <t>1:05 PM PT</t>
+          <t>1:10 PM PT</t>
         </is>
       </c>
       <c r="E93" t="inlineStr">
@@ -11205,7 +11214,7 @@
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>Top</t>
+          <t>Bottom</t>
         </is>
       </c>
       <c r="K93" t="inlineStr">
@@ -11215,37 +11224,37 @@
       </c>
       <c r="L93" t="inlineStr">
         <is>
-          <t>COL</t>
+          <t>CLE</t>
         </is>
       </c>
       <c r="M93" t="inlineStr">
         <is>
-          <t>SF</t>
+          <t>MIA</t>
         </is>
       </c>
       <c r="N93" t="inlineStr">
         <is>
-          <t>Brett Sullivan</t>
+          <t>Kahlil Watson</t>
         </is>
       </c>
       <c r="O93" t="n">
-        <v>664954</v>
+        <v>696135</v>
       </c>
       <c r="P93" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>RF</t>
         </is>
       </c>
       <c r="Q93" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>5</t>
         </is>
       </c>
       <c r="R93" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="S93" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="T93" t="n">
         <v>1</v>
@@ -11278,16 +11287,16 @@
         <v>0</v>
       </c>
       <c r="AD93" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AE93" s="4" t="n">
         <v>7</v>
       </c>
       <c r="AF93" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="AG93" t="n">
-        <v>6</v>
+        <v>11</v>
       </c>
     </row>
     <row r="94">
@@ -11298,15 +11307,15 @@
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>2026-07-11 08:15:18 PM PT</t>
+          <t>2026-07-11 08:17:17 PM PT</t>
         </is>
       </c>
       <c r="C94" t="n">
-        <v>822875</v>
+        <v>823198</v>
       </c>
       <c r="D94" t="inlineStr">
         <is>
-          <t>4:05 PM PT</t>
+          <t>1:05 PM PT</t>
         </is>
       </c>
       <c r="E94" t="inlineStr">
@@ -11319,7 +11328,7 @@
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>Bottom</t>
+          <t>Top</t>
         </is>
       </c>
       <c r="K94" t="inlineStr">
@@ -11329,46 +11338,46 @@
       </c>
       <c r="L94" t="inlineStr">
         <is>
-          <t>HOU</t>
+          <t>COL</t>
         </is>
       </c>
       <c r="M94" t="inlineStr">
         <is>
-          <t>TEX</t>
+          <t>SF</t>
         </is>
       </c>
       <c r="N94" t="inlineStr">
         <is>
-          <t>Jeremy Peña</t>
+          <t>Brett Sullivan</t>
         </is>
       </c>
       <c r="O94" t="n">
-        <v>665161</v>
+        <v>664954</v>
       </c>
       <c r="P94" t="inlineStr">
         <is>
-          <t>SS</t>
+          <t>C</t>
         </is>
       </c>
       <c r="Q94" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>9</t>
         </is>
       </c>
       <c r="R94" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="S94" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="T94" t="n">
         <v>1</v>
       </c>
       <c r="U94" t="n">
-        <v>1</v>
-      </c>
-      <c r="V94" t="n">
-        <v>0</v>
+        <v>0</v>
+      </c>
+      <c r="V94" s="7" t="n">
+        <v>1</v>
       </c>
       <c r="W94" t="n">
         <v>0</v>
@@ -11385,8 +11394,8 @@
       <c r="AA94" t="n">
         <v>0</v>
       </c>
-      <c r="AB94" s="9" t="n">
-        <v>1</v>
+      <c r="AB94" t="n">
+        <v>0</v>
       </c>
       <c r="AC94" t="n">
         <v>0</v>
@@ -11398,10 +11407,10 @@
         <v>7</v>
       </c>
       <c r="AF94" t="n">
-        <v>9</v>
+        <v>2</v>
       </c>
       <c r="AG94" t="n">
-        <v>10</v>
+        <v>6</v>
       </c>
     </row>
     <row r="95">
@@ -11412,7 +11421,7 @@
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>2026-07-11 08:15:18 PM PT</t>
+          <t>2026-07-11 08:17:18 PM PT</t>
         </is>
       </c>
       <c r="C95" t="n">
@@ -11453,36 +11462,36 @@
       </c>
       <c r="N95" t="inlineStr">
         <is>
-          <t>Christian Walker</t>
+          <t>Jeremy Peña</t>
         </is>
       </c>
       <c r="O95" t="n">
-        <v>572233</v>
+        <v>665161</v>
       </c>
       <c r="P95" t="inlineStr">
         <is>
-          <t>1B</t>
+          <t>SS</t>
         </is>
       </c>
       <c r="Q95" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>1</t>
         </is>
       </c>
       <c r="R95" t="n">
         <v>5</v>
       </c>
       <c r="S95" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="T95" t="n">
         <v>1</v>
       </c>
       <c r="U95" t="n">
-        <v>0</v>
-      </c>
-      <c r="V95" s="7" t="n">
-        <v>1</v>
+        <v>1</v>
+      </c>
+      <c r="V95" t="n">
+        <v>0</v>
       </c>
       <c r="W95" t="n">
         <v>0</v>
@@ -11499,14 +11508,14 @@
       <c r="AA95" t="n">
         <v>0</v>
       </c>
-      <c r="AB95" t="n">
-        <v>0</v>
+      <c r="AB95" s="9" t="n">
+        <v>1</v>
       </c>
       <c r="AC95" t="n">
         <v>0</v>
       </c>
       <c r="AD95" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="AE95" s="4" t="n">
         <v>7</v>
@@ -11526,77 +11535,68 @@
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>2026-07-11 08:15:19 PM PT</t>
+          <t>2026-07-11 08:17:18 PM PT</t>
         </is>
       </c>
       <c r="C96" t="n">
-        <v>823926</v>
+        <v>822875</v>
       </c>
       <c r="D96" t="inlineStr">
         <is>
-          <t>6:10 PM PT</t>
+          <t>4:05 PM PT</t>
         </is>
       </c>
       <c r="E96" t="inlineStr">
         <is>
-          <t>Top 7 | 1 out</t>
+          <t>Final</t>
         </is>
       </c>
       <c r="F96" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>Top</t>
-        </is>
-      </c>
-      <c r="H96" t="n">
-        <v>1</v>
-      </c>
-      <c r="I96" t="n">
-        <v>1</v>
-      </c>
-      <c r="J96" t="n">
-        <v>1</v>
+          <t>Bottom</t>
+        </is>
       </c>
       <c r="K96" t="inlineStr">
         <is>
-          <t>Home</t>
+          <t>Away</t>
         </is>
       </c>
       <c r="L96" t="inlineStr">
         <is>
-          <t>LAD</t>
+          <t>HOU</t>
         </is>
       </c>
       <c r="M96" t="inlineStr">
         <is>
-          <t>ARI</t>
+          <t>TEX</t>
         </is>
       </c>
       <c r="N96" t="inlineStr">
         <is>
-          <t>Tommy Edman</t>
+          <t>Christian Walker</t>
         </is>
       </c>
       <c r="O96" t="n">
-        <v>669242</v>
+        <v>572233</v>
       </c>
       <c r="P96" t="inlineStr">
         <is>
-          <t>2B</t>
+          <t>1B</t>
         </is>
       </c>
       <c r="Q96" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>4</t>
         </is>
       </c>
       <c r="R96" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="S96" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="T96" t="n">
         <v>1</v>
@@ -11629,16 +11629,16 @@
         <v>0</v>
       </c>
       <c r="AD96" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="AE96" s="4" t="n">
         <v>7</v>
       </c>
       <c r="AF96" t="n">
-        <v>2</v>
+        <v>9</v>
       </c>
       <c r="AG96" t="n">
-        <v>6</v>
+        <v>10</v>
       </c>
     </row>
     <row r="97">
@@ -11649,29 +11649,38 @@
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>2026-07-11 08:15:18 PM PT</t>
+          <t>2026-07-11 08:17:18 PM PT</t>
         </is>
       </c>
       <c r="C97" t="n">
-        <v>823844</v>
+        <v>823926</v>
       </c>
       <c r="D97" t="inlineStr">
         <is>
-          <t>1:10 PM PT</t>
+          <t>6:10 PM PT</t>
         </is>
       </c>
       <c r="E97" t="inlineStr">
         <is>
-          <t>Final</t>
+          <t>Top 7 | 1 out</t>
         </is>
       </c>
       <c r="F97" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>Bottom</t>
-        </is>
+          <t>Top</t>
+        </is>
+      </c>
+      <c r="H97" t="n">
+        <v>1</v>
+      </c>
+      <c r="I97" t="n">
+        <v>3</v>
+      </c>
+      <c r="J97" t="n">
+        <v>2</v>
       </c>
       <c r="K97" t="inlineStr">
         <is>
@@ -11680,37 +11689,37 @@
       </c>
       <c r="L97" t="inlineStr">
         <is>
-          <t>MIA</t>
+          <t>LAD</t>
         </is>
       </c>
       <c r="M97" t="inlineStr">
         <is>
-          <t>CLE</t>
+          <t>ARI</t>
         </is>
       </c>
       <c r="N97" t="inlineStr">
         <is>
-          <t>Joe Mack</t>
+          <t>Tommy Edman</t>
         </is>
       </c>
       <c r="O97" t="n">
-        <v>691788</v>
+        <v>669242</v>
       </c>
       <c r="P97" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>2B</t>
         </is>
       </c>
       <c r="Q97" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>9</t>
         </is>
       </c>
       <c r="R97" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="S97" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="T97" t="n">
         <v>1</v>
@@ -11743,16 +11752,16 @@
         <v>0</v>
       </c>
       <c r="AD97" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AE97" s="4" t="n">
         <v>7</v>
       </c>
       <c r="AF97" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AG97" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
     </row>
     <row r="98">
@@ -11763,15 +11772,15 @@
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>2026-07-11 08:15:17 PM PT</t>
+          <t>2026-07-11 08:17:18 PM PT</t>
         </is>
       </c>
       <c r="C98" t="n">
-        <v>823356</v>
+        <v>823844</v>
       </c>
       <c r="D98" t="inlineStr">
         <is>
-          <t>1:05 PM PT</t>
+          <t>1:10 PM PT</t>
         </is>
       </c>
       <c r="E98" t="inlineStr">
@@ -11784,56 +11793,56 @@
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>Top</t>
+          <t>Bottom</t>
         </is>
       </c>
       <c r="K98" t="inlineStr">
         <is>
-          <t>Away</t>
+          <t>Home</t>
         </is>
       </c>
       <c r="L98" t="inlineStr">
         <is>
-          <t>MIL</t>
+          <t>MIA</t>
         </is>
       </c>
       <c r="M98" t="inlineStr">
         <is>
-          <t>PIT</t>
+          <t>CLE</t>
         </is>
       </c>
       <c r="N98" t="inlineStr">
         <is>
-          <t>Christian Yelich</t>
+          <t>Joe Mack</t>
         </is>
       </c>
       <c r="O98" t="n">
-        <v>592885</v>
+        <v>691788</v>
       </c>
       <c r="P98" t="inlineStr">
         <is>
-          <t>DH</t>
+          <t>C</t>
         </is>
       </c>
       <c r="Q98" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>8</t>
         </is>
       </c>
       <c r="R98" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="S98" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="T98" t="n">
         <v>1</v>
       </c>
       <c r="U98" t="n">
-        <v>1</v>
-      </c>
-      <c r="V98" t="n">
-        <v>0</v>
+        <v>0</v>
+      </c>
+      <c r="V98" s="7" t="n">
+        <v>1</v>
       </c>
       <c r="W98" t="n">
         <v>0</v>
@@ -11842,28 +11851,28 @@
         <v>0</v>
       </c>
       <c r="Y98" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Z98" t="n">
         <v>0</v>
       </c>
-      <c r="AA98" s="5" t="n">
-        <v>1</v>
-      </c>
-      <c r="AB98" s="9" t="n">
-        <v>1</v>
+      <c r="AA98" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB98" t="n">
+        <v>0</v>
       </c>
       <c r="AC98" t="n">
         <v>0</v>
       </c>
       <c r="AD98" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AE98" s="4" t="n">
         <v>7</v>
       </c>
       <c r="AF98" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AG98" t="n">
         <v>7</v>
@@ -11877,15 +11886,15 @@
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>2026-07-11 08:15:17 PM PT</t>
+          <t>2026-07-11 08:17:16 PM PT</t>
         </is>
       </c>
       <c r="C99" t="n">
-        <v>823682</v>
+        <v>823356</v>
       </c>
       <c r="D99" t="inlineStr">
         <is>
-          <t>11:10 AM PT</t>
+          <t>1:05 PM PT</t>
         </is>
       </c>
       <c r="E99" t="inlineStr">
@@ -11903,84 +11912,84 @@
       </c>
       <c r="K99" t="inlineStr">
         <is>
-          <t>Home</t>
+          <t>Away</t>
         </is>
       </c>
       <c r="L99" t="inlineStr">
         <is>
-          <t>MIN</t>
+          <t>MIL</t>
         </is>
       </c>
       <c r="M99" t="inlineStr">
         <is>
-          <t>LAA</t>
+          <t>PIT</t>
         </is>
       </c>
       <c r="N99" t="inlineStr">
         <is>
-          <t>Alan Roden</t>
+          <t>Christian Yelich</t>
         </is>
       </c>
       <c r="O99" t="n">
-        <v>702176</v>
+        <v>592885</v>
       </c>
       <c r="P99" t="inlineStr">
         <is>
-          <t>RF</t>
+          <t>DH</t>
         </is>
       </c>
       <c r="Q99" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>1</t>
         </is>
       </c>
       <c r="R99" t="n">
+        <v>5</v>
+      </c>
+      <c r="S99" t="n">
         <v>3</v>
       </c>
-      <c r="S99" t="n">
+      <c r="T99" t="n">
+        <v>1</v>
+      </c>
+      <c r="U99" t="n">
+        <v>1</v>
+      </c>
+      <c r="V99" t="n">
+        <v>0</v>
+      </c>
+      <c r="W99" t="n">
+        <v>0</v>
+      </c>
+      <c r="X99" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y99" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z99" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA99" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="AB99" s="9" t="n">
+        <v>1</v>
+      </c>
+      <c r="AC99" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD99" t="n">
         <v>2</v>
-      </c>
-      <c r="T99" t="n">
-        <v>1</v>
-      </c>
-      <c r="U99" t="n">
-        <v>1</v>
-      </c>
-      <c r="V99" t="n">
-        <v>0</v>
-      </c>
-      <c r="W99" t="n">
-        <v>0</v>
-      </c>
-      <c r="X99" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y99" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z99" t="n">
-        <v>1</v>
-      </c>
-      <c r="AA99" s="5" t="n">
-        <v>1</v>
-      </c>
-      <c r="AB99" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC99" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD99" t="n">
-        <v>0</v>
       </c>
       <c r="AE99" s="4" t="n">
         <v>7</v>
       </c>
       <c r="AF99" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="AG99" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
     </row>
     <row r="100">
@@ -11991,15 +12000,15 @@
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>2026-07-11 08:15:17 PM PT</t>
+          <t>2026-07-11 08:17:17 PM PT</t>
         </is>
       </c>
       <c r="C100" t="n">
-        <v>823603</v>
+        <v>823682</v>
       </c>
       <c r="D100" t="inlineStr">
         <is>
-          <t>1:10 PM PT</t>
+          <t>11:10 AM PT</t>
         </is>
       </c>
       <c r="E100" t="inlineStr">
@@ -12012,7 +12021,7 @@
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t>Bottom</t>
+          <t>Top</t>
         </is>
       </c>
       <c r="K100" t="inlineStr">
@@ -12022,21 +12031,21 @@
       </c>
       <c r="L100" t="inlineStr">
         <is>
-          <t>NYM</t>
+          <t>MIN</t>
         </is>
       </c>
       <c r="M100" t="inlineStr">
         <is>
-          <t>BOS</t>
+          <t>LAA</t>
         </is>
       </c>
       <c r="N100" t="inlineStr">
         <is>
-          <t>Carson Benge</t>
+          <t>Alan Roden</t>
         </is>
       </c>
       <c r="O100" t="n">
-        <v>701807</v>
+        <v>702176</v>
       </c>
       <c r="P100" t="inlineStr">
         <is>
@@ -12045,20 +12054,20 @@
       </c>
       <c r="Q100" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>7</t>
         </is>
       </c>
       <c r="R100" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="S100" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="T100" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="U100" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="V100" t="n">
         <v>0</v>
@@ -12073,7 +12082,7 @@
         <v>0</v>
       </c>
       <c r="Z100" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AA100" s="5" t="n">
         <v>1</v>
@@ -12081,20 +12090,20 @@
       <c r="AB100" t="n">
         <v>0</v>
       </c>
-      <c r="AC100" s="6" t="n">
-        <v>1</v>
+      <c r="AC100" t="n">
+        <v>0</v>
       </c>
       <c r="AD100" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AE100" s="4" t="n">
         <v>7</v>
       </c>
       <c r="AF100" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="AG100" t="n">
-        <v>3</v>
+        <v>9</v>
       </c>
     </row>
     <row r="101">
@@ -12105,119 +12114,110 @@
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>2026-07-11 08:15:19 PM PT</t>
+          <t>2026-07-11 08:17:17 PM PT</t>
         </is>
       </c>
       <c r="C101" t="n">
-        <v>823276</v>
+        <v>823603</v>
       </c>
       <c r="D101" t="inlineStr">
         <is>
-          <t>5:40 PM PT</t>
+          <t>1:10 PM PT</t>
         </is>
       </c>
       <c r="E101" t="inlineStr">
         <is>
-          <t>Bottom 7 | 0 out</t>
+          <t>Final</t>
         </is>
       </c>
       <c r="F101" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="G101" t="inlineStr">
         <is>
           <t>Bottom</t>
         </is>
       </c>
-      <c r="H101" t="n">
-        <v>0</v>
-      </c>
-      <c r="I101" t="n">
+      <c r="K101" t="inlineStr">
+        <is>
+          <t>Home</t>
+        </is>
+      </c>
+      <c r="L101" t="inlineStr">
+        <is>
+          <t>NYM</t>
+        </is>
+      </c>
+      <c r="M101" t="inlineStr">
+        <is>
+          <t>BOS</t>
+        </is>
+      </c>
+      <c r="N101" t="inlineStr">
+        <is>
+          <t>Carson Benge</t>
+        </is>
+      </c>
+      <c r="O101" t="n">
+        <v>701807</v>
+      </c>
+      <c r="P101" t="inlineStr">
+        <is>
+          <t>RF</t>
+        </is>
+      </c>
+      <c r="Q101" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="R101" t="n">
+        <v>4</v>
+      </c>
+      <c r="S101" t="n">
+        <v>3</v>
+      </c>
+      <c r="T101" t="n">
+        <v>0</v>
+      </c>
+      <c r="U101" t="n">
+        <v>0</v>
+      </c>
+      <c r="V101" t="n">
+        <v>0</v>
+      </c>
+      <c r="W101" t="n">
+        <v>0</v>
+      </c>
+      <c r="X101" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y101" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z101" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA101" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="AB101" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC101" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="AD101" t="n">
         <v>2</v>
-      </c>
-      <c r="J101" t="n">
-        <v>1</v>
-      </c>
-      <c r="K101" t="inlineStr">
-        <is>
-          <t>Home</t>
-        </is>
-      </c>
-      <c r="L101" t="inlineStr">
-        <is>
-          <t>SD</t>
-        </is>
-      </c>
-      <c r="M101" t="inlineStr">
-        <is>
-          <t>TOR</t>
-        </is>
-      </c>
-      <c r="N101" t="inlineStr">
-        <is>
-          <t>Manny Machado</t>
-        </is>
-      </c>
-      <c r="O101" t="n">
-        <v>592518</v>
-      </c>
-      <c r="P101" t="inlineStr">
-        <is>
-          <t>DH</t>
-        </is>
-      </c>
-      <c r="Q101" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="R101" t="n">
-        <v>4</v>
-      </c>
-      <c r="S101" t="n">
-        <v>4</v>
-      </c>
-      <c r="T101" t="n">
-        <v>1</v>
-      </c>
-      <c r="U101" t="n">
-        <v>1</v>
-      </c>
-      <c r="V101" t="n">
-        <v>0</v>
-      </c>
-      <c r="W101" t="n">
-        <v>0</v>
-      </c>
-      <c r="X101" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y101" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z101" t="n">
-        <v>2</v>
-      </c>
-      <c r="AA101" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB101" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC101" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD101" t="n">
-        <v>1</v>
       </c>
       <c r="AE101" s="4" t="n">
         <v>7</v>
       </c>
       <c r="AF101" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="AG101" t="n">
-        <v>7</v>
+        <v>3</v>
       </c>
     </row>
     <row r="102">
@@ -12228,92 +12228,101 @@
       </c>
       <c r="B102" t="inlineStr">
         <is>
-          <t>2026-07-11 08:15:18 PM PT</t>
+          <t>2026-07-11 08:17:18 PM PT</t>
         </is>
       </c>
       <c r="C102" t="n">
-        <v>822953</v>
+        <v>823276</v>
       </c>
       <c r="D102" t="inlineStr">
         <is>
-          <t>1:10 PM PT</t>
+          <t>5:40 PM PT</t>
         </is>
       </c>
       <c r="E102" t="inlineStr">
         <is>
-          <t>Final</t>
+          <t>Bottom 7 | 1 out</t>
         </is>
       </c>
       <c r="F102" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="G102" t="inlineStr">
         <is>
-          <t>Top</t>
-        </is>
+          <t>Bottom</t>
+        </is>
+      </c>
+      <c r="H102" t="n">
+        <v>1</v>
+      </c>
+      <c r="I102" t="n">
+        <v>0</v>
+      </c>
+      <c r="J102" t="n">
+        <v>0</v>
       </c>
       <c r="K102" t="inlineStr">
         <is>
-          <t>Away</t>
+          <t>Home</t>
         </is>
       </c>
       <c r="L102" t="inlineStr">
         <is>
-          <t>SEA</t>
+          <t>SD</t>
         </is>
       </c>
       <c r="M102" t="inlineStr">
         <is>
-          <t>TB</t>
+          <t>TOR</t>
         </is>
       </c>
       <c r="N102" t="inlineStr">
         <is>
-          <t>Randy Arozarena</t>
+          <t>Manny Machado</t>
         </is>
       </c>
       <c r="O102" t="n">
-        <v>668227</v>
+        <v>592518</v>
       </c>
       <c r="P102" t="inlineStr">
         <is>
-          <t>LF</t>
+          <t>DH</t>
         </is>
       </c>
       <c r="Q102" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>4</t>
         </is>
       </c>
       <c r="R102" t="n">
         <v>4</v>
       </c>
       <c r="S102" t="n">
+        <v>4</v>
+      </c>
+      <c r="T102" t="n">
+        <v>1</v>
+      </c>
+      <c r="U102" t="n">
+        <v>1</v>
+      </c>
+      <c r="V102" t="n">
+        <v>0</v>
+      </c>
+      <c r="W102" t="n">
+        <v>0</v>
+      </c>
+      <c r="X102" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y102" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z102" t="n">
         <v>2</v>
       </c>
-      <c r="T102" t="n">
-        <v>1</v>
-      </c>
-      <c r="U102" t="n">
-        <v>1</v>
-      </c>
-      <c r="V102" t="n">
-        <v>0</v>
-      </c>
-      <c r="W102" t="n">
-        <v>0</v>
-      </c>
-      <c r="X102" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y102" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z102" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA102" s="5" t="n">
-        <v>2</v>
+      <c r="AA102" t="n">
+        <v>0</v>
       </c>
       <c r="AB102" t="n">
         <v>0</v>
@@ -12322,16 +12331,16 @@
         <v>0</v>
       </c>
       <c r="AD102" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AE102" s="4" t="n">
         <v>7</v>
       </c>
       <c r="AF102" t="n">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="AG102" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
     </row>
     <row r="103">
@@ -12342,7 +12351,7 @@
       </c>
       <c r="B103" t="inlineStr">
         <is>
-          <t>2026-07-11 08:15:18 PM PT</t>
+          <t>2026-07-11 08:17:17 PM PT</t>
         </is>
       </c>
       <c r="C103" t="n">
@@ -12383,20 +12392,20 @@
       </c>
       <c r="N103" t="inlineStr">
         <is>
-          <t>Cal Raleigh</t>
+          <t>Randy Arozarena</t>
         </is>
       </c>
       <c r="O103" t="n">
-        <v>663728</v>
+        <v>668227</v>
       </c>
       <c r="P103" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>LF</t>
         </is>
       </c>
       <c r="Q103" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>2</t>
         </is>
       </c>
       <c r="R103" t="n">
@@ -12436,7 +12445,7 @@
         <v>0</v>
       </c>
       <c r="AD103" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AE103" s="4" t="n">
         <v>7</v>
@@ -12456,7 +12465,7 @@
       </c>
       <c r="B104" t="inlineStr">
         <is>
-          <t>2026-07-11 08:15:18 PM PT</t>
+          <t>2026-07-11 08:17:17 PM PT</t>
         </is>
       </c>
       <c r="C104" t="n">
@@ -12497,36 +12506,36 @@
       </c>
       <c r="N104" t="inlineStr">
         <is>
-          <t>Cole Young</t>
+          <t>Cal Raleigh</t>
         </is>
       </c>
       <c r="O104" t="n">
-        <v>702284</v>
+        <v>663728</v>
       </c>
       <c r="P104" t="inlineStr">
         <is>
-          <t>2B</t>
+          <t>C</t>
         </is>
       </c>
       <c r="Q104" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>4</t>
         </is>
       </c>
       <c r="R104" t="n">
         <v>4</v>
       </c>
       <c r="S104" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="T104" t="n">
         <v>1</v>
       </c>
       <c r="U104" t="n">
-        <v>0</v>
-      </c>
-      <c r="V104" s="7" t="n">
-        <v>1</v>
+        <v>1</v>
+      </c>
+      <c r="V104" t="n">
+        <v>0</v>
       </c>
       <c r="W104" t="n">
         <v>0</v>
@@ -12535,13 +12544,13 @@
         <v>0</v>
       </c>
       <c r="Y104" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Z104" t="n">
         <v>0</v>
       </c>
-      <c r="AA104" t="n">
-        <v>0</v>
+      <c r="AA104" s="5" t="n">
+        <v>2</v>
       </c>
       <c r="AB104" t="n">
         <v>0</v>
@@ -12570,15 +12579,15 @@
       </c>
       <c r="B105" t="inlineStr">
         <is>
-          <t>2026-07-11 08:15:17 PM PT</t>
+          <t>2026-07-11 08:17:17 PM PT</t>
         </is>
       </c>
       <c r="C105" t="n">
-        <v>823198</v>
+        <v>822953</v>
       </c>
       <c r="D105" t="inlineStr">
         <is>
-          <t>1:05 PM PT</t>
+          <t>1:10 PM PT</t>
         </is>
       </c>
       <c r="E105" t="inlineStr">
@@ -12596,42 +12605,42 @@
       </c>
       <c r="K105" t="inlineStr">
         <is>
-          <t>Home</t>
+          <t>Away</t>
         </is>
       </c>
       <c r="L105" t="inlineStr">
         <is>
-          <t>SF</t>
+          <t>SEA</t>
         </is>
       </c>
       <c r="M105" t="inlineStr">
         <is>
-          <t>COL</t>
+          <t>TB</t>
         </is>
       </c>
       <c r="N105" t="inlineStr">
         <is>
-          <t>Bryce Eldridge</t>
+          <t>Cole Young</t>
         </is>
       </c>
       <c r="O105" t="n">
-        <v>805811</v>
+        <v>702284</v>
       </c>
       <c r="P105" t="inlineStr">
         <is>
-          <t>DH</t>
+          <t>2B</t>
         </is>
       </c>
       <c r="Q105" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="R105" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="S105" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="T105" t="n">
         <v>1</v>
@@ -12664,16 +12673,16 @@
         <v>0</v>
       </c>
       <c r="AD105" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AE105" s="4" t="n">
         <v>7</v>
       </c>
       <c r="AF105" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="AG105" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
     </row>
     <row r="106">
@@ -12684,7 +12693,7 @@
       </c>
       <c r="B106" t="inlineStr">
         <is>
-          <t>2026-07-11 08:15:17 PM PT</t>
+          <t>2026-07-11 08:17:17 PM PT</t>
         </is>
       </c>
       <c r="C106" t="n">
@@ -12725,20 +12734,20 @@
       </c>
       <c r="N106" t="inlineStr">
         <is>
-          <t>Jesus Rodriguez</t>
+          <t>Bryce Eldridge</t>
         </is>
       </c>
       <c r="O106" t="n">
-        <v>683679</v>
+        <v>805811</v>
       </c>
       <c r="P106" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>DH</t>
         </is>
       </c>
       <c r="Q106" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>6</t>
         </is>
       </c>
       <c r="R106" t="n">
@@ -12763,10 +12772,10 @@
         <v>0</v>
       </c>
       <c r="Y106" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Z106" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AA106" t="n">
         <v>0</v>
@@ -12778,7 +12787,7 @@
         <v>0</v>
       </c>
       <c r="AD106" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AE106" s="4" t="n">
         <v>7</v>
@@ -12798,15 +12807,15 @@
       </c>
       <c r="B107" t="inlineStr">
         <is>
-          <t>2026-07-11 08:15:18 PM PT</t>
+          <t>2026-07-11 08:17:17 PM PT</t>
         </is>
       </c>
       <c r="C107" t="n">
-        <v>822953</v>
+        <v>823198</v>
       </c>
       <c r="D107" t="inlineStr">
         <is>
-          <t>1:10 PM PT</t>
+          <t>1:05 PM PT</t>
         </is>
       </c>
       <c r="E107" t="inlineStr">
@@ -12829,37 +12838,37 @@
       </c>
       <c r="L107" t="inlineStr">
         <is>
-          <t>TB</t>
+          <t>SF</t>
         </is>
       </c>
       <c r="M107" t="inlineStr">
         <is>
-          <t>SEA</t>
+          <t>COL</t>
         </is>
       </c>
       <c r="N107" t="inlineStr">
         <is>
-          <t>Yandy Díaz</t>
+          <t>Jesus Rodriguez</t>
         </is>
       </c>
       <c r="O107" t="n">
-        <v>650490</v>
+        <v>683679</v>
       </c>
       <c r="P107" t="inlineStr">
         <is>
-          <t>DH</t>
+          <t>C</t>
         </is>
       </c>
       <c r="Q107" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>8</t>
         </is>
       </c>
       <c r="R107" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="S107" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="T107" t="n">
         <v>1</v>
@@ -12877,10 +12886,10 @@
         <v>0</v>
       </c>
       <c r="Y107" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Z107" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AA107" t="n">
         <v>0</v>
@@ -12898,10 +12907,10 @@
         <v>7</v>
       </c>
       <c r="AF107" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="AG107" t="n">
-        <v>12</v>
+        <v>7</v>
       </c>
     </row>
     <row r="108">
@@ -12912,119 +12921,110 @@
       </c>
       <c r="B108" t="inlineStr">
         <is>
-          <t>2026-07-11 08:15:19 PM PT</t>
+          <t>2026-07-11 08:17:17 PM PT</t>
         </is>
       </c>
       <c r="C108" t="n">
-        <v>823926</v>
+        <v>822953</v>
       </c>
       <c r="D108" t="inlineStr">
         <is>
-          <t>6:10 PM PT</t>
+          <t>1:10 PM PT</t>
         </is>
       </c>
       <c r="E108" t="inlineStr">
         <is>
-          <t>Top 7 | 1 out</t>
+          <t>Final</t>
         </is>
       </c>
       <c r="F108" t="n">
+        <v>9</v>
+      </c>
+      <c r="G108" t="inlineStr">
+        <is>
+          <t>Top</t>
+        </is>
+      </c>
+      <c r="K108" t="inlineStr">
+        <is>
+          <t>Home</t>
+        </is>
+      </c>
+      <c r="L108" t="inlineStr">
+        <is>
+          <t>TB</t>
+        </is>
+      </c>
+      <c r="M108" t="inlineStr">
+        <is>
+          <t>SEA</t>
+        </is>
+      </c>
+      <c r="N108" t="inlineStr">
+        <is>
+          <t>Yandy Díaz</t>
+        </is>
+      </c>
+      <c r="O108" t="n">
+        <v>650490</v>
+      </c>
+      <c r="P108" t="inlineStr">
+        <is>
+          <t>DH</t>
+        </is>
+      </c>
+      <c r="Q108" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="R108" t="n">
+        <v>5</v>
+      </c>
+      <c r="S108" t="n">
+        <v>5</v>
+      </c>
+      <c r="T108" t="n">
+        <v>1</v>
+      </c>
+      <c r="U108" t="n">
+        <v>0</v>
+      </c>
+      <c r="V108" s="7" t="n">
+        <v>1</v>
+      </c>
+      <c r="W108" t="n">
+        <v>0</v>
+      </c>
+      <c r="X108" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y108" t="n">
+        <v>1</v>
+      </c>
+      <c r="Z108" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA108" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB108" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC108" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD108" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE108" s="4" t="n">
         <v>7</v>
-      </c>
-      <c r="G108" t="inlineStr">
-        <is>
-          <t>Top</t>
-        </is>
-      </c>
-      <c r="H108" t="n">
-        <v>1</v>
-      </c>
-      <c r="I108" t="n">
-        <v>1</v>
-      </c>
-      <c r="J108" t="n">
-        <v>1</v>
-      </c>
-      <c r="K108" t="inlineStr">
-        <is>
-          <t>Away</t>
-        </is>
-      </c>
-      <c r="L108" t="inlineStr">
-        <is>
-          <t>ARI</t>
-        </is>
-      </c>
-      <c r="M108" t="inlineStr">
-        <is>
-          <t>LAD</t>
-        </is>
-      </c>
-      <c r="N108" t="inlineStr">
-        <is>
-          <t>Geraldo Perdomo</t>
-        </is>
-      </c>
-      <c r="O108" t="n">
-        <v>672695</v>
-      </c>
-      <c r="P108" t="inlineStr">
-        <is>
-          <t>SS</t>
-        </is>
-      </c>
-      <c r="Q108" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="R108" t="n">
-        <v>4</v>
-      </c>
-      <c r="S108" t="n">
-        <v>2</v>
-      </c>
-      <c r="T108" t="n">
-        <v>0</v>
-      </c>
-      <c r="U108" t="n">
-        <v>0</v>
-      </c>
-      <c r="V108" t="n">
-        <v>0</v>
-      </c>
-      <c r="W108" t="n">
-        <v>0</v>
-      </c>
-      <c r="X108" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y108" t="n">
-        <v>1</v>
-      </c>
-      <c r="Z108" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA108" s="5" t="n">
-        <v>1</v>
-      </c>
-      <c r="AB108" s="9" t="n">
-        <v>1</v>
-      </c>
-      <c r="AC108" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD108" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE108" s="4" t="n">
-        <v>6</v>
       </c>
       <c r="AF108" t="n">
         <v>6</v>
       </c>
       <c r="AG108" t="n">
-        <v>5</v>
+        <v>12</v>
       </c>
     </row>
     <row r="109">
@@ -13035,7 +13035,7 @@
       </c>
       <c r="B109" t="inlineStr">
         <is>
-          <t>2026-07-11 08:15:17 PM PT</t>
+          <t>2026-07-11 08:17:17 PM PT</t>
         </is>
       </c>
       <c r="C109" t="n">
@@ -13149,7 +13149,7 @@
       </c>
       <c r="B110" t="inlineStr">
         <is>
-          <t>2026-07-11 08:15:18 PM PT</t>
+          <t>2026-07-11 08:17:18 PM PT</t>
         </is>
       </c>
       <c r="C110" t="n">
@@ -13263,7 +13263,7 @@
       </c>
       <c r="B111" t="inlineStr">
         <is>
-          <t>2026-07-11 08:15:18 PM PT</t>
+          <t>2026-07-11 08:17:18 PM PT</t>
         </is>
       </c>
       <c r="C111" t="n">
@@ -13377,7 +13377,7 @@
       </c>
       <c r="B112" t="inlineStr">
         <is>
-          <t>2026-07-11 08:15:17 PM PT</t>
+          <t>2026-07-11 08:17:17 PM PT</t>
         </is>
       </c>
       <c r="C112" t="n">
@@ -13491,7 +13491,7 @@
       </c>
       <c r="B113" t="inlineStr">
         <is>
-          <t>2026-07-11 08:15:18 PM PT</t>
+          <t>2026-07-11 08:17:18 PM PT</t>
         </is>
       </c>
       <c r="C113" t="n">
@@ -13605,7 +13605,7 @@
       </c>
       <c r="B114" t="inlineStr">
         <is>
-          <t>2026-07-11 08:15:19 PM PT</t>
+          <t>2026-07-11 08:17:18 PM PT</t>
         </is>
       </c>
       <c r="C114" t="n">
@@ -13618,7 +13618,7 @@
       </c>
       <c r="E114" t="inlineStr">
         <is>
-          <t>Bottom 7 | 0 out</t>
+          <t>Bottom 7 | 1 out</t>
         </is>
       </c>
       <c r="F114" t="n">
@@ -13630,13 +13630,13 @@
         </is>
       </c>
       <c r="H114" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I114" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="J114" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K114" t="inlineStr">
         <is>
@@ -13728,7 +13728,7 @@
       </c>
       <c r="B115" t="inlineStr">
         <is>
-          <t>2026-07-11 08:15:18 PM PT</t>
+          <t>2026-07-11 08:17:18 PM PT</t>
         </is>
       </c>
       <c r="C115" t="n">
@@ -13842,7 +13842,7 @@
       </c>
       <c r="B116" t="inlineStr">
         <is>
-          <t>2026-07-11 08:15:19 PM PT</t>
+          <t>2026-07-11 08:17:18 PM PT</t>
         </is>
       </c>
       <c r="C116" t="n">
@@ -13870,10 +13870,10 @@
         <v>1</v>
       </c>
       <c r="I116" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="J116" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K116" t="inlineStr">
         <is>
@@ -13965,7 +13965,7 @@
       </c>
       <c r="B117" t="inlineStr">
         <is>
-          <t>2026-07-11 08:15:18 PM PT</t>
+          <t>2026-07-11 08:17:18 PM PT</t>
         </is>
       </c>
       <c r="C117" t="n">
@@ -14079,7 +14079,7 @@
       </c>
       <c r="B118" t="inlineStr">
         <is>
-          <t>2026-07-11 08:15:18 PM PT</t>
+          <t>2026-07-11 08:17:18 PM PT</t>
         </is>
       </c>
       <c r="C118" t="n">
@@ -14193,7 +14193,7 @@
       </c>
       <c r="B119" t="inlineStr">
         <is>
-          <t>2026-07-11 08:15:18 PM PT</t>
+          <t>2026-07-11 08:17:18 PM PT</t>
         </is>
       </c>
       <c r="C119" t="n">
@@ -14307,7 +14307,7 @@
       </c>
       <c r="B120" t="inlineStr">
         <is>
-          <t>2026-07-11 08:15:17 PM PT</t>
+          <t>2026-07-11 08:17:17 PM PT</t>
         </is>
       </c>
       <c r="C120" t="n">
@@ -14421,7 +14421,7 @@
       </c>
       <c r="B121" t="inlineStr">
         <is>
-          <t>2026-07-11 08:15:18 PM PT</t>
+          <t>2026-07-11 08:17:18 PM PT</t>
         </is>
       </c>
       <c r="C121" t="n">
@@ -14535,7 +14535,7 @@
       </c>
       <c r="B122" t="inlineStr">
         <is>
-          <t>2026-07-11 08:15:17 PM PT</t>
+          <t>2026-07-11 08:17:17 PM PT</t>
         </is>
       </c>
       <c r="C122" t="n">
@@ -14649,7 +14649,7 @@
       </c>
       <c r="B123" t="inlineStr">
         <is>
-          <t>2026-07-11 08:15:17 PM PT</t>
+          <t>2026-07-11 08:17:17 PM PT</t>
         </is>
       </c>
       <c r="C123" t="n">
@@ -14763,7 +14763,7 @@
       </c>
       <c r="B124" t="inlineStr">
         <is>
-          <t>2026-07-11 08:15:18 PM PT</t>
+          <t>2026-07-11 08:17:18 PM PT</t>
         </is>
       </c>
       <c r="C124" t="n">
@@ -14877,7 +14877,7 @@
       </c>
       <c r="B125" t="inlineStr">
         <is>
-          <t>2026-07-11 08:15:18 PM PT</t>
+          <t>2026-07-11 08:17:18 PM PT</t>
         </is>
       </c>
       <c r="C125" t="n">
@@ -14991,7 +14991,7 @@
       </c>
       <c r="B126" t="inlineStr">
         <is>
-          <t>2026-07-11 08:15:18 PM PT</t>
+          <t>2026-07-11 08:17:18 PM PT</t>
         </is>
       </c>
       <c r="C126" t="n">
@@ -15105,7 +15105,7 @@
       </c>
       <c r="B127" t="inlineStr">
         <is>
-          <t>2026-07-11 08:15:18 PM PT</t>
+          <t>2026-07-11 08:17:18 PM PT</t>
         </is>
       </c>
       <c r="C127" t="n">
@@ -15219,7 +15219,7 @@
       </c>
       <c r="B128" t="inlineStr">
         <is>
-          <t>2026-07-11 08:15:19 PM PT</t>
+          <t>2026-07-11 08:17:18 PM PT</t>
         </is>
       </c>
       <c r="C128" t="n">
@@ -15247,10 +15247,10 @@
         <v>1</v>
       </c>
       <c r="I128" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="J128" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K128" t="inlineStr">
         <is>
@@ -15342,7 +15342,7 @@
       </c>
       <c r="B129" t="inlineStr">
         <is>
-          <t>2026-07-11 08:15:18 PM PT</t>
+          <t>2026-07-11 08:17:18 PM PT</t>
         </is>
       </c>
       <c r="C129" t="n">
@@ -15456,7 +15456,7 @@
       </c>
       <c r="B130" t="inlineStr">
         <is>
-          <t>2026-07-11 08:15:18 PM PT</t>
+          <t>2026-07-11 08:17:18 PM PT</t>
         </is>
       </c>
       <c r="C130" t="n">
@@ -15570,7 +15570,7 @@
       </c>
       <c r="B131" t="inlineStr">
         <is>
-          <t>2026-07-11 08:15:17 PM PT</t>
+          <t>2026-07-11 08:17:16 PM PT</t>
         </is>
       </c>
       <c r="C131" t="n">
@@ -15684,7 +15684,7 @@
       </c>
       <c r="B132" t="inlineStr">
         <is>
-          <t>2026-07-11 08:15:17 PM PT</t>
+          <t>2026-07-11 08:17:17 PM PT</t>
         </is>
       </c>
       <c r="C132" t="n">
@@ -15798,7 +15798,7 @@
       </c>
       <c r="B133" t="inlineStr">
         <is>
-          <t>2026-07-11 08:15:17 PM PT</t>
+          <t>2026-07-11 08:17:17 PM PT</t>
         </is>
       </c>
       <c r="C133" t="n">
@@ -15912,7 +15912,7 @@
       </c>
       <c r="B134" t="inlineStr">
         <is>
-          <t>2026-07-11 08:15:17 PM PT</t>
+          <t>2026-07-11 08:17:17 PM PT</t>
         </is>
       </c>
       <c r="C134" t="n">
@@ -16026,7 +16026,7 @@
       </c>
       <c r="B135" t="inlineStr">
         <is>
-          <t>2026-07-11 08:15:16 PM PT</t>
+          <t>2026-07-11 08:17:16 PM PT</t>
         </is>
       </c>
       <c r="C135" t="n">
@@ -16140,7 +16140,7 @@
       </c>
       <c r="B136" t="inlineStr">
         <is>
-          <t>2026-07-11 08:15:16 PM PT</t>
+          <t>2026-07-11 08:17:16 PM PT</t>
         </is>
       </c>
       <c r="C136" t="n">
@@ -16254,7 +16254,7 @@
       </c>
       <c r="B137" t="inlineStr">
         <is>
-          <t>2026-07-11 08:15:18 PM PT</t>
+          <t>2026-07-11 08:17:17 PM PT</t>
         </is>
       </c>
       <c r="C137" t="n">
@@ -16368,7 +16368,7 @@
       </c>
       <c r="B138" t="inlineStr">
         <is>
-          <t>2026-07-11 08:15:18 PM PT</t>
+          <t>2026-07-11 08:17:17 PM PT</t>
         </is>
       </c>
       <c r="C138" t="n">
@@ -16482,7 +16482,7 @@
       </c>
       <c r="B139" t="inlineStr">
         <is>
-          <t>2026-07-11 08:15:17 PM PT</t>
+          <t>2026-07-11 08:17:17 PM PT</t>
         </is>
       </c>
       <c r="C139" t="n">
@@ -16596,7 +16596,7 @@
       </c>
       <c r="B140" t="inlineStr">
         <is>
-          <t>2026-07-11 08:15:18 PM PT</t>
+          <t>2026-07-11 08:17:18 PM PT</t>
         </is>
       </c>
       <c r="C140" t="n">
@@ -16710,7 +16710,7 @@
       </c>
       <c r="B141" t="inlineStr">
         <is>
-          <t>2026-07-11 08:15:18 PM PT</t>
+          <t>2026-07-11 08:17:18 PM PT</t>
         </is>
       </c>
       <c r="C141" t="n">
@@ -16824,7 +16824,7 @@
       </c>
       <c r="B142" t="inlineStr">
         <is>
-          <t>2026-07-11 08:15:18 PM PT</t>
+          <t>2026-07-11 08:17:18 PM PT</t>
         </is>
       </c>
       <c r="C142" t="n">
@@ -16938,7 +16938,7 @@
       </c>
       <c r="B143" t="inlineStr">
         <is>
-          <t>2026-07-11 08:15:18 PM PT</t>
+          <t>2026-07-11 08:17:17 PM PT</t>
         </is>
       </c>
       <c r="C143" t="n">
@@ -17052,7 +17052,7 @@
       </c>
       <c r="B144" t="inlineStr">
         <is>
-          <t>2026-07-11 08:15:18 PM PT</t>
+          <t>2026-07-11 08:17:18 PM PT</t>
         </is>
       </c>
       <c r="C144" t="n">
@@ -17166,7 +17166,7 @@
       </c>
       <c r="B145" t="inlineStr">
         <is>
-          <t>2026-07-11 08:15:18 PM PT</t>
+          <t>2026-07-11 08:17:18 PM PT</t>
         </is>
       </c>
       <c r="C145" t="n">
@@ -17280,7 +17280,7 @@
       </c>
       <c r="B146" t="inlineStr">
         <is>
-          <t>2026-07-11 08:15:19 PM PT</t>
+          <t>2026-07-11 08:17:18 PM PT</t>
         </is>
       </c>
       <c r="C146" t="n">
@@ -17308,10 +17308,10 @@
         <v>1</v>
       </c>
       <c r="I146" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="J146" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K146" t="inlineStr">
         <is>
@@ -17403,7 +17403,7 @@
       </c>
       <c r="B147" t="inlineStr">
         <is>
-          <t>2026-07-11 08:15:18 PM PT</t>
+          <t>2026-07-11 08:17:18 PM PT</t>
         </is>
       </c>
       <c r="C147" t="n">
@@ -17517,7 +17517,7 @@
       </c>
       <c r="B148" t="inlineStr">
         <is>
-          <t>2026-07-11 08:15:18 PM PT</t>
+          <t>2026-07-11 08:17:18 PM PT</t>
         </is>
       </c>
       <c r="C148" t="n">
@@ -17631,7 +17631,7 @@
       </c>
       <c r="B149" t="inlineStr">
         <is>
-          <t>2026-07-11 08:15:17 PM PT</t>
+          <t>2026-07-11 08:17:17 PM PT</t>
         </is>
       </c>
       <c r="C149" t="n">
@@ -17745,7 +17745,7 @@
       </c>
       <c r="B150" t="inlineStr">
         <is>
-          <t>2026-07-11 08:15:16 PM PT</t>
+          <t>2026-07-11 08:17:16 PM PT</t>
         </is>
       </c>
       <c r="C150" t="n">
@@ -17859,7 +17859,7 @@
       </c>
       <c r="B151" t="inlineStr">
         <is>
-          <t>2026-07-11 08:15:17 PM PT</t>
+          <t>2026-07-11 08:17:16 PM PT</t>
         </is>
       </c>
       <c r="C151" t="n">
@@ -17973,7 +17973,7 @@
       </c>
       <c r="B152" t="inlineStr">
         <is>
-          <t>2026-07-11 08:15:17 PM PT</t>
+          <t>2026-07-11 08:17:17 PM PT</t>
         </is>
       </c>
       <c r="C152" t="n">
@@ -18087,7 +18087,7 @@
       </c>
       <c r="B153" t="inlineStr">
         <is>
-          <t>2026-07-11 08:15:18 PM PT</t>
+          <t>2026-07-11 08:17:18 PM PT</t>
         </is>
       </c>
       <c r="C153" t="n">
@@ -18201,7 +18201,7 @@
       </c>
       <c r="B154" t="inlineStr">
         <is>
-          <t>2026-07-11 08:15:18 PM PT</t>
+          <t>2026-07-11 08:17:18 PM PT</t>
         </is>
       </c>
       <c r="C154" t="n">
@@ -18315,7 +18315,7 @@
       </c>
       <c r="B155" t="inlineStr">
         <is>
-          <t>2026-07-11 08:15:16 PM PT</t>
+          <t>2026-07-11 08:17:16 PM PT</t>
         </is>
       </c>
       <c r="C155" t="n">
@@ -18429,7 +18429,7 @@
       </c>
       <c r="B156" t="inlineStr">
         <is>
-          <t>2026-07-11 08:15:19 PM PT</t>
+          <t>2026-07-11 08:17:18 PM PT</t>
         </is>
       </c>
       <c r="C156" t="n">
@@ -18442,7 +18442,7 @@
       </c>
       <c r="E156" t="inlineStr">
         <is>
-          <t>Bottom 7 | 0 out</t>
+          <t>Bottom 7 | 1 out</t>
         </is>
       </c>
       <c r="F156" t="n">
@@ -18454,13 +18454,13 @@
         </is>
       </c>
       <c r="H156" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I156" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="J156" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K156" t="inlineStr">
         <is>
@@ -18552,7 +18552,7 @@
       </c>
       <c r="B157" t="inlineStr">
         <is>
-          <t>2026-07-11 08:15:19 PM PT</t>
+          <t>2026-07-11 08:17:18 PM PT</t>
         </is>
       </c>
       <c r="C157" t="n">
@@ -18565,7 +18565,7 @@
       </c>
       <c r="E157" t="inlineStr">
         <is>
-          <t>Bottom 7 | 0 out</t>
+          <t>Bottom 7 | 1 out</t>
         </is>
       </c>
       <c r="F157" t="n">
@@ -18577,13 +18577,13 @@
         </is>
       </c>
       <c r="H157" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I157" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="J157" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K157" t="inlineStr">
         <is>
@@ -18675,7 +18675,7 @@
       </c>
       <c r="B158" t="inlineStr">
         <is>
-          <t>2026-07-11 08:15:19 PM PT</t>
+          <t>2026-07-11 08:17:18 PM PT</t>
         </is>
       </c>
       <c r="C158" t="n">
@@ -18688,7 +18688,7 @@
       </c>
       <c r="E158" t="inlineStr">
         <is>
-          <t>Bottom 7 | 0 out</t>
+          <t>Bottom 7 | 1 out</t>
         </is>
       </c>
       <c r="F158" t="n">
@@ -18700,13 +18700,13 @@
         </is>
       </c>
       <c r="H158" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I158" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="J158" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K158" t="inlineStr">
         <is>
@@ -18798,7 +18798,7 @@
       </c>
       <c r="B159" t="inlineStr">
         <is>
-          <t>2026-07-11 08:15:19 PM PT</t>
+          <t>2026-07-11 08:17:18 PM PT</t>
         </is>
       </c>
       <c r="C159" t="n">
@@ -18811,7 +18811,7 @@
       </c>
       <c r="E159" t="inlineStr">
         <is>
-          <t>Bottom 7 | 0 out</t>
+          <t>Bottom 7 | 1 out</t>
         </is>
       </c>
       <c r="F159" t="n">
@@ -18823,13 +18823,13 @@
         </is>
       </c>
       <c r="H159" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I159" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="J159" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K159" t="inlineStr">
         <is>
@@ -18921,7 +18921,7 @@
       </c>
       <c r="B160" t="inlineStr">
         <is>
-          <t>2026-07-11 08:15:18 PM PT</t>
+          <t>2026-07-11 08:17:18 PM PT</t>
         </is>
       </c>
       <c r="C160" t="n">
@@ -19035,7 +19035,7 @@
       </c>
       <c r="B161" t="inlineStr">
         <is>
-          <t>2026-07-11 08:15:18 PM PT</t>
+          <t>2026-07-11 08:17:18 PM PT</t>
         </is>
       </c>
       <c r="C161" t="n">
@@ -19149,7 +19149,7 @@
       </c>
       <c r="B162" t="inlineStr">
         <is>
-          <t>2026-07-11 08:15:18 PM PT</t>
+          <t>2026-07-11 08:17:18 PM PT</t>
         </is>
       </c>
       <c r="C162" t="n">
@@ -19263,7 +19263,7 @@
       </c>
       <c r="B163" t="inlineStr">
         <is>
-          <t>2026-07-11 08:15:18 PM PT</t>
+          <t>2026-07-11 08:17:18 PM PT</t>
         </is>
       </c>
       <c r="C163" t="n">
@@ -19377,7 +19377,7 @@
       </c>
       <c r="B164" t="inlineStr">
         <is>
-          <t>2026-07-11 08:15:18 PM PT</t>
+          <t>2026-07-11 08:17:18 PM PT</t>
         </is>
       </c>
       <c r="C164" t="n">
@@ -19491,7 +19491,7 @@
       </c>
       <c r="B165" t="inlineStr">
         <is>
-          <t>2026-07-11 08:15:18 PM PT</t>
+          <t>2026-07-11 08:17:18 PM PT</t>
         </is>
       </c>
       <c r="C165" t="n">
@@ -19605,7 +19605,7 @@
       </c>
       <c r="B166" t="inlineStr">
         <is>
-          <t>2026-07-11 08:15:17 PM PT</t>
+          <t>2026-07-11 08:17:17 PM PT</t>
         </is>
       </c>
       <c r="C166" t="n">
@@ -19719,7 +19719,7 @@
       </c>
       <c r="B167" t="inlineStr">
         <is>
-          <t>2026-07-11 08:15:18 PM PT</t>
+          <t>2026-07-11 08:17:18 PM PT</t>
         </is>
       </c>
       <c r="C167" t="n">
@@ -19833,7 +19833,7 @@
       </c>
       <c r="B168" t="inlineStr">
         <is>
-          <t>2026-07-11 08:15:18 PM PT</t>
+          <t>2026-07-11 08:17:18 PM PT</t>
         </is>
       </c>
       <c r="C168" t="n">
@@ -19947,7 +19947,7 @@
       </c>
       <c r="B169" t="inlineStr">
         <is>
-          <t>2026-07-11 08:15:18 PM PT</t>
+          <t>2026-07-11 08:17:18 PM PT</t>
         </is>
       </c>
       <c r="C169" t="n">
@@ -20061,7 +20061,7 @@
       </c>
       <c r="B170" t="inlineStr">
         <is>
-          <t>2026-07-11 08:15:17 PM PT</t>
+          <t>2026-07-11 08:17:17 PM PT</t>
         </is>
       </c>
       <c r="C170" t="n">
@@ -20175,7 +20175,7 @@
       </c>
       <c r="B171" t="inlineStr">
         <is>
-          <t>2026-07-11 08:15:19 PM PT</t>
+          <t>2026-07-11 08:17:18 PM PT</t>
         </is>
       </c>
       <c r="C171" t="n">
@@ -20203,10 +20203,10 @@
         <v>1</v>
       </c>
       <c r="I171" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="J171" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K171" t="inlineStr">
         <is>
@@ -20298,7 +20298,7 @@
       </c>
       <c r="B172" t="inlineStr">
         <is>
-          <t>2026-07-11 08:15:19 PM PT</t>
+          <t>2026-07-11 08:17:18 PM PT</t>
         </is>
       </c>
       <c r="C172" t="n">
@@ -20326,10 +20326,10 @@
         <v>1</v>
       </c>
       <c r="I172" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="J172" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K172" t="inlineStr">
         <is>
@@ -20421,7 +20421,7 @@
       </c>
       <c r="B173" t="inlineStr">
         <is>
-          <t>2026-07-11 08:15:18 PM PT</t>
+          <t>2026-07-11 08:17:18 PM PT</t>
         </is>
       </c>
       <c r="C173" t="n">
@@ -20535,7 +20535,7 @@
       </c>
       <c r="B174" t="inlineStr">
         <is>
-          <t>2026-07-11 08:15:18 PM PT</t>
+          <t>2026-07-11 08:17:18 PM PT</t>
         </is>
       </c>
       <c r="C174" t="n">
@@ -20649,7 +20649,7 @@
       </c>
       <c r="B175" t="inlineStr">
         <is>
-          <t>2026-07-11 08:15:16 PM PT</t>
+          <t>2026-07-11 08:17:16 PM PT</t>
         </is>
       </c>
       <c r="C175" t="n">
@@ -20763,7 +20763,7 @@
       </c>
       <c r="B176" t="inlineStr">
         <is>
-          <t>2026-07-11 08:15:17 PM PT</t>
+          <t>2026-07-11 08:17:16 PM PT</t>
         </is>
       </c>
       <c r="C176" t="n">
@@ -20877,7 +20877,7 @@
       </c>
       <c r="B177" t="inlineStr">
         <is>
-          <t>2026-07-11 08:15:17 PM PT</t>
+          <t>2026-07-11 08:17:17 PM PT</t>
         </is>
       </c>
       <c r="C177" t="n">
@@ -20991,7 +20991,7 @@
       </c>
       <c r="B178" t="inlineStr">
         <is>
-          <t>2026-07-11 08:15:17 PM PT</t>
+          <t>2026-07-11 08:17:17 PM PT</t>
         </is>
       </c>
       <c r="C178" t="n">
@@ -21105,7 +21105,7 @@
       </c>
       <c r="B179" t="inlineStr">
         <is>
-          <t>2026-07-11 08:15:17 PM PT</t>
+          <t>2026-07-11 08:17:17 PM PT</t>
         </is>
       </c>
       <c r="C179" t="n">
@@ -21219,7 +21219,7 @@
       </c>
       <c r="B180" t="inlineStr">
         <is>
-          <t>2026-07-11 08:15:17 PM PT</t>
+          <t>2026-07-11 08:17:17 PM PT</t>
         </is>
       </c>
       <c r="C180" t="n">
@@ -21333,7 +21333,7 @@
       </c>
       <c r="B181" t="inlineStr">
         <is>
-          <t>2026-07-11 08:15:17 PM PT</t>
+          <t>2026-07-11 08:17:17 PM PT</t>
         </is>
       </c>
       <c r="C181" t="n">
@@ -21447,7 +21447,7 @@
       </c>
       <c r="B182" t="inlineStr">
         <is>
-          <t>2026-07-11 08:15:17 PM PT</t>
+          <t>2026-07-11 08:17:17 PM PT</t>
         </is>
       </c>
       <c r="C182" t="n">
@@ -21561,7 +21561,7 @@
       </c>
       <c r="B183" t="inlineStr">
         <is>
-          <t>2026-07-11 08:15:18 PM PT</t>
+          <t>2026-07-11 08:17:18 PM PT</t>
         </is>
       </c>
       <c r="C183" t="n">
@@ -21675,7 +21675,7 @@
       </c>
       <c r="B184" t="inlineStr">
         <is>
-          <t>2026-07-11 08:15:17 PM PT</t>
+          <t>2026-07-11 08:17:16 PM PT</t>
         </is>
       </c>
       <c r="C184" t="n">
@@ -21789,7 +21789,7 @@
       </c>
       <c r="B185" t="inlineStr">
         <is>
-          <t>2026-07-11 08:15:17 PM PT</t>
+          <t>2026-07-11 08:17:16 PM PT</t>
         </is>
       </c>
       <c r="C185" t="n">
@@ -21903,7 +21903,7 @@
       </c>
       <c r="B186" t="inlineStr">
         <is>
-          <t>2026-07-11 08:15:18 PM PT</t>
+          <t>2026-07-11 08:17:17 PM PT</t>
         </is>
       </c>
       <c r="C186" t="n">
@@ -22017,7 +22017,7 @@
       </c>
       <c r="B187" t="inlineStr">
         <is>
-          <t>2026-07-11 08:15:17 PM PT</t>
+          <t>2026-07-11 08:17:17 PM PT</t>
         </is>
       </c>
       <c r="C187" t="n">
@@ -22131,7 +22131,7 @@
       </c>
       <c r="B188" t="inlineStr">
         <is>
-          <t>2026-07-11 08:15:18 PM PT</t>
+          <t>2026-07-11 08:17:17 PM PT</t>
         </is>
       </c>
       <c r="C188" t="n">
@@ -22245,7 +22245,7 @@
       </c>
       <c r="B189" t="inlineStr">
         <is>
-          <t>2026-07-11 08:15:18 PM PT</t>
+          <t>2026-07-11 08:17:18 PM PT</t>
         </is>
       </c>
       <c r="C189" t="n">
@@ -22359,7 +22359,7 @@
       </c>
       <c r="B190" t="inlineStr">
         <is>
-          <t>2026-07-11 08:15:17 PM PT</t>
+          <t>2026-07-11 08:17:17 PM PT</t>
         </is>
       </c>
       <c r="C190" t="n">
@@ -22473,7 +22473,7 @@
       </c>
       <c r="B191" t="inlineStr">
         <is>
-          <t>2026-07-11 08:15:17 PM PT</t>
+          <t>2026-07-11 08:17:17 PM PT</t>
         </is>
       </c>
       <c r="C191" t="n">
@@ -22587,7 +22587,7 @@
       </c>
       <c r="B192" t="inlineStr">
         <is>
-          <t>2026-07-11 08:15:19 PM PT</t>
+          <t>2026-07-11 08:17:18 PM PT</t>
         </is>
       </c>
       <c r="C192" t="n">
@@ -22615,10 +22615,10 @@
         <v>1</v>
       </c>
       <c r="I192" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="J192" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K192" t="inlineStr">
         <is>
@@ -22710,7 +22710,7 @@
       </c>
       <c r="B193" t="inlineStr">
         <is>
-          <t>2026-07-11 08:15:17 PM PT</t>
+          <t>2026-07-11 08:17:17 PM PT</t>
         </is>
       </c>
       <c r="C193" t="n">
@@ -22824,7 +22824,7 @@
       </c>
       <c r="B194" t="inlineStr">
         <is>
-          <t>2026-07-11 08:15:18 PM PT</t>
+          <t>2026-07-11 08:17:18 PM PT</t>
         </is>
       </c>
       <c r="C194" t="n">
@@ -22938,7 +22938,7 @@
       </c>
       <c r="B195" t="inlineStr">
         <is>
-          <t>2026-07-11 08:15:18 PM PT</t>
+          <t>2026-07-11 08:17:18 PM PT</t>
         </is>
       </c>
       <c r="C195" t="n">
@@ -23052,7 +23052,7 @@
       </c>
       <c r="B196" t="inlineStr">
         <is>
-          <t>2026-07-11 08:15:18 PM PT</t>
+          <t>2026-07-11 08:17:18 PM PT</t>
         </is>
       </c>
       <c r="C196" t="n">
@@ -23166,7 +23166,7 @@
       </c>
       <c r="B197" t="inlineStr">
         <is>
-          <t>2026-07-11 08:15:17 PM PT</t>
+          <t>2026-07-11 08:17:17 PM PT</t>
         </is>
       </c>
       <c r="C197" t="n">
@@ -23280,7 +23280,7 @@
       </c>
       <c r="B198" t="inlineStr">
         <is>
-          <t>2026-07-11 08:15:17 PM PT</t>
+          <t>2026-07-11 08:17:17 PM PT</t>
         </is>
       </c>
       <c r="C198" t="n">
@@ -23394,7 +23394,7 @@
       </c>
       <c r="B199" t="inlineStr">
         <is>
-          <t>2026-07-11 08:15:17 PM PT</t>
+          <t>2026-07-11 08:17:17 PM PT</t>
         </is>
       </c>
       <c r="C199" t="n">
@@ -23508,7 +23508,7 @@
       </c>
       <c r="B200" t="inlineStr">
         <is>
-          <t>2026-07-11 08:15:18 PM PT</t>
+          <t>2026-07-11 08:17:18 PM PT</t>
         </is>
       </c>
       <c r="C200" t="n">
@@ -23622,7 +23622,7 @@
       </c>
       <c r="B201" t="inlineStr">
         <is>
-          <t>2026-07-11 08:15:17 PM PT</t>
+          <t>2026-07-11 08:17:17 PM PT</t>
         </is>
       </c>
       <c r="C201" t="n">
@@ -23736,7 +23736,7 @@
       </c>
       <c r="B202" t="inlineStr">
         <is>
-          <t>2026-07-11 08:15:17 PM PT</t>
+          <t>2026-07-11 08:17:17 PM PT</t>
         </is>
       </c>
       <c r="C202" t="n">
@@ -23850,7 +23850,7 @@
       </c>
       <c r="B203" t="inlineStr">
         <is>
-          <t>2026-07-11 08:15:17 PM PT</t>
+          <t>2026-07-11 08:17:17 PM PT</t>
         </is>
       </c>
       <c r="C203" t="n">
@@ -23964,7 +23964,7 @@
       </c>
       <c r="B204" t="inlineStr">
         <is>
-          <t>2026-07-11 08:15:17 PM PT</t>
+          <t>2026-07-11 08:17:17 PM PT</t>
         </is>
       </c>
       <c r="C204" t="n">
@@ -24078,7 +24078,7 @@
       </c>
       <c r="B205" t="inlineStr">
         <is>
-          <t>2026-07-11 08:15:17 PM PT</t>
+          <t>2026-07-11 08:17:17 PM PT</t>
         </is>
       </c>
       <c r="C205" t="n">
@@ -24192,7 +24192,7 @@
       </c>
       <c r="B206" t="inlineStr">
         <is>
-          <t>2026-07-11 08:15:18 PM PT</t>
+          <t>2026-07-11 08:17:18 PM PT</t>
         </is>
       </c>
       <c r="C206" t="n">
@@ -24306,7 +24306,7 @@
       </c>
       <c r="B207" t="inlineStr">
         <is>
-          <t>2026-07-11 08:15:18 PM PT</t>
+          <t>2026-07-11 08:17:18 PM PT</t>
         </is>
       </c>
       <c r="C207" t="n">
@@ -24420,7 +24420,7 @@
       </c>
       <c r="B208" t="inlineStr">
         <is>
-          <t>2026-07-11 08:15:18 PM PT</t>
+          <t>2026-07-11 08:17:18 PM PT</t>
         </is>
       </c>
       <c r="C208" t="n">
@@ -24534,7 +24534,7 @@
       </c>
       <c r="B209" t="inlineStr">
         <is>
-          <t>2026-07-11 08:15:18 PM PT</t>
+          <t>2026-07-11 08:17:18 PM PT</t>
         </is>
       </c>
       <c r="C209" t="n">
@@ -24648,7 +24648,7 @@
       </c>
       <c r="B210" t="inlineStr">
         <is>
-          <t>2026-07-11 08:15:18 PM PT</t>
+          <t>2026-07-11 08:17:18 PM PT</t>
         </is>
       </c>
       <c r="C210" t="n">
@@ -24762,7 +24762,7 @@
       </c>
       <c r="B211" t="inlineStr">
         <is>
-          <t>2026-07-11 08:15:17 PM PT</t>
+          <t>2026-07-11 08:17:17 PM PT</t>
         </is>
       </c>
       <c r="C211" t="n">
@@ -24876,7 +24876,7 @@
       </c>
       <c r="B212" t="inlineStr">
         <is>
-          <t>2026-07-11 08:15:18 PM PT</t>
+          <t>2026-07-11 08:17:18 PM PT</t>
         </is>
       </c>
       <c r="C212" t="n">
@@ -24990,7 +24990,7 @@
       </c>
       <c r="B213" t="inlineStr">
         <is>
-          <t>2026-07-11 08:15:18 PM PT</t>
+          <t>2026-07-11 08:17:18 PM PT</t>
         </is>
       </c>
       <c r="C213" t="n">
@@ -25104,7 +25104,7 @@
       </c>
       <c r="B214" t="inlineStr">
         <is>
-          <t>2026-07-11 08:15:17 PM PT</t>
+          <t>2026-07-11 08:17:17 PM PT</t>
         </is>
       </c>
       <c r="C214" t="n">
@@ -25218,7 +25218,7 @@
       </c>
       <c r="B215" t="inlineStr">
         <is>
-          <t>2026-07-11 08:15:17 PM PT</t>
+          <t>2026-07-11 08:17:17 PM PT</t>
         </is>
       </c>
       <c r="C215" t="n">
@@ -25332,7 +25332,7 @@
       </c>
       <c r="B216" t="inlineStr">
         <is>
-          <t>2026-07-11 08:15:17 PM PT</t>
+          <t>2026-07-11 08:17:17 PM PT</t>
         </is>
       </c>
       <c r="C216" t="n">
@@ -25446,7 +25446,7 @@
       </c>
       <c r="B217" t="inlineStr">
         <is>
-          <t>2026-07-11 08:15:17 PM PT</t>
+          <t>2026-07-11 08:17:17 PM PT</t>
         </is>
       </c>
       <c r="C217" t="n">
@@ -25560,7 +25560,7 @@
       </c>
       <c r="B218" t="inlineStr">
         <is>
-          <t>2026-07-11 08:15:17 PM PT</t>
+          <t>2026-07-11 08:17:17 PM PT</t>
         </is>
       </c>
       <c r="C218" t="n">
@@ -25674,7 +25674,7 @@
       </c>
       <c r="B219" t="inlineStr">
         <is>
-          <t>2026-07-11 08:15:17 PM PT</t>
+          <t>2026-07-11 08:17:17 PM PT</t>
         </is>
       </c>
       <c r="C219" t="n">
@@ -25788,7 +25788,7 @@
       </c>
       <c r="B220" t="inlineStr">
         <is>
-          <t>2026-07-11 08:15:17 PM PT</t>
+          <t>2026-07-11 08:17:17 PM PT</t>
         </is>
       </c>
       <c r="C220" t="n">
@@ -25902,7 +25902,7 @@
       </c>
       <c r="B221" t="inlineStr">
         <is>
-          <t>2026-07-11 08:15:17 PM PT</t>
+          <t>2026-07-11 08:17:17 PM PT</t>
         </is>
       </c>
       <c r="C221" t="n">
@@ -26016,7 +26016,7 @@
       </c>
       <c r="B222" t="inlineStr">
         <is>
-          <t>2026-07-11 08:15:16 PM PT</t>
+          <t>2026-07-11 08:17:16 PM PT</t>
         </is>
       </c>
       <c r="C222" t="n">
@@ -26130,7 +26130,7 @@
       </c>
       <c r="B223" t="inlineStr">
         <is>
-          <t>2026-07-11 08:15:17 PM PT</t>
+          <t>2026-07-11 08:17:16 PM PT</t>
         </is>
       </c>
       <c r="C223" t="n">
@@ -26244,7 +26244,7 @@
       </c>
       <c r="B224" t="inlineStr">
         <is>
-          <t>2026-07-11 08:15:18 PM PT</t>
+          <t>2026-07-11 08:17:17 PM PT</t>
         </is>
       </c>
       <c r="C224" t="n">
@@ -26358,7 +26358,7 @@
       </c>
       <c r="B225" t="inlineStr">
         <is>
-          <t>2026-07-11 08:15:17 PM PT</t>
+          <t>2026-07-11 08:17:17 PM PT</t>
         </is>
       </c>
       <c r="C225" t="n">
@@ -26472,7 +26472,7 @@
       </c>
       <c r="B226" t="inlineStr">
         <is>
-          <t>2026-07-11 08:15:18 PM PT</t>
+          <t>2026-07-11 08:17:18 PM PT</t>
         </is>
       </c>
       <c r="C226" t="n">
@@ -26586,7 +26586,7 @@
       </c>
       <c r="B227" t="inlineStr">
         <is>
-          <t>2026-07-11 08:15:18 PM PT</t>
+          <t>2026-07-11 08:17:18 PM PT</t>
         </is>
       </c>
       <c r="C227" t="n">
@@ -26700,7 +26700,7 @@
       </c>
       <c r="B228" t="inlineStr">
         <is>
-          <t>2026-07-11 08:15:19 PM PT</t>
+          <t>2026-07-11 08:17:18 PM PT</t>
         </is>
       </c>
       <c r="C228" t="n">
@@ -26713,7 +26713,7 @@
       </c>
       <c r="E228" t="inlineStr">
         <is>
-          <t>Bottom 7 | 0 out</t>
+          <t>Bottom 7 | 1 out</t>
         </is>
       </c>
       <c r="F228" t="n">
@@ -26725,13 +26725,13 @@
         </is>
       </c>
       <c r="H228" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I228" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="J228" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K228" t="inlineStr">
         <is>
@@ -26823,7 +26823,7 @@
       </c>
       <c r="B229" t="inlineStr">
         <is>
-          <t>2026-07-11 08:15:17 PM PT</t>
+          <t>2026-07-11 08:17:17 PM PT</t>
         </is>
       </c>
       <c r="C229" t="n">
@@ -26937,7 +26937,7 @@
       </c>
       <c r="B230" t="inlineStr">
         <is>
-          <t>2026-07-11 08:15:17 PM PT</t>
+          <t>2026-07-11 08:17:17 PM PT</t>
         </is>
       </c>
       <c r="C230" t="n">
@@ -27051,7 +27051,7 @@
       </c>
       <c r="B231" t="inlineStr">
         <is>
-          <t>2026-07-11 08:15:17 PM PT</t>
+          <t>2026-07-11 08:17:17 PM PT</t>
         </is>
       </c>
       <c r="C231" t="n">
@@ -27165,7 +27165,7 @@
       </c>
       <c r="B232" t="inlineStr">
         <is>
-          <t>2026-07-11 08:15:17 PM PT</t>
+          <t>2026-07-11 08:17:17 PM PT</t>
         </is>
       </c>
       <c r="C232" t="n">
@@ -27279,7 +27279,7 @@
       </c>
       <c r="B233" t="inlineStr">
         <is>
-          <t>2026-07-11 08:15:19 PM PT</t>
+          <t>2026-07-11 08:17:18 PM PT</t>
         </is>
       </c>
       <c r="C233" t="n">
@@ -27307,10 +27307,10 @@
         <v>1</v>
       </c>
       <c r="I233" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="J233" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K233" t="inlineStr">
         <is>
@@ -27402,7 +27402,7 @@
       </c>
       <c r="B234" t="inlineStr">
         <is>
-          <t>2026-07-11 08:15:19 PM PT</t>
+          <t>2026-07-11 08:17:18 PM PT</t>
         </is>
       </c>
       <c r="C234" t="n">
@@ -27430,10 +27430,10 @@
         <v>1</v>
       </c>
       <c r="I234" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="J234" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K234" t="inlineStr">
         <is>
@@ -27525,7 +27525,7 @@
       </c>
       <c r="B235" t="inlineStr">
         <is>
-          <t>2026-07-11 08:15:19 PM PT</t>
+          <t>2026-07-11 08:17:18 PM PT</t>
         </is>
       </c>
       <c r="C235" t="n">
@@ -27553,10 +27553,10 @@
         <v>1</v>
       </c>
       <c r="I235" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="J235" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K235" t="inlineStr">
         <is>
@@ -27648,7 +27648,7 @@
       </c>
       <c r="B236" t="inlineStr">
         <is>
-          <t>2026-07-11 08:15:17 PM PT</t>
+          <t>2026-07-11 08:17:17 PM PT</t>
         </is>
       </c>
       <c r="C236" t="n">
@@ -27762,7 +27762,7 @@
       </c>
       <c r="B237" t="inlineStr">
         <is>
-          <t>2026-07-11 08:15:17 PM PT</t>
+          <t>2026-07-11 08:17:17 PM PT</t>
         </is>
       </c>
       <c r="C237" t="n">
@@ -27876,7 +27876,7 @@
       </c>
       <c r="B238" t="inlineStr">
         <is>
-          <t>2026-07-11 08:15:17 PM PT</t>
+          <t>2026-07-11 08:17:17 PM PT</t>
         </is>
       </c>
       <c r="C238" t="n">
@@ -27990,7 +27990,7 @@
       </c>
       <c r="B239" t="inlineStr">
         <is>
-          <t>2026-07-11 08:15:17 PM PT</t>
+          <t>2026-07-11 08:17:17 PM PT</t>
         </is>
       </c>
       <c r="C239" t="n">
@@ -28104,7 +28104,7 @@
       </c>
       <c r="B240" t="inlineStr">
         <is>
-          <t>2026-07-11 08:15:17 PM PT</t>
+          <t>2026-07-11 08:17:17 PM PT</t>
         </is>
       </c>
       <c r="C240" t="n">
@@ -28218,7 +28218,7 @@
       </c>
       <c r="B241" t="inlineStr">
         <is>
-          <t>2026-07-11 08:15:17 PM PT</t>
+          <t>2026-07-11 08:17:17 PM PT</t>
         </is>
       </c>
       <c r="C241" t="n">
@@ -28332,7 +28332,7 @@
       </c>
       <c r="B242" t="inlineStr">
         <is>
-          <t>2026-07-11 08:15:17 PM PT</t>
+          <t>2026-07-11 08:17:17 PM PT</t>
         </is>
       </c>
       <c r="C242" t="n">
@@ -28446,7 +28446,7 @@
       </c>
       <c r="B243" t="inlineStr">
         <is>
-          <t>2026-07-11 08:15:18 PM PT</t>
+          <t>2026-07-11 08:17:18 PM PT</t>
         </is>
       </c>
       <c r="C243" t="n">
@@ -28560,7 +28560,7 @@
       </c>
       <c r="B244" t="inlineStr">
         <is>
-          <t>2026-07-11 08:15:18 PM PT</t>
+          <t>2026-07-11 08:17:18 PM PT</t>
         </is>
       </c>
       <c r="C244" t="n">
@@ -28674,7 +28674,7 @@
       </c>
       <c r="B245" t="inlineStr">
         <is>
-          <t>2026-07-11 08:15:18 PM PT</t>
+          <t>2026-07-11 08:17:18 PM PT</t>
         </is>
       </c>
       <c r="C245" t="n">
@@ -28788,7 +28788,7 @@
       </c>
       <c r="B246" t="inlineStr">
         <is>
-          <t>2026-07-11 08:15:18 PM PT</t>
+          <t>2026-07-11 08:17:18 PM PT</t>
         </is>
       </c>
       <c r="C246" t="n">
@@ -28902,7 +28902,7 @@
       </c>
       <c r="B247" t="inlineStr">
         <is>
-          <t>2026-07-11 08:15:18 PM PT</t>
+          <t>2026-07-11 08:17:18 PM PT</t>
         </is>
       </c>
       <c r="C247" t="n">
@@ -29016,7 +29016,7 @@
       </c>
       <c r="B248" t="inlineStr">
         <is>
-          <t>2026-07-11 08:15:18 PM PT</t>
+          <t>2026-07-11 08:17:18 PM PT</t>
         </is>
       </c>
       <c r="C248" t="n">
@@ -29130,7 +29130,7 @@
       </c>
       <c r="B249" t="inlineStr">
         <is>
-          <t>2026-07-11 08:15:17 PM PT</t>
+          <t>2026-07-11 08:17:17 PM PT</t>
         </is>
       </c>
       <c r="C249" t="n">
@@ -29244,7 +29244,7 @@
       </c>
       <c r="B250" t="inlineStr">
         <is>
-          <t>2026-07-11 08:15:17 PM PT</t>
+          <t>2026-07-11 08:17:17 PM PT</t>
         </is>
       </c>
       <c r="C250" t="n">
@@ -29358,7 +29358,7 @@
       </c>
       <c r="B251" t="inlineStr">
         <is>
-          <t>2026-07-11 08:15:17 PM PT</t>
+          <t>2026-07-11 08:17:17 PM PT</t>
         </is>
       </c>
       <c r="C251" t="n">
@@ -29472,7 +29472,7 @@
       </c>
       <c r="B252" t="inlineStr">
         <is>
-          <t>2026-07-11 08:15:18 PM PT</t>
+          <t>2026-07-11 08:17:18 PM PT</t>
         </is>
       </c>
       <c r="C252" t="n">
@@ -29586,7 +29586,7 @@
       </c>
       <c r="B253" t="inlineStr">
         <is>
-          <t>2026-07-11 08:15:18 PM PT</t>
+          <t>2026-07-11 08:17:18 PM PT</t>
         </is>
       </c>
       <c r="C253" t="n">
@@ -29700,7 +29700,7 @@
       </c>
       <c r="B254" t="inlineStr">
         <is>
-          <t>2026-07-11 08:15:18 PM PT</t>
+          <t>2026-07-11 08:17:18 PM PT</t>
         </is>
       </c>
       <c r="C254" t="n">
@@ -29814,7 +29814,7 @@
       </c>
       <c r="B255" t="inlineStr">
         <is>
-          <t>2026-07-11 08:15:18 PM PT</t>
+          <t>2026-07-11 08:17:18 PM PT</t>
         </is>
       </c>
       <c r="C255" t="n">
@@ -29928,7 +29928,7 @@
       </c>
       <c r="B256" t="inlineStr">
         <is>
-          <t>2026-07-11 08:15:18 PM PT</t>
+          <t>2026-07-11 08:17:18 PM PT</t>
         </is>
       </c>
       <c r="C256" t="n">
@@ -30042,7 +30042,7 @@
       </c>
       <c r="B257" t="inlineStr">
         <is>
-          <t>2026-07-11 08:15:17 PM PT</t>
+          <t>2026-07-11 08:17:17 PM PT</t>
         </is>
       </c>
       <c r="C257" t="n">
@@ -30156,7 +30156,7 @@
       </c>
       <c r="B258" t="inlineStr">
         <is>
-          <t>2026-07-11 08:15:17 PM PT</t>
+          <t>2026-07-11 08:17:17 PM PT</t>
         </is>
       </c>
       <c r="C258" t="n">
@@ -30270,7 +30270,7 @@
       </c>
       <c r="B259" t="inlineStr">
         <is>
-          <t>2026-07-11 08:15:17 PM PT</t>
+          <t>2026-07-11 08:17:17 PM PT</t>
         </is>
       </c>
       <c r="C259" t="n">
@@ -30384,7 +30384,7 @@
       </c>
       <c r="B260" t="inlineStr">
         <is>
-          <t>2026-07-11 08:15:17 PM PT</t>
+          <t>2026-07-11 08:17:17 PM PT</t>
         </is>
       </c>
       <c r="C260" t="n">
@@ -30498,7 +30498,7 @@
       </c>
       <c r="B261" t="inlineStr">
         <is>
-          <t>2026-07-11 08:15:17 PM PT</t>
+          <t>2026-07-11 08:17:17 PM PT</t>
         </is>
       </c>
       <c r="C261" t="n">
@@ -30612,7 +30612,7 @@
       </c>
       <c r="B262" t="inlineStr">
         <is>
-          <t>2026-07-11 08:15:17 PM PT</t>
+          <t>2026-07-11 08:17:17 PM PT</t>
         </is>
       </c>
       <c r="C262" t="n">
@@ -30726,7 +30726,7 @@
       </c>
       <c r="B263" t="inlineStr">
         <is>
-          <t>2026-07-11 08:15:17 PM PT</t>
+          <t>2026-07-11 08:17:17 PM PT</t>
         </is>
       </c>
       <c r="C263" t="n">
@@ -30840,7 +30840,7 @@
       </c>
       <c r="B264" t="inlineStr">
         <is>
-          <t>2026-07-11 08:15:18 PM PT</t>
+          <t>2026-07-11 08:17:18 PM PT</t>
         </is>
       </c>
       <c r="C264" t="n">
@@ -30954,7 +30954,7 @@
       </c>
       <c r="B265" t="inlineStr">
         <is>
-          <t>2026-07-11 08:15:18 PM PT</t>
+          <t>2026-07-11 08:17:18 PM PT</t>
         </is>
       </c>
       <c r="C265" t="n">
@@ -31068,7 +31068,7 @@
       </c>
       <c r="B266" t="inlineStr">
         <is>
-          <t>2026-07-11 08:15:18 PM PT</t>
+          <t>2026-07-11 08:17:18 PM PT</t>
         </is>
       </c>
       <c r="C266" t="n">
@@ -31182,7 +31182,7 @@
       </c>
       <c r="B267" t="inlineStr">
         <is>
-          <t>2026-07-11 08:15:18 PM PT</t>
+          <t>2026-07-11 08:17:18 PM PT</t>
         </is>
       </c>
       <c r="C267" t="n">
@@ -31296,7 +31296,7 @@
       </c>
       <c r="B268" t="inlineStr">
         <is>
-          <t>2026-07-11 08:15:18 PM PT</t>
+          <t>2026-07-11 08:17:18 PM PT</t>
         </is>
       </c>
       <c r="C268" t="n">
@@ -31410,7 +31410,7 @@
       </c>
       <c r="B269" t="inlineStr">
         <is>
-          <t>2026-07-11 08:15:18 PM PT</t>
+          <t>2026-07-11 08:17:18 PM PT</t>
         </is>
       </c>
       <c r="C269" t="n">
@@ -31524,7 +31524,7 @@
       </c>
       <c r="B270" t="inlineStr">
         <is>
-          <t>2026-07-11 08:15:18 PM PT</t>
+          <t>2026-07-11 08:17:18 PM PT</t>
         </is>
       </c>
       <c r="C270" t="n">
@@ -31638,7 +31638,7 @@
       </c>
       <c r="B271" t="inlineStr">
         <is>
-          <t>2026-07-11 08:15:18 PM PT</t>
+          <t>2026-07-11 08:17:18 PM PT</t>
         </is>
       </c>
       <c r="C271" t="n">
@@ -31752,7 +31752,7 @@
       </c>
       <c r="B272" t="inlineStr">
         <is>
-          <t>2026-07-11 08:15:18 PM PT</t>
+          <t>2026-07-11 08:17:18 PM PT</t>
         </is>
       </c>
       <c r="C272" t="n">
@@ -31866,7 +31866,7 @@
       </c>
       <c r="B273" t="inlineStr">
         <is>
-          <t>2026-07-11 08:15:18 PM PT</t>
+          <t>2026-07-11 08:17:18 PM PT</t>
         </is>
       </c>
       <c r="C273" t="n">
@@ -31980,7 +31980,7 @@
       </c>
       <c r="B274" t="inlineStr">
         <is>
-          <t>2026-07-11 08:15:18 PM PT</t>
+          <t>2026-07-11 08:17:18 PM PT</t>
         </is>
       </c>
       <c r="C274" t="n">
@@ -32094,7 +32094,7 @@
       </c>
       <c r="B275" t="inlineStr">
         <is>
-          <t>2026-07-11 08:15:17 PM PT</t>
+          <t>2026-07-11 08:17:17 PM PT</t>
         </is>
       </c>
       <c r="C275" t="n">
@@ -32208,7 +32208,7 @@
       </c>
       <c r="B276" t="inlineStr">
         <is>
-          <t>2026-07-11 08:15:17 PM PT</t>
+          <t>2026-07-11 08:17:17 PM PT</t>
         </is>
       </c>
       <c r="C276" t="n">
@@ -32322,7 +32322,7 @@
       </c>
       <c r="B277" t="inlineStr">
         <is>
-          <t>2026-07-11 08:15:17 PM PT</t>
+          <t>2026-07-11 08:17:17 PM PT</t>
         </is>
       </c>
       <c r="C277" t="n">
@@ -32436,7 +32436,7 @@
       </c>
       <c r="B278" t="inlineStr">
         <is>
-          <t>2026-07-11 08:15:19 PM PT</t>
+          <t>2026-07-11 08:17:18 PM PT</t>
         </is>
       </c>
       <c r="C278" t="n">
@@ -32464,10 +32464,10 @@
         <v>1</v>
       </c>
       <c r="I278" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="J278" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K278" t="inlineStr">
         <is>
@@ -32559,7 +32559,7 @@
       </c>
       <c r="B279" t="inlineStr">
         <is>
-          <t>2026-07-11 08:15:19 PM PT</t>
+          <t>2026-07-11 08:17:18 PM PT</t>
         </is>
       </c>
       <c r="C279" t="n">
@@ -32587,10 +32587,10 @@
         <v>1</v>
       </c>
       <c r="I279" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="J279" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K279" t="inlineStr">
         <is>
@@ -32682,7 +32682,7 @@
       </c>
       <c r="B280" t="inlineStr">
         <is>
-          <t>2026-07-11 08:15:19 PM PT</t>
+          <t>2026-07-11 08:17:18 PM PT</t>
         </is>
       </c>
       <c r="C280" t="n">
@@ -32710,10 +32710,10 @@
         <v>1</v>
       </c>
       <c r="I280" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="J280" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K280" t="inlineStr">
         <is>
@@ -32805,7 +32805,7 @@
       </c>
       <c r="B281" t="inlineStr">
         <is>
-          <t>2026-07-11 08:15:19 PM PT</t>
+          <t>2026-07-11 08:17:18 PM PT</t>
         </is>
       </c>
       <c r="C281" t="n">
@@ -32833,10 +32833,10 @@
         <v>1</v>
       </c>
       <c r="I281" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="J281" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K281" t="inlineStr">
         <is>
@@ -32928,7 +32928,7 @@
       </c>
       <c r="B282" t="inlineStr">
         <is>
-          <t>2026-07-11 08:15:18 PM PT</t>
+          <t>2026-07-11 08:17:18 PM PT</t>
         </is>
       </c>
       <c r="C282" t="n">
@@ -33042,7 +33042,7 @@
       </c>
       <c r="B283" t="inlineStr">
         <is>
-          <t>2026-07-11 08:15:16 PM PT</t>
+          <t>2026-07-11 08:17:16 PM PT</t>
         </is>
       </c>
       <c r="C283" t="n">
@@ -33156,7 +33156,7 @@
       </c>
       <c r="B284" t="inlineStr">
         <is>
-          <t>2026-07-11 08:15:17 PM PT</t>
+          <t>2026-07-11 08:17:16 PM PT</t>
         </is>
       </c>
       <c r="C284" t="n">
@@ -33270,7 +33270,7 @@
       </c>
       <c r="B285" t="inlineStr">
         <is>
-          <t>2026-07-11 08:15:16 PM PT</t>
+          <t>2026-07-11 08:17:16 PM PT</t>
         </is>
       </c>
       <c r="C285" t="n">
@@ -33384,7 +33384,7 @@
       </c>
       <c r="B286" t="inlineStr">
         <is>
-          <t>2026-07-11 08:15:17 PM PT</t>
+          <t>2026-07-11 08:17:16 PM PT</t>
         </is>
       </c>
       <c r="C286" t="n">
@@ -33498,7 +33498,7 @@
       </c>
       <c r="B287" t="inlineStr">
         <is>
-          <t>2026-07-11 08:15:17 PM PT</t>
+          <t>2026-07-11 08:17:16 PM PT</t>
         </is>
       </c>
       <c r="C287" t="n">
@@ -33612,7 +33612,7 @@
       </c>
       <c r="B288" t="inlineStr">
         <is>
-          <t>2026-07-11 08:15:16 PM PT</t>
+          <t>2026-07-11 08:17:16 PM PT</t>
         </is>
       </c>
       <c r="C288" t="n">
@@ -33726,7 +33726,7 @@
       </c>
       <c r="B289" t="inlineStr">
         <is>
-          <t>2026-07-11 08:15:17 PM PT</t>
+          <t>2026-07-11 08:17:17 PM PT</t>
         </is>
       </c>
       <c r="C289" t="n">
@@ -33840,7 +33840,7 @@
       </c>
       <c r="B290" t="inlineStr">
         <is>
-          <t>2026-07-11 08:15:17 PM PT</t>
+          <t>2026-07-11 08:17:17 PM PT</t>
         </is>
       </c>
       <c r="C290" t="n">
@@ -33954,7 +33954,7 @@
       </c>
       <c r="B291" t="inlineStr">
         <is>
-          <t>2026-07-11 08:15:17 PM PT</t>
+          <t>2026-07-11 08:17:17 PM PT</t>
         </is>
       </c>
       <c r="C291" t="n">
@@ -34068,7 +34068,7 @@
       </c>
       <c r="B292" t="inlineStr">
         <is>
-          <t>2026-07-11 08:15:17 PM PT</t>
+          <t>2026-07-11 08:17:17 PM PT</t>
         </is>
       </c>
       <c r="C292" t="n">
@@ -34182,7 +34182,7 @@
       </c>
       <c r="B293" t="inlineStr">
         <is>
-          <t>2026-07-11 08:15:17 PM PT</t>
+          <t>2026-07-11 08:17:17 PM PT</t>
         </is>
       </c>
       <c r="C293" t="n">
@@ -34296,7 +34296,7 @@
       </c>
       <c r="B294" t="inlineStr">
         <is>
-          <t>2026-07-11 08:15:17 PM PT</t>
+          <t>2026-07-11 08:17:17 PM PT</t>
         </is>
       </c>
       <c r="C294" t="n">
@@ -34410,7 +34410,7 @@
       </c>
       <c r="B295" t="inlineStr">
         <is>
-          <t>2026-07-11 08:15:17 PM PT</t>
+          <t>2026-07-11 08:17:17 PM PT</t>
         </is>
       </c>
       <c r="C295" t="n">
@@ -34524,7 +34524,7 @@
       </c>
       <c r="B296" t="inlineStr">
         <is>
-          <t>2026-07-11 08:15:18 PM PT</t>
+          <t>2026-07-11 08:17:18 PM PT</t>
         </is>
       </c>
       <c r="C296" t="n">
@@ -34638,7 +34638,7 @@
       </c>
       <c r="B297" t="inlineStr">
         <is>
-          <t>2026-07-11 08:15:18 PM PT</t>
+          <t>2026-07-11 08:17:18 PM PT</t>
         </is>
       </c>
       <c r="C297" t="n">
@@ -34752,7 +34752,7 @@
       </c>
       <c r="B298" t="inlineStr">
         <is>
-          <t>2026-07-11 08:15:17 PM PT</t>
+          <t>2026-07-11 08:17:16 PM PT</t>
         </is>
       </c>
       <c r="C298" t="n">
@@ -34866,7 +34866,7 @@
       </c>
       <c r="B299" t="inlineStr">
         <is>
-          <t>2026-07-11 08:15:17 PM PT</t>
+          <t>2026-07-11 08:17:16 PM PT</t>
         </is>
       </c>
       <c r="C299" t="n">
@@ -34980,7 +34980,7 @@
       </c>
       <c r="B300" t="inlineStr">
         <is>
-          <t>2026-07-11 08:15:17 PM PT</t>
+          <t>2026-07-11 08:17:16 PM PT</t>
         </is>
       </c>
       <c r="C300" t="n">
@@ -35094,7 +35094,7 @@
       </c>
       <c r="B301" t="inlineStr">
         <is>
-          <t>2026-07-11 08:15:16 PM PT</t>
+          <t>2026-07-11 08:17:16 PM PT</t>
         </is>
       </c>
       <c r="C301" t="n">
@@ -35208,7 +35208,7 @@
       </c>
       <c r="B302" t="inlineStr">
         <is>
-          <t>2026-07-11 08:15:17 PM PT</t>
+          <t>2026-07-11 08:17:16 PM PT</t>
         </is>
       </c>
       <c r="C302" t="n">
@@ -35322,7 +35322,7 @@
       </c>
       <c r="B303" t="inlineStr">
         <is>
-          <t>2026-07-11 08:15:16 PM PT</t>
+          <t>2026-07-11 08:17:16 PM PT</t>
         </is>
       </c>
       <c r="C303" t="n">
@@ -35436,7 +35436,7 @@
       </c>
       <c r="B304" t="inlineStr">
         <is>
-          <t>2026-07-11 08:15:16 PM PT</t>
+          <t>2026-07-11 08:17:16 PM PT</t>
         </is>
       </c>
       <c r="C304" t="n">
@@ -35550,7 +35550,7 @@
       </c>
       <c r="B305" t="inlineStr">
         <is>
-          <t>2026-07-11 08:15:17 PM PT</t>
+          <t>2026-07-11 08:17:16 PM PT</t>
         </is>
       </c>
       <c r="C305" t="n">
@@ -35664,7 +35664,7 @@
       </c>
       <c r="B306" t="inlineStr">
         <is>
-          <t>2026-07-11 08:15:19 PM PT</t>
+          <t>2026-07-11 08:17:18 PM PT</t>
         </is>
       </c>
       <c r="C306" t="n">
@@ -35677,7 +35677,7 @@
       </c>
       <c r="E306" t="inlineStr">
         <is>
-          <t>Bottom 7 | 0 out</t>
+          <t>Bottom 7 | 1 out</t>
         </is>
       </c>
       <c r="F306" t="n">
@@ -35689,13 +35689,13 @@
         </is>
       </c>
       <c r="H306" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I306" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="J306" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K306" t="inlineStr">
         <is>
@@ -35731,10 +35731,10 @@
         </is>
       </c>
       <c r="R306" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="S306" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="T306" t="n">
         <v>0</v>
@@ -35787,7 +35787,7 @@
       </c>
       <c r="B307" t="inlineStr">
         <is>
-          <t>2026-07-11 08:15:18 PM PT</t>
+          <t>2026-07-11 08:17:17 PM PT</t>
         </is>
       </c>
       <c r="C307" t="n">
@@ -35901,7 +35901,7 @@
       </c>
       <c r="B308" t="inlineStr">
         <is>
-          <t>2026-07-11 08:15:18 PM PT</t>
+          <t>2026-07-11 08:17:17 PM PT</t>
         </is>
       </c>
       <c r="C308" t="n">
@@ -36015,7 +36015,7 @@
       </c>
       <c r="B309" t="inlineStr">
         <is>
-          <t>2026-07-11 08:15:18 PM PT</t>
+          <t>2026-07-11 08:17:17 PM PT</t>
         </is>
       </c>
       <c r="C309" t="n">
@@ -36129,7 +36129,7 @@
       </c>
       <c r="B310" t="inlineStr">
         <is>
-          <t>2026-07-11 08:15:18 PM PT</t>
+          <t>2026-07-11 08:17:17 PM PT</t>
         </is>
       </c>
       <c r="C310" t="n">
@@ -36243,7 +36243,7 @@
       </c>
       <c r="B311" t="inlineStr">
         <is>
-          <t>2026-07-11 08:15:18 PM PT</t>
+          <t>2026-07-11 08:17:17 PM PT</t>
         </is>
       </c>
       <c r="C311" t="n">
@@ -36357,7 +36357,7 @@
       </c>
       <c r="B312" t="inlineStr">
         <is>
-          <t>2026-07-11 08:15:17 PM PT</t>
+          <t>2026-07-11 08:17:17 PM PT</t>
         </is>
       </c>
       <c r="C312" t="n">
@@ -36471,7 +36471,7 @@
       </c>
       <c r="B313" t="inlineStr">
         <is>
-          <t>2026-07-11 08:15:17 PM PT</t>
+          <t>2026-07-11 08:17:17 PM PT</t>
         </is>
       </c>
       <c r="C313" t="n">
@@ -36585,7 +36585,7 @@
       </c>
       <c r="B314" t="inlineStr">
         <is>
-          <t>2026-07-11 08:15:18 PM PT</t>
+          <t>2026-07-11 08:17:18 PM PT</t>
         </is>
       </c>
       <c r="C314" t="n">
@@ -36699,7 +36699,7 @@
       </c>
       <c r="B315" t="inlineStr">
         <is>
-          <t>2026-07-11 08:15:18 PM PT</t>
+          <t>2026-07-11 08:17:18 PM PT</t>
         </is>
       </c>
       <c r="C315" t="n">
@@ -36813,7 +36813,7 @@
       </c>
       <c r="B316" t="inlineStr">
         <is>
-          <t>2026-07-11 08:15:18 PM PT</t>
+          <t>2026-07-11 08:17:18 PM PT</t>
         </is>
       </c>
       <c r="C316" t="n">
@@ -36927,7 +36927,7 @@
       </c>
       <c r="B317" t="inlineStr">
         <is>
-          <t>2026-07-11 08:15:18 PM PT</t>
+          <t>2026-07-11 08:17:18 PM PT</t>
         </is>
       </c>
       <c r="C317" t="n">
@@ -37041,7 +37041,7 @@
       </c>
       <c r="B318" t="inlineStr">
         <is>
-          <t>2026-07-11 08:15:18 PM PT</t>
+          <t>2026-07-11 08:17:17 PM PT</t>
         </is>
       </c>
       <c r="C318" t="n">
@@ -37155,7 +37155,7 @@
       </c>
       <c r="B319" t="inlineStr">
         <is>
-          <t>2026-07-11 08:15:18 PM PT</t>
+          <t>2026-07-11 08:17:17 PM PT</t>
         </is>
       </c>
       <c r="C319" t="n">
@@ -37269,7 +37269,7 @@
       </c>
       <c r="B320" t="inlineStr">
         <is>
-          <t>2026-07-11 08:15:18 PM PT</t>
+          <t>2026-07-11 08:17:17 PM PT</t>
         </is>
       </c>
       <c r="C320" t="n">
@@ -37383,7 +37383,7 @@
       </c>
       <c r="B321" t="inlineStr">
         <is>
-          <t>2026-07-11 08:15:18 PM PT</t>
+          <t>2026-07-11 08:17:17 PM PT</t>
         </is>
       </c>
       <c r="C321" t="n">
@@ -37497,7 +37497,7 @@
       </c>
       <c r="B322" t="inlineStr">
         <is>
-          <t>2026-07-11 08:15:18 PM PT</t>
+          <t>2026-07-11 08:17:18 PM PT</t>
         </is>
       </c>
       <c r="C322" t="n">
@@ -37611,7 +37611,7 @@
       </c>
       <c r="B323" t="inlineStr">
         <is>
-          <t>2026-07-11 08:15:18 PM PT</t>
+          <t>2026-07-11 08:17:18 PM PT</t>
         </is>
       </c>
       <c r="C323" t="n">
@@ -37725,7 +37725,7 @@
       </c>
       <c r="B324" t="inlineStr">
         <is>
-          <t>2026-07-11 08:15:18 PM PT</t>
+          <t>2026-07-11 08:17:18 PM PT</t>
         </is>
       </c>
       <c r="C324" t="n">
@@ -37839,7 +37839,7 @@
       </c>
       <c r="B325" t="inlineStr">
         <is>
-          <t>2026-07-11 08:15:18 PM PT</t>
+          <t>2026-07-11 08:17:18 PM PT</t>
         </is>
       </c>
       <c r="C325" t="n">
@@ -37953,7 +37953,7 @@
       </c>
       <c r="B326" t="inlineStr">
         <is>
-          <t>2026-07-11 08:15:18 PM PT</t>
+          <t>2026-07-11 08:17:18 PM PT</t>
         </is>
       </c>
       <c r="C326" t="n">
@@ -38067,7 +38067,7 @@
       </c>
       <c r="B327" t="inlineStr">
         <is>
-          <t>2026-07-11 08:15:19 PM PT</t>
+          <t>2026-07-11 08:17:18 PM PT</t>
         </is>
       </c>
       <c r="C327" t="n">
@@ -38080,7 +38080,7 @@
       </c>
       <c r="E327" t="inlineStr">
         <is>
-          <t>Bottom 7 | 0 out</t>
+          <t>Bottom 7 | 1 out</t>
         </is>
       </c>
       <c r="F327" t="n">
@@ -38092,13 +38092,13 @@
         </is>
       </c>
       <c r="H327" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I327" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="J327" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K327" t="inlineStr">
         <is>
@@ -38190,7 +38190,7 @@
       </c>
       <c r="B328" t="inlineStr">
         <is>
-          <t>2026-07-11 08:15:17 PM PT</t>
+          <t>2026-07-11 08:17:17 PM PT</t>
         </is>
       </c>
       <c r="C328" t="n">
@@ -38304,7 +38304,7 @@
       </c>
       <c r="B329" t="inlineStr">
         <is>
-          <t>2026-07-11 08:15:17 PM PT</t>
+          <t>2026-07-11 08:17:17 PM PT</t>
         </is>
       </c>
       <c r="C329" t="n">

--- a/live_mlb_hitter_fantasy_scores_2026_07_11.xlsx
+++ b/live_mlb_hitter_fantasy_scores_2026_07_11.xlsx
@@ -693,7 +693,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-07-11 08:17:16 PM PT</t>
+          <t>2026-07-11 08:19:16 PM PT</t>
         </is>
       </c>
       <c r="C2" t="n">
@@ -807,7 +807,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>2026-07-11 08:17:18 PM PT</t>
+          <t>2026-07-11 08:19:17 PM PT</t>
         </is>
       </c>
       <c r="C3" t="n">
@@ -921,7 +921,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-07-11 08:17:18 PM PT</t>
+          <t>2026-07-11 08:19:18 PM PT</t>
         </is>
       </c>
       <c r="C4" t="n">
@@ -934,7 +934,7 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Bottom 7 | 1 out</t>
+          <t>Bottom 7 | 2 out</t>
         </is>
       </c>
       <c r="F4" t="n">
@@ -946,13 +946,13 @@
         </is>
       </c>
       <c r="H4" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I4" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="J4" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="K4" t="inlineStr">
         <is>
@@ -1044,7 +1044,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>2026-07-11 08:17:18 PM PT</t>
+          <t>2026-07-11 08:19:17 PM PT</t>
         </is>
       </c>
       <c r="C5" t="n">
@@ -1158,7 +1158,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>2026-07-11 08:17:18 PM PT</t>
+          <t>2026-07-11 08:19:17 PM PT</t>
         </is>
       </c>
       <c r="C6" t="n">
@@ -1272,7 +1272,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>2026-07-11 08:17:17 PM PT</t>
+          <t>2026-07-11 08:19:17 PM PT</t>
         </is>
       </c>
       <c r="C7" t="n">
@@ -1386,7 +1386,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>2026-07-11 08:17:18 PM PT</t>
+          <t>2026-07-11 08:19:17 PM PT</t>
         </is>
       </c>
       <c r="C8" t="n">
@@ -1500,7 +1500,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>2026-07-11 08:17:17 PM PT</t>
+          <t>2026-07-11 08:19:16 PM PT</t>
         </is>
       </c>
       <c r="C9" t="n">
@@ -1614,7 +1614,7 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>2026-07-11 08:17:18 PM PT</t>
+          <t>2026-07-11 08:19:18 PM PT</t>
         </is>
       </c>
       <c r="C10" t="n">
@@ -1627,7 +1627,7 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Bottom 7 | 1 out</t>
+          <t>Bottom 7 | 2 out</t>
         </is>
       </c>
       <c r="F10" t="n">
@@ -1639,13 +1639,13 @@
         </is>
       </c>
       <c r="H10" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I10" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="J10" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="K10" t="inlineStr">
         <is>
@@ -1737,7 +1737,7 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>2026-07-11 08:17:17 PM PT</t>
+          <t>2026-07-11 08:19:17 PM PT</t>
         </is>
       </c>
       <c r="C11" t="n">
@@ -1851,7 +1851,7 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>2026-07-11 08:17:18 PM PT</t>
+          <t>2026-07-11 08:19:17 PM PT</t>
         </is>
       </c>
       <c r="C12" t="n">
@@ -1965,7 +1965,7 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>2026-07-11 08:17:18 PM PT</t>
+          <t>2026-07-11 08:19:18 PM PT</t>
         </is>
       </c>
       <c r="C13" t="n">
@@ -1978,7 +1978,7 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Bottom 7 | 1 out</t>
+          <t>Bottom 7 | 2 out</t>
         </is>
       </c>
       <c r="F13" t="n">
@@ -1990,13 +1990,13 @@
         </is>
       </c>
       <c r="H13" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I13" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="J13" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="K13" t="inlineStr">
         <is>
@@ -2088,7 +2088,7 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>2026-07-11 08:17:18 PM PT</t>
+          <t>2026-07-11 08:19:17 PM PT</t>
         </is>
       </c>
       <c r="C14" t="n">
@@ -2202,7 +2202,7 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>2026-07-11 08:17:17 PM PT</t>
+          <t>2026-07-11 08:19:17 PM PT</t>
         </is>
       </c>
       <c r="C15" t="n">
@@ -2316,7 +2316,7 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>2026-07-11 08:17:18 PM PT</t>
+          <t>2026-07-11 08:19:17 PM PT</t>
         </is>
       </c>
       <c r="C16" t="n">
@@ -2430,7 +2430,7 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>2026-07-11 08:17:18 PM PT</t>
+          <t>2026-07-11 08:19:18 PM PT</t>
         </is>
       </c>
       <c r="C17" t="n">
@@ -2443,7 +2443,7 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Bottom 7 | 1 out</t>
+          <t>Bottom 7 | 2 out</t>
         </is>
       </c>
       <c r="F17" t="n">
@@ -2455,13 +2455,13 @@
         </is>
       </c>
       <c r="H17" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I17" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="J17" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="K17" t="inlineStr">
         <is>
@@ -2553,7 +2553,7 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>2026-07-11 08:17:17 PM PT</t>
+          <t>2026-07-11 08:19:17 PM PT</t>
         </is>
       </c>
       <c r="C18" t="n">
@@ -2667,7 +2667,7 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>2026-07-11 08:17:18 PM PT</t>
+          <t>2026-07-11 08:19:17 PM PT</t>
         </is>
       </c>
       <c r="C19" t="n">
@@ -2781,7 +2781,7 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>2026-07-11 08:17:17 PM PT</t>
+          <t>2026-07-11 08:19:17 PM PT</t>
         </is>
       </c>
       <c r="C20" t="n">
@@ -2895,7 +2895,7 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>2026-07-11 08:17:17 PM PT</t>
+          <t>2026-07-11 08:19:17 PM PT</t>
         </is>
       </c>
       <c r="C21" t="n">
@@ -3009,7 +3009,7 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>2026-07-11 08:17:18 PM PT</t>
+          <t>2026-07-11 08:19:18 PM PT</t>
         </is>
       </c>
       <c r="C22" t="n">
@@ -3037,10 +3037,10 @@
         <v>1</v>
       </c>
       <c r="I22" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="J22" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="K22" t="inlineStr">
         <is>
@@ -3132,7 +3132,7 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>2026-07-11 08:17:18 PM PT</t>
+          <t>2026-07-11 08:19:17 PM PT</t>
         </is>
       </c>
       <c r="C23" t="n">
@@ -3246,7 +3246,7 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>2026-07-11 08:17:17 PM PT</t>
+          <t>2026-07-11 08:19:17 PM PT</t>
         </is>
       </c>
       <c r="C24" t="n">
@@ -3360,7 +3360,7 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>2026-07-11 08:17:18 PM PT</t>
+          <t>2026-07-11 08:19:17 PM PT</t>
         </is>
       </c>
       <c r="C25" t="n">
@@ -3474,7 +3474,7 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>2026-07-11 08:17:16 PM PT</t>
+          <t>2026-07-11 08:19:16 PM PT</t>
         </is>
       </c>
       <c r="C26" t="n">
@@ -3588,7 +3588,7 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>2026-07-11 08:17:17 PM PT</t>
+          <t>2026-07-11 08:19:17 PM PT</t>
         </is>
       </c>
       <c r="C27" t="n">
@@ -3702,7 +3702,7 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>2026-07-11 08:17:17 PM PT</t>
+          <t>2026-07-11 08:19:17 PM PT</t>
         </is>
       </c>
       <c r="C28" t="n">
@@ -3816,7 +3816,7 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>2026-07-11 08:17:18 PM PT</t>
+          <t>2026-07-11 08:19:17 PM PT</t>
         </is>
       </c>
       <c r="C29" t="n">
@@ -3930,7 +3930,7 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>2026-07-11 08:17:18 PM PT</t>
+          <t>2026-07-11 08:19:17 PM PT</t>
         </is>
       </c>
       <c r="C30" t="n">
@@ -4044,7 +4044,7 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>2026-07-11 08:17:18 PM PT</t>
+          <t>2026-07-11 08:19:17 PM PT</t>
         </is>
       </c>
       <c r="C31" t="n">
@@ -4158,7 +4158,7 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>2026-07-11 08:17:17 PM PT</t>
+          <t>2026-07-11 08:19:17 PM PT</t>
         </is>
       </c>
       <c r="C32" t="n">
@@ -4272,7 +4272,7 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>2026-07-11 08:17:18 PM PT</t>
+          <t>2026-07-11 08:19:17 PM PT</t>
         </is>
       </c>
       <c r="C33" t="n">
@@ -4386,7 +4386,7 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>2026-07-11 08:17:16 PM PT</t>
+          <t>2026-07-11 08:19:16 PM PT</t>
         </is>
       </c>
       <c r="C34" t="n">
@@ -4500,7 +4500,7 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>2026-07-11 08:17:16 PM PT</t>
+          <t>2026-07-11 08:19:16 PM PT</t>
         </is>
       </c>
       <c r="C35" t="n">
@@ -4614,7 +4614,7 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>2026-07-11 08:17:18 PM PT</t>
+          <t>2026-07-11 08:19:18 PM PT</t>
         </is>
       </c>
       <c r="C36" t="n">
@@ -4627,7 +4627,7 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Bottom 7 | 1 out</t>
+          <t>Bottom 7 | 2 out</t>
         </is>
       </c>
       <c r="F36" t="n">
@@ -4639,13 +4639,13 @@
         </is>
       </c>
       <c r="H36" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I36" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="J36" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="K36" t="inlineStr">
         <is>
@@ -4681,10 +4681,10 @@
         </is>
       </c>
       <c r="R36" t="n">
+        <v>4</v>
+      </c>
+      <c r="S36" t="n">
         <v>3</v>
-      </c>
-      <c r="S36" t="n">
-        <v>2</v>
       </c>
       <c r="T36" t="n">
         <v>1</v>
@@ -4737,7 +4737,7 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>2026-07-11 08:17:17 PM PT</t>
+          <t>2026-07-11 08:19:17 PM PT</t>
         </is>
       </c>
       <c r="C37" t="n">
@@ -4851,7 +4851,7 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>2026-07-11 08:17:17 PM PT</t>
+          <t>2026-07-11 08:19:16 PM PT</t>
         </is>
       </c>
       <c r="C38" t="n">
@@ -4965,7 +4965,7 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>2026-07-11 08:17:18 PM PT</t>
+          <t>2026-07-11 08:19:17 PM PT</t>
         </is>
       </c>
       <c r="C39" t="n">
@@ -5079,7 +5079,7 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>2026-07-11 08:17:16 PM PT</t>
+          <t>2026-07-11 08:19:16 PM PT</t>
         </is>
       </c>
       <c r="C40" t="n">
@@ -5193,7 +5193,7 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>2026-07-11 08:17:18 PM PT</t>
+          <t>2026-07-11 08:19:18 PM PT</t>
         </is>
       </c>
       <c r="C41" t="n">
@@ -5221,10 +5221,10 @@
         <v>1</v>
       </c>
       <c r="I41" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="J41" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="K41" t="inlineStr">
         <is>
@@ -5316,7 +5316,7 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>2026-07-11 08:17:18 PM PT</t>
+          <t>2026-07-11 08:19:17 PM PT</t>
         </is>
       </c>
       <c r="C42" t="n">
@@ -5430,7 +5430,7 @@
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>2026-07-11 08:17:18 PM PT</t>
+          <t>2026-07-11 08:19:17 PM PT</t>
         </is>
       </c>
       <c r="C43" t="n">
@@ -5544,7 +5544,7 @@
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>2026-07-11 08:17:18 PM PT</t>
+          <t>2026-07-11 08:19:17 PM PT</t>
         </is>
       </c>
       <c r="C44" t="n">
@@ -5658,7 +5658,7 @@
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>2026-07-11 08:17:18 PM PT</t>
+          <t>2026-07-11 08:19:17 PM PT</t>
         </is>
       </c>
       <c r="C45" t="n">
@@ -5772,7 +5772,7 @@
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>2026-07-11 08:17:18 PM PT</t>
+          <t>2026-07-11 08:19:17 PM PT</t>
         </is>
       </c>
       <c r="C46" t="n">
@@ -5886,7 +5886,7 @@
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>2026-07-11 08:17:17 PM PT</t>
+          <t>2026-07-11 08:19:17 PM PT</t>
         </is>
       </c>
       <c r="C47" t="n">
@@ -6000,7 +6000,7 @@
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>2026-07-11 08:17:18 PM PT</t>
+          <t>2026-07-11 08:19:17 PM PT</t>
         </is>
       </c>
       <c r="C48" t="n">
@@ -6114,7 +6114,7 @@
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>2026-07-11 08:17:17 PM PT</t>
+          <t>2026-07-11 08:19:17 PM PT</t>
         </is>
       </c>
       <c r="C49" t="n">
@@ -6228,7 +6228,7 @@
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>2026-07-11 08:17:16 PM PT</t>
+          <t>2026-07-11 08:19:16 PM PT</t>
         </is>
       </c>
       <c r="C50" t="n">
@@ -6342,7 +6342,7 @@
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>2026-07-11 08:17:18 PM PT</t>
+          <t>2026-07-11 08:19:17 PM PT</t>
         </is>
       </c>
       <c r="C51" t="n">
@@ -6456,7 +6456,7 @@
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>2026-07-11 08:17:18 PM PT</t>
+          <t>2026-07-11 08:19:17 PM PT</t>
         </is>
       </c>
       <c r="C52" t="n">
@@ -6570,7 +6570,7 @@
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>2026-07-11 08:17:18 PM PT</t>
+          <t>2026-07-11 08:19:17 PM PT</t>
         </is>
       </c>
       <c r="C53" t="n">
@@ -6684,7 +6684,7 @@
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>2026-07-11 08:17:17 PM PT</t>
+          <t>2026-07-11 08:19:16 PM PT</t>
         </is>
       </c>
       <c r="C54" t="n">
@@ -6798,7 +6798,7 @@
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>2026-07-11 08:17:17 PM PT</t>
+          <t>2026-07-11 08:19:16 PM PT</t>
         </is>
       </c>
       <c r="C55" t="n">
@@ -6912,7 +6912,7 @@
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>2026-07-11 08:17:17 PM PT</t>
+          <t>2026-07-11 08:19:16 PM PT</t>
         </is>
       </c>
       <c r="C56" t="n">
@@ -7026,7 +7026,7 @@
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>2026-07-11 08:17:18 PM PT</t>
+          <t>2026-07-11 08:19:17 PM PT</t>
         </is>
       </c>
       <c r="C57" t="n">
@@ -7140,7 +7140,7 @@
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>2026-07-11 08:17:17 PM PT</t>
+          <t>2026-07-11 08:19:17 PM PT</t>
         </is>
       </c>
       <c r="C58" t="n">
@@ -7254,7 +7254,7 @@
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>2026-07-11 08:17:17 PM PT</t>
+          <t>2026-07-11 08:19:16 PM PT</t>
         </is>
       </c>
       <c r="C59" t="n">
@@ -7368,7 +7368,7 @@
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>2026-07-11 08:17:16 PM PT</t>
+          <t>2026-07-11 08:19:16 PM PT</t>
         </is>
       </c>
       <c r="C60" t="n">
@@ -7482,7 +7482,7 @@
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>2026-07-11 08:17:16 PM PT</t>
+          <t>2026-07-11 08:19:16 PM PT</t>
         </is>
       </c>
       <c r="C61" t="n">
@@ -7596,7 +7596,7 @@
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>2026-07-11 08:17:18 PM PT</t>
+          <t>2026-07-11 08:19:18 PM PT</t>
         </is>
       </c>
       <c r="C62" t="n">
@@ -7609,7 +7609,7 @@
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>Bottom 7 | 1 out</t>
+          <t>Bottom 7 | 2 out</t>
         </is>
       </c>
       <c r="F62" t="n">
@@ -7621,13 +7621,13 @@
         </is>
       </c>
       <c r="H62" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I62" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="J62" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="K62" t="inlineStr">
         <is>
@@ -7719,7 +7719,7 @@
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>2026-07-11 08:17:18 PM PT</t>
+          <t>2026-07-11 08:19:18 PM PT</t>
         </is>
       </c>
       <c r="C63" t="n">
@@ -7747,10 +7747,10 @@
         <v>1</v>
       </c>
       <c r="I63" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="J63" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="K63" t="inlineStr">
         <is>
@@ -7842,30 +7842,39 @@
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>2026-07-11 08:17:17 PM PT</t>
+          <t>2026-07-11 08:19:18 PM PT</t>
         </is>
       </c>
       <c r="C64" t="n">
-        <v>824576</v>
+        <v>823926</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>11:10 AM PT</t>
+          <t>6:10 PM PT</t>
         </is>
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>Final</t>
+          <t>Top 7 | 1 out</t>
         </is>
       </c>
       <c r="F64" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="G64" t="inlineStr">
         <is>
           <t>Top</t>
         </is>
       </c>
+      <c r="H64" t="n">
+        <v>1</v>
+      </c>
+      <c r="I64" t="n">
+        <v>0</v>
+      </c>
+      <c r="J64" t="n">
+        <v>0</v>
+      </c>
       <c r="K64" t="inlineStr">
         <is>
           <t>Away</t>
@@ -7873,61 +7882,61 @@
       </c>
       <c r="L64" t="inlineStr">
         <is>
-          <t>ATH</t>
+          <t>ARI</t>
         </is>
       </c>
       <c r="M64" t="inlineStr">
         <is>
-          <t>CWS</t>
+          <t>LAD</t>
         </is>
       </c>
       <c r="N64" t="inlineStr">
         <is>
-          <t>Jacob Wilson</t>
+          <t>Gabriel Moreno</t>
         </is>
       </c>
       <c r="O64" t="n">
-        <v>805779</v>
+        <v>672515</v>
       </c>
       <c r="P64" t="inlineStr">
         <is>
-          <t>SS</t>
+          <t>DH</t>
         </is>
       </c>
       <c r="Q64" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>4</t>
         </is>
       </c>
       <c r="R64" t="n">
         <v>4</v>
       </c>
       <c r="S64" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="T64" t="n">
+        <v>1</v>
+      </c>
+      <c r="U64" t="n">
+        <v>1</v>
+      </c>
+      <c r="V64" t="n">
+        <v>0</v>
+      </c>
+      <c r="W64" t="n">
+        <v>0</v>
+      </c>
+      <c r="X64" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y64" t="n">
         <v>2</v>
       </c>
-      <c r="U64" t="n">
-        <v>1</v>
-      </c>
-      <c r="V64" t="n">
-        <v>0</v>
-      </c>
-      <c r="W64" s="8" t="n">
-        <v>1</v>
-      </c>
-      <c r="X64" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y64" t="n">
-        <v>0</v>
-      </c>
       <c r="Z64" t="n">
         <v>0</v>
       </c>
-      <c r="AA64" t="n">
-        <v>0</v>
+      <c r="AA64" s="5" t="n">
+        <v>2</v>
       </c>
       <c r="AB64" t="n">
         <v>0</v>
@@ -7936,16 +7945,16 @@
         <v>0</v>
       </c>
       <c r="AD64" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AE64" s="4" t="n">
         <v>11</v>
       </c>
       <c r="AF64" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="AG64" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
     </row>
     <row r="65">
@@ -7956,15 +7965,15 @@
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>2026-07-11 08:17:18 PM PT</t>
+          <t>2026-07-11 08:19:17 PM PT</t>
         </is>
       </c>
       <c r="C65" t="n">
-        <v>824249</v>
+        <v>824576</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>3:10 PM PT</t>
+          <t>11:10 AM PT</t>
         </is>
       </c>
       <c r="E65" t="inlineStr">
@@ -7977,7 +7986,7 @@
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>Bottom</t>
+          <t>Top</t>
         </is>
       </c>
       <c r="K65" t="inlineStr">
@@ -7987,30 +7996,30 @@
       </c>
       <c r="L65" t="inlineStr">
         <is>
-          <t>PHI</t>
+          <t>ATH</t>
         </is>
       </c>
       <c r="M65" t="inlineStr">
         <is>
-          <t>DET</t>
+          <t>CWS</t>
         </is>
       </c>
       <c r="N65" t="inlineStr">
         <is>
-          <t>J.T. Realmuto</t>
+          <t>Jacob Wilson</t>
         </is>
       </c>
       <c r="O65" t="n">
-        <v>592663</v>
+        <v>805779</v>
       </c>
       <c r="P65" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>SS</t>
         </is>
       </c>
       <c r="Q65" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>1</t>
         </is>
       </c>
       <c r="R65" t="n">
@@ -8020,25 +8029,25 @@
         <v>4</v>
       </c>
       <c r="T65" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="U65" t="n">
-        <v>0</v>
-      </c>
-      <c r="V65" s="7" t="n">
-        <v>1</v>
-      </c>
-      <c r="W65" t="n">
-        <v>0</v>
+        <v>1</v>
+      </c>
+      <c r="V65" t="n">
+        <v>0</v>
+      </c>
+      <c r="W65" s="8" t="n">
+        <v>1</v>
       </c>
       <c r="X65" t="n">
         <v>0</v>
       </c>
       <c r="Y65" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Z65" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AA65" t="n">
         <v>0</v>
@@ -8050,16 +8059,16 @@
         <v>0</v>
       </c>
       <c r="AD65" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AE65" s="4" t="n">
         <v>11</v>
       </c>
       <c r="AF65" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="AG65" t="n">
-        <v>7</v>
+        <v>4</v>
       </c>
     </row>
     <row r="66">
@@ -8070,101 +8079,92 @@
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>2026-07-11 08:17:18 PM PT</t>
+          <t>2026-07-11 08:19:17 PM PT</t>
         </is>
       </c>
       <c r="C66" t="n">
-        <v>823276</v>
+        <v>824249</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>5:40 PM PT</t>
+          <t>3:10 PM PT</t>
         </is>
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>Bottom 7 | 1 out</t>
+          <t>Final</t>
         </is>
       </c>
       <c r="F66" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="G66" t="inlineStr">
         <is>
           <t>Bottom</t>
         </is>
       </c>
-      <c r="H66" t="n">
-        <v>1</v>
-      </c>
-      <c r="I66" t="n">
-        <v>0</v>
-      </c>
-      <c r="J66" t="n">
-        <v>0</v>
-      </c>
       <c r="K66" t="inlineStr">
         <is>
-          <t>Home</t>
+          <t>Away</t>
         </is>
       </c>
       <c r="L66" t="inlineStr">
         <is>
-          <t>SD</t>
+          <t>PHI</t>
         </is>
       </c>
       <c r="M66" t="inlineStr">
         <is>
-          <t>TOR</t>
+          <t>DET</t>
         </is>
       </c>
       <c r="N66" t="inlineStr">
         <is>
-          <t>Jackson Merrill</t>
+          <t>J.T. Realmuto</t>
         </is>
       </c>
       <c r="O66" t="n">
-        <v>701538</v>
+        <v>592663</v>
       </c>
       <c r="P66" t="inlineStr">
         <is>
-          <t>CF</t>
+          <t>C</t>
         </is>
       </c>
       <c r="Q66" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>7</t>
         </is>
       </c>
       <c r="R66" t="n">
         <v>4</v>
       </c>
       <c r="S66" t="n">
+        <v>4</v>
+      </c>
+      <c r="T66" t="n">
+        <v>1</v>
+      </c>
+      <c r="U66" t="n">
+        <v>0</v>
+      </c>
+      <c r="V66" s="7" t="n">
+        <v>1</v>
+      </c>
+      <c r="W66" t="n">
+        <v>0</v>
+      </c>
+      <c r="X66" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y66" t="n">
+        <v>1</v>
+      </c>
+      <c r="Z66" t="n">
         <v>2</v>
       </c>
-      <c r="T66" t="n">
-        <v>1</v>
-      </c>
-      <c r="U66" t="n">
-        <v>1</v>
-      </c>
-      <c r="V66" t="n">
-        <v>0</v>
-      </c>
-      <c r="W66" t="n">
-        <v>0</v>
-      </c>
-      <c r="X66" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y66" t="n">
-        <v>2</v>
-      </c>
-      <c r="Z66" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA66" s="5" t="n">
-        <v>2</v>
+      <c r="AA66" t="n">
+        <v>0</v>
       </c>
       <c r="AB66" t="n">
         <v>0</v>
@@ -8173,13 +8173,13 @@
         <v>0</v>
       </c>
       <c r="AD66" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AE66" s="4" t="n">
         <v>11</v>
       </c>
       <c r="AF66" t="n">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="AG66" t="n">
         <v>7</v>
@@ -8193,52 +8193,61 @@
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>2026-07-11 08:17:18 PM PT</t>
+          <t>2026-07-11 08:19:18 PM PT</t>
         </is>
       </c>
       <c r="C67" t="n">
-        <v>823844</v>
+        <v>823276</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>1:10 PM PT</t>
+          <t>5:40 PM PT</t>
         </is>
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>Final</t>
+          <t>Bottom 7 | 2 out</t>
         </is>
       </c>
       <c r="F67" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="G67" t="inlineStr">
         <is>
           <t>Bottom</t>
         </is>
       </c>
+      <c r="H67" t="n">
+        <v>2</v>
+      </c>
+      <c r="I67" t="n">
+        <v>3</v>
+      </c>
+      <c r="J67" t="n">
+        <v>2</v>
+      </c>
       <c r="K67" t="inlineStr">
         <is>
-          <t>Away</t>
+          <t>Home</t>
         </is>
       </c>
       <c r="L67" t="inlineStr">
         <is>
-          <t>CLE</t>
+          <t>SD</t>
         </is>
       </c>
       <c r="M67" t="inlineStr">
         <is>
-          <t>MIA</t>
+          <t>TOR</t>
         </is>
       </c>
       <c r="N67" t="inlineStr">
         <is>
-          <t>Petey Halpin</t>
+          <t>Jackson Merrill</t>
         </is>
       </c>
       <c r="O67" t="n">
-        <v>690984</v>
+        <v>701538</v>
       </c>
       <c r="P67" t="inlineStr">
         <is>
@@ -8247,14 +8256,14 @@
       </c>
       <c r="Q67" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>2</t>
         </is>
       </c>
       <c r="R67" t="n">
         <v>4</v>
       </c>
       <c r="S67" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="T67" t="n">
         <v>1</v>
@@ -8272,31 +8281,31 @@
         <v>0</v>
       </c>
       <c r="Y67" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="Z67" t="n">
         <v>0</v>
       </c>
-      <c r="AA67" t="n">
-        <v>0</v>
+      <c r="AA67" s="5" t="n">
+        <v>2</v>
       </c>
       <c r="AB67" t="n">
         <v>0</v>
       </c>
-      <c r="AC67" s="6" t="n">
-        <v>1</v>
+      <c r="AC67" t="n">
+        <v>0</v>
       </c>
       <c r="AD67" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="AE67" s="4" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="AF67" t="n">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="AG67" t="n">
-        <v>11</v>
+        <v>7</v>
       </c>
     </row>
     <row r="68">
@@ -8307,15 +8316,15 @@
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>2026-07-11 08:17:17 PM PT</t>
+          <t>2026-07-11 08:19:17 PM PT</t>
         </is>
       </c>
       <c r="C68" t="n">
-        <v>824576</v>
+        <v>823844</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>11:10 AM PT</t>
+          <t>1:10 PM PT</t>
         </is>
       </c>
       <c r="E68" t="inlineStr">
@@ -8328,89 +8337,89 @@
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>Top</t>
+          <t>Bottom</t>
         </is>
       </c>
       <c r="K68" t="inlineStr">
         <is>
-          <t>Home</t>
+          <t>Away</t>
         </is>
       </c>
       <c r="L68" t="inlineStr">
         <is>
-          <t>CWS</t>
+          <t>CLE</t>
         </is>
       </c>
       <c r="M68" t="inlineStr">
         <is>
-          <t>ATH</t>
+          <t>MIA</t>
         </is>
       </c>
       <c r="N68" t="inlineStr">
         <is>
-          <t>Chase Meidroth</t>
+          <t>Petey Halpin</t>
         </is>
       </c>
       <c r="O68" t="n">
-        <v>805367</v>
+        <v>690984</v>
       </c>
       <c r="P68" t="inlineStr">
         <is>
-          <t>2B</t>
+          <t>CF</t>
         </is>
       </c>
       <c r="Q68" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>7</t>
         </is>
       </c>
       <c r="R68" t="n">
+        <v>4</v>
+      </c>
+      <c r="S68" t="n">
+        <v>4</v>
+      </c>
+      <c r="T68" t="n">
+        <v>1</v>
+      </c>
+      <c r="U68" t="n">
+        <v>1</v>
+      </c>
+      <c r="V68" t="n">
+        <v>0</v>
+      </c>
+      <c r="W68" t="n">
+        <v>0</v>
+      </c>
+      <c r="X68" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y68" t="n">
+        <v>1</v>
+      </c>
+      <c r="Z68" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA68" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB68" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC68" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="AD68" t="n">
         <v>3</v>
-      </c>
-      <c r="S68" t="n">
-        <v>3</v>
-      </c>
-      <c r="T68" t="n">
-        <v>2</v>
-      </c>
-      <c r="U68" t="n">
-        <v>1</v>
-      </c>
-      <c r="V68" s="7" t="n">
-        <v>1</v>
-      </c>
-      <c r="W68" t="n">
-        <v>0</v>
-      </c>
-      <c r="X68" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y68" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z68" t="n">
-        <v>1</v>
-      </c>
-      <c r="AA68" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB68" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC68" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD68" t="n">
-        <v>0</v>
       </c>
       <c r="AE68" s="4" t="n">
         <v>10</v>
       </c>
       <c r="AF68" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="AG68" t="n">
-        <v>5</v>
+        <v>11</v>
       </c>
     </row>
     <row r="69">
@@ -8421,11 +8430,11 @@
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>2026-07-11 08:17:17 PM PT</t>
+          <t>2026-07-11 08:19:17 PM PT</t>
         </is>
       </c>
       <c r="C69" t="n">
-        <v>823682</v>
+        <v>824576</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
@@ -8447,42 +8456,42 @@
       </c>
       <c r="K69" t="inlineStr">
         <is>
-          <t>Away</t>
+          <t>Home</t>
         </is>
       </c>
       <c r="L69" t="inlineStr">
         <is>
-          <t>LAA</t>
+          <t>CWS</t>
         </is>
       </c>
       <c r="M69" t="inlineStr">
         <is>
-          <t>MIN</t>
+          <t>ATH</t>
         </is>
       </c>
       <c r="N69" t="inlineStr">
         <is>
-          <t>Mike Trout</t>
+          <t>Chase Meidroth</t>
         </is>
       </c>
       <c r="O69" t="n">
-        <v>545361</v>
+        <v>805367</v>
       </c>
       <c r="P69" t="inlineStr">
         <is>
-          <t>CF</t>
+          <t>2B</t>
         </is>
       </c>
       <c r="Q69" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>5</t>
         </is>
       </c>
       <c r="R69" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="S69" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="T69" t="n">
         <v>2</v>
@@ -8500,10 +8509,10 @@
         <v>0</v>
       </c>
       <c r="Y69" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Z69" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AA69" t="n">
         <v>0</v>
@@ -8515,16 +8524,16 @@
         <v>0</v>
       </c>
       <c r="AD69" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AE69" s="4" t="n">
         <v>10</v>
       </c>
       <c r="AF69" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="AG69" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
     </row>
     <row r="70">
@@ -8535,61 +8544,52 @@
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>2026-07-11 08:17:18 PM PT</t>
+          <t>2026-07-11 08:19:16 PM PT</t>
         </is>
       </c>
       <c r="C70" t="n">
-        <v>823926</v>
+        <v>823682</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>6:10 PM PT</t>
+          <t>11:10 AM PT</t>
         </is>
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>Top 7 | 1 out</t>
+          <t>Final</t>
         </is>
       </c>
       <c r="F70" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="G70" t="inlineStr">
         <is>
           <t>Top</t>
         </is>
       </c>
-      <c r="H70" t="n">
-        <v>1</v>
-      </c>
-      <c r="I70" t="n">
-        <v>3</v>
-      </c>
-      <c r="J70" t="n">
-        <v>2</v>
-      </c>
       <c r="K70" t="inlineStr">
         <is>
-          <t>Home</t>
+          <t>Away</t>
         </is>
       </c>
       <c r="L70" t="inlineStr">
         <is>
-          <t>LAD</t>
+          <t>LAA</t>
         </is>
       </c>
       <c r="M70" t="inlineStr">
         <is>
-          <t>ARI</t>
+          <t>MIN</t>
         </is>
       </c>
       <c r="N70" t="inlineStr">
         <is>
-          <t>Andy Pages</t>
+          <t>Mike Trout</t>
         </is>
       </c>
       <c r="O70" t="n">
-        <v>681624</v>
+        <v>545361</v>
       </c>
       <c r="P70" t="inlineStr">
         <is>
@@ -8602,19 +8602,19 @@
         </is>
       </c>
       <c r="R70" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="S70" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="T70" t="n">
         <v>2</v>
       </c>
       <c r="U70" t="n">
-        <v>2</v>
-      </c>
-      <c r="V70" t="n">
-        <v>0</v>
+        <v>1</v>
+      </c>
+      <c r="V70" s="7" t="n">
+        <v>1</v>
       </c>
       <c r="W70" t="n">
         <v>0</v>
@@ -8626,7 +8626,7 @@
         <v>1</v>
       </c>
       <c r="Z70" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AA70" t="n">
         <v>0</v>
@@ -8638,16 +8638,16 @@
         <v>0</v>
       </c>
       <c r="AD70" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AE70" s="4" t="n">
         <v>10</v>
       </c>
       <c r="AF70" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AG70" t="n">
-        <v>6</v>
+        <v>10</v>
       </c>
     </row>
     <row r="71">
@@ -8658,61 +8658,70 @@
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>2026-07-11 08:17:16 PM PT</t>
+          <t>2026-07-11 08:19:18 PM PT</t>
         </is>
       </c>
       <c r="C71" t="n">
-        <v>823356</v>
+        <v>823926</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>1:05 PM PT</t>
+          <t>6:10 PM PT</t>
         </is>
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>Final</t>
+          <t>Top 7 | 1 out</t>
         </is>
       </c>
       <c r="F71" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="G71" t="inlineStr">
         <is>
           <t>Top</t>
         </is>
       </c>
+      <c r="H71" t="n">
+        <v>1</v>
+      </c>
+      <c r="I71" t="n">
+        <v>0</v>
+      </c>
+      <c r="J71" t="n">
+        <v>0</v>
+      </c>
       <c r="K71" t="inlineStr">
         <is>
-          <t>Away</t>
+          <t>Home</t>
         </is>
       </c>
       <c r="L71" t="inlineStr">
         <is>
-          <t>MIL</t>
+          <t>LAD</t>
         </is>
       </c>
       <c r="M71" t="inlineStr">
         <is>
-          <t>PIT</t>
+          <t>ARI</t>
         </is>
       </c>
       <c r="N71" t="inlineStr">
         <is>
-          <t>Joey Ortiz</t>
+          <t>Andy Pages</t>
         </is>
       </c>
       <c r="O71" t="n">
-        <v>687401</v>
+        <v>681624</v>
       </c>
       <c r="P71" t="inlineStr">
         <is>
-          <t>3B</t>
+          <t>CF</t>
         </is>
       </c>
       <c r="Q71" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>2</t>
         </is>
       </c>
       <c r="R71" t="n">
@@ -8725,10 +8734,10 @@
         <v>2</v>
       </c>
       <c r="U71" t="n">
-        <v>1</v>
-      </c>
-      <c r="V71" s="7" t="n">
-        <v>1</v>
+        <v>2</v>
+      </c>
+      <c r="V71" t="n">
+        <v>0</v>
       </c>
       <c r="W71" t="n">
         <v>0</v>
@@ -8740,7 +8749,7 @@
         <v>1</v>
       </c>
       <c r="Z71" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AA71" t="n">
         <v>0</v>
@@ -8761,7 +8770,7 @@
         <v>2</v>
       </c>
       <c r="AG71" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
     </row>
     <row r="72">
@@ -8772,11 +8781,11 @@
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>2026-07-11 08:17:17 PM PT</t>
+          <t>2026-07-11 08:19:16 PM PT</t>
         </is>
       </c>
       <c r="C72" t="n">
-        <v>822711</v>
+        <v>823356</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
@@ -8793,7 +8802,7 @@
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>Bottom</t>
+          <t>Top</t>
         </is>
       </c>
       <c r="K72" t="inlineStr">
@@ -8803,46 +8812,46 @@
       </c>
       <c r="L72" t="inlineStr">
         <is>
-          <t>NYY</t>
+          <t>MIL</t>
         </is>
       </c>
       <c r="M72" t="inlineStr">
         <is>
-          <t>WSH</t>
+          <t>PIT</t>
         </is>
       </c>
       <c r="N72" t="inlineStr">
         <is>
-          <t>Ben Rice</t>
+          <t>Joey Ortiz</t>
         </is>
       </c>
       <c r="O72" t="n">
-        <v>700250</v>
+        <v>687401</v>
       </c>
       <c r="P72" t="inlineStr">
         <is>
-          <t>DH</t>
+          <t>3B</t>
         </is>
       </c>
       <c r="Q72" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>9</t>
         </is>
       </c>
       <c r="R72" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="S72" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="T72" t="n">
         <v>2</v>
       </c>
       <c r="U72" t="n">
-        <v>2</v>
-      </c>
-      <c r="V72" t="n">
-        <v>0</v>
+        <v>1</v>
+      </c>
+      <c r="V72" s="7" t="n">
+        <v>1</v>
       </c>
       <c r="W72" t="n">
         <v>0</v>
@@ -8851,13 +8860,13 @@
         <v>0</v>
       </c>
       <c r="Y72" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Z72" t="n">
         <v>0</v>
       </c>
-      <c r="AA72" s="5" t="n">
-        <v>2</v>
+      <c r="AA72" t="n">
+        <v>0</v>
       </c>
       <c r="AB72" t="n">
         <v>0</v>
@@ -8872,10 +8881,10 @@
         <v>10</v>
       </c>
       <c r="AF72" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="AG72" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
     </row>
     <row r="73">
@@ -8886,11 +8895,11 @@
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>2026-07-11 08:17:16 PM PT</t>
+          <t>2026-07-11 08:19:17 PM PT</t>
         </is>
       </c>
       <c r="C73" t="n">
-        <v>823356</v>
+        <v>822711</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
@@ -8907,35 +8916,35 @@
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>Top</t>
+          <t>Bottom</t>
         </is>
       </c>
       <c r="K73" t="inlineStr">
         <is>
-          <t>Home</t>
+          <t>Away</t>
         </is>
       </c>
       <c r="L73" t="inlineStr">
         <is>
-          <t>PIT</t>
+          <t>NYY</t>
         </is>
       </c>
       <c r="M73" t="inlineStr">
         <is>
-          <t>MIL</t>
+          <t>WSH</t>
         </is>
       </c>
       <c r="N73" t="inlineStr">
         <is>
-          <t>Brandon Lowe</t>
+          <t>Ben Rice</t>
         </is>
       </c>
       <c r="O73" t="n">
-        <v>664040</v>
+        <v>700250</v>
       </c>
       <c r="P73" t="inlineStr">
         <is>
-          <t>2B</t>
+          <t>DH</t>
         </is>
       </c>
       <c r="Q73" t="inlineStr">
@@ -8947,16 +8956,16 @@
         <v>4</v>
       </c>
       <c r="S73" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="T73" t="n">
         <v>2</v>
       </c>
       <c r="U73" t="n">
-        <v>1</v>
-      </c>
-      <c r="V73" s="7" t="n">
-        <v>1</v>
+        <v>2</v>
+      </c>
+      <c r="V73" t="n">
+        <v>0</v>
       </c>
       <c r="W73" t="n">
         <v>0</v>
@@ -8965,13 +8974,13 @@
         <v>0</v>
       </c>
       <c r="Y73" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Z73" t="n">
         <v>0</v>
       </c>
-      <c r="AA73" t="n">
-        <v>0</v>
+      <c r="AA73" s="5" t="n">
+        <v>2</v>
       </c>
       <c r="AB73" t="n">
         <v>0</v>
@@ -8980,16 +8989,16 @@
         <v>0</v>
       </c>
       <c r="AD73" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AE73" s="4" t="n">
         <v>10</v>
       </c>
       <c r="AF73" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="AG73" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
     </row>
     <row r="74">
@@ -9000,61 +9009,52 @@
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>2026-07-11 08:17:18 PM PT</t>
+          <t>2026-07-11 08:19:16 PM PT</t>
         </is>
       </c>
       <c r="C74" t="n">
-        <v>823276</v>
+        <v>823356</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>5:40 PM PT</t>
+          <t>1:05 PM PT</t>
         </is>
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>Bottom 7 | 1 out</t>
+          <t>Final</t>
         </is>
       </c>
       <c r="F74" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>Bottom</t>
-        </is>
-      </c>
-      <c r="H74" t="n">
-        <v>1</v>
-      </c>
-      <c r="I74" t="n">
-        <v>0</v>
-      </c>
-      <c r="J74" t="n">
-        <v>0</v>
+          <t>Top</t>
+        </is>
       </c>
       <c r="K74" t="inlineStr">
         <is>
-          <t>Away</t>
+          <t>Home</t>
         </is>
       </c>
       <c r="L74" t="inlineStr">
         <is>
-          <t>TOR</t>
+          <t>PIT</t>
         </is>
       </c>
       <c r="M74" t="inlineStr">
         <is>
-          <t>SD</t>
+          <t>MIL</t>
         </is>
       </c>
       <c r="N74" t="inlineStr">
         <is>
-          <t>Ernie Clement</t>
+          <t>Brandon Lowe</t>
         </is>
       </c>
       <c r="O74" t="n">
-        <v>676391</v>
+        <v>664040</v>
       </c>
       <c r="P74" t="inlineStr">
         <is>
@@ -9063,23 +9063,23 @@
       </c>
       <c r="Q74" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="R74" t="n">
         <v>4</v>
       </c>
       <c r="S74" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="T74" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="U74" t="n">
         <v>1</v>
       </c>
-      <c r="V74" t="n">
-        <v>0</v>
+      <c r="V74" s="7" t="n">
+        <v>1</v>
       </c>
       <c r="W74" t="n">
         <v>0</v>
@@ -9088,31 +9088,31 @@
         <v>0</v>
       </c>
       <c r="Y74" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Z74" t="n">
         <v>0</v>
       </c>
-      <c r="AA74" s="5" t="n">
-        <v>1</v>
+      <c r="AA74" t="n">
+        <v>0</v>
       </c>
       <c r="AB74" t="n">
         <v>0</v>
       </c>
-      <c r="AC74" s="6" t="n">
-        <v>1</v>
+      <c r="AC74" t="n">
+        <v>0</v>
       </c>
       <c r="AD74" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AE74" s="4" t="n">
         <v>10</v>
       </c>
       <c r="AF74" t="n">
+        <v>3</v>
+      </c>
+      <c r="AG74" t="n">
         <v>7</v>
-      </c>
-      <c r="AG74" t="n">
-        <v>6</v>
       </c>
     </row>
     <row r="75">
@@ -9123,20 +9123,20 @@
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>2026-07-11 08:17:18 PM PT</t>
+          <t>2026-07-11 08:19:18 PM PT</t>
         </is>
       </c>
       <c r="C75" t="n">
-        <v>823926</v>
+        <v>823276</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>6:10 PM PT</t>
+          <t>5:40 PM PT</t>
         </is>
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>Top 7 | 1 out</t>
+          <t>Bottom 7 | 2 out</t>
         </is>
       </c>
       <c r="F75" t="n">
@@ -9144,11 +9144,11 @@
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>Top</t>
+          <t>Bottom</t>
         </is>
       </c>
       <c r="H75" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I75" t="n">
         <v>3</v>
@@ -9163,38 +9163,38 @@
       </c>
       <c r="L75" t="inlineStr">
         <is>
-          <t>ARI</t>
+          <t>TOR</t>
         </is>
       </c>
       <c r="M75" t="inlineStr">
         <is>
-          <t>LAD</t>
+          <t>SD</t>
         </is>
       </c>
       <c r="N75" t="inlineStr">
         <is>
-          <t>Gabriel Moreno</t>
+          <t>Ernie Clement</t>
         </is>
       </c>
       <c r="O75" t="n">
-        <v>672515</v>
+        <v>676391</v>
       </c>
       <c r="P75" t="inlineStr">
         <is>
-          <t>DH</t>
+          <t>2B</t>
         </is>
       </c>
       <c r="Q75" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>1</t>
         </is>
       </c>
       <c r="R75" t="n">
+        <v>4</v>
+      </c>
+      <c r="S75" t="n">
         <v>3</v>
       </c>
-      <c r="S75" t="n">
-        <v>2</v>
-      </c>
       <c r="T75" t="n">
         <v>1</v>
       </c>
@@ -9211,7 +9211,7 @@
         <v>0</v>
       </c>
       <c r="Y75" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="Z75" t="n">
         <v>0</v>
@@ -9222,20 +9222,20 @@
       <c r="AB75" t="n">
         <v>0</v>
       </c>
-      <c r="AC75" t="n">
-        <v>0</v>
+      <c r="AC75" s="6" t="n">
+        <v>1</v>
       </c>
       <c r="AD75" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AE75" s="4" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AF75" t="n">
+        <v>7</v>
+      </c>
+      <c r="AG75" t="n">
         <v>6</v>
-      </c>
-      <c r="AG75" t="n">
-        <v>5</v>
       </c>
     </row>
     <row r="76">
@@ -9246,7 +9246,7 @@
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>2026-07-11 08:17:18 PM PT</t>
+          <t>2026-07-11 08:19:17 PM PT</t>
         </is>
       </c>
       <c r="C76" t="n">
@@ -9360,7 +9360,7 @@
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>2026-07-11 08:17:18 PM PT</t>
+          <t>2026-07-11 08:19:17 PM PT</t>
         </is>
       </c>
       <c r="C77" t="n">
@@ -9474,7 +9474,7 @@
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>2026-07-11 08:17:18 PM PT</t>
+          <t>2026-07-11 08:19:17 PM PT</t>
         </is>
       </c>
       <c r="C78" t="n">
@@ -9588,7 +9588,7 @@
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>2026-07-11 08:17:16 PM PT</t>
+          <t>2026-07-11 08:19:16 PM PT</t>
         </is>
       </c>
       <c r="C79" t="n">
@@ -9702,7 +9702,7 @@
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>2026-07-11 08:17:16 PM PT</t>
+          <t>2026-07-11 08:19:16 PM PT</t>
         </is>
       </c>
       <c r="C80" t="n">
@@ -9816,7 +9816,7 @@
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>2026-07-11 08:17:16 PM PT</t>
+          <t>2026-07-11 08:19:16 PM PT</t>
         </is>
       </c>
       <c r="C81" t="n">
@@ -9930,7 +9930,7 @@
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>2026-07-11 08:17:16 PM PT</t>
+          <t>2026-07-11 08:19:16 PM PT</t>
         </is>
       </c>
       <c r="C82" t="n">
@@ -10044,7 +10044,7 @@
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>2026-07-11 08:17:16 PM PT</t>
+          <t>2026-07-11 08:19:16 PM PT</t>
         </is>
       </c>
       <c r="C83" t="n">
@@ -10158,7 +10158,7 @@
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>2026-07-11 08:17:16 PM PT</t>
+          <t>2026-07-11 08:19:16 PM PT</t>
         </is>
       </c>
       <c r="C84" t="n">
@@ -10272,7 +10272,7 @@
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>2026-07-11 08:17:17 PM PT</t>
+          <t>2026-07-11 08:19:17 PM PT</t>
         </is>
       </c>
       <c r="C85" t="n">
@@ -10386,7 +10386,7 @@
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>2026-07-11 08:17:17 PM PT</t>
+          <t>2026-07-11 08:19:17 PM PT</t>
         </is>
       </c>
       <c r="C86" t="n">
@@ -10500,7 +10500,7 @@
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>2026-07-11 08:17:17 PM PT</t>
+          <t>2026-07-11 08:19:17 PM PT</t>
         </is>
       </c>
       <c r="C87" t="n">
@@ -10614,7 +10614,7 @@
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>2026-07-11 08:17:18 PM PT</t>
+          <t>2026-07-11 08:19:17 PM PT</t>
         </is>
       </c>
       <c r="C88" t="n">
@@ -10728,7 +10728,7 @@
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>2026-07-11 08:17:18 PM PT</t>
+          <t>2026-07-11 08:19:18 PM PT</t>
         </is>
       </c>
       <c r="C89" t="n">
@@ -10741,7 +10741,7 @@
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>Bottom 7 | 1 out</t>
+          <t>Bottom 7 | 2 out</t>
         </is>
       </c>
       <c r="F89" t="n">
@@ -10753,13 +10753,13 @@
         </is>
       </c>
       <c r="H89" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I89" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="J89" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="K89" t="inlineStr">
         <is>
@@ -10851,7 +10851,7 @@
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>2026-07-11 08:17:17 PM PT</t>
+          <t>2026-07-11 08:19:17 PM PT</t>
         </is>
       </c>
       <c r="C90" t="n">
@@ -10965,7 +10965,7 @@
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>2026-07-11 08:17:18 PM PT</t>
+          <t>2026-07-11 08:19:17 PM PT</t>
         </is>
       </c>
       <c r="C91" t="n">
@@ -11079,7 +11079,7 @@
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>2026-07-11 08:17:18 PM PT</t>
+          <t>2026-07-11 08:19:17 PM PT</t>
         </is>
       </c>
       <c r="C92" t="n">
@@ -11193,7 +11193,7 @@
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>2026-07-11 08:17:18 PM PT</t>
+          <t>2026-07-11 08:19:17 PM PT</t>
         </is>
       </c>
       <c r="C93" t="n">
@@ -11307,7 +11307,7 @@
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>2026-07-11 08:17:17 PM PT</t>
+          <t>2026-07-11 08:19:17 PM PT</t>
         </is>
       </c>
       <c r="C94" t="n">
@@ -11421,7 +11421,7 @@
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>2026-07-11 08:17:18 PM PT</t>
+          <t>2026-07-11 08:19:17 PM PT</t>
         </is>
       </c>
       <c r="C95" t="n">
@@ -11535,7 +11535,7 @@
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>2026-07-11 08:17:18 PM PT</t>
+          <t>2026-07-11 08:19:17 PM PT</t>
         </is>
       </c>
       <c r="C96" t="n">
@@ -11649,7 +11649,7 @@
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>2026-07-11 08:17:18 PM PT</t>
+          <t>2026-07-11 08:19:18 PM PT</t>
         </is>
       </c>
       <c r="C97" t="n">
@@ -11677,10 +11677,10 @@
         <v>1</v>
       </c>
       <c r="I97" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="J97" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="K97" t="inlineStr">
         <is>
@@ -11772,7 +11772,7 @@
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>2026-07-11 08:17:18 PM PT</t>
+          <t>2026-07-11 08:19:17 PM PT</t>
         </is>
       </c>
       <c r="C98" t="n">
@@ -11886,7 +11886,7 @@
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>2026-07-11 08:17:16 PM PT</t>
+          <t>2026-07-11 08:19:16 PM PT</t>
         </is>
       </c>
       <c r="C99" t="n">
@@ -12000,7 +12000,7 @@
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>2026-07-11 08:17:17 PM PT</t>
+          <t>2026-07-11 08:19:16 PM PT</t>
         </is>
       </c>
       <c r="C100" t="n">
@@ -12114,7 +12114,7 @@
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>2026-07-11 08:17:17 PM PT</t>
+          <t>2026-07-11 08:19:17 PM PT</t>
         </is>
       </c>
       <c r="C101" t="n">
@@ -12228,7 +12228,7 @@
       </c>
       <c r="B102" t="inlineStr">
         <is>
-          <t>2026-07-11 08:17:18 PM PT</t>
+          <t>2026-07-11 08:19:18 PM PT</t>
         </is>
       </c>
       <c r="C102" t="n">
@@ -12241,7 +12241,7 @@
       </c>
       <c r="E102" t="inlineStr">
         <is>
-          <t>Bottom 7 | 1 out</t>
+          <t>Bottom 7 | 2 out</t>
         </is>
       </c>
       <c r="F102" t="n">
@@ -12253,13 +12253,13 @@
         </is>
       </c>
       <c r="H102" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I102" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="J102" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="K102" t="inlineStr">
         <is>
@@ -12351,7 +12351,7 @@
       </c>
       <c r="B103" t="inlineStr">
         <is>
-          <t>2026-07-11 08:17:17 PM PT</t>
+          <t>2026-07-11 08:19:17 PM PT</t>
         </is>
       </c>
       <c r="C103" t="n">
@@ -12465,7 +12465,7 @@
       </c>
       <c r="B104" t="inlineStr">
         <is>
-          <t>2026-07-11 08:17:17 PM PT</t>
+          <t>2026-07-11 08:19:17 PM PT</t>
         </is>
       </c>
       <c r="C104" t="n">
@@ -12579,7 +12579,7 @@
       </c>
       <c r="B105" t="inlineStr">
         <is>
-          <t>2026-07-11 08:17:17 PM PT</t>
+          <t>2026-07-11 08:19:17 PM PT</t>
         </is>
       </c>
       <c r="C105" t="n">
@@ -12693,7 +12693,7 @@
       </c>
       <c r="B106" t="inlineStr">
         <is>
-          <t>2026-07-11 08:17:17 PM PT</t>
+          <t>2026-07-11 08:19:17 PM PT</t>
         </is>
       </c>
       <c r="C106" t="n">
@@ -12807,7 +12807,7 @@
       </c>
       <c r="B107" t="inlineStr">
         <is>
-          <t>2026-07-11 08:17:17 PM PT</t>
+          <t>2026-07-11 08:19:17 PM PT</t>
         </is>
       </c>
       <c r="C107" t="n">
@@ -12921,7 +12921,7 @@
       </c>
       <c r="B108" t="inlineStr">
         <is>
-          <t>2026-07-11 08:17:17 PM PT</t>
+          <t>2026-07-11 08:19:17 PM PT</t>
         </is>
       </c>
       <c r="C108" t="n">
@@ -13035,7 +13035,7 @@
       </c>
       <c r="B109" t="inlineStr">
         <is>
-          <t>2026-07-11 08:17:17 PM PT</t>
+          <t>2026-07-11 08:19:17 PM PT</t>
         </is>
       </c>
       <c r="C109" t="n">
@@ -13149,7 +13149,7 @@
       </c>
       <c r="B110" t="inlineStr">
         <is>
-          <t>2026-07-11 08:17:18 PM PT</t>
+          <t>2026-07-11 08:19:17 PM PT</t>
         </is>
       </c>
       <c r="C110" t="n">
@@ -13263,7 +13263,7 @@
       </c>
       <c r="B111" t="inlineStr">
         <is>
-          <t>2026-07-11 08:17:18 PM PT</t>
+          <t>2026-07-11 08:19:17 PM PT</t>
         </is>
       </c>
       <c r="C111" t="n">
@@ -13377,7 +13377,7 @@
       </c>
       <c r="B112" t="inlineStr">
         <is>
-          <t>2026-07-11 08:17:17 PM PT</t>
+          <t>2026-07-11 08:19:17 PM PT</t>
         </is>
       </c>
       <c r="C112" t="n">
@@ -13491,7 +13491,7 @@
       </c>
       <c r="B113" t="inlineStr">
         <is>
-          <t>2026-07-11 08:17:18 PM PT</t>
+          <t>2026-07-11 08:19:17 PM PT</t>
         </is>
       </c>
       <c r="C113" t="n">
@@ -13605,7 +13605,7 @@
       </c>
       <c r="B114" t="inlineStr">
         <is>
-          <t>2026-07-11 08:17:18 PM PT</t>
+          <t>2026-07-11 08:19:18 PM PT</t>
         </is>
       </c>
       <c r="C114" t="n">
@@ -13618,7 +13618,7 @@
       </c>
       <c r="E114" t="inlineStr">
         <is>
-          <t>Bottom 7 | 1 out</t>
+          <t>Bottom 7 | 2 out</t>
         </is>
       </c>
       <c r="F114" t="n">
@@ -13630,13 +13630,13 @@
         </is>
       </c>
       <c r="H114" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I114" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="J114" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="K114" t="inlineStr">
         <is>
@@ -13728,7 +13728,7 @@
       </c>
       <c r="B115" t="inlineStr">
         <is>
-          <t>2026-07-11 08:17:18 PM PT</t>
+          <t>2026-07-11 08:19:17 PM PT</t>
         </is>
       </c>
       <c r="C115" t="n">
@@ -13842,7 +13842,7 @@
       </c>
       <c r="B116" t="inlineStr">
         <is>
-          <t>2026-07-11 08:17:18 PM PT</t>
+          <t>2026-07-11 08:19:18 PM PT</t>
         </is>
       </c>
       <c r="C116" t="n">
@@ -13870,10 +13870,10 @@
         <v>1</v>
       </c>
       <c r="I116" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="J116" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="K116" t="inlineStr">
         <is>
@@ -13965,7 +13965,7 @@
       </c>
       <c r="B117" t="inlineStr">
         <is>
-          <t>2026-07-11 08:17:18 PM PT</t>
+          <t>2026-07-11 08:19:17 PM PT</t>
         </is>
       </c>
       <c r="C117" t="n">
@@ -14079,7 +14079,7 @@
       </c>
       <c r="B118" t="inlineStr">
         <is>
-          <t>2026-07-11 08:17:18 PM PT</t>
+          <t>2026-07-11 08:19:17 PM PT</t>
         </is>
       </c>
       <c r="C118" t="n">
@@ -14193,7 +14193,7 @@
       </c>
       <c r="B119" t="inlineStr">
         <is>
-          <t>2026-07-11 08:17:18 PM PT</t>
+          <t>2026-07-11 08:19:17 PM PT</t>
         </is>
       </c>
       <c r="C119" t="n">
@@ -14307,7 +14307,7 @@
       </c>
       <c r="B120" t="inlineStr">
         <is>
-          <t>2026-07-11 08:17:17 PM PT</t>
+          <t>2026-07-11 08:19:17 PM PT</t>
         </is>
       </c>
       <c r="C120" t="n">
@@ -14421,7 +14421,7 @@
       </c>
       <c r="B121" t="inlineStr">
         <is>
-          <t>2026-07-11 08:17:18 PM PT</t>
+          <t>2026-07-11 08:19:17 PM PT</t>
         </is>
       </c>
       <c r="C121" t="n">
@@ -14535,7 +14535,7 @@
       </c>
       <c r="B122" t="inlineStr">
         <is>
-          <t>2026-07-11 08:17:17 PM PT</t>
+          <t>2026-07-11 08:19:17 PM PT</t>
         </is>
       </c>
       <c r="C122" t="n">
@@ -14649,7 +14649,7 @@
       </c>
       <c r="B123" t="inlineStr">
         <is>
-          <t>2026-07-11 08:17:17 PM PT</t>
+          <t>2026-07-11 08:19:17 PM PT</t>
         </is>
       </c>
       <c r="C123" t="n">
@@ -14763,7 +14763,7 @@
       </c>
       <c r="B124" t="inlineStr">
         <is>
-          <t>2026-07-11 08:17:18 PM PT</t>
+          <t>2026-07-11 08:19:17 PM PT</t>
         </is>
       </c>
       <c r="C124" t="n">
@@ -14877,7 +14877,7 @@
       </c>
       <c r="B125" t="inlineStr">
         <is>
-          <t>2026-07-11 08:17:18 PM PT</t>
+          <t>2026-07-11 08:19:17 PM PT</t>
         </is>
       </c>
       <c r="C125" t="n">
@@ -14991,7 +14991,7 @@
       </c>
       <c r="B126" t="inlineStr">
         <is>
-          <t>2026-07-11 08:17:18 PM PT</t>
+          <t>2026-07-11 08:19:17 PM PT</t>
         </is>
       </c>
       <c r="C126" t="n">
@@ -15105,7 +15105,7 @@
       </c>
       <c r="B127" t="inlineStr">
         <is>
-          <t>2026-07-11 08:17:18 PM PT</t>
+          <t>2026-07-11 08:19:17 PM PT</t>
         </is>
       </c>
       <c r="C127" t="n">
@@ -15219,7 +15219,7 @@
       </c>
       <c r="B128" t="inlineStr">
         <is>
-          <t>2026-07-11 08:17:18 PM PT</t>
+          <t>2026-07-11 08:19:18 PM PT</t>
         </is>
       </c>
       <c r="C128" t="n">
@@ -15247,10 +15247,10 @@
         <v>1</v>
       </c>
       <c r="I128" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="J128" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="K128" t="inlineStr">
         <is>
@@ -15342,7 +15342,7 @@
       </c>
       <c r="B129" t="inlineStr">
         <is>
-          <t>2026-07-11 08:17:18 PM PT</t>
+          <t>2026-07-11 08:19:17 PM PT</t>
         </is>
       </c>
       <c r="C129" t="n">
@@ -15456,7 +15456,7 @@
       </c>
       <c r="B130" t="inlineStr">
         <is>
-          <t>2026-07-11 08:17:18 PM PT</t>
+          <t>2026-07-11 08:19:17 PM PT</t>
         </is>
       </c>
       <c r="C130" t="n">
@@ -15570,7 +15570,7 @@
       </c>
       <c r="B131" t="inlineStr">
         <is>
-          <t>2026-07-11 08:17:16 PM PT</t>
+          <t>2026-07-11 08:19:16 PM PT</t>
         </is>
       </c>
       <c r="C131" t="n">
@@ -15684,7 +15684,7 @@
       </c>
       <c r="B132" t="inlineStr">
         <is>
-          <t>2026-07-11 08:17:17 PM PT</t>
+          <t>2026-07-11 08:19:16 PM PT</t>
         </is>
       </c>
       <c r="C132" t="n">
@@ -15798,7 +15798,7 @@
       </c>
       <c r="B133" t="inlineStr">
         <is>
-          <t>2026-07-11 08:17:17 PM PT</t>
+          <t>2026-07-11 08:19:16 PM PT</t>
         </is>
       </c>
       <c r="C133" t="n">
@@ -15912,7 +15912,7 @@
       </c>
       <c r="B134" t="inlineStr">
         <is>
-          <t>2026-07-11 08:17:17 PM PT</t>
+          <t>2026-07-11 08:19:17 PM PT</t>
         </is>
       </c>
       <c r="C134" t="n">
@@ -16026,7 +16026,7 @@
       </c>
       <c r="B135" t="inlineStr">
         <is>
-          <t>2026-07-11 08:17:16 PM PT</t>
+          <t>2026-07-11 08:19:16 PM PT</t>
         </is>
       </c>
       <c r="C135" t="n">
@@ -16140,7 +16140,7 @@
       </c>
       <c r="B136" t="inlineStr">
         <is>
-          <t>2026-07-11 08:17:16 PM PT</t>
+          <t>2026-07-11 08:19:16 PM PT</t>
         </is>
       </c>
       <c r="C136" t="n">
@@ -16254,7 +16254,7 @@
       </c>
       <c r="B137" t="inlineStr">
         <is>
-          <t>2026-07-11 08:17:17 PM PT</t>
+          <t>2026-07-11 08:19:17 PM PT</t>
         </is>
       </c>
       <c r="C137" t="n">
@@ -16368,7 +16368,7 @@
       </c>
       <c r="B138" t="inlineStr">
         <is>
-          <t>2026-07-11 08:17:17 PM PT</t>
+          <t>2026-07-11 08:19:17 PM PT</t>
         </is>
       </c>
       <c r="C138" t="n">
@@ -16482,7 +16482,7 @@
       </c>
       <c r="B139" t="inlineStr">
         <is>
-          <t>2026-07-11 08:17:17 PM PT</t>
+          <t>2026-07-11 08:19:17 PM PT</t>
         </is>
       </c>
       <c r="C139" t="n">
@@ -16596,7 +16596,7 @@
       </c>
       <c r="B140" t="inlineStr">
         <is>
-          <t>2026-07-11 08:17:18 PM PT</t>
+          <t>2026-07-11 08:19:17 PM PT</t>
         </is>
       </c>
       <c r="C140" t="n">
@@ -16710,7 +16710,7 @@
       </c>
       <c r="B141" t="inlineStr">
         <is>
-          <t>2026-07-11 08:17:18 PM PT</t>
+          <t>2026-07-11 08:19:17 PM PT</t>
         </is>
       </c>
       <c r="C141" t="n">
@@ -16824,7 +16824,7 @@
       </c>
       <c r="B142" t="inlineStr">
         <is>
-          <t>2026-07-11 08:17:18 PM PT</t>
+          <t>2026-07-11 08:19:17 PM PT</t>
         </is>
       </c>
       <c r="C142" t="n">
@@ -16938,7 +16938,7 @@
       </c>
       <c r="B143" t="inlineStr">
         <is>
-          <t>2026-07-11 08:17:17 PM PT</t>
+          <t>2026-07-11 08:19:17 PM PT</t>
         </is>
       </c>
       <c r="C143" t="n">
@@ -17052,7 +17052,7 @@
       </c>
       <c r="B144" t="inlineStr">
         <is>
-          <t>2026-07-11 08:17:18 PM PT</t>
+          <t>2026-07-11 08:19:17 PM PT</t>
         </is>
       </c>
       <c r="C144" t="n">
@@ -17166,7 +17166,7 @@
       </c>
       <c r="B145" t="inlineStr">
         <is>
-          <t>2026-07-11 08:17:18 PM PT</t>
+          <t>2026-07-11 08:19:17 PM PT</t>
         </is>
       </c>
       <c r="C145" t="n">
@@ -17280,7 +17280,7 @@
       </c>
       <c r="B146" t="inlineStr">
         <is>
-          <t>2026-07-11 08:17:18 PM PT</t>
+          <t>2026-07-11 08:19:18 PM PT</t>
         </is>
       </c>
       <c r="C146" t="n">
@@ -17308,10 +17308,10 @@
         <v>1</v>
       </c>
       <c r="I146" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="J146" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="K146" t="inlineStr">
         <is>
@@ -17403,7 +17403,7 @@
       </c>
       <c r="B147" t="inlineStr">
         <is>
-          <t>2026-07-11 08:17:18 PM PT</t>
+          <t>2026-07-11 08:19:17 PM PT</t>
         </is>
       </c>
       <c r="C147" t="n">
@@ -17517,7 +17517,7 @@
       </c>
       <c r="B148" t="inlineStr">
         <is>
-          <t>2026-07-11 08:17:18 PM PT</t>
+          <t>2026-07-11 08:19:17 PM PT</t>
         </is>
       </c>
       <c r="C148" t="n">
@@ -17631,7 +17631,7 @@
       </c>
       <c r="B149" t="inlineStr">
         <is>
-          <t>2026-07-11 08:17:17 PM PT</t>
+          <t>2026-07-11 08:19:17 PM PT</t>
         </is>
       </c>
       <c r="C149" t="n">
@@ -17745,7 +17745,7 @@
       </c>
       <c r="B150" t="inlineStr">
         <is>
-          <t>2026-07-11 08:17:16 PM PT</t>
+          <t>2026-07-11 08:19:16 PM PT</t>
         </is>
       </c>
       <c r="C150" t="n">
@@ -17859,7 +17859,7 @@
       </c>
       <c r="B151" t="inlineStr">
         <is>
-          <t>2026-07-11 08:17:16 PM PT</t>
+          <t>2026-07-11 08:19:16 PM PT</t>
         </is>
       </c>
       <c r="C151" t="n">
@@ -17973,7 +17973,7 @@
       </c>
       <c r="B152" t="inlineStr">
         <is>
-          <t>2026-07-11 08:17:17 PM PT</t>
+          <t>2026-07-11 08:19:16 PM PT</t>
         </is>
       </c>
       <c r="C152" t="n">
@@ -18087,7 +18087,7 @@
       </c>
       <c r="B153" t="inlineStr">
         <is>
-          <t>2026-07-11 08:17:18 PM PT</t>
+          <t>2026-07-11 08:19:17 PM PT</t>
         </is>
       </c>
       <c r="C153" t="n">
@@ -18201,7 +18201,7 @@
       </c>
       <c r="B154" t="inlineStr">
         <is>
-          <t>2026-07-11 08:17:18 PM PT</t>
+          <t>2026-07-11 08:19:17 PM PT</t>
         </is>
       </c>
       <c r="C154" t="n">
@@ -18315,7 +18315,7 @@
       </c>
       <c r="B155" t="inlineStr">
         <is>
-          <t>2026-07-11 08:17:16 PM PT</t>
+          <t>2026-07-11 08:19:16 PM PT</t>
         </is>
       </c>
       <c r="C155" t="n">
@@ -18429,7 +18429,7 @@
       </c>
       <c r="B156" t="inlineStr">
         <is>
-          <t>2026-07-11 08:17:18 PM PT</t>
+          <t>2026-07-11 08:19:18 PM PT</t>
         </is>
       </c>
       <c r="C156" t="n">
@@ -18442,7 +18442,7 @@
       </c>
       <c r="E156" t="inlineStr">
         <is>
-          <t>Bottom 7 | 1 out</t>
+          <t>Bottom 7 | 2 out</t>
         </is>
       </c>
       <c r="F156" t="n">
@@ -18454,13 +18454,13 @@
         </is>
       </c>
       <c r="H156" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I156" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="J156" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="K156" t="inlineStr">
         <is>
@@ -18552,7 +18552,7 @@
       </c>
       <c r="B157" t="inlineStr">
         <is>
-          <t>2026-07-11 08:17:18 PM PT</t>
+          <t>2026-07-11 08:19:18 PM PT</t>
         </is>
       </c>
       <c r="C157" t="n">
@@ -18565,7 +18565,7 @@
       </c>
       <c r="E157" t="inlineStr">
         <is>
-          <t>Bottom 7 | 1 out</t>
+          <t>Bottom 7 | 2 out</t>
         </is>
       </c>
       <c r="F157" t="n">
@@ -18577,13 +18577,13 @@
         </is>
       </c>
       <c r="H157" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I157" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="J157" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="K157" t="inlineStr">
         <is>
@@ -18675,7 +18675,7 @@
       </c>
       <c r="B158" t="inlineStr">
         <is>
-          <t>2026-07-11 08:17:18 PM PT</t>
+          <t>2026-07-11 08:19:18 PM PT</t>
         </is>
       </c>
       <c r="C158" t="n">
@@ -18688,7 +18688,7 @@
       </c>
       <c r="E158" t="inlineStr">
         <is>
-          <t>Bottom 7 | 1 out</t>
+          <t>Bottom 7 | 2 out</t>
         </is>
       </c>
       <c r="F158" t="n">
@@ -18700,13 +18700,13 @@
         </is>
       </c>
       <c r="H158" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I158" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="J158" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="K158" t="inlineStr">
         <is>
@@ -18798,7 +18798,7 @@
       </c>
       <c r="B159" t="inlineStr">
         <is>
-          <t>2026-07-11 08:17:18 PM PT</t>
+          <t>2026-07-11 08:19:18 PM PT</t>
         </is>
       </c>
       <c r="C159" t="n">
@@ -18811,7 +18811,7 @@
       </c>
       <c r="E159" t="inlineStr">
         <is>
-          <t>Bottom 7 | 1 out</t>
+          <t>Bottom 7 | 2 out</t>
         </is>
       </c>
       <c r="F159" t="n">
@@ -18823,13 +18823,13 @@
         </is>
       </c>
       <c r="H159" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I159" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="J159" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="K159" t="inlineStr">
         <is>
@@ -18921,7 +18921,7 @@
       </c>
       <c r="B160" t="inlineStr">
         <is>
-          <t>2026-07-11 08:17:18 PM PT</t>
+          <t>2026-07-11 08:19:17 PM PT</t>
         </is>
       </c>
       <c r="C160" t="n">
@@ -19035,7 +19035,7 @@
       </c>
       <c r="B161" t="inlineStr">
         <is>
-          <t>2026-07-11 08:17:18 PM PT</t>
+          <t>2026-07-11 08:19:17 PM PT</t>
         </is>
       </c>
       <c r="C161" t="n">
@@ -19149,7 +19149,7 @@
       </c>
       <c r="B162" t="inlineStr">
         <is>
-          <t>2026-07-11 08:17:18 PM PT</t>
+          <t>2026-07-11 08:19:17 PM PT</t>
         </is>
       </c>
       <c r="C162" t="n">
@@ -19263,7 +19263,7 @@
       </c>
       <c r="B163" t="inlineStr">
         <is>
-          <t>2026-07-11 08:17:18 PM PT</t>
+          <t>2026-07-11 08:19:17 PM PT</t>
         </is>
       </c>
       <c r="C163" t="n">
@@ -19377,7 +19377,7 @@
       </c>
       <c r="B164" t="inlineStr">
         <is>
-          <t>2026-07-11 08:17:18 PM PT</t>
+          <t>2026-07-11 08:19:17 PM PT</t>
         </is>
       </c>
       <c r="C164" t="n">
@@ -19491,7 +19491,7 @@
       </c>
       <c r="B165" t="inlineStr">
         <is>
-          <t>2026-07-11 08:17:18 PM PT</t>
+          <t>2026-07-11 08:19:17 PM PT</t>
         </is>
       </c>
       <c r="C165" t="n">
@@ -19605,7 +19605,7 @@
       </c>
       <c r="B166" t="inlineStr">
         <is>
-          <t>2026-07-11 08:17:17 PM PT</t>
+          <t>2026-07-11 08:19:17 PM PT</t>
         </is>
       </c>
       <c r="C166" t="n">
@@ -19719,7 +19719,7 @@
       </c>
       <c r="B167" t="inlineStr">
         <is>
-          <t>2026-07-11 08:17:18 PM PT</t>
+          <t>2026-07-11 08:19:17 PM PT</t>
         </is>
       </c>
       <c r="C167" t="n">
@@ -19833,7 +19833,7 @@
       </c>
       <c r="B168" t="inlineStr">
         <is>
-          <t>2026-07-11 08:17:18 PM PT</t>
+          <t>2026-07-11 08:19:17 PM PT</t>
         </is>
       </c>
       <c r="C168" t="n">
@@ -19947,7 +19947,7 @@
       </c>
       <c r="B169" t="inlineStr">
         <is>
-          <t>2026-07-11 08:17:18 PM PT</t>
+          <t>2026-07-11 08:19:17 PM PT</t>
         </is>
       </c>
       <c r="C169" t="n">
@@ -20061,7 +20061,7 @@
       </c>
       <c r="B170" t="inlineStr">
         <is>
-          <t>2026-07-11 08:17:17 PM PT</t>
+          <t>2026-07-11 08:19:16 PM PT</t>
         </is>
       </c>
       <c r="C170" t="n">
@@ -20175,7 +20175,7 @@
       </c>
       <c r="B171" t="inlineStr">
         <is>
-          <t>2026-07-11 08:17:18 PM PT</t>
+          <t>2026-07-11 08:19:18 PM PT</t>
         </is>
       </c>
       <c r="C171" t="n">
@@ -20203,10 +20203,10 @@
         <v>1</v>
       </c>
       <c r="I171" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="J171" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="K171" t="inlineStr">
         <is>
@@ -20298,7 +20298,7 @@
       </c>
       <c r="B172" t="inlineStr">
         <is>
-          <t>2026-07-11 08:17:18 PM PT</t>
+          <t>2026-07-11 08:19:18 PM PT</t>
         </is>
       </c>
       <c r="C172" t="n">
@@ -20326,10 +20326,10 @@
         <v>1</v>
       </c>
       <c r="I172" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="J172" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="K172" t="inlineStr">
         <is>
@@ -20421,7 +20421,7 @@
       </c>
       <c r="B173" t="inlineStr">
         <is>
-          <t>2026-07-11 08:17:18 PM PT</t>
+          <t>2026-07-11 08:19:17 PM PT</t>
         </is>
       </c>
       <c r="C173" t="n">
@@ -20535,7 +20535,7 @@
       </c>
       <c r="B174" t="inlineStr">
         <is>
-          <t>2026-07-11 08:17:18 PM PT</t>
+          <t>2026-07-11 08:19:17 PM PT</t>
         </is>
       </c>
       <c r="C174" t="n">
@@ -20649,7 +20649,7 @@
       </c>
       <c r="B175" t="inlineStr">
         <is>
-          <t>2026-07-11 08:17:16 PM PT</t>
+          <t>2026-07-11 08:19:16 PM PT</t>
         </is>
       </c>
       <c r="C175" t="n">
@@ -20763,7 +20763,7 @@
       </c>
       <c r="B176" t="inlineStr">
         <is>
-          <t>2026-07-11 08:17:16 PM PT</t>
+          <t>2026-07-11 08:19:16 PM PT</t>
         </is>
       </c>
       <c r="C176" t="n">
@@ -20877,7 +20877,7 @@
       </c>
       <c r="B177" t="inlineStr">
         <is>
-          <t>2026-07-11 08:17:17 PM PT</t>
+          <t>2026-07-11 08:19:16 PM PT</t>
         </is>
       </c>
       <c r="C177" t="n">
@@ -20991,7 +20991,7 @@
       </c>
       <c r="B178" t="inlineStr">
         <is>
-          <t>2026-07-11 08:17:17 PM PT</t>
+          <t>2026-07-11 08:19:16 PM PT</t>
         </is>
       </c>
       <c r="C178" t="n">
@@ -21105,7 +21105,7 @@
       </c>
       <c r="B179" t="inlineStr">
         <is>
-          <t>2026-07-11 08:17:17 PM PT</t>
+          <t>2026-07-11 08:19:16 PM PT</t>
         </is>
       </c>
       <c r="C179" t="n">
@@ -21219,7 +21219,7 @@
       </c>
       <c r="B180" t="inlineStr">
         <is>
-          <t>2026-07-11 08:17:17 PM PT</t>
+          <t>2026-07-11 08:19:17 PM PT</t>
         </is>
       </c>
       <c r="C180" t="n">
@@ -21333,7 +21333,7 @@
       </c>
       <c r="B181" t="inlineStr">
         <is>
-          <t>2026-07-11 08:17:17 PM PT</t>
+          <t>2026-07-11 08:19:17 PM PT</t>
         </is>
       </c>
       <c r="C181" t="n">
@@ -21447,7 +21447,7 @@
       </c>
       <c r="B182" t="inlineStr">
         <is>
-          <t>2026-07-11 08:17:17 PM PT</t>
+          <t>2026-07-11 08:19:17 PM PT</t>
         </is>
       </c>
       <c r="C182" t="n">
@@ -21561,7 +21561,7 @@
       </c>
       <c r="B183" t="inlineStr">
         <is>
-          <t>2026-07-11 08:17:18 PM PT</t>
+          <t>2026-07-11 08:19:17 PM PT</t>
         </is>
       </c>
       <c r="C183" t="n">
@@ -21675,7 +21675,7 @@
       </c>
       <c r="B184" t="inlineStr">
         <is>
-          <t>2026-07-11 08:17:16 PM PT</t>
+          <t>2026-07-11 08:19:16 PM PT</t>
         </is>
       </c>
       <c r="C184" t="n">
@@ -21789,7 +21789,7 @@
       </c>
       <c r="B185" t="inlineStr">
         <is>
-          <t>2026-07-11 08:17:16 PM PT</t>
+          <t>2026-07-11 08:19:16 PM PT</t>
         </is>
       </c>
       <c r="C185" t="n">
@@ -21903,7 +21903,7 @@
       </c>
       <c r="B186" t="inlineStr">
         <is>
-          <t>2026-07-11 08:17:17 PM PT</t>
+          <t>2026-07-11 08:19:17 PM PT</t>
         </is>
       </c>
       <c r="C186" t="n">
@@ -22017,7 +22017,7 @@
       </c>
       <c r="B187" t="inlineStr">
         <is>
-          <t>2026-07-11 08:17:17 PM PT</t>
+          <t>2026-07-11 08:19:17 PM PT</t>
         </is>
       </c>
       <c r="C187" t="n">
@@ -22131,7 +22131,7 @@
       </c>
       <c r="B188" t="inlineStr">
         <is>
-          <t>2026-07-11 08:17:17 PM PT</t>
+          <t>2026-07-11 08:19:17 PM PT</t>
         </is>
       </c>
       <c r="C188" t="n">
@@ -22245,7 +22245,7 @@
       </c>
       <c r="B189" t="inlineStr">
         <is>
-          <t>2026-07-11 08:17:18 PM PT</t>
+          <t>2026-07-11 08:19:17 PM PT</t>
         </is>
       </c>
       <c r="C189" t="n">
@@ -22359,7 +22359,7 @@
       </c>
       <c r="B190" t="inlineStr">
         <is>
-          <t>2026-07-11 08:17:17 PM PT</t>
+          <t>2026-07-11 08:19:17 PM PT</t>
         </is>
       </c>
       <c r="C190" t="n">
@@ -22473,7 +22473,7 @@
       </c>
       <c r="B191" t="inlineStr">
         <is>
-          <t>2026-07-11 08:17:17 PM PT</t>
+          <t>2026-07-11 08:19:17 PM PT</t>
         </is>
       </c>
       <c r="C191" t="n">
@@ -22587,7 +22587,7 @@
       </c>
       <c r="B192" t="inlineStr">
         <is>
-          <t>2026-07-11 08:17:18 PM PT</t>
+          <t>2026-07-11 08:19:18 PM PT</t>
         </is>
       </c>
       <c r="C192" t="n">
@@ -22615,49 +22615,49 @@
         <v>1</v>
       </c>
       <c r="I192" t="n">
+        <v>0</v>
+      </c>
+      <c r="J192" t="n">
+        <v>0</v>
+      </c>
+      <c r="K192" t="inlineStr">
+        <is>
+          <t>Away</t>
+        </is>
+      </c>
+      <c r="L192" t="inlineStr">
+        <is>
+          <t>ARI</t>
+        </is>
+      </c>
+      <c r="M192" t="inlineStr">
+        <is>
+          <t>LAD</t>
+        </is>
+      </c>
+      <c r="N192" t="inlineStr">
+        <is>
+          <t>Corbin Carroll</t>
+        </is>
+      </c>
+      <c r="O192" t="n">
+        <v>682998</v>
+      </c>
+      <c r="P192" t="inlineStr">
+        <is>
+          <t>RF</t>
+        </is>
+      </c>
+      <c r="Q192" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="R192" t="n">
+        <v>4</v>
+      </c>
+      <c r="S192" t="n">
         <v>3</v>
-      </c>
-      <c r="J192" t="n">
-        <v>2</v>
-      </c>
-      <c r="K192" t="inlineStr">
-        <is>
-          <t>Away</t>
-        </is>
-      </c>
-      <c r="L192" t="inlineStr">
-        <is>
-          <t>ARI</t>
-        </is>
-      </c>
-      <c r="M192" t="inlineStr">
-        <is>
-          <t>LAD</t>
-        </is>
-      </c>
-      <c r="N192" t="inlineStr">
-        <is>
-          <t>Tommy Troy</t>
-        </is>
-      </c>
-      <c r="O192" t="n">
-        <v>694371</v>
-      </c>
-      <c r="P192" t="inlineStr">
-        <is>
-          <t>CF</t>
-        </is>
-      </c>
-      <c r="Q192" t="inlineStr">
-        <is>
-          <t>9</t>
-        </is>
-      </c>
-      <c r="R192" t="n">
-        <v>2</v>
-      </c>
-      <c r="S192" t="n">
-        <v>1</v>
       </c>
       <c r="T192" t="n">
         <v>0</v>
@@ -22710,30 +22710,39 @@
       </c>
       <c r="B193" t="inlineStr">
         <is>
-          <t>2026-07-11 08:17:17 PM PT</t>
+          <t>2026-07-11 08:19:18 PM PT</t>
         </is>
       </c>
       <c r="C193" t="n">
-        <v>824576</v>
+        <v>823926</v>
       </c>
       <c r="D193" t="inlineStr">
         <is>
-          <t>11:10 AM PT</t>
+          <t>6:10 PM PT</t>
         </is>
       </c>
       <c r="E193" t="inlineStr">
         <is>
-          <t>Final</t>
+          <t>Top 7 | 1 out</t>
         </is>
       </c>
       <c r="F193" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="G193" t="inlineStr">
         <is>
           <t>Top</t>
         </is>
       </c>
+      <c r="H193" t="n">
+        <v>1</v>
+      </c>
+      <c r="I193" t="n">
+        <v>0</v>
+      </c>
+      <c r="J193" t="n">
+        <v>0</v>
+      </c>
       <c r="K193" t="inlineStr">
         <is>
           <t>Away</t>
@@ -22741,37 +22750,37 @@
       </c>
       <c r="L193" t="inlineStr">
         <is>
-          <t>ATH</t>
+          <t>ARI</t>
         </is>
       </c>
       <c r="M193" t="inlineStr">
         <is>
-          <t>CWS</t>
+          <t>LAD</t>
         </is>
       </c>
       <c r="N193" t="inlineStr">
         <is>
-          <t>Tyler Soderstrom</t>
+          <t>Tommy Troy</t>
         </is>
       </c>
       <c r="O193" t="n">
-        <v>691016</v>
+        <v>694371</v>
       </c>
       <c r="P193" t="inlineStr">
         <is>
-          <t>DH</t>
+          <t>CF</t>
         </is>
       </c>
       <c r="Q193" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>9</t>
         </is>
       </c>
       <c r="R193" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="S193" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="T193" t="n">
         <v>0</v>
@@ -22804,16 +22813,16 @@
         <v>0</v>
       </c>
       <c r="AD193" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AE193" s="4" t="n">
         <v>2</v>
       </c>
       <c r="AF193" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="AG193" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
     </row>
     <row r="194">
@@ -22824,15 +22833,15 @@
       </c>
       <c r="B194" t="inlineStr">
         <is>
-          <t>2026-07-11 08:17:18 PM PT</t>
+          <t>2026-07-11 08:19:17 PM PT</t>
         </is>
       </c>
       <c r="C194" t="n">
-        <v>823030</v>
+        <v>824576</v>
       </c>
       <c r="D194" t="inlineStr">
         <is>
-          <t>4:15 PM PT</t>
+          <t>11:10 AM PT</t>
         </is>
       </c>
       <c r="E194" t="inlineStr">
@@ -22855,25 +22864,25 @@
       </c>
       <c r="L194" t="inlineStr">
         <is>
-          <t>ATL</t>
+          <t>ATH</t>
         </is>
       </c>
       <c r="M194" t="inlineStr">
         <is>
-          <t>STL</t>
+          <t>CWS</t>
         </is>
       </c>
       <c r="N194" t="inlineStr">
         <is>
-          <t>Ozzie Albies</t>
+          <t>Tyler Soderstrom</t>
         </is>
       </c>
       <c r="O194" t="n">
-        <v>645277</v>
+        <v>691016</v>
       </c>
       <c r="P194" t="inlineStr">
         <is>
-          <t>2B</t>
+          <t>DH</t>
         </is>
       </c>
       <c r="Q194" t="inlineStr">
@@ -22918,16 +22927,16 @@
         <v>0</v>
       </c>
       <c r="AD194" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AE194" s="4" t="n">
         <v>2</v>
       </c>
       <c r="AF194" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AG194" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
     </row>
     <row r="195">
@@ -22938,7 +22947,7 @@
       </c>
       <c r="B195" t="inlineStr">
         <is>
-          <t>2026-07-11 08:17:18 PM PT</t>
+          <t>2026-07-11 08:19:17 PM PT</t>
         </is>
       </c>
       <c r="C195" t="n">
@@ -22979,27 +22988,27 @@
       </c>
       <c r="N195" t="inlineStr">
         <is>
-          <t>Dominic Smith</t>
+          <t>Ozzie Albies</t>
         </is>
       </c>
       <c r="O195" t="n">
-        <v>642086</v>
+        <v>645277</v>
       </c>
       <c r="P195" t="inlineStr">
         <is>
-          <t>PH</t>
+          <t>2B</t>
         </is>
       </c>
       <c r="Q195" t="inlineStr">
         <is>
-          <t>7 (Sub)</t>
+          <t>2</t>
         </is>
       </c>
       <c r="R195" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="S195" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="T195" t="n">
         <v>0</v>
@@ -23022,17 +23031,17 @@
       <c r="Z195" t="n">
         <v>0</v>
       </c>
-      <c r="AA195" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB195" s="9" t="n">
-        <v>1</v>
+      <c r="AA195" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="AB195" t="n">
+        <v>0</v>
       </c>
       <c r="AC195" t="n">
         <v>0</v>
       </c>
       <c r="AD195" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AE195" s="4" t="n">
         <v>2</v>
@@ -23052,15 +23061,15 @@
       </c>
       <c r="B196" t="inlineStr">
         <is>
-          <t>2026-07-11 08:17:18 PM PT</t>
+          <t>2026-07-11 08:19:17 PM PT</t>
         </is>
       </c>
       <c r="C196" t="n">
-        <v>824813</v>
+        <v>823030</v>
       </c>
       <c r="D196" t="inlineStr">
         <is>
-          <t>4:05 PM PT</t>
+          <t>4:15 PM PT</t>
         </is>
       </c>
       <c r="E196" t="inlineStr">
@@ -23078,42 +23087,42 @@
       </c>
       <c r="K196" t="inlineStr">
         <is>
-          <t>Home</t>
+          <t>Away</t>
         </is>
       </c>
       <c r="L196" t="inlineStr">
         <is>
-          <t>BAL</t>
+          <t>ATL</t>
         </is>
       </c>
       <c r="M196" t="inlineStr">
         <is>
-          <t>KC</t>
+          <t>STL</t>
         </is>
       </c>
       <c r="N196" t="inlineStr">
         <is>
-          <t>Jackson Holliday</t>
+          <t>Dominic Smith</t>
         </is>
       </c>
       <c r="O196" t="n">
-        <v>702616</v>
+        <v>642086</v>
       </c>
       <c r="P196" t="inlineStr">
         <is>
-          <t>2B</t>
+          <t>PH</t>
         </is>
       </c>
       <c r="Q196" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>7 (Sub)</t>
         </is>
       </c>
       <c r="R196" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="S196" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="T196" t="n">
         <v>0</v>
@@ -23136,23 +23145,23 @@
       <c r="Z196" t="n">
         <v>0</v>
       </c>
-      <c r="AA196" s="5" t="n">
-        <v>1</v>
-      </c>
-      <c r="AB196" t="n">
-        <v>0</v>
+      <c r="AA196" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB196" s="9" t="n">
+        <v>1</v>
       </c>
       <c r="AC196" t="n">
         <v>0</v>
       </c>
       <c r="AD196" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AE196" s="4" t="n">
         <v>2</v>
       </c>
       <c r="AF196" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="AG196" t="n">
         <v>6</v>
@@ -23166,15 +23175,15 @@
       </c>
       <c r="B197" t="inlineStr">
         <is>
-          <t>2026-07-11 08:17:17 PM PT</t>
+          <t>2026-07-11 08:19:17 PM PT</t>
         </is>
       </c>
       <c r="C197" t="n">
-        <v>823603</v>
+        <v>824813</v>
       </c>
       <c r="D197" t="inlineStr">
         <is>
-          <t>1:10 PM PT</t>
+          <t>4:05 PM PT</t>
         </is>
       </c>
       <c r="E197" t="inlineStr">
@@ -23187,47 +23196,47 @@
       </c>
       <c r="G197" t="inlineStr">
         <is>
-          <t>Bottom</t>
+          <t>Top</t>
         </is>
       </c>
       <c r="K197" t="inlineStr">
         <is>
-          <t>Away</t>
+          <t>Home</t>
         </is>
       </c>
       <c r="L197" t="inlineStr">
         <is>
-          <t>BOS</t>
+          <t>BAL</t>
         </is>
       </c>
       <c r="M197" t="inlineStr">
         <is>
-          <t>NYM</t>
+          <t>KC</t>
         </is>
       </c>
       <c r="N197" t="inlineStr">
         <is>
-          <t>Wilyer Abreu</t>
+          <t>Jackson Holliday</t>
         </is>
       </c>
       <c r="O197" t="n">
-        <v>677800</v>
+        <v>702616</v>
       </c>
       <c r="P197" t="inlineStr">
         <is>
-          <t>RF</t>
+          <t>2B</t>
         </is>
       </c>
       <c r="Q197" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>8</t>
         </is>
       </c>
       <c r="R197" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="S197" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="T197" t="n">
         <v>0</v>
@@ -23266,7 +23275,7 @@
         <v>2</v>
       </c>
       <c r="AF197" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="AG197" t="n">
         <v>6</v>
@@ -23280,7 +23289,7 @@
       </c>
       <c r="B198" t="inlineStr">
         <is>
-          <t>2026-07-11 08:17:17 PM PT</t>
+          <t>2026-07-11 08:19:17 PM PT</t>
         </is>
       </c>
       <c r="C198" t="n">
@@ -23321,20 +23330,20 @@
       </c>
       <c r="N198" t="inlineStr">
         <is>
-          <t>Carlos Narváez</t>
+          <t>Wilyer Abreu</t>
         </is>
       </c>
       <c r="O198" t="n">
-        <v>665966</v>
+        <v>677800</v>
       </c>
       <c r="P198" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>RF</t>
         </is>
       </c>
       <c r="Q198" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>3</t>
         </is>
       </c>
       <c r="R198" t="n">
@@ -23394,7 +23403,7 @@
       </c>
       <c r="B199" t="inlineStr">
         <is>
-          <t>2026-07-11 08:17:17 PM PT</t>
+          <t>2026-07-11 08:19:17 PM PT</t>
         </is>
       </c>
       <c r="C199" t="n">
@@ -23435,27 +23444,27 @@
       </c>
       <c r="N199" t="inlineStr">
         <is>
-          <t>Tsung-Che Cheng</t>
+          <t>Carlos Narváez</t>
         </is>
       </c>
       <c r="O199" t="n">
-        <v>691907</v>
+        <v>665966</v>
       </c>
       <c r="P199" t="inlineStr">
         <is>
-          <t>SS</t>
+          <t>C</t>
         </is>
       </c>
       <c r="Q199" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>8</t>
         </is>
       </c>
       <c r="R199" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="S199" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="T199" t="n">
         <v>0</v>
@@ -23508,15 +23517,15 @@
       </c>
       <c r="B200" t="inlineStr">
         <is>
-          <t>2026-07-11 08:17:18 PM PT</t>
+          <t>2026-07-11 08:19:17 PM PT</t>
         </is>
       </c>
       <c r="C200" t="n">
-        <v>824492</v>
+        <v>823603</v>
       </c>
       <c r="D200" t="inlineStr">
         <is>
-          <t>4:10 PM PT</t>
+          <t>1:10 PM PT</t>
         </is>
       </c>
       <c r="E200" t="inlineStr">
@@ -23534,42 +23543,42 @@
       </c>
       <c r="K200" t="inlineStr">
         <is>
-          <t>Home</t>
+          <t>Away</t>
         </is>
       </c>
       <c r="L200" t="inlineStr">
         <is>
-          <t>CIN</t>
+          <t>BOS</t>
         </is>
       </c>
       <c r="M200" t="inlineStr">
         <is>
-          <t>CHC</t>
+          <t>NYM</t>
         </is>
       </c>
       <c r="N200" t="inlineStr">
         <is>
-          <t>Spencer Steer</t>
+          <t>Tsung-Che Cheng</t>
         </is>
       </c>
       <c r="O200" t="n">
-        <v>668715</v>
+        <v>691907</v>
       </c>
       <c r="P200" t="inlineStr">
         <is>
-          <t>RF</t>
+          <t>SS</t>
         </is>
       </c>
       <c r="Q200" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>9</t>
         </is>
       </c>
       <c r="R200" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="S200" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="T200" t="n">
         <v>0</v>
@@ -23608,10 +23617,10 @@
         <v>2</v>
       </c>
       <c r="AF200" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="AG200" t="n">
-        <v>11</v>
+        <v>6</v>
       </c>
     </row>
     <row r="201">
@@ -23622,15 +23631,15 @@
       </c>
       <c r="B201" t="inlineStr">
         <is>
-          <t>2026-07-11 08:17:17 PM PT</t>
+          <t>2026-07-11 08:19:17 PM PT</t>
         </is>
       </c>
       <c r="C201" t="n">
-        <v>823198</v>
+        <v>824492</v>
       </c>
       <c r="D201" t="inlineStr">
         <is>
-          <t>1:05 PM PT</t>
+          <t>4:10 PM PT</t>
         </is>
       </c>
       <c r="E201" t="inlineStr">
@@ -23643,35 +23652,35 @@
       </c>
       <c r="G201" t="inlineStr">
         <is>
-          <t>Top</t>
+          <t>Bottom</t>
         </is>
       </c>
       <c r="K201" t="inlineStr">
         <is>
-          <t>Away</t>
+          <t>Home</t>
         </is>
       </c>
       <c r="L201" t="inlineStr">
         <is>
-          <t>COL</t>
+          <t>CIN</t>
         </is>
       </c>
       <c r="M201" t="inlineStr">
         <is>
-          <t>SF</t>
+          <t>CHC</t>
         </is>
       </c>
       <c r="N201" t="inlineStr">
         <is>
-          <t>TJ Rumfield</t>
+          <t>Spencer Steer</t>
         </is>
       </c>
       <c r="O201" t="n">
-        <v>681198</v>
+        <v>668715</v>
       </c>
       <c r="P201" t="inlineStr">
         <is>
-          <t>1B</t>
+          <t>RF</t>
         </is>
       </c>
       <c r="Q201" t="inlineStr">
@@ -23716,16 +23725,16 @@
         <v>0</v>
       </c>
       <c r="AD201" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AE201" s="4" t="n">
         <v>2</v>
       </c>
       <c r="AF201" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AG201" t="n">
-        <v>6</v>
+        <v>11</v>
       </c>
     </row>
     <row r="202">
@@ -23736,7 +23745,7 @@
       </c>
       <c r="B202" t="inlineStr">
         <is>
-          <t>2026-07-11 08:17:17 PM PT</t>
+          <t>2026-07-11 08:19:17 PM PT</t>
         </is>
       </c>
       <c r="C202" t="n">
@@ -23777,20 +23786,20 @@
       </c>
       <c r="N202" t="inlineStr">
         <is>
-          <t>Troy Johnston</t>
+          <t>TJ Rumfield</t>
         </is>
       </c>
       <c r="O202" t="n">
-        <v>687859</v>
+        <v>681198</v>
       </c>
       <c r="P202" t="inlineStr">
         <is>
-          <t>RF</t>
+          <t>1B</t>
         </is>
       </c>
       <c r="Q202" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>4</t>
         </is>
       </c>
       <c r="R202" t="n">
@@ -23850,7 +23859,7 @@
       </c>
       <c r="B203" t="inlineStr">
         <is>
-          <t>2026-07-11 08:17:17 PM PT</t>
+          <t>2026-07-11 08:19:17 PM PT</t>
         </is>
       </c>
       <c r="C203" t="n">
@@ -23891,27 +23900,27 @@
       </c>
       <c r="N203" t="inlineStr">
         <is>
-          <t>Ezequiel Tovar</t>
+          <t>Troy Johnston</t>
         </is>
       </c>
       <c r="O203" t="n">
-        <v>678662</v>
+        <v>687859</v>
       </c>
       <c r="P203" t="inlineStr">
         <is>
-          <t>SS</t>
+          <t>RF</t>
         </is>
       </c>
       <c r="Q203" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>6</t>
         </is>
       </c>
       <c r="R203" t="n">
+        <v>4</v>
+      </c>
+      <c r="S203" t="n">
         <v>3</v>
-      </c>
-      <c r="S203" t="n">
-        <v>2</v>
       </c>
       <c r="T203" t="n">
         <v>0</v>
@@ -23964,15 +23973,15 @@
       </c>
       <c r="B204" t="inlineStr">
         <is>
-          <t>2026-07-11 08:17:17 PM PT</t>
+          <t>2026-07-11 08:19:17 PM PT</t>
         </is>
       </c>
       <c r="C204" t="n">
-        <v>824576</v>
+        <v>823198</v>
       </c>
       <c r="D204" t="inlineStr">
         <is>
-          <t>11:10 AM PT</t>
+          <t>1:05 PM PT</t>
         </is>
       </c>
       <c r="E204" t="inlineStr">
@@ -23990,42 +23999,42 @@
       </c>
       <c r="K204" t="inlineStr">
         <is>
-          <t>Home</t>
+          <t>Away</t>
         </is>
       </c>
       <c r="L204" t="inlineStr">
         <is>
-          <t>CWS</t>
+          <t>COL</t>
         </is>
       </c>
       <c r="M204" t="inlineStr">
         <is>
-          <t>ATH</t>
+          <t>SF</t>
         </is>
       </c>
       <c r="N204" t="inlineStr">
         <is>
-          <t>Munetaka Murakami</t>
+          <t>Ezequiel Tovar</t>
         </is>
       </c>
       <c r="O204" t="n">
-        <v>808959</v>
+        <v>678662</v>
       </c>
       <c r="P204" t="inlineStr">
         <is>
-          <t>DH</t>
+          <t>SS</t>
         </is>
       </c>
       <c r="Q204" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>8</t>
         </is>
       </c>
       <c r="R204" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="S204" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="T204" t="n">
         <v>0</v>
@@ -24058,16 +24067,16 @@
         <v>0</v>
       </c>
       <c r="AD204" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AE204" s="4" t="n">
         <v>2</v>
       </c>
       <c r="AF204" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AG204" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="205">
@@ -24078,7 +24087,7 @@
       </c>
       <c r="B205" t="inlineStr">
         <is>
-          <t>2026-07-11 08:17:17 PM PT</t>
+          <t>2026-07-11 08:19:17 PM PT</t>
         </is>
       </c>
       <c r="C205" t="n">
@@ -24119,28 +24128,28 @@
       </c>
       <c r="N205" t="inlineStr">
         <is>
-          <t>Braden Montgomery</t>
+          <t>Munetaka Murakami</t>
         </is>
       </c>
       <c r="O205" t="n">
-        <v>695731</v>
+        <v>808959</v>
       </c>
       <c r="P205" t="inlineStr">
         <is>
-          <t>RF</t>
+          <t>DH</t>
         </is>
       </c>
       <c r="Q205" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>2</t>
         </is>
       </c>
       <c r="R205" t="n">
+        <v>4</v>
+      </c>
+      <c r="S205" t="n">
         <v>3</v>
       </c>
-      <c r="S205" t="n">
-        <v>2</v>
-      </c>
       <c r="T205" t="n">
         <v>0</v>
       </c>
@@ -24162,11 +24171,11 @@
       <c r="Z205" t="n">
         <v>0</v>
       </c>
-      <c r="AA205" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB205" s="9" t="n">
-        <v>1</v>
+      <c r="AA205" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="AB205" t="n">
+        <v>0</v>
       </c>
       <c r="AC205" t="n">
         <v>0</v>
@@ -24192,15 +24201,15 @@
       </c>
       <c r="B206" t="inlineStr">
         <is>
-          <t>2026-07-11 08:17:18 PM PT</t>
+          <t>2026-07-11 08:19:17 PM PT</t>
         </is>
       </c>
       <c r="C206" t="n">
-        <v>824249</v>
+        <v>824576</v>
       </c>
       <c r="D206" t="inlineStr">
         <is>
-          <t>3:10 PM PT</t>
+          <t>11:10 AM PT</t>
         </is>
       </c>
       <c r="E206" t="inlineStr">
@@ -24213,7 +24222,7 @@
       </c>
       <c r="G206" t="inlineStr">
         <is>
-          <t>Bottom</t>
+          <t>Top</t>
         </is>
       </c>
       <c r="K206" t="inlineStr">
@@ -24223,37 +24232,37 @@
       </c>
       <c r="L206" t="inlineStr">
         <is>
-          <t>DET</t>
+          <t>CWS</t>
         </is>
       </c>
       <c r="M206" t="inlineStr">
         <is>
-          <t>PHI</t>
+          <t>ATH</t>
         </is>
       </c>
       <c r="N206" t="inlineStr">
         <is>
-          <t>Riley Greene</t>
+          <t>Braden Montgomery</t>
         </is>
       </c>
       <c r="O206" t="n">
-        <v>682985</v>
+        <v>695731</v>
       </c>
       <c r="P206" t="inlineStr">
         <is>
-          <t>LF</t>
+          <t>RF</t>
         </is>
       </c>
       <c r="Q206" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="R206" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="S206" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="T206" t="n">
         <v>0</v>
@@ -24276,26 +24285,26 @@
       <c r="Z206" t="n">
         <v>0</v>
       </c>
-      <c r="AA206" s="5" t="n">
-        <v>1</v>
-      </c>
-      <c r="AB206" t="n">
-        <v>0</v>
+      <c r="AA206" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB206" s="9" t="n">
+        <v>1</v>
       </c>
       <c r="AC206" t="n">
         <v>0</v>
       </c>
       <c r="AD206" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AE206" s="4" t="n">
         <v>2</v>
       </c>
       <c r="AF206" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AG206" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
     </row>
     <row r="207">
@@ -24306,15 +24315,15 @@
       </c>
       <c r="B207" t="inlineStr">
         <is>
-          <t>2026-07-11 08:17:18 PM PT</t>
+          <t>2026-07-11 08:19:17 PM PT</t>
         </is>
       </c>
       <c r="C207" t="n">
-        <v>822875</v>
+        <v>824249</v>
       </c>
       <c r="D207" t="inlineStr">
         <is>
-          <t>4:05 PM PT</t>
+          <t>3:10 PM PT</t>
         </is>
       </c>
       <c r="E207" t="inlineStr">
@@ -24332,42 +24341,42 @@
       </c>
       <c r="K207" t="inlineStr">
         <is>
-          <t>Away</t>
+          <t>Home</t>
         </is>
       </c>
       <c r="L207" t="inlineStr">
         <is>
-          <t>HOU</t>
+          <t>DET</t>
         </is>
       </c>
       <c r="M207" t="inlineStr">
         <is>
-          <t>TEX</t>
+          <t>PHI</t>
         </is>
       </c>
       <c r="N207" t="inlineStr">
         <is>
-          <t>Cam Smith</t>
+          <t>Riley Greene</t>
         </is>
       </c>
       <c r="O207" t="n">
-        <v>701358</v>
+        <v>682985</v>
       </c>
       <c r="P207" t="inlineStr">
         <is>
-          <t>RF</t>
+          <t>LF</t>
         </is>
       </c>
       <c r="Q207" t="inlineStr">
         <is>
-          <t>5 (Sub)</t>
+          <t>5</t>
         </is>
       </c>
       <c r="R207" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="S207" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="T207" t="n">
         <v>0</v>
@@ -24388,10 +24397,10 @@
         <v>0</v>
       </c>
       <c r="Z207" t="n">
-        <v>1</v>
-      </c>
-      <c r="AA207" t="n">
-        <v>0</v>
+        <v>0</v>
+      </c>
+      <c r="AA207" s="5" t="n">
+        <v>1</v>
       </c>
       <c r="AB207" t="n">
         <v>0</v>
@@ -24400,13 +24409,13 @@
         <v>0</v>
       </c>
       <c r="AD207" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AE207" s="4" t="n">
         <v>2</v>
       </c>
       <c r="AF207" t="n">
-        <v>9</v>
+        <v>2</v>
       </c>
       <c r="AG207" t="n">
         <v>10</v>
@@ -24420,11 +24429,11 @@
       </c>
       <c r="B208" t="inlineStr">
         <is>
-          <t>2026-07-11 08:17:18 PM PT</t>
+          <t>2026-07-11 08:19:17 PM PT</t>
         </is>
       </c>
       <c r="C208" t="n">
-        <v>824813</v>
+        <v>822875</v>
       </c>
       <c r="D208" t="inlineStr">
         <is>
@@ -24441,7 +24450,7 @@
       </c>
       <c r="G208" t="inlineStr">
         <is>
-          <t>Top</t>
+          <t>Bottom</t>
         </is>
       </c>
       <c r="K208" t="inlineStr">
@@ -24451,37 +24460,37 @@
       </c>
       <c r="L208" t="inlineStr">
         <is>
-          <t>KC</t>
+          <t>HOU</t>
         </is>
       </c>
       <c r="M208" t="inlineStr">
         <is>
-          <t>BAL</t>
+          <t>TEX</t>
         </is>
       </c>
       <c r="N208" t="inlineStr">
         <is>
-          <t>Carter Jensen</t>
+          <t>Cam Smith</t>
         </is>
       </c>
       <c r="O208" t="n">
-        <v>695600</v>
+        <v>701358</v>
       </c>
       <c r="P208" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>RF</t>
         </is>
       </c>
       <c r="Q208" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>5 (Sub)</t>
         </is>
       </c>
       <c r="R208" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="S208" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="T208" t="n">
         <v>0</v>
@@ -24502,10 +24511,10 @@
         <v>0</v>
       </c>
       <c r="Z208" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA208" s="5" t="n">
-        <v>1</v>
+        <v>1</v>
+      </c>
+      <c r="AA208" t="n">
+        <v>0</v>
       </c>
       <c r="AB208" t="n">
         <v>0</v>
@@ -24514,16 +24523,16 @@
         <v>0</v>
       </c>
       <c r="AD208" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AE208" s="4" t="n">
         <v>2</v>
       </c>
       <c r="AF208" t="n">
-        <v>1</v>
+        <v>9</v>
       </c>
       <c r="AG208" t="n">
-        <v>2</v>
+        <v>10</v>
       </c>
     </row>
     <row r="209">
@@ -24534,7 +24543,7 @@
       </c>
       <c r="B209" t="inlineStr">
         <is>
-          <t>2026-07-11 08:17:18 PM PT</t>
+          <t>2026-07-11 08:19:17 PM PT</t>
         </is>
       </c>
       <c r="C209" t="n">
@@ -24575,20 +24584,20 @@
       </c>
       <c r="N209" t="inlineStr">
         <is>
-          <t>Vinnie Pasquantino</t>
+          <t>Carter Jensen</t>
         </is>
       </c>
       <c r="O209" t="n">
-        <v>686469</v>
+        <v>695600</v>
       </c>
       <c r="P209" t="inlineStr">
         <is>
-          <t>1B</t>
+          <t>C</t>
         </is>
       </c>
       <c r="Q209" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>1</t>
         </is>
       </c>
       <c r="R209" t="n">
@@ -24628,7 +24637,7 @@
         <v>0</v>
       </c>
       <c r="AD209" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AE209" s="4" t="n">
         <v>2</v>
@@ -24648,7 +24657,7 @@
       </c>
       <c r="B210" t="inlineStr">
         <is>
-          <t>2026-07-11 08:17:18 PM PT</t>
+          <t>2026-07-11 08:19:17 PM PT</t>
         </is>
       </c>
       <c r="C210" t="n">
@@ -24689,28 +24698,28 @@
       </c>
       <c r="N210" t="inlineStr">
         <is>
-          <t>Salvador Perez</t>
+          <t>Vinnie Pasquantino</t>
         </is>
       </c>
       <c r="O210" t="n">
-        <v>521692</v>
+        <v>686469</v>
       </c>
       <c r="P210" t="inlineStr">
         <is>
-          <t>DH</t>
+          <t>1B</t>
         </is>
       </c>
       <c r="Q210" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>5</t>
         </is>
       </c>
       <c r="R210" t="n">
+        <v>4</v>
+      </c>
+      <c r="S210" t="n">
         <v>3</v>
       </c>
-      <c r="S210" t="n">
-        <v>2</v>
-      </c>
       <c r="T210" t="n">
         <v>0</v>
       </c>
@@ -24730,10 +24739,10 @@
         <v>0</v>
       </c>
       <c r="Z210" t="n">
-        <v>1</v>
-      </c>
-      <c r="AA210" t="n">
-        <v>0</v>
+        <v>0</v>
+      </c>
+      <c r="AA210" s="5" t="n">
+        <v>1</v>
       </c>
       <c r="AB210" t="n">
         <v>0</v>
@@ -24742,7 +24751,7 @@
         <v>0</v>
       </c>
       <c r="AD210" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AE210" s="4" t="n">
         <v>2</v>
@@ -24762,15 +24771,15 @@
       </c>
       <c r="B211" t="inlineStr">
         <is>
-          <t>2026-07-11 08:17:17 PM PT</t>
+          <t>2026-07-11 08:19:17 PM PT</t>
         </is>
       </c>
       <c r="C211" t="n">
-        <v>823682</v>
+        <v>824813</v>
       </c>
       <c r="D211" t="inlineStr">
         <is>
-          <t>11:10 AM PT</t>
+          <t>4:05 PM PT</t>
         </is>
       </c>
       <c r="E211" t="inlineStr">
@@ -24793,25 +24802,25 @@
       </c>
       <c r="L211" t="inlineStr">
         <is>
-          <t>LAA</t>
+          <t>KC</t>
         </is>
       </c>
       <c r="M211" t="inlineStr">
         <is>
-          <t>MIN</t>
+          <t>BAL</t>
         </is>
       </c>
       <c r="N211" t="inlineStr">
         <is>
-          <t>Jo Adell</t>
+          <t>Salvador Perez</t>
         </is>
       </c>
       <c r="O211" t="n">
-        <v>666176</v>
+        <v>521692</v>
       </c>
       <c r="P211" t="inlineStr">
         <is>
-          <t>RF</t>
+          <t>DH</t>
         </is>
       </c>
       <c r="Q211" t="inlineStr">
@@ -24820,10 +24829,10 @@
         </is>
       </c>
       <c r="R211" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="S211" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="T211" t="n">
         <v>0</v>
@@ -24844,10 +24853,10 @@
         <v>0</v>
       </c>
       <c r="Z211" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA211" s="5" t="n">
-        <v>1</v>
+        <v>1</v>
+      </c>
+      <c r="AA211" t="n">
+        <v>0</v>
       </c>
       <c r="AB211" t="n">
         <v>0</v>
@@ -24856,16 +24865,16 @@
         <v>0</v>
       </c>
       <c r="AD211" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AE211" s="4" t="n">
         <v>2</v>
       </c>
       <c r="AF211" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="AG211" t="n">
-        <v>10</v>
+        <v>2</v>
       </c>
     </row>
     <row r="212">
@@ -24876,15 +24885,15 @@
       </c>
       <c r="B212" t="inlineStr">
         <is>
-          <t>2026-07-11 08:17:18 PM PT</t>
+          <t>2026-07-11 08:19:16 PM PT</t>
         </is>
       </c>
       <c r="C212" t="n">
-        <v>823844</v>
+        <v>823682</v>
       </c>
       <c r="D212" t="inlineStr">
         <is>
-          <t>1:10 PM PT</t>
+          <t>11:10 AM PT</t>
         </is>
       </c>
       <c r="E212" t="inlineStr">
@@ -24897,40 +24906,40 @@
       </c>
       <c r="G212" t="inlineStr">
         <is>
-          <t>Bottom</t>
+          <t>Top</t>
         </is>
       </c>
       <c r="K212" t="inlineStr">
         <is>
-          <t>Home</t>
+          <t>Away</t>
         </is>
       </c>
       <c r="L212" t="inlineStr">
         <is>
-          <t>MIA</t>
+          <t>LAA</t>
         </is>
       </c>
       <c r="M212" t="inlineStr">
         <is>
-          <t>CLE</t>
+          <t>MIN</t>
         </is>
       </c>
       <c r="N212" t="inlineStr">
         <is>
-          <t>Otto Lopez</t>
+          <t>Jo Adell</t>
         </is>
       </c>
       <c r="O212" t="n">
-        <v>672640</v>
+        <v>666176</v>
       </c>
       <c r="P212" t="inlineStr">
         <is>
-          <t>SS</t>
+          <t>RF</t>
         </is>
       </c>
       <c r="Q212" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>6</t>
         </is>
       </c>
       <c r="R212" t="n">
@@ -24970,16 +24979,16 @@
         <v>0</v>
       </c>
       <c r="AD212" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AE212" s="4" t="n">
         <v>2</v>
       </c>
       <c r="AF212" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="AG212" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
     </row>
     <row r="213">
@@ -24990,7 +24999,7 @@
       </c>
       <c r="B213" t="inlineStr">
         <is>
-          <t>2026-07-11 08:17:18 PM PT</t>
+          <t>2026-07-11 08:19:17 PM PT</t>
         </is>
       </c>
       <c r="C213" t="n">
@@ -25031,20 +25040,20 @@
       </c>
       <c r="N213" t="inlineStr">
         <is>
-          <t>Jakob Marsee</t>
+          <t>Otto Lopez</t>
         </is>
       </c>
       <c r="O213" t="n">
-        <v>805300</v>
+        <v>672640</v>
       </c>
       <c r="P213" t="inlineStr">
         <is>
-          <t>CF</t>
+          <t>SS</t>
         </is>
       </c>
       <c r="Q213" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>2</t>
         </is>
       </c>
       <c r="R213" t="n">
@@ -25104,15 +25113,15 @@
       </c>
       <c r="B214" t="inlineStr">
         <is>
-          <t>2026-07-11 08:17:17 PM PT</t>
+          <t>2026-07-11 08:19:17 PM PT</t>
         </is>
       </c>
       <c r="C214" t="n">
-        <v>823682</v>
+        <v>823844</v>
       </c>
       <c r="D214" t="inlineStr">
         <is>
-          <t>11:10 AM PT</t>
+          <t>1:10 PM PT</t>
         </is>
       </c>
       <c r="E214" t="inlineStr">
@@ -25125,7 +25134,7 @@
       </c>
       <c r="G214" t="inlineStr">
         <is>
-          <t>Top</t>
+          <t>Bottom</t>
         </is>
       </c>
       <c r="K214" t="inlineStr">
@@ -25135,30 +25144,30 @@
       </c>
       <c r="L214" t="inlineStr">
         <is>
-          <t>MIN</t>
+          <t>MIA</t>
         </is>
       </c>
       <c r="M214" t="inlineStr">
         <is>
-          <t>LAA</t>
+          <t>CLE</t>
         </is>
       </c>
       <c r="N214" t="inlineStr">
         <is>
-          <t>Brooks Lee</t>
+          <t>Jakob Marsee</t>
         </is>
       </c>
       <c r="O214" t="n">
-        <v>686797</v>
+        <v>805300</v>
       </c>
       <c r="P214" t="inlineStr">
         <is>
-          <t>3B</t>
+          <t>CF</t>
         </is>
       </c>
       <c r="Q214" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>7</t>
         </is>
       </c>
       <c r="R214" t="n">
@@ -25204,10 +25213,10 @@
         <v>2</v>
       </c>
       <c r="AF214" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="AG214" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
     </row>
     <row r="215">
@@ -25218,15 +25227,15 @@
       </c>
       <c r="B215" t="inlineStr">
         <is>
-          <t>2026-07-11 08:17:17 PM PT</t>
+          <t>2026-07-11 08:19:16 PM PT</t>
         </is>
       </c>
       <c r="C215" t="n">
-        <v>823603</v>
+        <v>823682</v>
       </c>
       <c r="D215" t="inlineStr">
         <is>
-          <t>1:10 PM PT</t>
+          <t>11:10 AM PT</t>
         </is>
       </c>
       <c r="E215" t="inlineStr">
@@ -25239,7 +25248,7 @@
       </c>
       <c r="G215" t="inlineStr">
         <is>
-          <t>Bottom</t>
+          <t>Top</t>
         </is>
       </c>
       <c r="K215" t="inlineStr">
@@ -25249,25 +25258,25 @@
       </c>
       <c r="L215" t="inlineStr">
         <is>
-          <t>NYM</t>
+          <t>MIN</t>
         </is>
       </c>
       <c r="M215" t="inlineStr">
         <is>
-          <t>BOS</t>
+          <t>LAA</t>
         </is>
       </c>
       <c r="N215" t="inlineStr">
         <is>
-          <t>Juan Soto</t>
+          <t>Brooks Lee</t>
         </is>
       </c>
       <c r="O215" t="n">
-        <v>665742</v>
+        <v>686797</v>
       </c>
       <c r="P215" t="inlineStr">
         <is>
-          <t>LF</t>
+          <t>3B</t>
         </is>
       </c>
       <c r="Q215" t="inlineStr">
@@ -25312,16 +25321,16 @@
         <v>0</v>
       </c>
       <c r="AD215" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AE215" s="4" t="n">
         <v>2</v>
       </c>
       <c r="AF215" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="AG215" t="n">
-        <v>3</v>
+        <v>9</v>
       </c>
     </row>
     <row r="216">
@@ -25332,7 +25341,7 @@
       </c>
       <c r="B216" t="inlineStr">
         <is>
-          <t>2026-07-11 08:17:17 PM PT</t>
+          <t>2026-07-11 08:19:17 PM PT</t>
         </is>
       </c>
       <c r="C216" t="n">
@@ -25373,20 +25382,20 @@
       </c>
       <c r="N216" t="inlineStr">
         <is>
-          <t>Francisco Lindor</t>
+          <t>Juan Soto</t>
         </is>
       </c>
       <c r="O216" t="n">
-        <v>596019</v>
+        <v>665742</v>
       </c>
       <c r="P216" t="inlineStr">
         <is>
-          <t>SS</t>
+          <t>LF</t>
         </is>
       </c>
       <c r="Q216" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="R216" t="n">
@@ -25446,7 +25455,7 @@
       </c>
       <c r="B217" t="inlineStr">
         <is>
-          <t>2026-07-11 08:17:17 PM PT</t>
+          <t>2026-07-11 08:19:17 PM PT</t>
         </is>
       </c>
       <c r="C217" t="n">
@@ -25487,20 +25496,20 @@
       </c>
       <c r="N217" t="inlineStr">
         <is>
-          <t>Eric Wagaman</t>
+          <t>Francisco Lindor</t>
         </is>
       </c>
       <c r="O217" t="n">
-        <v>676572</v>
+        <v>596019</v>
       </c>
       <c r="P217" t="inlineStr">
         <is>
-          <t>1B</t>
+          <t>SS</t>
         </is>
       </c>
       <c r="Q217" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>3</t>
         </is>
       </c>
       <c r="R217" t="n">
@@ -25540,7 +25549,7 @@
         <v>0</v>
       </c>
       <c r="AD217" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AE217" s="4" t="n">
         <v>2</v>
@@ -25560,7 +25569,7 @@
       </c>
       <c r="B218" t="inlineStr">
         <is>
-          <t>2026-07-11 08:17:17 PM PT</t>
+          <t>2026-07-11 08:19:17 PM PT</t>
         </is>
       </c>
       <c r="C218" t="n">
@@ -25601,20 +25610,20 @@
       </c>
       <c r="N218" t="inlineStr">
         <is>
-          <t>Brett Baty</t>
+          <t>Eric Wagaman</t>
         </is>
       </c>
       <c r="O218" t="n">
-        <v>683146</v>
+        <v>676572</v>
       </c>
       <c r="P218" t="inlineStr">
         <is>
-          <t>3B</t>
+          <t>1B</t>
         </is>
       </c>
       <c r="Q218" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>6</t>
         </is>
       </c>
       <c r="R218" t="n">
@@ -25654,7 +25663,7 @@
         <v>0</v>
       </c>
       <c r="AD218" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AE218" s="4" t="n">
         <v>2</v>
@@ -25674,7 +25683,7 @@
       </c>
       <c r="B219" t="inlineStr">
         <is>
-          <t>2026-07-11 08:17:17 PM PT</t>
+          <t>2026-07-11 08:19:17 PM PT</t>
         </is>
       </c>
       <c r="C219" t="n">
@@ -25715,27 +25724,27 @@
       </c>
       <c r="N219" t="inlineStr">
         <is>
-          <t>Bo Bichette</t>
+          <t>Brett Baty</t>
         </is>
       </c>
       <c r="O219" t="n">
-        <v>666182</v>
+        <v>683146</v>
       </c>
       <c r="P219" t="inlineStr">
         <is>
-          <t>PH</t>
+          <t>3B</t>
         </is>
       </c>
       <c r="Q219" t="inlineStr">
         <is>
-          <t>9 (Sub)</t>
+          <t>8</t>
         </is>
       </c>
       <c r="R219" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="S219" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="T219" t="n">
         <v>0</v>
@@ -25768,7 +25777,7 @@
         <v>0</v>
       </c>
       <c r="AD219" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AE219" s="4" t="n">
         <v>2</v>
@@ -25788,15 +25797,15 @@
       </c>
       <c r="B220" t="inlineStr">
         <is>
-          <t>2026-07-11 08:17:17 PM PT</t>
+          <t>2026-07-11 08:19:17 PM PT</t>
         </is>
       </c>
       <c r="C220" t="n">
-        <v>822711</v>
+        <v>823603</v>
       </c>
       <c r="D220" t="inlineStr">
         <is>
-          <t>1:05 PM PT</t>
+          <t>1:10 PM PT</t>
         </is>
       </c>
       <c r="E220" t="inlineStr">
@@ -25814,35 +25823,35 @@
       </c>
       <c r="K220" t="inlineStr">
         <is>
-          <t>Away</t>
+          <t>Home</t>
         </is>
       </c>
       <c r="L220" t="inlineStr">
         <is>
-          <t>NYY</t>
+          <t>NYM</t>
         </is>
       </c>
       <c r="M220" t="inlineStr">
         <is>
-          <t>WSH</t>
+          <t>BOS</t>
         </is>
       </c>
       <c r="N220" t="inlineStr">
         <is>
-          <t>Amed Rosario</t>
+          <t>Bo Bichette</t>
         </is>
       </c>
       <c r="O220" t="n">
-        <v>642708</v>
+        <v>666182</v>
       </c>
       <c r="P220" t="inlineStr">
         <is>
-          <t>3B</t>
+          <t>PH</t>
         </is>
       </c>
       <c r="Q220" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>9 (Sub)</t>
         </is>
       </c>
       <c r="R220" t="n">
@@ -25888,10 +25897,10 @@
         <v>2</v>
       </c>
       <c r="AF220" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="AG220" t="n">
-        <v>9</v>
+        <v>3</v>
       </c>
     </row>
     <row r="221">
@@ -25902,7 +25911,7 @@
       </c>
       <c r="B221" t="inlineStr">
         <is>
-          <t>2026-07-11 08:17:17 PM PT</t>
+          <t>2026-07-11 08:19:17 PM PT</t>
         </is>
       </c>
       <c r="C221" t="n">
@@ -25943,27 +25952,27 @@
       </c>
       <c r="N221" t="inlineStr">
         <is>
-          <t>José Caballero</t>
+          <t>Amed Rosario</t>
         </is>
       </c>
       <c r="O221" t="n">
-        <v>676609</v>
+        <v>642708</v>
       </c>
       <c r="P221" t="inlineStr">
         <is>
-          <t>DH</t>
+          <t>3B</t>
         </is>
       </c>
       <c r="Q221" t="inlineStr">
         <is>
-          <t>2 (Sub)</t>
+          <t>1</t>
         </is>
       </c>
       <c r="R221" t="n">
         <v>1</v>
       </c>
       <c r="S221" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="T221" t="n">
         <v>0</v>
@@ -25981,13 +25990,13 @@
         <v>0</v>
       </c>
       <c r="Y221" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Z221" t="n">
         <v>0</v>
       </c>
-      <c r="AA221" t="n">
-        <v>0</v>
+      <c r="AA221" s="5" t="n">
+        <v>1</v>
       </c>
       <c r="AB221" t="n">
         <v>0</v>
@@ -26016,15 +26025,15 @@
       </c>
       <c r="B222" t="inlineStr">
         <is>
-          <t>2026-07-11 08:17:16 PM PT</t>
+          <t>2026-07-11 08:19:17 PM PT</t>
         </is>
       </c>
       <c r="C222" t="n">
-        <v>823357</v>
+        <v>822711</v>
       </c>
       <c r="D222" t="inlineStr">
         <is>
-          <t>9:05 AM PT</t>
+          <t>1:05 PM PT</t>
         </is>
       </c>
       <c r="E222" t="inlineStr">
@@ -26037,47 +26046,47 @@
       </c>
       <c r="G222" t="inlineStr">
         <is>
-          <t>Top</t>
+          <t>Bottom</t>
         </is>
       </c>
       <c r="K222" t="inlineStr">
         <is>
-          <t>Home</t>
+          <t>Away</t>
         </is>
       </c>
       <c r="L222" t="inlineStr">
         <is>
-          <t>PIT</t>
+          <t>NYY</t>
         </is>
       </c>
       <c r="M222" t="inlineStr">
         <is>
-          <t>MIL</t>
+          <t>WSH</t>
         </is>
       </c>
       <c r="N222" t="inlineStr">
         <is>
-          <t>Ryan O'Hearn</t>
+          <t>José Caballero</t>
         </is>
       </c>
       <c r="O222" t="n">
-        <v>656811</v>
+        <v>676609</v>
       </c>
       <c r="P222" t="inlineStr">
         <is>
-          <t>1B</t>
+          <t>DH</t>
         </is>
       </c>
       <c r="Q222" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>2 (Sub)</t>
         </is>
       </c>
       <c r="R222" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="S222" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="T222" t="n">
         <v>0</v>
@@ -26095,7 +26104,7 @@
         <v>0</v>
       </c>
       <c r="Y222" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Z222" t="n">
         <v>0</v>
@@ -26103,23 +26112,23 @@
       <c r="AA222" t="n">
         <v>0</v>
       </c>
-      <c r="AB222" s="9" t="n">
-        <v>1</v>
+      <c r="AB222" t="n">
+        <v>0</v>
       </c>
       <c r="AC222" t="n">
         <v>0</v>
       </c>
       <c r="AD222" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="AE222" s="4" t="n">
         <v>2</v>
       </c>
       <c r="AF222" t="n">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="AG222" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
     </row>
     <row r="223">
@@ -26130,15 +26139,15 @@
       </c>
       <c r="B223" t="inlineStr">
         <is>
-          <t>2026-07-11 08:17:16 PM PT</t>
+          <t>2026-07-11 08:19:16 PM PT</t>
         </is>
       </c>
       <c r="C223" t="n">
-        <v>823356</v>
+        <v>823357</v>
       </c>
       <c r="D223" t="inlineStr">
         <is>
-          <t>1:05 PM PT</t>
+          <t>9:05 AM PT</t>
         </is>
       </c>
       <c r="E223" t="inlineStr">
@@ -26224,13 +26233,13 @@
         <v>0</v>
       </c>
       <c r="AD223" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="AE223" s="4" t="n">
         <v>2</v>
       </c>
       <c r="AF223" t="n">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="AG223" t="n">
         <v>7</v>
@@ -26244,15 +26253,15 @@
       </c>
       <c r="B224" t="inlineStr">
         <is>
-          <t>2026-07-11 08:17:17 PM PT</t>
+          <t>2026-07-11 08:19:16 PM PT</t>
         </is>
       </c>
       <c r="C224" t="n">
-        <v>822953</v>
+        <v>823356</v>
       </c>
       <c r="D224" t="inlineStr">
         <is>
-          <t>1:10 PM PT</t>
+          <t>1:05 PM PT</t>
         </is>
       </c>
       <c r="E224" t="inlineStr">
@@ -26270,35 +26279,35 @@
       </c>
       <c r="K224" t="inlineStr">
         <is>
-          <t>Away</t>
+          <t>Home</t>
         </is>
       </c>
       <c r="L224" t="inlineStr">
         <is>
-          <t>SEA</t>
+          <t>PIT</t>
         </is>
       </c>
       <c r="M224" t="inlineStr">
         <is>
-          <t>TB</t>
+          <t>MIL</t>
         </is>
       </c>
       <c r="N224" t="inlineStr">
         <is>
-          <t>Colt Emerson</t>
+          <t>Ryan O'Hearn</t>
         </is>
       </c>
       <c r="O224" t="n">
-        <v>806068</v>
+        <v>656811</v>
       </c>
       <c r="P224" t="inlineStr">
         <is>
-          <t>SS</t>
+          <t>1B</t>
         </is>
       </c>
       <c r="Q224" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>5</t>
         </is>
       </c>
       <c r="R224" t="n">
@@ -26326,28 +26335,28 @@
         <v>0</v>
       </c>
       <c r="Z224" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AA224" t="n">
         <v>0</v>
       </c>
-      <c r="AB224" t="n">
-        <v>0</v>
+      <c r="AB224" s="9" t="n">
+        <v>1</v>
       </c>
       <c r="AC224" t="n">
         <v>0</v>
       </c>
       <c r="AD224" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AE224" s="4" t="n">
         <v>2</v>
       </c>
       <c r="AF224" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="AG224" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
     </row>
     <row r="225">
@@ -26358,15 +26367,15 @@
       </c>
       <c r="B225" t="inlineStr">
         <is>
-          <t>2026-07-11 08:17:17 PM PT</t>
+          <t>2026-07-11 08:19:17 PM PT</t>
         </is>
       </c>
       <c r="C225" t="n">
-        <v>823198</v>
+        <v>822953</v>
       </c>
       <c r="D225" t="inlineStr">
         <is>
-          <t>1:05 PM PT</t>
+          <t>1:10 PM PT</t>
         </is>
       </c>
       <c r="E225" t="inlineStr">
@@ -26384,35 +26393,35 @@
       </c>
       <c r="K225" t="inlineStr">
         <is>
-          <t>Home</t>
+          <t>Away</t>
         </is>
       </c>
       <c r="L225" t="inlineStr">
         <is>
-          <t>SF</t>
+          <t>SEA</t>
         </is>
       </c>
       <c r="M225" t="inlineStr">
         <is>
-          <t>COL</t>
+          <t>TB</t>
         </is>
       </c>
       <c r="N225" t="inlineStr">
         <is>
-          <t>Rafael Devers</t>
+          <t>Colt Emerson</t>
         </is>
       </c>
       <c r="O225" t="n">
-        <v>646240</v>
+        <v>806068</v>
       </c>
       <c r="P225" t="inlineStr">
         <is>
-          <t>1B</t>
+          <t>SS</t>
         </is>
       </c>
       <c r="Q225" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>9</t>
         </is>
       </c>
       <c r="R225" t="n">
@@ -26440,10 +26449,10 @@
         <v>0</v>
       </c>
       <c r="Z225" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA225" s="5" t="n">
-        <v>1</v>
+        <v>1</v>
+      </c>
+      <c r="AA225" t="n">
+        <v>0</v>
       </c>
       <c r="AB225" t="n">
         <v>0</v>
@@ -26452,16 +26461,16 @@
         <v>0</v>
       </c>
       <c r="AD225" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AE225" s="4" t="n">
         <v>2</v>
       </c>
       <c r="AF225" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="AG225" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
     </row>
     <row r="226">
@@ -26472,15 +26481,15 @@
       </c>
       <c r="B226" t="inlineStr">
         <is>
-          <t>2026-07-11 08:17:18 PM PT</t>
+          <t>2026-07-11 08:19:17 PM PT</t>
         </is>
       </c>
       <c r="C226" t="n">
-        <v>822875</v>
+        <v>823198</v>
       </c>
       <c r="D226" t="inlineStr">
         <is>
-          <t>4:05 PM PT</t>
+          <t>1:05 PM PT</t>
         </is>
       </c>
       <c r="E226" t="inlineStr">
@@ -26493,7 +26502,7 @@
       </c>
       <c r="G226" t="inlineStr">
         <is>
-          <t>Bottom</t>
+          <t>Top</t>
         </is>
       </c>
       <c r="K226" t="inlineStr">
@@ -26503,30 +26512,30 @@
       </c>
       <c r="L226" t="inlineStr">
         <is>
-          <t>TEX</t>
+          <t>SF</t>
         </is>
       </c>
       <c r="M226" t="inlineStr">
         <is>
-          <t>HOU</t>
+          <t>COL</t>
         </is>
       </c>
       <c r="N226" t="inlineStr">
         <is>
-          <t>Joc Pederson</t>
+          <t>Rafael Devers</t>
         </is>
       </c>
       <c r="O226" t="n">
-        <v>592626</v>
+        <v>646240</v>
       </c>
       <c r="P226" t="inlineStr">
         <is>
-          <t>DH</t>
+          <t>1B</t>
         </is>
       </c>
       <c r="Q226" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>4</t>
         </is>
       </c>
       <c r="R226" t="n">
@@ -26566,13 +26575,13 @@
         <v>0</v>
       </c>
       <c r="AD226" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AE226" s="4" t="n">
         <v>2</v>
       </c>
       <c r="AF226" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="AG226" t="n">
         <v>7</v>
@@ -26586,7 +26595,7 @@
       </c>
       <c r="B227" t="inlineStr">
         <is>
-          <t>2026-07-11 08:17:18 PM PT</t>
+          <t>2026-07-11 08:19:17 PM PT</t>
         </is>
       </c>
       <c r="C227" t="n">
@@ -26627,20 +26636,20 @@
       </c>
       <c r="N227" t="inlineStr">
         <is>
-          <t>Josh Jung</t>
+          <t>Joc Pederson</t>
         </is>
       </c>
       <c r="O227" t="n">
-        <v>673962</v>
+        <v>592626</v>
       </c>
       <c r="P227" t="inlineStr">
         <is>
-          <t>3B</t>
+          <t>DH</t>
         </is>
       </c>
       <c r="Q227" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>1</t>
         </is>
       </c>
       <c r="R227" t="n">
@@ -26670,17 +26679,17 @@
       <c r="Z227" t="n">
         <v>0</v>
       </c>
-      <c r="AA227" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB227" s="9" t="n">
-        <v>1</v>
+      <c r="AA227" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="AB227" t="n">
+        <v>0</v>
       </c>
       <c r="AC227" t="n">
         <v>0</v>
       </c>
       <c r="AD227" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AE227" s="4" t="n">
         <v>2</v>
@@ -26700,74 +26709,65 @@
       </c>
       <c r="B228" t="inlineStr">
         <is>
-          <t>2026-07-11 08:17:18 PM PT</t>
+          <t>2026-07-11 08:19:17 PM PT</t>
         </is>
       </c>
       <c r="C228" t="n">
-        <v>823276</v>
+        <v>822875</v>
       </c>
       <c r="D228" t="inlineStr">
         <is>
-          <t>5:40 PM PT</t>
+          <t>4:05 PM PT</t>
         </is>
       </c>
       <c r="E228" t="inlineStr">
         <is>
-          <t>Bottom 7 | 1 out</t>
+          <t>Final</t>
         </is>
       </c>
       <c r="F228" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="G228" t="inlineStr">
         <is>
           <t>Bottom</t>
         </is>
       </c>
-      <c r="H228" t="n">
-        <v>1</v>
-      </c>
-      <c r="I228" t="n">
-        <v>0</v>
-      </c>
-      <c r="J228" t="n">
-        <v>0</v>
-      </c>
       <c r="K228" t="inlineStr">
         <is>
-          <t>Away</t>
+          <t>Home</t>
         </is>
       </c>
       <c r="L228" t="inlineStr">
         <is>
-          <t>TOR</t>
+          <t>TEX</t>
         </is>
       </c>
       <c r="M228" t="inlineStr">
         <is>
-          <t>SD</t>
+          <t>HOU</t>
         </is>
       </c>
       <c r="N228" t="inlineStr">
         <is>
-          <t>Andrés Giménez</t>
+          <t>Josh Jung</t>
         </is>
       </c>
       <c r="O228" t="n">
-        <v>665926</v>
+        <v>673962</v>
       </c>
       <c r="P228" t="inlineStr">
         <is>
-          <t>SS</t>
+          <t>3B</t>
         </is>
       </c>
       <c r="Q228" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>3</t>
         </is>
       </c>
       <c r="R228" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="S228" t="n">
         <v>3</v>
@@ -26791,28 +26791,28 @@
         <v>0</v>
       </c>
       <c r="Z228" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AA228" t="n">
         <v>0</v>
       </c>
-      <c r="AB228" t="n">
-        <v>0</v>
+      <c r="AB228" s="9" t="n">
+        <v>1</v>
       </c>
       <c r="AC228" t="n">
         <v>0</v>
       </c>
       <c r="AD228" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AE228" s="4" t="n">
         <v>2</v>
       </c>
       <c r="AF228" t="n">
+        <v>3</v>
+      </c>
+      <c r="AG228" t="n">
         <v>7</v>
-      </c>
-      <c r="AG228" t="n">
-        <v>6</v>
       </c>
     </row>
     <row r="229">
@@ -26823,65 +26823,74 @@
       </c>
       <c r="B229" t="inlineStr">
         <is>
-          <t>2026-07-11 08:17:17 PM PT</t>
+          <t>2026-07-11 08:19:18 PM PT</t>
         </is>
       </c>
       <c r="C229" t="n">
-        <v>822711</v>
+        <v>823276</v>
       </c>
       <c r="D229" t="inlineStr">
         <is>
-          <t>1:05 PM PT</t>
+          <t>5:40 PM PT</t>
         </is>
       </c>
       <c r="E229" t="inlineStr">
         <is>
-          <t>Final</t>
+          <t>Bottom 7 | 2 out</t>
         </is>
       </c>
       <c r="F229" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="G229" t="inlineStr">
         <is>
           <t>Bottom</t>
         </is>
       </c>
+      <c r="H229" t="n">
+        <v>2</v>
+      </c>
+      <c r="I229" t="n">
+        <v>3</v>
+      </c>
+      <c r="J229" t="n">
+        <v>2</v>
+      </c>
       <c r="K229" t="inlineStr">
         <is>
-          <t>Home</t>
+          <t>Away</t>
         </is>
       </c>
       <c r="L229" t="inlineStr">
         <is>
-          <t>WSH</t>
+          <t>TOR</t>
         </is>
       </c>
       <c r="M229" t="inlineStr">
         <is>
-          <t>NYY</t>
+          <t>SD</t>
         </is>
       </c>
       <c r="N229" t="inlineStr">
         <is>
-          <t>Dylan Crews</t>
+          <t>Andrés Giménez</t>
         </is>
       </c>
       <c r="O229" t="n">
-        <v>686611</v>
+        <v>665926</v>
       </c>
       <c r="P229" t="inlineStr">
         <is>
-          <t>CF</t>
+          <t>SS</t>
         </is>
       </c>
       <c r="Q229" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>8</t>
         </is>
       </c>
       <c r="R229" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="S229" t="n">
         <v>3</v>
@@ -26905,10 +26914,10 @@
         <v>0</v>
       </c>
       <c r="Z229" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA229" s="5" t="n">
-        <v>1</v>
+        <v>1</v>
+      </c>
+      <c r="AA229" t="n">
+        <v>0</v>
       </c>
       <c r="AB229" t="n">
         <v>0</v>
@@ -26923,10 +26932,10 @@
         <v>2</v>
       </c>
       <c r="AF229" t="n">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="AG229" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
     </row>
     <row r="230">
@@ -26937,7 +26946,7 @@
       </c>
       <c r="B230" t="inlineStr">
         <is>
-          <t>2026-07-11 08:17:17 PM PT</t>
+          <t>2026-07-11 08:19:17 PM PT</t>
         </is>
       </c>
       <c r="C230" t="n">
@@ -26978,20 +26987,20 @@
       </c>
       <c r="N230" t="inlineStr">
         <is>
-          <t>Jorbit Vivas</t>
+          <t>Dylan Crews</t>
         </is>
       </c>
       <c r="O230" t="n">
-        <v>678391</v>
+        <v>686611</v>
       </c>
       <c r="P230" t="inlineStr">
         <is>
-          <t>3B</t>
+          <t>CF</t>
         </is>
       </c>
       <c r="Q230" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>6</t>
         </is>
       </c>
       <c r="R230" t="n">
@@ -27051,7 +27060,7 @@
       </c>
       <c r="B231" t="inlineStr">
         <is>
-          <t>2026-07-11 08:17:17 PM PT</t>
+          <t>2026-07-11 08:19:17 PM PT</t>
         </is>
       </c>
       <c r="C231" t="n">
@@ -27092,28 +27101,28 @@
       </c>
       <c r="N231" t="inlineStr">
         <is>
-          <t>Drew Millas</t>
+          <t>Jorbit Vivas</t>
         </is>
       </c>
       <c r="O231" t="n">
-        <v>686452</v>
+        <v>678391</v>
       </c>
       <c r="P231" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>3B</t>
         </is>
       </c>
       <c r="Q231" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>7</t>
         </is>
       </c>
       <c r="R231" t="n">
+        <v>4</v>
+      </c>
+      <c r="S231" t="n">
         <v>3</v>
       </c>
-      <c r="S231" t="n">
-        <v>2</v>
-      </c>
       <c r="T231" t="n">
         <v>0</v>
       </c>
@@ -27145,7 +27154,7 @@
         <v>0</v>
       </c>
       <c r="AD231" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AE231" s="4" t="n">
         <v>2</v>
@@ -27165,7 +27174,7 @@
       </c>
       <c r="B232" t="inlineStr">
         <is>
-          <t>2026-07-11 08:17:17 PM PT</t>
+          <t>2026-07-11 08:19:17 PM PT</t>
         </is>
       </c>
       <c r="C232" t="n">
@@ -27206,27 +27215,27 @@
       </c>
       <c r="N232" t="inlineStr">
         <is>
-          <t>Nasim Nuñez</t>
+          <t>Drew Millas</t>
         </is>
       </c>
       <c r="O232" t="n">
-        <v>683083</v>
+        <v>686452</v>
       </c>
       <c r="P232" t="inlineStr">
         <is>
-          <t>2B</t>
+          <t>C</t>
         </is>
       </c>
       <c r="Q232" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>8</t>
         </is>
       </c>
       <c r="R232" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="S232" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="T232" t="n">
         <v>0</v>
@@ -27279,119 +27288,110 @@
       </c>
       <c r="B233" t="inlineStr">
         <is>
-          <t>2026-07-11 08:17:18 PM PT</t>
+          <t>2026-07-11 08:19:17 PM PT</t>
         </is>
       </c>
       <c r="C233" t="n">
-        <v>823926</v>
+        <v>822711</v>
       </c>
       <c r="D233" t="inlineStr">
         <is>
-          <t>6:10 PM PT</t>
+          <t>1:05 PM PT</t>
         </is>
       </c>
       <c r="E233" t="inlineStr">
         <is>
-          <t>Top 7 | 1 out</t>
+          <t>Final</t>
         </is>
       </c>
       <c r="F233" t="n">
+        <v>9</v>
+      </c>
+      <c r="G233" t="inlineStr">
+        <is>
+          <t>Bottom</t>
+        </is>
+      </c>
+      <c r="K233" t="inlineStr">
+        <is>
+          <t>Home</t>
+        </is>
+      </c>
+      <c r="L233" t="inlineStr">
+        <is>
+          <t>WSH</t>
+        </is>
+      </c>
+      <c r="M233" t="inlineStr">
+        <is>
+          <t>NYY</t>
+        </is>
+      </c>
+      <c r="N233" t="inlineStr">
+        <is>
+          <t>Nasim Nuñez</t>
+        </is>
+      </c>
+      <c r="O233" t="n">
+        <v>683083</v>
+      </c>
+      <c r="P233" t="inlineStr">
+        <is>
+          <t>2B</t>
+        </is>
+      </c>
+      <c r="Q233" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="R233" t="n">
+        <v>4</v>
+      </c>
+      <c r="S233" t="n">
+        <v>3</v>
+      </c>
+      <c r="T233" t="n">
+        <v>0</v>
+      </c>
+      <c r="U233" t="n">
+        <v>0</v>
+      </c>
+      <c r="V233" t="n">
+        <v>0</v>
+      </c>
+      <c r="W233" t="n">
+        <v>0</v>
+      </c>
+      <c r="X233" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y233" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z233" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA233" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="AB233" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC233" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD233" t="n">
+        <v>1</v>
+      </c>
+      <c r="AE233" s="4" t="n">
+        <v>2</v>
+      </c>
+      <c r="AF233" t="n">
+        <v>2</v>
+      </c>
+      <c r="AG233" t="n">
         <v>7</v>
-      </c>
-      <c r="G233" t="inlineStr">
-        <is>
-          <t>Top</t>
-        </is>
-      </c>
-      <c r="H233" t="n">
-        <v>1</v>
-      </c>
-      <c r="I233" t="n">
-        <v>3</v>
-      </c>
-      <c r="J233" t="n">
-        <v>2</v>
-      </c>
-      <c r="K233" t="inlineStr">
-        <is>
-          <t>Away</t>
-        </is>
-      </c>
-      <c r="L233" t="inlineStr">
-        <is>
-          <t>ARI</t>
-        </is>
-      </c>
-      <c r="M233" t="inlineStr">
-        <is>
-          <t>LAD</t>
-        </is>
-      </c>
-      <c r="N233" t="inlineStr">
-        <is>
-          <t>Ketel Marte</t>
-        </is>
-      </c>
-      <c r="O233" t="n">
-        <v>606466</v>
-      </c>
-      <c r="P233" t="inlineStr">
-        <is>
-          <t>2B</t>
-        </is>
-      </c>
-      <c r="Q233" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="R233" t="n">
-        <v>4</v>
-      </c>
-      <c r="S233" t="n">
-        <v>4</v>
-      </c>
-      <c r="T233" t="n">
-        <v>0</v>
-      </c>
-      <c r="U233" t="n">
-        <v>0</v>
-      </c>
-      <c r="V233" t="n">
-        <v>0</v>
-      </c>
-      <c r="W233" t="n">
-        <v>0</v>
-      </c>
-      <c r="X233" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y233" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z233" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA233" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB233" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC233" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD233" t="n">
-        <v>2</v>
-      </c>
-      <c r="AE233" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="AF233" t="n">
-        <v>6</v>
-      </c>
-      <c r="AG233" t="n">
-        <v>5</v>
       </c>
     </row>
     <row r="234">
@@ -27402,7 +27402,7 @@
       </c>
       <c r="B234" t="inlineStr">
         <is>
-          <t>2026-07-11 08:17:18 PM PT</t>
+          <t>2026-07-11 08:19:18 PM PT</t>
         </is>
       </c>
       <c r="C234" t="n">
@@ -27430,82 +27430,82 @@
         <v>1</v>
       </c>
       <c r="I234" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="J234" t="n">
+        <v>0</v>
+      </c>
+      <c r="K234" t="inlineStr">
+        <is>
+          <t>Away</t>
+        </is>
+      </c>
+      <c r="L234" t="inlineStr">
+        <is>
+          <t>ARI</t>
+        </is>
+      </c>
+      <c r="M234" t="inlineStr">
+        <is>
+          <t>LAD</t>
+        </is>
+      </c>
+      <c r="N234" t="inlineStr">
+        <is>
+          <t>Ketel Marte</t>
+        </is>
+      </c>
+      <c r="O234" t="n">
+        <v>606466</v>
+      </c>
+      <c r="P234" t="inlineStr">
+        <is>
+          <t>2B</t>
+        </is>
+      </c>
+      <c r="Q234" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="R234" t="n">
+        <v>4</v>
+      </c>
+      <c r="S234" t="n">
+        <v>4</v>
+      </c>
+      <c r="T234" t="n">
+        <v>0</v>
+      </c>
+      <c r="U234" t="n">
+        <v>0</v>
+      </c>
+      <c r="V234" t="n">
+        <v>0</v>
+      </c>
+      <c r="W234" t="n">
+        <v>0</v>
+      </c>
+      <c r="X234" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y234" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z234" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA234" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB234" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC234" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD234" t="n">
         <v>2</v>
-      </c>
-      <c r="K234" t="inlineStr">
-        <is>
-          <t>Away</t>
-        </is>
-      </c>
-      <c r="L234" t="inlineStr">
-        <is>
-          <t>ARI</t>
-        </is>
-      </c>
-      <c r="M234" t="inlineStr">
-        <is>
-          <t>LAD</t>
-        </is>
-      </c>
-      <c r="N234" t="inlineStr">
-        <is>
-          <t>Corbin Carroll</t>
-        </is>
-      </c>
-      <c r="O234" t="n">
-        <v>682998</v>
-      </c>
-      <c r="P234" t="inlineStr">
-        <is>
-          <t>RF</t>
-        </is>
-      </c>
-      <c r="Q234" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="R234" t="n">
-        <v>3</v>
-      </c>
-      <c r="S234" t="n">
-        <v>3</v>
-      </c>
-      <c r="T234" t="n">
-        <v>0</v>
-      </c>
-      <c r="U234" t="n">
-        <v>0</v>
-      </c>
-      <c r="V234" t="n">
-        <v>0</v>
-      </c>
-      <c r="W234" t="n">
-        <v>0</v>
-      </c>
-      <c r="X234" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y234" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z234" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA234" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB234" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC234" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD234" t="n">
-        <v>1</v>
       </c>
       <c r="AE234" s="4" t="n">
         <v>0</v>
@@ -27525,7 +27525,7 @@
       </c>
       <c r="B235" t="inlineStr">
         <is>
-          <t>2026-07-11 08:17:18 PM PT</t>
+          <t>2026-07-11 08:19:18 PM PT</t>
         </is>
       </c>
       <c r="C235" t="n">
@@ -27553,10 +27553,10 @@
         <v>1</v>
       </c>
       <c r="I235" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="J235" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="K235" t="inlineStr">
         <is>
@@ -27648,7 +27648,7 @@
       </c>
       <c r="B236" t="inlineStr">
         <is>
-          <t>2026-07-11 08:17:17 PM PT</t>
+          <t>2026-07-11 08:19:17 PM PT</t>
         </is>
       </c>
       <c r="C236" t="n">
@@ -27762,7 +27762,7 @@
       </c>
       <c r="B237" t="inlineStr">
         <is>
-          <t>2026-07-11 08:17:17 PM PT</t>
+          <t>2026-07-11 08:19:17 PM PT</t>
         </is>
       </c>
       <c r="C237" t="n">
@@ -27876,7 +27876,7 @@
       </c>
       <c r="B238" t="inlineStr">
         <is>
-          <t>2026-07-11 08:17:17 PM PT</t>
+          <t>2026-07-11 08:19:17 PM PT</t>
         </is>
       </c>
       <c r="C238" t="n">
@@ -27990,7 +27990,7 @@
       </c>
       <c r="B239" t="inlineStr">
         <is>
-          <t>2026-07-11 08:17:17 PM PT</t>
+          <t>2026-07-11 08:19:17 PM PT</t>
         </is>
       </c>
       <c r="C239" t="n">
@@ -28104,7 +28104,7 @@
       </c>
       <c r="B240" t="inlineStr">
         <is>
-          <t>2026-07-11 08:17:17 PM PT</t>
+          <t>2026-07-11 08:19:17 PM PT</t>
         </is>
       </c>
       <c r="C240" t="n">
@@ -28218,7 +28218,7 @@
       </c>
       <c r="B241" t="inlineStr">
         <is>
-          <t>2026-07-11 08:17:17 PM PT</t>
+          <t>2026-07-11 08:19:17 PM PT</t>
         </is>
       </c>
       <c r="C241" t="n">
@@ -28332,7 +28332,7 @@
       </c>
       <c r="B242" t="inlineStr">
         <is>
-          <t>2026-07-11 08:17:17 PM PT</t>
+          <t>2026-07-11 08:19:17 PM PT</t>
         </is>
       </c>
       <c r="C242" t="n">
@@ -28446,7 +28446,7 @@
       </c>
       <c r="B243" t="inlineStr">
         <is>
-          <t>2026-07-11 08:17:18 PM PT</t>
+          <t>2026-07-11 08:19:17 PM PT</t>
         </is>
       </c>
       <c r="C243" t="n">
@@ -28560,7 +28560,7 @@
       </c>
       <c r="B244" t="inlineStr">
         <is>
-          <t>2026-07-11 08:17:18 PM PT</t>
+          <t>2026-07-11 08:19:17 PM PT</t>
         </is>
       </c>
       <c r="C244" t="n">
@@ -28674,7 +28674,7 @@
       </c>
       <c r="B245" t="inlineStr">
         <is>
-          <t>2026-07-11 08:17:18 PM PT</t>
+          <t>2026-07-11 08:19:17 PM PT</t>
         </is>
       </c>
       <c r="C245" t="n">
@@ -28788,7 +28788,7 @@
       </c>
       <c r="B246" t="inlineStr">
         <is>
-          <t>2026-07-11 08:17:18 PM PT</t>
+          <t>2026-07-11 08:19:17 PM PT</t>
         </is>
       </c>
       <c r="C246" t="n">
@@ -28902,7 +28902,7 @@
       </c>
       <c r="B247" t="inlineStr">
         <is>
-          <t>2026-07-11 08:17:18 PM PT</t>
+          <t>2026-07-11 08:19:17 PM PT</t>
         </is>
       </c>
       <c r="C247" t="n">
@@ -29016,7 +29016,7 @@
       </c>
       <c r="B248" t="inlineStr">
         <is>
-          <t>2026-07-11 08:17:18 PM PT</t>
+          <t>2026-07-11 08:19:17 PM PT</t>
         </is>
       </c>
       <c r="C248" t="n">
@@ -29130,7 +29130,7 @@
       </c>
       <c r="B249" t="inlineStr">
         <is>
-          <t>2026-07-11 08:17:17 PM PT</t>
+          <t>2026-07-11 08:19:17 PM PT</t>
         </is>
       </c>
       <c r="C249" t="n">
@@ -29244,7 +29244,7 @@
       </c>
       <c r="B250" t="inlineStr">
         <is>
-          <t>2026-07-11 08:17:17 PM PT</t>
+          <t>2026-07-11 08:19:17 PM PT</t>
         </is>
       </c>
       <c r="C250" t="n">
@@ -29358,7 +29358,7 @@
       </c>
       <c r="B251" t="inlineStr">
         <is>
-          <t>2026-07-11 08:17:17 PM PT</t>
+          <t>2026-07-11 08:19:17 PM PT</t>
         </is>
       </c>
       <c r="C251" t="n">
@@ -29472,7 +29472,7 @@
       </c>
       <c r="B252" t="inlineStr">
         <is>
-          <t>2026-07-11 08:17:18 PM PT</t>
+          <t>2026-07-11 08:19:17 PM PT</t>
         </is>
       </c>
       <c r="C252" t="n">
@@ -29586,7 +29586,7 @@
       </c>
       <c r="B253" t="inlineStr">
         <is>
-          <t>2026-07-11 08:17:18 PM PT</t>
+          <t>2026-07-11 08:19:17 PM PT</t>
         </is>
       </c>
       <c r="C253" t="n">
@@ -29700,7 +29700,7 @@
       </c>
       <c r="B254" t="inlineStr">
         <is>
-          <t>2026-07-11 08:17:18 PM PT</t>
+          <t>2026-07-11 08:19:17 PM PT</t>
         </is>
       </c>
       <c r="C254" t="n">
@@ -29814,7 +29814,7 @@
       </c>
       <c r="B255" t="inlineStr">
         <is>
-          <t>2026-07-11 08:17:18 PM PT</t>
+          <t>2026-07-11 08:19:17 PM PT</t>
         </is>
       </c>
       <c r="C255" t="n">
@@ -29928,7 +29928,7 @@
       </c>
       <c r="B256" t="inlineStr">
         <is>
-          <t>2026-07-11 08:17:18 PM PT</t>
+          <t>2026-07-11 08:19:17 PM PT</t>
         </is>
       </c>
       <c r="C256" t="n">
@@ -30042,7 +30042,7 @@
       </c>
       <c r="B257" t="inlineStr">
         <is>
-          <t>2026-07-11 08:17:17 PM PT</t>
+          <t>2026-07-11 08:19:17 PM PT</t>
         </is>
       </c>
       <c r="C257" t="n">
@@ -30156,7 +30156,7 @@
       </c>
       <c r="B258" t="inlineStr">
         <is>
-          <t>2026-07-11 08:17:17 PM PT</t>
+          <t>2026-07-11 08:19:17 PM PT</t>
         </is>
       </c>
       <c r="C258" t="n">
@@ -30270,7 +30270,7 @@
       </c>
       <c r="B259" t="inlineStr">
         <is>
-          <t>2026-07-11 08:17:17 PM PT</t>
+          <t>2026-07-11 08:19:17 PM PT</t>
         </is>
       </c>
       <c r="C259" t="n">
@@ -30384,7 +30384,7 @@
       </c>
       <c r="B260" t="inlineStr">
         <is>
-          <t>2026-07-11 08:17:17 PM PT</t>
+          <t>2026-07-11 08:19:17 PM PT</t>
         </is>
       </c>
       <c r="C260" t="n">
@@ -30498,7 +30498,7 @@
       </c>
       <c r="B261" t="inlineStr">
         <is>
-          <t>2026-07-11 08:17:17 PM PT</t>
+          <t>2026-07-11 08:19:17 PM PT</t>
         </is>
       </c>
       <c r="C261" t="n">
@@ -30612,7 +30612,7 @@
       </c>
       <c r="B262" t="inlineStr">
         <is>
-          <t>2026-07-11 08:17:17 PM PT</t>
+          <t>2026-07-11 08:19:17 PM PT</t>
         </is>
       </c>
       <c r="C262" t="n">
@@ -30726,7 +30726,7 @@
       </c>
       <c r="B263" t="inlineStr">
         <is>
-          <t>2026-07-11 08:17:17 PM PT</t>
+          <t>2026-07-11 08:19:17 PM PT</t>
         </is>
       </c>
       <c r="C263" t="n">
@@ -30840,7 +30840,7 @@
       </c>
       <c r="B264" t="inlineStr">
         <is>
-          <t>2026-07-11 08:17:18 PM PT</t>
+          <t>2026-07-11 08:19:17 PM PT</t>
         </is>
       </c>
       <c r="C264" t="n">
@@ -30954,7 +30954,7 @@
       </c>
       <c r="B265" t="inlineStr">
         <is>
-          <t>2026-07-11 08:17:18 PM PT</t>
+          <t>2026-07-11 08:19:17 PM PT</t>
         </is>
       </c>
       <c r="C265" t="n">
@@ -31068,7 +31068,7 @@
       </c>
       <c r="B266" t="inlineStr">
         <is>
-          <t>2026-07-11 08:17:18 PM PT</t>
+          <t>2026-07-11 08:19:17 PM PT</t>
         </is>
       </c>
       <c r="C266" t="n">
@@ -31182,7 +31182,7 @@
       </c>
       <c r="B267" t="inlineStr">
         <is>
-          <t>2026-07-11 08:17:18 PM PT</t>
+          <t>2026-07-11 08:19:17 PM PT</t>
         </is>
       </c>
       <c r="C267" t="n">
@@ -31296,7 +31296,7 @@
       </c>
       <c r="B268" t="inlineStr">
         <is>
-          <t>2026-07-11 08:17:18 PM PT</t>
+          <t>2026-07-11 08:19:17 PM PT</t>
         </is>
       </c>
       <c r="C268" t="n">
@@ -31410,7 +31410,7 @@
       </c>
       <c r="B269" t="inlineStr">
         <is>
-          <t>2026-07-11 08:17:18 PM PT</t>
+          <t>2026-07-11 08:19:17 PM PT</t>
         </is>
       </c>
       <c r="C269" t="n">
@@ -31524,7 +31524,7 @@
       </c>
       <c r="B270" t="inlineStr">
         <is>
-          <t>2026-07-11 08:17:18 PM PT</t>
+          <t>2026-07-11 08:19:17 PM PT</t>
         </is>
       </c>
       <c r="C270" t="n">
@@ -31638,7 +31638,7 @@
       </c>
       <c r="B271" t="inlineStr">
         <is>
-          <t>2026-07-11 08:17:18 PM PT</t>
+          <t>2026-07-11 08:19:17 PM PT</t>
         </is>
       </c>
       <c r="C271" t="n">
@@ -31752,7 +31752,7 @@
       </c>
       <c r="B272" t="inlineStr">
         <is>
-          <t>2026-07-11 08:17:18 PM PT</t>
+          <t>2026-07-11 08:19:17 PM PT</t>
         </is>
       </c>
       <c r="C272" t="n">
@@ -31866,7 +31866,7 @@
       </c>
       <c r="B273" t="inlineStr">
         <is>
-          <t>2026-07-11 08:17:18 PM PT</t>
+          <t>2026-07-11 08:19:17 PM PT</t>
         </is>
       </c>
       <c r="C273" t="n">
@@ -31980,7 +31980,7 @@
       </c>
       <c r="B274" t="inlineStr">
         <is>
-          <t>2026-07-11 08:17:18 PM PT</t>
+          <t>2026-07-11 08:19:17 PM PT</t>
         </is>
       </c>
       <c r="C274" t="n">
@@ -32094,7 +32094,7 @@
       </c>
       <c r="B275" t="inlineStr">
         <is>
-          <t>2026-07-11 08:17:17 PM PT</t>
+          <t>2026-07-11 08:19:16 PM PT</t>
         </is>
       </c>
       <c r="C275" t="n">
@@ -32208,7 +32208,7 @@
       </c>
       <c r="B276" t="inlineStr">
         <is>
-          <t>2026-07-11 08:17:17 PM PT</t>
+          <t>2026-07-11 08:19:16 PM PT</t>
         </is>
       </c>
       <c r="C276" t="n">
@@ -32322,7 +32322,7 @@
       </c>
       <c r="B277" t="inlineStr">
         <is>
-          <t>2026-07-11 08:17:17 PM PT</t>
+          <t>2026-07-11 08:19:16 PM PT</t>
         </is>
       </c>
       <c r="C277" t="n">
@@ -32436,7 +32436,7 @@
       </c>
       <c r="B278" t="inlineStr">
         <is>
-          <t>2026-07-11 08:17:18 PM PT</t>
+          <t>2026-07-11 08:19:18 PM PT</t>
         </is>
       </c>
       <c r="C278" t="n">
@@ -32464,10 +32464,10 @@
         <v>1</v>
       </c>
       <c r="I278" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="J278" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="K278" t="inlineStr">
         <is>
@@ -32559,7 +32559,7 @@
       </c>
       <c r="B279" t="inlineStr">
         <is>
-          <t>2026-07-11 08:17:18 PM PT</t>
+          <t>2026-07-11 08:19:18 PM PT</t>
         </is>
       </c>
       <c r="C279" t="n">
@@ -32587,10 +32587,10 @@
         <v>1</v>
       </c>
       <c r="I279" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="J279" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="K279" t="inlineStr">
         <is>
@@ -32682,7 +32682,7 @@
       </c>
       <c r="B280" t="inlineStr">
         <is>
-          <t>2026-07-11 08:17:18 PM PT</t>
+          <t>2026-07-11 08:19:18 PM PT</t>
         </is>
       </c>
       <c r="C280" t="n">
@@ -32710,10 +32710,10 @@
         <v>1</v>
       </c>
       <c r="I280" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="J280" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="K280" t="inlineStr">
         <is>
@@ -32805,7 +32805,7 @@
       </c>
       <c r="B281" t="inlineStr">
         <is>
-          <t>2026-07-11 08:17:18 PM PT</t>
+          <t>2026-07-11 08:19:18 PM PT</t>
         </is>
       </c>
       <c r="C281" t="n">
@@ -32833,10 +32833,10 @@
         <v>1</v>
       </c>
       <c r="I281" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="J281" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="K281" t="inlineStr">
         <is>
@@ -32928,7 +32928,7 @@
       </c>
       <c r="B282" t="inlineStr">
         <is>
-          <t>2026-07-11 08:17:18 PM PT</t>
+          <t>2026-07-11 08:19:17 PM PT</t>
         </is>
       </c>
       <c r="C282" t="n">
@@ -33042,7 +33042,7 @@
       </c>
       <c r="B283" t="inlineStr">
         <is>
-          <t>2026-07-11 08:17:16 PM PT</t>
+          <t>2026-07-11 08:19:16 PM PT</t>
         </is>
       </c>
       <c r="C283" t="n">
@@ -33156,7 +33156,7 @@
       </c>
       <c r="B284" t="inlineStr">
         <is>
-          <t>2026-07-11 08:17:16 PM PT</t>
+          <t>2026-07-11 08:19:16 PM PT</t>
         </is>
       </c>
       <c r="C284" t="n">
@@ -33270,7 +33270,7 @@
       </c>
       <c r="B285" t="inlineStr">
         <is>
-          <t>2026-07-11 08:17:16 PM PT</t>
+          <t>2026-07-11 08:19:16 PM PT</t>
         </is>
       </c>
       <c r="C285" t="n">
@@ -33384,7 +33384,7 @@
       </c>
       <c r="B286" t="inlineStr">
         <is>
-          <t>2026-07-11 08:17:16 PM PT</t>
+          <t>2026-07-11 08:19:16 PM PT</t>
         </is>
       </c>
       <c r="C286" t="n">
@@ -33498,7 +33498,7 @@
       </c>
       <c r="B287" t="inlineStr">
         <is>
-          <t>2026-07-11 08:17:16 PM PT</t>
+          <t>2026-07-11 08:19:16 PM PT</t>
         </is>
       </c>
       <c r="C287" t="n">
@@ -33612,7 +33612,7 @@
       </c>
       <c r="B288" t="inlineStr">
         <is>
-          <t>2026-07-11 08:17:16 PM PT</t>
+          <t>2026-07-11 08:19:16 PM PT</t>
         </is>
       </c>
       <c r="C288" t="n">
@@ -33726,7 +33726,7 @@
       </c>
       <c r="B289" t="inlineStr">
         <is>
-          <t>2026-07-11 08:17:17 PM PT</t>
+          <t>2026-07-11 08:19:16 PM PT</t>
         </is>
       </c>
       <c r="C289" t="n">
@@ -33840,7 +33840,7 @@
       </c>
       <c r="B290" t="inlineStr">
         <is>
-          <t>2026-07-11 08:17:17 PM PT</t>
+          <t>2026-07-11 08:19:17 PM PT</t>
         </is>
       </c>
       <c r="C290" t="n">
@@ -33954,7 +33954,7 @@
       </c>
       <c r="B291" t="inlineStr">
         <is>
-          <t>2026-07-11 08:17:17 PM PT</t>
+          <t>2026-07-11 08:19:17 PM PT</t>
         </is>
       </c>
       <c r="C291" t="n">
@@ -34068,7 +34068,7 @@
       </c>
       <c r="B292" t="inlineStr">
         <is>
-          <t>2026-07-11 08:17:17 PM PT</t>
+          <t>2026-07-11 08:19:17 PM PT</t>
         </is>
       </c>
       <c r="C292" t="n">
@@ -34182,7 +34182,7 @@
       </c>
       <c r="B293" t="inlineStr">
         <is>
-          <t>2026-07-11 08:17:17 PM PT</t>
+          <t>2026-07-11 08:19:17 PM PT</t>
         </is>
       </c>
       <c r="C293" t="n">
@@ -34296,7 +34296,7 @@
       </c>
       <c r="B294" t="inlineStr">
         <is>
-          <t>2026-07-11 08:17:17 PM PT</t>
+          <t>2026-07-11 08:19:17 PM PT</t>
         </is>
       </c>
       <c r="C294" t="n">
@@ -34410,7 +34410,7 @@
       </c>
       <c r="B295" t="inlineStr">
         <is>
-          <t>2026-07-11 08:17:17 PM PT</t>
+          <t>2026-07-11 08:19:17 PM PT</t>
         </is>
       </c>
       <c r="C295" t="n">
@@ -34524,7 +34524,7 @@
       </c>
       <c r="B296" t="inlineStr">
         <is>
-          <t>2026-07-11 08:17:18 PM PT</t>
+          <t>2026-07-11 08:19:17 PM PT</t>
         </is>
       </c>
       <c r="C296" t="n">
@@ -34638,7 +34638,7 @@
       </c>
       <c r="B297" t="inlineStr">
         <is>
-          <t>2026-07-11 08:17:18 PM PT</t>
+          <t>2026-07-11 08:19:17 PM PT</t>
         </is>
       </c>
       <c r="C297" t="n">
@@ -34752,7 +34752,7 @@
       </c>
       <c r="B298" t="inlineStr">
         <is>
-          <t>2026-07-11 08:17:16 PM PT</t>
+          <t>2026-07-11 08:19:16 PM PT</t>
         </is>
       </c>
       <c r="C298" t="n">
@@ -34866,7 +34866,7 @@
       </c>
       <c r="B299" t="inlineStr">
         <is>
-          <t>2026-07-11 08:17:16 PM PT</t>
+          <t>2026-07-11 08:19:16 PM PT</t>
         </is>
       </c>
       <c r="C299" t="n">
@@ -34980,7 +34980,7 @@
       </c>
       <c r="B300" t="inlineStr">
         <is>
-          <t>2026-07-11 08:17:16 PM PT</t>
+          <t>2026-07-11 08:19:16 PM PT</t>
         </is>
       </c>
       <c r="C300" t="n">
@@ -35094,7 +35094,7 @@
       </c>
       <c r="B301" t="inlineStr">
         <is>
-          <t>2026-07-11 08:17:16 PM PT</t>
+          <t>2026-07-11 08:19:16 PM PT</t>
         </is>
       </c>
       <c r="C301" t="n">
@@ -35208,7 +35208,7 @@
       </c>
       <c r="B302" t="inlineStr">
         <is>
-          <t>2026-07-11 08:17:16 PM PT</t>
+          <t>2026-07-11 08:19:16 PM PT</t>
         </is>
       </c>
       <c r="C302" t="n">
@@ -35322,7 +35322,7 @@
       </c>
       <c r="B303" t="inlineStr">
         <is>
-          <t>2026-07-11 08:17:16 PM PT</t>
+          <t>2026-07-11 08:19:16 PM PT</t>
         </is>
       </c>
       <c r="C303" t="n">
@@ -35436,7 +35436,7 @@
       </c>
       <c r="B304" t="inlineStr">
         <is>
-          <t>2026-07-11 08:17:16 PM PT</t>
+          <t>2026-07-11 08:19:16 PM PT</t>
         </is>
       </c>
       <c r="C304" t="n">
@@ -35550,7 +35550,7 @@
       </c>
       <c r="B305" t="inlineStr">
         <is>
-          <t>2026-07-11 08:17:16 PM PT</t>
+          <t>2026-07-11 08:19:16 PM PT</t>
         </is>
       </c>
       <c r="C305" t="n">
@@ -35664,7 +35664,7 @@
       </c>
       <c r="B306" t="inlineStr">
         <is>
-          <t>2026-07-11 08:17:18 PM PT</t>
+          <t>2026-07-11 08:19:18 PM PT</t>
         </is>
       </c>
       <c r="C306" t="n">
@@ -35677,7 +35677,7 @@
       </c>
       <c r="E306" t="inlineStr">
         <is>
-          <t>Bottom 7 | 1 out</t>
+          <t>Bottom 7 | 2 out</t>
         </is>
       </c>
       <c r="F306" t="n">
@@ -35689,13 +35689,13 @@
         </is>
       </c>
       <c r="H306" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I306" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="J306" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="K306" t="inlineStr">
         <is>
@@ -35787,7 +35787,7 @@
       </c>
       <c r="B307" t="inlineStr">
         <is>
-          <t>2026-07-11 08:17:17 PM PT</t>
+          <t>2026-07-11 08:19:17 PM PT</t>
         </is>
       </c>
       <c r="C307" t="n">
@@ -35901,7 +35901,7 @@
       </c>
       <c r="B308" t="inlineStr">
         <is>
-          <t>2026-07-11 08:17:17 PM PT</t>
+          <t>2026-07-11 08:19:17 PM PT</t>
         </is>
       </c>
       <c r="C308" t="n">
@@ -36015,7 +36015,7 @@
       </c>
       <c r="B309" t="inlineStr">
         <is>
-          <t>2026-07-11 08:17:17 PM PT</t>
+          <t>2026-07-11 08:19:17 PM PT</t>
         </is>
       </c>
       <c r="C309" t="n">
@@ -36129,7 +36129,7 @@
       </c>
       <c r="B310" t="inlineStr">
         <is>
-          <t>2026-07-11 08:17:17 PM PT</t>
+          <t>2026-07-11 08:19:17 PM PT</t>
         </is>
       </c>
       <c r="C310" t="n">
@@ -36243,7 +36243,7 @@
       </c>
       <c r="B311" t="inlineStr">
         <is>
-          <t>2026-07-11 08:17:17 PM PT</t>
+          <t>2026-07-11 08:19:17 PM PT</t>
         </is>
       </c>
       <c r="C311" t="n">
@@ -36357,7 +36357,7 @@
       </c>
       <c r="B312" t="inlineStr">
         <is>
-          <t>2026-07-11 08:17:17 PM PT</t>
+          <t>2026-07-11 08:19:17 PM PT</t>
         </is>
       </c>
       <c r="C312" t="n">
@@ -36471,7 +36471,7 @@
       </c>
       <c r="B313" t="inlineStr">
         <is>
-          <t>2026-07-11 08:17:17 PM PT</t>
+          <t>2026-07-11 08:19:17 PM PT</t>
         </is>
       </c>
       <c r="C313" t="n">
@@ -36585,7 +36585,7 @@
       </c>
       <c r="B314" t="inlineStr">
         <is>
-          <t>2026-07-11 08:17:18 PM PT</t>
+          <t>2026-07-11 08:19:17 PM PT</t>
         </is>
       </c>
       <c r="C314" t="n">
@@ -36699,7 +36699,7 @@
       </c>
       <c r="B315" t="inlineStr">
         <is>
-          <t>2026-07-11 08:17:18 PM PT</t>
+          <t>2026-07-11 08:19:17 PM PT</t>
         </is>
       </c>
       <c r="C315" t="n">
@@ -36813,7 +36813,7 @@
       </c>
       <c r="B316" t="inlineStr">
         <is>
-          <t>2026-07-11 08:17:18 PM PT</t>
+          <t>2026-07-11 08:19:17 PM PT</t>
         </is>
       </c>
       <c r="C316" t="n">
@@ -36927,7 +36927,7 @@
       </c>
       <c r="B317" t="inlineStr">
         <is>
-          <t>2026-07-11 08:17:18 PM PT</t>
+          <t>2026-07-11 08:19:17 PM PT</t>
         </is>
       </c>
       <c r="C317" t="n">
@@ -37041,7 +37041,7 @@
       </c>
       <c r="B318" t="inlineStr">
         <is>
-          <t>2026-07-11 08:17:17 PM PT</t>
+          <t>2026-07-11 08:19:17 PM PT</t>
         </is>
       </c>
       <c r="C318" t="n">
@@ -37155,7 +37155,7 @@
       </c>
       <c r="B319" t="inlineStr">
         <is>
-          <t>2026-07-11 08:17:17 PM PT</t>
+          <t>2026-07-11 08:19:17 PM PT</t>
         </is>
       </c>
       <c r="C319" t="n">
@@ -37269,7 +37269,7 @@
       </c>
       <c r="B320" t="inlineStr">
         <is>
-          <t>2026-07-11 08:17:17 PM PT</t>
+          <t>2026-07-11 08:19:17 PM PT</t>
         </is>
       </c>
       <c r="C320" t="n">
@@ -37383,7 +37383,7 @@
       </c>
       <c r="B321" t="inlineStr">
         <is>
-          <t>2026-07-11 08:17:17 PM PT</t>
+          <t>2026-07-11 08:19:17 PM PT</t>
         </is>
       </c>
       <c r="C321" t="n">
@@ -37497,7 +37497,7 @@
       </c>
       <c r="B322" t="inlineStr">
         <is>
-          <t>2026-07-11 08:17:18 PM PT</t>
+          <t>2026-07-11 08:19:17 PM PT</t>
         </is>
       </c>
       <c r="C322" t="n">
@@ -37611,7 +37611,7 @@
       </c>
       <c r="B323" t="inlineStr">
         <is>
-          <t>2026-07-11 08:17:18 PM PT</t>
+          <t>2026-07-11 08:19:17 PM PT</t>
         </is>
       </c>
       <c r="C323" t="n">
@@ -37725,7 +37725,7 @@
       </c>
       <c r="B324" t="inlineStr">
         <is>
-          <t>2026-07-11 08:17:18 PM PT</t>
+          <t>2026-07-11 08:19:17 PM PT</t>
         </is>
       </c>
       <c r="C324" t="n">
@@ -37839,7 +37839,7 @@
       </c>
       <c r="B325" t="inlineStr">
         <is>
-          <t>2026-07-11 08:17:18 PM PT</t>
+          <t>2026-07-11 08:19:17 PM PT</t>
         </is>
       </c>
       <c r="C325" t="n">
@@ -37953,7 +37953,7 @@
       </c>
       <c r="B326" t="inlineStr">
         <is>
-          <t>2026-07-11 08:17:18 PM PT</t>
+          <t>2026-07-11 08:19:17 PM PT</t>
         </is>
       </c>
       <c r="C326" t="n">
@@ -38067,7 +38067,7 @@
       </c>
       <c r="B327" t="inlineStr">
         <is>
-          <t>2026-07-11 08:17:18 PM PT</t>
+          <t>2026-07-11 08:19:18 PM PT</t>
         </is>
       </c>
       <c r="C327" t="n">
@@ -38080,7 +38080,7 @@
       </c>
       <c r="E327" t="inlineStr">
         <is>
-          <t>Bottom 7 | 1 out</t>
+          <t>Bottom 7 | 2 out</t>
         </is>
       </c>
       <c r="F327" t="n">
@@ -38092,13 +38092,13 @@
         </is>
       </c>
       <c r="H327" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I327" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="J327" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="K327" t="inlineStr">
         <is>
@@ -38190,7 +38190,7 @@
       </c>
       <c r="B328" t="inlineStr">
         <is>
-          <t>2026-07-11 08:17:17 PM PT</t>
+          <t>2026-07-11 08:19:17 PM PT</t>
         </is>
       </c>
       <c r="C328" t="n">
@@ -38304,7 +38304,7 @@
       </c>
       <c r="B329" t="inlineStr">
         <is>
-          <t>2026-07-11 08:17:17 PM PT</t>
+          <t>2026-07-11 08:19:17 PM PT</t>
         </is>
       </c>
       <c r="C329" t="n">

--- a/live_mlb_hitter_fantasy_scores_2026_07_11.xlsx
+++ b/live_mlb_hitter_fantasy_scores_2026_07_11.xlsx
@@ -693,7 +693,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-07-11 08:19:16 PM PT</t>
+          <t>2026-07-11 08:21:16 PM PT</t>
         </is>
       </c>
       <c r="C2" t="n">
@@ -807,7 +807,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>2026-07-11 08:19:17 PM PT</t>
+          <t>2026-07-11 08:21:18 PM PT</t>
         </is>
       </c>
       <c r="C3" t="n">
@@ -921,7 +921,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-07-11 08:19:18 PM PT</t>
+          <t>2026-07-11 08:21:18 PM PT</t>
         </is>
       </c>
       <c r="C4" t="n">
@@ -934,7 +934,7 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Bottom 7 | 2 out</t>
+          <t>Bottom 7 | 3 out</t>
         </is>
       </c>
       <c r="F4" t="n">
@@ -946,13 +946,13 @@
         </is>
       </c>
       <c r="H4" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="I4" t="n">
         <v>3</v>
       </c>
       <c r="J4" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="K4" t="inlineStr">
         <is>
@@ -1044,7 +1044,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>2026-07-11 08:19:17 PM PT</t>
+          <t>2026-07-11 08:21:18 PM PT</t>
         </is>
       </c>
       <c r="C5" t="n">
@@ -1158,7 +1158,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>2026-07-11 08:19:17 PM PT</t>
+          <t>2026-07-11 08:21:18 PM PT</t>
         </is>
       </c>
       <c r="C6" t="n">
@@ -1272,7 +1272,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>2026-07-11 08:19:17 PM PT</t>
+          <t>2026-07-11 08:21:17 PM PT</t>
         </is>
       </c>
       <c r="C7" t="n">
@@ -1386,7 +1386,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>2026-07-11 08:19:17 PM PT</t>
+          <t>2026-07-11 08:21:18 PM PT</t>
         </is>
       </c>
       <c r="C8" t="n">
@@ -1500,7 +1500,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>2026-07-11 08:19:16 PM PT</t>
+          <t>2026-07-11 08:21:16 PM PT</t>
         </is>
       </c>
       <c r="C9" t="n">
@@ -1614,7 +1614,7 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>2026-07-11 08:19:18 PM PT</t>
+          <t>2026-07-11 08:21:18 PM PT</t>
         </is>
       </c>
       <c r="C10" t="n">
@@ -1627,7 +1627,7 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Bottom 7 | 2 out</t>
+          <t>Bottom 7 | 3 out</t>
         </is>
       </c>
       <c r="F10" t="n">
@@ -1639,13 +1639,13 @@
         </is>
       </c>
       <c r="H10" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="I10" t="n">
         <v>3</v>
       </c>
       <c r="J10" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="K10" t="inlineStr">
         <is>
@@ -1737,7 +1737,7 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>2026-07-11 08:19:17 PM PT</t>
+          <t>2026-07-11 08:21:17 PM PT</t>
         </is>
       </c>
       <c r="C11" t="n">
@@ -1851,7 +1851,7 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>2026-07-11 08:19:17 PM PT</t>
+          <t>2026-07-11 08:21:17 PM PT</t>
         </is>
       </c>
       <c r="C12" t="n">
@@ -1965,7 +1965,7 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>2026-07-11 08:19:18 PM PT</t>
+          <t>2026-07-11 08:21:18 PM PT</t>
         </is>
       </c>
       <c r="C13" t="n">
@@ -1978,7 +1978,7 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Bottom 7 | 2 out</t>
+          <t>Bottom 7 | 3 out</t>
         </is>
       </c>
       <c r="F13" t="n">
@@ -1990,13 +1990,13 @@
         </is>
       </c>
       <c r="H13" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="I13" t="n">
         <v>3</v>
       </c>
       <c r="J13" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="K13" t="inlineStr">
         <is>
@@ -2088,7 +2088,7 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>2026-07-11 08:19:17 PM PT</t>
+          <t>2026-07-11 08:21:17 PM PT</t>
         </is>
       </c>
       <c r="C14" t="n">
@@ -2202,7 +2202,7 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>2026-07-11 08:19:17 PM PT</t>
+          <t>2026-07-11 08:21:17 PM PT</t>
         </is>
       </c>
       <c r="C15" t="n">
@@ -2316,7 +2316,7 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>2026-07-11 08:19:17 PM PT</t>
+          <t>2026-07-11 08:21:18 PM PT</t>
         </is>
       </c>
       <c r="C16" t="n">
@@ -2430,7 +2430,7 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>2026-07-11 08:19:18 PM PT</t>
+          <t>2026-07-11 08:21:18 PM PT</t>
         </is>
       </c>
       <c r="C17" t="n">
@@ -2443,7 +2443,7 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Bottom 7 | 2 out</t>
+          <t>Bottom 7 | 3 out</t>
         </is>
       </c>
       <c r="F17" t="n">
@@ -2455,13 +2455,13 @@
         </is>
       </c>
       <c r="H17" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="I17" t="n">
         <v>3</v>
       </c>
       <c r="J17" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="K17" t="inlineStr">
         <is>
@@ -2553,7 +2553,7 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>2026-07-11 08:19:17 PM PT</t>
+          <t>2026-07-11 08:21:17 PM PT</t>
         </is>
       </c>
       <c r="C18" t="n">
@@ -2667,7 +2667,7 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>2026-07-11 08:19:17 PM PT</t>
+          <t>2026-07-11 08:21:18 PM PT</t>
         </is>
       </c>
       <c r="C19" t="n">
@@ -2781,7 +2781,7 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>2026-07-11 08:19:17 PM PT</t>
+          <t>2026-07-11 08:21:17 PM PT</t>
         </is>
       </c>
       <c r="C20" t="n">
@@ -2895,7 +2895,7 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>2026-07-11 08:19:17 PM PT</t>
+          <t>2026-07-11 08:21:17 PM PT</t>
         </is>
       </c>
       <c r="C21" t="n">
@@ -3009,7 +3009,7 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>2026-07-11 08:19:18 PM PT</t>
+          <t>2026-07-11 08:21:18 PM PT</t>
         </is>
       </c>
       <c r="C22" t="n">
@@ -3022,7 +3022,7 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Top 7 | 1 out</t>
+          <t>Top 7 | 2 out</t>
         </is>
       </c>
       <c r="F22" t="n">
@@ -3034,7 +3034,7 @@
         </is>
       </c>
       <c r="H22" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I22" t="n">
         <v>0</v>
@@ -3118,7 +3118,7 @@
         <v>18</v>
       </c>
       <c r="AF22" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AG22" t="n">
         <v>5</v>
@@ -3132,7 +3132,7 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>2026-07-11 08:19:17 PM PT</t>
+          <t>2026-07-11 08:21:18 PM PT</t>
         </is>
       </c>
       <c r="C23" t="n">
@@ -3246,7 +3246,7 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>2026-07-11 08:19:17 PM PT</t>
+          <t>2026-07-11 08:21:17 PM PT</t>
         </is>
       </c>
       <c r="C24" t="n">
@@ -3360,7 +3360,7 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>2026-07-11 08:19:17 PM PT</t>
+          <t>2026-07-11 08:21:18 PM PT</t>
         </is>
       </c>
       <c r="C25" t="n">
@@ -3474,7 +3474,7 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>2026-07-11 08:19:16 PM PT</t>
+          <t>2026-07-11 08:21:16 PM PT</t>
         </is>
       </c>
       <c r="C26" t="n">
@@ -3588,7 +3588,7 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>2026-07-11 08:19:17 PM PT</t>
+          <t>2026-07-11 08:21:17 PM PT</t>
         </is>
       </c>
       <c r="C27" t="n">
@@ -3702,7 +3702,7 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>2026-07-11 08:19:17 PM PT</t>
+          <t>2026-07-11 08:21:17 PM PT</t>
         </is>
       </c>
       <c r="C28" t="n">
@@ -3816,7 +3816,7 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>2026-07-11 08:19:17 PM PT</t>
+          <t>2026-07-11 08:21:18 PM PT</t>
         </is>
       </c>
       <c r="C29" t="n">
@@ -3930,7 +3930,7 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>2026-07-11 08:19:17 PM PT</t>
+          <t>2026-07-11 08:21:18 PM PT</t>
         </is>
       </c>
       <c r="C30" t="n">
@@ -4044,7 +4044,7 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>2026-07-11 08:19:17 PM PT</t>
+          <t>2026-07-11 08:21:17 PM PT</t>
         </is>
       </c>
       <c r="C31" t="n">
@@ -4158,7 +4158,7 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>2026-07-11 08:19:17 PM PT</t>
+          <t>2026-07-11 08:21:17 PM PT</t>
         </is>
       </c>
       <c r="C32" t="n">
@@ -4272,7 +4272,7 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>2026-07-11 08:19:17 PM PT</t>
+          <t>2026-07-11 08:21:18 PM PT</t>
         </is>
       </c>
       <c r="C33" t="n">
@@ -4386,7 +4386,7 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>2026-07-11 08:19:16 PM PT</t>
+          <t>2026-07-11 08:21:16 PM PT</t>
         </is>
       </c>
       <c r="C34" t="n">
@@ -4500,7 +4500,7 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>2026-07-11 08:19:16 PM PT</t>
+          <t>2026-07-11 08:21:16 PM PT</t>
         </is>
       </c>
       <c r="C35" t="n">
@@ -4614,7 +4614,7 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>2026-07-11 08:19:18 PM PT</t>
+          <t>2026-07-11 08:21:18 PM PT</t>
         </is>
       </c>
       <c r="C36" t="n">
@@ -4627,7 +4627,7 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Bottom 7 | 2 out</t>
+          <t>Bottom 7 | 3 out</t>
         </is>
       </c>
       <c r="F36" t="n">
@@ -4639,13 +4639,13 @@
         </is>
       </c>
       <c r="H36" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="I36" t="n">
         <v>3</v>
       </c>
       <c r="J36" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="K36" t="inlineStr">
         <is>
@@ -4737,7 +4737,7 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>2026-07-11 08:19:17 PM PT</t>
+          <t>2026-07-11 08:21:17 PM PT</t>
         </is>
       </c>
       <c r="C37" t="n">
@@ -4851,7 +4851,7 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>2026-07-11 08:19:16 PM PT</t>
+          <t>2026-07-11 08:21:16 PM PT</t>
         </is>
       </c>
       <c r="C38" t="n">
@@ -4965,7 +4965,7 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>2026-07-11 08:19:17 PM PT</t>
+          <t>2026-07-11 08:21:17 PM PT</t>
         </is>
       </c>
       <c r="C39" t="n">
@@ -5079,7 +5079,7 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>2026-07-11 08:19:16 PM PT</t>
+          <t>2026-07-11 08:21:16 PM PT</t>
         </is>
       </c>
       <c r="C40" t="n">
@@ -5193,7 +5193,7 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>2026-07-11 08:19:18 PM PT</t>
+          <t>2026-07-11 08:21:18 PM PT</t>
         </is>
       </c>
       <c r="C41" t="n">
@@ -5206,7 +5206,7 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>Top 7 | 1 out</t>
+          <t>Top 7 | 2 out</t>
         </is>
       </c>
       <c r="F41" t="n">
@@ -5218,7 +5218,7 @@
         </is>
       </c>
       <c r="H41" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I41" t="n">
         <v>0</v>
@@ -5302,7 +5302,7 @@
         <v>14</v>
       </c>
       <c r="AF41" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AG41" t="n">
         <v>5</v>
@@ -5316,7 +5316,7 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>2026-07-11 08:19:17 PM PT</t>
+          <t>2026-07-11 08:21:18 PM PT</t>
         </is>
       </c>
       <c r="C42" t="n">
@@ -5430,7 +5430,7 @@
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>2026-07-11 08:19:17 PM PT</t>
+          <t>2026-07-11 08:21:18 PM PT</t>
         </is>
       </c>
       <c r="C43" t="n">
@@ -5544,7 +5544,7 @@
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>2026-07-11 08:19:17 PM PT</t>
+          <t>2026-07-11 08:21:18 PM PT</t>
         </is>
       </c>
       <c r="C44" t="n">
@@ -5658,7 +5658,7 @@
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>2026-07-11 08:19:17 PM PT</t>
+          <t>2026-07-11 08:21:18 PM PT</t>
         </is>
       </c>
       <c r="C45" t="n">
@@ -5772,7 +5772,7 @@
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>2026-07-11 08:19:17 PM PT</t>
+          <t>2026-07-11 08:21:17 PM PT</t>
         </is>
       </c>
       <c r="C46" t="n">
@@ -5886,7 +5886,7 @@
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>2026-07-11 08:19:17 PM PT</t>
+          <t>2026-07-11 08:21:17 PM PT</t>
         </is>
       </c>
       <c r="C47" t="n">
@@ -6000,7 +6000,7 @@
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>2026-07-11 08:19:17 PM PT</t>
+          <t>2026-07-11 08:21:18 PM PT</t>
         </is>
       </c>
       <c r="C48" t="n">
@@ -6114,7 +6114,7 @@
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>2026-07-11 08:19:17 PM PT</t>
+          <t>2026-07-11 08:21:17 PM PT</t>
         </is>
       </c>
       <c r="C49" t="n">
@@ -6228,7 +6228,7 @@
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>2026-07-11 08:19:16 PM PT</t>
+          <t>2026-07-11 08:21:16 PM PT</t>
         </is>
       </c>
       <c r="C50" t="n">
@@ -6342,29 +6342,38 @@
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>2026-07-11 08:19:17 PM PT</t>
+          <t>2026-07-11 08:21:18 PM PT</t>
         </is>
       </c>
       <c r="C51" t="n">
-        <v>824492</v>
+        <v>823926</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>4:10 PM PT</t>
+          <t>6:10 PM PT</t>
         </is>
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>Final</t>
+          <t>Top 7 | 2 out</t>
         </is>
       </c>
       <c r="F51" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Bottom</t>
-        </is>
+          <t>Top</t>
+        </is>
+      </c>
+      <c r="H51" t="n">
+        <v>2</v>
+      </c>
+      <c r="I51" t="n">
+        <v>0</v>
+      </c>
+      <c r="J51" t="n">
+        <v>0</v>
       </c>
       <c r="K51" t="inlineStr">
         <is>
@@ -6373,67 +6382,67 @@
       </c>
       <c r="L51" t="inlineStr">
         <is>
-          <t>CHC</t>
+          <t>ARI</t>
         </is>
       </c>
       <c r="M51" t="inlineStr">
         <is>
-          <t>CIN</t>
+          <t>LAD</t>
         </is>
       </c>
       <c r="N51" t="inlineStr">
         <is>
-          <t>Michael Busch</t>
+          <t>Geraldo Perdomo</t>
         </is>
       </c>
       <c r="O51" t="n">
-        <v>683737</v>
+        <v>672695</v>
       </c>
       <c r="P51" t="inlineStr">
         <is>
-          <t>1B</t>
+          <t>SS</t>
         </is>
       </c>
       <c r="Q51" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>2</t>
         </is>
       </c>
       <c r="R51" t="n">
         <v>4</v>
       </c>
       <c r="S51" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="T51" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="U51" t="n">
+        <v>0</v>
+      </c>
+      <c r="V51" t="n">
+        <v>0</v>
+      </c>
+      <c r="W51" t="n">
+        <v>0</v>
+      </c>
+      <c r="X51" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y51" t="n">
         <v>2</v>
       </c>
-      <c r="V51" s="7" t="n">
-        <v>1</v>
-      </c>
-      <c r="W51" t="n">
-        <v>0</v>
-      </c>
-      <c r="X51" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y51" t="n">
-        <v>1</v>
-      </c>
       <c r="Z51" t="n">
         <v>0</v>
       </c>
-      <c r="AA51" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB51" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC51" t="n">
-        <v>0</v>
+      <c r="AA51" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="AB51" s="9" t="n">
+        <v>1</v>
+      </c>
+      <c r="AC51" s="6" t="n">
+        <v>1</v>
       </c>
       <c r="AD51" t="n">
         <v>0</v>
@@ -6442,10 +6451,10 @@
         <v>13</v>
       </c>
       <c r="AF51" t="n">
+        <v>7</v>
+      </c>
+      <c r="AG51" t="n">
         <v>5</v>
-      </c>
-      <c r="AG51" t="n">
-        <v>9</v>
       </c>
     </row>
     <row r="52">
@@ -6456,7 +6465,7 @@
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>2026-07-11 08:19:17 PM PT</t>
+          <t>2026-07-11 08:21:18 PM PT</t>
         </is>
       </c>
       <c r="C52" t="n">
@@ -6482,51 +6491,51 @@
       </c>
       <c r="K52" t="inlineStr">
         <is>
-          <t>Home</t>
+          <t>Away</t>
         </is>
       </c>
       <c r="L52" t="inlineStr">
         <is>
+          <t>CHC</t>
+        </is>
+      </c>
+      <c r="M52" t="inlineStr">
+        <is>
           <t>CIN</t>
         </is>
       </c>
-      <c r="M52" t="inlineStr">
-        <is>
-          <t>CHC</t>
-        </is>
-      </c>
       <c r="N52" t="inlineStr">
         <is>
-          <t>Elly De La Cruz</t>
+          <t>Michael Busch</t>
         </is>
       </c>
       <c r="O52" t="n">
-        <v>682829</v>
+        <v>683737</v>
       </c>
       <c r="P52" t="inlineStr">
         <is>
-          <t>SS</t>
+          <t>1B</t>
         </is>
       </c>
       <c r="Q52" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>5</t>
         </is>
       </c>
       <c r="R52" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="S52" t="n">
         <v>4</v>
       </c>
       <c r="T52" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="U52" t="n">
         <v>2</v>
       </c>
-      <c r="V52" t="n">
-        <v>0</v>
+      <c r="V52" s="7" t="n">
+        <v>1</v>
       </c>
       <c r="W52" t="n">
         <v>0</v>
@@ -6535,31 +6544,31 @@
         <v>0</v>
       </c>
       <c r="Y52" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Z52" t="n">
         <v>0</v>
       </c>
-      <c r="AA52" s="5" t="n">
-        <v>1</v>
+      <c r="AA52" t="n">
+        <v>0</v>
       </c>
       <c r="AB52" t="n">
         <v>0</v>
       </c>
-      <c r="AC52" s="6" t="n">
-        <v>1</v>
+      <c r="AC52" t="n">
+        <v>0</v>
       </c>
       <c r="AD52" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AE52" s="4" t="n">
         <v>13</v>
       </c>
       <c r="AF52" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="AG52" t="n">
-        <v>11</v>
+        <v>9</v>
       </c>
     </row>
     <row r="53">
@@ -6570,15 +6579,15 @@
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>2026-07-11 08:19:17 PM PT</t>
+          <t>2026-07-11 08:21:18 PM PT</t>
         </is>
       </c>
       <c r="C53" t="n">
-        <v>824249</v>
+        <v>824492</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>3:10 PM PT</t>
+          <t>4:10 PM PT</t>
         </is>
       </c>
       <c r="E53" t="inlineStr">
@@ -6601,25 +6610,25 @@
       </c>
       <c r="L53" t="inlineStr">
         <is>
-          <t>DET</t>
+          <t>CIN</t>
         </is>
       </c>
       <c r="M53" t="inlineStr">
         <is>
-          <t>PHI</t>
+          <t>CHC</t>
         </is>
       </c>
       <c r="N53" t="inlineStr">
         <is>
-          <t>Matt Vierling</t>
+          <t>Elly De La Cruz</t>
         </is>
       </c>
       <c r="O53" t="n">
-        <v>663837</v>
+        <v>682829</v>
       </c>
       <c r="P53" t="inlineStr">
         <is>
-          <t>CF</t>
+          <t>SS</t>
         </is>
       </c>
       <c r="Q53" t="inlineStr">
@@ -6628,16 +6637,16 @@
         </is>
       </c>
       <c r="R53" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="S53" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="T53" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="U53" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="V53" t="n">
         <v>0</v>
@@ -6649,7 +6658,7 @@
         <v>0</v>
       </c>
       <c r="Y53" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Z53" t="n">
         <v>0</v>
@@ -6660,20 +6669,20 @@
       <c r="AB53" t="n">
         <v>0</v>
       </c>
-      <c r="AC53" t="n">
-        <v>0</v>
+      <c r="AC53" s="6" t="n">
+        <v>1</v>
       </c>
       <c r="AD53" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AE53" s="4" t="n">
         <v>13</v>
       </c>
       <c r="AF53" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AG53" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
     </row>
     <row r="54">
@@ -6684,15 +6693,15 @@
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>2026-07-11 08:19:16 PM PT</t>
+          <t>2026-07-11 08:21:17 PM PT</t>
         </is>
       </c>
       <c r="C54" t="n">
-        <v>823682</v>
+        <v>824249</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>11:10 AM PT</t>
+          <t>3:10 PM PT</t>
         </is>
       </c>
       <c r="E54" t="inlineStr">
@@ -6705,56 +6714,56 @@
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Top</t>
+          <t>Bottom</t>
         </is>
       </c>
       <c r="K54" t="inlineStr">
         <is>
-          <t>Away</t>
+          <t>Home</t>
         </is>
       </c>
       <c r="L54" t="inlineStr">
         <is>
-          <t>LAA</t>
+          <t>DET</t>
         </is>
       </c>
       <c r="M54" t="inlineStr">
         <is>
-          <t>MIN</t>
+          <t>PHI</t>
         </is>
       </c>
       <c r="N54" t="inlineStr">
         <is>
-          <t>Jorge Soler</t>
+          <t>Matt Vierling</t>
         </is>
       </c>
       <c r="O54" t="n">
-        <v>624585</v>
+        <v>663837</v>
       </c>
       <c r="P54" t="inlineStr">
         <is>
-          <t>DH</t>
+          <t>CF</t>
         </is>
       </c>
       <c r="Q54" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>1</t>
         </is>
       </c>
       <c r="R54" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="S54" t="n">
         <v>3</v>
       </c>
       <c r="T54" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="U54" t="n">
-        <v>0</v>
-      </c>
-      <c r="V54" s="7" t="n">
-        <v>1</v>
+        <v>3</v>
+      </c>
+      <c r="V54" t="n">
+        <v>0</v>
       </c>
       <c r="W54" t="n">
         <v>0</v>
@@ -6763,13 +6772,13 @@
         <v>0</v>
       </c>
       <c r="Y54" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Z54" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AA54" s="5" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AB54" t="n">
         <v>0</v>
@@ -6778,13 +6787,13 @@
         <v>0</v>
       </c>
       <c r="AD54" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AE54" s="4" t="n">
         <v>13</v>
       </c>
       <c r="AF54" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AG54" t="n">
         <v>10</v>
@@ -6798,7 +6807,7 @@
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>2026-07-11 08:19:16 PM PT</t>
+          <t>2026-07-11 08:21:16 PM PT</t>
         </is>
       </c>
       <c r="C55" t="n">
@@ -6839,57 +6848,57 @@
       </c>
       <c r="N55" t="inlineStr">
         <is>
-          <t>Wade Meckler</t>
+          <t>Jorge Soler</t>
         </is>
       </c>
       <c r="O55" t="n">
-        <v>685133</v>
+        <v>624585</v>
       </c>
       <c r="P55" t="inlineStr">
         <is>
-          <t>LF</t>
+          <t>DH</t>
         </is>
       </c>
       <c r="Q55" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>4</t>
         </is>
       </c>
       <c r="R55" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="S55" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="T55" t="n">
+        <v>1</v>
+      </c>
+      <c r="U55" t="n">
+        <v>0</v>
+      </c>
+      <c r="V55" s="7" t="n">
+        <v>1</v>
+      </c>
+      <c r="W55" t="n">
+        <v>0</v>
+      </c>
+      <c r="X55" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y55" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z55" t="n">
         <v>2</v>
       </c>
-      <c r="U55" t="n">
-        <v>1</v>
-      </c>
-      <c r="V55" s="7" t="n">
-        <v>1</v>
-      </c>
-      <c r="W55" t="n">
-        <v>0</v>
-      </c>
-      <c r="X55" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y55" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z55" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA55" t="n">
-        <v>0</v>
+      <c r="AA55" s="5" t="n">
+        <v>2</v>
       </c>
       <c r="AB55" t="n">
         <v>0</v>
       </c>
-      <c r="AC55" s="6" t="n">
-        <v>1</v>
+      <c r="AC55" t="n">
+        <v>0</v>
       </c>
       <c r="AD55" t="n">
         <v>1</v>
@@ -6912,7 +6921,7 @@
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>2026-07-11 08:19:16 PM PT</t>
+          <t>2026-07-11 08:21:16 PM PT</t>
         </is>
       </c>
       <c r="C56" t="n">
@@ -6938,48 +6947,48 @@
       </c>
       <c r="K56" t="inlineStr">
         <is>
-          <t>Home</t>
+          <t>Away</t>
         </is>
       </c>
       <c r="L56" t="inlineStr">
         <is>
+          <t>LAA</t>
+        </is>
+      </c>
+      <c r="M56" t="inlineStr">
+        <is>
           <t>MIN</t>
         </is>
       </c>
-      <c r="M56" t="inlineStr">
-        <is>
-          <t>LAA</t>
-        </is>
-      </c>
       <c r="N56" t="inlineStr">
         <is>
-          <t>Victor Caratini</t>
+          <t>Wade Meckler</t>
         </is>
       </c>
       <c r="O56" t="n">
-        <v>605170</v>
+        <v>685133</v>
       </c>
       <c r="P56" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>LF</t>
         </is>
       </c>
       <c r="Q56" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="R56" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="S56" t="n">
+        <v>4</v>
+      </c>
+      <c r="T56" t="n">
         <v>2</v>
       </c>
-      <c r="T56" t="n">
-        <v>1</v>
-      </c>
       <c r="U56" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="V56" s="7" t="n">
         <v>1</v>
@@ -6991,31 +7000,31 @@
         <v>0</v>
       </c>
       <c r="Y56" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="Z56" t="n">
-        <v>1</v>
-      </c>
-      <c r="AA56" s="5" t="n">
-        <v>1</v>
+        <v>0</v>
+      </c>
+      <c r="AA56" t="n">
+        <v>0</v>
       </c>
       <c r="AB56" t="n">
         <v>0</v>
       </c>
-      <c r="AC56" t="n">
-        <v>0</v>
+      <c r="AC56" s="6" t="n">
+        <v>1</v>
       </c>
       <c r="AD56" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AE56" s="4" t="n">
         <v>13</v>
       </c>
       <c r="AF56" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="AG56" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
     </row>
     <row r="57">
@@ -7026,15 +7035,15 @@
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>2026-07-11 08:19:17 PM PT</t>
+          <t>2026-07-11 08:21:16 PM PT</t>
         </is>
       </c>
       <c r="C57" t="n">
-        <v>824249</v>
+        <v>823682</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>3:10 PM PT</t>
+          <t>11:10 AM PT</t>
         </is>
       </c>
       <c r="E57" t="inlineStr">
@@ -7047,35 +7056,35 @@
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Bottom</t>
+          <t>Top</t>
         </is>
       </c>
       <c r="K57" t="inlineStr">
         <is>
-          <t>Away</t>
+          <t>Home</t>
         </is>
       </c>
       <c r="L57" t="inlineStr">
         <is>
-          <t>PHI</t>
+          <t>MIN</t>
         </is>
       </c>
       <c r="M57" t="inlineStr">
         <is>
-          <t>DET</t>
+          <t>LAA</t>
         </is>
       </c>
       <c r="N57" t="inlineStr">
         <is>
-          <t>Bryson Stott</t>
+          <t>Victor Caratini</t>
         </is>
       </c>
       <c r="O57" t="n">
-        <v>681082</v>
+        <v>605170</v>
       </c>
       <c r="P57" t="inlineStr">
         <is>
-          <t>2B</t>
+          <t>C</t>
         </is>
       </c>
       <c r="Q57" t="inlineStr">
@@ -7084,52 +7093,52 @@
         </is>
       </c>
       <c r="R57" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="S57" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="T57" t="n">
+        <v>1</v>
+      </c>
+      <c r="U57" t="n">
+        <v>0</v>
+      </c>
+      <c r="V57" s="7" t="n">
+        <v>1</v>
+      </c>
+      <c r="W57" t="n">
+        <v>0</v>
+      </c>
+      <c r="X57" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y57" t="n">
         <v>2</v>
       </c>
-      <c r="U57" t="n">
-        <v>2</v>
-      </c>
-      <c r="V57" t="n">
-        <v>0</v>
-      </c>
-      <c r="W57" t="n">
-        <v>0</v>
-      </c>
-      <c r="X57" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y57" t="n">
-        <v>1</v>
-      </c>
       <c r="Z57" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA57" t="n">
-        <v>0</v>
+        <v>1</v>
+      </c>
+      <c r="AA57" s="5" t="n">
+        <v>1</v>
       </c>
       <c r="AB57" t="n">
         <v>0</v>
       </c>
-      <c r="AC57" s="6" t="n">
-        <v>1</v>
+      <c r="AC57" t="n">
+        <v>0</v>
       </c>
       <c r="AD57" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AE57" s="4" t="n">
         <v>13</v>
       </c>
       <c r="AF57" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="AG57" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
     </row>
     <row r="58">
@@ -7140,15 +7149,15 @@
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>2026-07-11 08:19:17 PM PT</t>
+          <t>2026-07-11 08:21:17 PM PT</t>
         </is>
       </c>
       <c r="C58" t="n">
-        <v>823603</v>
+        <v>824249</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>1:10 PM PT</t>
+          <t>3:10 PM PT</t>
         </is>
       </c>
       <c r="E58" t="inlineStr">
@@ -7171,37 +7180,37 @@
       </c>
       <c r="L58" t="inlineStr">
         <is>
-          <t>BOS</t>
+          <t>PHI</t>
         </is>
       </c>
       <c r="M58" t="inlineStr">
         <is>
-          <t>NYM</t>
+          <t>DET</t>
         </is>
       </c>
       <c r="N58" t="inlineStr">
         <is>
-          <t>Caleb Durbin</t>
+          <t>Bryson Stott</t>
         </is>
       </c>
       <c r="O58" t="n">
-        <v>702332</v>
+        <v>681082</v>
       </c>
       <c r="P58" t="inlineStr">
         <is>
-          <t>3B</t>
+          <t>2B</t>
         </is>
       </c>
       <c r="Q58" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>6</t>
         </is>
       </c>
       <c r="R58" t="n">
         <v>4</v>
       </c>
       <c r="S58" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="T58" t="n">
         <v>2</v>
@@ -7219,31 +7228,31 @@
         <v>0</v>
       </c>
       <c r="Y58" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="Z58" t="n">
         <v>0</v>
       </c>
-      <c r="AA58" s="5" t="n">
-        <v>1</v>
+      <c r="AA58" t="n">
+        <v>0</v>
       </c>
       <c r="AB58" t="n">
         <v>0</v>
       </c>
-      <c r="AC58" t="n">
-        <v>0</v>
+      <c r="AC58" s="6" t="n">
+        <v>1</v>
       </c>
       <c r="AD58" t="n">
         <v>1</v>
       </c>
       <c r="AE58" s="4" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="AF58" t="n">
         <v>4</v>
       </c>
       <c r="AG58" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
     </row>
     <row r="59">
@@ -7254,15 +7263,15 @@
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>2026-07-11 08:19:16 PM PT</t>
+          <t>2026-07-11 08:21:17 PM PT</t>
         </is>
       </c>
       <c r="C59" t="n">
-        <v>823682</v>
+        <v>823603</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>11:10 AM PT</t>
+          <t>1:10 PM PT</t>
         </is>
       </c>
       <c r="E59" t="inlineStr">
@@ -7275,7 +7284,7 @@
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Top</t>
+          <t>Bottom</t>
         </is>
       </c>
       <c r="K59" t="inlineStr">
@@ -7285,46 +7294,46 @@
       </c>
       <c r="L59" t="inlineStr">
         <is>
-          <t>LAA</t>
+          <t>BOS</t>
         </is>
       </c>
       <c r="M59" t="inlineStr">
         <is>
-          <t>MIN</t>
+          <t>NYM</t>
         </is>
       </c>
       <c r="N59" t="inlineStr">
         <is>
-          <t>Nolan Schanuel</t>
+          <t>Caleb Durbin</t>
         </is>
       </c>
       <c r="O59" t="n">
-        <v>694384</v>
+        <v>702332</v>
       </c>
       <c r="P59" t="inlineStr">
         <is>
-          <t>1B</t>
+          <t>3B</t>
         </is>
       </c>
       <c r="Q59" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="R59" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="S59" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="T59" t="n">
         <v>2</v>
       </c>
       <c r="U59" t="n">
-        <v>1</v>
-      </c>
-      <c r="V59" s="7" t="n">
-        <v>1</v>
+        <v>2</v>
+      </c>
+      <c r="V59" t="n">
+        <v>0</v>
       </c>
       <c r="W59" t="n">
         <v>0</v>
@@ -7333,10 +7342,10 @@
         <v>0</v>
       </c>
       <c r="Y59" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="Z59" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AA59" s="5" t="n">
         <v>1</v>
@@ -7348,16 +7357,16 @@
         <v>0</v>
       </c>
       <c r="AD59" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AE59" s="4" t="n">
         <v>12</v>
       </c>
       <c r="AF59" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="AG59" t="n">
-        <v>10</v>
+        <v>6</v>
       </c>
     </row>
     <row r="60">
@@ -7368,15 +7377,15 @@
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>2026-07-11 08:19:16 PM PT</t>
+          <t>2026-07-11 08:21:16 PM PT</t>
         </is>
       </c>
       <c r="C60" t="n">
-        <v>823357</v>
+        <v>823682</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>9:05 AM PT</t>
+          <t>11:10 AM PT</t>
         </is>
       </c>
       <c r="E60" t="inlineStr">
@@ -7399,37 +7408,37 @@
       </c>
       <c r="L60" t="inlineStr">
         <is>
-          <t>MIL</t>
+          <t>LAA</t>
         </is>
       </c>
       <c r="M60" t="inlineStr">
         <is>
-          <t>PIT</t>
+          <t>MIN</t>
         </is>
       </c>
       <c r="N60" t="inlineStr">
         <is>
-          <t>William Contreras</t>
+          <t>Nolan Schanuel</t>
         </is>
       </c>
       <c r="O60" t="n">
-        <v>661388</v>
+        <v>694384</v>
       </c>
       <c r="P60" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>1B</t>
         </is>
       </c>
       <c r="Q60" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>3</t>
         </is>
       </c>
       <c r="R60" t="n">
         <v>5</v>
       </c>
       <c r="S60" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="T60" t="n">
         <v>2</v>
@@ -7447,13 +7456,13 @@
         <v>0</v>
       </c>
       <c r="Y60" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Z60" t="n">
         <v>1</v>
       </c>
-      <c r="AA60" t="n">
-        <v>0</v>
+      <c r="AA60" s="5" t="n">
+        <v>1</v>
       </c>
       <c r="AB60" t="n">
         <v>0</v>
@@ -7462,16 +7471,16 @@
         <v>0</v>
       </c>
       <c r="AD60" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AE60" s="4" t="n">
         <v>12</v>
       </c>
       <c r="AF60" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="AG60" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
     </row>
     <row r="61">
@@ -7482,7 +7491,7 @@
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>2026-07-11 08:19:16 PM PT</t>
+          <t>2026-07-11 08:21:16 PM PT</t>
         </is>
       </c>
       <c r="C61" t="n">
@@ -7523,27 +7532,27 @@
       </c>
       <c r="N61" t="inlineStr">
         <is>
-          <t>Cooper Pratt</t>
+          <t>William Contreras</t>
         </is>
       </c>
       <c r="O61" t="n">
-        <v>806198</v>
+        <v>661388</v>
       </c>
       <c r="P61" t="inlineStr">
         <is>
-          <t>SS</t>
+          <t>C</t>
         </is>
       </c>
       <c r="Q61" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>4</t>
         </is>
       </c>
       <c r="R61" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="S61" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="T61" t="n">
         <v>2</v>
@@ -7596,38 +7605,29 @@
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>2026-07-11 08:19:18 PM PT</t>
+          <t>2026-07-11 08:21:16 PM PT</t>
         </is>
       </c>
       <c r="C62" t="n">
-        <v>823276</v>
+        <v>823357</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>5:40 PM PT</t>
+          <t>9:05 AM PT</t>
         </is>
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>Bottom 7 | 2 out</t>
+          <t>Final</t>
         </is>
       </c>
       <c r="F62" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Bottom</t>
-        </is>
-      </c>
-      <c r="H62" t="n">
-        <v>2</v>
-      </c>
-      <c r="I62" t="n">
-        <v>3</v>
-      </c>
-      <c r="J62" t="n">
-        <v>2</v>
+          <t>Top</t>
+        </is>
       </c>
       <c r="K62" t="inlineStr">
         <is>
@@ -7636,25 +7636,25 @@
       </c>
       <c r="L62" t="inlineStr">
         <is>
-          <t>TOR</t>
+          <t>MIL</t>
         </is>
       </c>
       <c r="M62" t="inlineStr">
         <is>
-          <t>SD</t>
+          <t>PIT</t>
         </is>
       </c>
       <c r="N62" t="inlineStr">
         <is>
-          <t>Alejandro Kirk</t>
+          <t>Cooper Pratt</t>
         </is>
       </c>
       <c r="O62" t="n">
-        <v>672386</v>
+        <v>806198</v>
       </c>
       <c r="P62" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>SS</t>
         </is>
       </c>
       <c r="Q62" t="inlineStr">
@@ -7699,16 +7699,16 @@
         <v>0</v>
       </c>
       <c r="AD62" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AE62" s="4" t="n">
         <v>12</v>
       </c>
       <c r="AF62" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="AG62" t="n">
-        <v>6</v>
+        <v>9</v>
       </c>
     </row>
     <row r="63">
@@ -7719,20 +7719,20 @@
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>2026-07-11 08:19:18 PM PT</t>
+          <t>2026-07-11 08:21:18 PM PT</t>
         </is>
       </c>
       <c r="C63" t="n">
-        <v>823926</v>
+        <v>823276</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>6:10 PM PT</t>
+          <t>5:40 PM PT</t>
         </is>
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>Top 7 | 1 out</t>
+          <t>Bottom 7 | 3 out</t>
         </is>
       </c>
       <c r="F63" t="n">
@@ -7740,17 +7740,17 @@
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Top</t>
+          <t>Bottom</t>
         </is>
       </c>
       <c r="H63" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="I63" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="J63" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="K63" t="inlineStr">
         <is>
@@ -7759,46 +7759,46 @@
       </c>
       <c r="L63" t="inlineStr">
         <is>
-          <t>ARI</t>
+          <t>TOR</t>
         </is>
       </c>
       <c r="M63" t="inlineStr">
         <is>
-          <t>LAD</t>
+          <t>SD</t>
         </is>
       </c>
       <c r="N63" t="inlineStr">
         <is>
-          <t>Geraldo Perdomo</t>
+          <t>Alejandro Kirk</t>
         </is>
       </c>
       <c r="O63" t="n">
-        <v>672695</v>
+        <v>672386</v>
       </c>
       <c r="P63" t="inlineStr">
         <is>
-          <t>SS</t>
+          <t>C</t>
         </is>
       </c>
       <c r="Q63" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>7</t>
         </is>
       </c>
       <c r="R63" t="n">
         <v>4</v>
       </c>
       <c r="S63" t="n">
+        <v>4</v>
+      </c>
+      <c r="T63" t="n">
         <v>2</v>
       </c>
-      <c r="T63" t="n">
-        <v>0</v>
-      </c>
       <c r="U63" t="n">
-        <v>0</v>
-      </c>
-      <c r="V63" t="n">
-        <v>0</v>
+        <v>1</v>
+      </c>
+      <c r="V63" s="7" t="n">
+        <v>1</v>
       </c>
       <c r="W63" t="n">
         <v>0</v>
@@ -7810,28 +7810,28 @@
         <v>1</v>
       </c>
       <c r="Z63" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA63" s="5" t="n">
-        <v>1</v>
-      </c>
-      <c r="AB63" s="9" t="n">
-        <v>1</v>
-      </c>
-      <c r="AC63" s="6" t="n">
-        <v>1</v>
+        <v>1</v>
+      </c>
+      <c r="AA63" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB63" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC63" t="n">
+        <v>0</v>
       </c>
       <c r="AD63" t="n">
         <v>0</v>
       </c>
       <c r="AE63" s="4" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="AF63" t="n">
+        <v>7</v>
+      </c>
+      <c r="AG63" t="n">
         <v>6</v>
-      </c>
-      <c r="AG63" t="n">
-        <v>5</v>
       </c>
     </row>
     <row r="64">
@@ -7842,7 +7842,7 @@
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>2026-07-11 08:19:18 PM PT</t>
+          <t>2026-07-11 08:21:18 PM PT</t>
         </is>
       </c>
       <c r="C64" t="n">
@@ -7855,7 +7855,7 @@
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>Top 7 | 1 out</t>
+          <t>Top 7 | 2 out</t>
         </is>
       </c>
       <c r="F64" t="n">
@@ -7867,7 +7867,7 @@
         </is>
       </c>
       <c r="H64" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I64" t="n">
         <v>0</v>
@@ -7951,7 +7951,7 @@
         <v>11</v>
       </c>
       <c r="AF64" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AG64" t="n">
         <v>5</v>
@@ -7965,7 +7965,7 @@
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>2026-07-11 08:19:17 PM PT</t>
+          <t>2026-07-11 08:21:16 PM PT</t>
         </is>
       </c>
       <c r="C65" t="n">
@@ -8079,7 +8079,7 @@
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>2026-07-11 08:19:17 PM PT</t>
+          <t>2026-07-11 08:21:17 PM PT</t>
         </is>
       </c>
       <c r="C66" t="n">
@@ -8193,7 +8193,7 @@
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>2026-07-11 08:19:18 PM PT</t>
+          <t>2026-07-11 08:21:18 PM PT</t>
         </is>
       </c>
       <c r="C67" t="n">
@@ -8206,7 +8206,7 @@
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>Bottom 7 | 2 out</t>
+          <t>Bottom 7 | 3 out</t>
         </is>
       </c>
       <c r="F67" t="n">
@@ -8218,13 +8218,13 @@
         </is>
       </c>
       <c r="H67" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="I67" t="n">
         <v>3</v>
       </c>
       <c r="J67" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="K67" t="inlineStr">
         <is>
@@ -8316,7 +8316,7 @@
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>2026-07-11 08:19:17 PM PT</t>
+          <t>2026-07-11 08:21:17 PM PT</t>
         </is>
       </c>
       <c r="C68" t="n">
@@ -8430,7 +8430,7 @@
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>2026-07-11 08:19:17 PM PT</t>
+          <t>2026-07-11 08:21:16 PM PT</t>
         </is>
       </c>
       <c r="C69" t="n">
@@ -8544,7 +8544,7 @@
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>2026-07-11 08:19:16 PM PT</t>
+          <t>2026-07-11 08:21:16 PM PT</t>
         </is>
       </c>
       <c r="C70" t="n">
@@ -8658,7 +8658,7 @@
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>2026-07-11 08:19:18 PM PT</t>
+          <t>2026-07-11 08:21:18 PM PT</t>
         </is>
       </c>
       <c r="C71" t="n">
@@ -8671,7 +8671,7 @@
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>Top 7 | 1 out</t>
+          <t>Top 7 | 2 out</t>
         </is>
       </c>
       <c r="F71" t="n">
@@ -8683,7 +8683,7 @@
         </is>
       </c>
       <c r="H71" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I71" t="n">
         <v>0</v>
@@ -8781,7 +8781,7 @@
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>2026-07-11 08:19:16 PM PT</t>
+          <t>2026-07-11 08:21:16 PM PT</t>
         </is>
       </c>
       <c r="C72" t="n">
@@ -8895,7 +8895,7 @@
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>2026-07-11 08:19:17 PM PT</t>
+          <t>2026-07-11 08:21:17 PM PT</t>
         </is>
       </c>
       <c r="C73" t="n">
@@ -9009,7 +9009,7 @@
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>2026-07-11 08:19:16 PM PT</t>
+          <t>2026-07-11 08:21:16 PM PT</t>
         </is>
       </c>
       <c r="C74" t="n">
@@ -9123,7 +9123,7 @@
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>2026-07-11 08:19:18 PM PT</t>
+          <t>2026-07-11 08:21:18 PM PT</t>
         </is>
       </c>
       <c r="C75" t="n">
@@ -9136,7 +9136,7 @@
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>Bottom 7 | 2 out</t>
+          <t>Bottom 7 | 3 out</t>
         </is>
       </c>
       <c r="F75" t="n">
@@ -9148,13 +9148,13 @@
         </is>
       </c>
       <c r="H75" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="I75" t="n">
         <v>3</v>
       </c>
       <c r="J75" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="K75" t="inlineStr">
         <is>
@@ -9246,7 +9246,7 @@
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>2026-07-11 08:19:17 PM PT</t>
+          <t>2026-07-11 08:21:18 PM PT</t>
         </is>
       </c>
       <c r="C76" t="n">
@@ -9360,7 +9360,7 @@
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>2026-07-11 08:19:17 PM PT</t>
+          <t>2026-07-11 08:21:18 PM PT</t>
         </is>
       </c>
       <c r="C77" t="n">
@@ -9474,7 +9474,7 @@
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>2026-07-11 08:19:17 PM PT</t>
+          <t>2026-07-11 08:21:17 PM PT</t>
         </is>
       </c>
       <c r="C78" t="n">
@@ -9588,7 +9588,7 @@
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>2026-07-11 08:19:16 PM PT</t>
+          <t>2026-07-11 08:21:16 PM PT</t>
         </is>
       </c>
       <c r="C79" t="n">
@@ -9702,7 +9702,7 @@
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>2026-07-11 08:19:16 PM PT</t>
+          <t>2026-07-11 08:21:16 PM PT</t>
         </is>
       </c>
       <c r="C80" t="n">
@@ -9816,7 +9816,7 @@
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>2026-07-11 08:19:16 PM PT</t>
+          <t>2026-07-11 08:21:16 PM PT</t>
         </is>
       </c>
       <c r="C81" t="n">
@@ -9930,7 +9930,7 @@
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>2026-07-11 08:19:16 PM PT</t>
+          <t>2026-07-11 08:21:16 PM PT</t>
         </is>
       </c>
       <c r="C82" t="n">
@@ -10044,7 +10044,7 @@
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>2026-07-11 08:19:16 PM PT</t>
+          <t>2026-07-11 08:21:16 PM PT</t>
         </is>
       </c>
       <c r="C83" t="n">
@@ -10158,7 +10158,7 @@
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>2026-07-11 08:19:16 PM PT</t>
+          <t>2026-07-11 08:21:16 PM PT</t>
         </is>
       </c>
       <c r="C84" t="n">
@@ -10272,7 +10272,7 @@
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>2026-07-11 08:19:17 PM PT</t>
+          <t>2026-07-11 08:21:16 PM PT</t>
         </is>
       </c>
       <c r="C85" t="n">
@@ -10386,7 +10386,7 @@
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>2026-07-11 08:19:17 PM PT</t>
+          <t>2026-07-11 08:21:16 PM PT</t>
         </is>
       </c>
       <c r="C86" t="n">
@@ -10500,7 +10500,7 @@
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>2026-07-11 08:19:17 PM PT</t>
+          <t>2026-07-11 08:21:17 PM PT</t>
         </is>
       </c>
       <c r="C87" t="n">
@@ -10614,7 +10614,7 @@
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>2026-07-11 08:19:17 PM PT</t>
+          <t>2026-07-11 08:21:17 PM PT</t>
         </is>
       </c>
       <c r="C88" t="n">
@@ -10728,7 +10728,7 @@
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>2026-07-11 08:19:18 PM PT</t>
+          <t>2026-07-11 08:21:18 PM PT</t>
         </is>
       </c>
       <c r="C89" t="n">
@@ -10741,7 +10741,7 @@
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>Bottom 7 | 2 out</t>
+          <t>Bottom 7 | 3 out</t>
         </is>
       </c>
       <c r="F89" t="n">
@@ -10753,13 +10753,13 @@
         </is>
       </c>
       <c r="H89" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="I89" t="n">
         <v>3</v>
       </c>
       <c r="J89" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="K89" t="inlineStr">
         <is>
@@ -10851,7 +10851,7 @@
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>2026-07-11 08:19:17 PM PT</t>
+          <t>2026-07-11 08:21:17 PM PT</t>
         </is>
       </c>
       <c r="C90" t="n">
@@ -10965,7 +10965,7 @@
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>2026-07-11 08:19:17 PM PT</t>
+          <t>2026-07-11 08:21:18 PM PT</t>
         </is>
       </c>
       <c r="C91" t="n">
@@ -11079,29 +11079,38 @@
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>2026-07-11 08:19:17 PM PT</t>
+          <t>2026-07-11 08:21:18 PM PT</t>
         </is>
       </c>
       <c r="C92" t="n">
-        <v>823844</v>
+        <v>823926</v>
       </c>
       <c r="D92" t="inlineStr">
         <is>
-          <t>1:10 PM PT</t>
+          <t>6:10 PM PT</t>
         </is>
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>Final</t>
+          <t>Top 7 | 2 out</t>
         </is>
       </c>
       <c r="F92" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>Bottom</t>
-        </is>
+          <t>Top</t>
+        </is>
+      </c>
+      <c r="H92" t="n">
+        <v>2</v>
+      </c>
+      <c r="I92" t="n">
+        <v>0</v>
+      </c>
+      <c r="J92" t="n">
+        <v>0</v>
       </c>
       <c r="K92" t="inlineStr">
         <is>
@@ -11110,37 +11119,37 @@
       </c>
       <c r="L92" t="inlineStr">
         <is>
-          <t>CLE</t>
+          <t>ARI</t>
         </is>
       </c>
       <c r="M92" t="inlineStr">
         <is>
-          <t>MIA</t>
+          <t>LAD</t>
         </is>
       </c>
       <c r="N92" t="inlineStr">
         <is>
-          <t>Kyle Manzardo</t>
+          <t>Max Kepler</t>
         </is>
       </c>
       <c r="O92" t="n">
-        <v>700932</v>
+        <v>596146</v>
       </c>
       <c r="P92" t="inlineStr">
         <is>
-          <t>1B</t>
+          <t>LF</t>
         </is>
       </c>
       <c r="Q92" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="R92" t="n">
         <v>4</v>
       </c>
       <c r="S92" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="T92" t="n">
         <v>1</v>
@@ -11158,16 +11167,16 @@
         <v>0</v>
       </c>
       <c r="Y92" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Z92" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AA92" t="n">
         <v>0</v>
       </c>
-      <c r="AB92" s="9" t="n">
-        <v>1</v>
+      <c r="AB92" t="n">
+        <v>0</v>
       </c>
       <c r="AC92" t="n">
         <v>0</v>
@@ -11179,10 +11188,10 @@
         <v>7</v>
       </c>
       <c r="AF92" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="AG92" t="n">
-        <v>11</v>
+        <v>5</v>
       </c>
     </row>
     <row r="93">
@@ -11193,7 +11202,7 @@
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>2026-07-11 08:19:17 PM PT</t>
+          <t>2026-07-11 08:21:17 PM PT</t>
         </is>
       </c>
       <c r="C93" t="n">
@@ -11234,36 +11243,36 @@
       </c>
       <c r="N93" t="inlineStr">
         <is>
-          <t>Kahlil Watson</t>
+          <t>Kyle Manzardo</t>
         </is>
       </c>
       <c r="O93" t="n">
-        <v>696135</v>
+        <v>700932</v>
       </c>
       <c r="P93" t="inlineStr">
         <is>
-          <t>RF</t>
+          <t>1B</t>
         </is>
       </c>
       <c r="Q93" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>4</t>
         </is>
       </c>
       <c r="R93" t="n">
         <v>4</v>
       </c>
       <c r="S93" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="T93" t="n">
         <v>1</v>
       </c>
       <c r="U93" t="n">
-        <v>0</v>
-      </c>
-      <c r="V93" s="7" t="n">
-        <v>1</v>
+        <v>1</v>
+      </c>
+      <c r="V93" t="n">
+        <v>0</v>
       </c>
       <c r="W93" t="n">
         <v>0</v>
@@ -11280,8 +11289,8 @@
       <c r="AA93" t="n">
         <v>0</v>
       </c>
-      <c r="AB93" t="n">
-        <v>0</v>
+      <c r="AB93" s="9" t="n">
+        <v>1</v>
       </c>
       <c r="AC93" t="n">
         <v>0</v>
@@ -11307,15 +11316,15 @@
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>2026-07-11 08:19:17 PM PT</t>
+          <t>2026-07-11 08:21:17 PM PT</t>
         </is>
       </c>
       <c r="C94" t="n">
-        <v>823198</v>
+        <v>823844</v>
       </c>
       <c r="D94" t="inlineStr">
         <is>
-          <t>1:05 PM PT</t>
+          <t>1:10 PM PT</t>
         </is>
       </c>
       <c r="E94" t="inlineStr">
@@ -11328,7 +11337,7 @@
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>Top</t>
+          <t>Bottom</t>
         </is>
       </c>
       <c r="K94" t="inlineStr">
@@ -11338,37 +11347,37 @@
       </c>
       <c r="L94" t="inlineStr">
         <is>
-          <t>COL</t>
+          <t>CLE</t>
         </is>
       </c>
       <c r="M94" t="inlineStr">
         <is>
-          <t>SF</t>
+          <t>MIA</t>
         </is>
       </c>
       <c r="N94" t="inlineStr">
         <is>
-          <t>Brett Sullivan</t>
+          <t>Kahlil Watson</t>
         </is>
       </c>
       <c r="O94" t="n">
-        <v>664954</v>
+        <v>696135</v>
       </c>
       <c r="P94" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>RF</t>
         </is>
       </c>
       <c r="Q94" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>5</t>
         </is>
       </c>
       <c r="R94" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="S94" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="T94" t="n">
         <v>1</v>
@@ -11401,16 +11410,16 @@
         <v>0</v>
       </c>
       <c r="AD94" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AE94" s="4" t="n">
         <v>7</v>
       </c>
       <c r="AF94" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="AG94" t="n">
-        <v>6</v>
+        <v>11</v>
       </c>
     </row>
     <row r="95">
@@ -11421,15 +11430,15 @@
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>2026-07-11 08:19:17 PM PT</t>
+          <t>2026-07-11 08:21:17 PM PT</t>
         </is>
       </c>
       <c r="C95" t="n">
-        <v>822875</v>
+        <v>823198</v>
       </c>
       <c r="D95" t="inlineStr">
         <is>
-          <t>4:05 PM PT</t>
+          <t>1:05 PM PT</t>
         </is>
       </c>
       <c r="E95" t="inlineStr">
@@ -11442,7 +11451,7 @@
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>Bottom</t>
+          <t>Top</t>
         </is>
       </c>
       <c r="K95" t="inlineStr">
@@ -11452,46 +11461,46 @@
       </c>
       <c r="L95" t="inlineStr">
         <is>
-          <t>HOU</t>
+          <t>COL</t>
         </is>
       </c>
       <c r="M95" t="inlineStr">
         <is>
-          <t>TEX</t>
+          <t>SF</t>
         </is>
       </c>
       <c r="N95" t="inlineStr">
         <is>
-          <t>Jeremy Peña</t>
+          <t>Brett Sullivan</t>
         </is>
       </c>
       <c r="O95" t="n">
-        <v>665161</v>
+        <v>664954</v>
       </c>
       <c r="P95" t="inlineStr">
         <is>
-          <t>SS</t>
+          <t>C</t>
         </is>
       </c>
       <c r="Q95" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>9</t>
         </is>
       </c>
       <c r="R95" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="S95" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="T95" t="n">
         <v>1</v>
       </c>
       <c r="U95" t="n">
-        <v>1</v>
-      </c>
-      <c r="V95" t="n">
-        <v>0</v>
+        <v>0</v>
+      </c>
+      <c r="V95" s="7" t="n">
+        <v>1</v>
       </c>
       <c r="W95" t="n">
         <v>0</v>
@@ -11508,8 +11517,8 @@
       <c r="AA95" t="n">
         <v>0</v>
       </c>
-      <c r="AB95" s="9" t="n">
-        <v>1</v>
+      <c r="AB95" t="n">
+        <v>0</v>
       </c>
       <c r="AC95" t="n">
         <v>0</v>
@@ -11521,10 +11530,10 @@
         <v>7</v>
       </c>
       <c r="AF95" t="n">
-        <v>9</v>
+        <v>2</v>
       </c>
       <c r="AG95" t="n">
-        <v>10</v>
+        <v>6</v>
       </c>
     </row>
     <row r="96">
@@ -11535,7 +11544,7 @@
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>2026-07-11 08:19:17 PM PT</t>
+          <t>2026-07-11 08:21:18 PM PT</t>
         </is>
       </c>
       <c r="C96" t="n">
@@ -11576,36 +11585,36 @@
       </c>
       <c r="N96" t="inlineStr">
         <is>
-          <t>Christian Walker</t>
+          <t>Jeremy Peña</t>
         </is>
       </c>
       <c r="O96" t="n">
-        <v>572233</v>
+        <v>665161</v>
       </c>
       <c r="P96" t="inlineStr">
         <is>
-          <t>1B</t>
+          <t>SS</t>
         </is>
       </c>
       <c r="Q96" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>1</t>
         </is>
       </c>
       <c r="R96" t="n">
         <v>5</v>
       </c>
       <c r="S96" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="T96" t="n">
         <v>1</v>
       </c>
       <c r="U96" t="n">
-        <v>0</v>
-      </c>
-      <c r="V96" s="7" t="n">
-        <v>1</v>
+        <v>1</v>
+      </c>
+      <c r="V96" t="n">
+        <v>0</v>
       </c>
       <c r="W96" t="n">
         <v>0</v>
@@ -11622,14 +11631,14 @@
       <c r="AA96" t="n">
         <v>0</v>
       </c>
-      <c r="AB96" t="n">
-        <v>0</v>
+      <c r="AB96" s="9" t="n">
+        <v>1</v>
       </c>
       <c r="AC96" t="n">
         <v>0</v>
       </c>
       <c r="AD96" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="AE96" s="4" t="n">
         <v>7</v>
@@ -11649,77 +11658,68 @@
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>2026-07-11 08:19:18 PM PT</t>
+          <t>2026-07-11 08:21:18 PM PT</t>
         </is>
       </c>
       <c r="C97" t="n">
-        <v>823926</v>
+        <v>822875</v>
       </c>
       <c r="D97" t="inlineStr">
         <is>
-          <t>6:10 PM PT</t>
+          <t>4:05 PM PT</t>
         </is>
       </c>
       <c r="E97" t="inlineStr">
         <is>
-          <t>Top 7 | 1 out</t>
+          <t>Final</t>
         </is>
       </c>
       <c r="F97" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>Top</t>
-        </is>
-      </c>
-      <c r="H97" t="n">
-        <v>1</v>
-      </c>
-      <c r="I97" t="n">
-        <v>0</v>
-      </c>
-      <c r="J97" t="n">
-        <v>0</v>
+          <t>Bottom</t>
+        </is>
       </c>
       <c r="K97" t="inlineStr">
         <is>
-          <t>Home</t>
+          <t>Away</t>
         </is>
       </c>
       <c r="L97" t="inlineStr">
         <is>
-          <t>LAD</t>
+          <t>HOU</t>
         </is>
       </c>
       <c r="M97" t="inlineStr">
         <is>
-          <t>ARI</t>
+          <t>TEX</t>
         </is>
       </c>
       <c r="N97" t="inlineStr">
         <is>
-          <t>Tommy Edman</t>
+          <t>Christian Walker</t>
         </is>
       </c>
       <c r="O97" t="n">
-        <v>669242</v>
+        <v>572233</v>
       </c>
       <c r="P97" t="inlineStr">
         <is>
-          <t>2B</t>
+          <t>1B</t>
         </is>
       </c>
       <c r="Q97" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>4</t>
         </is>
       </c>
       <c r="R97" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="S97" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="T97" t="n">
         <v>1</v>
@@ -11752,16 +11752,16 @@
         <v>0</v>
       </c>
       <c r="AD97" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="AE97" s="4" t="n">
         <v>7</v>
       </c>
       <c r="AF97" t="n">
-        <v>2</v>
+        <v>9</v>
       </c>
       <c r="AG97" t="n">
-        <v>6</v>
+        <v>10</v>
       </c>
     </row>
     <row r="98">
@@ -11772,29 +11772,38 @@
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>2026-07-11 08:19:17 PM PT</t>
+          <t>2026-07-11 08:21:18 PM PT</t>
         </is>
       </c>
       <c r="C98" t="n">
-        <v>823844</v>
+        <v>823926</v>
       </c>
       <c r="D98" t="inlineStr">
         <is>
-          <t>1:10 PM PT</t>
+          <t>6:10 PM PT</t>
         </is>
       </c>
       <c r="E98" t="inlineStr">
         <is>
-          <t>Final</t>
+          <t>Top 7 | 2 out</t>
         </is>
       </c>
       <c r="F98" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>Bottom</t>
-        </is>
+          <t>Top</t>
+        </is>
+      </c>
+      <c r="H98" t="n">
+        <v>2</v>
+      </c>
+      <c r="I98" t="n">
+        <v>0</v>
+      </c>
+      <c r="J98" t="n">
+        <v>0</v>
       </c>
       <c r="K98" t="inlineStr">
         <is>
@@ -11803,37 +11812,37 @@
       </c>
       <c r="L98" t="inlineStr">
         <is>
-          <t>MIA</t>
+          <t>LAD</t>
         </is>
       </c>
       <c r="M98" t="inlineStr">
         <is>
-          <t>CLE</t>
+          <t>ARI</t>
         </is>
       </c>
       <c r="N98" t="inlineStr">
         <is>
-          <t>Joe Mack</t>
+          <t>Tommy Edman</t>
         </is>
       </c>
       <c r="O98" t="n">
-        <v>691788</v>
+        <v>669242</v>
       </c>
       <c r="P98" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>2B</t>
         </is>
       </c>
       <c r="Q98" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>9</t>
         </is>
       </c>
       <c r="R98" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="S98" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="T98" t="n">
         <v>1</v>
@@ -11866,16 +11875,16 @@
         <v>0</v>
       </c>
       <c r="AD98" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AE98" s="4" t="n">
         <v>7</v>
       </c>
       <c r="AF98" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AG98" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
     </row>
     <row r="99">
@@ -11886,15 +11895,15 @@
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>2026-07-11 08:19:16 PM PT</t>
+          <t>2026-07-11 08:21:17 PM PT</t>
         </is>
       </c>
       <c r="C99" t="n">
-        <v>823356</v>
+        <v>823844</v>
       </c>
       <c r="D99" t="inlineStr">
         <is>
-          <t>1:05 PM PT</t>
+          <t>1:10 PM PT</t>
         </is>
       </c>
       <c r="E99" t="inlineStr">
@@ -11907,56 +11916,56 @@
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>Top</t>
+          <t>Bottom</t>
         </is>
       </c>
       <c r="K99" t="inlineStr">
         <is>
-          <t>Away</t>
+          <t>Home</t>
         </is>
       </c>
       <c r="L99" t="inlineStr">
         <is>
-          <t>MIL</t>
+          <t>MIA</t>
         </is>
       </c>
       <c r="M99" t="inlineStr">
         <is>
-          <t>PIT</t>
+          <t>CLE</t>
         </is>
       </c>
       <c r="N99" t="inlineStr">
         <is>
-          <t>Christian Yelich</t>
+          <t>Joe Mack</t>
         </is>
       </c>
       <c r="O99" t="n">
-        <v>592885</v>
+        <v>691788</v>
       </c>
       <c r="P99" t="inlineStr">
         <is>
-          <t>DH</t>
+          <t>C</t>
         </is>
       </c>
       <c r="Q99" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>8</t>
         </is>
       </c>
       <c r="R99" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="S99" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="T99" t="n">
         <v>1</v>
       </c>
       <c r="U99" t="n">
-        <v>1</v>
-      </c>
-      <c r="V99" t="n">
-        <v>0</v>
+        <v>0</v>
+      </c>
+      <c r="V99" s="7" t="n">
+        <v>1</v>
       </c>
       <c r="W99" t="n">
         <v>0</v>
@@ -11965,28 +11974,28 @@
         <v>0</v>
       </c>
       <c r="Y99" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Z99" t="n">
         <v>0</v>
       </c>
-      <c r="AA99" s="5" t="n">
-        <v>1</v>
-      </c>
-      <c r="AB99" s="9" t="n">
-        <v>1</v>
+      <c r="AA99" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB99" t="n">
+        <v>0</v>
       </c>
       <c r="AC99" t="n">
         <v>0</v>
       </c>
       <c r="AD99" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AE99" s="4" t="n">
         <v>7</v>
       </c>
       <c r="AF99" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AG99" t="n">
         <v>7</v>
@@ -12000,15 +12009,15 @@
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>2026-07-11 08:19:16 PM PT</t>
+          <t>2026-07-11 08:21:16 PM PT</t>
         </is>
       </c>
       <c r="C100" t="n">
-        <v>823682</v>
+        <v>823356</v>
       </c>
       <c r="D100" t="inlineStr">
         <is>
-          <t>11:10 AM PT</t>
+          <t>1:05 PM PT</t>
         </is>
       </c>
       <c r="E100" t="inlineStr">
@@ -12026,84 +12035,84 @@
       </c>
       <c r="K100" t="inlineStr">
         <is>
-          <t>Home</t>
+          <t>Away</t>
         </is>
       </c>
       <c r="L100" t="inlineStr">
         <is>
-          <t>MIN</t>
+          <t>MIL</t>
         </is>
       </c>
       <c r="M100" t="inlineStr">
         <is>
-          <t>LAA</t>
+          <t>PIT</t>
         </is>
       </c>
       <c r="N100" t="inlineStr">
         <is>
-          <t>Alan Roden</t>
+          <t>Christian Yelich</t>
         </is>
       </c>
       <c r="O100" t="n">
-        <v>702176</v>
+        <v>592885</v>
       </c>
       <c r="P100" t="inlineStr">
         <is>
-          <t>RF</t>
+          <t>DH</t>
         </is>
       </c>
       <c r="Q100" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>1</t>
         </is>
       </c>
       <c r="R100" t="n">
+        <v>5</v>
+      </c>
+      <c r="S100" t="n">
         <v>3</v>
       </c>
-      <c r="S100" t="n">
+      <c r="T100" t="n">
+        <v>1</v>
+      </c>
+      <c r="U100" t="n">
+        <v>1</v>
+      </c>
+      <c r="V100" t="n">
+        <v>0</v>
+      </c>
+      <c r="W100" t="n">
+        <v>0</v>
+      </c>
+      <c r="X100" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y100" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z100" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA100" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="AB100" s="9" t="n">
+        <v>1</v>
+      </c>
+      <c r="AC100" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD100" t="n">
         <v>2</v>
-      </c>
-      <c r="T100" t="n">
-        <v>1</v>
-      </c>
-      <c r="U100" t="n">
-        <v>1</v>
-      </c>
-      <c r="V100" t="n">
-        <v>0</v>
-      </c>
-      <c r="W100" t="n">
-        <v>0</v>
-      </c>
-      <c r="X100" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y100" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z100" t="n">
-        <v>1</v>
-      </c>
-      <c r="AA100" s="5" t="n">
-        <v>1</v>
-      </c>
-      <c r="AB100" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC100" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD100" t="n">
-        <v>0</v>
       </c>
       <c r="AE100" s="4" t="n">
         <v>7</v>
       </c>
       <c r="AF100" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="AG100" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
     </row>
     <row r="101">
@@ -12114,15 +12123,15 @@
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>2026-07-11 08:19:17 PM PT</t>
+          <t>2026-07-11 08:21:16 PM PT</t>
         </is>
       </c>
       <c r="C101" t="n">
-        <v>823603</v>
+        <v>823682</v>
       </c>
       <c r="D101" t="inlineStr">
         <is>
-          <t>1:10 PM PT</t>
+          <t>11:10 AM PT</t>
         </is>
       </c>
       <c r="E101" t="inlineStr">
@@ -12135,7 +12144,7 @@
       </c>
       <c r="G101" t="inlineStr">
         <is>
-          <t>Bottom</t>
+          <t>Top</t>
         </is>
       </c>
       <c r="K101" t="inlineStr">
@@ -12145,21 +12154,21 @@
       </c>
       <c r="L101" t="inlineStr">
         <is>
-          <t>NYM</t>
+          <t>MIN</t>
         </is>
       </c>
       <c r="M101" t="inlineStr">
         <is>
-          <t>BOS</t>
+          <t>LAA</t>
         </is>
       </c>
       <c r="N101" t="inlineStr">
         <is>
-          <t>Carson Benge</t>
+          <t>Alan Roden</t>
         </is>
       </c>
       <c r="O101" t="n">
-        <v>701807</v>
+        <v>702176</v>
       </c>
       <c r="P101" t="inlineStr">
         <is>
@@ -12168,20 +12177,20 @@
       </c>
       <c r="Q101" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>7</t>
         </is>
       </c>
       <c r="R101" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="S101" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="T101" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="U101" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="V101" t="n">
         <v>0</v>
@@ -12196,7 +12205,7 @@
         <v>0</v>
       </c>
       <c r="Z101" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AA101" s="5" t="n">
         <v>1</v>
@@ -12204,20 +12213,20 @@
       <c r="AB101" t="n">
         <v>0</v>
       </c>
-      <c r="AC101" s="6" t="n">
-        <v>1</v>
+      <c r="AC101" t="n">
+        <v>0</v>
       </c>
       <c r="AD101" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AE101" s="4" t="n">
         <v>7</v>
       </c>
       <c r="AF101" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="AG101" t="n">
-        <v>3</v>
+        <v>9</v>
       </c>
     </row>
     <row r="102">
@@ -12228,119 +12237,110 @@
       </c>
       <c r="B102" t="inlineStr">
         <is>
-          <t>2026-07-11 08:19:18 PM PT</t>
+          <t>2026-07-11 08:21:17 PM PT</t>
         </is>
       </c>
       <c r="C102" t="n">
-        <v>823276</v>
+        <v>823603</v>
       </c>
       <c r="D102" t="inlineStr">
         <is>
-          <t>5:40 PM PT</t>
+          <t>1:10 PM PT</t>
         </is>
       </c>
       <c r="E102" t="inlineStr">
         <is>
-          <t>Bottom 7 | 2 out</t>
+          <t>Final</t>
         </is>
       </c>
       <c r="F102" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="G102" t="inlineStr">
         <is>
           <t>Bottom</t>
         </is>
       </c>
-      <c r="H102" t="n">
+      <c r="K102" t="inlineStr">
+        <is>
+          <t>Home</t>
+        </is>
+      </c>
+      <c r="L102" t="inlineStr">
+        <is>
+          <t>NYM</t>
+        </is>
+      </c>
+      <c r="M102" t="inlineStr">
+        <is>
+          <t>BOS</t>
+        </is>
+      </c>
+      <c r="N102" t="inlineStr">
+        <is>
+          <t>Carson Benge</t>
+        </is>
+      </c>
+      <c r="O102" t="n">
+        <v>701807</v>
+      </c>
+      <c r="P102" t="inlineStr">
+        <is>
+          <t>RF</t>
+        </is>
+      </c>
+      <c r="Q102" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="R102" t="n">
+        <v>4</v>
+      </c>
+      <c r="S102" t="n">
+        <v>3</v>
+      </c>
+      <c r="T102" t="n">
+        <v>0</v>
+      </c>
+      <c r="U102" t="n">
+        <v>0</v>
+      </c>
+      <c r="V102" t="n">
+        <v>0</v>
+      </c>
+      <c r="W102" t="n">
+        <v>0</v>
+      </c>
+      <c r="X102" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y102" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z102" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA102" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="AB102" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC102" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="AD102" t="n">
         <v>2</v>
-      </c>
-      <c r="I102" t="n">
-        <v>3</v>
-      </c>
-      <c r="J102" t="n">
-        <v>2</v>
-      </c>
-      <c r="K102" t="inlineStr">
-        <is>
-          <t>Home</t>
-        </is>
-      </c>
-      <c r="L102" t="inlineStr">
-        <is>
-          <t>SD</t>
-        </is>
-      </c>
-      <c r="M102" t="inlineStr">
-        <is>
-          <t>TOR</t>
-        </is>
-      </c>
-      <c r="N102" t="inlineStr">
-        <is>
-          <t>Manny Machado</t>
-        </is>
-      </c>
-      <c r="O102" t="n">
-        <v>592518</v>
-      </c>
-      <c r="P102" t="inlineStr">
-        <is>
-          <t>DH</t>
-        </is>
-      </c>
-      <c r="Q102" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="R102" t="n">
-        <v>4</v>
-      </c>
-      <c r="S102" t="n">
-        <v>4</v>
-      </c>
-      <c r="T102" t="n">
-        <v>1</v>
-      </c>
-      <c r="U102" t="n">
-        <v>1</v>
-      </c>
-      <c r="V102" t="n">
-        <v>0</v>
-      </c>
-      <c r="W102" t="n">
-        <v>0</v>
-      </c>
-      <c r="X102" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y102" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z102" t="n">
-        <v>2</v>
-      </c>
-      <c r="AA102" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB102" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC102" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD102" t="n">
-        <v>1</v>
       </c>
       <c r="AE102" s="4" t="n">
         <v>7</v>
       </c>
       <c r="AF102" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="AG102" t="n">
-        <v>7</v>
+        <v>3</v>
       </c>
     </row>
     <row r="103">
@@ -12351,92 +12351,101 @@
       </c>
       <c r="B103" t="inlineStr">
         <is>
-          <t>2026-07-11 08:19:17 PM PT</t>
+          <t>2026-07-11 08:21:18 PM PT</t>
         </is>
       </c>
       <c r="C103" t="n">
-        <v>822953</v>
+        <v>823276</v>
       </c>
       <c r="D103" t="inlineStr">
         <is>
-          <t>1:10 PM PT</t>
+          <t>5:40 PM PT</t>
         </is>
       </c>
       <c r="E103" t="inlineStr">
         <is>
-          <t>Final</t>
+          <t>Bottom 7 | 3 out</t>
         </is>
       </c>
       <c r="F103" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="G103" t="inlineStr">
         <is>
-          <t>Top</t>
-        </is>
+          <t>Bottom</t>
+        </is>
+      </c>
+      <c r="H103" t="n">
+        <v>3</v>
+      </c>
+      <c r="I103" t="n">
+        <v>3</v>
+      </c>
+      <c r="J103" t="n">
+        <v>3</v>
       </c>
       <c r="K103" t="inlineStr">
         <is>
-          <t>Away</t>
+          <t>Home</t>
         </is>
       </c>
       <c r="L103" t="inlineStr">
         <is>
-          <t>SEA</t>
+          <t>SD</t>
         </is>
       </c>
       <c r="M103" t="inlineStr">
         <is>
-          <t>TB</t>
+          <t>TOR</t>
         </is>
       </c>
       <c r="N103" t="inlineStr">
         <is>
-          <t>Randy Arozarena</t>
+          <t>Manny Machado</t>
         </is>
       </c>
       <c r="O103" t="n">
-        <v>668227</v>
+        <v>592518</v>
       </c>
       <c r="P103" t="inlineStr">
         <is>
-          <t>LF</t>
+          <t>DH</t>
         </is>
       </c>
       <c r="Q103" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>4</t>
         </is>
       </c>
       <c r="R103" t="n">
         <v>4</v>
       </c>
       <c r="S103" t="n">
+        <v>4</v>
+      </c>
+      <c r="T103" t="n">
+        <v>1</v>
+      </c>
+      <c r="U103" t="n">
+        <v>1</v>
+      </c>
+      <c r="V103" t="n">
+        <v>0</v>
+      </c>
+      <c r="W103" t="n">
+        <v>0</v>
+      </c>
+      <c r="X103" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y103" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z103" t="n">
         <v>2</v>
       </c>
-      <c r="T103" t="n">
-        <v>1</v>
-      </c>
-      <c r="U103" t="n">
-        <v>1</v>
-      </c>
-      <c r="V103" t="n">
-        <v>0</v>
-      </c>
-      <c r="W103" t="n">
-        <v>0</v>
-      </c>
-      <c r="X103" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y103" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z103" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA103" s="5" t="n">
-        <v>2</v>
+      <c r="AA103" t="n">
+        <v>0</v>
       </c>
       <c r="AB103" t="n">
         <v>0</v>
@@ -12445,16 +12454,16 @@
         <v>0</v>
       </c>
       <c r="AD103" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AE103" s="4" t="n">
         <v>7</v>
       </c>
       <c r="AF103" t="n">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="AG103" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
     </row>
     <row r="104">
@@ -12465,7 +12474,7 @@
       </c>
       <c r="B104" t="inlineStr">
         <is>
-          <t>2026-07-11 08:19:17 PM PT</t>
+          <t>2026-07-11 08:21:17 PM PT</t>
         </is>
       </c>
       <c r="C104" t="n">
@@ -12506,20 +12515,20 @@
       </c>
       <c r="N104" t="inlineStr">
         <is>
-          <t>Cal Raleigh</t>
+          <t>Randy Arozarena</t>
         </is>
       </c>
       <c r="O104" t="n">
-        <v>663728</v>
+        <v>668227</v>
       </c>
       <c r="P104" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>LF</t>
         </is>
       </c>
       <c r="Q104" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>2</t>
         </is>
       </c>
       <c r="R104" t="n">
@@ -12559,7 +12568,7 @@
         <v>0</v>
       </c>
       <c r="AD104" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AE104" s="4" t="n">
         <v>7</v>
@@ -12579,7 +12588,7 @@
       </c>
       <c r="B105" t="inlineStr">
         <is>
-          <t>2026-07-11 08:19:17 PM PT</t>
+          <t>2026-07-11 08:21:17 PM PT</t>
         </is>
       </c>
       <c r="C105" t="n">
@@ -12620,36 +12629,36 @@
       </c>
       <c r="N105" t="inlineStr">
         <is>
-          <t>Cole Young</t>
+          <t>Cal Raleigh</t>
         </is>
       </c>
       <c r="O105" t="n">
-        <v>702284</v>
+        <v>663728</v>
       </c>
       <c r="P105" t="inlineStr">
         <is>
-          <t>2B</t>
+          <t>C</t>
         </is>
       </c>
       <c r="Q105" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>4</t>
         </is>
       </c>
       <c r="R105" t="n">
         <v>4</v>
       </c>
       <c r="S105" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="T105" t="n">
         <v>1</v>
       </c>
       <c r="U105" t="n">
-        <v>0</v>
-      </c>
-      <c r="V105" s="7" t="n">
-        <v>1</v>
+        <v>1</v>
+      </c>
+      <c r="V105" t="n">
+        <v>0</v>
       </c>
       <c r="W105" t="n">
         <v>0</v>
@@ -12658,13 +12667,13 @@
         <v>0</v>
       </c>
       <c r="Y105" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Z105" t="n">
         <v>0</v>
       </c>
-      <c r="AA105" t="n">
-        <v>0</v>
+      <c r="AA105" s="5" t="n">
+        <v>2</v>
       </c>
       <c r="AB105" t="n">
         <v>0</v>
@@ -12693,15 +12702,15 @@
       </c>
       <c r="B106" t="inlineStr">
         <is>
-          <t>2026-07-11 08:19:17 PM PT</t>
+          <t>2026-07-11 08:21:17 PM PT</t>
         </is>
       </c>
       <c r="C106" t="n">
-        <v>823198</v>
+        <v>822953</v>
       </c>
       <c r="D106" t="inlineStr">
         <is>
-          <t>1:05 PM PT</t>
+          <t>1:10 PM PT</t>
         </is>
       </c>
       <c r="E106" t="inlineStr">
@@ -12719,42 +12728,42 @@
       </c>
       <c r="K106" t="inlineStr">
         <is>
-          <t>Home</t>
+          <t>Away</t>
         </is>
       </c>
       <c r="L106" t="inlineStr">
         <is>
-          <t>SF</t>
+          <t>SEA</t>
         </is>
       </c>
       <c r="M106" t="inlineStr">
         <is>
-          <t>COL</t>
+          <t>TB</t>
         </is>
       </c>
       <c r="N106" t="inlineStr">
         <is>
-          <t>Bryce Eldridge</t>
+          <t>Cole Young</t>
         </is>
       </c>
       <c r="O106" t="n">
-        <v>805811</v>
+        <v>702284</v>
       </c>
       <c r="P106" t="inlineStr">
         <is>
-          <t>DH</t>
+          <t>2B</t>
         </is>
       </c>
       <c r="Q106" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="R106" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="S106" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="T106" t="n">
         <v>1</v>
@@ -12787,16 +12796,16 @@
         <v>0</v>
       </c>
       <c r="AD106" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AE106" s="4" t="n">
         <v>7</v>
       </c>
       <c r="AF106" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="AG106" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
     </row>
     <row r="107">
@@ -12807,7 +12816,7 @@
       </c>
       <c r="B107" t="inlineStr">
         <is>
-          <t>2026-07-11 08:19:17 PM PT</t>
+          <t>2026-07-11 08:21:17 PM PT</t>
         </is>
       </c>
       <c r="C107" t="n">
@@ -12848,20 +12857,20 @@
       </c>
       <c r="N107" t="inlineStr">
         <is>
-          <t>Jesus Rodriguez</t>
+          <t>Bryce Eldridge</t>
         </is>
       </c>
       <c r="O107" t="n">
-        <v>683679</v>
+        <v>805811</v>
       </c>
       <c r="P107" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>DH</t>
         </is>
       </c>
       <c r="Q107" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>6</t>
         </is>
       </c>
       <c r="R107" t="n">
@@ -12886,10 +12895,10 @@
         <v>0</v>
       </c>
       <c r="Y107" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Z107" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AA107" t="n">
         <v>0</v>
@@ -12901,7 +12910,7 @@
         <v>0</v>
       </c>
       <c r="AD107" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AE107" s="4" t="n">
         <v>7</v>
@@ -12921,15 +12930,15 @@
       </c>
       <c r="B108" t="inlineStr">
         <is>
-          <t>2026-07-11 08:19:17 PM PT</t>
+          <t>2026-07-11 08:21:17 PM PT</t>
         </is>
       </c>
       <c r="C108" t="n">
-        <v>822953</v>
+        <v>823198</v>
       </c>
       <c r="D108" t="inlineStr">
         <is>
-          <t>1:10 PM PT</t>
+          <t>1:05 PM PT</t>
         </is>
       </c>
       <c r="E108" t="inlineStr">
@@ -12952,37 +12961,37 @@
       </c>
       <c r="L108" t="inlineStr">
         <is>
-          <t>TB</t>
+          <t>SF</t>
         </is>
       </c>
       <c r="M108" t="inlineStr">
         <is>
-          <t>SEA</t>
+          <t>COL</t>
         </is>
       </c>
       <c r="N108" t="inlineStr">
         <is>
-          <t>Yandy Díaz</t>
+          <t>Jesus Rodriguez</t>
         </is>
       </c>
       <c r="O108" t="n">
-        <v>650490</v>
+        <v>683679</v>
       </c>
       <c r="P108" t="inlineStr">
         <is>
-          <t>DH</t>
+          <t>C</t>
         </is>
       </c>
       <c r="Q108" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>8</t>
         </is>
       </c>
       <c r="R108" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="S108" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="T108" t="n">
         <v>1</v>
@@ -13000,10 +13009,10 @@
         <v>0</v>
       </c>
       <c r="Y108" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Z108" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AA108" t="n">
         <v>0</v>
@@ -13021,10 +13030,10 @@
         <v>7</v>
       </c>
       <c r="AF108" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="AG108" t="n">
-        <v>12</v>
+        <v>7</v>
       </c>
     </row>
     <row r="109">
@@ -13035,15 +13044,15 @@
       </c>
       <c r="B109" t="inlineStr">
         <is>
-          <t>2026-07-11 08:19:17 PM PT</t>
+          <t>2026-07-11 08:21:17 PM PT</t>
         </is>
       </c>
       <c r="C109" t="n">
-        <v>824576</v>
+        <v>822953</v>
       </c>
       <c r="D109" t="inlineStr">
         <is>
-          <t>11:10 AM PT</t>
+          <t>1:10 PM PT</t>
         </is>
       </c>
       <c r="E109" t="inlineStr">
@@ -13061,51 +13070,51 @@
       </c>
       <c r="K109" t="inlineStr">
         <is>
-          <t>Away</t>
+          <t>Home</t>
         </is>
       </c>
       <c r="L109" t="inlineStr">
         <is>
-          <t>ATH</t>
+          <t>TB</t>
         </is>
       </c>
       <c r="M109" t="inlineStr">
         <is>
-          <t>CWS</t>
+          <t>SEA</t>
         </is>
       </c>
       <c r="N109" t="inlineStr">
         <is>
-          <t>Lawrence Butler</t>
+          <t>Yandy Díaz</t>
         </is>
       </c>
       <c r="O109" t="n">
-        <v>671732</v>
+        <v>650490</v>
       </c>
       <c r="P109" t="inlineStr">
         <is>
-          <t>RF</t>
+          <t>DH</t>
         </is>
       </c>
       <c r="Q109" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>1</t>
         </is>
       </c>
       <c r="R109" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="S109" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="T109" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="U109" t="n">
         <v>0</v>
       </c>
-      <c r="V109" t="n">
-        <v>0</v>
+      <c r="V109" s="7" t="n">
+        <v>1</v>
       </c>
       <c r="W109" t="n">
         <v>0</v>
@@ -13114,13 +13123,13 @@
         <v>0</v>
       </c>
       <c r="Y109" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Z109" t="n">
         <v>0</v>
       </c>
-      <c r="AA109" s="5" t="n">
-        <v>3</v>
+      <c r="AA109" t="n">
+        <v>0</v>
       </c>
       <c r="AB109" t="n">
         <v>0</v>
@@ -13132,13 +13141,13 @@
         <v>0</v>
       </c>
       <c r="AE109" s="4" t="n">
+        <v>7</v>
+      </c>
+      <c r="AF109" t="n">
         <v>6</v>
       </c>
-      <c r="AF109" t="n">
-        <v>0</v>
-      </c>
       <c r="AG109" t="n">
-        <v>4</v>
+        <v>12</v>
       </c>
     </row>
     <row r="110">
@@ -13149,15 +13158,15 @@
       </c>
       <c r="B110" t="inlineStr">
         <is>
-          <t>2026-07-11 08:19:17 PM PT</t>
+          <t>2026-07-11 08:21:16 PM PT</t>
         </is>
       </c>
       <c r="C110" t="n">
-        <v>824492</v>
+        <v>824576</v>
       </c>
       <c r="D110" t="inlineStr">
         <is>
-          <t>4:10 PM PT</t>
+          <t>11:10 AM PT</t>
         </is>
       </c>
       <c r="E110" t="inlineStr">
@@ -13170,71 +13179,71 @@
       </c>
       <c r="G110" t="inlineStr">
         <is>
-          <t>Bottom</t>
+          <t>Top</t>
         </is>
       </c>
       <c r="K110" t="inlineStr">
         <is>
-          <t>Home</t>
+          <t>Away</t>
         </is>
       </c>
       <c r="L110" t="inlineStr">
         <is>
-          <t>CIN</t>
+          <t>ATH</t>
         </is>
       </c>
       <c r="M110" t="inlineStr">
         <is>
-          <t>CHC</t>
+          <t>CWS</t>
         </is>
       </c>
       <c r="N110" t="inlineStr">
         <is>
-          <t>TJ Friedl</t>
+          <t>Lawrence Butler</t>
         </is>
       </c>
       <c r="O110" t="n">
-        <v>670770</v>
+        <v>671732</v>
       </c>
       <c r="P110" t="inlineStr">
         <is>
-          <t>CF</t>
+          <t>RF</t>
         </is>
       </c>
       <c r="Q110" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>6</t>
         </is>
       </c>
       <c r="R110" t="n">
+        <v>4</v>
+      </c>
+      <c r="S110" t="n">
+        <v>1</v>
+      </c>
+      <c r="T110" t="n">
+        <v>0</v>
+      </c>
+      <c r="U110" t="n">
+        <v>0</v>
+      </c>
+      <c r="V110" t="n">
+        <v>0</v>
+      </c>
+      <c r="W110" t="n">
+        <v>0</v>
+      </c>
+      <c r="X110" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y110" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z110" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA110" s="5" t="n">
         <v>3</v>
-      </c>
-      <c r="S110" t="n">
-        <v>3</v>
-      </c>
-      <c r="T110" t="n">
-        <v>2</v>
-      </c>
-      <c r="U110" t="n">
-        <v>2</v>
-      </c>
-      <c r="V110" t="n">
-        <v>0</v>
-      </c>
-      <c r="W110" t="n">
-        <v>0</v>
-      </c>
-      <c r="X110" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y110" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z110" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA110" t="n">
-        <v>0</v>
       </c>
       <c r="AB110" t="n">
         <v>0</v>
@@ -13249,10 +13258,10 @@
         <v>6</v>
       </c>
       <c r="AF110" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="AG110" t="n">
-        <v>11</v>
+        <v>4</v>
       </c>
     </row>
     <row r="111">
@@ -13263,15 +13272,15 @@
       </c>
       <c r="B111" t="inlineStr">
         <is>
-          <t>2026-07-11 08:19:17 PM PT</t>
+          <t>2026-07-11 08:21:18 PM PT</t>
         </is>
       </c>
       <c r="C111" t="n">
-        <v>823844</v>
+        <v>824492</v>
       </c>
       <c r="D111" t="inlineStr">
         <is>
-          <t>1:10 PM PT</t>
+          <t>4:10 PM PT</t>
         </is>
       </c>
       <c r="E111" t="inlineStr">
@@ -13289,42 +13298,42 @@
       </c>
       <c r="K111" t="inlineStr">
         <is>
-          <t>Away</t>
+          <t>Home</t>
         </is>
       </c>
       <c r="L111" t="inlineStr">
         <is>
-          <t>CLE</t>
+          <t>CIN</t>
         </is>
       </c>
       <c r="M111" t="inlineStr">
         <is>
-          <t>MIA</t>
+          <t>CHC</t>
         </is>
       </c>
       <c r="N111" t="inlineStr">
         <is>
-          <t>Brayan Rocchio</t>
+          <t>TJ Friedl</t>
         </is>
       </c>
       <c r="O111" t="n">
-        <v>677587</v>
+        <v>670770</v>
       </c>
       <c r="P111" t="inlineStr">
         <is>
-          <t>SS</t>
+          <t>CF</t>
         </is>
       </c>
       <c r="Q111" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>9</t>
         </is>
       </c>
       <c r="R111" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="S111" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="T111" t="n">
         <v>2</v>
@@ -13363,7 +13372,7 @@
         <v>6</v>
       </c>
       <c r="AF111" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="AG111" t="n">
         <v>11</v>
@@ -13377,15 +13386,15 @@
       </c>
       <c r="B112" t="inlineStr">
         <is>
-          <t>2026-07-11 08:19:17 PM PT</t>
+          <t>2026-07-11 08:21:17 PM PT</t>
         </is>
       </c>
       <c r="C112" t="n">
-        <v>823198</v>
+        <v>823844</v>
       </c>
       <c r="D112" t="inlineStr">
         <is>
-          <t>1:05 PM PT</t>
+          <t>1:10 PM PT</t>
         </is>
       </c>
       <c r="E112" t="inlineStr">
@@ -13398,7 +13407,7 @@
       </c>
       <c r="G112" t="inlineStr">
         <is>
-          <t>Top</t>
+          <t>Bottom</t>
         </is>
       </c>
       <c r="K112" t="inlineStr">
@@ -13408,25 +13417,25 @@
       </c>
       <c r="L112" t="inlineStr">
         <is>
-          <t>COL</t>
+          <t>CLE</t>
         </is>
       </c>
       <c r="M112" t="inlineStr">
         <is>
-          <t>SF</t>
+          <t>MIA</t>
         </is>
       </c>
       <c r="N112" t="inlineStr">
         <is>
-          <t>Mickey Moniak</t>
+          <t>Brayan Rocchio</t>
         </is>
       </c>
       <c r="O112" t="n">
-        <v>666160</v>
+        <v>677587</v>
       </c>
       <c r="P112" t="inlineStr">
         <is>
-          <t>LF</t>
+          <t>SS</t>
         </is>
       </c>
       <c r="Q112" t="inlineStr">
@@ -13435,10 +13444,10 @@
         </is>
       </c>
       <c r="R112" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="S112" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="T112" t="n">
         <v>2</v>
@@ -13471,16 +13480,16 @@
         <v>0</v>
       </c>
       <c r="AD112" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AE112" s="4" t="n">
         <v>6</v>
       </c>
       <c r="AF112" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="AG112" t="n">
-        <v>6</v>
+        <v>11</v>
       </c>
     </row>
     <row r="113">
@@ -13491,15 +13500,15 @@
       </c>
       <c r="B113" t="inlineStr">
         <is>
-          <t>2026-07-11 08:19:17 PM PT</t>
+          <t>2026-07-11 08:21:17 PM PT</t>
         </is>
       </c>
       <c r="C113" t="n">
-        <v>824249</v>
+        <v>823198</v>
       </c>
       <c r="D113" t="inlineStr">
         <is>
-          <t>3:10 PM PT</t>
+          <t>1:05 PM PT</t>
         </is>
       </c>
       <c r="E113" t="inlineStr">
@@ -13512,47 +13521,47 @@
       </c>
       <c r="G113" t="inlineStr">
         <is>
-          <t>Bottom</t>
+          <t>Top</t>
         </is>
       </c>
       <c r="K113" t="inlineStr">
         <is>
-          <t>Home</t>
+          <t>Away</t>
         </is>
       </c>
       <c r="L113" t="inlineStr">
         <is>
-          <t>DET</t>
+          <t>COL</t>
         </is>
       </c>
       <c r="M113" t="inlineStr">
         <is>
-          <t>PHI</t>
+          <t>SF</t>
         </is>
       </c>
       <c r="N113" t="inlineStr">
         <is>
-          <t>Hao-Yu Lee</t>
+          <t>Mickey Moniak</t>
         </is>
       </c>
       <c r="O113" t="n">
-        <v>701678</v>
+        <v>666160</v>
       </c>
       <c r="P113" t="inlineStr">
         <is>
-          <t>2B</t>
+          <t>LF</t>
         </is>
       </c>
       <c r="Q113" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>2</t>
         </is>
       </c>
       <c r="R113" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="S113" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="T113" t="n">
         <v>2</v>
@@ -13585,7 +13594,7 @@
         <v>0</v>
       </c>
       <c r="AD113" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AE113" s="4" t="n">
         <v>6</v>
@@ -13594,7 +13603,7 @@
         <v>2</v>
       </c>
       <c r="AG113" t="n">
-        <v>10</v>
+        <v>6</v>
       </c>
     </row>
     <row r="114">
@@ -13605,84 +13614,75 @@
       </c>
       <c r="B114" t="inlineStr">
         <is>
-          <t>2026-07-11 08:19:18 PM PT</t>
+          <t>2026-07-11 08:21:17 PM PT</t>
         </is>
       </c>
       <c r="C114" t="n">
-        <v>823276</v>
+        <v>824249</v>
       </c>
       <c r="D114" t="inlineStr">
         <is>
-          <t>5:40 PM PT</t>
+          <t>3:10 PM PT</t>
         </is>
       </c>
       <c r="E114" t="inlineStr">
         <is>
-          <t>Bottom 7 | 2 out</t>
+          <t>Final</t>
         </is>
       </c>
       <c r="F114" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="G114" t="inlineStr">
         <is>
           <t>Bottom</t>
         </is>
       </c>
-      <c r="H114" t="n">
+      <c r="K114" t="inlineStr">
+        <is>
+          <t>Home</t>
+        </is>
+      </c>
+      <c r="L114" t="inlineStr">
+        <is>
+          <t>DET</t>
+        </is>
+      </c>
+      <c r="M114" t="inlineStr">
+        <is>
+          <t>PHI</t>
+        </is>
+      </c>
+      <c r="N114" t="inlineStr">
+        <is>
+          <t>Hao-Yu Lee</t>
+        </is>
+      </c>
+      <c r="O114" t="n">
+        <v>701678</v>
+      </c>
+      <c r="P114" t="inlineStr">
+        <is>
+          <t>2B</t>
+        </is>
+      </c>
+      <c r="Q114" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="R114" t="n">
+        <v>3</v>
+      </c>
+      <c r="S114" t="n">
+        <v>3</v>
+      </c>
+      <c r="T114" t="n">
         <v>2</v>
       </c>
-      <c r="I114" t="n">
-        <v>3</v>
-      </c>
-      <c r="J114" t="n">
+      <c r="U114" t="n">
         <v>2</v>
       </c>
-      <c r="K114" t="inlineStr">
-        <is>
-          <t>Home</t>
-        </is>
-      </c>
-      <c r="L114" t="inlineStr">
-        <is>
-          <t>SD</t>
-        </is>
-      </c>
-      <c r="M114" t="inlineStr">
-        <is>
-          <t>TOR</t>
-        </is>
-      </c>
-      <c r="N114" t="inlineStr">
-        <is>
-          <t>Fernando Tatis Jr.</t>
-        </is>
-      </c>
-      <c r="O114" t="n">
-        <v>665487</v>
-      </c>
-      <c r="P114" t="inlineStr">
-        <is>
-          <t>RF</t>
-        </is>
-      </c>
-      <c r="Q114" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="R114" t="n">
-        <v>4</v>
-      </c>
-      <c r="S114" t="n">
-        <v>2</v>
-      </c>
-      <c r="T114" t="n">
-        <v>0</v>
-      </c>
-      <c r="U114" t="n">
-        <v>0</v>
-      </c>
       <c r="V114" t="n">
         <v>0</v>
       </c>
@@ -13693,13 +13693,13 @@
         <v>0</v>
       </c>
       <c r="Y114" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Z114" t="n">
         <v>0</v>
       </c>
-      <c r="AA114" s="5" t="n">
-        <v>2</v>
+      <c r="AA114" t="n">
+        <v>0</v>
       </c>
       <c r="AB114" t="n">
         <v>0</v>
@@ -13714,10 +13714,10 @@
         <v>6</v>
       </c>
       <c r="AF114" t="n">
-        <v>8</v>
+        <v>2</v>
       </c>
       <c r="AG114" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
     </row>
     <row r="115">
@@ -13728,30 +13728,39 @@
       </c>
       <c r="B115" t="inlineStr">
         <is>
-          <t>2026-07-11 08:19:17 PM PT</t>
+          <t>2026-07-11 08:21:18 PM PT</t>
         </is>
       </c>
       <c r="C115" t="n">
-        <v>822875</v>
+        <v>823276</v>
       </c>
       <c r="D115" t="inlineStr">
         <is>
-          <t>4:05 PM PT</t>
+          <t>5:40 PM PT</t>
         </is>
       </c>
       <c r="E115" t="inlineStr">
         <is>
-          <t>Final</t>
+          <t>Bottom 7 | 3 out</t>
         </is>
       </c>
       <c r="F115" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="G115" t="inlineStr">
         <is>
           <t>Bottom</t>
         </is>
       </c>
+      <c r="H115" t="n">
+        <v>3</v>
+      </c>
+      <c r="I115" t="n">
+        <v>3</v>
+      </c>
+      <c r="J115" t="n">
+        <v>3</v>
+      </c>
       <c r="K115" t="inlineStr">
         <is>
           <t>Home</t>
@@ -13759,61 +13768,61 @@
       </c>
       <c r="L115" t="inlineStr">
         <is>
-          <t>TEX</t>
+          <t>SD</t>
         </is>
       </c>
       <c r="M115" t="inlineStr">
         <is>
-          <t>HOU</t>
+          <t>TOR</t>
         </is>
       </c>
       <c r="N115" t="inlineStr">
         <is>
-          <t>Evan Carter</t>
+          <t>Fernando Tatis Jr.</t>
         </is>
       </c>
       <c r="O115" t="n">
-        <v>694497</v>
+        <v>665487</v>
       </c>
       <c r="P115" t="inlineStr">
         <is>
-          <t>CF</t>
+          <t>RF</t>
         </is>
       </c>
       <c r="Q115" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>1</t>
         </is>
       </c>
       <c r="R115" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="S115" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="T115" t="n">
+        <v>0</v>
+      </c>
+      <c r="U115" t="n">
+        <v>0</v>
+      </c>
+      <c r="V115" t="n">
+        <v>0</v>
+      </c>
+      <c r="W115" t="n">
+        <v>0</v>
+      </c>
+      <c r="X115" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y115" t="n">
+        <v>1</v>
+      </c>
+      <c r="Z115" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA115" s="5" t="n">
         <v>2</v>
-      </c>
-      <c r="U115" t="n">
-        <v>2</v>
-      </c>
-      <c r="V115" t="n">
-        <v>0</v>
-      </c>
-      <c r="W115" t="n">
-        <v>0</v>
-      </c>
-      <c r="X115" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y115" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z115" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA115" t="n">
-        <v>0</v>
       </c>
       <c r="AB115" t="n">
         <v>0</v>
@@ -13828,7 +13837,7 @@
         <v>6</v>
       </c>
       <c r="AF115" t="n">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="AG115" t="n">
         <v>7</v>
@@ -13842,119 +13851,110 @@
       </c>
       <c r="B116" t="inlineStr">
         <is>
-          <t>2026-07-11 08:19:18 PM PT</t>
+          <t>2026-07-11 08:21:18 PM PT</t>
         </is>
       </c>
       <c r="C116" t="n">
-        <v>823926</v>
+        <v>822875</v>
       </c>
       <c r="D116" t="inlineStr">
         <is>
-          <t>6:10 PM PT</t>
+          <t>4:05 PM PT</t>
         </is>
       </c>
       <c r="E116" t="inlineStr">
         <is>
-          <t>Top 7 | 1 out</t>
+          <t>Final</t>
         </is>
       </c>
       <c r="F116" t="n">
+        <v>9</v>
+      </c>
+      <c r="G116" t="inlineStr">
+        <is>
+          <t>Bottom</t>
+        </is>
+      </c>
+      <c r="K116" t="inlineStr">
+        <is>
+          <t>Home</t>
+        </is>
+      </c>
+      <c r="L116" t="inlineStr">
+        <is>
+          <t>TEX</t>
+        </is>
+      </c>
+      <c r="M116" t="inlineStr">
+        <is>
+          <t>HOU</t>
+        </is>
+      </c>
+      <c r="N116" t="inlineStr">
+        <is>
+          <t>Evan Carter</t>
+        </is>
+      </c>
+      <c r="O116" t="n">
+        <v>694497</v>
+      </c>
+      <c r="P116" t="inlineStr">
+        <is>
+          <t>CF</t>
+        </is>
+      </c>
+      <c r="Q116" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="R116" t="n">
+        <v>4</v>
+      </c>
+      <c r="S116" t="n">
+        <v>4</v>
+      </c>
+      <c r="T116" t="n">
+        <v>2</v>
+      </c>
+      <c r="U116" t="n">
+        <v>2</v>
+      </c>
+      <c r="V116" t="n">
+        <v>0</v>
+      </c>
+      <c r="W116" t="n">
+        <v>0</v>
+      </c>
+      <c r="X116" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y116" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z116" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA116" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB116" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC116" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD116" t="n">
+        <v>1</v>
+      </c>
+      <c r="AE116" s="4" t="n">
+        <v>6</v>
+      </c>
+      <c r="AF116" t="n">
+        <v>3</v>
+      </c>
+      <c r="AG116" t="n">
         <v>7</v>
-      </c>
-      <c r="G116" t="inlineStr">
-        <is>
-          <t>Top</t>
-        </is>
-      </c>
-      <c r="H116" t="n">
-        <v>1</v>
-      </c>
-      <c r="I116" t="n">
-        <v>0</v>
-      </c>
-      <c r="J116" t="n">
-        <v>0</v>
-      </c>
-      <c r="K116" t="inlineStr">
-        <is>
-          <t>Away</t>
-        </is>
-      </c>
-      <c r="L116" t="inlineStr">
-        <is>
-          <t>ARI</t>
-        </is>
-      </c>
-      <c r="M116" t="inlineStr">
-        <is>
-          <t>LAD</t>
-        </is>
-      </c>
-      <c r="N116" t="inlineStr">
-        <is>
-          <t>Max Kepler</t>
-        </is>
-      </c>
-      <c r="O116" t="n">
-        <v>596146</v>
-      </c>
-      <c r="P116" t="inlineStr">
-        <is>
-          <t>LF</t>
-        </is>
-      </c>
-      <c r="Q116" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="R116" t="n">
-        <v>3</v>
-      </c>
-      <c r="S116" t="n">
-        <v>2</v>
-      </c>
-      <c r="T116" t="n">
-        <v>1</v>
-      </c>
-      <c r="U116" t="n">
-        <v>1</v>
-      </c>
-      <c r="V116" t="n">
-        <v>0</v>
-      </c>
-      <c r="W116" t="n">
-        <v>0</v>
-      </c>
-      <c r="X116" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y116" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z116" t="n">
-        <v>1</v>
-      </c>
-      <c r="AA116" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB116" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC116" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD116" t="n">
-        <v>1</v>
-      </c>
-      <c r="AE116" s="4" t="n">
-        <v>5</v>
-      </c>
-      <c r="AF116" t="n">
-        <v>6</v>
-      </c>
-      <c r="AG116" t="n">
-        <v>5</v>
       </c>
     </row>
     <row r="117">
@@ -13965,7 +13965,7 @@
       </c>
       <c r="B117" t="inlineStr">
         <is>
-          <t>2026-07-11 08:19:17 PM PT</t>
+          <t>2026-07-11 08:21:18 PM PT</t>
         </is>
       </c>
       <c r="C117" t="n">
@@ -14079,7 +14079,7 @@
       </c>
       <c r="B118" t="inlineStr">
         <is>
-          <t>2026-07-11 08:19:17 PM PT</t>
+          <t>2026-07-11 08:21:18 PM PT</t>
         </is>
       </c>
       <c r="C118" t="n">
@@ -14193,7 +14193,7 @@
       </c>
       <c r="B119" t="inlineStr">
         <is>
-          <t>2026-07-11 08:19:17 PM PT</t>
+          <t>2026-07-11 08:21:18 PM PT</t>
         </is>
       </c>
       <c r="C119" t="n">
@@ -14307,7 +14307,7 @@
       </c>
       <c r="B120" t="inlineStr">
         <is>
-          <t>2026-07-11 08:19:17 PM PT</t>
+          <t>2026-07-11 08:21:17 PM PT</t>
         </is>
       </c>
       <c r="C120" t="n">
@@ -14421,7 +14421,7 @@
       </c>
       <c r="B121" t="inlineStr">
         <is>
-          <t>2026-07-11 08:19:17 PM PT</t>
+          <t>2026-07-11 08:21:18 PM PT</t>
         </is>
       </c>
       <c r="C121" t="n">
@@ -14535,7 +14535,7 @@
       </c>
       <c r="B122" t="inlineStr">
         <is>
-          <t>2026-07-11 08:19:17 PM PT</t>
+          <t>2026-07-11 08:21:17 PM PT</t>
         </is>
       </c>
       <c r="C122" t="n">
@@ -14649,7 +14649,7 @@
       </c>
       <c r="B123" t="inlineStr">
         <is>
-          <t>2026-07-11 08:19:17 PM PT</t>
+          <t>2026-07-11 08:21:16 PM PT</t>
         </is>
       </c>
       <c r="C123" t="n">
@@ -14763,7 +14763,7 @@
       </c>
       <c r="B124" t="inlineStr">
         <is>
-          <t>2026-07-11 08:19:17 PM PT</t>
+          <t>2026-07-11 08:21:17 PM PT</t>
         </is>
       </c>
       <c r="C124" t="n">
@@ -14877,7 +14877,7 @@
       </c>
       <c r="B125" t="inlineStr">
         <is>
-          <t>2026-07-11 08:19:17 PM PT</t>
+          <t>2026-07-11 08:21:18 PM PT</t>
         </is>
       </c>
       <c r="C125" t="n">
@@ -14991,7 +14991,7 @@
       </c>
       <c r="B126" t="inlineStr">
         <is>
-          <t>2026-07-11 08:19:17 PM PT</t>
+          <t>2026-07-11 08:21:18 PM PT</t>
         </is>
       </c>
       <c r="C126" t="n">
@@ -15105,7 +15105,7 @@
       </c>
       <c r="B127" t="inlineStr">
         <is>
-          <t>2026-07-11 08:19:17 PM PT</t>
+          <t>2026-07-11 08:21:18 PM PT</t>
         </is>
       </c>
       <c r="C127" t="n">
@@ -15219,7 +15219,7 @@
       </c>
       <c r="B128" t="inlineStr">
         <is>
-          <t>2026-07-11 08:19:18 PM PT</t>
+          <t>2026-07-11 08:21:18 PM PT</t>
         </is>
       </c>
       <c r="C128" t="n">
@@ -15232,7 +15232,7 @@
       </c>
       <c r="E128" t="inlineStr">
         <is>
-          <t>Top 7 | 1 out</t>
+          <t>Top 7 | 2 out</t>
         </is>
       </c>
       <c r="F128" t="n">
@@ -15244,7 +15244,7 @@
         </is>
       </c>
       <c r="H128" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I128" t="n">
         <v>0</v>
@@ -15342,7 +15342,7 @@
       </c>
       <c r="B129" t="inlineStr">
         <is>
-          <t>2026-07-11 08:19:17 PM PT</t>
+          <t>2026-07-11 08:21:17 PM PT</t>
         </is>
       </c>
       <c r="C129" t="n">
@@ -15456,7 +15456,7 @@
       </c>
       <c r="B130" t="inlineStr">
         <is>
-          <t>2026-07-11 08:19:17 PM PT</t>
+          <t>2026-07-11 08:21:17 PM PT</t>
         </is>
       </c>
       <c r="C130" t="n">
@@ -15570,7 +15570,7 @@
       </c>
       <c r="B131" t="inlineStr">
         <is>
-          <t>2026-07-11 08:19:16 PM PT</t>
+          <t>2026-07-11 08:21:16 PM PT</t>
         </is>
       </c>
       <c r="C131" t="n">
@@ -15684,7 +15684,7 @@
       </c>
       <c r="B132" t="inlineStr">
         <is>
-          <t>2026-07-11 08:19:16 PM PT</t>
+          <t>2026-07-11 08:21:16 PM PT</t>
         </is>
       </c>
       <c r="C132" t="n">
@@ -15798,7 +15798,7 @@
       </c>
       <c r="B133" t="inlineStr">
         <is>
-          <t>2026-07-11 08:19:16 PM PT</t>
+          <t>2026-07-11 08:21:16 PM PT</t>
         </is>
       </c>
       <c r="C133" t="n">
@@ -15912,7 +15912,7 @@
       </c>
       <c r="B134" t="inlineStr">
         <is>
-          <t>2026-07-11 08:19:17 PM PT</t>
+          <t>2026-07-11 08:21:17 PM PT</t>
         </is>
       </c>
       <c r="C134" t="n">
@@ -16026,7 +16026,7 @@
       </c>
       <c r="B135" t="inlineStr">
         <is>
-          <t>2026-07-11 08:19:16 PM PT</t>
+          <t>2026-07-11 08:21:16 PM PT</t>
         </is>
       </c>
       <c r="C135" t="n">
@@ -16140,7 +16140,7 @@
       </c>
       <c r="B136" t="inlineStr">
         <is>
-          <t>2026-07-11 08:19:16 PM PT</t>
+          <t>2026-07-11 08:21:16 PM PT</t>
         </is>
       </c>
       <c r="C136" t="n">
@@ -16254,7 +16254,7 @@
       </c>
       <c r="B137" t="inlineStr">
         <is>
-          <t>2026-07-11 08:19:17 PM PT</t>
+          <t>2026-07-11 08:21:17 PM PT</t>
         </is>
       </c>
       <c r="C137" t="n">
@@ -16368,7 +16368,7 @@
       </c>
       <c r="B138" t="inlineStr">
         <is>
-          <t>2026-07-11 08:19:17 PM PT</t>
+          <t>2026-07-11 08:21:17 PM PT</t>
         </is>
       </c>
       <c r="C138" t="n">
@@ -16482,7 +16482,7 @@
       </c>
       <c r="B139" t="inlineStr">
         <is>
-          <t>2026-07-11 08:19:17 PM PT</t>
+          <t>2026-07-11 08:21:17 PM PT</t>
         </is>
       </c>
       <c r="C139" t="n">
@@ -16596,7 +16596,7 @@
       </c>
       <c r="B140" t="inlineStr">
         <is>
-          <t>2026-07-11 08:19:17 PM PT</t>
+          <t>2026-07-11 08:21:18 PM PT</t>
         </is>
       </c>
       <c r="C140" t="n">
@@ -16710,7 +16710,7 @@
       </c>
       <c r="B141" t="inlineStr">
         <is>
-          <t>2026-07-11 08:19:17 PM PT</t>
+          <t>2026-07-11 08:21:18 PM PT</t>
         </is>
       </c>
       <c r="C141" t="n">
@@ -16824,7 +16824,7 @@
       </c>
       <c r="B142" t="inlineStr">
         <is>
-          <t>2026-07-11 08:19:17 PM PT</t>
+          <t>2026-07-11 08:21:18 PM PT</t>
         </is>
       </c>
       <c r="C142" t="n">
@@ -16938,7 +16938,7 @@
       </c>
       <c r="B143" t="inlineStr">
         <is>
-          <t>2026-07-11 08:19:17 PM PT</t>
+          <t>2026-07-11 08:21:17 PM PT</t>
         </is>
       </c>
       <c r="C143" t="n">
@@ -17052,7 +17052,7 @@
       </c>
       <c r="B144" t="inlineStr">
         <is>
-          <t>2026-07-11 08:19:17 PM PT</t>
+          <t>2026-07-11 08:21:18 PM PT</t>
         </is>
       </c>
       <c r="C144" t="n">
@@ -17166,7 +17166,7 @@
       </c>
       <c r="B145" t="inlineStr">
         <is>
-          <t>2026-07-11 08:19:17 PM PT</t>
+          <t>2026-07-11 08:21:18 PM PT</t>
         </is>
       </c>
       <c r="C145" t="n">
@@ -17280,7 +17280,7 @@
       </c>
       <c r="B146" t="inlineStr">
         <is>
-          <t>2026-07-11 08:19:18 PM PT</t>
+          <t>2026-07-11 08:21:18 PM PT</t>
         </is>
       </c>
       <c r="C146" t="n">
@@ -17293,7 +17293,7 @@
       </c>
       <c r="E146" t="inlineStr">
         <is>
-          <t>Top 7 | 1 out</t>
+          <t>Top 7 | 2 out</t>
         </is>
       </c>
       <c r="F146" t="n">
@@ -17305,7 +17305,7 @@
         </is>
       </c>
       <c r="H146" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I146" t="n">
         <v>0</v>
@@ -17389,7 +17389,7 @@
         <v>4</v>
       </c>
       <c r="AF146" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AG146" t="n">
         <v>5</v>
@@ -17403,7 +17403,7 @@
       </c>
       <c r="B147" t="inlineStr">
         <is>
-          <t>2026-07-11 08:19:17 PM PT</t>
+          <t>2026-07-11 08:21:18 PM PT</t>
         </is>
       </c>
       <c r="C147" t="n">
@@ -17517,7 +17517,7 @@
       </c>
       <c r="B148" t="inlineStr">
         <is>
-          <t>2026-07-11 08:19:17 PM PT</t>
+          <t>2026-07-11 08:21:17 PM PT</t>
         </is>
       </c>
       <c r="C148" t="n">
@@ -17631,7 +17631,7 @@
       </c>
       <c r="B149" t="inlineStr">
         <is>
-          <t>2026-07-11 08:19:17 PM PT</t>
+          <t>2026-07-11 08:21:16 PM PT</t>
         </is>
       </c>
       <c r="C149" t="n">
@@ -17745,7 +17745,7 @@
       </c>
       <c r="B150" t="inlineStr">
         <is>
-          <t>2026-07-11 08:19:16 PM PT</t>
+          <t>2026-07-11 08:21:16 PM PT</t>
         </is>
       </c>
       <c r="C150" t="n">
@@ -17859,7 +17859,7 @@
       </c>
       <c r="B151" t="inlineStr">
         <is>
-          <t>2026-07-11 08:19:16 PM PT</t>
+          <t>2026-07-11 08:21:16 PM PT</t>
         </is>
       </c>
       <c r="C151" t="n">
@@ -17973,7 +17973,7 @@
       </c>
       <c r="B152" t="inlineStr">
         <is>
-          <t>2026-07-11 08:19:16 PM PT</t>
+          <t>2026-07-11 08:21:16 PM PT</t>
         </is>
       </c>
       <c r="C152" t="n">
@@ -18087,7 +18087,7 @@
       </c>
       <c r="B153" t="inlineStr">
         <is>
-          <t>2026-07-11 08:19:17 PM PT</t>
+          <t>2026-07-11 08:21:17 PM PT</t>
         </is>
       </c>
       <c r="C153" t="n">
@@ -18201,7 +18201,7 @@
       </c>
       <c r="B154" t="inlineStr">
         <is>
-          <t>2026-07-11 08:19:17 PM PT</t>
+          <t>2026-07-11 08:21:17 PM PT</t>
         </is>
       </c>
       <c r="C154" t="n">
@@ -18315,7 +18315,7 @@
       </c>
       <c r="B155" t="inlineStr">
         <is>
-          <t>2026-07-11 08:19:16 PM PT</t>
+          <t>2026-07-11 08:21:16 PM PT</t>
         </is>
       </c>
       <c r="C155" t="n">
@@ -18429,7 +18429,7 @@
       </c>
       <c r="B156" t="inlineStr">
         <is>
-          <t>2026-07-11 08:19:18 PM PT</t>
+          <t>2026-07-11 08:21:18 PM PT</t>
         </is>
       </c>
       <c r="C156" t="n">
@@ -18442,7 +18442,7 @@
       </c>
       <c r="E156" t="inlineStr">
         <is>
-          <t>Bottom 7 | 2 out</t>
+          <t>Bottom 7 | 3 out</t>
         </is>
       </c>
       <c r="F156" t="n">
@@ -18454,13 +18454,13 @@
         </is>
       </c>
       <c r="H156" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="I156" t="n">
         <v>3</v>
       </c>
       <c r="J156" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="K156" t="inlineStr">
         <is>
@@ -18552,7 +18552,7 @@
       </c>
       <c r="B157" t="inlineStr">
         <is>
-          <t>2026-07-11 08:19:18 PM PT</t>
+          <t>2026-07-11 08:21:18 PM PT</t>
         </is>
       </c>
       <c r="C157" t="n">
@@ -18565,7 +18565,7 @@
       </c>
       <c r="E157" t="inlineStr">
         <is>
-          <t>Bottom 7 | 2 out</t>
+          <t>Bottom 7 | 3 out</t>
         </is>
       </c>
       <c r="F157" t="n">
@@ -18577,13 +18577,13 @@
         </is>
       </c>
       <c r="H157" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="I157" t="n">
         <v>3</v>
       </c>
       <c r="J157" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="K157" t="inlineStr">
         <is>
@@ -18675,7 +18675,7 @@
       </c>
       <c r="B158" t="inlineStr">
         <is>
-          <t>2026-07-11 08:19:18 PM PT</t>
+          <t>2026-07-11 08:21:18 PM PT</t>
         </is>
       </c>
       <c r="C158" t="n">
@@ -18688,7 +18688,7 @@
       </c>
       <c r="E158" t="inlineStr">
         <is>
-          <t>Bottom 7 | 2 out</t>
+          <t>Bottom 7 | 3 out</t>
         </is>
       </c>
       <c r="F158" t="n">
@@ -18700,13 +18700,13 @@
         </is>
       </c>
       <c r="H158" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="I158" t="n">
         <v>3</v>
       </c>
       <c r="J158" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="K158" t="inlineStr">
         <is>
@@ -18798,7 +18798,7 @@
       </c>
       <c r="B159" t="inlineStr">
         <is>
-          <t>2026-07-11 08:19:18 PM PT</t>
+          <t>2026-07-11 08:21:18 PM PT</t>
         </is>
       </c>
       <c r="C159" t="n">
@@ -18811,7 +18811,7 @@
       </c>
       <c r="E159" t="inlineStr">
         <is>
-          <t>Bottom 7 | 2 out</t>
+          <t>Bottom 7 | 3 out</t>
         </is>
       </c>
       <c r="F159" t="n">
@@ -18823,13 +18823,13 @@
         </is>
       </c>
       <c r="H159" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="I159" t="n">
         <v>3</v>
       </c>
       <c r="J159" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="K159" t="inlineStr">
         <is>
@@ -18921,7 +18921,7 @@
       </c>
       <c r="B160" t="inlineStr">
         <is>
-          <t>2026-07-11 08:19:17 PM PT</t>
+          <t>2026-07-11 08:21:18 PM PT</t>
         </is>
       </c>
       <c r="C160" t="n">
@@ -19035,7 +19035,7 @@
       </c>
       <c r="B161" t="inlineStr">
         <is>
-          <t>2026-07-11 08:19:17 PM PT</t>
+          <t>2026-07-11 08:21:18 PM PT</t>
         </is>
       </c>
       <c r="C161" t="n">
@@ -19149,7 +19149,7 @@
       </c>
       <c r="B162" t="inlineStr">
         <is>
-          <t>2026-07-11 08:19:17 PM PT</t>
+          <t>2026-07-11 08:21:18 PM PT</t>
         </is>
       </c>
       <c r="C162" t="n">
@@ -19263,7 +19263,7 @@
       </c>
       <c r="B163" t="inlineStr">
         <is>
-          <t>2026-07-11 08:19:17 PM PT</t>
+          <t>2026-07-11 08:21:18 PM PT</t>
         </is>
       </c>
       <c r="C163" t="n">
@@ -19377,7 +19377,7 @@
       </c>
       <c r="B164" t="inlineStr">
         <is>
-          <t>2026-07-11 08:19:17 PM PT</t>
+          <t>2026-07-11 08:21:18 PM PT</t>
         </is>
       </c>
       <c r="C164" t="n">
@@ -19491,7 +19491,7 @@
       </c>
       <c r="B165" t="inlineStr">
         <is>
-          <t>2026-07-11 08:19:17 PM PT</t>
+          <t>2026-07-11 08:21:17 PM PT</t>
         </is>
       </c>
       <c r="C165" t="n">
@@ -19605,7 +19605,7 @@
       </c>
       <c r="B166" t="inlineStr">
         <is>
-          <t>2026-07-11 08:19:17 PM PT</t>
+          <t>2026-07-11 08:21:17 PM PT</t>
         </is>
       </c>
       <c r="C166" t="n">
@@ -19719,7 +19719,7 @@
       </c>
       <c r="B167" t="inlineStr">
         <is>
-          <t>2026-07-11 08:19:17 PM PT</t>
+          <t>2026-07-11 08:21:17 PM PT</t>
         </is>
       </c>
       <c r="C167" t="n">
@@ -19833,7 +19833,7 @@
       </c>
       <c r="B168" t="inlineStr">
         <is>
-          <t>2026-07-11 08:19:17 PM PT</t>
+          <t>2026-07-11 08:21:17 PM PT</t>
         </is>
       </c>
       <c r="C168" t="n">
@@ -19947,7 +19947,7 @@
       </c>
       <c r="B169" t="inlineStr">
         <is>
-          <t>2026-07-11 08:19:17 PM PT</t>
+          <t>2026-07-11 08:21:18 PM PT</t>
         </is>
       </c>
       <c r="C169" t="n">
@@ -20061,7 +20061,7 @@
       </c>
       <c r="B170" t="inlineStr">
         <is>
-          <t>2026-07-11 08:19:16 PM PT</t>
+          <t>2026-07-11 08:21:16 PM PT</t>
         </is>
       </c>
       <c r="C170" t="n">
@@ -20175,7 +20175,7 @@
       </c>
       <c r="B171" t="inlineStr">
         <is>
-          <t>2026-07-11 08:19:18 PM PT</t>
+          <t>2026-07-11 08:21:18 PM PT</t>
         </is>
       </c>
       <c r="C171" t="n">
@@ -20188,7 +20188,7 @@
       </c>
       <c r="E171" t="inlineStr">
         <is>
-          <t>Top 7 | 1 out</t>
+          <t>Top 7 | 2 out</t>
         </is>
       </c>
       <c r="F171" t="n">
@@ -20200,7 +20200,7 @@
         </is>
       </c>
       <c r="H171" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I171" t="n">
         <v>0</v>
@@ -20298,7 +20298,7 @@
       </c>
       <c r="B172" t="inlineStr">
         <is>
-          <t>2026-07-11 08:19:18 PM PT</t>
+          <t>2026-07-11 08:21:18 PM PT</t>
         </is>
       </c>
       <c r="C172" t="n">
@@ -20311,7 +20311,7 @@
       </c>
       <c r="E172" t="inlineStr">
         <is>
-          <t>Top 7 | 1 out</t>
+          <t>Top 7 | 2 out</t>
         </is>
       </c>
       <c r="F172" t="n">
@@ -20323,7 +20323,7 @@
         </is>
       </c>
       <c r="H172" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I172" t="n">
         <v>0</v>
@@ -20421,7 +20421,7 @@
       </c>
       <c r="B173" t="inlineStr">
         <is>
-          <t>2026-07-11 08:19:17 PM PT</t>
+          <t>2026-07-11 08:21:17 PM PT</t>
         </is>
       </c>
       <c r="C173" t="n">
@@ -20535,7 +20535,7 @@
       </c>
       <c r="B174" t="inlineStr">
         <is>
-          <t>2026-07-11 08:19:17 PM PT</t>
+          <t>2026-07-11 08:21:17 PM PT</t>
         </is>
       </c>
       <c r="C174" t="n">
@@ -20649,7 +20649,7 @@
       </c>
       <c r="B175" t="inlineStr">
         <is>
-          <t>2026-07-11 08:19:16 PM PT</t>
+          <t>2026-07-11 08:21:16 PM PT</t>
         </is>
       </c>
       <c r="C175" t="n">
@@ -20763,7 +20763,7 @@
       </c>
       <c r="B176" t="inlineStr">
         <is>
-          <t>2026-07-11 08:19:16 PM PT</t>
+          <t>2026-07-11 08:21:16 PM PT</t>
         </is>
       </c>
       <c r="C176" t="n">
@@ -20877,7 +20877,7 @@
       </c>
       <c r="B177" t="inlineStr">
         <is>
-          <t>2026-07-11 08:19:16 PM PT</t>
+          <t>2026-07-11 08:21:16 PM PT</t>
         </is>
       </c>
       <c r="C177" t="n">
@@ -20991,7 +20991,7 @@
       </c>
       <c r="B178" t="inlineStr">
         <is>
-          <t>2026-07-11 08:19:16 PM PT</t>
+          <t>2026-07-11 08:21:16 PM PT</t>
         </is>
       </c>
       <c r="C178" t="n">
@@ -21105,7 +21105,7 @@
       </c>
       <c r="B179" t="inlineStr">
         <is>
-          <t>2026-07-11 08:19:16 PM PT</t>
+          <t>2026-07-11 08:21:16 PM PT</t>
         </is>
       </c>
       <c r="C179" t="n">
@@ -21219,7 +21219,7 @@
       </c>
       <c r="B180" t="inlineStr">
         <is>
-          <t>2026-07-11 08:19:17 PM PT</t>
+          <t>2026-07-11 08:21:17 PM PT</t>
         </is>
       </c>
       <c r="C180" t="n">
@@ -21333,7 +21333,7 @@
       </c>
       <c r="B181" t="inlineStr">
         <is>
-          <t>2026-07-11 08:19:17 PM PT</t>
+          <t>2026-07-11 08:21:17 PM PT</t>
         </is>
       </c>
       <c r="C181" t="n">
@@ -21447,7 +21447,7 @@
       </c>
       <c r="B182" t="inlineStr">
         <is>
-          <t>2026-07-11 08:19:17 PM PT</t>
+          <t>2026-07-11 08:21:17 PM PT</t>
         </is>
       </c>
       <c r="C182" t="n">
@@ -21561,7 +21561,7 @@
       </c>
       <c r="B183" t="inlineStr">
         <is>
-          <t>2026-07-11 08:19:17 PM PT</t>
+          <t>2026-07-11 08:21:17 PM PT</t>
         </is>
       </c>
       <c r="C183" t="n">
@@ -21675,7 +21675,7 @@
       </c>
       <c r="B184" t="inlineStr">
         <is>
-          <t>2026-07-11 08:19:16 PM PT</t>
+          <t>2026-07-11 08:21:16 PM PT</t>
         </is>
       </c>
       <c r="C184" t="n">
@@ -21789,7 +21789,7 @@
       </c>
       <c r="B185" t="inlineStr">
         <is>
-          <t>2026-07-11 08:19:16 PM PT</t>
+          <t>2026-07-11 08:21:16 PM PT</t>
         </is>
       </c>
       <c r="C185" t="n">
@@ -21903,7 +21903,7 @@
       </c>
       <c r="B186" t="inlineStr">
         <is>
-          <t>2026-07-11 08:19:17 PM PT</t>
+          <t>2026-07-11 08:21:17 PM PT</t>
         </is>
       </c>
       <c r="C186" t="n">
@@ -22017,7 +22017,7 @@
       </c>
       <c r="B187" t="inlineStr">
         <is>
-          <t>2026-07-11 08:19:17 PM PT</t>
+          <t>2026-07-11 08:21:17 PM PT</t>
         </is>
       </c>
       <c r="C187" t="n">
@@ -22131,7 +22131,7 @@
       </c>
       <c r="B188" t="inlineStr">
         <is>
-          <t>2026-07-11 08:19:17 PM PT</t>
+          <t>2026-07-11 08:21:17 PM PT</t>
         </is>
       </c>
       <c r="C188" t="n">
@@ -22245,7 +22245,7 @@
       </c>
       <c r="B189" t="inlineStr">
         <is>
-          <t>2026-07-11 08:19:17 PM PT</t>
+          <t>2026-07-11 08:21:18 PM PT</t>
         </is>
       </c>
       <c r="C189" t="n">
@@ -22359,7 +22359,7 @@
       </c>
       <c r="B190" t="inlineStr">
         <is>
-          <t>2026-07-11 08:19:17 PM PT</t>
+          <t>2026-07-11 08:21:17 PM PT</t>
         </is>
       </c>
       <c r="C190" t="n">
@@ -22473,7 +22473,7 @@
       </c>
       <c r="B191" t="inlineStr">
         <is>
-          <t>2026-07-11 08:19:17 PM PT</t>
+          <t>2026-07-11 08:21:17 PM PT</t>
         </is>
       </c>
       <c r="C191" t="n">
@@ -22587,7 +22587,7 @@
       </c>
       <c r="B192" t="inlineStr">
         <is>
-          <t>2026-07-11 08:19:18 PM PT</t>
+          <t>2026-07-11 08:21:18 PM PT</t>
         </is>
       </c>
       <c r="C192" t="n">
@@ -22600,7 +22600,7 @@
       </c>
       <c r="E192" t="inlineStr">
         <is>
-          <t>Top 7 | 1 out</t>
+          <t>Top 7 | 2 out</t>
         </is>
       </c>
       <c r="F192" t="n">
@@ -22612,7 +22612,7 @@
         </is>
       </c>
       <c r="H192" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I192" t="n">
         <v>0</v>
@@ -22696,7 +22696,7 @@
         <v>2</v>
       </c>
       <c r="AF192" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AG192" t="n">
         <v>5</v>
@@ -22710,7 +22710,7 @@
       </c>
       <c r="B193" t="inlineStr">
         <is>
-          <t>2026-07-11 08:19:18 PM PT</t>
+          <t>2026-07-11 08:21:18 PM PT</t>
         </is>
       </c>
       <c r="C193" t="n">
@@ -22723,7 +22723,7 @@
       </c>
       <c r="E193" t="inlineStr">
         <is>
-          <t>Top 7 | 1 out</t>
+          <t>Top 7 | 2 out</t>
         </is>
       </c>
       <c r="F193" t="n">
@@ -22735,7 +22735,7 @@
         </is>
       </c>
       <c r="H193" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I193" t="n">
         <v>0</v>
@@ -22819,7 +22819,7 @@
         <v>2</v>
       </c>
       <c r="AF193" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AG193" t="n">
         <v>5</v>
@@ -22833,7 +22833,7 @@
       </c>
       <c r="B194" t="inlineStr">
         <is>
-          <t>2026-07-11 08:19:17 PM PT</t>
+          <t>2026-07-11 08:21:16 PM PT</t>
         </is>
       </c>
       <c r="C194" t="n">
@@ -22947,7 +22947,7 @@
       </c>
       <c r="B195" t="inlineStr">
         <is>
-          <t>2026-07-11 08:19:17 PM PT</t>
+          <t>2026-07-11 08:21:18 PM PT</t>
         </is>
       </c>
       <c r="C195" t="n">
@@ -23061,7 +23061,7 @@
       </c>
       <c r="B196" t="inlineStr">
         <is>
-          <t>2026-07-11 08:19:17 PM PT</t>
+          <t>2026-07-11 08:21:18 PM PT</t>
         </is>
       </c>
       <c r="C196" t="n">
@@ -23175,7 +23175,7 @@
       </c>
       <c r="B197" t="inlineStr">
         <is>
-          <t>2026-07-11 08:19:17 PM PT</t>
+          <t>2026-07-11 08:21:18 PM PT</t>
         </is>
       </c>
       <c r="C197" t="n">
@@ -23289,7 +23289,7 @@
       </c>
       <c r="B198" t="inlineStr">
         <is>
-          <t>2026-07-11 08:19:17 PM PT</t>
+          <t>2026-07-11 08:21:17 PM PT</t>
         </is>
       </c>
       <c r="C198" t="n">
@@ -23403,7 +23403,7 @@
       </c>
       <c r="B199" t="inlineStr">
         <is>
-          <t>2026-07-11 08:19:17 PM PT</t>
+          <t>2026-07-11 08:21:17 PM PT</t>
         </is>
       </c>
       <c r="C199" t="n">
@@ -23517,7 +23517,7 @@
       </c>
       <c r="B200" t="inlineStr">
         <is>
-          <t>2026-07-11 08:19:17 PM PT</t>
+          <t>2026-07-11 08:21:17 PM PT</t>
         </is>
       </c>
       <c r="C200" t="n">
@@ -23631,7 +23631,7 @@
       </c>
       <c r="B201" t="inlineStr">
         <is>
-          <t>2026-07-11 08:19:17 PM PT</t>
+          <t>2026-07-11 08:21:18 PM PT</t>
         </is>
       </c>
       <c r="C201" t="n">
@@ -23745,7 +23745,7 @@
       </c>
       <c r="B202" t="inlineStr">
         <is>
-          <t>2026-07-11 08:19:17 PM PT</t>
+          <t>2026-07-11 08:21:17 PM PT</t>
         </is>
       </c>
       <c r="C202" t="n">
@@ -23859,7 +23859,7 @@
       </c>
       <c r="B203" t="inlineStr">
         <is>
-          <t>2026-07-11 08:19:17 PM PT</t>
+          <t>2026-07-11 08:21:17 PM PT</t>
         </is>
       </c>
       <c r="C203" t="n">
@@ -23973,7 +23973,7 @@
       </c>
       <c r="B204" t="inlineStr">
         <is>
-          <t>2026-07-11 08:19:17 PM PT</t>
+          <t>2026-07-11 08:21:17 PM PT</t>
         </is>
       </c>
       <c r="C204" t="n">
@@ -24087,7 +24087,7 @@
       </c>
       <c r="B205" t="inlineStr">
         <is>
-          <t>2026-07-11 08:19:17 PM PT</t>
+          <t>2026-07-11 08:21:16 PM PT</t>
         </is>
       </c>
       <c r="C205" t="n">
@@ -24201,7 +24201,7 @@
       </c>
       <c r="B206" t="inlineStr">
         <is>
-          <t>2026-07-11 08:19:17 PM PT</t>
+          <t>2026-07-11 08:21:16 PM PT</t>
         </is>
       </c>
       <c r="C206" t="n">
@@ -24315,7 +24315,7 @@
       </c>
       <c r="B207" t="inlineStr">
         <is>
-          <t>2026-07-11 08:19:17 PM PT</t>
+          <t>2026-07-11 08:21:17 PM PT</t>
         </is>
       </c>
       <c r="C207" t="n">
@@ -24429,7 +24429,7 @@
       </c>
       <c r="B208" t="inlineStr">
         <is>
-          <t>2026-07-11 08:19:17 PM PT</t>
+          <t>2026-07-11 08:21:18 PM PT</t>
         </is>
       </c>
       <c r="C208" t="n">
@@ -24543,7 +24543,7 @@
       </c>
       <c r="B209" t="inlineStr">
         <is>
-          <t>2026-07-11 08:19:17 PM PT</t>
+          <t>2026-07-11 08:21:18 PM PT</t>
         </is>
       </c>
       <c r="C209" t="n">
@@ -24657,7 +24657,7 @@
       </c>
       <c r="B210" t="inlineStr">
         <is>
-          <t>2026-07-11 08:19:17 PM PT</t>
+          <t>2026-07-11 08:21:18 PM PT</t>
         </is>
       </c>
       <c r="C210" t="n">
@@ -24771,7 +24771,7 @@
       </c>
       <c r="B211" t="inlineStr">
         <is>
-          <t>2026-07-11 08:19:17 PM PT</t>
+          <t>2026-07-11 08:21:18 PM PT</t>
         </is>
       </c>
       <c r="C211" t="n">
@@ -24885,7 +24885,7 @@
       </c>
       <c r="B212" t="inlineStr">
         <is>
-          <t>2026-07-11 08:19:16 PM PT</t>
+          <t>2026-07-11 08:21:16 PM PT</t>
         </is>
       </c>
       <c r="C212" t="n">
@@ -24999,7 +24999,7 @@
       </c>
       <c r="B213" t="inlineStr">
         <is>
-          <t>2026-07-11 08:19:17 PM PT</t>
+          <t>2026-07-11 08:21:17 PM PT</t>
         </is>
       </c>
       <c r="C213" t="n">
@@ -25113,7 +25113,7 @@
       </c>
       <c r="B214" t="inlineStr">
         <is>
-          <t>2026-07-11 08:19:17 PM PT</t>
+          <t>2026-07-11 08:21:17 PM PT</t>
         </is>
       </c>
       <c r="C214" t="n">
@@ -25227,7 +25227,7 @@
       </c>
       <c r="B215" t="inlineStr">
         <is>
-          <t>2026-07-11 08:19:16 PM PT</t>
+          <t>2026-07-11 08:21:16 PM PT</t>
         </is>
       </c>
       <c r="C215" t="n">
@@ -25341,7 +25341,7 @@
       </c>
       <c r="B216" t="inlineStr">
         <is>
-          <t>2026-07-11 08:19:17 PM PT</t>
+          <t>2026-07-11 08:21:17 PM PT</t>
         </is>
       </c>
       <c r="C216" t="n">
@@ -25455,7 +25455,7 @@
       </c>
       <c r="B217" t="inlineStr">
         <is>
-          <t>2026-07-11 08:19:17 PM PT</t>
+          <t>2026-07-11 08:21:17 PM PT</t>
         </is>
       </c>
       <c r="C217" t="n">
@@ -25569,7 +25569,7 @@
       </c>
       <c r="B218" t="inlineStr">
         <is>
-          <t>2026-07-11 08:19:17 PM PT</t>
+          <t>2026-07-11 08:21:17 PM PT</t>
         </is>
       </c>
       <c r="C218" t="n">
@@ -25683,7 +25683,7 @@
       </c>
       <c r="B219" t="inlineStr">
         <is>
-          <t>2026-07-11 08:19:17 PM PT</t>
+          <t>2026-07-11 08:21:17 PM PT</t>
         </is>
       </c>
       <c r="C219" t="n">
@@ -25797,7 +25797,7 @@
       </c>
       <c r="B220" t="inlineStr">
         <is>
-          <t>2026-07-11 08:19:17 PM PT</t>
+          <t>2026-07-11 08:21:17 PM PT</t>
         </is>
       </c>
       <c r="C220" t="n">
@@ -25911,7 +25911,7 @@
       </c>
       <c r="B221" t="inlineStr">
         <is>
-          <t>2026-07-11 08:19:17 PM PT</t>
+          <t>2026-07-11 08:21:17 PM PT</t>
         </is>
       </c>
       <c r="C221" t="n">
@@ -26025,7 +26025,7 @@
       </c>
       <c r="B222" t="inlineStr">
         <is>
-          <t>2026-07-11 08:19:17 PM PT</t>
+          <t>2026-07-11 08:21:17 PM PT</t>
         </is>
       </c>
       <c r="C222" t="n">
@@ -26139,7 +26139,7 @@
       </c>
       <c r="B223" t="inlineStr">
         <is>
-          <t>2026-07-11 08:19:16 PM PT</t>
+          <t>2026-07-11 08:21:16 PM PT</t>
         </is>
       </c>
       <c r="C223" t="n">
@@ -26253,7 +26253,7 @@
       </c>
       <c r="B224" t="inlineStr">
         <is>
-          <t>2026-07-11 08:19:16 PM PT</t>
+          <t>2026-07-11 08:21:16 PM PT</t>
         </is>
       </c>
       <c r="C224" t="n">
@@ -26367,7 +26367,7 @@
       </c>
       <c r="B225" t="inlineStr">
         <is>
-          <t>2026-07-11 08:19:17 PM PT</t>
+          <t>2026-07-11 08:21:17 PM PT</t>
         </is>
       </c>
       <c r="C225" t="n">
@@ -26481,7 +26481,7 @@
       </c>
       <c r="B226" t="inlineStr">
         <is>
-          <t>2026-07-11 08:19:17 PM PT</t>
+          <t>2026-07-11 08:21:17 PM PT</t>
         </is>
       </c>
       <c r="C226" t="n">
@@ -26595,7 +26595,7 @@
       </c>
       <c r="B227" t="inlineStr">
         <is>
-          <t>2026-07-11 08:19:17 PM PT</t>
+          <t>2026-07-11 08:21:18 PM PT</t>
         </is>
       </c>
       <c r="C227" t="n">
@@ -26709,7 +26709,7 @@
       </c>
       <c r="B228" t="inlineStr">
         <is>
-          <t>2026-07-11 08:19:17 PM PT</t>
+          <t>2026-07-11 08:21:18 PM PT</t>
         </is>
       </c>
       <c r="C228" t="n">
@@ -26823,7 +26823,7 @@
       </c>
       <c r="B229" t="inlineStr">
         <is>
-          <t>2026-07-11 08:19:18 PM PT</t>
+          <t>2026-07-11 08:21:18 PM PT</t>
         </is>
       </c>
       <c r="C229" t="n">
@@ -26836,7 +26836,7 @@
       </c>
       <c r="E229" t="inlineStr">
         <is>
-          <t>Bottom 7 | 2 out</t>
+          <t>Bottom 7 | 3 out</t>
         </is>
       </c>
       <c r="F229" t="n">
@@ -26848,13 +26848,13 @@
         </is>
       </c>
       <c r="H229" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="I229" t="n">
         <v>3</v>
       </c>
       <c r="J229" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="K229" t="inlineStr">
         <is>
@@ -26946,7 +26946,7 @@
       </c>
       <c r="B230" t="inlineStr">
         <is>
-          <t>2026-07-11 08:19:17 PM PT</t>
+          <t>2026-07-11 08:21:17 PM PT</t>
         </is>
       </c>
       <c r="C230" t="n">
@@ -27060,7 +27060,7 @@
       </c>
       <c r="B231" t="inlineStr">
         <is>
-          <t>2026-07-11 08:19:17 PM PT</t>
+          <t>2026-07-11 08:21:17 PM PT</t>
         </is>
       </c>
       <c r="C231" t="n">
@@ -27174,7 +27174,7 @@
       </c>
       <c r="B232" t="inlineStr">
         <is>
-          <t>2026-07-11 08:19:17 PM PT</t>
+          <t>2026-07-11 08:21:17 PM PT</t>
         </is>
       </c>
       <c r="C232" t="n">
@@ -27288,7 +27288,7 @@
       </c>
       <c r="B233" t="inlineStr">
         <is>
-          <t>2026-07-11 08:19:17 PM PT</t>
+          <t>2026-07-11 08:21:17 PM PT</t>
         </is>
       </c>
       <c r="C233" t="n">
@@ -27402,7 +27402,7 @@
       </c>
       <c r="B234" t="inlineStr">
         <is>
-          <t>2026-07-11 08:19:18 PM PT</t>
+          <t>2026-07-11 08:21:18 PM PT</t>
         </is>
       </c>
       <c r="C234" t="n">
@@ -27415,7 +27415,7 @@
       </c>
       <c r="E234" t="inlineStr">
         <is>
-          <t>Top 7 | 1 out</t>
+          <t>Top 7 | 2 out</t>
         </is>
       </c>
       <c r="F234" t="n">
@@ -27427,7 +27427,7 @@
         </is>
       </c>
       <c r="H234" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I234" t="n">
         <v>0</v>
@@ -27511,7 +27511,7 @@
         <v>0</v>
       </c>
       <c r="AF234" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AG234" t="n">
         <v>5</v>
@@ -27525,7 +27525,7 @@
       </c>
       <c r="B235" t="inlineStr">
         <is>
-          <t>2026-07-11 08:19:18 PM PT</t>
+          <t>2026-07-11 08:21:18 PM PT</t>
         </is>
       </c>
       <c r="C235" t="n">
@@ -27538,7 +27538,7 @@
       </c>
       <c r="E235" t="inlineStr">
         <is>
-          <t>Top 7 | 1 out</t>
+          <t>Top 7 | 2 out</t>
         </is>
       </c>
       <c r="F235" t="n">
@@ -27550,7 +27550,7 @@
         </is>
       </c>
       <c r="H235" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I235" t="n">
         <v>0</v>
@@ -27634,7 +27634,7 @@
         <v>0</v>
       </c>
       <c r="AF235" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AG235" t="n">
         <v>5</v>
@@ -27648,7 +27648,7 @@
       </c>
       <c r="B236" t="inlineStr">
         <is>
-          <t>2026-07-11 08:19:17 PM PT</t>
+          <t>2026-07-11 08:21:16 PM PT</t>
         </is>
       </c>
       <c r="C236" t="n">
@@ -27762,7 +27762,7 @@
       </c>
       <c r="B237" t="inlineStr">
         <is>
-          <t>2026-07-11 08:19:17 PM PT</t>
+          <t>2026-07-11 08:21:16 PM PT</t>
         </is>
       </c>
       <c r="C237" t="n">
@@ -27876,7 +27876,7 @@
       </c>
       <c r="B238" t="inlineStr">
         <is>
-          <t>2026-07-11 08:19:17 PM PT</t>
+          <t>2026-07-11 08:21:16 PM PT</t>
         </is>
       </c>
       <c r="C238" t="n">
@@ -27990,7 +27990,7 @@
       </c>
       <c r="B239" t="inlineStr">
         <is>
-          <t>2026-07-11 08:19:17 PM PT</t>
+          <t>2026-07-11 08:21:16 PM PT</t>
         </is>
       </c>
       <c r="C239" t="n">
@@ -28104,7 +28104,7 @@
       </c>
       <c r="B240" t="inlineStr">
         <is>
-          <t>2026-07-11 08:19:17 PM PT</t>
+          <t>2026-07-11 08:21:16 PM PT</t>
         </is>
       </c>
       <c r="C240" t="n">
@@ -28218,7 +28218,7 @@
       </c>
       <c r="B241" t="inlineStr">
         <is>
-          <t>2026-07-11 08:19:17 PM PT</t>
+          <t>2026-07-11 08:21:16 PM PT</t>
         </is>
       </c>
       <c r="C241" t="n">
@@ -28332,7 +28332,7 @@
       </c>
       <c r="B242" t="inlineStr">
         <is>
-          <t>2026-07-11 08:19:17 PM PT</t>
+          <t>2026-07-11 08:21:16 PM PT</t>
         </is>
       </c>
       <c r="C242" t="n">
@@ -28446,7 +28446,7 @@
       </c>
       <c r="B243" t="inlineStr">
         <is>
-          <t>2026-07-11 08:19:17 PM PT</t>
+          <t>2026-07-11 08:21:18 PM PT</t>
         </is>
       </c>
       <c r="C243" t="n">
@@ -28560,7 +28560,7 @@
       </c>
       <c r="B244" t="inlineStr">
         <is>
-          <t>2026-07-11 08:19:17 PM PT</t>
+          <t>2026-07-11 08:21:18 PM PT</t>
         </is>
       </c>
       <c r="C244" t="n">
@@ -28674,7 +28674,7 @@
       </c>
       <c r="B245" t="inlineStr">
         <is>
-          <t>2026-07-11 08:19:17 PM PT</t>
+          <t>2026-07-11 08:21:18 PM PT</t>
         </is>
       </c>
       <c r="C245" t="n">
@@ -28788,7 +28788,7 @@
       </c>
       <c r="B246" t="inlineStr">
         <is>
-          <t>2026-07-11 08:19:17 PM PT</t>
+          <t>2026-07-11 08:21:18 PM PT</t>
         </is>
       </c>
       <c r="C246" t="n">
@@ -28902,7 +28902,7 @@
       </c>
       <c r="B247" t="inlineStr">
         <is>
-          <t>2026-07-11 08:19:17 PM PT</t>
+          <t>2026-07-11 08:21:18 PM PT</t>
         </is>
       </c>
       <c r="C247" t="n">
@@ -29016,7 +29016,7 @@
       </c>
       <c r="B248" t="inlineStr">
         <is>
-          <t>2026-07-11 08:19:17 PM PT</t>
+          <t>2026-07-11 08:21:18 PM PT</t>
         </is>
       </c>
       <c r="C248" t="n">
@@ -29130,7 +29130,7 @@
       </c>
       <c r="B249" t="inlineStr">
         <is>
-          <t>2026-07-11 08:19:17 PM PT</t>
+          <t>2026-07-11 08:21:17 PM PT</t>
         </is>
       </c>
       <c r="C249" t="n">
@@ -29244,7 +29244,7 @@
       </c>
       <c r="B250" t="inlineStr">
         <is>
-          <t>2026-07-11 08:19:17 PM PT</t>
+          <t>2026-07-11 08:21:17 PM PT</t>
         </is>
       </c>
       <c r="C250" t="n">
@@ -29358,7 +29358,7 @@
       </c>
       <c r="B251" t="inlineStr">
         <is>
-          <t>2026-07-11 08:19:17 PM PT</t>
+          <t>2026-07-11 08:21:17 PM PT</t>
         </is>
       </c>
       <c r="C251" t="n">
@@ -29472,7 +29472,7 @@
       </c>
       <c r="B252" t="inlineStr">
         <is>
-          <t>2026-07-11 08:19:17 PM PT</t>
+          <t>2026-07-11 08:21:18 PM PT</t>
         </is>
       </c>
       <c r="C252" t="n">
@@ -29586,7 +29586,7 @@
       </c>
       <c r="B253" t="inlineStr">
         <is>
-          <t>2026-07-11 08:19:17 PM PT</t>
+          <t>2026-07-11 08:21:18 PM PT</t>
         </is>
       </c>
       <c r="C253" t="n">
@@ -29700,7 +29700,7 @@
       </c>
       <c r="B254" t="inlineStr">
         <is>
-          <t>2026-07-11 08:19:17 PM PT</t>
+          <t>2026-07-11 08:21:18 PM PT</t>
         </is>
       </c>
       <c r="C254" t="n">
@@ -29814,7 +29814,7 @@
       </c>
       <c r="B255" t="inlineStr">
         <is>
-          <t>2026-07-11 08:19:17 PM PT</t>
+          <t>2026-07-11 08:21:18 PM PT</t>
         </is>
       </c>
       <c r="C255" t="n">
@@ -29928,7 +29928,7 @@
       </c>
       <c r="B256" t="inlineStr">
         <is>
-          <t>2026-07-11 08:19:17 PM PT</t>
+          <t>2026-07-11 08:21:18 PM PT</t>
         </is>
       </c>
       <c r="C256" t="n">
@@ -30042,7 +30042,7 @@
       </c>
       <c r="B257" t="inlineStr">
         <is>
-          <t>2026-07-11 08:19:17 PM PT</t>
+          <t>2026-07-11 08:21:17 PM PT</t>
         </is>
       </c>
       <c r="C257" t="n">
@@ -30156,7 +30156,7 @@
       </c>
       <c r="B258" t="inlineStr">
         <is>
-          <t>2026-07-11 08:19:17 PM PT</t>
+          <t>2026-07-11 08:21:17 PM PT</t>
         </is>
       </c>
       <c r="C258" t="n">
@@ -30270,7 +30270,7 @@
       </c>
       <c r="B259" t="inlineStr">
         <is>
-          <t>2026-07-11 08:19:17 PM PT</t>
+          <t>2026-07-11 08:21:17 PM PT</t>
         </is>
       </c>
       <c r="C259" t="n">
@@ -30384,7 +30384,7 @@
       </c>
       <c r="B260" t="inlineStr">
         <is>
-          <t>2026-07-11 08:19:17 PM PT</t>
+          <t>2026-07-11 08:21:16 PM PT</t>
         </is>
       </c>
       <c r="C260" t="n">
@@ -30498,7 +30498,7 @@
       </c>
       <c r="B261" t="inlineStr">
         <is>
-          <t>2026-07-11 08:19:17 PM PT</t>
+          <t>2026-07-11 08:21:16 PM PT</t>
         </is>
       </c>
       <c r="C261" t="n">
@@ -30612,7 +30612,7 @@
       </c>
       <c r="B262" t="inlineStr">
         <is>
-          <t>2026-07-11 08:19:17 PM PT</t>
+          <t>2026-07-11 08:21:16 PM PT</t>
         </is>
       </c>
       <c r="C262" t="n">
@@ -30726,7 +30726,7 @@
       </c>
       <c r="B263" t="inlineStr">
         <is>
-          <t>2026-07-11 08:19:17 PM PT</t>
+          <t>2026-07-11 08:21:16 PM PT</t>
         </is>
       </c>
       <c r="C263" t="n">
@@ -30840,7 +30840,7 @@
       </c>
       <c r="B264" t="inlineStr">
         <is>
-          <t>2026-07-11 08:19:17 PM PT</t>
+          <t>2026-07-11 08:21:17 PM PT</t>
         </is>
       </c>
       <c r="C264" t="n">
@@ -30954,7 +30954,7 @@
       </c>
       <c r="B265" t="inlineStr">
         <is>
-          <t>2026-07-11 08:19:17 PM PT</t>
+          <t>2026-07-11 08:21:17 PM PT</t>
         </is>
       </c>
       <c r="C265" t="n">
@@ -31068,7 +31068,7 @@
       </c>
       <c r="B266" t="inlineStr">
         <is>
-          <t>2026-07-11 08:19:17 PM PT</t>
+          <t>2026-07-11 08:21:17 PM PT</t>
         </is>
       </c>
       <c r="C266" t="n">
@@ -31182,7 +31182,7 @@
       </c>
       <c r="B267" t="inlineStr">
         <is>
-          <t>2026-07-11 08:19:17 PM PT</t>
+          <t>2026-07-11 08:21:17 PM PT</t>
         </is>
       </c>
       <c r="C267" t="n">
@@ -31296,7 +31296,7 @@
       </c>
       <c r="B268" t="inlineStr">
         <is>
-          <t>2026-07-11 08:19:17 PM PT</t>
+          <t>2026-07-11 08:21:18 PM PT</t>
         </is>
       </c>
       <c r="C268" t="n">
@@ -31410,7 +31410,7 @@
       </c>
       <c r="B269" t="inlineStr">
         <is>
-          <t>2026-07-11 08:19:17 PM PT</t>
+          <t>2026-07-11 08:21:18 PM PT</t>
         </is>
       </c>
       <c r="C269" t="n">
@@ -31524,7 +31524,7 @@
       </c>
       <c r="B270" t="inlineStr">
         <is>
-          <t>2026-07-11 08:19:17 PM PT</t>
+          <t>2026-07-11 08:21:18 PM PT</t>
         </is>
       </c>
       <c r="C270" t="n">
@@ -31638,7 +31638,7 @@
       </c>
       <c r="B271" t="inlineStr">
         <is>
-          <t>2026-07-11 08:19:17 PM PT</t>
+          <t>2026-07-11 08:21:18 PM PT</t>
         </is>
       </c>
       <c r="C271" t="n">
@@ -31752,7 +31752,7 @@
       </c>
       <c r="B272" t="inlineStr">
         <is>
-          <t>2026-07-11 08:19:17 PM PT</t>
+          <t>2026-07-11 08:21:18 PM PT</t>
         </is>
       </c>
       <c r="C272" t="n">
@@ -31866,7 +31866,7 @@
       </c>
       <c r="B273" t="inlineStr">
         <is>
-          <t>2026-07-11 08:19:17 PM PT</t>
+          <t>2026-07-11 08:21:18 PM PT</t>
         </is>
       </c>
       <c r="C273" t="n">
@@ -31980,7 +31980,7 @@
       </c>
       <c r="B274" t="inlineStr">
         <is>
-          <t>2026-07-11 08:19:17 PM PT</t>
+          <t>2026-07-11 08:21:18 PM PT</t>
         </is>
       </c>
       <c r="C274" t="n">
@@ -32094,7 +32094,7 @@
       </c>
       <c r="B275" t="inlineStr">
         <is>
-          <t>2026-07-11 08:19:16 PM PT</t>
+          <t>2026-07-11 08:21:16 PM PT</t>
         </is>
       </c>
       <c r="C275" t="n">
@@ -32208,7 +32208,7 @@
       </c>
       <c r="B276" t="inlineStr">
         <is>
-          <t>2026-07-11 08:19:16 PM PT</t>
+          <t>2026-07-11 08:21:16 PM PT</t>
         </is>
       </c>
       <c r="C276" t="n">
@@ -32322,7 +32322,7 @@
       </c>
       <c r="B277" t="inlineStr">
         <is>
-          <t>2026-07-11 08:19:16 PM PT</t>
+          <t>2026-07-11 08:21:16 PM PT</t>
         </is>
       </c>
       <c r="C277" t="n">
@@ -32436,7 +32436,7 @@
       </c>
       <c r="B278" t="inlineStr">
         <is>
-          <t>2026-07-11 08:19:18 PM PT</t>
+          <t>2026-07-11 08:21:18 PM PT</t>
         </is>
       </c>
       <c r="C278" t="n">
@@ -32449,7 +32449,7 @@
       </c>
       <c r="E278" t="inlineStr">
         <is>
-          <t>Top 7 | 1 out</t>
+          <t>Top 7 | 2 out</t>
         </is>
       </c>
       <c r="F278" t="n">
@@ -32461,7 +32461,7 @@
         </is>
       </c>
       <c r="H278" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I278" t="n">
         <v>0</v>
@@ -32559,7 +32559,7 @@
       </c>
       <c r="B279" t="inlineStr">
         <is>
-          <t>2026-07-11 08:19:18 PM PT</t>
+          <t>2026-07-11 08:21:18 PM PT</t>
         </is>
       </c>
       <c r="C279" t="n">
@@ -32572,7 +32572,7 @@
       </c>
       <c r="E279" t="inlineStr">
         <is>
-          <t>Top 7 | 1 out</t>
+          <t>Top 7 | 2 out</t>
         </is>
       </c>
       <c r="F279" t="n">
@@ -32584,7 +32584,7 @@
         </is>
       </c>
       <c r="H279" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I279" t="n">
         <v>0</v>
@@ -32682,7 +32682,7 @@
       </c>
       <c r="B280" t="inlineStr">
         <is>
-          <t>2026-07-11 08:19:18 PM PT</t>
+          <t>2026-07-11 08:21:18 PM PT</t>
         </is>
       </c>
       <c r="C280" t="n">
@@ -32695,7 +32695,7 @@
       </c>
       <c r="E280" t="inlineStr">
         <is>
-          <t>Top 7 | 1 out</t>
+          <t>Top 7 | 2 out</t>
         </is>
       </c>
       <c r="F280" t="n">
@@ -32707,7 +32707,7 @@
         </is>
       </c>
       <c r="H280" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I280" t="n">
         <v>0</v>
@@ -32805,7 +32805,7 @@
       </c>
       <c r="B281" t="inlineStr">
         <is>
-          <t>2026-07-11 08:19:18 PM PT</t>
+          <t>2026-07-11 08:21:18 PM PT</t>
         </is>
       </c>
       <c r="C281" t="n">
@@ -32818,7 +32818,7 @@
       </c>
       <c r="E281" t="inlineStr">
         <is>
-          <t>Top 7 | 1 out</t>
+          <t>Top 7 | 2 out</t>
         </is>
       </c>
       <c r="F281" t="n">
@@ -32830,7 +32830,7 @@
         </is>
       </c>
       <c r="H281" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I281" t="n">
         <v>0</v>
@@ -32928,7 +32928,7 @@
       </c>
       <c r="B282" t="inlineStr">
         <is>
-          <t>2026-07-11 08:19:17 PM PT</t>
+          <t>2026-07-11 08:21:17 PM PT</t>
         </is>
       </c>
       <c r="C282" t="n">
@@ -33042,7 +33042,7 @@
       </c>
       <c r="B283" t="inlineStr">
         <is>
-          <t>2026-07-11 08:19:16 PM PT</t>
+          <t>2026-07-11 08:21:16 PM PT</t>
         </is>
       </c>
       <c r="C283" t="n">
@@ -33156,7 +33156,7 @@
       </c>
       <c r="B284" t="inlineStr">
         <is>
-          <t>2026-07-11 08:19:16 PM PT</t>
+          <t>2026-07-11 08:21:16 PM PT</t>
         </is>
       </c>
       <c r="C284" t="n">
@@ -33270,7 +33270,7 @@
       </c>
       <c r="B285" t="inlineStr">
         <is>
-          <t>2026-07-11 08:19:16 PM PT</t>
+          <t>2026-07-11 08:21:16 PM PT</t>
         </is>
       </c>
       <c r="C285" t="n">
@@ -33384,7 +33384,7 @@
       </c>
       <c r="B286" t="inlineStr">
         <is>
-          <t>2026-07-11 08:19:16 PM PT</t>
+          <t>2026-07-11 08:21:16 PM PT</t>
         </is>
       </c>
       <c r="C286" t="n">
@@ -33498,7 +33498,7 @@
       </c>
       <c r="B287" t="inlineStr">
         <is>
-          <t>2026-07-11 08:19:16 PM PT</t>
+          <t>2026-07-11 08:21:16 PM PT</t>
         </is>
       </c>
       <c r="C287" t="n">
@@ -33612,7 +33612,7 @@
       </c>
       <c r="B288" t="inlineStr">
         <is>
-          <t>2026-07-11 08:19:16 PM PT</t>
+          <t>2026-07-11 08:21:16 PM PT</t>
         </is>
       </c>
       <c r="C288" t="n">
@@ -33726,7 +33726,7 @@
       </c>
       <c r="B289" t="inlineStr">
         <is>
-          <t>2026-07-11 08:19:16 PM PT</t>
+          <t>2026-07-11 08:21:16 PM PT</t>
         </is>
       </c>
       <c r="C289" t="n">
@@ -33840,7 +33840,7 @@
       </c>
       <c r="B290" t="inlineStr">
         <is>
-          <t>2026-07-11 08:19:17 PM PT</t>
+          <t>2026-07-11 08:21:17 PM PT</t>
         </is>
       </c>
       <c r="C290" t="n">
@@ -33954,7 +33954,7 @@
       </c>
       <c r="B291" t="inlineStr">
         <is>
-          <t>2026-07-11 08:19:17 PM PT</t>
+          <t>2026-07-11 08:21:17 PM PT</t>
         </is>
       </c>
       <c r="C291" t="n">
@@ -34068,7 +34068,7 @@
       </c>
       <c r="B292" t="inlineStr">
         <is>
-          <t>2026-07-11 08:19:17 PM PT</t>
+          <t>2026-07-11 08:21:17 PM PT</t>
         </is>
       </c>
       <c r="C292" t="n">
@@ -34182,7 +34182,7 @@
       </c>
       <c r="B293" t="inlineStr">
         <is>
-          <t>2026-07-11 08:19:17 PM PT</t>
+          <t>2026-07-11 08:21:17 PM PT</t>
         </is>
       </c>
       <c r="C293" t="n">
@@ -34296,7 +34296,7 @@
       </c>
       <c r="B294" t="inlineStr">
         <is>
-          <t>2026-07-11 08:19:17 PM PT</t>
+          <t>2026-07-11 08:21:17 PM PT</t>
         </is>
       </c>
       <c r="C294" t="n">
@@ -34410,7 +34410,7 @@
       </c>
       <c r="B295" t="inlineStr">
         <is>
-          <t>2026-07-11 08:19:17 PM PT</t>
+          <t>2026-07-11 08:21:17 PM PT</t>
         </is>
       </c>
       <c r="C295" t="n">
@@ -34524,7 +34524,7 @@
       </c>
       <c r="B296" t="inlineStr">
         <is>
-          <t>2026-07-11 08:19:17 PM PT</t>
+          <t>2026-07-11 08:21:17 PM PT</t>
         </is>
       </c>
       <c r="C296" t="n">
@@ -34638,7 +34638,7 @@
       </c>
       <c r="B297" t="inlineStr">
         <is>
-          <t>2026-07-11 08:19:17 PM PT</t>
+          <t>2026-07-11 08:21:17 PM PT</t>
         </is>
       </c>
       <c r="C297" t="n">
@@ -34752,7 +34752,7 @@
       </c>
       <c r="B298" t="inlineStr">
         <is>
-          <t>2026-07-11 08:19:16 PM PT</t>
+          <t>2026-07-11 08:21:16 PM PT</t>
         </is>
       </c>
       <c r="C298" t="n">
@@ -34866,7 +34866,7 @@
       </c>
       <c r="B299" t="inlineStr">
         <is>
-          <t>2026-07-11 08:19:16 PM PT</t>
+          <t>2026-07-11 08:21:16 PM PT</t>
         </is>
       </c>
       <c r="C299" t="n">
@@ -34980,7 +34980,7 @@
       </c>
       <c r="B300" t="inlineStr">
         <is>
-          <t>2026-07-11 08:19:16 PM PT</t>
+          <t>2026-07-11 08:21:16 PM PT</t>
         </is>
       </c>
       <c r="C300" t="n">
@@ -35094,7 +35094,7 @@
       </c>
       <c r="B301" t="inlineStr">
         <is>
-          <t>2026-07-11 08:19:16 PM PT</t>
+          <t>2026-07-11 08:21:16 PM PT</t>
         </is>
       </c>
       <c r="C301" t="n">
@@ -35208,7 +35208,7 @@
       </c>
       <c r="B302" t="inlineStr">
         <is>
-          <t>2026-07-11 08:19:16 PM PT</t>
+          <t>2026-07-11 08:21:16 PM PT</t>
         </is>
       </c>
       <c r="C302" t="n">
@@ -35322,7 +35322,7 @@
       </c>
       <c r="B303" t="inlineStr">
         <is>
-          <t>2026-07-11 08:19:16 PM PT</t>
+          <t>2026-07-11 08:21:16 PM PT</t>
         </is>
       </c>
       <c r="C303" t="n">
@@ -35436,7 +35436,7 @@
       </c>
       <c r="B304" t="inlineStr">
         <is>
-          <t>2026-07-11 08:19:16 PM PT</t>
+          <t>2026-07-11 08:21:16 PM PT</t>
         </is>
       </c>
       <c r="C304" t="n">
@@ -35550,7 +35550,7 @@
       </c>
       <c r="B305" t="inlineStr">
         <is>
-          <t>2026-07-11 08:19:16 PM PT</t>
+          <t>2026-07-11 08:21:16 PM PT</t>
         </is>
       </c>
       <c r="C305" t="n">
@@ -35664,7 +35664,7 @@
       </c>
       <c r="B306" t="inlineStr">
         <is>
-          <t>2026-07-11 08:19:18 PM PT</t>
+          <t>2026-07-11 08:21:18 PM PT</t>
         </is>
       </c>
       <c r="C306" t="n">
@@ -35677,7 +35677,7 @@
       </c>
       <c r="E306" t="inlineStr">
         <is>
-          <t>Bottom 7 | 2 out</t>
+          <t>Bottom 7 | 3 out</t>
         </is>
       </c>
       <c r="F306" t="n">
@@ -35689,13 +35689,13 @@
         </is>
       </c>
       <c r="H306" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="I306" t="n">
         <v>3</v>
       </c>
       <c r="J306" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="K306" t="inlineStr">
         <is>
@@ -35787,7 +35787,7 @@
       </c>
       <c r="B307" t="inlineStr">
         <is>
-          <t>2026-07-11 08:19:17 PM PT</t>
+          <t>2026-07-11 08:21:17 PM PT</t>
         </is>
       </c>
       <c r="C307" t="n">
@@ -35901,7 +35901,7 @@
       </c>
       <c r="B308" t="inlineStr">
         <is>
-          <t>2026-07-11 08:19:17 PM PT</t>
+          <t>2026-07-11 08:21:17 PM PT</t>
         </is>
       </c>
       <c r="C308" t="n">
@@ -36015,7 +36015,7 @@
       </c>
       <c r="B309" t="inlineStr">
         <is>
-          <t>2026-07-11 08:19:17 PM PT</t>
+          <t>2026-07-11 08:21:17 PM PT</t>
         </is>
       </c>
       <c r="C309" t="n">
@@ -36129,7 +36129,7 @@
       </c>
       <c r="B310" t="inlineStr">
         <is>
-          <t>2026-07-11 08:19:17 PM PT</t>
+          <t>2026-07-11 08:21:17 PM PT</t>
         </is>
       </c>
       <c r="C310" t="n">
@@ -36243,7 +36243,7 @@
       </c>
       <c r="B311" t="inlineStr">
         <is>
-          <t>2026-07-11 08:19:17 PM PT</t>
+          <t>2026-07-11 08:21:17 PM PT</t>
         </is>
       </c>
       <c r="C311" t="n">
@@ -36357,7 +36357,7 @@
       </c>
       <c r="B312" t="inlineStr">
         <is>
-          <t>2026-07-11 08:19:17 PM PT</t>
+          <t>2026-07-11 08:21:17 PM PT</t>
         </is>
       </c>
       <c r="C312" t="n">
@@ -36471,7 +36471,7 @@
       </c>
       <c r="B313" t="inlineStr">
         <is>
-          <t>2026-07-11 08:19:17 PM PT</t>
+          <t>2026-07-11 08:21:17 PM PT</t>
         </is>
       </c>
       <c r="C313" t="n">
@@ -36585,7 +36585,7 @@
       </c>
       <c r="B314" t="inlineStr">
         <is>
-          <t>2026-07-11 08:19:17 PM PT</t>
+          <t>2026-07-11 08:21:18 PM PT</t>
         </is>
       </c>
       <c r="C314" t="n">
@@ -36699,7 +36699,7 @@
       </c>
       <c r="B315" t="inlineStr">
         <is>
-          <t>2026-07-11 08:19:17 PM PT</t>
+          <t>2026-07-11 08:21:18 PM PT</t>
         </is>
       </c>
       <c r="C315" t="n">
@@ -36813,7 +36813,7 @@
       </c>
       <c r="B316" t="inlineStr">
         <is>
-          <t>2026-07-11 08:19:17 PM PT</t>
+          <t>2026-07-11 08:21:18 PM PT</t>
         </is>
       </c>
       <c r="C316" t="n">
@@ -36927,7 +36927,7 @@
       </c>
       <c r="B317" t="inlineStr">
         <is>
-          <t>2026-07-11 08:19:17 PM PT</t>
+          <t>2026-07-11 08:21:18 PM PT</t>
         </is>
       </c>
       <c r="C317" t="n">
@@ -37041,7 +37041,7 @@
       </c>
       <c r="B318" t="inlineStr">
         <is>
-          <t>2026-07-11 08:19:17 PM PT</t>
+          <t>2026-07-11 08:21:17 PM PT</t>
         </is>
       </c>
       <c r="C318" t="n">
@@ -37155,7 +37155,7 @@
       </c>
       <c r="B319" t="inlineStr">
         <is>
-          <t>2026-07-11 08:19:17 PM PT</t>
+          <t>2026-07-11 08:21:17 PM PT</t>
         </is>
       </c>
       <c r="C319" t="n">
@@ -37269,7 +37269,7 @@
       </c>
       <c r="B320" t="inlineStr">
         <is>
-          <t>2026-07-11 08:19:17 PM PT</t>
+          <t>2026-07-11 08:21:17 PM PT</t>
         </is>
       </c>
       <c r="C320" t="n">
@@ -37383,7 +37383,7 @@
       </c>
       <c r="B321" t="inlineStr">
         <is>
-          <t>2026-07-11 08:19:17 PM PT</t>
+          <t>2026-07-11 08:21:17 PM PT</t>
         </is>
       </c>
       <c r="C321" t="n">
@@ -37497,7 +37497,7 @@
       </c>
       <c r="B322" t="inlineStr">
         <is>
-          <t>2026-07-11 08:19:17 PM PT</t>
+          <t>2026-07-11 08:21:18 PM PT</t>
         </is>
       </c>
       <c r="C322" t="n">
@@ -37611,7 +37611,7 @@
       </c>
       <c r="B323" t="inlineStr">
         <is>
-          <t>2026-07-11 08:19:17 PM PT</t>
+          <t>2026-07-11 08:21:18 PM PT</t>
         </is>
       </c>
       <c r="C323" t="n">
@@ -37725,7 +37725,7 @@
       </c>
       <c r="B324" t="inlineStr">
         <is>
-          <t>2026-07-11 08:19:17 PM PT</t>
+          <t>2026-07-11 08:21:18 PM PT</t>
         </is>
       </c>
       <c r="C324" t="n">
@@ -37839,7 +37839,7 @@
       </c>
       <c r="B325" t="inlineStr">
         <is>
-          <t>2026-07-11 08:19:17 PM PT</t>
+          <t>2026-07-11 08:21:18 PM PT</t>
         </is>
       </c>
       <c r="C325" t="n">
@@ -37953,7 +37953,7 @@
       </c>
       <c r="B326" t="inlineStr">
         <is>
-          <t>2026-07-11 08:19:17 PM PT</t>
+          <t>2026-07-11 08:21:18 PM PT</t>
         </is>
       </c>
       <c r="C326" t="n">
@@ -38067,7 +38067,7 @@
       </c>
       <c r="B327" t="inlineStr">
         <is>
-          <t>2026-07-11 08:19:18 PM PT</t>
+          <t>2026-07-11 08:21:18 PM PT</t>
         </is>
       </c>
       <c r="C327" t="n">
@@ -38080,7 +38080,7 @@
       </c>
       <c r="E327" t="inlineStr">
         <is>
-          <t>Bottom 7 | 2 out</t>
+          <t>Bottom 7 | 3 out</t>
         </is>
       </c>
       <c r="F327" t="n">
@@ -38092,13 +38092,13 @@
         </is>
       </c>
       <c r="H327" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="I327" t="n">
         <v>3</v>
       </c>
       <c r="J327" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="K327" t="inlineStr">
         <is>
@@ -38190,7 +38190,7 @@
       </c>
       <c r="B328" t="inlineStr">
         <is>
-          <t>2026-07-11 08:19:17 PM PT</t>
+          <t>2026-07-11 08:21:17 PM PT</t>
         </is>
       </c>
       <c r="C328" t="n">
@@ -38304,7 +38304,7 @@
       </c>
       <c r="B329" t="inlineStr">
         <is>
-          <t>2026-07-11 08:19:17 PM PT</t>
+          <t>2026-07-11 08:21:17 PM PT</t>
         </is>
       </c>
       <c r="C329" t="n">

--- a/live_mlb_hitter_fantasy_scores_2026_07_11.xlsx
+++ b/live_mlb_hitter_fantasy_scores_2026_07_11.xlsx
@@ -11,7 +11,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Scoring" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Live Fantasy Scores'!$A$1:$AG$329</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Live Fantasy Scores'!$A$1:$AG$330</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -480,14 +480,14 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AG329"/>
+  <dimension ref="A1:AG330"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
     <col width="27" customWidth="1" min="2" max="2"/>
     <col width="10" customWidth="1" min="3" max="3"/>
     <col width="14" customWidth="1" min="4" max="4"/>
-    <col width="18" customWidth="1" min="5" max="5"/>
+    <col width="15" customWidth="1" min="5" max="5"/>
     <col width="10" customWidth="1" min="6" max="6"/>
     <col width="13" customWidth="1" min="7" max="7"/>
     <col width="10" customWidth="1" min="8" max="8"/>
@@ -693,7 +693,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-07-11 08:21:16 PM PT</t>
+          <t>2026-07-11 08:23:16 PM PT</t>
         </is>
       </c>
       <c r="C2" t="n">
@@ -807,7 +807,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>2026-07-11 08:21:18 PM PT</t>
+          <t>2026-07-11 08:23:17 PM PT</t>
         </is>
       </c>
       <c r="C3" t="n">
@@ -921,7 +921,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-07-11 08:21:18 PM PT</t>
+          <t>2026-07-11 08:23:18 PM PT</t>
         </is>
       </c>
       <c r="C4" t="n">
@@ -934,25 +934,25 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Bottom 7 | 3 out</t>
+          <t>Top 8 | 0 out</t>
         </is>
       </c>
       <c r="F4" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Bottom</t>
+          <t>Top</t>
         </is>
       </c>
       <c r="H4" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="I4" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="J4" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="K4" t="inlineStr">
         <is>
@@ -1044,7 +1044,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>2026-07-11 08:21:18 PM PT</t>
+          <t>2026-07-11 08:23:17 PM PT</t>
         </is>
       </c>
       <c r="C5" t="n">
@@ -1158,7 +1158,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>2026-07-11 08:21:18 PM PT</t>
+          <t>2026-07-11 08:23:18 PM PT</t>
         </is>
       </c>
       <c r="C6" t="n">
@@ -1272,7 +1272,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>2026-07-11 08:21:17 PM PT</t>
+          <t>2026-07-11 08:23:17 PM PT</t>
         </is>
       </c>
       <c r="C7" t="n">
@@ -1386,7 +1386,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>2026-07-11 08:21:18 PM PT</t>
+          <t>2026-07-11 08:23:17 PM PT</t>
         </is>
       </c>
       <c r="C8" t="n">
@@ -1500,7 +1500,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>2026-07-11 08:21:16 PM PT</t>
+          <t>2026-07-11 08:23:16 PM PT</t>
         </is>
       </c>
       <c r="C9" t="n">
@@ -1614,7 +1614,7 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>2026-07-11 08:21:18 PM PT</t>
+          <t>2026-07-11 08:23:18 PM PT</t>
         </is>
       </c>
       <c r="C10" t="n">
@@ -1627,25 +1627,25 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Bottom 7 | 3 out</t>
+          <t>Top 8 | 0 out</t>
         </is>
       </c>
       <c r="F10" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Bottom</t>
+          <t>Top</t>
         </is>
       </c>
       <c r="H10" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="I10" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="J10" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="K10" t="inlineStr">
         <is>
@@ -1737,7 +1737,7 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>2026-07-11 08:21:17 PM PT</t>
+          <t>2026-07-11 08:23:17 PM PT</t>
         </is>
       </c>
       <c r="C11" t="n">
@@ -1851,7 +1851,7 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>2026-07-11 08:21:17 PM PT</t>
+          <t>2026-07-11 08:23:17 PM PT</t>
         </is>
       </c>
       <c r="C12" t="n">
@@ -1965,7 +1965,7 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>2026-07-11 08:21:18 PM PT</t>
+          <t>2026-07-11 08:23:18 PM PT</t>
         </is>
       </c>
       <c r="C13" t="n">
@@ -1978,25 +1978,25 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Bottom 7 | 3 out</t>
+          <t>Top 8 | 0 out</t>
         </is>
       </c>
       <c r="F13" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Bottom</t>
+          <t>Top</t>
         </is>
       </c>
       <c r="H13" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="I13" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="J13" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="K13" t="inlineStr">
         <is>
@@ -2088,7 +2088,7 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>2026-07-11 08:21:17 PM PT</t>
+          <t>2026-07-11 08:23:17 PM PT</t>
         </is>
       </c>
       <c r="C14" t="n">
@@ -2202,7 +2202,7 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>2026-07-11 08:21:17 PM PT</t>
+          <t>2026-07-11 08:23:17 PM PT</t>
         </is>
       </c>
       <c r="C15" t="n">
@@ -2316,7 +2316,7 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>2026-07-11 08:21:18 PM PT</t>
+          <t>2026-07-11 08:23:17 PM PT</t>
         </is>
       </c>
       <c r="C16" t="n">
@@ -2430,7 +2430,7 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>2026-07-11 08:21:18 PM PT</t>
+          <t>2026-07-11 08:23:18 PM PT</t>
         </is>
       </c>
       <c r="C17" t="n">
@@ -2443,25 +2443,25 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Bottom 7 | 3 out</t>
+          <t>Top 8 | 0 out</t>
         </is>
       </c>
       <c r="F17" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Bottom</t>
+          <t>Top</t>
         </is>
       </c>
       <c r="H17" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="I17" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="J17" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="K17" t="inlineStr">
         <is>
@@ -2553,7 +2553,7 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>2026-07-11 08:21:17 PM PT</t>
+          <t>2026-07-11 08:23:17 PM PT</t>
         </is>
       </c>
       <c r="C18" t="n">
@@ -2667,7 +2667,7 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>2026-07-11 08:21:18 PM PT</t>
+          <t>2026-07-11 08:23:18 PM PT</t>
         </is>
       </c>
       <c r="C19" t="n">
@@ -2781,7 +2781,7 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>2026-07-11 08:21:17 PM PT</t>
+          <t>2026-07-11 08:23:17 PM PT</t>
         </is>
       </c>
       <c r="C20" t="n">
@@ -2895,7 +2895,7 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>2026-07-11 08:21:17 PM PT</t>
+          <t>2026-07-11 08:23:17 PM PT</t>
         </is>
       </c>
       <c r="C21" t="n">
@@ -3009,7 +3009,7 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>2026-07-11 08:21:18 PM PT</t>
+          <t>2026-07-11 08:23:18 PM PT</t>
         </is>
       </c>
       <c r="C22" t="n">
@@ -3022,7 +3022,7 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Top 7 | 2 out</t>
+          <t>Top 7 | 3 out</t>
         </is>
       </c>
       <c r="F22" t="n">
@@ -3034,13 +3034,13 @@
         </is>
       </c>
       <c r="H22" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="I22" t="n">
         <v>0</v>
       </c>
       <c r="J22" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="K22" t="inlineStr">
         <is>
@@ -3132,7 +3132,7 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>2026-07-11 08:21:18 PM PT</t>
+          <t>2026-07-11 08:23:17 PM PT</t>
         </is>
       </c>
       <c r="C23" t="n">
@@ -3246,7 +3246,7 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>2026-07-11 08:21:17 PM PT</t>
+          <t>2026-07-11 08:23:17 PM PT</t>
         </is>
       </c>
       <c r="C24" t="n">
@@ -3360,7 +3360,7 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>2026-07-11 08:21:18 PM PT</t>
+          <t>2026-07-11 08:23:18 PM PT</t>
         </is>
       </c>
       <c r="C25" t="n">
@@ -3474,7 +3474,7 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>2026-07-11 08:21:16 PM PT</t>
+          <t>2026-07-11 08:23:16 PM PT</t>
         </is>
       </c>
       <c r="C26" t="n">
@@ -3588,7 +3588,7 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>2026-07-11 08:21:17 PM PT</t>
+          <t>2026-07-11 08:23:17 PM PT</t>
         </is>
       </c>
       <c r="C27" t="n">
@@ -3702,7 +3702,7 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>2026-07-11 08:21:17 PM PT</t>
+          <t>2026-07-11 08:23:17 PM PT</t>
         </is>
       </c>
       <c r="C28" t="n">
@@ -3816,7 +3816,7 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>2026-07-11 08:21:18 PM PT</t>
+          <t>2026-07-11 08:23:18 PM PT</t>
         </is>
       </c>
       <c r="C29" t="n">
@@ -3930,7 +3930,7 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>2026-07-11 08:21:18 PM PT</t>
+          <t>2026-07-11 08:23:18 PM PT</t>
         </is>
       </c>
       <c r="C30" t="n">
@@ -4044,7 +4044,7 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>2026-07-11 08:21:17 PM PT</t>
+          <t>2026-07-11 08:23:17 PM PT</t>
         </is>
       </c>
       <c r="C31" t="n">
@@ -4158,7 +4158,7 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>2026-07-11 08:21:17 PM PT</t>
+          <t>2026-07-11 08:23:17 PM PT</t>
         </is>
       </c>
       <c r="C32" t="n">
@@ -4272,7 +4272,7 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>2026-07-11 08:21:18 PM PT</t>
+          <t>2026-07-11 08:23:17 PM PT</t>
         </is>
       </c>
       <c r="C33" t="n">
@@ -4386,7 +4386,7 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>2026-07-11 08:21:16 PM PT</t>
+          <t>2026-07-11 08:23:16 PM PT</t>
         </is>
       </c>
       <c r="C34" t="n">
@@ -4500,7 +4500,7 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>2026-07-11 08:21:16 PM PT</t>
+          <t>2026-07-11 08:23:16 PM PT</t>
         </is>
       </c>
       <c r="C35" t="n">
@@ -4614,7 +4614,7 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>2026-07-11 08:21:18 PM PT</t>
+          <t>2026-07-11 08:23:18 PM PT</t>
         </is>
       </c>
       <c r="C36" t="n">
@@ -4627,25 +4627,25 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Bottom 7 | 3 out</t>
+          <t>Top 8 | 0 out</t>
         </is>
       </c>
       <c r="F36" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Bottom</t>
+          <t>Top</t>
         </is>
       </c>
       <c r="H36" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="I36" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="J36" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="K36" t="inlineStr">
         <is>
@@ -4737,7 +4737,7 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>2026-07-11 08:21:17 PM PT</t>
+          <t>2026-07-11 08:23:17 PM PT</t>
         </is>
       </c>
       <c r="C37" t="n">
@@ -4851,7 +4851,7 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>2026-07-11 08:21:16 PM PT</t>
+          <t>2026-07-11 08:23:16 PM PT</t>
         </is>
       </c>
       <c r="C38" t="n">
@@ -4965,7 +4965,7 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>2026-07-11 08:21:17 PM PT</t>
+          <t>2026-07-11 08:23:17 PM PT</t>
         </is>
       </c>
       <c r="C39" t="n">
@@ -5079,7 +5079,7 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>2026-07-11 08:21:16 PM PT</t>
+          <t>2026-07-11 08:23:16 PM PT</t>
         </is>
       </c>
       <c r="C40" t="n">
@@ -5193,7 +5193,7 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>2026-07-11 08:21:18 PM PT</t>
+          <t>2026-07-11 08:23:18 PM PT</t>
         </is>
       </c>
       <c r="C41" t="n">
@@ -5206,7 +5206,7 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>Top 7 | 2 out</t>
+          <t>Top 7 | 3 out</t>
         </is>
       </c>
       <c r="F41" t="n">
@@ -5218,13 +5218,13 @@
         </is>
       </c>
       <c r="H41" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="I41" t="n">
         <v>0</v>
       </c>
       <c r="J41" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="K41" t="inlineStr">
         <is>
@@ -5260,10 +5260,10 @@
         </is>
       </c>
       <c r="R41" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="S41" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="T41" t="n">
         <v>2</v>
@@ -5296,7 +5296,7 @@
         <v>0</v>
       </c>
       <c r="AD41" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AE41" s="4" t="n">
         <v>14</v>
@@ -5316,7 +5316,7 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>2026-07-11 08:21:18 PM PT</t>
+          <t>2026-07-11 08:23:18 PM PT</t>
         </is>
       </c>
       <c r="C42" t="n">
@@ -5430,7 +5430,7 @@
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>2026-07-11 08:21:18 PM PT</t>
+          <t>2026-07-11 08:23:17 PM PT</t>
         </is>
       </c>
       <c r="C43" t="n">
@@ -5544,7 +5544,7 @@
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>2026-07-11 08:21:18 PM PT</t>
+          <t>2026-07-11 08:23:17 PM PT</t>
         </is>
       </c>
       <c r="C44" t="n">
@@ -5658,7 +5658,7 @@
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>2026-07-11 08:21:18 PM PT</t>
+          <t>2026-07-11 08:23:18 PM PT</t>
         </is>
       </c>
       <c r="C45" t="n">
@@ -5772,7 +5772,7 @@
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>2026-07-11 08:21:17 PM PT</t>
+          <t>2026-07-11 08:23:17 PM PT</t>
         </is>
       </c>
       <c r="C46" t="n">
@@ -5886,7 +5886,7 @@
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>2026-07-11 08:21:17 PM PT</t>
+          <t>2026-07-11 08:23:17 PM PT</t>
         </is>
       </c>
       <c r="C47" t="n">
@@ -6000,7 +6000,7 @@
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>2026-07-11 08:21:18 PM PT</t>
+          <t>2026-07-11 08:23:17 PM PT</t>
         </is>
       </c>
       <c r="C48" t="n">
@@ -6114,7 +6114,7 @@
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>2026-07-11 08:21:17 PM PT</t>
+          <t>2026-07-11 08:23:17 PM PT</t>
         </is>
       </c>
       <c r="C49" t="n">
@@ -6228,7 +6228,7 @@
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>2026-07-11 08:21:16 PM PT</t>
+          <t>2026-07-11 08:23:16 PM PT</t>
         </is>
       </c>
       <c r="C50" t="n">
@@ -6342,7 +6342,7 @@
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>2026-07-11 08:21:18 PM PT</t>
+          <t>2026-07-11 08:23:18 PM PT</t>
         </is>
       </c>
       <c r="C51" t="n">
@@ -6355,7 +6355,7 @@
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>Top 7 | 2 out</t>
+          <t>Top 7 | 3 out</t>
         </is>
       </c>
       <c r="F51" t="n">
@@ -6367,13 +6367,13 @@
         </is>
       </c>
       <c r="H51" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="I51" t="n">
         <v>0</v>
       </c>
       <c r="J51" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="K51" t="inlineStr">
         <is>
@@ -6465,7 +6465,7 @@
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>2026-07-11 08:21:18 PM PT</t>
+          <t>2026-07-11 08:23:18 PM PT</t>
         </is>
       </c>
       <c r="C52" t="n">
@@ -6579,7 +6579,7 @@
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>2026-07-11 08:21:18 PM PT</t>
+          <t>2026-07-11 08:23:18 PM PT</t>
         </is>
       </c>
       <c r="C53" t="n">
@@ -6693,7 +6693,7 @@
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>2026-07-11 08:21:17 PM PT</t>
+          <t>2026-07-11 08:23:17 PM PT</t>
         </is>
       </c>
       <c r="C54" t="n">
@@ -6807,7 +6807,7 @@
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>2026-07-11 08:21:16 PM PT</t>
+          <t>2026-07-11 08:23:16 PM PT</t>
         </is>
       </c>
       <c r="C55" t="n">
@@ -6921,7 +6921,7 @@
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>2026-07-11 08:21:16 PM PT</t>
+          <t>2026-07-11 08:23:16 PM PT</t>
         </is>
       </c>
       <c r="C56" t="n">
@@ -7035,7 +7035,7 @@
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>2026-07-11 08:21:16 PM PT</t>
+          <t>2026-07-11 08:23:16 PM PT</t>
         </is>
       </c>
       <c r="C57" t="n">
@@ -7149,7 +7149,7 @@
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>2026-07-11 08:21:17 PM PT</t>
+          <t>2026-07-11 08:23:17 PM PT</t>
         </is>
       </c>
       <c r="C58" t="n">
@@ -7263,7 +7263,7 @@
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>2026-07-11 08:21:17 PM PT</t>
+          <t>2026-07-11 08:23:17 PM PT</t>
         </is>
       </c>
       <c r="C59" t="n">
@@ -7377,7 +7377,7 @@
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>2026-07-11 08:21:16 PM PT</t>
+          <t>2026-07-11 08:23:16 PM PT</t>
         </is>
       </c>
       <c r="C60" t="n">
@@ -7491,7 +7491,7 @@
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>2026-07-11 08:21:16 PM PT</t>
+          <t>2026-07-11 08:23:16 PM PT</t>
         </is>
       </c>
       <c r="C61" t="n">
@@ -7605,7 +7605,7 @@
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>2026-07-11 08:21:16 PM PT</t>
+          <t>2026-07-11 08:23:16 PM PT</t>
         </is>
       </c>
       <c r="C62" t="n">
@@ -7719,7 +7719,7 @@
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>2026-07-11 08:21:18 PM PT</t>
+          <t>2026-07-11 08:23:18 PM PT</t>
         </is>
       </c>
       <c r="C63" t="n">
@@ -7732,25 +7732,25 @@
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>Bottom 7 | 3 out</t>
+          <t>Top 8 | 0 out</t>
         </is>
       </c>
       <c r="F63" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Bottom</t>
+          <t>Top</t>
         </is>
       </c>
       <c r="H63" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="I63" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="J63" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="K63" t="inlineStr">
         <is>
@@ -7842,7 +7842,7 @@
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>2026-07-11 08:21:18 PM PT</t>
+          <t>2026-07-11 08:23:18 PM PT</t>
         </is>
       </c>
       <c r="C64" t="n">
@@ -7855,7 +7855,7 @@
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>Top 7 | 2 out</t>
+          <t>Top 7 | 3 out</t>
         </is>
       </c>
       <c r="F64" t="n">
@@ -7867,13 +7867,13 @@
         </is>
       </c>
       <c r="H64" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="I64" t="n">
         <v>0</v>
       </c>
       <c r="J64" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="K64" t="inlineStr">
         <is>
@@ -7965,7 +7965,7 @@
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>2026-07-11 08:21:16 PM PT</t>
+          <t>2026-07-11 08:23:16 PM PT</t>
         </is>
       </c>
       <c r="C65" t="n">
@@ -8079,7 +8079,7 @@
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>2026-07-11 08:21:17 PM PT</t>
+          <t>2026-07-11 08:23:17 PM PT</t>
         </is>
       </c>
       <c r="C66" t="n">
@@ -8193,7 +8193,7 @@
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>2026-07-11 08:21:18 PM PT</t>
+          <t>2026-07-11 08:23:18 PM PT</t>
         </is>
       </c>
       <c r="C67" t="n">
@@ -8206,25 +8206,25 @@
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>Bottom 7 | 3 out</t>
+          <t>Top 8 | 0 out</t>
         </is>
       </c>
       <c r="F67" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>Bottom</t>
+          <t>Top</t>
         </is>
       </c>
       <c r="H67" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="I67" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="J67" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="K67" t="inlineStr">
         <is>
@@ -8316,7 +8316,7 @@
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>2026-07-11 08:21:17 PM PT</t>
+          <t>2026-07-11 08:23:17 PM PT</t>
         </is>
       </c>
       <c r="C68" t="n">
@@ -8430,7 +8430,7 @@
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>2026-07-11 08:21:16 PM PT</t>
+          <t>2026-07-11 08:23:16 PM PT</t>
         </is>
       </c>
       <c r="C69" t="n">
@@ -8544,7 +8544,7 @@
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>2026-07-11 08:21:16 PM PT</t>
+          <t>2026-07-11 08:23:16 PM PT</t>
         </is>
       </c>
       <c r="C70" t="n">
@@ -8658,7 +8658,7 @@
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>2026-07-11 08:21:18 PM PT</t>
+          <t>2026-07-11 08:23:18 PM PT</t>
         </is>
       </c>
       <c r="C71" t="n">
@@ -8671,7 +8671,7 @@
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>Top 7 | 2 out</t>
+          <t>Top 7 | 3 out</t>
         </is>
       </c>
       <c r="F71" t="n">
@@ -8683,13 +8683,13 @@
         </is>
       </c>
       <c r="H71" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="I71" t="n">
         <v>0</v>
       </c>
       <c r="J71" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="K71" t="inlineStr">
         <is>
@@ -8781,7 +8781,7 @@
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>2026-07-11 08:21:16 PM PT</t>
+          <t>2026-07-11 08:23:16 PM PT</t>
         </is>
       </c>
       <c r="C72" t="n">
@@ -8895,7 +8895,7 @@
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>2026-07-11 08:21:17 PM PT</t>
+          <t>2026-07-11 08:23:17 PM PT</t>
         </is>
       </c>
       <c r="C73" t="n">
@@ -9009,7 +9009,7 @@
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>2026-07-11 08:21:16 PM PT</t>
+          <t>2026-07-11 08:23:16 PM PT</t>
         </is>
       </c>
       <c r="C74" t="n">
@@ -9123,7 +9123,7 @@
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>2026-07-11 08:21:18 PM PT</t>
+          <t>2026-07-11 08:23:18 PM PT</t>
         </is>
       </c>
       <c r="C75" t="n">
@@ -9136,25 +9136,25 @@
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>Bottom 7 | 3 out</t>
+          <t>Top 8 | 0 out</t>
         </is>
       </c>
       <c r="F75" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>Bottom</t>
+          <t>Top</t>
         </is>
       </c>
       <c r="H75" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="I75" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="J75" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="K75" t="inlineStr">
         <is>
@@ -9246,7 +9246,7 @@
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>2026-07-11 08:21:18 PM PT</t>
+          <t>2026-07-11 08:23:18 PM PT</t>
         </is>
       </c>
       <c r="C76" t="n">
@@ -9360,7 +9360,7 @@
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>2026-07-11 08:21:18 PM PT</t>
+          <t>2026-07-11 08:23:18 PM PT</t>
         </is>
       </c>
       <c r="C77" t="n">
@@ -9474,7 +9474,7 @@
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>2026-07-11 08:21:17 PM PT</t>
+          <t>2026-07-11 08:23:17 PM PT</t>
         </is>
       </c>
       <c r="C78" t="n">
@@ -9588,7 +9588,7 @@
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>2026-07-11 08:21:16 PM PT</t>
+          <t>2026-07-11 08:23:16 PM PT</t>
         </is>
       </c>
       <c r="C79" t="n">
@@ -9702,7 +9702,7 @@
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>2026-07-11 08:21:16 PM PT</t>
+          <t>2026-07-11 08:23:16 PM PT</t>
         </is>
       </c>
       <c r="C80" t="n">
@@ -9816,7 +9816,7 @@
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>2026-07-11 08:21:16 PM PT</t>
+          <t>2026-07-11 08:23:16 PM PT</t>
         </is>
       </c>
       <c r="C81" t="n">
@@ -9930,7 +9930,7 @@
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>2026-07-11 08:21:16 PM PT</t>
+          <t>2026-07-11 08:23:16 PM PT</t>
         </is>
       </c>
       <c r="C82" t="n">
@@ -10044,7 +10044,7 @@
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>2026-07-11 08:21:16 PM PT</t>
+          <t>2026-07-11 08:23:16 PM PT</t>
         </is>
       </c>
       <c r="C83" t="n">
@@ -10158,7 +10158,7 @@
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>2026-07-11 08:21:16 PM PT</t>
+          <t>2026-07-11 08:23:16 PM PT</t>
         </is>
       </c>
       <c r="C84" t="n">
@@ -10272,7 +10272,7 @@
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>2026-07-11 08:21:16 PM PT</t>
+          <t>2026-07-11 08:23:16 PM PT</t>
         </is>
       </c>
       <c r="C85" t="n">
@@ -10386,7 +10386,7 @@
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>2026-07-11 08:21:16 PM PT</t>
+          <t>2026-07-11 08:23:16 PM PT</t>
         </is>
       </c>
       <c r="C86" t="n">
@@ -10500,7 +10500,7 @@
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>2026-07-11 08:21:17 PM PT</t>
+          <t>2026-07-11 08:23:17 PM PT</t>
         </is>
       </c>
       <c r="C87" t="n">
@@ -10614,7 +10614,7 @@
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>2026-07-11 08:21:17 PM PT</t>
+          <t>2026-07-11 08:23:17 PM PT</t>
         </is>
       </c>
       <c r="C88" t="n">
@@ -10728,7 +10728,7 @@
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>2026-07-11 08:21:18 PM PT</t>
+          <t>2026-07-11 08:23:18 PM PT</t>
         </is>
       </c>
       <c r="C89" t="n">
@@ -10741,25 +10741,25 @@
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>Bottom 7 | 3 out</t>
+          <t>Top 8 | 0 out</t>
         </is>
       </c>
       <c r="F89" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>Bottom</t>
+          <t>Top</t>
         </is>
       </c>
       <c r="H89" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="I89" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="J89" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="K89" t="inlineStr">
         <is>
@@ -10851,7 +10851,7 @@
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>2026-07-11 08:21:17 PM PT</t>
+          <t>2026-07-11 08:23:17 PM PT</t>
         </is>
       </c>
       <c r="C90" t="n">
@@ -10965,7 +10965,7 @@
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>2026-07-11 08:21:18 PM PT</t>
+          <t>2026-07-11 08:23:18 PM PT</t>
         </is>
       </c>
       <c r="C91" t="n">
@@ -11079,7 +11079,7 @@
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>2026-07-11 08:21:18 PM PT</t>
+          <t>2026-07-11 08:23:18 PM PT</t>
         </is>
       </c>
       <c r="C92" t="n">
@@ -11092,7 +11092,7 @@
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>Top 7 | 2 out</t>
+          <t>Top 7 | 3 out</t>
         </is>
       </c>
       <c r="F92" t="n">
@@ -11104,13 +11104,13 @@
         </is>
       </c>
       <c r="H92" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="I92" t="n">
         <v>0</v>
       </c>
       <c r="J92" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="K92" t="inlineStr">
         <is>
@@ -11202,7 +11202,7 @@
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>2026-07-11 08:21:17 PM PT</t>
+          <t>2026-07-11 08:23:17 PM PT</t>
         </is>
       </c>
       <c r="C93" t="n">
@@ -11316,7 +11316,7 @@
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>2026-07-11 08:21:17 PM PT</t>
+          <t>2026-07-11 08:23:17 PM PT</t>
         </is>
       </c>
       <c r="C94" t="n">
@@ -11430,7 +11430,7 @@
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>2026-07-11 08:21:17 PM PT</t>
+          <t>2026-07-11 08:23:17 PM PT</t>
         </is>
       </c>
       <c r="C95" t="n">
@@ -11544,7 +11544,7 @@
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>2026-07-11 08:21:18 PM PT</t>
+          <t>2026-07-11 08:23:17 PM PT</t>
         </is>
       </c>
       <c r="C96" t="n">
@@ -11658,7 +11658,7 @@
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>2026-07-11 08:21:18 PM PT</t>
+          <t>2026-07-11 08:23:17 PM PT</t>
         </is>
       </c>
       <c r="C97" t="n">
@@ -11772,7 +11772,7 @@
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>2026-07-11 08:21:18 PM PT</t>
+          <t>2026-07-11 08:23:18 PM PT</t>
         </is>
       </c>
       <c r="C98" t="n">
@@ -11785,7 +11785,7 @@
       </c>
       <c r="E98" t="inlineStr">
         <is>
-          <t>Top 7 | 2 out</t>
+          <t>Top 7 | 3 out</t>
         </is>
       </c>
       <c r="F98" t="n">
@@ -11797,13 +11797,13 @@
         </is>
       </c>
       <c r="H98" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="I98" t="n">
         <v>0</v>
       </c>
       <c r="J98" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="K98" t="inlineStr">
         <is>
@@ -11895,7 +11895,7 @@
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>2026-07-11 08:21:17 PM PT</t>
+          <t>2026-07-11 08:23:17 PM PT</t>
         </is>
       </c>
       <c r="C99" t="n">
@@ -12009,7 +12009,7 @@
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>2026-07-11 08:21:16 PM PT</t>
+          <t>2026-07-11 08:23:16 PM PT</t>
         </is>
       </c>
       <c r="C100" t="n">
@@ -12123,7 +12123,7 @@
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>2026-07-11 08:21:16 PM PT</t>
+          <t>2026-07-11 08:23:16 PM PT</t>
         </is>
       </c>
       <c r="C101" t="n">
@@ -12237,7 +12237,7 @@
       </c>
       <c r="B102" t="inlineStr">
         <is>
-          <t>2026-07-11 08:21:17 PM PT</t>
+          <t>2026-07-11 08:23:17 PM PT</t>
         </is>
       </c>
       <c r="C102" t="n">
@@ -12351,7 +12351,7 @@
       </c>
       <c r="B103" t="inlineStr">
         <is>
-          <t>2026-07-11 08:21:18 PM PT</t>
+          <t>2026-07-11 08:23:18 PM PT</t>
         </is>
       </c>
       <c r="C103" t="n">
@@ -12364,25 +12364,25 @@
       </c>
       <c r="E103" t="inlineStr">
         <is>
-          <t>Bottom 7 | 3 out</t>
+          <t>Top 8 | 0 out</t>
         </is>
       </c>
       <c r="F103" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="G103" t="inlineStr">
         <is>
-          <t>Bottom</t>
+          <t>Top</t>
         </is>
       </c>
       <c r="H103" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="I103" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="J103" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="K103" t="inlineStr">
         <is>
@@ -12474,7 +12474,7 @@
       </c>
       <c r="B104" t="inlineStr">
         <is>
-          <t>2026-07-11 08:21:17 PM PT</t>
+          <t>2026-07-11 08:23:17 PM PT</t>
         </is>
       </c>
       <c r="C104" t="n">
@@ -12588,7 +12588,7 @@
       </c>
       <c r="B105" t="inlineStr">
         <is>
-          <t>2026-07-11 08:21:17 PM PT</t>
+          <t>2026-07-11 08:23:17 PM PT</t>
         </is>
       </c>
       <c r="C105" t="n">
@@ -12702,7 +12702,7 @@
       </c>
       <c r="B106" t="inlineStr">
         <is>
-          <t>2026-07-11 08:21:17 PM PT</t>
+          <t>2026-07-11 08:23:17 PM PT</t>
         </is>
       </c>
       <c r="C106" t="n">
@@ -12816,7 +12816,7 @@
       </c>
       <c r="B107" t="inlineStr">
         <is>
-          <t>2026-07-11 08:21:17 PM PT</t>
+          <t>2026-07-11 08:23:17 PM PT</t>
         </is>
       </c>
       <c r="C107" t="n">
@@ -12930,7 +12930,7 @@
       </c>
       <c r="B108" t="inlineStr">
         <is>
-          <t>2026-07-11 08:21:17 PM PT</t>
+          <t>2026-07-11 08:23:17 PM PT</t>
         </is>
       </c>
       <c r="C108" t="n">
@@ -13044,7 +13044,7 @@
       </c>
       <c r="B109" t="inlineStr">
         <is>
-          <t>2026-07-11 08:21:17 PM PT</t>
+          <t>2026-07-11 08:23:17 PM PT</t>
         </is>
       </c>
       <c r="C109" t="n">
@@ -13158,7 +13158,7 @@
       </c>
       <c r="B110" t="inlineStr">
         <is>
-          <t>2026-07-11 08:21:16 PM PT</t>
+          <t>2026-07-11 08:23:16 PM PT</t>
         </is>
       </c>
       <c r="C110" t="n">
@@ -13272,7 +13272,7 @@
       </c>
       <c r="B111" t="inlineStr">
         <is>
-          <t>2026-07-11 08:21:18 PM PT</t>
+          <t>2026-07-11 08:23:18 PM PT</t>
         </is>
       </c>
       <c r="C111" t="n">
@@ -13386,7 +13386,7 @@
       </c>
       <c r="B112" t="inlineStr">
         <is>
-          <t>2026-07-11 08:21:17 PM PT</t>
+          <t>2026-07-11 08:23:17 PM PT</t>
         </is>
       </c>
       <c r="C112" t="n">
@@ -13500,7 +13500,7 @@
       </c>
       <c r="B113" t="inlineStr">
         <is>
-          <t>2026-07-11 08:21:17 PM PT</t>
+          <t>2026-07-11 08:23:17 PM PT</t>
         </is>
       </c>
       <c r="C113" t="n">
@@ -13614,7 +13614,7 @@
       </c>
       <c r="B114" t="inlineStr">
         <is>
-          <t>2026-07-11 08:21:17 PM PT</t>
+          <t>2026-07-11 08:23:17 PM PT</t>
         </is>
       </c>
       <c r="C114" t="n">
@@ -13728,7 +13728,7 @@
       </c>
       <c r="B115" t="inlineStr">
         <is>
-          <t>2026-07-11 08:21:18 PM PT</t>
+          <t>2026-07-11 08:23:18 PM PT</t>
         </is>
       </c>
       <c r="C115" t="n">
@@ -13741,25 +13741,25 @@
       </c>
       <c r="E115" t="inlineStr">
         <is>
-          <t>Bottom 7 | 3 out</t>
+          <t>Top 8 | 0 out</t>
         </is>
       </c>
       <c r="F115" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="G115" t="inlineStr">
         <is>
-          <t>Bottom</t>
+          <t>Top</t>
         </is>
       </c>
       <c r="H115" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="I115" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="J115" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="K115" t="inlineStr">
         <is>
@@ -13851,7 +13851,7 @@
       </c>
       <c r="B116" t="inlineStr">
         <is>
-          <t>2026-07-11 08:21:18 PM PT</t>
+          <t>2026-07-11 08:23:17 PM PT</t>
         </is>
       </c>
       <c r="C116" t="n">
@@ -13965,7 +13965,7 @@
       </c>
       <c r="B117" t="inlineStr">
         <is>
-          <t>2026-07-11 08:21:18 PM PT</t>
+          <t>2026-07-11 08:23:18 PM PT</t>
         </is>
       </c>
       <c r="C117" t="n">
@@ -14079,7 +14079,7 @@
       </c>
       <c r="B118" t="inlineStr">
         <is>
-          <t>2026-07-11 08:21:18 PM PT</t>
+          <t>2026-07-11 08:23:18 PM PT</t>
         </is>
       </c>
       <c r="C118" t="n">
@@ -14193,7 +14193,7 @@
       </c>
       <c r="B119" t="inlineStr">
         <is>
-          <t>2026-07-11 08:21:18 PM PT</t>
+          <t>2026-07-11 08:23:17 PM PT</t>
         </is>
       </c>
       <c r="C119" t="n">
@@ -14307,7 +14307,7 @@
       </c>
       <c r="B120" t="inlineStr">
         <is>
-          <t>2026-07-11 08:21:17 PM PT</t>
+          <t>2026-07-11 08:23:17 PM PT</t>
         </is>
       </c>
       <c r="C120" t="n">
@@ -14421,7 +14421,7 @@
       </c>
       <c r="B121" t="inlineStr">
         <is>
-          <t>2026-07-11 08:21:18 PM PT</t>
+          <t>2026-07-11 08:23:18 PM PT</t>
         </is>
       </c>
       <c r="C121" t="n">
@@ -14535,7 +14535,7 @@
       </c>
       <c r="B122" t="inlineStr">
         <is>
-          <t>2026-07-11 08:21:17 PM PT</t>
+          <t>2026-07-11 08:23:17 PM PT</t>
         </is>
       </c>
       <c r="C122" t="n">
@@ -14649,7 +14649,7 @@
       </c>
       <c r="B123" t="inlineStr">
         <is>
-          <t>2026-07-11 08:21:16 PM PT</t>
+          <t>2026-07-11 08:23:16 PM PT</t>
         </is>
       </c>
       <c r="C123" t="n">
@@ -14763,7 +14763,7 @@
       </c>
       <c r="B124" t="inlineStr">
         <is>
-          <t>2026-07-11 08:21:17 PM PT</t>
+          <t>2026-07-11 08:23:17 PM PT</t>
         </is>
       </c>
       <c r="C124" t="n">
@@ -14877,7 +14877,7 @@
       </c>
       <c r="B125" t="inlineStr">
         <is>
-          <t>2026-07-11 08:21:18 PM PT</t>
+          <t>2026-07-11 08:23:17 PM PT</t>
         </is>
       </c>
       <c r="C125" t="n">
@@ -14991,7 +14991,7 @@
       </c>
       <c r="B126" t="inlineStr">
         <is>
-          <t>2026-07-11 08:21:18 PM PT</t>
+          <t>2026-07-11 08:23:17 PM PT</t>
         </is>
       </c>
       <c r="C126" t="n">
@@ -15105,7 +15105,7 @@
       </c>
       <c r="B127" t="inlineStr">
         <is>
-          <t>2026-07-11 08:21:18 PM PT</t>
+          <t>2026-07-11 08:23:17 PM PT</t>
         </is>
       </c>
       <c r="C127" t="n">
@@ -15219,7 +15219,7 @@
       </c>
       <c r="B128" t="inlineStr">
         <is>
-          <t>2026-07-11 08:21:18 PM PT</t>
+          <t>2026-07-11 08:23:18 PM PT</t>
         </is>
       </c>
       <c r="C128" t="n">
@@ -15232,7 +15232,7 @@
       </c>
       <c r="E128" t="inlineStr">
         <is>
-          <t>Top 7 | 2 out</t>
+          <t>Top 7 | 3 out</t>
         </is>
       </c>
       <c r="F128" t="n">
@@ -15244,13 +15244,13 @@
         </is>
       </c>
       <c r="H128" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="I128" t="n">
         <v>0</v>
       </c>
       <c r="J128" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="K128" t="inlineStr">
         <is>
@@ -15342,7 +15342,7 @@
       </c>
       <c r="B129" t="inlineStr">
         <is>
-          <t>2026-07-11 08:21:17 PM PT</t>
+          <t>2026-07-11 08:23:17 PM PT</t>
         </is>
       </c>
       <c r="C129" t="n">
@@ -15456,7 +15456,7 @@
       </c>
       <c r="B130" t="inlineStr">
         <is>
-          <t>2026-07-11 08:21:17 PM PT</t>
+          <t>2026-07-11 08:23:17 PM PT</t>
         </is>
       </c>
       <c r="C130" t="n">
@@ -15570,7 +15570,7 @@
       </c>
       <c r="B131" t="inlineStr">
         <is>
-          <t>2026-07-11 08:21:16 PM PT</t>
+          <t>2026-07-11 08:23:16 PM PT</t>
         </is>
       </c>
       <c r="C131" t="n">
@@ -15684,7 +15684,7 @@
       </c>
       <c r="B132" t="inlineStr">
         <is>
-          <t>2026-07-11 08:21:16 PM PT</t>
+          <t>2026-07-11 08:23:16 PM PT</t>
         </is>
       </c>
       <c r="C132" t="n">
@@ -15798,7 +15798,7 @@
       </c>
       <c r="B133" t="inlineStr">
         <is>
-          <t>2026-07-11 08:21:16 PM PT</t>
+          <t>2026-07-11 08:23:16 PM PT</t>
         </is>
       </c>
       <c r="C133" t="n">
@@ -15912,7 +15912,7 @@
       </c>
       <c r="B134" t="inlineStr">
         <is>
-          <t>2026-07-11 08:21:17 PM PT</t>
+          <t>2026-07-11 08:23:17 PM PT</t>
         </is>
       </c>
       <c r="C134" t="n">
@@ -16026,7 +16026,7 @@
       </c>
       <c r="B135" t="inlineStr">
         <is>
-          <t>2026-07-11 08:21:16 PM PT</t>
+          <t>2026-07-11 08:23:16 PM PT</t>
         </is>
       </c>
       <c r="C135" t="n">
@@ -16140,7 +16140,7 @@
       </c>
       <c r="B136" t="inlineStr">
         <is>
-          <t>2026-07-11 08:21:16 PM PT</t>
+          <t>2026-07-11 08:23:16 PM PT</t>
         </is>
       </c>
       <c r="C136" t="n">
@@ -16254,7 +16254,7 @@
       </c>
       <c r="B137" t="inlineStr">
         <is>
-          <t>2026-07-11 08:21:17 PM PT</t>
+          <t>2026-07-11 08:23:17 PM PT</t>
         </is>
       </c>
       <c r="C137" t="n">
@@ -16368,7 +16368,7 @@
       </c>
       <c r="B138" t="inlineStr">
         <is>
-          <t>2026-07-11 08:21:17 PM PT</t>
+          <t>2026-07-11 08:23:17 PM PT</t>
         </is>
       </c>
       <c r="C138" t="n">
@@ -16482,7 +16482,7 @@
       </c>
       <c r="B139" t="inlineStr">
         <is>
-          <t>2026-07-11 08:21:17 PM PT</t>
+          <t>2026-07-11 08:23:17 PM PT</t>
         </is>
       </c>
       <c r="C139" t="n">
@@ -16596,7 +16596,7 @@
       </c>
       <c r="B140" t="inlineStr">
         <is>
-          <t>2026-07-11 08:21:18 PM PT</t>
+          <t>2026-07-11 08:23:18 PM PT</t>
         </is>
       </c>
       <c r="C140" t="n">
@@ -16710,7 +16710,7 @@
       </c>
       <c r="B141" t="inlineStr">
         <is>
-          <t>2026-07-11 08:21:18 PM PT</t>
+          <t>2026-07-11 08:23:18 PM PT</t>
         </is>
       </c>
       <c r="C141" t="n">
@@ -16824,7 +16824,7 @@
       </c>
       <c r="B142" t="inlineStr">
         <is>
-          <t>2026-07-11 08:21:18 PM PT</t>
+          <t>2026-07-11 08:23:18 PM PT</t>
         </is>
       </c>
       <c r="C142" t="n">
@@ -16938,7 +16938,7 @@
       </c>
       <c r="B143" t="inlineStr">
         <is>
-          <t>2026-07-11 08:21:17 PM PT</t>
+          <t>2026-07-11 08:23:17 PM PT</t>
         </is>
       </c>
       <c r="C143" t="n">
@@ -17052,7 +17052,7 @@
       </c>
       <c r="B144" t="inlineStr">
         <is>
-          <t>2026-07-11 08:21:18 PM PT</t>
+          <t>2026-07-11 08:23:17 PM PT</t>
         </is>
       </c>
       <c r="C144" t="n">
@@ -17166,7 +17166,7 @@
       </c>
       <c r="B145" t="inlineStr">
         <is>
-          <t>2026-07-11 08:21:18 PM PT</t>
+          <t>2026-07-11 08:23:17 PM PT</t>
         </is>
       </c>
       <c r="C145" t="n">
@@ -17280,7 +17280,7 @@
       </c>
       <c r="B146" t="inlineStr">
         <is>
-          <t>2026-07-11 08:21:18 PM PT</t>
+          <t>2026-07-11 08:23:18 PM PT</t>
         </is>
       </c>
       <c r="C146" t="n">
@@ -17293,7 +17293,7 @@
       </c>
       <c r="E146" t="inlineStr">
         <is>
-          <t>Top 7 | 2 out</t>
+          <t>Top 7 | 3 out</t>
         </is>
       </c>
       <c r="F146" t="n">
@@ -17305,13 +17305,13 @@
         </is>
       </c>
       <c r="H146" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="I146" t="n">
         <v>0</v>
       </c>
       <c r="J146" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="K146" t="inlineStr">
         <is>
@@ -17403,7 +17403,7 @@
       </c>
       <c r="B147" t="inlineStr">
         <is>
-          <t>2026-07-11 08:21:18 PM PT</t>
+          <t>2026-07-11 08:23:18 PM PT</t>
         </is>
       </c>
       <c r="C147" t="n">
@@ -17517,7 +17517,7 @@
       </c>
       <c r="B148" t="inlineStr">
         <is>
-          <t>2026-07-11 08:21:17 PM PT</t>
+          <t>2026-07-11 08:23:17 PM PT</t>
         </is>
       </c>
       <c r="C148" t="n">
@@ -17631,7 +17631,7 @@
       </c>
       <c r="B149" t="inlineStr">
         <is>
-          <t>2026-07-11 08:21:16 PM PT</t>
+          <t>2026-07-11 08:23:16 PM PT</t>
         </is>
       </c>
       <c r="C149" t="n">
@@ -17745,7 +17745,7 @@
       </c>
       <c r="B150" t="inlineStr">
         <is>
-          <t>2026-07-11 08:21:16 PM PT</t>
+          <t>2026-07-11 08:23:16 PM PT</t>
         </is>
       </c>
       <c r="C150" t="n">
@@ -17859,7 +17859,7 @@
       </c>
       <c r="B151" t="inlineStr">
         <is>
-          <t>2026-07-11 08:21:16 PM PT</t>
+          <t>2026-07-11 08:23:16 PM PT</t>
         </is>
       </c>
       <c r="C151" t="n">
@@ -17973,7 +17973,7 @@
       </c>
       <c r="B152" t="inlineStr">
         <is>
-          <t>2026-07-11 08:21:16 PM PT</t>
+          <t>2026-07-11 08:23:16 PM PT</t>
         </is>
       </c>
       <c r="C152" t="n">
@@ -18087,7 +18087,7 @@
       </c>
       <c r="B153" t="inlineStr">
         <is>
-          <t>2026-07-11 08:21:17 PM PT</t>
+          <t>2026-07-11 08:23:17 PM PT</t>
         </is>
       </c>
       <c r="C153" t="n">
@@ -18201,7 +18201,7 @@
       </c>
       <c r="B154" t="inlineStr">
         <is>
-          <t>2026-07-11 08:21:17 PM PT</t>
+          <t>2026-07-11 08:23:17 PM PT</t>
         </is>
       </c>
       <c r="C154" t="n">
@@ -18315,7 +18315,7 @@
       </c>
       <c r="B155" t="inlineStr">
         <is>
-          <t>2026-07-11 08:21:16 PM PT</t>
+          <t>2026-07-11 08:23:16 PM PT</t>
         </is>
       </c>
       <c r="C155" t="n">
@@ -18429,7 +18429,7 @@
       </c>
       <c r="B156" t="inlineStr">
         <is>
-          <t>2026-07-11 08:21:18 PM PT</t>
+          <t>2026-07-11 08:23:18 PM PT</t>
         </is>
       </c>
       <c r="C156" t="n">
@@ -18442,25 +18442,25 @@
       </c>
       <c r="E156" t="inlineStr">
         <is>
-          <t>Bottom 7 | 3 out</t>
+          <t>Top 8 | 0 out</t>
         </is>
       </c>
       <c r="F156" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="G156" t="inlineStr">
         <is>
-          <t>Bottom</t>
+          <t>Top</t>
         </is>
       </c>
       <c r="H156" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="I156" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="J156" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="K156" t="inlineStr">
         <is>
@@ -18552,7 +18552,7 @@
       </c>
       <c r="B157" t="inlineStr">
         <is>
-          <t>2026-07-11 08:21:18 PM PT</t>
+          <t>2026-07-11 08:23:18 PM PT</t>
         </is>
       </c>
       <c r="C157" t="n">
@@ -18565,25 +18565,25 @@
       </c>
       <c r="E157" t="inlineStr">
         <is>
-          <t>Bottom 7 | 3 out</t>
+          <t>Top 8 | 0 out</t>
         </is>
       </c>
       <c r="F157" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="G157" t="inlineStr">
         <is>
-          <t>Bottom</t>
+          <t>Top</t>
         </is>
       </c>
       <c r="H157" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="I157" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="J157" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="K157" t="inlineStr">
         <is>
@@ -18675,7 +18675,7 @@
       </c>
       <c r="B158" t="inlineStr">
         <is>
-          <t>2026-07-11 08:21:18 PM PT</t>
+          <t>2026-07-11 08:23:18 PM PT</t>
         </is>
       </c>
       <c r="C158" t="n">
@@ -18688,25 +18688,25 @@
       </c>
       <c r="E158" t="inlineStr">
         <is>
-          <t>Bottom 7 | 3 out</t>
+          <t>Top 8 | 0 out</t>
         </is>
       </c>
       <c r="F158" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="G158" t="inlineStr">
         <is>
-          <t>Bottom</t>
+          <t>Top</t>
         </is>
       </c>
       <c r="H158" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="I158" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="J158" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="K158" t="inlineStr">
         <is>
@@ -18798,7 +18798,7 @@
       </c>
       <c r="B159" t="inlineStr">
         <is>
-          <t>2026-07-11 08:21:18 PM PT</t>
+          <t>2026-07-11 08:23:18 PM PT</t>
         </is>
       </c>
       <c r="C159" t="n">
@@ -18811,25 +18811,25 @@
       </c>
       <c r="E159" t="inlineStr">
         <is>
-          <t>Bottom 7 | 3 out</t>
+          <t>Top 8 | 0 out</t>
         </is>
       </c>
       <c r="F159" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="G159" t="inlineStr">
         <is>
-          <t>Bottom</t>
+          <t>Top</t>
         </is>
       </c>
       <c r="H159" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="I159" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="J159" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="K159" t="inlineStr">
         <is>
@@ -18921,7 +18921,7 @@
       </c>
       <c r="B160" t="inlineStr">
         <is>
-          <t>2026-07-11 08:21:18 PM PT</t>
+          <t>2026-07-11 08:23:18 PM PT</t>
         </is>
       </c>
       <c r="C160" t="n">
@@ -19035,7 +19035,7 @@
       </c>
       <c r="B161" t="inlineStr">
         <is>
-          <t>2026-07-11 08:21:18 PM PT</t>
+          <t>2026-07-11 08:23:18 PM PT</t>
         </is>
       </c>
       <c r="C161" t="n">
@@ -19149,7 +19149,7 @@
       </c>
       <c r="B162" t="inlineStr">
         <is>
-          <t>2026-07-11 08:21:18 PM PT</t>
+          <t>2026-07-11 08:23:18 PM PT</t>
         </is>
       </c>
       <c r="C162" t="n">
@@ -19263,7 +19263,7 @@
       </c>
       <c r="B163" t="inlineStr">
         <is>
-          <t>2026-07-11 08:21:18 PM PT</t>
+          <t>2026-07-11 08:23:18 PM PT</t>
         </is>
       </c>
       <c r="C163" t="n">
@@ -19377,7 +19377,7 @@
       </c>
       <c r="B164" t="inlineStr">
         <is>
-          <t>2026-07-11 08:21:18 PM PT</t>
+          <t>2026-07-11 08:23:18 PM PT</t>
         </is>
       </c>
       <c r="C164" t="n">
@@ -19491,7 +19491,7 @@
       </c>
       <c r="B165" t="inlineStr">
         <is>
-          <t>2026-07-11 08:21:17 PM PT</t>
+          <t>2026-07-11 08:23:17 PM PT</t>
         </is>
       </c>
       <c r="C165" t="n">
@@ -19605,7 +19605,7 @@
       </c>
       <c r="B166" t="inlineStr">
         <is>
-          <t>2026-07-11 08:21:17 PM PT</t>
+          <t>2026-07-11 08:23:17 PM PT</t>
         </is>
       </c>
       <c r="C166" t="n">
@@ -19719,7 +19719,7 @@
       </c>
       <c r="B167" t="inlineStr">
         <is>
-          <t>2026-07-11 08:21:17 PM PT</t>
+          <t>2026-07-11 08:23:17 PM PT</t>
         </is>
       </c>
       <c r="C167" t="n">
@@ -19833,7 +19833,7 @@
       </c>
       <c r="B168" t="inlineStr">
         <is>
-          <t>2026-07-11 08:21:17 PM PT</t>
+          <t>2026-07-11 08:23:17 PM PT</t>
         </is>
       </c>
       <c r="C168" t="n">
@@ -19947,7 +19947,7 @@
       </c>
       <c r="B169" t="inlineStr">
         <is>
-          <t>2026-07-11 08:21:18 PM PT</t>
+          <t>2026-07-11 08:23:17 PM PT</t>
         </is>
       </c>
       <c r="C169" t="n">
@@ -20061,7 +20061,7 @@
       </c>
       <c r="B170" t="inlineStr">
         <is>
-          <t>2026-07-11 08:21:16 PM PT</t>
+          <t>2026-07-11 08:23:16 PM PT</t>
         </is>
       </c>
       <c r="C170" t="n">
@@ -20175,7 +20175,7 @@
       </c>
       <c r="B171" t="inlineStr">
         <is>
-          <t>2026-07-11 08:21:18 PM PT</t>
+          <t>2026-07-11 08:23:18 PM PT</t>
         </is>
       </c>
       <c r="C171" t="n">
@@ -20188,7 +20188,7 @@
       </c>
       <c r="E171" t="inlineStr">
         <is>
-          <t>Top 7 | 2 out</t>
+          <t>Top 7 | 3 out</t>
         </is>
       </c>
       <c r="F171" t="n">
@@ -20200,13 +20200,13 @@
         </is>
       </c>
       <c r="H171" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="I171" t="n">
         <v>0</v>
       </c>
       <c r="J171" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="K171" t="inlineStr">
         <is>
@@ -20298,7 +20298,7 @@
       </c>
       <c r="B172" t="inlineStr">
         <is>
-          <t>2026-07-11 08:21:18 PM PT</t>
+          <t>2026-07-11 08:23:18 PM PT</t>
         </is>
       </c>
       <c r="C172" t="n">
@@ -20311,7 +20311,7 @@
       </c>
       <c r="E172" t="inlineStr">
         <is>
-          <t>Top 7 | 2 out</t>
+          <t>Top 7 | 3 out</t>
         </is>
       </c>
       <c r="F172" t="n">
@@ -20323,13 +20323,13 @@
         </is>
       </c>
       <c r="H172" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="I172" t="n">
         <v>0</v>
       </c>
       <c r="J172" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="K172" t="inlineStr">
         <is>
@@ -20421,7 +20421,7 @@
       </c>
       <c r="B173" t="inlineStr">
         <is>
-          <t>2026-07-11 08:21:17 PM PT</t>
+          <t>2026-07-11 08:23:17 PM PT</t>
         </is>
       </c>
       <c r="C173" t="n">
@@ -20535,7 +20535,7 @@
       </c>
       <c r="B174" t="inlineStr">
         <is>
-          <t>2026-07-11 08:21:17 PM PT</t>
+          <t>2026-07-11 08:23:17 PM PT</t>
         </is>
       </c>
       <c r="C174" t="n">
@@ -20649,7 +20649,7 @@
       </c>
       <c r="B175" t="inlineStr">
         <is>
-          <t>2026-07-11 08:21:16 PM PT</t>
+          <t>2026-07-11 08:23:16 PM PT</t>
         </is>
       </c>
       <c r="C175" t="n">
@@ -20763,7 +20763,7 @@
       </c>
       <c r="B176" t="inlineStr">
         <is>
-          <t>2026-07-11 08:21:16 PM PT</t>
+          <t>2026-07-11 08:23:16 PM PT</t>
         </is>
       </c>
       <c r="C176" t="n">
@@ -20877,7 +20877,7 @@
       </c>
       <c r="B177" t="inlineStr">
         <is>
-          <t>2026-07-11 08:21:16 PM PT</t>
+          <t>2026-07-11 08:23:16 PM PT</t>
         </is>
       </c>
       <c r="C177" t="n">
@@ -20991,7 +20991,7 @@
       </c>
       <c r="B178" t="inlineStr">
         <is>
-          <t>2026-07-11 08:21:16 PM PT</t>
+          <t>2026-07-11 08:23:16 PM PT</t>
         </is>
       </c>
       <c r="C178" t="n">
@@ -21105,7 +21105,7 @@
       </c>
       <c r="B179" t="inlineStr">
         <is>
-          <t>2026-07-11 08:21:16 PM PT</t>
+          <t>2026-07-11 08:23:16 PM PT</t>
         </is>
       </c>
       <c r="C179" t="n">
@@ -21219,7 +21219,7 @@
       </c>
       <c r="B180" t="inlineStr">
         <is>
-          <t>2026-07-11 08:21:17 PM PT</t>
+          <t>2026-07-11 08:23:17 PM PT</t>
         </is>
       </c>
       <c r="C180" t="n">
@@ -21333,7 +21333,7 @@
       </c>
       <c r="B181" t="inlineStr">
         <is>
-          <t>2026-07-11 08:21:17 PM PT</t>
+          <t>2026-07-11 08:23:17 PM PT</t>
         </is>
       </c>
       <c r="C181" t="n">
@@ -21447,7 +21447,7 @@
       </c>
       <c r="B182" t="inlineStr">
         <is>
-          <t>2026-07-11 08:21:17 PM PT</t>
+          <t>2026-07-11 08:23:17 PM PT</t>
         </is>
       </c>
       <c r="C182" t="n">
@@ -21561,7 +21561,7 @@
       </c>
       <c r="B183" t="inlineStr">
         <is>
-          <t>2026-07-11 08:21:17 PM PT</t>
+          <t>2026-07-11 08:23:17 PM PT</t>
         </is>
       </c>
       <c r="C183" t="n">
@@ -21675,7 +21675,7 @@
       </c>
       <c r="B184" t="inlineStr">
         <is>
-          <t>2026-07-11 08:21:16 PM PT</t>
+          <t>2026-07-11 08:23:16 PM PT</t>
         </is>
       </c>
       <c r="C184" t="n">
@@ -21789,7 +21789,7 @@
       </c>
       <c r="B185" t="inlineStr">
         <is>
-          <t>2026-07-11 08:21:16 PM PT</t>
+          <t>2026-07-11 08:23:16 PM PT</t>
         </is>
       </c>
       <c r="C185" t="n">
@@ -21903,7 +21903,7 @@
       </c>
       <c r="B186" t="inlineStr">
         <is>
-          <t>2026-07-11 08:21:17 PM PT</t>
+          <t>2026-07-11 08:23:17 PM PT</t>
         </is>
       </c>
       <c r="C186" t="n">
@@ -22017,7 +22017,7 @@
       </c>
       <c r="B187" t="inlineStr">
         <is>
-          <t>2026-07-11 08:21:17 PM PT</t>
+          <t>2026-07-11 08:23:17 PM PT</t>
         </is>
       </c>
       <c r="C187" t="n">
@@ -22131,7 +22131,7 @@
       </c>
       <c r="B188" t="inlineStr">
         <is>
-          <t>2026-07-11 08:21:17 PM PT</t>
+          <t>2026-07-11 08:23:17 PM PT</t>
         </is>
       </c>
       <c r="C188" t="n">
@@ -22245,7 +22245,7 @@
       </c>
       <c r="B189" t="inlineStr">
         <is>
-          <t>2026-07-11 08:21:18 PM PT</t>
+          <t>2026-07-11 08:23:17 PM PT</t>
         </is>
       </c>
       <c r="C189" t="n">
@@ -22359,7 +22359,7 @@
       </c>
       <c r="B190" t="inlineStr">
         <is>
-          <t>2026-07-11 08:21:17 PM PT</t>
+          <t>2026-07-11 08:23:17 PM PT</t>
         </is>
       </c>
       <c r="C190" t="n">
@@ -22473,7 +22473,7 @@
       </c>
       <c r="B191" t="inlineStr">
         <is>
-          <t>2026-07-11 08:21:17 PM PT</t>
+          <t>2026-07-11 08:23:17 PM PT</t>
         </is>
       </c>
       <c r="C191" t="n">
@@ -22587,7 +22587,7 @@
       </c>
       <c r="B192" t="inlineStr">
         <is>
-          <t>2026-07-11 08:21:18 PM PT</t>
+          <t>2026-07-11 08:23:18 PM PT</t>
         </is>
       </c>
       <c r="C192" t="n">
@@ -22600,7 +22600,7 @@
       </c>
       <c r="E192" t="inlineStr">
         <is>
-          <t>Top 7 | 2 out</t>
+          <t>Top 7 | 3 out</t>
         </is>
       </c>
       <c r="F192" t="n">
@@ -22612,13 +22612,13 @@
         </is>
       </c>
       <c r="H192" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="I192" t="n">
         <v>0</v>
       </c>
       <c r="J192" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="K192" t="inlineStr">
         <is>
@@ -22710,7 +22710,7 @@
       </c>
       <c r="B193" t="inlineStr">
         <is>
-          <t>2026-07-11 08:21:18 PM PT</t>
+          <t>2026-07-11 08:23:18 PM PT</t>
         </is>
       </c>
       <c r="C193" t="n">
@@ -22723,7 +22723,7 @@
       </c>
       <c r="E193" t="inlineStr">
         <is>
-          <t>Top 7 | 2 out</t>
+          <t>Top 7 | 3 out</t>
         </is>
       </c>
       <c r="F193" t="n">
@@ -22735,13 +22735,13 @@
         </is>
       </c>
       <c r="H193" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="I193" t="n">
         <v>0</v>
       </c>
       <c r="J193" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="K193" t="inlineStr">
         <is>
@@ -22833,7 +22833,7 @@
       </c>
       <c r="B194" t="inlineStr">
         <is>
-          <t>2026-07-11 08:21:16 PM PT</t>
+          <t>2026-07-11 08:23:16 PM PT</t>
         </is>
       </c>
       <c r="C194" t="n">
@@ -22947,7 +22947,7 @@
       </c>
       <c r="B195" t="inlineStr">
         <is>
-          <t>2026-07-11 08:21:18 PM PT</t>
+          <t>2026-07-11 08:23:18 PM PT</t>
         </is>
       </c>
       <c r="C195" t="n">
@@ -23061,7 +23061,7 @@
       </c>
       <c r="B196" t="inlineStr">
         <is>
-          <t>2026-07-11 08:21:18 PM PT</t>
+          <t>2026-07-11 08:23:18 PM PT</t>
         </is>
       </c>
       <c r="C196" t="n">
@@ -23175,7 +23175,7 @@
       </c>
       <c r="B197" t="inlineStr">
         <is>
-          <t>2026-07-11 08:21:18 PM PT</t>
+          <t>2026-07-11 08:23:17 PM PT</t>
         </is>
       </c>
       <c r="C197" t="n">
@@ -23289,7 +23289,7 @@
       </c>
       <c r="B198" t="inlineStr">
         <is>
-          <t>2026-07-11 08:21:17 PM PT</t>
+          <t>2026-07-11 08:23:17 PM PT</t>
         </is>
       </c>
       <c r="C198" t="n">
@@ -23403,7 +23403,7 @@
       </c>
       <c r="B199" t="inlineStr">
         <is>
-          <t>2026-07-11 08:21:17 PM PT</t>
+          <t>2026-07-11 08:23:17 PM PT</t>
         </is>
       </c>
       <c r="C199" t="n">
@@ -23517,7 +23517,7 @@
       </c>
       <c r="B200" t="inlineStr">
         <is>
-          <t>2026-07-11 08:21:17 PM PT</t>
+          <t>2026-07-11 08:23:17 PM PT</t>
         </is>
       </c>
       <c r="C200" t="n">
@@ -23631,7 +23631,7 @@
       </c>
       <c r="B201" t="inlineStr">
         <is>
-          <t>2026-07-11 08:21:18 PM PT</t>
+          <t>2026-07-11 08:23:18 PM PT</t>
         </is>
       </c>
       <c r="C201" t="n">
@@ -23745,7 +23745,7 @@
       </c>
       <c r="B202" t="inlineStr">
         <is>
-          <t>2026-07-11 08:21:17 PM PT</t>
+          <t>2026-07-11 08:23:17 PM PT</t>
         </is>
       </c>
       <c r="C202" t="n">
@@ -23859,7 +23859,7 @@
       </c>
       <c r="B203" t="inlineStr">
         <is>
-          <t>2026-07-11 08:21:17 PM PT</t>
+          <t>2026-07-11 08:23:17 PM PT</t>
         </is>
       </c>
       <c r="C203" t="n">
@@ -23973,7 +23973,7 @@
       </c>
       <c r="B204" t="inlineStr">
         <is>
-          <t>2026-07-11 08:21:17 PM PT</t>
+          <t>2026-07-11 08:23:17 PM PT</t>
         </is>
       </c>
       <c r="C204" t="n">
@@ -24087,7 +24087,7 @@
       </c>
       <c r="B205" t="inlineStr">
         <is>
-          <t>2026-07-11 08:21:16 PM PT</t>
+          <t>2026-07-11 08:23:16 PM PT</t>
         </is>
       </c>
       <c r="C205" t="n">
@@ -24201,7 +24201,7 @@
       </c>
       <c r="B206" t="inlineStr">
         <is>
-          <t>2026-07-11 08:21:16 PM PT</t>
+          <t>2026-07-11 08:23:16 PM PT</t>
         </is>
       </c>
       <c r="C206" t="n">
@@ -24315,7 +24315,7 @@
       </c>
       <c r="B207" t="inlineStr">
         <is>
-          <t>2026-07-11 08:21:17 PM PT</t>
+          <t>2026-07-11 08:23:17 PM PT</t>
         </is>
       </c>
       <c r="C207" t="n">
@@ -24429,7 +24429,7 @@
       </c>
       <c r="B208" t="inlineStr">
         <is>
-          <t>2026-07-11 08:21:18 PM PT</t>
+          <t>2026-07-11 08:23:17 PM PT</t>
         </is>
       </c>
       <c r="C208" t="n">
@@ -24543,7 +24543,7 @@
       </c>
       <c r="B209" t="inlineStr">
         <is>
-          <t>2026-07-11 08:21:18 PM PT</t>
+          <t>2026-07-11 08:23:17 PM PT</t>
         </is>
       </c>
       <c r="C209" t="n">
@@ -24657,7 +24657,7 @@
       </c>
       <c r="B210" t="inlineStr">
         <is>
-          <t>2026-07-11 08:21:18 PM PT</t>
+          <t>2026-07-11 08:23:17 PM PT</t>
         </is>
       </c>
       <c r="C210" t="n">
@@ -24771,7 +24771,7 @@
       </c>
       <c r="B211" t="inlineStr">
         <is>
-          <t>2026-07-11 08:21:18 PM PT</t>
+          <t>2026-07-11 08:23:17 PM PT</t>
         </is>
       </c>
       <c r="C211" t="n">
@@ -24885,7 +24885,7 @@
       </c>
       <c r="B212" t="inlineStr">
         <is>
-          <t>2026-07-11 08:21:16 PM PT</t>
+          <t>2026-07-11 08:23:16 PM PT</t>
         </is>
       </c>
       <c r="C212" t="n">
@@ -24999,7 +24999,7 @@
       </c>
       <c r="B213" t="inlineStr">
         <is>
-          <t>2026-07-11 08:21:17 PM PT</t>
+          <t>2026-07-11 08:23:17 PM PT</t>
         </is>
       </c>
       <c r="C213" t="n">
@@ -25113,7 +25113,7 @@
       </c>
       <c r="B214" t="inlineStr">
         <is>
-          <t>2026-07-11 08:21:17 PM PT</t>
+          <t>2026-07-11 08:23:17 PM PT</t>
         </is>
       </c>
       <c r="C214" t="n">
@@ -25227,7 +25227,7 @@
       </c>
       <c r="B215" t="inlineStr">
         <is>
-          <t>2026-07-11 08:21:16 PM PT</t>
+          <t>2026-07-11 08:23:16 PM PT</t>
         </is>
       </c>
       <c r="C215" t="n">
@@ -25341,7 +25341,7 @@
       </c>
       <c r="B216" t="inlineStr">
         <is>
-          <t>2026-07-11 08:21:17 PM PT</t>
+          <t>2026-07-11 08:23:17 PM PT</t>
         </is>
       </c>
       <c r="C216" t="n">
@@ -25455,7 +25455,7 @@
       </c>
       <c r="B217" t="inlineStr">
         <is>
-          <t>2026-07-11 08:21:17 PM PT</t>
+          <t>2026-07-11 08:23:17 PM PT</t>
         </is>
       </c>
       <c r="C217" t="n">
@@ -25569,7 +25569,7 @@
       </c>
       <c r="B218" t="inlineStr">
         <is>
-          <t>2026-07-11 08:21:17 PM PT</t>
+          <t>2026-07-11 08:23:17 PM PT</t>
         </is>
       </c>
       <c r="C218" t="n">
@@ -25683,7 +25683,7 @@
       </c>
       <c r="B219" t="inlineStr">
         <is>
-          <t>2026-07-11 08:21:17 PM PT</t>
+          <t>2026-07-11 08:23:17 PM PT</t>
         </is>
       </c>
       <c r="C219" t="n">
@@ -25797,7 +25797,7 @@
       </c>
       <c r="B220" t="inlineStr">
         <is>
-          <t>2026-07-11 08:21:17 PM PT</t>
+          <t>2026-07-11 08:23:17 PM PT</t>
         </is>
       </c>
       <c r="C220" t="n">
@@ -25911,7 +25911,7 @@
       </c>
       <c r="B221" t="inlineStr">
         <is>
-          <t>2026-07-11 08:21:17 PM PT</t>
+          <t>2026-07-11 08:23:17 PM PT</t>
         </is>
       </c>
       <c r="C221" t="n">
@@ -26025,7 +26025,7 @@
       </c>
       <c r="B222" t="inlineStr">
         <is>
-          <t>2026-07-11 08:21:17 PM PT</t>
+          <t>2026-07-11 08:23:17 PM PT</t>
         </is>
       </c>
       <c r="C222" t="n">
@@ -26139,7 +26139,7 @@
       </c>
       <c r="B223" t="inlineStr">
         <is>
-          <t>2026-07-11 08:21:16 PM PT</t>
+          <t>2026-07-11 08:23:16 PM PT</t>
         </is>
       </c>
       <c r="C223" t="n">
@@ -26253,7 +26253,7 @@
       </c>
       <c r="B224" t="inlineStr">
         <is>
-          <t>2026-07-11 08:21:16 PM PT</t>
+          <t>2026-07-11 08:23:16 PM PT</t>
         </is>
       </c>
       <c r="C224" t="n">
@@ -26367,7 +26367,7 @@
       </c>
       <c r="B225" t="inlineStr">
         <is>
-          <t>2026-07-11 08:21:17 PM PT</t>
+          <t>2026-07-11 08:23:17 PM PT</t>
         </is>
       </c>
       <c r="C225" t="n">
@@ -26481,7 +26481,7 @@
       </c>
       <c r="B226" t="inlineStr">
         <is>
-          <t>2026-07-11 08:21:17 PM PT</t>
+          <t>2026-07-11 08:23:17 PM PT</t>
         </is>
       </c>
       <c r="C226" t="n">
@@ -26595,7 +26595,7 @@
       </c>
       <c r="B227" t="inlineStr">
         <is>
-          <t>2026-07-11 08:21:18 PM PT</t>
+          <t>2026-07-11 08:23:17 PM PT</t>
         </is>
       </c>
       <c r="C227" t="n">
@@ -26709,7 +26709,7 @@
       </c>
       <c r="B228" t="inlineStr">
         <is>
-          <t>2026-07-11 08:21:18 PM PT</t>
+          <t>2026-07-11 08:23:17 PM PT</t>
         </is>
       </c>
       <c r="C228" t="n">
@@ -26823,7 +26823,7 @@
       </c>
       <c r="B229" t="inlineStr">
         <is>
-          <t>2026-07-11 08:21:18 PM PT</t>
+          <t>2026-07-11 08:23:18 PM PT</t>
         </is>
       </c>
       <c r="C229" t="n">
@@ -26836,25 +26836,25 @@
       </c>
       <c r="E229" t="inlineStr">
         <is>
-          <t>Bottom 7 | 3 out</t>
+          <t>Top 8 | 0 out</t>
         </is>
       </c>
       <c r="F229" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="G229" t="inlineStr">
         <is>
-          <t>Bottom</t>
+          <t>Top</t>
         </is>
       </c>
       <c r="H229" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="I229" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="J229" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="K229" t="inlineStr">
         <is>
@@ -26946,7 +26946,7 @@
       </c>
       <c r="B230" t="inlineStr">
         <is>
-          <t>2026-07-11 08:21:17 PM PT</t>
+          <t>2026-07-11 08:23:17 PM PT</t>
         </is>
       </c>
       <c r="C230" t="n">
@@ -27060,7 +27060,7 @@
       </c>
       <c r="B231" t="inlineStr">
         <is>
-          <t>2026-07-11 08:21:17 PM PT</t>
+          <t>2026-07-11 08:23:17 PM PT</t>
         </is>
       </c>
       <c r="C231" t="n">
@@ -27174,7 +27174,7 @@
       </c>
       <c r="B232" t="inlineStr">
         <is>
-          <t>2026-07-11 08:21:17 PM PT</t>
+          <t>2026-07-11 08:23:17 PM PT</t>
         </is>
       </c>
       <c r="C232" t="n">
@@ -27288,7 +27288,7 @@
       </c>
       <c r="B233" t="inlineStr">
         <is>
-          <t>2026-07-11 08:21:17 PM PT</t>
+          <t>2026-07-11 08:23:17 PM PT</t>
         </is>
       </c>
       <c r="C233" t="n">
@@ -27402,7 +27402,7 @@
       </c>
       <c r="B234" t="inlineStr">
         <is>
-          <t>2026-07-11 08:21:18 PM PT</t>
+          <t>2026-07-11 08:23:18 PM PT</t>
         </is>
       </c>
       <c r="C234" t="n">
@@ -27415,7 +27415,7 @@
       </c>
       <c r="E234" t="inlineStr">
         <is>
-          <t>Top 7 | 2 out</t>
+          <t>Top 7 | 3 out</t>
         </is>
       </c>
       <c r="F234" t="n">
@@ -27427,13 +27427,13 @@
         </is>
       </c>
       <c r="H234" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="I234" t="n">
         <v>0</v>
       </c>
       <c r="J234" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="K234" t="inlineStr">
         <is>
@@ -27525,7 +27525,7 @@
       </c>
       <c r="B235" t="inlineStr">
         <is>
-          <t>2026-07-11 08:21:18 PM PT</t>
+          <t>2026-07-11 08:23:18 PM PT</t>
         </is>
       </c>
       <c r="C235" t="n">
@@ -27538,7 +27538,7 @@
       </c>
       <c r="E235" t="inlineStr">
         <is>
-          <t>Top 7 | 2 out</t>
+          <t>Top 7 | 3 out</t>
         </is>
       </c>
       <c r="F235" t="n">
@@ -27550,13 +27550,13 @@
         </is>
       </c>
       <c r="H235" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="I235" t="n">
         <v>0</v>
       </c>
       <c r="J235" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="K235" t="inlineStr">
         <is>
@@ -27648,7 +27648,7 @@
       </c>
       <c r="B236" t="inlineStr">
         <is>
-          <t>2026-07-11 08:21:16 PM PT</t>
+          <t>2026-07-11 08:23:16 PM PT</t>
         </is>
       </c>
       <c r="C236" t="n">
@@ -27762,7 +27762,7 @@
       </c>
       <c r="B237" t="inlineStr">
         <is>
-          <t>2026-07-11 08:21:16 PM PT</t>
+          <t>2026-07-11 08:23:16 PM PT</t>
         </is>
       </c>
       <c r="C237" t="n">
@@ -27876,7 +27876,7 @@
       </c>
       <c r="B238" t="inlineStr">
         <is>
-          <t>2026-07-11 08:21:16 PM PT</t>
+          <t>2026-07-11 08:23:16 PM PT</t>
         </is>
       </c>
       <c r="C238" t="n">
@@ -27990,7 +27990,7 @@
       </c>
       <c r="B239" t="inlineStr">
         <is>
-          <t>2026-07-11 08:21:16 PM PT</t>
+          <t>2026-07-11 08:23:16 PM PT</t>
         </is>
       </c>
       <c r="C239" t="n">
@@ -28104,7 +28104,7 @@
       </c>
       <c r="B240" t="inlineStr">
         <is>
-          <t>2026-07-11 08:21:16 PM PT</t>
+          <t>2026-07-11 08:23:16 PM PT</t>
         </is>
       </c>
       <c r="C240" t="n">
@@ -28218,7 +28218,7 @@
       </c>
       <c r="B241" t="inlineStr">
         <is>
-          <t>2026-07-11 08:21:16 PM PT</t>
+          <t>2026-07-11 08:23:16 PM PT</t>
         </is>
       </c>
       <c r="C241" t="n">
@@ -28332,7 +28332,7 @@
       </c>
       <c r="B242" t="inlineStr">
         <is>
-          <t>2026-07-11 08:21:16 PM PT</t>
+          <t>2026-07-11 08:23:16 PM PT</t>
         </is>
       </c>
       <c r="C242" t="n">
@@ -28446,7 +28446,7 @@
       </c>
       <c r="B243" t="inlineStr">
         <is>
-          <t>2026-07-11 08:21:18 PM PT</t>
+          <t>2026-07-11 08:23:18 PM PT</t>
         </is>
       </c>
       <c r="C243" t="n">
@@ -28560,7 +28560,7 @@
       </c>
       <c r="B244" t="inlineStr">
         <is>
-          <t>2026-07-11 08:21:18 PM PT</t>
+          <t>2026-07-11 08:23:18 PM PT</t>
         </is>
       </c>
       <c r="C244" t="n">
@@ -28674,7 +28674,7 @@
       </c>
       <c r="B245" t="inlineStr">
         <is>
-          <t>2026-07-11 08:21:18 PM PT</t>
+          <t>2026-07-11 08:23:18 PM PT</t>
         </is>
       </c>
       <c r="C245" t="n">
@@ -28788,7 +28788,7 @@
       </c>
       <c r="B246" t="inlineStr">
         <is>
-          <t>2026-07-11 08:21:18 PM PT</t>
+          <t>2026-07-11 08:23:17 PM PT</t>
         </is>
       </c>
       <c r="C246" t="n">
@@ -28902,7 +28902,7 @@
       </c>
       <c r="B247" t="inlineStr">
         <is>
-          <t>2026-07-11 08:21:18 PM PT</t>
+          <t>2026-07-11 08:23:17 PM PT</t>
         </is>
       </c>
       <c r="C247" t="n">
@@ -29016,7 +29016,7 @@
       </c>
       <c r="B248" t="inlineStr">
         <is>
-          <t>2026-07-11 08:21:18 PM PT</t>
+          <t>2026-07-11 08:23:17 PM PT</t>
         </is>
       </c>
       <c r="C248" t="n">
@@ -29130,7 +29130,7 @@
       </c>
       <c r="B249" t="inlineStr">
         <is>
-          <t>2026-07-11 08:21:17 PM PT</t>
+          <t>2026-07-11 08:23:17 PM PT</t>
         </is>
       </c>
       <c r="C249" t="n">
@@ -29244,7 +29244,7 @@
       </c>
       <c r="B250" t="inlineStr">
         <is>
-          <t>2026-07-11 08:21:17 PM PT</t>
+          <t>2026-07-11 08:23:17 PM PT</t>
         </is>
       </c>
       <c r="C250" t="n">
@@ -29358,7 +29358,7 @@
       </c>
       <c r="B251" t="inlineStr">
         <is>
-          <t>2026-07-11 08:21:17 PM PT</t>
+          <t>2026-07-11 08:23:17 PM PT</t>
         </is>
       </c>
       <c r="C251" t="n">
@@ -29472,7 +29472,7 @@
       </c>
       <c r="B252" t="inlineStr">
         <is>
-          <t>2026-07-11 08:21:18 PM PT</t>
+          <t>2026-07-11 08:23:18 PM PT</t>
         </is>
       </c>
       <c r="C252" t="n">
@@ -29586,7 +29586,7 @@
       </c>
       <c r="B253" t="inlineStr">
         <is>
-          <t>2026-07-11 08:21:18 PM PT</t>
+          <t>2026-07-11 08:23:18 PM PT</t>
         </is>
       </c>
       <c r="C253" t="n">
@@ -29700,7 +29700,7 @@
       </c>
       <c r="B254" t="inlineStr">
         <is>
-          <t>2026-07-11 08:21:18 PM PT</t>
+          <t>2026-07-11 08:23:18 PM PT</t>
         </is>
       </c>
       <c r="C254" t="n">
@@ -29814,7 +29814,7 @@
       </c>
       <c r="B255" t="inlineStr">
         <is>
-          <t>2026-07-11 08:21:18 PM PT</t>
+          <t>2026-07-11 08:23:18 PM PT</t>
         </is>
       </c>
       <c r="C255" t="n">
@@ -29928,7 +29928,7 @@
       </c>
       <c r="B256" t="inlineStr">
         <is>
-          <t>2026-07-11 08:21:18 PM PT</t>
+          <t>2026-07-11 08:23:18 PM PT</t>
         </is>
       </c>
       <c r="C256" t="n">
@@ -30042,7 +30042,7 @@
       </c>
       <c r="B257" t="inlineStr">
         <is>
-          <t>2026-07-11 08:21:17 PM PT</t>
+          <t>2026-07-11 08:23:17 PM PT</t>
         </is>
       </c>
       <c r="C257" t="n">
@@ -30156,7 +30156,7 @@
       </c>
       <c r="B258" t="inlineStr">
         <is>
-          <t>2026-07-11 08:21:17 PM PT</t>
+          <t>2026-07-11 08:23:17 PM PT</t>
         </is>
       </c>
       <c r="C258" t="n">
@@ -30270,7 +30270,7 @@
       </c>
       <c r="B259" t="inlineStr">
         <is>
-          <t>2026-07-11 08:21:17 PM PT</t>
+          <t>2026-07-11 08:23:17 PM PT</t>
         </is>
       </c>
       <c r="C259" t="n">
@@ -30384,7 +30384,7 @@
       </c>
       <c r="B260" t="inlineStr">
         <is>
-          <t>2026-07-11 08:21:16 PM PT</t>
+          <t>2026-07-11 08:23:16 PM PT</t>
         </is>
       </c>
       <c r="C260" t="n">
@@ -30498,7 +30498,7 @@
       </c>
       <c r="B261" t="inlineStr">
         <is>
-          <t>2026-07-11 08:21:16 PM PT</t>
+          <t>2026-07-11 08:23:16 PM PT</t>
         </is>
       </c>
       <c r="C261" t="n">
@@ -30612,7 +30612,7 @@
       </c>
       <c r="B262" t="inlineStr">
         <is>
-          <t>2026-07-11 08:21:16 PM PT</t>
+          <t>2026-07-11 08:23:16 PM PT</t>
         </is>
       </c>
       <c r="C262" t="n">
@@ -30726,7 +30726,7 @@
       </c>
       <c r="B263" t="inlineStr">
         <is>
-          <t>2026-07-11 08:21:16 PM PT</t>
+          <t>2026-07-11 08:23:16 PM PT</t>
         </is>
       </c>
       <c r="C263" t="n">
@@ -30840,7 +30840,7 @@
       </c>
       <c r="B264" t="inlineStr">
         <is>
-          <t>2026-07-11 08:21:17 PM PT</t>
+          <t>2026-07-11 08:23:17 PM PT</t>
         </is>
       </c>
       <c r="C264" t="n">
@@ -30954,7 +30954,7 @@
       </c>
       <c r="B265" t="inlineStr">
         <is>
-          <t>2026-07-11 08:21:17 PM PT</t>
+          <t>2026-07-11 08:23:17 PM PT</t>
         </is>
       </c>
       <c r="C265" t="n">
@@ -31068,7 +31068,7 @@
       </c>
       <c r="B266" t="inlineStr">
         <is>
-          <t>2026-07-11 08:21:17 PM PT</t>
+          <t>2026-07-11 08:23:17 PM PT</t>
         </is>
       </c>
       <c r="C266" t="n">
@@ -31182,7 +31182,7 @@
       </c>
       <c r="B267" t="inlineStr">
         <is>
-          <t>2026-07-11 08:21:17 PM PT</t>
+          <t>2026-07-11 08:23:17 PM PT</t>
         </is>
       </c>
       <c r="C267" t="n">
@@ -31296,7 +31296,7 @@
       </c>
       <c r="B268" t="inlineStr">
         <is>
-          <t>2026-07-11 08:21:18 PM PT</t>
+          <t>2026-07-11 08:23:17 PM PT</t>
         </is>
       </c>
       <c r="C268" t="n">
@@ -31410,7 +31410,7 @@
       </c>
       <c r="B269" t="inlineStr">
         <is>
-          <t>2026-07-11 08:21:18 PM PT</t>
+          <t>2026-07-11 08:23:17 PM PT</t>
         </is>
       </c>
       <c r="C269" t="n">
@@ -31524,7 +31524,7 @@
       </c>
       <c r="B270" t="inlineStr">
         <is>
-          <t>2026-07-11 08:21:18 PM PT</t>
+          <t>2026-07-11 08:23:17 PM PT</t>
         </is>
       </c>
       <c r="C270" t="n">
@@ -31638,7 +31638,7 @@
       </c>
       <c r="B271" t="inlineStr">
         <is>
-          <t>2026-07-11 08:21:18 PM PT</t>
+          <t>2026-07-11 08:23:17 PM PT</t>
         </is>
       </c>
       <c r="C271" t="n">
@@ -31752,7 +31752,7 @@
       </c>
       <c r="B272" t="inlineStr">
         <is>
-          <t>2026-07-11 08:21:18 PM PT</t>
+          <t>2026-07-11 08:23:17 PM PT</t>
         </is>
       </c>
       <c r="C272" t="n">
@@ -31866,7 +31866,7 @@
       </c>
       <c r="B273" t="inlineStr">
         <is>
-          <t>2026-07-11 08:21:18 PM PT</t>
+          <t>2026-07-11 08:23:17 PM PT</t>
         </is>
       </c>
       <c r="C273" t="n">
@@ -31980,7 +31980,7 @@
       </c>
       <c r="B274" t="inlineStr">
         <is>
-          <t>2026-07-11 08:21:18 PM PT</t>
+          <t>2026-07-11 08:23:17 PM PT</t>
         </is>
       </c>
       <c r="C274" t="n">
@@ -32094,7 +32094,7 @@
       </c>
       <c r="B275" t="inlineStr">
         <is>
-          <t>2026-07-11 08:21:16 PM PT</t>
+          <t>2026-07-11 08:23:16 PM PT</t>
         </is>
       </c>
       <c r="C275" t="n">
@@ -32208,7 +32208,7 @@
       </c>
       <c r="B276" t="inlineStr">
         <is>
-          <t>2026-07-11 08:21:16 PM PT</t>
+          <t>2026-07-11 08:23:16 PM PT</t>
         </is>
       </c>
       <c r="C276" t="n">
@@ -32322,7 +32322,7 @@
       </c>
       <c r="B277" t="inlineStr">
         <is>
-          <t>2026-07-11 08:21:16 PM PT</t>
+          <t>2026-07-11 08:23:16 PM PT</t>
         </is>
       </c>
       <c r="C277" t="n">
@@ -32436,7 +32436,7 @@
       </c>
       <c r="B278" t="inlineStr">
         <is>
-          <t>2026-07-11 08:21:18 PM PT</t>
+          <t>2026-07-11 08:23:18 PM PT</t>
         </is>
       </c>
       <c r="C278" t="n">
@@ -32449,7 +32449,7 @@
       </c>
       <c r="E278" t="inlineStr">
         <is>
-          <t>Top 7 | 2 out</t>
+          <t>Top 7 | 3 out</t>
         </is>
       </c>
       <c r="F278" t="n">
@@ -32461,13 +32461,13 @@
         </is>
       </c>
       <c r="H278" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="I278" t="n">
         <v>0</v>
       </c>
       <c r="J278" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="K278" t="inlineStr">
         <is>
@@ -32559,7 +32559,7 @@
       </c>
       <c r="B279" t="inlineStr">
         <is>
-          <t>2026-07-11 08:21:18 PM PT</t>
+          <t>2026-07-11 08:23:18 PM PT</t>
         </is>
       </c>
       <c r="C279" t="n">
@@ -32572,7 +32572,7 @@
       </c>
       <c r="E279" t="inlineStr">
         <is>
-          <t>Top 7 | 2 out</t>
+          <t>Top 7 | 3 out</t>
         </is>
       </c>
       <c r="F279" t="n">
@@ -32584,13 +32584,13 @@
         </is>
       </c>
       <c r="H279" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="I279" t="n">
         <v>0</v>
       </c>
       <c r="J279" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="K279" t="inlineStr">
         <is>
@@ -32682,7 +32682,7 @@
       </c>
       <c r="B280" t="inlineStr">
         <is>
-          <t>2026-07-11 08:21:18 PM PT</t>
+          <t>2026-07-11 08:23:18 PM PT</t>
         </is>
       </c>
       <c r="C280" t="n">
@@ -32695,7 +32695,7 @@
       </c>
       <c r="E280" t="inlineStr">
         <is>
-          <t>Top 7 | 2 out</t>
+          <t>Top 7 | 3 out</t>
         </is>
       </c>
       <c r="F280" t="n">
@@ -32707,13 +32707,13 @@
         </is>
       </c>
       <c r="H280" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="I280" t="n">
         <v>0</v>
       </c>
       <c r="J280" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="K280" t="inlineStr">
         <is>
@@ -32805,7 +32805,7 @@
       </c>
       <c r="B281" t="inlineStr">
         <is>
-          <t>2026-07-11 08:21:18 PM PT</t>
+          <t>2026-07-11 08:23:18 PM PT</t>
         </is>
       </c>
       <c r="C281" t="n">
@@ -32818,7 +32818,7 @@
       </c>
       <c r="E281" t="inlineStr">
         <is>
-          <t>Top 7 | 2 out</t>
+          <t>Top 7 | 3 out</t>
         </is>
       </c>
       <c r="F281" t="n">
@@ -32830,13 +32830,13 @@
         </is>
       </c>
       <c r="H281" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="I281" t="n">
         <v>0</v>
       </c>
       <c r="J281" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="K281" t="inlineStr">
         <is>
@@ -32928,7 +32928,7 @@
       </c>
       <c r="B282" t="inlineStr">
         <is>
-          <t>2026-07-11 08:21:17 PM PT</t>
+          <t>2026-07-11 08:23:17 PM PT</t>
         </is>
       </c>
       <c r="C282" t="n">
@@ -33042,7 +33042,7 @@
       </c>
       <c r="B283" t="inlineStr">
         <is>
-          <t>2026-07-11 08:21:16 PM PT</t>
+          <t>2026-07-11 08:23:16 PM PT</t>
         </is>
       </c>
       <c r="C283" t="n">
@@ -33156,7 +33156,7 @@
       </c>
       <c r="B284" t="inlineStr">
         <is>
-          <t>2026-07-11 08:21:16 PM PT</t>
+          <t>2026-07-11 08:23:16 PM PT</t>
         </is>
       </c>
       <c r="C284" t="n">
@@ -33270,7 +33270,7 @@
       </c>
       <c r="B285" t="inlineStr">
         <is>
-          <t>2026-07-11 08:21:16 PM PT</t>
+          <t>2026-07-11 08:23:16 PM PT</t>
         </is>
       </c>
       <c r="C285" t="n">
@@ -33384,7 +33384,7 @@
       </c>
       <c r="B286" t="inlineStr">
         <is>
-          <t>2026-07-11 08:21:16 PM PT</t>
+          <t>2026-07-11 08:23:16 PM PT</t>
         </is>
       </c>
       <c r="C286" t="n">
@@ -33498,7 +33498,7 @@
       </c>
       <c r="B287" t="inlineStr">
         <is>
-          <t>2026-07-11 08:21:16 PM PT</t>
+          <t>2026-07-11 08:23:16 PM PT</t>
         </is>
       </c>
       <c r="C287" t="n">
@@ -33612,7 +33612,7 @@
       </c>
       <c r="B288" t="inlineStr">
         <is>
-          <t>2026-07-11 08:21:16 PM PT</t>
+          <t>2026-07-11 08:23:16 PM PT</t>
         </is>
       </c>
       <c r="C288" t="n">
@@ -33726,7 +33726,7 @@
       </c>
       <c r="B289" t="inlineStr">
         <is>
-          <t>2026-07-11 08:21:16 PM PT</t>
+          <t>2026-07-11 08:23:16 PM PT</t>
         </is>
       </c>
       <c r="C289" t="n">
@@ -33840,7 +33840,7 @@
       </c>
       <c r="B290" t="inlineStr">
         <is>
-          <t>2026-07-11 08:21:17 PM PT</t>
+          <t>2026-07-11 08:23:17 PM PT</t>
         </is>
       </c>
       <c r="C290" t="n">
@@ -33954,7 +33954,7 @@
       </c>
       <c r="B291" t="inlineStr">
         <is>
-          <t>2026-07-11 08:21:17 PM PT</t>
+          <t>2026-07-11 08:23:17 PM PT</t>
         </is>
       </c>
       <c r="C291" t="n">
@@ -34068,7 +34068,7 @@
       </c>
       <c r="B292" t="inlineStr">
         <is>
-          <t>2026-07-11 08:21:17 PM PT</t>
+          <t>2026-07-11 08:23:17 PM PT</t>
         </is>
       </c>
       <c r="C292" t="n">
@@ -34182,7 +34182,7 @@
       </c>
       <c r="B293" t="inlineStr">
         <is>
-          <t>2026-07-11 08:21:17 PM PT</t>
+          <t>2026-07-11 08:23:17 PM PT</t>
         </is>
       </c>
       <c r="C293" t="n">
@@ -34296,7 +34296,7 @@
       </c>
       <c r="B294" t="inlineStr">
         <is>
-          <t>2026-07-11 08:21:17 PM PT</t>
+          <t>2026-07-11 08:23:17 PM PT</t>
         </is>
       </c>
       <c r="C294" t="n">
@@ -34410,7 +34410,7 @@
       </c>
       <c r="B295" t="inlineStr">
         <is>
-          <t>2026-07-11 08:21:17 PM PT</t>
+          <t>2026-07-11 08:23:17 PM PT</t>
         </is>
       </c>
       <c r="C295" t="n">
@@ -34524,7 +34524,7 @@
       </c>
       <c r="B296" t="inlineStr">
         <is>
-          <t>2026-07-11 08:21:17 PM PT</t>
+          <t>2026-07-11 08:23:17 PM PT</t>
         </is>
       </c>
       <c r="C296" t="n">
@@ -34638,7 +34638,7 @@
       </c>
       <c r="B297" t="inlineStr">
         <is>
-          <t>2026-07-11 08:21:17 PM PT</t>
+          <t>2026-07-11 08:23:17 PM PT</t>
         </is>
       </c>
       <c r="C297" t="n">
@@ -34752,7 +34752,7 @@
       </c>
       <c r="B298" t="inlineStr">
         <is>
-          <t>2026-07-11 08:21:16 PM PT</t>
+          <t>2026-07-11 08:23:16 PM PT</t>
         </is>
       </c>
       <c r="C298" t="n">
@@ -34866,7 +34866,7 @@
       </c>
       <c r="B299" t="inlineStr">
         <is>
-          <t>2026-07-11 08:21:16 PM PT</t>
+          <t>2026-07-11 08:23:16 PM PT</t>
         </is>
       </c>
       <c r="C299" t="n">
@@ -34980,7 +34980,7 @@
       </c>
       <c r="B300" t="inlineStr">
         <is>
-          <t>2026-07-11 08:21:16 PM PT</t>
+          <t>2026-07-11 08:23:16 PM PT</t>
         </is>
       </c>
       <c r="C300" t="n">
@@ -35094,7 +35094,7 @@
       </c>
       <c r="B301" t="inlineStr">
         <is>
-          <t>2026-07-11 08:21:16 PM PT</t>
+          <t>2026-07-11 08:23:16 PM PT</t>
         </is>
       </c>
       <c r="C301" t="n">
@@ -35208,7 +35208,7 @@
       </c>
       <c r="B302" t="inlineStr">
         <is>
-          <t>2026-07-11 08:21:16 PM PT</t>
+          <t>2026-07-11 08:23:16 PM PT</t>
         </is>
       </c>
       <c r="C302" t="n">
@@ -35322,7 +35322,7 @@
       </c>
       <c r="B303" t="inlineStr">
         <is>
-          <t>2026-07-11 08:21:16 PM PT</t>
+          <t>2026-07-11 08:23:16 PM PT</t>
         </is>
       </c>
       <c r="C303" t="n">
@@ -35436,7 +35436,7 @@
       </c>
       <c r="B304" t="inlineStr">
         <is>
-          <t>2026-07-11 08:21:16 PM PT</t>
+          <t>2026-07-11 08:23:16 PM PT</t>
         </is>
       </c>
       <c r="C304" t="n">
@@ -35550,7 +35550,7 @@
       </c>
       <c r="B305" t="inlineStr">
         <is>
-          <t>2026-07-11 08:21:16 PM PT</t>
+          <t>2026-07-11 08:23:16 PM PT</t>
         </is>
       </c>
       <c r="C305" t="n">
@@ -35664,7 +35664,7 @@
       </c>
       <c r="B306" t="inlineStr">
         <is>
-          <t>2026-07-11 08:21:18 PM PT</t>
+          <t>2026-07-11 08:23:18 PM PT</t>
         </is>
       </c>
       <c r="C306" t="n">
@@ -35677,25 +35677,25 @@
       </c>
       <c r="E306" t="inlineStr">
         <is>
-          <t>Bottom 7 | 3 out</t>
+          <t>Top 8 | 0 out</t>
         </is>
       </c>
       <c r="F306" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="G306" t="inlineStr">
         <is>
-          <t>Bottom</t>
+          <t>Top</t>
         </is>
       </c>
       <c r="H306" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="I306" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="J306" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="K306" t="inlineStr">
         <is>
@@ -35787,7 +35787,7 @@
       </c>
       <c r="B307" t="inlineStr">
         <is>
-          <t>2026-07-11 08:21:17 PM PT</t>
+          <t>2026-07-11 08:23:17 PM PT</t>
         </is>
       </c>
       <c r="C307" t="n">
@@ -35901,7 +35901,7 @@
       </c>
       <c r="B308" t="inlineStr">
         <is>
-          <t>2026-07-11 08:21:17 PM PT</t>
+          <t>2026-07-11 08:23:17 PM PT</t>
         </is>
       </c>
       <c r="C308" t="n">
@@ -36015,7 +36015,7 @@
       </c>
       <c r="B309" t="inlineStr">
         <is>
-          <t>2026-07-11 08:21:17 PM PT</t>
+          <t>2026-07-11 08:23:17 PM PT</t>
         </is>
       </c>
       <c r="C309" t="n">
@@ -36129,7 +36129,7 @@
       </c>
       <c r="B310" t="inlineStr">
         <is>
-          <t>2026-07-11 08:21:17 PM PT</t>
+          <t>2026-07-11 08:23:17 PM PT</t>
         </is>
       </c>
       <c r="C310" t="n">
@@ -36243,7 +36243,7 @@
       </c>
       <c r="B311" t="inlineStr">
         <is>
-          <t>2026-07-11 08:21:17 PM PT</t>
+          <t>2026-07-11 08:23:17 PM PT</t>
         </is>
       </c>
       <c r="C311" t="n">
@@ -36357,7 +36357,7 @@
       </c>
       <c r="B312" t="inlineStr">
         <is>
-          <t>2026-07-11 08:21:17 PM PT</t>
+          <t>2026-07-11 08:23:17 PM PT</t>
         </is>
       </c>
       <c r="C312" t="n">
@@ -36471,7 +36471,7 @@
       </c>
       <c r="B313" t="inlineStr">
         <is>
-          <t>2026-07-11 08:21:17 PM PT</t>
+          <t>2026-07-11 08:23:17 PM PT</t>
         </is>
       </c>
       <c r="C313" t="n">
@@ -36585,7 +36585,7 @@
       </c>
       <c r="B314" t="inlineStr">
         <is>
-          <t>2026-07-11 08:21:18 PM PT</t>
+          <t>2026-07-11 08:23:18 PM PT</t>
         </is>
       </c>
       <c r="C314" t="n">
@@ -36699,7 +36699,7 @@
       </c>
       <c r="B315" t="inlineStr">
         <is>
-          <t>2026-07-11 08:21:18 PM PT</t>
+          <t>2026-07-11 08:23:18 PM PT</t>
         </is>
       </c>
       <c r="C315" t="n">
@@ -36813,7 +36813,7 @@
       </c>
       <c r="B316" t="inlineStr">
         <is>
-          <t>2026-07-11 08:21:18 PM PT</t>
+          <t>2026-07-11 08:23:18 PM PT</t>
         </is>
       </c>
       <c r="C316" t="n">
@@ -36927,7 +36927,7 @@
       </c>
       <c r="B317" t="inlineStr">
         <is>
-          <t>2026-07-11 08:21:18 PM PT</t>
+          <t>2026-07-11 08:23:18 PM PT</t>
         </is>
       </c>
       <c r="C317" t="n">
@@ -37041,7 +37041,7 @@
       </c>
       <c r="B318" t="inlineStr">
         <is>
-          <t>2026-07-11 08:21:17 PM PT</t>
+          <t>2026-07-11 08:23:17 PM PT</t>
         </is>
       </c>
       <c r="C318" t="n">
@@ -37155,7 +37155,7 @@
       </c>
       <c r="B319" t="inlineStr">
         <is>
-          <t>2026-07-11 08:21:17 PM PT</t>
+          <t>2026-07-11 08:23:17 PM PT</t>
         </is>
       </c>
       <c r="C319" t="n">
@@ -37269,7 +37269,7 @@
       </c>
       <c r="B320" t="inlineStr">
         <is>
-          <t>2026-07-11 08:21:17 PM PT</t>
+          <t>2026-07-11 08:23:17 PM PT</t>
         </is>
       </c>
       <c r="C320" t="n">
@@ -37383,7 +37383,7 @@
       </c>
       <c r="B321" t="inlineStr">
         <is>
-          <t>2026-07-11 08:21:17 PM PT</t>
+          <t>2026-07-11 08:23:17 PM PT</t>
         </is>
       </c>
       <c r="C321" t="n">
@@ -37497,7 +37497,7 @@
       </c>
       <c r="B322" t="inlineStr">
         <is>
-          <t>2026-07-11 08:21:18 PM PT</t>
+          <t>2026-07-11 08:23:17 PM PT</t>
         </is>
       </c>
       <c r="C322" t="n">
@@ -37611,7 +37611,7 @@
       </c>
       <c r="B323" t="inlineStr">
         <is>
-          <t>2026-07-11 08:21:18 PM PT</t>
+          <t>2026-07-11 08:23:17 PM PT</t>
         </is>
       </c>
       <c r="C323" t="n">
@@ -37725,7 +37725,7 @@
       </c>
       <c r="B324" t="inlineStr">
         <is>
-          <t>2026-07-11 08:21:18 PM PT</t>
+          <t>2026-07-11 08:23:17 PM PT</t>
         </is>
       </c>
       <c r="C324" t="n">
@@ -37839,7 +37839,7 @@
       </c>
       <c r="B325" t="inlineStr">
         <is>
-          <t>2026-07-11 08:21:18 PM PT</t>
+          <t>2026-07-11 08:23:17 PM PT</t>
         </is>
       </c>
       <c r="C325" t="n">
@@ -37953,7 +37953,7 @@
       </c>
       <c r="B326" t="inlineStr">
         <is>
-          <t>2026-07-11 08:21:18 PM PT</t>
+          <t>2026-07-11 08:23:17 PM PT</t>
         </is>
       </c>
       <c r="C326" t="n">
@@ -38067,7 +38067,7 @@
       </c>
       <c r="B327" t="inlineStr">
         <is>
-          <t>2026-07-11 08:21:18 PM PT</t>
+          <t>2026-07-11 08:23:18 PM PT</t>
         </is>
       </c>
       <c r="C327" t="n">
@@ -38080,25 +38080,25 @@
       </c>
       <c r="E327" t="inlineStr">
         <is>
-          <t>Bottom 7 | 3 out</t>
+          <t>Top 8 | 0 out</t>
         </is>
       </c>
       <c r="F327" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="G327" t="inlineStr">
         <is>
-          <t>Bottom</t>
+          <t>Top</t>
         </is>
       </c>
       <c r="H327" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="I327" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="J327" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="K327" t="inlineStr">
         <is>
@@ -38190,68 +38190,77 @@
       </c>
       <c r="B328" t="inlineStr">
         <is>
-          <t>2026-07-11 08:21:17 PM PT</t>
+          <t>2026-07-11 08:23:18 PM PT</t>
         </is>
       </c>
       <c r="C328" t="n">
-        <v>822711</v>
+        <v>823276</v>
       </c>
       <c r="D328" t="inlineStr">
         <is>
-          <t>1:05 PM PT</t>
+          <t>5:40 PM PT</t>
         </is>
       </c>
       <c r="E328" t="inlineStr">
         <is>
-          <t>Final</t>
+          <t>Top 8 | 0 out</t>
         </is>
       </c>
       <c r="F328" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="G328" t="inlineStr">
         <is>
-          <t>Bottom</t>
-        </is>
+          <t>Top</t>
+        </is>
+      </c>
+      <c r="H328" t="n">
+        <v>0</v>
+      </c>
+      <c r="I328" t="n">
+        <v>0</v>
+      </c>
+      <c r="J328" t="n">
+        <v>0</v>
       </c>
       <c r="K328" t="inlineStr">
         <is>
-          <t>Home</t>
+          <t>Away</t>
         </is>
       </c>
       <c r="L328" t="inlineStr">
         <is>
-          <t>WSH</t>
+          <t>TOR</t>
         </is>
       </c>
       <c r="M328" t="inlineStr">
         <is>
-          <t>NYY</t>
+          <t>SD</t>
         </is>
       </c>
       <c r="N328" t="inlineStr">
         <is>
-          <t>Daylen Lile</t>
+          <t>Luis Urías</t>
         </is>
       </c>
       <c r="O328" t="n">
-        <v>695734</v>
+        <v>649966</v>
       </c>
       <c r="P328" t="inlineStr">
         <is>
-          <t>LF</t>
+          <t>PH</t>
         </is>
       </c>
       <c r="Q328" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>8 (Sub)</t>
         </is>
       </c>
       <c r="R328" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="S328" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="T328" t="n">
         <v>0</v>
@@ -38284,16 +38293,16 @@
         <v>0</v>
       </c>
       <c r="AD328" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AE328" s="4" t="n">
         <v>0</v>
       </c>
       <c r="AF328" t="n">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="AG328" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
     </row>
     <row r="329">
@@ -38304,7 +38313,7 @@
       </c>
       <c r="B329" t="inlineStr">
         <is>
-          <t>2026-07-11 08:21:17 PM PT</t>
+          <t>2026-07-11 08:23:17 PM PT</t>
         </is>
       </c>
       <c r="C329" t="n">
@@ -38345,27 +38354,27 @@
       </c>
       <c r="N329" t="inlineStr">
         <is>
-          <t>José Tena</t>
+          <t>Daylen Lile</t>
         </is>
       </c>
       <c r="O329" t="n">
-        <v>677588</v>
+        <v>695734</v>
       </c>
       <c r="P329" t="inlineStr">
         <is>
-          <t>PH</t>
+          <t>LF</t>
         </is>
       </c>
       <c r="Q329" t="inlineStr">
         <is>
-          <t>8 (Sub)</t>
+          <t>5</t>
         </is>
       </c>
       <c r="R329" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="S329" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="T329" t="n">
         <v>0</v>
@@ -38398,7 +38407,7 @@
         <v>0</v>
       </c>
       <c r="AD329" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AE329" s="4" t="n">
         <v>0</v>
@@ -38410,9 +38419,123 @@
         <v>7</v>
       </c>
     </row>
+    <row r="330">
+      <c r="A330" t="inlineStr">
+        <is>
+          <t>2026-07-11</t>
+        </is>
+      </c>
+      <c r="B330" t="inlineStr">
+        <is>
+          <t>2026-07-11 08:23:17 PM PT</t>
+        </is>
+      </c>
+      <c r="C330" t="n">
+        <v>822711</v>
+      </c>
+      <c r="D330" t="inlineStr">
+        <is>
+          <t>1:05 PM PT</t>
+        </is>
+      </c>
+      <c r="E330" t="inlineStr">
+        <is>
+          <t>Final</t>
+        </is>
+      </c>
+      <c r="F330" t="n">
+        <v>9</v>
+      </c>
+      <c r="G330" t="inlineStr">
+        <is>
+          <t>Bottom</t>
+        </is>
+      </c>
+      <c r="K330" t="inlineStr">
+        <is>
+          <t>Home</t>
+        </is>
+      </c>
+      <c r="L330" t="inlineStr">
+        <is>
+          <t>WSH</t>
+        </is>
+      </c>
+      <c r="M330" t="inlineStr">
+        <is>
+          <t>NYY</t>
+        </is>
+      </c>
+      <c r="N330" t="inlineStr">
+        <is>
+          <t>José Tena</t>
+        </is>
+      </c>
+      <c r="O330" t="n">
+        <v>677588</v>
+      </c>
+      <c r="P330" t="inlineStr">
+        <is>
+          <t>PH</t>
+        </is>
+      </c>
+      <c r="Q330" t="inlineStr">
+        <is>
+          <t>8 (Sub)</t>
+        </is>
+      </c>
+      <c r="R330" t="n">
+        <v>1</v>
+      </c>
+      <c r="S330" t="n">
+        <v>1</v>
+      </c>
+      <c r="T330" t="n">
+        <v>0</v>
+      </c>
+      <c r="U330" t="n">
+        <v>0</v>
+      </c>
+      <c r="V330" t="n">
+        <v>0</v>
+      </c>
+      <c r="W330" t="n">
+        <v>0</v>
+      </c>
+      <c r="X330" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y330" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z330" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA330" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB330" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC330" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD330" t="n">
+        <v>1</v>
+      </c>
+      <c r="AE330" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF330" t="n">
+        <v>2</v>
+      </c>
+      <c r="AG330" t="n">
+        <v>7</v>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:AG329"/>
-  <conditionalFormatting sqref="AE2:AE329">
+  <autoFilter ref="A1:AG330"/>
+  <conditionalFormatting sqref="AE2:AE330">
     <cfRule type="colorScale" priority="1">
       <colorScale>
         <cfvo type="num" val="0"/>

--- a/live_mlb_hitter_fantasy_scores_2026_07_11.xlsx
+++ b/live_mlb_hitter_fantasy_scores_2026_07_11.xlsx
@@ -487,7 +487,7 @@
     <col width="27" customWidth="1" min="2" max="2"/>
     <col width="10" customWidth="1" min="3" max="3"/>
     <col width="14" customWidth="1" min="4" max="4"/>
-    <col width="15" customWidth="1" min="5" max="5"/>
+    <col width="18" customWidth="1" min="5" max="5"/>
     <col width="10" customWidth="1" min="6" max="6"/>
     <col width="13" customWidth="1" min="7" max="7"/>
     <col width="10" customWidth="1" min="8" max="8"/>
@@ -693,7 +693,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-07-11 08:23:16 PM PT</t>
+          <t>2026-07-11 08:25:16 PM PT</t>
         </is>
       </c>
       <c r="C2" t="n">
@@ -807,7 +807,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>2026-07-11 08:23:17 PM PT</t>
+          <t>2026-07-11 08:25:17 PM PT</t>
         </is>
       </c>
       <c r="C3" t="n">
@@ -921,7 +921,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-07-11 08:23:18 PM PT</t>
+          <t>2026-07-11 08:25:18 PM PT</t>
         </is>
       </c>
       <c r="C4" t="n">
@@ -949,10 +949,10 @@
         <v>0</v>
       </c>
       <c r="I4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J4" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="K4" t="inlineStr">
         <is>
@@ -1044,7 +1044,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>2026-07-11 08:23:17 PM PT</t>
+          <t>2026-07-11 08:25:17 PM PT</t>
         </is>
       </c>
       <c r="C5" t="n">
@@ -1158,7 +1158,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>2026-07-11 08:23:18 PM PT</t>
+          <t>2026-07-11 08:25:18 PM PT</t>
         </is>
       </c>
       <c r="C6" t="n">
@@ -1272,7 +1272,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>2026-07-11 08:23:17 PM PT</t>
+          <t>2026-07-11 08:25:17 PM PT</t>
         </is>
       </c>
       <c r="C7" t="n">
@@ -1386,7 +1386,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>2026-07-11 08:23:17 PM PT</t>
+          <t>2026-07-11 08:25:17 PM PT</t>
         </is>
       </c>
       <c r="C8" t="n">
@@ -1500,7 +1500,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>2026-07-11 08:23:16 PM PT</t>
+          <t>2026-07-11 08:25:16 PM PT</t>
         </is>
       </c>
       <c r="C9" t="n">
@@ -1614,7 +1614,7 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>2026-07-11 08:23:18 PM PT</t>
+          <t>2026-07-11 08:25:18 PM PT</t>
         </is>
       </c>
       <c r="C10" t="n">
@@ -1642,10 +1642,10 @@
         <v>0</v>
       </c>
       <c r="I10" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J10" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="K10" t="inlineStr">
         <is>
@@ -1737,7 +1737,7 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>2026-07-11 08:23:17 PM PT</t>
+          <t>2026-07-11 08:25:17 PM PT</t>
         </is>
       </c>
       <c r="C11" t="n">
@@ -1851,7 +1851,7 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>2026-07-11 08:23:17 PM PT</t>
+          <t>2026-07-11 08:25:17 PM PT</t>
         </is>
       </c>
       <c r="C12" t="n">
@@ -1965,7 +1965,7 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>2026-07-11 08:23:18 PM PT</t>
+          <t>2026-07-11 08:25:18 PM PT</t>
         </is>
       </c>
       <c r="C13" t="n">
@@ -1993,10 +1993,10 @@
         <v>0</v>
       </c>
       <c r="I13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J13" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="K13" t="inlineStr">
         <is>
@@ -2088,7 +2088,7 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>2026-07-11 08:23:17 PM PT</t>
+          <t>2026-07-11 08:25:17 PM PT</t>
         </is>
       </c>
       <c r="C14" t="n">
@@ -2202,7 +2202,7 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>2026-07-11 08:23:17 PM PT</t>
+          <t>2026-07-11 08:25:17 PM PT</t>
         </is>
       </c>
       <c r="C15" t="n">
@@ -2316,7 +2316,7 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>2026-07-11 08:23:17 PM PT</t>
+          <t>2026-07-11 08:25:17 PM PT</t>
         </is>
       </c>
       <c r="C16" t="n">
@@ -2430,7 +2430,7 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>2026-07-11 08:23:18 PM PT</t>
+          <t>2026-07-11 08:25:18 PM PT</t>
         </is>
       </c>
       <c r="C17" t="n">
@@ -2458,10 +2458,10 @@
         <v>0</v>
       </c>
       <c r="I17" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J17" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="K17" t="inlineStr">
         <is>
@@ -2553,7 +2553,7 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>2026-07-11 08:23:17 PM PT</t>
+          <t>2026-07-11 08:25:17 PM PT</t>
         </is>
       </c>
       <c r="C18" t="n">
@@ -2667,7 +2667,7 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>2026-07-11 08:23:18 PM PT</t>
+          <t>2026-07-11 08:25:18 PM PT</t>
         </is>
       </c>
       <c r="C19" t="n">
@@ -2781,7 +2781,7 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>2026-07-11 08:23:17 PM PT</t>
+          <t>2026-07-11 08:25:17 PM PT</t>
         </is>
       </c>
       <c r="C20" t="n">
@@ -2895,7 +2895,7 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>2026-07-11 08:23:17 PM PT</t>
+          <t>2026-07-11 08:25:17 PM PT</t>
         </is>
       </c>
       <c r="C21" t="n">
@@ -3009,7 +3009,7 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>2026-07-11 08:23:18 PM PT</t>
+          <t>2026-07-11 08:25:18 PM PT</t>
         </is>
       </c>
       <c r="C22" t="n">
@@ -3022,7 +3022,7 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Top 7 | 3 out</t>
+          <t>Bottom 7 | 0 out</t>
         </is>
       </c>
       <c r="F22" t="n">
@@ -3030,17 +3030,17 @@
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Top</t>
+          <t>Bottom</t>
         </is>
       </c>
       <c r="H22" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="I22" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J22" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="K22" t="inlineStr">
         <is>
@@ -3132,7 +3132,7 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>2026-07-11 08:23:17 PM PT</t>
+          <t>2026-07-11 08:25:17 PM PT</t>
         </is>
       </c>
       <c r="C23" t="n">
@@ -3246,7 +3246,7 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>2026-07-11 08:23:17 PM PT</t>
+          <t>2026-07-11 08:25:17 PM PT</t>
         </is>
       </c>
       <c r="C24" t="n">
@@ -3360,7 +3360,7 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>2026-07-11 08:23:18 PM PT</t>
+          <t>2026-07-11 08:25:18 PM PT</t>
         </is>
       </c>
       <c r="C25" t="n">
@@ -3474,7 +3474,7 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>2026-07-11 08:23:16 PM PT</t>
+          <t>2026-07-11 08:25:16 PM PT</t>
         </is>
       </c>
       <c r="C26" t="n">
@@ -3588,7 +3588,7 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>2026-07-11 08:23:17 PM PT</t>
+          <t>2026-07-11 08:25:17 PM PT</t>
         </is>
       </c>
       <c r="C27" t="n">
@@ -3702,7 +3702,7 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>2026-07-11 08:23:17 PM PT</t>
+          <t>2026-07-11 08:25:17 PM PT</t>
         </is>
       </c>
       <c r="C28" t="n">
@@ -3816,7 +3816,7 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>2026-07-11 08:23:18 PM PT</t>
+          <t>2026-07-11 08:25:18 PM PT</t>
         </is>
       </c>
       <c r="C29" t="n">
@@ -3930,7 +3930,7 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>2026-07-11 08:23:18 PM PT</t>
+          <t>2026-07-11 08:25:18 PM PT</t>
         </is>
       </c>
       <c r="C30" t="n">
@@ -4044,7 +4044,7 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>2026-07-11 08:23:17 PM PT</t>
+          <t>2026-07-11 08:25:17 PM PT</t>
         </is>
       </c>
       <c r="C31" t="n">
@@ -4158,7 +4158,7 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>2026-07-11 08:23:17 PM PT</t>
+          <t>2026-07-11 08:25:17 PM PT</t>
         </is>
       </c>
       <c r="C32" t="n">
@@ -4272,7 +4272,7 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>2026-07-11 08:23:17 PM PT</t>
+          <t>2026-07-11 08:25:17 PM PT</t>
         </is>
       </c>
       <c r="C33" t="n">
@@ -4386,7 +4386,7 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>2026-07-11 08:23:16 PM PT</t>
+          <t>2026-07-11 08:25:16 PM PT</t>
         </is>
       </c>
       <c r="C34" t="n">
@@ -4500,7 +4500,7 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>2026-07-11 08:23:16 PM PT</t>
+          <t>2026-07-11 08:25:16 PM PT</t>
         </is>
       </c>
       <c r="C35" t="n">
@@ -4614,7 +4614,7 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>2026-07-11 08:23:18 PM PT</t>
+          <t>2026-07-11 08:25:18 PM PT</t>
         </is>
       </c>
       <c r="C36" t="n">
@@ -4642,10 +4642,10 @@
         <v>0</v>
       </c>
       <c r="I36" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J36" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="K36" t="inlineStr">
         <is>
@@ -4737,7 +4737,7 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>2026-07-11 08:23:17 PM PT</t>
+          <t>2026-07-11 08:25:17 PM PT</t>
         </is>
       </c>
       <c r="C37" t="n">
@@ -4851,7 +4851,7 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>2026-07-11 08:23:16 PM PT</t>
+          <t>2026-07-11 08:25:16 PM PT</t>
         </is>
       </c>
       <c r="C38" t="n">
@@ -4965,7 +4965,7 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>2026-07-11 08:23:17 PM PT</t>
+          <t>2026-07-11 08:25:17 PM PT</t>
         </is>
       </c>
       <c r="C39" t="n">
@@ -5079,7 +5079,7 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>2026-07-11 08:23:16 PM PT</t>
+          <t>2026-07-11 08:25:16 PM PT</t>
         </is>
       </c>
       <c r="C40" t="n">
@@ -5193,7 +5193,7 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>2026-07-11 08:23:18 PM PT</t>
+          <t>2026-07-11 08:25:18 PM PT</t>
         </is>
       </c>
       <c r="C41" t="n">
@@ -5206,7 +5206,7 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>Top 7 | 3 out</t>
+          <t>Bottom 7 | 0 out</t>
         </is>
       </c>
       <c r="F41" t="n">
@@ -5214,17 +5214,17 @@
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Top</t>
+          <t>Bottom</t>
         </is>
       </c>
       <c r="H41" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="I41" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J41" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="K41" t="inlineStr">
         <is>
@@ -5316,7 +5316,7 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>2026-07-11 08:23:18 PM PT</t>
+          <t>2026-07-11 08:25:18 PM PT</t>
         </is>
       </c>
       <c r="C42" t="n">
@@ -5430,7 +5430,7 @@
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>2026-07-11 08:23:17 PM PT</t>
+          <t>2026-07-11 08:25:17 PM PT</t>
         </is>
       </c>
       <c r="C43" t="n">
@@ -5544,7 +5544,7 @@
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>2026-07-11 08:23:17 PM PT</t>
+          <t>2026-07-11 08:25:17 PM PT</t>
         </is>
       </c>
       <c r="C44" t="n">
@@ -5658,7 +5658,7 @@
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>2026-07-11 08:23:18 PM PT</t>
+          <t>2026-07-11 08:25:18 PM PT</t>
         </is>
       </c>
       <c r="C45" t="n">
@@ -5772,7 +5772,7 @@
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>2026-07-11 08:23:17 PM PT</t>
+          <t>2026-07-11 08:25:17 PM PT</t>
         </is>
       </c>
       <c r="C46" t="n">
@@ -5886,7 +5886,7 @@
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>2026-07-11 08:23:17 PM PT</t>
+          <t>2026-07-11 08:25:17 PM PT</t>
         </is>
       </c>
       <c r="C47" t="n">
@@ -6000,7 +6000,7 @@
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>2026-07-11 08:23:17 PM PT</t>
+          <t>2026-07-11 08:25:17 PM PT</t>
         </is>
       </c>
       <c r="C48" t="n">
@@ -6114,7 +6114,7 @@
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>2026-07-11 08:23:17 PM PT</t>
+          <t>2026-07-11 08:25:17 PM PT</t>
         </is>
       </c>
       <c r="C49" t="n">
@@ -6228,7 +6228,7 @@
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>2026-07-11 08:23:16 PM PT</t>
+          <t>2026-07-11 08:25:16 PM PT</t>
         </is>
       </c>
       <c r="C50" t="n">
@@ -6342,7 +6342,7 @@
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>2026-07-11 08:23:18 PM PT</t>
+          <t>2026-07-11 08:25:18 PM PT</t>
         </is>
       </c>
       <c r="C51" t="n">
@@ -6355,7 +6355,7 @@
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>Top 7 | 3 out</t>
+          <t>Bottom 7 | 0 out</t>
         </is>
       </c>
       <c r="F51" t="n">
@@ -6363,17 +6363,17 @@
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Top</t>
+          <t>Bottom</t>
         </is>
       </c>
       <c r="H51" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="I51" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J51" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="K51" t="inlineStr">
         <is>
@@ -6465,7 +6465,7 @@
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>2026-07-11 08:23:18 PM PT</t>
+          <t>2026-07-11 08:25:18 PM PT</t>
         </is>
       </c>
       <c r="C52" t="n">
@@ -6579,7 +6579,7 @@
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>2026-07-11 08:23:18 PM PT</t>
+          <t>2026-07-11 08:25:18 PM PT</t>
         </is>
       </c>
       <c r="C53" t="n">
@@ -6693,7 +6693,7 @@
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>2026-07-11 08:23:17 PM PT</t>
+          <t>2026-07-11 08:25:17 PM PT</t>
         </is>
       </c>
       <c r="C54" t="n">
@@ -6807,7 +6807,7 @@
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>2026-07-11 08:23:16 PM PT</t>
+          <t>2026-07-11 08:25:16 PM PT</t>
         </is>
       </c>
       <c r="C55" t="n">
@@ -6921,7 +6921,7 @@
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>2026-07-11 08:23:16 PM PT</t>
+          <t>2026-07-11 08:25:16 PM PT</t>
         </is>
       </c>
       <c r="C56" t="n">
@@ -7035,7 +7035,7 @@
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>2026-07-11 08:23:16 PM PT</t>
+          <t>2026-07-11 08:25:16 PM PT</t>
         </is>
       </c>
       <c r="C57" t="n">
@@ -7149,7 +7149,7 @@
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>2026-07-11 08:23:17 PM PT</t>
+          <t>2026-07-11 08:25:17 PM PT</t>
         </is>
       </c>
       <c r="C58" t="n">
@@ -7263,7 +7263,7 @@
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>2026-07-11 08:23:17 PM PT</t>
+          <t>2026-07-11 08:25:17 PM PT</t>
         </is>
       </c>
       <c r="C59" t="n">
@@ -7377,7 +7377,7 @@
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>2026-07-11 08:23:16 PM PT</t>
+          <t>2026-07-11 08:25:16 PM PT</t>
         </is>
       </c>
       <c r="C60" t="n">
@@ -7491,7 +7491,7 @@
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>2026-07-11 08:23:16 PM PT</t>
+          <t>2026-07-11 08:25:16 PM PT</t>
         </is>
       </c>
       <c r="C61" t="n">
@@ -7605,7 +7605,7 @@
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>2026-07-11 08:23:16 PM PT</t>
+          <t>2026-07-11 08:25:16 PM PT</t>
         </is>
       </c>
       <c r="C62" t="n">
@@ -7719,7 +7719,7 @@
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>2026-07-11 08:23:18 PM PT</t>
+          <t>2026-07-11 08:25:18 PM PT</t>
         </is>
       </c>
       <c r="C63" t="n">
@@ -7747,10 +7747,10 @@
         <v>0</v>
       </c>
       <c r="I63" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J63" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="K63" t="inlineStr">
         <is>
@@ -7842,7 +7842,7 @@
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>2026-07-11 08:23:18 PM PT</t>
+          <t>2026-07-11 08:25:18 PM PT</t>
         </is>
       </c>
       <c r="C64" t="n">
@@ -7855,7 +7855,7 @@
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>Top 7 | 3 out</t>
+          <t>Bottom 7 | 0 out</t>
         </is>
       </c>
       <c r="F64" t="n">
@@ -7863,17 +7863,17 @@
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>Top</t>
+          <t>Bottom</t>
         </is>
       </c>
       <c r="H64" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="I64" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J64" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="K64" t="inlineStr">
         <is>
@@ -7965,7 +7965,7 @@
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>2026-07-11 08:23:16 PM PT</t>
+          <t>2026-07-11 08:25:16 PM PT</t>
         </is>
       </c>
       <c r="C65" t="n">
@@ -8079,7 +8079,7 @@
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>2026-07-11 08:23:17 PM PT</t>
+          <t>2026-07-11 08:25:17 PM PT</t>
         </is>
       </c>
       <c r="C66" t="n">
@@ -8193,7 +8193,7 @@
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>2026-07-11 08:23:18 PM PT</t>
+          <t>2026-07-11 08:25:18 PM PT</t>
         </is>
       </c>
       <c r="C67" t="n">
@@ -8221,10 +8221,10 @@
         <v>0</v>
       </c>
       <c r="I67" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J67" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="K67" t="inlineStr">
         <is>
@@ -8316,7 +8316,7 @@
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>2026-07-11 08:23:17 PM PT</t>
+          <t>2026-07-11 08:25:17 PM PT</t>
         </is>
       </c>
       <c r="C68" t="n">
@@ -8430,7 +8430,7 @@
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>2026-07-11 08:23:16 PM PT</t>
+          <t>2026-07-11 08:25:16 PM PT</t>
         </is>
       </c>
       <c r="C69" t="n">
@@ -8544,7 +8544,7 @@
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>2026-07-11 08:23:16 PM PT</t>
+          <t>2026-07-11 08:25:16 PM PT</t>
         </is>
       </c>
       <c r="C70" t="n">
@@ -8658,7 +8658,7 @@
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>2026-07-11 08:23:18 PM PT</t>
+          <t>2026-07-11 08:25:18 PM PT</t>
         </is>
       </c>
       <c r="C71" t="n">
@@ -8671,7 +8671,7 @@
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>Top 7 | 3 out</t>
+          <t>Bottom 7 | 0 out</t>
         </is>
       </c>
       <c r="F71" t="n">
@@ -8679,17 +8679,17 @@
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>Top</t>
+          <t>Bottom</t>
         </is>
       </c>
       <c r="H71" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="I71" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J71" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="K71" t="inlineStr">
         <is>
@@ -8781,7 +8781,7 @@
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>2026-07-11 08:23:16 PM PT</t>
+          <t>2026-07-11 08:25:16 PM PT</t>
         </is>
       </c>
       <c r="C72" t="n">
@@ -8895,7 +8895,7 @@
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>2026-07-11 08:23:17 PM PT</t>
+          <t>2026-07-11 08:25:17 PM PT</t>
         </is>
       </c>
       <c r="C73" t="n">
@@ -9009,7 +9009,7 @@
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>2026-07-11 08:23:16 PM PT</t>
+          <t>2026-07-11 08:25:16 PM PT</t>
         </is>
       </c>
       <c r="C74" t="n">
@@ -9123,7 +9123,7 @@
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>2026-07-11 08:23:18 PM PT</t>
+          <t>2026-07-11 08:25:18 PM PT</t>
         </is>
       </c>
       <c r="C75" t="n">
@@ -9151,10 +9151,10 @@
         <v>0</v>
       </c>
       <c r="I75" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J75" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="K75" t="inlineStr">
         <is>
@@ -9246,7 +9246,7 @@
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>2026-07-11 08:23:18 PM PT</t>
+          <t>2026-07-11 08:25:18 PM PT</t>
         </is>
       </c>
       <c r="C76" t="n">
@@ -9360,7 +9360,7 @@
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>2026-07-11 08:23:18 PM PT</t>
+          <t>2026-07-11 08:25:18 PM PT</t>
         </is>
       </c>
       <c r="C77" t="n">
@@ -9474,7 +9474,7 @@
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>2026-07-11 08:23:17 PM PT</t>
+          <t>2026-07-11 08:25:17 PM PT</t>
         </is>
       </c>
       <c r="C78" t="n">
@@ -9588,7 +9588,7 @@
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>2026-07-11 08:23:16 PM PT</t>
+          <t>2026-07-11 08:25:16 PM PT</t>
         </is>
       </c>
       <c r="C79" t="n">
@@ -9702,7 +9702,7 @@
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>2026-07-11 08:23:16 PM PT</t>
+          <t>2026-07-11 08:25:16 PM PT</t>
         </is>
       </c>
       <c r="C80" t="n">
@@ -9816,7 +9816,7 @@
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>2026-07-11 08:23:16 PM PT</t>
+          <t>2026-07-11 08:25:16 PM PT</t>
         </is>
       </c>
       <c r="C81" t="n">
@@ -9930,7 +9930,7 @@
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>2026-07-11 08:23:16 PM PT</t>
+          <t>2026-07-11 08:25:16 PM PT</t>
         </is>
       </c>
       <c r="C82" t="n">
@@ -10044,7 +10044,7 @@
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>2026-07-11 08:23:16 PM PT</t>
+          <t>2026-07-11 08:25:16 PM PT</t>
         </is>
       </c>
       <c r="C83" t="n">
@@ -10158,7 +10158,7 @@
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>2026-07-11 08:23:16 PM PT</t>
+          <t>2026-07-11 08:25:16 PM PT</t>
         </is>
       </c>
       <c r="C84" t="n">
@@ -10272,7 +10272,7 @@
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>2026-07-11 08:23:16 PM PT</t>
+          <t>2026-07-11 08:25:16 PM PT</t>
         </is>
       </c>
       <c r="C85" t="n">
@@ -10386,7 +10386,7 @@
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>2026-07-11 08:23:16 PM PT</t>
+          <t>2026-07-11 08:25:16 PM PT</t>
         </is>
       </c>
       <c r="C86" t="n">
@@ -10500,7 +10500,7 @@
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>2026-07-11 08:23:17 PM PT</t>
+          <t>2026-07-11 08:25:17 PM PT</t>
         </is>
       </c>
       <c r="C87" t="n">
@@ -10614,7 +10614,7 @@
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>2026-07-11 08:23:17 PM PT</t>
+          <t>2026-07-11 08:25:17 PM PT</t>
         </is>
       </c>
       <c r="C88" t="n">
@@ -10728,7 +10728,7 @@
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>2026-07-11 08:23:18 PM PT</t>
+          <t>2026-07-11 08:25:18 PM PT</t>
         </is>
       </c>
       <c r="C89" t="n">
@@ -10756,10 +10756,10 @@
         <v>0</v>
       </c>
       <c r="I89" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J89" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="K89" t="inlineStr">
         <is>
@@ -10851,7 +10851,7 @@
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>2026-07-11 08:23:17 PM PT</t>
+          <t>2026-07-11 08:25:17 PM PT</t>
         </is>
       </c>
       <c r="C90" t="n">
@@ -10965,7 +10965,7 @@
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>2026-07-11 08:23:18 PM PT</t>
+          <t>2026-07-11 08:25:18 PM PT</t>
         </is>
       </c>
       <c r="C91" t="n">
@@ -11079,7 +11079,7 @@
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>2026-07-11 08:23:18 PM PT</t>
+          <t>2026-07-11 08:25:18 PM PT</t>
         </is>
       </c>
       <c r="C92" t="n">
@@ -11092,7 +11092,7 @@
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>Top 7 | 3 out</t>
+          <t>Bottom 7 | 0 out</t>
         </is>
       </c>
       <c r="F92" t="n">
@@ -11100,17 +11100,17 @@
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>Top</t>
+          <t>Bottom</t>
         </is>
       </c>
       <c r="H92" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="I92" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J92" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="K92" t="inlineStr">
         <is>
@@ -11202,7 +11202,7 @@
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>2026-07-11 08:23:17 PM PT</t>
+          <t>2026-07-11 08:25:17 PM PT</t>
         </is>
       </c>
       <c r="C93" t="n">
@@ -11316,7 +11316,7 @@
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>2026-07-11 08:23:17 PM PT</t>
+          <t>2026-07-11 08:25:17 PM PT</t>
         </is>
       </c>
       <c r="C94" t="n">
@@ -11430,7 +11430,7 @@
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>2026-07-11 08:23:17 PM PT</t>
+          <t>2026-07-11 08:25:17 PM PT</t>
         </is>
       </c>
       <c r="C95" t="n">
@@ -11544,7 +11544,7 @@
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>2026-07-11 08:23:17 PM PT</t>
+          <t>2026-07-11 08:25:17 PM PT</t>
         </is>
       </c>
       <c r="C96" t="n">
@@ -11658,7 +11658,7 @@
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>2026-07-11 08:23:17 PM PT</t>
+          <t>2026-07-11 08:25:17 PM PT</t>
         </is>
       </c>
       <c r="C97" t="n">
@@ -11772,7 +11772,7 @@
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>2026-07-11 08:23:18 PM PT</t>
+          <t>2026-07-11 08:25:18 PM PT</t>
         </is>
       </c>
       <c r="C98" t="n">
@@ -11785,7 +11785,7 @@
       </c>
       <c r="E98" t="inlineStr">
         <is>
-          <t>Top 7 | 3 out</t>
+          <t>Bottom 7 | 0 out</t>
         </is>
       </c>
       <c r="F98" t="n">
@@ -11793,17 +11793,17 @@
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>Top</t>
+          <t>Bottom</t>
         </is>
       </c>
       <c r="H98" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="I98" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J98" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="K98" t="inlineStr">
         <is>
@@ -11895,7 +11895,7 @@
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>2026-07-11 08:23:17 PM PT</t>
+          <t>2026-07-11 08:25:17 PM PT</t>
         </is>
       </c>
       <c r="C99" t="n">
@@ -12009,7 +12009,7 @@
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>2026-07-11 08:23:16 PM PT</t>
+          <t>2026-07-11 08:25:16 PM PT</t>
         </is>
       </c>
       <c r="C100" t="n">
@@ -12123,7 +12123,7 @@
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>2026-07-11 08:23:16 PM PT</t>
+          <t>2026-07-11 08:25:16 PM PT</t>
         </is>
       </c>
       <c r="C101" t="n">
@@ -12237,7 +12237,7 @@
       </c>
       <c r="B102" t="inlineStr">
         <is>
-          <t>2026-07-11 08:23:17 PM PT</t>
+          <t>2026-07-11 08:25:17 PM PT</t>
         </is>
       </c>
       <c r="C102" t="n">
@@ -12351,7 +12351,7 @@
       </c>
       <c r="B103" t="inlineStr">
         <is>
-          <t>2026-07-11 08:23:18 PM PT</t>
+          <t>2026-07-11 08:25:18 PM PT</t>
         </is>
       </c>
       <c r="C103" t="n">
@@ -12379,10 +12379,10 @@
         <v>0</v>
       </c>
       <c r="I103" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J103" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="K103" t="inlineStr">
         <is>
@@ -12474,7 +12474,7 @@
       </c>
       <c r="B104" t="inlineStr">
         <is>
-          <t>2026-07-11 08:23:17 PM PT</t>
+          <t>2026-07-11 08:25:17 PM PT</t>
         </is>
       </c>
       <c r="C104" t="n">
@@ -12588,7 +12588,7 @@
       </c>
       <c r="B105" t="inlineStr">
         <is>
-          <t>2026-07-11 08:23:17 PM PT</t>
+          <t>2026-07-11 08:25:17 PM PT</t>
         </is>
       </c>
       <c r="C105" t="n">
@@ -12702,7 +12702,7 @@
       </c>
       <c r="B106" t="inlineStr">
         <is>
-          <t>2026-07-11 08:23:17 PM PT</t>
+          <t>2026-07-11 08:25:17 PM PT</t>
         </is>
       </c>
       <c r="C106" t="n">
@@ -12816,7 +12816,7 @@
       </c>
       <c r="B107" t="inlineStr">
         <is>
-          <t>2026-07-11 08:23:17 PM PT</t>
+          <t>2026-07-11 08:25:17 PM PT</t>
         </is>
       </c>
       <c r="C107" t="n">
@@ -12930,7 +12930,7 @@
       </c>
       <c r="B108" t="inlineStr">
         <is>
-          <t>2026-07-11 08:23:17 PM PT</t>
+          <t>2026-07-11 08:25:17 PM PT</t>
         </is>
       </c>
       <c r="C108" t="n">
@@ -13044,7 +13044,7 @@
       </c>
       <c r="B109" t="inlineStr">
         <is>
-          <t>2026-07-11 08:23:17 PM PT</t>
+          <t>2026-07-11 08:25:17 PM PT</t>
         </is>
       </c>
       <c r="C109" t="n">
@@ -13158,7 +13158,7 @@
       </c>
       <c r="B110" t="inlineStr">
         <is>
-          <t>2026-07-11 08:23:16 PM PT</t>
+          <t>2026-07-11 08:25:16 PM PT</t>
         </is>
       </c>
       <c r="C110" t="n">
@@ -13272,7 +13272,7 @@
       </c>
       <c r="B111" t="inlineStr">
         <is>
-          <t>2026-07-11 08:23:18 PM PT</t>
+          <t>2026-07-11 08:25:18 PM PT</t>
         </is>
       </c>
       <c r="C111" t="n">
@@ -13386,7 +13386,7 @@
       </c>
       <c r="B112" t="inlineStr">
         <is>
-          <t>2026-07-11 08:23:17 PM PT</t>
+          <t>2026-07-11 08:25:17 PM PT</t>
         </is>
       </c>
       <c r="C112" t="n">
@@ -13500,7 +13500,7 @@
       </c>
       <c r="B113" t="inlineStr">
         <is>
-          <t>2026-07-11 08:23:17 PM PT</t>
+          <t>2026-07-11 08:25:17 PM PT</t>
         </is>
       </c>
       <c r="C113" t="n">
@@ -13614,7 +13614,7 @@
       </c>
       <c r="B114" t="inlineStr">
         <is>
-          <t>2026-07-11 08:23:17 PM PT</t>
+          <t>2026-07-11 08:25:17 PM PT</t>
         </is>
       </c>
       <c r="C114" t="n">
@@ -13728,7 +13728,7 @@
       </c>
       <c r="B115" t="inlineStr">
         <is>
-          <t>2026-07-11 08:23:18 PM PT</t>
+          <t>2026-07-11 08:25:18 PM PT</t>
         </is>
       </c>
       <c r="C115" t="n">
@@ -13756,10 +13756,10 @@
         <v>0</v>
       </c>
       <c r="I115" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J115" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="K115" t="inlineStr">
         <is>
@@ -13851,7 +13851,7 @@
       </c>
       <c r="B116" t="inlineStr">
         <is>
-          <t>2026-07-11 08:23:17 PM PT</t>
+          <t>2026-07-11 08:25:17 PM PT</t>
         </is>
       </c>
       <c r="C116" t="n">
@@ -13965,7 +13965,7 @@
       </c>
       <c r="B117" t="inlineStr">
         <is>
-          <t>2026-07-11 08:23:18 PM PT</t>
+          <t>2026-07-11 08:25:18 PM PT</t>
         </is>
       </c>
       <c r="C117" t="n">
@@ -14079,7 +14079,7 @@
       </c>
       <c r="B118" t="inlineStr">
         <is>
-          <t>2026-07-11 08:23:18 PM PT</t>
+          <t>2026-07-11 08:25:18 PM PT</t>
         </is>
       </c>
       <c r="C118" t="n">
@@ -14193,7 +14193,7 @@
       </c>
       <c r="B119" t="inlineStr">
         <is>
-          <t>2026-07-11 08:23:17 PM PT</t>
+          <t>2026-07-11 08:25:17 PM PT</t>
         </is>
       </c>
       <c r="C119" t="n">
@@ -14307,7 +14307,7 @@
       </c>
       <c r="B120" t="inlineStr">
         <is>
-          <t>2026-07-11 08:23:17 PM PT</t>
+          <t>2026-07-11 08:25:17 PM PT</t>
         </is>
       </c>
       <c r="C120" t="n">
@@ -14421,7 +14421,7 @@
       </c>
       <c r="B121" t="inlineStr">
         <is>
-          <t>2026-07-11 08:23:18 PM PT</t>
+          <t>2026-07-11 08:25:18 PM PT</t>
         </is>
       </c>
       <c r="C121" t="n">
@@ -14535,7 +14535,7 @@
       </c>
       <c r="B122" t="inlineStr">
         <is>
-          <t>2026-07-11 08:23:17 PM PT</t>
+          <t>2026-07-11 08:25:17 PM PT</t>
         </is>
       </c>
       <c r="C122" t="n">
@@ -14649,7 +14649,7 @@
       </c>
       <c r="B123" t="inlineStr">
         <is>
-          <t>2026-07-11 08:23:16 PM PT</t>
+          <t>2026-07-11 08:25:16 PM PT</t>
         </is>
       </c>
       <c r="C123" t="n">
@@ -14763,7 +14763,7 @@
       </c>
       <c r="B124" t="inlineStr">
         <is>
-          <t>2026-07-11 08:23:17 PM PT</t>
+          <t>2026-07-11 08:25:17 PM PT</t>
         </is>
       </c>
       <c r="C124" t="n">
@@ -14877,7 +14877,7 @@
       </c>
       <c r="B125" t="inlineStr">
         <is>
-          <t>2026-07-11 08:23:17 PM PT</t>
+          <t>2026-07-11 08:25:17 PM PT</t>
         </is>
       </c>
       <c r="C125" t="n">
@@ -14991,7 +14991,7 @@
       </c>
       <c r="B126" t="inlineStr">
         <is>
-          <t>2026-07-11 08:23:17 PM PT</t>
+          <t>2026-07-11 08:25:17 PM PT</t>
         </is>
       </c>
       <c r="C126" t="n">
@@ -15105,7 +15105,7 @@
       </c>
       <c r="B127" t="inlineStr">
         <is>
-          <t>2026-07-11 08:23:17 PM PT</t>
+          <t>2026-07-11 08:25:17 PM PT</t>
         </is>
       </c>
       <c r="C127" t="n">
@@ -15219,7 +15219,7 @@
       </c>
       <c r="B128" t="inlineStr">
         <is>
-          <t>2026-07-11 08:23:18 PM PT</t>
+          <t>2026-07-11 08:25:18 PM PT</t>
         </is>
       </c>
       <c r="C128" t="n">
@@ -15232,7 +15232,7 @@
       </c>
       <c r="E128" t="inlineStr">
         <is>
-          <t>Top 7 | 3 out</t>
+          <t>Bottom 7 | 0 out</t>
         </is>
       </c>
       <c r="F128" t="n">
@@ -15240,17 +15240,17 @@
       </c>
       <c r="G128" t="inlineStr">
         <is>
-          <t>Top</t>
+          <t>Bottom</t>
         </is>
       </c>
       <c r="H128" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="I128" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J128" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="K128" t="inlineStr">
         <is>
@@ -15342,7 +15342,7 @@
       </c>
       <c r="B129" t="inlineStr">
         <is>
-          <t>2026-07-11 08:23:17 PM PT</t>
+          <t>2026-07-11 08:25:17 PM PT</t>
         </is>
       </c>
       <c r="C129" t="n">
@@ -15456,7 +15456,7 @@
       </c>
       <c r="B130" t="inlineStr">
         <is>
-          <t>2026-07-11 08:23:17 PM PT</t>
+          <t>2026-07-11 08:25:17 PM PT</t>
         </is>
       </c>
       <c r="C130" t="n">
@@ -15570,7 +15570,7 @@
       </c>
       <c r="B131" t="inlineStr">
         <is>
-          <t>2026-07-11 08:23:16 PM PT</t>
+          <t>2026-07-11 08:25:16 PM PT</t>
         </is>
       </c>
       <c r="C131" t="n">
@@ -15684,7 +15684,7 @@
       </c>
       <c r="B132" t="inlineStr">
         <is>
-          <t>2026-07-11 08:23:16 PM PT</t>
+          <t>2026-07-11 08:25:16 PM PT</t>
         </is>
       </c>
       <c r="C132" t="n">
@@ -15798,7 +15798,7 @@
       </c>
       <c r="B133" t="inlineStr">
         <is>
-          <t>2026-07-11 08:23:16 PM PT</t>
+          <t>2026-07-11 08:25:16 PM PT</t>
         </is>
       </c>
       <c r="C133" t="n">
@@ -15912,7 +15912,7 @@
       </c>
       <c r="B134" t="inlineStr">
         <is>
-          <t>2026-07-11 08:23:17 PM PT</t>
+          <t>2026-07-11 08:25:17 PM PT</t>
         </is>
       </c>
       <c r="C134" t="n">
@@ -16026,7 +16026,7 @@
       </c>
       <c r="B135" t="inlineStr">
         <is>
-          <t>2026-07-11 08:23:16 PM PT</t>
+          <t>2026-07-11 08:25:16 PM PT</t>
         </is>
       </c>
       <c r="C135" t="n">
@@ -16140,7 +16140,7 @@
       </c>
       <c r="B136" t="inlineStr">
         <is>
-          <t>2026-07-11 08:23:16 PM PT</t>
+          <t>2026-07-11 08:25:16 PM PT</t>
         </is>
       </c>
       <c r="C136" t="n">
@@ -16254,7 +16254,7 @@
       </c>
       <c r="B137" t="inlineStr">
         <is>
-          <t>2026-07-11 08:23:17 PM PT</t>
+          <t>2026-07-11 08:25:17 PM PT</t>
         </is>
       </c>
       <c r="C137" t="n">
@@ -16368,7 +16368,7 @@
       </c>
       <c r="B138" t="inlineStr">
         <is>
-          <t>2026-07-11 08:23:17 PM PT</t>
+          <t>2026-07-11 08:25:17 PM PT</t>
         </is>
       </c>
       <c r="C138" t="n">
@@ -16482,7 +16482,7 @@
       </c>
       <c r="B139" t="inlineStr">
         <is>
-          <t>2026-07-11 08:23:17 PM PT</t>
+          <t>2026-07-11 08:25:17 PM PT</t>
         </is>
       </c>
       <c r="C139" t="n">
@@ -16596,7 +16596,7 @@
       </c>
       <c r="B140" t="inlineStr">
         <is>
-          <t>2026-07-11 08:23:18 PM PT</t>
+          <t>2026-07-11 08:25:18 PM PT</t>
         </is>
       </c>
       <c r="C140" t="n">
@@ -16710,7 +16710,7 @@
       </c>
       <c r="B141" t="inlineStr">
         <is>
-          <t>2026-07-11 08:23:18 PM PT</t>
+          <t>2026-07-11 08:25:18 PM PT</t>
         </is>
       </c>
       <c r="C141" t="n">
@@ -16824,7 +16824,7 @@
       </c>
       <c r="B142" t="inlineStr">
         <is>
-          <t>2026-07-11 08:23:18 PM PT</t>
+          <t>2026-07-11 08:25:18 PM PT</t>
         </is>
       </c>
       <c r="C142" t="n">
@@ -16938,7 +16938,7 @@
       </c>
       <c r="B143" t="inlineStr">
         <is>
-          <t>2026-07-11 08:23:17 PM PT</t>
+          <t>2026-07-11 08:25:17 PM PT</t>
         </is>
       </c>
       <c r="C143" t="n">
@@ -17052,7 +17052,7 @@
       </c>
       <c r="B144" t="inlineStr">
         <is>
-          <t>2026-07-11 08:23:17 PM PT</t>
+          <t>2026-07-11 08:25:17 PM PT</t>
         </is>
       </c>
       <c r="C144" t="n">
@@ -17166,7 +17166,7 @@
       </c>
       <c r="B145" t="inlineStr">
         <is>
-          <t>2026-07-11 08:23:17 PM PT</t>
+          <t>2026-07-11 08:25:17 PM PT</t>
         </is>
       </c>
       <c r="C145" t="n">
@@ -17280,7 +17280,7 @@
       </c>
       <c r="B146" t="inlineStr">
         <is>
-          <t>2026-07-11 08:23:18 PM PT</t>
+          <t>2026-07-11 08:25:18 PM PT</t>
         </is>
       </c>
       <c r="C146" t="n">
@@ -17293,7 +17293,7 @@
       </c>
       <c r="E146" t="inlineStr">
         <is>
-          <t>Top 7 | 3 out</t>
+          <t>Bottom 7 | 0 out</t>
         </is>
       </c>
       <c r="F146" t="n">
@@ -17301,17 +17301,17 @@
       </c>
       <c r="G146" t="inlineStr">
         <is>
-          <t>Top</t>
+          <t>Bottom</t>
         </is>
       </c>
       <c r="H146" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="I146" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J146" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="K146" t="inlineStr">
         <is>
@@ -17403,7 +17403,7 @@
       </c>
       <c r="B147" t="inlineStr">
         <is>
-          <t>2026-07-11 08:23:18 PM PT</t>
+          <t>2026-07-11 08:25:18 PM PT</t>
         </is>
       </c>
       <c r="C147" t="n">
@@ -17517,7 +17517,7 @@
       </c>
       <c r="B148" t="inlineStr">
         <is>
-          <t>2026-07-11 08:23:17 PM PT</t>
+          <t>2026-07-11 08:25:17 PM PT</t>
         </is>
       </c>
       <c r="C148" t="n">
@@ -17631,7 +17631,7 @@
       </c>
       <c r="B149" t="inlineStr">
         <is>
-          <t>2026-07-11 08:23:16 PM PT</t>
+          <t>2026-07-11 08:25:16 PM PT</t>
         </is>
       </c>
       <c r="C149" t="n">
@@ -17745,7 +17745,7 @@
       </c>
       <c r="B150" t="inlineStr">
         <is>
-          <t>2026-07-11 08:23:16 PM PT</t>
+          <t>2026-07-11 08:25:16 PM PT</t>
         </is>
       </c>
       <c r="C150" t="n">
@@ -17859,7 +17859,7 @@
       </c>
       <c r="B151" t="inlineStr">
         <is>
-          <t>2026-07-11 08:23:16 PM PT</t>
+          <t>2026-07-11 08:25:16 PM PT</t>
         </is>
       </c>
       <c r="C151" t="n">
@@ -17973,7 +17973,7 @@
       </c>
       <c r="B152" t="inlineStr">
         <is>
-          <t>2026-07-11 08:23:16 PM PT</t>
+          <t>2026-07-11 08:25:16 PM PT</t>
         </is>
       </c>
       <c r="C152" t="n">
@@ -18087,7 +18087,7 @@
       </c>
       <c r="B153" t="inlineStr">
         <is>
-          <t>2026-07-11 08:23:17 PM PT</t>
+          <t>2026-07-11 08:25:17 PM PT</t>
         </is>
       </c>
       <c r="C153" t="n">
@@ -18201,7 +18201,7 @@
       </c>
       <c r="B154" t="inlineStr">
         <is>
-          <t>2026-07-11 08:23:17 PM PT</t>
+          <t>2026-07-11 08:25:17 PM PT</t>
         </is>
       </c>
       <c r="C154" t="n">
@@ -18315,7 +18315,7 @@
       </c>
       <c r="B155" t="inlineStr">
         <is>
-          <t>2026-07-11 08:23:16 PM PT</t>
+          <t>2026-07-11 08:25:16 PM PT</t>
         </is>
       </c>
       <c r="C155" t="n">
@@ -18429,7 +18429,7 @@
       </c>
       <c r="B156" t="inlineStr">
         <is>
-          <t>2026-07-11 08:23:18 PM PT</t>
+          <t>2026-07-11 08:25:18 PM PT</t>
         </is>
       </c>
       <c r="C156" t="n">
@@ -18457,10 +18457,10 @@
         <v>0</v>
       </c>
       <c r="I156" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J156" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="K156" t="inlineStr">
         <is>
@@ -18552,7 +18552,7 @@
       </c>
       <c r="B157" t="inlineStr">
         <is>
-          <t>2026-07-11 08:23:18 PM PT</t>
+          <t>2026-07-11 08:25:18 PM PT</t>
         </is>
       </c>
       <c r="C157" t="n">
@@ -18580,10 +18580,10 @@
         <v>0</v>
       </c>
       <c r="I157" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J157" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="K157" t="inlineStr">
         <is>
@@ -18675,7 +18675,7 @@
       </c>
       <c r="B158" t="inlineStr">
         <is>
-          <t>2026-07-11 08:23:18 PM PT</t>
+          <t>2026-07-11 08:25:18 PM PT</t>
         </is>
       </c>
       <c r="C158" t="n">
@@ -18703,10 +18703,10 @@
         <v>0</v>
       </c>
       <c r="I158" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J158" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="K158" t="inlineStr">
         <is>
@@ -18798,7 +18798,7 @@
       </c>
       <c r="B159" t="inlineStr">
         <is>
-          <t>2026-07-11 08:23:18 PM PT</t>
+          <t>2026-07-11 08:25:18 PM PT</t>
         </is>
       </c>
       <c r="C159" t="n">
@@ -18826,10 +18826,10 @@
         <v>0</v>
       </c>
       <c r="I159" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J159" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="K159" t="inlineStr">
         <is>
@@ -18921,7 +18921,7 @@
       </c>
       <c r="B160" t="inlineStr">
         <is>
-          <t>2026-07-11 08:23:18 PM PT</t>
+          <t>2026-07-11 08:25:18 PM PT</t>
         </is>
       </c>
       <c r="C160" t="n">
@@ -19035,7 +19035,7 @@
       </c>
       <c r="B161" t="inlineStr">
         <is>
-          <t>2026-07-11 08:23:18 PM PT</t>
+          <t>2026-07-11 08:25:18 PM PT</t>
         </is>
       </c>
       <c r="C161" t="n">
@@ -19149,7 +19149,7 @@
       </c>
       <c r="B162" t="inlineStr">
         <is>
-          <t>2026-07-11 08:23:18 PM PT</t>
+          <t>2026-07-11 08:25:18 PM PT</t>
         </is>
       </c>
       <c r="C162" t="n">
@@ -19263,7 +19263,7 @@
       </c>
       <c r="B163" t="inlineStr">
         <is>
-          <t>2026-07-11 08:23:18 PM PT</t>
+          <t>2026-07-11 08:25:18 PM PT</t>
         </is>
       </c>
       <c r="C163" t="n">
@@ -19377,7 +19377,7 @@
       </c>
       <c r="B164" t="inlineStr">
         <is>
-          <t>2026-07-11 08:23:18 PM PT</t>
+          <t>2026-07-11 08:25:18 PM PT</t>
         </is>
       </c>
       <c r="C164" t="n">
@@ -19491,7 +19491,7 @@
       </c>
       <c r="B165" t="inlineStr">
         <is>
-          <t>2026-07-11 08:23:17 PM PT</t>
+          <t>2026-07-11 08:25:17 PM PT</t>
         </is>
       </c>
       <c r="C165" t="n">
@@ -19605,7 +19605,7 @@
       </c>
       <c r="B166" t="inlineStr">
         <is>
-          <t>2026-07-11 08:23:17 PM PT</t>
+          <t>2026-07-11 08:25:17 PM PT</t>
         </is>
       </c>
       <c r="C166" t="n">
@@ -19719,7 +19719,7 @@
       </c>
       <c r="B167" t="inlineStr">
         <is>
-          <t>2026-07-11 08:23:17 PM PT</t>
+          <t>2026-07-11 08:25:17 PM PT</t>
         </is>
       </c>
       <c r="C167" t="n">
@@ -19833,7 +19833,7 @@
       </c>
       <c r="B168" t="inlineStr">
         <is>
-          <t>2026-07-11 08:23:17 PM PT</t>
+          <t>2026-07-11 08:25:17 PM PT</t>
         </is>
       </c>
       <c r="C168" t="n">
@@ -19947,7 +19947,7 @@
       </c>
       <c r="B169" t="inlineStr">
         <is>
-          <t>2026-07-11 08:23:17 PM PT</t>
+          <t>2026-07-11 08:25:17 PM PT</t>
         </is>
       </c>
       <c r="C169" t="n">
@@ -20061,7 +20061,7 @@
       </c>
       <c r="B170" t="inlineStr">
         <is>
-          <t>2026-07-11 08:23:16 PM PT</t>
+          <t>2026-07-11 08:25:16 PM PT</t>
         </is>
       </c>
       <c r="C170" t="n">
@@ -20175,7 +20175,7 @@
       </c>
       <c r="B171" t="inlineStr">
         <is>
-          <t>2026-07-11 08:23:18 PM PT</t>
+          <t>2026-07-11 08:25:18 PM PT</t>
         </is>
       </c>
       <c r="C171" t="n">
@@ -20188,7 +20188,7 @@
       </c>
       <c r="E171" t="inlineStr">
         <is>
-          <t>Top 7 | 3 out</t>
+          <t>Bottom 7 | 0 out</t>
         </is>
       </c>
       <c r="F171" t="n">
@@ -20196,17 +20196,17 @@
       </c>
       <c r="G171" t="inlineStr">
         <is>
-          <t>Top</t>
+          <t>Bottom</t>
         </is>
       </c>
       <c r="H171" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="I171" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J171" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="K171" t="inlineStr">
         <is>
@@ -20298,7 +20298,7 @@
       </c>
       <c r="B172" t="inlineStr">
         <is>
-          <t>2026-07-11 08:23:18 PM PT</t>
+          <t>2026-07-11 08:25:18 PM PT</t>
         </is>
       </c>
       <c r="C172" t="n">
@@ -20311,7 +20311,7 @@
       </c>
       <c r="E172" t="inlineStr">
         <is>
-          <t>Top 7 | 3 out</t>
+          <t>Bottom 7 | 0 out</t>
         </is>
       </c>
       <c r="F172" t="n">
@@ -20319,17 +20319,17 @@
       </c>
       <c r="G172" t="inlineStr">
         <is>
-          <t>Top</t>
+          <t>Bottom</t>
         </is>
       </c>
       <c r="H172" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="I172" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J172" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="K172" t="inlineStr">
         <is>
@@ -20421,7 +20421,7 @@
       </c>
       <c r="B173" t="inlineStr">
         <is>
-          <t>2026-07-11 08:23:17 PM PT</t>
+          <t>2026-07-11 08:25:17 PM PT</t>
         </is>
       </c>
       <c r="C173" t="n">
@@ -20535,7 +20535,7 @@
       </c>
       <c r="B174" t="inlineStr">
         <is>
-          <t>2026-07-11 08:23:17 PM PT</t>
+          <t>2026-07-11 08:25:17 PM PT</t>
         </is>
       </c>
       <c r="C174" t="n">
@@ -20649,7 +20649,7 @@
       </c>
       <c r="B175" t="inlineStr">
         <is>
-          <t>2026-07-11 08:23:16 PM PT</t>
+          <t>2026-07-11 08:25:16 PM PT</t>
         </is>
       </c>
       <c r="C175" t="n">
@@ -20763,7 +20763,7 @@
       </c>
       <c r="B176" t="inlineStr">
         <is>
-          <t>2026-07-11 08:23:16 PM PT</t>
+          <t>2026-07-11 08:25:16 PM PT</t>
         </is>
       </c>
       <c r="C176" t="n">
@@ -20877,7 +20877,7 @@
       </c>
       <c r="B177" t="inlineStr">
         <is>
-          <t>2026-07-11 08:23:16 PM PT</t>
+          <t>2026-07-11 08:25:16 PM PT</t>
         </is>
       </c>
       <c r="C177" t="n">
@@ -20991,7 +20991,7 @@
       </c>
       <c r="B178" t="inlineStr">
         <is>
-          <t>2026-07-11 08:23:16 PM PT</t>
+          <t>2026-07-11 08:25:16 PM PT</t>
         </is>
       </c>
       <c r="C178" t="n">
@@ -21105,7 +21105,7 @@
       </c>
       <c r="B179" t="inlineStr">
         <is>
-          <t>2026-07-11 08:23:16 PM PT</t>
+          <t>2026-07-11 08:25:16 PM PT</t>
         </is>
       </c>
       <c r="C179" t="n">
@@ -21219,7 +21219,7 @@
       </c>
       <c r="B180" t="inlineStr">
         <is>
-          <t>2026-07-11 08:23:17 PM PT</t>
+          <t>2026-07-11 08:25:17 PM PT</t>
         </is>
       </c>
       <c r="C180" t="n">
@@ -21333,7 +21333,7 @@
       </c>
       <c r="B181" t="inlineStr">
         <is>
-          <t>2026-07-11 08:23:17 PM PT</t>
+          <t>2026-07-11 08:25:17 PM PT</t>
         </is>
       </c>
       <c r="C181" t="n">
@@ -21447,7 +21447,7 @@
       </c>
       <c r="B182" t="inlineStr">
         <is>
-          <t>2026-07-11 08:23:17 PM PT</t>
+          <t>2026-07-11 08:25:17 PM PT</t>
         </is>
       </c>
       <c r="C182" t="n">
@@ -21561,7 +21561,7 @@
       </c>
       <c r="B183" t="inlineStr">
         <is>
-          <t>2026-07-11 08:23:17 PM PT</t>
+          <t>2026-07-11 08:25:17 PM PT</t>
         </is>
       </c>
       <c r="C183" t="n">
@@ -21675,7 +21675,7 @@
       </c>
       <c r="B184" t="inlineStr">
         <is>
-          <t>2026-07-11 08:23:16 PM PT</t>
+          <t>2026-07-11 08:25:16 PM PT</t>
         </is>
       </c>
       <c r="C184" t="n">
@@ -21789,7 +21789,7 @@
       </c>
       <c r="B185" t="inlineStr">
         <is>
-          <t>2026-07-11 08:23:16 PM PT</t>
+          <t>2026-07-11 08:25:16 PM PT</t>
         </is>
       </c>
       <c r="C185" t="n">
@@ -21903,7 +21903,7 @@
       </c>
       <c r="B186" t="inlineStr">
         <is>
-          <t>2026-07-11 08:23:17 PM PT</t>
+          <t>2026-07-11 08:25:17 PM PT</t>
         </is>
       </c>
       <c r="C186" t="n">
@@ -22017,7 +22017,7 @@
       </c>
       <c r="B187" t="inlineStr">
         <is>
-          <t>2026-07-11 08:23:17 PM PT</t>
+          <t>2026-07-11 08:25:17 PM PT</t>
         </is>
       </c>
       <c r="C187" t="n">
@@ -22131,7 +22131,7 @@
       </c>
       <c r="B188" t="inlineStr">
         <is>
-          <t>2026-07-11 08:23:17 PM PT</t>
+          <t>2026-07-11 08:25:17 PM PT</t>
         </is>
       </c>
       <c r="C188" t="n">
@@ -22245,7 +22245,7 @@
       </c>
       <c r="B189" t="inlineStr">
         <is>
-          <t>2026-07-11 08:23:17 PM PT</t>
+          <t>2026-07-11 08:25:17 PM PT</t>
         </is>
       </c>
       <c r="C189" t="n">
@@ -22359,7 +22359,7 @@
       </c>
       <c r="B190" t="inlineStr">
         <is>
-          <t>2026-07-11 08:23:17 PM PT</t>
+          <t>2026-07-11 08:25:17 PM PT</t>
         </is>
       </c>
       <c r="C190" t="n">
@@ -22473,7 +22473,7 @@
       </c>
       <c r="B191" t="inlineStr">
         <is>
-          <t>2026-07-11 08:23:17 PM PT</t>
+          <t>2026-07-11 08:25:17 PM PT</t>
         </is>
       </c>
       <c r="C191" t="n">
@@ -22587,7 +22587,7 @@
       </c>
       <c r="B192" t="inlineStr">
         <is>
-          <t>2026-07-11 08:23:18 PM PT</t>
+          <t>2026-07-11 08:25:18 PM PT</t>
         </is>
       </c>
       <c r="C192" t="n">
@@ -22600,7 +22600,7 @@
       </c>
       <c r="E192" t="inlineStr">
         <is>
-          <t>Top 7 | 3 out</t>
+          <t>Bottom 7 | 0 out</t>
         </is>
       </c>
       <c r="F192" t="n">
@@ -22608,17 +22608,17 @@
       </c>
       <c r="G192" t="inlineStr">
         <is>
-          <t>Top</t>
+          <t>Bottom</t>
         </is>
       </c>
       <c r="H192" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="I192" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J192" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="K192" t="inlineStr">
         <is>
@@ -22710,7 +22710,7 @@
       </c>
       <c r="B193" t="inlineStr">
         <is>
-          <t>2026-07-11 08:23:18 PM PT</t>
+          <t>2026-07-11 08:25:18 PM PT</t>
         </is>
       </c>
       <c r="C193" t="n">
@@ -22723,7 +22723,7 @@
       </c>
       <c r="E193" t="inlineStr">
         <is>
-          <t>Top 7 | 3 out</t>
+          <t>Bottom 7 | 0 out</t>
         </is>
       </c>
       <c r="F193" t="n">
@@ -22731,17 +22731,17 @@
       </c>
       <c r="G193" t="inlineStr">
         <is>
-          <t>Top</t>
+          <t>Bottom</t>
         </is>
       </c>
       <c r="H193" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="I193" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J193" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="K193" t="inlineStr">
         <is>
@@ -22833,7 +22833,7 @@
       </c>
       <c r="B194" t="inlineStr">
         <is>
-          <t>2026-07-11 08:23:16 PM PT</t>
+          <t>2026-07-11 08:25:16 PM PT</t>
         </is>
       </c>
       <c r="C194" t="n">
@@ -22947,7 +22947,7 @@
       </c>
       <c r="B195" t="inlineStr">
         <is>
-          <t>2026-07-11 08:23:18 PM PT</t>
+          <t>2026-07-11 08:25:18 PM PT</t>
         </is>
       </c>
       <c r="C195" t="n">
@@ -23061,7 +23061,7 @@
       </c>
       <c r="B196" t="inlineStr">
         <is>
-          <t>2026-07-11 08:23:18 PM PT</t>
+          <t>2026-07-11 08:25:18 PM PT</t>
         </is>
       </c>
       <c r="C196" t="n">
@@ -23175,7 +23175,7 @@
       </c>
       <c r="B197" t="inlineStr">
         <is>
-          <t>2026-07-11 08:23:17 PM PT</t>
+          <t>2026-07-11 08:25:17 PM PT</t>
         </is>
       </c>
       <c r="C197" t="n">
@@ -23289,7 +23289,7 @@
       </c>
       <c r="B198" t="inlineStr">
         <is>
-          <t>2026-07-11 08:23:17 PM PT</t>
+          <t>2026-07-11 08:25:17 PM PT</t>
         </is>
       </c>
       <c r="C198" t="n">
@@ -23403,7 +23403,7 @@
       </c>
       <c r="B199" t="inlineStr">
         <is>
-          <t>2026-07-11 08:23:17 PM PT</t>
+          <t>2026-07-11 08:25:17 PM PT</t>
         </is>
       </c>
       <c r="C199" t="n">
@@ -23517,7 +23517,7 @@
       </c>
       <c r="B200" t="inlineStr">
         <is>
-          <t>2026-07-11 08:23:17 PM PT</t>
+          <t>2026-07-11 08:25:17 PM PT</t>
         </is>
       </c>
       <c r="C200" t="n">
@@ -23631,7 +23631,7 @@
       </c>
       <c r="B201" t="inlineStr">
         <is>
-          <t>2026-07-11 08:23:18 PM PT</t>
+          <t>2026-07-11 08:25:18 PM PT</t>
         </is>
       </c>
       <c r="C201" t="n">
@@ -23745,7 +23745,7 @@
       </c>
       <c r="B202" t="inlineStr">
         <is>
-          <t>2026-07-11 08:23:17 PM PT</t>
+          <t>2026-07-11 08:25:17 PM PT</t>
         </is>
       </c>
       <c r="C202" t="n">
@@ -23859,7 +23859,7 @@
       </c>
       <c r="B203" t="inlineStr">
         <is>
-          <t>2026-07-11 08:23:17 PM PT</t>
+          <t>2026-07-11 08:25:17 PM PT</t>
         </is>
       </c>
       <c r="C203" t="n">
@@ -23973,7 +23973,7 @@
       </c>
       <c r="B204" t="inlineStr">
         <is>
-          <t>2026-07-11 08:23:17 PM PT</t>
+          <t>2026-07-11 08:25:17 PM PT</t>
         </is>
       </c>
       <c r="C204" t="n">
@@ -24087,7 +24087,7 @@
       </c>
       <c r="B205" t="inlineStr">
         <is>
-          <t>2026-07-11 08:23:16 PM PT</t>
+          <t>2026-07-11 08:25:16 PM PT</t>
         </is>
       </c>
       <c r="C205" t="n">
@@ -24201,7 +24201,7 @@
       </c>
       <c r="B206" t="inlineStr">
         <is>
-          <t>2026-07-11 08:23:16 PM PT</t>
+          <t>2026-07-11 08:25:16 PM PT</t>
         </is>
       </c>
       <c r="C206" t="n">
@@ -24315,7 +24315,7 @@
       </c>
       <c r="B207" t="inlineStr">
         <is>
-          <t>2026-07-11 08:23:17 PM PT</t>
+          <t>2026-07-11 08:25:17 PM PT</t>
         </is>
       </c>
       <c r="C207" t="n">
@@ -24429,7 +24429,7 @@
       </c>
       <c r="B208" t="inlineStr">
         <is>
-          <t>2026-07-11 08:23:17 PM PT</t>
+          <t>2026-07-11 08:25:17 PM PT</t>
         </is>
       </c>
       <c r="C208" t="n">
@@ -24543,7 +24543,7 @@
       </c>
       <c r="B209" t="inlineStr">
         <is>
-          <t>2026-07-11 08:23:17 PM PT</t>
+          <t>2026-07-11 08:25:17 PM PT</t>
         </is>
       </c>
       <c r="C209" t="n">
@@ -24657,7 +24657,7 @@
       </c>
       <c r="B210" t="inlineStr">
         <is>
-          <t>2026-07-11 08:23:17 PM PT</t>
+          <t>2026-07-11 08:25:17 PM PT</t>
         </is>
       </c>
       <c r="C210" t="n">
@@ -24771,7 +24771,7 @@
       </c>
       <c r="B211" t="inlineStr">
         <is>
-          <t>2026-07-11 08:23:17 PM PT</t>
+          <t>2026-07-11 08:25:17 PM PT</t>
         </is>
       </c>
       <c r="C211" t="n">
@@ -24885,7 +24885,7 @@
       </c>
       <c r="B212" t="inlineStr">
         <is>
-          <t>2026-07-11 08:23:16 PM PT</t>
+          <t>2026-07-11 08:25:16 PM PT</t>
         </is>
       </c>
       <c r="C212" t="n">
@@ -24999,7 +24999,7 @@
       </c>
       <c r="B213" t="inlineStr">
         <is>
-          <t>2026-07-11 08:23:17 PM PT</t>
+          <t>2026-07-11 08:25:17 PM PT</t>
         </is>
       </c>
       <c r="C213" t="n">
@@ -25113,7 +25113,7 @@
       </c>
       <c r="B214" t="inlineStr">
         <is>
-          <t>2026-07-11 08:23:17 PM PT</t>
+          <t>2026-07-11 08:25:17 PM PT</t>
         </is>
       </c>
       <c r="C214" t="n">
@@ -25227,7 +25227,7 @@
       </c>
       <c r="B215" t="inlineStr">
         <is>
-          <t>2026-07-11 08:23:16 PM PT</t>
+          <t>2026-07-11 08:25:16 PM PT</t>
         </is>
       </c>
       <c r="C215" t="n">
@@ -25341,7 +25341,7 @@
       </c>
       <c r="B216" t="inlineStr">
         <is>
-          <t>2026-07-11 08:23:17 PM PT</t>
+          <t>2026-07-11 08:25:17 PM PT</t>
         </is>
       </c>
       <c r="C216" t="n">
@@ -25455,7 +25455,7 @@
       </c>
       <c r="B217" t="inlineStr">
         <is>
-          <t>2026-07-11 08:23:17 PM PT</t>
+          <t>2026-07-11 08:25:17 PM PT</t>
         </is>
       </c>
       <c r="C217" t="n">
@@ -25569,7 +25569,7 @@
       </c>
       <c r="B218" t="inlineStr">
         <is>
-          <t>2026-07-11 08:23:17 PM PT</t>
+          <t>2026-07-11 08:25:17 PM PT</t>
         </is>
       </c>
       <c r="C218" t="n">
@@ -25683,7 +25683,7 @@
       </c>
       <c r="B219" t="inlineStr">
         <is>
-          <t>2026-07-11 08:23:17 PM PT</t>
+          <t>2026-07-11 08:25:17 PM PT</t>
         </is>
       </c>
       <c r="C219" t="n">
@@ -25797,7 +25797,7 @@
       </c>
       <c r="B220" t="inlineStr">
         <is>
-          <t>2026-07-11 08:23:17 PM PT</t>
+          <t>2026-07-11 08:25:17 PM PT</t>
         </is>
       </c>
       <c r="C220" t="n">
@@ -25911,7 +25911,7 @@
       </c>
       <c r="B221" t="inlineStr">
         <is>
-          <t>2026-07-11 08:23:17 PM PT</t>
+          <t>2026-07-11 08:25:17 PM PT</t>
         </is>
       </c>
       <c r="C221" t="n">
@@ -26025,7 +26025,7 @@
       </c>
       <c r="B222" t="inlineStr">
         <is>
-          <t>2026-07-11 08:23:17 PM PT</t>
+          <t>2026-07-11 08:25:17 PM PT</t>
         </is>
       </c>
       <c r="C222" t="n">
@@ -26139,7 +26139,7 @@
       </c>
       <c r="B223" t="inlineStr">
         <is>
-          <t>2026-07-11 08:23:16 PM PT</t>
+          <t>2026-07-11 08:25:16 PM PT</t>
         </is>
       </c>
       <c r="C223" t="n">
@@ -26253,7 +26253,7 @@
       </c>
       <c r="B224" t="inlineStr">
         <is>
-          <t>2026-07-11 08:23:16 PM PT</t>
+          <t>2026-07-11 08:25:16 PM PT</t>
         </is>
       </c>
       <c r="C224" t="n">
@@ -26367,7 +26367,7 @@
       </c>
       <c r="B225" t="inlineStr">
         <is>
-          <t>2026-07-11 08:23:17 PM PT</t>
+          <t>2026-07-11 08:25:17 PM PT</t>
         </is>
       </c>
       <c r="C225" t="n">
@@ -26481,7 +26481,7 @@
       </c>
       <c r="B226" t="inlineStr">
         <is>
-          <t>2026-07-11 08:23:17 PM PT</t>
+          <t>2026-07-11 08:25:17 PM PT</t>
         </is>
       </c>
       <c r="C226" t="n">
@@ -26595,7 +26595,7 @@
       </c>
       <c r="B227" t="inlineStr">
         <is>
-          <t>2026-07-11 08:23:17 PM PT</t>
+          <t>2026-07-11 08:25:17 PM PT</t>
         </is>
       </c>
       <c r="C227" t="n">
@@ -26709,7 +26709,7 @@
       </c>
       <c r="B228" t="inlineStr">
         <is>
-          <t>2026-07-11 08:23:17 PM PT</t>
+          <t>2026-07-11 08:25:17 PM PT</t>
         </is>
       </c>
       <c r="C228" t="n">
@@ -26823,7 +26823,7 @@
       </c>
       <c r="B229" t="inlineStr">
         <is>
-          <t>2026-07-11 08:23:18 PM PT</t>
+          <t>2026-07-11 08:25:18 PM PT</t>
         </is>
       </c>
       <c r="C229" t="n">
@@ -26851,10 +26851,10 @@
         <v>0</v>
       </c>
       <c r="I229" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J229" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="K229" t="inlineStr">
         <is>
@@ -26946,7 +26946,7 @@
       </c>
       <c r="B230" t="inlineStr">
         <is>
-          <t>2026-07-11 08:23:17 PM PT</t>
+          <t>2026-07-11 08:25:17 PM PT</t>
         </is>
       </c>
       <c r="C230" t="n">
@@ -27060,7 +27060,7 @@
       </c>
       <c r="B231" t="inlineStr">
         <is>
-          <t>2026-07-11 08:23:17 PM PT</t>
+          <t>2026-07-11 08:25:17 PM PT</t>
         </is>
       </c>
       <c r="C231" t="n">
@@ -27174,7 +27174,7 @@
       </c>
       <c r="B232" t="inlineStr">
         <is>
-          <t>2026-07-11 08:23:17 PM PT</t>
+          <t>2026-07-11 08:25:17 PM PT</t>
         </is>
       </c>
       <c r="C232" t="n">
@@ -27288,7 +27288,7 @@
       </c>
       <c r="B233" t="inlineStr">
         <is>
-          <t>2026-07-11 08:23:17 PM PT</t>
+          <t>2026-07-11 08:25:17 PM PT</t>
         </is>
       </c>
       <c r="C233" t="n">
@@ -27402,7 +27402,7 @@
       </c>
       <c r="B234" t="inlineStr">
         <is>
-          <t>2026-07-11 08:23:18 PM PT</t>
+          <t>2026-07-11 08:25:18 PM PT</t>
         </is>
       </c>
       <c r="C234" t="n">
@@ -27415,7 +27415,7 @@
       </c>
       <c r="E234" t="inlineStr">
         <is>
-          <t>Top 7 | 3 out</t>
+          <t>Bottom 7 | 0 out</t>
         </is>
       </c>
       <c r="F234" t="n">
@@ -27423,17 +27423,17 @@
       </c>
       <c r="G234" t="inlineStr">
         <is>
-          <t>Top</t>
+          <t>Bottom</t>
         </is>
       </c>
       <c r="H234" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="I234" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J234" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="K234" t="inlineStr">
         <is>
@@ -27525,7 +27525,7 @@
       </c>
       <c r="B235" t="inlineStr">
         <is>
-          <t>2026-07-11 08:23:18 PM PT</t>
+          <t>2026-07-11 08:25:18 PM PT</t>
         </is>
       </c>
       <c r="C235" t="n">
@@ -27538,7 +27538,7 @@
       </c>
       <c r="E235" t="inlineStr">
         <is>
-          <t>Top 7 | 3 out</t>
+          <t>Bottom 7 | 0 out</t>
         </is>
       </c>
       <c r="F235" t="n">
@@ -27546,17 +27546,17 @@
       </c>
       <c r="G235" t="inlineStr">
         <is>
-          <t>Top</t>
+          <t>Bottom</t>
         </is>
       </c>
       <c r="H235" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="I235" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J235" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="K235" t="inlineStr">
         <is>
@@ -27648,7 +27648,7 @@
       </c>
       <c r="B236" t="inlineStr">
         <is>
-          <t>2026-07-11 08:23:16 PM PT</t>
+          <t>2026-07-11 08:25:16 PM PT</t>
         </is>
       </c>
       <c r="C236" t="n">
@@ -27762,7 +27762,7 @@
       </c>
       <c r="B237" t="inlineStr">
         <is>
-          <t>2026-07-11 08:23:16 PM PT</t>
+          <t>2026-07-11 08:25:16 PM PT</t>
         </is>
       </c>
       <c r="C237" t="n">
@@ -27876,7 +27876,7 @@
       </c>
       <c r="B238" t="inlineStr">
         <is>
-          <t>2026-07-11 08:23:16 PM PT</t>
+          <t>2026-07-11 08:25:16 PM PT</t>
         </is>
       </c>
       <c r="C238" t="n">
@@ -27990,7 +27990,7 @@
       </c>
       <c r="B239" t="inlineStr">
         <is>
-          <t>2026-07-11 08:23:16 PM PT</t>
+          <t>2026-07-11 08:25:16 PM PT</t>
         </is>
       </c>
       <c r="C239" t="n">
@@ -28104,7 +28104,7 @@
       </c>
       <c r="B240" t="inlineStr">
         <is>
-          <t>2026-07-11 08:23:16 PM PT</t>
+          <t>2026-07-11 08:25:16 PM PT</t>
         </is>
       </c>
       <c r="C240" t="n">
@@ -28218,7 +28218,7 @@
       </c>
       <c r="B241" t="inlineStr">
         <is>
-          <t>2026-07-11 08:23:16 PM PT</t>
+          <t>2026-07-11 08:25:16 PM PT</t>
         </is>
       </c>
       <c r="C241" t="n">
@@ -28332,7 +28332,7 @@
       </c>
       <c r="B242" t="inlineStr">
         <is>
-          <t>2026-07-11 08:23:16 PM PT</t>
+          <t>2026-07-11 08:25:16 PM PT</t>
         </is>
       </c>
       <c r="C242" t="n">
@@ -28446,7 +28446,7 @@
       </c>
       <c r="B243" t="inlineStr">
         <is>
-          <t>2026-07-11 08:23:18 PM PT</t>
+          <t>2026-07-11 08:25:18 PM PT</t>
         </is>
       </c>
       <c r="C243" t="n">
@@ -28560,7 +28560,7 @@
       </c>
       <c r="B244" t="inlineStr">
         <is>
-          <t>2026-07-11 08:23:18 PM PT</t>
+          <t>2026-07-11 08:25:18 PM PT</t>
         </is>
       </c>
       <c r="C244" t="n">
@@ -28674,7 +28674,7 @@
       </c>
       <c r="B245" t="inlineStr">
         <is>
-          <t>2026-07-11 08:23:18 PM PT</t>
+          <t>2026-07-11 08:25:18 PM PT</t>
         </is>
       </c>
       <c r="C245" t="n">
@@ -28788,7 +28788,7 @@
       </c>
       <c r="B246" t="inlineStr">
         <is>
-          <t>2026-07-11 08:23:17 PM PT</t>
+          <t>2026-07-11 08:25:17 PM PT</t>
         </is>
       </c>
       <c r="C246" t="n">
@@ -28902,7 +28902,7 @@
       </c>
       <c r="B247" t="inlineStr">
         <is>
-          <t>2026-07-11 08:23:17 PM PT</t>
+          <t>2026-07-11 08:25:17 PM PT</t>
         </is>
       </c>
       <c r="C247" t="n">
@@ -29016,7 +29016,7 @@
       </c>
       <c r="B248" t="inlineStr">
         <is>
-          <t>2026-07-11 08:23:17 PM PT</t>
+          <t>2026-07-11 08:25:17 PM PT</t>
         </is>
       </c>
       <c r="C248" t="n">
@@ -29130,7 +29130,7 @@
       </c>
       <c r="B249" t="inlineStr">
         <is>
-          <t>2026-07-11 08:23:17 PM PT</t>
+          <t>2026-07-11 08:25:17 PM PT</t>
         </is>
       </c>
       <c r="C249" t="n">
@@ -29244,7 +29244,7 @@
       </c>
       <c r="B250" t="inlineStr">
         <is>
-          <t>2026-07-11 08:23:17 PM PT</t>
+          <t>2026-07-11 08:25:17 PM PT</t>
         </is>
       </c>
       <c r="C250" t="n">
@@ -29358,7 +29358,7 @@
       </c>
       <c r="B251" t="inlineStr">
         <is>
-          <t>2026-07-11 08:23:17 PM PT</t>
+          <t>2026-07-11 08:25:17 PM PT</t>
         </is>
       </c>
       <c r="C251" t="n">
@@ -29472,7 +29472,7 @@
       </c>
       <c r="B252" t="inlineStr">
         <is>
-          <t>2026-07-11 08:23:18 PM PT</t>
+          <t>2026-07-11 08:25:18 PM PT</t>
         </is>
       </c>
       <c r="C252" t="n">
@@ -29586,7 +29586,7 @@
       </c>
       <c r="B253" t="inlineStr">
         <is>
-          <t>2026-07-11 08:23:18 PM PT</t>
+          <t>2026-07-11 08:25:18 PM PT</t>
         </is>
       </c>
       <c r="C253" t="n">
@@ -29700,7 +29700,7 @@
       </c>
       <c r="B254" t="inlineStr">
         <is>
-          <t>2026-07-11 08:23:18 PM PT</t>
+          <t>2026-07-11 08:25:18 PM PT</t>
         </is>
       </c>
       <c r="C254" t="n">
@@ -29814,7 +29814,7 @@
       </c>
       <c r="B255" t="inlineStr">
         <is>
-          <t>2026-07-11 08:23:18 PM PT</t>
+          <t>2026-07-11 08:25:18 PM PT</t>
         </is>
       </c>
       <c r="C255" t="n">
@@ -29928,7 +29928,7 @@
       </c>
       <c r="B256" t="inlineStr">
         <is>
-          <t>2026-07-11 08:23:18 PM PT</t>
+          <t>2026-07-11 08:25:18 PM PT</t>
         </is>
       </c>
       <c r="C256" t="n">
@@ -30042,7 +30042,7 @@
       </c>
       <c r="B257" t="inlineStr">
         <is>
-          <t>2026-07-11 08:23:17 PM PT</t>
+          <t>2026-07-11 08:25:17 PM PT</t>
         </is>
       </c>
       <c r="C257" t="n">
@@ -30156,7 +30156,7 @@
       </c>
       <c r="B258" t="inlineStr">
         <is>
-          <t>2026-07-11 08:23:17 PM PT</t>
+          <t>2026-07-11 08:25:17 PM PT</t>
         </is>
       </c>
       <c r="C258" t="n">
@@ -30270,7 +30270,7 @@
       </c>
       <c r="B259" t="inlineStr">
         <is>
-          <t>2026-07-11 08:23:17 PM PT</t>
+          <t>2026-07-11 08:25:17 PM PT</t>
         </is>
       </c>
       <c r="C259" t="n">
@@ -30384,7 +30384,7 @@
       </c>
       <c r="B260" t="inlineStr">
         <is>
-          <t>2026-07-11 08:23:16 PM PT</t>
+          <t>2026-07-11 08:25:16 PM PT</t>
         </is>
       </c>
       <c r="C260" t="n">
@@ -30498,7 +30498,7 @@
       </c>
       <c r="B261" t="inlineStr">
         <is>
-          <t>2026-07-11 08:23:16 PM PT</t>
+          <t>2026-07-11 08:25:16 PM PT</t>
         </is>
       </c>
       <c r="C261" t="n">
@@ -30612,7 +30612,7 @@
       </c>
       <c r="B262" t="inlineStr">
         <is>
-          <t>2026-07-11 08:23:16 PM PT</t>
+          <t>2026-07-11 08:25:16 PM PT</t>
         </is>
       </c>
       <c r="C262" t="n">
@@ -30726,7 +30726,7 @@
       </c>
       <c r="B263" t="inlineStr">
         <is>
-          <t>2026-07-11 08:23:16 PM PT</t>
+          <t>2026-07-11 08:25:16 PM PT</t>
         </is>
       </c>
       <c r="C263" t="n">
@@ -30840,7 +30840,7 @@
       </c>
       <c r="B264" t="inlineStr">
         <is>
-          <t>2026-07-11 08:23:17 PM PT</t>
+          <t>2026-07-11 08:25:17 PM PT</t>
         </is>
       </c>
       <c r="C264" t="n">
@@ -30954,7 +30954,7 @@
       </c>
       <c r="B265" t="inlineStr">
         <is>
-          <t>2026-07-11 08:23:17 PM PT</t>
+          <t>2026-07-11 08:25:17 PM PT</t>
         </is>
       </c>
       <c r="C265" t="n">
@@ -31068,7 +31068,7 @@
       </c>
       <c r="B266" t="inlineStr">
         <is>
-          <t>2026-07-11 08:23:17 PM PT</t>
+          <t>2026-07-11 08:25:17 PM PT</t>
         </is>
       </c>
       <c r="C266" t="n">
@@ -31182,7 +31182,7 @@
       </c>
       <c r="B267" t="inlineStr">
         <is>
-          <t>2026-07-11 08:23:17 PM PT</t>
+          <t>2026-07-11 08:25:17 PM PT</t>
         </is>
       </c>
       <c r="C267" t="n">
@@ -31296,7 +31296,7 @@
       </c>
       <c r="B268" t="inlineStr">
         <is>
-          <t>2026-07-11 08:23:17 PM PT</t>
+          <t>2026-07-11 08:25:17 PM PT</t>
         </is>
       </c>
       <c r="C268" t="n">
@@ -31410,7 +31410,7 @@
       </c>
       <c r="B269" t="inlineStr">
         <is>
-          <t>2026-07-11 08:23:17 PM PT</t>
+          <t>2026-07-11 08:25:17 PM PT</t>
         </is>
       </c>
       <c r="C269" t="n">
@@ -31524,7 +31524,7 @@
       </c>
       <c r="B270" t="inlineStr">
         <is>
-          <t>2026-07-11 08:23:17 PM PT</t>
+          <t>2026-07-11 08:25:17 PM PT</t>
         </is>
       </c>
       <c r="C270" t="n">
@@ -31638,7 +31638,7 @@
       </c>
       <c r="B271" t="inlineStr">
         <is>
-          <t>2026-07-11 08:23:17 PM PT</t>
+          <t>2026-07-11 08:25:17 PM PT</t>
         </is>
       </c>
       <c r="C271" t="n">
@@ -31752,7 +31752,7 @@
       </c>
       <c r="B272" t="inlineStr">
         <is>
-          <t>2026-07-11 08:23:17 PM PT</t>
+          <t>2026-07-11 08:25:17 PM PT</t>
         </is>
       </c>
       <c r="C272" t="n">
@@ -31866,7 +31866,7 @@
       </c>
       <c r="B273" t="inlineStr">
         <is>
-          <t>2026-07-11 08:23:17 PM PT</t>
+          <t>2026-07-11 08:25:17 PM PT</t>
         </is>
       </c>
       <c r="C273" t="n">
@@ -31980,7 +31980,7 @@
       </c>
       <c r="B274" t="inlineStr">
         <is>
-          <t>2026-07-11 08:23:17 PM PT</t>
+          <t>2026-07-11 08:25:17 PM PT</t>
         </is>
       </c>
       <c r="C274" t="n">
@@ -32094,7 +32094,7 @@
       </c>
       <c r="B275" t="inlineStr">
         <is>
-          <t>2026-07-11 08:23:16 PM PT</t>
+          <t>2026-07-11 08:25:16 PM PT</t>
         </is>
       </c>
       <c r="C275" t="n">
@@ -32208,7 +32208,7 @@
       </c>
       <c r="B276" t="inlineStr">
         <is>
-          <t>2026-07-11 08:23:16 PM PT</t>
+          <t>2026-07-11 08:25:16 PM PT</t>
         </is>
       </c>
       <c r="C276" t="n">
@@ -32322,7 +32322,7 @@
       </c>
       <c r="B277" t="inlineStr">
         <is>
-          <t>2026-07-11 08:23:16 PM PT</t>
+          <t>2026-07-11 08:25:16 PM PT</t>
         </is>
       </c>
       <c r="C277" t="n">
@@ -32436,7 +32436,7 @@
       </c>
       <c r="B278" t="inlineStr">
         <is>
-          <t>2026-07-11 08:23:18 PM PT</t>
+          <t>2026-07-11 08:25:18 PM PT</t>
         </is>
       </c>
       <c r="C278" t="n">
@@ -32449,7 +32449,7 @@
       </c>
       <c r="E278" t="inlineStr">
         <is>
-          <t>Top 7 | 3 out</t>
+          <t>Bottom 7 | 0 out</t>
         </is>
       </c>
       <c r="F278" t="n">
@@ -32457,17 +32457,17 @@
       </c>
       <c r="G278" t="inlineStr">
         <is>
-          <t>Top</t>
+          <t>Bottom</t>
         </is>
       </c>
       <c r="H278" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="I278" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J278" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="K278" t="inlineStr">
         <is>
@@ -32559,7 +32559,7 @@
       </c>
       <c r="B279" t="inlineStr">
         <is>
-          <t>2026-07-11 08:23:18 PM PT</t>
+          <t>2026-07-11 08:25:18 PM PT</t>
         </is>
       </c>
       <c r="C279" t="n">
@@ -32572,7 +32572,7 @@
       </c>
       <c r="E279" t="inlineStr">
         <is>
-          <t>Top 7 | 3 out</t>
+          <t>Bottom 7 | 0 out</t>
         </is>
       </c>
       <c r="F279" t="n">
@@ -32580,17 +32580,17 @@
       </c>
       <c r="G279" t="inlineStr">
         <is>
-          <t>Top</t>
+          <t>Bottom</t>
         </is>
       </c>
       <c r="H279" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="I279" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J279" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="K279" t="inlineStr">
         <is>
@@ -32682,7 +32682,7 @@
       </c>
       <c r="B280" t="inlineStr">
         <is>
-          <t>2026-07-11 08:23:18 PM PT</t>
+          <t>2026-07-11 08:25:18 PM PT</t>
         </is>
       </c>
       <c r="C280" t="n">
@@ -32695,7 +32695,7 @@
       </c>
       <c r="E280" t="inlineStr">
         <is>
-          <t>Top 7 | 3 out</t>
+          <t>Bottom 7 | 0 out</t>
         </is>
       </c>
       <c r="F280" t="n">
@@ -32703,17 +32703,17 @@
       </c>
       <c r="G280" t="inlineStr">
         <is>
-          <t>Top</t>
+          <t>Bottom</t>
         </is>
       </c>
       <c r="H280" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="I280" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J280" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="K280" t="inlineStr">
         <is>
@@ -32805,7 +32805,7 @@
       </c>
       <c r="B281" t="inlineStr">
         <is>
-          <t>2026-07-11 08:23:18 PM PT</t>
+          <t>2026-07-11 08:25:18 PM PT</t>
         </is>
       </c>
       <c r="C281" t="n">
@@ -32818,7 +32818,7 @@
       </c>
       <c r="E281" t="inlineStr">
         <is>
-          <t>Top 7 | 3 out</t>
+          <t>Bottom 7 | 0 out</t>
         </is>
       </c>
       <c r="F281" t="n">
@@ -32826,17 +32826,17 @@
       </c>
       <c r="G281" t="inlineStr">
         <is>
-          <t>Top</t>
+          <t>Bottom</t>
         </is>
       </c>
       <c r="H281" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="I281" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J281" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="K281" t="inlineStr">
         <is>
@@ -32928,7 +32928,7 @@
       </c>
       <c r="B282" t="inlineStr">
         <is>
-          <t>2026-07-11 08:23:17 PM PT</t>
+          <t>2026-07-11 08:25:17 PM PT</t>
         </is>
       </c>
       <c r="C282" t="n">
@@ -33042,7 +33042,7 @@
       </c>
       <c r="B283" t="inlineStr">
         <is>
-          <t>2026-07-11 08:23:16 PM PT</t>
+          <t>2026-07-11 08:25:16 PM PT</t>
         </is>
       </c>
       <c r="C283" t="n">
@@ -33156,7 +33156,7 @@
       </c>
       <c r="B284" t="inlineStr">
         <is>
-          <t>2026-07-11 08:23:16 PM PT</t>
+          <t>2026-07-11 08:25:16 PM PT</t>
         </is>
       </c>
       <c r="C284" t="n">
@@ -33270,7 +33270,7 @@
       </c>
       <c r="B285" t="inlineStr">
         <is>
-          <t>2026-07-11 08:23:16 PM PT</t>
+          <t>2026-07-11 08:25:16 PM PT</t>
         </is>
       </c>
       <c r="C285" t="n">
@@ -33384,7 +33384,7 @@
       </c>
       <c r="B286" t="inlineStr">
         <is>
-          <t>2026-07-11 08:23:16 PM PT</t>
+          <t>2026-07-11 08:25:16 PM PT</t>
         </is>
       </c>
       <c r="C286" t="n">
@@ -33498,7 +33498,7 @@
       </c>
       <c r="B287" t="inlineStr">
         <is>
-          <t>2026-07-11 08:23:16 PM PT</t>
+          <t>2026-07-11 08:25:16 PM PT</t>
         </is>
       </c>
       <c r="C287" t="n">
@@ -33612,7 +33612,7 @@
       </c>
       <c r="B288" t="inlineStr">
         <is>
-          <t>2026-07-11 08:23:16 PM PT</t>
+          <t>2026-07-11 08:25:16 PM PT</t>
         </is>
       </c>
       <c r="C288" t="n">
@@ -33726,7 +33726,7 @@
       </c>
       <c r="B289" t="inlineStr">
         <is>
-          <t>2026-07-11 08:23:16 PM PT</t>
+          <t>2026-07-11 08:25:16 PM PT</t>
         </is>
       </c>
       <c r="C289" t="n">
@@ -33840,7 +33840,7 @@
       </c>
       <c r="B290" t="inlineStr">
         <is>
-          <t>2026-07-11 08:23:17 PM PT</t>
+          <t>2026-07-11 08:25:17 PM PT</t>
         </is>
       </c>
       <c r="C290" t="n">
@@ -33954,7 +33954,7 @@
       </c>
       <c r="B291" t="inlineStr">
         <is>
-          <t>2026-07-11 08:23:17 PM PT</t>
+          <t>2026-07-11 08:25:17 PM PT</t>
         </is>
       </c>
       <c r="C291" t="n">
@@ -34068,7 +34068,7 @@
       </c>
       <c r="B292" t="inlineStr">
         <is>
-          <t>2026-07-11 08:23:17 PM PT</t>
+          <t>2026-07-11 08:25:17 PM PT</t>
         </is>
       </c>
       <c r="C292" t="n">
@@ -34182,7 +34182,7 @@
       </c>
       <c r="B293" t="inlineStr">
         <is>
-          <t>2026-07-11 08:23:17 PM PT</t>
+          <t>2026-07-11 08:25:17 PM PT</t>
         </is>
       </c>
       <c r="C293" t="n">
@@ -34296,7 +34296,7 @@
       </c>
       <c r="B294" t="inlineStr">
         <is>
-          <t>2026-07-11 08:23:17 PM PT</t>
+          <t>2026-07-11 08:25:17 PM PT</t>
         </is>
       </c>
       <c r="C294" t="n">
@@ -34410,7 +34410,7 @@
       </c>
       <c r="B295" t="inlineStr">
         <is>
-          <t>2026-07-11 08:23:17 PM PT</t>
+          <t>2026-07-11 08:25:17 PM PT</t>
         </is>
       </c>
       <c r="C295" t="n">
@@ -34524,7 +34524,7 @@
       </c>
       <c r="B296" t="inlineStr">
         <is>
-          <t>2026-07-11 08:23:17 PM PT</t>
+          <t>2026-07-11 08:25:17 PM PT</t>
         </is>
       </c>
       <c r="C296" t="n">
@@ -34638,7 +34638,7 @@
       </c>
       <c r="B297" t="inlineStr">
         <is>
-          <t>2026-07-11 08:23:17 PM PT</t>
+          <t>2026-07-11 08:25:17 PM PT</t>
         </is>
       </c>
       <c r="C297" t="n">
@@ -34752,7 +34752,7 @@
       </c>
       <c r="B298" t="inlineStr">
         <is>
-          <t>2026-07-11 08:23:16 PM PT</t>
+          <t>2026-07-11 08:25:16 PM PT</t>
         </is>
       </c>
       <c r="C298" t="n">
@@ -34866,7 +34866,7 @@
       </c>
       <c r="B299" t="inlineStr">
         <is>
-          <t>2026-07-11 08:23:16 PM PT</t>
+          <t>2026-07-11 08:25:16 PM PT</t>
         </is>
       </c>
       <c r="C299" t="n">
@@ -34980,7 +34980,7 @@
       </c>
       <c r="B300" t="inlineStr">
         <is>
-          <t>2026-07-11 08:23:16 PM PT</t>
+          <t>2026-07-11 08:25:16 PM PT</t>
         </is>
       </c>
       <c r="C300" t="n">
@@ -35094,7 +35094,7 @@
       </c>
       <c r="B301" t="inlineStr">
         <is>
-          <t>2026-07-11 08:23:16 PM PT</t>
+          <t>2026-07-11 08:25:16 PM PT</t>
         </is>
       </c>
       <c r="C301" t="n">
@@ -35208,7 +35208,7 @@
       </c>
       <c r="B302" t="inlineStr">
         <is>
-          <t>2026-07-11 08:23:16 PM PT</t>
+          <t>2026-07-11 08:25:16 PM PT</t>
         </is>
       </c>
       <c r="C302" t="n">
@@ -35322,7 +35322,7 @@
       </c>
       <c r="B303" t="inlineStr">
         <is>
-          <t>2026-07-11 08:23:16 PM PT</t>
+          <t>2026-07-11 08:25:16 PM PT</t>
         </is>
       </c>
       <c r="C303" t="n">
@@ -35436,7 +35436,7 @@
       </c>
       <c r="B304" t="inlineStr">
         <is>
-          <t>2026-07-11 08:23:16 PM PT</t>
+          <t>2026-07-11 08:25:16 PM PT</t>
         </is>
       </c>
       <c r="C304" t="n">
@@ -35550,7 +35550,7 @@
       </c>
       <c r="B305" t="inlineStr">
         <is>
-          <t>2026-07-11 08:23:16 PM PT</t>
+          <t>2026-07-11 08:25:16 PM PT</t>
         </is>
       </c>
       <c r="C305" t="n">
@@ -35664,7 +35664,7 @@
       </c>
       <c r="B306" t="inlineStr">
         <is>
-          <t>2026-07-11 08:23:18 PM PT</t>
+          <t>2026-07-11 08:25:18 PM PT</t>
         </is>
       </c>
       <c r="C306" t="n">
@@ -35692,10 +35692,10 @@
         <v>0</v>
       </c>
       <c r="I306" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J306" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="K306" t="inlineStr">
         <is>
@@ -35787,7 +35787,7 @@
       </c>
       <c r="B307" t="inlineStr">
         <is>
-          <t>2026-07-11 08:23:17 PM PT</t>
+          <t>2026-07-11 08:25:17 PM PT</t>
         </is>
       </c>
       <c r="C307" t="n">
@@ -35901,7 +35901,7 @@
       </c>
       <c r="B308" t="inlineStr">
         <is>
-          <t>2026-07-11 08:23:17 PM PT</t>
+          <t>2026-07-11 08:25:17 PM PT</t>
         </is>
       </c>
       <c r="C308" t="n">
@@ -36015,7 +36015,7 @@
       </c>
       <c r="B309" t="inlineStr">
         <is>
-          <t>2026-07-11 08:23:17 PM PT</t>
+          <t>2026-07-11 08:25:17 PM PT</t>
         </is>
       </c>
       <c r="C309" t="n">
@@ -36129,7 +36129,7 @@
       </c>
       <c r="B310" t="inlineStr">
         <is>
-          <t>2026-07-11 08:23:17 PM PT</t>
+          <t>2026-07-11 08:25:17 PM PT</t>
         </is>
       </c>
       <c r="C310" t="n">
@@ -36243,7 +36243,7 @@
       </c>
       <c r="B311" t="inlineStr">
         <is>
-          <t>2026-07-11 08:23:17 PM PT</t>
+          <t>2026-07-11 08:25:17 PM PT</t>
         </is>
       </c>
       <c r="C311" t="n">
@@ -36357,7 +36357,7 @@
       </c>
       <c r="B312" t="inlineStr">
         <is>
-          <t>2026-07-11 08:23:17 PM PT</t>
+          <t>2026-07-11 08:25:17 PM PT</t>
         </is>
       </c>
       <c r="C312" t="n">
@@ -36471,7 +36471,7 @@
       </c>
       <c r="B313" t="inlineStr">
         <is>
-          <t>2026-07-11 08:23:17 PM PT</t>
+          <t>2026-07-11 08:25:17 PM PT</t>
         </is>
       </c>
       <c r="C313" t="n">
@@ -36585,7 +36585,7 @@
       </c>
       <c r="B314" t="inlineStr">
         <is>
-          <t>2026-07-11 08:23:18 PM PT</t>
+          <t>2026-07-11 08:25:18 PM PT</t>
         </is>
       </c>
       <c r="C314" t="n">
@@ -36699,7 +36699,7 @@
       </c>
       <c r="B315" t="inlineStr">
         <is>
-          <t>2026-07-11 08:23:18 PM PT</t>
+          <t>2026-07-11 08:25:18 PM PT</t>
         </is>
       </c>
       <c r="C315" t="n">
@@ -36813,7 +36813,7 @@
       </c>
       <c r="B316" t="inlineStr">
         <is>
-          <t>2026-07-11 08:23:18 PM PT</t>
+          <t>2026-07-11 08:25:18 PM PT</t>
         </is>
       </c>
       <c r="C316" t="n">
@@ -36927,7 +36927,7 @@
       </c>
       <c r="B317" t="inlineStr">
         <is>
-          <t>2026-07-11 08:23:18 PM PT</t>
+          <t>2026-07-11 08:25:18 PM PT</t>
         </is>
       </c>
       <c r="C317" t="n">
@@ -37041,7 +37041,7 @@
       </c>
       <c r="B318" t="inlineStr">
         <is>
-          <t>2026-07-11 08:23:17 PM PT</t>
+          <t>2026-07-11 08:25:17 PM PT</t>
         </is>
       </c>
       <c r="C318" t="n">
@@ -37155,7 +37155,7 @@
       </c>
       <c r="B319" t="inlineStr">
         <is>
-          <t>2026-07-11 08:23:17 PM PT</t>
+          <t>2026-07-11 08:25:17 PM PT</t>
         </is>
       </c>
       <c r="C319" t="n">
@@ -37269,7 +37269,7 @@
       </c>
       <c r="B320" t="inlineStr">
         <is>
-          <t>2026-07-11 08:23:17 PM PT</t>
+          <t>2026-07-11 08:25:17 PM PT</t>
         </is>
       </c>
       <c r="C320" t="n">
@@ -37383,7 +37383,7 @@
       </c>
       <c r="B321" t="inlineStr">
         <is>
-          <t>2026-07-11 08:23:17 PM PT</t>
+          <t>2026-07-11 08:25:17 PM PT</t>
         </is>
       </c>
       <c r="C321" t="n">
@@ -37497,7 +37497,7 @@
       </c>
       <c r="B322" t="inlineStr">
         <is>
-          <t>2026-07-11 08:23:17 PM PT</t>
+          <t>2026-07-11 08:25:17 PM PT</t>
         </is>
       </c>
       <c r="C322" t="n">
@@ -37611,7 +37611,7 @@
       </c>
       <c r="B323" t="inlineStr">
         <is>
-          <t>2026-07-11 08:23:17 PM PT</t>
+          <t>2026-07-11 08:25:17 PM PT</t>
         </is>
       </c>
       <c r="C323" t="n">
@@ -37725,7 +37725,7 @@
       </c>
       <c r="B324" t="inlineStr">
         <is>
-          <t>2026-07-11 08:23:17 PM PT</t>
+          <t>2026-07-11 08:25:17 PM PT</t>
         </is>
       </c>
       <c r="C324" t="n">
@@ -37839,7 +37839,7 @@
       </c>
       <c r="B325" t="inlineStr">
         <is>
-          <t>2026-07-11 08:23:17 PM PT</t>
+          <t>2026-07-11 08:25:17 PM PT</t>
         </is>
       </c>
       <c r="C325" t="n">
@@ -37953,7 +37953,7 @@
       </c>
       <c r="B326" t="inlineStr">
         <is>
-          <t>2026-07-11 08:23:17 PM PT</t>
+          <t>2026-07-11 08:25:17 PM PT</t>
         </is>
       </c>
       <c r="C326" t="n">
@@ -38067,7 +38067,7 @@
       </c>
       <c r="B327" t="inlineStr">
         <is>
-          <t>2026-07-11 08:23:18 PM PT</t>
+          <t>2026-07-11 08:25:18 PM PT</t>
         </is>
       </c>
       <c r="C327" t="n">
@@ -38095,10 +38095,10 @@
         <v>0</v>
       </c>
       <c r="I327" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J327" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="K327" t="inlineStr">
         <is>
@@ -38190,7 +38190,7 @@
       </c>
       <c r="B328" t="inlineStr">
         <is>
-          <t>2026-07-11 08:23:18 PM PT</t>
+          <t>2026-07-11 08:25:18 PM PT</t>
         </is>
       </c>
       <c r="C328" t="n">
@@ -38218,10 +38218,10 @@
         <v>0</v>
       </c>
       <c r="I328" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J328" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="K328" t="inlineStr">
         <is>
@@ -38313,7 +38313,7 @@
       </c>
       <c r="B329" t="inlineStr">
         <is>
-          <t>2026-07-11 08:23:17 PM PT</t>
+          <t>2026-07-11 08:25:17 PM PT</t>
         </is>
       </c>
       <c r="C329" t="n">
@@ -38427,7 +38427,7 @@
       </c>
       <c r="B330" t="inlineStr">
         <is>
-          <t>2026-07-11 08:23:17 PM PT</t>
+          <t>2026-07-11 08:25:17 PM PT</t>
         </is>
       </c>
       <c r="C330" t="n">

--- a/live_mlb_hitter_fantasy_scores_2026_07_11.xlsx
+++ b/live_mlb_hitter_fantasy_scores_2026_07_11.xlsx
@@ -693,7 +693,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-07-11 08:27:16 PM PT</t>
+          <t>2026-07-11 08:29:16 PM PT</t>
         </is>
       </c>
       <c r="C2" t="n">
@@ -807,7 +807,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>2026-07-11 08:27:17 PM PT</t>
+          <t>2026-07-11 08:29:18 PM PT</t>
         </is>
       </c>
       <c r="C3" t="n">
@@ -921,7 +921,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-07-11 08:27:18 PM PT</t>
+          <t>2026-07-11 08:29:18 PM PT</t>
         </is>
       </c>
       <c r="C4" t="n">
@@ -934,7 +934,7 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Top 8 | 0 out</t>
+          <t>Top 8 | 3 out</t>
         </is>
       </c>
       <c r="F4" t="n">
@@ -946,13 +946,13 @@
         </is>
       </c>
       <c r="H4" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="I4" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J4" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="K4" t="inlineStr">
         <is>
@@ -1044,7 +1044,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>2026-07-11 08:27:17 PM PT</t>
+          <t>2026-07-11 08:29:18 PM PT</t>
         </is>
       </c>
       <c r="C5" t="n">
@@ -1158,7 +1158,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>2026-07-11 08:27:18 PM PT</t>
+          <t>2026-07-11 08:29:18 PM PT</t>
         </is>
       </c>
       <c r="C6" t="n">
@@ -1272,7 +1272,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>2026-07-11 08:27:17 PM PT</t>
+          <t>2026-07-11 08:29:17 PM PT</t>
         </is>
       </c>
       <c r="C7" t="n">
@@ -1386,7 +1386,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>2026-07-11 08:27:17 PM PT</t>
+          <t>2026-07-11 08:29:17 PM PT</t>
         </is>
       </c>
       <c r="C8" t="n">
@@ -1500,7 +1500,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>2026-07-11 08:27:16 PM PT</t>
+          <t>2026-07-11 08:29:16 PM PT</t>
         </is>
       </c>
       <c r="C9" t="n">
@@ -1614,7 +1614,7 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>2026-07-11 08:27:18 PM PT</t>
+          <t>2026-07-11 08:29:18 PM PT</t>
         </is>
       </c>
       <c r="C10" t="n">
@@ -1627,7 +1627,7 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Top 8 | 0 out</t>
+          <t>Top 8 | 3 out</t>
         </is>
       </c>
       <c r="F10" t="n">
@@ -1639,13 +1639,13 @@
         </is>
       </c>
       <c r="H10" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="I10" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J10" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="K10" t="inlineStr">
         <is>
@@ -1737,7 +1737,7 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>2026-07-11 08:27:17 PM PT</t>
+          <t>2026-07-11 08:29:17 PM PT</t>
         </is>
       </c>
       <c r="C11" t="n">
@@ -1851,7 +1851,7 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>2026-07-11 08:27:17 PM PT</t>
+          <t>2026-07-11 08:29:17 PM PT</t>
         </is>
       </c>
       <c r="C12" t="n">
@@ -1965,7 +1965,7 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>2026-07-11 08:27:18 PM PT</t>
+          <t>2026-07-11 08:29:18 PM PT</t>
         </is>
       </c>
       <c r="C13" t="n">
@@ -1978,7 +1978,7 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Top 8 | 0 out</t>
+          <t>Top 8 | 3 out</t>
         </is>
       </c>
       <c r="F13" t="n">
@@ -1990,13 +1990,13 @@
         </is>
       </c>
       <c r="H13" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="I13" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J13" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="K13" t="inlineStr">
         <is>
@@ -2032,10 +2032,10 @@
         </is>
       </c>
       <c r="R13" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="S13" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="T13" t="n">
         <v>1</v>
@@ -2068,7 +2068,7 @@
         <v>0</v>
       </c>
       <c r="AD13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AE13" s="4" t="n">
         <v>22</v>
@@ -2088,7 +2088,7 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>2026-07-11 08:27:17 PM PT</t>
+          <t>2026-07-11 08:29:17 PM PT</t>
         </is>
       </c>
       <c r="C14" t="n">
@@ -2202,7 +2202,7 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>2026-07-11 08:27:17 PM PT</t>
+          <t>2026-07-11 08:29:17 PM PT</t>
         </is>
       </c>
       <c r="C15" t="n">
@@ -2316,7 +2316,7 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>2026-07-11 08:27:17 PM PT</t>
+          <t>2026-07-11 08:29:18 PM PT</t>
         </is>
       </c>
       <c r="C16" t="n">
@@ -2430,7 +2430,7 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>2026-07-11 08:27:18 PM PT</t>
+          <t>2026-07-11 08:29:18 PM PT</t>
         </is>
       </c>
       <c r="C17" t="n">
@@ -2443,7 +2443,7 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Top 8 | 0 out</t>
+          <t>Top 8 | 3 out</t>
         </is>
       </c>
       <c r="F17" t="n">
@@ -2455,13 +2455,13 @@
         </is>
       </c>
       <c r="H17" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="I17" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J17" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="K17" t="inlineStr">
         <is>
@@ -2553,7 +2553,7 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>2026-07-11 08:27:17 PM PT</t>
+          <t>2026-07-11 08:29:17 PM PT</t>
         </is>
       </c>
       <c r="C18" t="n">
@@ -2667,7 +2667,7 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>2026-07-11 08:27:18 PM PT</t>
+          <t>2026-07-11 08:29:18 PM PT</t>
         </is>
       </c>
       <c r="C19" t="n">
@@ -2781,7 +2781,7 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>2026-07-11 08:27:17 PM PT</t>
+          <t>2026-07-11 08:29:17 PM PT</t>
         </is>
       </c>
       <c r="C20" t="n">
@@ -2895,7 +2895,7 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>2026-07-11 08:27:17 PM PT</t>
+          <t>2026-07-11 08:29:17 PM PT</t>
         </is>
       </c>
       <c r="C21" t="n">
@@ -3009,7 +3009,7 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>2026-07-11 08:27:18 PM PT</t>
+          <t>2026-07-11 08:29:18 PM PT</t>
         </is>
       </c>
       <c r="C22" t="n">
@@ -3022,7 +3022,7 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Bottom 7 | 1 out</t>
+          <t>Bottom 7 | 3 out</t>
         </is>
       </c>
       <c r="F22" t="n">
@@ -3034,13 +3034,13 @@
         </is>
       </c>
       <c r="H22" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="I22" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J22" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="K22" t="inlineStr">
         <is>
@@ -3132,7 +3132,7 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>2026-07-11 08:27:17 PM PT</t>
+          <t>2026-07-11 08:29:17 PM PT</t>
         </is>
       </c>
       <c r="C23" t="n">
@@ -3246,7 +3246,7 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>2026-07-11 08:27:17 PM PT</t>
+          <t>2026-07-11 08:29:17 PM PT</t>
         </is>
       </c>
       <c r="C24" t="n">
@@ -3360,7 +3360,7 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>2026-07-11 08:27:18 PM PT</t>
+          <t>2026-07-11 08:29:18 PM PT</t>
         </is>
       </c>
       <c r="C25" t="n">
@@ -3474,7 +3474,7 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>2026-07-11 08:27:16 PM PT</t>
+          <t>2026-07-11 08:29:16 PM PT</t>
         </is>
       </c>
       <c r="C26" t="n">
@@ -3588,7 +3588,7 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>2026-07-11 08:27:16 PM PT</t>
+          <t>2026-07-11 08:29:17 PM PT</t>
         </is>
       </c>
       <c r="C27" t="n">
@@ -3702,7 +3702,7 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>2026-07-11 08:27:17 PM PT</t>
+          <t>2026-07-11 08:29:17 PM PT</t>
         </is>
       </c>
       <c r="C28" t="n">
@@ -3816,7 +3816,7 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>2026-07-11 08:27:18 PM PT</t>
+          <t>2026-07-11 08:29:18 PM PT</t>
         </is>
       </c>
       <c r="C29" t="n">
@@ -3930,7 +3930,7 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>2026-07-11 08:27:18 PM PT</t>
+          <t>2026-07-11 08:29:18 PM PT</t>
         </is>
       </c>
       <c r="C30" t="n">
@@ -4044,7 +4044,7 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>2026-07-11 08:27:17 PM PT</t>
+          <t>2026-07-11 08:29:17 PM PT</t>
         </is>
       </c>
       <c r="C31" t="n">
@@ -4158,7 +4158,7 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>2026-07-11 08:27:17 PM PT</t>
+          <t>2026-07-11 08:29:17 PM PT</t>
         </is>
       </c>
       <c r="C32" t="n">
@@ -4272,7 +4272,7 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>2026-07-11 08:27:17 PM PT</t>
+          <t>2026-07-11 08:29:18 PM PT</t>
         </is>
       </c>
       <c r="C33" t="n">
@@ -4386,7 +4386,7 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>2026-07-11 08:27:16 PM PT</t>
+          <t>2026-07-11 08:29:16 PM PT</t>
         </is>
       </c>
       <c r="C34" t="n">
@@ -4500,7 +4500,7 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>2026-07-11 08:27:16 PM PT</t>
+          <t>2026-07-11 08:29:16 PM PT</t>
         </is>
       </c>
       <c r="C35" t="n">
@@ -4614,7 +4614,7 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>2026-07-11 08:27:18 PM PT</t>
+          <t>2026-07-11 08:29:18 PM PT</t>
         </is>
       </c>
       <c r="C36" t="n">
@@ -4627,7 +4627,7 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Top 8 | 0 out</t>
+          <t>Top 8 | 3 out</t>
         </is>
       </c>
       <c r="F36" t="n">
@@ -4639,13 +4639,13 @@
         </is>
       </c>
       <c r="H36" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="I36" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J36" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="K36" t="inlineStr">
         <is>
@@ -4737,7 +4737,7 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>2026-07-11 08:27:17 PM PT</t>
+          <t>2026-07-11 08:29:17 PM PT</t>
         </is>
       </c>
       <c r="C37" t="n">
@@ -4851,7 +4851,7 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>2026-07-11 08:27:16 PM PT</t>
+          <t>2026-07-11 08:29:16 PM PT</t>
         </is>
       </c>
       <c r="C38" t="n">
@@ -4965,7 +4965,7 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>2026-07-11 08:27:17 PM PT</t>
+          <t>2026-07-11 08:29:17 PM PT</t>
         </is>
       </c>
       <c r="C39" t="n">
@@ -5079,7 +5079,7 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>2026-07-11 08:27:16 PM PT</t>
+          <t>2026-07-11 08:29:16 PM PT</t>
         </is>
       </c>
       <c r="C40" t="n">
@@ -5193,7 +5193,7 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>2026-07-11 08:27:18 PM PT</t>
+          <t>2026-07-11 08:29:18 PM PT</t>
         </is>
       </c>
       <c r="C41" t="n">
@@ -5206,7 +5206,7 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>Bottom 7 | 1 out</t>
+          <t>Bottom 7 | 3 out</t>
         </is>
       </c>
       <c r="F41" t="n">
@@ -5218,13 +5218,13 @@
         </is>
       </c>
       <c r="H41" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="I41" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J41" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="K41" t="inlineStr">
         <is>
@@ -5316,7 +5316,7 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>2026-07-11 08:27:18 PM PT</t>
+          <t>2026-07-11 08:29:18 PM PT</t>
         </is>
       </c>
       <c r="C42" t="n">
@@ -5430,7 +5430,7 @@
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>2026-07-11 08:27:17 PM PT</t>
+          <t>2026-07-11 08:29:17 PM PT</t>
         </is>
       </c>
       <c r="C43" t="n">
@@ -5544,7 +5544,7 @@
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>2026-07-11 08:27:17 PM PT</t>
+          <t>2026-07-11 08:29:17 PM PT</t>
         </is>
       </c>
       <c r="C44" t="n">
@@ -5658,7 +5658,7 @@
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>2026-07-11 08:27:18 PM PT</t>
+          <t>2026-07-11 08:29:18 PM PT</t>
         </is>
       </c>
       <c r="C45" t="n">
@@ -5772,7 +5772,7 @@
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>2026-07-11 08:27:17 PM PT</t>
+          <t>2026-07-11 08:29:17 PM PT</t>
         </is>
       </c>
       <c r="C46" t="n">
@@ -5886,7 +5886,7 @@
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>2026-07-11 08:27:16 PM PT</t>
+          <t>2026-07-11 08:29:17 PM PT</t>
         </is>
       </c>
       <c r="C47" t="n">
@@ -6000,7 +6000,7 @@
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>2026-07-11 08:27:17 PM PT</t>
+          <t>2026-07-11 08:29:18 PM PT</t>
         </is>
       </c>
       <c r="C48" t="n">
@@ -6114,7 +6114,7 @@
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>2026-07-11 08:27:17 PM PT</t>
+          <t>2026-07-11 08:29:17 PM PT</t>
         </is>
       </c>
       <c r="C49" t="n">
@@ -6228,7 +6228,7 @@
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>2026-07-11 08:27:16 PM PT</t>
+          <t>2026-07-11 08:29:16 PM PT</t>
         </is>
       </c>
       <c r="C50" t="n">
@@ -6342,7 +6342,7 @@
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>2026-07-11 08:27:18 PM PT</t>
+          <t>2026-07-11 08:29:18 PM PT</t>
         </is>
       </c>
       <c r="C51" t="n">
@@ -6355,7 +6355,7 @@
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>Bottom 7 | 1 out</t>
+          <t>Bottom 7 | 3 out</t>
         </is>
       </c>
       <c r="F51" t="n">
@@ -6367,13 +6367,13 @@
         </is>
       </c>
       <c r="H51" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="I51" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J51" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="K51" t="inlineStr">
         <is>
@@ -6465,7 +6465,7 @@
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>2026-07-11 08:27:18 PM PT</t>
+          <t>2026-07-11 08:29:18 PM PT</t>
         </is>
       </c>
       <c r="C52" t="n">
@@ -6579,7 +6579,7 @@
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>2026-07-11 08:27:18 PM PT</t>
+          <t>2026-07-11 08:29:18 PM PT</t>
         </is>
       </c>
       <c r="C53" t="n">
@@ -6693,7 +6693,7 @@
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>2026-07-11 08:27:17 PM PT</t>
+          <t>2026-07-11 08:29:17 PM PT</t>
         </is>
       </c>
       <c r="C54" t="n">
@@ -6807,7 +6807,7 @@
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>2026-07-11 08:27:16 PM PT</t>
+          <t>2026-07-11 08:29:16 PM PT</t>
         </is>
       </c>
       <c r="C55" t="n">
@@ -6921,7 +6921,7 @@
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>2026-07-11 08:27:16 PM PT</t>
+          <t>2026-07-11 08:29:16 PM PT</t>
         </is>
       </c>
       <c r="C56" t="n">
@@ -7035,7 +7035,7 @@
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>2026-07-11 08:27:16 PM PT</t>
+          <t>2026-07-11 08:29:16 PM PT</t>
         </is>
       </c>
       <c r="C57" t="n">
@@ -7149,7 +7149,7 @@
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>2026-07-11 08:27:17 PM PT</t>
+          <t>2026-07-11 08:29:17 PM PT</t>
         </is>
       </c>
       <c r="C58" t="n">
@@ -7263,7 +7263,7 @@
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>2026-07-11 08:27:17 PM PT</t>
+          <t>2026-07-11 08:29:17 PM PT</t>
         </is>
       </c>
       <c r="C59" t="n">
@@ -7377,7 +7377,7 @@
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>2026-07-11 08:27:16 PM PT</t>
+          <t>2026-07-11 08:29:16 PM PT</t>
         </is>
       </c>
       <c r="C60" t="n">
@@ -7491,7 +7491,7 @@
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>2026-07-11 08:27:16 PM PT</t>
+          <t>2026-07-11 08:29:16 PM PT</t>
         </is>
       </c>
       <c r="C61" t="n">
@@ -7605,7 +7605,7 @@
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>2026-07-11 08:27:16 PM PT</t>
+          <t>2026-07-11 08:29:16 PM PT</t>
         </is>
       </c>
       <c r="C62" t="n">
@@ -7719,7 +7719,7 @@
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>2026-07-11 08:27:18 PM PT</t>
+          <t>2026-07-11 08:29:18 PM PT</t>
         </is>
       </c>
       <c r="C63" t="n">
@@ -7732,7 +7732,7 @@
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>Top 8 | 0 out</t>
+          <t>Top 8 | 3 out</t>
         </is>
       </c>
       <c r="F63" t="n">
@@ -7744,13 +7744,13 @@
         </is>
       </c>
       <c r="H63" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="I63" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J63" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="K63" t="inlineStr">
         <is>
@@ -7842,7 +7842,7 @@
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>2026-07-11 08:27:18 PM PT</t>
+          <t>2026-07-11 08:29:18 PM PT</t>
         </is>
       </c>
       <c r="C64" t="n">
@@ -7855,7 +7855,7 @@
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>Bottom 7 | 1 out</t>
+          <t>Bottom 7 | 3 out</t>
         </is>
       </c>
       <c r="F64" t="n">
@@ -7867,13 +7867,13 @@
         </is>
       </c>
       <c r="H64" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="I64" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J64" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="K64" t="inlineStr">
         <is>
@@ -7965,7 +7965,7 @@
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>2026-07-11 08:27:16 PM PT</t>
+          <t>2026-07-11 08:29:17 PM PT</t>
         </is>
       </c>
       <c r="C65" t="n">
@@ -8079,7 +8079,7 @@
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>2026-07-11 08:27:17 PM PT</t>
+          <t>2026-07-11 08:29:17 PM PT</t>
         </is>
       </c>
       <c r="C66" t="n">
@@ -8193,7 +8193,7 @@
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>2026-07-11 08:27:18 PM PT</t>
+          <t>2026-07-11 08:29:18 PM PT</t>
         </is>
       </c>
       <c r="C67" t="n">
@@ -8206,7 +8206,7 @@
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>Top 8 | 0 out</t>
+          <t>Top 8 | 3 out</t>
         </is>
       </c>
       <c r="F67" t="n">
@@ -8218,13 +8218,13 @@
         </is>
       </c>
       <c r="H67" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="I67" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J67" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="K67" t="inlineStr">
         <is>
@@ -8316,7 +8316,7 @@
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>2026-07-11 08:27:17 PM PT</t>
+          <t>2026-07-11 08:29:17 PM PT</t>
         </is>
       </c>
       <c r="C68" t="n">
@@ -8430,7 +8430,7 @@
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>2026-07-11 08:27:16 PM PT</t>
+          <t>2026-07-11 08:29:17 PM PT</t>
         </is>
       </c>
       <c r="C69" t="n">
@@ -8544,7 +8544,7 @@
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>2026-07-11 08:27:16 PM PT</t>
+          <t>2026-07-11 08:29:16 PM PT</t>
         </is>
       </c>
       <c r="C70" t="n">
@@ -8658,7 +8658,7 @@
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>2026-07-11 08:27:18 PM PT</t>
+          <t>2026-07-11 08:29:18 PM PT</t>
         </is>
       </c>
       <c r="C71" t="n">
@@ -8671,7 +8671,7 @@
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>Bottom 7 | 1 out</t>
+          <t>Bottom 7 | 3 out</t>
         </is>
       </c>
       <c r="F71" t="n">
@@ -8683,13 +8683,13 @@
         </is>
       </c>
       <c r="H71" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="I71" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J71" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="K71" t="inlineStr">
         <is>
@@ -8781,7 +8781,7 @@
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>2026-07-11 08:27:16 PM PT</t>
+          <t>2026-07-11 08:29:16 PM PT</t>
         </is>
       </c>
       <c r="C72" t="n">
@@ -8895,7 +8895,7 @@
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>2026-07-11 08:27:17 PM PT</t>
+          <t>2026-07-11 08:29:17 PM PT</t>
         </is>
       </c>
       <c r="C73" t="n">
@@ -9009,7 +9009,7 @@
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>2026-07-11 08:27:16 PM PT</t>
+          <t>2026-07-11 08:29:16 PM PT</t>
         </is>
       </c>
       <c r="C74" t="n">
@@ -9123,7 +9123,7 @@
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>2026-07-11 08:27:18 PM PT</t>
+          <t>2026-07-11 08:29:18 PM PT</t>
         </is>
       </c>
       <c r="C75" t="n">
@@ -9136,7 +9136,7 @@
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>Top 8 | 0 out</t>
+          <t>Top 8 | 3 out</t>
         </is>
       </c>
       <c r="F75" t="n">
@@ -9148,13 +9148,13 @@
         </is>
       </c>
       <c r="H75" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="I75" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J75" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="K75" t="inlineStr">
         <is>
@@ -9190,10 +9190,10 @@
         </is>
       </c>
       <c r="R75" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="S75" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="T75" t="n">
         <v>1</v>
@@ -9246,7 +9246,7 @@
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>2026-07-11 08:27:18 PM PT</t>
+          <t>2026-07-11 08:29:18 PM PT</t>
         </is>
       </c>
       <c r="C76" t="n">
@@ -9360,7 +9360,7 @@
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>2026-07-11 08:27:18 PM PT</t>
+          <t>2026-07-11 08:29:18 PM PT</t>
         </is>
       </c>
       <c r="C77" t="n">
@@ -9474,7 +9474,7 @@
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>2026-07-11 08:27:17 PM PT</t>
+          <t>2026-07-11 08:29:17 PM PT</t>
         </is>
       </c>
       <c r="C78" t="n">
@@ -9588,7 +9588,7 @@
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>2026-07-11 08:27:16 PM PT</t>
+          <t>2026-07-11 08:29:16 PM PT</t>
         </is>
       </c>
       <c r="C79" t="n">
@@ -9702,7 +9702,7 @@
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>2026-07-11 08:27:16 PM PT</t>
+          <t>2026-07-11 08:29:16 PM PT</t>
         </is>
       </c>
       <c r="C80" t="n">
@@ -9816,7 +9816,7 @@
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>2026-07-11 08:27:16 PM PT</t>
+          <t>2026-07-11 08:29:16 PM PT</t>
         </is>
       </c>
       <c r="C81" t="n">
@@ -9930,7 +9930,7 @@
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>2026-07-11 08:27:16 PM PT</t>
+          <t>2026-07-11 08:29:16 PM PT</t>
         </is>
       </c>
       <c r="C82" t="n">
@@ -10044,7 +10044,7 @@
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>2026-07-11 08:27:16 PM PT</t>
+          <t>2026-07-11 08:29:16 PM PT</t>
         </is>
       </c>
       <c r="C83" t="n">
@@ -10158,7 +10158,7 @@
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>2026-07-11 08:27:16 PM PT</t>
+          <t>2026-07-11 08:29:16 PM PT</t>
         </is>
       </c>
       <c r="C84" t="n">
@@ -10272,7 +10272,7 @@
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>2026-07-11 08:27:16 PM PT</t>
+          <t>2026-07-11 08:29:17 PM PT</t>
         </is>
       </c>
       <c r="C85" t="n">
@@ -10386,7 +10386,7 @@
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>2026-07-11 08:27:16 PM PT</t>
+          <t>2026-07-11 08:29:17 PM PT</t>
         </is>
       </c>
       <c r="C86" t="n">
@@ -10500,7 +10500,7 @@
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>2026-07-11 08:27:17 PM PT</t>
+          <t>2026-07-11 08:29:17 PM PT</t>
         </is>
       </c>
       <c r="C87" t="n">
@@ -10614,7 +10614,7 @@
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>2026-07-11 08:27:17 PM PT</t>
+          <t>2026-07-11 08:29:17 PM PT</t>
         </is>
       </c>
       <c r="C88" t="n">
@@ -10728,7 +10728,7 @@
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>2026-07-11 08:27:18 PM PT</t>
+          <t>2026-07-11 08:29:18 PM PT</t>
         </is>
       </c>
       <c r="C89" t="n">
@@ -10741,7 +10741,7 @@
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>Top 8 | 0 out</t>
+          <t>Top 8 | 3 out</t>
         </is>
       </c>
       <c r="F89" t="n">
@@ -10753,13 +10753,13 @@
         </is>
       </c>
       <c r="H89" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="I89" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J89" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="K89" t="inlineStr">
         <is>
@@ -10851,7 +10851,7 @@
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>2026-07-11 08:27:16 PM PT</t>
+          <t>2026-07-11 08:29:17 PM PT</t>
         </is>
       </c>
       <c r="C90" t="n">
@@ -10965,7 +10965,7 @@
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>2026-07-11 08:27:18 PM PT</t>
+          <t>2026-07-11 08:29:18 PM PT</t>
         </is>
       </c>
       <c r="C91" t="n">
@@ -11079,7 +11079,7 @@
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>2026-07-11 08:27:18 PM PT</t>
+          <t>2026-07-11 08:29:18 PM PT</t>
         </is>
       </c>
       <c r="C92" t="n">
@@ -11092,7 +11092,7 @@
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>Bottom 7 | 1 out</t>
+          <t>Bottom 7 | 3 out</t>
         </is>
       </c>
       <c r="F92" t="n">
@@ -11104,13 +11104,13 @@
         </is>
       </c>
       <c r="H92" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="I92" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J92" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="K92" t="inlineStr">
         <is>
@@ -11202,7 +11202,7 @@
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>2026-07-11 08:27:17 PM PT</t>
+          <t>2026-07-11 08:29:17 PM PT</t>
         </is>
       </c>
       <c r="C93" t="n">
@@ -11316,7 +11316,7 @@
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>2026-07-11 08:27:17 PM PT</t>
+          <t>2026-07-11 08:29:17 PM PT</t>
         </is>
       </c>
       <c r="C94" t="n">
@@ -11430,7 +11430,7 @@
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>2026-07-11 08:27:16 PM PT</t>
+          <t>2026-07-11 08:29:17 PM PT</t>
         </is>
       </c>
       <c r="C95" t="n">
@@ -11544,7 +11544,7 @@
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>2026-07-11 08:27:17 PM PT</t>
+          <t>2026-07-11 08:29:18 PM PT</t>
         </is>
       </c>
       <c r="C96" t="n">
@@ -11658,7 +11658,7 @@
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>2026-07-11 08:27:17 PM PT</t>
+          <t>2026-07-11 08:29:18 PM PT</t>
         </is>
       </c>
       <c r="C97" t="n">
@@ -11772,7 +11772,7 @@
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>2026-07-11 08:27:18 PM PT</t>
+          <t>2026-07-11 08:29:18 PM PT</t>
         </is>
       </c>
       <c r="C98" t="n">
@@ -11785,7 +11785,7 @@
       </c>
       <c r="E98" t="inlineStr">
         <is>
-          <t>Bottom 7 | 1 out</t>
+          <t>Bottom 7 | 3 out</t>
         </is>
       </c>
       <c r="F98" t="n">
@@ -11797,13 +11797,13 @@
         </is>
       </c>
       <c r="H98" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="I98" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J98" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="K98" t="inlineStr">
         <is>
@@ -11839,10 +11839,10 @@
         </is>
       </c>
       <c r="R98" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="S98" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="T98" t="n">
         <v>1</v>
@@ -11895,7 +11895,7 @@
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>2026-07-11 08:27:17 PM PT</t>
+          <t>2026-07-11 08:29:17 PM PT</t>
         </is>
       </c>
       <c r="C99" t="n">
@@ -12009,7 +12009,7 @@
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>2026-07-11 08:27:16 PM PT</t>
+          <t>2026-07-11 08:29:16 PM PT</t>
         </is>
       </c>
       <c r="C100" t="n">
@@ -12123,7 +12123,7 @@
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>2026-07-11 08:27:16 PM PT</t>
+          <t>2026-07-11 08:29:16 PM PT</t>
         </is>
       </c>
       <c r="C101" t="n">
@@ -12237,7 +12237,7 @@
       </c>
       <c r="B102" t="inlineStr">
         <is>
-          <t>2026-07-11 08:27:17 PM PT</t>
+          <t>2026-07-11 08:29:17 PM PT</t>
         </is>
       </c>
       <c r="C102" t="n">
@@ -12351,7 +12351,7 @@
       </c>
       <c r="B103" t="inlineStr">
         <is>
-          <t>2026-07-11 08:27:18 PM PT</t>
+          <t>2026-07-11 08:29:18 PM PT</t>
         </is>
       </c>
       <c r="C103" t="n">
@@ -12364,7 +12364,7 @@
       </c>
       <c r="E103" t="inlineStr">
         <is>
-          <t>Top 8 | 0 out</t>
+          <t>Top 8 | 3 out</t>
         </is>
       </c>
       <c r="F103" t="n">
@@ -12376,13 +12376,13 @@
         </is>
       </c>
       <c r="H103" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="I103" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J103" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="K103" t="inlineStr">
         <is>
@@ -12474,7 +12474,7 @@
       </c>
       <c r="B104" t="inlineStr">
         <is>
-          <t>2026-07-11 08:27:17 PM PT</t>
+          <t>2026-07-11 08:29:17 PM PT</t>
         </is>
       </c>
       <c r="C104" t="n">
@@ -12588,7 +12588,7 @@
       </c>
       <c r="B105" t="inlineStr">
         <is>
-          <t>2026-07-11 08:27:17 PM PT</t>
+          <t>2026-07-11 08:29:17 PM PT</t>
         </is>
       </c>
       <c r="C105" t="n">
@@ -12702,7 +12702,7 @@
       </c>
       <c r="B106" t="inlineStr">
         <is>
-          <t>2026-07-11 08:27:17 PM PT</t>
+          <t>2026-07-11 08:29:17 PM PT</t>
         </is>
       </c>
       <c r="C106" t="n">
@@ -12816,7 +12816,7 @@
       </c>
       <c r="B107" t="inlineStr">
         <is>
-          <t>2026-07-11 08:27:16 PM PT</t>
+          <t>2026-07-11 08:29:17 PM PT</t>
         </is>
       </c>
       <c r="C107" t="n">
@@ -12930,7 +12930,7 @@
       </c>
       <c r="B108" t="inlineStr">
         <is>
-          <t>2026-07-11 08:27:16 PM PT</t>
+          <t>2026-07-11 08:29:17 PM PT</t>
         </is>
       </c>
       <c r="C108" t="n">
@@ -13044,7 +13044,7 @@
       </c>
       <c r="B109" t="inlineStr">
         <is>
-          <t>2026-07-11 08:27:17 PM PT</t>
+          <t>2026-07-11 08:29:17 PM PT</t>
         </is>
       </c>
       <c r="C109" t="n">
@@ -13158,7 +13158,7 @@
       </c>
       <c r="B110" t="inlineStr">
         <is>
-          <t>2026-07-11 08:27:16 PM PT</t>
+          <t>2026-07-11 08:29:17 PM PT</t>
         </is>
       </c>
       <c r="C110" t="n">
@@ -13272,7 +13272,7 @@
       </c>
       <c r="B111" t="inlineStr">
         <is>
-          <t>2026-07-11 08:27:18 PM PT</t>
+          <t>2026-07-11 08:29:18 PM PT</t>
         </is>
       </c>
       <c r="C111" t="n">
@@ -13386,7 +13386,7 @@
       </c>
       <c r="B112" t="inlineStr">
         <is>
-          <t>2026-07-11 08:27:17 PM PT</t>
+          <t>2026-07-11 08:29:17 PM PT</t>
         </is>
       </c>
       <c r="C112" t="n">
@@ -13500,7 +13500,7 @@
       </c>
       <c r="B113" t="inlineStr">
         <is>
-          <t>2026-07-11 08:27:16 PM PT</t>
+          <t>2026-07-11 08:29:17 PM PT</t>
         </is>
       </c>
       <c r="C113" t="n">
@@ -13614,7 +13614,7 @@
       </c>
       <c r="B114" t="inlineStr">
         <is>
-          <t>2026-07-11 08:27:17 PM PT</t>
+          <t>2026-07-11 08:29:17 PM PT</t>
         </is>
       </c>
       <c r="C114" t="n">
@@ -13728,7 +13728,7 @@
       </c>
       <c r="B115" t="inlineStr">
         <is>
-          <t>2026-07-11 08:27:18 PM PT</t>
+          <t>2026-07-11 08:29:18 PM PT</t>
         </is>
       </c>
       <c r="C115" t="n">
@@ -13741,7 +13741,7 @@
       </c>
       <c r="E115" t="inlineStr">
         <is>
-          <t>Top 8 | 0 out</t>
+          <t>Top 8 | 3 out</t>
         </is>
       </c>
       <c r="F115" t="n">
@@ -13753,13 +13753,13 @@
         </is>
       </c>
       <c r="H115" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="I115" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J115" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="K115" t="inlineStr">
         <is>
@@ -13851,7 +13851,7 @@
       </c>
       <c r="B116" t="inlineStr">
         <is>
-          <t>2026-07-11 08:27:17 PM PT</t>
+          <t>2026-07-11 08:29:18 PM PT</t>
         </is>
       </c>
       <c r="C116" t="n">
@@ -13965,7 +13965,7 @@
       </c>
       <c r="B117" t="inlineStr">
         <is>
-          <t>2026-07-11 08:27:18 PM PT</t>
+          <t>2026-07-11 08:29:18 PM PT</t>
         </is>
       </c>
       <c r="C117" t="n">
@@ -14079,7 +14079,7 @@
       </c>
       <c r="B118" t="inlineStr">
         <is>
-          <t>2026-07-11 08:27:18 PM PT</t>
+          <t>2026-07-11 08:29:18 PM PT</t>
         </is>
       </c>
       <c r="C118" t="n">
@@ -14193,7 +14193,7 @@
       </c>
       <c r="B119" t="inlineStr">
         <is>
-          <t>2026-07-11 08:27:17 PM PT</t>
+          <t>2026-07-11 08:29:17 PM PT</t>
         </is>
       </c>
       <c r="C119" t="n">
@@ -14307,7 +14307,7 @@
       </c>
       <c r="B120" t="inlineStr">
         <is>
-          <t>2026-07-11 08:27:17 PM PT</t>
+          <t>2026-07-11 08:29:17 PM PT</t>
         </is>
       </c>
       <c r="C120" t="n">
@@ -14421,7 +14421,7 @@
       </c>
       <c r="B121" t="inlineStr">
         <is>
-          <t>2026-07-11 08:27:18 PM PT</t>
+          <t>2026-07-11 08:29:18 PM PT</t>
         </is>
       </c>
       <c r="C121" t="n">
@@ -14535,7 +14535,7 @@
       </c>
       <c r="B122" t="inlineStr">
         <is>
-          <t>2026-07-11 08:27:16 PM PT</t>
+          <t>2026-07-11 08:29:17 PM PT</t>
         </is>
       </c>
       <c r="C122" t="n">
@@ -14649,7 +14649,7 @@
       </c>
       <c r="B123" t="inlineStr">
         <is>
-          <t>2026-07-11 08:27:16 PM PT</t>
+          <t>2026-07-11 08:29:17 PM PT</t>
         </is>
       </c>
       <c r="C123" t="n">
@@ -14763,7 +14763,7 @@
       </c>
       <c r="B124" t="inlineStr">
         <is>
-          <t>2026-07-11 08:27:17 PM PT</t>
+          <t>2026-07-11 08:29:17 PM PT</t>
         </is>
       </c>
       <c r="C124" t="n">
@@ -14877,7 +14877,7 @@
       </c>
       <c r="B125" t="inlineStr">
         <is>
-          <t>2026-07-11 08:27:17 PM PT</t>
+          <t>2026-07-11 08:29:18 PM PT</t>
         </is>
       </c>
       <c r="C125" t="n">
@@ -14991,7 +14991,7 @@
       </c>
       <c r="B126" t="inlineStr">
         <is>
-          <t>2026-07-11 08:27:17 PM PT</t>
+          <t>2026-07-11 08:29:18 PM PT</t>
         </is>
       </c>
       <c r="C126" t="n">
@@ -15105,7 +15105,7 @@
       </c>
       <c r="B127" t="inlineStr">
         <is>
-          <t>2026-07-11 08:27:17 PM PT</t>
+          <t>2026-07-11 08:29:17 PM PT</t>
         </is>
       </c>
       <c r="C127" t="n">
@@ -15219,7 +15219,7 @@
       </c>
       <c r="B128" t="inlineStr">
         <is>
-          <t>2026-07-11 08:27:18 PM PT</t>
+          <t>2026-07-11 08:29:18 PM PT</t>
         </is>
       </c>
       <c r="C128" t="n">
@@ -15232,7 +15232,7 @@
       </c>
       <c r="E128" t="inlineStr">
         <is>
-          <t>Bottom 7 | 1 out</t>
+          <t>Bottom 7 | 3 out</t>
         </is>
       </c>
       <c r="F128" t="n">
@@ -15244,13 +15244,13 @@
         </is>
       </c>
       <c r="H128" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="I128" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J128" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="K128" t="inlineStr">
         <is>
@@ -15342,7 +15342,7 @@
       </c>
       <c r="B129" t="inlineStr">
         <is>
-          <t>2026-07-11 08:27:17 PM PT</t>
+          <t>2026-07-11 08:29:17 PM PT</t>
         </is>
       </c>
       <c r="C129" t="n">
@@ -15456,7 +15456,7 @@
       </c>
       <c r="B130" t="inlineStr">
         <is>
-          <t>2026-07-11 08:27:17 PM PT</t>
+          <t>2026-07-11 08:29:17 PM PT</t>
         </is>
       </c>
       <c r="C130" t="n">
@@ -15570,7 +15570,7 @@
       </c>
       <c r="B131" t="inlineStr">
         <is>
-          <t>2026-07-11 08:27:16 PM PT</t>
+          <t>2026-07-11 08:29:16 PM PT</t>
         </is>
       </c>
       <c r="C131" t="n">
@@ -15684,7 +15684,7 @@
       </c>
       <c r="B132" t="inlineStr">
         <is>
-          <t>2026-07-11 08:27:16 PM PT</t>
+          <t>2026-07-11 08:29:16 PM PT</t>
         </is>
       </c>
       <c r="C132" t="n">
@@ -15798,7 +15798,7 @@
       </c>
       <c r="B133" t="inlineStr">
         <is>
-          <t>2026-07-11 08:27:16 PM PT</t>
+          <t>2026-07-11 08:29:16 PM PT</t>
         </is>
       </c>
       <c r="C133" t="n">
@@ -15912,7 +15912,7 @@
       </c>
       <c r="B134" t="inlineStr">
         <is>
-          <t>2026-07-11 08:27:17 PM PT</t>
+          <t>2026-07-11 08:29:17 PM PT</t>
         </is>
       </c>
       <c r="C134" t="n">
@@ -16026,7 +16026,7 @@
       </c>
       <c r="B135" t="inlineStr">
         <is>
-          <t>2026-07-11 08:27:16 PM PT</t>
+          <t>2026-07-11 08:29:16 PM PT</t>
         </is>
       </c>
       <c r="C135" t="n">
@@ -16140,7 +16140,7 @@
       </c>
       <c r="B136" t="inlineStr">
         <is>
-          <t>2026-07-11 08:27:16 PM PT</t>
+          <t>2026-07-11 08:29:16 PM PT</t>
         </is>
       </c>
       <c r="C136" t="n">
@@ -16254,7 +16254,7 @@
       </c>
       <c r="B137" t="inlineStr">
         <is>
-          <t>2026-07-11 08:27:17 PM PT</t>
+          <t>2026-07-11 08:29:17 PM PT</t>
         </is>
       </c>
       <c r="C137" t="n">
@@ -16368,7 +16368,7 @@
       </c>
       <c r="B138" t="inlineStr">
         <is>
-          <t>2026-07-11 08:27:17 PM PT</t>
+          <t>2026-07-11 08:29:17 PM PT</t>
         </is>
       </c>
       <c r="C138" t="n">
@@ -16482,7 +16482,7 @@
       </c>
       <c r="B139" t="inlineStr">
         <is>
-          <t>2026-07-11 08:27:16 PM PT</t>
+          <t>2026-07-11 08:29:17 PM PT</t>
         </is>
       </c>
       <c r="C139" t="n">
@@ -16596,7 +16596,7 @@
       </c>
       <c r="B140" t="inlineStr">
         <is>
-          <t>2026-07-11 08:27:18 PM PT</t>
+          <t>2026-07-11 08:29:18 PM PT</t>
         </is>
       </c>
       <c r="C140" t="n">
@@ -16710,7 +16710,7 @@
       </c>
       <c r="B141" t="inlineStr">
         <is>
-          <t>2026-07-11 08:27:18 PM PT</t>
+          <t>2026-07-11 08:29:18 PM PT</t>
         </is>
       </c>
       <c r="C141" t="n">
@@ -16824,7 +16824,7 @@
       </c>
       <c r="B142" t="inlineStr">
         <is>
-          <t>2026-07-11 08:27:18 PM PT</t>
+          <t>2026-07-11 08:29:18 PM PT</t>
         </is>
       </c>
       <c r="C142" t="n">
@@ -16938,7 +16938,7 @@
       </c>
       <c r="B143" t="inlineStr">
         <is>
-          <t>2026-07-11 08:27:17 PM PT</t>
+          <t>2026-07-11 08:29:17 PM PT</t>
         </is>
       </c>
       <c r="C143" t="n">
@@ -17052,7 +17052,7 @@
       </c>
       <c r="B144" t="inlineStr">
         <is>
-          <t>2026-07-11 08:27:17 PM PT</t>
+          <t>2026-07-11 08:29:18 PM PT</t>
         </is>
       </c>
       <c r="C144" t="n">
@@ -17166,7 +17166,7 @@
       </c>
       <c r="B145" t="inlineStr">
         <is>
-          <t>2026-07-11 08:27:17 PM PT</t>
+          <t>2026-07-11 08:29:18 PM PT</t>
         </is>
       </c>
       <c r="C145" t="n">
@@ -17280,7 +17280,7 @@
       </c>
       <c r="B146" t="inlineStr">
         <is>
-          <t>2026-07-11 08:27:18 PM PT</t>
+          <t>2026-07-11 08:29:18 PM PT</t>
         </is>
       </c>
       <c r="C146" t="n">
@@ -17293,7 +17293,7 @@
       </c>
       <c r="E146" t="inlineStr">
         <is>
-          <t>Bottom 7 | 1 out</t>
+          <t>Bottom 7 | 3 out</t>
         </is>
       </c>
       <c r="F146" t="n">
@@ -17305,13 +17305,13 @@
         </is>
       </c>
       <c r="H146" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="I146" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J146" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="K146" t="inlineStr">
         <is>
@@ -17403,7 +17403,7 @@
       </c>
       <c r="B147" t="inlineStr">
         <is>
-          <t>2026-07-11 08:27:18 PM PT</t>
+          <t>2026-07-11 08:29:18 PM PT</t>
         </is>
       </c>
       <c r="C147" t="n">
@@ -17517,7 +17517,7 @@
       </c>
       <c r="B148" t="inlineStr">
         <is>
-          <t>2026-07-11 08:27:17 PM PT</t>
+          <t>2026-07-11 08:29:17 PM PT</t>
         </is>
       </c>
       <c r="C148" t="n">
@@ -17631,7 +17631,7 @@
       </c>
       <c r="B149" t="inlineStr">
         <is>
-          <t>2026-07-11 08:27:16 PM PT</t>
+          <t>2026-07-11 08:29:17 PM PT</t>
         </is>
       </c>
       <c r="C149" t="n">
@@ -17745,7 +17745,7 @@
       </c>
       <c r="B150" t="inlineStr">
         <is>
-          <t>2026-07-11 08:27:16 PM PT</t>
+          <t>2026-07-11 08:29:16 PM PT</t>
         </is>
       </c>
       <c r="C150" t="n">
@@ -17859,7 +17859,7 @@
       </c>
       <c r="B151" t="inlineStr">
         <is>
-          <t>2026-07-11 08:27:16 PM PT</t>
+          <t>2026-07-11 08:29:16 PM PT</t>
         </is>
       </c>
       <c r="C151" t="n">
@@ -17973,7 +17973,7 @@
       </c>
       <c r="B152" t="inlineStr">
         <is>
-          <t>2026-07-11 08:27:16 PM PT</t>
+          <t>2026-07-11 08:29:16 PM PT</t>
         </is>
       </c>
       <c r="C152" t="n">
@@ -18087,7 +18087,7 @@
       </c>
       <c r="B153" t="inlineStr">
         <is>
-          <t>2026-07-11 08:27:17 PM PT</t>
+          <t>2026-07-11 08:29:17 PM PT</t>
         </is>
       </c>
       <c r="C153" t="n">
@@ -18201,7 +18201,7 @@
       </c>
       <c r="B154" t="inlineStr">
         <is>
-          <t>2026-07-11 08:27:17 PM PT</t>
+          <t>2026-07-11 08:29:17 PM PT</t>
         </is>
       </c>
       <c r="C154" t="n">
@@ -18315,7 +18315,7 @@
       </c>
       <c r="B155" t="inlineStr">
         <is>
-          <t>2026-07-11 08:27:16 PM PT</t>
+          <t>2026-07-11 08:29:16 PM PT</t>
         </is>
       </c>
       <c r="C155" t="n">
@@ -18429,7 +18429,7 @@
       </c>
       <c r="B156" t="inlineStr">
         <is>
-          <t>2026-07-11 08:27:18 PM PT</t>
+          <t>2026-07-11 08:29:18 PM PT</t>
         </is>
       </c>
       <c r="C156" t="n">
@@ -18442,7 +18442,7 @@
       </c>
       <c r="E156" t="inlineStr">
         <is>
-          <t>Top 8 | 0 out</t>
+          <t>Top 8 | 3 out</t>
         </is>
       </c>
       <c r="F156" t="n">
@@ -18454,13 +18454,13 @@
         </is>
       </c>
       <c r="H156" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="I156" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J156" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="K156" t="inlineStr">
         <is>
@@ -18552,7 +18552,7 @@
       </c>
       <c r="B157" t="inlineStr">
         <is>
-          <t>2026-07-11 08:27:18 PM PT</t>
+          <t>2026-07-11 08:29:18 PM PT</t>
         </is>
       </c>
       <c r="C157" t="n">
@@ -18565,7 +18565,7 @@
       </c>
       <c r="E157" t="inlineStr">
         <is>
-          <t>Top 8 | 0 out</t>
+          <t>Top 8 | 3 out</t>
         </is>
       </c>
       <c r="F157" t="n">
@@ -18577,13 +18577,13 @@
         </is>
       </c>
       <c r="H157" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="I157" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J157" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="K157" t="inlineStr">
         <is>
@@ -18675,7 +18675,7 @@
       </c>
       <c r="B158" t="inlineStr">
         <is>
-          <t>2026-07-11 08:27:18 PM PT</t>
+          <t>2026-07-11 08:29:18 PM PT</t>
         </is>
       </c>
       <c r="C158" t="n">
@@ -18688,7 +18688,7 @@
       </c>
       <c r="E158" t="inlineStr">
         <is>
-          <t>Top 8 | 0 out</t>
+          <t>Top 8 | 3 out</t>
         </is>
       </c>
       <c r="F158" t="n">
@@ -18700,13 +18700,13 @@
         </is>
       </c>
       <c r="H158" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="I158" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J158" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="K158" t="inlineStr">
         <is>
@@ -18798,7 +18798,7 @@
       </c>
       <c r="B159" t="inlineStr">
         <is>
-          <t>2026-07-11 08:27:18 PM PT</t>
+          <t>2026-07-11 08:29:18 PM PT</t>
         </is>
       </c>
       <c r="C159" t="n">
@@ -18811,7 +18811,7 @@
       </c>
       <c r="E159" t="inlineStr">
         <is>
-          <t>Top 8 | 0 out</t>
+          <t>Top 8 | 3 out</t>
         </is>
       </c>
       <c r="F159" t="n">
@@ -18823,13 +18823,13 @@
         </is>
       </c>
       <c r="H159" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="I159" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J159" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="K159" t="inlineStr">
         <is>
@@ -18921,7 +18921,7 @@
       </c>
       <c r="B160" t="inlineStr">
         <is>
-          <t>2026-07-11 08:27:18 PM PT</t>
+          <t>2026-07-11 08:29:18 PM PT</t>
         </is>
       </c>
       <c r="C160" t="n">
@@ -19035,7 +19035,7 @@
       </c>
       <c r="B161" t="inlineStr">
         <is>
-          <t>2026-07-11 08:27:18 PM PT</t>
+          <t>2026-07-11 08:29:18 PM PT</t>
         </is>
       </c>
       <c r="C161" t="n">
@@ -19149,7 +19149,7 @@
       </c>
       <c r="B162" t="inlineStr">
         <is>
-          <t>2026-07-11 08:27:18 PM PT</t>
+          <t>2026-07-11 08:29:18 PM PT</t>
         </is>
       </c>
       <c r="C162" t="n">
@@ -19263,7 +19263,7 @@
       </c>
       <c r="B163" t="inlineStr">
         <is>
-          <t>2026-07-11 08:27:18 PM PT</t>
+          <t>2026-07-11 08:29:18 PM PT</t>
         </is>
       </c>
       <c r="C163" t="n">
@@ -19377,7 +19377,7 @@
       </c>
       <c r="B164" t="inlineStr">
         <is>
-          <t>2026-07-11 08:27:18 PM PT</t>
+          <t>2026-07-11 08:29:18 PM PT</t>
         </is>
       </c>
       <c r="C164" t="n">
@@ -19491,7 +19491,7 @@
       </c>
       <c r="B165" t="inlineStr">
         <is>
-          <t>2026-07-11 08:27:17 PM PT</t>
+          <t>2026-07-11 08:29:17 PM PT</t>
         </is>
       </c>
       <c r="C165" t="n">
@@ -19605,7 +19605,7 @@
       </c>
       <c r="B166" t="inlineStr">
         <is>
-          <t>2026-07-11 08:27:16 PM PT</t>
+          <t>2026-07-11 08:29:17 PM PT</t>
         </is>
       </c>
       <c r="C166" t="n">
@@ -19719,7 +19719,7 @@
       </c>
       <c r="B167" t="inlineStr">
         <is>
-          <t>2026-07-11 08:27:17 PM PT</t>
+          <t>2026-07-11 08:29:17 PM PT</t>
         </is>
       </c>
       <c r="C167" t="n">
@@ -19833,7 +19833,7 @@
       </c>
       <c r="B168" t="inlineStr">
         <is>
-          <t>2026-07-11 08:27:17 PM PT</t>
+          <t>2026-07-11 08:29:17 PM PT</t>
         </is>
       </c>
       <c r="C168" t="n">
@@ -19947,7 +19947,7 @@
       </c>
       <c r="B169" t="inlineStr">
         <is>
-          <t>2026-07-11 08:27:17 PM PT</t>
+          <t>2026-07-11 08:29:17 PM PT</t>
         </is>
       </c>
       <c r="C169" t="n">
@@ -20061,7 +20061,7 @@
       </c>
       <c r="B170" t="inlineStr">
         <is>
-          <t>2026-07-11 08:27:16 PM PT</t>
+          <t>2026-07-11 08:29:16 PM PT</t>
         </is>
       </c>
       <c r="C170" t="n">
@@ -20175,7 +20175,7 @@
       </c>
       <c r="B171" t="inlineStr">
         <is>
-          <t>2026-07-11 08:27:18 PM PT</t>
+          <t>2026-07-11 08:29:18 PM PT</t>
         </is>
       </c>
       <c r="C171" t="n">
@@ -20188,7 +20188,7 @@
       </c>
       <c r="E171" t="inlineStr">
         <is>
-          <t>Bottom 7 | 1 out</t>
+          <t>Bottom 7 | 3 out</t>
         </is>
       </c>
       <c r="F171" t="n">
@@ -20200,13 +20200,13 @@
         </is>
       </c>
       <c r="H171" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="I171" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J171" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="K171" t="inlineStr">
         <is>
@@ -20298,7 +20298,7 @@
       </c>
       <c r="B172" t="inlineStr">
         <is>
-          <t>2026-07-11 08:27:18 PM PT</t>
+          <t>2026-07-11 08:29:18 PM PT</t>
         </is>
       </c>
       <c r="C172" t="n">
@@ -20311,7 +20311,7 @@
       </c>
       <c r="E172" t="inlineStr">
         <is>
-          <t>Bottom 7 | 1 out</t>
+          <t>Bottom 7 | 3 out</t>
         </is>
       </c>
       <c r="F172" t="n">
@@ -20323,13 +20323,13 @@
         </is>
       </c>
       <c r="H172" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="I172" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J172" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="K172" t="inlineStr">
         <is>
@@ -20421,7 +20421,7 @@
       </c>
       <c r="B173" t="inlineStr">
         <is>
-          <t>2026-07-11 08:27:17 PM PT</t>
+          <t>2026-07-11 08:29:17 PM PT</t>
         </is>
       </c>
       <c r="C173" t="n">
@@ -20535,7 +20535,7 @@
       </c>
       <c r="B174" t="inlineStr">
         <is>
-          <t>2026-07-11 08:27:17 PM PT</t>
+          <t>2026-07-11 08:29:17 PM PT</t>
         </is>
       </c>
       <c r="C174" t="n">
@@ -20649,7 +20649,7 @@
       </c>
       <c r="B175" t="inlineStr">
         <is>
-          <t>2026-07-11 08:27:16 PM PT</t>
+          <t>2026-07-11 08:29:16 PM PT</t>
         </is>
       </c>
       <c r="C175" t="n">
@@ -20763,7 +20763,7 @@
       </c>
       <c r="B176" t="inlineStr">
         <is>
-          <t>2026-07-11 08:27:16 PM PT</t>
+          <t>2026-07-11 08:29:16 PM PT</t>
         </is>
       </c>
       <c r="C176" t="n">
@@ -20877,7 +20877,7 @@
       </c>
       <c r="B177" t="inlineStr">
         <is>
-          <t>2026-07-11 08:27:16 PM PT</t>
+          <t>2026-07-11 08:29:16 PM PT</t>
         </is>
       </c>
       <c r="C177" t="n">
@@ -20991,7 +20991,7 @@
       </c>
       <c r="B178" t="inlineStr">
         <is>
-          <t>2026-07-11 08:27:16 PM PT</t>
+          <t>2026-07-11 08:29:16 PM PT</t>
         </is>
       </c>
       <c r="C178" t="n">
@@ -21105,7 +21105,7 @@
       </c>
       <c r="B179" t="inlineStr">
         <is>
-          <t>2026-07-11 08:27:16 PM PT</t>
+          <t>2026-07-11 08:29:16 PM PT</t>
         </is>
       </c>
       <c r="C179" t="n">
@@ -21219,7 +21219,7 @@
       </c>
       <c r="B180" t="inlineStr">
         <is>
-          <t>2026-07-11 08:27:17 PM PT</t>
+          <t>2026-07-11 08:29:17 PM PT</t>
         </is>
       </c>
       <c r="C180" t="n">
@@ -21333,7 +21333,7 @@
       </c>
       <c r="B181" t="inlineStr">
         <is>
-          <t>2026-07-11 08:27:17 PM PT</t>
+          <t>2026-07-11 08:29:17 PM PT</t>
         </is>
       </c>
       <c r="C181" t="n">
@@ -21447,7 +21447,7 @@
       </c>
       <c r="B182" t="inlineStr">
         <is>
-          <t>2026-07-11 08:27:17 PM PT</t>
+          <t>2026-07-11 08:29:17 PM PT</t>
         </is>
       </c>
       <c r="C182" t="n">
@@ -21561,7 +21561,7 @@
       </c>
       <c r="B183" t="inlineStr">
         <is>
-          <t>2026-07-11 08:27:17 PM PT</t>
+          <t>2026-07-11 08:29:17 PM PT</t>
         </is>
       </c>
       <c r="C183" t="n">
@@ -21675,7 +21675,7 @@
       </c>
       <c r="B184" t="inlineStr">
         <is>
-          <t>2026-07-11 08:27:16 PM PT</t>
+          <t>2026-07-11 08:29:16 PM PT</t>
         </is>
       </c>
       <c r="C184" t="n">
@@ -21789,7 +21789,7 @@
       </c>
       <c r="B185" t="inlineStr">
         <is>
-          <t>2026-07-11 08:27:16 PM PT</t>
+          <t>2026-07-11 08:29:16 PM PT</t>
         </is>
       </c>
       <c r="C185" t="n">
@@ -21903,7 +21903,7 @@
       </c>
       <c r="B186" t="inlineStr">
         <is>
-          <t>2026-07-11 08:27:17 PM PT</t>
+          <t>2026-07-11 08:29:17 PM PT</t>
         </is>
       </c>
       <c r="C186" t="n">
@@ -22017,7 +22017,7 @@
       </c>
       <c r="B187" t="inlineStr">
         <is>
-          <t>2026-07-11 08:27:16 PM PT</t>
+          <t>2026-07-11 08:29:17 PM PT</t>
         </is>
       </c>
       <c r="C187" t="n">
@@ -22131,7 +22131,7 @@
       </c>
       <c r="B188" t="inlineStr">
         <is>
-          <t>2026-07-11 08:27:17 PM PT</t>
+          <t>2026-07-11 08:29:17 PM PT</t>
         </is>
       </c>
       <c r="C188" t="n">
@@ -22245,7 +22245,7 @@
       </c>
       <c r="B189" t="inlineStr">
         <is>
-          <t>2026-07-11 08:27:17 PM PT</t>
+          <t>2026-07-11 08:29:18 PM PT</t>
         </is>
       </c>
       <c r="C189" t="n">
@@ -22359,7 +22359,7 @@
       </c>
       <c r="B190" t="inlineStr">
         <is>
-          <t>2026-07-11 08:27:18 PM PT</t>
+          <t>2026-07-11 08:29:18 PM PT</t>
         </is>
       </c>
       <c r="C190" t="n">
@@ -22372,7 +22372,7 @@
       </c>
       <c r="E190" t="inlineStr">
         <is>
-          <t>Top 8 | 0 out</t>
+          <t>Top 8 | 3 out</t>
         </is>
       </c>
       <c r="F190" t="n">
@@ -22384,13 +22384,13 @@
         </is>
       </c>
       <c r="H190" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="I190" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J190" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="K190" t="inlineStr">
         <is>
@@ -22482,7 +22482,7 @@
       </c>
       <c r="B191" t="inlineStr">
         <is>
-          <t>2026-07-11 08:27:17 PM PT</t>
+          <t>2026-07-11 08:29:17 PM PT</t>
         </is>
       </c>
       <c r="C191" t="n">
@@ -22596,7 +22596,7 @@
       </c>
       <c r="B192" t="inlineStr">
         <is>
-          <t>2026-07-11 08:27:17 PM PT</t>
+          <t>2026-07-11 08:29:17 PM PT</t>
         </is>
       </c>
       <c r="C192" t="n">
@@ -22710,7 +22710,7 @@
       </c>
       <c r="B193" t="inlineStr">
         <is>
-          <t>2026-07-11 08:27:18 PM PT</t>
+          <t>2026-07-11 08:29:18 PM PT</t>
         </is>
       </c>
       <c r="C193" t="n">
@@ -22723,7 +22723,7 @@
       </c>
       <c r="E193" t="inlineStr">
         <is>
-          <t>Bottom 7 | 1 out</t>
+          <t>Bottom 7 | 3 out</t>
         </is>
       </c>
       <c r="F193" t="n">
@@ -22735,13 +22735,13 @@
         </is>
       </c>
       <c r="H193" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="I193" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J193" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="K193" t="inlineStr">
         <is>
@@ -22833,7 +22833,7 @@
       </c>
       <c r="B194" t="inlineStr">
         <is>
-          <t>2026-07-11 08:27:18 PM PT</t>
+          <t>2026-07-11 08:29:18 PM PT</t>
         </is>
       </c>
       <c r="C194" t="n">
@@ -22846,7 +22846,7 @@
       </c>
       <c r="E194" t="inlineStr">
         <is>
-          <t>Bottom 7 | 1 out</t>
+          <t>Bottom 7 | 3 out</t>
         </is>
       </c>
       <c r="F194" t="n">
@@ -22858,13 +22858,13 @@
         </is>
       </c>
       <c r="H194" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="I194" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J194" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="K194" t="inlineStr">
         <is>
@@ -22956,7 +22956,7 @@
       </c>
       <c r="B195" t="inlineStr">
         <is>
-          <t>2026-07-11 08:27:16 PM PT</t>
+          <t>2026-07-11 08:29:17 PM PT</t>
         </is>
       </c>
       <c r="C195" t="n">
@@ -23070,7 +23070,7 @@
       </c>
       <c r="B196" t="inlineStr">
         <is>
-          <t>2026-07-11 08:27:18 PM PT</t>
+          <t>2026-07-11 08:29:18 PM PT</t>
         </is>
       </c>
       <c r="C196" t="n">
@@ -23184,7 +23184,7 @@
       </c>
       <c r="B197" t="inlineStr">
         <is>
-          <t>2026-07-11 08:27:18 PM PT</t>
+          <t>2026-07-11 08:29:18 PM PT</t>
         </is>
       </c>
       <c r="C197" t="n">
@@ -23298,7 +23298,7 @@
       </c>
       <c r="B198" t="inlineStr">
         <is>
-          <t>2026-07-11 08:27:17 PM PT</t>
+          <t>2026-07-11 08:29:17 PM PT</t>
         </is>
       </c>
       <c r="C198" t="n">
@@ -23412,7 +23412,7 @@
       </c>
       <c r="B199" t="inlineStr">
         <is>
-          <t>2026-07-11 08:27:17 PM PT</t>
+          <t>2026-07-11 08:29:17 PM PT</t>
         </is>
       </c>
       <c r="C199" t="n">
@@ -23526,7 +23526,7 @@
       </c>
       <c r="B200" t="inlineStr">
         <is>
-          <t>2026-07-11 08:27:17 PM PT</t>
+          <t>2026-07-11 08:29:17 PM PT</t>
         </is>
       </c>
       <c r="C200" t="n">
@@ -23640,7 +23640,7 @@
       </c>
       <c r="B201" t="inlineStr">
         <is>
-          <t>2026-07-11 08:27:17 PM PT</t>
+          <t>2026-07-11 08:29:17 PM PT</t>
         </is>
       </c>
       <c r="C201" t="n">
@@ -23754,7 +23754,7 @@
       </c>
       <c r="B202" t="inlineStr">
         <is>
-          <t>2026-07-11 08:27:18 PM PT</t>
+          <t>2026-07-11 08:29:18 PM PT</t>
         </is>
       </c>
       <c r="C202" t="n">
@@ -23868,7 +23868,7 @@
       </c>
       <c r="B203" t="inlineStr">
         <is>
-          <t>2026-07-11 08:27:16 PM PT</t>
+          <t>2026-07-11 08:29:17 PM PT</t>
         </is>
       </c>
       <c r="C203" t="n">
@@ -23982,7 +23982,7 @@
       </c>
       <c r="B204" t="inlineStr">
         <is>
-          <t>2026-07-11 08:27:16 PM PT</t>
+          <t>2026-07-11 08:29:17 PM PT</t>
         </is>
       </c>
       <c r="C204" t="n">
@@ -24096,7 +24096,7 @@
       </c>
       <c r="B205" t="inlineStr">
         <is>
-          <t>2026-07-11 08:27:16 PM PT</t>
+          <t>2026-07-11 08:29:17 PM PT</t>
         </is>
       </c>
       <c r="C205" t="n">
@@ -24210,7 +24210,7 @@
       </c>
       <c r="B206" t="inlineStr">
         <is>
-          <t>2026-07-11 08:27:16 PM PT</t>
+          <t>2026-07-11 08:29:17 PM PT</t>
         </is>
       </c>
       <c r="C206" t="n">
@@ -24324,7 +24324,7 @@
       </c>
       <c r="B207" t="inlineStr">
         <is>
-          <t>2026-07-11 08:27:16 PM PT</t>
+          <t>2026-07-11 08:29:17 PM PT</t>
         </is>
       </c>
       <c r="C207" t="n">
@@ -24438,7 +24438,7 @@
       </c>
       <c r="B208" t="inlineStr">
         <is>
-          <t>2026-07-11 08:27:17 PM PT</t>
+          <t>2026-07-11 08:29:17 PM PT</t>
         </is>
       </c>
       <c r="C208" t="n">
@@ -24552,7 +24552,7 @@
       </c>
       <c r="B209" t="inlineStr">
         <is>
-          <t>2026-07-11 08:27:17 PM PT</t>
+          <t>2026-07-11 08:29:18 PM PT</t>
         </is>
       </c>
       <c r="C209" t="n">
@@ -24666,7 +24666,7 @@
       </c>
       <c r="B210" t="inlineStr">
         <is>
-          <t>2026-07-11 08:27:17 PM PT</t>
+          <t>2026-07-11 08:29:17 PM PT</t>
         </is>
       </c>
       <c r="C210" t="n">
@@ -24780,7 +24780,7 @@
       </c>
       <c r="B211" t="inlineStr">
         <is>
-          <t>2026-07-11 08:27:17 PM PT</t>
+          <t>2026-07-11 08:29:17 PM PT</t>
         </is>
       </c>
       <c r="C211" t="n">
@@ -24894,7 +24894,7 @@
       </c>
       <c r="B212" t="inlineStr">
         <is>
-          <t>2026-07-11 08:27:17 PM PT</t>
+          <t>2026-07-11 08:29:17 PM PT</t>
         </is>
       </c>
       <c r="C212" t="n">
@@ -25008,7 +25008,7 @@
       </c>
       <c r="B213" t="inlineStr">
         <is>
-          <t>2026-07-11 08:27:16 PM PT</t>
+          <t>2026-07-11 08:29:16 PM PT</t>
         </is>
       </c>
       <c r="C213" t="n">
@@ -25122,7 +25122,7 @@
       </c>
       <c r="B214" t="inlineStr">
         <is>
-          <t>2026-07-11 08:27:17 PM PT</t>
+          <t>2026-07-11 08:29:17 PM PT</t>
         </is>
       </c>
       <c r="C214" t="n">
@@ -25236,7 +25236,7 @@
       </c>
       <c r="B215" t="inlineStr">
         <is>
-          <t>2026-07-11 08:27:17 PM PT</t>
+          <t>2026-07-11 08:29:17 PM PT</t>
         </is>
       </c>
       <c r="C215" t="n">
@@ -25350,7 +25350,7 @@
       </c>
       <c r="B216" t="inlineStr">
         <is>
-          <t>2026-07-11 08:27:16 PM PT</t>
+          <t>2026-07-11 08:29:16 PM PT</t>
         </is>
       </c>
       <c r="C216" t="n">
@@ -25464,7 +25464,7 @@
       </c>
       <c r="B217" t="inlineStr">
         <is>
-          <t>2026-07-11 08:27:17 PM PT</t>
+          <t>2026-07-11 08:29:17 PM PT</t>
         </is>
       </c>
       <c r="C217" t="n">
@@ -25578,7 +25578,7 @@
       </c>
       <c r="B218" t="inlineStr">
         <is>
-          <t>2026-07-11 08:27:17 PM PT</t>
+          <t>2026-07-11 08:29:17 PM PT</t>
         </is>
       </c>
       <c r="C218" t="n">
@@ -25692,7 +25692,7 @@
       </c>
       <c r="B219" t="inlineStr">
         <is>
-          <t>2026-07-11 08:27:17 PM PT</t>
+          <t>2026-07-11 08:29:17 PM PT</t>
         </is>
       </c>
       <c r="C219" t="n">
@@ -25806,7 +25806,7 @@
       </c>
       <c r="B220" t="inlineStr">
         <is>
-          <t>2026-07-11 08:27:17 PM PT</t>
+          <t>2026-07-11 08:29:17 PM PT</t>
         </is>
       </c>
       <c r="C220" t="n">
@@ -25920,7 +25920,7 @@
       </c>
       <c r="B221" t="inlineStr">
         <is>
-          <t>2026-07-11 08:27:17 PM PT</t>
+          <t>2026-07-11 08:29:17 PM PT</t>
         </is>
       </c>
       <c r="C221" t="n">
@@ -26034,7 +26034,7 @@
       </c>
       <c r="B222" t="inlineStr">
         <is>
-          <t>2026-07-11 08:27:17 PM PT</t>
+          <t>2026-07-11 08:29:17 PM PT</t>
         </is>
       </c>
       <c r="C222" t="n">
@@ -26148,7 +26148,7 @@
       </c>
       <c r="B223" t="inlineStr">
         <is>
-          <t>2026-07-11 08:27:17 PM PT</t>
+          <t>2026-07-11 08:29:17 PM PT</t>
         </is>
       </c>
       <c r="C223" t="n">
@@ -26262,7 +26262,7 @@
       </c>
       <c r="B224" t="inlineStr">
         <is>
-          <t>2026-07-11 08:27:16 PM PT</t>
+          <t>2026-07-11 08:29:16 PM PT</t>
         </is>
       </c>
       <c r="C224" t="n">
@@ -26376,7 +26376,7 @@
       </c>
       <c r="B225" t="inlineStr">
         <is>
-          <t>2026-07-11 08:27:16 PM PT</t>
+          <t>2026-07-11 08:29:16 PM PT</t>
         </is>
       </c>
       <c r="C225" t="n">
@@ -26490,7 +26490,7 @@
       </c>
       <c r="B226" t="inlineStr">
         <is>
-          <t>2026-07-11 08:27:17 PM PT</t>
+          <t>2026-07-11 08:29:17 PM PT</t>
         </is>
       </c>
       <c r="C226" t="n">
@@ -26604,7 +26604,7 @@
       </c>
       <c r="B227" t="inlineStr">
         <is>
-          <t>2026-07-11 08:27:16 PM PT</t>
+          <t>2026-07-11 08:29:17 PM PT</t>
         </is>
       </c>
       <c r="C227" t="n">
@@ -26718,7 +26718,7 @@
       </c>
       <c r="B228" t="inlineStr">
         <is>
-          <t>2026-07-11 08:27:17 PM PT</t>
+          <t>2026-07-11 08:29:18 PM PT</t>
         </is>
       </c>
       <c r="C228" t="n">
@@ -26832,7 +26832,7 @@
       </c>
       <c r="B229" t="inlineStr">
         <is>
-          <t>2026-07-11 08:27:17 PM PT</t>
+          <t>2026-07-11 08:29:18 PM PT</t>
         </is>
       </c>
       <c r="C229" t="n">
@@ -26946,7 +26946,7 @@
       </c>
       <c r="B230" t="inlineStr">
         <is>
-          <t>2026-07-11 08:27:18 PM PT</t>
+          <t>2026-07-11 08:29:18 PM PT</t>
         </is>
       </c>
       <c r="C230" t="n">
@@ -26959,7 +26959,7 @@
       </c>
       <c r="E230" t="inlineStr">
         <is>
-          <t>Top 8 | 0 out</t>
+          <t>Top 8 | 3 out</t>
         </is>
       </c>
       <c r="F230" t="n">
@@ -26971,13 +26971,13 @@
         </is>
       </c>
       <c r="H230" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="I230" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J230" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="K230" t="inlineStr">
         <is>
@@ -27069,7 +27069,7 @@
       </c>
       <c r="B231" t="inlineStr">
         <is>
-          <t>2026-07-11 08:27:17 PM PT</t>
+          <t>2026-07-11 08:29:17 PM PT</t>
         </is>
       </c>
       <c r="C231" t="n">
@@ -27183,7 +27183,7 @@
       </c>
       <c r="B232" t="inlineStr">
         <is>
-          <t>2026-07-11 08:27:17 PM PT</t>
+          <t>2026-07-11 08:29:17 PM PT</t>
         </is>
       </c>
       <c r="C232" t="n">
@@ -27297,7 +27297,7 @@
       </c>
       <c r="B233" t="inlineStr">
         <is>
-          <t>2026-07-11 08:27:17 PM PT</t>
+          <t>2026-07-11 08:29:17 PM PT</t>
         </is>
       </c>
       <c r="C233" t="n">
@@ -27411,7 +27411,7 @@
       </c>
       <c r="B234" t="inlineStr">
         <is>
-          <t>2026-07-11 08:27:17 PM PT</t>
+          <t>2026-07-11 08:29:17 PM PT</t>
         </is>
       </c>
       <c r="C234" t="n">
@@ -27525,7 +27525,7 @@
       </c>
       <c r="B235" t="inlineStr">
         <is>
-          <t>2026-07-11 08:27:18 PM PT</t>
+          <t>2026-07-11 08:29:18 PM PT</t>
         </is>
       </c>
       <c r="C235" t="n">
@@ -27538,7 +27538,7 @@
       </c>
       <c r="E235" t="inlineStr">
         <is>
-          <t>Bottom 7 | 1 out</t>
+          <t>Bottom 7 | 3 out</t>
         </is>
       </c>
       <c r="F235" t="n">
@@ -27550,13 +27550,13 @@
         </is>
       </c>
       <c r="H235" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="I235" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J235" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="K235" t="inlineStr">
         <is>
@@ -27648,7 +27648,7 @@
       </c>
       <c r="B236" t="inlineStr">
         <is>
-          <t>2026-07-11 08:27:18 PM PT</t>
+          <t>2026-07-11 08:29:18 PM PT</t>
         </is>
       </c>
       <c r="C236" t="n">
@@ -27661,7 +27661,7 @@
       </c>
       <c r="E236" t="inlineStr">
         <is>
-          <t>Bottom 7 | 1 out</t>
+          <t>Bottom 7 | 3 out</t>
         </is>
       </c>
       <c r="F236" t="n">
@@ -27673,13 +27673,13 @@
         </is>
       </c>
       <c r="H236" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="I236" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J236" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="K236" t="inlineStr">
         <is>
@@ -27771,7 +27771,7 @@
       </c>
       <c r="B237" t="inlineStr">
         <is>
-          <t>2026-07-11 08:27:16 PM PT</t>
+          <t>2026-07-11 08:29:17 PM PT</t>
         </is>
       </c>
       <c r="C237" t="n">
@@ -27885,7 +27885,7 @@
       </c>
       <c r="B238" t="inlineStr">
         <is>
-          <t>2026-07-11 08:27:16 PM PT</t>
+          <t>2026-07-11 08:29:17 PM PT</t>
         </is>
       </c>
       <c r="C238" t="n">
@@ -27999,7 +27999,7 @@
       </c>
       <c r="B239" t="inlineStr">
         <is>
-          <t>2026-07-11 08:27:16 PM PT</t>
+          <t>2026-07-11 08:29:17 PM PT</t>
         </is>
       </c>
       <c r="C239" t="n">
@@ -28113,7 +28113,7 @@
       </c>
       <c r="B240" t="inlineStr">
         <is>
-          <t>2026-07-11 08:27:16 PM PT</t>
+          <t>2026-07-11 08:29:17 PM PT</t>
         </is>
       </c>
       <c r="C240" t="n">
@@ -28227,7 +28227,7 @@
       </c>
       <c r="B241" t="inlineStr">
         <is>
-          <t>2026-07-11 08:27:16 PM PT</t>
+          <t>2026-07-11 08:29:17 PM PT</t>
         </is>
       </c>
       <c r="C241" t="n">
@@ -28341,7 +28341,7 @@
       </c>
       <c r="B242" t="inlineStr">
         <is>
-          <t>2026-07-11 08:27:16 PM PT</t>
+          <t>2026-07-11 08:29:17 PM PT</t>
         </is>
       </c>
       <c r="C242" t="n">
@@ -28455,7 +28455,7 @@
       </c>
       <c r="B243" t="inlineStr">
         <is>
-          <t>2026-07-11 08:27:16 PM PT</t>
+          <t>2026-07-11 08:29:17 PM PT</t>
         </is>
       </c>
       <c r="C243" t="n">
@@ -28569,7 +28569,7 @@
       </c>
       <c r="B244" t="inlineStr">
         <is>
-          <t>2026-07-11 08:27:18 PM PT</t>
+          <t>2026-07-11 08:29:18 PM PT</t>
         </is>
       </c>
       <c r="C244" t="n">
@@ -28683,7 +28683,7 @@
       </c>
       <c r="B245" t="inlineStr">
         <is>
-          <t>2026-07-11 08:27:18 PM PT</t>
+          <t>2026-07-11 08:29:18 PM PT</t>
         </is>
       </c>
       <c r="C245" t="n">
@@ -28797,7 +28797,7 @@
       </c>
       <c r="B246" t="inlineStr">
         <is>
-          <t>2026-07-11 08:27:18 PM PT</t>
+          <t>2026-07-11 08:29:18 PM PT</t>
         </is>
       </c>
       <c r="C246" t="n">
@@ -28911,7 +28911,7 @@
       </c>
       <c r="B247" t="inlineStr">
         <is>
-          <t>2026-07-11 08:27:17 PM PT</t>
+          <t>2026-07-11 08:29:17 PM PT</t>
         </is>
       </c>
       <c r="C247" t="n">
@@ -29025,7 +29025,7 @@
       </c>
       <c r="B248" t="inlineStr">
         <is>
-          <t>2026-07-11 08:27:17 PM PT</t>
+          <t>2026-07-11 08:29:17 PM PT</t>
         </is>
       </c>
       <c r="C248" t="n">
@@ -29139,7 +29139,7 @@
       </c>
       <c r="B249" t="inlineStr">
         <is>
-          <t>2026-07-11 08:27:17 PM PT</t>
+          <t>2026-07-11 08:29:17 PM PT</t>
         </is>
       </c>
       <c r="C249" t="n">
@@ -29253,7 +29253,7 @@
       </c>
       <c r="B250" t="inlineStr">
         <is>
-          <t>2026-07-11 08:27:17 PM PT</t>
+          <t>2026-07-11 08:29:17 PM PT</t>
         </is>
       </c>
       <c r="C250" t="n">
@@ -29367,7 +29367,7 @@
       </c>
       <c r="B251" t="inlineStr">
         <is>
-          <t>2026-07-11 08:27:17 PM PT</t>
+          <t>2026-07-11 08:29:17 PM PT</t>
         </is>
       </c>
       <c r="C251" t="n">
@@ -29481,7 +29481,7 @@
       </c>
       <c r="B252" t="inlineStr">
         <is>
-          <t>2026-07-11 08:27:17 PM PT</t>
+          <t>2026-07-11 08:29:17 PM PT</t>
         </is>
       </c>
       <c r="C252" t="n">
@@ -29595,7 +29595,7 @@
       </c>
       <c r="B253" t="inlineStr">
         <is>
-          <t>2026-07-11 08:27:18 PM PT</t>
+          <t>2026-07-11 08:29:18 PM PT</t>
         </is>
       </c>
       <c r="C253" t="n">
@@ -29709,7 +29709,7 @@
       </c>
       <c r="B254" t="inlineStr">
         <is>
-          <t>2026-07-11 08:27:18 PM PT</t>
+          <t>2026-07-11 08:29:18 PM PT</t>
         </is>
       </c>
       <c r="C254" t="n">
@@ -29823,7 +29823,7 @@
       </c>
       <c r="B255" t="inlineStr">
         <is>
-          <t>2026-07-11 08:27:18 PM PT</t>
+          <t>2026-07-11 08:29:18 PM PT</t>
         </is>
       </c>
       <c r="C255" t="n">
@@ -29937,7 +29937,7 @@
       </c>
       <c r="B256" t="inlineStr">
         <is>
-          <t>2026-07-11 08:27:18 PM PT</t>
+          <t>2026-07-11 08:29:18 PM PT</t>
         </is>
       </c>
       <c r="C256" t="n">
@@ -30051,7 +30051,7 @@
       </c>
       <c r="B257" t="inlineStr">
         <is>
-          <t>2026-07-11 08:27:18 PM PT</t>
+          <t>2026-07-11 08:29:18 PM PT</t>
         </is>
       </c>
       <c r="C257" t="n">
@@ -30165,7 +30165,7 @@
       </c>
       <c r="B258" t="inlineStr">
         <is>
-          <t>2026-07-11 08:27:16 PM PT</t>
+          <t>2026-07-11 08:29:17 PM PT</t>
         </is>
       </c>
       <c r="C258" t="n">
@@ -30279,7 +30279,7 @@
       </c>
       <c r="B259" t="inlineStr">
         <is>
-          <t>2026-07-11 08:27:16 PM PT</t>
+          <t>2026-07-11 08:29:17 PM PT</t>
         </is>
       </c>
       <c r="C259" t="n">
@@ -30393,7 +30393,7 @@
       </c>
       <c r="B260" t="inlineStr">
         <is>
-          <t>2026-07-11 08:27:16 PM PT</t>
+          <t>2026-07-11 08:29:17 PM PT</t>
         </is>
       </c>
       <c r="C260" t="n">
@@ -30507,7 +30507,7 @@
       </c>
       <c r="B261" t="inlineStr">
         <is>
-          <t>2026-07-11 08:27:16 PM PT</t>
+          <t>2026-07-11 08:29:17 PM PT</t>
         </is>
       </c>
       <c r="C261" t="n">
@@ -30621,7 +30621,7 @@
       </c>
       <c r="B262" t="inlineStr">
         <is>
-          <t>2026-07-11 08:27:16 PM PT</t>
+          <t>2026-07-11 08:29:17 PM PT</t>
         </is>
       </c>
       <c r="C262" t="n">
@@ -30735,7 +30735,7 @@
       </c>
       <c r="B263" t="inlineStr">
         <is>
-          <t>2026-07-11 08:27:16 PM PT</t>
+          <t>2026-07-11 08:29:17 PM PT</t>
         </is>
       </c>
       <c r="C263" t="n">
@@ -30849,7 +30849,7 @@
       </c>
       <c r="B264" t="inlineStr">
         <is>
-          <t>2026-07-11 08:27:16 PM PT</t>
+          <t>2026-07-11 08:29:17 PM PT</t>
         </is>
       </c>
       <c r="C264" t="n">
@@ -30963,7 +30963,7 @@
       </c>
       <c r="B265" t="inlineStr">
         <is>
-          <t>2026-07-11 08:27:17 PM PT</t>
+          <t>2026-07-11 08:29:17 PM PT</t>
         </is>
       </c>
       <c r="C265" t="n">
@@ -31077,7 +31077,7 @@
       </c>
       <c r="B266" t="inlineStr">
         <is>
-          <t>2026-07-11 08:27:17 PM PT</t>
+          <t>2026-07-11 08:29:17 PM PT</t>
         </is>
       </c>
       <c r="C266" t="n">
@@ -31191,7 +31191,7 @@
       </c>
       <c r="B267" t="inlineStr">
         <is>
-          <t>2026-07-11 08:27:17 PM PT</t>
+          <t>2026-07-11 08:29:17 PM PT</t>
         </is>
       </c>
       <c r="C267" t="n">
@@ -31305,7 +31305,7 @@
       </c>
       <c r="B268" t="inlineStr">
         <is>
-          <t>2026-07-11 08:27:17 PM PT</t>
+          <t>2026-07-11 08:29:17 PM PT</t>
         </is>
       </c>
       <c r="C268" t="n">
@@ -31419,7 +31419,7 @@
       </c>
       <c r="B269" t="inlineStr">
         <is>
-          <t>2026-07-11 08:27:17 PM PT</t>
+          <t>2026-07-11 08:29:18 PM PT</t>
         </is>
       </c>
       <c r="C269" t="n">
@@ -31533,7 +31533,7 @@
       </c>
       <c r="B270" t="inlineStr">
         <is>
-          <t>2026-07-11 08:27:17 PM PT</t>
+          <t>2026-07-11 08:29:18 PM PT</t>
         </is>
       </c>
       <c r="C270" t="n">
@@ -31647,7 +31647,7 @@
       </c>
       <c r="B271" t="inlineStr">
         <is>
-          <t>2026-07-11 08:27:17 PM PT</t>
+          <t>2026-07-11 08:29:18 PM PT</t>
         </is>
       </c>
       <c r="C271" t="n">
@@ -31761,7 +31761,7 @@
       </c>
       <c r="B272" t="inlineStr">
         <is>
-          <t>2026-07-11 08:27:17 PM PT</t>
+          <t>2026-07-11 08:29:17 PM PT</t>
         </is>
       </c>
       <c r="C272" t="n">
@@ -31875,7 +31875,7 @@
       </c>
       <c r="B273" t="inlineStr">
         <is>
-          <t>2026-07-11 08:27:17 PM PT</t>
+          <t>2026-07-11 08:29:17 PM PT</t>
         </is>
       </c>
       <c r="C273" t="n">
@@ -31989,7 +31989,7 @@
       </c>
       <c r="B274" t="inlineStr">
         <is>
-          <t>2026-07-11 08:27:17 PM PT</t>
+          <t>2026-07-11 08:29:17 PM PT</t>
         </is>
       </c>
       <c r="C274" t="n">
@@ -32103,7 +32103,7 @@
       </c>
       <c r="B275" t="inlineStr">
         <is>
-          <t>2026-07-11 08:27:17 PM PT</t>
+          <t>2026-07-11 08:29:17 PM PT</t>
         </is>
       </c>
       <c r="C275" t="n">
@@ -32217,7 +32217,7 @@
       </c>
       <c r="B276" t="inlineStr">
         <is>
-          <t>2026-07-11 08:27:16 PM PT</t>
+          <t>2026-07-11 08:29:16 PM PT</t>
         </is>
       </c>
       <c r="C276" t="n">
@@ -32331,7 +32331,7 @@
       </c>
       <c r="B277" t="inlineStr">
         <is>
-          <t>2026-07-11 08:27:16 PM PT</t>
+          <t>2026-07-11 08:29:16 PM PT</t>
         </is>
       </c>
       <c r="C277" t="n">
@@ -32445,7 +32445,7 @@
       </c>
       <c r="B278" t="inlineStr">
         <is>
-          <t>2026-07-11 08:27:16 PM PT</t>
+          <t>2026-07-11 08:29:16 PM PT</t>
         </is>
       </c>
       <c r="C278" t="n">
@@ -32559,7 +32559,7 @@
       </c>
       <c r="B279" t="inlineStr">
         <is>
-          <t>2026-07-11 08:27:18 PM PT</t>
+          <t>2026-07-11 08:29:18 PM PT</t>
         </is>
       </c>
       <c r="C279" t="n">
@@ -32572,7 +32572,7 @@
       </c>
       <c r="E279" t="inlineStr">
         <is>
-          <t>Bottom 7 | 1 out</t>
+          <t>Bottom 7 | 3 out</t>
         </is>
       </c>
       <c r="F279" t="n">
@@ -32584,13 +32584,13 @@
         </is>
       </c>
       <c r="H279" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="I279" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J279" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="K279" t="inlineStr">
         <is>
@@ -32682,7 +32682,7 @@
       </c>
       <c r="B280" t="inlineStr">
         <is>
-          <t>2026-07-11 08:27:18 PM PT</t>
+          <t>2026-07-11 08:29:18 PM PT</t>
         </is>
       </c>
       <c r="C280" t="n">
@@ -32695,7 +32695,7 @@
       </c>
       <c r="E280" t="inlineStr">
         <is>
-          <t>Bottom 7 | 1 out</t>
+          <t>Bottom 7 | 3 out</t>
         </is>
       </c>
       <c r="F280" t="n">
@@ -32707,13 +32707,13 @@
         </is>
       </c>
       <c r="H280" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="I280" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J280" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="K280" t="inlineStr">
         <is>
@@ -32805,7 +32805,7 @@
       </c>
       <c r="B281" t="inlineStr">
         <is>
-          <t>2026-07-11 08:27:18 PM PT</t>
+          <t>2026-07-11 08:29:18 PM PT</t>
         </is>
       </c>
       <c r="C281" t="n">
@@ -32818,7 +32818,7 @@
       </c>
       <c r="E281" t="inlineStr">
         <is>
-          <t>Bottom 7 | 1 out</t>
+          <t>Bottom 7 | 3 out</t>
         </is>
       </c>
       <c r="F281" t="n">
@@ -32830,13 +32830,13 @@
         </is>
       </c>
       <c r="H281" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="I281" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J281" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="K281" t="inlineStr">
         <is>
@@ -32928,7 +32928,7 @@
       </c>
       <c r="B282" t="inlineStr">
         <is>
-          <t>2026-07-11 08:27:18 PM PT</t>
+          <t>2026-07-11 08:29:18 PM PT</t>
         </is>
       </c>
       <c r="C282" t="n">
@@ -32941,7 +32941,7 @@
       </c>
       <c r="E282" t="inlineStr">
         <is>
-          <t>Bottom 7 | 1 out</t>
+          <t>Bottom 7 | 3 out</t>
         </is>
       </c>
       <c r="F282" t="n">
@@ -32953,13 +32953,13 @@
         </is>
       </c>
       <c r="H282" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="I282" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J282" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="K282" t="inlineStr">
         <is>
@@ -32995,10 +32995,10 @@
         </is>
       </c>
       <c r="R282" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="S282" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="T282" t="n">
         <v>0</v>
@@ -33051,7 +33051,7 @@
       </c>
       <c r="B283" t="inlineStr">
         <is>
-          <t>2026-07-11 08:27:17 PM PT</t>
+          <t>2026-07-11 08:29:17 PM PT</t>
         </is>
       </c>
       <c r="C283" t="n">
@@ -33165,7 +33165,7 @@
       </c>
       <c r="B284" t="inlineStr">
         <is>
-          <t>2026-07-11 08:27:16 PM PT</t>
+          <t>2026-07-11 08:29:16 PM PT</t>
         </is>
       </c>
       <c r="C284" t="n">
@@ -33279,7 +33279,7 @@
       </c>
       <c r="B285" t="inlineStr">
         <is>
-          <t>2026-07-11 08:27:16 PM PT</t>
+          <t>2026-07-11 08:29:16 PM PT</t>
         </is>
       </c>
       <c r="C285" t="n">
@@ -33393,7 +33393,7 @@
       </c>
       <c r="B286" t="inlineStr">
         <is>
-          <t>2026-07-11 08:27:16 PM PT</t>
+          <t>2026-07-11 08:29:16 PM PT</t>
         </is>
       </c>
       <c r="C286" t="n">
@@ -33507,7 +33507,7 @@
       </c>
       <c r="B287" t="inlineStr">
         <is>
-          <t>2026-07-11 08:27:16 PM PT</t>
+          <t>2026-07-11 08:29:16 PM PT</t>
         </is>
       </c>
       <c r="C287" t="n">
@@ -33621,7 +33621,7 @@
       </c>
       <c r="B288" t="inlineStr">
         <is>
-          <t>2026-07-11 08:27:16 PM PT</t>
+          <t>2026-07-11 08:29:16 PM PT</t>
         </is>
       </c>
       <c r="C288" t="n">
@@ -33735,7 +33735,7 @@
       </c>
       <c r="B289" t="inlineStr">
         <is>
-          <t>2026-07-11 08:27:16 PM PT</t>
+          <t>2026-07-11 08:29:16 PM PT</t>
         </is>
       </c>
       <c r="C289" t="n">
@@ -33849,7 +33849,7 @@
       </c>
       <c r="B290" t="inlineStr">
         <is>
-          <t>2026-07-11 08:27:16 PM PT</t>
+          <t>2026-07-11 08:29:16 PM PT</t>
         </is>
       </c>
       <c r="C290" t="n">
@@ -33963,7 +33963,7 @@
       </c>
       <c r="B291" t="inlineStr">
         <is>
-          <t>2026-07-11 08:27:17 PM PT</t>
+          <t>2026-07-11 08:29:17 PM PT</t>
         </is>
       </c>
       <c r="C291" t="n">
@@ -34077,7 +34077,7 @@
       </c>
       <c r="B292" t="inlineStr">
         <is>
-          <t>2026-07-11 08:27:17 PM PT</t>
+          <t>2026-07-11 08:29:17 PM PT</t>
         </is>
       </c>
       <c r="C292" t="n">
@@ -34191,7 +34191,7 @@
       </c>
       <c r="B293" t="inlineStr">
         <is>
-          <t>2026-07-11 08:27:17 PM PT</t>
+          <t>2026-07-11 08:29:17 PM PT</t>
         </is>
       </c>
       <c r="C293" t="n">
@@ -34305,7 +34305,7 @@
       </c>
       <c r="B294" t="inlineStr">
         <is>
-          <t>2026-07-11 08:27:17 PM PT</t>
+          <t>2026-07-11 08:29:17 PM PT</t>
         </is>
       </c>
       <c r="C294" t="n">
@@ -34419,7 +34419,7 @@
       </c>
       <c r="B295" t="inlineStr">
         <is>
-          <t>2026-07-11 08:27:17 PM PT</t>
+          <t>2026-07-11 08:29:17 PM PT</t>
         </is>
       </c>
       <c r="C295" t="n">
@@ -34533,7 +34533,7 @@
       </c>
       <c r="B296" t="inlineStr">
         <is>
-          <t>2026-07-11 08:27:17 PM PT</t>
+          <t>2026-07-11 08:29:17 PM PT</t>
         </is>
       </c>
       <c r="C296" t="n">
@@ -34647,7 +34647,7 @@
       </c>
       <c r="B297" t="inlineStr">
         <is>
-          <t>2026-07-11 08:27:17 PM PT</t>
+          <t>2026-07-11 08:29:17 PM PT</t>
         </is>
       </c>
       <c r="C297" t="n">
@@ -34761,7 +34761,7 @@
       </c>
       <c r="B298" t="inlineStr">
         <is>
-          <t>2026-07-11 08:27:17 PM PT</t>
+          <t>2026-07-11 08:29:17 PM PT</t>
         </is>
       </c>
       <c r="C298" t="n">
@@ -34875,7 +34875,7 @@
       </c>
       <c r="B299" t="inlineStr">
         <is>
-          <t>2026-07-11 08:27:16 PM PT</t>
+          <t>2026-07-11 08:29:16 PM PT</t>
         </is>
       </c>
       <c r="C299" t="n">
@@ -34989,7 +34989,7 @@
       </c>
       <c r="B300" t="inlineStr">
         <is>
-          <t>2026-07-11 08:27:16 PM PT</t>
+          <t>2026-07-11 08:29:16 PM PT</t>
         </is>
       </c>
       <c r="C300" t="n">
@@ -35103,7 +35103,7 @@
       </c>
       <c r="B301" t="inlineStr">
         <is>
-          <t>2026-07-11 08:27:16 PM PT</t>
+          <t>2026-07-11 08:29:16 PM PT</t>
         </is>
       </c>
       <c r="C301" t="n">
@@ -35217,7 +35217,7 @@
       </c>
       <c r="B302" t="inlineStr">
         <is>
-          <t>2026-07-11 08:27:16 PM PT</t>
+          <t>2026-07-11 08:29:16 PM PT</t>
         </is>
       </c>
       <c r="C302" t="n">
@@ -35331,7 +35331,7 @@
       </c>
       <c r="B303" t="inlineStr">
         <is>
-          <t>2026-07-11 08:27:16 PM PT</t>
+          <t>2026-07-11 08:29:16 PM PT</t>
         </is>
       </c>
       <c r="C303" t="n">
@@ -35445,7 +35445,7 @@
       </c>
       <c r="B304" t="inlineStr">
         <is>
-          <t>2026-07-11 08:27:16 PM PT</t>
+          <t>2026-07-11 08:29:16 PM PT</t>
         </is>
       </c>
       <c r="C304" t="n">
@@ -35559,7 +35559,7 @@
       </c>
       <c r="B305" t="inlineStr">
         <is>
-          <t>2026-07-11 08:27:16 PM PT</t>
+          <t>2026-07-11 08:29:16 PM PT</t>
         </is>
       </c>
       <c r="C305" t="n">
@@ -35673,7 +35673,7 @@
       </c>
       <c r="B306" t="inlineStr">
         <is>
-          <t>2026-07-11 08:27:16 PM PT</t>
+          <t>2026-07-11 08:29:16 PM PT</t>
         </is>
       </c>
       <c r="C306" t="n">
@@ -35787,7 +35787,7 @@
       </c>
       <c r="B307" t="inlineStr">
         <is>
-          <t>2026-07-11 08:27:18 PM PT</t>
+          <t>2026-07-11 08:29:18 PM PT</t>
         </is>
       </c>
       <c r="C307" t="n">
@@ -35800,7 +35800,7 @@
       </c>
       <c r="E307" t="inlineStr">
         <is>
-          <t>Top 8 | 0 out</t>
+          <t>Top 8 | 3 out</t>
         </is>
       </c>
       <c r="F307" t="n">
@@ -35812,13 +35812,13 @@
         </is>
       </c>
       <c r="H307" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="I307" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J307" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="K307" t="inlineStr">
         <is>
@@ -35910,7 +35910,7 @@
       </c>
       <c r="B308" t="inlineStr">
         <is>
-          <t>2026-07-11 08:27:17 PM PT</t>
+          <t>2026-07-11 08:29:17 PM PT</t>
         </is>
       </c>
       <c r="C308" t="n">
@@ -36024,7 +36024,7 @@
       </c>
       <c r="B309" t="inlineStr">
         <is>
-          <t>2026-07-11 08:27:17 PM PT</t>
+          <t>2026-07-11 08:29:17 PM PT</t>
         </is>
       </c>
       <c r="C309" t="n">
@@ -36138,7 +36138,7 @@
       </c>
       <c r="B310" t="inlineStr">
         <is>
-          <t>2026-07-11 08:27:17 PM PT</t>
+          <t>2026-07-11 08:29:17 PM PT</t>
         </is>
       </c>
       <c r="C310" t="n">
@@ -36252,7 +36252,7 @@
       </c>
       <c r="B311" t="inlineStr">
         <is>
-          <t>2026-07-11 08:27:17 PM PT</t>
+          <t>2026-07-11 08:29:17 PM PT</t>
         </is>
       </c>
       <c r="C311" t="n">
@@ -36366,7 +36366,7 @@
       </c>
       <c r="B312" t="inlineStr">
         <is>
-          <t>2026-07-11 08:27:17 PM PT</t>
+          <t>2026-07-11 08:29:17 PM PT</t>
         </is>
       </c>
       <c r="C312" t="n">
@@ -36480,7 +36480,7 @@
       </c>
       <c r="B313" t="inlineStr">
         <is>
-          <t>2026-07-11 08:27:16 PM PT</t>
+          <t>2026-07-11 08:29:17 PM PT</t>
         </is>
       </c>
       <c r="C313" t="n">
@@ -36594,7 +36594,7 @@
       </c>
       <c r="B314" t="inlineStr">
         <is>
-          <t>2026-07-11 08:27:16 PM PT</t>
+          <t>2026-07-11 08:29:17 PM PT</t>
         </is>
       </c>
       <c r="C314" t="n">
@@ -36708,7 +36708,7 @@
       </c>
       <c r="B315" t="inlineStr">
         <is>
-          <t>2026-07-11 08:27:18 PM PT</t>
+          <t>2026-07-11 08:29:18 PM PT</t>
         </is>
       </c>
       <c r="C315" t="n">
@@ -36822,7 +36822,7 @@
       </c>
       <c r="B316" t="inlineStr">
         <is>
-          <t>2026-07-11 08:27:18 PM PT</t>
+          <t>2026-07-11 08:29:18 PM PT</t>
         </is>
       </c>
       <c r="C316" t="n">
@@ -36936,7 +36936,7 @@
       </c>
       <c r="B317" t="inlineStr">
         <is>
-          <t>2026-07-11 08:27:18 PM PT</t>
+          <t>2026-07-11 08:29:18 PM PT</t>
         </is>
       </c>
       <c r="C317" t="n">
@@ -37050,7 +37050,7 @@
       </c>
       <c r="B318" t="inlineStr">
         <is>
-          <t>2026-07-11 08:27:18 PM PT</t>
+          <t>2026-07-11 08:29:18 PM PT</t>
         </is>
       </c>
       <c r="C318" t="n">
@@ -37164,7 +37164,7 @@
       </c>
       <c r="B319" t="inlineStr">
         <is>
-          <t>2026-07-11 08:27:17 PM PT</t>
+          <t>2026-07-11 08:29:17 PM PT</t>
         </is>
       </c>
       <c r="C319" t="n">
@@ -37278,7 +37278,7 @@
       </c>
       <c r="B320" t="inlineStr">
         <is>
-          <t>2026-07-11 08:27:17 PM PT</t>
+          <t>2026-07-11 08:29:17 PM PT</t>
         </is>
       </c>
       <c r="C320" t="n">
@@ -37392,7 +37392,7 @@
       </c>
       <c r="B321" t="inlineStr">
         <is>
-          <t>2026-07-11 08:27:17 PM PT</t>
+          <t>2026-07-11 08:29:17 PM PT</t>
         </is>
       </c>
       <c r="C321" t="n">
@@ -37506,7 +37506,7 @@
       </c>
       <c r="B322" t="inlineStr">
         <is>
-          <t>2026-07-11 08:27:17 PM PT</t>
+          <t>2026-07-11 08:29:17 PM PT</t>
         </is>
       </c>
       <c r="C322" t="n">
@@ -37620,7 +37620,7 @@
       </c>
       <c r="B323" t="inlineStr">
         <is>
-          <t>2026-07-11 08:27:17 PM PT</t>
+          <t>2026-07-11 08:29:18 PM PT</t>
         </is>
       </c>
       <c r="C323" t="n">
@@ -37734,7 +37734,7 @@
       </c>
       <c r="B324" t="inlineStr">
         <is>
-          <t>2026-07-11 08:27:17 PM PT</t>
+          <t>2026-07-11 08:29:18 PM PT</t>
         </is>
       </c>
       <c r="C324" t="n">
@@ -37848,7 +37848,7 @@
       </c>
       <c r="B325" t="inlineStr">
         <is>
-          <t>2026-07-11 08:27:17 PM PT</t>
+          <t>2026-07-11 08:29:18 PM PT</t>
         </is>
       </c>
       <c r="C325" t="n">
@@ -37962,7 +37962,7 @@
       </c>
       <c r="B326" t="inlineStr">
         <is>
-          <t>2026-07-11 08:27:17 PM PT</t>
+          <t>2026-07-11 08:29:18 PM PT</t>
         </is>
       </c>
       <c r="C326" t="n">
@@ -38076,7 +38076,7 @@
       </c>
       <c r="B327" t="inlineStr">
         <is>
-          <t>2026-07-11 08:27:17 PM PT</t>
+          <t>2026-07-11 08:29:18 PM PT</t>
         </is>
       </c>
       <c r="C327" t="n">
@@ -38190,7 +38190,7 @@
       </c>
       <c r="B328" t="inlineStr">
         <is>
-          <t>2026-07-11 08:27:18 PM PT</t>
+          <t>2026-07-11 08:29:18 PM PT</t>
         </is>
       </c>
       <c r="C328" t="n">
@@ -38203,7 +38203,7 @@
       </c>
       <c r="E328" t="inlineStr">
         <is>
-          <t>Top 8 | 0 out</t>
+          <t>Top 8 | 3 out</t>
         </is>
       </c>
       <c r="F328" t="n">
@@ -38215,13 +38215,13 @@
         </is>
       </c>
       <c r="H328" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="I328" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J328" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="K328" t="inlineStr">
         <is>
@@ -38313,7 +38313,7 @@
       </c>
       <c r="B329" t="inlineStr">
         <is>
-          <t>2026-07-11 08:27:17 PM PT</t>
+          <t>2026-07-11 08:29:17 PM PT</t>
         </is>
       </c>
       <c r="C329" t="n">
@@ -38427,7 +38427,7 @@
       </c>
       <c r="B330" t="inlineStr">
         <is>
-          <t>2026-07-11 08:27:17 PM PT</t>
+          <t>2026-07-11 08:29:17 PM PT</t>
         </is>
       </c>
       <c r="C330" t="n">

--- a/live_mlb_hitter_fantasy_scores_2026_07_11.xlsx
+++ b/live_mlb_hitter_fantasy_scores_2026_07_11.xlsx
@@ -693,7 +693,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-07-11 08:31:16 PM PT</t>
+          <t>2026-07-11 08:33:16 PM PT</t>
         </is>
       </c>
       <c r="C2" t="n">
@@ -807,61 +807,70 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>2026-07-11 08:31:18 PM PT</t>
+          <t>2026-07-11 08:33:18 PM PT</t>
         </is>
       </c>
       <c r="C3" t="n">
-        <v>822875</v>
+        <v>823926</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>4:05 PM PT</t>
+          <t>6:10 PM PT</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Final</t>
+          <t>Top 8 | 1 out</t>
         </is>
       </c>
       <c r="F3" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Bottom</t>
-        </is>
+          <t>Top</t>
+        </is>
+      </c>
+      <c r="H3" t="n">
+        <v>1</v>
+      </c>
+      <c r="I3" t="n">
+        <v>1</v>
+      </c>
+      <c r="J3" t="n">
+        <v>1</v>
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>Home</t>
+          <t>Away</t>
         </is>
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>TEX</t>
+          <t>ARI</t>
         </is>
       </c>
       <c r="M3" t="inlineStr">
         <is>
-          <t>HOU</t>
+          <t>LAD</t>
         </is>
       </c>
       <c r="N3" t="inlineStr">
         <is>
-          <t>Ezequiel Duran</t>
+          <t>James McCann</t>
         </is>
       </c>
       <c r="O3" t="n">
-        <v>677649</v>
+        <v>543510</v>
       </c>
       <c r="P3" t="inlineStr">
         <is>
-          <t>SS</t>
+          <t>C</t>
         </is>
       </c>
       <c r="Q3" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>8</t>
         </is>
       </c>
       <c r="R3" t="n">
@@ -889,7 +898,7 @@
         <v>2</v>
       </c>
       <c r="Z3" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="AA3" t="n">
         <v>0</v>
@@ -901,13 +910,13 @@
         <v>0</v>
       </c>
       <c r="AD3" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AE3" s="4" t="n">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="AF3" t="n">
-        <v>3</v>
+        <v>9</v>
       </c>
       <c r="AG3" t="n">
         <v>7</v>
@@ -921,83 +930,74 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-07-11 08:31:18 PM PT</t>
+          <t>2026-07-11 08:33:17 PM PT</t>
         </is>
       </c>
       <c r="C4" t="n">
-        <v>823276</v>
+        <v>822875</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>5:40 PM PT</t>
+          <t>4:05 PM PT</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Bottom 8 | 0 out</t>
+          <t>Final</t>
         </is>
       </c>
       <c r="F4" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
           <t>Bottom</t>
         </is>
       </c>
-      <c r="H4" t="n">
-        <v>0</v>
-      </c>
-      <c r="I4" t="n">
-        <v>1</v>
-      </c>
-      <c r="J4" t="n">
-        <v>1</v>
-      </c>
       <c r="K4" t="inlineStr">
         <is>
-          <t>Away</t>
+          <t>Home</t>
         </is>
       </c>
       <c r="L4" t="inlineStr">
         <is>
-          <t>TOR</t>
+          <t>TEX</t>
         </is>
       </c>
       <c r="M4" t="inlineStr">
         <is>
-          <t>SD</t>
+          <t>HOU</t>
         </is>
       </c>
       <c r="N4" t="inlineStr">
         <is>
-          <t>Vladimir Guerrero Jr.</t>
+          <t>Ezequiel Duran</t>
         </is>
       </c>
       <c r="O4" t="n">
-        <v>665489</v>
+        <v>677649</v>
       </c>
       <c r="P4" t="inlineStr">
         <is>
-          <t>1B</t>
+          <t>SS</t>
         </is>
       </c>
       <c r="Q4" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>6</t>
         </is>
       </c>
       <c r="R4" t="n">
         <v>4</v>
       </c>
       <c r="S4" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="T4" t="n">
         <v>2</v>
       </c>
       <c r="U4" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="V4" t="n">
         <v>0</v>
@@ -1006,31 +1006,31 @@
         <v>0</v>
       </c>
       <c r="X4" s="3" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="Y4" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="Z4" t="n">
         <v>3</v>
       </c>
-      <c r="AA4" s="5" t="n">
-        <v>1</v>
+      <c r="AA4" t="n">
+        <v>0</v>
       </c>
       <c r="AB4" t="n">
         <v>0</v>
       </c>
-      <c r="AC4" s="6" t="n">
-        <v>1</v>
+      <c r="AC4" t="n">
+        <v>0</v>
       </c>
       <c r="AD4" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AE4" s="4" t="n">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="AF4" t="n">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="AG4" t="n">
         <v>7</v>
@@ -1044,30 +1044,39 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>2026-07-11 08:31:18 PM PT</t>
+          <t>2026-07-11 08:33:18 PM PT</t>
         </is>
       </c>
       <c r="C5" t="n">
-        <v>822875</v>
+        <v>823276</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>4:05 PM PT</t>
+          <t>5:40 PM PT</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Final</t>
+          <t>Bottom 8 | 0 out</t>
         </is>
       </c>
       <c r="F5" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
           <t>Bottom</t>
         </is>
       </c>
+      <c r="H5" t="n">
+        <v>0</v>
+      </c>
+      <c r="I5" t="n">
+        <v>1</v>
+      </c>
+      <c r="J5" t="n">
+        <v>0</v>
+      </c>
       <c r="K5" t="inlineStr">
         <is>
           <t>Away</t>
@@ -1075,34 +1084,34 @@
       </c>
       <c r="L5" t="inlineStr">
         <is>
-          <t>HOU</t>
+          <t>TOR</t>
         </is>
       </c>
       <c r="M5" t="inlineStr">
         <is>
-          <t>TEX</t>
+          <t>SD</t>
         </is>
       </c>
       <c r="N5" t="inlineStr">
         <is>
-          <t>Yordan Alvarez</t>
+          <t>Vladimir Guerrero Jr.</t>
         </is>
       </c>
       <c r="O5" t="n">
-        <v>670541</v>
+        <v>665489</v>
       </c>
       <c r="P5" t="inlineStr">
         <is>
-          <t>LF</t>
+          <t>1B</t>
         </is>
       </c>
       <c r="Q5" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="R5" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="S5" t="n">
         <v>3</v>
@@ -1111,10 +1120,10 @@
         <v>2</v>
       </c>
       <c r="U5" t="n">
-        <v>0</v>
-      </c>
-      <c r="V5" s="7" t="n">
-        <v>1</v>
+        <v>1</v>
+      </c>
+      <c r="V5" t="n">
+        <v>0</v>
       </c>
       <c r="W5" t="n">
         <v>0</v>
@@ -1123,31 +1132,31 @@
         <v>1</v>
       </c>
       <c r="Y5" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="Z5" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AA5" s="5" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AB5" t="n">
         <v>0</v>
       </c>
-      <c r="AC5" t="n">
-        <v>0</v>
+      <c r="AC5" s="6" t="n">
+        <v>1</v>
       </c>
       <c r="AD5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AE5" s="4" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="AF5" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="AG5" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
     </row>
     <row r="6">
@@ -1158,15 +1167,15 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>2026-07-11 08:31:18 PM PT</t>
+          <t>2026-07-11 08:33:17 PM PT</t>
         </is>
       </c>
       <c r="C6" t="n">
-        <v>823030</v>
+        <v>822875</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>4:15 PM PT</t>
+          <t>4:05 PM PT</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
@@ -1179,31 +1188,31 @@
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Top</t>
+          <t>Bottom</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
         <is>
-          <t>Home</t>
+          <t>Away</t>
         </is>
       </c>
       <c r="L6" t="inlineStr">
         <is>
-          <t>STL</t>
+          <t>HOU</t>
         </is>
       </c>
       <c r="M6" t="inlineStr">
         <is>
-          <t>ATL</t>
+          <t>TEX</t>
         </is>
       </c>
       <c r="N6" t="inlineStr">
         <is>
-          <t>Lars Nootbaar</t>
+          <t>Yordan Alvarez</t>
         </is>
       </c>
       <c r="O6" t="n">
-        <v>663457</v>
+        <v>670541</v>
       </c>
       <c r="P6" t="inlineStr">
         <is>
@@ -1212,23 +1221,23 @@
       </c>
       <c r="Q6" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>2</t>
         </is>
       </c>
       <c r="R6" t="n">
+        <v>5</v>
+      </c>
+      <c r="S6" t="n">
         <v>3</v>
       </c>
-      <c r="S6" t="n">
+      <c r="T6" t="n">
         <v>2</v>
       </c>
-      <c r="T6" t="n">
-        <v>1</v>
-      </c>
       <c r="U6" t="n">
         <v>0</v>
       </c>
-      <c r="V6" t="n">
-        <v>0</v>
+      <c r="V6" s="7" t="n">
+        <v>1</v>
       </c>
       <c r="W6" t="n">
         <v>0</v>
@@ -1240,16 +1249,16 @@
         <v>2</v>
       </c>
       <c r="Z6" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AA6" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AB6" t="n">
         <v>0</v>
       </c>
-      <c r="AC6" s="6" t="n">
-        <v>1</v>
+      <c r="AC6" t="n">
+        <v>0</v>
       </c>
       <c r="AD6" t="n">
         <v>0</v>
@@ -1258,10 +1267,10 @@
         <v>27</v>
       </c>
       <c r="AF6" t="n">
-        <v>4</v>
+        <v>9</v>
       </c>
       <c r="AG6" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
     </row>
     <row r="7">
@@ -1272,15 +1281,15 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>2026-07-11 08:31:17 PM PT</t>
+          <t>2026-07-11 08:33:18 PM PT</t>
         </is>
       </c>
       <c r="C7" t="n">
-        <v>823603</v>
+        <v>823030</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>1:10 PM PT</t>
+          <t>4:15 PM PT</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -1293,89 +1302,89 @@
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Bottom</t>
+          <t>Top</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
         <is>
-          <t>Away</t>
+          <t>Home</t>
         </is>
       </c>
       <c r="L7" t="inlineStr">
         <is>
-          <t>BOS</t>
+          <t>STL</t>
         </is>
       </c>
       <c r="M7" t="inlineStr">
         <is>
-          <t>NYM</t>
+          <t>ATL</t>
         </is>
       </c>
       <c r="N7" t="inlineStr">
         <is>
-          <t>Andruw Monasterio</t>
+          <t>Lars Nootbaar</t>
         </is>
       </c>
       <c r="O7" t="n">
-        <v>655316</v>
+        <v>663457</v>
       </c>
       <c r="P7" t="inlineStr">
         <is>
-          <t>SS</t>
+          <t>LF</t>
         </is>
       </c>
       <c r="Q7" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>5</t>
         </is>
       </c>
       <c r="R7" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="S7" t="n">
+        <v>2</v>
+      </c>
+      <c r="T7" t="n">
+        <v>1</v>
+      </c>
+      <c r="U7" t="n">
+        <v>0</v>
+      </c>
+      <c r="V7" t="n">
+        <v>0</v>
+      </c>
+      <c r="W7" t="n">
+        <v>0</v>
+      </c>
+      <c r="X7" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="Y7" t="n">
+        <v>2</v>
+      </c>
+      <c r="Z7" t="n">
         <v>3</v>
       </c>
-      <c r="T7" t="n">
-        <v>2</v>
-      </c>
-      <c r="U7" t="n">
-        <v>0</v>
-      </c>
-      <c r="V7" t="n">
-        <v>0</v>
-      </c>
-      <c r="W7" s="8" t="n">
-        <v>1</v>
-      </c>
-      <c r="X7" s="3" t="n">
-        <v>1</v>
-      </c>
-      <c r="Y7" t="n">
-        <v>1</v>
-      </c>
-      <c r="Z7" t="n">
-        <v>2</v>
-      </c>
-      <c r="AA7" t="n">
-        <v>0</v>
+      <c r="AA7" s="5" t="n">
+        <v>1</v>
       </c>
       <c r="AB7" t="n">
         <v>0</v>
       </c>
-      <c r="AC7" t="n">
-        <v>0</v>
+      <c r="AC7" s="6" t="n">
+        <v>1</v>
       </c>
       <c r="AD7" t="n">
         <v>0</v>
       </c>
       <c r="AE7" s="4" t="n">
-        <v>24</v>
+        <v>27</v>
       </c>
       <c r="AF7" t="n">
         <v>4</v>
       </c>
       <c r="AG7" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="8">
@@ -1386,15 +1395,15 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>2026-07-11 08:31:18 PM PT</t>
+          <t>2026-07-11 08:33:17 PM PT</t>
         </is>
       </c>
       <c r="C8" t="n">
-        <v>824813</v>
+        <v>823603</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>4:05 PM PT</t>
+          <t>1:10 PM PT</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
@@ -1407,47 +1416,47 @@
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Top</t>
+          <t>Bottom</t>
         </is>
       </c>
       <c r="K8" t="inlineStr">
         <is>
-          <t>Home</t>
+          <t>Away</t>
         </is>
       </c>
       <c r="L8" t="inlineStr">
         <is>
-          <t>BAL</t>
+          <t>BOS</t>
         </is>
       </c>
       <c r="M8" t="inlineStr">
         <is>
-          <t>KC</t>
+          <t>NYM</t>
         </is>
       </c>
       <c r="N8" t="inlineStr">
         <is>
-          <t>Pete Alonso</t>
+          <t>Andruw Monasterio</t>
         </is>
       </c>
       <c r="O8" t="n">
-        <v>624413</v>
+        <v>655316</v>
       </c>
       <c r="P8" t="inlineStr">
         <is>
-          <t>1B</t>
+          <t>SS</t>
         </is>
       </c>
       <c r="Q8" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>6</t>
         </is>
       </c>
       <c r="R8" t="n">
         <v>4</v>
       </c>
       <c r="S8" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="T8" t="n">
         <v>2</v>
@@ -1455,17 +1464,17 @@
       <c r="U8" t="n">
         <v>0</v>
       </c>
-      <c r="V8" s="7" t="n">
-        <v>1</v>
-      </c>
-      <c r="W8" t="n">
-        <v>0</v>
+      <c r="V8" t="n">
+        <v>0</v>
+      </c>
+      <c r="W8" s="8" t="n">
+        <v>1</v>
       </c>
       <c r="X8" s="3" t="n">
         <v>1</v>
       </c>
       <c r="Y8" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="Z8" t="n">
         <v>2</v>
@@ -1480,13 +1489,13 @@
         <v>0</v>
       </c>
       <c r="AD8" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AE8" s="4" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="AF8" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="AG8" t="n">
         <v>6</v>
@@ -1500,15 +1509,15 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>2026-07-11 08:31:16 PM PT</t>
+          <t>2026-07-11 08:33:17 PM PT</t>
         </is>
       </c>
       <c r="C9" t="n">
-        <v>823682</v>
+        <v>824813</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>11:10 AM PT</t>
+          <t>4:05 PM PT</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
@@ -1531,21 +1540,21 @@
       </c>
       <c r="L9" t="inlineStr">
         <is>
-          <t>MIN</t>
+          <t>BAL</t>
         </is>
       </c>
       <c r="M9" t="inlineStr">
         <is>
-          <t>LAA</t>
+          <t>KC</t>
         </is>
       </c>
       <c r="N9" t="inlineStr">
         <is>
-          <t>Royce Lewis</t>
+          <t>Pete Alonso</t>
         </is>
       </c>
       <c r="O9" t="n">
-        <v>668904</v>
+        <v>624413</v>
       </c>
       <c r="P9" t="inlineStr">
         <is>
@@ -1554,7 +1563,7 @@
       </c>
       <c r="Q9" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>4</t>
         </is>
       </c>
       <c r="R9" t="n">
@@ -1594,16 +1603,16 @@
         <v>0</v>
       </c>
       <c r="AD9" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AE9" s="4" t="n">
         <v>23</v>
       </c>
       <c r="AF9" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AG9" t="n">
-        <v>9</v>
+        <v>6</v>
       </c>
     </row>
     <row r="10">
@@ -1614,38 +1623,29 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>2026-07-11 08:31:18 PM PT</t>
+          <t>2026-07-11 08:33:16 PM PT</t>
         </is>
       </c>
       <c r="C10" t="n">
-        <v>823276</v>
+        <v>823682</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>5:40 PM PT</t>
+          <t>11:10 AM PT</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Bottom 8 | 0 out</t>
+          <t>Final</t>
         </is>
       </c>
       <c r="F10" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Bottom</t>
-        </is>
-      </c>
-      <c r="H10" t="n">
-        <v>0</v>
-      </c>
-      <c r="I10" t="n">
-        <v>1</v>
-      </c>
-      <c r="J10" t="n">
-        <v>1</v>
+          <t>Top</t>
+        </is>
       </c>
       <c r="K10" t="inlineStr">
         <is>
@@ -1654,21 +1654,21 @@
       </c>
       <c r="L10" t="inlineStr">
         <is>
-          <t>SD</t>
+          <t>MIN</t>
         </is>
       </c>
       <c r="M10" t="inlineStr">
         <is>
-          <t>TOR</t>
+          <t>LAA</t>
         </is>
       </c>
       <c r="N10" t="inlineStr">
         <is>
-          <t>Ty France</t>
+          <t>Royce Lewis</t>
         </is>
       </c>
       <c r="O10" t="n">
-        <v>664034</v>
+        <v>668904</v>
       </c>
       <c r="P10" t="inlineStr">
         <is>
@@ -1677,23 +1677,23 @@
       </c>
       <c r="Q10" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>5</t>
         </is>
       </c>
       <c r="R10" t="n">
         <v>4</v>
       </c>
       <c r="S10" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="T10" t="n">
         <v>2</v>
       </c>
       <c r="U10" t="n">
-        <v>1</v>
-      </c>
-      <c r="V10" t="n">
-        <v>0</v>
+        <v>0</v>
+      </c>
+      <c r="V10" s="7" t="n">
+        <v>1</v>
       </c>
       <c r="W10" t="n">
         <v>0</v>
@@ -1710,23 +1710,23 @@
       <c r="AA10" t="n">
         <v>0</v>
       </c>
-      <c r="AB10" s="9" t="n">
-        <v>1</v>
+      <c r="AB10" t="n">
+        <v>0</v>
       </c>
       <c r="AC10" t="n">
         <v>0</v>
       </c>
       <c r="AD10" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AE10" s="4" t="n">
         <v>23</v>
       </c>
       <c r="AF10" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="AG10" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
     </row>
     <row r="11">
@@ -1737,29 +1737,38 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>2026-07-11 08:31:17 PM PT</t>
+          <t>2026-07-11 08:33:18 PM PT</t>
         </is>
       </c>
       <c r="C11" t="n">
-        <v>822953</v>
+        <v>823276</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>1:10 PM PT</t>
+          <t>5:40 PM PT</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Final</t>
+          <t>Bottom 8 | 0 out</t>
         </is>
       </c>
       <c r="F11" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Top</t>
-        </is>
+          <t>Bottom</t>
+        </is>
+      </c>
+      <c r="H11" t="n">
+        <v>0</v>
+      </c>
+      <c r="I11" t="n">
+        <v>1</v>
+      </c>
+      <c r="J11" t="n">
+        <v>0</v>
       </c>
       <c r="K11" t="inlineStr">
         <is>
@@ -1768,67 +1777,67 @@
       </c>
       <c r="L11" t="inlineStr">
         <is>
-          <t>TB</t>
+          <t>SD</t>
         </is>
       </c>
       <c r="M11" t="inlineStr">
         <is>
-          <t>SEA</t>
+          <t>TOR</t>
         </is>
       </c>
       <c r="N11" t="inlineStr">
         <is>
-          <t>Ben Williamson</t>
+          <t>Ty France</t>
         </is>
       </c>
       <c r="O11" t="n">
-        <v>810938</v>
+        <v>664034</v>
       </c>
       <c r="P11" t="inlineStr">
         <is>
-          <t>SS</t>
+          <t>1B</t>
         </is>
       </c>
       <c r="Q11" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>6</t>
         </is>
       </c>
       <c r="R11" t="n">
         <v>4</v>
       </c>
       <c r="S11" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="T11" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="U11" t="n">
-        <v>3</v>
-      </c>
-      <c r="V11" s="7" t="n">
-        <v>1</v>
+        <v>1</v>
+      </c>
+      <c r="V11" t="n">
+        <v>0</v>
       </c>
       <c r="W11" t="n">
         <v>0</v>
       </c>
-      <c r="X11" t="n">
-        <v>0</v>
+      <c r="X11" s="3" t="n">
+        <v>1</v>
       </c>
       <c r="Y11" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="Z11" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AA11" t="n">
         <v>0</v>
       </c>
-      <c r="AB11" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC11" s="6" t="n">
-        <v>1</v>
+      <c r="AB11" s="9" t="n">
+        <v>1</v>
+      </c>
+      <c r="AC11" t="n">
+        <v>0</v>
       </c>
       <c r="AD11" t="n">
         <v>0</v>
@@ -1837,10 +1846,10 @@
         <v>23</v>
       </c>
       <c r="AF11" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="AG11" t="n">
-        <v>12</v>
+        <v>8</v>
       </c>
     </row>
     <row r="12">
@@ -1851,15 +1860,15 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>2026-07-11 08:31:18 PM PT</t>
+          <t>2026-07-11 08:33:17 PM PT</t>
         </is>
       </c>
       <c r="C12" t="n">
-        <v>824249</v>
+        <v>822953</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>3:10 PM PT</t>
+          <t>1:10 PM PT</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
@@ -1872,56 +1881,56 @@
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Bottom</t>
+          <t>Top</t>
         </is>
       </c>
       <c r="K12" t="inlineStr">
         <is>
-          <t>Away</t>
+          <t>Home</t>
         </is>
       </c>
       <c r="L12" t="inlineStr">
         <is>
-          <t>PHI</t>
+          <t>TB</t>
         </is>
       </c>
       <c r="M12" t="inlineStr">
         <is>
-          <t>DET</t>
+          <t>SEA</t>
         </is>
       </c>
       <c r="N12" t="inlineStr">
         <is>
-          <t>Derek Hill</t>
+          <t>Ben Williamson</t>
         </is>
       </c>
       <c r="O12" t="n">
-        <v>656537</v>
+        <v>810938</v>
       </c>
       <c r="P12" t="inlineStr">
         <is>
-          <t>CF</t>
+          <t>SS</t>
         </is>
       </c>
       <c r="Q12" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>7</t>
         </is>
       </c>
       <c r="R12" t="n">
+        <v>4</v>
+      </c>
+      <c r="S12" t="n">
+        <v>4</v>
+      </c>
+      <c r="T12" t="n">
+        <v>4</v>
+      </c>
+      <c r="U12" t="n">
         <v>3</v>
       </c>
-      <c r="S12" t="n">
-        <v>3</v>
-      </c>
-      <c r="T12" t="n">
-        <v>1</v>
-      </c>
-      <c r="U12" t="n">
-        <v>1</v>
-      </c>
-      <c r="V12" t="n">
-        <v>0</v>
+      <c r="V12" s="7" t="n">
+        <v>1</v>
       </c>
       <c r="W12" t="n">
         <v>0</v>
@@ -1942,19 +1951,19 @@
         <v>0</v>
       </c>
       <c r="AC12" s="6" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="AD12" t="n">
         <v>0</v>
       </c>
       <c r="AE12" s="4" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="AF12" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="AG12" t="n">
-        <v>7</v>
+        <v>12</v>
       </c>
     </row>
     <row r="13">
@@ -1965,39 +1974,30 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>2026-07-11 08:31:18 PM PT</t>
+          <t>2026-07-11 08:33:17 PM PT</t>
         </is>
       </c>
       <c r="C13" t="n">
-        <v>823276</v>
+        <v>824249</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>5:40 PM PT</t>
+          <t>3:10 PM PT</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Bottom 8 | 0 out</t>
+          <t>Final</t>
         </is>
       </c>
       <c r="F13" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="G13" t="inlineStr">
         <is>
           <t>Bottom</t>
         </is>
       </c>
-      <c r="H13" t="n">
-        <v>0</v>
-      </c>
-      <c r="I13" t="n">
-        <v>1</v>
-      </c>
-      <c r="J13" t="n">
-        <v>1</v>
-      </c>
       <c r="K13" t="inlineStr">
         <is>
           <t>Away</t>
@@ -2005,25 +2005,25 @@
       </c>
       <c r="L13" t="inlineStr">
         <is>
-          <t>TOR</t>
+          <t>PHI</t>
         </is>
       </c>
       <c r="M13" t="inlineStr">
         <is>
-          <t>SD</t>
+          <t>DET</t>
         </is>
       </c>
       <c r="N13" t="inlineStr">
         <is>
-          <t>Jonatan Clase</t>
+          <t>Derek Hill</t>
         </is>
       </c>
       <c r="O13" t="n">
-        <v>682729</v>
+        <v>656537</v>
       </c>
       <c r="P13" t="inlineStr">
         <is>
-          <t>LF</t>
+          <t>CF</t>
         </is>
       </c>
       <c r="Q13" t="inlineStr">
@@ -2032,16 +2032,16 @@
         </is>
       </c>
       <c r="R13" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="S13" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="T13" t="n">
         <v>1</v>
       </c>
       <c r="U13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="V13" t="n">
         <v>0</v>
@@ -2049,32 +2049,32 @@
       <c r="W13" t="n">
         <v>0</v>
       </c>
-      <c r="X13" s="3" t="n">
-        <v>1</v>
+      <c r="X13" t="n">
+        <v>0</v>
       </c>
       <c r="Y13" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="Z13" t="n">
-        <v>2</v>
-      </c>
-      <c r="AA13" s="5" t="n">
-        <v>2</v>
+        <v>1</v>
+      </c>
+      <c r="AA13" t="n">
+        <v>0</v>
       </c>
       <c r="AB13" t="n">
         <v>0</v>
       </c>
-      <c r="AC13" t="n">
-        <v>0</v>
+      <c r="AC13" s="6" t="n">
+        <v>3</v>
       </c>
       <c r="AD13" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AE13" s="4" t="n">
         <v>22</v>
       </c>
       <c r="AF13" t="n">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="AG13" t="n">
         <v>7</v>
@@ -2088,30 +2088,39 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>2026-07-11 08:31:17 PM PT</t>
+          <t>2026-07-11 08:33:18 PM PT</t>
         </is>
       </c>
       <c r="C14" t="n">
-        <v>823844</v>
+        <v>823276</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>1:10 PM PT</t>
+          <t>5:40 PM PT</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Final</t>
+          <t>Bottom 8 | 0 out</t>
         </is>
       </c>
       <c r="F14" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="G14" t="inlineStr">
         <is>
           <t>Bottom</t>
         </is>
       </c>
+      <c r="H14" t="n">
+        <v>0</v>
+      </c>
+      <c r="I14" t="n">
+        <v>1</v>
+      </c>
+      <c r="J14" t="n">
+        <v>0</v>
+      </c>
       <c r="K14" t="inlineStr">
         <is>
           <t>Away</t>
@@ -2119,43 +2128,43 @@
       </c>
       <c r="L14" t="inlineStr">
         <is>
-          <t>CLE</t>
+          <t>TOR</t>
         </is>
       </c>
       <c r="M14" t="inlineStr">
         <is>
-          <t>MIA</t>
+          <t>SD</t>
         </is>
       </c>
       <c r="N14" t="inlineStr">
         <is>
-          <t>Gabriel Arias</t>
+          <t>Jonatan Clase</t>
         </is>
       </c>
       <c r="O14" t="n">
-        <v>672356</v>
+        <v>682729</v>
       </c>
       <c r="P14" t="inlineStr">
         <is>
-          <t>3B</t>
+          <t>LF</t>
         </is>
       </c>
       <c r="Q14" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>9</t>
         </is>
       </c>
       <c r="R14" t="n">
         <v>4</v>
       </c>
       <c r="S14" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="T14" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="U14" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="V14" t="n">
         <v>0</v>
@@ -2163,35 +2172,35 @@
       <c r="W14" t="n">
         <v>0</v>
       </c>
-      <c r="X14" t="n">
-        <v>0</v>
+      <c r="X14" s="3" t="n">
+        <v>1</v>
       </c>
       <c r="Y14" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="Z14" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA14" t="n">
-        <v>0</v>
+        <v>2</v>
+      </c>
+      <c r="AA14" s="5" t="n">
+        <v>2</v>
       </c>
       <c r="AB14" t="n">
         <v>0</v>
       </c>
-      <c r="AC14" s="6" t="n">
-        <v>2</v>
+      <c r="AC14" t="n">
+        <v>0</v>
       </c>
       <c r="AD14" t="n">
         <v>1</v>
       </c>
       <c r="AE14" s="4" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="AF14" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="AG14" t="n">
-        <v>11</v>
+        <v>7</v>
       </c>
     </row>
     <row r="15">
@@ -2202,15 +2211,15 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>2026-07-11 08:31:17 PM PT</t>
+          <t>2026-07-11 08:33:17 PM PT</t>
         </is>
       </c>
       <c r="C15" t="n">
-        <v>822711</v>
+        <v>823844</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>1:05 PM PT</t>
+          <t>1:10 PM PT</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
@@ -2233,21 +2242,21 @@
       </c>
       <c r="L15" t="inlineStr">
         <is>
-          <t>NYY</t>
+          <t>CLE</t>
         </is>
       </c>
       <c r="M15" t="inlineStr">
         <is>
-          <t>WSH</t>
+          <t>MIA</t>
         </is>
       </c>
       <c r="N15" t="inlineStr">
         <is>
-          <t>Ryan McMahon</t>
+          <t>Gabriel Arias</t>
         </is>
       </c>
       <c r="O15" t="n">
-        <v>641857</v>
+        <v>672356</v>
       </c>
       <c r="P15" t="inlineStr">
         <is>
@@ -2256,20 +2265,20 @@
       </c>
       <c r="Q15" t="inlineStr">
         <is>
-          <t>1 (Sub)</t>
+          <t>6</t>
         </is>
       </c>
       <c r="R15" t="n">
         <v>4</v>
       </c>
       <c r="S15" t="n">
+        <v>4</v>
+      </c>
+      <c r="T15" t="n">
         <v>3</v>
       </c>
-      <c r="T15" t="n">
-        <v>1</v>
-      </c>
       <c r="U15" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="V15" t="n">
         <v>0</v>
@@ -2277,26 +2286,26 @@
       <c r="W15" t="n">
         <v>0</v>
       </c>
-      <c r="X15" s="3" t="n">
-        <v>1</v>
+      <c r="X15" t="n">
+        <v>0</v>
       </c>
       <c r="Y15" t="n">
         <v>1</v>
       </c>
       <c r="Z15" t="n">
-        <v>1</v>
-      </c>
-      <c r="AA15" s="5" t="n">
-        <v>1</v>
+        <v>0</v>
+      </c>
+      <c r="AA15" t="n">
+        <v>0</v>
       </c>
       <c r="AB15" t="n">
         <v>0</v>
       </c>
       <c r="AC15" s="6" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AD15" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AE15" s="4" t="n">
         <v>21</v>
@@ -2305,7 +2314,7 @@
         <v>4</v>
       </c>
       <c r="AG15" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
     </row>
     <row r="16">
@@ -2316,15 +2325,15 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>2026-07-11 08:31:18 PM PT</t>
+          <t>2026-07-11 08:33:17 PM PT</t>
         </is>
       </c>
       <c r="C16" t="n">
-        <v>822875</v>
+        <v>822711</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>4:05 PM PT</t>
+          <t>1:05 PM PT</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
@@ -2347,37 +2356,37 @@
       </c>
       <c r="L16" t="inlineStr">
         <is>
-          <t>HOU</t>
+          <t>NYY</t>
         </is>
       </c>
       <c r="M16" t="inlineStr">
         <is>
-          <t>TEX</t>
+          <t>WSH</t>
         </is>
       </c>
       <c r="N16" t="inlineStr">
         <is>
-          <t>LaMonte Wade Jr.</t>
+          <t>Ryan McMahon</t>
         </is>
       </c>
       <c r="O16" t="n">
-        <v>664774</v>
+        <v>641857</v>
       </c>
       <c r="P16" t="inlineStr">
         <is>
-          <t>RF</t>
+          <t>3B</t>
         </is>
       </c>
       <c r="Q16" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>1 (Sub)</t>
         </is>
       </c>
       <c r="R16" t="n">
         <v>4</v>
       </c>
       <c r="S16" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="T16" t="n">
         <v>1</v>
@@ -2398,28 +2407,28 @@
         <v>1</v>
       </c>
       <c r="Z16" t="n">
-        <v>4</v>
-      </c>
-      <c r="AA16" t="n">
-        <v>0</v>
+        <v>1</v>
+      </c>
+      <c r="AA16" s="5" t="n">
+        <v>1</v>
       </c>
       <c r="AB16" t="n">
         <v>0</v>
       </c>
-      <c r="AC16" t="n">
-        <v>0</v>
+      <c r="AC16" s="6" t="n">
+        <v>1</v>
       </c>
       <c r="AD16" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AE16" s="4" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="AF16" t="n">
+        <v>4</v>
+      </c>
+      <c r="AG16" t="n">
         <v>9</v>
-      </c>
-      <c r="AG16" t="n">
-        <v>10</v>
       </c>
     </row>
     <row r="17">
@@ -2430,70 +2439,61 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>2026-07-11 08:31:18 PM PT</t>
+          <t>2026-07-11 08:33:17 PM PT</t>
         </is>
       </c>
       <c r="C17" t="n">
-        <v>823276</v>
+        <v>822875</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>5:40 PM PT</t>
+          <t>4:05 PM PT</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Bottom 8 | 0 out</t>
+          <t>Final</t>
         </is>
       </c>
       <c r="F17" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="G17" t="inlineStr">
         <is>
           <t>Bottom</t>
         </is>
       </c>
-      <c r="H17" t="n">
-        <v>0</v>
-      </c>
-      <c r="I17" t="n">
-        <v>1</v>
-      </c>
-      <c r="J17" t="n">
-        <v>1</v>
-      </c>
       <c r="K17" t="inlineStr">
         <is>
-          <t>Home</t>
+          <t>Away</t>
         </is>
       </c>
       <c r="L17" t="inlineStr">
         <is>
-          <t>SD</t>
+          <t>HOU</t>
         </is>
       </c>
       <c r="M17" t="inlineStr">
         <is>
-          <t>TOR</t>
+          <t>TEX</t>
         </is>
       </c>
       <c r="N17" t="inlineStr">
         <is>
-          <t>Jake Cronenworth</t>
+          <t>LaMonte Wade Jr.</t>
         </is>
       </c>
       <c r="O17" t="n">
-        <v>630105</v>
+        <v>664774</v>
       </c>
       <c r="P17" t="inlineStr">
         <is>
-          <t>2B</t>
+          <t>RF</t>
         </is>
       </c>
       <c r="Q17" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>6</t>
         </is>
       </c>
       <c r="R17" t="n">
@@ -2503,46 +2503,46 @@
         <v>4</v>
       </c>
       <c r="T17" t="n">
+        <v>1</v>
+      </c>
+      <c r="U17" t="n">
+        <v>0</v>
+      </c>
+      <c r="V17" t="n">
+        <v>0</v>
+      </c>
+      <c r="W17" t="n">
+        <v>0</v>
+      </c>
+      <c r="X17" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="Y17" t="n">
+        <v>1</v>
+      </c>
+      <c r="Z17" t="n">
+        <v>4</v>
+      </c>
+      <c r="AA17" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB17" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC17" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD17" t="n">
         <v>2</v>
-      </c>
-      <c r="U17" t="n">
-        <v>2</v>
-      </c>
-      <c r="V17" t="n">
-        <v>0</v>
-      </c>
-      <c r="W17" t="n">
-        <v>0</v>
-      </c>
-      <c r="X17" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y17" t="n">
-        <v>1</v>
-      </c>
-      <c r="Z17" t="n">
-        <v>1</v>
-      </c>
-      <c r="AA17" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB17" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC17" s="6" t="n">
-        <v>2</v>
-      </c>
-      <c r="AD17" t="n">
-        <v>0</v>
       </c>
       <c r="AE17" s="4" t="n">
         <v>20</v>
       </c>
       <c r="AF17" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="AG17" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
     </row>
     <row r="18">
@@ -2553,30 +2553,39 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>2026-07-11 08:31:17 PM PT</t>
+          <t>2026-07-11 08:33:18 PM PT</t>
         </is>
       </c>
       <c r="C18" t="n">
-        <v>822711</v>
+        <v>823276</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>1:05 PM PT</t>
+          <t>5:40 PM PT</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Final</t>
+          <t>Bottom 8 | 0 out</t>
         </is>
       </c>
       <c r="F18" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="G18" t="inlineStr">
         <is>
           <t>Bottom</t>
         </is>
       </c>
+      <c r="H18" t="n">
+        <v>0</v>
+      </c>
+      <c r="I18" t="n">
+        <v>1</v>
+      </c>
+      <c r="J18" t="n">
+        <v>0</v>
+      </c>
       <c r="K18" t="inlineStr">
         <is>
           <t>Home</t>
@@ -2584,40 +2593,40 @@
       </c>
       <c r="L18" t="inlineStr">
         <is>
-          <t>WSH</t>
+          <t>SD</t>
         </is>
       </c>
       <c r="M18" t="inlineStr">
         <is>
-          <t>NYY</t>
+          <t>TOR</t>
         </is>
       </c>
       <c r="N18" t="inlineStr">
         <is>
-          <t>James Wood</t>
+          <t>Jake Cronenworth</t>
         </is>
       </c>
       <c r="O18" t="n">
-        <v>695578</v>
+        <v>630105</v>
       </c>
       <c r="P18" t="inlineStr">
         <is>
-          <t>RF</t>
+          <t>2B</t>
         </is>
       </c>
       <c r="Q18" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>7</t>
         </is>
       </c>
       <c r="R18" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="S18" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="T18" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="U18" t="n">
         <v>2</v>
@@ -2628,8 +2637,8 @@
       <c r="W18" t="n">
         <v>0</v>
       </c>
-      <c r="X18" s="3" t="n">
-        <v>1</v>
+      <c r="X18" t="n">
+        <v>0</v>
       </c>
       <c r="Y18" t="n">
         <v>1</v>
@@ -2643,20 +2652,20 @@
       <c r="AB18" t="n">
         <v>0</v>
       </c>
-      <c r="AC18" t="n">
-        <v>0</v>
+      <c r="AC18" s="6" t="n">
+        <v>2</v>
       </c>
       <c r="AD18" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AE18" s="4" t="n">
         <v>20</v>
       </c>
       <c r="AF18" t="n">
-        <v>2</v>
+        <v>8</v>
       </c>
       <c r="AG18" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
     </row>
     <row r="19">
@@ -2667,15 +2676,15 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>2026-07-11 08:31:18 PM PT</t>
+          <t>2026-07-11 08:33:17 PM PT</t>
         </is>
       </c>
       <c r="C19" t="n">
-        <v>824492</v>
+        <v>822711</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>4:10 PM PT</t>
+          <t>1:05 PM PT</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
@@ -2698,44 +2707,44 @@
       </c>
       <c r="L19" t="inlineStr">
         <is>
-          <t>CIN</t>
+          <t>WSH</t>
         </is>
       </c>
       <c r="M19" t="inlineStr">
         <is>
-          <t>CHC</t>
+          <t>NYY</t>
         </is>
       </c>
       <c r="N19" t="inlineStr">
         <is>
-          <t>Eugenio Suárez</t>
+          <t>James Wood</t>
         </is>
       </c>
       <c r="O19" t="n">
-        <v>553993</v>
+        <v>695578</v>
       </c>
       <c r="P19" t="inlineStr">
         <is>
-          <t>DH</t>
+          <t>RF</t>
         </is>
       </c>
       <c r="Q19" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>1</t>
         </is>
       </c>
       <c r="R19" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="S19" t="n">
+        <v>5</v>
+      </c>
+      <c r="T19" t="n">
         <v>3</v>
       </c>
-      <c r="T19" t="n">
+      <c r="U19" t="n">
         <v>2</v>
       </c>
-      <c r="U19" t="n">
-        <v>1</v>
-      </c>
       <c r="V19" t="n">
         <v>0</v>
       </c>
@@ -2751,8 +2760,8 @@
       <c r="Z19" t="n">
         <v>1</v>
       </c>
-      <c r="AA19" s="5" t="n">
-        <v>1</v>
+      <c r="AA19" t="n">
+        <v>0</v>
       </c>
       <c r="AB19" t="n">
         <v>0</v>
@@ -2764,13 +2773,13 @@
         <v>1</v>
       </c>
       <c r="AE19" s="4" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="AF19" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AG19" t="n">
-        <v>11</v>
+        <v>7</v>
       </c>
     </row>
     <row r="20">
@@ -2781,15 +2790,15 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>2026-07-11 08:31:17 PM PT</t>
+          <t>2026-07-11 08:33:18 PM PT</t>
         </is>
       </c>
       <c r="C20" t="n">
-        <v>822711</v>
+        <v>824492</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>1:05 PM PT</t>
+          <t>4:10 PM PT</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
@@ -2807,42 +2816,42 @@
       </c>
       <c r="K20" t="inlineStr">
         <is>
-          <t>Away</t>
+          <t>Home</t>
         </is>
       </c>
       <c r="L20" t="inlineStr">
         <is>
-          <t>NYY</t>
+          <t>CIN</t>
         </is>
       </c>
       <c r="M20" t="inlineStr">
         <is>
-          <t>WSH</t>
+          <t>CHC</t>
         </is>
       </c>
       <c r="N20" t="inlineStr">
         <is>
-          <t>Trent Grisham</t>
+          <t>Eugenio Suárez</t>
         </is>
       </c>
       <c r="O20" t="n">
-        <v>663757</v>
+        <v>553993</v>
       </c>
       <c r="P20" t="inlineStr">
         <is>
-          <t>CF</t>
+          <t>DH</t>
         </is>
       </c>
       <c r="Q20" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>6</t>
         </is>
       </c>
       <c r="R20" t="n">
         <v>4</v>
       </c>
       <c r="S20" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="T20" t="n">
         <v>2</v>
@@ -2863,10 +2872,10 @@
         <v>1</v>
       </c>
       <c r="Z20" t="n">
-        <v>2</v>
-      </c>
-      <c r="AA20" t="n">
-        <v>0</v>
+        <v>1</v>
+      </c>
+      <c r="AA20" s="5" t="n">
+        <v>1</v>
       </c>
       <c r="AB20" t="n">
         <v>0</v>
@@ -2881,10 +2890,10 @@
         <v>19</v>
       </c>
       <c r="AF20" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="AG20" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
     </row>
     <row r="21">
@@ -2895,7 +2904,7 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>2026-07-11 08:31:17 PM PT</t>
+          <t>2026-07-11 08:33:17 PM PT</t>
         </is>
       </c>
       <c r="C21" t="n">
@@ -2921,30 +2930,30 @@
       </c>
       <c r="K21" t="inlineStr">
         <is>
-          <t>Home</t>
+          <t>Away</t>
         </is>
       </c>
       <c r="L21" t="inlineStr">
         <is>
+          <t>NYY</t>
+        </is>
+      </c>
+      <c r="M21" t="inlineStr">
+        <is>
           <t>WSH</t>
         </is>
       </c>
-      <c r="M21" t="inlineStr">
-        <is>
-          <t>NYY</t>
-        </is>
-      </c>
       <c r="N21" t="inlineStr">
         <is>
-          <t>Curtis Mead</t>
+          <t>Trent Grisham</t>
         </is>
       </c>
       <c r="O21" t="n">
-        <v>678554</v>
+        <v>663757</v>
       </c>
       <c r="P21" t="inlineStr">
         <is>
-          <t>1B</t>
+          <t>CF</t>
         </is>
       </c>
       <c r="Q21" t="inlineStr">
@@ -2956,7 +2965,7 @@
         <v>4</v>
       </c>
       <c r="S21" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="T21" t="n">
         <v>2</v>
@@ -2977,10 +2986,10 @@
         <v>1</v>
       </c>
       <c r="Z21" t="n">
-        <v>1</v>
-      </c>
-      <c r="AA21" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
+      </c>
+      <c r="AA21" t="n">
+        <v>0</v>
       </c>
       <c r="AB21" t="n">
         <v>0</v>
@@ -2989,16 +2998,16 @@
         <v>0</v>
       </c>
       <c r="AD21" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AE21" s="4" t="n">
         <v>19</v>
       </c>
       <c r="AF21" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="AG21" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
     </row>
     <row r="22">
@@ -3009,70 +3018,61 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>2026-07-11 08:31:18 PM PT</t>
+          <t>2026-07-11 08:33:17 PM PT</t>
         </is>
       </c>
       <c r="C22" t="n">
-        <v>823926</v>
+        <v>822711</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>6:10 PM PT</t>
+          <t>1:05 PM PT</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Top 8 | 0 out</t>
+          <t>Final</t>
         </is>
       </c>
       <c r="F22" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Top</t>
-        </is>
-      </c>
-      <c r="H22" t="n">
-        <v>0</v>
-      </c>
-      <c r="I22" t="n">
-        <v>0</v>
-      </c>
-      <c r="J22" t="n">
-        <v>0</v>
+          <t>Bottom</t>
+        </is>
       </c>
       <c r="K22" t="inlineStr">
         <is>
-          <t>Away</t>
+          <t>Home</t>
         </is>
       </c>
       <c r="L22" t="inlineStr">
         <is>
-          <t>ARI</t>
+          <t>WSH</t>
         </is>
       </c>
       <c r="M22" t="inlineStr">
         <is>
-          <t>LAD</t>
+          <t>NYY</t>
         </is>
       </c>
       <c r="N22" t="inlineStr">
         <is>
-          <t>Nolan Arenado</t>
+          <t>Curtis Mead</t>
         </is>
       </c>
       <c r="O22" t="n">
-        <v>571448</v>
+        <v>678554</v>
       </c>
       <c r="P22" t="inlineStr">
         <is>
-          <t>3B</t>
+          <t>1B</t>
         </is>
       </c>
       <c r="Q22" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>3</t>
         </is>
       </c>
       <c r="R22" t="n">
@@ -3082,10 +3082,10 @@
         <v>3</v>
       </c>
       <c r="T22" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="U22" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="V22" t="n">
         <v>0</v>
@@ -3097,31 +3097,31 @@
         <v>1</v>
       </c>
       <c r="Y22" t="n">
+        <v>1</v>
+      </c>
+      <c r="Z22" t="n">
+        <v>1</v>
+      </c>
+      <c r="AA22" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="AB22" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC22" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD22" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE22" s="4" t="n">
+        <v>19</v>
+      </c>
+      <c r="AF22" t="n">
         <v>2</v>
       </c>
-      <c r="Z22" t="n">
-        <v>1</v>
-      </c>
-      <c r="AA22" s="5" t="n">
-        <v>1</v>
-      </c>
-      <c r="AB22" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC22" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD22" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE22" s="4" t="n">
-        <v>18</v>
-      </c>
-      <c r="AF22" t="n">
-        <v>8</v>
-      </c>
       <c r="AG22" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
     </row>
     <row r="23">
@@ -3132,7 +3132,7 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>2026-07-11 08:31:18 PM PT</t>
+          <t>2026-07-11 08:33:18 PM PT</t>
         </is>
       </c>
       <c r="C23" t="n">
@@ -3145,7 +3145,7 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Top 8 | 0 out</t>
+          <t>Top 8 | 1 out</t>
         </is>
       </c>
       <c r="F23" t="n">
@@ -3157,13 +3157,13 @@
         </is>
       </c>
       <c r="H23" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I23" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J23" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K23" t="inlineStr">
         <is>
@@ -3182,24 +3182,24 @@
       </c>
       <c r="N23" t="inlineStr">
         <is>
-          <t>James McCann</t>
+          <t>Nolan Arenado</t>
         </is>
       </c>
       <c r="O23" t="n">
-        <v>543510</v>
+        <v>571448</v>
       </c>
       <c r="P23" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>3B</t>
         </is>
       </c>
       <c r="Q23" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>7</t>
         </is>
       </c>
       <c r="R23" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="S23" t="n">
         <v>3</v>
@@ -3220,13 +3220,13 @@
         <v>1</v>
       </c>
       <c r="Y23" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="Z23" t="n">
-        <v>3</v>
-      </c>
-      <c r="AA23" t="n">
-        <v>0</v>
+        <v>1</v>
+      </c>
+      <c r="AA23" s="5" t="n">
+        <v>1</v>
       </c>
       <c r="AB23" t="n">
         <v>0</v>
@@ -3235,16 +3235,16 @@
         <v>0</v>
       </c>
       <c r="AD23" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AE23" s="4" t="n">
         <v>18</v>
       </c>
       <c r="AF23" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="AG23" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
     </row>
     <row r="24">
@@ -3255,7 +3255,7 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>2026-07-11 08:31:18 PM PT</t>
+          <t>2026-07-11 08:33:17 PM PT</t>
         </is>
       </c>
       <c r="C24" t="n">
@@ -3369,7 +3369,7 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>2026-07-11 08:31:17 PM PT</t>
+          <t>2026-07-11 08:33:17 PM PT</t>
         </is>
       </c>
       <c r="C25" t="n">
@@ -3483,7 +3483,7 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>2026-07-11 08:31:18 PM PT</t>
+          <t>2026-07-11 08:33:18 PM PT</t>
         </is>
       </c>
       <c r="C26" t="n">
@@ -3597,7 +3597,7 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>2026-07-11 08:31:16 PM PT</t>
+          <t>2026-07-11 08:33:16 PM PT</t>
         </is>
       </c>
       <c r="C27" t="n">
@@ -3711,7 +3711,7 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>2026-07-11 08:31:17 PM PT</t>
+          <t>2026-07-11 08:33:17 PM PT</t>
         </is>
       </c>
       <c r="C28" t="n">
@@ -3825,7 +3825,7 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>2026-07-11 08:31:17 PM PT</t>
+          <t>2026-07-11 08:33:17 PM PT</t>
         </is>
       </c>
       <c r="C29" t="n">
@@ -3939,7 +3939,7 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>2026-07-11 08:31:18 PM PT</t>
+          <t>2026-07-11 08:33:18 PM PT</t>
         </is>
       </c>
       <c r="C30" t="n">
@@ -4053,7 +4053,7 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>2026-07-11 08:31:18 PM PT</t>
+          <t>2026-07-11 08:33:18 PM PT</t>
         </is>
       </c>
       <c r="C31" t="n">
@@ -4167,7 +4167,7 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>2026-07-11 08:31:18 PM PT</t>
+          <t>2026-07-11 08:33:17 PM PT</t>
         </is>
       </c>
       <c r="C32" t="n">
@@ -4281,7 +4281,7 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>2026-07-11 08:31:17 PM PT</t>
+          <t>2026-07-11 08:33:17 PM PT</t>
         </is>
       </c>
       <c r="C33" t="n">
@@ -4395,7 +4395,7 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>2026-07-11 08:31:18 PM PT</t>
+          <t>2026-07-11 08:33:17 PM PT</t>
         </is>
       </c>
       <c r="C34" t="n">
@@ -4509,7 +4509,7 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>2026-07-11 08:31:16 PM PT</t>
+          <t>2026-07-11 08:33:16 PM PT</t>
         </is>
       </c>
       <c r="C35" t="n">
@@ -4623,7 +4623,7 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>2026-07-11 08:31:16 PM PT</t>
+          <t>2026-07-11 08:33:16 PM PT</t>
         </is>
       </c>
       <c r="C36" t="n">
@@ -4737,7 +4737,7 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>2026-07-11 08:31:18 PM PT</t>
+          <t>2026-07-11 08:33:18 PM PT</t>
         </is>
       </c>
       <c r="C37" t="n">
@@ -4768,7 +4768,7 @@
         <v>1</v>
       </c>
       <c r="J37" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K37" t="inlineStr">
         <is>
@@ -4849,7 +4849,7 @@
         <v>8</v>
       </c>
       <c r="AG37" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
     </row>
     <row r="38">
@@ -4860,7 +4860,7 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>2026-07-11 08:31:17 PM PT</t>
+          <t>2026-07-11 08:33:17 PM PT</t>
         </is>
       </c>
       <c r="C38" t="n">
@@ -4974,7 +4974,7 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>2026-07-11 08:31:16 PM PT</t>
+          <t>2026-07-11 08:33:16 PM PT</t>
         </is>
       </c>
       <c r="C39" t="n">
@@ -5088,7 +5088,7 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>2026-07-11 08:31:17 PM PT</t>
+          <t>2026-07-11 08:33:17 PM PT</t>
         </is>
       </c>
       <c r="C40" t="n">
@@ -5202,7 +5202,7 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>2026-07-11 08:31:16 PM PT</t>
+          <t>2026-07-11 08:33:16 PM PT</t>
         </is>
       </c>
       <c r="C41" t="n">
@@ -5316,7 +5316,7 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>2026-07-11 08:31:18 PM PT</t>
+          <t>2026-07-11 08:33:18 PM PT</t>
         </is>
       </c>
       <c r="C42" t="n">
@@ -5329,7 +5329,7 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>Top 8 | 0 out</t>
+          <t>Top 8 | 1 out</t>
         </is>
       </c>
       <c r="F42" t="n">
@@ -5341,13 +5341,13 @@
         </is>
       </c>
       <c r="H42" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I42" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J42" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K42" t="inlineStr">
         <is>
@@ -5425,10 +5425,10 @@
         <v>14</v>
       </c>
       <c r="AF42" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="AG42" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
     </row>
     <row r="43">
@@ -5439,7 +5439,7 @@
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>2026-07-11 08:31:18 PM PT</t>
+          <t>2026-07-11 08:33:18 PM PT</t>
         </is>
       </c>
       <c r="C43" t="n">
@@ -5553,7 +5553,7 @@
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>2026-07-11 08:31:18 PM PT</t>
+          <t>2026-07-11 08:33:17 PM PT</t>
         </is>
       </c>
       <c r="C44" t="n">
@@ -5667,7 +5667,7 @@
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>2026-07-11 08:31:18 PM PT</t>
+          <t>2026-07-11 08:33:17 PM PT</t>
         </is>
       </c>
       <c r="C45" t="n">
@@ -5781,7 +5781,7 @@
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>2026-07-11 08:31:18 PM PT</t>
+          <t>2026-07-11 08:33:18 PM PT</t>
         </is>
       </c>
       <c r="C46" t="n">
@@ -5895,7 +5895,7 @@
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>2026-07-11 08:31:17 PM PT</t>
+          <t>2026-07-11 08:33:17 PM PT</t>
         </is>
       </c>
       <c r="C47" t="n">
@@ -6009,7 +6009,7 @@
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>2026-07-11 08:31:17 PM PT</t>
+          <t>2026-07-11 08:33:17 PM PT</t>
         </is>
       </c>
       <c r="C48" t="n">
@@ -6123,7 +6123,7 @@
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>2026-07-11 08:31:18 PM PT</t>
+          <t>2026-07-11 08:33:17 PM PT</t>
         </is>
       </c>
       <c r="C49" t="n">
@@ -6237,7 +6237,7 @@
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>2026-07-11 08:31:17 PM PT</t>
+          <t>2026-07-11 08:33:17 PM PT</t>
         </is>
       </c>
       <c r="C50" t="n">
@@ -6351,7 +6351,7 @@
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>2026-07-11 08:31:16 PM PT</t>
+          <t>2026-07-11 08:33:16 PM PT</t>
         </is>
       </c>
       <c r="C51" t="n">
@@ -6465,20 +6465,20 @@
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>2026-07-11 08:31:18 PM PT</t>
+          <t>2026-07-11 08:33:18 PM PT</t>
         </is>
       </c>
       <c r="C52" t="n">
-        <v>823926</v>
+        <v>823276</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>6:10 PM PT</t>
+          <t>5:40 PM PT</t>
         </is>
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>Top 8 | 0 out</t>
+          <t>Bottom 8 | 0 out</t>
         </is>
       </c>
       <c r="F52" t="n">
@@ -6486,44 +6486,44 @@
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Top</t>
+          <t>Bottom</t>
         </is>
       </c>
       <c r="H52" t="n">
         <v>0</v>
       </c>
       <c r="I52" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J52" t="n">
         <v>0</v>
       </c>
       <c r="K52" t="inlineStr">
         <is>
-          <t>Away</t>
+          <t>Home</t>
         </is>
       </c>
       <c r="L52" t="inlineStr">
         <is>
-          <t>ARI</t>
+          <t>SD</t>
         </is>
       </c>
       <c r="M52" t="inlineStr">
         <is>
-          <t>LAD</t>
+          <t>TOR</t>
         </is>
       </c>
       <c r="N52" t="inlineStr">
         <is>
-          <t>Geraldo Perdomo</t>
+          <t>Jackson Merrill</t>
         </is>
       </c>
       <c r="O52" t="n">
-        <v>672695</v>
+        <v>701538</v>
       </c>
       <c r="P52" t="inlineStr">
         <is>
-          <t>SS</t>
+          <t>CF</t>
         </is>
       </c>
       <c r="Q52" t="inlineStr">
@@ -6532,16 +6532,16 @@
         </is>
       </c>
       <c r="R52" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="S52" t="n">
+        <v>3</v>
+      </c>
+      <c r="T52" t="n">
         <v>2</v>
       </c>
-      <c r="T52" t="n">
-        <v>0</v>
-      </c>
       <c r="U52" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="V52" t="n">
         <v>0</v>
@@ -6559,25 +6559,25 @@
         <v>0</v>
       </c>
       <c r="AA52" s="5" t="n">
-        <v>1</v>
-      </c>
-      <c r="AB52" s="9" t="n">
-        <v>1</v>
-      </c>
-      <c r="AC52" s="6" t="n">
-        <v>1</v>
+        <v>2</v>
+      </c>
+      <c r="AB52" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC52" t="n">
+        <v>0</v>
       </c>
       <c r="AD52" t="n">
         <v>0</v>
       </c>
       <c r="AE52" s="4" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="AF52" t="n">
         <v>8</v>
       </c>
       <c r="AG52" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
     </row>
     <row r="53">
@@ -6588,29 +6588,38 @@
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>2026-07-11 08:31:18 PM PT</t>
+          <t>2026-07-11 08:33:18 PM PT</t>
         </is>
       </c>
       <c r="C53" t="n">
-        <v>824492</v>
+        <v>823926</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>4:10 PM PT</t>
+          <t>6:10 PM PT</t>
         </is>
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>Final</t>
+          <t>Top 8 | 1 out</t>
         </is>
       </c>
       <c r="F53" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Bottom</t>
-        </is>
+          <t>Top</t>
+        </is>
+      </c>
+      <c r="H53" t="n">
+        <v>1</v>
+      </c>
+      <c r="I53" t="n">
+        <v>1</v>
+      </c>
+      <c r="J53" t="n">
+        <v>1</v>
       </c>
       <c r="K53" t="inlineStr">
         <is>
@@ -6619,67 +6628,67 @@
       </c>
       <c r="L53" t="inlineStr">
         <is>
-          <t>CHC</t>
+          <t>ARI</t>
         </is>
       </c>
       <c r="M53" t="inlineStr">
         <is>
-          <t>CIN</t>
+          <t>LAD</t>
         </is>
       </c>
       <c r="N53" t="inlineStr">
         <is>
-          <t>Michael Busch</t>
+          <t>Geraldo Perdomo</t>
         </is>
       </c>
       <c r="O53" t="n">
-        <v>683737</v>
+        <v>672695</v>
       </c>
       <c r="P53" t="inlineStr">
         <is>
-          <t>1B</t>
+          <t>SS</t>
         </is>
       </c>
       <c r="Q53" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>2</t>
         </is>
       </c>
       <c r="R53" t="n">
         <v>4</v>
       </c>
       <c r="S53" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="T53" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="U53" t="n">
+        <v>0</v>
+      </c>
+      <c r="V53" t="n">
+        <v>0</v>
+      </c>
+      <c r="W53" t="n">
+        <v>0</v>
+      </c>
+      <c r="X53" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y53" t="n">
         <v>2</v>
       </c>
-      <c r="V53" s="7" t="n">
-        <v>1</v>
-      </c>
-      <c r="W53" t="n">
-        <v>0</v>
-      </c>
-      <c r="X53" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y53" t="n">
-        <v>1</v>
-      </c>
       <c r="Z53" t="n">
         <v>0</v>
       </c>
-      <c r="AA53" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB53" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC53" t="n">
-        <v>0</v>
+      <c r="AA53" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="AB53" s="9" t="n">
+        <v>1</v>
+      </c>
+      <c r="AC53" s="6" t="n">
+        <v>1</v>
       </c>
       <c r="AD53" t="n">
         <v>0</v>
@@ -6688,10 +6697,10 @@
         <v>13</v>
       </c>
       <c r="AF53" t="n">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="AG53" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
     </row>
     <row r="54">
@@ -6702,7 +6711,7 @@
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>2026-07-11 08:31:18 PM PT</t>
+          <t>2026-07-11 08:33:18 PM PT</t>
         </is>
       </c>
       <c r="C54" t="n">
@@ -6728,51 +6737,51 @@
       </c>
       <c r="K54" t="inlineStr">
         <is>
-          <t>Home</t>
+          <t>Away</t>
         </is>
       </c>
       <c r="L54" t="inlineStr">
         <is>
+          <t>CHC</t>
+        </is>
+      </c>
+      <c r="M54" t="inlineStr">
+        <is>
           <t>CIN</t>
         </is>
       </c>
-      <c r="M54" t="inlineStr">
-        <is>
-          <t>CHC</t>
-        </is>
-      </c>
       <c r="N54" t="inlineStr">
         <is>
-          <t>Elly De La Cruz</t>
+          <t>Michael Busch</t>
         </is>
       </c>
       <c r="O54" t="n">
-        <v>682829</v>
+        <v>683737</v>
       </c>
       <c r="P54" t="inlineStr">
         <is>
-          <t>SS</t>
+          <t>1B</t>
         </is>
       </c>
       <c r="Q54" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>5</t>
         </is>
       </c>
       <c r="R54" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="S54" t="n">
         <v>4</v>
       </c>
       <c r="T54" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="U54" t="n">
         <v>2</v>
       </c>
-      <c r="V54" t="n">
-        <v>0</v>
+      <c r="V54" s="7" t="n">
+        <v>1</v>
       </c>
       <c r="W54" t="n">
         <v>0</v>
@@ -6781,31 +6790,31 @@
         <v>0</v>
       </c>
       <c r="Y54" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Z54" t="n">
         <v>0</v>
       </c>
-      <c r="AA54" s="5" t="n">
-        <v>1</v>
+      <c r="AA54" t="n">
+        <v>0</v>
       </c>
       <c r="AB54" t="n">
         <v>0</v>
       </c>
-      <c r="AC54" s="6" t="n">
-        <v>1</v>
+      <c r="AC54" t="n">
+        <v>0</v>
       </c>
       <c r="AD54" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AE54" s="4" t="n">
         <v>13</v>
       </c>
       <c r="AF54" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="AG54" t="n">
-        <v>11</v>
+        <v>9</v>
       </c>
     </row>
     <row r="55">
@@ -6816,15 +6825,15 @@
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>2026-07-11 08:31:18 PM PT</t>
+          <t>2026-07-11 08:33:18 PM PT</t>
         </is>
       </c>
       <c r="C55" t="n">
-        <v>824249</v>
+        <v>824492</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>3:10 PM PT</t>
+          <t>4:10 PM PT</t>
         </is>
       </c>
       <c r="E55" t="inlineStr">
@@ -6847,25 +6856,25 @@
       </c>
       <c r="L55" t="inlineStr">
         <is>
-          <t>DET</t>
+          <t>CIN</t>
         </is>
       </c>
       <c r="M55" t="inlineStr">
         <is>
-          <t>PHI</t>
+          <t>CHC</t>
         </is>
       </c>
       <c r="N55" t="inlineStr">
         <is>
-          <t>Matt Vierling</t>
+          <t>Elly De La Cruz</t>
         </is>
       </c>
       <c r="O55" t="n">
-        <v>663837</v>
+        <v>682829</v>
       </c>
       <c r="P55" t="inlineStr">
         <is>
-          <t>CF</t>
+          <t>SS</t>
         </is>
       </c>
       <c r="Q55" t="inlineStr">
@@ -6874,16 +6883,16 @@
         </is>
       </c>
       <c r="R55" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="S55" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="T55" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="U55" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="V55" t="n">
         <v>0</v>
@@ -6895,7 +6904,7 @@
         <v>0</v>
       </c>
       <c r="Y55" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Z55" t="n">
         <v>0</v>
@@ -6906,20 +6915,20 @@
       <c r="AB55" t="n">
         <v>0</v>
       </c>
-      <c r="AC55" t="n">
-        <v>0</v>
+      <c r="AC55" s="6" t="n">
+        <v>1</v>
       </c>
       <c r="AD55" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AE55" s="4" t="n">
         <v>13</v>
       </c>
       <c r="AF55" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AG55" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
     </row>
     <row r="56">
@@ -6930,15 +6939,15 @@
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>2026-07-11 08:31:16 PM PT</t>
+          <t>2026-07-11 08:33:17 PM PT</t>
         </is>
       </c>
       <c r="C56" t="n">
-        <v>823682</v>
+        <v>824249</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>11:10 AM PT</t>
+          <t>3:10 PM PT</t>
         </is>
       </c>
       <c r="E56" t="inlineStr">
@@ -6951,56 +6960,56 @@
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Top</t>
+          <t>Bottom</t>
         </is>
       </c>
       <c r="K56" t="inlineStr">
         <is>
-          <t>Away</t>
+          <t>Home</t>
         </is>
       </c>
       <c r="L56" t="inlineStr">
         <is>
-          <t>LAA</t>
+          <t>DET</t>
         </is>
       </c>
       <c r="M56" t="inlineStr">
         <is>
-          <t>MIN</t>
+          <t>PHI</t>
         </is>
       </c>
       <c r="N56" t="inlineStr">
         <is>
-          <t>Jorge Soler</t>
+          <t>Matt Vierling</t>
         </is>
       </c>
       <c r="O56" t="n">
-        <v>624585</v>
+        <v>663837</v>
       </c>
       <c r="P56" t="inlineStr">
         <is>
-          <t>DH</t>
+          <t>CF</t>
         </is>
       </c>
       <c r="Q56" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>1</t>
         </is>
       </c>
       <c r="R56" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="S56" t="n">
         <v>3</v>
       </c>
       <c r="T56" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="U56" t="n">
-        <v>0</v>
-      </c>
-      <c r="V56" s="7" t="n">
-        <v>1</v>
+        <v>3</v>
+      </c>
+      <c r="V56" t="n">
+        <v>0</v>
       </c>
       <c r="W56" t="n">
         <v>0</v>
@@ -7009,13 +7018,13 @@
         <v>0</v>
       </c>
       <c r="Y56" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Z56" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AA56" s="5" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AB56" t="n">
         <v>0</v>
@@ -7024,13 +7033,13 @@
         <v>0</v>
       </c>
       <c r="AD56" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AE56" s="4" t="n">
         <v>13</v>
       </c>
       <c r="AF56" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AG56" t="n">
         <v>10</v>
@@ -7044,7 +7053,7 @@
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>2026-07-11 08:31:16 PM PT</t>
+          <t>2026-07-11 08:33:16 PM PT</t>
         </is>
       </c>
       <c r="C57" t="n">
@@ -7085,57 +7094,57 @@
       </c>
       <c r="N57" t="inlineStr">
         <is>
-          <t>Wade Meckler</t>
+          <t>Jorge Soler</t>
         </is>
       </c>
       <c r="O57" t="n">
-        <v>685133</v>
+        <v>624585</v>
       </c>
       <c r="P57" t="inlineStr">
         <is>
-          <t>LF</t>
+          <t>DH</t>
         </is>
       </c>
       <c r="Q57" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>4</t>
         </is>
       </c>
       <c r="R57" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="S57" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="T57" t="n">
+        <v>1</v>
+      </c>
+      <c r="U57" t="n">
+        <v>0</v>
+      </c>
+      <c r="V57" s="7" t="n">
+        <v>1</v>
+      </c>
+      <c r="W57" t="n">
+        <v>0</v>
+      </c>
+      <c r="X57" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y57" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z57" t="n">
         <v>2</v>
       </c>
-      <c r="U57" t="n">
-        <v>1</v>
-      </c>
-      <c r="V57" s="7" t="n">
-        <v>1</v>
-      </c>
-      <c r="W57" t="n">
-        <v>0</v>
-      </c>
-      <c r="X57" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y57" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z57" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA57" t="n">
-        <v>0</v>
+      <c r="AA57" s="5" t="n">
+        <v>2</v>
       </c>
       <c r="AB57" t="n">
         <v>0</v>
       </c>
-      <c r="AC57" s="6" t="n">
-        <v>1</v>
+      <c r="AC57" t="n">
+        <v>0</v>
       </c>
       <c r="AD57" t="n">
         <v>1</v>
@@ -7158,7 +7167,7 @@
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>2026-07-11 08:31:16 PM PT</t>
+          <t>2026-07-11 08:33:16 PM PT</t>
         </is>
       </c>
       <c r="C58" t="n">
@@ -7184,48 +7193,48 @@
       </c>
       <c r="K58" t="inlineStr">
         <is>
-          <t>Home</t>
+          <t>Away</t>
         </is>
       </c>
       <c r="L58" t="inlineStr">
         <is>
+          <t>LAA</t>
+        </is>
+      </c>
+      <c r="M58" t="inlineStr">
+        <is>
           <t>MIN</t>
         </is>
       </c>
-      <c r="M58" t="inlineStr">
-        <is>
-          <t>LAA</t>
-        </is>
-      </c>
       <c r="N58" t="inlineStr">
         <is>
-          <t>Victor Caratini</t>
+          <t>Wade Meckler</t>
         </is>
       </c>
       <c r="O58" t="n">
-        <v>605170</v>
+        <v>685133</v>
       </c>
       <c r="P58" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>LF</t>
         </is>
       </c>
       <c r="Q58" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="R58" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="S58" t="n">
+        <v>4</v>
+      </c>
+      <c r="T58" t="n">
         <v>2</v>
       </c>
-      <c r="T58" t="n">
-        <v>1</v>
-      </c>
       <c r="U58" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="V58" s="7" t="n">
         <v>1</v>
@@ -7237,31 +7246,31 @@
         <v>0</v>
       </c>
       <c r="Y58" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="Z58" t="n">
-        <v>1</v>
-      </c>
-      <c r="AA58" s="5" t="n">
-        <v>1</v>
+        <v>0</v>
+      </c>
+      <c r="AA58" t="n">
+        <v>0</v>
       </c>
       <c r="AB58" t="n">
         <v>0</v>
       </c>
-      <c r="AC58" t="n">
-        <v>0</v>
+      <c r="AC58" s="6" t="n">
+        <v>1</v>
       </c>
       <c r="AD58" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AE58" s="4" t="n">
         <v>13</v>
       </c>
       <c r="AF58" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="AG58" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
     </row>
     <row r="59">
@@ -7272,15 +7281,15 @@
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>2026-07-11 08:31:18 PM PT</t>
+          <t>2026-07-11 08:33:16 PM PT</t>
         </is>
       </c>
       <c r="C59" t="n">
-        <v>824249</v>
+        <v>823682</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>3:10 PM PT</t>
+          <t>11:10 AM PT</t>
         </is>
       </c>
       <c r="E59" t="inlineStr">
@@ -7293,35 +7302,35 @@
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Bottom</t>
+          <t>Top</t>
         </is>
       </c>
       <c r="K59" t="inlineStr">
         <is>
-          <t>Away</t>
+          <t>Home</t>
         </is>
       </c>
       <c r="L59" t="inlineStr">
         <is>
-          <t>PHI</t>
+          <t>MIN</t>
         </is>
       </c>
       <c r="M59" t="inlineStr">
         <is>
-          <t>DET</t>
+          <t>LAA</t>
         </is>
       </c>
       <c r="N59" t="inlineStr">
         <is>
-          <t>Bryson Stott</t>
+          <t>Victor Caratini</t>
         </is>
       </c>
       <c r="O59" t="n">
-        <v>681082</v>
+        <v>605170</v>
       </c>
       <c r="P59" t="inlineStr">
         <is>
-          <t>2B</t>
+          <t>C</t>
         </is>
       </c>
       <c r="Q59" t="inlineStr">
@@ -7330,52 +7339,52 @@
         </is>
       </c>
       <c r="R59" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="S59" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="T59" t="n">
+        <v>1</v>
+      </c>
+      <c r="U59" t="n">
+        <v>0</v>
+      </c>
+      <c r="V59" s="7" t="n">
+        <v>1</v>
+      </c>
+      <c r="W59" t="n">
+        <v>0</v>
+      </c>
+      <c r="X59" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y59" t="n">
         <v>2</v>
       </c>
-      <c r="U59" t="n">
-        <v>2</v>
-      </c>
-      <c r="V59" t="n">
-        <v>0</v>
-      </c>
-      <c r="W59" t="n">
-        <v>0</v>
-      </c>
-      <c r="X59" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y59" t="n">
-        <v>1</v>
-      </c>
       <c r="Z59" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA59" t="n">
-        <v>0</v>
+        <v>1</v>
+      </c>
+      <c r="AA59" s="5" t="n">
+        <v>1</v>
       </c>
       <c r="AB59" t="n">
         <v>0</v>
       </c>
-      <c r="AC59" s="6" t="n">
-        <v>1</v>
+      <c r="AC59" t="n">
+        <v>0</v>
       </c>
       <c r="AD59" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AE59" s="4" t="n">
         <v>13</v>
       </c>
       <c r="AF59" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="AG59" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
     </row>
     <row r="60">
@@ -7386,15 +7395,15 @@
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>2026-07-11 08:31:17 PM PT</t>
+          <t>2026-07-11 08:33:17 PM PT</t>
         </is>
       </c>
       <c r="C60" t="n">
-        <v>823603</v>
+        <v>824249</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>1:10 PM PT</t>
+          <t>3:10 PM PT</t>
         </is>
       </c>
       <c r="E60" t="inlineStr">
@@ -7417,37 +7426,37 @@
       </c>
       <c r="L60" t="inlineStr">
         <is>
-          <t>BOS</t>
+          <t>PHI</t>
         </is>
       </c>
       <c r="M60" t="inlineStr">
         <is>
-          <t>NYM</t>
+          <t>DET</t>
         </is>
       </c>
       <c r="N60" t="inlineStr">
         <is>
-          <t>Caleb Durbin</t>
+          <t>Bryson Stott</t>
         </is>
       </c>
       <c r="O60" t="n">
-        <v>702332</v>
+        <v>681082</v>
       </c>
       <c r="P60" t="inlineStr">
         <is>
-          <t>3B</t>
+          <t>2B</t>
         </is>
       </c>
       <c r="Q60" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>6</t>
         </is>
       </c>
       <c r="R60" t="n">
         <v>4</v>
       </c>
       <c r="S60" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="T60" t="n">
         <v>2</v>
@@ -7465,31 +7474,31 @@
         <v>0</v>
       </c>
       <c r="Y60" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="Z60" t="n">
         <v>0</v>
       </c>
-      <c r="AA60" s="5" t="n">
-        <v>1</v>
+      <c r="AA60" t="n">
+        <v>0</v>
       </c>
       <c r="AB60" t="n">
         <v>0</v>
       </c>
-      <c r="AC60" t="n">
-        <v>0</v>
+      <c r="AC60" s="6" t="n">
+        <v>1</v>
       </c>
       <c r="AD60" t="n">
         <v>1</v>
       </c>
       <c r="AE60" s="4" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="AF60" t="n">
         <v>4</v>
       </c>
       <c r="AG60" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
     </row>
     <row r="61">
@@ -7500,15 +7509,15 @@
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>2026-07-11 08:31:16 PM PT</t>
+          <t>2026-07-11 08:33:17 PM PT</t>
         </is>
       </c>
       <c r="C61" t="n">
-        <v>823682</v>
+        <v>823603</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>11:10 AM PT</t>
+          <t>1:10 PM PT</t>
         </is>
       </c>
       <c r="E61" t="inlineStr">
@@ -7521,7 +7530,7 @@
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Top</t>
+          <t>Bottom</t>
         </is>
       </c>
       <c r="K61" t="inlineStr">
@@ -7531,46 +7540,46 @@
       </c>
       <c r="L61" t="inlineStr">
         <is>
-          <t>LAA</t>
+          <t>BOS</t>
         </is>
       </c>
       <c r="M61" t="inlineStr">
         <is>
-          <t>MIN</t>
+          <t>NYM</t>
         </is>
       </c>
       <c r="N61" t="inlineStr">
         <is>
-          <t>Nolan Schanuel</t>
+          <t>Caleb Durbin</t>
         </is>
       </c>
       <c r="O61" t="n">
-        <v>694384</v>
+        <v>702332</v>
       </c>
       <c r="P61" t="inlineStr">
         <is>
-          <t>1B</t>
+          <t>3B</t>
         </is>
       </c>
       <c r="Q61" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="R61" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="S61" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="T61" t="n">
         <v>2</v>
       </c>
       <c r="U61" t="n">
-        <v>1</v>
-      </c>
-      <c r="V61" s="7" t="n">
-        <v>1</v>
+        <v>2</v>
+      </c>
+      <c r="V61" t="n">
+        <v>0</v>
       </c>
       <c r="W61" t="n">
         <v>0</v>
@@ -7579,10 +7588,10 @@
         <v>0</v>
       </c>
       <c r="Y61" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="Z61" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AA61" s="5" t="n">
         <v>1</v>
@@ -7594,16 +7603,16 @@
         <v>0</v>
       </c>
       <c r="AD61" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AE61" s="4" t="n">
         <v>12</v>
       </c>
       <c r="AF61" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="AG61" t="n">
-        <v>10</v>
+        <v>6</v>
       </c>
     </row>
     <row r="62">
@@ -7614,15 +7623,15 @@
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>2026-07-11 08:31:16 PM PT</t>
+          <t>2026-07-11 08:33:16 PM PT</t>
         </is>
       </c>
       <c r="C62" t="n">
-        <v>823357</v>
+        <v>823682</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>9:05 AM PT</t>
+          <t>11:10 AM PT</t>
         </is>
       </c>
       <c r="E62" t="inlineStr">
@@ -7645,37 +7654,37 @@
       </c>
       <c r="L62" t="inlineStr">
         <is>
-          <t>MIL</t>
+          <t>LAA</t>
         </is>
       </c>
       <c r="M62" t="inlineStr">
         <is>
-          <t>PIT</t>
+          <t>MIN</t>
         </is>
       </c>
       <c r="N62" t="inlineStr">
         <is>
-          <t>William Contreras</t>
+          <t>Nolan Schanuel</t>
         </is>
       </c>
       <c r="O62" t="n">
-        <v>661388</v>
+        <v>694384</v>
       </c>
       <c r="P62" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>1B</t>
         </is>
       </c>
       <c r="Q62" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>3</t>
         </is>
       </c>
       <c r="R62" t="n">
         <v>5</v>
       </c>
       <c r="S62" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="T62" t="n">
         <v>2</v>
@@ -7693,13 +7702,13 @@
         <v>0</v>
       </c>
       <c r="Y62" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Z62" t="n">
         <v>1</v>
       </c>
-      <c r="AA62" t="n">
-        <v>0</v>
+      <c r="AA62" s="5" t="n">
+        <v>1</v>
       </c>
       <c r="AB62" t="n">
         <v>0</v>
@@ -7708,16 +7717,16 @@
         <v>0</v>
       </c>
       <c r="AD62" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AE62" s="4" t="n">
         <v>12</v>
       </c>
       <c r="AF62" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="AG62" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
     </row>
     <row r="63">
@@ -7728,7 +7737,7 @@
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>2026-07-11 08:31:16 PM PT</t>
+          <t>2026-07-11 08:33:16 PM PT</t>
         </is>
       </c>
       <c r="C63" t="n">
@@ -7769,27 +7778,27 @@
       </c>
       <c r="N63" t="inlineStr">
         <is>
-          <t>Cooper Pratt</t>
+          <t>William Contreras</t>
         </is>
       </c>
       <c r="O63" t="n">
-        <v>806198</v>
+        <v>661388</v>
       </c>
       <c r="P63" t="inlineStr">
         <is>
-          <t>SS</t>
+          <t>C</t>
         </is>
       </c>
       <c r="Q63" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>4</t>
         </is>
       </c>
       <c r="R63" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="S63" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="T63" t="n">
         <v>2</v>
@@ -7842,38 +7851,29 @@
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>2026-07-11 08:31:18 PM PT</t>
+          <t>2026-07-11 08:33:16 PM PT</t>
         </is>
       </c>
       <c r="C64" t="n">
-        <v>823276</v>
+        <v>823357</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>5:40 PM PT</t>
+          <t>9:05 AM PT</t>
         </is>
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>Bottom 8 | 0 out</t>
+          <t>Final</t>
         </is>
       </c>
       <c r="F64" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>Bottom</t>
-        </is>
-      </c>
-      <c r="H64" t="n">
-        <v>0</v>
-      </c>
-      <c r="I64" t="n">
-        <v>1</v>
-      </c>
-      <c r="J64" t="n">
-        <v>1</v>
+          <t>Top</t>
+        </is>
       </c>
       <c r="K64" t="inlineStr">
         <is>
@@ -7882,25 +7882,25 @@
       </c>
       <c r="L64" t="inlineStr">
         <is>
-          <t>TOR</t>
+          <t>MIL</t>
         </is>
       </c>
       <c r="M64" t="inlineStr">
         <is>
-          <t>SD</t>
+          <t>PIT</t>
         </is>
       </c>
       <c r="N64" t="inlineStr">
         <is>
-          <t>Alejandro Kirk</t>
+          <t>Cooper Pratt</t>
         </is>
       </c>
       <c r="O64" t="n">
-        <v>672386</v>
+        <v>806198</v>
       </c>
       <c r="P64" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>SS</t>
         </is>
       </c>
       <c r="Q64" t="inlineStr">
@@ -7945,16 +7945,16 @@
         <v>0</v>
       </c>
       <c r="AD64" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AE64" s="4" t="n">
         <v>12</v>
       </c>
       <c r="AF64" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="AG64" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
     </row>
     <row r="65">
@@ -7965,20 +7965,20 @@
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>2026-07-11 08:31:18 PM PT</t>
+          <t>2026-07-11 08:33:18 PM PT</t>
         </is>
       </c>
       <c r="C65" t="n">
-        <v>823926</v>
+        <v>823276</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>6:10 PM PT</t>
+          <t>5:40 PM PT</t>
         </is>
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>Top 8 | 0 out</t>
+          <t>Bottom 8 | 0 out</t>
         </is>
       </c>
       <c r="F65" t="n">
@@ -7986,14 +7986,14 @@
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>Top</t>
+          <t>Bottom</t>
         </is>
       </c>
       <c r="H65" t="n">
         <v>0</v>
       </c>
       <c r="I65" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J65" t="n">
         <v>0</v>
@@ -8005,46 +8005,46 @@
       </c>
       <c r="L65" t="inlineStr">
         <is>
-          <t>ARI</t>
+          <t>TOR</t>
         </is>
       </c>
       <c r="M65" t="inlineStr">
         <is>
-          <t>LAD</t>
+          <t>SD</t>
         </is>
       </c>
       <c r="N65" t="inlineStr">
         <is>
-          <t>Gabriel Moreno</t>
+          <t>Alejandro Kirk</t>
         </is>
       </c>
       <c r="O65" t="n">
-        <v>672515</v>
+        <v>672386</v>
       </c>
       <c r="P65" t="inlineStr">
         <is>
-          <t>DH</t>
+          <t>C</t>
         </is>
       </c>
       <c r="Q65" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>7</t>
         </is>
       </c>
       <c r="R65" t="n">
         <v>4</v>
       </c>
       <c r="S65" t="n">
+        <v>4</v>
+      </c>
+      <c r="T65" t="n">
         <v>2</v>
       </c>
-      <c r="T65" t="n">
-        <v>1</v>
-      </c>
       <c r="U65" t="n">
         <v>1</v>
       </c>
-      <c r="V65" t="n">
-        <v>0</v>
+      <c r="V65" s="7" t="n">
+        <v>1</v>
       </c>
       <c r="W65" t="n">
         <v>0</v>
@@ -8053,13 +8053,13 @@
         <v>0</v>
       </c>
       <c r="Y65" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="Z65" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA65" s="5" t="n">
-        <v>2</v>
+        <v>1</v>
+      </c>
+      <c r="AA65" t="n">
+        <v>0</v>
       </c>
       <c r="AB65" t="n">
         <v>0</v>
@@ -8068,16 +8068,16 @@
         <v>0</v>
       </c>
       <c r="AD65" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AE65" s="4" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="AF65" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="AG65" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
     </row>
     <row r="66">
@@ -8088,30 +8088,39 @@
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>2026-07-11 08:31:17 PM PT</t>
+          <t>2026-07-11 08:33:18 PM PT</t>
         </is>
       </c>
       <c r="C66" t="n">
-        <v>824576</v>
+        <v>823926</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>11:10 AM PT</t>
+          <t>6:10 PM PT</t>
         </is>
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>Final</t>
+          <t>Top 8 | 1 out</t>
         </is>
       </c>
       <c r="F66" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="G66" t="inlineStr">
         <is>
           <t>Top</t>
         </is>
       </c>
+      <c r="H66" t="n">
+        <v>1</v>
+      </c>
+      <c r="I66" t="n">
+        <v>1</v>
+      </c>
+      <c r="J66" t="n">
+        <v>1</v>
+      </c>
       <c r="K66" t="inlineStr">
         <is>
           <t>Away</t>
@@ -8119,61 +8128,61 @@
       </c>
       <c r="L66" t="inlineStr">
         <is>
-          <t>ATH</t>
+          <t>ARI</t>
         </is>
       </c>
       <c r="M66" t="inlineStr">
         <is>
-          <t>CWS</t>
+          <t>LAD</t>
         </is>
       </c>
       <c r="N66" t="inlineStr">
         <is>
-          <t>Jacob Wilson</t>
+          <t>Gabriel Moreno</t>
         </is>
       </c>
       <c r="O66" t="n">
-        <v>805779</v>
+        <v>672515</v>
       </c>
       <c r="P66" t="inlineStr">
         <is>
-          <t>SS</t>
+          <t>DH</t>
         </is>
       </c>
       <c r="Q66" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>4</t>
         </is>
       </c>
       <c r="R66" t="n">
         <v>4</v>
       </c>
       <c r="S66" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="T66" t="n">
+        <v>1</v>
+      </c>
+      <c r="U66" t="n">
+        <v>1</v>
+      </c>
+      <c r="V66" t="n">
+        <v>0</v>
+      </c>
+      <c r="W66" t="n">
+        <v>0</v>
+      </c>
+      <c r="X66" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y66" t="n">
         <v>2</v>
       </c>
-      <c r="U66" t="n">
-        <v>1</v>
-      </c>
-      <c r="V66" t="n">
-        <v>0</v>
-      </c>
-      <c r="W66" s="8" t="n">
-        <v>1</v>
-      </c>
-      <c r="X66" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y66" t="n">
-        <v>0</v>
-      </c>
       <c r="Z66" t="n">
         <v>0</v>
       </c>
-      <c r="AA66" t="n">
-        <v>0</v>
+      <c r="AA66" s="5" t="n">
+        <v>2</v>
       </c>
       <c r="AB66" t="n">
         <v>0</v>
@@ -8182,16 +8191,16 @@
         <v>0</v>
       </c>
       <c r="AD66" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AE66" s="4" t="n">
         <v>11</v>
       </c>
       <c r="AF66" t="n">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="AG66" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
     </row>
     <row r="67">
@@ -8202,15 +8211,15 @@
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>2026-07-11 08:31:18 PM PT</t>
+          <t>2026-07-11 08:33:16 PM PT</t>
         </is>
       </c>
       <c r="C67" t="n">
-        <v>824249</v>
+        <v>824576</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>3:10 PM PT</t>
+          <t>11:10 AM PT</t>
         </is>
       </c>
       <c r="E67" t="inlineStr">
@@ -8223,7 +8232,7 @@
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>Bottom</t>
+          <t>Top</t>
         </is>
       </c>
       <c r="K67" t="inlineStr">
@@ -8233,30 +8242,30 @@
       </c>
       <c r="L67" t="inlineStr">
         <is>
-          <t>PHI</t>
+          <t>ATH</t>
         </is>
       </c>
       <c r="M67" t="inlineStr">
         <is>
-          <t>DET</t>
+          <t>CWS</t>
         </is>
       </c>
       <c r="N67" t="inlineStr">
         <is>
-          <t>J.T. Realmuto</t>
+          <t>Jacob Wilson</t>
         </is>
       </c>
       <c r="O67" t="n">
-        <v>592663</v>
+        <v>805779</v>
       </c>
       <c r="P67" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>SS</t>
         </is>
       </c>
       <c r="Q67" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>1</t>
         </is>
       </c>
       <c r="R67" t="n">
@@ -8266,25 +8275,25 @@
         <v>4</v>
       </c>
       <c r="T67" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="U67" t="n">
-        <v>0</v>
-      </c>
-      <c r="V67" s="7" t="n">
-        <v>1</v>
-      </c>
-      <c r="W67" t="n">
-        <v>0</v>
+        <v>1</v>
+      </c>
+      <c r="V67" t="n">
+        <v>0</v>
+      </c>
+      <c r="W67" s="8" t="n">
+        <v>1</v>
       </c>
       <c r="X67" t="n">
         <v>0</v>
       </c>
       <c r="Y67" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Z67" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AA67" t="n">
         <v>0</v>
@@ -8296,16 +8305,16 @@
         <v>0</v>
       </c>
       <c r="AD67" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AE67" s="4" t="n">
         <v>11</v>
       </c>
       <c r="AF67" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="AG67" t="n">
-        <v>7</v>
+        <v>4</v>
       </c>
     </row>
     <row r="68">
@@ -8316,101 +8325,92 @@
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>2026-07-11 08:31:18 PM PT</t>
+          <t>2026-07-11 08:33:17 PM PT</t>
         </is>
       </c>
       <c r="C68" t="n">
-        <v>823276</v>
+        <v>824249</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>5:40 PM PT</t>
+          <t>3:10 PM PT</t>
         </is>
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>Bottom 8 | 0 out</t>
+          <t>Final</t>
         </is>
       </c>
       <c r="F68" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="G68" t="inlineStr">
         <is>
           <t>Bottom</t>
         </is>
       </c>
-      <c r="H68" t="n">
-        <v>0</v>
-      </c>
-      <c r="I68" t="n">
-        <v>1</v>
-      </c>
-      <c r="J68" t="n">
-        <v>1</v>
-      </c>
       <c r="K68" t="inlineStr">
         <is>
-          <t>Home</t>
+          <t>Away</t>
         </is>
       </c>
       <c r="L68" t="inlineStr">
         <is>
-          <t>SD</t>
+          <t>PHI</t>
         </is>
       </c>
       <c r="M68" t="inlineStr">
         <is>
-          <t>TOR</t>
+          <t>DET</t>
         </is>
       </c>
       <c r="N68" t="inlineStr">
         <is>
-          <t>Jackson Merrill</t>
+          <t>J.T. Realmuto</t>
         </is>
       </c>
       <c r="O68" t="n">
-        <v>701538</v>
+        <v>592663</v>
       </c>
       <c r="P68" t="inlineStr">
         <is>
-          <t>CF</t>
+          <t>C</t>
         </is>
       </c>
       <c r="Q68" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>7</t>
         </is>
       </c>
       <c r="R68" t="n">
         <v>4</v>
       </c>
       <c r="S68" t="n">
+        <v>4</v>
+      </c>
+      <c r="T68" t="n">
+        <v>1</v>
+      </c>
+      <c r="U68" t="n">
+        <v>0</v>
+      </c>
+      <c r="V68" s="7" t="n">
+        <v>1</v>
+      </c>
+      <c r="W68" t="n">
+        <v>0</v>
+      </c>
+      <c r="X68" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y68" t="n">
+        <v>1</v>
+      </c>
+      <c r="Z68" t="n">
         <v>2</v>
       </c>
-      <c r="T68" t="n">
-        <v>1</v>
-      </c>
-      <c r="U68" t="n">
-        <v>1</v>
-      </c>
-      <c r="V68" t="n">
-        <v>0</v>
-      </c>
-      <c r="W68" t="n">
-        <v>0</v>
-      </c>
-      <c r="X68" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y68" t="n">
-        <v>2</v>
-      </c>
-      <c r="Z68" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA68" s="5" t="n">
-        <v>2</v>
+      <c r="AA68" t="n">
+        <v>0</v>
       </c>
       <c r="AB68" t="n">
         <v>0</v>
@@ -8419,13 +8419,13 @@
         <v>0</v>
       </c>
       <c r="AD68" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AE68" s="4" t="n">
         <v>11</v>
       </c>
       <c r="AF68" t="n">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="AG68" t="n">
         <v>7</v>
@@ -8439,7 +8439,7 @@
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>2026-07-11 08:31:17 PM PT</t>
+          <t>2026-07-11 08:33:17 PM PT</t>
         </is>
       </c>
       <c r="C69" t="n">
@@ -8553,7 +8553,7 @@
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>2026-07-11 08:31:17 PM PT</t>
+          <t>2026-07-11 08:33:16 PM PT</t>
         </is>
       </c>
       <c r="C70" t="n">
@@ -8667,7 +8667,7 @@
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>2026-07-11 08:31:16 PM PT</t>
+          <t>2026-07-11 08:33:16 PM PT</t>
         </is>
       </c>
       <c r="C71" t="n">
@@ -8781,7 +8781,7 @@
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>2026-07-11 08:31:18 PM PT</t>
+          <t>2026-07-11 08:33:18 PM PT</t>
         </is>
       </c>
       <c r="C72" t="n">
@@ -8794,7 +8794,7 @@
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>Top 8 | 0 out</t>
+          <t>Top 8 | 1 out</t>
         </is>
       </c>
       <c r="F72" t="n">
@@ -8806,13 +8806,13 @@
         </is>
       </c>
       <c r="H72" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I72" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J72" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K72" t="inlineStr">
         <is>
@@ -8904,7 +8904,7 @@
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>2026-07-11 08:31:16 PM PT</t>
+          <t>2026-07-11 08:33:16 PM PT</t>
         </is>
       </c>
       <c r="C73" t="n">
@@ -9018,7 +9018,7 @@
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>2026-07-11 08:31:17 PM PT</t>
+          <t>2026-07-11 08:33:17 PM PT</t>
         </is>
       </c>
       <c r="C74" t="n">
@@ -9132,7 +9132,7 @@
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>2026-07-11 08:31:16 PM PT</t>
+          <t>2026-07-11 08:33:16 PM PT</t>
         </is>
       </c>
       <c r="C75" t="n">
@@ -9246,7 +9246,7 @@
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>2026-07-11 08:31:18 PM PT</t>
+          <t>2026-07-11 08:33:18 PM PT</t>
         </is>
       </c>
       <c r="C76" t="n">
@@ -9277,7 +9277,7 @@
         <v>1</v>
       </c>
       <c r="J76" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K76" t="inlineStr">
         <is>
@@ -9369,7 +9369,7 @@
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>2026-07-11 08:31:18 PM PT</t>
+          <t>2026-07-11 08:33:18 PM PT</t>
         </is>
       </c>
       <c r="C77" t="n">
@@ -9483,7 +9483,7 @@
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>2026-07-11 08:31:18 PM PT</t>
+          <t>2026-07-11 08:33:18 PM PT</t>
         </is>
       </c>
       <c r="C78" t="n">
@@ -9597,7 +9597,7 @@
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>2026-07-11 08:31:17 PM PT</t>
+          <t>2026-07-11 08:33:17 PM PT</t>
         </is>
       </c>
       <c r="C79" t="n">
@@ -9711,7 +9711,7 @@
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>2026-07-11 08:31:16 PM PT</t>
+          <t>2026-07-11 08:33:16 PM PT</t>
         </is>
       </c>
       <c r="C80" t="n">
@@ -9825,7 +9825,7 @@
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>2026-07-11 08:31:16 PM PT</t>
+          <t>2026-07-11 08:33:16 PM PT</t>
         </is>
       </c>
       <c r="C81" t="n">
@@ -9939,7 +9939,7 @@
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>2026-07-11 08:31:16 PM PT</t>
+          <t>2026-07-11 08:33:16 PM PT</t>
         </is>
       </c>
       <c r="C82" t="n">
@@ -10053,7 +10053,7 @@
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>2026-07-11 08:31:16 PM PT</t>
+          <t>2026-07-11 08:33:16 PM PT</t>
         </is>
       </c>
       <c r="C83" t="n">
@@ -10167,7 +10167,7 @@
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>2026-07-11 08:31:16 PM PT</t>
+          <t>2026-07-11 08:33:16 PM PT</t>
         </is>
       </c>
       <c r="C84" t="n">
@@ -10281,7 +10281,7 @@
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>2026-07-11 08:31:16 PM PT</t>
+          <t>2026-07-11 08:33:16 PM PT</t>
         </is>
       </c>
       <c r="C85" t="n">
@@ -10395,7 +10395,7 @@
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>2026-07-11 08:31:17 PM PT</t>
+          <t>2026-07-11 08:33:16 PM PT</t>
         </is>
       </c>
       <c r="C86" t="n">
@@ -10509,7 +10509,7 @@
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>2026-07-11 08:31:17 PM PT</t>
+          <t>2026-07-11 08:33:16 PM PT</t>
         </is>
       </c>
       <c r="C87" t="n">
@@ -10623,7 +10623,7 @@
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>2026-07-11 08:31:17 PM PT</t>
+          <t>2026-07-11 08:33:17 PM PT</t>
         </is>
       </c>
       <c r="C88" t="n">
@@ -10737,7 +10737,7 @@
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>2026-07-11 08:31:18 PM PT</t>
+          <t>2026-07-11 08:33:17 PM PT</t>
         </is>
       </c>
       <c r="C89" t="n">
@@ -10851,7 +10851,7 @@
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>2026-07-11 08:31:18 PM PT</t>
+          <t>2026-07-11 08:33:18 PM PT</t>
         </is>
       </c>
       <c r="C90" t="n">
@@ -10882,7 +10882,7 @@
         <v>1</v>
       </c>
       <c r="J90" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K90" t="inlineStr">
         <is>
@@ -10963,7 +10963,7 @@
         <v>8</v>
       </c>
       <c r="AG90" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
     </row>
     <row r="91">
@@ -10974,7 +10974,7 @@
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>2026-07-11 08:31:17 PM PT</t>
+          <t>2026-07-11 08:33:17 PM PT</t>
         </is>
       </c>
       <c r="C91" t="n">
@@ -11088,7 +11088,7 @@
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>2026-07-11 08:31:18 PM PT</t>
+          <t>2026-07-11 08:33:18 PM PT</t>
         </is>
       </c>
       <c r="C92" t="n">
@@ -11202,7 +11202,7 @@
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>2026-07-11 08:31:18 PM PT</t>
+          <t>2026-07-11 08:33:18 PM PT</t>
         </is>
       </c>
       <c r="C93" t="n">
@@ -11215,7 +11215,7 @@
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>Top 8 | 0 out</t>
+          <t>Top 8 | 1 out</t>
         </is>
       </c>
       <c r="F93" t="n">
@@ -11227,13 +11227,13 @@
         </is>
       </c>
       <c r="H93" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I93" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J93" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K93" t="inlineStr">
         <is>
@@ -11311,10 +11311,10 @@
         <v>7</v>
       </c>
       <c r="AF93" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="AG93" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
     </row>
     <row r="94">
@@ -11325,7 +11325,7 @@
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>2026-07-11 08:31:17 PM PT</t>
+          <t>2026-07-11 08:33:17 PM PT</t>
         </is>
       </c>
       <c r="C94" t="n">
@@ -11439,7 +11439,7 @@
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>2026-07-11 08:31:17 PM PT</t>
+          <t>2026-07-11 08:33:17 PM PT</t>
         </is>
       </c>
       <c r="C95" t="n">
@@ -11553,7 +11553,7 @@
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>2026-07-11 08:31:17 PM PT</t>
+          <t>2026-07-11 08:33:17 PM PT</t>
         </is>
       </c>
       <c r="C96" t="n">
@@ -11667,7 +11667,7 @@
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>2026-07-11 08:31:18 PM PT</t>
+          <t>2026-07-11 08:33:17 PM PT</t>
         </is>
       </c>
       <c r="C97" t="n">
@@ -11781,7 +11781,7 @@
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>2026-07-11 08:31:18 PM PT</t>
+          <t>2026-07-11 08:33:17 PM PT</t>
         </is>
       </c>
       <c r="C98" t="n">
@@ -11895,7 +11895,7 @@
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>2026-07-11 08:31:18 PM PT</t>
+          <t>2026-07-11 08:33:18 PM PT</t>
         </is>
       </c>
       <c r="C99" t="n">
@@ -11908,7 +11908,7 @@
       </c>
       <c r="E99" t="inlineStr">
         <is>
-          <t>Top 8 | 0 out</t>
+          <t>Top 8 | 1 out</t>
         </is>
       </c>
       <c r="F99" t="n">
@@ -11920,13 +11920,13 @@
         </is>
       </c>
       <c r="H99" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I99" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J99" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K99" t="inlineStr">
         <is>
@@ -12018,7 +12018,7 @@
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>2026-07-11 08:31:17 PM PT</t>
+          <t>2026-07-11 08:33:17 PM PT</t>
         </is>
       </c>
       <c r="C100" t="n">
@@ -12132,7 +12132,7 @@
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>2026-07-11 08:31:16 PM PT</t>
+          <t>2026-07-11 08:33:16 PM PT</t>
         </is>
       </c>
       <c r="C101" t="n">
@@ -12246,7 +12246,7 @@
       </c>
       <c r="B102" t="inlineStr">
         <is>
-          <t>2026-07-11 08:31:16 PM PT</t>
+          <t>2026-07-11 08:33:16 PM PT</t>
         </is>
       </c>
       <c r="C102" t="n">
@@ -12360,7 +12360,7 @@
       </c>
       <c r="B103" t="inlineStr">
         <is>
-          <t>2026-07-11 08:31:17 PM PT</t>
+          <t>2026-07-11 08:33:17 PM PT</t>
         </is>
       </c>
       <c r="C103" t="n">
@@ -12474,7 +12474,7 @@
       </c>
       <c r="B104" t="inlineStr">
         <is>
-          <t>2026-07-11 08:31:18 PM PT</t>
+          <t>2026-07-11 08:33:18 PM PT</t>
         </is>
       </c>
       <c r="C104" t="n">
@@ -12505,7 +12505,7 @@
         <v>1</v>
       </c>
       <c r="J104" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K104" t="inlineStr">
         <is>
@@ -12586,7 +12586,7 @@
         <v>8</v>
       </c>
       <c r="AG104" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
     </row>
     <row r="105">
@@ -12597,7 +12597,7 @@
       </c>
       <c r="B105" t="inlineStr">
         <is>
-          <t>2026-07-11 08:31:17 PM PT</t>
+          <t>2026-07-11 08:33:17 PM PT</t>
         </is>
       </c>
       <c r="C105" t="n">
@@ -12711,7 +12711,7 @@
       </c>
       <c r="B106" t="inlineStr">
         <is>
-          <t>2026-07-11 08:31:17 PM PT</t>
+          <t>2026-07-11 08:33:17 PM PT</t>
         </is>
       </c>
       <c r="C106" t="n">
@@ -12825,7 +12825,7 @@
       </c>
       <c r="B107" t="inlineStr">
         <is>
-          <t>2026-07-11 08:31:17 PM PT</t>
+          <t>2026-07-11 08:33:17 PM PT</t>
         </is>
       </c>
       <c r="C107" t="n">
@@ -12939,7 +12939,7 @@
       </c>
       <c r="B108" t="inlineStr">
         <is>
-          <t>2026-07-11 08:31:17 PM PT</t>
+          <t>2026-07-11 08:33:17 PM PT</t>
         </is>
       </c>
       <c r="C108" t="n">
@@ -13053,7 +13053,7 @@
       </c>
       <c r="B109" t="inlineStr">
         <is>
-          <t>2026-07-11 08:31:17 PM PT</t>
+          <t>2026-07-11 08:33:17 PM PT</t>
         </is>
       </c>
       <c r="C109" t="n">
@@ -13167,7 +13167,7 @@
       </c>
       <c r="B110" t="inlineStr">
         <is>
-          <t>2026-07-11 08:31:17 PM PT</t>
+          <t>2026-07-11 08:33:17 PM PT</t>
         </is>
       </c>
       <c r="C110" t="n">
@@ -13281,7 +13281,7 @@
       </c>
       <c r="B111" t="inlineStr">
         <is>
-          <t>2026-07-11 08:31:17 PM PT</t>
+          <t>2026-07-11 08:33:16 PM PT</t>
         </is>
       </c>
       <c r="C111" t="n">
@@ -13395,7 +13395,7 @@
       </c>
       <c r="B112" t="inlineStr">
         <is>
-          <t>2026-07-11 08:31:18 PM PT</t>
+          <t>2026-07-11 08:33:18 PM PT</t>
         </is>
       </c>
       <c r="C112" t="n">
@@ -13509,7 +13509,7 @@
       </c>
       <c r="B113" t="inlineStr">
         <is>
-          <t>2026-07-11 08:31:17 PM PT</t>
+          <t>2026-07-11 08:33:17 PM PT</t>
         </is>
       </c>
       <c r="C113" t="n">
@@ -13623,7 +13623,7 @@
       </c>
       <c r="B114" t="inlineStr">
         <is>
-          <t>2026-07-11 08:31:17 PM PT</t>
+          <t>2026-07-11 08:33:17 PM PT</t>
         </is>
       </c>
       <c r="C114" t="n">
@@ -13737,7 +13737,7 @@
       </c>
       <c r="B115" t="inlineStr">
         <is>
-          <t>2026-07-11 08:31:18 PM PT</t>
+          <t>2026-07-11 08:33:17 PM PT</t>
         </is>
       </c>
       <c r="C115" t="n">
@@ -13851,7 +13851,7 @@
       </c>
       <c r="B116" t="inlineStr">
         <is>
-          <t>2026-07-11 08:31:18 PM PT</t>
+          <t>2026-07-11 08:33:18 PM PT</t>
         </is>
       </c>
       <c r="C116" t="n">
@@ -13882,7 +13882,7 @@
         <v>1</v>
       </c>
       <c r="J116" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K116" t="inlineStr">
         <is>
@@ -13963,7 +13963,7 @@
         <v>8</v>
       </c>
       <c r="AG116" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
     </row>
     <row r="117">
@@ -13974,7 +13974,7 @@
       </c>
       <c r="B117" t="inlineStr">
         <is>
-          <t>2026-07-11 08:31:18 PM PT</t>
+          <t>2026-07-11 08:33:17 PM PT</t>
         </is>
       </c>
       <c r="C117" t="n">
@@ -14088,7 +14088,7 @@
       </c>
       <c r="B118" t="inlineStr">
         <is>
-          <t>2026-07-11 08:31:18 PM PT</t>
+          <t>2026-07-11 08:33:18 PM PT</t>
         </is>
       </c>
       <c r="C118" t="n">
@@ -14202,7 +14202,7 @@
       </c>
       <c r="B119" t="inlineStr">
         <is>
-          <t>2026-07-11 08:31:18 PM PT</t>
+          <t>2026-07-11 08:33:18 PM PT</t>
         </is>
       </c>
       <c r="C119" t="n">
@@ -14316,7 +14316,7 @@
       </c>
       <c r="B120" t="inlineStr">
         <is>
-          <t>2026-07-11 08:31:18 PM PT</t>
+          <t>2026-07-11 08:33:17 PM PT</t>
         </is>
       </c>
       <c r="C120" t="n">
@@ -14430,7 +14430,7 @@
       </c>
       <c r="B121" t="inlineStr">
         <is>
-          <t>2026-07-11 08:31:17 PM PT</t>
+          <t>2026-07-11 08:33:17 PM PT</t>
         </is>
       </c>
       <c r="C121" t="n">
@@ -14544,7 +14544,7 @@
       </c>
       <c r="B122" t="inlineStr">
         <is>
-          <t>2026-07-11 08:31:18 PM PT</t>
+          <t>2026-07-11 08:33:18 PM PT</t>
         </is>
       </c>
       <c r="C122" t="n">
@@ -14658,7 +14658,7 @@
       </c>
       <c r="B123" t="inlineStr">
         <is>
-          <t>2026-07-11 08:31:17 PM PT</t>
+          <t>2026-07-11 08:33:17 PM PT</t>
         </is>
       </c>
       <c r="C123" t="n">
@@ -14772,7 +14772,7 @@
       </c>
       <c r="B124" t="inlineStr">
         <is>
-          <t>2026-07-11 08:31:17 PM PT</t>
+          <t>2026-07-11 08:33:16 PM PT</t>
         </is>
       </c>
       <c r="C124" t="n">
@@ -14886,7 +14886,7 @@
       </c>
       <c r="B125" t="inlineStr">
         <is>
-          <t>2026-07-11 08:31:18 PM PT</t>
+          <t>2026-07-11 08:33:17 PM PT</t>
         </is>
       </c>
       <c r="C125" t="n">
@@ -15000,7 +15000,7 @@
       </c>
       <c r="B126" t="inlineStr">
         <is>
-          <t>2026-07-11 08:31:18 PM PT</t>
+          <t>2026-07-11 08:33:17 PM PT</t>
         </is>
       </c>
       <c r="C126" t="n">
@@ -15114,7 +15114,7 @@
       </c>
       <c r="B127" t="inlineStr">
         <is>
-          <t>2026-07-11 08:31:18 PM PT</t>
+          <t>2026-07-11 08:33:17 PM PT</t>
         </is>
       </c>
       <c r="C127" t="n">
@@ -15228,7 +15228,7 @@
       </c>
       <c r="B128" t="inlineStr">
         <is>
-          <t>2026-07-11 08:31:18 PM PT</t>
+          <t>2026-07-11 08:33:17 PM PT</t>
         </is>
       </c>
       <c r="C128" t="n">
@@ -15342,7 +15342,7 @@
       </c>
       <c r="B129" t="inlineStr">
         <is>
-          <t>2026-07-11 08:31:18 PM PT</t>
+          <t>2026-07-11 08:33:18 PM PT</t>
         </is>
       </c>
       <c r="C129" t="n">
@@ -15355,7 +15355,7 @@
       </c>
       <c r="E129" t="inlineStr">
         <is>
-          <t>Top 8 | 0 out</t>
+          <t>Top 8 | 1 out</t>
         </is>
       </c>
       <c r="F129" t="n">
@@ -15367,13 +15367,13 @@
         </is>
       </c>
       <c r="H129" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I129" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J129" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K129" t="inlineStr">
         <is>
@@ -15465,7 +15465,7 @@
       </c>
       <c r="B130" t="inlineStr">
         <is>
-          <t>2026-07-11 08:31:17 PM PT</t>
+          <t>2026-07-11 08:33:17 PM PT</t>
         </is>
       </c>
       <c r="C130" t="n">
@@ -15579,7 +15579,7 @@
       </c>
       <c r="B131" t="inlineStr">
         <is>
-          <t>2026-07-11 08:31:17 PM PT</t>
+          <t>2026-07-11 08:33:17 PM PT</t>
         </is>
       </c>
       <c r="C131" t="n">
@@ -15693,7 +15693,7 @@
       </c>
       <c r="B132" t="inlineStr">
         <is>
-          <t>2026-07-11 08:31:16 PM PT</t>
+          <t>2026-07-11 08:33:16 PM PT</t>
         </is>
       </c>
       <c r="C132" t="n">
@@ -15807,7 +15807,7 @@
       </c>
       <c r="B133" t="inlineStr">
         <is>
-          <t>2026-07-11 08:31:16 PM PT</t>
+          <t>2026-07-11 08:33:16 PM PT</t>
         </is>
       </c>
       <c r="C133" t="n">
@@ -15921,7 +15921,7 @@
       </c>
       <c r="B134" t="inlineStr">
         <is>
-          <t>2026-07-11 08:31:16 PM PT</t>
+          <t>2026-07-11 08:33:16 PM PT</t>
         </is>
       </c>
       <c r="C134" t="n">
@@ -16035,7 +16035,7 @@
       </c>
       <c r="B135" t="inlineStr">
         <is>
-          <t>2026-07-11 08:31:17 PM PT</t>
+          <t>2026-07-11 08:33:17 PM PT</t>
         </is>
       </c>
       <c r="C135" t="n">
@@ -16149,7 +16149,7 @@
       </c>
       <c r="B136" t="inlineStr">
         <is>
-          <t>2026-07-11 08:31:16 PM PT</t>
+          <t>2026-07-11 08:33:16 PM PT</t>
         </is>
       </c>
       <c r="C136" t="n">
@@ -16263,7 +16263,7 @@
       </c>
       <c r="B137" t="inlineStr">
         <is>
-          <t>2026-07-11 08:31:16 PM PT</t>
+          <t>2026-07-11 08:33:16 PM PT</t>
         </is>
       </c>
       <c r="C137" t="n">
@@ -16377,7 +16377,7 @@
       </c>
       <c r="B138" t="inlineStr">
         <is>
-          <t>2026-07-11 08:31:17 PM PT</t>
+          <t>2026-07-11 08:33:17 PM PT</t>
         </is>
       </c>
       <c r="C138" t="n">
@@ -16491,7 +16491,7 @@
       </c>
       <c r="B139" t="inlineStr">
         <is>
-          <t>2026-07-11 08:31:17 PM PT</t>
+          <t>2026-07-11 08:33:17 PM PT</t>
         </is>
       </c>
       <c r="C139" t="n">
@@ -16605,7 +16605,7 @@
       </c>
       <c r="B140" t="inlineStr">
         <is>
-          <t>2026-07-11 08:31:17 PM PT</t>
+          <t>2026-07-11 08:33:17 PM PT</t>
         </is>
       </c>
       <c r="C140" t="n">
@@ -16719,7 +16719,7 @@
       </c>
       <c r="B141" t="inlineStr">
         <is>
-          <t>2026-07-11 08:31:18 PM PT</t>
+          <t>2026-07-11 08:33:18 PM PT</t>
         </is>
       </c>
       <c r="C141" t="n">
@@ -16833,7 +16833,7 @@
       </c>
       <c r="B142" t="inlineStr">
         <is>
-          <t>2026-07-11 08:31:18 PM PT</t>
+          <t>2026-07-11 08:33:18 PM PT</t>
         </is>
       </c>
       <c r="C142" t="n">
@@ -16947,7 +16947,7 @@
       </c>
       <c r="B143" t="inlineStr">
         <is>
-          <t>2026-07-11 08:31:18 PM PT</t>
+          <t>2026-07-11 08:33:18 PM PT</t>
         </is>
       </c>
       <c r="C143" t="n">
@@ -17061,7 +17061,7 @@
       </c>
       <c r="B144" t="inlineStr">
         <is>
-          <t>2026-07-11 08:31:17 PM PT</t>
+          <t>2026-07-11 08:33:17 PM PT</t>
         </is>
       </c>
       <c r="C144" t="n">
@@ -17175,7 +17175,7 @@
       </c>
       <c r="B145" t="inlineStr">
         <is>
-          <t>2026-07-11 08:31:18 PM PT</t>
+          <t>2026-07-11 08:33:17 PM PT</t>
         </is>
       </c>
       <c r="C145" t="n">
@@ -17289,7 +17289,7 @@
       </c>
       <c r="B146" t="inlineStr">
         <is>
-          <t>2026-07-11 08:31:18 PM PT</t>
+          <t>2026-07-11 08:33:17 PM PT</t>
         </is>
       </c>
       <c r="C146" t="n">
@@ -17403,7 +17403,7 @@
       </c>
       <c r="B147" t="inlineStr">
         <is>
-          <t>2026-07-11 08:31:18 PM PT</t>
+          <t>2026-07-11 08:33:18 PM PT</t>
         </is>
       </c>
       <c r="C147" t="n">
@@ -17517,7 +17517,7 @@
       </c>
       <c r="B148" t="inlineStr">
         <is>
-          <t>2026-07-11 08:31:17 PM PT</t>
+          <t>2026-07-11 08:33:17 PM PT</t>
         </is>
       </c>
       <c r="C148" t="n">
@@ -17631,7 +17631,7 @@
       </c>
       <c r="B149" t="inlineStr">
         <is>
-          <t>2026-07-11 08:31:17 PM PT</t>
+          <t>2026-07-11 08:33:16 PM PT</t>
         </is>
       </c>
       <c r="C149" t="n">
@@ -17745,7 +17745,7 @@
       </c>
       <c r="B150" t="inlineStr">
         <is>
-          <t>2026-07-11 08:31:16 PM PT</t>
+          <t>2026-07-11 08:33:16 PM PT</t>
         </is>
       </c>
       <c r="C150" t="n">
@@ -17859,7 +17859,7 @@
       </c>
       <c r="B151" t="inlineStr">
         <is>
-          <t>2026-07-11 08:31:16 PM PT</t>
+          <t>2026-07-11 08:33:16 PM PT</t>
         </is>
       </c>
       <c r="C151" t="n">
@@ -17973,7 +17973,7 @@
       </c>
       <c r="B152" t="inlineStr">
         <is>
-          <t>2026-07-11 08:31:16 PM PT</t>
+          <t>2026-07-11 08:33:16 PM PT</t>
         </is>
       </c>
       <c r="C152" t="n">
@@ -18087,7 +18087,7 @@
       </c>
       <c r="B153" t="inlineStr">
         <is>
-          <t>2026-07-11 08:31:18 PM PT</t>
+          <t>2026-07-11 08:33:17 PM PT</t>
         </is>
       </c>
       <c r="C153" t="n">
@@ -18201,7 +18201,7 @@
       </c>
       <c r="B154" t="inlineStr">
         <is>
-          <t>2026-07-11 08:31:18 PM PT</t>
+          <t>2026-07-11 08:33:17 PM PT</t>
         </is>
       </c>
       <c r="C154" t="n">
@@ -18315,7 +18315,7 @@
       </c>
       <c r="B155" t="inlineStr">
         <is>
-          <t>2026-07-11 08:31:16 PM PT</t>
+          <t>2026-07-11 08:33:16 PM PT</t>
         </is>
       </c>
       <c r="C155" t="n">
@@ -18429,7 +18429,7 @@
       </c>
       <c r="B156" t="inlineStr">
         <is>
-          <t>2026-07-11 08:31:18 PM PT</t>
+          <t>2026-07-11 08:33:18 PM PT</t>
         </is>
       </c>
       <c r="C156" t="n">
@@ -18460,7 +18460,7 @@
         <v>1</v>
       </c>
       <c r="J156" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K156" t="inlineStr">
         <is>
@@ -18541,7 +18541,7 @@
         <v>8</v>
       </c>
       <c r="AG156" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
     </row>
     <row r="157">
@@ -18552,7 +18552,7 @@
       </c>
       <c r="B157" t="inlineStr">
         <is>
-          <t>2026-07-11 08:31:18 PM PT</t>
+          <t>2026-07-11 08:33:18 PM PT</t>
         </is>
       </c>
       <c r="C157" t="n">
@@ -18583,7 +18583,7 @@
         <v>1</v>
       </c>
       <c r="J157" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K157" t="inlineStr">
         <is>
@@ -18675,7 +18675,7 @@
       </c>
       <c r="B158" t="inlineStr">
         <is>
-          <t>2026-07-11 08:31:18 PM PT</t>
+          <t>2026-07-11 08:33:18 PM PT</t>
         </is>
       </c>
       <c r="C158" t="n">
@@ -18706,7 +18706,7 @@
         <v>1</v>
       </c>
       <c r="J158" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K158" t="inlineStr">
         <is>
@@ -18798,7 +18798,7 @@
       </c>
       <c r="B159" t="inlineStr">
         <is>
-          <t>2026-07-11 08:31:18 PM PT</t>
+          <t>2026-07-11 08:33:18 PM PT</t>
         </is>
       </c>
       <c r="C159" t="n">
@@ -18829,7 +18829,7 @@
         <v>1</v>
       </c>
       <c r="J159" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K159" t="inlineStr">
         <is>
@@ -18921,7 +18921,7 @@
       </c>
       <c r="B160" t="inlineStr">
         <is>
-          <t>2026-07-11 08:31:18 PM PT</t>
+          <t>2026-07-11 08:33:18 PM PT</t>
         </is>
       </c>
       <c r="C160" t="n">
@@ -19035,7 +19035,7 @@
       </c>
       <c r="B161" t="inlineStr">
         <is>
-          <t>2026-07-11 08:31:18 PM PT</t>
+          <t>2026-07-11 08:33:18 PM PT</t>
         </is>
       </c>
       <c r="C161" t="n">
@@ -19149,7 +19149,7 @@
       </c>
       <c r="B162" t="inlineStr">
         <is>
-          <t>2026-07-11 08:31:18 PM PT</t>
+          <t>2026-07-11 08:33:18 PM PT</t>
         </is>
       </c>
       <c r="C162" t="n">
@@ -19263,7 +19263,7 @@
       </c>
       <c r="B163" t="inlineStr">
         <is>
-          <t>2026-07-11 08:31:18 PM PT</t>
+          <t>2026-07-11 08:33:18 PM PT</t>
         </is>
       </c>
       <c r="C163" t="n">
@@ -19377,7 +19377,7 @@
       </c>
       <c r="B164" t="inlineStr">
         <is>
-          <t>2026-07-11 08:31:18 PM PT</t>
+          <t>2026-07-11 08:33:18 PM PT</t>
         </is>
       </c>
       <c r="C164" t="n">
@@ -19491,7 +19491,7 @@
       </c>
       <c r="B165" t="inlineStr">
         <is>
-          <t>2026-07-11 08:31:17 PM PT</t>
+          <t>2026-07-11 08:33:17 PM PT</t>
         </is>
       </c>
       <c r="C165" t="n">
@@ -19605,7 +19605,7 @@
       </c>
       <c r="B166" t="inlineStr">
         <is>
-          <t>2026-07-11 08:31:17 PM PT</t>
+          <t>2026-07-11 08:33:17 PM PT</t>
         </is>
       </c>
       <c r="C166" t="n">
@@ -19719,7 +19719,7 @@
       </c>
       <c r="B167" t="inlineStr">
         <is>
-          <t>2026-07-11 08:31:18 PM PT</t>
+          <t>2026-07-11 08:33:17 PM PT</t>
         </is>
       </c>
       <c r="C167" t="n">
@@ -19833,7 +19833,7 @@
       </c>
       <c r="B168" t="inlineStr">
         <is>
-          <t>2026-07-11 08:31:18 PM PT</t>
+          <t>2026-07-11 08:33:17 PM PT</t>
         </is>
       </c>
       <c r="C168" t="n">
@@ -19947,7 +19947,7 @@
       </c>
       <c r="B169" t="inlineStr">
         <is>
-          <t>2026-07-11 08:31:18 PM PT</t>
+          <t>2026-07-11 08:33:17 PM PT</t>
         </is>
       </c>
       <c r="C169" t="n">
@@ -20061,7 +20061,7 @@
       </c>
       <c r="B170" t="inlineStr">
         <is>
-          <t>2026-07-11 08:31:16 PM PT</t>
+          <t>2026-07-11 08:33:16 PM PT</t>
         </is>
       </c>
       <c r="C170" t="n">
@@ -20175,7 +20175,7 @@
       </c>
       <c r="B171" t="inlineStr">
         <is>
-          <t>2026-07-11 08:31:18 PM PT</t>
+          <t>2026-07-11 08:33:18 PM PT</t>
         </is>
       </c>
       <c r="C171" t="n">
@@ -20188,7 +20188,7 @@
       </c>
       <c r="E171" t="inlineStr">
         <is>
-          <t>Top 8 | 0 out</t>
+          <t>Top 8 | 1 out</t>
         </is>
       </c>
       <c r="F171" t="n">
@@ -20200,13 +20200,13 @@
         </is>
       </c>
       <c r="H171" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I171" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J171" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K171" t="inlineStr">
         <is>
@@ -20298,7 +20298,7 @@
       </c>
       <c r="B172" t="inlineStr">
         <is>
-          <t>2026-07-11 08:31:18 PM PT</t>
+          <t>2026-07-11 08:33:18 PM PT</t>
         </is>
       </c>
       <c r="C172" t="n">
@@ -20311,7 +20311,7 @@
       </c>
       <c r="E172" t="inlineStr">
         <is>
-          <t>Top 8 | 0 out</t>
+          <t>Top 8 | 1 out</t>
         </is>
       </c>
       <c r="F172" t="n">
@@ -20323,13 +20323,13 @@
         </is>
       </c>
       <c r="H172" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I172" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J172" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K172" t="inlineStr">
         <is>
@@ -20421,7 +20421,7 @@
       </c>
       <c r="B173" t="inlineStr">
         <is>
-          <t>2026-07-11 08:31:17 PM PT</t>
+          <t>2026-07-11 08:33:17 PM PT</t>
         </is>
       </c>
       <c r="C173" t="n">
@@ -20535,7 +20535,7 @@
       </c>
       <c r="B174" t="inlineStr">
         <is>
-          <t>2026-07-11 08:31:17 PM PT</t>
+          <t>2026-07-11 08:33:17 PM PT</t>
         </is>
       </c>
       <c r="C174" t="n">
@@ -20649,7 +20649,7 @@
       </c>
       <c r="B175" t="inlineStr">
         <is>
-          <t>2026-07-11 08:31:16 PM PT</t>
+          <t>2026-07-11 08:33:16 PM PT</t>
         </is>
       </c>
       <c r="C175" t="n">
@@ -20763,7 +20763,7 @@
       </c>
       <c r="B176" t="inlineStr">
         <is>
-          <t>2026-07-11 08:31:16 PM PT</t>
+          <t>2026-07-11 08:33:16 PM PT</t>
         </is>
       </c>
       <c r="C176" t="n">
@@ -20877,7 +20877,7 @@
       </c>
       <c r="B177" t="inlineStr">
         <is>
-          <t>2026-07-11 08:31:16 PM PT</t>
+          <t>2026-07-11 08:33:16 PM PT</t>
         </is>
       </c>
       <c r="C177" t="n">
@@ -20991,7 +20991,7 @@
       </c>
       <c r="B178" t="inlineStr">
         <is>
-          <t>2026-07-11 08:31:16 PM PT</t>
+          <t>2026-07-11 08:33:16 PM PT</t>
         </is>
       </c>
       <c r="C178" t="n">
@@ -21105,7 +21105,7 @@
       </c>
       <c r="B179" t="inlineStr">
         <is>
-          <t>2026-07-11 08:31:16 PM PT</t>
+          <t>2026-07-11 08:33:16 PM PT</t>
         </is>
       </c>
       <c r="C179" t="n">
@@ -21219,7 +21219,7 @@
       </c>
       <c r="B180" t="inlineStr">
         <is>
-          <t>2026-07-11 08:31:17 PM PT</t>
+          <t>2026-07-11 08:33:17 PM PT</t>
         </is>
       </c>
       <c r="C180" t="n">
@@ -21333,7 +21333,7 @@
       </c>
       <c r="B181" t="inlineStr">
         <is>
-          <t>2026-07-11 08:31:17 PM PT</t>
+          <t>2026-07-11 08:33:17 PM PT</t>
         </is>
       </c>
       <c r="C181" t="n">
@@ -21447,7 +21447,7 @@
       </c>
       <c r="B182" t="inlineStr">
         <is>
-          <t>2026-07-11 08:31:17 PM PT</t>
+          <t>2026-07-11 08:33:17 PM PT</t>
         </is>
       </c>
       <c r="C182" t="n">
@@ -21561,7 +21561,7 @@
       </c>
       <c r="B183" t="inlineStr">
         <is>
-          <t>2026-07-11 08:31:18 PM PT</t>
+          <t>2026-07-11 08:33:17 PM PT</t>
         </is>
       </c>
       <c r="C183" t="n">
@@ -21675,7 +21675,7 @@
       </c>
       <c r="B184" t="inlineStr">
         <is>
-          <t>2026-07-11 08:31:16 PM PT</t>
+          <t>2026-07-11 08:33:16 PM PT</t>
         </is>
       </c>
       <c r="C184" t="n">
@@ -21789,7 +21789,7 @@
       </c>
       <c r="B185" t="inlineStr">
         <is>
-          <t>2026-07-11 08:31:16 PM PT</t>
+          <t>2026-07-11 08:33:16 PM PT</t>
         </is>
       </c>
       <c r="C185" t="n">
@@ -21903,7 +21903,7 @@
       </c>
       <c r="B186" t="inlineStr">
         <is>
-          <t>2026-07-11 08:31:17 PM PT</t>
+          <t>2026-07-11 08:33:17 PM PT</t>
         </is>
       </c>
       <c r="C186" t="n">
@@ -22017,7 +22017,7 @@
       </c>
       <c r="B187" t="inlineStr">
         <is>
-          <t>2026-07-11 08:31:17 PM PT</t>
+          <t>2026-07-11 08:33:17 PM PT</t>
         </is>
       </c>
       <c r="C187" t="n">
@@ -22131,7 +22131,7 @@
       </c>
       <c r="B188" t="inlineStr">
         <is>
-          <t>2026-07-11 08:31:17 PM PT</t>
+          <t>2026-07-11 08:33:17 PM PT</t>
         </is>
       </c>
       <c r="C188" t="n">
@@ -22245,7 +22245,7 @@
       </c>
       <c r="B189" t="inlineStr">
         <is>
-          <t>2026-07-11 08:31:18 PM PT</t>
+          <t>2026-07-11 08:33:17 PM PT</t>
         </is>
       </c>
       <c r="C189" t="n">
@@ -22359,7 +22359,7 @@
       </c>
       <c r="B190" t="inlineStr">
         <is>
-          <t>2026-07-11 08:31:18 PM PT</t>
+          <t>2026-07-11 08:33:18 PM PT</t>
         </is>
       </c>
       <c r="C190" t="n">
@@ -22390,7 +22390,7 @@
         <v>1</v>
       </c>
       <c r="J190" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K190" t="inlineStr">
         <is>
@@ -22482,7 +22482,7 @@
       </c>
       <c r="B191" t="inlineStr">
         <is>
-          <t>2026-07-11 08:31:17 PM PT</t>
+          <t>2026-07-11 08:33:17 PM PT</t>
         </is>
       </c>
       <c r="C191" t="n">
@@ -22596,7 +22596,7 @@
       </c>
       <c r="B192" t="inlineStr">
         <is>
-          <t>2026-07-11 08:31:17 PM PT</t>
+          <t>2026-07-11 08:33:17 PM PT</t>
         </is>
       </c>
       <c r="C192" t="n">
@@ -22710,7 +22710,7 @@
       </c>
       <c r="B193" t="inlineStr">
         <is>
-          <t>2026-07-11 08:31:18 PM PT</t>
+          <t>2026-07-11 08:33:18 PM PT</t>
         </is>
       </c>
       <c r="C193" t="n">
@@ -22723,7 +22723,7 @@
       </c>
       <c r="E193" t="inlineStr">
         <is>
-          <t>Top 8 | 0 out</t>
+          <t>Top 8 | 1 out</t>
         </is>
       </c>
       <c r="F193" t="n">
@@ -22735,13 +22735,13 @@
         </is>
       </c>
       <c r="H193" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I193" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J193" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K193" t="inlineStr">
         <is>
@@ -22819,10 +22819,10 @@
         <v>2</v>
       </c>
       <c r="AF193" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="AG193" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
     </row>
     <row r="194">
@@ -22833,7 +22833,7 @@
       </c>
       <c r="B194" t="inlineStr">
         <is>
-          <t>2026-07-11 08:31:18 PM PT</t>
+          <t>2026-07-11 08:33:18 PM PT</t>
         </is>
       </c>
       <c r="C194" t="n">
@@ -22846,7 +22846,7 @@
       </c>
       <c r="E194" t="inlineStr">
         <is>
-          <t>Top 8 | 0 out</t>
+          <t>Top 8 | 1 out</t>
         </is>
       </c>
       <c r="F194" t="n">
@@ -22858,13 +22858,13 @@
         </is>
       </c>
       <c r="H194" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I194" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J194" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K194" t="inlineStr">
         <is>
@@ -22942,10 +22942,10 @@
         <v>2</v>
       </c>
       <c r="AF194" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="AG194" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
     </row>
     <row r="195">
@@ -22956,7 +22956,7 @@
       </c>
       <c r="B195" t="inlineStr">
         <is>
-          <t>2026-07-11 08:31:17 PM PT</t>
+          <t>2026-07-11 08:33:16 PM PT</t>
         </is>
       </c>
       <c r="C195" t="n">
@@ -23070,7 +23070,7 @@
       </c>
       <c r="B196" t="inlineStr">
         <is>
-          <t>2026-07-11 08:31:18 PM PT</t>
+          <t>2026-07-11 08:33:18 PM PT</t>
         </is>
       </c>
       <c r="C196" t="n">
@@ -23184,7 +23184,7 @@
       </c>
       <c r="B197" t="inlineStr">
         <is>
-          <t>2026-07-11 08:31:18 PM PT</t>
+          <t>2026-07-11 08:33:18 PM PT</t>
         </is>
       </c>
       <c r="C197" t="n">
@@ -23298,7 +23298,7 @@
       </c>
       <c r="B198" t="inlineStr">
         <is>
-          <t>2026-07-11 08:31:18 PM PT</t>
+          <t>2026-07-11 08:33:17 PM PT</t>
         </is>
       </c>
       <c r="C198" t="n">
@@ -23412,7 +23412,7 @@
       </c>
       <c r="B199" t="inlineStr">
         <is>
-          <t>2026-07-11 08:31:17 PM PT</t>
+          <t>2026-07-11 08:33:17 PM PT</t>
         </is>
       </c>
       <c r="C199" t="n">
@@ -23526,7 +23526,7 @@
       </c>
       <c r="B200" t="inlineStr">
         <is>
-          <t>2026-07-11 08:31:17 PM PT</t>
+          <t>2026-07-11 08:33:17 PM PT</t>
         </is>
       </c>
       <c r="C200" t="n">
@@ -23640,7 +23640,7 @@
       </c>
       <c r="B201" t="inlineStr">
         <is>
-          <t>2026-07-11 08:31:17 PM PT</t>
+          <t>2026-07-11 08:33:17 PM PT</t>
         </is>
       </c>
       <c r="C201" t="n">
@@ -23754,7 +23754,7 @@
       </c>
       <c r="B202" t="inlineStr">
         <is>
-          <t>2026-07-11 08:31:18 PM PT</t>
+          <t>2026-07-11 08:33:18 PM PT</t>
         </is>
       </c>
       <c r="C202" t="n">
@@ -23868,7 +23868,7 @@
       </c>
       <c r="B203" t="inlineStr">
         <is>
-          <t>2026-07-11 08:31:17 PM PT</t>
+          <t>2026-07-11 08:33:17 PM PT</t>
         </is>
       </c>
       <c r="C203" t="n">
@@ -23982,7 +23982,7 @@
       </c>
       <c r="B204" t="inlineStr">
         <is>
-          <t>2026-07-11 08:31:17 PM PT</t>
+          <t>2026-07-11 08:33:17 PM PT</t>
         </is>
       </c>
       <c r="C204" t="n">
@@ -24096,7 +24096,7 @@
       </c>
       <c r="B205" t="inlineStr">
         <is>
-          <t>2026-07-11 08:31:17 PM PT</t>
+          <t>2026-07-11 08:33:17 PM PT</t>
         </is>
       </c>
       <c r="C205" t="n">
@@ -24210,7 +24210,7 @@
       </c>
       <c r="B206" t="inlineStr">
         <is>
-          <t>2026-07-11 08:31:17 PM PT</t>
+          <t>2026-07-11 08:33:16 PM PT</t>
         </is>
       </c>
       <c r="C206" t="n">
@@ -24324,7 +24324,7 @@
       </c>
       <c r="B207" t="inlineStr">
         <is>
-          <t>2026-07-11 08:31:17 PM PT</t>
+          <t>2026-07-11 08:33:16 PM PT</t>
         </is>
       </c>
       <c r="C207" t="n">
@@ -24438,7 +24438,7 @@
       </c>
       <c r="B208" t="inlineStr">
         <is>
-          <t>2026-07-11 08:31:18 PM PT</t>
+          <t>2026-07-11 08:33:17 PM PT</t>
         </is>
       </c>
       <c r="C208" t="n">
@@ -24552,7 +24552,7 @@
       </c>
       <c r="B209" t="inlineStr">
         <is>
-          <t>2026-07-11 08:31:18 PM PT</t>
+          <t>2026-07-11 08:33:17 PM PT</t>
         </is>
       </c>
       <c r="C209" t="n">
@@ -24666,7 +24666,7 @@
       </c>
       <c r="B210" t="inlineStr">
         <is>
-          <t>2026-07-11 08:31:18 PM PT</t>
+          <t>2026-07-11 08:33:17 PM PT</t>
         </is>
       </c>
       <c r="C210" t="n">
@@ -24780,7 +24780,7 @@
       </c>
       <c r="B211" t="inlineStr">
         <is>
-          <t>2026-07-11 08:31:18 PM PT</t>
+          <t>2026-07-11 08:33:17 PM PT</t>
         </is>
       </c>
       <c r="C211" t="n">
@@ -24894,7 +24894,7 @@
       </c>
       <c r="B212" t="inlineStr">
         <is>
-          <t>2026-07-11 08:31:18 PM PT</t>
+          <t>2026-07-11 08:33:17 PM PT</t>
         </is>
       </c>
       <c r="C212" t="n">
@@ -25008,7 +25008,7 @@
       </c>
       <c r="B213" t="inlineStr">
         <is>
-          <t>2026-07-11 08:31:16 PM PT</t>
+          <t>2026-07-11 08:33:16 PM PT</t>
         </is>
       </c>
       <c r="C213" t="n">
@@ -25122,7 +25122,7 @@
       </c>
       <c r="B214" t="inlineStr">
         <is>
-          <t>2026-07-11 08:31:17 PM PT</t>
+          <t>2026-07-11 08:33:17 PM PT</t>
         </is>
       </c>
       <c r="C214" t="n">
@@ -25236,7 +25236,7 @@
       </c>
       <c r="B215" t="inlineStr">
         <is>
-          <t>2026-07-11 08:31:17 PM PT</t>
+          <t>2026-07-11 08:33:17 PM PT</t>
         </is>
       </c>
       <c r="C215" t="n">
@@ -25350,7 +25350,7 @@
       </c>
       <c r="B216" t="inlineStr">
         <is>
-          <t>2026-07-11 08:31:16 PM PT</t>
+          <t>2026-07-11 08:33:16 PM PT</t>
         </is>
       </c>
       <c r="C216" t="n">
@@ -25464,7 +25464,7 @@
       </c>
       <c r="B217" t="inlineStr">
         <is>
-          <t>2026-07-11 08:31:17 PM PT</t>
+          <t>2026-07-11 08:33:17 PM PT</t>
         </is>
       </c>
       <c r="C217" t="n">
@@ -25578,7 +25578,7 @@
       </c>
       <c r="B218" t="inlineStr">
         <is>
-          <t>2026-07-11 08:31:17 PM PT</t>
+          <t>2026-07-11 08:33:17 PM PT</t>
         </is>
       </c>
       <c r="C218" t="n">
@@ -25692,7 +25692,7 @@
       </c>
       <c r="B219" t="inlineStr">
         <is>
-          <t>2026-07-11 08:31:17 PM PT</t>
+          <t>2026-07-11 08:33:17 PM PT</t>
         </is>
       </c>
       <c r="C219" t="n">
@@ -25806,7 +25806,7 @@
       </c>
       <c r="B220" t="inlineStr">
         <is>
-          <t>2026-07-11 08:31:17 PM PT</t>
+          <t>2026-07-11 08:33:17 PM PT</t>
         </is>
       </c>
       <c r="C220" t="n">
@@ -25920,7 +25920,7 @@
       </c>
       <c r="B221" t="inlineStr">
         <is>
-          <t>2026-07-11 08:31:17 PM PT</t>
+          <t>2026-07-11 08:33:17 PM PT</t>
         </is>
       </c>
       <c r="C221" t="n">
@@ -26034,7 +26034,7 @@
       </c>
       <c r="B222" t="inlineStr">
         <is>
-          <t>2026-07-11 08:31:17 PM PT</t>
+          <t>2026-07-11 08:33:17 PM PT</t>
         </is>
       </c>
       <c r="C222" t="n">
@@ -26148,7 +26148,7 @@
       </c>
       <c r="B223" t="inlineStr">
         <is>
-          <t>2026-07-11 08:31:17 PM PT</t>
+          <t>2026-07-11 08:33:17 PM PT</t>
         </is>
       </c>
       <c r="C223" t="n">
@@ -26262,7 +26262,7 @@
       </c>
       <c r="B224" t="inlineStr">
         <is>
-          <t>2026-07-11 08:31:16 PM PT</t>
+          <t>2026-07-11 08:33:16 PM PT</t>
         </is>
       </c>
       <c r="C224" t="n">
@@ -26376,7 +26376,7 @@
       </c>
       <c r="B225" t="inlineStr">
         <is>
-          <t>2026-07-11 08:31:16 PM PT</t>
+          <t>2026-07-11 08:33:16 PM PT</t>
         </is>
       </c>
       <c r="C225" t="n">
@@ -26490,7 +26490,7 @@
       </c>
       <c r="B226" t="inlineStr">
         <is>
-          <t>2026-07-11 08:31:17 PM PT</t>
+          <t>2026-07-11 08:33:17 PM PT</t>
         </is>
       </c>
       <c r="C226" t="n">
@@ -26604,7 +26604,7 @@
       </c>
       <c r="B227" t="inlineStr">
         <is>
-          <t>2026-07-11 08:31:17 PM PT</t>
+          <t>2026-07-11 08:33:17 PM PT</t>
         </is>
       </c>
       <c r="C227" t="n">
@@ -26718,7 +26718,7 @@
       </c>
       <c r="B228" t="inlineStr">
         <is>
-          <t>2026-07-11 08:31:18 PM PT</t>
+          <t>2026-07-11 08:33:17 PM PT</t>
         </is>
       </c>
       <c r="C228" t="n">
@@ -26832,7 +26832,7 @@
       </c>
       <c r="B229" t="inlineStr">
         <is>
-          <t>2026-07-11 08:31:18 PM PT</t>
+          <t>2026-07-11 08:33:17 PM PT</t>
         </is>
       </c>
       <c r="C229" t="n">
@@ -26946,7 +26946,7 @@
       </c>
       <c r="B230" t="inlineStr">
         <is>
-          <t>2026-07-11 08:31:18 PM PT</t>
+          <t>2026-07-11 08:33:18 PM PT</t>
         </is>
       </c>
       <c r="C230" t="n">
@@ -26977,7 +26977,7 @@
         <v>1</v>
       </c>
       <c r="J230" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K230" t="inlineStr">
         <is>
@@ -27069,7 +27069,7 @@
       </c>
       <c r="B231" t="inlineStr">
         <is>
-          <t>2026-07-11 08:31:17 PM PT</t>
+          <t>2026-07-11 08:33:17 PM PT</t>
         </is>
       </c>
       <c r="C231" t="n">
@@ -27183,7 +27183,7 @@
       </c>
       <c r="B232" t="inlineStr">
         <is>
-          <t>2026-07-11 08:31:17 PM PT</t>
+          <t>2026-07-11 08:33:17 PM PT</t>
         </is>
       </c>
       <c r="C232" t="n">
@@ -27297,7 +27297,7 @@
       </c>
       <c r="B233" t="inlineStr">
         <is>
-          <t>2026-07-11 08:31:17 PM PT</t>
+          <t>2026-07-11 08:33:17 PM PT</t>
         </is>
       </c>
       <c r="C233" t="n">
@@ -27411,7 +27411,7 @@
       </c>
       <c r="B234" t="inlineStr">
         <is>
-          <t>2026-07-11 08:31:17 PM PT</t>
+          <t>2026-07-11 08:33:17 PM PT</t>
         </is>
       </c>
       <c r="C234" t="n">
@@ -27525,7 +27525,7 @@
       </c>
       <c r="B235" t="inlineStr">
         <is>
-          <t>2026-07-11 08:31:18 PM PT</t>
+          <t>2026-07-11 08:33:18 PM PT</t>
         </is>
       </c>
       <c r="C235" t="n">
@@ -27538,7 +27538,7 @@
       </c>
       <c r="E235" t="inlineStr">
         <is>
-          <t>Top 8 | 0 out</t>
+          <t>Top 8 | 1 out</t>
         </is>
       </c>
       <c r="F235" t="n">
@@ -27550,13 +27550,13 @@
         </is>
       </c>
       <c r="H235" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I235" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J235" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K235" t="inlineStr">
         <is>
@@ -27634,10 +27634,10 @@
         <v>0</v>
       </c>
       <c r="AF235" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="AG235" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
     </row>
     <row r="236">
@@ -27648,7 +27648,7 @@
       </c>
       <c r="B236" t="inlineStr">
         <is>
-          <t>2026-07-11 08:31:18 PM PT</t>
+          <t>2026-07-11 08:33:18 PM PT</t>
         </is>
       </c>
       <c r="C236" t="n">
@@ -27661,7 +27661,7 @@
       </c>
       <c r="E236" t="inlineStr">
         <is>
-          <t>Top 8 | 0 out</t>
+          <t>Top 8 | 1 out</t>
         </is>
       </c>
       <c r="F236" t="n">
@@ -27673,13 +27673,13 @@
         </is>
       </c>
       <c r="H236" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I236" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J236" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K236" t="inlineStr">
         <is>
@@ -27715,10 +27715,10 @@
         </is>
       </c>
       <c r="R236" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="S236" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="T236" t="n">
         <v>0</v>
@@ -27757,10 +27757,10 @@
         <v>0</v>
       </c>
       <c r="AF236" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="AG236" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
     </row>
     <row r="237">
@@ -27771,7 +27771,7 @@
       </c>
       <c r="B237" t="inlineStr">
         <is>
-          <t>2026-07-11 08:31:17 PM PT</t>
+          <t>2026-07-11 08:33:16 PM PT</t>
         </is>
       </c>
       <c r="C237" t="n">
@@ -27885,7 +27885,7 @@
       </c>
       <c r="B238" t="inlineStr">
         <is>
-          <t>2026-07-11 08:31:17 PM PT</t>
+          <t>2026-07-11 08:33:16 PM PT</t>
         </is>
       </c>
       <c r="C238" t="n">
@@ -27999,7 +27999,7 @@
       </c>
       <c r="B239" t="inlineStr">
         <is>
-          <t>2026-07-11 08:31:17 PM PT</t>
+          <t>2026-07-11 08:33:16 PM PT</t>
         </is>
       </c>
       <c r="C239" t="n">
@@ -28113,7 +28113,7 @@
       </c>
       <c r="B240" t="inlineStr">
         <is>
-          <t>2026-07-11 08:31:17 PM PT</t>
+          <t>2026-07-11 08:33:16 PM PT</t>
         </is>
       </c>
       <c r="C240" t="n">
@@ -28227,7 +28227,7 @@
       </c>
       <c r="B241" t="inlineStr">
         <is>
-          <t>2026-07-11 08:31:17 PM PT</t>
+          <t>2026-07-11 08:33:16 PM PT</t>
         </is>
       </c>
       <c r="C241" t="n">
@@ -28341,7 +28341,7 @@
       </c>
       <c r="B242" t="inlineStr">
         <is>
-          <t>2026-07-11 08:31:17 PM PT</t>
+          <t>2026-07-11 08:33:16 PM PT</t>
         </is>
       </c>
       <c r="C242" t="n">
@@ -28455,7 +28455,7 @@
       </c>
       <c r="B243" t="inlineStr">
         <is>
-          <t>2026-07-11 08:31:17 PM PT</t>
+          <t>2026-07-11 08:33:16 PM PT</t>
         </is>
       </c>
       <c r="C243" t="n">
@@ -28569,7 +28569,7 @@
       </c>
       <c r="B244" t="inlineStr">
         <is>
-          <t>2026-07-11 08:31:18 PM PT</t>
+          <t>2026-07-11 08:33:18 PM PT</t>
         </is>
       </c>
       <c r="C244" t="n">
@@ -28683,7 +28683,7 @@
       </c>
       <c r="B245" t="inlineStr">
         <is>
-          <t>2026-07-11 08:31:18 PM PT</t>
+          <t>2026-07-11 08:33:18 PM PT</t>
         </is>
       </c>
       <c r="C245" t="n">
@@ -28797,7 +28797,7 @@
       </c>
       <c r="B246" t="inlineStr">
         <is>
-          <t>2026-07-11 08:31:18 PM PT</t>
+          <t>2026-07-11 08:33:18 PM PT</t>
         </is>
       </c>
       <c r="C246" t="n">
@@ -28911,7 +28911,7 @@
       </c>
       <c r="B247" t="inlineStr">
         <is>
-          <t>2026-07-11 08:31:18 PM PT</t>
+          <t>2026-07-11 08:33:17 PM PT</t>
         </is>
       </c>
       <c r="C247" t="n">
@@ -29025,7 +29025,7 @@
       </c>
       <c r="B248" t="inlineStr">
         <is>
-          <t>2026-07-11 08:31:18 PM PT</t>
+          <t>2026-07-11 08:33:17 PM PT</t>
         </is>
       </c>
       <c r="C248" t="n">
@@ -29139,7 +29139,7 @@
       </c>
       <c r="B249" t="inlineStr">
         <is>
-          <t>2026-07-11 08:31:18 PM PT</t>
+          <t>2026-07-11 08:33:17 PM PT</t>
         </is>
       </c>
       <c r="C249" t="n">
@@ -29253,7 +29253,7 @@
       </c>
       <c r="B250" t="inlineStr">
         <is>
-          <t>2026-07-11 08:31:17 PM PT</t>
+          <t>2026-07-11 08:33:17 PM PT</t>
         </is>
       </c>
       <c r="C250" t="n">
@@ -29367,7 +29367,7 @@
       </c>
       <c r="B251" t="inlineStr">
         <is>
-          <t>2026-07-11 08:31:17 PM PT</t>
+          <t>2026-07-11 08:33:17 PM PT</t>
         </is>
       </c>
       <c r="C251" t="n">
@@ -29481,7 +29481,7 @@
       </c>
       <c r="B252" t="inlineStr">
         <is>
-          <t>2026-07-11 08:31:17 PM PT</t>
+          <t>2026-07-11 08:33:17 PM PT</t>
         </is>
       </c>
       <c r="C252" t="n">
@@ -29595,7 +29595,7 @@
       </c>
       <c r="B253" t="inlineStr">
         <is>
-          <t>2026-07-11 08:31:18 PM PT</t>
+          <t>2026-07-11 08:33:18 PM PT</t>
         </is>
       </c>
       <c r="C253" t="n">
@@ -29709,7 +29709,7 @@
       </c>
       <c r="B254" t="inlineStr">
         <is>
-          <t>2026-07-11 08:31:18 PM PT</t>
+          <t>2026-07-11 08:33:18 PM PT</t>
         </is>
       </c>
       <c r="C254" t="n">
@@ -29823,7 +29823,7 @@
       </c>
       <c r="B255" t="inlineStr">
         <is>
-          <t>2026-07-11 08:31:18 PM PT</t>
+          <t>2026-07-11 08:33:18 PM PT</t>
         </is>
       </c>
       <c r="C255" t="n">
@@ -29937,7 +29937,7 @@
       </c>
       <c r="B256" t="inlineStr">
         <is>
-          <t>2026-07-11 08:31:18 PM PT</t>
+          <t>2026-07-11 08:33:18 PM PT</t>
         </is>
       </c>
       <c r="C256" t="n">
@@ -30051,7 +30051,7 @@
       </c>
       <c r="B257" t="inlineStr">
         <is>
-          <t>2026-07-11 08:31:18 PM PT</t>
+          <t>2026-07-11 08:33:18 PM PT</t>
         </is>
       </c>
       <c r="C257" t="n">
@@ -30165,7 +30165,7 @@
       </c>
       <c r="B258" t="inlineStr">
         <is>
-          <t>2026-07-11 08:31:17 PM PT</t>
+          <t>2026-07-11 08:33:17 PM PT</t>
         </is>
       </c>
       <c r="C258" t="n">
@@ -30279,7 +30279,7 @@
       </c>
       <c r="B259" t="inlineStr">
         <is>
-          <t>2026-07-11 08:31:17 PM PT</t>
+          <t>2026-07-11 08:33:17 PM PT</t>
         </is>
       </c>
       <c r="C259" t="n">
@@ -30393,7 +30393,7 @@
       </c>
       <c r="B260" t="inlineStr">
         <is>
-          <t>2026-07-11 08:31:17 PM PT</t>
+          <t>2026-07-11 08:33:17 PM PT</t>
         </is>
       </c>
       <c r="C260" t="n">
@@ -30507,7 +30507,7 @@
       </c>
       <c r="B261" t="inlineStr">
         <is>
-          <t>2026-07-11 08:31:17 PM PT</t>
+          <t>2026-07-11 08:33:16 PM PT</t>
         </is>
       </c>
       <c r="C261" t="n">
@@ -30621,7 +30621,7 @@
       </c>
       <c r="B262" t="inlineStr">
         <is>
-          <t>2026-07-11 08:31:17 PM PT</t>
+          <t>2026-07-11 08:33:16 PM PT</t>
         </is>
       </c>
       <c r="C262" t="n">
@@ -30735,7 +30735,7 @@
       </c>
       <c r="B263" t="inlineStr">
         <is>
-          <t>2026-07-11 08:31:17 PM PT</t>
+          <t>2026-07-11 08:33:16 PM PT</t>
         </is>
       </c>
       <c r="C263" t="n">
@@ -30849,7 +30849,7 @@
       </c>
       <c r="B264" t="inlineStr">
         <is>
-          <t>2026-07-11 08:31:17 PM PT</t>
+          <t>2026-07-11 08:33:16 PM PT</t>
         </is>
       </c>
       <c r="C264" t="n">
@@ -30963,7 +30963,7 @@
       </c>
       <c r="B265" t="inlineStr">
         <is>
-          <t>2026-07-11 08:31:18 PM PT</t>
+          <t>2026-07-11 08:33:17 PM PT</t>
         </is>
       </c>
       <c r="C265" t="n">
@@ -31077,7 +31077,7 @@
       </c>
       <c r="B266" t="inlineStr">
         <is>
-          <t>2026-07-11 08:31:18 PM PT</t>
+          <t>2026-07-11 08:33:17 PM PT</t>
         </is>
       </c>
       <c r="C266" t="n">
@@ -31191,7 +31191,7 @@
       </c>
       <c r="B267" t="inlineStr">
         <is>
-          <t>2026-07-11 08:31:18 PM PT</t>
+          <t>2026-07-11 08:33:17 PM PT</t>
         </is>
       </c>
       <c r="C267" t="n">
@@ -31305,7 +31305,7 @@
       </c>
       <c r="B268" t="inlineStr">
         <is>
-          <t>2026-07-11 08:31:18 PM PT</t>
+          <t>2026-07-11 08:33:17 PM PT</t>
         </is>
       </c>
       <c r="C268" t="n">
@@ -31419,7 +31419,7 @@
       </c>
       <c r="B269" t="inlineStr">
         <is>
-          <t>2026-07-11 08:31:18 PM PT</t>
+          <t>2026-07-11 08:33:17 PM PT</t>
         </is>
       </c>
       <c r="C269" t="n">
@@ -31533,7 +31533,7 @@
       </c>
       <c r="B270" t="inlineStr">
         <is>
-          <t>2026-07-11 08:31:18 PM PT</t>
+          <t>2026-07-11 08:33:17 PM PT</t>
         </is>
       </c>
       <c r="C270" t="n">
@@ -31647,7 +31647,7 @@
       </c>
       <c r="B271" t="inlineStr">
         <is>
-          <t>2026-07-11 08:31:18 PM PT</t>
+          <t>2026-07-11 08:33:17 PM PT</t>
         </is>
       </c>
       <c r="C271" t="n">
@@ -31761,7 +31761,7 @@
       </c>
       <c r="B272" t="inlineStr">
         <is>
-          <t>2026-07-11 08:31:18 PM PT</t>
+          <t>2026-07-11 08:33:17 PM PT</t>
         </is>
       </c>
       <c r="C272" t="n">
@@ -31875,7 +31875,7 @@
       </c>
       <c r="B273" t="inlineStr">
         <is>
-          <t>2026-07-11 08:31:18 PM PT</t>
+          <t>2026-07-11 08:33:17 PM PT</t>
         </is>
       </c>
       <c r="C273" t="n">
@@ -31989,7 +31989,7 @@
       </c>
       <c r="B274" t="inlineStr">
         <is>
-          <t>2026-07-11 08:31:18 PM PT</t>
+          <t>2026-07-11 08:33:17 PM PT</t>
         </is>
       </c>
       <c r="C274" t="n">
@@ -32103,7 +32103,7 @@
       </c>
       <c r="B275" t="inlineStr">
         <is>
-          <t>2026-07-11 08:31:18 PM PT</t>
+          <t>2026-07-11 08:33:17 PM PT</t>
         </is>
       </c>
       <c r="C275" t="n">
@@ -32217,7 +32217,7 @@
       </c>
       <c r="B276" t="inlineStr">
         <is>
-          <t>2026-07-11 08:31:16 PM PT</t>
+          <t>2026-07-11 08:33:16 PM PT</t>
         </is>
       </c>
       <c r="C276" t="n">
@@ -32331,7 +32331,7 @@
       </c>
       <c r="B277" t="inlineStr">
         <is>
-          <t>2026-07-11 08:31:16 PM PT</t>
+          <t>2026-07-11 08:33:16 PM PT</t>
         </is>
       </c>
       <c r="C277" t="n">
@@ -32445,7 +32445,7 @@
       </c>
       <c r="B278" t="inlineStr">
         <is>
-          <t>2026-07-11 08:31:16 PM PT</t>
+          <t>2026-07-11 08:33:16 PM PT</t>
         </is>
       </c>
       <c r="C278" t="n">
@@ -32559,7 +32559,7 @@
       </c>
       <c r="B279" t="inlineStr">
         <is>
-          <t>2026-07-11 08:31:18 PM PT</t>
+          <t>2026-07-11 08:33:18 PM PT</t>
         </is>
       </c>
       <c r="C279" t="n">
@@ -32572,7 +32572,7 @@
       </c>
       <c r="E279" t="inlineStr">
         <is>
-          <t>Top 8 | 0 out</t>
+          <t>Top 8 | 1 out</t>
         </is>
       </c>
       <c r="F279" t="n">
@@ -32584,13 +32584,13 @@
         </is>
       </c>
       <c r="H279" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I279" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J279" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K279" t="inlineStr">
         <is>
@@ -32682,7 +32682,7 @@
       </c>
       <c r="B280" t="inlineStr">
         <is>
-          <t>2026-07-11 08:31:18 PM PT</t>
+          <t>2026-07-11 08:33:18 PM PT</t>
         </is>
       </c>
       <c r="C280" t="n">
@@ -32695,7 +32695,7 @@
       </c>
       <c r="E280" t="inlineStr">
         <is>
-          <t>Top 8 | 0 out</t>
+          <t>Top 8 | 1 out</t>
         </is>
       </c>
       <c r="F280" t="n">
@@ -32707,13 +32707,13 @@
         </is>
       </c>
       <c r="H280" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I280" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J280" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K280" t="inlineStr">
         <is>
@@ -32805,7 +32805,7 @@
       </c>
       <c r="B281" t="inlineStr">
         <is>
-          <t>2026-07-11 08:31:18 PM PT</t>
+          <t>2026-07-11 08:33:18 PM PT</t>
         </is>
       </c>
       <c r="C281" t="n">
@@ -32818,7 +32818,7 @@
       </c>
       <c r="E281" t="inlineStr">
         <is>
-          <t>Top 8 | 0 out</t>
+          <t>Top 8 | 1 out</t>
         </is>
       </c>
       <c r="F281" t="n">
@@ -32830,13 +32830,13 @@
         </is>
       </c>
       <c r="H281" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I281" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J281" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K281" t="inlineStr">
         <is>
@@ -32928,7 +32928,7 @@
       </c>
       <c r="B282" t="inlineStr">
         <is>
-          <t>2026-07-11 08:31:18 PM PT</t>
+          <t>2026-07-11 08:33:18 PM PT</t>
         </is>
       </c>
       <c r="C282" t="n">
@@ -32941,7 +32941,7 @@
       </c>
       <c r="E282" t="inlineStr">
         <is>
-          <t>Top 8 | 0 out</t>
+          <t>Top 8 | 1 out</t>
         </is>
       </c>
       <c r="F282" t="n">
@@ -32953,13 +32953,13 @@
         </is>
       </c>
       <c r="H282" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I282" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J282" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K282" t="inlineStr">
         <is>
@@ -33051,7 +33051,7 @@
       </c>
       <c r="B283" t="inlineStr">
         <is>
-          <t>2026-07-11 08:31:18 PM PT</t>
+          <t>2026-07-11 08:33:18 PM PT</t>
         </is>
       </c>
       <c r="C283" t="n">
@@ -33064,7 +33064,7 @@
       </c>
       <c r="E283" t="inlineStr">
         <is>
-          <t>Top 8 | 0 out</t>
+          <t>Top 8 | 1 out</t>
         </is>
       </c>
       <c r="F283" t="n">
@@ -33076,13 +33076,13 @@
         </is>
       </c>
       <c r="H283" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I283" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J283" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K283" t="inlineStr">
         <is>
@@ -33174,7 +33174,7 @@
       </c>
       <c r="B284" t="inlineStr">
         <is>
-          <t>2026-07-11 08:31:18 PM PT</t>
+          <t>2026-07-11 08:33:18 PM PT</t>
         </is>
       </c>
       <c r="C284" t="n">
@@ -33187,7 +33187,7 @@
       </c>
       <c r="E284" t="inlineStr">
         <is>
-          <t>Top 8 | 0 out</t>
+          <t>Top 8 | 1 out</t>
         </is>
       </c>
       <c r="F284" t="n">
@@ -33199,13 +33199,13 @@
         </is>
       </c>
       <c r="H284" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I284" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J284" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K284" t="inlineStr">
         <is>
@@ -33297,7 +33297,7 @@
       </c>
       <c r="B285" t="inlineStr">
         <is>
-          <t>2026-07-11 08:31:18 PM PT</t>
+          <t>2026-07-11 08:33:18 PM PT</t>
         </is>
       </c>
       <c r="C285" t="n">
@@ -33310,7 +33310,7 @@
       </c>
       <c r="E285" t="inlineStr">
         <is>
-          <t>Top 8 | 0 out</t>
+          <t>Top 8 | 1 out</t>
         </is>
       </c>
       <c r="F285" t="n">
@@ -33322,13 +33322,13 @@
         </is>
       </c>
       <c r="H285" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I285" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J285" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K285" t="inlineStr">
         <is>
@@ -33420,7 +33420,7 @@
       </c>
       <c r="B286" t="inlineStr">
         <is>
-          <t>2026-07-11 08:31:17 PM PT</t>
+          <t>2026-07-11 08:33:17 PM PT</t>
         </is>
       </c>
       <c r="C286" t="n">
@@ -33534,7 +33534,7 @@
       </c>
       <c r="B287" t="inlineStr">
         <is>
-          <t>2026-07-11 08:31:16 PM PT</t>
+          <t>2026-07-11 08:33:16 PM PT</t>
         </is>
       </c>
       <c r="C287" t="n">
@@ -33648,7 +33648,7 @@
       </c>
       <c r="B288" t="inlineStr">
         <is>
-          <t>2026-07-11 08:31:16 PM PT</t>
+          <t>2026-07-11 08:33:16 PM PT</t>
         </is>
       </c>
       <c r="C288" t="n">
@@ -33762,7 +33762,7 @@
       </c>
       <c r="B289" t="inlineStr">
         <is>
-          <t>2026-07-11 08:31:16 PM PT</t>
+          <t>2026-07-11 08:33:16 PM PT</t>
         </is>
       </c>
       <c r="C289" t="n">
@@ -33876,7 +33876,7 @@
       </c>
       <c r="B290" t="inlineStr">
         <is>
-          <t>2026-07-11 08:31:16 PM PT</t>
+          <t>2026-07-11 08:33:16 PM PT</t>
         </is>
       </c>
       <c r="C290" t="n">
@@ -33990,7 +33990,7 @@
       </c>
       <c r="B291" t="inlineStr">
         <is>
-          <t>2026-07-11 08:31:16 PM PT</t>
+          <t>2026-07-11 08:33:16 PM PT</t>
         </is>
       </c>
       <c r="C291" t="n">
@@ -34104,7 +34104,7 @@
       </c>
       <c r="B292" t="inlineStr">
         <is>
-          <t>2026-07-11 08:31:16 PM PT</t>
+          <t>2026-07-11 08:33:16 PM PT</t>
         </is>
       </c>
       <c r="C292" t="n">
@@ -34218,7 +34218,7 @@
       </c>
       <c r="B293" t="inlineStr">
         <is>
-          <t>2026-07-11 08:31:16 PM PT</t>
+          <t>2026-07-11 08:33:16 PM PT</t>
         </is>
       </c>
       <c r="C293" t="n">
@@ -34332,7 +34332,7 @@
       </c>
       <c r="B294" t="inlineStr">
         <is>
-          <t>2026-07-11 08:31:17 PM PT</t>
+          <t>2026-07-11 08:33:17 PM PT</t>
         </is>
       </c>
       <c r="C294" t="n">
@@ -34446,7 +34446,7 @@
       </c>
       <c r="B295" t="inlineStr">
         <is>
-          <t>2026-07-11 08:31:17 PM PT</t>
+          <t>2026-07-11 08:33:17 PM PT</t>
         </is>
       </c>
       <c r="C295" t="n">
@@ -34560,7 +34560,7 @@
       </c>
       <c r="B296" t="inlineStr">
         <is>
-          <t>2026-07-11 08:31:17 PM PT</t>
+          <t>2026-07-11 08:33:17 PM PT</t>
         </is>
       </c>
       <c r="C296" t="n">
@@ -34674,7 +34674,7 @@
       </c>
       <c r="B297" t="inlineStr">
         <is>
-          <t>2026-07-11 08:31:17 PM PT</t>
+          <t>2026-07-11 08:33:17 PM PT</t>
         </is>
       </c>
       <c r="C297" t="n">
@@ -34788,7 +34788,7 @@
       </c>
       <c r="B298" t="inlineStr">
         <is>
-          <t>2026-07-11 08:31:17 PM PT</t>
+          <t>2026-07-11 08:33:17 PM PT</t>
         </is>
       </c>
       <c r="C298" t="n">
@@ -34902,7 +34902,7 @@
       </c>
       <c r="B299" t="inlineStr">
         <is>
-          <t>2026-07-11 08:31:17 PM PT</t>
+          <t>2026-07-11 08:33:17 PM PT</t>
         </is>
       </c>
       <c r="C299" t="n">
@@ -35016,7 +35016,7 @@
       </c>
       <c r="B300" t="inlineStr">
         <is>
-          <t>2026-07-11 08:31:18 PM PT</t>
+          <t>2026-07-11 08:33:17 PM PT</t>
         </is>
       </c>
       <c r="C300" t="n">
@@ -35130,7 +35130,7 @@
       </c>
       <c r="B301" t="inlineStr">
         <is>
-          <t>2026-07-11 08:31:18 PM PT</t>
+          <t>2026-07-11 08:33:17 PM PT</t>
         </is>
       </c>
       <c r="C301" t="n">
@@ -35244,7 +35244,7 @@
       </c>
       <c r="B302" t="inlineStr">
         <is>
-          <t>2026-07-11 08:31:16 PM PT</t>
+          <t>2026-07-11 08:33:16 PM PT</t>
         </is>
       </c>
       <c r="C302" t="n">
@@ -35358,7 +35358,7 @@
       </c>
       <c r="B303" t="inlineStr">
         <is>
-          <t>2026-07-11 08:31:16 PM PT</t>
+          <t>2026-07-11 08:33:16 PM PT</t>
         </is>
       </c>
       <c r="C303" t="n">
@@ -35472,7 +35472,7 @@
       </c>
       <c r="B304" t="inlineStr">
         <is>
-          <t>2026-07-11 08:31:16 PM PT</t>
+          <t>2026-07-11 08:33:16 PM PT</t>
         </is>
       </c>
       <c r="C304" t="n">
@@ -35586,7 +35586,7 @@
       </c>
       <c r="B305" t="inlineStr">
         <is>
-          <t>2026-07-11 08:31:16 PM PT</t>
+          <t>2026-07-11 08:33:16 PM PT</t>
         </is>
       </c>
       <c r="C305" t="n">
@@ -35700,7 +35700,7 @@
       </c>
       <c r="B306" t="inlineStr">
         <is>
-          <t>2026-07-11 08:31:16 PM PT</t>
+          <t>2026-07-11 08:33:16 PM PT</t>
         </is>
       </c>
       <c r="C306" t="n">
@@ -35814,7 +35814,7 @@
       </c>
       <c r="B307" t="inlineStr">
         <is>
-          <t>2026-07-11 08:31:16 PM PT</t>
+          <t>2026-07-11 08:33:16 PM PT</t>
         </is>
       </c>
       <c r="C307" t="n">
@@ -35928,7 +35928,7 @@
       </c>
       <c r="B308" t="inlineStr">
         <is>
-          <t>2026-07-11 08:31:16 PM PT</t>
+          <t>2026-07-11 08:33:16 PM PT</t>
         </is>
       </c>
       <c r="C308" t="n">
@@ -36042,7 +36042,7 @@
       </c>
       <c r="B309" t="inlineStr">
         <is>
-          <t>2026-07-11 08:31:16 PM PT</t>
+          <t>2026-07-11 08:33:16 PM PT</t>
         </is>
       </c>
       <c r="C309" t="n">
@@ -36156,7 +36156,7 @@
       </c>
       <c r="B310" t="inlineStr">
         <is>
-          <t>2026-07-11 08:31:18 PM PT</t>
+          <t>2026-07-11 08:33:18 PM PT</t>
         </is>
       </c>
       <c r="C310" t="n">
@@ -36187,7 +36187,7 @@
         <v>1</v>
       </c>
       <c r="J310" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K310" t="inlineStr">
         <is>
@@ -36268,7 +36268,7 @@
         <v>8</v>
       </c>
       <c r="AG310" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
     </row>
     <row r="311">
@@ -36279,7 +36279,7 @@
       </c>
       <c r="B311" t="inlineStr">
         <is>
-          <t>2026-07-11 08:31:17 PM PT</t>
+          <t>2026-07-11 08:33:17 PM PT</t>
         </is>
       </c>
       <c r="C311" t="n">
@@ -36393,7 +36393,7 @@
       </c>
       <c r="B312" t="inlineStr">
         <is>
-          <t>2026-07-11 08:31:17 PM PT</t>
+          <t>2026-07-11 08:33:17 PM PT</t>
         </is>
       </c>
       <c r="C312" t="n">
@@ -36507,7 +36507,7 @@
       </c>
       <c r="B313" t="inlineStr">
         <is>
-          <t>2026-07-11 08:31:17 PM PT</t>
+          <t>2026-07-11 08:33:17 PM PT</t>
         </is>
       </c>
       <c r="C313" t="n">
@@ -36621,7 +36621,7 @@
       </c>
       <c r="B314" t="inlineStr">
         <is>
-          <t>2026-07-11 08:31:17 PM PT</t>
+          <t>2026-07-11 08:33:17 PM PT</t>
         </is>
       </c>
       <c r="C314" t="n">
@@ -36735,7 +36735,7 @@
       </c>
       <c r="B315" t="inlineStr">
         <is>
-          <t>2026-07-11 08:31:17 PM PT</t>
+          <t>2026-07-11 08:33:17 PM PT</t>
         </is>
       </c>
       <c r="C315" t="n">
@@ -36849,7 +36849,7 @@
       </c>
       <c r="B316" t="inlineStr">
         <is>
-          <t>2026-07-11 08:31:17 PM PT</t>
+          <t>2026-07-11 08:33:17 PM PT</t>
         </is>
       </c>
       <c r="C316" t="n">
@@ -36963,7 +36963,7 @@
       </c>
       <c r="B317" t="inlineStr">
         <is>
-          <t>2026-07-11 08:31:17 PM PT</t>
+          <t>2026-07-11 08:33:17 PM PT</t>
         </is>
       </c>
       <c r="C317" t="n">
@@ -37077,7 +37077,7 @@
       </c>
       <c r="B318" t="inlineStr">
         <is>
-          <t>2026-07-11 08:31:18 PM PT</t>
+          <t>2026-07-11 08:33:18 PM PT</t>
         </is>
       </c>
       <c r="C318" t="n">
@@ -37191,7 +37191,7 @@
       </c>
       <c r="B319" t="inlineStr">
         <is>
-          <t>2026-07-11 08:31:18 PM PT</t>
+          <t>2026-07-11 08:33:18 PM PT</t>
         </is>
       </c>
       <c r="C319" t="n">
@@ -37305,7 +37305,7 @@
       </c>
       <c r="B320" t="inlineStr">
         <is>
-          <t>2026-07-11 08:31:18 PM PT</t>
+          <t>2026-07-11 08:33:18 PM PT</t>
         </is>
       </c>
       <c r="C320" t="n">
@@ -37419,7 +37419,7 @@
       </c>
       <c r="B321" t="inlineStr">
         <is>
-          <t>2026-07-11 08:31:18 PM PT</t>
+          <t>2026-07-11 08:33:18 PM PT</t>
         </is>
       </c>
       <c r="C321" t="n">
@@ -37533,7 +37533,7 @@
       </c>
       <c r="B322" t="inlineStr">
         <is>
-          <t>2026-07-11 08:31:17 PM PT</t>
+          <t>2026-07-11 08:33:17 PM PT</t>
         </is>
       </c>
       <c r="C322" t="n">
@@ -37647,7 +37647,7 @@
       </c>
       <c r="B323" t="inlineStr">
         <is>
-          <t>2026-07-11 08:31:17 PM PT</t>
+          <t>2026-07-11 08:33:17 PM PT</t>
         </is>
       </c>
       <c r="C323" t="n">
@@ -37761,7 +37761,7 @@
       </c>
       <c r="B324" t="inlineStr">
         <is>
-          <t>2026-07-11 08:31:17 PM PT</t>
+          <t>2026-07-11 08:33:17 PM PT</t>
         </is>
       </c>
       <c r="C324" t="n">
@@ -37875,7 +37875,7 @@
       </c>
       <c r="B325" t="inlineStr">
         <is>
-          <t>2026-07-11 08:31:17 PM PT</t>
+          <t>2026-07-11 08:33:17 PM PT</t>
         </is>
       </c>
       <c r="C325" t="n">
@@ -37989,7 +37989,7 @@
       </c>
       <c r="B326" t="inlineStr">
         <is>
-          <t>2026-07-11 08:31:18 PM PT</t>
+          <t>2026-07-11 08:33:17 PM PT</t>
         </is>
       </c>
       <c r="C326" t="n">
@@ -38103,7 +38103,7 @@
       </c>
       <c r="B327" t="inlineStr">
         <is>
-          <t>2026-07-11 08:31:18 PM PT</t>
+          <t>2026-07-11 08:33:17 PM PT</t>
         </is>
       </c>
       <c r="C327" t="n">
@@ -38217,7 +38217,7 @@
       </c>
       <c r="B328" t="inlineStr">
         <is>
-          <t>2026-07-11 08:31:18 PM PT</t>
+          <t>2026-07-11 08:33:17 PM PT</t>
         </is>
       </c>
       <c r="C328" t="n">
@@ -38331,7 +38331,7 @@
       </c>
       <c r="B329" t="inlineStr">
         <is>
-          <t>2026-07-11 08:31:18 PM PT</t>
+          <t>2026-07-11 08:33:17 PM PT</t>
         </is>
       </c>
       <c r="C329" t="n">
@@ -38445,7 +38445,7 @@
       </c>
       <c r="B330" t="inlineStr">
         <is>
-          <t>2026-07-11 08:31:18 PM PT</t>
+          <t>2026-07-11 08:33:17 PM PT</t>
         </is>
       </c>
       <c r="C330" t="n">
@@ -38559,7 +38559,7 @@
       </c>
       <c r="B331" t="inlineStr">
         <is>
-          <t>2026-07-11 08:31:18 PM PT</t>
+          <t>2026-07-11 08:33:18 PM PT</t>
         </is>
       </c>
       <c r="C331" t="n">
@@ -38590,7 +38590,7 @@
         <v>1</v>
       </c>
       <c r="J331" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K331" t="inlineStr">
         <is>
@@ -38682,7 +38682,7 @@
       </c>
       <c r="B332" t="inlineStr">
         <is>
-          <t>2026-07-11 08:31:17 PM PT</t>
+          <t>2026-07-11 08:33:17 PM PT</t>
         </is>
       </c>
       <c r="C332" t="n">
@@ -38796,7 +38796,7 @@
       </c>
       <c r="B333" t="inlineStr">
         <is>
-          <t>2026-07-11 08:31:17 PM PT</t>
+          <t>2026-07-11 08:33:17 PM PT</t>
         </is>
       </c>
       <c r="C333" t="n">

--- a/live_mlb_hitter_fantasy_scores_2026_07_11.xlsx
+++ b/live_mlb_hitter_fantasy_scores_2026_07_11.xlsx
@@ -693,7 +693,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-07-11 08:33:16 PM PT</t>
+          <t>2026-07-11 08:33:52 PM PT</t>
         </is>
       </c>
       <c r="C2" t="n">
@@ -807,7 +807,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>2026-07-11 08:33:18 PM PT</t>
+          <t>2026-07-11 08:33:54 PM PT</t>
         </is>
       </c>
       <c r="C3" t="n">
@@ -835,7 +835,7 @@
         <v>1</v>
       </c>
       <c r="I3" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="J3" t="n">
         <v>1</v>
@@ -930,7 +930,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-07-11 08:33:17 PM PT</t>
+          <t>2026-07-11 08:33:53 PM PT</t>
         </is>
       </c>
       <c r="C4" t="n">
@@ -1044,7 +1044,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>2026-07-11 08:33:18 PM PT</t>
+          <t>2026-07-11 08:33:54 PM PT</t>
         </is>
       </c>
       <c r="C5" t="n">
@@ -1167,7 +1167,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>2026-07-11 08:33:17 PM PT</t>
+          <t>2026-07-11 08:33:53 PM PT</t>
         </is>
       </c>
       <c r="C6" t="n">
@@ -1281,7 +1281,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>2026-07-11 08:33:18 PM PT</t>
+          <t>2026-07-11 08:33:54 PM PT</t>
         </is>
       </c>
       <c r="C7" t="n">
@@ -1395,7 +1395,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>2026-07-11 08:33:17 PM PT</t>
+          <t>2026-07-11 08:33:53 PM PT</t>
         </is>
       </c>
       <c r="C8" t="n">
@@ -1509,7 +1509,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>2026-07-11 08:33:17 PM PT</t>
+          <t>2026-07-11 08:33:53 PM PT</t>
         </is>
       </c>
       <c r="C9" t="n">
@@ -1623,7 +1623,7 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>2026-07-11 08:33:16 PM PT</t>
+          <t>2026-07-11 08:33:52 PM PT</t>
         </is>
       </c>
       <c r="C10" t="n">
@@ -1737,7 +1737,7 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>2026-07-11 08:33:18 PM PT</t>
+          <t>2026-07-11 08:33:54 PM PT</t>
         </is>
       </c>
       <c r="C11" t="n">
@@ -1860,7 +1860,7 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>2026-07-11 08:33:17 PM PT</t>
+          <t>2026-07-11 08:33:53 PM PT</t>
         </is>
       </c>
       <c r="C12" t="n">
@@ -1974,7 +1974,7 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>2026-07-11 08:33:17 PM PT</t>
+          <t>2026-07-11 08:33:53 PM PT</t>
         </is>
       </c>
       <c r="C13" t="n">
@@ -2088,7 +2088,7 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>2026-07-11 08:33:18 PM PT</t>
+          <t>2026-07-11 08:33:54 PM PT</t>
         </is>
       </c>
       <c r="C14" t="n">
@@ -2211,7 +2211,7 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>2026-07-11 08:33:17 PM PT</t>
+          <t>2026-07-11 08:33:53 PM PT</t>
         </is>
       </c>
       <c r="C15" t="n">
@@ -2325,7 +2325,7 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>2026-07-11 08:33:17 PM PT</t>
+          <t>2026-07-11 08:33:53 PM PT</t>
         </is>
       </c>
       <c r="C16" t="n">
@@ -2439,7 +2439,7 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>2026-07-11 08:33:17 PM PT</t>
+          <t>2026-07-11 08:33:53 PM PT</t>
         </is>
       </c>
       <c r="C17" t="n">
@@ -2553,7 +2553,7 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>2026-07-11 08:33:18 PM PT</t>
+          <t>2026-07-11 08:33:54 PM PT</t>
         </is>
       </c>
       <c r="C18" t="n">
@@ -2676,7 +2676,7 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>2026-07-11 08:33:17 PM PT</t>
+          <t>2026-07-11 08:33:53 PM PT</t>
         </is>
       </c>
       <c r="C19" t="n">
@@ -2790,7 +2790,7 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>2026-07-11 08:33:18 PM PT</t>
+          <t>2026-07-11 08:33:53 PM PT</t>
         </is>
       </c>
       <c r="C20" t="n">
@@ -2904,7 +2904,7 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>2026-07-11 08:33:17 PM PT</t>
+          <t>2026-07-11 08:33:53 PM PT</t>
         </is>
       </c>
       <c r="C21" t="n">
@@ -3018,7 +3018,7 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>2026-07-11 08:33:17 PM PT</t>
+          <t>2026-07-11 08:33:53 PM PT</t>
         </is>
       </c>
       <c r="C22" t="n">
@@ -3132,7 +3132,7 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>2026-07-11 08:33:18 PM PT</t>
+          <t>2026-07-11 08:33:54 PM PT</t>
         </is>
       </c>
       <c r="C23" t="n">
@@ -3160,7 +3160,7 @@
         <v>1</v>
       </c>
       <c r="I23" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="J23" t="n">
         <v>1</v>
@@ -3255,7 +3255,7 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>2026-07-11 08:33:17 PM PT</t>
+          <t>2026-07-11 08:33:53 PM PT</t>
         </is>
       </c>
       <c r="C24" t="n">
@@ -3369,7 +3369,7 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>2026-07-11 08:33:17 PM PT</t>
+          <t>2026-07-11 08:33:53 PM PT</t>
         </is>
       </c>
       <c r="C25" t="n">
@@ -3483,7 +3483,7 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>2026-07-11 08:33:18 PM PT</t>
+          <t>2026-07-11 08:33:53 PM PT</t>
         </is>
       </c>
       <c r="C26" t="n">
@@ -3597,7 +3597,7 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>2026-07-11 08:33:16 PM PT</t>
+          <t>2026-07-11 08:33:52 PM PT</t>
         </is>
       </c>
       <c r="C27" t="n">
@@ -3711,7 +3711,7 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>2026-07-11 08:33:17 PM PT</t>
+          <t>2026-07-11 08:33:53 PM PT</t>
         </is>
       </c>
       <c r="C28" t="n">
@@ -3825,7 +3825,7 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>2026-07-11 08:33:17 PM PT</t>
+          <t>2026-07-11 08:33:53 PM PT</t>
         </is>
       </c>
       <c r="C29" t="n">
@@ -3939,7 +3939,7 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>2026-07-11 08:33:18 PM PT</t>
+          <t>2026-07-11 08:33:53 PM PT</t>
         </is>
       </c>
       <c r="C30" t="n">
@@ -4053,7 +4053,7 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>2026-07-11 08:33:18 PM PT</t>
+          <t>2026-07-11 08:33:53 PM PT</t>
         </is>
       </c>
       <c r="C31" t="n">
@@ -4167,7 +4167,7 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>2026-07-11 08:33:17 PM PT</t>
+          <t>2026-07-11 08:33:53 PM PT</t>
         </is>
       </c>
       <c r="C32" t="n">
@@ -4281,7 +4281,7 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>2026-07-11 08:33:17 PM PT</t>
+          <t>2026-07-11 08:33:53 PM PT</t>
         </is>
       </c>
       <c r="C33" t="n">
@@ -4395,7 +4395,7 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>2026-07-11 08:33:17 PM PT</t>
+          <t>2026-07-11 08:33:53 PM PT</t>
         </is>
       </c>
       <c r="C34" t="n">
@@ -4509,7 +4509,7 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>2026-07-11 08:33:16 PM PT</t>
+          <t>2026-07-11 08:33:52 PM PT</t>
         </is>
       </c>
       <c r="C35" t="n">
@@ -4623,7 +4623,7 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>2026-07-11 08:33:16 PM PT</t>
+          <t>2026-07-11 08:33:52 PM PT</t>
         </is>
       </c>
       <c r="C36" t="n">
@@ -4737,7 +4737,7 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>2026-07-11 08:33:18 PM PT</t>
+          <t>2026-07-11 08:33:54 PM PT</t>
         </is>
       </c>
       <c r="C37" t="n">
@@ -4860,7 +4860,7 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>2026-07-11 08:33:17 PM PT</t>
+          <t>2026-07-11 08:33:53 PM PT</t>
         </is>
       </c>
       <c r="C38" t="n">
@@ -4974,7 +4974,7 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>2026-07-11 08:33:16 PM PT</t>
+          <t>2026-07-11 08:33:52 PM PT</t>
         </is>
       </c>
       <c r="C39" t="n">
@@ -5088,7 +5088,7 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>2026-07-11 08:33:17 PM PT</t>
+          <t>2026-07-11 08:33:53 PM PT</t>
         </is>
       </c>
       <c r="C40" t="n">
@@ -5202,7 +5202,7 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>2026-07-11 08:33:16 PM PT</t>
+          <t>2026-07-11 08:33:52 PM PT</t>
         </is>
       </c>
       <c r="C41" t="n">
@@ -5316,7 +5316,7 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>2026-07-11 08:33:18 PM PT</t>
+          <t>2026-07-11 08:33:54 PM PT</t>
         </is>
       </c>
       <c r="C42" t="n">
@@ -5344,7 +5344,7 @@
         <v>1</v>
       </c>
       <c r="I42" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="J42" t="n">
         <v>1</v>
@@ -5439,7 +5439,7 @@
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>2026-07-11 08:33:18 PM PT</t>
+          <t>2026-07-11 08:33:54 PM PT</t>
         </is>
       </c>
       <c r="C43" t="n">
@@ -5553,7 +5553,7 @@
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>2026-07-11 08:33:17 PM PT</t>
+          <t>2026-07-11 08:33:53 PM PT</t>
         </is>
       </c>
       <c r="C44" t="n">
@@ -5667,7 +5667,7 @@
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>2026-07-11 08:33:17 PM PT</t>
+          <t>2026-07-11 08:33:53 PM PT</t>
         </is>
       </c>
       <c r="C45" t="n">
@@ -5781,7 +5781,7 @@
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>2026-07-11 08:33:18 PM PT</t>
+          <t>2026-07-11 08:33:53 PM PT</t>
         </is>
       </c>
       <c r="C46" t="n">
@@ -5895,7 +5895,7 @@
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>2026-07-11 08:33:17 PM PT</t>
+          <t>2026-07-11 08:33:53 PM PT</t>
         </is>
       </c>
       <c r="C47" t="n">
@@ -6009,7 +6009,7 @@
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>2026-07-11 08:33:17 PM PT</t>
+          <t>2026-07-11 08:33:53 PM PT</t>
         </is>
       </c>
       <c r="C48" t="n">
@@ -6123,7 +6123,7 @@
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>2026-07-11 08:33:17 PM PT</t>
+          <t>2026-07-11 08:33:53 PM PT</t>
         </is>
       </c>
       <c r="C49" t="n">
@@ -6237,7 +6237,7 @@
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>2026-07-11 08:33:17 PM PT</t>
+          <t>2026-07-11 08:33:53 PM PT</t>
         </is>
       </c>
       <c r="C50" t="n">
@@ -6351,7 +6351,7 @@
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>2026-07-11 08:33:16 PM PT</t>
+          <t>2026-07-11 08:33:52 PM PT</t>
         </is>
       </c>
       <c r="C51" t="n">
@@ -6465,7 +6465,7 @@
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>2026-07-11 08:33:18 PM PT</t>
+          <t>2026-07-11 08:33:54 PM PT</t>
         </is>
       </c>
       <c r="C52" t="n">
@@ -6588,7 +6588,7 @@
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>2026-07-11 08:33:18 PM PT</t>
+          <t>2026-07-11 08:33:54 PM PT</t>
         </is>
       </c>
       <c r="C53" t="n">
@@ -6616,7 +6616,7 @@
         <v>1</v>
       </c>
       <c r="I53" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="J53" t="n">
         <v>1</v>
@@ -6711,7 +6711,7 @@
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>2026-07-11 08:33:18 PM PT</t>
+          <t>2026-07-11 08:33:53 PM PT</t>
         </is>
       </c>
       <c r="C54" t="n">
@@ -6825,7 +6825,7 @@
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>2026-07-11 08:33:18 PM PT</t>
+          <t>2026-07-11 08:33:53 PM PT</t>
         </is>
       </c>
       <c r="C55" t="n">
@@ -6939,7 +6939,7 @@
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>2026-07-11 08:33:17 PM PT</t>
+          <t>2026-07-11 08:33:53 PM PT</t>
         </is>
       </c>
       <c r="C56" t="n">
@@ -7053,7 +7053,7 @@
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>2026-07-11 08:33:16 PM PT</t>
+          <t>2026-07-11 08:33:52 PM PT</t>
         </is>
       </c>
       <c r="C57" t="n">
@@ -7167,7 +7167,7 @@
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>2026-07-11 08:33:16 PM PT</t>
+          <t>2026-07-11 08:33:52 PM PT</t>
         </is>
       </c>
       <c r="C58" t="n">
@@ -7281,7 +7281,7 @@
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>2026-07-11 08:33:16 PM PT</t>
+          <t>2026-07-11 08:33:52 PM PT</t>
         </is>
       </c>
       <c r="C59" t="n">
@@ -7395,7 +7395,7 @@
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>2026-07-11 08:33:17 PM PT</t>
+          <t>2026-07-11 08:33:53 PM PT</t>
         </is>
       </c>
       <c r="C60" t="n">
@@ -7509,7 +7509,7 @@
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>2026-07-11 08:33:17 PM PT</t>
+          <t>2026-07-11 08:33:53 PM PT</t>
         </is>
       </c>
       <c r="C61" t="n">
@@ -7623,7 +7623,7 @@
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>2026-07-11 08:33:16 PM PT</t>
+          <t>2026-07-11 08:33:52 PM PT</t>
         </is>
       </c>
       <c r="C62" t="n">
@@ -7737,7 +7737,7 @@
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>2026-07-11 08:33:16 PM PT</t>
+          <t>2026-07-11 08:33:52 PM PT</t>
         </is>
       </c>
       <c r="C63" t="n">
@@ -7851,7 +7851,7 @@
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>2026-07-11 08:33:16 PM PT</t>
+          <t>2026-07-11 08:33:52 PM PT</t>
         </is>
       </c>
       <c r="C64" t="n">
@@ -7965,7 +7965,7 @@
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>2026-07-11 08:33:18 PM PT</t>
+          <t>2026-07-11 08:33:54 PM PT</t>
         </is>
       </c>
       <c r="C65" t="n">
@@ -8088,7 +8088,7 @@
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>2026-07-11 08:33:18 PM PT</t>
+          <t>2026-07-11 08:33:54 PM PT</t>
         </is>
       </c>
       <c r="C66" t="n">
@@ -8116,7 +8116,7 @@
         <v>1</v>
       </c>
       <c r="I66" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="J66" t="n">
         <v>1</v>
@@ -8211,7 +8211,7 @@
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>2026-07-11 08:33:16 PM PT</t>
+          <t>2026-07-11 08:33:53 PM PT</t>
         </is>
       </c>
       <c r="C67" t="n">
@@ -8325,7 +8325,7 @@
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>2026-07-11 08:33:17 PM PT</t>
+          <t>2026-07-11 08:33:53 PM PT</t>
         </is>
       </c>
       <c r="C68" t="n">
@@ -8439,7 +8439,7 @@
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>2026-07-11 08:33:17 PM PT</t>
+          <t>2026-07-11 08:33:53 PM PT</t>
         </is>
       </c>
       <c r="C69" t="n">
@@ -8553,7 +8553,7 @@
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>2026-07-11 08:33:16 PM PT</t>
+          <t>2026-07-11 08:33:53 PM PT</t>
         </is>
       </c>
       <c r="C70" t="n">
@@ -8667,7 +8667,7 @@
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>2026-07-11 08:33:16 PM PT</t>
+          <t>2026-07-11 08:33:52 PM PT</t>
         </is>
       </c>
       <c r="C71" t="n">
@@ -8781,7 +8781,7 @@
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>2026-07-11 08:33:18 PM PT</t>
+          <t>2026-07-11 08:33:54 PM PT</t>
         </is>
       </c>
       <c r="C72" t="n">
@@ -8809,7 +8809,7 @@
         <v>1</v>
       </c>
       <c r="I72" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="J72" t="n">
         <v>1</v>
@@ -8904,7 +8904,7 @@
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>2026-07-11 08:33:16 PM PT</t>
+          <t>2026-07-11 08:33:52 PM PT</t>
         </is>
       </c>
       <c r="C73" t="n">
@@ -9018,7 +9018,7 @@
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>2026-07-11 08:33:17 PM PT</t>
+          <t>2026-07-11 08:33:53 PM PT</t>
         </is>
       </c>
       <c r="C74" t="n">
@@ -9132,7 +9132,7 @@
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>2026-07-11 08:33:16 PM PT</t>
+          <t>2026-07-11 08:33:52 PM PT</t>
         </is>
       </c>
       <c r="C75" t="n">
@@ -9246,7 +9246,7 @@
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>2026-07-11 08:33:18 PM PT</t>
+          <t>2026-07-11 08:33:54 PM PT</t>
         </is>
       </c>
       <c r="C76" t="n">
@@ -9369,7 +9369,7 @@
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>2026-07-11 08:33:18 PM PT</t>
+          <t>2026-07-11 08:33:53 PM PT</t>
         </is>
       </c>
       <c r="C77" t="n">
@@ -9483,7 +9483,7 @@
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>2026-07-11 08:33:18 PM PT</t>
+          <t>2026-07-11 08:33:53 PM PT</t>
         </is>
       </c>
       <c r="C78" t="n">
@@ -9597,7 +9597,7 @@
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>2026-07-11 08:33:17 PM PT</t>
+          <t>2026-07-11 08:33:53 PM PT</t>
         </is>
       </c>
       <c r="C79" t="n">
@@ -9711,7 +9711,7 @@
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>2026-07-11 08:33:16 PM PT</t>
+          <t>2026-07-11 08:33:52 PM PT</t>
         </is>
       </c>
       <c r="C80" t="n">
@@ -9825,7 +9825,7 @@
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>2026-07-11 08:33:16 PM PT</t>
+          <t>2026-07-11 08:33:52 PM PT</t>
         </is>
       </c>
       <c r="C81" t="n">
@@ -9939,7 +9939,7 @@
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>2026-07-11 08:33:16 PM PT</t>
+          <t>2026-07-11 08:33:52 PM PT</t>
         </is>
       </c>
       <c r="C82" t="n">
@@ -10053,7 +10053,7 @@
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>2026-07-11 08:33:16 PM PT</t>
+          <t>2026-07-11 08:33:52 PM PT</t>
         </is>
       </c>
       <c r="C83" t="n">
@@ -10167,7 +10167,7 @@
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>2026-07-11 08:33:16 PM PT</t>
+          <t>2026-07-11 08:33:52 PM PT</t>
         </is>
       </c>
       <c r="C84" t="n">
@@ -10281,7 +10281,7 @@
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>2026-07-11 08:33:16 PM PT</t>
+          <t>2026-07-11 08:33:52 PM PT</t>
         </is>
       </c>
       <c r="C85" t="n">
@@ -10395,7 +10395,7 @@
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>2026-07-11 08:33:16 PM PT</t>
+          <t>2026-07-11 08:33:53 PM PT</t>
         </is>
       </c>
       <c r="C86" t="n">
@@ -10509,7 +10509,7 @@
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>2026-07-11 08:33:16 PM PT</t>
+          <t>2026-07-11 08:33:53 PM PT</t>
         </is>
       </c>
       <c r="C87" t="n">
@@ -10623,7 +10623,7 @@
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>2026-07-11 08:33:17 PM PT</t>
+          <t>2026-07-11 08:33:53 PM PT</t>
         </is>
       </c>
       <c r="C88" t="n">
@@ -10737,7 +10737,7 @@
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>2026-07-11 08:33:17 PM PT</t>
+          <t>2026-07-11 08:33:53 PM PT</t>
         </is>
       </c>
       <c r="C89" t="n">
@@ -10851,7 +10851,7 @@
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>2026-07-11 08:33:18 PM PT</t>
+          <t>2026-07-11 08:33:54 PM PT</t>
         </is>
       </c>
       <c r="C90" t="n">
@@ -10974,7 +10974,7 @@
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>2026-07-11 08:33:17 PM PT</t>
+          <t>2026-07-11 08:33:53 PM PT</t>
         </is>
       </c>
       <c r="C91" t="n">
@@ -11088,7 +11088,7 @@
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>2026-07-11 08:33:18 PM PT</t>
+          <t>2026-07-11 08:33:54 PM PT</t>
         </is>
       </c>
       <c r="C92" t="n">
@@ -11202,7 +11202,7 @@
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>2026-07-11 08:33:18 PM PT</t>
+          <t>2026-07-11 08:33:54 PM PT</t>
         </is>
       </c>
       <c r="C93" t="n">
@@ -11230,7 +11230,7 @@
         <v>1</v>
       </c>
       <c r="I93" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="J93" t="n">
         <v>1</v>
@@ -11325,7 +11325,7 @@
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>2026-07-11 08:33:17 PM PT</t>
+          <t>2026-07-11 08:33:53 PM PT</t>
         </is>
       </c>
       <c r="C94" t="n">
@@ -11439,7 +11439,7 @@
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>2026-07-11 08:33:17 PM PT</t>
+          <t>2026-07-11 08:33:53 PM PT</t>
         </is>
       </c>
       <c r="C95" t="n">
@@ -11553,7 +11553,7 @@
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>2026-07-11 08:33:17 PM PT</t>
+          <t>2026-07-11 08:33:53 PM PT</t>
         </is>
       </c>
       <c r="C96" t="n">
@@ -11667,7 +11667,7 @@
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>2026-07-11 08:33:17 PM PT</t>
+          <t>2026-07-11 08:33:53 PM PT</t>
         </is>
       </c>
       <c r="C97" t="n">
@@ -11781,7 +11781,7 @@
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>2026-07-11 08:33:17 PM PT</t>
+          <t>2026-07-11 08:33:53 PM PT</t>
         </is>
       </c>
       <c r="C98" t="n">
@@ -11895,7 +11895,7 @@
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>2026-07-11 08:33:18 PM PT</t>
+          <t>2026-07-11 08:33:54 PM PT</t>
         </is>
       </c>
       <c r="C99" t="n">
@@ -11923,7 +11923,7 @@
         <v>1</v>
       </c>
       <c r="I99" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="J99" t="n">
         <v>1</v>
@@ -12018,7 +12018,7 @@
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>2026-07-11 08:33:17 PM PT</t>
+          <t>2026-07-11 08:33:53 PM PT</t>
         </is>
       </c>
       <c r="C100" t="n">
@@ -12132,7 +12132,7 @@
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>2026-07-11 08:33:16 PM PT</t>
+          <t>2026-07-11 08:33:52 PM PT</t>
         </is>
       </c>
       <c r="C101" t="n">
@@ -12246,7 +12246,7 @@
       </c>
       <c r="B102" t="inlineStr">
         <is>
-          <t>2026-07-11 08:33:16 PM PT</t>
+          <t>2026-07-11 08:33:52 PM PT</t>
         </is>
       </c>
       <c r="C102" t="n">
@@ -12360,7 +12360,7 @@
       </c>
       <c r="B103" t="inlineStr">
         <is>
-          <t>2026-07-11 08:33:17 PM PT</t>
+          <t>2026-07-11 08:33:53 PM PT</t>
         </is>
       </c>
       <c r="C103" t="n">
@@ -12474,7 +12474,7 @@
       </c>
       <c r="B104" t="inlineStr">
         <is>
-          <t>2026-07-11 08:33:18 PM PT</t>
+          <t>2026-07-11 08:33:54 PM PT</t>
         </is>
       </c>
       <c r="C104" t="n">
@@ -12597,7 +12597,7 @@
       </c>
       <c r="B105" t="inlineStr">
         <is>
-          <t>2026-07-11 08:33:17 PM PT</t>
+          <t>2026-07-11 08:33:53 PM PT</t>
         </is>
       </c>
       <c r="C105" t="n">
@@ -12711,7 +12711,7 @@
       </c>
       <c r="B106" t="inlineStr">
         <is>
-          <t>2026-07-11 08:33:17 PM PT</t>
+          <t>2026-07-11 08:33:53 PM PT</t>
         </is>
       </c>
       <c r="C106" t="n">
@@ -12825,7 +12825,7 @@
       </c>
       <c r="B107" t="inlineStr">
         <is>
-          <t>2026-07-11 08:33:17 PM PT</t>
+          <t>2026-07-11 08:33:53 PM PT</t>
         </is>
       </c>
       <c r="C107" t="n">
@@ -12939,7 +12939,7 @@
       </c>
       <c r="B108" t="inlineStr">
         <is>
-          <t>2026-07-11 08:33:17 PM PT</t>
+          <t>2026-07-11 08:33:53 PM PT</t>
         </is>
       </c>
       <c r="C108" t="n">
@@ -13053,7 +13053,7 @@
       </c>
       <c r="B109" t="inlineStr">
         <is>
-          <t>2026-07-11 08:33:17 PM PT</t>
+          <t>2026-07-11 08:33:53 PM PT</t>
         </is>
       </c>
       <c r="C109" t="n">
@@ -13167,7 +13167,7 @@
       </c>
       <c r="B110" t="inlineStr">
         <is>
-          <t>2026-07-11 08:33:17 PM PT</t>
+          <t>2026-07-11 08:33:53 PM PT</t>
         </is>
       </c>
       <c r="C110" t="n">
@@ -13281,7 +13281,7 @@
       </c>
       <c r="B111" t="inlineStr">
         <is>
-          <t>2026-07-11 08:33:16 PM PT</t>
+          <t>2026-07-11 08:33:53 PM PT</t>
         </is>
       </c>
       <c r="C111" t="n">
@@ -13395,7 +13395,7 @@
       </c>
       <c r="B112" t="inlineStr">
         <is>
-          <t>2026-07-11 08:33:18 PM PT</t>
+          <t>2026-07-11 08:33:53 PM PT</t>
         </is>
       </c>
       <c r="C112" t="n">
@@ -13509,7 +13509,7 @@
       </c>
       <c r="B113" t="inlineStr">
         <is>
-          <t>2026-07-11 08:33:17 PM PT</t>
+          <t>2026-07-11 08:33:53 PM PT</t>
         </is>
       </c>
       <c r="C113" t="n">
@@ -13623,7 +13623,7 @@
       </c>
       <c r="B114" t="inlineStr">
         <is>
-          <t>2026-07-11 08:33:17 PM PT</t>
+          <t>2026-07-11 08:33:53 PM PT</t>
         </is>
       </c>
       <c r="C114" t="n">
@@ -13737,7 +13737,7 @@
       </c>
       <c r="B115" t="inlineStr">
         <is>
-          <t>2026-07-11 08:33:17 PM PT</t>
+          <t>2026-07-11 08:33:53 PM PT</t>
         </is>
       </c>
       <c r="C115" t="n">
@@ -13851,7 +13851,7 @@
       </c>
       <c r="B116" t="inlineStr">
         <is>
-          <t>2026-07-11 08:33:18 PM PT</t>
+          <t>2026-07-11 08:33:54 PM PT</t>
         </is>
       </c>
       <c r="C116" t="n">
@@ -13974,7 +13974,7 @@
       </c>
       <c r="B117" t="inlineStr">
         <is>
-          <t>2026-07-11 08:33:17 PM PT</t>
+          <t>2026-07-11 08:33:53 PM PT</t>
         </is>
       </c>
       <c r="C117" t="n">
@@ -14088,7 +14088,7 @@
       </c>
       <c r="B118" t="inlineStr">
         <is>
-          <t>2026-07-11 08:33:18 PM PT</t>
+          <t>2026-07-11 08:33:54 PM PT</t>
         </is>
       </c>
       <c r="C118" t="n">
@@ -14202,7 +14202,7 @@
       </c>
       <c r="B119" t="inlineStr">
         <is>
-          <t>2026-07-11 08:33:18 PM PT</t>
+          <t>2026-07-11 08:33:54 PM PT</t>
         </is>
       </c>
       <c r="C119" t="n">
@@ -14316,7 +14316,7 @@
       </c>
       <c r="B120" t="inlineStr">
         <is>
-          <t>2026-07-11 08:33:17 PM PT</t>
+          <t>2026-07-11 08:33:53 PM PT</t>
         </is>
       </c>
       <c r="C120" t="n">
@@ -14430,7 +14430,7 @@
       </c>
       <c r="B121" t="inlineStr">
         <is>
-          <t>2026-07-11 08:33:17 PM PT</t>
+          <t>2026-07-11 08:33:53 PM PT</t>
         </is>
       </c>
       <c r="C121" t="n">
@@ -14544,7 +14544,7 @@
       </c>
       <c r="B122" t="inlineStr">
         <is>
-          <t>2026-07-11 08:33:18 PM PT</t>
+          <t>2026-07-11 08:33:53 PM PT</t>
         </is>
       </c>
       <c r="C122" t="n">
@@ -14658,7 +14658,7 @@
       </c>
       <c r="B123" t="inlineStr">
         <is>
-          <t>2026-07-11 08:33:17 PM PT</t>
+          <t>2026-07-11 08:33:53 PM PT</t>
         </is>
       </c>
       <c r="C123" t="n">
@@ -14772,7 +14772,7 @@
       </c>
       <c r="B124" t="inlineStr">
         <is>
-          <t>2026-07-11 08:33:16 PM PT</t>
+          <t>2026-07-11 08:33:53 PM PT</t>
         </is>
       </c>
       <c r="C124" t="n">
@@ -14886,7 +14886,7 @@
       </c>
       <c r="B125" t="inlineStr">
         <is>
-          <t>2026-07-11 08:33:17 PM PT</t>
+          <t>2026-07-11 08:33:53 PM PT</t>
         </is>
       </c>
       <c r="C125" t="n">
@@ -15000,7 +15000,7 @@
       </c>
       <c r="B126" t="inlineStr">
         <is>
-          <t>2026-07-11 08:33:17 PM PT</t>
+          <t>2026-07-11 08:33:53 PM PT</t>
         </is>
       </c>
       <c r="C126" t="n">
@@ -15114,7 +15114,7 @@
       </c>
       <c r="B127" t="inlineStr">
         <is>
-          <t>2026-07-11 08:33:17 PM PT</t>
+          <t>2026-07-11 08:33:53 PM PT</t>
         </is>
       </c>
       <c r="C127" t="n">
@@ -15228,7 +15228,7 @@
       </c>
       <c r="B128" t="inlineStr">
         <is>
-          <t>2026-07-11 08:33:17 PM PT</t>
+          <t>2026-07-11 08:33:53 PM PT</t>
         </is>
       </c>
       <c r="C128" t="n">
@@ -15342,7 +15342,7 @@
       </c>
       <c r="B129" t="inlineStr">
         <is>
-          <t>2026-07-11 08:33:18 PM PT</t>
+          <t>2026-07-11 08:33:54 PM PT</t>
         </is>
       </c>
       <c r="C129" t="n">
@@ -15370,7 +15370,7 @@
         <v>1</v>
       </c>
       <c r="I129" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="J129" t="n">
         <v>1</v>
@@ -15465,7 +15465,7 @@
       </c>
       <c r="B130" t="inlineStr">
         <is>
-          <t>2026-07-11 08:33:17 PM PT</t>
+          <t>2026-07-11 08:33:53 PM PT</t>
         </is>
       </c>
       <c r="C130" t="n">
@@ -15579,7 +15579,7 @@
       </c>
       <c r="B131" t="inlineStr">
         <is>
-          <t>2026-07-11 08:33:17 PM PT</t>
+          <t>2026-07-11 08:33:53 PM PT</t>
         </is>
       </c>
       <c r="C131" t="n">
@@ -15693,7 +15693,7 @@
       </c>
       <c r="B132" t="inlineStr">
         <is>
-          <t>2026-07-11 08:33:16 PM PT</t>
+          <t>2026-07-11 08:33:52 PM PT</t>
         </is>
       </c>
       <c r="C132" t="n">
@@ -15807,7 +15807,7 @@
       </c>
       <c r="B133" t="inlineStr">
         <is>
-          <t>2026-07-11 08:33:16 PM PT</t>
+          <t>2026-07-11 08:33:52 PM PT</t>
         </is>
       </c>
       <c r="C133" t="n">
@@ -15921,7 +15921,7 @@
       </c>
       <c r="B134" t="inlineStr">
         <is>
-          <t>2026-07-11 08:33:16 PM PT</t>
+          <t>2026-07-11 08:33:52 PM PT</t>
         </is>
       </c>
       <c r="C134" t="n">
@@ -16035,7 +16035,7 @@
       </c>
       <c r="B135" t="inlineStr">
         <is>
-          <t>2026-07-11 08:33:17 PM PT</t>
+          <t>2026-07-11 08:33:53 PM PT</t>
         </is>
       </c>
       <c r="C135" t="n">
@@ -16149,7 +16149,7 @@
       </c>
       <c r="B136" t="inlineStr">
         <is>
-          <t>2026-07-11 08:33:16 PM PT</t>
+          <t>2026-07-11 08:33:52 PM PT</t>
         </is>
       </c>
       <c r="C136" t="n">
@@ -16263,7 +16263,7 @@
       </c>
       <c r="B137" t="inlineStr">
         <is>
-          <t>2026-07-11 08:33:16 PM PT</t>
+          <t>2026-07-11 08:33:52 PM PT</t>
         </is>
       </c>
       <c r="C137" t="n">
@@ -16377,7 +16377,7 @@
       </c>
       <c r="B138" t="inlineStr">
         <is>
-          <t>2026-07-11 08:33:17 PM PT</t>
+          <t>2026-07-11 08:33:53 PM PT</t>
         </is>
       </c>
       <c r="C138" t="n">
@@ -16491,7 +16491,7 @@
       </c>
       <c r="B139" t="inlineStr">
         <is>
-          <t>2026-07-11 08:33:17 PM PT</t>
+          <t>2026-07-11 08:33:53 PM PT</t>
         </is>
       </c>
       <c r="C139" t="n">
@@ -16605,7 +16605,7 @@
       </c>
       <c r="B140" t="inlineStr">
         <is>
-          <t>2026-07-11 08:33:17 PM PT</t>
+          <t>2026-07-11 08:33:53 PM PT</t>
         </is>
       </c>
       <c r="C140" t="n">
@@ -16719,7 +16719,7 @@
       </c>
       <c r="B141" t="inlineStr">
         <is>
-          <t>2026-07-11 08:33:18 PM PT</t>
+          <t>2026-07-11 08:33:54 PM PT</t>
         </is>
       </c>
       <c r="C141" t="n">
@@ -16833,7 +16833,7 @@
       </c>
       <c r="B142" t="inlineStr">
         <is>
-          <t>2026-07-11 08:33:18 PM PT</t>
+          <t>2026-07-11 08:33:54 PM PT</t>
         </is>
       </c>
       <c r="C142" t="n">
@@ -16947,7 +16947,7 @@
       </c>
       <c r="B143" t="inlineStr">
         <is>
-          <t>2026-07-11 08:33:18 PM PT</t>
+          <t>2026-07-11 08:33:54 PM PT</t>
         </is>
       </c>
       <c r="C143" t="n">
@@ -17061,7 +17061,7 @@
       </c>
       <c r="B144" t="inlineStr">
         <is>
-          <t>2026-07-11 08:33:17 PM PT</t>
+          <t>2026-07-11 08:33:53 PM PT</t>
         </is>
       </c>
       <c r="C144" t="n">
@@ -17175,7 +17175,7 @@
       </c>
       <c r="B145" t="inlineStr">
         <is>
-          <t>2026-07-11 08:33:17 PM PT</t>
+          <t>2026-07-11 08:33:53 PM PT</t>
         </is>
       </c>
       <c r="C145" t="n">
@@ -17289,7 +17289,7 @@
       </c>
       <c r="B146" t="inlineStr">
         <is>
-          <t>2026-07-11 08:33:17 PM PT</t>
+          <t>2026-07-11 08:33:53 PM PT</t>
         </is>
       </c>
       <c r="C146" t="n">
@@ -17403,7 +17403,7 @@
       </c>
       <c r="B147" t="inlineStr">
         <is>
-          <t>2026-07-11 08:33:18 PM PT</t>
+          <t>2026-07-11 08:33:53 PM PT</t>
         </is>
       </c>
       <c r="C147" t="n">
@@ -17517,7 +17517,7 @@
       </c>
       <c r="B148" t="inlineStr">
         <is>
-          <t>2026-07-11 08:33:17 PM PT</t>
+          <t>2026-07-11 08:33:53 PM PT</t>
         </is>
       </c>
       <c r="C148" t="n">
@@ -17631,7 +17631,7 @@
       </c>
       <c r="B149" t="inlineStr">
         <is>
-          <t>2026-07-11 08:33:16 PM PT</t>
+          <t>2026-07-11 08:33:53 PM PT</t>
         </is>
       </c>
       <c r="C149" t="n">
@@ -17745,7 +17745,7 @@
       </c>
       <c r="B150" t="inlineStr">
         <is>
-          <t>2026-07-11 08:33:16 PM PT</t>
+          <t>2026-07-11 08:33:52 PM PT</t>
         </is>
       </c>
       <c r="C150" t="n">
@@ -17859,7 +17859,7 @@
       </c>
       <c r="B151" t="inlineStr">
         <is>
-          <t>2026-07-11 08:33:16 PM PT</t>
+          <t>2026-07-11 08:33:52 PM PT</t>
         </is>
       </c>
       <c r="C151" t="n">
@@ -17973,7 +17973,7 @@
       </c>
       <c r="B152" t="inlineStr">
         <is>
-          <t>2026-07-11 08:33:16 PM PT</t>
+          <t>2026-07-11 08:33:52 PM PT</t>
         </is>
       </c>
       <c r="C152" t="n">
@@ -18087,7 +18087,7 @@
       </c>
       <c r="B153" t="inlineStr">
         <is>
-          <t>2026-07-11 08:33:17 PM PT</t>
+          <t>2026-07-11 08:33:53 PM PT</t>
         </is>
       </c>
       <c r="C153" t="n">
@@ -18201,7 +18201,7 @@
       </c>
       <c r="B154" t="inlineStr">
         <is>
-          <t>2026-07-11 08:33:17 PM PT</t>
+          <t>2026-07-11 08:33:53 PM PT</t>
         </is>
       </c>
       <c r="C154" t="n">
@@ -18315,7 +18315,7 @@
       </c>
       <c r="B155" t="inlineStr">
         <is>
-          <t>2026-07-11 08:33:16 PM PT</t>
+          <t>2026-07-11 08:33:52 PM PT</t>
         </is>
       </c>
       <c r="C155" t="n">
@@ -18429,7 +18429,7 @@
       </c>
       <c r="B156" t="inlineStr">
         <is>
-          <t>2026-07-11 08:33:18 PM PT</t>
+          <t>2026-07-11 08:33:54 PM PT</t>
         </is>
       </c>
       <c r="C156" t="n">
@@ -18552,7 +18552,7 @@
       </c>
       <c r="B157" t="inlineStr">
         <is>
-          <t>2026-07-11 08:33:18 PM PT</t>
+          <t>2026-07-11 08:33:54 PM PT</t>
         </is>
       </c>
       <c r="C157" t="n">
@@ -18675,7 +18675,7 @@
       </c>
       <c r="B158" t="inlineStr">
         <is>
-          <t>2026-07-11 08:33:18 PM PT</t>
+          <t>2026-07-11 08:33:54 PM PT</t>
         </is>
       </c>
       <c r="C158" t="n">
@@ -18798,7 +18798,7 @@
       </c>
       <c r="B159" t="inlineStr">
         <is>
-          <t>2026-07-11 08:33:18 PM PT</t>
+          <t>2026-07-11 08:33:54 PM PT</t>
         </is>
       </c>
       <c r="C159" t="n">
@@ -18921,7 +18921,7 @@
       </c>
       <c r="B160" t="inlineStr">
         <is>
-          <t>2026-07-11 08:33:18 PM PT</t>
+          <t>2026-07-11 08:33:54 PM PT</t>
         </is>
       </c>
       <c r="C160" t="n">
@@ -19035,7 +19035,7 @@
       </c>
       <c r="B161" t="inlineStr">
         <is>
-          <t>2026-07-11 08:33:18 PM PT</t>
+          <t>2026-07-11 08:33:54 PM PT</t>
         </is>
       </c>
       <c r="C161" t="n">
@@ -19149,7 +19149,7 @@
       </c>
       <c r="B162" t="inlineStr">
         <is>
-          <t>2026-07-11 08:33:18 PM PT</t>
+          <t>2026-07-11 08:33:54 PM PT</t>
         </is>
       </c>
       <c r="C162" t="n">
@@ -19263,7 +19263,7 @@
       </c>
       <c r="B163" t="inlineStr">
         <is>
-          <t>2026-07-11 08:33:18 PM PT</t>
+          <t>2026-07-11 08:33:53 PM PT</t>
         </is>
       </c>
       <c r="C163" t="n">
@@ -19377,7 +19377,7 @@
       </c>
       <c r="B164" t="inlineStr">
         <is>
-          <t>2026-07-11 08:33:18 PM PT</t>
+          <t>2026-07-11 08:33:53 PM PT</t>
         </is>
       </c>
       <c r="C164" t="n">
@@ -19491,7 +19491,7 @@
       </c>
       <c r="B165" t="inlineStr">
         <is>
-          <t>2026-07-11 08:33:17 PM PT</t>
+          <t>2026-07-11 08:33:53 PM PT</t>
         </is>
       </c>
       <c r="C165" t="n">
@@ -19605,7 +19605,7 @@
       </c>
       <c r="B166" t="inlineStr">
         <is>
-          <t>2026-07-11 08:33:17 PM PT</t>
+          <t>2026-07-11 08:33:53 PM PT</t>
         </is>
       </c>
       <c r="C166" t="n">
@@ -19719,7 +19719,7 @@
       </c>
       <c r="B167" t="inlineStr">
         <is>
-          <t>2026-07-11 08:33:17 PM PT</t>
+          <t>2026-07-11 08:33:53 PM PT</t>
         </is>
       </c>
       <c r="C167" t="n">
@@ -19833,7 +19833,7 @@
       </c>
       <c r="B168" t="inlineStr">
         <is>
-          <t>2026-07-11 08:33:17 PM PT</t>
+          <t>2026-07-11 08:33:53 PM PT</t>
         </is>
       </c>
       <c r="C168" t="n">
@@ -19947,7 +19947,7 @@
       </c>
       <c r="B169" t="inlineStr">
         <is>
-          <t>2026-07-11 08:33:17 PM PT</t>
+          <t>2026-07-11 08:33:53 PM PT</t>
         </is>
       </c>
       <c r="C169" t="n">
@@ -20061,7 +20061,7 @@
       </c>
       <c r="B170" t="inlineStr">
         <is>
-          <t>2026-07-11 08:33:16 PM PT</t>
+          <t>2026-07-11 08:33:52 PM PT</t>
         </is>
       </c>
       <c r="C170" t="n">
@@ -20175,7 +20175,7 @@
       </c>
       <c r="B171" t="inlineStr">
         <is>
-          <t>2026-07-11 08:33:18 PM PT</t>
+          <t>2026-07-11 08:33:54 PM PT</t>
         </is>
       </c>
       <c r="C171" t="n">
@@ -20203,7 +20203,7 @@
         <v>1</v>
       </c>
       <c r="I171" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="J171" t="n">
         <v>1</v>
@@ -20298,7 +20298,7 @@
       </c>
       <c r="B172" t="inlineStr">
         <is>
-          <t>2026-07-11 08:33:18 PM PT</t>
+          <t>2026-07-11 08:33:54 PM PT</t>
         </is>
       </c>
       <c r="C172" t="n">
@@ -20326,7 +20326,7 @@
         <v>1</v>
       </c>
       <c r="I172" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="J172" t="n">
         <v>1</v>
@@ -20421,7 +20421,7 @@
       </c>
       <c r="B173" t="inlineStr">
         <is>
-          <t>2026-07-11 08:33:17 PM PT</t>
+          <t>2026-07-11 08:33:53 PM PT</t>
         </is>
       </c>
       <c r="C173" t="n">
@@ -20535,7 +20535,7 @@
       </c>
       <c r="B174" t="inlineStr">
         <is>
-          <t>2026-07-11 08:33:17 PM PT</t>
+          <t>2026-07-11 08:33:53 PM PT</t>
         </is>
       </c>
       <c r="C174" t="n">
@@ -20649,7 +20649,7 @@
       </c>
       <c r="B175" t="inlineStr">
         <is>
-          <t>2026-07-11 08:33:16 PM PT</t>
+          <t>2026-07-11 08:33:52 PM PT</t>
         </is>
       </c>
       <c r="C175" t="n">
@@ -20763,7 +20763,7 @@
       </c>
       <c r="B176" t="inlineStr">
         <is>
-          <t>2026-07-11 08:33:16 PM PT</t>
+          <t>2026-07-11 08:33:52 PM PT</t>
         </is>
       </c>
       <c r="C176" t="n">
@@ -20877,7 +20877,7 @@
       </c>
       <c r="B177" t="inlineStr">
         <is>
-          <t>2026-07-11 08:33:16 PM PT</t>
+          <t>2026-07-11 08:33:52 PM PT</t>
         </is>
       </c>
       <c r="C177" t="n">
@@ -20991,7 +20991,7 @@
       </c>
       <c r="B178" t="inlineStr">
         <is>
-          <t>2026-07-11 08:33:16 PM PT</t>
+          <t>2026-07-11 08:33:52 PM PT</t>
         </is>
       </c>
       <c r="C178" t="n">
@@ -21105,7 +21105,7 @@
       </c>
       <c r="B179" t="inlineStr">
         <is>
-          <t>2026-07-11 08:33:16 PM PT</t>
+          <t>2026-07-11 08:33:52 PM PT</t>
         </is>
       </c>
       <c r="C179" t="n">
@@ -21219,7 +21219,7 @@
       </c>
       <c r="B180" t="inlineStr">
         <is>
-          <t>2026-07-11 08:33:17 PM PT</t>
+          <t>2026-07-11 08:33:53 PM PT</t>
         </is>
       </c>
       <c r="C180" t="n">
@@ -21333,7 +21333,7 @@
       </c>
       <c r="B181" t="inlineStr">
         <is>
-          <t>2026-07-11 08:33:17 PM PT</t>
+          <t>2026-07-11 08:33:53 PM PT</t>
         </is>
       </c>
       <c r="C181" t="n">
@@ -21447,7 +21447,7 @@
       </c>
       <c r="B182" t="inlineStr">
         <is>
-          <t>2026-07-11 08:33:17 PM PT</t>
+          <t>2026-07-11 08:33:53 PM PT</t>
         </is>
       </c>
       <c r="C182" t="n">
@@ -21561,7 +21561,7 @@
       </c>
       <c r="B183" t="inlineStr">
         <is>
-          <t>2026-07-11 08:33:17 PM PT</t>
+          <t>2026-07-11 08:33:53 PM PT</t>
         </is>
       </c>
       <c r="C183" t="n">
@@ -21675,7 +21675,7 @@
       </c>
       <c r="B184" t="inlineStr">
         <is>
-          <t>2026-07-11 08:33:16 PM PT</t>
+          <t>2026-07-11 08:33:52 PM PT</t>
         </is>
       </c>
       <c r="C184" t="n">
@@ -21789,7 +21789,7 @@
       </c>
       <c r="B185" t="inlineStr">
         <is>
-          <t>2026-07-11 08:33:16 PM PT</t>
+          <t>2026-07-11 08:33:52 PM PT</t>
         </is>
       </c>
       <c r="C185" t="n">
@@ -21903,7 +21903,7 @@
       </c>
       <c r="B186" t="inlineStr">
         <is>
-          <t>2026-07-11 08:33:17 PM PT</t>
+          <t>2026-07-11 08:33:53 PM PT</t>
         </is>
       </c>
       <c r="C186" t="n">
@@ -22017,7 +22017,7 @@
       </c>
       <c r="B187" t="inlineStr">
         <is>
-          <t>2026-07-11 08:33:17 PM PT</t>
+          <t>2026-07-11 08:33:53 PM PT</t>
         </is>
       </c>
       <c r="C187" t="n">
@@ -22131,7 +22131,7 @@
       </c>
       <c r="B188" t="inlineStr">
         <is>
-          <t>2026-07-11 08:33:17 PM PT</t>
+          <t>2026-07-11 08:33:53 PM PT</t>
         </is>
       </c>
       <c r="C188" t="n">
@@ -22245,7 +22245,7 @@
       </c>
       <c r="B189" t="inlineStr">
         <is>
-          <t>2026-07-11 08:33:17 PM PT</t>
+          <t>2026-07-11 08:33:53 PM PT</t>
         </is>
       </c>
       <c r="C189" t="n">
@@ -22359,7 +22359,7 @@
       </c>
       <c r="B190" t="inlineStr">
         <is>
-          <t>2026-07-11 08:33:18 PM PT</t>
+          <t>2026-07-11 08:33:54 PM PT</t>
         </is>
       </c>
       <c r="C190" t="n">
@@ -22482,7 +22482,7 @@
       </c>
       <c r="B191" t="inlineStr">
         <is>
-          <t>2026-07-11 08:33:17 PM PT</t>
+          <t>2026-07-11 08:33:53 PM PT</t>
         </is>
       </c>
       <c r="C191" t="n">
@@ -22596,7 +22596,7 @@
       </c>
       <c r="B192" t="inlineStr">
         <is>
-          <t>2026-07-11 08:33:17 PM PT</t>
+          <t>2026-07-11 08:33:53 PM PT</t>
         </is>
       </c>
       <c r="C192" t="n">
@@ -22710,7 +22710,7 @@
       </c>
       <c r="B193" t="inlineStr">
         <is>
-          <t>2026-07-11 08:33:18 PM PT</t>
+          <t>2026-07-11 08:33:54 PM PT</t>
         </is>
       </c>
       <c r="C193" t="n">
@@ -22738,7 +22738,7 @@
         <v>1</v>
       </c>
       <c r="I193" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="J193" t="n">
         <v>1</v>
@@ -22833,7 +22833,7 @@
       </c>
       <c r="B194" t="inlineStr">
         <is>
-          <t>2026-07-11 08:33:18 PM PT</t>
+          <t>2026-07-11 08:33:54 PM PT</t>
         </is>
       </c>
       <c r="C194" t="n">
@@ -22861,7 +22861,7 @@
         <v>1</v>
       </c>
       <c r="I194" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="J194" t="n">
         <v>1</v>
@@ -22956,7 +22956,7 @@
       </c>
       <c r="B195" t="inlineStr">
         <is>
-          <t>2026-07-11 08:33:16 PM PT</t>
+          <t>2026-07-11 08:33:53 PM PT</t>
         </is>
       </c>
       <c r="C195" t="n">
@@ -23070,7 +23070,7 @@
       </c>
       <c r="B196" t="inlineStr">
         <is>
-          <t>2026-07-11 08:33:18 PM PT</t>
+          <t>2026-07-11 08:33:54 PM PT</t>
         </is>
       </c>
       <c r="C196" t="n">
@@ -23184,7 +23184,7 @@
       </c>
       <c r="B197" t="inlineStr">
         <is>
-          <t>2026-07-11 08:33:18 PM PT</t>
+          <t>2026-07-11 08:33:54 PM PT</t>
         </is>
       </c>
       <c r="C197" t="n">
@@ -23298,7 +23298,7 @@
       </c>
       <c r="B198" t="inlineStr">
         <is>
-          <t>2026-07-11 08:33:17 PM PT</t>
+          <t>2026-07-11 08:33:53 PM PT</t>
         </is>
       </c>
       <c r="C198" t="n">
@@ -23412,7 +23412,7 @@
       </c>
       <c r="B199" t="inlineStr">
         <is>
-          <t>2026-07-11 08:33:17 PM PT</t>
+          <t>2026-07-11 08:33:53 PM PT</t>
         </is>
       </c>
       <c r="C199" t="n">
@@ -23526,7 +23526,7 @@
       </c>
       <c r="B200" t="inlineStr">
         <is>
-          <t>2026-07-11 08:33:17 PM PT</t>
+          <t>2026-07-11 08:33:53 PM PT</t>
         </is>
       </c>
       <c r="C200" t="n">
@@ -23640,7 +23640,7 @@
       </c>
       <c r="B201" t="inlineStr">
         <is>
-          <t>2026-07-11 08:33:17 PM PT</t>
+          <t>2026-07-11 08:33:53 PM PT</t>
         </is>
       </c>
       <c r="C201" t="n">
@@ -23754,7 +23754,7 @@
       </c>
       <c r="B202" t="inlineStr">
         <is>
-          <t>2026-07-11 08:33:18 PM PT</t>
+          <t>2026-07-11 08:33:53 PM PT</t>
         </is>
       </c>
       <c r="C202" t="n">
@@ -23868,7 +23868,7 @@
       </c>
       <c r="B203" t="inlineStr">
         <is>
-          <t>2026-07-11 08:33:17 PM PT</t>
+          <t>2026-07-11 08:33:53 PM PT</t>
         </is>
       </c>
       <c r="C203" t="n">
@@ -23982,7 +23982,7 @@
       </c>
       <c r="B204" t="inlineStr">
         <is>
-          <t>2026-07-11 08:33:17 PM PT</t>
+          <t>2026-07-11 08:33:53 PM PT</t>
         </is>
       </c>
       <c r="C204" t="n">
@@ -24096,7 +24096,7 @@
       </c>
       <c r="B205" t="inlineStr">
         <is>
-          <t>2026-07-11 08:33:17 PM PT</t>
+          <t>2026-07-11 08:33:53 PM PT</t>
         </is>
       </c>
       <c r="C205" t="n">
@@ -24210,7 +24210,7 @@
       </c>
       <c r="B206" t="inlineStr">
         <is>
-          <t>2026-07-11 08:33:16 PM PT</t>
+          <t>2026-07-11 08:33:53 PM PT</t>
         </is>
       </c>
       <c r="C206" t="n">
@@ -24324,7 +24324,7 @@
       </c>
       <c r="B207" t="inlineStr">
         <is>
-          <t>2026-07-11 08:33:16 PM PT</t>
+          <t>2026-07-11 08:33:53 PM PT</t>
         </is>
       </c>
       <c r="C207" t="n">
@@ -24438,7 +24438,7 @@
       </c>
       <c r="B208" t="inlineStr">
         <is>
-          <t>2026-07-11 08:33:17 PM PT</t>
+          <t>2026-07-11 08:33:53 PM PT</t>
         </is>
       </c>
       <c r="C208" t="n">
@@ -24552,7 +24552,7 @@
       </c>
       <c r="B209" t="inlineStr">
         <is>
-          <t>2026-07-11 08:33:17 PM PT</t>
+          <t>2026-07-11 08:33:53 PM PT</t>
         </is>
       </c>
       <c r="C209" t="n">
@@ -24666,7 +24666,7 @@
       </c>
       <c r="B210" t="inlineStr">
         <is>
-          <t>2026-07-11 08:33:17 PM PT</t>
+          <t>2026-07-11 08:33:53 PM PT</t>
         </is>
       </c>
       <c r="C210" t="n">
@@ -24780,7 +24780,7 @@
       </c>
       <c r="B211" t="inlineStr">
         <is>
-          <t>2026-07-11 08:33:17 PM PT</t>
+          <t>2026-07-11 08:33:53 PM PT</t>
         </is>
       </c>
       <c r="C211" t="n">
@@ -24894,7 +24894,7 @@
       </c>
       <c r="B212" t="inlineStr">
         <is>
-          <t>2026-07-11 08:33:17 PM PT</t>
+          <t>2026-07-11 08:33:53 PM PT</t>
         </is>
       </c>
       <c r="C212" t="n">
@@ -25008,7 +25008,7 @@
       </c>
       <c r="B213" t="inlineStr">
         <is>
-          <t>2026-07-11 08:33:16 PM PT</t>
+          <t>2026-07-11 08:33:52 PM PT</t>
         </is>
       </c>
       <c r="C213" t="n">
@@ -25122,7 +25122,7 @@
       </c>
       <c r="B214" t="inlineStr">
         <is>
-          <t>2026-07-11 08:33:17 PM PT</t>
+          <t>2026-07-11 08:33:53 PM PT</t>
         </is>
       </c>
       <c r="C214" t="n">
@@ -25236,7 +25236,7 @@
       </c>
       <c r="B215" t="inlineStr">
         <is>
-          <t>2026-07-11 08:33:17 PM PT</t>
+          <t>2026-07-11 08:33:53 PM PT</t>
         </is>
       </c>
       <c r="C215" t="n">
@@ -25350,7 +25350,7 @@
       </c>
       <c r="B216" t="inlineStr">
         <is>
-          <t>2026-07-11 08:33:16 PM PT</t>
+          <t>2026-07-11 08:33:52 PM PT</t>
         </is>
       </c>
       <c r="C216" t="n">
@@ -25464,7 +25464,7 @@
       </c>
       <c r="B217" t="inlineStr">
         <is>
-          <t>2026-07-11 08:33:17 PM PT</t>
+          <t>2026-07-11 08:33:53 PM PT</t>
         </is>
       </c>
       <c r="C217" t="n">
@@ -25578,7 +25578,7 @@
       </c>
       <c r="B218" t="inlineStr">
         <is>
-          <t>2026-07-11 08:33:17 PM PT</t>
+          <t>2026-07-11 08:33:53 PM PT</t>
         </is>
       </c>
       <c r="C218" t="n">
@@ -25692,7 +25692,7 @@
       </c>
       <c r="B219" t="inlineStr">
         <is>
-          <t>2026-07-11 08:33:17 PM PT</t>
+          <t>2026-07-11 08:33:53 PM PT</t>
         </is>
       </c>
       <c r="C219" t="n">
@@ -25806,7 +25806,7 @@
       </c>
       <c r="B220" t="inlineStr">
         <is>
-          <t>2026-07-11 08:33:17 PM PT</t>
+          <t>2026-07-11 08:33:53 PM PT</t>
         </is>
       </c>
       <c r="C220" t="n">
@@ -25920,7 +25920,7 @@
       </c>
       <c r="B221" t="inlineStr">
         <is>
-          <t>2026-07-11 08:33:17 PM PT</t>
+          <t>2026-07-11 08:33:53 PM PT</t>
         </is>
       </c>
       <c r="C221" t="n">
@@ -26034,7 +26034,7 @@
       </c>
       <c r="B222" t="inlineStr">
         <is>
-          <t>2026-07-11 08:33:17 PM PT</t>
+          <t>2026-07-11 08:33:53 PM PT</t>
         </is>
       </c>
       <c r="C222" t="n">
@@ -26148,7 +26148,7 @@
       </c>
       <c r="B223" t="inlineStr">
         <is>
-          <t>2026-07-11 08:33:17 PM PT</t>
+          <t>2026-07-11 08:33:53 PM PT</t>
         </is>
       </c>
       <c r="C223" t="n">
@@ -26262,7 +26262,7 @@
       </c>
       <c r="B224" t="inlineStr">
         <is>
-          <t>2026-07-11 08:33:16 PM PT</t>
+          <t>2026-07-11 08:33:52 PM PT</t>
         </is>
       </c>
       <c r="C224" t="n">
@@ -26376,7 +26376,7 @@
       </c>
       <c r="B225" t="inlineStr">
         <is>
-          <t>2026-07-11 08:33:16 PM PT</t>
+          <t>2026-07-11 08:33:52 PM PT</t>
         </is>
       </c>
       <c r="C225" t="n">
@@ -26490,7 +26490,7 @@
       </c>
       <c r="B226" t="inlineStr">
         <is>
-          <t>2026-07-11 08:33:17 PM PT</t>
+          <t>2026-07-11 08:33:53 PM PT</t>
         </is>
       </c>
       <c r="C226" t="n">
@@ -26604,7 +26604,7 @@
       </c>
       <c r="B227" t="inlineStr">
         <is>
-          <t>2026-07-11 08:33:17 PM PT</t>
+          <t>2026-07-11 08:33:53 PM PT</t>
         </is>
       </c>
       <c r="C227" t="n">
@@ -26718,7 +26718,7 @@
       </c>
       <c r="B228" t="inlineStr">
         <is>
-          <t>2026-07-11 08:33:17 PM PT</t>
+          <t>2026-07-11 08:33:53 PM PT</t>
         </is>
       </c>
       <c r="C228" t="n">
@@ -26832,7 +26832,7 @@
       </c>
       <c r="B229" t="inlineStr">
         <is>
-          <t>2026-07-11 08:33:17 PM PT</t>
+          <t>2026-07-11 08:33:53 PM PT</t>
         </is>
       </c>
       <c r="C229" t="n">
@@ -26946,7 +26946,7 @@
       </c>
       <c r="B230" t="inlineStr">
         <is>
-          <t>2026-07-11 08:33:18 PM PT</t>
+          <t>2026-07-11 08:33:54 PM PT</t>
         </is>
       </c>
       <c r="C230" t="n">
@@ -27069,7 +27069,7 @@
       </c>
       <c r="B231" t="inlineStr">
         <is>
-          <t>2026-07-11 08:33:17 PM PT</t>
+          <t>2026-07-11 08:33:53 PM PT</t>
         </is>
       </c>
       <c r="C231" t="n">
@@ -27183,7 +27183,7 @@
       </c>
       <c r="B232" t="inlineStr">
         <is>
-          <t>2026-07-11 08:33:17 PM PT</t>
+          <t>2026-07-11 08:33:53 PM PT</t>
         </is>
       </c>
       <c r="C232" t="n">
@@ -27297,7 +27297,7 @@
       </c>
       <c r="B233" t="inlineStr">
         <is>
-          <t>2026-07-11 08:33:17 PM PT</t>
+          <t>2026-07-11 08:33:53 PM PT</t>
         </is>
       </c>
       <c r="C233" t="n">
@@ -27411,7 +27411,7 @@
       </c>
       <c r="B234" t="inlineStr">
         <is>
-          <t>2026-07-11 08:33:17 PM PT</t>
+          <t>2026-07-11 08:33:53 PM PT</t>
         </is>
       </c>
       <c r="C234" t="n">
@@ -27525,7 +27525,7 @@
       </c>
       <c r="B235" t="inlineStr">
         <is>
-          <t>2026-07-11 08:33:18 PM PT</t>
+          <t>2026-07-11 08:33:54 PM PT</t>
         </is>
       </c>
       <c r="C235" t="n">
@@ -27553,7 +27553,7 @@
         <v>1</v>
       </c>
       <c r="I235" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="J235" t="n">
         <v>1</v>
@@ -27648,7 +27648,7 @@
       </c>
       <c r="B236" t="inlineStr">
         <is>
-          <t>2026-07-11 08:33:18 PM PT</t>
+          <t>2026-07-11 08:33:54 PM PT</t>
         </is>
       </c>
       <c r="C236" t="n">
@@ -27676,7 +27676,7 @@
         <v>1</v>
       </c>
       <c r="I236" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="J236" t="n">
         <v>1</v>
@@ -27771,7 +27771,7 @@
       </c>
       <c r="B237" t="inlineStr">
         <is>
-          <t>2026-07-11 08:33:16 PM PT</t>
+          <t>2026-07-11 08:33:53 PM PT</t>
         </is>
       </c>
       <c r="C237" t="n">
@@ -27885,7 +27885,7 @@
       </c>
       <c r="B238" t="inlineStr">
         <is>
-          <t>2026-07-11 08:33:16 PM PT</t>
+          <t>2026-07-11 08:33:53 PM PT</t>
         </is>
       </c>
       <c r="C238" t="n">
@@ -27999,7 +27999,7 @@
       </c>
       <c r="B239" t="inlineStr">
         <is>
-          <t>2026-07-11 08:33:16 PM PT</t>
+          <t>2026-07-11 08:33:53 PM PT</t>
         </is>
       </c>
       <c r="C239" t="n">
@@ -28113,7 +28113,7 @@
       </c>
       <c r="B240" t="inlineStr">
         <is>
-          <t>2026-07-11 08:33:16 PM PT</t>
+          <t>2026-07-11 08:33:53 PM PT</t>
         </is>
       </c>
       <c r="C240" t="n">
@@ -28227,7 +28227,7 @@
       </c>
       <c r="B241" t="inlineStr">
         <is>
-          <t>2026-07-11 08:33:16 PM PT</t>
+          <t>2026-07-11 08:33:53 PM PT</t>
         </is>
       </c>
       <c r="C241" t="n">
@@ -28341,7 +28341,7 @@
       </c>
       <c r="B242" t="inlineStr">
         <is>
-          <t>2026-07-11 08:33:16 PM PT</t>
+          <t>2026-07-11 08:33:53 PM PT</t>
         </is>
       </c>
       <c r="C242" t="n">
@@ -28455,7 +28455,7 @@
       </c>
       <c r="B243" t="inlineStr">
         <is>
-          <t>2026-07-11 08:33:16 PM PT</t>
+          <t>2026-07-11 08:33:53 PM PT</t>
         </is>
       </c>
       <c r="C243" t="n">
@@ -28569,7 +28569,7 @@
       </c>
       <c r="B244" t="inlineStr">
         <is>
-          <t>2026-07-11 08:33:18 PM PT</t>
+          <t>2026-07-11 08:33:54 PM PT</t>
         </is>
       </c>
       <c r="C244" t="n">
@@ -28683,7 +28683,7 @@
       </c>
       <c r="B245" t="inlineStr">
         <is>
-          <t>2026-07-11 08:33:18 PM PT</t>
+          <t>2026-07-11 08:33:54 PM PT</t>
         </is>
       </c>
       <c r="C245" t="n">
@@ -28797,7 +28797,7 @@
       </c>
       <c r="B246" t="inlineStr">
         <is>
-          <t>2026-07-11 08:33:18 PM PT</t>
+          <t>2026-07-11 08:33:54 PM PT</t>
         </is>
       </c>
       <c r="C246" t="n">
@@ -28911,7 +28911,7 @@
       </c>
       <c r="B247" t="inlineStr">
         <is>
-          <t>2026-07-11 08:33:17 PM PT</t>
+          <t>2026-07-11 08:33:53 PM PT</t>
         </is>
       </c>
       <c r="C247" t="n">
@@ -29025,7 +29025,7 @@
       </c>
       <c r="B248" t="inlineStr">
         <is>
-          <t>2026-07-11 08:33:17 PM PT</t>
+          <t>2026-07-11 08:33:53 PM PT</t>
         </is>
       </c>
       <c r="C248" t="n">
@@ -29139,7 +29139,7 @@
       </c>
       <c r="B249" t="inlineStr">
         <is>
-          <t>2026-07-11 08:33:17 PM PT</t>
+          <t>2026-07-11 08:33:53 PM PT</t>
         </is>
       </c>
       <c r="C249" t="n">
@@ -29253,7 +29253,7 @@
       </c>
       <c r="B250" t="inlineStr">
         <is>
-          <t>2026-07-11 08:33:17 PM PT</t>
+          <t>2026-07-11 08:33:53 PM PT</t>
         </is>
       </c>
       <c r="C250" t="n">
@@ -29367,7 +29367,7 @@
       </c>
       <c r="B251" t="inlineStr">
         <is>
-          <t>2026-07-11 08:33:17 PM PT</t>
+          <t>2026-07-11 08:33:53 PM PT</t>
         </is>
       </c>
       <c r="C251" t="n">
@@ -29481,7 +29481,7 @@
       </c>
       <c r="B252" t="inlineStr">
         <is>
-          <t>2026-07-11 08:33:17 PM PT</t>
+          <t>2026-07-11 08:33:53 PM PT</t>
         </is>
       </c>
       <c r="C252" t="n">
@@ -29595,7 +29595,7 @@
       </c>
       <c r="B253" t="inlineStr">
         <is>
-          <t>2026-07-11 08:33:18 PM PT</t>
+          <t>2026-07-11 08:33:53 PM PT</t>
         </is>
       </c>
       <c r="C253" t="n">
@@ -29709,7 +29709,7 @@
       </c>
       <c r="B254" t="inlineStr">
         <is>
-          <t>2026-07-11 08:33:18 PM PT</t>
+          <t>2026-07-11 08:33:53 PM PT</t>
         </is>
       </c>
       <c r="C254" t="n">
@@ -29823,7 +29823,7 @@
       </c>
       <c r="B255" t="inlineStr">
         <is>
-          <t>2026-07-11 08:33:18 PM PT</t>
+          <t>2026-07-11 08:33:53 PM PT</t>
         </is>
       </c>
       <c r="C255" t="n">
@@ -29937,7 +29937,7 @@
       </c>
       <c r="B256" t="inlineStr">
         <is>
-          <t>2026-07-11 08:33:18 PM PT</t>
+          <t>2026-07-11 08:33:53 PM PT</t>
         </is>
       </c>
       <c r="C256" t="n">
@@ -30051,7 +30051,7 @@
       </c>
       <c r="B257" t="inlineStr">
         <is>
-          <t>2026-07-11 08:33:18 PM PT</t>
+          <t>2026-07-11 08:33:53 PM PT</t>
         </is>
       </c>
       <c r="C257" t="n">
@@ -30165,7 +30165,7 @@
       </c>
       <c r="B258" t="inlineStr">
         <is>
-          <t>2026-07-11 08:33:17 PM PT</t>
+          <t>2026-07-11 08:33:53 PM PT</t>
         </is>
       </c>
       <c r="C258" t="n">
@@ -30279,7 +30279,7 @@
       </c>
       <c r="B259" t="inlineStr">
         <is>
-          <t>2026-07-11 08:33:17 PM PT</t>
+          <t>2026-07-11 08:33:53 PM PT</t>
         </is>
       </c>
       <c r="C259" t="n">
@@ -30393,7 +30393,7 @@
       </c>
       <c r="B260" t="inlineStr">
         <is>
-          <t>2026-07-11 08:33:17 PM PT</t>
+          <t>2026-07-11 08:33:53 PM PT</t>
         </is>
       </c>
       <c r="C260" t="n">
@@ -30507,7 +30507,7 @@
       </c>
       <c r="B261" t="inlineStr">
         <is>
-          <t>2026-07-11 08:33:16 PM PT</t>
+          <t>2026-07-11 08:33:53 PM PT</t>
         </is>
       </c>
       <c r="C261" t="n">
@@ -30621,7 +30621,7 @@
       </c>
       <c r="B262" t="inlineStr">
         <is>
-          <t>2026-07-11 08:33:16 PM PT</t>
+          <t>2026-07-11 08:33:53 PM PT</t>
         </is>
       </c>
       <c r="C262" t="n">
@@ -30735,7 +30735,7 @@
       </c>
       <c r="B263" t="inlineStr">
         <is>
-          <t>2026-07-11 08:33:16 PM PT</t>
+          <t>2026-07-11 08:33:53 PM PT</t>
         </is>
       </c>
       <c r="C263" t="n">
@@ -30849,7 +30849,7 @@
       </c>
       <c r="B264" t="inlineStr">
         <is>
-          <t>2026-07-11 08:33:16 PM PT</t>
+          <t>2026-07-11 08:33:53 PM PT</t>
         </is>
       </c>
       <c r="C264" t="n">
@@ -30963,7 +30963,7 @@
       </c>
       <c r="B265" t="inlineStr">
         <is>
-          <t>2026-07-11 08:33:17 PM PT</t>
+          <t>2026-07-11 08:33:53 PM PT</t>
         </is>
       </c>
       <c r="C265" t="n">
@@ -31077,7 +31077,7 @@
       </c>
       <c r="B266" t="inlineStr">
         <is>
-          <t>2026-07-11 08:33:17 PM PT</t>
+          <t>2026-07-11 08:33:53 PM PT</t>
         </is>
       </c>
       <c r="C266" t="n">
@@ -31191,7 +31191,7 @@
       </c>
       <c r="B267" t="inlineStr">
         <is>
-          <t>2026-07-11 08:33:17 PM PT</t>
+          <t>2026-07-11 08:33:53 PM PT</t>
         </is>
       </c>
       <c r="C267" t="n">
@@ -31305,7 +31305,7 @@
       </c>
       <c r="B268" t="inlineStr">
         <is>
-          <t>2026-07-11 08:33:17 PM PT</t>
+          <t>2026-07-11 08:33:53 PM PT</t>
         </is>
       </c>
       <c r="C268" t="n">
@@ -31419,7 +31419,7 @@
       </c>
       <c r="B269" t="inlineStr">
         <is>
-          <t>2026-07-11 08:33:17 PM PT</t>
+          <t>2026-07-11 08:33:53 PM PT</t>
         </is>
       </c>
       <c r="C269" t="n">
@@ -31533,7 +31533,7 @@
       </c>
       <c r="B270" t="inlineStr">
         <is>
-          <t>2026-07-11 08:33:17 PM PT</t>
+          <t>2026-07-11 08:33:53 PM PT</t>
         </is>
       </c>
       <c r="C270" t="n">
@@ -31647,7 +31647,7 @@
       </c>
       <c r="B271" t="inlineStr">
         <is>
-          <t>2026-07-11 08:33:17 PM PT</t>
+          <t>2026-07-11 08:33:53 PM PT</t>
         </is>
       </c>
       <c r="C271" t="n">
@@ -31761,7 +31761,7 @@
       </c>
       <c r="B272" t="inlineStr">
         <is>
-          <t>2026-07-11 08:33:17 PM PT</t>
+          <t>2026-07-11 08:33:53 PM PT</t>
         </is>
       </c>
       <c r="C272" t="n">
@@ -31875,7 +31875,7 @@
       </c>
       <c r="B273" t="inlineStr">
         <is>
-          <t>2026-07-11 08:33:17 PM PT</t>
+          <t>2026-07-11 08:33:53 PM PT</t>
         </is>
       </c>
       <c r="C273" t="n">
@@ -31989,7 +31989,7 @@
       </c>
       <c r="B274" t="inlineStr">
         <is>
-          <t>2026-07-11 08:33:17 PM PT</t>
+          <t>2026-07-11 08:33:53 PM PT</t>
         </is>
       </c>
       <c r="C274" t="n">
@@ -32103,7 +32103,7 @@
       </c>
       <c r="B275" t="inlineStr">
         <is>
-          <t>2026-07-11 08:33:17 PM PT</t>
+          <t>2026-07-11 08:33:53 PM PT</t>
         </is>
       </c>
       <c r="C275" t="n">
@@ -32217,7 +32217,7 @@
       </c>
       <c r="B276" t="inlineStr">
         <is>
-          <t>2026-07-11 08:33:16 PM PT</t>
+          <t>2026-07-11 08:33:52 PM PT</t>
         </is>
       </c>
       <c r="C276" t="n">
@@ -32331,7 +32331,7 @@
       </c>
       <c r="B277" t="inlineStr">
         <is>
-          <t>2026-07-11 08:33:16 PM PT</t>
+          <t>2026-07-11 08:33:52 PM PT</t>
         </is>
       </c>
       <c r="C277" t="n">
@@ -32445,7 +32445,7 @@
       </c>
       <c r="B278" t="inlineStr">
         <is>
-          <t>2026-07-11 08:33:16 PM PT</t>
+          <t>2026-07-11 08:33:52 PM PT</t>
         </is>
       </c>
       <c r="C278" t="n">
@@ -32559,7 +32559,7 @@
       </c>
       <c r="B279" t="inlineStr">
         <is>
-          <t>2026-07-11 08:33:18 PM PT</t>
+          <t>2026-07-11 08:33:54 PM PT</t>
         </is>
       </c>
       <c r="C279" t="n">
@@ -32587,7 +32587,7 @@
         <v>1</v>
       </c>
       <c r="I279" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="J279" t="n">
         <v>1</v>
@@ -32682,7 +32682,7 @@
       </c>
       <c r="B280" t="inlineStr">
         <is>
-          <t>2026-07-11 08:33:18 PM PT</t>
+          <t>2026-07-11 08:33:54 PM PT</t>
         </is>
       </c>
       <c r="C280" t="n">
@@ -32710,7 +32710,7 @@
         <v>1</v>
       </c>
       <c r="I280" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="J280" t="n">
         <v>1</v>
@@ -32805,7 +32805,7 @@
       </c>
       <c r="B281" t="inlineStr">
         <is>
-          <t>2026-07-11 08:33:18 PM PT</t>
+          <t>2026-07-11 08:33:54 PM PT</t>
         </is>
       </c>
       <c r="C281" t="n">
@@ -32833,7 +32833,7 @@
         <v>1</v>
       </c>
       <c r="I281" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="J281" t="n">
         <v>1</v>
@@ -32928,7 +32928,7 @@
       </c>
       <c r="B282" t="inlineStr">
         <is>
-          <t>2026-07-11 08:33:18 PM PT</t>
+          <t>2026-07-11 08:33:54 PM PT</t>
         </is>
       </c>
       <c r="C282" t="n">
@@ -32956,7 +32956,7 @@
         <v>1</v>
       </c>
       <c r="I282" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="J282" t="n">
         <v>1</v>
@@ -33051,7 +33051,7 @@
       </c>
       <c r="B283" t="inlineStr">
         <is>
-          <t>2026-07-11 08:33:18 PM PT</t>
+          <t>2026-07-11 08:33:54 PM PT</t>
         </is>
       </c>
       <c r="C283" t="n">
@@ -33079,7 +33079,7 @@
         <v>1</v>
       </c>
       <c r="I283" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="J283" t="n">
         <v>1</v>
@@ -33174,7 +33174,7 @@
       </c>
       <c r="B284" t="inlineStr">
         <is>
-          <t>2026-07-11 08:33:18 PM PT</t>
+          <t>2026-07-11 08:33:54 PM PT</t>
         </is>
       </c>
       <c r="C284" t="n">
@@ -33202,7 +33202,7 @@
         <v>1</v>
       </c>
       <c r="I284" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="J284" t="n">
         <v>1</v>
@@ -33297,7 +33297,7 @@
       </c>
       <c r="B285" t="inlineStr">
         <is>
-          <t>2026-07-11 08:33:18 PM PT</t>
+          <t>2026-07-11 08:33:54 PM PT</t>
         </is>
       </c>
       <c r="C285" t="n">
@@ -33325,7 +33325,7 @@
         <v>1</v>
       </c>
       <c r="I285" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="J285" t="n">
         <v>1</v>
@@ -33420,7 +33420,7 @@
       </c>
       <c r="B286" t="inlineStr">
         <is>
-          <t>2026-07-11 08:33:17 PM PT</t>
+          <t>2026-07-11 08:33:53 PM PT</t>
         </is>
       </c>
       <c r="C286" t="n">
@@ -33534,7 +33534,7 @@
       </c>
       <c r="B287" t="inlineStr">
         <is>
-          <t>2026-07-11 08:33:16 PM PT</t>
+          <t>2026-07-11 08:33:52 PM PT</t>
         </is>
       </c>
       <c r="C287" t="n">
@@ -33648,7 +33648,7 @@
       </c>
       <c r="B288" t="inlineStr">
         <is>
-          <t>2026-07-11 08:33:16 PM PT</t>
+          <t>2026-07-11 08:33:52 PM PT</t>
         </is>
       </c>
       <c r="C288" t="n">
@@ -33762,7 +33762,7 @@
       </c>
       <c r="B289" t="inlineStr">
         <is>
-          <t>2026-07-11 08:33:16 PM PT</t>
+          <t>2026-07-11 08:33:52 PM PT</t>
         </is>
       </c>
       <c r="C289" t="n">
@@ -33876,7 +33876,7 @@
       </c>
       <c r="B290" t="inlineStr">
         <is>
-          <t>2026-07-11 08:33:16 PM PT</t>
+          <t>2026-07-11 08:33:52 PM PT</t>
         </is>
       </c>
       <c r="C290" t="n">
@@ -33990,7 +33990,7 @@
       </c>
       <c r="B291" t="inlineStr">
         <is>
-          <t>2026-07-11 08:33:16 PM PT</t>
+          <t>2026-07-11 08:33:52 PM PT</t>
         </is>
       </c>
       <c r="C291" t="n">
@@ -34104,7 +34104,7 @@
       </c>
       <c r="B292" t="inlineStr">
         <is>
-          <t>2026-07-11 08:33:16 PM PT</t>
+          <t>2026-07-11 08:33:52 PM PT</t>
         </is>
       </c>
       <c r="C292" t="n">
@@ -34218,7 +34218,7 @@
       </c>
       <c r="B293" t="inlineStr">
         <is>
-          <t>2026-07-11 08:33:16 PM PT</t>
+          <t>2026-07-11 08:33:52 PM PT</t>
         </is>
       </c>
       <c r="C293" t="n">
@@ -34332,7 +34332,7 @@
       </c>
       <c r="B294" t="inlineStr">
         <is>
-          <t>2026-07-11 08:33:17 PM PT</t>
+          <t>2026-07-11 08:33:53 PM PT</t>
         </is>
       </c>
       <c r="C294" t="n">
@@ -34446,7 +34446,7 @@
       </c>
       <c r="B295" t="inlineStr">
         <is>
-          <t>2026-07-11 08:33:17 PM PT</t>
+          <t>2026-07-11 08:33:53 PM PT</t>
         </is>
       </c>
       <c r="C295" t="n">
@@ -34560,7 +34560,7 @@
       </c>
       <c r="B296" t="inlineStr">
         <is>
-          <t>2026-07-11 08:33:17 PM PT</t>
+          <t>2026-07-11 08:33:53 PM PT</t>
         </is>
       </c>
       <c r="C296" t="n">
@@ -34674,7 +34674,7 @@
       </c>
       <c r="B297" t="inlineStr">
         <is>
-          <t>2026-07-11 08:33:17 PM PT</t>
+          <t>2026-07-11 08:33:53 PM PT</t>
         </is>
       </c>
       <c r="C297" t="n">
@@ -34788,7 +34788,7 @@
       </c>
       <c r="B298" t="inlineStr">
         <is>
-          <t>2026-07-11 08:33:17 PM PT</t>
+          <t>2026-07-11 08:33:53 PM PT</t>
         </is>
       </c>
       <c r="C298" t="n">
@@ -34902,7 +34902,7 @@
       </c>
       <c r="B299" t="inlineStr">
         <is>
-          <t>2026-07-11 08:33:17 PM PT</t>
+          <t>2026-07-11 08:33:53 PM PT</t>
         </is>
       </c>
       <c r="C299" t="n">
@@ -35016,7 +35016,7 @@
       </c>
       <c r="B300" t="inlineStr">
         <is>
-          <t>2026-07-11 08:33:17 PM PT</t>
+          <t>2026-07-11 08:33:53 PM PT</t>
         </is>
       </c>
       <c r="C300" t="n">
@@ -35130,7 +35130,7 @@
       </c>
       <c r="B301" t="inlineStr">
         <is>
-          <t>2026-07-11 08:33:17 PM PT</t>
+          <t>2026-07-11 08:33:53 PM PT</t>
         </is>
       </c>
       <c r="C301" t="n">
@@ -35244,7 +35244,7 @@
       </c>
       <c r="B302" t="inlineStr">
         <is>
-          <t>2026-07-11 08:33:16 PM PT</t>
+          <t>2026-07-11 08:33:52 PM PT</t>
         </is>
       </c>
       <c r="C302" t="n">
@@ -35358,7 +35358,7 @@
       </c>
       <c r="B303" t="inlineStr">
         <is>
-          <t>2026-07-11 08:33:16 PM PT</t>
+          <t>2026-07-11 08:33:52 PM PT</t>
         </is>
       </c>
       <c r="C303" t="n">
@@ -35472,7 +35472,7 @@
       </c>
       <c r="B304" t="inlineStr">
         <is>
-          <t>2026-07-11 08:33:16 PM PT</t>
+          <t>2026-07-11 08:33:52 PM PT</t>
         </is>
       </c>
       <c r="C304" t="n">
@@ -35586,7 +35586,7 @@
       </c>
       <c r="B305" t="inlineStr">
         <is>
-          <t>2026-07-11 08:33:16 PM PT</t>
+          <t>2026-07-11 08:33:52 PM PT</t>
         </is>
       </c>
       <c r="C305" t="n">
@@ -35700,7 +35700,7 @@
       </c>
       <c r="B306" t="inlineStr">
         <is>
-          <t>2026-07-11 08:33:16 PM PT</t>
+          <t>2026-07-11 08:33:52 PM PT</t>
         </is>
       </c>
       <c r="C306" t="n">
@@ -35814,7 +35814,7 @@
       </c>
       <c r="B307" t="inlineStr">
         <is>
-          <t>2026-07-11 08:33:16 PM PT</t>
+          <t>2026-07-11 08:33:52 PM PT</t>
         </is>
       </c>
       <c r="C307" t="n">
@@ -35928,7 +35928,7 @@
       </c>
       <c r="B308" t="inlineStr">
         <is>
-          <t>2026-07-11 08:33:16 PM PT</t>
+          <t>2026-07-11 08:33:52 PM PT</t>
         </is>
       </c>
       <c r="C308" t="n">
@@ -36042,7 +36042,7 @@
       </c>
       <c r="B309" t="inlineStr">
         <is>
-          <t>2026-07-11 08:33:16 PM PT</t>
+          <t>2026-07-11 08:33:52 PM PT</t>
         </is>
       </c>
       <c r="C309" t="n">
@@ -36156,7 +36156,7 @@
       </c>
       <c r="B310" t="inlineStr">
         <is>
-          <t>2026-07-11 08:33:18 PM PT</t>
+          <t>2026-07-11 08:33:54 PM PT</t>
         </is>
       </c>
       <c r="C310" t="n">
@@ -36279,7 +36279,7 @@
       </c>
       <c r="B311" t="inlineStr">
         <is>
-          <t>2026-07-11 08:33:17 PM PT</t>
+          <t>2026-07-11 08:33:53 PM PT</t>
         </is>
       </c>
       <c r="C311" t="n">
@@ -36393,7 +36393,7 @@
       </c>
       <c r="B312" t="inlineStr">
         <is>
-          <t>2026-07-11 08:33:17 PM PT</t>
+          <t>2026-07-11 08:33:53 PM PT</t>
         </is>
       </c>
       <c r="C312" t="n">
@@ -36507,7 +36507,7 @@
       </c>
       <c r="B313" t="inlineStr">
         <is>
-          <t>2026-07-11 08:33:17 PM PT</t>
+          <t>2026-07-11 08:33:53 PM PT</t>
         </is>
       </c>
       <c r="C313" t="n">
@@ -36621,7 +36621,7 @@
       </c>
       <c r="B314" t="inlineStr">
         <is>
-          <t>2026-07-11 08:33:17 PM PT</t>
+          <t>2026-07-11 08:33:53 PM PT</t>
         </is>
       </c>
       <c r="C314" t="n">
@@ -36735,7 +36735,7 @@
       </c>
       <c r="B315" t="inlineStr">
         <is>
-          <t>2026-07-11 08:33:17 PM PT</t>
+          <t>2026-07-11 08:33:53 PM PT</t>
         </is>
       </c>
       <c r="C315" t="n">
@@ -36849,7 +36849,7 @@
       </c>
       <c r="B316" t="inlineStr">
         <is>
-          <t>2026-07-11 08:33:17 PM PT</t>
+          <t>2026-07-11 08:33:53 PM PT</t>
         </is>
       </c>
       <c r="C316" t="n">
@@ -36963,7 +36963,7 @@
       </c>
       <c r="B317" t="inlineStr">
         <is>
-          <t>2026-07-11 08:33:17 PM PT</t>
+          <t>2026-07-11 08:33:53 PM PT</t>
         </is>
       </c>
       <c r="C317" t="n">
@@ -37077,7 +37077,7 @@
       </c>
       <c r="B318" t="inlineStr">
         <is>
-          <t>2026-07-11 08:33:18 PM PT</t>
+          <t>2026-07-11 08:33:54 PM PT</t>
         </is>
       </c>
       <c r="C318" t="n">
@@ -37191,7 +37191,7 @@
       </c>
       <c r="B319" t="inlineStr">
         <is>
-          <t>2026-07-11 08:33:18 PM PT</t>
+          <t>2026-07-11 08:33:54 PM PT</t>
         </is>
       </c>
       <c r="C319" t="n">
@@ -37305,7 +37305,7 @@
       </c>
       <c r="B320" t="inlineStr">
         <is>
-          <t>2026-07-11 08:33:18 PM PT</t>
+          <t>2026-07-11 08:33:54 PM PT</t>
         </is>
       </c>
       <c r="C320" t="n">
@@ -37419,7 +37419,7 @@
       </c>
       <c r="B321" t="inlineStr">
         <is>
-          <t>2026-07-11 08:33:18 PM PT</t>
+          <t>2026-07-11 08:33:54 PM PT</t>
         </is>
       </c>
       <c r="C321" t="n">
@@ -37533,7 +37533,7 @@
       </c>
       <c r="B322" t="inlineStr">
         <is>
-          <t>2026-07-11 08:33:17 PM PT</t>
+          <t>2026-07-11 08:33:53 PM PT</t>
         </is>
       </c>
       <c r="C322" t="n">
@@ -37647,7 +37647,7 @@
       </c>
       <c r="B323" t="inlineStr">
         <is>
-          <t>2026-07-11 08:33:17 PM PT</t>
+          <t>2026-07-11 08:33:53 PM PT</t>
         </is>
       </c>
       <c r="C323" t="n">
@@ -37761,7 +37761,7 @@
       </c>
       <c r="B324" t="inlineStr">
         <is>
-          <t>2026-07-11 08:33:17 PM PT</t>
+          <t>2026-07-11 08:33:53 PM PT</t>
         </is>
       </c>
       <c r="C324" t="n">
@@ -37875,7 +37875,7 @@
       </c>
       <c r="B325" t="inlineStr">
         <is>
-          <t>2026-07-11 08:33:17 PM PT</t>
+          <t>2026-07-11 08:33:53 PM PT</t>
         </is>
       </c>
       <c r="C325" t="n">
@@ -37989,7 +37989,7 @@
       </c>
       <c r="B326" t="inlineStr">
         <is>
-          <t>2026-07-11 08:33:17 PM PT</t>
+          <t>2026-07-11 08:33:53 PM PT</t>
         </is>
       </c>
       <c r="C326" t="n">
@@ -38103,7 +38103,7 @@
       </c>
       <c r="B327" t="inlineStr">
         <is>
-          <t>2026-07-11 08:33:17 PM PT</t>
+          <t>2026-07-11 08:33:53 PM PT</t>
         </is>
       </c>
       <c r="C327" t="n">
@@ -38217,7 +38217,7 @@
       </c>
       <c r="B328" t="inlineStr">
         <is>
-          <t>2026-07-11 08:33:17 PM PT</t>
+          <t>2026-07-11 08:33:53 PM PT</t>
         </is>
       </c>
       <c r="C328" t="n">
@@ -38331,7 +38331,7 @@
       </c>
       <c r="B329" t="inlineStr">
         <is>
-          <t>2026-07-11 08:33:17 PM PT</t>
+          <t>2026-07-11 08:33:53 PM PT</t>
         </is>
       </c>
       <c r="C329" t="n">
@@ -38445,7 +38445,7 @@
       </c>
       <c r="B330" t="inlineStr">
         <is>
-          <t>2026-07-11 08:33:17 PM PT</t>
+          <t>2026-07-11 08:33:53 PM PT</t>
         </is>
       </c>
       <c r="C330" t="n">
@@ -38559,7 +38559,7 @@
       </c>
       <c r="B331" t="inlineStr">
         <is>
-          <t>2026-07-11 08:33:18 PM PT</t>
+          <t>2026-07-11 08:33:54 PM PT</t>
         </is>
       </c>
       <c r="C331" t="n">
@@ -38682,7 +38682,7 @@
       </c>
       <c r="B332" t="inlineStr">
         <is>
-          <t>2026-07-11 08:33:17 PM PT</t>
+          <t>2026-07-11 08:33:53 PM PT</t>
         </is>
       </c>
       <c r="C332" t="n">
@@ -38796,7 +38796,7 @@
       </c>
       <c r="B333" t="inlineStr">
         <is>
-          <t>2026-07-11 08:33:17 PM PT</t>
+          <t>2026-07-11 08:33:53 PM PT</t>
         </is>
       </c>
       <c r="C333" t="n">

--- a/live_mlb_hitter_fantasy_scores_2026_07_11.xlsx
+++ b/live_mlb_hitter_fantasy_scores_2026_07_11.xlsx
@@ -693,7 +693,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-07-11 08:33:52 PM PT</t>
+          <t>2026-07-11 08:35:52 PM PT</t>
         </is>
       </c>
       <c r="C2" t="n">
@@ -807,7 +807,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>2026-07-11 08:33:54 PM PT</t>
+          <t>2026-07-11 08:35:54 PM PT</t>
         </is>
       </c>
       <c r="C3" t="n">
@@ -820,7 +820,7 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Top 8 | 1 out</t>
+          <t>Top 8 | 2 out</t>
         </is>
       </c>
       <c r="F3" t="n">
@@ -832,13 +832,13 @@
         </is>
       </c>
       <c r="H3" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I3" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="J3" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K3" t="inlineStr">
         <is>
@@ -930,7 +930,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-07-11 08:33:53 PM PT</t>
+          <t>2026-07-11 08:35:53 PM PT</t>
         </is>
       </c>
       <c r="C4" t="n">
@@ -1044,7 +1044,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>2026-07-11 08:33:54 PM PT</t>
+          <t>2026-07-11 08:35:54 PM PT</t>
         </is>
       </c>
       <c r="C5" t="n">
@@ -1057,7 +1057,7 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Bottom 8 | 0 out</t>
+          <t>Bottom 8 | 1 out</t>
         </is>
       </c>
       <c r="F5" t="n">
@@ -1069,10 +1069,10 @@
         </is>
       </c>
       <c r="H5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="J5" t="n">
         <v>0</v>
@@ -1167,7 +1167,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>2026-07-11 08:33:53 PM PT</t>
+          <t>2026-07-11 08:35:53 PM PT</t>
         </is>
       </c>
       <c r="C6" t="n">
@@ -1281,7 +1281,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>2026-07-11 08:33:54 PM PT</t>
+          <t>2026-07-11 08:35:54 PM PT</t>
         </is>
       </c>
       <c r="C7" t="n">
@@ -1395,7 +1395,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>2026-07-11 08:33:53 PM PT</t>
+          <t>2026-07-11 08:35:53 PM PT</t>
         </is>
       </c>
       <c r="C8" t="n">
@@ -1509,7 +1509,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>2026-07-11 08:33:53 PM PT</t>
+          <t>2026-07-11 08:35:53 PM PT</t>
         </is>
       </c>
       <c r="C9" t="n">
@@ -1623,7 +1623,7 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>2026-07-11 08:33:52 PM PT</t>
+          <t>2026-07-11 08:35:52 PM PT</t>
         </is>
       </c>
       <c r="C10" t="n">
@@ -1737,7 +1737,7 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>2026-07-11 08:33:54 PM PT</t>
+          <t>2026-07-11 08:35:54 PM PT</t>
         </is>
       </c>
       <c r="C11" t="n">
@@ -1750,7 +1750,7 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Bottom 8 | 0 out</t>
+          <t>Bottom 8 | 1 out</t>
         </is>
       </c>
       <c r="F11" t="n">
@@ -1762,10 +1762,10 @@
         </is>
       </c>
       <c r="H11" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I11" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="J11" t="n">
         <v>0</v>
@@ -1860,7 +1860,7 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>2026-07-11 08:33:53 PM PT</t>
+          <t>2026-07-11 08:35:53 PM PT</t>
         </is>
       </c>
       <c r="C12" t="n">
@@ -1974,7 +1974,7 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>2026-07-11 08:33:53 PM PT</t>
+          <t>2026-07-11 08:35:53 PM PT</t>
         </is>
       </c>
       <c r="C13" t="n">
@@ -2088,7 +2088,7 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>2026-07-11 08:33:54 PM PT</t>
+          <t>2026-07-11 08:35:54 PM PT</t>
         </is>
       </c>
       <c r="C14" t="n">
@@ -2101,7 +2101,7 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Bottom 8 | 0 out</t>
+          <t>Bottom 8 | 1 out</t>
         </is>
       </c>
       <c r="F14" t="n">
@@ -2113,10 +2113,10 @@
         </is>
       </c>
       <c r="H14" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I14" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="J14" t="n">
         <v>0</v>
@@ -2211,7 +2211,7 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>2026-07-11 08:33:53 PM PT</t>
+          <t>2026-07-11 08:35:53 PM PT</t>
         </is>
       </c>
       <c r="C15" t="n">
@@ -2325,7 +2325,7 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>2026-07-11 08:33:53 PM PT</t>
+          <t>2026-07-11 08:35:53 PM PT</t>
         </is>
       </c>
       <c r="C16" t="n">
@@ -2439,7 +2439,7 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>2026-07-11 08:33:53 PM PT</t>
+          <t>2026-07-11 08:35:53 PM PT</t>
         </is>
       </c>
       <c r="C17" t="n">
@@ -2553,7 +2553,7 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>2026-07-11 08:33:54 PM PT</t>
+          <t>2026-07-11 08:35:54 PM PT</t>
         </is>
       </c>
       <c r="C18" t="n">
@@ -2566,7 +2566,7 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Bottom 8 | 0 out</t>
+          <t>Bottom 8 | 1 out</t>
         </is>
       </c>
       <c r="F18" t="n">
@@ -2578,10 +2578,10 @@
         </is>
       </c>
       <c r="H18" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I18" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="J18" t="n">
         <v>0</v>
@@ -2676,7 +2676,7 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>2026-07-11 08:33:53 PM PT</t>
+          <t>2026-07-11 08:35:53 PM PT</t>
         </is>
       </c>
       <c r="C19" t="n">
@@ -2790,7 +2790,7 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>2026-07-11 08:33:53 PM PT</t>
+          <t>2026-07-11 08:35:54 PM PT</t>
         </is>
       </c>
       <c r="C20" t="n">
@@ -2904,7 +2904,7 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>2026-07-11 08:33:53 PM PT</t>
+          <t>2026-07-11 08:35:53 PM PT</t>
         </is>
       </c>
       <c r="C21" t="n">
@@ -3018,7 +3018,7 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>2026-07-11 08:33:53 PM PT</t>
+          <t>2026-07-11 08:35:53 PM PT</t>
         </is>
       </c>
       <c r="C22" t="n">
@@ -3132,7 +3132,7 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>2026-07-11 08:33:54 PM PT</t>
+          <t>2026-07-11 08:35:54 PM PT</t>
         </is>
       </c>
       <c r="C23" t="n">
@@ -3145,7 +3145,7 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Top 8 | 1 out</t>
+          <t>Top 8 | 2 out</t>
         </is>
       </c>
       <c r="F23" t="n">
@@ -3157,13 +3157,13 @@
         </is>
       </c>
       <c r="H23" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I23" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="J23" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K23" t="inlineStr">
         <is>
@@ -3255,7 +3255,7 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>2026-07-11 08:33:53 PM PT</t>
+          <t>2026-07-11 08:35:53 PM PT</t>
         </is>
       </c>
       <c r="C24" t="n">
@@ -3369,7 +3369,7 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>2026-07-11 08:33:53 PM PT</t>
+          <t>2026-07-11 08:35:53 PM PT</t>
         </is>
       </c>
       <c r="C25" t="n">
@@ -3483,7 +3483,7 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>2026-07-11 08:33:53 PM PT</t>
+          <t>2026-07-11 08:35:54 PM PT</t>
         </is>
       </c>
       <c r="C26" t="n">
@@ -3597,7 +3597,7 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>2026-07-11 08:33:52 PM PT</t>
+          <t>2026-07-11 08:35:52 PM PT</t>
         </is>
       </c>
       <c r="C27" t="n">
@@ -3711,7 +3711,7 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>2026-07-11 08:33:53 PM PT</t>
+          <t>2026-07-11 08:35:53 PM PT</t>
         </is>
       </c>
       <c r="C28" t="n">
@@ -3825,7 +3825,7 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>2026-07-11 08:33:53 PM PT</t>
+          <t>2026-07-11 08:35:53 PM PT</t>
         </is>
       </c>
       <c r="C29" t="n">
@@ -3939,7 +3939,7 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>2026-07-11 08:33:53 PM PT</t>
+          <t>2026-07-11 08:35:54 PM PT</t>
         </is>
       </c>
       <c r="C30" t="n">
@@ -4053,7 +4053,7 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>2026-07-11 08:33:53 PM PT</t>
+          <t>2026-07-11 08:35:54 PM PT</t>
         </is>
       </c>
       <c r="C31" t="n">
@@ -4167,7 +4167,7 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>2026-07-11 08:33:53 PM PT</t>
+          <t>2026-07-11 08:35:53 PM PT</t>
         </is>
       </c>
       <c r="C32" t="n">
@@ -4281,7 +4281,7 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>2026-07-11 08:33:53 PM PT</t>
+          <t>2026-07-11 08:35:53 PM PT</t>
         </is>
       </c>
       <c r="C33" t="n">
@@ -4395,7 +4395,7 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>2026-07-11 08:33:53 PM PT</t>
+          <t>2026-07-11 08:35:53 PM PT</t>
         </is>
       </c>
       <c r="C34" t="n">
@@ -4509,7 +4509,7 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>2026-07-11 08:33:52 PM PT</t>
+          <t>2026-07-11 08:35:52 PM PT</t>
         </is>
       </c>
       <c r="C35" t="n">
@@ -4623,7 +4623,7 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>2026-07-11 08:33:52 PM PT</t>
+          <t>2026-07-11 08:35:52 PM PT</t>
         </is>
       </c>
       <c r="C36" t="n">
@@ -4737,7 +4737,7 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>2026-07-11 08:33:54 PM PT</t>
+          <t>2026-07-11 08:35:54 PM PT</t>
         </is>
       </c>
       <c r="C37" t="n">
@@ -4750,7 +4750,7 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Bottom 8 | 0 out</t>
+          <t>Bottom 8 | 1 out</t>
         </is>
       </c>
       <c r="F37" t="n">
@@ -4762,10 +4762,10 @@
         </is>
       </c>
       <c r="H37" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I37" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="J37" t="n">
         <v>0</v>
@@ -4860,7 +4860,7 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>2026-07-11 08:33:53 PM PT</t>
+          <t>2026-07-11 08:35:53 PM PT</t>
         </is>
       </c>
       <c r="C38" t="n">
@@ -4974,7 +4974,7 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>2026-07-11 08:33:52 PM PT</t>
+          <t>2026-07-11 08:35:52 PM PT</t>
         </is>
       </c>
       <c r="C39" t="n">
@@ -5088,7 +5088,7 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>2026-07-11 08:33:53 PM PT</t>
+          <t>2026-07-11 08:35:53 PM PT</t>
         </is>
       </c>
       <c r="C40" t="n">
@@ -5202,7 +5202,7 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>2026-07-11 08:33:52 PM PT</t>
+          <t>2026-07-11 08:35:52 PM PT</t>
         </is>
       </c>
       <c r="C41" t="n">
@@ -5316,7 +5316,7 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>2026-07-11 08:33:54 PM PT</t>
+          <t>2026-07-11 08:35:54 PM PT</t>
         </is>
       </c>
       <c r="C42" t="n">
@@ -5329,7 +5329,7 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>Top 8 | 1 out</t>
+          <t>Top 8 | 2 out</t>
         </is>
       </c>
       <c r="F42" t="n">
@@ -5341,13 +5341,13 @@
         </is>
       </c>
       <c r="H42" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I42" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="J42" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K42" t="inlineStr">
         <is>
@@ -5439,7 +5439,7 @@
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>2026-07-11 08:33:54 PM PT</t>
+          <t>2026-07-11 08:35:54 PM PT</t>
         </is>
       </c>
       <c r="C43" t="n">
@@ -5553,7 +5553,7 @@
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>2026-07-11 08:33:53 PM PT</t>
+          <t>2026-07-11 08:35:53 PM PT</t>
         </is>
       </c>
       <c r="C44" t="n">
@@ -5667,7 +5667,7 @@
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>2026-07-11 08:33:53 PM PT</t>
+          <t>2026-07-11 08:35:53 PM PT</t>
         </is>
       </c>
       <c r="C45" t="n">
@@ -5781,7 +5781,7 @@
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>2026-07-11 08:33:53 PM PT</t>
+          <t>2026-07-11 08:35:54 PM PT</t>
         </is>
       </c>
       <c r="C46" t="n">
@@ -5895,7 +5895,7 @@
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>2026-07-11 08:33:53 PM PT</t>
+          <t>2026-07-11 08:35:53 PM PT</t>
         </is>
       </c>
       <c r="C47" t="n">
@@ -6009,7 +6009,7 @@
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>2026-07-11 08:33:53 PM PT</t>
+          <t>2026-07-11 08:35:53 PM PT</t>
         </is>
       </c>
       <c r="C48" t="n">
@@ -6123,7 +6123,7 @@
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>2026-07-11 08:33:53 PM PT</t>
+          <t>2026-07-11 08:35:53 PM PT</t>
         </is>
       </c>
       <c r="C49" t="n">
@@ -6237,7 +6237,7 @@
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>2026-07-11 08:33:53 PM PT</t>
+          <t>2026-07-11 08:35:53 PM PT</t>
         </is>
       </c>
       <c r="C50" t="n">
@@ -6351,7 +6351,7 @@
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>2026-07-11 08:33:52 PM PT</t>
+          <t>2026-07-11 08:35:52 PM PT</t>
         </is>
       </c>
       <c r="C51" t="n">
@@ -6465,7 +6465,7 @@
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>2026-07-11 08:33:54 PM PT</t>
+          <t>2026-07-11 08:35:54 PM PT</t>
         </is>
       </c>
       <c r="C52" t="n">
@@ -6478,7 +6478,7 @@
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>Bottom 8 | 0 out</t>
+          <t>Bottom 8 | 1 out</t>
         </is>
       </c>
       <c r="F52" t="n">
@@ -6490,10 +6490,10 @@
         </is>
       </c>
       <c r="H52" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I52" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="J52" t="n">
         <v>0</v>
@@ -6588,7 +6588,7 @@
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>2026-07-11 08:33:54 PM PT</t>
+          <t>2026-07-11 08:35:54 PM PT</t>
         </is>
       </c>
       <c r="C53" t="n">
@@ -6601,7 +6601,7 @@
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>Top 8 | 1 out</t>
+          <t>Top 8 | 2 out</t>
         </is>
       </c>
       <c r="F53" t="n">
@@ -6613,13 +6613,13 @@
         </is>
       </c>
       <c r="H53" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I53" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="J53" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K53" t="inlineStr">
         <is>
@@ -6711,7 +6711,7 @@
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>2026-07-11 08:33:53 PM PT</t>
+          <t>2026-07-11 08:35:54 PM PT</t>
         </is>
       </c>
       <c r="C54" t="n">
@@ -6825,7 +6825,7 @@
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>2026-07-11 08:33:53 PM PT</t>
+          <t>2026-07-11 08:35:54 PM PT</t>
         </is>
       </c>
       <c r="C55" t="n">
@@ -6939,7 +6939,7 @@
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>2026-07-11 08:33:53 PM PT</t>
+          <t>2026-07-11 08:35:53 PM PT</t>
         </is>
       </c>
       <c r="C56" t="n">
@@ -7053,7 +7053,7 @@
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>2026-07-11 08:33:52 PM PT</t>
+          <t>2026-07-11 08:35:52 PM PT</t>
         </is>
       </c>
       <c r="C57" t="n">
@@ -7167,7 +7167,7 @@
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>2026-07-11 08:33:52 PM PT</t>
+          <t>2026-07-11 08:35:52 PM PT</t>
         </is>
       </c>
       <c r="C58" t="n">
@@ -7281,7 +7281,7 @@
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>2026-07-11 08:33:52 PM PT</t>
+          <t>2026-07-11 08:35:52 PM PT</t>
         </is>
       </c>
       <c r="C59" t="n">
@@ -7395,7 +7395,7 @@
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>2026-07-11 08:33:53 PM PT</t>
+          <t>2026-07-11 08:35:53 PM PT</t>
         </is>
       </c>
       <c r="C60" t="n">
@@ -7509,7 +7509,7 @@
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>2026-07-11 08:33:53 PM PT</t>
+          <t>2026-07-11 08:35:53 PM PT</t>
         </is>
       </c>
       <c r="C61" t="n">
@@ -7623,7 +7623,7 @@
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>2026-07-11 08:33:52 PM PT</t>
+          <t>2026-07-11 08:35:52 PM PT</t>
         </is>
       </c>
       <c r="C62" t="n">
@@ -7737,7 +7737,7 @@
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>2026-07-11 08:33:52 PM PT</t>
+          <t>2026-07-11 08:35:52 PM PT</t>
         </is>
       </c>
       <c r="C63" t="n">
@@ -7851,7 +7851,7 @@
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>2026-07-11 08:33:52 PM PT</t>
+          <t>2026-07-11 08:35:52 PM PT</t>
         </is>
       </c>
       <c r="C64" t="n">
@@ -7965,7 +7965,7 @@
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>2026-07-11 08:33:54 PM PT</t>
+          <t>2026-07-11 08:35:54 PM PT</t>
         </is>
       </c>
       <c r="C65" t="n">
@@ -7978,7 +7978,7 @@
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>Bottom 8 | 0 out</t>
+          <t>Bottom 8 | 1 out</t>
         </is>
       </c>
       <c r="F65" t="n">
@@ -7990,10 +7990,10 @@
         </is>
       </c>
       <c r="H65" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I65" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="J65" t="n">
         <v>0</v>
@@ -8088,7 +8088,7 @@
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>2026-07-11 08:33:54 PM PT</t>
+          <t>2026-07-11 08:35:54 PM PT</t>
         </is>
       </c>
       <c r="C66" t="n">
@@ -8101,7 +8101,7 @@
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>Top 8 | 1 out</t>
+          <t>Top 8 | 2 out</t>
         </is>
       </c>
       <c r="F66" t="n">
@@ -8113,13 +8113,13 @@
         </is>
       </c>
       <c r="H66" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I66" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="J66" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K66" t="inlineStr">
         <is>
@@ -8211,7 +8211,7 @@
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>2026-07-11 08:33:53 PM PT</t>
+          <t>2026-07-11 08:35:53 PM PT</t>
         </is>
       </c>
       <c r="C67" t="n">
@@ -8325,7 +8325,7 @@
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>2026-07-11 08:33:53 PM PT</t>
+          <t>2026-07-11 08:35:53 PM PT</t>
         </is>
       </c>
       <c r="C68" t="n">
@@ -8439,7 +8439,7 @@
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>2026-07-11 08:33:53 PM PT</t>
+          <t>2026-07-11 08:35:53 PM PT</t>
         </is>
       </c>
       <c r="C69" t="n">
@@ -8553,7 +8553,7 @@
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>2026-07-11 08:33:53 PM PT</t>
+          <t>2026-07-11 08:35:53 PM PT</t>
         </is>
       </c>
       <c r="C70" t="n">
@@ -8667,7 +8667,7 @@
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>2026-07-11 08:33:52 PM PT</t>
+          <t>2026-07-11 08:35:52 PM PT</t>
         </is>
       </c>
       <c r="C71" t="n">
@@ -8781,7 +8781,7 @@
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>2026-07-11 08:33:54 PM PT</t>
+          <t>2026-07-11 08:35:54 PM PT</t>
         </is>
       </c>
       <c r="C72" t="n">
@@ -8794,7 +8794,7 @@
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>Top 8 | 1 out</t>
+          <t>Top 8 | 2 out</t>
         </is>
       </c>
       <c r="F72" t="n">
@@ -8806,13 +8806,13 @@
         </is>
       </c>
       <c r="H72" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I72" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="J72" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K72" t="inlineStr">
         <is>
@@ -8904,7 +8904,7 @@
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>2026-07-11 08:33:52 PM PT</t>
+          <t>2026-07-11 08:35:52 PM PT</t>
         </is>
       </c>
       <c r="C73" t="n">
@@ -9018,7 +9018,7 @@
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>2026-07-11 08:33:53 PM PT</t>
+          <t>2026-07-11 08:35:53 PM PT</t>
         </is>
       </c>
       <c r="C74" t="n">
@@ -9132,7 +9132,7 @@
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>2026-07-11 08:33:52 PM PT</t>
+          <t>2026-07-11 08:35:52 PM PT</t>
         </is>
       </c>
       <c r="C75" t="n">
@@ -9246,7 +9246,7 @@
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>2026-07-11 08:33:54 PM PT</t>
+          <t>2026-07-11 08:35:54 PM PT</t>
         </is>
       </c>
       <c r="C76" t="n">
@@ -9259,7 +9259,7 @@
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>Bottom 8 | 0 out</t>
+          <t>Bottom 8 | 1 out</t>
         </is>
       </c>
       <c r="F76" t="n">
@@ -9271,10 +9271,10 @@
         </is>
       </c>
       <c r="H76" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I76" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="J76" t="n">
         <v>0</v>
@@ -9369,7 +9369,7 @@
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>2026-07-11 08:33:53 PM PT</t>
+          <t>2026-07-11 08:35:54 PM PT</t>
         </is>
       </c>
       <c r="C77" t="n">
@@ -9483,7 +9483,7 @@
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>2026-07-11 08:33:53 PM PT</t>
+          <t>2026-07-11 08:35:54 PM PT</t>
         </is>
       </c>
       <c r="C78" t="n">
@@ -9597,7 +9597,7 @@
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>2026-07-11 08:33:53 PM PT</t>
+          <t>2026-07-11 08:35:53 PM PT</t>
         </is>
       </c>
       <c r="C79" t="n">
@@ -9711,7 +9711,7 @@
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>2026-07-11 08:33:52 PM PT</t>
+          <t>2026-07-11 08:35:52 PM PT</t>
         </is>
       </c>
       <c r="C80" t="n">
@@ -9825,7 +9825,7 @@
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>2026-07-11 08:33:52 PM PT</t>
+          <t>2026-07-11 08:35:52 PM PT</t>
         </is>
       </c>
       <c r="C81" t="n">
@@ -9939,7 +9939,7 @@
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>2026-07-11 08:33:52 PM PT</t>
+          <t>2026-07-11 08:35:52 PM PT</t>
         </is>
       </c>
       <c r="C82" t="n">
@@ -10053,7 +10053,7 @@
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>2026-07-11 08:33:52 PM PT</t>
+          <t>2026-07-11 08:35:52 PM PT</t>
         </is>
       </c>
       <c r="C83" t="n">
@@ -10167,7 +10167,7 @@
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>2026-07-11 08:33:52 PM PT</t>
+          <t>2026-07-11 08:35:52 PM PT</t>
         </is>
       </c>
       <c r="C84" t="n">
@@ -10281,7 +10281,7 @@
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>2026-07-11 08:33:52 PM PT</t>
+          <t>2026-07-11 08:35:52 PM PT</t>
         </is>
       </c>
       <c r="C85" t="n">
@@ -10395,7 +10395,7 @@
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>2026-07-11 08:33:53 PM PT</t>
+          <t>2026-07-11 08:35:53 PM PT</t>
         </is>
       </c>
       <c r="C86" t="n">
@@ -10509,7 +10509,7 @@
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>2026-07-11 08:33:53 PM PT</t>
+          <t>2026-07-11 08:35:53 PM PT</t>
         </is>
       </c>
       <c r="C87" t="n">
@@ -10623,7 +10623,7 @@
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>2026-07-11 08:33:53 PM PT</t>
+          <t>2026-07-11 08:35:53 PM PT</t>
         </is>
       </c>
       <c r="C88" t="n">
@@ -10737,7 +10737,7 @@
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>2026-07-11 08:33:53 PM PT</t>
+          <t>2026-07-11 08:35:53 PM PT</t>
         </is>
       </c>
       <c r="C89" t="n">
@@ -10851,7 +10851,7 @@
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>2026-07-11 08:33:54 PM PT</t>
+          <t>2026-07-11 08:35:54 PM PT</t>
         </is>
       </c>
       <c r="C90" t="n">
@@ -10864,7 +10864,7 @@
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>Bottom 8 | 0 out</t>
+          <t>Bottom 8 | 1 out</t>
         </is>
       </c>
       <c r="F90" t="n">
@@ -10876,10 +10876,10 @@
         </is>
       </c>
       <c r="H90" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I90" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="J90" t="n">
         <v>0</v>
@@ -10974,7 +10974,7 @@
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>2026-07-11 08:33:53 PM PT</t>
+          <t>2026-07-11 08:35:53 PM PT</t>
         </is>
       </c>
       <c r="C91" t="n">
@@ -11088,7 +11088,7 @@
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>2026-07-11 08:33:54 PM PT</t>
+          <t>2026-07-11 08:35:54 PM PT</t>
         </is>
       </c>
       <c r="C92" t="n">
@@ -11202,7 +11202,7 @@
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>2026-07-11 08:33:54 PM PT</t>
+          <t>2026-07-11 08:35:54 PM PT</t>
         </is>
       </c>
       <c r="C93" t="n">
@@ -11215,7 +11215,7 @@
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>Top 8 | 1 out</t>
+          <t>Top 8 | 2 out</t>
         </is>
       </c>
       <c r="F93" t="n">
@@ -11227,13 +11227,13 @@
         </is>
       </c>
       <c r="H93" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I93" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="J93" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K93" t="inlineStr">
         <is>
@@ -11325,7 +11325,7 @@
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>2026-07-11 08:33:53 PM PT</t>
+          <t>2026-07-11 08:35:53 PM PT</t>
         </is>
       </c>
       <c r="C94" t="n">
@@ -11439,7 +11439,7 @@
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>2026-07-11 08:33:53 PM PT</t>
+          <t>2026-07-11 08:35:53 PM PT</t>
         </is>
       </c>
       <c r="C95" t="n">
@@ -11553,7 +11553,7 @@
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>2026-07-11 08:33:53 PM PT</t>
+          <t>2026-07-11 08:35:53 PM PT</t>
         </is>
       </c>
       <c r="C96" t="n">
@@ -11667,7 +11667,7 @@
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>2026-07-11 08:33:53 PM PT</t>
+          <t>2026-07-11 08:35:53 PM PT</t>
         </is>
       </c>
       <c r="C97" t="n">
@@ -11781,7 +11781,7 @@
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>2026-07-11 08:33:53 PM PT</t>
+          <t>2026-07-11 08:35:53 PM PT</t>
         </is>
       </c>
       <c r="C98" t="n">
@@ -11895,7 +11895,7 @@
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>2026-07-11 08:33:54 PM PT</t>
+          <t>2026-07-11 08:35:54 PM PT</t>
         </is>
       </c>
       <c r="C99" t="n">
@@ -11908,7 +11908,7 @@
       </c>
       <c r="E99" t="inlineStr">
         <is>
-          <t>Top 8 | 1 out</t>
+          <t>Top 8 | 2 out</t>
         </is>
       </c>
       <c r="F99" t="n">
@@ -11920,13 +11920,13 @@
         </is>
       </c>
       <c r="H99" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I99" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="J99" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K99" t="inlineStr">
         <is>
@@ -12018,7 +12018,7 @@
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>2026-07-11 08:33:53 PM PT</t>
+          <t>2026-07-11 08:35:53 PM PT</t>
         </is>
       </c>
       <c r="C100" t="n">
@@ -12132,7 +12132,7 @@
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>2026-07-11 08:33:52 PM PT</t>
+          <t>2026-07-11 08:35:52 PM PT</t>
         </is>
       </c>
       <c r="C101" t="n">
@@ -12246,7 +12246,7 @@
       </c>
       <c r="B102" t="inlineStr">
         <is>
-          <t>2026-07-11 08:33:52 PM PT</t>
+          <t>2026-07-11 08:35:52 PM PT</t>
         </is>
       </c>
       <c r="C102" t="n">
@@ -12360,7 +12360,7 @@
       </c>
       <c r="B103" t="inlineStr">
         <is>
-          <t>2026-07-11 08:33:53 PM PT</t>
+          <t>2026-07-11 08:35:53 PM PT</t>
         </is>
       </c>
       <c r="C103" t="n">
@@ -12474,7 +12474,7 @@
       </c>
       <c r="B104" t="inlineStr">
         <is>
-          <t>2026-07-11 08:33:54 PM PT</t>
+          <t>2026-07-11 08:35:54 PM PT</t>
         </is>
       </c>
       <c r="C104" t="n">
@@ -12487,7 +12487,7 @@
       </c>
       <c r="E104" t="inlineStr">
         <is>
-          <t>Bottom 8 | 0 out</t>
+          <t>Bottom 8 | 1 out</t>
         </is>
       </c>
       <c r="F104" t="n">
@@ -12499,10 +12499,10 @@
         </is>
       </c>
       <c r="H104" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I104" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="J104" t="n">
         <v>0</v>
@@ -12597,7 +12597,7 @@
       </c>
       <c r="B105" t="inlineStr">
         <is>
-          <t>2026-07-11 08:33:53 PM PT</t>
+          <t>2026-07-11 08:35:53 PM PT</t>
         </is>
       </c>
       <c r="C105" t="n">
@@ -12711,7 +12711,7 @@
       </c>
       <c r="B106" t="inlineStr">
         <is>
-          <t>2026-07-11 08:33:53 PM PT</t>
+          <t>2026-07-11 08:35:53 PM PT</t>
         </is>
       </c>
       <c r="C106" t="n">
@@ -12825,7 +12825,7 @@
       </c>
       <c r="B107" t="inlineStr">
         <is>
-          <t>2026-07-11 08:33:53 PM PT</t>
+          <t>2026-07-11 08:35:53 PM PT</t>
         </is>
       </c>
       <c r="C107" t="n">
@@ -12939,7 +12939,7 @@
       </c>
       <c r="B108" t="inlineStr">
         <is>
-          <t>2026-07-11 08:33:53 PM PT</t>
+          <t>2026-07-11 08:35:53 PM PT</t>
         </is>
       </c>
       <c r="C108" t="n">
@@ -13053,7 +13053,7 @@
       </c>
       <c r="B109" t="inlineStr">
         <is>
-          <t>2026-07-11 08:33:53 PM PT</t>
+          <t>2026-07-11 08:35:53 PM PT</t>
         </is>
       </c>
       <c r="C109" t="n">
@@ -13167,7 +13167,7 @@
       </c>
       <c r="B110" t="inlineStr">
         <is>
-          <t>2026-07-11 08:33:53 PM PT</t>
+          <t>2026-07-11 08:35:53 PM PT</t>
         </is>
       </c>
       <c r="C110" t="n">
@@ -13281,7 +13281,7 @@
       </c>
       <c r="B111" t="inlineStr">
         <is>
-          <t>2026-07-11 08:33:53 PM PT</t>
+          <t>2026-07-11 08:35:53 PM PT</t>
         </is>
       </c>
       <c r="C111" t="n">
@@ -13395,7 +13395,7 @@
       </c>
       <c r="B112" t="inlineStr">
         <is>
-          <t>2026-07-11 08:33:53 PM PT</t>
+          <t>2026-07-11 08:35:54 PM PT</t>
         </is>
       </c>
       <c r="C112" t="n">
@@ -13509,7 +13509,7 @@
       </c>
       <c r="B113" t="inlineStr">
         <is>
-          <t>2026-07-11 08:33:53 PM PT</t>
+          <t>2026-07-11 08:35:53 PM PT</t>
         </is>
       </c>
       <c r="C113" t="n">
@@ -13623,7 +13623,7 @@
       </c>
       <c r="B114" t="inlineStr">
         <is>
-          <t>2026-07-11 08:33:53 PM PT</t>
+          <t>2026-07-11 08:35:53 PM PT</t>
         </is>
       </c>
       <c r="C114" t="n">
@@ -13737,7 +13737,7 @@
       </c>
       <c r="B115" t="inlineStr">
         <is>
-          <t>2026-07-11 08:33:53 PM PT</t>
+          <t>2026-07-11 08:35:53 PM PT</t>
         </is>
       </c>
       <c r="C115" t="n">
@@ -13851,7 +13851,7 @@
       </c>
       <c r="B116" t="inlineStr">
         <is>
-          <t>2026-07-11 08:33:54 PM PT</t>
+          <t>2026-07-11 08:35:54 PM PT</t>
         </is>
       </c>
       <c r="C116" t="n">
@@ -13864,7 +13864,7 @@
       </c>
       <c r="E116" t="inlineStr">
         <is>
-          <t>Bottom 8 | 0 out</t>
+          <t>Bottom 8 | 1 out</t>
         </is>
       </c>
       <c r="F116" t="n">
@@ -13876,10 +13876,10 @@
         </is>
       </c>
       <c r="H116" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I116" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="J116" t="n">
         <v>0</v>
@@ -13974,7 +13974,7 @@
       </c>
       <c r="B117" t="inlineStr">
         <is>
-          <t>2026-07-11 08:33:53 PM PT</t>
+          <t>2026-07-11 08:35:53 PM PT</t>
         </is>
       </c>
       <c r="C117" t="n">
@@ -14088,7 +14088,7 @@
       </c>
       <c r="B118" t="inlineStr">
         <is>
-          <t>2026-07-11 08:33:54 PM PT</t>
+          <t>2026-07-11 08:35:54 PM PT</t>
         </is>
       </c>
       <c r="C118" t="n">
@@ -14202,7 +14202,7 @@
       </c>
       <c r="B119" t="inlineStr">
         <is>
-          <t>2026-07-11 08:33:54 PM PT</t>
+          <t>2026-07-11 08:35:54 PM PT</t>
         </is>
       </c>
       <c r="C119" t="n">
@@ -14316,7 +14316,7 @@
       </c>
       <c r="B120" t="inlineStr">
         <is>
-          <t>2026-07-11 08:33:53 PM PT</t>
+          <t>2026-07-11 08:35:53 PM PT</t>
         </is>
       </c>
       <c r="C120" t="n">
@@ -14430,7 +14430,7 @@
       </c>
       <c r="B121" t="inlineStr">
         <is>
-          <t>2026-07-11 08:33:53 PM PT</t>
+          <t>2026-07-11 08:35:53 PM PT</t>
         </is>
       </c>
       <c r="C121" t="n">
@@ -14544,7 +14544,7 @@
       </c>
       <c r="B122" t="inlineStr">
         <is>
-          <t>2026-07-11 08:33:53 PM PT</t>
+          <t>2026-07-11 08:35:54 PM PT</t>
         </is>
       </c>
       <c r="C122" t="n">
@@ -14658,7 +14658,7 @@
       </c>
       <c r="B123" t="inlineStr">
         <is>
-          <t>2026-07-11 08:33:53 PM PT</t>
+          <t>2026-07-11 08:35:53 PM PT</t>
         </is>
       </c>
       <c r="C123" t="n">
@@ -14772,7 +14772,7 @@
       </c>
       <c r="B124" t="inlineStr">
         <is>
-          <t>2026-07-11 08:33:53 PM PT</t>
+          <t>2026-07-11 08:35:53 PM PT</t>
         </is>
       </c>
       <c r="C124" t="n">
@@ -14886,7 +14886,7 @@
       </c>
       <c r="B125" t="inlineStr">
         <is>
-          <t>2026-07-11 08:33:53 PM PT</t>
+          <t>2026-07-11 08:35:53 PM PT</t>
         </is>
       </c>
       <c r="C125" t="n">
@@ -15000,7 +15000,7 @@
       </c>
       <c r="B126" t="inlineStr">
         <is>
-          <t>2026-07-11 08:33:53 PM PT</t>
+          <t>2026-07-11 08:35:53 PM PT</t>
         </is>
       </c>
       <c r="C126" t="n">
@@ -15114,7 +15114,7 @@
       </c>
       <c r="B127" t="inlineStr">
         <is>
-          <t>2026-07-11 08:33:53 PM PT</t>
+          <t>2026-07-11 08:35:53 PM PT</t>
         </is>
       </c>
       <c r="C127" t="n">
@@ -15228,7 +15228,7 @@
       </c>
       <c r="B128" t="inlineStr">
         <is>
-          <t>2026-07-11 08:33:53 PM PT</t>
+          <t>2026-07-11 08:35:53 PM PT</t>
         </is>
       </c>
       <c r="C128" t="n">
@@ -15342,7 +15342,7 @@
       </c>
       <c r="B129" t="inlineStr">
         <is>
-          <t>2026-07-11 08:33:54 PM PT</t>
+          <t>2026-07-11 08:35:54 PM PT</t>
         </is>
       </c>
       <c r="C129" t="n">
@@ -15355,7 +15355,7 @@
       </c>
       <c r="E129" t="inlineStr">
         <is>
-          <t>Top 8 | 1 out</t>
+          <t>Top 8 | 2 out</t>
         </is>
       </c>
       <c r="F129" t="n">
@@ -15367,13 +15367,13 @@
         </is>
       </c>
       <c r="H129" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I129" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="J129" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K129" t="inlineStr">
         <is>
@@ -15465,7 +15465,7 @@
       </c>
       <c r="B130" t="inlineStr">
         <is>
-          <t>2026-07-11 08:33:53 PM PT</t>
+          <t>2026-07-11 08:35:53 PM PT</t>
         </is>
       </c>
       <c r="C130" t="n">
@@ -15579,7 +15579,7 @@
       </c>
       <c r="B131" t="inlineStr">
         <is>
-          <t>2026-07-11 08:33:53 PM PT</t>
+          <t>2026-07-11 08:35:53 PM PT</t>
         </is>
       </c>
       <c r="C131" t="n">
@@ -15693,7 +15693,7 @@
       </c>
       <c r="B132" t="inlineStr">
         <is>
-          <t>2026-07-11 08:33:52 PM PT</t>
+          <t>2026-07-11 08:35:52 PM PT</t>
         </is>
       </c>
       <c r="C132" t="n">
@@ -15807,7 +15807,7 @@
       </c>
       <c r="B133" t="inlineStr">
         <is>
-          <t>2026-07-11 08:33:52 PM PT</t>
+          <t>2026-07-11 08:35:52 PM PT</t>
         </is>
       </c>
       <c r="C133" t="n">
@@ -15921,7 +15921,7 @@
       </c>
       <c r="B134" t="inlineStr">
         <is>
-          <t>2026-07-11 08:33:52 PM PT</t>
+          <t>2026-07-11 08:35:52 PM PT</t>
         </is>
       </c>
       <c r="C134" t="n">
@@ -16035,7 +16035,7 @@
       </c>
       <c r="B135" t="inlineStr">
         <is>
-          <t>2026-07-11 08:33:53 PM PT</t>
+          <t>2026-07-11 08:35:53 PM PT</t>
         </is>
       </c>
       <c r="C135" t="n">
@@ -16149,7 +16149,7 @@
       </c>
       <c r="B136" t="inlineStr">
         <is>
-          <t>2026-07-11 08:33:52 PM PT</t>
+          <t>2026-07-11 08:35:52 PM PT</t>
         </is>
       </c>
       <c r="C136" t="n">
@@ -16263,7 +16263,7 @@
       </c>
       <c r="B137" t="inlineStr">
         <is>
-          <t>2026-07-11 08:33:52 PM PT</t>
+          <t>2026-07-11 08:35:52 PM PT</t>
         </is>
       </c>
       <c r="C137" t="n">
@@ -16377,7 +16377,7 @@
       </c>
       <c r="B138" t="inlineStr">
         <is>
-          <t>2026-07-11 08:33:53 PM PT</t>
+          <t>2026-07-11 08:35:53 PM PT</t>
         </is>
       </c>
       <c r="C138" t="n">
@@ -16491,7 +16491,7 @@
       </c>
       <c r="B139" t="inlineStr">
         <is>
-          <t>2026-07-11 08:33:53 PM PT</t>
+          <t>2026-07-11 08:35:53 PM PT</t>
         </is>
       </c>
       <c r="C139" t="n">
@@ -16605,7 +16605,7 @@
       </c>
       <c r="B140" t="inlineStr">
         <is>
-          <t>2026-07-11 08:33:53 PM PT</t>
+          <t>2026-07-11 08:35:53 PM PT</t>
         </is>
       </c>
       <c r="C140" t="n">
@@ -16719,7 +16719,7 @@
       </c>
       <c r="B141" t="inlineStr">
         <is>
-          <t>2026-07-11 08:33:54 PM PT</t>
+          <t>2026-07-11 08:35:54 PM PT</t>
         </is>
       </c>
       <c r="C141" t="n">
@@ -16833,7 +16833,7 @@
       </c>
       <c r="B142" t="inlineStr">
         <is>
-          <t>2026-07-11 08:33:54 PM PT</t>
+          <t>2026-07-11 08:35:54 PM PT</t>
         </is>
       </c>
       <c r="C142" t="n">
@@ -16947,7 +16947,7 @@
       </c>
       <c r="B143" t="inlineStr">
         <is>
-          <t>2026-07-11 08:33:54 PM PT</t>
+          <t>2026-07-11 08:35:54 PM PT</t>
         </is>
       </c>
       <c r="C143" t="n">
@@ -17061,7 +17061,7 @@
       </c>
       <c r="B144" t="inlineStr">
         <is>
-          <t>2026-07-11 08:33:53 PM PT</t>
+          <t>2026-07-11 08:35:53 PM PT</t>
         </is>
       </c>
       <c r="C144" t="n">
@@ -17175,7 +17175,7 @@
       </c>
       <c r="B145" t="inlineStr">
         <is>
-          <t>2026-07-11 08:33:53 PM PT</t>
+          <t>2026-07-11 08:35:53 PM PT</t>
         </is>
       </c>
       <c r="C145" t="n">
@@ -17289,7 +17289,7 @@
       </c>
       <c r="B146" t="inlineStr">
         <is>
-          <t>2026-07-11 08:33:53 PM PT</t>
+          <t>2026-07-11 08:35:53 PM PT</t>
         </is>
       </c>
       <c r="C146" t="n">
@@ -17403,7 +17403,7 @@
       </c>
       <c r="B147" t="inlineStr">
         <is>
-          <t>2026-07-11 08:33:53 PM PT</t>
+          <t>2026-07-11 08:35:54 PM PT</t>
         </is>
       </c>
       <c r="C147" t="n">
@@ -17517,7 +17517,7 @@
       </c>
       <c r="B148" t="inlineStr">
         <is>
-          <t>2026-07-11 08:33:53 PM PT</t>
+          <t>2026-07-11 08:35:53 PM PT</t>
         </is>
       </c>
       <c r="C148" t="n">
@@ -17631,7 +17631,7 @@
       </c>
       <c r="B149" t="inlineStr">
         <is>
-          <t>2026-07-11 08:33:53 PM PT</t>
+          <t>2026-07-11 08:35:53 PM PT</t>
         </is>
       </c>
       <c r="C149" t="n">
@@ -17745,7 +17745,7 @@
       </c>
       <c r="B150" t="inlineStr">
         <is>
-          <t>2026-07-11 08:33:52 PM PT</t>
+          <t>2026-07-11 08:35:52 PM PT</t>
         </is>
       </c>
       <c r="C150" t="n">
@@ -17859,7 +17859,7 @@
       </c>
       <c r="B151" t="inlineStr">
         <is>
-          <t>2026-07-11 08:33:52 PM PT</t>
+          <t>2026-07-11 08:35:52 PM PT</t>
         </is>
       </c>
       <c r="C151" t="n">
@@ -17973,7 +17973,7 @@
       </c>
       <c r="B152" t="inlineStr">
         <is>
-          <t>2026-07-11 08:33:52 PM PT</t>
+          <t>2026-07-11 08:35:52 PM PT</t>
         </is>
       </c>
       <c r="C152" t="n">
@@ -18087,7 +18087,7 @@
       </c>
       <c r="B153" t="inlineStr">
         <is>
-          <t>2026-07-11 08:33:53 PM PT</t>
+          <t>2026-07-11 08:35:53 PM PT</t>
         </is>
       </c>
       <c r="C153" t="n">
@@ -18201,7 +18201,7 @@
       </c>
       <c r="B154" t="inlineStr">
         <is>
-          <t>2026-07-11 08:33:53 PM PT</t>
+          <t>2026-07-11 08:35:53 PM PT</t>
         </is>
       </c>
       <c r="C154" t="n">
@@ -18315,7 +18315,7 @@
       </c>
       <c r="B155" t="inlineStr">
         <is>
-          <t>2026-07-11 08:33:52 PM PT</t>
+          <t>2026-07-11 08:35:52 PM PT</t>
         </is>
       </c>
       <c r="C155" t="n">
@@ -18429,7 +18429,7 @@
       </c>
       <c r="B156" t="inlineStr">
         <is>
-          <t>2026-07-11 08:33:54 PM PT</t>
+          <t>2026-07-11 08:35:54 PM PT</t>
         </is>
       </c>
       <c r="C156" t="n">
@@ -18442,7 +18442,7 @@
       </c>
       <c r="E156" t="inlineStr">
         <is>
-          <t>Bottom 8 | 0 out</t>
+          <t>Bottom 8 | 1 out</t>
         </is>
       </c>
       <c r="F156" t="n">
@@ -18454,10 +18454,10 @@
         </is>
       </c>
       <c r="H156" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I156" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="J156" t="n">
         <v>0</v>
@@ -18552,7 +18552,7 @@
       </c>
       <c r="B157" t="inlineStr">
         <is>
-          <t>2026-07-11 08:33:54 PM PT</t>
+          <t>2026-07-11 08:35:54 PM PT</t>
         </is>
       </c>
       <c r="C157" t="n">
@@ -18565,7 +18565,7 @@
       </c>
       <c r="E157" t="inlineStr">
         <is>
-          <t>Bottom 8 | 0 out</t>
+          <t>Bottom 8 | 1 out</t>
         </is>
       </c>
       <c r="F157" t="n">
@@ -18577,10 +18577,10 @@
         </is>
       </c>
       <c r="H157" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I157" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="J157" t="n">
         <v>0</v>
@@ -18675,7 +18675,7 @@
       </c>
       <c r="B158" t="inlineStr">
         <is>
-          <t>2026-07-11 08:33:54 PM PT</t>
+          <t>2026-07-11 08:35:54 PM PT</t>
         </is>
       </c>
       <c r="C158" t="n">
@@ -18688,7 +18688,7 @@
       </c>
       <c r="E158" t="inlineStr">
         <is>
-          <t>Bottom 8 | 0 out</t>
+          <t>Bottom 8 | 1 out</t>
         </is>
       </c>
       <c r="F158" t="n">
@@ -18700,10 +18700,10 @@
         </is>
       </c>
       <c r="H158" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I158" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="J158" t="n">
         <v>0</v>
@@ -18798,7 +18798,7 @@
       </c>
       <c r="B159" t="inlineStr">
         <is>
-          <t>2026-07-11 08:33:54 PM PT</t>
+          <t>2026-07-11 08:35:54 PM PT</t>
         </is>
       </c>
       <c r="C159" t="n">
@@ -18811,7 +18811,7 @@
       </c>
       <c r="E159" t="inlineStr">
         <is>
-          <t>Bottom 8 | 0 out</t>
+          <t>Bottom 8 | 1 out</t>
         </is>
       </c>
       <c r="F159" t="n">
@@ -18823,10 +18823,10 @@
         </is>
       </c>
       <c r="H159" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I159" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="J159" t="n">
         <v>0</v>
@@ -18921,7 +18921,7 @@
       </c>
       <c r="B160" t="inlineStr">
         <is>
-          <t>2026-07-11 08:33:54 PM PT</t>
+          <t>2026-07-11 08:35:54 PM PT</t>
         </is>
       </c>
       <c r="C160" t="n">
@@ -19035,7 +19035,7 @@
       </c>
       <c r="B161" t="inlineStr">
         <is>
-          <t>2026-07-11 08:33:54 PM PT</t>
+          <t>2026-07-11 08:35:54 PM PT</t>
         </is>
       </c>
       <c r="C161" t="n">
@@ -19149,7 +19149,7 @@
       </c>
       <c r="B162" t="inlineStr">
         <is>
-          <t>2026-07-11 08:33:54 PM PT</t>
+          <t>2026-07-11 08:35:54 PM PT</t>
         </is>
       </c>
       <c r="C162" t="n">
@@ -19263,7 +19263,7 @@
       </c>
       <c r="B163" t="inlineStr">
         <is>
-          <t>2026-07-11 08:33:53 PM PT</t>
+          <t>2026-07-11 08:35:54 PM PT</t>
         </is>
       </c>
       <c r="C163" t="n">
@@ -19377,7 +19377,7 @@
       </c>
       <c r="B164" t="inlineStr">
         <is>
-          <t>2026-07-11 08:33:53 PM PT</t>
+          <t>2026-07-11 08:35:54 PM PT</t>
         </is>
       </c>
       <c r="C164" t="n">
@@ -19491,7 +19491,7 @@
       </c>
       <c r="B165" t="inlineStr">
         <is>
-          <t>2026-07-11 08:33:53 PM PT</t>
+          <t>2026-07-11 08:35:53 PM PT</t>
         </is>
       </c>
       <c r="C165" t="n">
@@ -19605,7 +19605,7 @@
       </c>
       <c r="B166" t="inlineStr">
         <is>
-          <t>2026-07-11 08:33:53 PM PT</t>
+          <t>2026-07-11 08:35:53 PM PT</t>
         </is>
       </c>
       <c r="C166" t="n">
@@ -19719,7 +19719,7 @@
       </c>
       <c r="B167" t="inlineStr">
         <is>
-          <t>2026-07-11 08:33:53 PM PT</t>
+          <t>2026-07-11 08:35:53 PM PT</t>
         </is>
       </c>
       <c r="C167" t="n">
@@ -19833,7 +19833,7 @@
       </c>
       <c r="B168" t="inlineStr">
         <is>
-          <t>2026-07-11 08:33:53 PM PT</t>
+          <t>2026-07-11 08:35:53 PM PT</t>
         </is>
       </c>
       <c r="C168" t="n">
@@ -19947,7 +19947,7 @@
       </c>
       <c r="B169" t="inlineStr">
         <is>
-          <t>2026-07-11 08:33:53 PM PT</t>
+          <t>2026-07-11 08:35:53 PM PT</t>
         </is>
       </c>
       <c r="C169" t="n">
@@ -20061,7 +20061,7 @@
       </c>
       <c r="B170" t="inlineStr">
         <is>
-          <t>2026-07-11 08:33:52 PM PT</t>
+          <t>2026-07-11 08:35:52 PM PT</t>
         </is>
       </c>
       <c r="C170" t="n">
@@ -20175,7 +20175,7 @@
       </c>
       <c r="B171" t="inlineStr">
         <is>
-          <t>2026-07-11 08:33:54 PM PT</t>
+          <t>2026-07-11 08:35:54 PM PT</t>
         </is>
       </c>
       <c r="C171" t="n">
@@ -20188,7 +20188,7 @@
       </c>
       <c r="E171" t="inlineStr">
         <is>
-          <t>Top 8 | 1 out</t>
+          <t>Top 8 | 2 out</t>
         </is>
       </c>
       <c r="F171" t="n">
@@ -20200,13 +20200,13 @@
         </is>
       </c>
       <c r="H171" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I171" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="J171" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K171" t="inlineStr">
         <is>
@@ -20298,7 +20298,7 @@
       </c>
       <c r="B172" t="inlineStr">
         <is>
-          <t>2026-07-11 08:33:54 PM PT</t>
+          <t>2026-07-11 08:35:54 PM PT</t>
         </is>
       </c>
       <c r="C172" t="n">
@@ -20311,7 +20311,7 @@
       </c>
       <c r="E172" t="inlineStr">
         <is>
-          <t>Top 8 | 1 out</t>
+          <t>Top 8 | 2 out</t>
         </is>
       </c>
       <c r="F172" t="n">
@@ -20323,13 +20323,13 @@
         </is>
       </c>
       <c r="H172" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I172" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="J172" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K172" t="inlineStr">
         <is>
@@ -20421,7 +20421,7 @@
       </c>
       <c r="B173" t="inlineStr">
         <is>
-          <t>2026-07-11 08:33:53 PM PT</t>
+          <t>2026-07-11 08:35:53 PM PT</t>
         </is>
       </c>
       <c r="C173" t="n">
@@ -20535,7 +20535,7 @@
       </c>
       <c r="B174" t="inlineStr">
         <is>
-          <t>2026-07-11 08:33:53 PM PT</t>
+          <t>2026-07-11 08:35:53 PM PT</t>
         </is>
       </c>
       <c r="C174" t="n">
@@ -20649,7 +20649,7 @@
       </c>
       <c r="B175" t="inlineStr">
         <is>
-          <t>2026-07-11 08:33:52 PM PT</t>
+          <t>2026-07-11 08:35:52 PM PT</t>
         </is>
       </c>
       <c r="C175" t="n">
@@ -20763,7 +20763,7 @@
       </c>
       <c r="B176" t="inlineStr">
         <is>
-          <t>2026-07-11 08:33:52 PM PT</t>
+          <t>2026-07-11 08:35:52 PM PT</t>
         </is>
       </c>
       <c r="C176" t="n">
@@ -20877,7 +20877,7 @@
       </c>
       <c r="B177" t="inlineStr">
         <is>
-          <t>2026-07-11 08:33:52 PM PT</t>
+          <t>2026-07-11 08:35:52 PM PT</t>
         </is>
       </c>
       <c r="C177" t="n">
@@ -20991,7 +20991,7 @@
       </c>
       <c r="B178" t="inlineStr">
         <is>
-          <t>2026-07-11 08:33:52 PM PT</t>
+          <t>2026-07-11 08:35:52 PM PT</t>
         </is>
       </c>
       <c r="C178" t="n">
@@ -21105,7 +21105,7 @@
       </c>
       <c r="B179" t="inlineStr">
         <is>
-          <t>2026-07-11 08:33:52 PM PT</t>
+          <t>2026-07-11 08:35:52 PM PT</t>
         </is>
       </c>
       <c r="C179" t="n">
@@ -21219,7 +21219,7 @@
       </c>
       <c r="B180" t="inlineStr">
         <is>
-          <t>2026-07-11 08:33:53 PM PT</t>
+          <t>2026-07-11 08:35:53 PM PT</t>
         </is>
       </c>
       <c r="C180" t="n">
@@ -21333,7 +21333,7 @@
       </c>
       <c r="B181" t="inlineStr">
         <is>
-          <t>2026-07-11 08:33:53 PM PT</t>
+          <t>2026-07-11 08:35:53 PM PT</t>
         </is>
       </c>
       <c r="C181" t="n">
@@ -21447,7 +21447,7 @@
       </c>
       <c r="B182" t="inlineStr">
         <is>
-          <t>2026-07-11 08:33:53 PM PT</t>
+          <t>2026-07-11 08:35:53 PM PT</t>
         </is>
       </c>
       <c r="C182" t="n">
@@ -21561,7 +21561,7 @@
       </c>
       <c r="B183" t="inlineStr">
         <is>
-          <t>2026-07-11 08:33:53 PM PT</t>
+          <t>2026-07-11 08:35:53 PM PT</t>
         </is>
       </c>
       <c r="C183" t="n">
@@ -21675,7 +21675,7 @@
       </c>
       <c r="B184" t="inlineStr">
         <is>
-          <t>2026-07-11 08:33:52 PM PT</t>
+          <t>2026-07-11 08:35:52 PM PT</t>
         </is>
       </c>
       <c r="C184" t="n">
@@ -21789,7 +21789,7 @@
       </c>
       <c r="B185" t="inlineStr">
         <is>
-          <t>2026-07-11 08:33:52 PM PT</t>
+          <t>2026-07-11 08:35:52 PM PT</t>
         </is>
       </c>
       <c r="C185" t="n">
@@ -21903,7 +21903,7 @@
       </c>
       <c r="B186" t="inlineStr">
         <is>
-          <t>2026-07-11 08:33:53 PM PT</t>
+          <t>2026-07-11 08:35:53 PM PT</t>
         </is>
       </c>
       <c r="C186" t="n">
@@ -22017,7 +22017,7 @@
       </c>
       <c r="B187" t="inlineStr">
         <is>
-          <t>2026-07-11 08:33:53 PM PT</t>
+          <t>2026-07-11 08:35:53 PM PT</t>
         </is>
       </c>
       <c r="C187" t="n">
@@ -22131,7 +22131,7 @@
       </c>
       <c r="B188" t="inlineStr">
         <is>
-          <t>2026-07-11 08:33:53 PM PT</t>
+          <t>2026-07-11 08:35:53 PM PT</t>
         </is>
       </c>
       <c r="C188" t="n">
@@ -22245,7 +22245,7 @@
       </c>
       <c r="B189" t="inlineStr">
         <is>
-          <t>2026-07-11 08:33:53 PM PT</t>
+          <t>2026-07-11 08:35:53 PM PT</t>
         </is>
       </c>
       <c r="C189" t="n">
@@ -22359,7 +22359,7 @@
       </c>
       <c r="B190" t="inlineStr">
         <is>
-          <t>2026-07-11 08:33:54 PM PT</t>
+          <t>2026-07-11 08:35:54 PM PT</t>
         </is>
       </c>
       <c r="C190" t="n">
@@ -22372,7 +22372,7 @@
       </c>
       <c r="E190" t="inlineStr">
         <is>
-          <t>Bottom 8 | 0 out</t>
+          <t>Bottom 8 | 1 out</t>
         </is>
       </c>
       <c r="F190" t="n">
@@ -22384,10 +22384,10 @@
         </is>
       </c>
       <c r="H190" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I190" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="J190" t="n">
         <v>0</v>
@@ -22482,7 +22482,7 @@
       </c>
       <c r="B191" t="inlineStr">
         <is>
-          <t>2026-07-11 08:33:53 PM PT</t>
+          <t>2026-07-11 08:35:53 PM PT</t>
         </is>
       </c>
       <c r="C191" t="n">
@@ -22596,7 +22596,7 @@
       </c>
       <c r="B192" t="inlineStr">
         <is>
-          <t>2026-07-11 08:33:53 PM PT</t>
+          <t>2026-07-11 08:35:53 PM PT</t>
         </is>
       </c>
       <c r="C192" t="n">
@@ -22710,7 +22710,7 @@
       </c>
       <c r="B193" t="inlineStr">
         <is>
-          <t>2026-07-11 08:33:54 PM PT</t>
+          <t>2026-07-11 08:35:54 PM PT</t>
         </is>
       </c>
       <c r="C193" t="n">
@@ -22723,7 +22723,7 @@
       </c>
       <c r="E193" t="inlineStr">
         <is>
-          <t>Top 8 | 1 out</t>
+          <t>Top 8 | 2 out</t>
         </is>
       </c>
       <c r="F193" t="n">
@@ -22735,13 +22735,13 @@
         </is>
       </c>
       <c r="H193" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I193" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="J193" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K193" t="inlineStr">
         <is>
@@ -22833,7 +22833,7 @@
       </c>
       <c r="B194" t="inlineStr">
         <is>
-          <t>2026-07-11 08:33:54 PM PT</t>
+          <t>2026-07-11 08:35:54 PM PT</t>
         </is>
       </c>
       <c r="C194" t="n">
@@ -22846,7 +22846,7 @@
       </c>
       <c r="E194" t="inlineStr">
         <is>
-          <t>Top 8 | 1 out</t>
+          <t>Top 8 | 2 out</t>
         </is>
       </c>
       <c r="F194" t="n">
@@ -22858,13 +22858,13 @@
         </is>
       </c>
       <c r="H194" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I194" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="J194" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K194" t="inlineStr">
         <is>
@@ -22956,7 +22956,7 @@
       </c>
       <c r="B195" t="inlineStr">
         <is>
-          <t>2026-07-11 08:33:53 PM PT</t>
+          <t>2026-07-11 08:35:53 PM PT</t>
         </is>
       </c>
       <c r="C195" t="n">
@@ -23070,7 +23070,7 @@
       </c>
       <c r="B196" t="inlineStr">
         <is>
-          <t>2026-07-11 08:33:54 PM PT</t>
+          <t>2026-07-11 08:35:54 PM PT</t>
         </is>
       </c>
       <c r="C196" t="n">
@@ -23184,7 +23184,7 @@
       </c>
       <c r="B197" t="inlineStr">
         <is>
-          <t>2026-07-11 08:33:54 PM PT</t>
+          <t>2026-07-11 08:35:54 PM PT</t>
         </is>
       </c>
       <c r="C197" t="n">
@@ -23298,7 +23298,7 @@
       </c>
       <c r="B198" t="inlineStr">
         <is>
-          <t>2026-07-11 08:33:53 PM PT</t>
+          <t>2026-07-11 08:35:53 PM PT</t>
         </is>
       </c>
       <c r="C198" t="n">
@@ -23412,7 +23412,7 @@
       </c>
       <c r="B199" t="inlineStr">
         <is>
-          <t>2026-07-11 08:33:53 PM PT</t>
+          <t>2026-07-11 08:35:53 PM PT</t>
         </is>
       </c>
       <c r="C199" t="n">
@@ -23526,7 +23526,7 @@
       </c>
       <c r="B200" t="inlineStr">
         <is>
-          <t>2026-07-11 08:33:53 PM PT</t>
+          <t>2026-07-11 08:35:53 PM PT</t>
         </is>
       </c>
       <c r="C200" t="n">
@@ -23640,7 +23640,7 @@
       </c>
       <c r="B201" t="inlineStr">
         <is>
-          <t>2026-07-11 08:33:53 PM PT</t>
+          <t>2026-07-11 08:35:53 PM PT</t>
         </is>
       </c>
       <c r="C201" t="n">
@@ -23754,7 +23754,7 @@
       </c>
       <c r="B202" t="inlineStr">
         <is>
-          <t>2026-07-11 08:33:53 PM PT</t>
+          <t>2026-07-11 08:35:54 PM PT</t>
         </is>
       </c>
       <c r="C202" t="n">
@@ -23868,7 +23868,7 @@
       </c>
       <c r="B203" t="inlineStr">
         <is>
-          <t>2026-07-11 08:33:53 PM PT</t>
+          <t>2026-07-11 08:35:53 PM PT</t>
         </is>
       </c>
       <c r="C203" t="n">
@@ -23982,7 +23982,7 @@
       </c>
       <c r="B204" t="inlineStr">
         <is>
-          <t>2026-07-11 08:33:53 PM PT</t>
+          <t>2026-07-11 08:35:53 PM PT</t>
         </is>
       </c>
       <c r="C204" t="n">
@@ -24096,7 +24096,7 @@
       </c>
       <c r="B205" t="inlineStr">
         <is>
-          <t>2026-07-11 08:33:53 PM PT</t>
+          <t>2026-07-11 08:35:53 PM PT</t>
         </is>
       </c>
       <c r="C205" t="n">
@@ -24210,7 +24210,7 @@
       </c>
       <c r="B206" t="inlineStr">
         <is>
-          <t>2026-07-11 08:33:53 PM PT</t>
+          <t>2026-07-11 08:35:53 PM PT</t>
         </is>
       </c>
       <c r="C206" t="n">
@@ -24324,7 +24324,7 @@
       </c>
       <c r="B207" t="inlineStr">
         <is>
-          <t>2026-07-11 08:33:53 PM PT</t>
+          <t>2026-07-11 08:35:53 PM PT</t>
         </is>
       </c>
       <c r="C207" t="n">
@@ -24438,7 +24438,7 @@
       </c>
       <c r="B208" t="inlineStr">
         <is>
-          <t>2026-07-11 08:33:53 PM PT</t>
+          <t>2026-07-11 08:35:53 PM PT</t>
         </is>
       </c>
       <c r="C208" t="n">
@@ -24552,7 +24552,7 @@
       </c>
       <c r="B209" t="inlineStr">
         <is>
-          <t>2026-07-11 08:33:53 PM PT</t>
+          <t>2026-07-11 08:35:53 PM PT</t>
         </is>
       </c>
       <c r="C209" t="n">
@@ -24666,7 +24666,7 @@
       </c>
       <c r="B210" t="inlineStr">
         <is>
-          <t>2026-07-11 08:33:53 PM PT</t>
+          <t>2026-07-11 08:35:53 PM PT</t>
         </is>
       </c>
       <c r="C210" t="n">
@@ -24780,7 +24780,7 @@
       </c>
       <c r="B211" t="inlineStr">
         <is>
-          <t>2026-07-11 08:33:53 PM PT</t>
+          <t>2026-07-11 08:35:53 PM PT</t>
         </is>
       </c>
       <c r="C211" t="n">
@@ -24894,7 +24894,7 @@
       </c>
       <c r="B212" t="inlineStr">
         <is>
-          <t>2026-07-11 08:33:53 PM PT</t>
+          <t>2026-07-11 08:35:53 PM PT</t>
         </is>
       </c>
       <c r="C212" t="n">
@@ -25008,7 +25008,7 @@
       </c>
       <c r="B213" t="inlineStr">
         <is>
-          <t>2026-07-11 08:33:52 PM PT</t>
+          <t>2026-07-11 08:35:52 PM PT</t>
         </is>
       </c>
       <c r="C213" t="n">
@@ -25122,7 +25122,7 @@
       </c>
       <c r="B214" t="inlineStr">
         <is>
-          <t>2026-07-11 08:33:53 PM PT</t>
+          <t>2026-07-11 08:35:53 PM PT</t>
         </is>
       </c>
       <c r="C214" t="n">
@@ -25236,7 +25236,7 @@
       </c>
       <c r="B215" t="inlineStr">
         <is>
-          <t>2026-07-11 08:33:53 PM PT</t>
+          <t>2026-07-11 08:35:53 PM PT</t>
         </is>
       </c>
       <c r="C215" t="n">
@@ -25350,7 +25350,7 @@
       </c>
       <c r="B216" t="inlineStr">
         <is>
-          <t>2026-07-11 08:33:52 PM PT</t>
+          <t>2026-07-11 08:35:52 PM PT</t>
         </is>
       </c>
       <c r="C216" t="n">
@@ -25464,7 +25464,7 @@
       </c>
       <c r="B217" t="inlineStr">
         <is>
-          <t>2026-07-11 08:33:53 PM PT</t>
+          <t>2026-07-11 08:35:53 PM PT</t>
         </is>
       </c>
       <c r="C217" t="n">
@@ -25578,7 +25578,7 @@
       </c>
       <c r="B218" t="inlineStr">
         <is>
-          <t>2026-07-11 08:33:53 PM PT</t>
+          <t>2026-07-11 08:35:53 PM PT</t>
         </is>
       </c>
       <c r="C218" t="n">
@@ -25692,7 +25692,7 @@
       </c>
       <c r="B219" t="inlineStr">
         <is>
-          <t>2026-07-11 08:33:53 PM PT</t>
+          <t>2026-07-11 08:35:53 PM PT</t>
         </is>
       </c>
       <c r="C219" t="n">
@@ -25806,7 +25806,7 @@
       </c>
       <c r="B220" t="inlineStr">
         <is>
-          <t>2026-07-11 08:33:53 PM PT</t>
+          <t>2026-07-11 08:35:53 PM PT</t>
         </is>
       </c>
       <c r="C220" t="n">
@@ -25920,7 +25920,7 @@
       </c>
       <c r="B221" t="inlineStr">
         <is>
-          <t>2026-07-11 08:33:53 PM PT</t>
+          <t>2026-07-11 08:35:53 PM PT</t>
         </is>
       </c>
       <c r="C221" t="n">
@@ -26034,7 +26034,7 @@
       </c>
       <c r="B222" t="inlineStr">
         <is>
-          <t>2026-07-11 08:33:53 PM PT</t>
+          <t>2026-07-11 08:35:53 PM PT</t>
         </is>
       </c>
       <c r="C222" t="n">
@@ -26148,7 +26148,7 @@
       </c>
       <c r="B223" t="inlineStr">
         <is>
-          <t>2026-07-11 08:33:53 PM PT</t>
+          <t>2026-07-11 08:35:53 PM PT</t>
         </is>
       </c>
       <c r="C223" t="n">
@@ -26262,7 +26262,7 @@
       </c>
       <c r="B224" t="inlineStr">
         <is>
-          <t>2026-07-11 08:33:52 PM PT</t>
+          <t>2026-07-11 08:35:52 PM PT</t>
         </is>
       </c>
       <c r="C224" t="n">
@@ -26376,7 +26376,7 @@
       </c>
       <c r="B225" t="inlineStr">
         <is>
-          <t>2026-07-11 08:33:52 PM PT</t>
+          <t>2026-07-11 08:35:52 PM PT</t>
         </is>
       </c>
       <c r="C225" t="n">
@@ -26490,7 +26490,7 @@
       </c>
       <c r="B226" t="inlineStr">
         <is>
-          <t>2026-07-11 08:33:53 PM PT</t>
+          <t>2026-07-11 08:35:53 PM PT</t>
         </is>
       </c>
       <c r="C226" t="n">
@@ -26604,7 +26604,7 @@
       </c>
       <c r="B227" t="inlineStr">
         <is>
-          <t>2026-07-11 08:33:53 PM PT</t>
+          <t>2026-07-11 08:35:53 PM PT</t>
         </is>
       </c>
       <c r="C227" t="n">
@@ -26718,7 +26718,7 @@
       </c>
       <c r="B228" t="inlineStr">
         <is>
-          <t>2026-07-11 08:33:53 PM PT</t>
+          <t>2026-07-11 08:35:53 PM PT</t>
         </is>
       </c>
       <c r="C228" t="n">
@@ -26832,7 +26832,7 @@
       </c>
       <c r="B229" t="inlineStr">
         <is>
-          <t>2026-07-11 08:33:53 PM PT</t>
+          <t>2026-07-11 08:35:53 PM PT</t>
         </is>
       </c>
       <c r="C229" t="n">
@@ -26946,7 +26946,7 @@
       </c>
       <c r="B230" t="inlineStr">
         <is>
-          <t>2026-07-11 08:33:54 PM PT</t>
+          <t>2026-07-11 08:35:54 PM PT</t>
         </is>
       </c>
       <c r="C230" t="n">
@@ -26959,7 +26959,7 @@
       </c>
       <c r="E230" t="inlineStr">
         <is>
-          <t>Bottom 8 | 0 out</t>
+          <t>Bottom 8 | 1 out</t>
         </is>
       </c>
       <c r="F230" t="n">
@@ -26971,10 +26971,10 @@
         </is>
       </c>
       <c r="H230" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I230" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="J230" t="n">
         <v>0</v>
@@ -27069,7 +27069,7 @@
       </c>
       <c r="B231" t="inlineStr">
         <is>
-          <t>2026-07-11 08:33:53 PM PT</t>
+          <t>2026-07-11 08:35:53 PM PT</t>
         </is>
       </c>
       <c r="C231" t="n">
@@ -27183,7 +27183,7 @@
       </c>
       <c r="B232" t="inlineStr">
         <is>
-          <t>2026-07-11 08:33:53 PM PT</t>
+          <t>2026-07-11 08:35:53 PM PT</t>
         </is>
       </c>
       <c r="C232" t="n">
@@ -27297,7 +27297,7 @@
       </c>
       <c r="B233" t="inlineStr">
         <is>
-          <t>2026-07-11 08:33:53 PM PT</t>
+          <t>2026-07-11 08:35:53 PM PT</t>
         </is>
       </c>
       <c r="C233" t="n">
@@ -27411,7 +27411,7 @@
       </c>
       <c r="B234" t="inlineStr">
         <is>
-          <t>2026-07-11 08:33:53 PM PT</t>
+          <t>2026-07-11 08:35:53 PM PT</t>
         </is>
       </c>
       <c r="C234" t="n">
@@ -27525,7 +27525,7 @@
       </c>
       <c r="B235" t="inlineStr">
         <is>
-          <t>2026-07-11 08:33:54 PM PT</t>
+          <t>2026-07-11 08:35:54 PM PT</t>
         </is>
       </c>
       <c r="C235" t="n">
@@ -27538,7 +27538,7 @@
       </c>
       <c r="E235" t="inlineStr">
         <is>
-          <t>Top 8 | 1 out</t>
+          <t>Top 8 | 2 out</t>
         </is>
       </c>
       <c r="F235" t="n">
@@ -27550,13 +27550,13 @@
         </is>
       </c>
       <c r="H235" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I235" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="J235" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K235" t="inlineStr">
         <is>
@@ -27592,10 +27592,10 @@
         </is>
       </c>
       <c r="R235" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="S235" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="T235" t="n">
         <v>0</v>
@@ -27648,7 +27648,7 @@
       </c>
       <c r="B236" t="inlineStr">
         <is>
-          <t>2026-07-11 08:33:54 PM PT</t>
+          <t>2026-07-11 08:35:54 PM PT</t>
         </is>
       </c>
       <c r="C236" t="n">
@@ -27661,7 +27661,7 @@
       </c>
       <c r="E236" t="inlineStr">
         <is>
-          <t>Top 8 | 1 out</t>
+          <t>Top 8 | 2 out</t>
         </is>
       </c>
       <c r="F236" t="n">
@@ -27673,13 +27673,13 @@
         </is>
       </c>
       <c r="H236" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I236" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="J236" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K236" t="inlineStr">
         <is>
@@ -27771,7 +27771,7 @@
       </c>
       <c r="B237" t="inlineStr">
         <is>
-          <t>2026-07-11 08:33:53 PM PT</t>
+          <t>2026-07-11 08:35:53 PM PT</t>
         </is>
       </c>
       <c r="C237" t="n">
@@ -27885,7 +27885,7 @@
       </c>
       <c r="B238" t="inlineStr">
         <is>
-          <t>2026-07-11 08:33:53 PM PT</t>
+          <t>2026-07-11 08:35:53 PM PT</t>
         </is>
       </c>
       <c r="C238" t="n">
@@ -27999,7 +27999,7 @@
       </c>
       <c r="B239" t="inlineStr">
         <is>
-          <t>2026-07-11 08:33:53 PM PT</t>
+          <t>2026-07-11 08:35:53 PM PT</t>
         </is>
       </c>
       <c r="C239" t="n">
@@ -28113,7 +28113,7 @@
       </c>
       <c r="B240" t="inlineStr">
         <is>
-          <t>2026-07-11 08:33:53 PM PT</t>
+          <t>2026-07-11 08:35:53 PM PT</t>
         </is>
       </c>
       <c r="C240" t="n">
@@ -28227,7 +28227,7 @@
       </c>
       <c r="B241" t="inlineStr">
         <is>
-          <t>2026-07-11 08:33:53 PM PT</t>
+          <t>2026-07-11 08:35:53 PM PT</t>
         </is>
       </c>
       <c r="C241" t="n">
@@ -28341,7 +28341,7 @@
       </c>
       <c r="B242" t="inlineStr">
         <is>
-          <t>2026-07-11 08:33:53 PM PT</t>
+          <t>2026-07-11 08:35:53 PM PT</t>
         </is>
       </c>
       <c r="C242" t="n">
@@ -28455,7 +28455,7 @@
       </c>
       <c r="B243" t="inlineStr">
         <is>
-          <t>2026-07-11 08:33:53 PM PT</t>
+          <t>2026-07-11 08:35:53 PM PT</t>
         </is>
       </c>
       <c r="C243" t="n">
@@ -28569,7 +28569,7 @@
       </c>
       <c r="B244" t="inlineStr">
         <is>
-          <t>2026-07-11 08:33:54 PM PT</t>
+          <t>2026-07-11 08:35:54 PM PT</t>
         </is>
       </c>
       <c r="C244" t="n">
@@ -28683,7 +28683,7 @@
       </c>
       <c r="B245" t="inlineStr">
         <is>
-          <t>2026-07-11 08:33:54 PM PT</t>
+          <t>2026-07-11 08:35:54 PM PT</t>
         </is>
       </c>
       <c r="C245" t="n">
@@ -28797,7 +28797,7 @@
       </c>
       <c r="B246" t="inlineStr">
         <is>
-          <t>2026-07-11 08:33:54 PM PT</t>
+          <t>2026-07-11 08:35:54 PM PT</t>
         </is>
       </c>
       <c r="C246" t="n">
@@ -28911,7 +28911,7 @@
       </c>
       <c r="B247" t="inlineStr">
         <is>
-          <t>2026-07-11 08:33:53 PM PT</t>
+          <t>2026-07-11 08:35:53 PM PT</t>
         </is>
       </c>
       <c r="C247" t="n">
@@ -29025,7 +29025,7 @@
       </c>
       <c r="B248" t="inlineStr">
         <is>
-          <t>2026-07-11 08:33:53 PM PT</t>
+          <t>2026-07-11 08:35:53 PM PT</t>
         </is>
       </c>
       <c r="C248" t="n">
@@ -29139,7 +29139,7 @@
       </c>
       <c r="B249" t="inlineStr">
         <is>
-          <t>2026-07-11 08:33:53 PM PT</t>
+          <t>2026-07-11 08:35:53 PM PT</t>
         </is>
       </c>
       <c r="C249" t="n">
@@ -29253,7 +29253,7 @@
       </c>
       <c r="B250" t="inlineStr">
         <is>
-          <t>2026-07-11 08:33:53 PM PT</t>
+          <t>2026-07-11 08:35:53 PM PT</t>
         </is>
       </c>
       <c r="C250" t="n">
@@ -29367,7 +29367,7 @@
       </c>
       <c r="B251" t="inlineStr">
         <is>
-          <t>2026-07-11 08:33:53 PM PT</t>
+          <t>2026-07-11 08:35:53 PM PT</t>
         </is>
       </c>
       <c r="C251" t="n">
@@ -29481,7 +29481,7 @@
       </c>
       <c r="B252" t="inlineStr">
         <is>
-          <t>2026-07-11 08:33:53 PM PT</t>
+          <t>2026-07-11 08:35:53 PM PT</t>
         </is>
       </c>
       <c r="C252" t="n">
@@ -29595,7 +29595,7 @@
       </c>
       <c r="B253" t="inlineStr">
         <is>
-          <t>2026-07-11 08:33:53 PM PT</t>
+          <t>2026-07-11 08:35:54 PM PT</t>
         </is>
       </c>
       <c r="C253" t="n">
@@ -29709,7 +29709,7 @@
       </c>
       <c r="B254" t="inlineStr">
         <is>
-          <t>2026-07-11 08:33:53 PM PT</t>
+          <t>2026-07-11 08:35:54 PM PT</t>
         </is>
       </c>
       <c r="C254" t="n">
@@ -29823,7 +29823,7 @@
       </c>
       <c r="B255" t="inlineStr">
         <is>
-          <t>2026-07-11 08:33:53 PM PT</t>
+          <t>2026-07-11 08:35:54 PM PT</t>
         </is>
       </c>
       <c r="C255" t="n">
@@ -29937,7 +29937,7 @@
       </c>
       <c r="B256" t="inlineStr">
         <is>
-          <t>2026-07-11 08:33:53 PM PT</t>
+          <t>2026-07-11 08:35:54 PM PT</t>
         </is>
       </c>
       <c r="C256" t="n">
@@ -30051,7 +30051,7 @@
       </c>
       <c r="B257" t="inlineStr">
         <is>
-          <t>2026-07-11 08:33:53 PM PT</t>
+          <t>2026-07-11 08:35:54 PM PT</t>
         </is>
       </c>
       <c r="C257" t="n">
@@ -30165,7 +30165,7 @@
       </c>
       <c r="B258" t="inlineStr">
         <is>
-          <t>2026-07-11 08:33:53 PM PT</t>
+          <t>2026-07-11 08:35:53 PM PT</t>
         </is>
       </c>
       <c r="C258" t="n">
@@ -30279,7 +30279,7 @@
       </c>
       <c r="B259" t="inlineStr">
         <is>
-          <t>2026-07-11 08:33:53 PM PT</t>
+          <t>2026-07-11 08:35:53 PM PT</t>
         </is>
       </c>
       <c r="C259" t="n">
@@ -30393,7 +30393,7 @@
       </c>
       <c r="B260" t="inlineStr">
         <is>
-          <t>2026-07-11 08:33:53 PM PT</t>
+          <t>2026-07-11 08:35:53 PM PT</t>
         </is>
       </c>
       <c r="C260" t="n">
@@ -30507,7 +30507,7 @@
       </c>
       <c r="B261" t="inlineStr">
         <is>
-          <t>2026-07-11 08:33:53 PM PT</t>
+          <t>2026-07-11 08:35:53 PM PT</t>
         </is>
       </c>
       <c r="C261" t="n">
@@ -30621,7 +30621,7 @@
       </c>
       <c r="B262" t="inlineStr">
         <is>
-          <t>2026-07-11 08:33:53 PM PT</t>
+          <t>2026-07-11 08:35:53 PM PT</t>
         </is>
       </c>
       <c r="C262" t="n">
@@ -30735,7 +30735,7 @@
       </c>
       <c r="B263" t="inlineStr">
         <is>
-          <t>2026-07-11 08:33:53 PM PT</t>
+          <t>2026-07-11 08:35:53 PM PT</t>
         </is>
       </c>
       <c r="C263" t="n">
@@ -30849,7 +30849,7 @@
       </c>
       <c r="B264" t="inlineStr">
         <is>
-          <t>2026-07-11 08:33:53 PM PT</t>
+          <t>2026-07-11 08:35:53 PM PT</t>
         </is>
       </c>
       <c r="C264" t="n">
@@ -30963,7 +30963,7 @@
       </c>
       <c r="B265" t="inlineStr">
         <is>
-          <t>2026-07-11 08:33:53 PM PT</t>
+          <t>2026-07-11 08:35:53 PM PT</t>
         </is>
       </c>
       <c r="C265" t="n">
@@ -31077,7 +31077,7 @@
       </c>
       <c r="B266" t="inlineStr">
         <is>
-          <t>2026-07-11 08:33:53 PM PT</t>
+          <t>2026-07-11 08:35:53 PM PT</t>
         </is>
       </c>
       <c r="C266" t="n">
@@ -31191,7 +31191,7 @@
       </c>
       <c r="B267" t="inlineStr">
         <is>
-          <t>2026-07-11 08:33:53 PM PT</t>
+          <t>2026-07-11 08:35:53 PM PT</t>
         </is>
       </c>
       <c r="C267" t="n">
@@ -31305,7 +31305,7 @@
       </c>
       <c r="B268" t="inlineStr">
         <is>
-          <t>2026-07-11 08:33:53 PM PT</t>
+          <t>2026-07-11 08:35:53 PM PT</t>
         </is>
       </c>
       <c r="C268" t="n">
@@ -31419,7 +31419,7 @@
       </c>
       <c r="B269" t="inlineStr">
         <is>
-          <t>2026-07-11 08:33:53 PM PT</t>
+          <t>2026-07-11 08:35:53 PM PT</t>
         </is>
       </c>
       <c r="C269" t="n">
@@ -31533,7 +31533,7 @@
       </c>
       <c r="B270" t="inlineStr">
         <is>
-          <t>2026-07-11 08:33:53 PM PT</t>
+          <t>2026-07-11 08:35:53 PM PT</t>
         </is>
       </c>
       <c r="C270" t="n">
@@ -31647,7 +31647,7 @@
       </c>
       <c r="B271" t="inlineStr">
         <is>
-          <t>2026-07-11 08:33:53 PM PT</t>
+          <t>2026-07-11 08:35:53 PM PT</t>
         </is>
       </c>
       <c r="C271" t="n">
@@ -31761,7 +31761,7 @@
       </c>
       <c r="B272" t="inlineStr">
         <is>
-          <t>2026-07-11 08:33:53 PM PT</t>
+          <t>2026-07-11 08:35:53 PM PT</t>
         </is>
       </c>
       <c r="C272" t="n">
@@ -31875,7 +31875,7 @@
       </c>
       <c r="B273" t="inlineStr">
         <is>
-          <t>2026-07-11 08:33:53 PM PT</t>
+          <t>2026-07-11 08:35:53 PM PT</t>
         </is>
       </c>
       <c r="C273" t="n">
@@ -31989,7 +31989,7 @@
       </c>
       <c r="B274" t="inlineStr">
         <is>
-          <t>2026-07-11 08:33:53 PM PT</t>
+          <t>2026-07-11 08:35:53 PM PT</t>
         </is>
       </c>
       <c r="C274" t="n">
@@ -32103,7 +32103,7 @@
       </c>
       <c r="B275" t="inlineStr">
         <is>
-          <t>2026-07-11 08:33:53 PM PT</t>
+          <t>2026-07-11 08:35:53 PM PT</t>
         </is>
       </c>
       <c r="C275" t="n">
@@ -32217,7 +32217,7 @@
       </c>
       <c r="B276" t="inlineStr">
         <is>
-          <t>2026-07-11 08:33:52 PM PT</t>
+          <t>2026-07-11 08:35:52 PM PT</t>
         </is>
       </c>
       <c r="C276" t="n">
@@ -32331,7 +32331,7 @@
       </c>
       <c r="B277" t="inlineStr">
         <is>
-          <t>2026-07-11 08:33:52 PM PT</t>
+          <t>2026-07-11 08:35:52 PM PT</t>
         </is>
       </c>
       <c r="C277" t="n">
@@ -32445,7 +32445,7 @@
       </c>
       <c r="B278" t="inlineStr">
         <is>
-          <t>2026-07-11 08:33:52 PM PT</t>
+          <t>2026-07-11 08:35:52 PM PT</t>
         </is>
       </c>
       <c r="C278" t="n">
@@ -32559,7 +32559,7 @@
       </c>
       <c r="B279" t="inlineStr">
         <is>
-          <t>2026-07-11 08:33:54 PM PT</t>
+          <t>2026-07-11 08:35:54 PM PT</t>
         </is>
       </c>
       <c r="C279" t="n">
@@ -32572,7 +32572,7 @@
       </c>
       <c r="E279" t="inlineStr">
         <is>
-          <t>Top 8 | 1 out</t>
+          <t>Top 8 | 2 out</t>
         </is>
       </c>
       <c r="F279" t="n">
@@ -32584,13 +32584,13 @@
         </is>
       </c>
       <c r="H279" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I279" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="J279" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K279" t="inlineStr">
         <is>
@@ -32682,7 +32682,7 @@
       </c>
       <c r="B280" t="inlineStr">
         <is>
-          <t>2026-07-11 08:33:54 PM PT</t>
+          <t>2026-07-11 08:35:54 PM PT</t>
         </is>
       </c>
       <c r="C280" t="n">
@@ -32695,7 +32695,7 @@
       </c>
       <c r="E280" t="inlineStr">
         <is>
-          <t>Top 8 | 1 out</t>
+          <t>Top 8 | 2 out</t>
         </is>
       </c>
       <c r="F280" t="n">
@@ -32707,13 +32707,13 @@
         </is>
       </c>
       <c r="H280" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I280" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="J280" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K280" t="inlineStr">
         <is>
@@ -32805,7 +32805,7 @@
       </c>
       <c r="B281" t="inlineStr">
         <is>
-          <t>2026-07-11 08:33:54 PM PT</t>
+          <t>2026-07-11 08:35:54 PM PT</t>
         </is>
       </c>
       <c r="C281" t="n">
@@ -32818,7 +32818,7 @@
       </c>
       <c r="E281" t="inlineStr">
         <is>
-          <t>Top 8 | 1 out</t>
+          <t>Top 8 | 2 out</t>
         </is>
       </c>
       <c r="F281" t="n">
@@ -32830,13 +32830,13 @@
         </is>
       </c>
       <c r="H281" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I281" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="J281" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K281" t="inlineStr">
         <is>
@@ -32928,7 +32928,7 @@
       </c>
       <c r="B282" t="inlineStr">
         <is>
-          <t>2026-07-11 08:33:54 PM PT</t>
+          <t>2026-07-11 08:35:54 PM PT</t>
         </is>
       </c>
       <c r="C282" t="n">
@@ -32941,7 +32941,7 @@
       </c>
       <c r="E282" t="inlineStr">
         <is>
-          <t>Top 8 | 1 out</t>
+          <t>Top 8 | 2 out</t>
         </is>
       </c>
       <c r="F282" t="n">
@@ -32953,13 +32953,13 @@
         </is>
       </c>
       <c r="H282" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I282" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="J282" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K282" t="inlineStr">
         <is>
@@ -33051,7 +33051,7 @@
       </c>
       <c r="B283" t="inlineStr">
         <is>
-          <t>2026-07-11 08:33:54 PM PT</t>
+          <t>2026-07-11 08:35:54 PM PT</t>
         </is>
       </c>
       <c r="C283" t="n">
@@ -33064,7 +33064,7 @@
       </c>
       <c r="E283" t="inlineStr">
         <is>
-          <t>Top 8 | 1 out</t>
+          <t>Top 8 | 2 out</t>
         </is>
       </c>
       <c r="F283" t="n">
@@ -33076,13 +33076,13 @@
         </is>
       </c>
       <c r="H283" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I283" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="J283" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K283" t="inlineStr">
         <is>
@@ -33174,7 +33174,7 @@
       </c>
       <c r="B284" t="inlineStr">
         <is>
-          <t>2026-07-11 08:33:54 PM PT</t>
+          <t>2026-07-11 08:35:54 PM PT</t>
         </is>
       </c>
       <c r="C284" t="n">
@@ -33187,7 +33187,7 @@
       </c>
       <c r="E284" t="inlineStr">
         <is>
-          <t>Top 8 | 1 out</t>
+          <t>Top 8 | 2 out</t>
         </is>
       </c>
       <c r="F284" t="n">
@@ -33199,13 +33199,13 @@
         </is>
       </c>
       <c r="H284" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I284" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="J284" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K284" t="inlineStr">
         <is>
@@ -33297,7 +33297,7 @@
       </c>
       <c r="B285" t="inlineStr">
         <is>
-          <t>2026-07-11 08:33:54 PM PT</t>
+          <t>2026-07-11 08:35:54 PM PT</t>
         </is>
       </c>
       <c r="C285" t="n">
@@ -33310,7 +33310,7 @@
       </c>
       <c r="E285" t="inlineStr">
         <is>
-          <t>Top 8 | 1 out</t>
+          <t>Top 8 | 2 out</t>
         </is>
       </c>
       <c r="F285" t="n">
@@ -33322,13 +33322,13 @@
         </is>
       </c>
       <c r="H285" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I285" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="J285" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K285" t="inlineStr">
         <is>
@@ -33420,7 +33420,7 @@
       </c>
       <c r="B286" t="inlineStr">
         <is>
-          <t>2026-07-11 08:33:53 PM PT</t>
+          <t>2026-07-11 08:35:53 PM PT</t>
         </is>
       </c>
       <c r="C286" t="n">
@@ -33534,7 +33534,7 @@
       </c>
       <c r="B287" t="inlineStr">
         <is>
-          <t>2026-07-11 08:33:52 PM PT</t>
+          <t>2026-07-11 08:35:52 PM PT</t>
         </is>
       </c>
       <c r="C287" t="n">
@@ -33648,7 +33648,7 @@
       </c>
       <c r="B288" t="inlineStr">
         <is>
-          <t>2026-07-11 08:33:52 PM PT</t>
+          <t>2026-07-11 08:35:52 PM PT</t>
         </is>
       </c>
       <c r="C288" t="n">
@@ -33762,7 +33762,7 @@
       </c>
       <c r="B289" t="inlineStr">
         <is>
-          <t>2026-07-11 08:33:52 PM PT</t>
+          <t>2026-07-11 08:35:52 PM PT</t>
         </is>
       </c>
       <c r="C289" t="n">
@@ -33876,7 +33876,7 @@
       </c>
       <c r="B290" t="inlineStr">
         <is>
-          <t>2026-07-11 08:33:52 PM PT</t>
+          <t>2026-07-11 08:35:52 PM PT</t>
         </is>
       </c>
       <c r="C290" t="n">
@@ -33990,7 +33990,7 @@
       </c>
       <c r="B291" t="inlineStr">
         <is>
-          <t>2026-07-11 08:33:52 PM PT</t>
+          <t>2026-07-11 08:35:52 PM PT</t>
         </is>
       </c>
       <c r="C291" t="n">
@@ -34104,7 +34104,7 @@
       </c>
       <c r="B292" t="inlineStr">
         <is>
-          <t>2026-07-11 08:33:52 PM PT</t>
+          <t>2026-07-11 08:35:52 PM PT</t>
         </is>
       </c>
       <c r="C292" t="n">
@@ -34218,7 +34218,7 @@
       </c>
       <c r="B293" t="inlineStr">
         <is>
-          <t>2026-07-11 08:33:52 PM PT</t>
+          <t>2026-07-11 08:35:52 PM PT</t>
         </is>
       </c>
       <c r="C293" t="n">
@@ -34332,7 +34332,7 @@
       </c>
       <c r="B294" t="inlineStr">
         <is>
-          <t>2026-07-11 08:33:53 PM PT</t>
+          <t>2026-07-11 08:35:53 PM PT</t>
         </is>
       </c>
       <c r="C294" t="n">
@@ -34446,7 +34446,7 @@
       </c>
       <c r="B295" t="inlineStr">
         <is>
-          <t>2026-07-11 08:33:53 PM PT</t>
+          <t>2026-07-11 08:35:53 PM PT</t>
         </is>
       </c>
       <c r="C295" t="n">
@@ -34560,7 +34560,7 @@
       </c>
       <c r="B296" t="inlineStr">
         <is>
-          <t>2026-07-11 08:33:53 PM PT</t>
+          <t>2026-07-11 08:35:53 PM PT</t>
         </is>
       </c>
       <c r="C296" t="n">
@@ -34674,7 +34674,7 @@
       </c>
       <c r="B297" t="inlineStr">
         <is>
-          <t>2026-07-11 08:33:53 PM PT</t>
+          <t>2026-07-11 08:35:53 PM PT</t>
         </is>
       </c>
       <c r="C297" t="n">
@@ -34788,7 +34788,7 @@
       </c>
       <c r="B298" t="inlineStr">
         <is>
-          <t>2026-07-11 08:33:53 PM PT</t>
+          <t>2026-07-11 08:35:53 PM PT</t>
         </is>
       </c>
       <c r="C298" t="n">
@@ -34902,7 +34902,7 @@
       </c>
       <c r="B299" t="inlineStr">
         <is>
-          <t>2026-07-11 08:33:53 PM PT</t>
+          <t>2026-07-11 08:35:53 PM PT</t>
         </is>
       </c>
       <c r="C299" t="n">
@@ -35016,7 +35016,7 @@
       </c>
       <c r="B300" t="inlineStr">
         <is>
-          <t>2026-07-11 08:33:53 PM PT</t>
+          <t>2026-07-11 08:35:53 PM PT</t>
         </is>
       </c>
       <c r="C300" t="n">
@@ -35130,7 +35130,7 @@
       </c>
       <c r="B301" t="inlineStr">
         <is>
-          <t>2026-07-11 08:33:53 PM PT</t>
+          <t>2026-07-11 08:35:53 PM PT</t>
         </is>
       </c>
       <c r="C301" t="n">
@@ -35244,7 +35244,7 @@
       </c>
       <c r="B302" t="inlineStr">
         <is>
-          <t>2026-07-11 08:33:52 PM PT</t>
+          <t>2026-07-11 08:35:52 PM PT</t>
         </is>
       </c>
       <c r="C302" t="n">
@@ -35358,7 +35358,7 @@
       </c>
       <c r="B303" t="inlineStr">
         <is>
-          <t>2026-07-11 08:33:52 PM PT</t>
+          <t>2026-07-11 08:35:52 PM PT</t>
         </is>
       </c>
       <c r="C303" t="n">
@@ -35472,7 +35472,7 @@
       </c>
       <c r="B304" t="inlineStr">
         <is>
-          <t>2026-07-11 08:33:52 PM PT</t>
+          <t>2026-07-11 08:35:52 PM PT</t>
         </is>
       </c>
       <c r="C304" t="n">
@@ -35586,7 +35586,7 @@
       </c>
       <c r="B305" t="inlineStr">
         <is>
-          <t>2026-07-11 08:33:52 PM PT</t>
+          <t>2026-07-11 08:35:52 PM PT</t>
         </is>
       </c>
       <c r="C305" t="n">
@@ -35700,7 +35700,7 @@
       </c>
       <c r="B306" t="inlineStr">
         <is>
-          <t>2026-07-11 08:33:52 PM PT</t>
+          <t>2026-07-11 08:35:52 PM PT</t>
         </is>
       </c>
       <c r="C306" t="n">
@@ -35814,7 +35814,7 @@
       </c>
       <c r="B307" t="inlineStr">
         <is>
-          <t>2026-07-11 08:33:52 PM PT</t>
+          <t>2026-07-11 08:35:52 PM PT</t>
         </is>
       </c>
       <c r="C307" t="n">
@@ -35928,7 +35928,7 @@
       </c>
       <c r="B308" t="inlineStr">
         <is>
-          <t>2026-07-11 08:33:52 PM PT</t>
+          <t>2026-07-11 08:35:52 PM PT</t>
         </is>
       </c>
       <c r="C308" t="n">
@@ -36042,7 +36042,7 @@
       </c>
       <c r="B309" t="inlineStr">
         <is>
-          <t>2026-07-11 08:33:52 PM PT</t>
+          <t>2026-07-11 08:35:52 PM PT</t>
         </is>
       </c>
       <c r="C309" t="n">
@@ -36156,7 +36156,7 @@
       </c>
       <c r="B310" t="inlineStr">
         <is>
-          <t>2026-07-11 08:33:54 PM PT</t>
+          <t>2026-07-11 08:35:54 PM PT</t>
         </is>
       </c>
       <c r="C310" t="n">
@@ -36169,7 +36169,7 @@
       </c>
       <c r="E310" t="inlineStr">
         <is>
-          <t>Bottom 8 | 0 out</t>
+          <t>Bottom 8 | 1 out</t>
         </is>
       </c>
       <c r="F310" t="n">
@@ -36181,10 +36181,10 @@
         </is>
       </c>
       <c r="H310" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I310" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="J310" t="n">
         <v>0</v>
@@ -36279,7 +36279,7 @@
       </c>
       <c r="B311" t="inlineStr">
         <is>
-          <t>2026-07-11 08:33:53 PM PT</t>
+          <t>2026-07-11 08:35:53 PM PT</t>
         </is>
       </c>
       <c r="C311" t="n">
@@ -36393,7 +36393,7 @@
       </c>
       <c r="B312" t="inlineStr">
         <is>
-          <t>2026-07-11 08:33:53 PM PT</t>
+          <t>2026-07-11 08:35:53 PM PT</t>
         </is>
       </c>
       <c r="C312" t="n">
@@ -36507,7 +36507,7 @@
       </c>
       <c r="B313" t="inlineStr">
         <is>
-          <t>2026-07-11 08:33:53 PM PT</t>
+          <t>2026-07-11 08:35:53 PM PT</t>
         </is>
       </c>
       <c r="C313" t="n">
@@ -36621,7 +36621,7 @@
       </c>
       <c r="B314" t="inlineStr">
         <is>
-          <t>2026-07-11 08:33:53 PM PT</t>
+          <t>2026-07-11 08:35:53 PM PT</t>
         </is>
       </c>
       <c r="C314" t="n">
@@ -36735,7 +36735,7 @@
       </c>
       <c r="B315" t="inlineStr">
         <is>
-          <t>2026-07-11 08:33:53 PM PT</t>
+          <t>2026-07-11 08:35:53 PM PT</t>
         </is>
       </c>
       <c r="C315" t="n">
@@ -36849,7 +36849,7 @@
       </c>
       <c r="B316" t="inlineStr">
         <is>
-          <t>2026-07-11 08:33:53 PM PT</t>
+          <t>2026-07-11 08:35:53 PM PT</t>
         </is>
       </c>
       <c r="C316" t="n">
@@ -36963,7 +36963,7 @@
       </c>
       <c r="B317" t="inlineStr">
         <is>
-          <t>2026-07-11 08:33:53 PM PT</t>
+          <t>2026-07-11 08:35:53 PM PT</t>
         </is>
       </c>
       <c r="C317" t="n">
@@ -37077,7 +37077,7 @@
       </c>
       <c r="B318" t="inlineStr">
         <is>
-          <t>2026-07-11 08:33:54 PM PT</t>
+          <t>2026-07-11 08:35:54 PM PT</t>
         </is>
       </c>
       <c r="C318" t="n">
@@ -37191,7 +37191,7 @@
       </c>
       <c r="B319" t="inlineStr">
         <is>
-          <t>2026-07-11 08:33:54 PM PT</t>
+          <t>2026-07-11 08:35:54 PM PT</t>
         </is>
       </c>
       <c r="C319" t="n">
@@ -37305,7 +37305,7 @@
       </c>
       <c r="B320" t="inlineStr">
         <is>
-          <t>2026-07-11 08:33:54 PM PT</t>
+          <t>2026-07-11 08:35:54 PM PT</t>
         </is>
       </c>
       <c r="C320" t="n">
@@ -37419,7 +37419,7 @@
       </c>
       <c r="B321" t="inlineStr">
         <is>
-          <t>2026-07-11 08:33:54 PM PT</t>
+          <t>2026-07-11 08:35:54 PM PT</t>
         </is>
       </c>
       <c r="C321" t="n">
@@ -37533,7 +37533,7 @@
       </c>
       <c r="B322" t="inlineStr">
         <is>
-          <t>2026-07-11 08:33:53 PM PT</t>
+          <t>2026-07-11 08:35:53 PM PT</t>
         </is>
       </c>
       <c r="C322" t="n">
@@ -37647,7 +37647,7 @@
       </c>
       <c r="B323" t="inlineStr">
         <is>
-          <t>2026-07-11 08:33:53 PM PT</t>
+          <t>2026-07-11 08:35:53 PM PT</t>
         </is>
       </c>
       <c r="C323" t="n">
@@ -37761,7 +37761,7 @@
       </c>
       <c r="B324" t="inlineStr">
         <is>
-          <t>2026-07-11 08:33:53 PM PT</t>
+          <t>2026-07-11 08:35:53 PM PT</t>
         </is>
       </c>
       <c r="C324" t="n">
@@ -37875,7 +37875,7 @@
       </c>
       <c r="B325" t="inlineStr">
         <is>
-          <t>2026-07-11 08:33:53 PM PT</t>
+          <t>2026-07-11 08:35:53 PM PT</t>
         </is>
       </c>
       <c r="C325" t="n">
@@ -37989,7 +37989,7 @@
       </c>
       <c r="B326" t="inlineStr">
         <is>
-          <t>2026-07-11 08:33:53 PM PT</t>
+          <t>2026-07-11 08:35:53 PM PT</t>
         </is>
       </c>
       <c r="C326" t="n">
@@ -38103,7 +38103,7 @@
       </c>
       <c r="B327" t="inlineStr">
         <is>
-          <t>2026-07-11 08:33:53 PM PT</t>
+          <t>2026-07-11 08:35:53 PM PT</t>
         </is>
       </c>
       <c r="C327" t="n">
@@ -38217,7 +38217,7 @@
       </c>
       <c r="B328" t="inlineStr">
         <is>
-          <t>2026-07-11 08:33:53 PM PT</t>
+          <t>2026-07-11 08:35:53 PM PT</t>
         </is>
       </c>
       <c r="C328" t="n">
@@ -38331,7 +38331,7 @@
       </c>
       <c r="B329" t="inlineStr">
         <is>
-          <t>2026-07-11 08:33:53 PM PT</t>
+          <t>2026-07-11 08:35:53 PM PT</t>
         </is>
       </c>
       <c r="C329" t="n">
@@ -38445,7 +38445,7 @@
       </c>
       <c r="B330" t="inlineStr">
         <is>
-          <t>2026-07-11 08:33:53 PM PT</t>
+          <t>2026-07-11 08:35:53 PM PT</t>
         </is>
       </c>
       <c r="C330" t="n">
@@ -38559,7 +38559,7 @@
       </c>
       <c r="B331" t="inlineStr">
         <is>
-          <t>2026-07-11 08:33:54 PM PT</t>
+          <t>2026-07-11 08:35:54 PM PT</t>
         </is>
       </c>
       <c r="C331" t="n">
@@ -38572,7 +38572,7 @@
       </c>
       <c r="E331" t="inlineStr">
         <is>
-          <t>Bottom 8 | 0 out</t>
+          <t>Bottom 8 | 1 out</t>
         </is>
       </c>
       <c r="F331" t="n">
@@ -38584,10 +38584,10 @@
         </is>
       </c>
       <c r="H331" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I331" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="J331" t="n">
         <v>0</v>
@@ -38682,7 +38682,7 @@
       </c>
       <c r="B332" t="inlineStr">
         <is>
-          <t>2026-07-11 08:33:53 PM PT</t>
+          <t>2026-07-11 08:35:53 PM PT</t>
         </is>
       </c>
       <c r="C332" t="n">
@@ -38796,7 +38796,7 @@
       </c>
       <c r="B333" t="inlineStr">
         <is>
-          <t>2026-07-11 08:33:53 PM PT</t>
+          <t>2026-07-11 08:35:53 PM PT</t>
         </is>
       </c>
       <c r="C333" t="n">

--- a/live_mlb_hitter_fantasy_scores_2026_07_11.xlsx
+++ b/live_mlb_hitter_fantasy_scores_2026_07_11.xlsx
@@ -693,7 +693,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-07-11 08:35:52 PM PT</t>
+          <t>2026-07-11 08:37:52 PM PT</t>
         </is>
       </c>
       <c r="C2" t="n">
@@ -807,7 +807,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>2026-07-11 08:35:54 PM PT</t>
+          <t>2026-07-11 08:37:54 PM PT</t>
         </is>
       </c>
       <c r="C3" t="n">
@@ -820,7 +820,7 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Top 8 | 2 out</t>
+          <t>Bottom 8 | 0 out</t>
         </is>
       </c>
       <c r="F3" t="n">
@@ -828,17 +828,17 @@
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Top</t>
+          <t>Bottom</t>
         </is>
       </c>
       <c r="H3" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="I3" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J3" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="K3" t="inlineStr">
         <is>
@@ -930,7 +930,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-07-11 08:35:53 PM PT</t>
+          <t>2026-07-11 08:37:54 PM PT</t>
         </is>
       </c>
       <c r="C4" t="n">
@@ -1044,7 +1044,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>2026-07-11 08:35:54 PM PT</t>
+          <t>2026-07-11 08:37:54 PM PT</t>
         </is>
       </c>
       <c r="C5" t="n">
@@ -1072,7 +1072,7 @@
         <v>1</v>
       </c>
       <c r="I5" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="J5" t="n">
         <v>0</v>
@@ -1167,7 +1167,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>2026-07-11 08:35:53 PM PT</t>
+          <t>2026-07-11 08:37:54 PM PT</t>
         </is>
       </c>
       <c r="C6" t="n">
@@ -1281,7 +1281,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>2026-07-11 08:35:54 PM PT</t>
+          <t>2026-07-11 08:37:54 PM PT</t>
         </is>
       </c>
       <c r="C7" t="n">
@@ -1395,7 +1395,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>2026-07-11 08:35:53 PM PT</t>
+          <t>2026-07-11 08:37:53 PM PT</t>
         </is>
       </c>
       <c r="C8" t="n">
@@ -1509,7 +1509,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>2026-07-11 08:35:53 PM PT</t>
+          <t>2026-07-11 08:37:54 PM PT</t>
         </is>
       </c>
       <c r="C9" t="n">
@@ -1623,7 +1623,7 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>2026-07-11 08:35:52 PM PT</t>
+          <t>2026-07-11 08:37:53 PM PT</t>
         </is>
       </c>
       <c r="C10" t="n">
@@ -1737,7 +1737,7 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>2026-07-11 08:35:54 PM PT</t>
+          <t>2026-07-11 08:37:54 PM PT</t>
         </is>
       </c>
       <c r="C11" t="n">
@@ -1765,7 +1765,7 @@
         <v>1</v>
       </c>
       <c r="I11" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="J11" t="n">
         <v>0</v>
@@ -1860,7 +1860,7 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>2026-07-11 08:35:53 PM PT</t>
+          <t>2026-07-11 08:37:53 PM PT</t>
         </is>
       </c>
       <c r="C12" t="n">
@@ -1974,7 +1974,7 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>2026-07-11 08:35:53 PM PT</t>
+          <t>2026-07-11 08:37:53 PM PT</t>
         </is>
       </c>
       <c r="C13" t="n">
@@ -2088,7 +2088,7 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>2026-07-11 08:35:54 PM PT</t>
+          <t>2026-07-11 08:37:54 PM PT</t>
         </is>
       </c>
       <c r="C14" t="n">
@@ -2116,7 +2116,7 @@
         <v>1</v>
       </c>
       <c r="I14" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="J14" t="n">
         <v>0</v>
@@ -2211,7 +2211,7 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>2026-07-11 08:35:53 PM PT</t>
+          <t>2026-07-11 08:37:53 PM PT</t>
         </is>
       </c>
       <c r="C15" t="n">
@@ -2325,7 +2325,7 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>2026-07-11 08:35:53 PM PT</t>
+          <t>2026-07-11 08:37:53 PM PT</t>
         </is>
       </c>
       <c r="C16" t="n">
@@ -2439,7 +2439,7 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>2026-07-11 08:35:53 PM PT</t>
+          <t>2026-07-11 08:37:54 PM PT</t>
         </is>
       </c>
       <c r="C17" t="n">
@@ -2553,7 +2553,7 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>2026-07-11 08:35:54 PM PT</t>
+          <t>2026-07-11 08:37:54 PM PT</t>
         </is>
       </c>
       <c r="C18" t="n">
@@ -2581,7 +2581,7 @@
         <v>1</v>
       </c>
       <c r="I18" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="J18" t="n">
         <v>0</v>
@@ -2676,7 +2676,7 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>2026-07-11 08:35:53 PM PT</t>
+          <t>2026-07-11 08:37:53 PM PT</t>
         </is>
       </c>
       <c r="C19" t="n">
@@ -2790,7 +2790,7 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>2026-07-11 08:35:54 PM PT</t>
+          <t>2026-07-11 08:37:54 PM PT</t>
         </is>
       </c>
       <c r="C20" t="n">
@@ -2904,7 +2904,7 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>2026-07-11 08:35:53 PM PT</t>
+          <t>2026-07-11 08:37:53 PM PT</t>
         </is>
       </c>
       <c r="C21" t="n">
@@ -3018,7 +3018,7 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>2026-07-11 08:35:53 PM PT</t>
+          <t>2026-07-11 08:37:53 PM PT</t>
         </is>
       </c>
       <c r="C22" t="n">
@@ -3132,7 +3132,7 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>2026-07-11 08:35:54 PM PT</t>
+          <t>2026-07-11 08:37:54 PM PT</t>
         </is>
       </c>
       <c r="C23" t="n">
@@ -3145,7 +3145,7 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Top 8 | 2 out</t>
+          <t>Bottom 8 | 0 out</t>
         </is>
       </c>
       <c r="F23" t="n">
@@ -3153,17 +3153,17 @@
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Top</t>
+          <t>Bottom</t>
         </is>
       </c>
       <c r="H23" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="I23" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J23" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="K23" t="inlineStr">
         <is>
@@ -3255,7 +3255,7 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>2026-07-11 08:35:53 PM PT</t>
+          <t>2026-07-11 08:37:54 PM PT</t>
         </is>
       </c>
       <c r="C24" t="n">
@@ -3369,7 +3369,7 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>2026-07-11 08:35:53 PM PT</t>
+          <t>2026-07-11 08:37:53 PM PT</t>
         </is>
       </c>
       <c r="C25" t="n">
@@ -3483,7 +3483,7 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>2026-07-11 08:35:54 PM PT</t>
+          <t>2026-07-11 08:37:54 PM PT</t>
         </is>
       </c>
       <c r="C26" t="n">
@@ -3597,7 +3597,7 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>2026-07-11 08:35:52 PM PT</t>
+          <t>2026-07-11 08:37:52 PM PT</t>
         </is>
       </c>
       <c r="C27" t="n">
@@ -3711,7 +3711,7 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>2026-07-11 08:35:53 PM PT</t>
+          <t>2026-07-11 08:37:53 PM PT</t>
         </is>
       </c>
       <c r="C28" t="n">
@@ -3825,7 +3825,7 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>2026-07-11 08:35:53 PM PT</t>
+          <t>2026-07-11 08:37:53 PM PT</t>
         </is>
       </c>
       <c r="C29" t="n">
@@ -3939,7 +3939,7 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>2026-07-11 08:35:54 PM PT</t>
+          <t>2026-07-11 08:37:54 PM PT</t>
         </is>
       </c>
       <c r="C30" t="n">
@@ -4053,7 +4053,7 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>2026-07-11 08:35:54 PM PT</t>
+          <t>2026-07-11 08:37:54 PM PT</t>
         </is>
       </c>
       <c r="C31" t="n">
@@ -4167,7 +4167,7 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>2026-07-11 08:35:53 PM PT</t>
+          <t>2026-07-11 08:37:53 PM PT</t>
         </is>
       </c>
       <c r="C32" t="n">
@@ -4281,7 +4281,7 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>2026-07-11 08:35:53 PM PT</t>
+          <t>2026-07-11 08:37:53 PM PT</t>
         </is>
       </c>
       <c r="C33" t="n">
@@ -4395,7 +4395,7 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>2026-07-11 08:35:53 PM PT</t>
+          <t>2026-07-11 08:37:54 PM PT</t>
         </is>
       </c>
       <c r="C34" t="n">
@@ -4509,7 +4509,7 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>2026-07-11 08:35:52 PM PT</t>
+          <t>2026-07-11 08:37:52 PM PT</t>
         </is>
       </c>
       <c r="C35" t="n">
@@ -4623,7 +4623,7 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>2026-07-11 08:35:52 PM PT</t>
+          <t>2026-07-11 08:37:52 PM PT</t>
         </is>
       </c>
       <c r="C36" t="n">
@@ -4737,7 +4737,7 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>2026-07-11 08:35:54 PM PT</t>
+          <t>2026-07-11 08:37:54 PM PT</t>
         </is>
       </c>
       <c r="C37" t="n">
@@ -4765,7 +4765,7 @@
         <v>1</v>
       </c>
       <c r="I37" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="J37" t="n">
         <v>0</v>
@@ -4860,7 +4860,7 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>2026-07-11 08:35:53 PM PT</t>
+          <t>2026-07-11 08:37:53 PM PT</t>
         </is>
       </c>
       <c r="C38" t="n">
@@ -4974,7 +4974,7 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>2026-07-11 08:35:52 PM PT</t>
+          <t>2026-07-11 08:37:53 PM PT</t>
         </is>
       </c>
       <c r="C39" t="n">
@@ -5088,7 +5088,7 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>2026-07-11 08:35:53 PM PT</t>
+          <t>2026-07-11 08:37:53 PM PT</t>
         </is>
       </c>
       <c r="C40" t="n">
@@ -5202,7 +5202,7 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>2026-07-11 08:35:52 PM PT</t>
+          <t>2026-07-11 08:37:52 PM PT</t>
         </is>
       </c>
       <c r="C41" t="n">
@@ -5316,7 +5316,7 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>2026-07-11 08:35:54 PM PT</t>
+          <t>2026-07-11 08:37:54 PM PT</t>
         </is>
       </c>
       <c r="C42" t="n">
@@ -5329,7 +5329,7 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>Top 8 | 2 out</t>
+          <t>Bottom 8 | 0 out</t>
         </is>
       </c>
       <c r="F42" t="n">
@@ -5337,17 +5337,17 @@
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Top</t>
+          <t>Bottom</t>
         </is>
       </c>
       <c r="H42" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="I42" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J42" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="K42" t="inlineStr">
         <is>
@@ -5439,7 +5439,7 @@
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>2026-07-11 08:35:54 PM PT</t>
+          <t>2026-07-11 08:37:54 PM PT</t>
         </is>
       </c>
       <c r="C43" t="n">
@@ -5553,7 +5553,7 @@
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>2026-07-11 08:35:53 PM PT</t>
+          <t>2026-07-11 08:37:54 PM PT</t>
         </is>
       </c>
       <c r="C44" t="n">
@@ -5667,7 +5667,7 @@
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>2026-07-11 08:35:53 PM PT</t>
+          <t>2026-07-11 08:37:54 PM PT</t>
         </is>
       </c>
       <c r="C45" t="n">
@@ -5781,7 +5781,7 @@
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>2026-07-11 08:35:54 PM PT</t>
+          <t>2026-07-11 08:37:54 PM PT</t>
         </is>
       </c>
       <c r="C46" t="n">
@@ -5895,7 +5895,7 @@
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>2026-07-11 08:35:53 PM PT</t>
+          <t>2026-07-11 08:37:53 PM PT</t>
         </is>
       </c>
       <c r="C47" t="n">
@@ -6009,7 +6009,7 @@
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>2026-07-11 08:35:53 PM PT</t>
+          <t>2026-07-11 08:37:53 PM PT</t>
         </is>
       </c>
       <c r="C48" t="n">
@@ -6123,7 +6123,7 @@
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>2026-07-11 08:35:53 PM PT</t>
+          <t>2026-07-11 08:37:54 PM PT</t>
         </is>
       </c>
       <c r="C49" t="n">
@@ -6237,7 +6237,7 @@
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>2026-07-11 08:35:53 PM PT</t>
+          <t>2026-07-11 08:37:53 PM PT</t>
         </is>
       </c>
       <c r="C50" t="n">
@@ -6351,7 +6351,7 @@
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>2026-07-11 08:35:52 PM PT</t>
+          <t>2026-07-11 08:37:52 PM PT</t>
         </is>
       </c>
       <c r="C51" t="n">
@@ -6465,7 +6465,7 @@
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>2026-07-11 08:35:54 PM PT</t>
+          <t>2026-07-11 08:37:54 PM PT</t>
         </is>
       </c>
       <c r="C52" t="n">
@@ -6493,7 +6493,7 @@
         <v>1</v>
       </c>
       <c r="I52" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="J52" t="n">
         <v>0</v>
@@ -6588,7 +6588,7 @@
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>2026-07-11 08:35:54 PM PT</t>
+          <t>2026-07-11 08:37:54 PM PT</t>
         </is>
       </c>
       <c r="C53" t="n">
@@ -6601,7 +6601,7 @@
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>Top 8 | 2 out</t>
+          <t>Bottom 8 | 0 out</t>
         </is>
       </c>
       <c r="F53" t="n">
@@ -6609,17 +6609,17 @@
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Top</t>
+          <t>Bottom</t>
         </is>
       </c>
       <c r="H53" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="I53" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J53" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="K53" t="inlineStr">
         <is>
@@ -6655,10 +6655,10 @@
         </is>
       </c>
       <c r="R53" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="S53" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="T53" t="n">
         <v>0</v>
@@ -6711,7 +6711,7 @@
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>2026-07-11 08:35:54 PM PT</t>
+          <t>2026-07-11 08:37:54 PM PT</t>
         </is>
       </c>
       <c r="C54" t="n">
@@ -6825,7 +6825,7 @@
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>2026-07-11 08:35:54 PM PT</t>
+          <t>2026-07-11 08:37:54 PM PT</t>
         </is>
       </c>
       <c r="C55" t="n">
@@ -6939,7 +6939,7 @@
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>2026-07-11 08:35:53 PM PT</t>
+          <t>2026-07-11 08:37:53 PM PT</t>
         </is>
       </c>
       <c r="C56" t="n">
@@ -7053,7 +7053,7 @@
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>2026-07-11 08:35:52 PM PT</t>
+          <t>2026-07-11 08:37:53 PM PT</t>
         </is>
       </c>
       <c r="C57" t="n">
@@ -7167,7 +7167,7 @@
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>2026-07-11 08:35:52 PM PT</t>
+          <t>2026-07-11 08:37:53 PM PT</t>
         </is>
       </c>
       <c r="C58" t="n">
@@ -7281,7 +7281,7 @@
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>2026-07-11 08:35:52 PM PT</t>
+          <t>2026-07-11 08:37:53 PM PT</t>
         </is>
       </c>
       <c r="C59" t="n">
@@ -7395,7 +7395,7 @@
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>2026-07-11 08:35:53 PM PT</t>
+          <t>2026-07-11 08:37:53 PM PT</t>
         </is>
       </c>
       <c r="C60" t="n">
@@ -7509,7 +7509,7 @@
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>2026-07-11 08:35:53 PM PT</t>
+          <t>2026-07-11 08:37:53 PM PT</t>
         </is>
       </c>
       <c r="C61" t="n">
@@ -7623,7 +7623,7 @@
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>2026-07-11 08:35:52 PM PT</t>
+          <t>2026-07-11 08:37:53 PM PT</t>
         </is>
       </c>
       <c r="C62" t="n">
@@ -7737,7 +7737,7 @@
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>2026-07-11 08:35:52 PM PT</t>
+          <t>2026-07-11 08:37:52 PM PT</t>
         </is>
       </c>
       <c r="C63" t="n">
@@ -7851,7 +7851,7 @@
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>2026-07-11 08:35:52 PM PT</t>
+          <t>2026-07-11 08:37:52 PM PT</t>
         </is>
       </c>
       <c r="C64" t="n">
@@ -7965,7 +7965,7 @@
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>2026-07-11 08:35:54 PM PT</t>
+          <t>2026-07-11 08:37:54 PM PT</t>
         </is>
       </c>
       <c r="C65" t="n">
@@ -7993,7 +7993,7 @@
         <v>1</v>
       </c>
       <c r="I65" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="J65" t="n">
         <v>0</v>
@@ -8088,7 +8088,7 @@
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>2026-07-11 08:35:54 PM PT</t>
+          <t>2026-07-11 08:37:54 PM PT</t>
         </is>
       </c>
       <c r="C66" t="n">
@@ -8101,7 +8101,7 @@
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>Top 8 | 2 out</t>
+          <t>Bottom 8 | 0 out</t>
         </is>
       </c>
       <c r="F66" t="n">
@@ -8109,17 +8109,17 @@
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>Top</t>
+          <t>Bottom</t>
         </is>
       </c>
       <c r="H66" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="I66" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J66" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="K66" t="inlineStr">
         <is>
@@ -8211,7 +8211,7 @@
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>2026-07-11 08:35:53 PM PT</t>
+          <t>2026-07-11 08:37:53 PM PT</t>
         </is>
       </c>
       <c r="C67" t="n">
@@ -8325,7 +8325,7 @@
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>2026-07-11 08:35:53 PM PT</t>
+          <t>2026-07-11 08:37:53 PM PT</t>
         </is>
       </c>
       <c r="C68" t="n">
@@ -8439,7 +8439,7 @@
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>2026-07-11 08:35:53 PM PT</t>
+          <t>2026-07-11 08:37:53 PM PT</t>
         </is>
       </c>
       <c r="C69" t="n">
@@ -8553,7 +8553,7 @@
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>2026-07-11 08:35:53 PM PT</t>
+          <t>2026-07-11 08:37:53 PM PT</t>
         </is>
       </c>
       <c r="C70" t="n">
@@ -8667,7 +8667,7 @@
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>2026-07-11 08:35:52 PM PT</t>
+          <t>2026-07-11 08:37:53 PM PT</t>
         </is>
       </c>
       <c r="C71" t="n">
@@ -8781,7 +8781,7 @@
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>2026-07-11 08:35:54 PM PT</t>
+          <t>2026-07-11 08:37:54 PM PT</t>
         </is>
       </c>
       <c r="C72" t="n">
@@ -8794,7 +8794,7 @@
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>Top 8 | 2 out</t>
+          <t>Bottom 8 | 0 out</t>
         </is>
       </c>
       <c r="F72" t="n">
@@ -8802,17 +8802,17 @@
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>Top</t>
+          <t>Bottom</t>
         </is>
       </c>
       <c r="H72" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="I72" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J72" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="K72" t="inlineStr">
         <is>
@@ -8904,7 +8904,7 @@
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>2026-07-11 08:35:52 PM PT</t>
+          <t>2026-07-11 08:37:52 PM PT</t>
         </is>
       </c>
       <c r="C73" t="n">
@@ -9018,7 +9018,7 @@
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>2026-07-11 08:35:53 PM PT</t>
+          <t>2026-07-11 08:37:53 PM PT</t>
         </is>
       </c>
       <c r="C74" t="n">
@@ -9132,7 +9132,7 @@
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>2026-07-11 08:35:52 PM PT</t>
+          <t>2026-07-11 08:37:52 PM PT</t>
         </is>
       </c>
       <c r="C75" t="n">
@@ -9246,7 +9246,7 @@
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>2026-07-11 08:35:54 PM PT</t>
+          <t>2026-07-11 08:37:54 PM PT</t>
         </is>
       </c>
       <c r="C76" t="n">
@@ -9274,7 +9274,7 @@
         <v>1</v>
       </c>
       <c r="I76" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="J76" t="n">
         <v>0</v>
@@ -9369,7 +9369,7 @@
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>2026-07-11 08:35:54 PM PT</t>
+          <t>2026-07-11 08:37:54 PM PT</t>
         </is>
       </c>
       <c r="C77" t="n">
@@ -9483,7 +9483,7 @@
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>2026-07-11 08:35:54 PM PT</t>
+          <t>2026-07-11 08:37:54 PM PT</t>
         </is>
       </c>
       <c r="C78" t="n">
@@ -9597,7 +9597,7 @@
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>2026-07-11 08:35:53 PM PT</t>
+          <t>2026-07-11 08:37:53 PM PT</t>
         </is>
       </c>
       <c r="C79" t="n">
@@ -9711,7 +9711,7 @@
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>2026-07-11 08:35:52 PM PT</t>
+          <t>2026-07-11 08:37:52 PM PT</t>
         </is>
       </c>
       <c r="C80" t="n">
@@ -9825,7 +9825,7 @@
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>2026-07-11 08:35:52 PM PT</t>
+          <t>2026-07-11 08:37:52 PM PT</t>
         </is>
       </c>
       <c r="C81" t="n">
@@ -9939,7 +9939,7 @@
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>2026-07-11 08:35:52 PM PT</t>
+          <t>2026-07-11 08:37:52 PM PT</t>
         </is>
       </c>
       <c r="C82" t="n">
@@ -10053,7 +10053,7 @@
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>2026-07-11 08:35:52 PM PT</t>
+          <t>2026-07-11 08:37:52 PM PT</t>
         </is>
       </c>
       <c r="C83" t="n">
@@ -10167,7 +10167,7 @@
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>2026-07-11 08:35:52 PM PT</t>
+          <t>2026-07-11 08:37:52 PM PT</t>
         </is>
       </c>
       <c r="C84" t="n">
@@ -10281,7 +10281,7 @@
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>2026-07-11 08:35:52 PM PT</t>
+          <t>2026-07-11 08:37:52 PM PT</t>
         </is>
       </c>
       <c r="C85" t="n">
@@ -10395,7 +10395,7 @@
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>2026-07-11 08:35:53 PM PT</t>
+          <t>2026-07-11 08:37:53 PM PT</t>
         </is>
       </c>
       <c r="C86" t="n">
@@ -10509,7 +10509,7 @@
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>2026-07-11 08:35:53 PM PT</t>
+          <t>2026-07-11 08:37:53 PM PT</t>
         </is>
       </c>
       <c r="C87" t="n">
@@ -10623,7 +10623,7 @@
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>2026-07-11 08:35:53 PM PT</t>
+          <t>2026-07-11 08:37:53 PM PT</t>
         </is>
       </c>
       <c r="C88" t="n">
@@ -10737,7 +10737,7 @@
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>2026-07-11 08:35:53 PM PT</t>
+          <t>2026-07-11 08:37:53 PM PT</t>
         </is>
       </c>
       <c r="C89" t="n">
@@ -10851,7 +10851,7 @@
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>2026-07-11 08:35:54 PM PT</t>
+          <t>2026-07-11 08:37:54 PM PT</t>
         </is>
       </c>
       <c r="C90" t="n">
@@ -10879,7 +10879,7 @@
         <v>1</v>
       </c>
       <c r="I90" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="J90" t="n">
         <v>0</v>
@@ -10974,7 +10974,7 @@
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>2026-07-11 08:35:53 PM PT</t>
+          <t>2026-07-11 08:37:53 PM PT</t>
         </is>
       </c>
       <c r="C91" t="n">
@@ -11088,7 +11088,7 @@
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>2026-07-11 08:35:54 PM PT</t>
+          <t>2026-07-11 08:37:54 PM PT</t>
         </is>
       </c>
       <c r="C92" t="n">
@@ -11202,7 +11202,7 @@
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>2026-07-11 08:35:54 PM PT</t>
+          <t>2026-07-11 08:37:54 PM PT</t>
         </is>
       </c>
       <c r="C93" t="n">
@@ -11215,7 +11215,7 @@
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>Top 8 | 2 out</t>
+          <t>Bottom 8 | 0 out</t>
         </is>
       </c>
       <c r="F93" t="n">
@@ -11223,17 +11223,17 @@
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>Top</t>
+          <t>Bottom</t>
         </is>
       </c>
       <c r="H93" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="I93" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J93" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="K93" t="inlineStr">
         <is>
@@ -11325,7 +11325,7 @@
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>2026-07-11 08:35:53 PM PT</t>
+          <t>2026-07-11 08:37:53 PM PT</t>
         </is>
       </c>
       <c r="C94" t="n">
@@ -11439,7 +11439,7 @@
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>2026-07-11 08:35:53 PM PT</t>
+          <t>2026-07-11 08:37:53 PM PT</t>
         </is>
       </c>
       <c r="C95" t="n">
@@ -11553,7 +11553,7 @@
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>2026-07-11 08:35:53 PM PT</t>
+          <t>2026-07-11 08:37:53 PM PT</t>
         </is>
       </c>
       <c r="C96" t="n">
@@ -11667,7 +11667,7 @@
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>2026-07-11 08:35:53 PM PT</t>
+          <t>2026-07-11 08:37:54 PM PT</t>
         </is>
       </c>
       <c r="C97" t="n">
@@ -11781,7 +11781,7 @@
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>2026-07-11 08:35:53 PM PT</t>
+          <t>2026-07-11 08:37:54 PM PT</t>
         </is>
       </c>
       <c r="C98" t="n">
@@ -11895,7 +11895,7 @@
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>2026-07-11 08:35:54 PM PT</t>
+          <t>2026-07-11 08:37:54 PM PT</t>
         </is>
       </c>
       <c r="C99" t="n">
@@ -11908,7 +11908,7 @@
       </c>
       <c r="E99" t="inlineStr">
         <is>
-          <t>Top 8 | 2 out</t>
+          <t>Bottom 8 | 0 out</t>
         </is>
       </c>
       <c r="F99" t="n">
@@ -11916,17 +11916,17 @@
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>Top</t>
+          <t>Bottom</t>
         </is>
       </c>
       <c r="H99" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="I99" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J99" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="K99" t="inlineStr">
         <is>
@@ -12018,7 +12018,7 @@
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>2026-07-11 08:35:53 PM PT</t>
+          <t>2026-07-11 08:37:53 PM PT</t>
         </is>
       </c>
       <c r="C100" t="n">
@@ -12132,7 +12132,7 @@
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>2026-07-11 08:35:52 PM PT</t>
+          <t>2026-07-11 08:37:52 PM PT</t>
         </is>
       </c>
       <c r="C101" t="n">
@@ -12246,7 +12246,7 @@
       </c>
       <c r="B102" t="inlineStr">
         <is>
-          <t>2026-07-11 08:35:52 PM PT</t>
+          <t>2026-07-11 08:37:53 PM PT</t>
         </is>
       </c>
       <c r="C102" t="n">
@@ -12360,7 +12360,7 @@
       </c>
       <c r="B103" t="inlineStr">
         <is>
-          <t>2026-07-11 08:35:53 PM PT</t>
+          <t>2026-07-11 08:37:53 PM PT</t>
         </is>
       </c>
       <c r="C103" t="n">
@@ -12474,7 +12474,7 @@
       </c>
       <c r="B104" t="inlineStr">
         <is>
-          <t>2026-07-11 08:35:54 PM PT</t>
+          <t>2026-07-11 08:37:54 PM PT</t>
         </is>
       </c>
       <c r="C104" t="n">
@@ -12502,7 +12502,7 @@
         <v>1</v>
       </c>
       <c r="I104" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="J104" t="n">
         <v>0</v>
@@ -12597,7 +12597,7 @@
       </c>
       <c r="B105" t="inlineStr">
         <is>
-          <t>2026-07-11 08:35:53 PM PT</t>
+          <t>2026-07-11 08:37:53 PM PT</t>
         </is>
       </c>
       <c r="C105" t="n">
@@ -12711,7 +12711,7 @@
       </c>
       <c r="B106" t="inlineStr">
         <is>
-          <t>2026-07-11 08:35:53 PM PT</t>
+          <t>2026-07-11 08:37:53 PM PT</t>
         </is>
       </c>
       <c r="C106" t="n">
@@ -12825,7 +12825,7 @@
       </c>
       <c r="B107" t="inlineStr">
         <is>
-          <t>2026-07-11 08:35:53 PM PT</t>
+          <t>2026-07-11 08:37:53 PM PT</t>
         </is>
       </c>
       <c r="C107" t="n">
@@ -12939,7 +12939,7 @@
       </c>
       <c r="B108" t="inlineStr">
         <is>
-          <t>2026-07-11 08:35:53 PM PT</t>
+          <t>2026-07-11 08:37:53 PM PT</t>
         </is>
       </c>
       <c r="C108" t="n">
@@ -13053,7 +13053,7 @@
       </c>
       <c r="B109" t="inlineStr">
         <is>
-          <t>2026-07-11 08:35:53 PM PT</t>
+          <t>2026-07-11 08:37:53 PM PT</t>
         </is>
       </c>
       <c r="C109" t="n">
@@ -13167,7 +13167,7 @@
       </c>
       <c r="B110" t="inlineStr">
         <is>
-          <t>2026-07-11 08:35:53 PM PT</t>
+          <t>2026-07-11 08:37:53 PM PT</t>
         </is>
       </c>
       <c r="C110" t="n">
@@ -13281,7 +13281,7 @@
       </c>
       <c r="B111" t="inlineStr">
         <is>
-          <t>2026-07-11 08:35:53 PM PT</t>
+          <t>2026-07-11 08:37:53 PM PT</t>
         </is>
       </c>
       <c r="C111" t="n">
@@ -13395,7 +13395,7 @@
       </c>
       <c r="B112" t="inlineStr">
         <is>
-          <t>2026-07-11 08:35:54 PM PT</t>
+          <t>2026-07-11 08:37:54 PM PT</t>
         </is>
       </c>
       <c r="C112" t="n">
@@ -13509,7 +13509,7 @@
       </c>
       <c r="B113" t="inlineStr">
         <is>
-          <t>2026-07-11 08:35:53 PM PT</t>
+          <t>2026-07-11 08:37:53 PM PT</t>
         </is>
       </c>
       <c r="C113" t="n">
@@ -13623,7 +13623,7 @@
       </c>
       <c r="B114" t="inlineStr">
         <is>
-          <t>2026-07-11 08:35:53 PM PT</t>
+          <t>2026-07-11 08:37:53 PM PT</t>
         </is>
       </c>
       <c r="C114" t="n">
@@ -13737,7 +13737,7 @@
       </c>
       <c r="B115" t="inlineStr">
         <is>
-          <t>2026-07-11 08:35:53 PM PT</t>
+          <t>2026-07-11 08:37:53 PM PT</t>
         </is>
       </c>
       <c r="C115" t="n">
@@ -13851,7 +13851,7 @@
       </c>
       <c r="B116" t="inlineStr">
         <is>
-          <t>2026-07-11 08:35:54 PM PT</t>
+          <t>2026-07-11 08:37:54 PM PT</t>
         </is>
       </c>
       <c r="C116" t="n">
@@ -13879,7 +13879,7 @@
         <v>1</v>
       </c>
       <c r="I116" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="J116" t="n">
         <v>0</v>
@@ -13974,30 +13974,39 @@
       </c>
       <c r="B117" t="inlineStr">
         <is>
-          <t>2026-07-11 08:35:53 PM PT</t>
+          <t>2026-07-11 08:37:54 PM PT</t>
         </is>
       </c>
       <c r="C117" t="n">
-        <v>822875</v>
+        <v>823276</v>
       </c>
       <c r="D117" t="inlineStr">
         <is>
-          <t>4:05 PM PT</t>
+          <t>5:40 PM PT</t>
         </is>
       </c>
       <c r="E117" t="inlineStr">
         <is>
-          <t>Final</t>
+          <t>Bottom 8 | 1 out</t>
         </is>
       </c>
       <c r="F117" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="G117" t="inlineStr">
         <is>
           <t>Bottom</t>
         </is>
       </c>
+      <c r="H117" t="n">
+        <v>1</v>
+      </c>
+      <c r="I117" t="n">
+        <v>0</v>
+      </c>
+      <c r="J117" t="n">
+        <v>0</v>
+      </c>
       <c r="K117" t="inlineStr">
         <is>
           <t>Home</t>
@@ -14005,43 +14014,43 @@
       </c>
       <c r="L117" t="inlineStr">
         <is>
-          <t>TEX</t>
+          <t>SD</t>
         </is>
       </c>
       <c r="M117" t="inlineStr">
         <is>
-          <t>HOU</t>
+          <t>TOR</t>
         </is>
       </c>
       <c r="N117" t="inlineStr">
         <is>
-          <t>Evan Carter</t>
+          <t>Xander Bogaerts</t>
         </is>
       </c>
       <c r="O117" t="n">
-        <v>694497</v>
+        <v>593428</v>
       </c>
       <c r="P117" t="inlineStr">
         <is>
-          <t>CF</t>
+          <t>SS</t>
         </is>
       </c>
       <c r="Q117" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>3</t>
         </is>
       </c>
       <c r="R117" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="S117" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="T117" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="U117" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="V117" t="n">
         <v>0</v>
@@ -14058,8 +14067,8 @@
       <c r="Z117" t="n">
         <v>0</v>
       </c>
-      <c r="AA117" t="n">
-        <v>0</v>
+      <c r="AA117" s="5" t="n">
+        <v>3</v>
       </c>
       <c r="AB117" t="n">
         <v>0</v>
@@ -14074,10 +14083,10 @@
         <v>6</v>
       </c>
       <c r="AF117" t="n">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="AG117" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
     </row>
     <row r="118">
@@ -14088,15 +14097,15 @@
       </c>
       <c r="B118" t="inlineStr">
         <is>
-          <t>2026-07-11 08:35:54 PM PT</t>
+          <t>2026-07-11 08:37:54 PM PT</t>
         </is>
       </c>
       <c r="C118" t="n">
-        <v>823030</v>
+        <v>822875</v>
       </c>
       <c r="D118" t="inlineStr">
         <is>
-          <t>4:15 PM PT</t>
+          <t>4:05 PM PT</t>
         </is>
       </c>
       <c r="E118" t="inlineStr">
@@ -14109,89 +14118,89 @@
       </c>
       <c r="G118" t="inlineStr">
         <is>
-          <t>Top</t>
+          <t>Bottom</t>
         </is>
       </c>
       <c r="K118" t="inlineStr">
         <is>
-          <t>Away</t>
+          <t>Home</t>
         </is>
       </c>
       <c r="L118" t="inlineStr">
         <is>
-          <t>ATL</t>
+          <t>TEX</t>
         </is>
       </c>
       <c r="M118" t="inlineStr">
         <is>
-          <t>STL</t>
+          <t>HOU</t>
         </is>
       </c>
       <c r="N118" t="inlineStr">
         <is>
-          <t>Drake Baldwin</t>
+          <t>Evan Carter</t>
         </is>
       </c>
       <c r="O118" t="n">
-        <v>686948</v>
+        <v>694497</v>
       </c>
       <c r="P118" t="inlineStr">
         <is>
-          <t>DH</t>
+          <t>CF</t>
         </is>
       </c>
       <c r="Q118" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>7</t>
         </is>
       </c>
       <c r="R118" t="n">
         <v>4</v>
       </c>
       <c r="S118" t="n">
+        <v>4</v>
+      </c>
+      <c r="T118" t="n">
+        <v>2</v>
+      </c>
+      <c r="U118" t="n">
+        <v>2</v>
+      </c>
+      <c r="V118" t="n">
+        <v>0</v>
+      </c>
+      <c r="W118" t="n">
+        <v>0</v>
+      </c>
+      <c r="X118" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y118" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z118" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA118" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB118" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC118" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD118" t="n">
+        <v>1</v>
+      </c>
+      <c r="AE118" s="4" t="n">
+        <v>6</v>
+      </c>
+      <c r="AF118" t="n">
         <v>3</v>
       </c>
-      <c r="T118" t="n">
-        <v>1</v>
-      </c>
-      <c r="U118" t="n">
-        <v>1</v>
-      </c>
-      <c r="V118" t="n">
-        <v>0</v>
-      </c>
-      <c r="W118" t="n">
-        <v>0</v>
-      </c>
-      <c r="X118" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y118" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z118" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA118" s="5" t="n">
-        <v>1</v>
-      </c>
-      <c r="AB118" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC118" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD118" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE118" s="4" t="n">
-        <v>5</v>
-      </c>
-      <c r="AF118" t="n">
-        <v>1</v>
-      </c>
       <c r="AG118" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
     </row>
     <row r="119">
@@ -14202,7 +14211,7 @@
       </c>
       <c r="B119" t="inlineStr">
         <is>
-          <t>2026-07-11 08:35:54 PM PT</t>
+          <t>2026-07-11 08:37:54 PM PT</t>
         </is>
       </c>
       <c r="C119" t="n">
@@ -14243,24 +14252,24 @@
       </c>
       <c r="N119" t="inlineStr">
         <is>
-          <t>Eli White</t>
+          <t>Drake Baldwin</t>
         </is>
       </c>
       <c r="O119" t="n">
-        <v>642201</v>
+        <v>686948</v>
       </c>
       <c r="P119" t="inlineStr">
         <is>
-          <t>RF</t>
+          <t>DH</t>
         </is>
       </c>
       <c r="Q119" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>4</t>
         </is>
       </c>
       <c r="R119" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="S119" t="n">
         <v>3</v>
@@ -14269,10 +14278,10 @@
         <v>1</v>
       </c>
       <c r="U119" t="n">
-        <v>0</v>
-      </c>
-      <c r="V119" s="7" t="n">
-        <v>1</v>
+        <v>1</v>
+      </c>
+      <c r="V119" t="n">
+        <v>0</v>
       </c>
       <c r="W119" t="n">
         <v>0</v>
@@ -14286,8 +14295,8 @@
       <c r="Z119" t="n">
         <v>0</v>
       </c>
-      <c r="AA119" t="n">
-        <v>0</v>
+      <c r="AA119" s="5" t="n">
+        <v>1</v>
       </c>
       <c r="AB119" t="n">
         <v>0</v>
@@ -14316,15 +14325,15 @@
       </c>
       <c r="B120" t="inlineStr">
         <is>
-          <t>2026-07-11 08:35:53 PM PT</t>
+          <t>2026-07-11 08:37:54 PM PT</t>
         </is>
       </c>
       <c r="C120" t="n">
-        <v>824813</v>
+        <v>823030</v>
       </c>
       <c r="D120" t="inlineStr">
         <is>
-          <t>4:05 PM PT</t>
+          <t>4:15 PM PT</t>
         </is>
       </c>
       <c r="E120" t="inlineStr">
@@ -14342,35 +14351,35 @@
       </c>
       <c r="K120" t="inlineStr">
         <is>
-          <t>Home</t>
+          <t>Away</t>
         </is>
       </c>
       <c r="L120" t="inlineStr">
         <is>
-          <t>BAL</t>
+          <t>ATL</t>
         </is>
       </c>
       <c r="M120" t="inlineStr">
         <is>
-          <t>KC</t>
+          <t>STL</t>
         </is>
       </c>
       <c r="N120" t="inlineStr">
         <is>
-          <t>Samuel Basallo</t>
+          <t>Eli White</t>
         </is>
       </c>
       <c r="O120" t="n">
-        <v>694212</v>
+        <v>642201</v>
       </c>
       <c r="P120" t="inlineStr">
         <is>
-          <t>DH</t>
+          <t>RF</t>
         </is>
       </c>
       <c r="Q120" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>7</t>
         </is>
       </c>
       <c r="R120" t="n">
@@ -14383,10 +14392,10 @@
         <v>1</v>
       </c>
       <c r="U120" t="n">
-        <v>1</v>
-      </c>
-      <c r="V120" t="n">
-        <v>0</v>
+        <v>0</v>
+      </c>
+      <c r="V120" s="7" t="n">
+        <v>1</v>
       </c>
       <c r="W120" t="n">
         <v>0</v>
@@ -14398,7 +14407,7 @@
         <v>0</v>
       </c>
       <c r="Z120" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AA120" t="n">
         <v>0</v>
@@ -14410,13 +14419,13 @@
         <v>0</v>
       </c>
       <c r="AD120" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AE120" s="4" t="n">
         <v>5</v>
       </c>
       <c r="AF120" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="AG120" t="n">
         <v>6</v>
@@ -14430,15 +14439,15 @@
       </c>
       <c r="B121" t="inlineStr">
         <is>
-          <t>2026-07-11 08:35:53 PM PT</t>
+          <t>2026-07-11 08:37:54 PM PT</t>
         </is>
       </c>
       <c r="C121" t="n">
-        <v>823603</v>
+        <v>824813</v>
       </c>
       <c r="D121" t="inlineStr">
         <is>
-          <t>1:10 PM PT</t>
+          <t>4:05 PM PT</t>
         </is>
       </c>
       <c r="E121" t="inlineStr">
@@ -14451,56 +14460,56 @@
       </c>
       <c r="G121" t="inlineStr">
         <is>
-          <t>Bottom</t>
+          <t>Top</t>
         </is>
       </c>
       <c r="K121" t="inlineStr">
         <is>
-          <t>Away</t>
+          <t>Home</t>
         </is>
       </c>
       <c r="L121" t="inlineStr">
         <is>
-          <t>BOS</t>
+          <t>BAL</t>
         </is>
       </c>
       <c r="M121" t="inlineStr">
         <is>
-          <t>NYM</t>
+          <t>KC</t>
         </is>
       </c>
       <c r="N121" t="inlineStr">
         <is>
-          <t>Ceddanne Rafaela</t>
+          <t>Samuel Basallo</t>
         </is>
       </c>
       <c r="O121" t="n">
-        <v>678882</v>
+        <v>694212</v>
       </c>
       <c r="P121" t="inlineStr">
         <is>
-          <t>CF</t>
+          <t>DH</t>
         </is>
       </c>
       <c r="Q121" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>5</t>
         </is>
       </c>
       <c r="R121" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="S121" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="T121" t="n">
         <v>1</v>
       </c>
       <c r="U121" t="n">
-        <v>0</v>
-      </c>
-      <c r="V121" s="7" t="n">
-        <v>1</v>
+        <v>1</v>
+      </c>
+      <c r="V121" t="n">
+        <v>0</v>
       </c>
       <c r="W121" t="n">
         <v>0</v>
@@ -14512,7 +14521,7 @@
         <v>0</v>
       </c>
       <c r="Z121" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AA121" t="n">
         <v>0</v>
@@ -14524,13 +14533,13 @@
         <v>0</v>
       </c>
       <c r="AD121" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AE121" s="4" t="n">
         <v>5</v>
       </c>
       <c r="AF121" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="AG121" t="n">
         <v>6</v>
@@ -14544,15 +14553,15 @@
       </c>
       <c r="B122" t="inlineStr">
         <is>
-          <t>2026-07-11 08:35:54 PM PT</t>
+          <t>2026-07-11 08:37:53 PM PT</t>
         </is>
       </c>
       <c r="C122" t="n">
-        <v>824492</v>
+        <v>823603</v>
       </c>
       <c r="D122" t="inlineStr">
         <is>
-          <t>4:10 PM PT</t>
+          <t>1:10 PM PT</t>
         </is>
       </c>
       <c r="E122" t="inlineStr">
@@ -14575,46 +14584,46 @@
       </c>
       <c r="L122" t="inlineStr">
         <is>
-          <t>CHC</t>
+          <t>BOS</t>
         </is>
       </c>
       <c r="M122" t="inlineStr">
         <is>
-          <t>CIN</t>
+          <t>NYM</t>
         </is>
       </c>
       <c r="N122" t="inlineStr">
         <is>
-          <t>Miguel Amaya</t>
+          <t>Ceddanne Rafaela</t>
         </is>
       </c>
       <c r="O122" t="n">
-        <v>665804</v>
+        <v>678882</v>
       </c>
       <c r="P122" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>CF</t>
         </is>
       </c>
       <c r="Q122" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>2</t>
         </is>
       </c>
       <c r="R122" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="S122" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="T122" t="n">
         <v>1</v>
       </c>
       <c r="U122" t="n">
-        <v>1</v>
-      </c>
-      <c r="V122" t="n">
-        <v>0</v>
+        <v>0</v>
+      </c>
+      <c r="V122" s="7" t="n">
+        <v>1</v>
       </c>
       <c r="W122" t="n">
         <v>0</v>
@@ -14623,7 +14632,7 @@
         <v>0</v>
       </c>
       <c r="Y122" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Z122" t="n">
         <v>0</v>
@@ -14638,16 +14647,16 @@
         <v>0</v>
       </c>
       <c r="AD122" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AE122" s="4" t="n">
         <v>5</v>
       </c>
       <c r="AF122" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="AG122" t="n">
-        <v>9</v>
+        <v>6</v>
       </c>
     </row>
     <row r="123">
@@ -14658,15 +14667,15 @@
       </c>
       <c r="B123" t="inlineStr">
         <is>
-          <t>2026-07-11 08:35:53 PM PT</t>
+          <t>2026-07-11 08:37:54 PM PT</t>
         </is>
       </c>
       <c r="C123" t="n">
-        <v>823198</v>
+        <v>824492</v>
       </c>
       <c r="D123" t="inlineStr">
         <is>
-          <t>1:05 PM PT</t>
+          <t>4:10 PM PT</t>
         </is>
       </c>
       <c r="E123" t="inlineStr">
@@ -14679,7 +14688,7 @@
       </c>
       <c r="G123" t="inlineStr">
         <is>
-          <t>Top</t>
+          <t>Bottom</t>
         </is>
       </c>
       <c r="K123" t="inlineStr">
@@ -14689,30 +14698,30 @@
       </c>
       <c r="L123" t="inlineStr">
         <is>
-          <t>COL</t>
+          <t>CHC</t>
         </is>
       </c>
       <c r="M123" t="inlineStr">
         <is>
-          <t>SF</t>
+          <t>CIN</t>
         </is>
       </c>
       <c r="N123" t="inlineStr">
         <is>
-          <t>Hunter Goodman</t>
+          <t>Miguel Amaya</t>
         </is>
       </c>
       <c r="O123" t="n">
-        <v>696100</v>
+        <v>665804</v>
       </c>
       <c r="P123" t="inlineStr">
         <is>
-          <t>DH</t>
+          <t>C</t>
         </is>
       </c>
       <c r="Q123" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>9</t>
         </is>
       </c>
       <c r="R123" t="n">
@@ -14725,10 +14734,10 @@
         <v>1</v>
       </c>
       <c r="U123" t="n">
-        <v>0</v>
-      </c>
-      <c r="V123" s="7" t="n">
-        <v>1</v>
+        <v>1</v>
+      </c>
+      <c r="V123" t="n">
+        <v>0</v>
       </c>
       <c r="W123" t="n">
         <v>0</v>
@@ -14737,7 +14746,7 @@
         <v>0</v>
       </c>
       <c r="Y123" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Z123" t="n">
         <v>0</v>
@@ -14758,10 +14767,10 @@
         <v>5</v>
       </c>
       <c r="AF123" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="AG123" t="n">
-        <v>6</v>
+        <v>9</v>
       </c>
     </row>
     <row r="124">
@@ -14772,15 +14781,15 @@
       </c>
       <c r="B124" t="inlineStr">
         <is>
-          <t>2026-07-11 08:35:53 PM PT</t>
+          <t>2026-07-11 08:37:53 PM PT</t>
         </is>
       </c>
       <c r="C124" t="n">
-        <v>824576</v>
+        <v>823198</v>
       </c>
       <c r="D124" t="inlineStr">
         <is>
-          <t>11:10 AM PT</t>
+          <t>1:05 PM PT</t>
         </is>
       </c>
       <c r="E124" t="inlineStr">
@@ -14798,35 +14807,35 @@
       </c>
       <c r="K124" t="inlineStr">
         <is>
-          <t>Home</t>
+          <t>Away</t>
         </is>
       </c>
       <c r="L124" t="inlineStr">
         <is>
-          <t>CWS</t>
+          <t>COL</t>
         </is>
       </c>
       <c r="M124" t="inlineStr">
         <is>
-          <t>ATH</t>
+          <t>SF</t>
         </is>
       </c>
       <c r="N124" t="inlineStr">
         <is>
-          <t>Randal Grichuk</t>
+          <t>Hunter Goodman</t>
         </is>
       </c>
       <c r="O124" t="n">
-        <v>545341</v>
+        <v>696100</v>
       </c>
       <c r="P124" t="inlineStr">
         <is>
-          <t>LF</t>
+          <t>DH</t>
         </is>
       </c>
       <c r="Q124" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>3</t>
         </is>
       </c>
       <c r="R124" t="n">
@@ -14872,10 +14881,10 @@
         <v>5</v>
       </c>
       <c r="AF124" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AG124" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="125">
@@ -14886,15 +14895,15 @@
       </c>
       <c r="B125" t="inlineStr">
         <is>
-          <t>2026-07-11 08:35:53 PM PT</t>
+          <t>2026-07-11 08:37:53 PM PT</t>
         </is>
       </c>
       <c r="C125" t="n">
-        <v>824249</v>
+        <v>824576</v>
       </c>
       <c r="D125" t="inlineStr">
         <is>
-          <t>3:10 PM PT</t>
+          <t>11:10 AM PT</t>
         </is>
       </c>
       <c r="E125" t="inlineStr">
@@ -14907,7 +14916,7 @@
       </c>
       <c r="G125" t="inlineStr">
         <is>
-          <t>Bottom</t>
+          <t>Top</t>
         </is>
       </c>
       <c r="K125" t="inlineStr">
@@ -14917,46 +14926,46 @@
       </c>
       <c r="L125" t="inlineStr">
         <is>
-          <t>DET</t>
+          <t>CWS</t>
         </is>
       </c>
       <c r="M125" t="inlineStr">
         <is>
-          <t>PHI</t>
+          <t>ATH</t>
         </is>
       </c>
       <c r="N125" t="inlineStr">
         <is>
-          <t>Dillon Dingler</t>
+          <t>Randal Grichuk</t>
         </is>
       </c>
       <c r="O125" t="n">
-        <v>693307</v>
+        <v>545341</v>
       </c>
       <c r="P125" t="inlineStr">
         <is>
-          <t>DH</t>
+          <t>LF</t>
         </is>
       </c>
       <c r="Q125" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>1</t>
         </is>
       </c>
       <c r="R125" t="n">
         <v>4</v>
       </c>
       <c r="S125" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="T125" t="n">
         <v>1</v>
       </c>
       <c r="U125" t="n">
-        <v>1</v>
-      </c>
-      <c r="V125" t="n">
-        <v>0</v>
+        <v>0</v>
+      </c>
+      <c r="V125" s="7" t="n">
+        <v>1</v>
       </c>
       <c r="W125" t="n">
         <v>0</v>
@@ -14973,8 +14982,8 @@
       <c r="AA125" t="n">
         <v>0</v>
       </c>
-      <c r="AB125" s="9" t="n">
-        <v>1</v>
+      <c r="AB125" t="n">
+        <v>0</v>
       </c>
       <c r="AC125" t="n">
         <v>0</v>
@@ -14986,10 +14995,10 @@
         <v>5</v>
       </c>
       <c r="AF125" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AG125" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
     </row>
     <row r="126">
@@ -15000,15 +15009,15 @@
       </c>
       <c r="B126" t="inlineStr">
         <is>
-          <t>2026-07-11 08:35:53 PM PT</t>
+          <t>2026-07-11 08:37:53 PM PT</t>
         </is>
       </c>
       <c r="C126" t="n">
-        <v>822875</v>
+        <v>824249</v>
       </c>
       <c r="D126" t="inlineStr">
         <is>
-          <t>4:05 PM PT</t>
+          <t>3:10 PM PT</t>
         </is>
       </c>
       <c r="E126" t="inlineStr">
@@ -15026,42 +15035,42 @@
       </c>
       <c r="K126" t="inlineStr">
         <is>
-          <t>Away</t>
+          <t>Home</t>
         </is>
       </c>
       <c r="L126" t="inlineStr">
         <is>
-          <t>HOU</t>
+          <t>DET</t>
         </is>
       </c>
       <c r="M126" t="inlineStr">
         <is>
-          <t>TEX</t>
+          <t>PHI</t>
         </is>
       </c>
       <c r="N126" t="inlineStr">
         <is>
-          <t>Jose Altuve</t>
+          <t>Dillon Dingler</t>
         </is>
       </c>
       <c r="O126" t="n">
-        <v>514888</v>
+        <v>693307</v>
       </c>
       <c r="P126" t="inlineStr">
         <is>
-          <t>2B</t>
+          <t>DH</t>
         </is>
       </c>
       <c r="Q126" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>3</t>
         </is>
       </c>
       <c r="R126" t="n">
         <v>4</v>
       </c>
       <c r="S126" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="T126" t="n">
         <v>1</v>
@@ -15079,7 +15088,7 @@
         <v>0</v>
       </c>
       <c r="Y126" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Z126" t="n">
         <v>0</v>
@@ -15087,20 +15096,20 @@
       <c r="AA126" t="n">
         <v>0</v>
       </c>
-      <c r="AB126" t="n">
-        <v>0</v>
+      <c r="AB126" s="9" t="n">
+        <v>1</v>
       </c>
       <c r="AC126" t="n">
         <v>0</v>
       </c>
       <c r="AD126" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AE126" s="4" t="n">
         <v>5</v>
       </c>
       <c r="AF126" t="n">
-        <v>9</v>
+        <v>2</v>
       </c>
       <c r="AG126" t="n">
         <v>10</v>
@@ -15114,7 +15123,7 @@
       </c>
       <c r="B127" t="inlineStr">
         <is>
-          <t>2026-07-11 08:35:53 PM PT</t>
+          <t>2026-07-11 08:37:54 PM PT</t>
         </is>
       </c>
       <c r="C127" t="n">
@@ -15155,20 +15164,20 @@
       </c>
       <c r="N127" t="inlineStr">
         <is>
-          <t>Yainer Diaz</t>
+          <t>Jose Altuve</t>
         </is>
       </c>
       <c r="O127" t="n">
-        <v>673237</v>
+        <v>514888</v>
       </c>
       <c r="P127" t="inlineStr">
         <is>
-          <t>DH</t>
+          <t>2B</t>
         </is>
       </c>
       <c r="Q127" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>5</t>
         </is>
       </c>
       <c r="R127" t="n">
@@ -15181,10 +15190,10 @@
         <v>1</v>
       </c>
       <c r="U127" t="n">
-        <v>0</v>
-      </c>
-      <c r="V127" s="7" t="n">
-        <v>1</v>
+        <v>1</v>
+      </c>
+      <c r="V127" t="n">
+        <v>0</v>
       </c>
       <c r="W127" t="n">
         <v>0</v>
@@ -15193,7 +15202,7 @@
         <v>0</v>
       </c>
       <c r="Y127" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Z127" t="n">
         <v>0</v>
@@ -15228,11 +15237,11 @@
       </c>
       <c r="B128" t="inlineStr">
         <is>
-          <t>2026-07-11 08:35:53 PM PT</t>
+          <t>2026-07-11 08:37:54 PM PT</t>
         </is>
       </c>
       <c r="C128" t="n">
-        <v>824813</v>
+        <v>822875</v>
       </c>
       <c r="D128" t="inlineStr">
         <is>
@@ -15249,7 +15258,7 @@
       </c>
       <c r="G128" t="inlineStr">
         <is>
-          <t>Top</t>
+          <t>Bottom</t>
         </is>
       </c>
       <c r="K128" t="inlineStr">
@@ -15259,30 +15268,30 @@
       </c>
       <c r="L128" t="inlineStr">
         <is>
-          <t>KC</t>
+          <t>HOU</t>
         </is>
       </c>
       <c r="M128" t="inlineStr">
         <is>
-          <t>BAL</t>
+          <t>TEX</t>
         </is>
       </c>
       <c r="N128" t="inlineStr">
         <is>
-          <t>Jac Caglianone</t>
+          <t>Yainer Diaz</t>
         </is>
       </c>
       <c r="O128" t="n">
-        <v>695506</v>
+        <v>673237</v>
       </c>
       <c r="P128" t="inlineStr">
         <is>
-          <t>RF</t>
+          <t>DH</t>
         </is>
       </c>
       <c r="Q128" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>7</t>
         </is>
       </c>
       <c r="R128" t="n">
@@ -15295,10 +15304,10 @@
         <v>1</v>
       </c>
       <c r="U128" t="n">
-        <v>1</v>
-      </c>
-      <c r="V128" t="n">
-        <v>0</v>
+        <v>0</v>
+      </c>
+      <c r="V128" s="7" t="n">
+        <v>1</v>
       </c>
       <c r="W128" t="n">
         <v>0</v>
@@ -15307,7 +15316,7 @@
         <v>0</v>
       </c>
       <c r="Y128" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Z128" t="n">
         <v>0</v>
@@ -15328,10 +15337,10 @@
         <v>5</v>
       </c>
       <c r="AF128" t="n">
-        <v>1</v>
+        <v>9</v>
       </c>
       <c r="AG128" t="n">
-        <v>2</v>
+        <v>10</v>
       </c>
     </row>
     <row r="129">
@@ -15342,77 +15351,68 @@
       </c>
       <c r="B129" t="inlineStr">
         <is>
-          <t>2026-07-11 08:35:54 PM PT</t>
+          <t>2026-07-11 08:37:54 PM PT</t>
         </is>
       </c>
       <c r="C129" t="n">
-        <v>823926</v>
+        <v>824813</v>
       </c>
       <c r="D129" t="inlineStr">
         <is>
-          <t>6:10 PM PT</t>
+          <t>4:05 PM PT</t>
         </is>
       </c>
       <c r="E129" t="inlineStr">
         <is>
-          <t>Top 8 | 2 out</t>
+          <t>Final</t>
         </is>
       </c>
       <c r="F129" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="G129" t="inlineStr">
         <is>
           <t>Top</t>
         </is>
       </c>
-      <c r="H129" t="n">
-        <v>2</v>
-      </c>
-      <c r="I129" t="n">
-        <v>1</v>
-      </c>
-      <c r="J129" t="n">
-        <v>2</v>
-      </c>
       <c r="K129" t="inlineStr">
         <is>
-          <t>Home</t>
+          <t>Away</t>
         </is>
       </c>
       <c r="L129" t="inlineStr">
         <is>
-          <t>LAD</t>
+          <t>KC</t>
         </is>
       </c>
       <c r="M129" t="inlineStr">
         <is>
-          <t>ARI</t>
+          <t>BAL</t>
         </is>
       </c>
       <c r="N129" t="inlineStr">
         <is>
-          <t>Mookie Betts</t>
+          <t>Jac Caglianone</t>
         </is>
       </c>
       <c r="O129" t="n">
-        <v>605141</v>
+        <v>695506</v>
       </c>
       <c r="P129" t="inlineStr">
         <is>
-          <t>SS</t>
+          <t>RF</t>
         </is>
       </c>
       <c r="Q129" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>3</t>
         </is>
       </c>
       <c r="R129" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="S129" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="T129" t="n">
         <v>1</v>
@@ -15430,10 +15430,10 @@
         <v>0</v>
       </c>
       <c r="Y129" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Z129" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AA129" t="n">
         <v>0</v>
@@ -15451,10 +15451,10 @@
         <v>5</v>
       </c>
       <c r="AF129" t="n">
+        <v>1</v>
+      </c>
+      <c r="AG129" t="n">
         <v>2</v>
-      </c>
-      <c r="AG129" t="n">
-        <v>6</v>
       </c>
     </row>
     <row r="130">
@@ -15465,30 +15465,39 @@
       </c>
       <c r="B130" t="inlineStr">
         <is>
-          <t>2026-07-11 08:35:53 PM PT</t>
+          <t>2026-07-11 08:37:54 PM PT</t>
         </is>
       </c>
       <c r="C130" t="n">
-        <v>823844</v>
+        <v>823926</v>
       </c>
       <c r="D130" t="inlineStr">
         <is>
-          <t>1:10 PM PT</t>
+          <t>6:10 PM PT</t>
         </is>
       </c>
       <c r="E130" t="inlineStr">
         <is>
-          <t>Final</t>
+          <t>Bottom 8 | 0 out</t>
         </is>
       </c>
       <c r="F130" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="G130" t="inlineStr">
         <is>
           <t>Bottom</t>
         </is>
       </c>
+      <c r="H130" t="n">
+        <v>0</v>
+      </c>
+      <c r="I130" t="n">
+        <v>0</v>
+      </c>
+      <c r="J130" t="n">
+        <v>0</v>
+      </c>
       <c r="K130" t="inlineStr">
         <is>
           <t>Home</t>
@@ -15496,34 +15505,34 @@
       </c>
       <c r="L130" t="inlineStr">
         <is>
-          <t>MIA</t>
+          <t>LAD</t>
         </is>
       </c>
       <c r="M130" t="inlineStr">
         <is>
-          <t>CLE</t>
+          <t>ARI</t>
         </is>
       </c>
       <c r="N130" t="inlineStr">
         <is>
-          <t>Kyle Stowers</t>
+          <t>Mookie Betts</t>
         </is>
       </c>
       <c r="O130" t="n">
-        <v>669065</v>
+        <v>605141</v>
       </c>
       <c r="P130" t="inlineStr">
         <is>
-          <t>1B</t>
+          <t>SS</t>
         </is>
       </c>
       <c r="Q130" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="R130" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="S130" t="n">
         <v>3</v>
@@ -15547,10 +15556,10 @@
         <v>0</v>
       </c>
       <c r="Z130" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA130" s="5" t="n">
-        <v>1</v>
+        <v>1</v>
+      </c>
+      <c r="AA130" t="n">
+        <v>0</v>
       </c>
       <c r="AB130" t="n">
         <v>0</v>
@@ -15565,10 +15574,10 @@
         <v>5</v>
       </c>
       <c r="AF130" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AG130" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
     </row>
     <row r="131">
@@ -15579,7 +15588,7 @@
       </c>
       <c r="B131" t="inlineStr">
         <is>
-          <t>2026-07-11 08:35:53 PM PT</t>
+          <t>2026-07-11 08:37:53 PM PT</t>
         </is>
       </c>
       <c r="C131" t="n">
@@ -15620,36 +15629,36 @@
       </c>
       <c r="N131" t="inlineStr">
         <is>
-          <t>Heriberto Hernández</t>
+          <t>Kyle Stowers</t>
         </is>
       </c>
       <c r="O131" t="n">
-        <v>681715</v>
+        <v>669065</v>
       </c>
       <c r="P131" t="inlineStr">
         <is>
-          <t>LF</t>
+          <t>1B</t>
         </is>
       </c>
       <c r="Q131" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>3</t>
         </is>
       </c>
       <c r="R131" t="n">
         <v>4</v>
       </c>
       <c r="S131" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="T131" t="n">
         <v>1</v>
       </c>
       <c r="U131" t="n">
-        <v>0</v>
-      </c>
-      <c r="V131" s="7" t="n">
-        <v>1</v>
+        <v>1</v>
+      </c>
+      <c r="V131" t="n">
+        <v>0</v>
       </c>
       <c r="W131" t="n">
         <v>0</v>
@@ -15663,8 +15672,8 @@
       <c r="Z131" t="n">
         <v>0</v>
       </c>
-      <c r="AA131" t="n">
-        <v>0</v>
+      <c r="AA131" s="5" t="n">
+        <v>1</v>
       </c>
       <c r="AB131" t="n">
         <v>0</v>
@@ -15673,7 +15682,7 @@
         <v>0</v>
       </c>
       <c r="AD131" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AE131" s="4" t="n">
         <v>5</v>
@@ -15693,15 +15702,15 @@
       </c>
       <c r="B132" t="inlineStr">
         <is>
-          <t>2026-07-11 08:35:52 PM PT</t>
+          <t>2026-07-11 08:37:53 PM PT</t>
         </is>
       </c>
       <c r="C132" t="n">
-        <v>823356</v>
+        <v>823844</v>
       </c>
       <c r="D132" t="inlineStr">
         <is>
-          <t>1:05 PM PT</t>
+          <t>1:10 PM PT</t>
         </is>
       </c>
       <c r="E132" t="inlineStr">
@@ -15714,56 +15723,56 @@
       </c>
       <c r="G132" t="inlineStr">
         <is>
-          <t>Top</t>
+          <t>Bottom</t>
         </is>
       </c>
       <c r="K132" t="inlineStr">
         <is>
-          <t>Away</t>
+          <t>Home</t>
         </is>
       </c>
       <c r="L132" t="inlineStr">
         <is>
-          <t>MIL</t>
+          <t>MIA</t>
         </is>
       </c>
       <c r="M132" t="inlineStr">
         <is>
-          <t>PIT</t>
+          <t>CLE</t>
         </is>
       </c>
       <c r="N132" t="inlineStr">
         <is>
-          <t>Luis Lara</t>
+          <t>Heriberto Hernández</t>
         </is>
       </c>
       <c r="O132" t="n">
-        <v>800325</v>
+        <v>681715</v>
       </c>
       <c r="P132" t="inlineStr">
         <is>
-          <t>RF</t>
+          <t>LF</t>
         </is>
       </c>
       <c r="Q132" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>5</t>
         </is>
       </c>
       <c r="R132" t="n">
         <v>4</v>
       </c>
       <c r="S132" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="T132" t="n">
         <v>1</v>
       </c>
       <c r="U132" t="n">
-        <v>1</v>
-      </c>
-      <c r="V132" t="n">
-        <v>0</v>
+        <v>0</v>
+      </c>
+      <c r="V132" s="7" t="n">
+        <v>1</v>
       </c>
       <c r="W132" t="n">
         <v>0</v>
@@ -15777,8 +15786,8 @@
       <c r="Z132" t="n">
         <v>0</v>
       </c>
-      <c r="AA132" s="5" t="n">
-        <v>1</v>
+      <c r="AA132" t="n">
+        <v>0</v>
       </c>
       <c r="AB132" t="n">
         <v>0</v>
@@ -15793,7 +15802,7 @@
         <v>5</v>
       </c>
       <c r="AF132" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AG132" t="n">
         <v>7</v>
@@ -15807,15 +15816,15 @@
       </c>
       <c r="B133" t="inlineStr">
         <is>
-          <t>2026-07-11 08:35:52 PM PT</t>
+          <t>2026-07-11 08:37:52 PM PT</t>
         </is>
       </c>
       <c r="C133" t="n">
-        <v>823682</v>
+        <v>823356</v>
       </c>
       <c r="D133" t="inlineStr">
         <is>
-          <t>11:10 AM PT</t>
+          <t>1:05 PM PT</t>
         </is>
       </c>
       <c r="E133" t="inlineStr">
@@ -15833,51 +15842,51 @@
       </c>
       <c r="K133" t="inlineStr">
         <is>
-          <t>Home</t>
+          <t>Away</t>
         </is>
       </c>
       <c r="L133" t="inlineStr">
         <is>
-          <t>MIN</t>
+          <t>MIL</t>
         </is>
       </c>
       <c r="M133" t="inlineStr">
         <is>
-          <t>LAA</t>
+          <t>PIT</t>
         </is>
       </c>
       <c r="N133" t="inlineStr">
         <is>
-          <t>Josh Bell</t>
+          <t>Luis Lara</t>
         </is>
       </c>
       <c r="O133" t="n">
-        <v>605137</v>
+        <v>800325</v>
       </c>
       <c r="P133" t="inlineStr">
         <is>
-          <t>DH</t>
+          <t>RF</t>
         </is>
       </c>
       <c r="Q133" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>7</t>
         </is>
       </c>
       <c r="R133" t="n">
         <v>4</v>
       </c>
       <c r="S133" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="T133" t="n">
         <v>1</v>
       </c>
       <c r="U133" t="n">
-        <v>0</v>
-      </c>
-      <c r="V133" s="7" t="n">
-        <v>1</v>
+        <v>1</v>
+      </c>
+      <c r="V133" t="n">
+        <v>0</v>
       </c>
       <c r="W133" t="n">
         <v>0</v>
@@ -15891,8 +15900,8 @@
       <c r="Z133" t="n">
         <v>0</v>
       </c>
-      <c r="AA133" t="n">
-        <v>0</v>
+      <c r="AA133" s="5" t="n">
+        <v>1</v>
       </c>
       <c r="AB133" t="n">
         <v>0</v>
@@ -15901,16 +15910,16 @@
         <v>0</v>
       </c>
       <c r="AD133" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AE133" s="4" t="n">
         <v>5</v>
       </c>
       <c r="AF133" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="AG133" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
     </row>
     <row r="134">
@@ -15921,7 +15930,7 @@
       </c>
       <c r="B134" t="inlineStr">
         <is>
-          <t>2026-07-11 08:35:52 PM PT</t>
+          <t>2026-07-11 08:37:53 PM PT</t>
         </is>
       </c>
       <c r="C134" t="n">
@@ -15962,36 +15971,36 @@
       </c>
       <c r="N134" t="inlineStr">
         <is>
-          <t>Luke Keaschall</t>
+          <t>Josh Bell</t>
         </is>
       </c>
       <c r="O134" t="n">
-        <v>807712</v>
+        <v>605137</v>
       </c>
       <c r="P134" t="inlineStr">
         <is>
-          <t>CF</t>
+          <t>DH</t>
         </is>
       </c>
       <c r="Q134" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>3</t>
         </is>
       </c>
       <c r="R134" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="S134" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="T134" t="n">
         <v>1</v>
       </c>
       <c r="U134" t="n">
-        <v>1</v>
-      </c>
-      <c r="V134" t="n">
-        <v>0</v>
+        <v>0</v>
+      </c>
+      <c r="V134" s="7" t="n">
+        <v>1</v>
       </c>
       <c r="W134" t="n">
         <v>0</v>
@@ -16003,7 +16012,7 @@
         <v>0</v>
       </c>
       <c r="Z134" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AA134" t="n">
         <v>0</v>
@@ -16035,15 +16044,15 @@
       </c>
       <c r="B135" t="inlineStr">
         <is>
-          <t>2026-07-11 08:35:53 PM PT</t>
+          <t>2026-07-11 08:37:53 PM PT</t>
         </is>
       </c>
       <c r="C135" t="n">
-        <v>822711</v>
+        <v>823682</v>
       </c>
       <c r="D135" t="inlineStr">
         <is>
-          <t>1:05 PM PT</t>
+          <t>11:10 AM PT</t>
         </is>
       </c>
       <c r="E135" t="inlineStr">
@@ -16056,56 +16065,56 @@
       </c>
       <c r="G135" t="inlineStr">
         <is>
-          <t>Bottom</t>
+          <t>Top</t>
         </is>
       </c>
       <c r="K135" t="inlineStr">
         <is>
-          <t>Away</t>
+          <t>Home</t>
         </is>
       </c>
       <c r="L135" t="inlineStr">
         <is>
-          <t>NYY</t>
+          <t>MIN</t>
         </is>
       </c>
       <c r="M135" t="inlineStr">
         <is>
-          <t>WSH</t>
+          <t>LAA</t>
         </is>
       </c>
       <c r="N135" t="inlineStr">
         <is>
-          <t>Cody Bellinger</t>
+          <t>Luke Keaschall</t>
         </is>
       </c>
       <c r="O135" t="n">
-        <v>641355</v>
+        <v>807712</v>
       </c>
       <c r="P135" t="inlineStr">
         <is>
-          <t>LF</t>
+          <t>CF</t>
         </is>
       </c>
       <c r="Q135" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>9</t>
         </is>
       </c>
       <c r="R135" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="S135" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="T135" t="n">
         <v>1</v>
       </c>
       <c r="U135" t="n">
-        <v>0</v>
-      </c>
-      <c r="V135" s="7" t="n">
-        <v>1</v>
+        <v>1</v>
+      </c>
+      <c r="V135" t="n">
+        <v>0</v>
       </c>
       <c r="W135" t="n">
         <v>0</v>
@@ -16117,7 +16126,7 @@
         <v>0</v>
       </c>
       <c r="Z135" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AA135" t="n">
         <v>0</v>
@@ -16135,7 +16144,7 @@
         <v>5</v>
       </c>
       <c r="AF135" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="AG135" t="n">
         <v>9</v>
@@ -16149,15 +16158,15 @@
       </c>
       <c r="B136" t="inlineStr">
         <is>
-          <t>2026-07-11 08:35:52 PM PT</t>
+          <t>2026-07-11 08:37:53 PM PT</t>
         </is>
       </c>
       <c r="C136" t="n">
-        <v>823357</v>
+        <v>822711</v>
       </c>
       <c r="D136" t="inlineStr">
         <is>
-          <t>9:05 AM PT</t>
+          <t>1:05 PM PT</t>
         </is>
       </c>
       <c r="E136" t="inlineStr">
@@ -16170,40 +16179,40 @@
       </c>
       <c r="G136" t="inlineStr">
         <is>
-          <t>Top</t>
+          <t>Bottom</t>
         </is>
       </c>
       <c r="K136" t="inlineStr">
         <is>
-          <t>Home</t>
+          <t>Away</t>
         </is>
       </c>
       <c r="L136" t="inlineStr">
         <is>
-          <t>PIT</t>
+          <t>NYY</t>
         </is>
       </c>
       <c r="M136" t="inlineStr">
         <is>
-          <t>MIL</t>
+          <t>WSH</t>
         </is>
       </c>
       <c r="N136" t="inlineStr">
         <is>
-          <t>Brandon Lowe</t>
+          <t>Cody Bellinger</t>
         </is>
       </c>
       <c r="O136" t="n">
-        <v>664040</v>
+        <v>641355</v>
       </c>
       <c r="P136" t="inlineStr">
         <is>
-          <t>2B</t>
+          <t>LF</t>
         </is>
       </c>
       <c r="Q136" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>5</t>
         </is>
       </c>
       <c r="R136" t="n">
@@ -16216,10 +16225,10 @@
         <v>1</v>
       </c>
       <c r="U136" t="n">
-        <v>1</v>
-      </c>
-      <c r="V136" t="n">
-        <v>0</v>
+        <v>0</v>
+      </c>
+      <c r="V136" s="7" t="n">
+        <v>1</v>
       </c>
       <c r="W136" t="n">
         <v>0</v>
@@ -16228,7 +16237,7 @@
         <v>0</v>
       </c>
       <c r="Y136" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Z136" t="n">
         <v>0</v>
@@ -16243,16 +16252,16 @@
         <v>0</v>
       </c>
       <c r="AD136" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AE136" s="4" t="n">
         <v>5</v>
       </c>
       <c r="AF136" t="n">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="AG136" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
     </row>
     <row r="137">
@@ -16263,7 +16272,7 @@
       </c>
       <c r="B137" t="inlineStr">
         <is>
-          <t>2026-07-11 08:35:52 PM PT</t>
+          <t>2026-07-11 08:37:52 PM PT</t>
         </is>
       </c>
       <c r="C137" t="n">
@@ -16304,27 +16313,27 @@
       </c>
       <c r="N137" t="inlineStr">
         <is>
-          <t>Nick Gonzales</t>
+          <t>Brandon Lowe</t>
         </is>
       </c>
       <c r="O137" t="n">
-        <v>693304</v>
+        <v>664040</v>
       </c>
       <c r="P137" t="inlineStr">
         <is>
-          <t>3B</t>
+          <t>2B</t>
         </is>
       </c>
       <c r="Q137" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>2</t>
         </is>
       </c>
       <c r="R137" t="n">
         <v>4</v>
       </c>
       <c r="S137" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="T137" t="n">
         <v>1</v>
@@ -16342,13 +16351,13 @@
         <v>0</v>
       </c>
       <c r="Y137" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Z137" t="n">
         <v>0</v>
       </c>
-      <c r="AA137" s="5" t="n">
-        <v>1</v>
+      <c r="AA137" t="n">
+        <v>0</v>
       </c>
       <c r="AB137" t="n">
         <v>0</v>
@@ -16377,15 +16386,15 @@
       </c>
       <c r="B138" t="inlineStr">
         <is>
-          <t>2026-07-11 08:35:53 PM PT</t>
+          <t>2026-07-11 08:37:52 PM PT</t>
         </is>
       </c>
       <c r="C138" t="n">
-        <v>822953</v>
+        <v>823357</v>
       </c>
       <c r="D138" t="inlineStr">
         <is>
-          <t>1:10 PM PT</t>
+          <t>9:05 AM PT</t>
         </is>
       </c>
       <c r="E138" t="inlineStr">
@@ -16403,51 +16412,51 @@
       </c>
       <c r="K138" t="inlineStr">
         <is>
-          <t>Away</t>
+          <t>Home</t>
         </is>
       </c>
       <c r="L138" t="inlineStr">
         <is>
-          <t>SEA</t>
+          <t>PIT</t>
         </is>
       </c>
       <c r="M138" t="inlineStr">
         <is>
-          <t>TB</t>
+          <t>MIL</t>
         </is>
       </c>
       <c r="N138" t="inlineStr">
         <is>
-          <t>Josh Naylor</t>
+          <t>Nick Gonzales</t>
         </is>
       </c>
       <c r="O138" t="n">
-        <v>647304</v>
+        <v>693304</v>
       </c>
       <c r="P138" t="inlineStr">
         <is>
-          <t>1B</t>
+          <t>3B</t>
         </is>
       </c>
       <c r="Q138" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="R138" t="n">
         <v>4</v>
       </c>
       <c r="S138" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="T138" t="n">
         <v>1</v>
       </c>
       <c r="U138" t="n">
-        <v>0</v>
-      </c>
-      <c r="V138" s="7" t="n">
-        <v>1</v>
+        <v>1</v>
+      </c>
+      <c r="V138" t="n">
+        <v>0</v>
       </c>
       <c r="W138" t="n">
         <v>0</v>
@@ -16461,8 +16470,8 @@
       <c r="Z138" t="n">
         <v>0</v>
       </c>
-      <c r="AA138" t="n">
-        <v>0</v>
+      <c r="AA138" s="5" t="n">
+        <v>1</v>
       </c>
       <c r="AB138" t="n">
         <v>0</v>
@@ -16471,16 +16480,16 @@
         <v>0</v>
       </c>
       <c r="AD138" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AE138" s="4" t="n">
         <v>5</v>
       </c>
       <c r="AF138" t="n">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="AG138" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
     </row>
     <row r="139">
@@ -16491,7 +16500,7 @@
       </c>
       <c r="B139" t="inlineStr">
         <is>
-          <t>2026-07-11 08:35:53 PM PT</t>
+          <t>2026-07-11 08:37:53 PM PT</t>
         </is>
       </c>
       <c r="C139" t="n">
@@ -16532,60 +16541,60 @@
       </c>
       <c r="N139" t="inlineStr">
         <is>
-          <t>Victor Robles</t>
+          <t>Josh Naylor</t>
         </is>
       </c>
       <c r="O139" t="n">
-        <v>645302</v>
+        <v>647304</v>
       </c>
       <c r="P139" t="inlineStr">
         <is>
-          <t>CF</t>
+          <t>1B</t>
         </is>
       </c>
       <c r="Q139" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>5</t>
         </is>
       </c>
       <c r="R139" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="S139" t="n">
+        <v>4</v>
+      </c>
+      <c r="T139" t="n">
+        <v>1</v>
+      </c>
+      <c r="U139" t="n">
+        <v>0</v>
+      </c>
+      <c r="V139" s="7" t="n">
+        <v>1</v>
+      </c>
+      <c r="W139" t="n">
+        <v>0</v>
+      </c>
+      <c r="X139" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y139" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z139" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA139" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB139" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC139" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD139" t="n">
         <v>2</v>
-      </c>
-      <c r="T139" t="n">
-        <v>1</v>
-      </c>
-      <c r="U139" t="n">
-        <v>0</v>
-      </c>
-      <c r="V139" s="7" t="n">
-        <v>1</v>
-      </c>
-      <c r="W139" t="n">
-        <v>0</v>
-      </c>
-      <c r="X139" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y139" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z139" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA139" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB139" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC139" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD139" t="n">
-        <v>0</v>
       </c>
       <c r="AE139" s="4" t="n">
         <v>5</v>
@@ -16605,15 +16614,15 @@
       </c>
       <c r="B140" t="inlineStr">
         <is>
-          <t>2026-07-11 08:35:53 PM PT</t>
+          <t>2026-07-11 08:37:53 PM PT</t>
         </is>
       </c>
       <c r="C140" t="n">
-        <v>823198</v>
+        <v>822953</v>
       </c>
       <c r="D140" t="inlineStr">
         <is>
-          <t>1:05 PM PT</t>
+          <t>1:10 PM PT</t>
         </is>
       </c>
       <c r="E140" t="inlineStr">
@@ -16631,51 +16640,51 @@
       </c>
       <c r="K140" t="inlineStr">
         <is>
-          <t>Home</t>
+          <t>Away</t>
         </is>
       </c>
       <c r="L140" t="inlineStr">
         <is>
-          <t>SF</t>
+          <t>SEA</t>
         </is>
       </c>
       <c r="M140" t="inlineStr">
         <is>
-          <t>COL</t>
+          <t>TB</t>
         </is>
       </c>
       <c r="N140" t="inlineStr">
         <is>
-          <t>Heliot Ramos</t>
+          <t>Victor Robles</t>
         </is>
       </c>
       <c r="O140" t="n">
-        <v>671218</v>
+        <v>645302</v>
       </c>
       <c r="P140" t="inlineStr">
         <is>
-          <t>LF</t>
+          <t>CF</t>
         </is>
       </c>
       <c r="Q140" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>8</t>
         </is>
       </c>
       <c r="R140" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="S140" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="T140" t="n">
         <v>1</v>
       </c>
       <c r="U140" t="n">
-        <v>1</v>
-      </c>
-      <c r="V140" t="n">
-        <v>0</v>
+        <v>0</v>
+      </c>
+      <c r="V140" s="7" t="n">
+        <v>1</v>
       </c>
       <c r="W140" t="n">
         <v>0</v>
@@ -16684,7 +16693,7 @@
         <v>0</v>
       </c>
       <c r="Y140" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Z140" t="n">
         <v>0</v>
@@ -16705,10 +16714,10 @@
         <v>5</v>
       </c>
       <c r="AF140" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="AG140" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
     </row>
     <row r="141">
@@ -16719,15 +16728,15 @@
       </c>
       <c r="B141" t="inlineStr">
         <is>
-          <t>2026-07-11 08:35:54 PM PT</t>
+          <t>2026-07-11 08:37:53 PM PT</t>
         </is>
       </c>
       <c r="C141" t="n">
-        <v>823030</v>
+        <v>823198</v>
       </c>
       <c r="D141" t="inlineStr">
         <is>
-          <t>4:15 PM PT</t>
+          <t>1:05 PM PT</t>
         </is>
       </c>
       <c r="E141" t="inlineStr">
@@ -16750,30 +16759,30 @@
       </c>
       <c r="L141" t="inlineStr">
         <is>
-          <t>STL</t>
+          <t>SF</t>
         </is>
       </c>
       <c r="M141" t="inlineStr">
         <is>
-          <t>ATL</t>
+          <t>COL</t>
         </is>
       </c>
       <c r="N141" t="inlineStr">
         <is>
-          <t>Iván Herrera</t>
+          <t>Heliot Ramos</t>
         </is>
       </c>
       <c r="O141" t="n">
-        <v>671056</v>
+        <v>671218</v>
       </c>
       <c r="P141" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>LF</t>
         </is>
       </c>
       <c r="Q141" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="R141" t="n">
@@ -16822,7 +16831,7 @@
         <v>4</v>
       </c>
       <c r="AG141" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
     </row>
     <row r="142">
@@ -16833,7 +16842,7 @@
       </c>
       <c r="B142" t="inlineStr">
         <is>
-          <t>2026-07-11 08:35:54 PM PT</t>
+          <t>2026-07-11 08:37:54 PM PT</t>
         </is>
       </c>
       <c r="C142" t="n">
@@ -16874,27 +16883,27 @@
       </c>
       <c r="N142" t="inlineStr">
         <is>
-          <t>Jordan Walker</t>
+          <t>Iván Herrera</t>
         </is>
       </c>
       <c r="O142" t="n">
-        <v>691023</v>
+        <v>671056</v>
       </c>
       <c r="P142" t="inlineStr">
         <is>
-          <t>RF</t>
+          <t>C</t>
         </is>
       </c>
       <c r="Q142" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>2</t>
         </is>
       </c>
       <c r="R142" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="S142" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="T142" t="n">
         <v>1</v>
@@ -16947,7 +16956,7 @@
       </c>
       <c r="B143" t="inlineStr">
         <is>
-          <t>2026-07-11 08:35:54 PM PT</t>
+          <t>2026-07-11 08:37:54 PM PT</t>
         </is>
       </c>
       <c r="C143" t="n">
@@ -16988,20 +16997,20 @@
       </c>
       <c r="N143" t="inlineStr">
         <is>
-          <t>Blaze Jordan</t>
+          <t>Jordan Walker</t>
         </is>
       </c>
       <c r="O143" t="n">
-        <v>691458</v>
+        <v>691023</v>
       </c>
       <c r="P143" t="inlineStr">
         <is>
-          <t>3B</t>
+          <t>RF</t>
         </is>
       </c>
       <c r="Q143" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>4</t>
         </is>
       </c>
       <c r="R143" t="n">
@@ -17026,10 +17035,10 @@
         <v>0</v>
       </c>
       <c r="Y143" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Z143" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AA143" t="n">
         <v>0</v>
@@ -17041,7 +17050,7 @@
         <v>0</v>
       </c>
       <c r="AD143" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AE143" s="4" t="n">
         <v>5</v>
@@ -17061,15 +17070,15 @@
       </c>
       <c r="B144" t="inlineStr">
         <is>
-          <t>2026-07-11 08:35:53 PM PT</t>
+          <t>2026-07-11 08:37:54 PM PT</t>
         </is>
       </c>
       <c r="C144" t="n">
-        <v>822953</v>
+        <v>823030</v>
       </c>
       <c r="D144" t="inlineStr">
         <is>
-          <t>1:10 PM PT</t>
+          <t>4:15 PM PT</t>
         </is>
       </c>
       <c r="E144" t="inlineStr">
@@ -17092,37 +17101,37 @@
       </c>
       <c r="L144" t="inlineStr">
         <is>
-          <t>TB</t>
+          <t>STL</t>
         </is>
       </c>
       <c r="M144" t="inlineStr">
         <is>
-          <t>SEA</t>
+          <t>ATL</t>
         </is>
       </c>
       <c r="N144" t="inlineStr">
         <is>
-          <t>Chandler Simpson</t>
+          <t>Blaze Jordan</t>
         </is>
       </c>
       <c r="O144" t="n">
-        <v>802415</v>
+        <v>691458</v>
       </c>
       <c r="P144" t="inlineStr">
         <is>
-          <t>LF</t>
+          <t>3B</t>
         </is>
       </c>
       <c r="Q144" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>8</t>
         </is>
       </c>
       <c r="R144" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="S144" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="T144" t="n">
         <v>1</v>
@@ -17140,10 +17149,10 @@
         <v>0</v>
       </c>
       <c r="Y144" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Z144" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AA144" t="n">
         <v>0</v>
@@ -17155,16 +17164,16 @@
         <v>0</v>
       </c>
       <c r="AD144" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AE144" s="4" t="n">
         <v>5</v>
       </c>
       <c r="AF144" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="AG144" t="n">
-        <v>12</v>
+        <v>5</v>
       </c>
     </row>
     <row r="145">
@@ -17175,15 +17184,15 @@
       </c>
       <c r="B145" t="inlineStr">
         <is>
-          <t>2026-07-11 08:35:53 PM PT</t>
+          <t>2026-07-11 08:37:53 PM PT</t>
         </is>
       </c>
       <c r="C145" t="n">
-        <v>822875</v>
+        <v>822953</v>
       </c>
       <c r="D145" t="inlineStr">
         <is>
-          <t>4:05 PM PT</t>
+          <t>1:10 PM PT</t>
         </is>
       </c>
       <c r="E145" t="inlineStr">
@@ -17196,7 +17205,7 @@
       </c>
       <c r="G145" t="inlineStr">
         <is>
-          <t>Bottom</t>
+          <t>Top</t>
         </is>
       </c>
       <c r="K145" t="inlineStr">
@@ -17206,21 +17215,21 @@
       </c>
       <c r="L145" t="inlineStr">
         <is>
-          <t>TEX</t>
+          <t>TB</t>
         </is>
       </c>
       <c r="M145" t="inlineStr">
         <is>
-          <t>HOU</t>
+          <t>SEA</t>
         </is>
       </c>
       <c r="N145" t="inlineStr">
         <is>
-          <t>Wyatt Langford</t>
+          <t>Chandler Simpson</t>
         </is>
       </c>
       <c r="O145" t="n">
-        <v>694671</v>
+        <v>802415</v>
       </c>
       <c r="P145" t="inlineStr">
         <is>
@@ -17229,14 +17238,14 @@
       </c>
       <c r="Q145" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>6</t>
         </is>
       </c>
       <c r="R145" t="n">
         <v>4</v>
       </c>
       <c r="S145" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="T145" t="n">
         <v>1</v>
@@ -17254,13 +17263,13 @@
         <v>0</v>
       </c>
       <c r="Y145" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Z145" t="n">
         <v>0</v>
       </c>
-      <c r="AA145" s="5" t="n">
-        <v>1</v>
+      <c r="AA145" t="n">
+        <v>0</v>
       </c>
       <c r="AB145" t="n">
         <v>0</v>
@@ -17275,10 +17284,10 @@
         <v>5</v>
       </c>
       <c r="AF145" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="AG145" t="n">
-        <v>7</v>
+        <v>12</v>
       </c>
     </row>
     <row r="146">
@@ -17289,7 +17298,7 @@
       </c>
       <c r="B146" t="inlineStr">
         <is>
-          <t>2026-07-11 08:35:53 PM PT</t>
+          <t>2026-07-11 08:37:54 PM PT</t>
         </is>
       </c>
       <c r="C146" t="n">
@@ -17330,27 +17339,27 @@
       </c>
       <c r="N146" t="inlineStr">
         <is>
-          <t>Cam Cauley</t>
+          <t>Wyatt Langford</t>
         </is>
       </c>
       <c r="O146" t="n">
-        <v>695508</v>
+        <v>694671</v>
       </c>
       <c r="P146" t="inlineStr">
         <is>
-          <t>PH</t>
+          <t>LF</t>
         </is>
       </c>
       <c r="Q146" t="inlineStr">
         <is>
-          <t>4 (Sub)</t>
+          <t>2</t>
         </is>
       </c>
       <c r="R146" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="S146" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="T146" t="n">
         <v>1</v>
@@ -17368,13 +17377,13 @@
         <v>0</v>
       </c>
       <c r="Y146" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Z146" t="n">
         <v>0</v>
       </c>
-      <c r="AA146" t="n">
-        <v>0</v>
+      <c r="AA146" s="5" t="n">
+        <v>1</v>
       </c>
       <c r="AB146" t="n">
         <v>0</v>
@@ -17403,15 +17412,15 @@
       </c>
       <c r="B147" t="inlineStr">
         <is>
-          <t>2026-07-11 08:35:54 PM PT</t>
+          <t>2026-07-11 08:37:54 PM PT</t>
         </is>
       </c>
       <c r="C147" t="n">
-        <v>824492</v>
+        <v>822875</v>
       </c>
       <c r="D147" t="inlineStr">
         <is>
-          <t>4:10 PM PT</t>
+          <t>4:05 PM PT</t>
         </is>
       </c>
       <c r="E147" t="inlineStr">
@@ -17429,84 +17438,84 @@
       </c>
       <c r="K147" t="inlineStr">
         <is>
-          <t>Away</t>
+          <t>Home</t>
         </is>
       </c>
       <c r="L147" t="inlineStr">
         <is>
-          <t>CHC</t>
+          <t>TEX</t>
         </is>
       </c>
       <c r="M147" t="inlineStr">
         <is>
-          <t>CIN</t>
+          <t>HOU</t>
         </is>
       </c>
       <c r="N147" t="inlineStr">
         <is>
-          <t>Pete Crow-Armstrong</t>
+          <t>Cam Cauley</t>
         </is>
       </c>
       <c r="O147" t="n">
-        <v>691718</v>
+        <v>695508</v>
       </c>
       <c r="P147" t="inlineStr">
         <is>
-          <t>CF</t>
+          <t>PH</t>
         </is>
       </c>
       <c r="Q147" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>4 (Sub)</t>
         </is>
       </c>
       <c r="R147" t="n">
+        <v>1</v>
+      </c>
+      <c r="S147" t="n">
+        <v>1</v>
+      </c>
+      <c r="T147" t="n">
+        <v>1</v>
+      </c>
+      <c r="U147" t="n">
+        <v>1</v>
+      </c>
+      <c r="V147" t="n">
+        <v>0</v>
+      </c>
+      <c r="W147" t="n">
+        <v>0</v>
+      </c>
+      <c r="X147" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y147" t="n">
+        <v>1</v>
+      </c>
+      <c r="Z147" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA147" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB147" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC147" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD147" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE147" s="4" t="n">
         <v>5</v>
       </c>
-      <c r="S147" t="n">
+      <c r="AF147" t="n">
         <v>3</v>
       </c>
-      <c r="T147" t="n">
-        <v>0</v>
-      </c>
-      <c r="U147" t="n">
-        <v>0</v>
-      </c>
-      <c r="V147" t="n">
-        <v>0</v>
-      </c>
-      <c r="W147" t="n">
-        <v>0</v>
-      </c>
-      <c r="X147" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y147" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z147" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA147" s="5" t="n">
-        <v>2</v>
-      </c>
-      <c r="AB147" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC147" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD147" t="n">
-        <v>2</v>
-      </c>
-      <c r="AE147" s="4" t="n">
-        <v>4</v>
-      </c>
-      <c r="AF147" t="n">
-        <v>5</v>
-      </c>
       <c r="AG147" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
     </row>
     <row r="148">
@@ -17517,15 +17526,15 @@
       </c>
       <c r="B148" t="inlineStr">
         <is>
-          <t>2026-07-11 08:35:53 PM PT</t>
+          <t>2026-07-11 08:37:54 PM PT</t>
         </is>
       </c>
       <c r="C148" t="n">
-        <v>823844</v>
+        <v>824492</v>
       </c>
       <c r="D148" t="inlineStr">
         <is>
-          <t>1:10 PM PT</t>
+          <t>4:10 PM PT</t>
         </is>
       </c>
       <c r="E148" t="inlineStr">
@@ -17548,30 +17557,30 @@
       </c>
       <c r="L148" t="inlineStr">
         <is>
-          <t>CLE</t>
+          <t>CHC</t>
         </is>
       </c>
       <c r="M148" t="inlineStr">
         <is>
-          <t>MIA</t>
+          <t>CIN</t>
         </is>
       </c>
       <c r="N148" t="inlineStr">
         <is>
-          <t>Chase DeLauter</t>
+          <t>Pete Crow-Armstrong</t>
         </is>
       </c>
       <c r="O148" t="n">
-        <v>800050</v>
+        <v>691718</v>
       </c>
       <c r="P148" t="inlineStr">
         <is>
-          <t>DH</t>
+          <t>CF</t>
         </is>
       </c>
       <c r="Q148" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>1</t>
         </is>
       </c>
       <c r="R148" t="n">
@@ -17611,16 +17620,16 @@
         <v>0</v>
       </c>
       <c r="AD148" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AE148" s="4" t="n">
         <v>4</v>
       </c>
       <c r="AF148" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="AG148" t="n">
-        <v>11</v>
+        <v>9</v>
       </c>
     </row>
     <row r="149">
@@ -17631,15 +17640,15 @@
       </c>
       <c r="B149" t="inlineStr">
         <is>
-          <t>2026-07-11 08:35:53 PM PT</t>
+          <t>2026-07-11 08:37:53 PM PT</t>
         </is>
       </c>
       <c r="C149" t="n">
-        <v>824576</v>
+        <v>823844</v>
       </c>
       <c r="D149" t="inlineStr">
         <is>
-          <t>11:10 AM PT</t>
+          <t>1:10 PM PT</t>
         </is>
       </c>
       <c r="E149" t="inlineStr">
@@ -17652,44 +17661,44 @@
       </c>
       <c r="G149" t="inlineStr">
         <is>
-          <t>Top</t>
+          <t>Bottom</t>
         </is>
       </c>
       <c r="K149" t="inlineStr">
         <is>
-          <t>Home</t>
+          <t>Away</t>
         </is>
       </c>
       <c r="L149" t="inlineStr">
         <is>
-          <t>CWS</t>
+          <t>CLE</t>
         </is>
       </c>
       <c r="M149" t="inlineStr">
         <is>
-          <t>ATH</t>
+          <t>MIA</t>
         </is>
       </c>
       <c r="N149" t="inlineStr">
         <is>
-          <t>Colson Montgomery</t>
+          <t>Chase DeLauter</t>
         </is>
       </c>
       <c r="O149" t="n">
-        <v>695657</v>
+        <v>800050</v>
       </c>
       <c r="P149" t="inlineStr">
         <is>
-          <t>3B</t>
+          <t>DH</t>
         </is>
       </c>
       <c r="Q149" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>3</t>
         </is>
       </c>
       <c r="R149" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="S149" t="n">
         <v>3</v>
@@ -17710,13 +17719,13 @@
         <v>0</v>
       </c>
       <c r="Y149" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Z149" t="n">
         <v>0</v>
       </c>
       <c r="AA149" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AB149" t="n">
         <v>0</v>
@@ -17725,16 +17734,16 @@
         <v>0</v>
       </c>
       <c r="AD149" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="AE149" s="4" t="n">
         <v>4</v>
       </c>
       <c r="AF149" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="AG149" t="n">
-        <v>5</v>
+        <v>11</v>
       </c>
     </row>
     <row r="150">
@@ -17745,15 +17754,15 @@
       </c>
       <c r="B150" t="inlineStr">
         <is>
-          <t>2026-07-11 08:35:52 PM PT</t>
+          <t>2026-07-11 08:37:53 PM PT</t>
         </is>
       </c>
       <c r="C150" t="n">
-        <v>823357</v>
+        <v>824576</v>
       </c>
       <c r="D150" t="inlineStr">
         <is>
-          <t>9:05 AM PT</t>
+          <t>11:10 AM PT</t>
         </is>
       </c>
       <c r="E150" t="inlineStr">
@@ -17771,39 +17780,39 @@
       </c>
       <c r="K150" t="inlineStr">
         <is>
-          <t>Away</t>
+          <t>Home</t>
         </is>
       </c>
       <c r="L150" t="inlineStr">
         <is>
-          <t>MIL</t>
+          <t>CWS</t>
         </is>
       </c>
       <c r="M150" t="inlineStr">
         <is>
-          <t>PIT</t>
+          <t>ATH</t>
         </is>
       </c>
       <c r="N150" t="inlineStr">
         <is>
-          <t>Brice Turang</t>
+          <t>Colson Montgomery</t>
         </is>
       </c>
       <c r="O150" t="n">
-        <v>668930</v>
+        <v>695657</v>
       </c>
       <c r="P150" t="inlineStr">
         <is>
-          <t>2B</t>
+          <t>3B</t>
         </is>
       </c>
       <c r="Q150" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="R150" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="S150" t="n">
         <v>3</v>
@@ -17824,13 +17833,13 @@
         <v>0</v>
       </c>
       <c r="Y150" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Z150" t="n">
         <v>0</v>
       </c>
       <c r="AA150" s="5" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AB150" t="n">
         <v>0</v>
@@ -17839,16 +17848,16 @@
         <v>0</v>
       </c>
       <c r="AD150" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="AE150" s="4" t="n">
         <v>4</v>
       </c>
       <c r="AF150" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="AG150" t="n">
-        <v>9</v>
+        <v>5</v>
       </c>
     </row>
     <row r="151">
@@ -17859,15 +17868,15 @@
       </c>
       <c r="B151" t="inlineStr">
         <is>
-          <t>2026-07-11 08:35:52 PM PT</t>
+          <t>2026-07-11 08:37:52 PM PT</t>
         </is>
       </c>
       <c r="C151" t="n">
-        <v>823356</v>
+        <v>823357</v>
       </c>
       <c r="D151" t="inlineStr">
         <is>
-          <t>1:05 PM PT</t>
+          <t>9:05 AM PT</t>
         </is>
       </c>
       <c r="E151" t="inlineStr">
@@ -17900,27 +17909,27 @@
       </c>
       <c r="N151" t="inlineStr">
         <is>
-          <t>Gary Sánchez</t>
+          <t>Brice Turang</t>
         </is>
       </c>
       <c r="O151" t="n">
-        <v>596142</v>
+        <v>668930</v>
       </c>
       <c r="P151" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>2B</t>
         </is>
       </c>
       <c r="Q151" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>3</t>
         </is>
       </c>
       <c r="R151" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="S151" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="T151" t="n">
         <v>0</v>
@@ -17959,10 +17968,10 @@
         <v>4</v>
       </c>
       <c r="AF151" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="AG151" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
     </row>
     <row r="152">
@@ -17973,15 +17982,15 @@
       </c>
       <c r="B152" t="inlineStr">
         <is>
-          <t>2026-07-11 08:35:52 PM PT</t>
+          <t>2026-07-11 08:37:52 PM PT</t>
         </is>
       </c>
       <c r="C152" t="n">
-        <v>823682</v>
+        <v>823356</v>
       </c>
       <c r="D152" t="inlineStr">
         <is>
-          <t>11:10 AM PT</t>
+          <t>1:05 PM PT</t>
         </is>
       </c>
       <c r="E152" t="inlineStr">
@@ -17999,42 +18008,42 @@
       </c>
       <c r="K152" t="inlineStr">
         <is>
-          <t>Home</t>
+          <t>Away</t>
         </is>
       </c>
       <c r="L152" t="inlineStr">
         <is>
-          <t>MIN</t>
+          <t>MIL</t>
         </is>
       </c>
       <c r="M152" t="inlineStr">
         <is>
-          <t>LAA</t>
+          <t>PIT</t>
         </is>
       </c>
       <c r="N152" t="inlineStr">
         <is>
-          <t>Kody Clemens</t>
+          <t>Gary Sánchez</t>
         </is>
       </c>
       <c r="O152" t="n">
-        <v>665019</v>
+        <v>596142</v>
       </c>
       <c r="P152" t="inlineStr">
         <is>
-          <t>2B</t>
+          <t>C</t>
         </is>
       </c>
       <c r="Q152" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="R152" t="n">
         <v>4</v>
       </c>
       <c r="S152" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="T152" t="n">
         <v>0</v>
@@ -18052,13 +18061,13 @@
         <v>0</v>
       </c>
       <c r="Y152" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Z152" t="n">
         <v>0</v>
       </c>
       <c r="AA152" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AB152" t="n">
         <v>0</v>
@@ -18067,16 +18076,16 @@
         <v>0</v>
       </c>
       <c r="AD152" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AE152" s="4" t="n">
         <v>4</v>
       </c>
       <c r="AF152" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="AG152" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
     </row>
     <row r="153">
@@ -18087,15 +18096,15 @@
       </c>
       <c r="B153" t="inlineStr">
         <is>
-          <t>2026-07-11 08:35:53 PM PT</t>
+          <t>2026-07-11 08:37:53 PM PT</t>
         </is>
       </c>
       <c r="C153" t="n">
-        <v>824249</v>
+        <v>823682</v>
       </c>
       <c r="D153" t="inlineStr">
         <is>
-          <t>3:10 PM PT</t>
+          <t>11:10 AM PT</t>
         </is>
       </c>
       <c r="E153" t="inlineStr">
@@ -18108,89 +18117,89 @@
       </c>
       <c r="G153" t="inlineStr">
         <is>
-          <t>Bottom</t>
+          <t>Top</t>
         </is>
       </c>
       <c r="K153" t="inlineStr">
         <is>
-          <t>Away</t>
+          <t>Home</t>
         </is>
       </c>
       <c r="L153" t="inlineStr">
         <is>
-          <t>PHI</t>
+          <t>MIN</t>
         </is>
       </c>
       <c r="M153" t="inlineStr">
         <is>
-          <t>DET</t>
+          <t>LAA</t>
         </is>
       </c>
       <c r="N153" t="inlineStr">
         <is>
-          <t>Trea Turner</t>
+          <t>Kody Clemens</t>
         </is>
       </c>
       <c r="O153" t="n">
-        <v>607208</v>
+        <v>665019</v>
       </c>
       <c r="P153" t="inlineStr">
         <is>
-          <t>SS</t>
+          <t>2B</t>
         </is>
       </c>
       <c r="Q153" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>4</t>
         </is>
       </c>
       <c r="R153" t="n">
         <v>4</v>
       </c>
       <c r="S153" t="n">
+        <v>3</v>
+      </c>
+      <c r="T153" t="n">
+        <v>0</v>
+      </c>
+      <c r="U153" t="n">
+        <v>0</v>
+      </c>
+      <c r="V153" t="n">
+        <v>0</v>
+      </c>
+      <c r="W153" t="n">
+        <v>0</v>
+      </c>
+      <c r="X153" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y153" t="n">
+        <v>1</v>
+      </c>
+      <c r="Z153" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA153" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="AB153" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC153" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD153" t="n">
         <v>2</v>
-      </c>
-      <c r="T153" t="n">
-        <v>0</v>
-      </c>
-      <c r="U153" t="n">
-        <v>0</v>
-      </c>
-      <c r="V153" t="n">
-        <v>0</v>
-      </c>
-      <c r="W153" t="n">
-        <v>0</v>
-      </c>
-      <c r="X153" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y153" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z153" t="n">
-        <v>1</v>
-      </c>
-      <c r="AA153" s="5" t="n">
-        <v>1</v>
-      </c>
-      <c r="AB153" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC153" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD153" t="n">
-        <v>1</v>
       </c>
       <c r="AE153" s="4" t="n">
         <v>4</v>
       </c>
       <c r="AF153" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="AG153" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
     </row>
     <row r="154">
@@ -18201,7 +18210,7 @@
       </c>
       <c r="B154" t="inlineStr">
         <is>
-          <t>2026-07-11 08:35:53 PM PT</t>
+          <t>2026-07-11 08:37:53 PM PT</t>
         </is>
       </c>
       <c r="C154" t="n">
@@ -18242,27 +18251,27 @@
       </c>
       <c r="N154" t="inlineStr">
         <is>
-          <t>Brandon Marsh</t>
+          <t>Trea Turner</t>
         </is>
       </c>
       <c r="O154" t="n">
-        <v>669016</v>
+        <v>607208</v>
       </c>
       <c r="P154" t="inlineStr">
         <is>
-          <t>LF</t>
+          <t>SS</t>
         </is>
       </c>
       <c r="Q154" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>1</t>
         </is>
       </c>
       <c r="R154" t="n">
         <v>4</v>
       </c>
       <c r="S154" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="T154" t="n">
         <v>0</v>
@@ -18280,10 +18289,10 @@
         <v>0</v>
       </c>
       <c r="Y154" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Z154" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AA154" s="5" t="n">
         <v>1</v>
@@ -18315,15 +18324,15 @@
       </c>
       <c r="B155" t="inlineStr">
         <is>
-          <t>2026-07-11 08:35:52 PM PT</t>
+          <t>2026-07-11 08:37:53 PM PT</t>
         </is>
       </c>
       <c r="C155" t="n">
-        <v>823357</v>
+        <v>824249</v>
       </c>
       <c r="D155" t="inlineStr">
         <is>
-          <t>9:05 AM PT</t>
+          <t>3:10 PM PT</t>
         </is>
       </c>
       <c r="E155" t="inlineStr">
@@ -18336,40 +18345,40 @@
       </c>
       <c r="G155" t="inlineStr">
         <is>
-          <t>Top</t>
+          <t>Bottom</t>
         </is>
       </c>
       <c r="K155" t="inlineStr">
         <is>
-          <t>Home</t>
+          <t>Away</t>
         </is>
       </c>
       <c r="L155" t="inlineStr">
         <is>
-          <t>PIT</t>
+          <t>PHI</t>
         </is>
       </c>
       <c r="M155" t="inlineStr">
         <is>
-          <t>MIL</t>
+          <t>DET</t>
         </is>
       </c>
       <c r="N155" t="inlineStr">
         <is>
-          <t>Bryan Reynolds</t>
+          <t>Brandon Marsh</t>
         </is>
       </c>
       <c r="O155" t="n">
-        <v>668804</v>
+        <v>669016</v>
       </c>
       <c r="P155" t="inlineStr">
         <is>
-          <t>DH</t>
+          <t>LF</t>
         </is>
       </c>
       <c r="Q155" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="R155" t="n">
@@ -18399,23 +18408,23 @@
       <c r="Z155" t="n">
         <v>0</v>
       </c>
-      <c r="AA155" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB155" s="9" t="n">
-        <v>1</v>
+      <c r="AA155" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="AB155" t="n">
+        <v>0</v>
       </c>
       <c r="AC155" t="n">
         <v>0</v>
       </c>
       <c r="AD155" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AE155" s="4" t="n">
         <v>4</v>
       </c>
       <c r="AF155" t="n">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="AG155" t="n">
         <v>7</v>
@@ -18429,38 +18438,29 @@
       </c>
       <c r="B156" t="inlineStr">
         <is>
-          <t>2026-07-11 08:35:54 PM PT</t>
+          <t>2026-07-11 08:37:52 PM PT</t>
         </is>
       </c>
       <c r="C156" t="n">
-        <v>823276</v>
+        <v>823357</v>
       </c>
       <c r="D156" t="inlineStr">
         <is>
-          <t>5:40 PM PT</t>
+          <t>9:05 AM PT</t>
         </is>
       </c>
       <c r="E156" t="inlineStr">
         <is>
-          <t>Bottom 8 | 1 out</t>
+          <t>Final</t>
         </is>
       </c>
       <c r="F156" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="G156" t="inlineStr">
         <is>
-          <t>Bottom</t>
-        </is>
-      </c>
-      <c r="H156" t="n">
-        <v>1</v>
-      </c>
-      <c r="I156" t="n">
-        <v>2</v>
-      </c>
-      <c r="J156" t="n">
-        <v>0</v>
+          <t>Top</t>
+        </is>
       </c>
       <c r="K156" t="inlineStr">
         <is>
@@ -18469,25 +18469,25 @@
       </c>
       <c r="L156" t="inlineStr">
         <is>
-          <t>SD</t>
+          <t>PIT</t>
         </is>
       </c>
       <c r="M156" t="inlineStr">
         <is>
-          <t>TOR</t>
+          <t>MIL</t>
         </is>
       </c>
       <c r="N156" t="inlineStr">
         <is>
-          <t>Xander Bogaerts</t>
+          <t>Bryan Reynolds</t>
         </is>
       </c>
       <c r="O156" t="n">
-        <v>593428</v>
+        <v>668804</v>
       </c>
       <c r="P156" t="inlineStr">
         <is>
-          <t>SS</t>
+          <t>DH</t>
         </is>
       </c>
       <c r="Q156" t="inlineStr">
@@ -18499,49 +18499,49 @@
         <v>4</v>
       </c>
       <c r="S156" t="n">
+        <v>3</v>
+      </c>
+      <c r="T156" t="n">
+        <v>0</v>
+      </c>
+      <c r="U156" t="n">
+        <v>0</v>
+      </c>
+      <c r="V156" t="n">
+        <v>0</v>
+      </c>
+      <c r="W156" t="n">
+        <v>0</v>
+      </c>
+      <c r="X156" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y156" t="n">
+        <v>1</v>
+      </c>
+      <c r="Z156" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA156" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB156" s="9" t="n">
+        <v>1</v>
+      </c>
+      <c r="AC156" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD156" t="n">
         <v>2</v>
-      </c>
-      <c r="T156" t="n">
-        <v>0</v>
-      </c>
-      <c r="U156" t="n">
-        <v>0</v>
-      </c>
-      <c r="V156" t="n">
-        <v>0</v>
-      </c>
-      <c r="W156" t="n">
-        <v>0</v>
-      </c>
-      <c r="X156" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y156" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z156" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA156" s="5" t="n">
-        <v>2</v>
-      </c>
-      <c r="AB156" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC156" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD156" t="n">
-        <v>1</v>
       </c>
       <c r="AE156" s="4" t="n">
         <v>4</v>
       </c>
       <c r="AF156" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="AG156" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
     </row>
     <row r="157">
@@ -18552,7 +18552,7 @@
       </c>
       <c r="B157" t="inlineStr">
         <is>
-          <t>2026-07-11 08:35:54 PM PT</t>
+          <t>2026-07-11 08:37:54 PM PT</t>
         </is>
       </c>
       <c r="C157" t="n">
@@ -18580,7 +18580,7 @@
         <v>1</v>
       </c>
       <c r="I157" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="J157" t="n">
         <v>0</v>
@@ -18675,7 +18675,7 @@
       </c>
       <c r="B158" t="inlineStr">
         <is>
-          <t>2026-07-11 08:35:54 PM PT</t>
+          <t>2026-07-11 08:37:54 PM PT</t>
         </is>
       </c>
       <c r="C158" t="n">
@@ -18703,7 +18703,7 @@
         <v>1</v>
       </c>
       <c r="I158" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="J158" t="n">
         <v>0</v>
@@ -18798,7 +18798,7 @@
       </c>
       <c r="B159" t="inlineStr">
         <is>
-          <t>2026-07-11 08:35:54 PM PT</t>
+          <t>2026-07-11 08:37:54 PM PT</t>
         </is>
       </c>
       <c r="C159" t="n">
@@ -18826,7 +18826,7 @@
         <v>1</v>
       </c>
       <c r="I159" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="J159" t="n">
         <v>0</v>
@@ -18921,7 +18921,7 @@
       </c>
       <c r="B160" t="inlineStr">
         <is>
-          <t>2026-07-11 08:35:54 PM PT</t>
+          <t>2026-07-11 08:37:54 PM PT</t>
         </is>
       </c>
       <c r="C160" t="n">
@@ -19035,7 +19035,7 @@
       </c>
       <c r="B161" t="inlineStr">
         <is>
-          <t>2026-07-11 08:35:54 PM PT</t>
+          <t>2026-07-11 08:37:54 PM PT</t>
         </is>
       </c>
       <c r="C161" t="n">
@@ -19149,7 +19149,7 @@
       </c>
       <c r="B162" t="inlineStr">
         <is>
-          <t>2026-07-11 08:35:54 PM PT</t>
+          <t>2026-07-11 08:37:54 PM PT</t>
         </is>
       </c>
       <c r="C162" t="n">
@@ -19263,7 +19263,7 @@
       </c>
       <c r="B163" t="inlineStr">
         <is>
-          <t>2026-07-11 08:35:54 PM PT</t>
+          <t>2026-07-11 08:37:54 PM PT</t>
         </is>
       </c>
       <c r="C163" t="n">
@@ -19377,7 +19377,7 @@
       </c>
       <c r="B164" t="inlineStr">
         <is>
-          <t>2026-07-11 08:35:54 PM PT</t>
+          <t>2026-07-11 08:37:54 PM PT</t>
         </is>
       </c>
       <c r="C164" t="n">
@@ -19491,7 +19491,7 @@
       </c>
       <c r="B165" t="inlineStr">
         <is>
-          <t>2026-07-11 08:35:53 PM PT</t>
+          <t>2026-07-11 08:37:53 PM PT</t>
         </is>
       </c>
       <c r="C165" t="n">
@@ -19605,7 +19605,7 @@
       </c>
       <c r="B166" t="inlineStr">
         <is>
-          <t>2026-07-11 08:35:53 PM PT</t>
+          <t>2026-07-11 08:37:53 PM PT</t>
         </is>
       </c>
       <c r="C166" t="n">
@@ -19719,7 +19719,7 @@
       </c>
       <c r="B167" t="inlineStr">
         <is>
-          <t>2026-07-11 08:35:53 PM PT</t>
+          <t>2026-07-11 08:37:53 PM PT</t>
         </is>
       </c>
       <c r="C167" t="n">
@@ -19833,7 +19833,7 @@
       </c>
       <c r="B168" t="inlineStr">
         <is>
-          <t>2026-07-11 08:35:53 PM PT</t>
+          <t>2026-07-11 08:37:53 PM PT</t>
         </is>
       </c>
       <c r="C168" t="n">
@@ -19947,7 +19947,7 @@
       </c>
       <c r="B169" t="inlineStr">
         <is>
-          <t>2026-07-11 08:35:53 PM PT</t>
+          <t>2026-07-11 08:37:54 PM PT</t>
         </is>
       </c>
       <c r="C169" t="n">
@@ -20061,7 +20061,7 @@
       </c>
       <c r="B170" t="inlineStr">
         <is>
-          <t>2026-07-11 08:35:52 PM PT</t>
+          <t>2026-07-11 08:37:53 PM PT</t>
         </is>
       </c>
       <c r="C170" t="n">
@@ -20175,7 +20175,7 @@
       </c>
       <c r="B171" t="inlineStr">
         <is>
-          <t>2026-07-11 08:35:54 PM PT</t>
+          <t>2026-07-11 08:37:54 PM PT</t>
         </is>
       </c>
       <c r="C171" t="n">
@@ -20188,7 +20188,7 @@
       </c>
       <c r="E171" t="inlineStr">
         <is>
-          <t>Top 8 | 2 out</t>
+          <t>Bottom 8 | 0 out</t>
         </is>
       </c>
       <c r="F171" t="n">
@@ -20196,17 +20196,17 @@
       </c>
       <c r="G171" t="inlineStr">
         <is>
-          <t>Top</t>
+          <t>Bottom</t>
         </is>
       </c>
       <c r="H171" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="I171" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J171" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="K171" t="inlineStr">
         <is>
@@ -20298,7 +20298,7 @@
       </c>
       <c r="B172" t="inlineStr">
         <is>
-          <t>2026-07-11 08:35:54 PM PT</t>
+          <t>2026-07-11 08:37:54 PM PT</t>
         </is>
       </c>
       <c r="C172" t="n">
@@ -20311,7 +20311,7 @@
       </c>
       <c r="E172" t="inlineStr">
         <is>
-          <t>Top 8 | 2 out</t>
+          <t>Bottom 8 | 0 out</t>
         </is>
       </c>
       <c r="F172" t="n">
@@ -20319,17 +20319,17 @@
       </c>
       <c r="G172" t="inlineStr">
         <is>
-          <t>Top</t>
+          <t>Bottom</t>
         </is>
       </c>
       <c r="H172" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="I172" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J172" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="K172" t="inlineStr">
         <is>
@@ -20421,7 +20421,7 @@
       </c>
       <c r="B173" t="inlineStr">
         <is>
-          <t>2026-07-11 08:35:53 PM PT</t>
+          <t>2026-07-11 08:37:53 PM PT</t>
         </is>
       </c>
       <c r="C173" t="n">
@@ -20535,7 +20535,7 @@
       </c>
       <c r="B174" t="inlineStr">
         <is>
-          <t>2026-07-11 08:35:53 PM PT</t>
+          <t>2026-07-11 08:37:53 PM PT</t>
         </is>
       </c>
       <c r="C174" t="n">
@@ -20649,7 +20649,7 @@
       </c>
       <c r="B175" t="inlineStr">
         <is>
-          <t>2026-07-11 08:35:52 PM PT</t>
+          <t>2026-07-11 08:37:52 PM PT</t>
         </is>
       </c>
       <c r="C175" t="n">
@@ -20763,7 +20763,7 @@
       </c>
       <c r="B176" t="inlineStr">
         <is>
-          <t>2026-07-11 08:35:52 PM PT</t>
+          <t>2026-07-11 08:37:52 PM PT</t>
         </is>
       </c>
       <c r="C176" t="n">
@@ -20877,7 +20877,7 @@
       </c>
       <c r="B177" t="inlineStr">
         <is>
-          <t>2026-07-11 08:35:52 PM PT</t>
+          <t>2026-07-11 08:37:53 PM PT</t>
         </is>
       </c>
       <c r="C177" t="n">
@@ -20991,7 +20991,7 @@
       </c>
       <c r="B178" t="inlineStr">
         <is>
-          <t>2026-07-11 08:35:52 PM PT</t>
+          <t>2026-07-11 08:37:53 PM PT</t>
         </is>
       </c>
       <c r="C178" t="n">
@@ -21105,7 +21105,7 @@
       </c>
       <c r="B179" t="inlineStr">
         <is>
-          <t>2026-07-11 08:35:52 PM PT</t>
+          <t>2026-07-11 08:37:53 PM PT</t>
         </is>
       </c>
       <c r="C179" t="n">
@@ -21219,7 +21219,7 @@
       </c>
       <c r="B180" t="inlineStr">
         <is>
-          <t>2026-07-11 08:35:53 PM PT</t>
+          <t>2026-07-11 08:37:53 PM PT</t>
         </is>
       </c>
       <c r="C180" t="n">
@@ -21333,7 +21333,7 @@
       </c>
       <c r="B181" t="inlineStr">
         <is>
-          <t>2026-07-11 08:35:53 PM PT</t>
+          <t>2026-07-11 08:37:53 PM PT</t>
         </is>
       </c>
       <c r="C181" t="n">
@@ -21447,7 +21447,7 @@
       </c>
       <c r="B182" t="inlineStr">
         <is>
-          <t>2026-07-11 08:35:53 PM PT</t>
+          <t>2026-07-11 08:37:53 PM PT</t>
         </is>
       </c>
       <c r="C182" t="n">
@@ -21561,7 +21561,7 @@
       </c>
       <c r="B183" t="inlineStr">
         <is>
-          <t>2026-07-11 08:35:53 PM PT</t>
+          <t>2026-07-11 08:37:53 PM PT</t>
         </is>
       </c>
       <c r="C183" t="n">
@@ -21675,7 +21675,7 @@
       </c>
       <c r="B184" t="inlineStr">
         <is>
-          <t>2026-07-11 08:35:52 PM PT</t>
+          <t>2026-07-11 08:37:52 PM PT</t>
         </is>
       </c>
       <c r="C184" t="n">
@@ -21789,7 +21789,7 @@
       </c>
       <c r="B185" t="inlineStr">
         <is>
-          <t>2026-07-11 08:35:52 PM PT</t>
+          <t>2026-07-11 08:37:52 PM PT</t>
         </is>
       </c>
       <c r="C185" t="n">
@@ -21903,7 +21903,7 @@
       </c>
       <c r="B186" t="inlineStr">
         <is>
-          <t>2026-07-11 08:35:53 PM PT</t>
+          <t>2026-07-11 08:37:53 PM PT</t>
         </is>
       </c>
       <c r="C186" t="n">
@@ -22017,7 +22017,7 @@
       </c>
       <c r="B187" t="inlineStr">
         <is>
-          <t>2026-07-11 08:35:53 PM PT</t>
+          <t>2026-07-11 08:37:53 PM PT</t>
         </is>
       </c>
       <c r="C187" t="n">
@@ -22131,7 +22131,7 @@
       </c>
       <c r="B188" t="inlineStr">
         <is>
-          <t>2026-07-11 08:35:53 PM PT</t>
+          <t>2026-07-11 08:37:53 PM PT</t>
         </is>
       </c>
       <c r="C188" t="n">
@@ -22245,7 +22245,7 @@
       </c>
       <c r="B189" t="inlineStr">
         <is>
-          <t>2026-07-11 08:35:53 PM PT</t>
+          <t>2026-07-11 08:37:54 PM PT</t>
         </is>
       </c>
       <c r="C189" t="n">
@@ -22359,7 +22359,7 @@
       </c>
       <c r="B190" t="inlineStr">
         <is>
-          <t>2026-07-11 08:35:54 PM PT</t>
+          <t>2026-07-11 08:37:54 PM PT</t>
         </is>
       </c>
       <c r="C190" t="n">
@@ -22387,7 +22387,7 @@
         <v>1</v>
       </c>
       <c r="I190" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="J190" t="n">
         <v>0</v>
@@ -22482,7 +22482,7 @@
       </c>
       <c r="B191" t="inlineStr">
         <is>
-          <t>2026-07-11 08:35:53 PM PT</t>
+          <t>2026-07-11 08:37:53 PM PT</t>
         </is>
       </c>
       <c r="C191" t="n">
@@ -22596,7 +22596,7 @@
       </c>
       <c r="B192" t="inlineStr">
         <is>
-          <t>2026-07-11 08:35:53 PM PT</t>
+          <t>2026-07-11 08:37:53 PM PT</t>
         </is>
       </c>
       <c r="C192" t="n">
@@ -22710,7 +22710,7 @@
       </c>
       <c r="B193" t="inlineStr">
         <is>
-          <t>2026-07-11 08:35:54 PM PT</t>
+          <t>2026-07-11 08:37:54 PM PT</t>
         </is>
       </c>
       <c r="C193" t="n">
@@ -22723,7 +22723,7 @@
       </c>
       <c r="E193" t="inlineStr">
         <is>
-          <t>Top 8 | 2 out</t>
+          <t>Bottom 8 | 0 out</t>
         </is>
       </c>
       <c r="F193" t="n">
@@ -22731,17 +22731,17 @@
       </c>
       <c r="G193" t="inlineStr">
         <is>
-          <t>Top</t>
+          <t>Bottom</t>
         </is>
       </c>
       <c r="H193" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="I193" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J193" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="K193" t="inlineStr">
         <is>
@@ -22833,7 +22833,7 @@
       </c>
       <c r="B194" t="inlineStr">
         <is>
-          <t>2026-07-11 08:35:54 PM PT</t>
+          <t>2026-07-11 08:37:54 PM PT</t>
         </is>
       </c>
       <c r="C194" t="n">
@@ -22846,7 +22846,7 @@
       </c>
       <c r="E194" t="inlineStr">
         <is>
-          <t>Top 8 | 2 out</t>
+          <t>Bottom 8 | 0 out</t>
         </is>
       </c>
       <c r="F194" t="n">
@@ -22854,17 +22854,17 @@
       </c>
       <c r="G194" t="inlineStr">
         <is>
-          <t>Top</t>
+          <t>Bottom</t>
         </is>
       </c>
       <c r="H194" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="I194" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J194" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="K194" t="inlineStr">
         <is>
@@ -22956,7 +22956,7 @@
       </c>
       <c r="B195" t="inlineStr">
         <is>
-          <t>2026-07-11 08:35:53 PM PT</t>
+          <t>2026-07-11 08:37:53 PM PT</t>
         </is>
       </c>
       <c r="C195" t="n">
@@ -23070,7 +23070,7 @@
       </c>
       <c r="B196" t="inlineStr">
         <is>
-          <t>2026-07-11 08:35:54 PM PT</t>
+          <t>2026-07-11 08:37:54 PM PT</t>
         </is>
       </c>
       <c r="C196" t="n">
@@ -23184,7 +23184,7 @@
       </c>
       <c r="B197" t="inlineStr">
         <is>
-          <t>2026-07-11 08:35:54 PM PT</t>
+          <t>2026-07-11 08:37:54 PM PT</t>
         </is>
       </c>
       <c r="C197" t="n">
@@ -23298,7 +23298,7 @@
       </c>
       <c r="B198" t="inlineStr">
         <is>
-          <t>2026-07-11 08:35:53 PM PT</t>
+          <t>2026-07-11 08:37:54 PM PT</t>
         </is>
       </c>
       <c r="C198" t="n">
@@ -23412,7 +23412,7 @@
       </c>
       <c r="B199" t="inlineStr">
         <is>
-          <t>2026-07-11 08:35:53 PM PT</t>
+          <t>2026-07-11 08:37:53 PM PT</t>
         </is>
       </c>
       <c r="C199" t="n">
@@ -23526,7 +23526,7 @@
       </c>
       <c r="B200" t="inlineStr">
         <is>
-          <t>2026-07-11 08:35:53 PM PT</t>
+          <t>2026-07-11 08:37:53 PM PT</t>
         </is>
       </c>
       <c r="C200" t="n">
@@ -23640,7 +23640,7 @@
       </c>
       <c r="B201" t="inlineStr">
         <is>
-          <t>2026-07-11 08:35:53 PM PT</t>
+          <t>2026-07-11 08:37:53 PM PT</t>
         </is>
       </c>
       <c r="C201" t="n">
@@ -23754,7 +23754,7 @@
       </c>
       <c r="B202" t="inlineStr">
         <is>
-          <t>2026-07-11 08:35:54 PM PT</t>
+          <t>2026-07-11 08:37:54 PM PT</t>
         </is>
       </c>
       <c r="C202" t="n">
@@ -23868,7 +23868,7 @@
       </c>
       <c r="B203" t="inlineStr">
         <is>
-          <t>2026-07-11 08:35:53 PM PT</t>
+          <t>2026-07-11 08:37:53 PM PT</t>
         </is>
       </c>
       <c r="C203" t="n">
@@ -23982,7 +23982,7 @@
       </c>
       <c r="B204" t="inlineStr">
         <is>
-          <t>2026-07-11 08:35:53 PM PT</t>
+          <t>2026-07-11 08:37:53 PM PT</t>
         </is>
       </c>
       <c r="C204" t="n">
@@ -24096,7 +24096,7 @@
       </c>
       <c r="B205" t="inlineStr">
         <is>
-          <t>2026-07-11 08:35:53 PM PT</t>
+          <t>2026-07-11 08:37:53 PM PT</t>
         </is>
       </c>
       <c r="C205" t="n">
@@ -24210,7 +24210,7 @@
       </c>
       <c r="B206" t="inlineStr">
         <is>
-          <t>2026-07-11 08:35:53 PM PT</t>
+          <t>2026-07-11 08:37:53 PM PT</t>
         </is>
       </c>
       <c r="C206" t="n">
@@ -24324,7 +24324,7 @@
       </c>
       <c r="B207" t="inlineStr">
         <is>
-          <t>2026-07-11 08:35:53 PM PT</t>
+          <t>2026-07-11 08:37:53 PM PT</t>
         </is>
       </c>
       <c r="C207" t="n">
@@ -24438,7 +24438,7 @@
       </c>
       <c r="B208" t="inlineStr">
         <is>
-          <t>2026-07-11 08:35:53 PM PT</t>
+          <t>2026-07-11 08:37:53 PM PT</t>
         </is>
       </c>
       <c r="C208" t="n">
@@ -24552,7 +24552,7 @@
       </c>
       <c r="B209" t="inlineStr">
         <is>
-          <t>2026-07-11 08:35:53 PM PT</t>
+          <t>2026-07-11 08:37:54 PM PT</t>
         </is>
       </c>
       <c r="C209" t="n">
@@ -24666,7 +24666,7 @@
       </c>
       <c r="B210" t="inlineStr">
         <is>
-          <t>2026-07-11 08:35:53 PM PT</t>
+          <t>2026-07-11 08:37:54 PM PT</t>
         </is>
       </c>
       <c r="C210" t="n">
@@ -24780,7 +24780,7 @@
       </c>
       <c r="B211" t="inlineStr">
         <is>
-          <t>2026-07-11 08:35:53 PM PT</t>
+          <t>2026-07-11 08:37:54 PM PT</t>
         </is>
       </c>
       <c r="C211" t="n">
@@ -24894,7 +24894,7 @@
       </c>
       <c r="B212" t="inlineStr">
         <is>
-          <t>2026-07-11 08:35:53 PM PT</t>
+          <t>2026-07-11 08:37:54 PM PT</t>
         </is>
       </c>
       <c r="C212" t="n">
@@ -25008,7 +25008,7 @@
       </c>
       <c r="B213" t="inlineStr">
         <is>
-          <t>2026-07-11 08:35:52 PM PT</t>
+          <t>2026-07-11 08:37:53 PM PT</t>
         </is>
       </c>
       <c r="C213" t="n">
@@ -25122,7 +25122,7 @@
       </c>
       <c r="B214" t="inlineStr">
         <is>
-          <t>2026-07-11 08:35:53 PM PT</t>
+          <t>2026-07-11 08:37:53 PM PT</t>
         </is>
       </c>
       <c r="C214" t="n">
@@ -25236,7 +25236,7 @@
       </c>
       <c r="B215" t="inlineStr">
         <is>
-          <t>2026-07-11 08:35:53 PM PT</t>
+          <t>2026-07-11 08:37:53 PM PT</t>
         </is>
       </c>
       <c r="C215" t="n">
@@ -25350,7 +25350,7 @@
       </c>
       <c r="B216" t="inlineStr">
         <is>
-          <t>2026-07-11 08:35:52 PM PT</t>
+          <t>2026-07-11 08:37:53 PM PT</t>
         </is>
       </c>
       <c r="C216" t="n">
@@ -25464,7 +25464,7 @@
       </c>
       <c r="B217" t="inlineStr">
         <is>
-          <t>2026-07-11 08:35:53 PM PT</t>
+          <t>2026-07-11 08:37:53 PM PT</t>
         </is>
       </c>
       <c r="C217" t="n">
@@ -25578,7 +25578,7 @@
       </c>
       <c r="B218" t="inlineStr">
         <is>
-          <t>2026-07-11 08:35:53 PM PT</t>
+          <t>2026-07-11 08:37:53 PM PT</t>
         </is>
       </c>
       <c r="C218" t="n">
@@ -25692,7 +25692,7 @@
       </c>
       <c r="B219" t="inlineStr">
         <is>
-          <t>2026-07-11 08:35:53 PM PT</t>
+          <t>2026-07-11 08:37:53 PM PT</t>
         </is>
       </c>
       <c r="C219" t="n">
@@ -25806,7 +25806,7 @@
       </c>
       <c r="B220" t="inlineStr">
         <is>
-          <t>2026-07-11 08:35:53 PM PT</t>
+          <t>2026-07-11 08:37:53 PM PT</t>
         </is>
       </c>
       <c r="C220" t="n">
@@ -25920,7 +25920,7 @@
       </c>
       <c r="B221" t="inlineStr">
         <is>
-          <t>2026-07-11 08:35:53 PM PT</t>
+          <t>2026-07-11 08:37:53 PM PT</t>
         </is>
       </c>
       <c r="C221" t="n">
@@ -26034,7 +26034,7 @@
       </c>
       <c r="B222" t="inlineStr">
         <is>
-          <t>2026-07-11 08:35:53 PM PT</t>
+          <t>2026-07-11 08:37:53 PM PT</t>
         </is>
       </c>
       <c r="C222" t="n">
@@ -26148,7 +26148,7 @@
       </c>
       <c r="B223" t="inlineStr">
         <is>
-          <t>2026-07-11 08:35:53 PM PT</t>
+          <t>2026-07-11 08:37:53 PM PT</t>
         </is>
       </c>
       <c r="C223" t="n">
@@ -26262,7 +26262,7 @@
       </c>
       <c r="B224" t="inlineStr">
         <is>
-          <t>2026-07-11 08:35:52 PM PT</t>
+          <t>2026-07-11 08:37:52 PM PT</t>
         </is>
       </c>
       <c r="C224" t="n">
@@ -26376,7 +26376,7 @@
       </c>
       <c r="B225" t="inlineStr">
         <is>
-          <t>2026-07-11 08:35:52 PM PT</t>
+          <t>2026-07-11 08:37:52 PM PT</t>
         </is>
       </c>
       <c r="C225" t="n">
@@ -26490,7 +26490,7 @@
       </c>
       <c r="B226" t="inlineStr">
         <is>
-          <t>2026-07-11 08:35:53 PM PT</t>
+          <t>2026-07-11 08:37:53 PM PT</t>
         </is>
       </c>
       <c r="C226" t="n">
@@ -26604,7 +26604,7 @@
       </c>
       <c r="B227" t="inlineStr">
         <is>
-          <t>2026-07-11 08:35:53 PM PT</t>
+          <t>2026-07-11 08:37:53 PM PT</t>
         </is>
       </c>
       <c r="C227" t="n">
@@ -26718,7 +26718,7 @@
       </c>
       <c r="B228" t="inlineStr">
         <is>
-          <t>2026-07-11 08:35:53 PM PT</t>
+          <t>2026-07-11 08:37:54 PM PT</t>
         </is>
       </c>
       <c r="C228" t="n">
@@ -26832,7 +26832,7 @@
       </c>
       <c r="B229" t="inlineStr">
         <is>
-          <t>2026-07-11 08:35:53 PM PT</t>
+          <t>2026-07-11 08:37:54 PM PT</t>
         </is>
       </c>
       <c r="C229" t="n">
@@ -26946,7 +26946,7 @@
       </c>
       <c r="B230" t="inlineStr">
         <is>
-          <t>2026-07-11 08:35:54 PM PT</t>
+          <t>2026-07-11 08:37:54 PM PT</t>
         </is>
       </c>
       <c r="C230" t="n">
@@ -26974,7 +26974,7 @@
         <v>1</v>
       </c>
       <c r="I230" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="J230" t="n">
         <v>0</v>
@@ -27069,7 +27069,7 @@
       </c>
       <c r="B231" t="inlineStr">
         <is>
-          <t>2026-07-11 08:35:53 PM PT</t>
+          <t>2026-07-11 08:37:53 PM PT</t>
         </is>
       </c>
       <c r="C231" t="n">
@@ -27183,7 +27183,7 @@
       </c>
       <c r="B232" t="inlineStr">
         <is>
-          <t>2026-07-11 08:35:53 PM PT</t>
+          <t>2026-07-11 08:37:53 PM PT</t>
         </is>
       </c>
       <c r="C232" t="n">
@@ -27297,7 +27297,7 @@
       </c>
       <c r="B233" t="inlineStr">
         <is>
-          <t>2026-07-11 08:35:53 PM PT</t>
+          <t>2026-07-11 08:37:53 PM PT</t>
         </is>
       </c>
       <c r="C233" t="n">
@@ -27411,7 +27411,7 @@
       </c>
       <c r="B234" t="inlineStr">
         <is>
-          <t>2026-07-11 08:35:53 PM PT</t>
+          <t>2026-07-11 08:37:53 PM PT</t>
         </is>
       </c>
       <c r="C234" t="n">
@@ -27525,7 +27525,7 @@
       </c>
       <c r="B235" t="inlineStr">
         <is>
-          <t>2026-07-11 08:35:54 PM PT</t>
+          <t>2026-07-11 08:37:54 PM PT</t>
         </is>
       </c>
       <c r="C235" t="n">
@@ -27538,7 +27538,7 @@
       </c>
       <c r="E235" t="inlineStr">
         <is>
-          <t>Top 8 | 2 out</t>
+          <t>Bottom 8 | 0 out</t>
         </is>
       </c>
       <c r="F235" t="n">
@@ -27546,17 +27546,17 @@
       </c>
       <c r="G235" t="inlineStr">
         <is>
-          <t>Top</t>
+          <t>Bottom</t>
         </is>
       </c>
       <c r="H235" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="I235" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J235" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="K235" t="inlineStr">
         <is>
@@ -27648,7 +27648,7 @@
       </c>
       <c r="B236" t="inlineStr">
         <is>
-          <t>2026-07-11 08:35:54 PM PT</t>
+          <t>2026-07-11 08:37:54 PM PT</t>
         </is>
       </c>
       <c r="C236" t="n">
@@ -27661,7 +27661,7 @@
       </c>
       <c r="E236" t="inlineStr">
         <is>
-          <t>Top 8 | 2 out</t>
+          <t>Bottom 8 | 0 out</t>
         </is>
       </c>
       <c r="F236" t="n">
@@ -27669,17 +27669,17 @@
       </c>
       <c r="G236" t="inlineStr">
         <is>
-          <t>Top</t>
+          <t>Bottom</t>
         </is>
       </c>
       <c r="H236" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="I236" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J236" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="K236" t="inlineStr">
         <is>
@@ -27771,7 +27771,7 @@
       </c>
       <c r="B237" t="inlineStr">
         <is>
-          <t>2026-07-11 08:35:53 PM PT</t>
+          <t>2026-07-11 08:37:53 PM PT</t>
         </is>
       </c>
       <c r="C237" t="n">
@@ -27885,7 +27885,7 @@
       </c>
       <c r="B238" t="inlineStr">
         <is>
-          <t>2026-07-11 08:35:53 PM PT</t>
+          <t>2026-07-11 08:37:53 PM PT</t>
         </is>
       </c>
       <c r="C238" t="n">
@@ -27999,7 +27999,7 @@
       </c>
       <c r="B239" t="inlineStr">
         <is>
-          <t>2026-07-11 08:35:53 PM PT</t>
+          <t>2026-07-11 08:37:53 PM PT</t>
         </is>
       </c>
       <c r="C239" t="n">
@@ -28113,7 +28113,7 @@
       </c>
       <c r="B240" t="inlineStr">
         <is>
-          <t>2026-07-11 08:35:53 PM PT</t>
+          <t>2026-07-11 08:37:53 PM PT</t>
         </is>
       </c>
       <c r="C240" t="n">
@@ -28227,7 +28227,7 @@
       </c>
       <c r="B241" t="inlineStr">
         <is>
-          <t>2026-07-11 08:35:53 PM PT</t>
+          <t>2026-07-11 08:37:53 PM PT</t>
         </is>
       </c>
       <c r="C241" t="n">
@@ -28341,7 +28341,7 @@
       </c>
       <c r="B242" t="inlineStr">
         <is>
-          <t>2026-07-11 08:35:53 PM PT</t>
+          <t>2026-07-11 08:37:53 PM PT</t>
         </is>
       </c>
       <c r="C242" t="n">
@@ -28455,7 +28455,7 @@
       </c>
       <c r="B243" t="inlineStr">
         <is>
-          <t>2026-07-11 08:35:53 PM PT</t>
+          <t>2026-07-11 08:37:53 PM PT</t>
         </is>
       </c>
       <c r="C243" t="n">
@@ -28569,7 +28569,7 @@
       </c>
       <c r="B244" t="inlineStr">
         <is>
-          <t>2026-07-11 08:35:54 PM PT</t>
+          <t>2026-07-11 08:37:54 PM PT</t>
         </is>
       </c>
       <c r="C244" t="n">
@@ -28683,7 +28683,7 @@
       </c>
       <c r="B245" t="inlineStr">
         <is>
-          <t>2026-07-11 08:35:54 PM PT</t>
+          <t>2026-07-11 08:37:54 PM PT</t>
         </is>
       </c>
       <c r="C245" t="n">
@@ -28797,7 +28797,7 @@
       </c>
       <c r="B246" t="inlineStr">
         <is>
-          <t>2026-07-11 08:35:54 PM PT</t>
+          <t>2026-07-11 08:37:54 PM PT</t>
         </is>
       </c>
       <c r="C246" t="n">
@@ -28911,7 +28911,7 @@
       </c>
       <c r="B247" t="inlineStr">
         <is>
-          <t>2026-07-11 08:35:53 PM PT</t>
+          <t>2026-07-11 08:37:54 PM PT</t>
         </is>
       </c>
       <c r="C247" t="n">
@@ -29025,7 +29025,7 @@
       </c>
       <c r="B248" t="inlineStr">
         <is>
-          <t>2026-07-11 08:35:53 PM PT</t>
+          <t>2026-07-11 08:37:54 PM PT</t>
         </is>
       </c>
       <c r="C248" t="n">
@@ -29139,7 +29139,7 @@
       </c>
       <c r="B249" t="inlineStr">
         <is>
-          <t>2026-07-11 08:35:53 PM PT</t>
+          <t>2026-07-11 08:37:54 PM PT</t>
         </is>
       </c>
       <c r="C249" t="n">
@@ -29253,7 +29253,7 @@
       </c>
       <c r="B250" t="inlineStr">
         <is>
-          <t>2026-07-11 08:35:53 PM PT</t>
+          <t>2026-07-11 08:37:53 PM PT</t>
         </is>
       </c>
       <c r="C250" t="n">
@@ -29367,7 +29367,7 @@
       </c>
       <c r="B251" t="inlineStr">
         <is>
-          <t>2026-07-11 08:35:53 PM PT</t>
+          <t>2026-07-11 08:37:53 PM PT</t>
         </is>
       </c>
       <c r="C251" t="n">
@@ -29481,7 +29481,7 @@
       </c>
       <c r="B252" t="inlineStr">
         <is>
-          <t>2026-07-11 08:35:53 PM PT</t>
+          <t>2026-07-11 08:37:53 PM PT</t>
         </is>
       </c>
       <c r="C252" t="n">
@@ -29595,7 +29595,7 @@
       </c>
       <c r="B253" t="inlineStr">
         <is>
-          <t>2026-07-11 08:35:54 PM PT</t>
+          <t>2026-07-11 08:37:54 PM PT</t>
         </is>
       </c>
       <c r="C253" t="n">
@@ -29709,7 +29709,7 @@
       </c>
       <c r="B254" t="inlineStr">
         <is>
-          <t>2026-07-11 08:35:54 PM PT</t>
+          <t>2026-07-11 08:37:54 PM PT</t>
         </is>
       </c>
       <c r="C254" t="n">
@@ -29823,7 +29823,7 @@
       </c>
       <c r="B255" t="inlineStr">
         <is>
-          <t>2026-07-11 08:35:54 PM PT</t>
+          <t>2026-07-11 08:37:54 PM PT</t>
         </is>
       </c>
       <c r="C255" t="n">
@@ -29937,7 +29937,7 @@
       </c>
       <c r="B256" t="inlineStr">
         <is>
-          <t>2026-07-11 08:35:54 PM PT</t>
+          <t>2026-07-11 08:37:54 PM PT</t>
         </is>
       </c>
       <c r="C256" t="n">
@@ -30051,7 +30051,7 @@
       </c>
       <c r="B257" t="inlineStr">
         <is>
-          <t>2026-07-11 08:35:54 PM PT</t>
+          <t>2026-07-11 08:37:54 PM PT</t>
         </is>
       </c>
       <c r="C257" t="n">
@@ -30165,7 +30165,7 @@
       </c>
       <c r="B258" t="inlineStr">
         <is>
-          <t>2026-07-11 08:35:53 PM PT</t>
+          <t>2026-07-11 08:37:53 PM PT</t>
         </is>
       </c>
       <c r="C258" t="n">
@@ -30279,7 +30279,7 @@
       </c>
       <c r="B259" t="inlineStr">
         <is>
-          <t>2026-07-11 08:35:53 PM PT</t>
+          <t>2026-07-11 08:37:53 PM PT</t>
         </is>
       </c>
       <c r="C259" t="n">
@@ -30393,7 +30393,7 @@
       </c>
       <c r="B260" t="inlineStr">
         <is>
-          <t>2026-07-11 08:35:53 PM PT</t>
+          <t>2026-07-11 08:37:53 PM PT</t>
         </is>
       </c>
       <c r="C260" t="n">
@@ -30507,7 +30507,7 @@
       </c>
       <c r="B261" t="inlineStr">
         <is>
-          <t>2026-07-11 08:35:53 PM PT</t>
+          <t>2026-07-11 08:37:53 PM PT</t>
         </is>
       </c>
       <c r="C261" t="n">
@@ -30621,7 +30621,7 @@
       </c>
       <c r="B262" t="inlineStr">
         <is>
-          <t>2026-07-11 08:35:53 PM PT</t>
+          <t>2026-07-11 08:37:53 PM PT</t>
         </is>
       </c>
       <c r="C262" t="n">
@@ -30735,7 +30735,7 @@
       </c>
       <c r="B263" t="inlineStr">
         <is>
-          <t>2026-07-11 08:35:53 PM PT</t>
+          <t>2026-07-11 08:37:53 PM PT</t>
         </is>
       </c>
       <c r="C263" t="n">
@@ -30849,7 +30849,7 @@
       </c>
       <c r="B264" t="inlineStr">
         <is>
-          <t>2026-07-11 08:35:53 PM PT</t>
+          <t>2026-07-11 08:37:53 PM PT</t>
         </is>
       </c>
       <c r="C264" t="n">
@@ -30963,7 +30963,7 @@
       </c>
       <c r="B265" t="inlineStr">
         <is>
-          <t>2026-07-11 08:35:53 PM PT</t>
+          <t>2026-07-11 08:37:53 PM PT</t>
         </is>
       </c>
       <c r="C265" t="n">
@@ -31077,7 +31077,7 @@
       </c>
       <c r="B266" t="inlineStr">
         <is>
-          <t>2026-07-11 08:35:53 PM PT</t>
+          <t>2026-07-11 08:37:53 PM PT</t>
         </is>
       </c>
       <c r="C266" t="n">
@@ -31191,7 +31191,7 @@
       </c>
       <c r="B267" t="inlineStr">
         <is>
-          <t>2026-07-11 08:35:53 PM PT</t>
+          <t>2026-07-11 08:37:53 PM PT</t>
         </is>
       </c>
       <c r="C267" t="n">
@@ -31305,7 +31305,7 @@
       </c>
       <c r="B268" t="inlineStr">
         <is>
-          <t>2026-07-11 08:35:53 PM PT</t>
+          <t>2026-07-11 08:37:53 PM PT</t>
         </is>
       </c>
       <c r="C268" t="n">
@@ -31419,7 +31419,7 @@
       </c>
       <c r="B269" t="inlineStr">
         <is>
-          <t>2026-07-11 08:35:53 PM PT</t>
+          <t>2026-07-11 08:37:54 PM PT</t>
         </is>
       </c>
       <c r="C269" t="n">
@@ -31533,7 +31533,7 @@
       </c>
       <c r="B270" t="inlineStr">
         <is>
-          <t>2026-07-11 08:35:53 PM PT</t>
+          <t>2026-07-11 08:37:54 PM PT</t>
         </is>
       </c>
       <c r="C270" t="n">
@@ -31647,7 +31647,7 @@
       </c>
       <c r="B271" t="inlineStr">
         <is>
-          <t>2026-07-11 08:35:53 PM PT</t>
+          <t>2026-07-11 08:37:54 PM PT</t>
         </is>
       </c>
       <c r="C271" t="n">
@@ -31761,7 +31761,7 @@
       </c>
       <c r="B272" t="inlineStr">
         <is>
-          <t>2026-07-11 08:35:53 PM PT</t>
+          <t>2026-07-11 08:37:54 PM PT</t>
         </is>
       </c>
       <c r="C272" t="n">
@@ -31875,7 +31875,7 @@
       </c>
       <c r="B273" t="inlineStr">
         <is>
-          <t>2026-07-11 08:35:53 PM PT</t>
+          <t>2026-07-11 08:37:54 PM PT</t>
         </is>
       </c>
       <c r="C273" t="n">
@@ -31989,7 +31989,7 @@
       </c>
       <c r="B274" t="inlineStr">
         <is>
-          <t>2026-07-11 08:35:53 PM PT</t>
+          <t>2026-07-11 08:37:54 PM PT</t>
         </is>
       </c>
       <c r="C274" t="n">
@@ -32103,7 +32103,7 @@
       </c>
       <c r="B275" t="inlineStr">
         <is>
-          <t>2026-07-11 08:35:53 PM PT</t>
+          <t>2026-07-11 08:37:54 PM PT</t>
         </is>
       </c>
       <c r="C275" t="n">
@@ -32217,7 +32217,7 @@
       </c>
       <c r="B276" t="inlineStr">
         <is>
-          <t>2026-07-11 08:35:52 PM PT</t>
+          <t>2026-07-11 08:37:53 PM PT</t>
         </is>
       </c>
       <c r="C276" t="n">
@@ -32331,7 +32331,7 @@
       </c>
       <c r="B277" t="inlineStr">
         <is>
-          <t>2026-07-11 08:35:52 PM PT</t>
+          <t>2026-07-11 08:37:53 PM PT</t>
         </is>
       </c>
       <c r="C277" t="n">
@@ -32445,7 +32445,7 @@
       </c>
       <c r="B278" t="inlineStr">
         <is>
-          <t>2026-07-11 08:35:52 PM PT</t>
+          <t>2026-07-11 08:37:53 PM PT</t>
         </is>
       </c>
       <c r="C278" t="n">
@@ -32559,7 +32559,7 @@
       </c>
       <c r="B279" t="inlineStr">
         <is>
-          <t>2026-07-11 08:35:54 PM PT</t>
+          <t>2026-07-11 08:37:54 PM PT</t>
         </is>
       </c>
       <c r="C279" t="n">
@@ -32572,7 +32572,7 @@
       </c>
       <c r="E279" t="inlineStr">
         <is>
-          <t>Top 8 | 2 out</t>
+          <t>Bottom 8 | 0 out</t>
         </is>
       </c>
       <c r="F279" t="n">
@@ -32580,17 +32580,17 @@
       </c>
       <c r="G279" t="inlineStr">
         <is>
-          <t>Top</t>
+          <t>Bottom</t>
         </is>
       </c>
       <c r="H279" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="I279" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J279" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="K279" t="inlineStr">
         <is>
@@ -32682,7 +32682,7 @@
       </c>
       <c r="B280" t="inlineStr">
         <is>
-          <t>2026-07-11 08:35:54 PM PT</t>
+          <t>2026-07-11 08:37:54 PM PT</t>
         </is>
       </c>
       <c r="C280" t="n">
@@ -32695,7 +32695,7 @@
       </c>
       <c r="E280" t="inlineStr">
         <is>
-          <t>Top 8 | 2 out</t>
+          <t>Bottom 8 | 0 out</t>
         </is>
       </c>
       <c r="F280" t="n">
@@ -32703,17 +32703,17 @@
       </c>
       <c r="G280" t="inlineStr">
         <is>
-          <t>Top</t>
+          <t>Bottom</t>
         </is>
       </c>
       <c r="H280" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="I280" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J280" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="K280" t="inlineStr">
         <is>
@@ -32805,7 +32805,7 @@
       </c>
       <c r="B281" t="inlineStr">
         <is>
-          <t>2026-07-11 08:35:54 PM PT</t>
+          <t>2026-07-11 08:37:54 PM PT</t>
         </is>
       </c>
       <c r="C281" t="n">
@@ -32818,7 +32818,7 @@
       </c>
       <c r="E281" t="inlineStr">
         <is>
-          <t>Top 8 | 2 out</t>
+          <t>Bottom 8 | 0 out</t>
         </is>
       </c>
       <c r="F281" t="n">
@@ -32826,17 +32826,17 @@
       </c>
       <c r="G281" t="inlineStr">
         <is>
-          <t>Top</t>
+          <t>Bottom</t>
         </is>
       </c>
       <c r="H281" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="I281" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J281" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="K281" t="inlineStr">
         <is>
@@ -32928,7 +32928,7 @@
       </c>
       <c r="B282" t="inlineStr">
         <is>
-          <t>2026-07-11 08:35:54 PM PT</t>
+          <t>2026-07-11 08:37:54 PM PT</t>
         </is>
       </c>
       <c r="C282" t="n">
@@ -32941,7 +32941,7 @@
       </c>
       <c r="E282" t="inlineStr">
         <is>
-          <t>Top 8 | 2 out</t>
+          <t>Bottom 8 | 0 out</t>
         </is>
       </c>
       <c r="F282" t="n">
@@ -32949,17 +32949,17 @@
       </c>
       <c r="G282" t="inlineStr">
         <is>
-          <t>Top</t>
+          <t>Bottom</t>
         </is>
       </c>
       <c r="H282" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="I282" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J282" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="K282" t="inlineStr">
         <is>
@@ -33051,7 +33051,7 @@
       </c>
       <c r="B283" t="inlineStr">
         <is>
-          <t>2026-07-11 08:35:54 PM PT</t>
+          <t>2026-07-11 08:37:54 PM PT</t>
         </is>
       </c>
       <c r="C283" t="n">
@@ -33064,7 +33064,7 @@
       </c>
       <c r="E283" t="inlineStr">
         <is>
-          <t>Top 8 | 2 out</t>
+          <t>Bottom 8 | 0 out</t>
         </is>
       </c>
       <c r="F283" t="n">
@@ -33072,17 +33072,17 @@
       </c>
       <c r="G283" t="inlineStr">
         <is>
-          <t>Top</t>
+          <t>Bottom</t>
         </is>
       </c>
       <c r="H283" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="I283" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J283" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="K283" t="inlineStr">
         <is>
@@ -33174,7 +33174,7 @@
       </c>
       <c r="B284" t="inlineStr">
         <is>
-          <t>2026-07-11 08:35:54 PM PT</t>
+          <t>2026-07-11 08:37:54 PM PT</t>
         </is>
       </c>
       <c r="C284" t="n">
@@ -33187,7 +33187,7 @@
       </c>
       <c r="E284" t="inlineStr">
         <is>
-          <t>Top 8 | 2 out</t>
+          <t>Bottom 8 | 0 out</t>
         </is>
       </c>
       <c r="F284" t="n">
@@ -33195,17 +33195,17 @@
       </c>
       <c r="G284" t="inlineStr">
         <is>
-          <t>Top</t>
+          <t>Bottom</t>
         </is>
       </c>
       <c r="H284" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="I284" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J284" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="K284" t="inlineStr">
         <is>
@@ -33297,7 +33297,7 @@
       </c>
       <c r="B285" t="inlineStr">
         <is>
-          <t>2026-07-11 08:35:54 PM PT</t>
+          <t>2026-07-11 08:37:54 PM PT</t>
         </is>
       </c>
       <c r="C285" t="n">
@@ -33310,7 +33310,7 @@
       </c>
       <c r="E285" t="inlineStr">
         <is>
-          <t>Top 8 | 2 out</t>
+          <t>Bottom 8 | 0 out</t>
         </is>
       </c>
       <c r="F285" t="n">
@@ -33318,17 +33318,17 @@
       </c>
       <c r="G285" t="inlineStr">
         <is>
-          <t>Top</t>
+          <t>Bottom</t>
         </is>
       </c>
       <c r="H285" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="I285" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J285" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="K285" t="inlineStr">
         <is>
@@ -33420,7 +33420,7 @@
       </c>
       <c r="B286" t="inlineStr">
         <is>
-          <t>2026-07-11 08:35:53 PM PT</t>
+          <t>2026-07-11 08:37:53 PM PT</t>
         </is>
       </c>
       <c r="C286" t="n">
@@ -33534,7 +33534,7 @@
       </c>
       <c r="B287" t="inlineStr">
         <is>
-          <t>2026-07-11 08:35:52 PM PT</t>
+          <t>2026-07-11 08:37:52 PM PT</t>
         </is>
       </c>
       <c r="C287" t="n">
@@ -33648,7 +33648,7 @@
       </c>
       <c r="B288" t="inlineStr">
         <is>
-          <t>2026-07-11 08:35:52 PM PT</t>
+          <t>2026-07-11 08:37:52 PM PT</t>
         </is>
       </c>
       <c r="C288" t="n">
@@ -33762,7 +33762,7 @@
       </c>
       <c r="B289" t="inlineStr">
         <is>
-          <t>2026-07-11 08:35:52 PM PT</t>
+          <t>2026-07-11 08:37:52 PM PT</t>
         </is>
       </c>
       <c r="C289" t="n">
@@ -33876,7 +33876,7 @@
       </c>
       <c r="B290" t="inlineStr">
         <is>
-          <t>2026-07-11 08:35:52 PM PT</t>
+          <t>2026-07-11 08:37:52 PM PT</t>
         </is>
       </c>
       <c r="C290" t="n">
@@ -33990,7 +33990,7 @@
       </c>
       <c r="B291" t="inlineStr">
         <is>
-          <t>2026-07-11 08:35:52 PM PT</t>
+          <t>2026-07-11 08:37:52 PM PT</t>
         </is>
       </c>
       <c r="C291" t="n">
@@ -34104,7 +34104,7 @@
       </c>
       <c r="B292" t="inlineStr">
         <is>
-          <t>2026-07-11 08:35:52 PM PT</t>
+          <t>2026-07-11 08:37:52 PM PT</t>
         </is>
       </c>
       <c r="C292" t="n">
@@ -34218,7 +34218,7 @@
       </c>
       <c r="B293" t="inlineStr">
         <is>
-          <t>2026-07-11 08:35:52 PM PT</t>
+          <t>2026-07-11 08:37:53 PM PT</t>
         </is>
       </c>
       <c r="C293" t="n">
@@ -34332,7 +34332,7 @@
       </c>
       <c r="B294" t="inlineStr">
         <is>
-          <t>2026-07-11 08:35:53 PM PT</t>
+          <t>2026-07-11 08:37:53 PM PT</t>
         </is>
       </c>
       <c r="C294" t="n">
@@ -34446,7 +34446,7 @@
       </c>
       <c r="B295" t="inlineStr">
         <is>
-          <t>2026-07-11 08:35:53 PM PT</t>
+          <t>2026-07-11 08:37:53 PM PT</t>
         </is>
       </c>
       <c r="C295" t="n">
@@ -34560,7 +34560,7 @@
       </c>
       <c r="B296" t="inlineStr">
         <is>
-          <t>2026-07-11 08:35:53 PM PT</t>
+          <t>2026-07-11 08:37:53 PM PT</t>
         </is>
       </c>
       <c r="C296" t="n">
@@ -34674,7 +34674,7 @@
       </c>
       <c r="B297" t="inlineStr">
         <is>
-          <t>2026-07-11 08:35:53 PM PT</t>
+          <t>2026-07-11 08:37:53 PM PT</t>
         </is>
       </c>
       <c r="C297" t="n">
@@ -34788,7 +34788,7 @@
       </c>
       <c r="B298" t="inlineStr">
         <is>
-          <t>2026-07-11 08:35:53 PM PT</t>
+          <t>2026-07-11 08:37:53 PM PT</t>
         </is>
       </c>
       <c r="C298" t="n">
@@ -34902,7 +34902,7 @@
       </c>
       <c r="B299" t="inlineStr">
         <is>
-          <t>2026-07-11 08:35:53 PM PT</t>
+          <t>2026-07-11 08:37:53 PM PT</t>
         </is>
       </c>
       <c r="C299" t="n">
@@ -35016,7 +35016,7 @@
       </c>
       <c r="B300" t="inlineStr">
         <is>
-          <t>2026-07-11 08:35:53 PM PT</t>
+          <t>2026-07-11 08:37:53 PM PT</t>
         </is>
       </c>
       <c r="C300" t="n">
@@ -35130,7 +35130,7 @@
       </c>
       <c r="B301" t="inlineStr">
         <is>
-          <t>2026-07-11 08:35:53 PM PT</t>
+          <t>2026-07-11 08:37:53 PM PT</t>
         </is>
       </c>
       <c r="C301" t="n">
@@ -35244,7 +35244,7 @@
       </c>
       <c r="B302" t="inlineStr">
         <is>
-          <t>2026-07-11 08:35:52 PM PT</t>
+          <t>2026-07-11 08:37:52 PM PT</t>
         </is>
       </c>
       <c r="C302" t="n">
@@ -35358,7 +35358,7 @@
       </c>
       <c r="B303" t="inlineStr">
         <is>
-          <t>2026-07-11 08:35:52 PM PT</t>
+          <t>2026-07-11 08:37:52 PM PT</t>
         </is>
       </c>
       <c r="C303" t="n">
@@ -35472,7 +35472,7 @@
       </c>
       <c r="B304" t="inlineStr">
         <is>
-          <t>2026-07-11 08:35:52 PM PT</t>
+          <t>2026-07-11 08:37:52 PM PT</t>
         </is>
       </c>
       <c r="C304" t="n">
@@ -35586,7 +35586,7 @@
       </c>
       <c r="B305" t="inlineStr">
         <is>
-          <t>2026-07-11 08:35:52 PM PT</t>
+          <t>2026-07-11 08:37:52 PM PT</t>
         </is>
       </c>
       <c r="C305" t="n">
@@ -35700,7 +35700,7 @@
       </c>
       <c r="B306" t="inlineStr">
         <is>
-          <t>2026-07-11 08:35:52 PM PT</t>
+          <t>2026-07-11 08:37:52 PM PT</t>
         </is>
       </c>
       <c r="C306" t="n">
@@ -35814,7 +35814,7 @@
       </c>
       <c r="B307" t="inlineStr">
         <is>
-          <t>2026-07-11 08:35:52 PM PT</t>
+          <t>2026-07-11 08:37:52 PM PT</t>
         </is>
       </c>
       <c r="C307" t="n">
@@ -35928,7 +35928,7 @@
       </c>
       <c r="B308" t="inlineStr">
         <is>
-          <t>2026-07-11 08:35:52 PM PT</t>
+          <t>2026-07-11 08:37:52 PM PT</t>
         </is>
       </c>
       <c r="C308" t="n">
@@ -36042,7 +36042,7 @@
       </c>
       <c r="B309" t="inlineStr">
         <is>
-          <t>2026-07-11 08:35:52 PM PT</t>
+          <t>2026-07-11 08:37:52 PM PT</t>
         </is>
       </c>
       <c r="C309" t="n">
@@ -36156,7 +36156,7 @@
       </c>
       <c r="B310" t="inlineStr">
         <is>
-          <t>2026-07-11 08:35:54 PM PT</t>
+          <t>2026-07-11 08:37:54 PM PT</t>
         </is>
       </c>
       <c r="C310" t="n">
@@ -36184,7 +36184,7 @@
         <v>1</v>
       </c>
       <c r="I310" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="J310" t="n">
         <v>0</v>
@@ -36279,7 +36279,7 @@
       </c>
       <c r="B311" t="inlineStr">
         <is>
-          <t>2026-07-11 08:35:53 PM PT</t>
+          <t>2026-07-11 08:37:53 PM PT</t>
         </is>
       </c>
       <c r="C311" t="n">
@@ -36393,7 +36393,7 @@
       </c>
       <c r="B312" t="inlineStr">
         <is>
-          <t>2026-07-11 08:35:53 PM PT</t>
+          <t>2026-07-11 08:37:53 PM PT</t>
         </is>
       </c>
       <c r="C312" t="n">
@@ -36507,7 +36507,7 @@
       </c>
       <c r="B313" t="inlineStr">
         <is>
-          <t>2026-07-11 08:35:53 PM PT</t>
+          <t>2026-07-11 08:37:53 PM PT</t>
         </is>
       </c>
       <c r="C313" t="n">
@@ -36621,7 +36621,7 @@
       </c>
       <c r="B314" t="inlineStr">
         <is>
-          <t>2026-07-11 08:35:53 PM PT</t>
+          <t>2026-07-11 08:37:53 PM PT</t>
         </is>
       </c>
       <c r="C314" t="n">
@@ -36735,7 +36735,7 @@
       </c>
       <c r="B315" t="inlineStr">
         <is>
-          <t>2026-07-11 08:35:53 PM PT</t>
+          <t>2026-07-11 08:37:53 PM PT</t>
         </is>
       </c>
       <c r="C315" t="n">
@@ -36849,7 +36849,7 @@
       </c>
       <c r="B316" t="inlineStr">
         <is>
-          <t>2026-07-11 08:35:53 PM PT</t>
+          <t>2026-07-11 08:37:53 PM PT</t>
         </is>
       </c>
       <c r="C316" t="n">
@@ -36963,7 +36963,7 @@
       </c>
       <c r="B317" t="inlineStr">
         <is>
-          <t>2026-07-11 08:35:53 PM PT</t>
+          <t>2026-07-11 08:37:53 PM PT</t>
         </is>
       </c>
       <c r="C317" t="n">
@@ -37077,7 +37077,7 @@
       </c>
       <c r="B318" t="inlineStr">
         <is>
-          <t>2026-07-11 08:35:54 PM PT</t>
+          <t>2026-07-11 08:37:54 PM PT</t>
         </is>
       </c>
       <c r="C318" t="n">
@@ -37191,7 +37191,7 @@
       </c>
       <c r="B319" t="inlineStr">
         <is>
-          <t>2026-07-11 08:35:54 PM PT</t>
+          <t>2026-07-11 08:37:54 PM PT</t>
         </is>
       </c>
       <c r="C319" t="n">
@@ -37305,7 +37305,7 @@
       </c>
       <c r="B320" t="inlineStr">
         <is>
-          <t>2026-07-11 08:35:54 PM PT</t>
+          <t>2026-07-11 08:37:54 PM PT</t>
         </is>
       </c>
       <c r="C320" t="n">
@@ -37419,7 +37419,7 @@
       </c>
       <c r="B321" t="inlineStr">
         <is>
-          <t>2026-07-11 08:35:54 PM PT</t>
+          <t>2026-07-11 08:37:54 PM PT</t>
         </is>
       </c>
       <c r="C321" t="n">
@@ -37533,7 +37533,7 @@
       </c>
       <c r="B322" t="inlineStr">
         <is>
-          <t>2026-07-11 08:35:53 PM PT</t>
+          <t>2026-07-11 08:37:53 PM PT</t>
         </is>
       </c>
       <c r="C322" t="n">
@@ -37647,7 +37647,7 @@
       </c>
       <c r="B323" t="inlineStr">
         <is>
-          <t>2026-07-11 08:35:53 PM PT</t>
+          <t>2026-07-11 08:37:53 PM PT</t>
         </is>
       </c>
       <c r="C323" t="n">
@@ -37761,7 +37761,7 @@
       </c>
       <c r="B324" t="inlineStr">
         <is>
-          <t>2026-07-11 08:35:53 PM PT</t>
+          <t>2026-07-11 08:37:53 PM PT</t>
         </is>
       </c>
       <c r="C324" t="n">
@@ -37875,7 +37875,7 @@
       </c>
       <c r="B325" t="inlineStr">
         <is>
-          <t>2026-07-11 08:35:53 PM PT</t>
+          <t>2026-07-11 08:37:53 PM PT</t>
         </is>
       </c>
       <c r="C325" t="n">
@@ -37989,7 +37989,7 @@
       </c>
       <c r="B326" t="inlineStr">
         <is>
-          <t>2026-07-11 08:35:53 PM PT</t>
+          <t>2026-07-11 08:37:54 PM PT</t>
         </is>
       </c>
       <c r="C326" t="n">
@@ -38103,7 +38103,7 @@
       </c>
       <c r="B327" t="inlineStr">
         <is>
-          <t>2026-07-11 08:35:53 PM PT</t>
+          <t>2026-07-11 08:37:54 PM PT</t>
         </is>
       </c>
       <c r="C327" t="n">
@@ -38217,7 +38217,7 @@
       </c>
       <c r="B328" t="inlineStr">
         <is>
-          <t>2026-07-11 08:35:53 PM PT</t>
+          <t>2026-07-11 08:37:54 PM PT</t>
         </is>
       </c>
       <c r="C328" t="n">
@@ -38331,7 +38331,7 @@
       </c>
       <c r="B329" t="inlineStr">
         <is>
-          <t>2026-07-11 08:35:53 PM PT</t>
+          <t>2026-07-11 08:37:54 PM PT</t>
         </is>
       </c>
       <c r="C329" t="n">
@@ -38445,7 +38445,7 @@
       </c>
       <c r="B330" t="inlineStr">
         <is>
-          <t>2026-07-11 08:35:53 PM PT</t>
+          <t>2026-07-11 08:37:54 PM PT</t>
         </is>
       </c>
       <c r="C330" t="n">
@@ -38559,7 +38559,7 @@
       </c>
       <c r="B331" t="inlineStr">
         <is>
-          <t>2026-07-11 08:35:54 PM PT</t>
+          <t>2026-07-11 08:37:54 PM PT</t>
         </is>
       </c>
       <c r="C331" t="n">
@@ -38587,7 +38587,7 @@
         <v>1</v>
       </c>
       <c r="I331" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="J331" t="n">
         <v>0</v>
@@ -38682,7 +38682,7 @@
       </c>
       <c r="B332" t="inlineStr">
         <is>
-          <t>2026-07-11 08:35:53 PM PT</t>
+          <t>2026-07-11 08:37:53 PM PT</t>
         </is>
       </c>
       <c r="C332" t="n">
@@ -38796,7 +38796,7 @@
       </c>
       <c r="B333" t="inlineStr">
         <is>
-          <t>2026-07-11 08:35:53 PM PT</t>
+          <t>2026-07-11 08:37:53 PM PT</t>
         </is>
       </c>
       <c r="C333" t="n">

--- a/live_mlb_hitter_fantasy_scores_2026_07_11.xlsx
+++ b/live_mlb_hitter_fantasy_scores_2026_07_11.xlsx
@@ -11,7 +11,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Scoring" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Live Fantasy Scores'!$A$1:$AG$333</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Live Fantasy Scores'!$A$1:$AG$334</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -480,7 +480,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AG333"/>
+  <dimension ref="A1:AG334"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -693,7 +693,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-07-11 08:37:52 PM PT</t>
+          <t>2026-07-11 08:39:52 PM PT</t>
         </is>
       </c>
       <c r="C2" t="n">
@@ -807,7 +807,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>2026-07-11 08:37:54 PM PT</t>
+          <t>2026-07-11 08:39:54 PM PT</t>
         </is>
       </c>
       <c r="C3" t="n">
@@ -820,7 +820,7 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Bottom 8 | 0 out</t>
+          <t>Bottom 8 | 1 out</t>
         </is>
       </c>
       <c r="F3" t="n">
@@ -832,13 +832,13 @@
         </is>
       </c>
       <c r="H3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I3" t="n">
         <v>0</v>
       </c>
       <c r="J3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K3" t="inlineStr">
         <is>
@@ -930,7 +930,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-07-11 08:37:54 PM PT</t>
+          <t>2026-07-11 08:39:53 PM PT</t>
         </is>
       </c>
       <c r="C4" t="n">
@@ -1044,7 +1044,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>2026-07-11 08:37:54 PM PT</t>
+          <t>2026-07-11 08:39:54 PM PT</t>
         </is>
       </c>
       <c r="C5" t="n">
@@ -1057,7 +1057,7 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Bottom 8 | 1 out</t>
+          <t>Bottom 8 | 2 out</t>
         </is>
       </c>
       <c r="F5" t="n">
@@ -1069,10 +1069,10 @@
         </is>
       </c>
       <c r="H5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I5" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="J5" t="n">
         <v>0</v>
@@ -1167,7 +1167,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>2026-07-11 08:37:54 PM PT</t>
+          <t>2026-07-11 08:39:53 PM PT</t>
         </is>
       </c>
       <c r="C6" t="n">
@@ -1281,7 +1281,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>2026-07-11 08:37:54 PM PT</t>
+          <t>2026-07-11 08:39:54 PM PT</t>
         </is>
       </c>
       <c r="C7" t="n">
@@ -1395,7 +1395,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>2026-07-11 08:37:53 PM PT</t>
+          <t>2026-07-11 08:39:53 PM PT</t>
         </is>
       </c>
       <c r="C8" t="n">
@@ -1509,7 +1509,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>2026-07-11 08:37:54 PM PT</t>
+          <t>2026-07-11 08:39:53 PM PT</t>
         </is>
       </c>
       <c r="C9" t="n">
@@ -1623,7 +1623,7 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>2026-07-11 08:37:53 PM PT</t>
+          <t>2026-07-11 08:39:53 PM PT</t>
         </is>
       </c>
       <c r="C10" t="n">
@@ -1737,7 +1737,7 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>2026-07-11 08:37:54 PM PT</t>
+          <t>2026-07-11 08:39:54 PM PT</t>
         </is>
       </c>
       <c r="C11" t="n">
@@ -1750,7 +1750,7 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Bottom 8 | 1 out</t>
+          <t>Bottom 8 | 2 out</t>
         </is>
       </c>
       <c r="F11" t="n">
@@ -1762,10 +1762,10 @@
         </is>
       </c>
       <c r="H11" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I11" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="J11" t="n">
         <v>0</v>
@@ -1860,7 +1860,7 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>2026-07-11 08:37:53 PM PT</t>
+          <t>2026-07-11 08:39:53 PM PT</t>
         </is>
       </c>
       <c r="C12" t="n">
@@ -1974,7 +1974,7 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>2026-07-11 08:37:53 PM PT</t>
+          <t>2026-07-11 08:39:53 PM PT</t>
         </is>
       </c>
       <c r="C13" t="n">
@@ -2088,7 +2088,7 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>2026-07-11 08:37:54 PM PT</t>
+          <t>2026-07-11 08:39:54 PM PT</t>
         </is>
       </c>
       <c r="C14" t="n">
@@ -2101,7 +2101,7 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Bottom 8 | 1 out</t>
+          <t>Bottom 8 | 2 out</t>
         </is>
       </c>
       <c r="F14" t="n">
@@ -2113,10 +2113,10 @@
         </is>
       </c>
       <c r="H14" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I14" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="J14" t="n">
         <v>0</v>
@@ -2211,7 +2211,7 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>2026-07-11 08:37:53 PM PT</t>
+          <t>2026-07-11 08:39:53 PM PT</t>
         </is>
       </c>
       <c r="C15" t="n">
@@ -2325,7 +2325,7 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>2026-07-11 08:37:53 PM PT</t>
+          <t>2026-07-11 08:39:53 PM PT</t>
         </is>
       </c>
       <c r="C16" t="n">
@@ -2439,7 +2439,7 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>2026-07-11 08:37:54 PM PT</t>
+          <t>2026-07-11 08:39:53 PM PT</t>
         </is>
       </c>
       <c r="C17" t="n">
@@ -2553,7 +2553,7 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>2026-07-11 08:37:54 PM PT</t>
+          <t>2026-07-11 08:39:54 PM PT</t>
         </is>
       </c>
       <c r="C18" t="n">
@@ -2566,7 +2566,7 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Bottom 8 | 1 out</t>
+          <t>Bottom 8 | 2 out</t>
         </is>
       </c>
       <c r="F18" t="n">
@@ -2578,10 +2578,10 @@
         </is>
       </c>
       <c r="H18" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I18" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="J18" t="n">
         <v>0</v>
@@ -2676,7 +2676,7 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>2026-07-11 08:37:53 PM PT</t>
+          <t>2026-07-11 08:39:53 PM PT</t>
         </is>
       </c>
       <c r="C19" t="n">
@@ -2790,7 +2790,7 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>2026-07-11 08:37:54 PM PT</t>
+          <t>2026-07-11 08:39:54 PM PT</t>
         </is>
       </c>
       <c r="C20" t="n">
@@ -2904,7 +2904,7 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>2026-07-11 08:37:53 PM PT</t>
+          <t>2026-07-11 08:39:53 PM PT</t>
         </is>
       </c>
       <c r="C21" t="n">
@@ -3018,7 +3018,7 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>2026-07-11 08:37:53 PM PT</t>
+          <t>2026-07-11 08:39:53 PM PT</t>
         </is>
       </c>
       <c r="C22" t="n">
@@ -3132,7 +3132,7 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>2026-07-11 08:37:54 PM PT</t>
+          <t>2026-07-11 08:39:54 PM PT</t>
         </is>
       </c>
       <c r="C23" t="n">
@@ -3145,7 +3145,7 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Bottom 8 | 0 out</t>
+          <t>Bottom 8 | 1 out</t>
         </is>
       </c>
       <c r="F23" t="n">
@@ -3157,13 +3157,13 @@
         </is>
       </c>
       <c r="H23" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I23" t="n">
         <v>0</v>
       </c>
       <c r="J23" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K23" t="inlineStr">
         <is>
@@ -3255,7 +3255,7 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>2026-07-11 08:37:54 PM PT</t>
+          <t>2026-07-11 08:39:53 PM PT</t>
         </is>
       </c>
       <c r="C24" t="n">
@@ -3369,7 +3369,7 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>2026-07-11 08:37:53 PM PT</t>
+          <t>2026-07-11 08:39:53 PM PT</t>
         </is>
       </c>
       <c r="C25" t="n">
@@ -3483,7 +3483,7 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>2026-07-11 08:37:54 PM PT</t>
+          <t>2026-07-11 08:39:54 PM PT</t>
         </is>
       </c>
       <c r="C26" t="n">
@@ -3597,7 +3597,7 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>2026-07-11 08:37:52 PM PT</t>
+          <t>2026-07-11 08:39:52 PM PT</t>
         </is>
       </c>
       <c r="C27" t="n">
@@ -3711,7 +3711,7 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>2026-07-11 08:37:53 PM PT</t>
+          <t>2026-07-11 08:39:53 PM PT</t>
         </is>
       </c>
       <c r="C28" t="n">
@@ -3825,7 +3825,7 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>2026-07-11 08:37:53 PM PT</t>
+          <t>2026-07-11 08:39:53 PM PT</t>
         </is>
       </c>
       <c r="C29" t="n">
@@ -3939,7 +3939,7 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>2026-07-11 08:37:54 PM PT</t>
+          <t>2026-07-11 08:39:54 PM PT</t>
         </is>
       </c>
       <c r="C30" t="n">
@@ -4053,7 +4053,7 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>2026-07-11 08:37:54 PM PT</t>
+          <t>2026-07-11 08:39:54 PM PT</t>
         </is>
       </c>
       <c r="C31" t="n">
@@ -4167,7 +4167,7 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>2026-07-11 08:37:53 PM PT</t>
+          <t>2026-07-11 08:39:53 PM PT</t>
         </is>
       </c>
       <c r="C32" t="n">
@@ -4281,7 +4281,7 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>2026-07-11 08:37:53 PM PT</t>
+          <t>2026-07-11 08:39:53 PM PT</t>
         </is>
       </c>
       <c r="C33" t="n">
@@ -4395,7 +4395,7 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>2026-07-11 08:37:54 PM PT</t>
+          <t>2026-07-11 08:39:53 PM PT</t>
         </is>
       </c>
       <c r="C34" t="n">
@@ -4509,7 +4509,7 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>2026-07-11 08:37:52 PM PT</t>
+          <t>2026-07-11 08:39:52 PM PT</t>
         </is>
       </c>
       <c r="C35" t="n">
@@ -4623,7 +4623,7 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>2026-07-11 08:37:52 PM PT</t>
+          <t>2026-07-11 08:39:53 PM PT</t>
         </is>
       </c>
       <c r="C36" t="n">
@@ -4737,7 +4737,7 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>2026-07-11 08:37:54 PM PT</t>
+          <t>2026-07-11 08:39:54 PM PT</t>
         </is>
       </c>
       <c r="C37" t="n">
@@ -4750,7 +4750,7 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Bottom 8 | 1 out</t>
+          <t>Bottom 8 | 2 out</t>
         </is>
       </c>
       <c r="F37" t="n">
@@ -4762,10 +4762,10 @@
         </is>
       </c>
       <c r="H37" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I37" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="J37" t="n">
         <v>0</v>
@@ -4860,7 +4860,7 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>2026-07-11 08:37:53 PM PT</t>
+          <t>2026-07-11 08:39:53 PM PT</t>
         </is>
       </c>
       <c r="C38" t="n">
@@ -4974,7 +4974,7 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>2026-07-11 08:37:53 PM PT</t>
+          <t>2026-07-11 08:39:53 PM PT</t>
         </is>
       </c>
       <c r="C39" t="n">
@@ -5088,7 +5088,7 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>2026-07-11 08:37:53 PM PT</t>
+          <t>2026-07-11 08:39:53 PM PT</t>
         </is>
       </c>
       <c r="C40" t="n">
@@ -5202,7 +5202,7 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>2026-07-11 08:37:52 PM PT</t>
+          <t>2026-07-11 08:39:53 PM PT</t>
         </is>
       </c>
       <c r="C41" t="n">
@@ -5316,7 +5316,7 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>2026-07-11 08:37:54 PM PT</t>
+          <t>2026-07-11 08:39:54 PM PT</t>
         </is>
       </c>
       <c r="C42" t="n">
@@ -5329,7 +5329,7 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>Bottom 8 | 0 out</t>
+          <t>Bottom 8 | 1 out</t>
         </is>
       </c>
       <c r="F42" t="n">
@@ -5341,13 +5341,13 @@
         </is>
       </c>
       <c r="H42" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I42" t="n">
         <v>0</v>
       </c>
       <c r="J42" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K42" t="inlineStr">
         <is>
@@ -5439,7 +5439,7 @@
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>2026-07-11 08:37:54 PM PT</t>
+          <t>2026-07-11 08:39:54 PM PT</t>
         </is>
       </c>
       <c r="C43" t="n">
@@ -5553,7 +5553,7 @@
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>2026-07-11 08:37:54 PM PT</t>
+          <t>2026-07-11 08:39:53 PM PT</t>
         </is>
       </c>
       <c r="C44" t="n">
@@ -5667,7 +5667,7 @@
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>2026-07-11 08:37:54 PM PT</t>
+          <t>2026-07-11 08:39:53 PM PT</t>
         </is>
       </c>
       <c r="C45" t="n">
@@ -5781,7 +5781,7 @@
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>2026-07-11 08:37:54 PM PT</t>
+          <t>2026-07-11 08:39:54 PM PT</t>
         </is>
       </c>
       <c r="C46" t="n">
@@ -5895,7 +5895,7 @@
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>2026-07-11 08:37:53 PM PT</t>
+          <t>2026-07-11 08:39:53 PM PT</t>
         </is>
       </c>
       <c r="C47" t="n">
@@ -6009,7 +6009,7 @@
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>2026-07-11 08:37:53 PM PT</t>
+          <t>2026-07-11 08:39:53 PM PT</t>
         </is>
       </c>
       <c r="C48" t="n">
@@ -6123,7 +6123,7 @@
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>2026-07-11 08:37:54 PM PT</t>
+          <t>2026-07-11 08:39:53 PM PT</t>
         </is>
       </c>
       <c r="C49" t="n">
@@ -6237,7 +6237,7 @@
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>2026-07-11 08:37:53 PM PT</t>
+          <t>2026-07-11 08:39:53 PM PT</t>
         </is>
       </c>
       <c r="C50" t="n">
@@ -6351,7 +6351,7 @@
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>2026-07-11 08:37:52 PM PT</t>
+          <t>2026-07-11 08:39:53 PM PT</t>
         </is>
       </c>
       <c r="C51" t="n">
@@ -6465,7 +6465,7 @@
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>2026-07-11 08:37:54 PM PT</t>
+          <t>2026-07-11 08:39:54 PM PT</t>
         </is>
       </c>
       <c r="C52" t="n">
@@ -6478,7 +6478,7 @@
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>Bottom 8 | 1 out</t>
+          <t>Bottom 8 | 2 out</t>
         </is>
       </c>
       <c r="F52" t="n">
@@ -6490,10 +6490,10 @@
         </is>
       </c>
       <c r="H52" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I52" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="J52" t="n">
         <v>0</v>
@@ -6588,7 +6588,7 @@
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>2026-07-11 08:37:54 PM PT</t>
+          <t>2026-07-11 08:39:54 PM PT</t>
         </is>
       </c>
       <c r="C53" t="n">
@@ -6601,7 +6601,7 @@
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>Bottom 8 | 0 out</t>
+          <t>Bottom 8 | 1 out</t>
         </is>
       </c>
       <c r="F53" t="n">
@@ -6613,13 +6613,13 @@
         </is>
       </c>
       <c r="H53" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I53" t="n">
         <v>0</v>
       </c>
       <c r="J53" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K53" t="inlineStr">
         <is>
@@ -6711,7 +6711,7 @@
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>2026-07-11 08:37:54 PM PT</t>
+          <t>2026-07-11 08:39:54 PM PT</t>
         </is>
       </c>
       <c r="C54" t="n">
@@ -6825,7 +6825,7 @@
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>2026-07-11 08:37:54 PM PT</t>
+          <t>2026-07-11 08:39:54 PM PT</t>
         </is>
       </c>
       <c r="C55" t="n">
@@ -6939,7 +6939,7 @@
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>2026-07-11 08:37:53 PM PT</t>
+          <t>2026-07-11 08:39:53 PM PT</t>
         </is>
       </c>
       <c r="C56" t="n">
@@ -7053,7 +7053,7 @@
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>2026-07-11 08:37:53 PM PT</t>
+          <t>2026-07-11 08:39:53 PM PT</t>
         </is>
       </c>
       <c r="C57" t="n">
@@ -7167,7 +7167,7 @@
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>2026-07-11 08:37:53 PM PT</t>
+          <t>2026-07-11 08:39:53 PM PT</t>
         </is>
       </c>
       <c r="C58" t="n">
@@ -7281,7 +7281,7 @@
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>2026-07-11 08:37:53 PM PT</t>
+          <t>2026-07-11 08:39:53 PM PT</t>
         </is>
       </c>
       <c r="C59" t="n">
@@ -7395,7 +7395,7 @@
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>2026-07-11 08:37:53 PM PT</t>
+          <t>2026-07-11 08:39:53 PM PT</t>
         </is>
       </c>
       <c r="C60" t="n">
@@ -7509,7 +7509,7 @@
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>2026-07-11 08:37:53 PM PT</t>
+          <t>2026-07-11 08:39:53 PM PT</t>
         </is>
       </c>
       <c r="C61" t="n">
@@ -7623,7 +7623,7 @@
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>2026-07-11 08:37:53 PM PT</t>
+          <t>2026-07-11 08:39:53 PM PT</t>
         </is>
       </c>
       <c r="C62" t="n">
@@ -7737,7 +7737,7 @@
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>2026-07-11 08:37:52 PM PT</t>
+          <t>2026-07-11 08:39:52 PM PT</t>
         </is>
       </c>
       <c r="C63" t="n">
@@ -7851,7 +7851,7 @@
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>2026-07-11 08:37:52 PM PT</t>
+          <t>2026-07-11 08:39:52 PM PT</t>
         </is>
       </c>
       <c r="C64" t="n">
@@ -7965,7 +7965,7 @@
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>2026-07-11 08:37:54 PM PT</t>
+          <t>2026-07-11 08:39:54 PM PT</t>
         </is>
       </c>
       <c r="C65" t="n">
@@ -7978,7 +7978,7 @@
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>Bottom 8 | 1 out</t>
+          <t>Bottom 8 | 2 out</t>
         </is>
       </c>
       <c r="F65" t="n">
@@ -7990,10 +7990,10 @@
         </is>
       </c>
       <c r="H65" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I65" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="J65" t="n">
         <v>0</v>
@@ -8088,7 +8088,7 @@
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>2026-07-11 08:37:54 PM PT</t>
+          <t>2026-07-11 08:39:54 PM PT</t>
         </is>
       </c>
       <c r="C66" t="n">
@@ -8101,7 +8101,7 @@
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>Bottom 8 | 0 out</t>
+          <t>Bottom 8 | 1 out</t>
         </is>
       </c>
       <c r="F66" t="n">
@@ -8113,13 +8113,13 @@
         </is>
       </c>
       <c r="H66" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I66" t="n">
         <v>0</v>
       </c>
       <c r="J66" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K66" t="inlineStr">
         <is>
@@ -8211,7 +8211,7 @@
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>2026-07-11 08:37:53 PM PT</t>
+          <t>2026-07-11 08:39:53 PM PT</t>
         </is>
       </c>
       <c r="C67" t="n">
@@ -8325,7 +8325,7 @@
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>2026-07-11 08:37:53 PM PT</t>
+          <t>2026-07-11 08:39:53 PM PT</t>
         </is>
       </c>
       <c r="C68" t="n">
@@ -8439,7 +8439,7 @@
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>2026-07-11 08:37:53 PM PT</t>
+          <t>2026-07-11 08:39:53 PM PT</t>
         </is>
       </c>
       <c r="C69" t="n">
@@ -8553,7 +8553,7 @@
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>2026-07-11 08:37:53 PM PT</t>
+          <t>2026-07-11 08:39:53 PM PT</t>
         </is>
       </c>
       <c r="C70" t="n">
@@ -8667,7 +8667,7 @@
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>2026-07-11 08:37:53 PM PT</t>
+          <t>2026-07-11 08:39:53 PM PT</t>
         </is>
       </c>
       <c r="C71" t="n">
@@ -8781,7 +8781,7 @@
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>2026-07-11 08:37:54 PM PT</t>
+          <t>2026-07-11 08:39:54 PM PT</t>
         </is>
       </c>
       <c r="C72" t="n">
@@ -8794,7 +8794,7 @@
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>Bottom 8 | 0 out</t>
+          <t>Bottom 8 | 1 out</t>
         </is>
       </c>
       <c r="F72" t="n">
@@ -8806,13 +8806,13 @@
         </is>
       </c>
       <c r="H72" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I72" t="n">
         <v>0</v>
       </c>
       <c r="J72" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K72" t="inlineStr">
         <is>
@@ -8904,7 +8904,7 @@
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>2026-07-11 08:37:52 PM PT</t>
+          <t>2026-07-11 08:39:53 PM PT</t>
         </is>
       </c>
       <c r="C73" t="n">
@@ -9018,7 +9018,7 @@
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>2026-07-11 08:37:53 PM PT</t>
+          <t>2026-07-11 08:39:53 PM PT</t>
         </is>
       </c>
       <c r="C74" t="n">
@@ -9132,7 +9132,7 @@
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>2026-07-11 08:37:52 PM PT</t>
+          <t>2026-07-11 08:39:53 PM PT</t>
         </is>
       </c>
       <c r="C75" t="n">
@@ -9246,7 +9246,7 @@
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>2026-07-11 08:37:54 PM PT</t>
+          <t>2026-07-11 08:39:54 PM PT</t>
         </is>
       </c>
       <c r="C76" t="n">
@@ -9259,7 +9259,7 @@
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>Bottom 8 | 1 out</t>
+          <t>Bottom 8 | 2 out</t>
         </is>
       </c>
       <c r="F76" t="n">
@@ -9271,58 +9271,58 @@
         </is>
       </c>
       <c r="H76" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I76" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="J76" t="n">
         <v>0</v>
       </c>
       <c r="K76" t="inlineStr">
         <is>
-          <t>Away</t>
+          <t>Home</t>
         </is>
       </c>
       <c r="L76" t="inlineStr">
         <is>
+          <t>SD</t>
+        </is>
+      </c>
+      <c r="M76" t="inlineStr">
+        <is>
           <t>TOR</t>
         </is>
       </c>
-      <c r="M76" t="inlineStr">
-        <is>
-          <t>SD</t>
-        </is>
-      </c>
       <c r="N76" t="inlineStr">
         <is>
-          <t>Ernie Clement</t>
+          <t>Gavin Sheets</t>
         </is>
       </c>
       <c r="O76" t="n">
-        <v>676391</v>
+        <v>657757</v>
       </c>
       <c r="P76" t="inlineStr">
         <is>
-          <t>SS</t>
+          <t>LF</t>
         </is>
       </c>
       <c r="Q76" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>5</t>
         </is>
       </c>
       <c r="R76" t="n">
         <v>5</v>
       </c>
       <c r="S76" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="T76" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="U76" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="V76" t="n">
         <v>0</v>
@@ -9334,31 +9334,31 @@
         <v>0</v>
       </c>
       <c r="Y76" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Z76" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AA76" s="5" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="AB76" t="n">
         <v>0</v>
       </c>
-      <c r="AC76" s="6" t="n">
-        <v>1</v>
+      <c r="AC76" t="n">
+        <v>0</v>
       </c>
       <c r="AD76" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AE76" s="4" t="n">
         <v>10</v>
       </c>
       <c r="AF76" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AG76" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
     </row>
     <row r="77">
@@ -9369,30 +9369,39 @@
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>2026-07-11 08:37:54 PM PT</t>
+          <t>2026-07-11 08:39:54 PM PT</t>
         </is>
       </c>
       <c r="C77" t="n">
-        <v>824492</v>
+        <v>823276</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>4:10 PM PT</t>
+          <t>5:40 PM PT</t>
         </is>
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>Final</t>
+          <t>Bottom 8 | 2 out</t>
         </is>
       </c>
       <c r="F77" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="G77" t="inlineStr">
         <is>
           <t>Bottom</t>
         </is>
       </c>
+      <c r="H77" t="n">
+        <v>2</v>
+      </c>
+      <c r="I77" t="n">
+        <v>4</v>
+      </c>
+      <c r="J77" t="n">
+        <v>0</v>
+      </c>
       <c r="K77" t="inlineStr">
         <is>
           <t>Away</t>
@@ -9400,30 +9409,30 @@
       </c>
       <c r="L77" t="inlineStr">
         <is>
-          <t>CHC</t>
+          <t>TOR</t>
         </is>
       </c>
       <c r="M77" t="inlineStr">
         <is>
-          <t>CIN</t>
+          <t>SD</t>
         </is>
       </c>
       <c r="N77" t="inlineStr">
         <is>
-          <t>Seiya Suzuki</t>
+          <t>Ernie Clement</t>
         </is>
       </c>
       <c r="O77" t="n">
-        <v>673548</v>
+        <v>676391</v>
       </c>
       <c r="P77" t="inlineStr">
         <is>
-          <t>RF</t>
+          <t>SS</t>
         </is>
       </c>
       <c r="Q77" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="R77" t="n">
@@ -9448,10 +9457,10 @@
         <v>0</v>
       </c>
       <c r="Y77" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Z77" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AA77" s="5" t="n">
         <v>1</v>
@@ -9459,20 +9468,20 @@
       <c r="AB77" t="n">
         <v>0</v>
       </c>
-      <c r="AC77" t="n">
-        <v>0</v>
+      <c r="AC77" s="6" t="n">
+        <v>1</v>
       </c>
       <c r="AD77" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AE77" s="4" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AF77" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="AG77" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
     </row>
     <row r="78">
@@ -9483,7 +9492,7 @@
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>2026-07-11 08:37:54 PM PT</t>
+          <t>2026-07-11 08:39:54 PM PT</t>
         </is>
       </c>
       <c r="C78" t="n">
@@ -9524,36 +9533,36 @@
       </c>
       <c r="N78" t="inlineStr">
         <is>
-          <t>Ian Happ</t>
+          <t>Seiya Suzuki</t>
         </is>
       </c>
       <c r="O78" t="n">
-        <v>664023</v>
+        <v>673548</v>
       </c>
       <c r="P78" t="inlineStr">
         <is>
-          <t>LF</t>
+          <t>RF</t>
         </is>
       </c>
       <c r="Q78" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>2</t>
         </is>
       </c>
       <c r="R78" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="S78" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="T78" t="n">
         <v>1</v>
       </c>
       <c r="U78" t="n">
-        <v>0</v>
-      </c>
-      <c r="V78" s="7" t="n">
-        <v>1</v>
+        <v>1</v>
+      </c>
+      <c r="V78" t="n">
+        <v>0</v>
       </c>
       <c r="W78" t="n">
         <v>0</v>
@@ -9562,7 +9571,7 @@
         <v>0</v>
       </c>
       <c r="Y78" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Z78" t="n">
         <v>1</v>
@@ -9577,7 +9586,7 @@
         <v>0</v>
       </c>
       <c r="AD78" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AE78" s="4" t="n">
         <v>9</v>
@@ -9597,15 +9606,15 @@
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>2026-07-11 08:37:53 PM PT</t>
+          <t>2026-07-11 08:39:54 PM PT</t>
         </is>
       </c>
       <c r="C79" t="n">
-        <v>823844</v>
+        <v>824492</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>1:10 PM PT</t>
+          <t>4:10 PM PT</t>
         </is>
       </c>
       <c r="E79" t="inlineStr">
@@ -9628,37 +9637,37 @@
       </c>
       <c r="L79" t="inlineStr">
         <is>
-          <t>CLE</t>
+          <t>CHC</t>
         </is>
       </c>
       <c r="M79" t="inlineStr">
         <is>
-          <t>MIA</t>
+          <t>CIN</t>
         </is>
       </c>
       <c r="N79" t="inlineStr">
         <is>
-          <t>Patrick Bailey</t>
+          <t>Ian Happ</t>
         </is>
       </c>
       <c r="O79" t="n">
-        <v>672275</v>
+        <v>664023</v>
       </c>
       <c r="P79" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>LF</t>
         </is>
       </c>
       <c r="Q79" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>7</t>
         </is>
       </c>
       <c r="R79" t="n">
         <v>4</v>
       </c>
       <c r="S79" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="T79" t="n">
         <v>1</v>
@@ -9679,10 +9688,10 @@
         <v>0</v>
       </c>
       <c r="Z79" t="n">
-        <v>2</v>
-      </c>
-      <c r="AA79" t="n">
-        <v>0</v>
+        <v>1</v>
+      </c>
+      <c r="AA79" s="5" t="n">
+        <v>1</v>
       </c>
       <c r="AB79" t="n">
         <v>0</v>
@@ -9691,16 +9700,16 @@
         <v>0</v>
       </c>
       <c r="AD79" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AE79" s="4" t="n">
         <v>9</v>
       </c>
       <c r="AF79" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="AG79" t="n">
-        <v>11</v>
+        <v>9</v>
       </c>
     </row>
     <row r="80">
@@ -9711,15 +9720,15 @@
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>2026-07-11 08:37:52 PM PT</t>
+          <t>2026-07-11 08:39:53 PM PT</t>
         </is>
       </c>
       <c r="C80" t="n">
-        <v>823357</v>
+        <v>823844</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>9:05 AM PT</t>
+          <t>1:10 PM PT</t>
         </is>
       </c>
       <c r="E80" t="inlineStr">
@@ -9732,7 +9741,7 @@
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>Top</t>
+          <t>Bottom</t>
         </is>
       </c>
       <c r="K80" t="inlineStr">
@@ -9742,37 +9751,37 @@
       </c>
       <c r="L80" t="inlineStr">
         <is>
-          <t>MIL</t>
+          <t>CLE</t>
         </is>
       </c>
       <c r="M80" t="inlineStr">
         <is>
-          <t>PIT</t>
+          <t>MIA</t>
         </is>
       </c>
       <c r="N80" t="inlineStr">
         <is>
-          <t>Garrett Mitchell</t>
+          <t>Patrick Bailey</t>
         </is>
       </c>
       <c r="O80" t="n">
-        <v>669003</v>
+        <v>672275</v>
       </c>
       <c r="P80" t="inlineStr">
         <is>
-          <t>CF</t>
+          <t>C</t>
         </is>
       </c>
       <c r="Q80" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>8</t>
         </is>
       </c>
       <c r="R80" t="n">
         <v>4</v>
       </c>
       <c r="S80" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="T80" t="n">
         <v>1</v>
@@ -9790,13 +9799,13 @@
         <v>0</v>
       </c>
       <c r="Y80" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Z80" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA80" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
+      </c>
+      <c r="AA80" t="n">
+        <v>0</v>
       </c>
       <c r="AB80" t="n">
         <v>0</v>
@@ -9811,10 +9820,10 @@
         <v>9</v>
       </c>
       <c r="AF80" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="AG80" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
     </row>
     <row r="81">
@@ -9825,15 +9834,15 @@
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>2026-07-11 08:37:52 PM PT</t>
+          <t>2026-07-11 08:39:52 PM PT</t>
         </is>
       </c>
       <c r="C81" t="n">
-        <v>823356</v>
+        <v>823357</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>1:05 PM PT</t>
+          <t>9:05 AM PT</t>
         </is>
       </c>
       <c r="E81" t="inlineStr">
@@ -9866,27 +9875,27 @@
       </c>
       <c r="N81" t="inlineStr">
         <is>
-          <t>Brice Turang</t>
+          <t>Garrett Mitchell</t>
         </is>
       </c>
       <c r="O81" t="n">
-        <v>668930</v>
+        <v>669003</v>
       </c>
       <c r="P81" t="inlineStr">
         <is>
-          <t>2B</t>
+          <t>CF</t>
         </is>
       </c>
       <c r="Q81" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="R81" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="S81" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="T81" t="n">
         <v>1</v>
@@ -9904,31 +9913,31 @@
         <v>0</v>
       </c>
       <c r="Y81" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Z81" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA81" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="AB81" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC81" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD81" t="n">
         <v>2</v>
-      </c>
-      <c r="AA81" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB81" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC81" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD81" t="n">
-        <v>1</v>
       </c>
       <c r="AE81" s="4" t="n">
         <v>9</v>
       </c>
       <c r="AF81" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="AG81" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
     </row>
     <row r="82">
@@ -9939,7 +9948,7 @@
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>2026-07-11 08:37:52 PM PT</t>
+          <t>2026-07-11 08:39:53 PM PT</t>
         </is>
       </c>
       <c r="C82" t="n">
@@ -9980,60 +9989,60 @@
       </c>
       <c r="N82" t="inlineStr">
         <is>
-          <t>Jake Bauers</t>
+          <t>Brice Turang</t>
         </is>
       </c>
       <c r="O82" t="n">
-        <v>641343</v>
+        <v>668930</v>
       </c>
       <c r="P82" t="inlineStr">
         <is>
-          <t>1B</t>
+          <t>2B</t>
         </is>
       </c>
       <c r="Q82" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>3</t>
         </is>
       </c>
       <c r="R82" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="S82" t="n">
+        <v>5</v>
+      </c>
+      <c r="T82" t="n">
+        <v>1</v>
+      </c>
+      <c r="U82" t="n">
+        <v>0</v>
+      </c>
+      <c r="V82" s="7" t="n">
+        <v>1</v>
+      </c>
+      <c r="W82" t="n">
+        <v>0</v>
+      </c>
+      <c r="X82" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y82" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z82" t="n">
         <v>2</v>
       </c>
-      <c r="T82" t="n">
-        <v>0</v>
-      </c>
-      <c r="U82" t="n">
-        <v>0</v>
-      </c>
-      <c r="V82" t="n">
-        <v>0</v>
-      </c>
-      <c r="W82" t="n">
-        <v>0</v>
-      </c>
-      <c r="X82" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y82" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z82" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA82" s="5" t="n">
-        <v>2</v>
+      <c r="AA82" t="n">
+        <v>0</v>
       </c>
       <c r="AB82" t="n">
         <v>0</v>
       </c>
-      <c r="AC82" s="6" t="n">
-        <v>1</v>
+      <c r="AC82" t="n">
+        <v>0</v>
       </c>
       <c r="AD82" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AE82" s="4" t="n">
         <v>9</v>
@@ -10053,15 +10062,15 @@
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>2026-07-11 08:37:52 PM PT</t>
+          <t>2026-07-11 08:39:53 PM PT</t>
         </is>
       </c>
       <c r="C83" t="n">
-        <v>823357</v>
+        <v>823356</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t>9:05 AM PT</t>
+          <t>1:05 PM PT</t>
         </is>
       </c>
       <c r="E83" t="inlineStr">
@@ -10094,36 +10103,36 @@
       </c>
       <c r="N83" t="inlineStr">
         <is>
-          <t>Luis Lara</t>
+          <t>Jake Bauers</t>
         </is>
       </c>
       <c r="O83" t="n">
-        <v>800325</v>
+        <v>641343</v>
       </c>
       <c r="P83" t="inlineStr">
         <is>
-          <t>LF</t>
+          <t>1B</t>
         </is>
       </c>
       <c r="Q83" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>4</t>
         </is>
       </c>
       <c r="R83" t="n">
         <v>4</v>
       </c>
       <c r="S83" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="T83" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="U83" t="n">
         <v>0</v>
       </c>
-      <c r="V83" s="7" t="n">
-        <v>1</v>
+      <c r="V83" t="n">
+        <v>0</v>
       </c>
       <c r="W83" t="n">
         <v>0</v>
@@ -10132,31 +10141,31 @@
         <v>0</v>
       </c>
       <c r="Y83" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Z83" t="n">
         <v>0</v>
       </c>
       <c r="AA83" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AB83" t="n">
         <v>0</v>
       </c>
-      <c r="AC83" t="n">
-        <v>0</v>
+      <c r="AC83" s="6" t="n">
+        <v>1</v>
       </c>
       <c r="AD83" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AE83" s="4" t="n">
         <v>9</v>
       </c>
       <c r="AF83" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="AG83" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
     </row>
     <row r="84">
@@ -10167,7 +10176,7 @@
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>2026-07-11 08:37:52 PM PT</t>
+          <t>2026-07-11 08:39:52 PM PT</t>
         </is>
       </c>
       <c r="C84" t="n">
@@ -10193,26 +10202,26 @@
       </c>
       <c r="K84" t="inlineStr">
         <is>
-          <t>Home</t>
+          <t>Away</t>
         </is>
       </c>
       <c r="L84" t="inlineStr">
         <is>
+          <t>MIL</t>
+        </is>
+      </c>
+      <c r="M84" t="inlineStr">
+        <is>
           <t>PIT</t>
         </is>
       </c>
-      <c r="M84" t="inlineStr">
-        <is>
-          <t>MIL</t>
-        </is>
-      </c>
       <c r="N84" t="inlineStr">
         <is>
-          <t>Jake Mangum</t>
+          <t>Luis Lara</t>
         </is>
       </c>
       <c r="O84" t="n">
-        <v>663968</v>
+        <v>800325</v>
       </c>
       <c r="P84" t="inlineStr">
         <is>
@@ -10221,7 +10230,7 @@
       </c>
       <c r="Q84" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>6</t>
         </is>
       </c>
       <c r="R84" t="n">
@@ -10234,10 +10243,10 @@
         <v>1</v>
       </c>
       <c r="U84" t="n">
-        <v>1</v>
-      </c>
-      <c r="V84" t="n">
-        <v>0</v>
+        <v>0</v>
+      </c>
+      <c r="V84" s="7" t="n">
+        <v>1</v>
       </c>
       <c r="W84" t="n">
         <v>0</v>
@@ -10246,16 +10255,16 @@
         <v>0</v>
       </c>
       <c r="Y84" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="Z84" t="n">
         <v>0</v>
       </c>
-      <c r="AA84" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB84" s="9" t="n">
-        <v>1</v>
+      <c r="AA84" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="AB84" t="n">
+        <v>0</v>
       </c>
       <c r="AC84" t="n">
         <v>0</v>
@@ -10267,10 +10276,10 @@
         <v>9</v>
       </c>
       <c r="AF84" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="AG84" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
     </row>
     <row r="85">
@@ -10281,7 +10290,7 @@
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>2026-07-11 08:37:52 PM PT</t>
+          <t>2026-07-11 08:39:52 PM PT</t>
         </is>
       </c>
       <c r="C85" t="n">
@@ -10322,54 +10331,54 @@
       </c>
       <c r="N85" t="inlineStr">
         <is>
-          <t>Henry Davis</t>
+          <t>Jake Mangum</t>
         </is>
       </c>
       <c r="O85" t="n">
-        <v>680779</v>
+        <v>663968</v>
       </c>
       <c r="P85" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>LF</t>
         </is>
       </c>
       <c r="Q85" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>1</t>
         </is>
       </c>
       <c r="R85" t="n">
         <v>4</v>
       </c>
       <c r="S85" t="n">
+        <v>3</v>
+      </c>
+      <c r="T85" t="n">
+        <v>1</v>
+      </c>
+      <c r="U85" t="n">
+        <v>1</v>
+      </c>
+      <c r="V85" t="n">
+        <v>0</v>
+      </c>
+      <c r="W85" t="n">
+        <v>0</v>
+      </c>
+      <c r="X85" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y85" t="n">
         <v>2</v>
       </c>
-      <c r="T85" t="n">
-        <v>1</v>
-      </c>
-      <c r="U85" t="n">
-        <v>1</v>
-      </c>
-      <c r="V85" t="n">
-        <v>0</v>
-      </c>
-      <c r="W85" t="n">
-        <v>0</v>
-      </c>
-      <c r="X85" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y85" t="n">
-        <v>1</v>
-      </c>
       <c r="Z85" t="n">
         <v>0</v>
       </c>
-      <c r="AA85" s="5" t="n">
-        <v>2</v>
-      </c>
-      <c r="AB85" t="n">
-        <v>0</v>
+      <c r="AA85" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB85" s="9" t="n">
+        <v>1</v>
       </c>
       <c r="AC85" t="n">
         <v>0</v>
@@ -10395,15 +10404,15 @@
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>2026-07-11 08:37:53 PM PT</t>
+          <t>2026-07-11 08:39:52 PM PT</t>
         </is>
       </c>
       <c r="C86" t="n">
-        <v>824576</v>
+        <v>823357</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>
-          <t>11:10 AM PT</t>
+          <t>9:05 AM PT</t>
         </is>
       </c>
       <c r="E86" t="inlineStr">
@@ -10421,67 +10430,67 @@
       </c>
       <c r="K86" t="inlineStr">
         <is>
-          <t>Away</t>
+          <t>Home</t>
         </is>
       </c>
       <c r="L86" t="inlineStr">
         <is>
-          <t>ATH</t>
+          <t>PIT</t>
         </is>
       </c>
       <c r="M86" t="inlineStr">
         <is>
-          <t>CWS</t>
+          <t>MIL</t>
         </is>
       </c>
       <c r="N86" t="inlineStr">
         <is>
-          <t>Joshua Kuroda-Grauer</t>
+          <t>Henry Davis</t>
         </is>
       </c>
       <c r="O86" t="n">
-        <v>811965</v>
+        <v>680779</v>
       </c>
       <c r="P86" t="inlineStr">
         <is>
-          <t>3B</t>
+          <t>C</t>
         </is>
       </c>
       <c r="Q86" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>9</t>
         </is>
       </c>
       <c r="R86" t="n">
         <v>4</v>
       </c>
       <c r="S86" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="T86" t="n">
+        <v>1</v>
+      </c>
+      <c r="U86" t="n">
+        <v>1</v>
+      </c>
+      <c r="V86" t="n">
+        <v>0</v>
+      </c>
+      <c r="W86" t="n">
+        <v>0</v>
+      </c>
+      <c r="X86" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y86" t="n">
+        <v>1</v>
+      </c>
+      <c r="Z86" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA86" s="5" t="n">
         <v>2</v>
       </c>
-      <c r="U86" t="n">
-        <v>1</v>
-      </c>
-      <c r="V86" s="7" t="n">
-        <v>1</v>
-      </c>
-      <c r="W86" t="n">
-        <v>0</v>
-      </c>
-      <c r="X86" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y86" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z86" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA86" t="n">
-        <v>0</v>
-      </c>
       <c r="AB86" t="n">
         <v>0</v>
       </c>
@@ -10492,13 +10501,13 @@
         <v>0</v>
       </c>
       <c r="AE86" s="4" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="AF86" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="AG86" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
     </row>
     <row r="87">
@@ -10509,7 +10518,7 @@
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>2026-07-11 08:37:53 PM PT</t>
+          <t>2026-07-11 08:39:53 PM PT</t>
         </is>
       </c>
       <c r="C87" t="n">
@@ -10535,42 +10544,42 @@
       </c>
       <c r="K87" t="inlineStr">
         <is>
-          <t>Home</t>
+          <t>Away</t>
         </is>
       </c>
       <c r="L87" t="inlineStr">
         <is>
+          <t>ATH</t>
+        </is>
+      </c>
+      <c r="M87" t="inlineStr">
+        <is>
           <t>CWS</t>
         </is>
       </c>
-      <c r="M87" t="inlineStr">
-        <is>
-          <t>ATH</t>
-        </is>
-      </c>
       <c r="N87" t="inlineStr">
         <is>
-          <t>Luisangel Acuña</t>
+          <t>Joshua Kuroda-Grauer</t>
         </is>
       </c>
       <c r="O87" t="n">
-        <v>682668</v>
+        <v>811965</v>
       </c>
       <c r="P87" t="inlineStr">
         <is>
-          <t>SS</t>
+          <t>3B</t>
         </is>
       </c>
       <c r="Q87" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>5</t>
         </is>
       </c>
       <c r="R87" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="S87" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="T87" t="n">
         <v>2</v>
@@ -10603,16 +10612,16 @@
         <v>0</v>
       </c>
       <c r="AD87" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AE87" s="4" t="n">
         <v>8</v>
       </c>
       <c r="AF87" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AG87" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
     </row>
     <row r="88">
@@ -10623,15 +10632,15 @@
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>2026-07-11 08:37:53 PM PT</t>
+          <t>2026-07-11 08:39:53 PM PT</t>
         </is>
       </c>
       <c r="C88" t="n">
-        <v>823603</v>
+        <v>824576</v>
       </c>
       <c r="D88" t="inlineStr">
         <is>
-          <t>1:10 PM PT</t>
+          <t>11:10 AM PT</t>
         </is>
       </c>
       <c r="E88" t="inlineStr">
@@ -10644,7 +10653,7 @@
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>Bottom</t>
+          <t>Top</t>
         </is>
       </c>
       <c r="K88" t="inlineStr">
@@ -10654,25 +10663,25 @@
       </c>
       <c r="L88" t="inlineStr">
         <is>
-          <t>NYM</t>
+          <t>CWS</t>
         </is>
       </c>
       <c r="M88" t="inlineStr">
         <is>
-          <t>BOS</t>
+          <t>ATH</t>
         </is>
       </c>
       <c r="N88" t="inlineStr">
         <is>
-          <t>Francisco Alvarez</t>
+          <t>Luisangel Acuña</t>
         </is>
       </c>
       <c r="O88" t="n">
-        <v>682626</v>
+        <v>682668</v>
       </c>
       <c r="P88" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>SS</t>
         </is>
       </c>
       <c r="Q88" t="inlineStr">
@@ -10681,7 +10690,7 @@
         </is>
       </c>
       <c r="R88" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="S88" t="n">
         <v>3</v>
@@ -10690,10 +10699,10 @@
         <v>2</v>
       </c>
       <c r="U88" t="n">
-        <v>2</v>
-      </c>
-      <c r="V88" t="n">
-        <v>0</v>
+        <v>1</v>
+      </c>
+      <c r="V88" s="7" t="n">
+        <v>1</v>
       </c>
       <c r="W88" t="n">
         <v>0</v>
@@ -10707,8 +10716,8 @@
       <c r="Z88" t="n">
         <v>0</v>
       </c>
-      <c r="AA88" s="5" t="n">
-        <v>1</v>
+      <c r="AA88" t="n">
+        <v>0</v>
       </c>
       <c r="AB88" t="n">
         <v>0</v>
@@ -10723,10 +10732,10 @@
         <v>8</v>
       </c>
       <c r="AF88" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AG88" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
     </row>
     <row r="89">
@@ -10737,15 +10746,15 @@
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>2026-07-11 08:37:53 PM PT</t>
+          <t>2026-07-11 08:39:53 PM PT</t>
         </is>
       </c>
       <c r="C89" t="n">
-        <v>824249</v>
+        <v>823603</v>
       </c>
       <c r="D89" t="inlineStr">
         <is>
-          <t>3:10 PM PT</t>
+          <t>1:10 PM PT</t>
         </is>
       </c>
       <c r="E89" t="inlineStr">
@@ -10763,51 +10772,51 @@
       </c>
       <c r="K89" t="inlineStr">
         <is>
-          <t>Away</t>
+          <t>Home</t>
         </is>
       </c>
       <c r="L89" t="inlineStr">
         <is>
-          <t>PHI</t>
+          <t>NYM</t>
         </is>
       </c>
       <c r="M89" t="inlineStr">
         <is>
-          <t>DET</t>
+          <t>BOS</t>
         </is>
       </c>
       <c r="N89" t="inlineStr">
         <is>
-          <t>Bryce Harper</t>
+          <t>Francisco Alvarez</t>
         </is>
       </c>
       <c r="O89" t="n">
-        <v>547180</v>
+        <v>682626</v>
       </c>
       <c r="P89" t="inlineStr">
         <is>
-          <t>1B</t>
+          <t>C</t>
         </is>
       </c>
       <c r="Q89" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>7</t>
         </is>
       </c>
       <c r="R89" t="n">
         <v>4</v>
       </c>
       <c r="S89" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="T89" t="n">
         <v>2</v>
       </c>
       <c r="U89" t="n">
-        <v>1</v>
-      </c>
-      <c r="V89" s="7" t="n">
-        <v>1</v>
+        <v>2</v>
+      </c>
+      <c r="V89" t="n">
+        <v>0</v>
       </c>
       <c r="W89" t="n">
         <v>0</v>
@@ -10821,8 +10830,8 @@
       <c r="Z89" t="n">
         <v>0</v>
       </c>
-      <c r="AA89" t="n">
-        <v>0</v>
+      <c r="AA89" s="5" t="n">
+        <v>1</v>
       </c>
       <c r="AB89" t="n">
         <v>0</v>
@@ -10831,16 +10840,16 @@
         <v>0</v>
       </c>
       <c r="AD89" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AE89" s="4" t="n">
         <v>8</v>
       </c>
       <c r="AF89" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="AG89" t="n">
-        <v>7</v>
+        <v>3</v>
       </c>
     </row>
     <row r="90">
@@ -10851,86 +10860,77 @@
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>2026-07-11 08:37:54 PM PT</t>
+          <t>2026-07-11 08:39:53 PM PT</t>
         </is>
       </c>
       <c r="C90" t="n">
-        <v>823276</v>
+        <v>824249</v>
       </c>
       <c r="D90" t="inlineStr">
         <is>
-          <t>5:40 PM PT</t>
+          <t>3:10 PM PT</t>
         </is>
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>Bottom 8 | 1 out</t>
+          <t>Final</t>
         </is>
       </c>
       <c r="F90" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="G90" t="inlineStr">
         <is>
           <t>Bottom</t>
         </is>
       </c>
-      <c r="H90" t="n">
-        <v>1</v>
-      </c>
-      <c r="I90" t="n">
-        <v>0</v>
-      </c>
-      <c r="J90" t="n">
-        <v>0</v>
-      </c>
       <c r="K90" t="inlineStr">
         <is>
-          <t>Home</t>
+          <t>Away</t>
         </is>
       </c>
       <c r="L90" t="inlineStr">
         <is>
-          <t>SD</t>
+          <t>PHI</t>
         </is>
       </c>
       <c r="M90" t="inlineStr">
         <is>
-          <t>TOR</t>
+          <t>DET</t>
         </is>
       </c>
       <c r="N90" t="inlineStr">
         <is>
-          <t>Gavin Sheets</t>
+          <t>Bryce Harper</t>
         </is>
       </c>
       <c r="O90" t="n">
-        <v>657757</v>
+        <v>547180</v>
       </c>
       <c r="P90" t="inlineStr">
         <is>
-          <t>LF</t>
+          <t>1B</t>
         </is>
       </c>
       <c r="Q90" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>3</t>
         </is>
       </c>
       <c r="R90" t="n">
         <v>4</v>
       </c>
       <c r="S90" t="n">
+        <v>4</v>
+      </c>
+      <c r="T90" t="n">
         <v>2</v>
       </c>
-      <c r="T90" t="n">
-        <v>0</v>
-      </c>
       <c r="U90" t="n">
-        <v>0</v>
-      </c>
-      <c r="V90" t="n">
-        <v>0</v>
+        <v>1</v>
+      </c>
+      <c r="V90" s="7" t="n">
+        <v>1</v>
       </c>
       <c r="W90" t="n">
         <v>0</v>
@@ -10939,13 +10939,13 @@
         <v>0</v>
       </c>
       <c r="Y90" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Z90" t="n">
-        <v>1</v>
-      </c>
-      <c r="AA90" s="5" t="n">
-        <v>2</v>
+        <v>0</v>
+      </c>
+      <c r="AA90" t="n">
+        <v>0</v>
       </c>
       <c r="AB90" t="n">
         <v>0</v>
@@ -10954,16 +10954,16 @@
         <v>0</v>
       </c>
       <c r="AD90" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AE90" s="4" t="n">
         <v>8</v>
       </c>
       <c r="AF90" t="n">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="AG90" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
     </row>
     <row r="91">
@@ -10974,7 +10974,7 @@
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>2026-07-11 08:37:53 PM PT</t>
+          <t>2026-07-11 08:39:53 PM PT</t>
         </is>
       </c>
       <c r="C91" t="n">
@@ -11088,7 +11088,7 @@
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>2026-07-11 08:37:54 PM PT</t>
+          <t>2026-07-11 08:39:54 PM PT</t>
         </is>
       </c>
       <c r="C92" t="n">
@@ -11202,7 +11202,7 @@
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>2026-07-11 08:37:54 PM PT</t>
+          <t>2026-07-11 08:39:54 PM PT</t>
         </is>
       </c>
       <c r="C93" t="n">
@@ -11215,7 +11215,7 @@
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>Bottom 8 | 0 out</t>
+          <t>Bottom 8 | 1 out</t>
         </is>
       </c>
       <c r="F93" t="n">
@@ -11227,13 +11227,13 @@
         </is>
       </c>
       <c r="H93" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I93" t="n">
         <v>0</v>
       </c>
       <c r="J93" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K93" t="inlineStr">
         <is>
@@ -11325,7 +11325,7 @@
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>2026-07-11 08:37:53 PM PT</t>
+          <t>2026-07-11 08:39:53 PM PT</t>
         </is>
       </c>
       <c r="C94" t="n">
@@ -11439,7 +11439,7 @@
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>2026-07-11 08:37:53 PM PT</t>
+          <t>2026-07-11 08:39:53 PM PT</t>
         </is>
       </c>
       <c r="C95" t="n">
@@ -11553,7 +11553,7 @@
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>2026-07-11 08:37:53 PM PT</t>
+          <t>2026-07-11 08:39:53 PM PT</t>
         </is>
       </c>
       <c r="C96" t="n">
@@ -11667,7 +11667,7 @@
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>2026-07-11 08:37:54 PM PT</t>
+          <t>2026-07-11 08:39:53 PM PT</t>
         </is>
       </c>
       <c r="C97" t="n">
@@ -11781,7 +11781,7 @@
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>2026-07-11 08:37:54 PM PT</t>
+          <t>2026-07-11 08:39:53 PM PT</t>
         </is>
       </c>
       <c r="C98" t="n">
@@ -11895,7 +11895,7 @@
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>2026-07-11 08:37:54 PM PT</t>
+          <t>2026-07-11 08:39:54 PM PT</t>
         </is>
       </c>
       <c r="C99" t="n">
@@ -11908,7 +11908,7 @@
       </c>
       <c r="E99" t="inlineStr">
         <is>
-          <t>Bottom 8 | 0 out</t>
+          <t>Bottom 8 | 1 out</t>
         </is>
       </c>
       <c r="F99" t="n">
@@ -11920,13 +11920,13 @@
         </is>
       </c>
       <c r="H99" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I99" t="n">
         <v>0</v>
       </c>
       <c r="J99" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K99" t="inlineStr">
         <is>
@@ -12018,7 +12018,7 @@
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>2026-07-11 08:37:53 PM PT</t>
+          <t>2026-07-11 08:39:53 PM PT</t>
         </is>
       </c>
       <c r="C100" t="n">
@@ -12132,7 +12132,7 @@
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>2026-07-11 08:37:52 PM PT</t>
+          <t>2026-07-11 08:39:53 PM PT</t>
         </is>
       </c>
       <c r="C101" t="n">
@@ -12246,7 +12246,7 @@
       </c>
       <c r="B102" t="inlineStr">
         <is>
-          <t>2026-07-11 08:37:53 PM PT</t>
+          <t>2026-07-11 08:39:53 PM PT</t>
         </is>
       </c>
       <c r="C102" t="n">
@@ -12360,7 +12360,7 @@
       </c>
       <c r="B103" t="inlineStr">
         <is>
-          <t>2026-07-11 08:37:53 PM PT</t>
+          <t>2026-07-11 08:39:53 PM PT</t>
         </is>
       </c>
       <c r="C103" t="n">
@@ -12474,7 +12474,7 @@
       </c>
       <c r="B104" t="inlineStr">
         <is>
-          <t>2026-07-11 08:37:54 PM PT</t>
+          <t>2026-07-11 08:39:54 PM PT</t>
         </is>
       </c>
       <c r="C104" t="n">
@@ -12487,7 +12487,7 @@
       </c>
       <c r="E104" t="inlineStr">
         <is>
-          <t>Bottom 8 | 1 out</t>
+          <t>Bottom 8 | 2 out</t>
         </is>
       </c>
       <c r="F104" t="n">
@@ -12499,10 +12499,10 @@
         </is>
       </c>
       <c r="H104" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I104" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="J104" t="n">
         <v>0</v>
@@ -12541,10 +12541,10 @@
         </is>
       </c>
       <c r="R104" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="S104" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="T104" t="n">
         <v>1</v>
@@ -12597,7 +12597,7 @@
       </c>
       <c r="B105" t="inlineStr">
         <is>
-          <t>2026-07-11 08:37:53 PM PT</t>
+          <t>2026-07-11 08:39:53 PM PT</t>
         </is>
       </c>
       <c r="C105" t="n">
@@ -12711,7 +12711,7 @@
       </c>
       <c r="B106" t="inlineStr">
         <is>
-          <t>2026-07-11 08:37:53 PM PT</t>
+          <t>2026-07-11 08:39:53 PM PT</t>
         </is>
       </c>
       <c r="C106" t="n">
@@ -12825,7 +12825,7 @@
       </c>
       <c r="B107" t="inlineStr">
         <is>
-          <t>2026-07-11 08:37:53 PM PT</t>
+          <t>2026-07-11 08:39:53 PM PT</t>
         </is>
       </c>
       <c r="C107" t="n">
@@ -12939,7 +12939,7 @@
       </c>
       <c r="B108" t="inlineStr">
         <is>
-          <t>2026-07-11 08:37:53 PM PT</t>
+          <t>2026-07-11 08:39:53 PM PT</t>
         </is>
       </c>
       <c r="C108" t="n">
@@ -13053,7 +13053,7 @@
       </c>
       <c r="B109" t="inlineStr">
         <is>
-          <t>2026-07-11 08:37:53 PM PT</t>
+          <t>2026-07-11 08:39:53 PM PT</t>
         </is>
       </c>
       <c r="C109" t="n">
@@ -13167,7 +13167,7 @@
       </c>
       <c r="B110" t="inlineStr">
         <is>
-          <t>2026-07-11 08:37:53 PM PT</t>
+          <t>2026-07-11 08:39:53 PM PT</t>
         </is>
       </c>
       <c r="C110" t="n">
@@ -13281,7 +13281,7 @@
       </c>
       <c r="B111" t="inlineStr">
         <is>
-          <t>2026-07-11 08:37:53 PM PT</t>
+          <t>2026-07-11 08:39:53 PM PT</t>
         </is>
       </c>
       <c r="C111" t="n">
@@ -13395,7 +13395,7 @@
       </c>
       <c r="B112" t="inlineStr">
         <is>
-          <t>2026-07-11 08:37:54 PM PT</t>
+          <t>2026-07-11 08:39:54 PM PT</t>
         </is>
       </c>
       <c r="C112" t="n">
@@ -13509,7 +13509,7 @@
       </c>
       <c r="B113" t="inlineStr">
         <is>
-          <t>2026-07-11 08:37:53 PM PT</t>
+          <t>2026-07-11 08:39:53 PM PT</t>
         </is>
       </c>
       <c r="C113" t="n">
@@ -13623,7 +13623,7 @@
       </c>
       <c r="B114" t="inlineStr">
         <is>
-          <t>2026-07-11 08:37:53 PM PT</t>
+          <t>2026-07-11 08:39:53 PM PT</t>
         </is>
       </c>
       <c r="C114" t="n">
@@ -13737,7 +13737,7 @@
       </c>
       <c r="B115" t="inlineStr">
         <is>
-          <t>2026-07-11 08:37:53 PM PT</t>
+          <t>2026-07-11 08:39:53 PM PT</t>
         </is>
       </c>
       <c r="C115" t="n">
@@ -13851,7 +13851,7 @@
       </c>
       <c r="B116" t="inlineStr">
         <is>
-          <t>2026-07-11 08:37:54 PM PT</t>
+          <t>2026-07-11 08:39:54 PM PT</t>
         </is>
       </c>
       <c r="C116" t="n">
@@ -13864,7 +13864,7 @@
       </c>
       <c r="E116" t="inlineStr">
         <is>
-          <t>Bottom 8 | 1 out</t>
+          <t>Bottom 8 | 2 out</t>
         </is>
       </c>
       <c r="F116" t="n">
@@ -13876,10 +13876,10 @@
         </is>
       </c>
       <c r="H116" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I116" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="J116" t="n">
         <v>0</v>
@@ -13974,7 +13974,7 @@
       </c>
       <c r="B117" t="inlineStr">
         <is>
-          <t>2026-07-11 08:37:54 PM PT</t>
+          <t>2026-07-11 08:39:54 PM PT</t>
         </is>
       </c>
       <c r="C117" t="n">
@@ -13987,7 +13987,7 @@
       </c>
       <c r="E117" t="inlineStr">
         <is>
-          <t>Bottom 8 | 1 out</t>
+          <t>Bottom 8 | 2 out</t>
         </is>
       </c>
       <c r="F117" t="n">
@@ -13999,10 +13999,10 @@
         </is>
       </c>
       <c r="H117" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I117" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="J117" t="n">
         <v>0</v>
@@ -14097,7 +14097,7 @@
       </c>
       <c r="B118" t="inlineStr">
         <is>
-          <t>2026-07-11 08:37:54 PM PT</t>
+          <t>2026-07-11 08:39:53 PM PT</t>
         </is>
       </c>
       <c r="C118" t="n">
@@ -14211,7 +14211,7 @@
       </c>
       <c r="B119" t="inlineStr">
         <is>
-          <t>2026-07-11 08:37:54 PM PT</t>
+          <t>2026-07-11 08:39:54 PM PT</t>
         </is>
       </c>
       <c r="C119" t="n">
@@ -14325,7 +14325,7 @@
       </c>
       <c r="B120" t="inlineStr">
         <is>
-          <t>2026-07-11 08:37:54 PM PT</t>
+          <t>2026-07-11 08:39:54 PM PT</t>
         </is>
       </c>
       <c r="C120" t="n">
@@ -14439,7 +14439,7 @@
       </c>
       <c r="B121" t="inlineStr">
         <is>
-          <t>2026-07-11 08:37:54 PM PT</t>
+          <t>2026-07-11 08:39:53 PM PT</t>
         </is>
       </c>
       <c r="C121" t="n">
@@ -14553,7 +14553,7 @@
       </c>
       <c r="B122" t="inlineStr">
         <is>
-          <t>2026-07-11 08:37:53 PM PT</t>
+          <t>2026-07-11 08:39:53 PM PT</t>
         </is>
       </c>
       <c r="C122" t="n">
@@ -14667,7 +14667,7 @@
       </c>
       <c r="B123" t="inlineStr">
         <is>
-          <t>2026-07-11 08:37:54 PM PT</t>
+          <t>2026-07-11 08:39:54 PM PT</t>
         </is>
       </c>
       <c r="C123" t="n">
@@ -14781,7 +14781,7 @@
       </c>
       <c r="B124" t="inlineStr">
         <is>
-          <t>2026-07-11 08:37:53 PM PT</t>
+          <t>2026-07-11 08:39:53 PM PT</t>
         </is>
       </c>
       <c r="C124" t="n">
@@ -14895,7 +14895,7 @@
       </c>
       <c r="B125" t="inlineStr">
         <is>
-          <t>2026-07-11 08:37:53 PM PT</t>
+          <t>2026-07-11 08:39:53 PM PT</t>
         </is>
       </c>
       <c r="C125" t="n">
@@ -15009,7 +15009,7 @@
       </c>
       <c r="B126" t="inlineStr">
         <is>
-          <t>2026-07-11 08:37:53 PM PT</t>
+          <t>2026-07-11 08:39:53 PM PT</t>
         </is>
       </c>
       <c r="C126" t="n">
@@ -15123,7 +15123,7 @@
       </c>
       <c r="B127" t="inlineStr">
         <is>
-          <t>2026-07-11 08:37:54 PM PT</t>
+          <t>2026-07-11 08:39:53 PM PT</t>
         </is>
       </c>
       <c r="C127" t="n">
@@ -15237,7 +15237,7 @@
       </c>
       <c r="B128" t="inlineStr">
         <is>
-          <t>2026-07-11 08:37:54 PM PT</t>
+          <t>2026-07-11 08:39:53 PM PT</t>
         </is>
       </c>
       <c r="C128" t="n">
@@ -15351,7 +15351,7 @@
       </c>
       <c r="B129" t="inlineStr">
         <is>
-          <t>2026-07-11 08:37:54 PM PT</t>
+          <t>2026-07-11 08:39:53 PM PT</t>
         </is>
       </c>
       <c r="C129" t="n">
@@ -15465,7 +15465,7 @@
       </c>
       <c r="B130" t="inlineStr">
         <is>
-          <t>2026-07-11 08:37:54 PM PT</t>
+          <t>2026-07-11 08:39:54 PM PT</t>
         </is>
       </c>
       <c r="C130" t="n">
@@ -15478,7 +15478,7 @@
       </c>
       <c r="E130" t="inlineStr">
         <is>
-          <t>Bottom 8 | 0 out</t>
+          <t>Bottom 8 | 1 out</t>
         </is>
       </c>
       <c r="F130" t="n">
@@ -15490,13 +15490,13 @@
         </is>
       </c>
       <c r="H130" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I130" t="n">
         <v>0</v>
       </c>
       <c r="J130" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K130" t="inlineStr">
         <is>
@@ -15588,7 +15588,7 @@
       </c>
       <c r="B131" t="inlineStr">
         <is>
-          <t>2026-07-11 08:37:53 PM PT</t>
+          <t>2026-07-11 08:39:53 PM PT</t>
         </is>
       </c>
       <c r="C131" t="n">
@@ -15702,7 +15702,7 @@
       </c>
       <c r="B132" t="inlineStr">
         <is>
-          <t>2026-07-11 08:37:53 PM PT</t>
+          <t>2026-07-11 08:39:53 PM PT</t>
         </is>
       </c>
       <c r="C132" t="n">
@@ -15816,7 +15816,7 @@
       </c>
       <c r="B133" t="inlineStr">
         <is>
-          <t>2026-07-11 08:37:52 PM PT</t>
+          <t>2026-07-11 08:39:53 PM PT</t>
         </is>
       </c>
       <c r="C133" t="n">
@@ -15930,7 +15930,7 @@
       </c>
       <c r="B134" t="inlineStr">
         <is>
-          <t>2026-07-11 08:37:53 PM PT</t>
+          <t>2026-07-11 08:39:53 PM PT</t>
         </is>
       </c>
       <c r="C134" t="n">
@@ -16044,7 +16044,7 @@
       </c>
       <c r="B135" t="inlineStr">
         <is>
-          <t>2026-07-11 08:37:53 PM PT</t>
+          <t>2026-07-11 08:39:53 PM PT</t>
         </is>
       </c>
       <c r="C135" t="n">
@@ -16158,7 +16158,7 @@
       </c>
       <c r="B136" t="inlineStr">
         <is>
-          <t>2026-07-11 08:37:53 PM PT</t>
+          <t>2026-07-11 08:39:53 PM PT</t>
         </is>
       </c>
       <c r="C136" t="n">
@@ -16272,7 +16272,7 @@
       </c>
       <c r="B137" t="inlineStr">
         <is>
-          <t>2026-07-11 08:37:52 PM PT</t>
+          <t>2026-07-11 08:39:52 PM PT</t>
         </is>
       </c>
       <c r="C137" t="n">
@@ -16386,7 +16386,7 @@
       </c>
       <c r="B138" t="inlineStr">
         <is>
-          <t>2026-07-11 08:37:52 PM PT</t>
+          <t>2026-07-11 08:39:52 PM PT</t>
         </is>
       </c>
       <c r="C138" t="n">
@@ -16500,7 +16500,7 @@
       </c>
       <c r="B139" t="inlineStr">
         <is>
-          <t>2026-07-11 08:37:53 PM PT</t>
+          <t>2026-07-11 08:39:53 PM PT</t>
         </is>
       </c>
       <c r="C139" t="n">
@@ -16614,7 +16614,7 @@
       </c>
       <c r="B140" t="inlineStr">
         <is>
-          <t>2026-07-11 08:37:53 PM PT</t>
+          <t>2026-07-11 08:39:53 PM PT</t>
         </is>
       </c>
       <c r="C140" t="n">
@@ -16728,7 +16728,7 @@
       </c>
       <c r="B141" t="inlineStr">
         <is>
-          <t>2026-07-11 08:37:53 PM PT</t>
+          <t>2026-07-11 08:39:53 PM PT</t>
         </is>
       </c>
       <c r="C141" t="n">
@@ -16842,7 +16842,7 @@
       </c>
       <c r="B142" t="inlineStr">
         <is>
-          <t>2026-07-11 08:37:54 PM PT</t>
+          <t>2026-07-11 08:39:54 PM PT</t>
         </is>
       </c>
       <c r="C142" t="n">
@@ -16956,7 +16956,7 @@
       </c>
       <c r="B143" t="inlineStr">
         <is>
-          <t>2026-07-11 08:37:54 PM PT</t>
+          <t>2026-07-11 08:39:54 PM PT</t>
         </is>
       </c>
       <c r="C143" t="n">
@@ -17070,7 +17070,7 @@
       </c>
       <c r="B144" t="inlineStr">
         <is>
-          <t>2026-07-11 08:37:54 PM PT</t>
+          <t>2026-07-11 08:39:54 PM PT</t>
         </is>
       </c>
       <c r="C144" t="n">
@@ -17184,7 +17184,7 @@
       </c>
       <c r="B145" t="inlineStr">
         <is>
-          <t>2026-07-11 08:37:53 PM PT</t>
+          <t>2026-07-11 08:39:53 PM PT</t>
         </is>
       </c>
       <c r="C145" t="n">
@@ -17298,7 +17298,7 @@
       </c>
       <c r="B146" t="inlineStr">
         <is>
-          <t>2026-07-11 08:37:54 PM PT</t>
+          <t>2026-07-11 08:39:53 PM PT</t>
         </is>
       </c>
       <c r="C146" t="n">
@@ -17412,7 +17412,7 @@
       </c>
       <c r="B147" t="inlineStr">
         <is>
-          <t>2026-07-11 08:37:54 PM PT</t>
+          <t>2026-07-11 08:39:53 PM PT</t>
         </is>
       </c>
       <c r="C147" t="n">
@@ -17526,7 +17526,7 @@
       </c>
       <c r="B148" t="inlineStr">
         <is>
-          <t>2026-07-11 08:37:54 PM PT</t>
+          <t>2026-07-11 08:39:54 PM PT</t>
         </is>
       </c>
       <c r="C148" t="n">
@@ -17640,7 +17640,7 @@
       </c>
       <c r="B149" t="inlineStr">
         <is>
-          <t>2026-07-11 08:37:53 PM PT</t>
+          <t>2026-07-11 08:39:53 PM PT</t>
         </is>
       </c>
       <c r="C149" t="n">
@@ -17754,7 +17754,7 @@
       </c>
       <c r="B150" t="inlineStr">
         <is>
-          <t>2026-07-11 08:37:53 PM PT</t>
+          <t>2026-07-11 08:39:53 PM PT</t>
         </is>
       </c>
       <c r="C150" t="n">
@@ -17868,7 +17868,7 @@
       </c>
       <c r="B151" t="inlineStr">
         <is>
-          <t>2026-07-11 08:37:52 PM PT</t>
+          <t>2026-07-11 08:39:52 PM PT</t>
         </is>
       </c>
       <c r="C151" t="n">
@@ -17982,7 +17982,7 @@
       </c>
       <c r="B152" t="inlineStr">
         <is>
-          <t>2026-07-11 08:37:52 PM PT</t>
+          <t>2026-07-11 08:39:53 PM PT</t>
         </is>
       </c>
       <c r="C152" t="n">
@@ -18096,7 +18096,7 @@
       </c>
       <c r="B153" t="inlineStr">
         <is>
-          <t>2026-07-11 08:37:53 PM PT</t>
+          <t>2026-07-11 08:39:53 PM PT</t>
         </is>
       </c>
       <c r="C153" t="n">
@@ -18210,7 +18210,7 @@
       </c>
       <c r="B154" t="inlineStr">
         <is>
-          <t>2026-07-11 08:37:53 PM PT</t>
+          <t>2026-07-11 08:39:53 PM PT</t>
         </is>
       </c>
       <c r="C154" t="n">
@@ -18324,7 +18324,7 @@
       </c>
       <c r="B155" t="inlineStr">
         <is>
-          <t>2026-07-11 08:37:53 PM PT</t>
+          <t>2026-07-11 08:39:53 PM PT</t>
         </is>
       </c>
       <c r="C155" t="n">
@@ -18438,7 +18438,7 @@
       </c>
       <c r="B156" t="inlineStr">
         <is>
-          <t>2026-07-11 08:37:52 PM PT</t>
+          <t>2026-07-11 08:39:52 PM PT</t>
         </is>
       </c>
       <c r="C156" t="n">
@@ -18552,7 +18552,7 @@
       </c>
       <c r="B157" t="inlineStr">
         <is>
-          <t>2026-07-11 08:37:54 PM PT</t>
+          <t>2026-07-11 08:39:54 PM PT</t>
         </is>
       </c>
       <c r="C157" t="n">
@@ -18565,7 +18565,7 @@
       </c>
       <c r="E157" t="inlineStr">
         <is>
-          <t>Bottom 8 | 1 out</t>
+          <t>Bottom 8 | 2 out</t>
         </is>
       </c>
       <c r="F157" t="n">
@@ -18577,10 +18577,10 @@
         </is>
       </c>
       <c r="H157" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I157" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="J157" t="n">
         <v>0</v>
@@ -18675,7 +18675,7 @@
       </c>
       <c r="B158" t="inlineStr">
         <is>
-          <t>2026-07-11 08:37:54 PM PT</t>
+          <t>2026-07-11 08:39:54 PM PT</t>
         </is>
       </c>
       <c r="C158" t="n">
@@ -18688,7 +18688,7 @@
       </c>
       <c r="E158" t="inlineStr">
         <is>
-          <t>Bottom 8 | 1 out</t>
+          <t>Bottom 8 | 2 out</t>
         </is>
       </c>
       <c r="F158" t="n">
@@ -18700,10 +18700,10 @@
         </is>
       </c>
       <c r="H158" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I158" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="J158" t="n">
         <v>0</v>
@@ -18798,7 +18798,7 @@
       </c>
       <c r="B159" t="inlineStr">
         <is>
-          <t>2026-07-11 08:37:54 PM PT</t>
+          <t>2026-07-11 08:39:54 PM PT</t>
         </is>
       </c>
       <c r="C159" t="n">
@@ -18811,7 +18811,7 @@
       </c>
       <c r="E159" t="inlineStr">
         <is>
-          <t>Bottom 8 | 1 out</t>
+          <t>Bottom 8 | 2 out</t>
         </is>
       </c>
       <c r="F159" t="n">
@@ -18823,10 +18823,10 @@
         </is>
       </c>
       <c r="H159" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I159" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="J159" t="n">
         <v>0</v>
@@ -18921,7 +18921,7 @@
       </c>
       <c r="B160" t="inlineStr">
         <is>
-          <t>2026-07-11 08:37:54 PM PT</t>
+          <t>2026-07-11 08:39:54 PM PT</t>
         </is>
       </c>
       <c r="C160" t="n">
@@ -19035,7 +19035,7 @@
       </c>
       <c r="B161" t="inlineStr">
         <is>
-          <t>2026-07-11 08:37:54 PM PT</t>
+          <t>2026-07-11 08:39:54 PM PT</t>
         </is>
       </c>
       <c r="C161" t="n">
@@ -19149,7 +19149,7 @@
       </c>
       <c r="B162" t="inlineStr">
         <is>
-          <t>2026-07-11 08:37:54 PM PT</t>
+          <t>2026-07-11 08:39:54 PM PT</t>
         </is>
       </c>
       <c r="C162" t="n">
@@ -19263,7 +19263,7 @@
       </c>
       <c r="B163" t="inlineStr">
         <is>
-          <t>2026-07-11 08:37:54 PM PT</t>
+          <t>2026-07-11 08:39:54 PM PT</t>
         </is>
       </c>
       <c r="C163" t="n">
@@ -19377,7 +19377,7 @@
       </c>
       <c r="B164" t="inlineStr">
         <is>
-          <t>2026-07-11 08:37:54 PM PT</t>
+          <t>2026-07-11 08:39:54 PM PT</t>
         </is>
       </c>
       <c r="C164" t="n">
@@ -19491,7 +19491,7 @@
       </c>
       <c r="B165" t="inlineStr">
         <is>
-          <t>2026-07-11 08:37:53 PM PT</t>
+          <t>2026-07-11 08:39:53 PM PT</t>
         </is>
       </c>
       <c r="C165" t="n">
@@ -19605,7 +19605,7 @@
       </c>
       <c r="B166" t="inlineStr">
         <is>
-          <t>2026-07-11 08:37:53 PM PT</t>
+          <t>2026-07-11 08:39:53 PM PT</t>
         </is>
       </c>
       <c r="C166" t="n">
@@ -19719,7 +19719,7 @@
       </c>
       <c r="B167" t="inlineStr">
         <is>
-          <t>2026-07-11 08:37:53 PM PT</t>
+          <t>2026-07-11 08:39:53 PM PT</t>
         </is>
       </c>
       <c r="C167" t="n">
@@ -19833,7 +19833,7 @@
       </c>
       <c r="B168" t="inlineStr">
         <is>
-          <t>2026-07-11 08:37:53 PM PT</t>
+          <t>2026-07-11 08:39:53 PM PT</t>
         </is>
       </c>
       <c r="C168" t="n">
@@ -19947,7 +19947,7 @@
       </c>
       <c r="B169" t="inlineStr">
         <is>
-          <t>2026-07-11 08:37:54 PM PT</t>
+          <t>2026-07-11 08:39:53 PM PT</t>
         </is>
       </c>
       <c r="C169" t="n">
@@ -20061,7 +20061,7 @@
       </c>
       <c r="B170" t="inlineStr">
         <is>
-          <t>2026-07-11 08:37:53 PM PT</t>
+          <t>2026-07-11 08:39:53 PM PT</t>
         </is>
       </c>
       <c r="C170" t="n">
@@ -20175,7 +20175,7 @@
       </c>
       <c r="B171" t="inlineStr">
         <is>
-          <t>2026-07-11 08:37:54 PM PT</t>
+          <t>2026-07-11 08:39:54 PM PT</t>
         </is>
       </c>
       <c r="C171" t="n">
@@ -20188,7 +20188,7 @@
       </c>
       <c r="E171" t="inlineStr">
         <is>
-          <t>Bottom 8 | 0 out</t>
+          <t>Bottom 8 | 1 out</t>
         </is>
       </c>
       <c r="F171" t="n">
@@ -20200,13 +20200,13 @@
         </is>
       </c>
       <c r="H171" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I171" t="n">
         <v>0</v>
       </c>
       <c r="J171" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K171" t="inlineStr">
         <is>
@@ -20298,7 +20298,7 @@
       </c>
       <c r="B172" t="inlineStr">
         <is>
-          <t>2026-07-11 08:37:54 PM PT</t>
+          <t>2026-07-11 08:39:54 PM PT</t>
         </is>
       </c>
       <c r="C172" t="n">
@@ -20311,7 +20311,7 @@
       </c>
       <c r="E172" t="inlineStr">
         <is>
-          <t>Bottom 8 | 0 out</t>
+          <t>Bottom 8 | 1 out</t>
         </is>
       </c>
       <c r="F172" t="n">
@@ -20323,13 +20323,13 @@
         </is>
       </c>
       <c r="H172" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I172" t="n">
         <v>0</v>
       </c>
       <c r="J172" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K172" t="inlineStr">
         <is>
@@ -20421,7 +20421,7 @@
       </c>
       <c r="B173" t="inlineStr">
         <is>
-          <t>2026-07-11 08:37:53 PM PT</t>
+          <t>2026-07-11 08:39:53 PM PT</t>
         </is>
       </c>
       <c r="C173" t="n">
@@ -20535,7 +20535,7 @@
       </c>
       <c r="B174" t="inlineStr">
         <is>
-          <t>2026-07-11 08:37:53 PM PT</t>
+          <t>2026-07-11 08:39:53 PM PT</t>
         </is>
       </c>
       <c r="C174" t="n">
@@ -20649,7 +20649,7 @@
       </c>
       <c r="B175" t="inlineStr">
         <is>
-          <t>2026-07-11 08:37:52 PM PT</t>
+          <t>2026-07-11 08:39:52 PM PT</t>
         </is>
       </c>
       <c r="C175" t="n">
@@ -20763,7 +20763,7 @@
       </c>
       <c r="B176" t="inlineStr">
         <is>
-          <t>2026-07-11 08:37:52 PM PT</t>
+          <t>2026-07-11 08:39:53 PM PT</t>
         </is>
       </c>
       <c r="C176" t="n">
@@ -20877,7 +20877,7 @@
       </c>
       <c r="B177" t="inlineStr">
         <is>
-          <t>2026-07-11 08:37:53 PM PT</t>
+          <t>2026-07-11 08:39:53 PM PT</t>
         </is>
       </c>
       <c r="C177" t="n">
@@ -20991,7 +20991,7 @@
       </c>
       <c r="B178" t="inlineStr">
         <is>
-          <t>2026-07-11 08:37:53 PM PT</t>
+          <t>2026-07-11 08:39:53 PM PT</t>
         </is>
       </c>
       <c r="C178" t="n">
@@ -21105,7 +21105,7 @@
       </c>
       <c r="B179" t="inlineStr">
         <is>
-          <t>2026-07-11 08:37:53 PM PT</t>
+          <t>2026-07-11 08:39:53 PM PT</t>
         </is>
       </c>
       <c r="C179" t="n">
@@ -21219,7 +21219,7 @@
       </c>
       <c r="B180" t="inlineStr">
         <is>
-          <t>2026-07-11 08:37:53 PM PT</t>
+          <t>2026-07-11 08:39:53 PM PT</t>
         </is>
       </c>
       <c r="C180" t="n">
@@ -21333,7 +21333,7 @@
       </c>
       <c r="B181" t="inlineStr">
         <is>
-          <t>2026-07-11 08:37:53 PM PT</t>
+          <t>2026-07-11 08:39:53 PM PT</t>
         </is>
       </c>
       <c r="C181" t="n">
@@ -21447,7 +21447,7 @@
       </c>
       <c r="B182" t="inlineStr">
         <is>
-          <t>2026-07-11 08:37:53 PM PT</t>
+          <t>2026-07-11 08:39:53 PM PT</t>
         </is>
       </c>
       <c r="C182" t="n">
@@ -21561,7 +21561,7 @@
       </c>
       <c r="B183" t="inlineStr">
         <is>
-          <t>2026-07-11 08:37:53 PM PT</t>
+          <t>2026-07-11 08:39:53 PM PT</t>
         </is>
       </c>
       <c r="C183" t="n">
@@ -21675,7 +21675,7 @@
       </c>
       <c r="B184" t="inlineStr">
         <is>
-          <t>2026-07-11 08:37:52 PM PT</t>
+          <t>2026-07-11 08:39:53 PM PT</t>
         </is>
       </c>
       <c r="C184" t="n">
@@ -21789,7 +21789,7 @@
       </c>
       <c r="B185" t="inlineStr">
         <is>
-          <t>2026-07-11 08:37:52 PM PT</t>
+          <t>2026-07-11 08:39:53 PM PT</t>
         </is>
       </c>
       <c r="C185" t="n">
@@ -21903,7 +21903,7 @@
       </c>
       <c r="B186" t="inlineStr">
         <is>
-          <t>2026-07-11 08:37:53 PM PT</t>
+          <t>2026-07-11 08:39:53 PM PT</t>
         </is>
       </c>
       <c r="C186" t="n">
@@ -22017,7 +22017,7 @@
       </c>
       <c r="B187" t="inlineStr">
         <is>
-          <t>2026-07-11 08:37:53 PM PT</t>
+          <t>2026-07-11 08:39:53 PM PT</t>
         </is>
       </c>
       <c r="C187" t="n">
@@ -22131,7 +22131,7 @@
       </c>
       <c r="B188" t="inlineStr">
         <is>
-          <t>2026-07-11 08:37:53 PM PT</t>
+          <t>2026-07-11 08:39:53 PM PT</t>
         </is>
       </c>
       <c r="C188" t="n">
@@ -22245,7 +22245,7 @@
       </c>
       <c r="B189" t="inlineStr">
         <is>
-          <t>2026-07-11 08:37:54 PM PT</t>
+          <t>2026-07-11 08:39:53 PM PT</t>
         </is>
       </c>
       <c r="C189" t="n">
@@ -22359,7 +22359,7 @@
       </c>
       <c r="B190" t="inlineStr">
         <is>
-          <t>2026-07-11 08:37:54 PM PT</t>
+          <t>2026-07-11 08:39:54 PM PT</t>
         </is>
       </c>
       <c r="C190" t="n">
@@ -22372,7 +22372,7 @@
       </c>
       <c r="E190" t="inlineStr">
         <is>
-          <t>Bottom 8 | 1 out</t>
+          <t>Bottom 8 | 2 out</t>
         </is>
       </c>
       <c r="F190" t="n">
@@ -22384,10 +22384,10 @@
         </is>
       </c>
       <c r="H190" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I190" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="J190" t="n">
         <v>0</v>
@@ -22482,7 +22482,7 @@
       </c>
       <c r="B191" t="inlineStr">
         <is>
-          <t>2026-07-11 08:37:53 PM PT</t>
+          <t>2026-07-11 08:39:53 PM PT</t>
         </is>
       </c>
       <c r="C191" t="n">
@@ -22596,7 +22596,7 @@
       </c>
       <c r="B192" t="inlineStr">
         <is>
-          <t>2026-07-11 08:37:53 PM PT</t>
+          <t>2026-07-11 08:39:53 PM PT</t>
         </is>
       </c>
       <c r="C192" t="n">
@@ -22710,7 +22710,7 @@
       </c>
       <c r="B193" t="inlineStr">
         <is>
-          <t>2026-07-11 08:37:54 PM PT</t>
+          <t>2026-07-11 08:39:54 PM PT</t>
         </is>
       </c>
       <c r="C193" t="n">
@@ -22723,7 +22723,7 @@
       </c>
       <c r="E193" t="inlineStr">
         <is>
-          <t>Bottom 8 | 0 out</t>
+          <t>Bottom 8 | 1 out</t>
         </is>
       </c>
       <c r="F193" t="n">
@@ -22735,13 +22735,13 @@
         </is>
       </c>
       <c r="H193" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I193" t="n">
         <v>0</v>
       </c>
       <c r="J193" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K193" t="inlineStr">
         <is>
@@ -22833,7 +22833,7 @@
       </c>
       <c r="B194" t="inlineStr">
         <is>
-          <t>2026-07-11 08:37:54 PM PT</t>
+          <t>2026-07-11 08:39:54 PM PT</t>
         </is>
       </c>
       <c r="C194" t="n">
@@ -22846,7 +22846,7 @@
       </c>
       <c r="E194" t="inlineStr">
         <is>
-          <t>Bottom 8 | 0 out</t>
+          <t>Bottom 8 | 1 out</t>
         </is>
       </c>
       <c r="F194" t="n">
@@ -22858,13 +22858,13 @@
         </is>
       </c>
       <c r="H194" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I194" t="n">
         <v>0</v>
       </c>
       <c r="J194" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K194" t="inlineStr">
         <is>
@@ -22956,7 +22956,7 @@
       </c>
       <c r="B195" t="inlineStr">
         <is>
-          <t>2026-07-11 08:37:53 PM PT</t>
+          <t>2026-07-11 08:39:53 PM PT</t>
         </is>
       </c>
       <c r="C195" t="n">
@@ -23070,7 +23070,7 @@
       </c>
       <c r="B196" t="inlineStr">
         <is>
-          <t>2026-07-11 08:37:54 PM PT</t>
+          <t>2026-07-11 08:39:54 PM PT</t>
         </is>
       </c>
       <c r="C196" t="n">
@@ -23184,7 +23184,7 @@
       </c>
       <c r="B197" t="inlineStr">
         <is>
-          <t>2026-07-11 08:37:54 PM PT</t>
+          <t>2026-07-11 08:39:54 PM PT</t>
         </is>
       </c>
       <c r="C197" t="n">
@@ -23298,7 +23298,7 @@
       </c>
       <c r="B198" t="inlineStr">
         <is>
-          <t>2026-07-11 08:37:54 PM PT</t>
+          <t>2026-07-11 08:39:53 PM PT</t>
         </is>
       </c>
       <c r="C198" t="n">
@@ -23412,7 +23412,7 @@
       </c>
       <c r="B199" t="inlineStr">
         <is>
-          <t>2026-07-11 08:37:53 PM PT</t>
+          <t>2026-07-11 08:39:53 PM PT</t>
         </is>
       </c>
       <c r="C199" t="n">
@@ -23526,7 +23526,7 @@
       </c>
       <c r="B200" t="inlineStr">
         <is>
-          <t>2026-07-11 08:37:53 PM PT</t>
+          <t>2026-07-11 08:39:53 PM PT</t>
         </is>
       </c>
       <c r="C200" t="n">
@@ -23640,7 +23640,7 @@
       </c>
       <c r="B201" t="inlineStr">
         <is>
-          <t>2026-07-11 08:37:53 PM PT</t>
+          <t>2026-07-11 08:39:53 PM PT</t>
         </is>
       </c>
       <c r="C201" t="n">
@@ -23754,7 +23754,7 @@
       </c>
       <c r="B202" t="inlineStr">
         <is>
-          <t>2026-07-11 08:37:54 PM PT</t>
+          <t>2026-07-11 08:39:54 PM PT</t>
         </is>
       </c>
       <c r="C202" t="n">
@@ -23868,7 +23868,7 @@
       </c>
       <c r="B203" t="inlineStr">
         <is>
-          <t>2026-07-11 08:37:53 PM PT</t>
+          <t>2026-07-11 08:39:53 PM PT</t>
         </is>
       </c>
       <c r="C203" t="n">
@@ -23982,7 +23982,7 @@
       </c>
       <c r="B204" t="inlineStr">
         <is>
-          <t>2026-07-11 08:37:53 PM PT</t>
+          <t>2026-07-11 08:39:53 PM PT</t>
         </is>
       </c>
       <c r="C204" t="n">
@@ -24096,7 +24096,7 @@
       </c>
       <c r="B205" t="inlineStr">
         <is>
-          <t>2026-07-11 08:37:53 PM PT</t>
+          <t>2026-07-11 08:39:53 PM PT</t>
         </is>
       </c>
       <c r="C205" t="n">
@@ -24210,7 +24210,7 @@
       </c>
       <c r="B206" t="inlineStr">
         <is>
-          <t>2026-07-11 08:37:53 PM PT</t>
+          <t>2026-07-11 08:39:53 PM PT</t>
         </is>
       </c>
       <c r="C206" t="n">
@@ -24324,7 +24324,7 @@
       </c>
       <c r="B207" t="inlineStr">
         <is>
-          <t>2026-07-11 08:37:53 PM PT</t>
+          <t>2026-07-11 08:39:53 PM PT</t>
         </is>
       </c>
       <c r="C207" t="n">
@@ -24438,7 +24438,7 @@
       </c>
       <c r="B208" t="inlineStr">
         <is>
-          <t>2026-07-11 08:37:53 PM PT</t>
+          <t>2026-07-11 08:39:53 PM PT</t>
         </is>
       </c>
       <c r="C208" t="n">
@@ -24552,7 +24552,7 @@
       </c>
       <c r="B209" t="inlineStr">
         <is>
-          <t>2026-07-11 08:37:54 PM PT</t>
+          <t>2026-07-11 08:39:53 PM PT</t>
         </is>
       </c>
       <c r="C209" t="n">
@@ -24666,7 +24666,7 @@
       </c>
       <c r="B210" t="inlineStr">
         <is>
-          <t>2026-07-11 08:37:54 PM PT</t>
+          <t>2026-07-11 08:39:53 PM PT</t>
         </is>
       </c>
       <c r="C210" t="n">
@@ -24780,7 +24780,7 @@
       </c>
       <c r="B211" t="inlineStr">
         <is>
-          <t>2026-07-11 08:37:54 PM PT</t>
+          <t>2026-07-11 08:39:53 PM PT</t>
         </is>
       </c>
       <c r="C211" t="n">
@@ -24894,7 +24894,7 @@
       </c>
       <c r="B212" t="inlineStr">
         <is>
-          <t>2026-07-11 08:37:54 PM PT</t>
+          <t>2026-07-11 08:39:53 PM PT</t>
         </is>
       </c>
       <c r="C212" t="n">
@@ -25008,7 +25008,7 @@
       </c>
       <c r="B213" t="inlineStr">
         <is>
-          <t>2026-07-11 08:37:53 PM PT</t>
+          <t>2026-07-11 08:39:53 PM PT</t>
         </is>
       </c>
       <c r="C213" t="n">
@@ -25122,7 +25122,7 @@
       </c>
       <c r="B214" t="inlineStr">
         <is>
-          <t>2026-07-11 08:37:53 PM PT</t>
+          <t>2026-07-11 08:39:53 PM PT</t>
         </is>
       </c>
       <c r="C214" t="n">
@@ -25236,7 +25236,7 @@
       </c>
       <c r="B215" t="inlineStr">
         <is>
-          <t>2026-07-11 08:37:53 PM PT</t>
+          <t>2026-07-11 08:39:53 PM PT</t>
         </is>
       </c>
       <c r="C215" t="n">
@@ -25350,7 +25350,7 @@
       </c>
       <c r="B216" t="inlineStr">
         <is>
-          <t>2026-07-11 08:37:53 PM PT</t>
+          <t>2026-07-11 08:39:53 PM PT</t>
         </is>
       </c>
       <c r="C216" t="n">
@@ -25464,7 +25464,7 @@
       </c>
       <c r="B217" t="inlineStr">
         <is>
-          <t>2026-07-11 08:37:53 PM PT</t>
+          <t>2026-07-11 08:39:53 PM PT</t>
         </is>
       </c>
       <c r="C217" t="n">
@@ -25578,7 +25578,7 @@
       </c>
       <c r="B218" t="inlineStr">
         <is>
-          <t>2026-07-11 08:37:53 PM PT</t>
+          <t>2026-07-11 08:39:53 PM PT</t>
         </is>
       </c>
       <c r="C218" t="n">
@@ -25692,7 +25692,7 @@
       </c>
       <c r="B219" t="inlineStr">
         <is>
-          <t>2026-07-11 08:37:53 PM PT</t>
+          <t>2026-07-11 08:39:53 PM PT</t>
         </is>
       </c>
       <c r="C219" t="n">
@@ -25806,7 +25806,7 @@
       </c>
       <c r="B220" t="inlineStr">
         <is>
-          <t>2026-07-11 08:37:53 PM PT</t>
+          <t>2026-07-11 08:39:53 PM PT</t>
         </is>
       </c>
       <c r="C220" t="n">
@@ -25920,7 +25920,7 @@
       </c>
       <c r="B221" t="inlineStr">
         <is>
-          <t>2026-07-11 08:37:53 PM PT</t>
+          <t>2026-07-11 08:39:53 PM PT</t>
         </is>
       </c>
       <c r="C221" t="n">
@@ -26034,7 +26034,7 @@
       </c>
       <c r="B222" t="inlineStr">
         <is>
-          <t>2026-07-11 08:37:53 PM PT</t>
+          <t>2026-07-11 08:39:53 PM PT</t>
         </is>
       </c>
       <c r="C222" t="n">
@@ -26148,7 +26148,7 @@
       </c>
       <c r="B223" t="inlineStr">
         <is>
-          <t>2026-07-11 08:37:53 PM PT</t>
+          <t>2026-07-11 08:39:53 PM PT</t>
         </is>
       </c>
       <c r="C223" t="n">
@@ -26262,7 +26262,7 @@
       </c>
       <c r="B224" t="inlineStr">
         <is>
-          <t>2026-07-11 08:37:52 PM PT</t>
+          <t>2026-07-11 08:39:52 PM PT</t>
         </is>
       </c>
       <c r="C224" t="n">
@@ -26376,7 +26376,7 @@
       </c>
       <c r="B225" t="inlineStr">
         <is>
-          <t>2026-07-11 08:37:52 PM PT</t>
+          <t>2026-07-11 08:39:53 PM PT</t>
         </is>
       </c>
       <c r="C225" t="n">
@@ -26490,7 +26490,7 @@
       </c>
       <c r="B226" t="inlineStr">
         <is>
-          <t>2026-07-11 08:37:53 PM PT</t>
+          <t>2026-07-11 08:39:53 PM PT</t>
         </is>
       </c>
       <c r="C226" t="n">
@@ -26604,7 +26604,7 @@
       </c>
       <c r="B227" t="inlineStr">
         <is>
-          <t>2026-07-11 08:37:53 PM PT</t>
+          <t>2026-07-11 08:39:53 PM PT</t>
         </is>
       </c>
       <c r="C227" t="n">
@@ -26718,7 +26718,7 @@
       </c>
       <c r="B228" t="inlineStr">
         <is>
-          <t>2026-07-11 08:37:54 PM PT</t>
+          <t>2026-07-11 08:39:53 PM PT</t>
         </is>
       </c>
       <c r="C228" t="n">
@@ -26832,7 +26832,7 @@
       </c>
       <c r="B229" t="inlineStr">
         <is>
-          <t>2026-07-11 08:37:54 PM PT</t>
+          <t>2026-07-11 08:39:53 PM PT</t>
         </is>
       </c>
       <c r="C229" t="n">
@@ -26946,7 +26946,7 @@
       </c>
       <c r="B230" t="inlineStr">
         <is>
-          <t>2026-07-11 08:37:54 PM PT</t>
+          <t>2026-07-11 08:39:54 PM PT</t>
         </is>
       </c>
       <c r="C230" t="n">
@@ -26959,7 +26959,7 @@
       </c>
       <c r="E230" t="inlineStr">
         <is>
-          <t>Bottom 8 | 1 out</t>
+          <t>Bottom 8 | 2 out</t>
         </is>
       </c>
       <c r="F230" t="n">
@@ -26971,10 +26971,10 @@
         </is>
       </c>
       <c r="H230" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I230" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="J230" t="n">
         <v>0</v>
@@ -27069,7 +27069,7 @@
       </c>
       <c r="B231" t="inlineStr">
         <is>
-          <t>2026-07-11 08:37:53 PM PT</t>
+          <t>2026-07-11 08:39:53 PM PT</t>
         </is>
       </c>
       <c r="C231" t="n">
@@ -27183,7 +27183,7 @@
       </c>
       <c r="B232" t="inlineStr">
         <is>
-          <t>2026-07-11 08:37:53 PM PT</t>
+          <t>2026-07-11 08:39:53 PM PT</t>
         </is>
       </c>
       <c r="C232" t="n">
@@ -27297,7 +27297,7 @@
       </c>
       <c r="B233" t="inlineStr">
         <is>
-          <t>2026-07-11 08:37:53 PM PT</t>
+          <t>2026-07-11 08:39:53 PM PT</t>
         </is>
       </c>
       <c r="C233" t="n">
@@ -27411,7 +27411,7 @@
       </c>
       <c r="B234" t="inlineStr">
         <is>
-          <t>2026-07-11 08:37:53 PM PT</t>
+          <t>2026-07-11 08:39:53 PM PT</t>
         </is>
       </c>
       <c r="C234" t="n">
@@ -27525,7 +27525,7 @@
       </c>
       <c r="B235" t="inlineStr">
         <is>
-          <t>2026-07-11 08:37:54 PM PT</t>
+          <t>2026-07-11 08:39:54 PM PT</t>
         </is>
       </c>
       <c r="C235" t="n">
@@ -27538,7 +27538,7 @@
       </c>
       <c r="E235" t="inlineStr">
         <is>
-          <t>Bottom 8 | 0 out</t>
+          <t>Bottom 8 | 1 out</t>
         </is>
       </c>
       <c r="F235" t="n">
@@ -27550,13 +27550,13 @@
         </is>
       </c>
       <c r="H235" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I235" t="n">
         <v>0</v>
       </c>
       <c r="J235" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K235" t="inlineStr">
         <is>
@@ -27648,7 +27648,7 @@
       </c>
       <c r="B236" t="inlineStr">
         <is>
-          <t>2026-07-11 08:37:54 PM PT</t>
+          <t>2026-07-11 08:39:54 PM PT</t>
         </is>
       </c>
       <c r="C236" t="n">
@@ -27661,7 +27661,7 @@
       </c>
       <c r="E236" t="inlineStr">
         <is>
-          <t>Bottom 8 | 0 out</t>
+          <t>Bottom 8 | 1 out</t>
         </is>
       </c>
       <c r="F236" t="n">
@@ -27673,13 +27673,13 @@
         </is>
       </c>
       <c r="H236" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I236" t="n">
         <v>0</v>
       </c>
       <c r="J236" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K236" t="inlineStr">
         <is>
@@ -27771,7 +27771,7 @@
       </c>
       <c r="B237" t="inlineStr">
         <is>
-          <t>2026-07-11 08:37:53 PM PT</t>
+          <t>2026-07-11 08:39:53 PM PT</t>
         </is>
       </c>
       <c r="C237" t="n">
@@ -27885,7 +27885,7 @@
       </c>
       <c r="B238" t="inlineStr">
         <is>
-          <t>2026-07-11 08:37:53 PM PT</t>
+          <t>2026-07-11 08:39:53 PM PT</t>
         </is>
       </c>
       <c r="C238" t="n">
@@ -27999,7 +27999,7 @@
       </c>
       <c r="B239" t="inlineStr">
         <is>
-          <t>2026-07-11 08:37:53 PM PT</t>
+          <t>2026-07-11 08:39:53 PM PT</t>
         </is>
       </c>
       <c r="C239" t="n">
@@ -28113,7 +28113,7 @@
       </c>
       <c r="B240" t="inlineStr">
         <is>
-          <t>2026-07-11 08:37:53 PM PT</t>
+          <t>2026-07-11 08:39:53 PM PT</t>
         </is>
       </c>
       <c r="C240" t="n">
@@ -28227,7 +28227,7 @@
       </c>
       <c r="B241" t="inlineStr">
         <is>
-          <t>2026-07-11 08:37:53 PM PT</t>
+          <t>2026-07-11 08:39:53 PM PT</t>
         </is>
       </c>
       <c r="C241" t="n">
@@ -28341,7 +28341,7 @@
       </c>
       <c r="B242" t="inlineStr">
         <is>
-          <t>2026-07-11 08:37:53 PM PT</t>
+          <t>2026-07-11 08:39:53 PM PT</t>
         </is>
       </c>
       <c r="C242" t="n">
@@ -28455,7 +28455,7 @@
       </c>
       <c r="B243" t="inlineStr">
         <is>
-          <t>2026-07-11 08:37:53 PM PT</t>
+          <t>2026-07-11 08:39:53 PM PT</t>
         </is>
       </c>
       <c r="C243" t="n">
@@ -28569,7 +28569,7 @@
       </c>
       <c r="B244" t="inlineStr">
         <is>
-          <t>2026-07-11 08:37:54 PM PT</t>
+          <t>2026-07-11 08:39:54 PM PT</t>
         </is>
       </c>
       <c r="C244" t="n">
@@ -28683,7 +28683,7 @@
       </c>
       <c r="B245" t="inlineStr">
         <is>
-          <t>2026-07-11 08:37:54 PM PT</t>
+          <t>2026-07-11 08:39:54 PM PT</t>
         </is>
       </c>
       <c r="C245" t="n">
@@ -28797,7 +28797,7 @@
       </c>
       <c r="B246" t="inlineStr">
         <is>
-          <t>2026-07-11 08:37:54 PM PT</t>
+          <t>2026-07-11 08:39:54 PM PT</t>
         </is>
       </c>
       <c r="C246" t="n">
@@ -28911,7 +28911,7 @@
       </c>
       <c r="B247" t="inlineStr">
         <is>
-          <t>2026-07-11 08:37:54 PM PT</t>
+          <t>2026-07-11 08:39:53 PM PT</t>
         </is>
       </c>
       <c r="C247" t="n">
@@ -29025,7 +29025,7 @@
       </c>
       <c r="B248" t="inlineStr">
         <is>
-          <t>2026-07-11 08:37:54 PM PT</t>
+          <t>2026-07-11 08:39:53 PM PT</t>
         </is>
       </c>
       <c r="C248" t="n">
@@ -29139,7 +29139,7 @@
       </c>
       <c r="B249" t="inlineStr">
         <is>
-          <t>2026-07-11 08:37:54 PM PT</t>
+          <t>2026-07-11 08:39:53 PM PT</t>
         </is>
       </c>
       <c r="C249" t="n">
@@ -29253,7 +29253,7 @@
       </c>
       <c r="B250" t="inlineStr">
         <is>
-          <t>2026-07-11 08:37:53 PM PT</t>
+          <t>2026-07-11 08:39:53 PM PT</t>
         </is>
       </c>
       <c r="C250" t="n">
@@ -29367,7 +29367,7 @@
       </c>
       <c r="B251" t="inlineStr">
         <is>
-          <t>2026-07-11 08:37:53 PM PT</t>
+          <t>2026-07-11 08:39:53 PM PT</t>
         </is>
       </c>
       <c r="C251" t="n">
@@ -29481,7 +29481,7 @@
       </c>
       <c r="B252" t="inlineStr">
         <is>
-          <t>2026-07-11 08:37:53 PM PT</t>
+          <t>2026-07-11 08:39:53 PM PT</t>
         </is>
       </c>
       <c r="C252" t="n">
@@ -29595,7 +29595,7 @@
       </c>
       <c r="B253" t="inlineStr">
         <is>
-          <t>2026-07-11 08:37:54 PM PT</t>
+          <t>2026-07-11 08:39:54 PM PT</t>
         </is>
       </c>
       <c r="C253" t="n">
@@ -29709,7 +29709,7 @@
       </c>
       <c r="B254" t="inlineStr">
         <is>
-          <t>2026-07-11 08:37:54 PM PT</t>
+          <t>2026-07-11 08:39:54 PM PT</t>
         </is>
       </c>
       <c r="C254" t="n">
@@ -29823,7 +29823,7 @@
       </c>
       <c r="B255" t="inlineStr">
         <is>
-          <t>2026-07-11 08:37:54 PM PT</t>
+          <t>2026-07-11 08:39:54 PM PT</t>
         </is>
       </c>
       <c r="C255" t="n">
@@ -29937,7 +29937,7 @@
       </c>
       <c r="B256" t="inlineStr">
         <is>
-          <t>2026-07-11 08:37:54 PM PT</t>
+          <t>2026-07-11 08:39:54 PM PT</t>
         </is>
       </c>
       <c r="C256" t="n">
@@ -30051,7 +30051,7 @@
       </c>
       <c r="B257" t="inlineStr">
         <is>
-          <t>2026-07-11 08:37:54 PM PT</t>
+          <t>2026-07-11 08:39:54 PM PT</t>
         </is>
       </c>
       <c r="C257" t="n">
@@ -30165,7 +30165,7 @@
       </c>
       <c r="B258" t="inlineStr">
         <is>
-          <t>2026-07-11 08:37:53 PM PT</t>
+          <t>2026-07-11 08:39:53 PM PT</t>
         </is>
       </c>
       <c r="C258" t="n">
@@ -30279,7 +30279,7 @@
       </c>
       <c r="B259" t="inlineStr">
         <is>
-          <t>2026-07-11 08:37:53 PM PT</t>
+          <t>2026-07-11 08:39:53 PM PT</t>
         </is>
       </c>
       <c r="C259" t="n">
@@ -30393,7 +30393,7 @@
       </c>
       <c r="B260" t="inlineStr">
         <is>
-          <t>2026-07-11 08:37:53 PM PT</t>
+          <t>2026-07-11 08:39:53 PM PT</t>
         </is>
       </c>
       <c r="C260" t="n">
@@ -30507,7 +30507,7 @@
       </c>
       <c r="B261" t="inlineStr">
         <is>
-          <t>2026-07-11 08:37:53 PM PT</t>
+          <t>2026-07-11 08:39:53 PM PT</t>
         </is>
       </c>
       <c r="C261" t="n">
@@ -30621,7 +30621,7 @@
       </c>
       <c r="B262" t="inlineStr">
         <is>
-          <t>2026-07-11 08:37:53 PM PT</t>
+          <t>2026-07-11 08:39:53 PM PT</t>
         </is>
       </c>
       <c r="C262" t="n">
@@ -30735,7 +30735,7 @@
       </c>
       <c r="B263" t="inlineStr">
         <is>
-          <t>2026-07-11 08:37:53 PM PT</t>
+          <t>2026-07-11 08:39:53 PM PT</t>
         </is>
       </c>
       <c r="C263" t="n">
@@ -30849,7 +30849,7 @@
       </c>
       <c r="B264" t="inlineStr">
         <is>
-          <t>2026-07-11 08:37:53 PM PT</t>
+          <t>2026-07-11 08:39:53 PM PT</t>
         </is>
       </c>
       <c r="C264" t="n">
@@ -30963,7 +30963,7 @@
       </c>
       <c r="B265" t="inlineStr">
         <is>
-          <t>2026-07-11 08:37:53 PM PT</t>
+          <t>2026-07-11 08:39:53 PM PT</t>
         </is>
       </c>
       <c r="C265" t="n">
@@ -31077,7 +31077,7 @@
       </c>
       <c r="B266" t="inlineStr">
         <is>
-          <t>2026-07-11 08:37:53 PM PT</t>
+          <t>2026-07-11 08:39:53 PM PT</t>
         </is>
       </c>
       <c r="C266" t="n">
@@ -31191,7 +31191,7 @@
       </c>
       <c r="B267" t="inlineStr">
         <is>
-          <t>2026-07-11 08:37:53 PM PT</t>
+          <t>2026-07-11 08:39:53 PM PT</t>
         </is>
       </c>
       <c r="C267" t="n">
@@ -31305,7 +31305,7 @@
       </c>
       <c r="B268" t="inlineStr">
         <is>
-          <t>2026-07-11 08:37:53 PM PT</t>
+          <t>2026-07-11 08:39:53 PM PT</t>
         </is>
       </c>
       <c r="C268" t="n">
@@ -31419,7 +31419,7 @@
       </c>
       <c r="B269" t="inlineStr">
         <is>
-          <t>2026-07-11 08:37:54 PM PT</t>
+          <t>2026-07-11 08:39:53 PM PT</t>
         </is>
       </c>
       <c r="C269" t="n">
@@ -31533,7 +31533,7 @@
       </c>
       <c r="B270" t="inlineStr">
         <is>
-          <t>2026-07-11 08:37:54 PM PT</t>
+          <t>2026-07-11 08:39:53 PM PT</t>
         </is>
       </c>
       <c r="C270" t="n">
@@ -31647,7 +31647,7 @@
       </c>
       <c r="B271" t="inlineStr">
         <is>
-          <t>2026-07-11 08:37:54 PM PT</t>
+          <t>2026-07-11 08:39:53 PM PT</t>
         </is>
       </c>
       <c r="C271" t="n">
@@ -31761,7 +31761,7 @@
       </c>
       <c r="B272" t="inlineStr">
         <is>
-          <t>2026-07-11 08:37:54 PM PT</t>
+          <t>2026-07-11 08:39:53 PM PT</t>
         </is>
       </c>
       <c r="C272" t="n">
@@ -31875,7 +31875,7 @@
       </c>
       <c r="B273" t="inlineStr">
         <is>
-          <t>2026-07-11 08:37:54 PM PT</t>
+          <t>2026-07-11 08:39:53 PM PT</t>
         </is>
       </c>
       <c r="C273" t="n">
@@ -31989,7 +31989,7 @@
       </c>
       <c r="B274" t="inlineStr">
         <is>
-          <t>2026-07-11 08:37:54 PM PT</t>
+          <t>2026-07-11 08:39:53 PM PT</t>
         </is>
       </c>
       <c r="C274" t="n">
@@ -32103,7 +32103,7 @@
       </c>
       <c r="B275" t="inlineStr">
         <is>
-          <t>2026-07-11 08:37:54 PM PT</t>
+          <t>2026-07-11 08:39:53 PM PT</t>
         </is>
       </c>
       <c r="C275" t="n">
@@ -32217,7 +32217,7 @@
       </c>
       <c r="B276" t="inlineStr">
         <is>
-          <t>2026-07-11 08:37:53 PM PT</t>
+          <t>2026-07-11 08:39:53 PM PT</t>
         </is>
       </c>
       <c r="C276" t="n">
@@ -32331,7 +32331,7 @@
       </c>
       <c r="B277" t="inlineStr">
         <is>
-          <t>2026-07-11 08:37:53 PM PT</t>
+          <t>2026-07-11 08:39:53 PM PT</t>
         </is>
       </c>
       <c r="C277" t="n">
@@ -32445,7 +32445,7 @@
       </c>
       <c r="B278" t="inlineStr">
         <is>
-          <t>2026-07-11 08:37:53 PM PT</t>
+          <t>2026-07-11 08:39:53 PM PT</t>
         </is>
       </c>
       <c r="C278" t="n">
@@ -32559,7 +32559,7 @@
       </c>
       <c r="B279" t="inlineStr">
         <is>
-          <t>2026-07-11 08:37:54 PM PT</t>
+          <t>2026-07-11 08:39:54 PM PT</t>
         </is>
       </c>
       <c r="C279" t="n">
@@ -32572,7 +32572,7 @@
       </c>
       <c r="E279" t="inlineStr">
         <is>
-          <t>Bottom 8 | 0 out</t>
+          <t>Bottom 8 | 1 out</t>
         </is>
       </c>
       <c r="F279" t="n">
@@ -32584,13 +32584,13 @@
         </is>
       </c>
       <c r="H279" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I279" t="n">
         <v>0</v>
       </c>
       <c r="J279" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K279" t="inlineStr">
         <is>
@@ -32609,27 +32609,27 @@
       </c>
       <c r="N279" t="inlineStr">
         <is>
-          <t>Eliezer Alfonzo</t>
+          <t>Alex Call</t>
         </is>
       </c>
       <c r="O279" t="n">
-        <v>672613</v>
+        <v>669743</v>
       </c>
       <c r="P279" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>PH</t>
         </is>
       </c>
       <c r="Q279" t="inlineStr">
         <is>
-          <t>3 (Sub)</t>
+          <t>1 (Sub)</t>
         </is>
       </c>
       <c r="R279" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S279" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T279" t="n">
         <v>0</v>
@@ -32682,7 +32682,7 @@
       </c>
       <c r="B280" t="inlineStr">
         <is>
-          <t>2026-07-11 08:37:54 PM PT</t>
+          <t>2026-07-11 08:39:54 PM PT</t>
         </is>
       </c>
       <c r="C280" t="n">
@@ -32695,7 +32695,7 @@
       </c>
       <c r="E280" t="inlineStr">
         <is>
-          <t>Bottom 8 | 0 out</t>
+          <t>Bottom 8 | 1 out</t>
         </is>
       </c>
       <c r="F280" t="n">
@@ -32707,13 +32707,13 @@
         </is>
       </c>
       <c r="H280" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I280" t="n">
         <v>0</v>
       </c>
       <c r="J280" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K280" t="inlineStr">
         <is>
@@ -32745,7 +32745,7 @@
       </c>
       <c r="Q280" t="inlineStr">
         <is>
-          <t>4 (Sub)</t>
+          <t>3 (Sub)</t>
         </is>
       </c>
       <c r="R280" t="n">
@@ -32805,7 +32805,7 @@
       </c>
       <c r="B281" t="inlineStr">
         <is>
-          <t>2026-07-11 08:37:54 PM PT</t>
+          <t>2026-07-11 08:39:54 PM PT</t>
         </is>
       </c>
       <c r="C281" t="n">
@@ -32818,7 +32818,7 @@
       </c>
       <c r="E281" t="inlineStr">
         <is>
-          <t>Bottom 8 | 0 out</t>
+          <t>Bottom 8 | 1 out</t>
         </is>
       </c>
       <c r="F281" t="n">
@@ -32830,13 +32830,13 @@
         </is>
       </c>
       <c r="H281" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I281" t="n">
         <v>0</v>
       </c>
       <c r="J281" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K281" t="inlineStr">
         <is>
@@ -32855,27 +32855,27 @@
       </c>
       <c r="N281" t="inlineStr">
         <is>
-          <t>Max Muncy</t>
+          <t>Eliezer Alfonzo</t>
         </is>
       </c>
       <c r="O281" t="n">
-        <v>571970</v>
+        <v>672613</v>
       </c>
       <c r="P281" t="inlineStr">
         <is>
-          <t>3B</t>
+          <t>C</t>
         </is>
       </c>
       <c r="Q281" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>4 (Sub)</t>
         </is>
       </c>
       <c r="R281" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="S281" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="T281" t="n">
         <v>0</v>
@@ -32908,7 +32908,7 @@
         <v>0</v>
       </c>
       <c r="AD281" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AE281" s="4" t="n">
         <v>0</v>
@@ -32928,7 +32928,7 @@
       </c>
       <c r="B282" t="inlineStr">
         <is>
-          <t>2026-07-11 08:37:54 PM PT</t>
+          <t>2026-07-11 08:39:54 PM PT</t>
         </is>
       </c>
       <c r="C282" t="n">
@@ -32941,7 +32941,7 @@
       </c>
       <c r="E282" t="inlineStr">
         <is>
-          <t>Bottom 8 | 0 out</t>
+          <t>Bottom 8 | 1 out</t>
         </is>
       </c>
       <c r="F282" t="n">
@@ -32953,13 +32953,13 @@
         </is>
       </c>
       <c r="H282" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I282" t="n">
         <v>0</v>
       </c>
       <c r="J282" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K282" t="inlineStr">
         <is>
@@ -32978,20 +32978,20 @@
       </c>
       <c r="N282" t="inlineStr">
         <is>
-          <t>Kyle Tucker</t>
+          <t>Max Muncy</t>
         </is>
       </c>
       <c r="O282" t="n">
-        <v>663656</v>
+        <v>571970</v>
       </c>
       <c r="P282" t="inlineStr">
         <is>
-          <t>RF</t>
+          <t>3B</t>
         </is>
       </c>
       <c r="Q282" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>5</t>
         </is>
       </c>
       <c r="R282" t="n">
@@ -33031,7 +33031,7 @@
         <v>0</v>
       </c>
       <c r="AD282" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AE282" s="4" t="n">
         <v>0</v>
@@ -33051,7 +33051,7 @@
       </c>
       <c r="B283" t="inlineStr">
         <is>
-          <t>2026-07-11 08:37:54 PM PT</t>
+          <t>2026-07-11 08:39:54 PM PT</t>
         </is>
       </c>
       <c r="C283" t="n">
@@ -33064,7 +33064,7 @@
       </c>
       <c r="E283" t="inlineStr">
         <is>
-          <t>Bottom 8 | 0 out</t>
+          <t>Bottom 8 | 1 out</t>
         </is>
       </c>
       <c r="F283" t="n">
@@ -33076,13 +33076,13 @@
         </is>
       </c>
       <c r="H283" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I283" t="n">
         <v>0</v>
       </c>
       <c r="J283" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K283" t="inlineStr">
         <is>
@@ -33101,20 +33101,20 @@
       </c>
       <c r="N283" t="inlineStr">
         <is>
-          <t>Teoscar Hernández</t>
+          <t>Kyle Tucker</t>
         </is>
       </c>
       <c r="O283" t="n">
-        <v>606192</v>
+        <v>663656</v>
       </c>
       <c r="P283" t="inlineStr">
         <is>
-          <t>LF</t>
+          <t>RF</t>
         </is>
       </c>
       <c r="Q283" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>6</t>
         </is>
       </c>
       <c r="R283" t="n">
@@ -33154,7 +33154,7 @@
         <v>0</v>
       </c>
       <c r="AD283" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AE283" s="4" t="n">
         <v>0</v>
@@ -33174,7 +33174,7 @@
       </c>
       <c r="B284" t="inlineStr">
         <is>
-          <t>2026-07-11 08:37:54 PM PT</t>
+          <t>2026-07-11 08:39:54 PM PT</t>
         </is>
       </c>
       <c r="C284" t="n">
@@ -33187,7 +33187,7 @@
       </c>
       <c r="E284" t="inlineStr">
         <is>
-          <t>Bottom 8 | 0 out</t>
+          <t>Bottom 8 | 1 out</t>
         </is>
       </c>
       <c r="F284" t="n">
@@ -33199,13 +33199,13 @@
         </is>
       </c>
       <c r="H284" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I284" t="n">
         <v>0</v>
       </c>
       <c r="J284" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K284" t="inlineStr">
         <is>
@@ -33224,20 +33224,20 @@
       </c>
       <c r="N284" t="inlineStr">
         <is>
-          <t>Dalton Rushing</t>
+          <t>Teoscar Hernández</t>
         </is>
       </c>
       <c r="O284" t="n">
-        <v>687221</v>
+        <v>606192</v>
       </c>
       <c r="P284" t="inlineStr">
         <is>
-          <t>1B</t>
+          <t>LF</t>
         </is>
       </c>
       <c r="Q284" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>7</t>
         </is>
       </c>
       <c r="R284" t="n">
@@ -33297,7 +33297,7 @@
       </c>
       <c r="B285" t="inlineStr">
         <is>
-          <t>2026-07-11 08:37:54 PM PT</t>
+          <t>2026-07-11 08:39:54 PM PT</t>
         </is>
       </c>
       <c r="C285" t="n">
@@ -33310,7 +33310,7 @@
       </c>
       <c r="E285" t="inlineStr">
         <is>
-          <t>Bottom 8 | 0 out</t>
+          <t>Bottom 8 | 1 out</t>
         </is>
       </c>
       <c r="F285" t="n">
@@ -33322,13 +33322,13 @@
         </is>
       </c>
       <c r="H285" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I285" t="n">
         <v>0</v>
       </c>
       <c r="J285" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K285" t="inlineStr">
         <is>
@@ -33347,27 +33347,27 @@
       </c>
       <c r="N285" t="inlineStr">
         <is>
-          <t>Miguel Rojas</t>
+          <t>Dalton Rushing</t>
         </is>
       </c>
       <c r="O285" t="n">
-        <v>500743</v>
+        <v>687221</v>
       </c>
       <c r="P285" t="inlineStr">
         <is>
-          <t>2B</t>
+          <t>1B</t>
         </is>
       </c>
       <c r="Q285" t="inlineStr">
         <is>
-          <t>9 (Sub)</t>
+          <t>8</t>
         </is>
       </c>
       <c r="R285" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="S285" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="T285" t="n">
         <v>0</v>
@@ -33400,7 +33400,7 @@
         <v>0</v>
       </c>
       <c r="AD285" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AE285" s="4" t="n">
         <v>0</v>
@@ -33420,30 +33420,39 @@
       </c>
       <c r="B286" t="inlineStr">
         <is>
-          <t>2026-07-11 08:37:53 PM PT</t>
+          <t>2026-07-11 08:39:54 PM PT</t>
         </is>
       </c>
       <c r="C286" t="n">
-        <v>823844</v>
+        <v>823926</v>
       </c>
       <c r="D286" t="inlineStr">
         <is>
-          <t>1:10 PM PT</t>
+          <t>6:10 PM PT</t>
         </is>
       </c>
       <c r="E286" t="inlineStr">
         <is>
-          <t>Final</t>
+          <t>Bottom 8 | 1 out</t>
         </is>
       </c>
       <c r="F286" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="G286" t="inlineStr">
         <is>
           <t>Bottom</t>
         </is>
       </c>
+      <c r="H286" t="n">
+        <v>1</v>
+      </c>
+      <c r="I286" t="n">
+        <v>0</v>
+      </c>
+      <c r="J286" t="n">
+        <v>1</v>
+      </c>
       <c r="K286" t="inlineStr">
         <is>
           <t>Home</t>
@@ -33451,37 +33460,37 @@
       </c>
       <c r="L286" t="inlineStr">
         <is>
-          <t>MIA</t>
+          <t>LAD</t>
         </is>
       </c>
       <c r="M286" t="inlineStr">
         <is>
-          <t>CLE</t>
+          <t>ARI</t>
         </is>
       </c>
       <c r="N286" t="inlineStr">
         <is>
-          <t>Javier Sanoja</t>
+          <t>Miguel Rojas</t>
         </is>
       </c>
       <c r="O286" t="n">
-        <v>691594</v>
+        <v>500743</v>
       </c>
       <c r="P286" t="inlineStr">
         <is>
-          <t>3B</t>
+          <t>2B</t>
         </is>
       </c>
       <c r="Q286" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>9 (Sub)</t>
         </is>
       </c>
       <c r="R286" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="S286" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="T286" t="n">
         <v>0</v>
@@ -33520,10 +33529,10 @@
         <v>0</v>
       </c>
       <c r="AF286" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AG286" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
     </row>
     <row r="287">
@@ -33534,15 +33543,15 @@
       </c>
       <c r="B287" t="inlineStr">
         <is>
-          <t>2026-07-11 08:37:52 PM PT</t>
+          <t>2026-07-11 08:39:53 PM PT</t>
         </is>
       </c>
       <c r="C287" t="n">
-        <v>823357</v>
+        <v>823844</v>
       </c>
       <c r="D287" t="inlineStr">
         <is>
-          <t>9:05 AM PT</t>
+          <t>1:10 PM PT</t>
         </is>
       </c>
       <c r="E287" t="inlineStr">
@@ -33555,47 +33564,47 @@
       </c>
       <c r="G287" t="inlineStr">
         <is>
-          <t>Top</t>
+          <t>Bottom</t>
         </is>
       </c>
       <c r="K287" t="inlineStr">
         <is>
-          <t>Away</t>
+          <t>Home</t>
         </is>
       </c>
       <c r="L287" t="inlineStr">
         <is>
-          <t>MIL</t>
+          <t>MIA</t>
         </is>
       </c>
       <c r="M287" t="inlineStr">
         <is>
-          <t>PIT</t>
+          <t>CLE</t>
         </is>
       </c>
       <c r="N287" t="inlineStr">
         <is>
-          <t>Jackson Chourio</t>
+          <t>Javier Sanoja</t>
         </is>
       </c>
       <c r="O287" t="n">
-        <v>694192</v>
+        <v>691594</v>
       </c>
       <c r="P287" t="inlineStr">
         <is>
-          <t>PH</t>
+          <t>3B</t>
         </is>
       </c>
       <c r="Q287" t="inlineStr">
         <is>
-          <t>2 (Sub)</t>
+          <t>9</t>
         </is>
       </c>
       <c r="R287" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="S287" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="T287" t="n">
         <v>0</v>
@@ -33634,10 +33643,10 @@
         <v>0</v>
       </c>
       <c r="AF287" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="AG287" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
     </row>
     <row r="288">
@@ -33648,15 +33657,15 @@
       </c>
       <c r="B288" t="inlineStr">
         <is>
-          <t>2026-07-11 08:37:52 PM PT</t>
+          <t>2026-07-11 08:39:52 PM PT</t>
         </is>
       </c>
       <c r="C288" t="n">
-        <v>823356</v>
+        <v>823357</v>
       </c>
       <c r="D288" t="inlineStr">
         <is>
-          <t>1:05 PM PT</t>
+          <t>9:05 AM PT</t>
         </is>
       </c>
       <c r="E288" t="inlineStr">
@@ -33689,11 +33698,11 @@
       </c>
       <c r="N288" t="inlineStr">
         <is>
-          <t>William Contreras</t>
+          <t>Jackson Chourio</t>
         </is>
       </c>
       <c r="O288" t="n">
-        <v>661388</v>
+        <v>694192</v>
       </c>
       <c r="P288" t="inlineStr">
         <is>
@@ -33702,7 +33711,7 @@
       </c>
       <c r="Q288" t="inlineStr">
         <is>
-          <t>4 (Sub)</t>
+          <t>2 (Sub)</t>
         </is>
       </c>
       <c r="R288" t="n">
@@ -33742,16 +33751,16 @@
         <v>0</v>
       </c>
       <c r="AD288" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AE288" s="4" t="n">
         <v>0</v>
       </c>
       <c r="AF288" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="AG288" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
     </row>
     <row r="289">
@@ -33762,15 +33771,15 @@
       </c>
       <c r="B289" t="inlineStr">
         <is>
-          <t>2026-07-11 08:37:52 PM PT</t>
+          <t>2026-07-11 08:39:53 PM PT</t>
         </is>
       </c>
       <c r="C289" t="n">
-        <v>823357</v>
+        <v>823356</v>
       </c>
       <c r="D289" t="inlineStr">
         <is>
-          <t>9:05 AM PT</t>
+          <t>1:05 PM PT</t>
         </is>
       </c>
       <c r="E289" t="inlineStr">
@@ -33803,11 +33812,11 @@
       </c>
       <c r="N289" t="inlineStr">
         <is>
-          <t>Andrew Vaughn</t>
+          <t>William Contreras</t>
         </is>
       </c>
       <c r="O289" t="n">
-        <v>683734</v>
+        <v>661388</v>
       </c>
       <c r="P289" t="inlineStr">
         <is>
@@ -33816,7 +33825,7 @@
       </c>
       <c r="Q289" t="inlineStr">
         <is>
-          <t>5 (Sub)</t>
+          <t>4 (Sub)</t>
         </is>
       </c>
       <c r="R289" t="n">
@@ -33856,16 +33865,16 @@
         <v>0</v>
       </c>
       <c r="AD289" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AE289" s="4" t="n">
         <v>0</v>
       </c>
       <c r="AF289" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="AG289" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
     </row>
     <row r="290">
@@ -33876,15 +33885,15 @@
       </c>
       <c r="B290" t="inlineStr">
         <is>
-          <t>2026-07-11 08:37:52 PM PT</t>
+          <t>2026-07-11 08:39:52 PM PT</t>
         </is>
       </c>
       <c r="C290" t="n">
-        <v>823356</v>
+        <v>823357</v>
       </c>
       <c r="D290" t="inlineStr">
         <is>
-          <t>1:05 PM PT</t>
+          <t>9:05 AM PT</t>
         </is>
       </c>
       <c r="E290" t="inlineStr">
@@ -33917,27 +33926,27 @@
       </c>
       <c r="N290" t="inlineStr">
         <is>
-          <t>Cooper Pratt</t>
+          <t>Andrew Vaughn</t>
         </is>
       </c>
       <c r="O290" t="n">
-        <v>806198</v>
+        <v>683734</v>
       </c>
       <c r="P290" t="inlineStr">
         <is>
-          <t>SS</t>
+          <t>PH</t>
         </is>
       </c>
       <c r="Q290" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>5 (Sub)</t>
         </is>
       </c>
       <c r="R290" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="S290" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="T290" t="n">
         <v>0</v>
@@ -33976,10 +33985,10 @@
         <v>0</v>
       </c>
       <c r="AF290" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="AG290" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
     </row>
     <row r="291">
@@ -33990,7 +33999,7 @@
       </c>
       <c r="B291" t="inlineStr">
         <is>
-          <t>2026-07-11 08:37:52 PM PT</t>
+          <t>2026-07-11 08:39:53 PM PT</t>
         </is>
       </c>
       <c r="C291" t="n">
@@ -34031,27 +34040,27 @@
       </c>
       <c r="N291" t="inlineStr">
         <is>
-          <t>Andrew Vaughn</t>
+          <t>Cooper Pratt</t>
         </is>
       </c>
       <c r="O291" t="n">
-        <v>683734</v>
+        <v>806198</v>
       </c>
       <c r="P291" t="inlineStr">
         <is>
-          <t>3B</t>
+          <t>SS</t>
         </is>
       </c>
       <c r="Q291" t="inlineStr">
         <is>
-          <t>9 (Sub)</t>
+          <t>8</t>
         </is>
       </c>
       <c r="R291" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="S291" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="T291" t="n">
         <v>0</v>
@@ -34104,15 +34113,15 @@
       </c>
       <c r="B292" t="inlineStr">
         <is>
-          <t>2026-07-11 08:37:52 PM PT</t>
+          <t>2026-07-11 08:39:53 PM PT</t>
         </is>
       </c>
       <c r="C292" t="n">
-        <v>823357</v>
+        <v>823356</v>
       </c>
       <c r="D292" t="inlineStr">
         <is>
-          <t>9:05 AM PT</t>
+          <t>1:05 PM PT</t>
         </is>
       </c>
       <c r="E292" t="inlineStr">
@@ -34145,11 +34154,11 @@
       </c>
       <c r="N292" t="inlineStr">
         <is>
-          <t>Joey Ortiz</t>
+          <t>Andrew Vaughn</t>
         </is>
       </c>
       <c r="O292" t="n">
-        <v>687401</v>
+        <v>683734</v>
       </c>
       <c r="P292" t="inlineStr">
         <is>
@@ -34158,14 +34167,14 @@
       </c>
       <c r="Q292" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>9 (Sub)</t>
         </is>
       </c>
       <c r="R292" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="S292" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="T292" t="n">
         <v>0</v>
@@ -34204,10 +34213,10 @@
         <v>0</v>
       </c>
       <c r="AF292" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="AG292" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
     </row>
     <row r="293">
@@ -34218,15 +34227,15 @@
       </c>
       <c r="B293" t="inlineStr">
         <is>
-          <t>2026-07-11 08:37:53 PM PT</t>
+          <t>2026-07-11 08:39:52 PM PT</t>
         </is>
       </c>
       <c r="C293" t="n">
-        <v>823682</v>
+        <v>823357</v>
       </c>
       <c r="D293" t="inlineStr">
         <is>
-          <t>11:10 AM PT</t>
+          <t>9:05 AM PT</t>
         </is>
       </c>
       <c r="E293" t="inlineStr">
@@ -34244,42 +34253,42 @@
       </c>
       <c r="K293" t="inlineStr">
         <is>
-          <t>Home</t>
+          <t>Away</t>
         </is>
       </c>
       <c r="L293" t="inlineStr">
         <is>
-          <t>MIN</t>
+          <t>MIL</t>
         </is>
       </c>
       <c r="M293" t="inlineStr">
         <is>
-          <t>LAA</t>
+          <t>PIT</t>
         </is>
       </c>
       <c r="N293" t="inlineStr">
         <is>
-          <t>Ryan Kreidler</t>
+          <t>Joey Ortiz</t>
         </is>
       </c>
       <c r="O293" t="n">
-        <v>668952</v>
+        <v>687401</v>
       </c>
       <c r="P293" t="inlineStr">
         <is>
-          <t>SS</t>
+          <t>3B</t>
         </is>
       </c>
       <c r="Q293" t="inlineStr">
         <is>
-          <t>8 (Sub)</t>
+          <t>9</t>
         </is>
       </c>
       <c r="R293" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="S293" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="T293" t="n">
         <v>0</v>
@@ -34318,7 +34327,7 @@
         <v>0</v>
       </c>
       <c r="AF293" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AG293" t="n">
         <v>9</v>
@@ -34332,15 +34341,15 @@
       </c>
       <c r="B294" t="inlineStr">
         <is>
-          <t>2026-07-11 08:37:53 PM PT</t>
+          <t>2026-07-11 08:39:53 PM PT</t>
         </is>
       </c>
       <c r="C294" t="n">
-        <v>823603</v>
+        <v>823682</v>
       </c>
       <c r="D294" t="inlineStr">
         <is>
-          <t>1:10 PM PT</t>
+          <t>11:10 AM PT</t>
         </is>
       </c>
       <c r="E294" t="inlineStr">
@@ -34353,7 +34362,7 @@
       </c>
       <c r="G294" t="inlineStr">
         <is>
-          <t>Bottom</t>
+          <t>Top</t>
         </is>
       </c>
       <c r="K294" t="inlineStr">
@@ -34363,37 +34372,37 @@
       </c>
       <c r="L294" t="inlineStr">
         <is>
-          <t>NYM</t>
+          <t>MIN</t>
         </is>
       </c>
       <c r="M294" t="inlineStr">
         <is>
-          <t>BOS</t>
+          <t>LAA</t>
         </is>
       </c>
       <c r="N294" t="inlineStr">
         <is>
-          <t>A.J. Ewing</t>
+          <t>Ryan Kreidler</t>
         </is>
       </c>
       <c r="O294" t="n">
-        <v>805999</v>
+        <v>668952</v>
       </c>
       <c r="P294" t="inlineStr">
         <is>
-          <t>2B</t>
+          <t>SS</t>
         </is>
       </c>
       <c r="Q294" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>8 (Sub)</t>
         </is>
       </c>
       <c r="R294" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="S294" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="T294" t="n">
         <v>0</v>
@@ -34426,16 +34435,16 @@
         <v>0</v>
       </c>
       <c r="AD294" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AE294" s="4" t="n">
         <v>0</v>
       </c>
       <c r="AF294" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="AG294" t="n">
-        <v>3</v>
+        <v>9</v>
       </c>
     </row>
     <row r="295">
@@ -34446,7 +34455,7 @@
       </c>
       <c r="B295" t="inlineStr">
         <is>
-          <t>2026-07-11 08:37:53 PM PT</t>
+          <t>2026-07-11 08:39:53 PM PT</t>
         </is>
       </c>
       <c r="C295" t="n">
@@ -34487,27 +34496,27 @@
       </c>
       <c r="N295" t="inlineStr">
         <is>
-          <t>Tyrone Taylor</t>
+          <t>A.J. Ewing</t>
         </is>
       </c>
       <c r="O295" t="n">
-        <v>621438</v>
+        <v>805999</v>
       </c>
       <c r="P295" t="inlineStr">
         <is>
-          <t>CF</t>
+          <t>2B</t>
         </is>
       </c>
       <c r="Q295" t="inlineStr">
         <is>
-          <t>9 (Sub)</t>
+          <t>1</t>
         </is>
       </c>
       <c r="R295" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="S295" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="T295" t="n">
         <v>0</v>
@@ -34540,7 +34549,7 @@
         <v>0</v>
       </c>
       <c r="AD295" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AE295" s="4" t="n">
         <v>0</v>
@@ -34560,7 +34569,7 @@
       </c>
       <c r="B296" t="inlineStr">
         <is>
-          <t>2026-07-11 08:37:53 PM PT</t>
+          <t>2026-07-11 08:39:53 PM PT</t>
         </is>
       </c>
       <c r="C296" t="n">
@@ -34601,27 +34610,27 @@
       </c>
       <c r="N296" t="inlineStr">
         <is>
-          <t>Zack Short</t>
+          <t>Tyrone Taylor</t>
         </is>
       </c>
       <c r="O296" t="n">
-        <v>670097</v>
+        <v>621438</v>
       </c>
       <c r="P296" t="inlineStr">
         <is>
-          <t>2B</t>
+          <t>CF</t>
         </is>
       </c>
       <c r="Q296" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>9 (Sub)</t>
         </is>
       </c>
       <c r="R296" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="S296" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="T296" t="n">
         <v>0</v>
@@ -34674,15 +34683,15 @@
       </c>
       <c r="B297" t="inlineStr">
         <is>
-          <t>2026-07-11 08:37:53 PM PT</t>
+          <t>2026-07-11 08:39:53 PM PT</t>
         </is>
       </c>
       <c r="C297" t="n">
-        <v>822711</v>
+        <v>823603</v>
       </c>
       <c r="D297" t="inlineStr">
         <is>
-          <t>1:05 PM PT</t>
+          <t>1:10 PM PT</t>
         </is>
       </c>
       <c r="E297" t="inlineStr">
@@ -34700,26 +34709,26 @@
       </c>
       <c r="K297" t="inlineStr">
         <is>
-          <t>Away</t>
+          <t>Home</t>
         </is>
       </c>
       <c r="L297" t="inlineStr">
         <is>
-          <t>NYY</t>
+          <t>NYM</t>
         </is>
       </c>
       <c r="M297" t="inlineStr">
         <is>
-          <t>WSH</t>
+          <t>BOS</t>
         </is>
       </c>
       <c r="N297" t="inlineStr">
         <is>
-          <t>Jazz Chisholm Jr.</t>
+          <t>Zack Short</t>
         </is>
       </c>
       <c r="O297" t="n">
-        <v>665862</v>
+        <v>670097</v>
       </c>
       <c r="P297" t="inlineStr">
         <is>
@@ -34728,14 +34737,14 @@
       </c>
       <c r="Q297" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>9</t>
         </is>
       </c>
       <c r="R297" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="S297" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="T297" t="n">
         <v>0</v>
@@ -34768,16 +34777,16 @@
         <v>0</v>
       </c>
       <c r="AD297" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE297" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF297" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG297" t="n">
         <v>3</v>
-      </c>
-      <c r="AE297" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="AF297" t="n">
-        <v>4</v>
-      </c>
-      <c r="AG297" t="n">
-        <v>9</v>
       </c>
     </row>
     <row r="298">
@@ -34788,7 +34797,7 @@
       </c>
       <c r="B298" t="inlineStr">
         <is>
-          <t>2026-07-11 08:37:53 PM PT</t>
+          <t>2026-07-11 08:39:53 PM PT</t>
         </is>
       </c>
       <c r="C298" t="n">
@@ -34829,27 +34838,27 @@
       </c>
       <c r="N298" t="inlineStr">
         <is>
-          <t>Ali Sánchez</t>
+          <t>Jazz Chisholm Jr.</t>
         </is>
       </c>
       <c r="O298" t="n">
-        <v>645305</v>
+        <v>665862</v>
       </c>
       <c r="P298" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>2B</t>
         </is>
       </c>
       <c r="Q298" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>7</t>
         </is>
       </c>
       <c r="R298" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="S298" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="T298" t="n">
         <v>0</v>
@@ -34882,7 +34891,7 @@
         <v>0</v>
       </c>
       <c r="AD298" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="AE298" s="4" t="n">
         <v>0</v>
@@ -34902,7 +34911,7 @@
       </c>
       <c r="B299" t="inlineStr">
         <is>
-          <t>2026-07-11 08:37:53 PM PT</t>
+          <t>2026-07-11 08:39:53 PM PT</t>
         </is>
       </c>
       <c r="C299" t="n">
@@ -34943,11 +34952,11 @@
       </c>
       <c r="N299" t="inlineStr">
         <is>
-          <t>Austin Wells</t>
+          <t>Ali Sánchez</t>
         </is>
       </c>
       <c r="O299" t="n">
-        <v>669224</v>
+        <v>645305</v>
       </c>
       <c r="P299" t="inlineStr">
         <is>
@@ -34956,7 +34965,7 @@
       </c>
       <c r="Q299" t="inlineStr">
         <is>
-          <t>9 (Sub)</t>
+          <t>9</t>
         </is>
       </c>
       <c r="R299" t="n">
@@ -35016,15 +35025,15 @@
       </c>
       <c r="B300" t="inlineStr">
         <is>
-          <t>2026-07-11 08:37:53 PM PT</t>
+          <t>2026-07-11 08:39:53 PM PT</t>
         </is>
       </c>
       <c r="C300" t="n">
-        <v>824249</v>
+        <v>822711</v>
       </c>
       <c r="D300" t="inlineStr">
         <is>
-          <t>3:10 PM PT</t>
+          <t>1:05 PM PT</t>
         </is>
       </c>
       <c r="E300" t="inlineStr">
@@ -35047,37 +35056,37 @@
       </c>
       <c r="L300" t="inlineStr">
         <is>
-          <t>PHI</t>
+          <t>NYY</t>
         </is>
       </c>
       <c r="M300" t="inlineStr">
         <is>
-          <t>DET</t>
+          <t>WSH</t>
         </is>
       </c>
       <c r="N300" t="inlineStr">
         <is>
-          <t>Alec Bohm</t>
+          <t>Austin Wells</t>
         </is>
       </c>
       <c r="O300" t="n">
-        <v>664761</v>
+        <v>669224</v>
       </c>
       <c r="P300" t="inlineStr">
         <is>
-          <t>3B</t>
+          <t>C</t>
         </is>
       </c>
       <c r="Q300" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>9 (Sub)</t>
         </is>
       </c>
       <c r="R300" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="S300" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="T300" t="n">
         <v>0</v>
@@ -35110,7 +35119,7 @@
         <v>0</v>
       </c>
       <c r="AD300" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="AE300" s="4" t="n">
         <v>0</v>
@@ -35119,7 +35128,7 @@
         <v>4</v>
       </c>
       <c r="AG300" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
     </row>
     <row r="301">
@@ -35130,7 +35139,7 @@
       </c>
       <c r="B301" t="inlineStr">
         <is>
-          <t>2026-07-11 08:37:53 PM PT</t>
+          <t>2026-07-11 08:39:53 PM PT</t>
         </is>
       </c>
       <c r="C301" t="n">
@@ -35171,20 +35180,20 @@
       </c>
       <c r="N301" t="inlineStr">
         <is>
-          <t>Gabriel Rincones Jr.</t>
+          <t>Alec Bohm</t>
         </is>
       </c>
       <c r="O301" t="n">
-        <v>687282</v>
+        <v>664761</v>
       </c>
       <c r="P301" t="inlineStr">
         <is>
-          <t>RF</t>
+          <t>3B</t>
         </is>
       </c>
       <c r="Q301" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>5</t>
         </is>
       </c>
       <c r="R301" t="n">
@@ -35224,7 +35233,7 @@
         <v>0</v>
       </c>
       <c r="AD301" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="AE301" s="4" t="n">
         <v>0</v>
@@ -35244,15 +35253,15 @@
       </c>
       <c r="B302" t="inlineStr">
         <is>
-          <t>2026-07-11 08:37:52 PM PT</t>
+          <t>2026-07-11 08:39:53 PM PT</t>
         </is>
       </c>
       <c r="C302" t="n">
-        <v>823356</v>
+        <v>824249</v>
       </c>
       <c r="D302" t="inlineStr">
         <is>
-          <t>1:05 PM PT</t>
+          <t>3:10 PM PT</t>
         </is>
       </c>
       <c r="E302" t="inlineStr">
@@ -35265,40 +35274,40 @@
       </c>
       <c r="G302" t="inlineStr">
         <is>
-          <t>Top</t>
+          <t>Bottom</t>
         </is>
       </c>
       <c r="K302" t="inlineStr">
         <is>
-          <t>Home</t>
+          <t>Away</t>
         </is>
       </c>
       <c r="L302" t="inlineStr">
         <is>
-          <t>PIT</t>
+          <t>PHI</t>
         </is>
       </c>
       <c r="M302" t="inlineStr">
         <is>
-          <t>MIL</t>
+          <t>DET</t>
         </is>
       </c>
       <c r="N302" t="inlineStr">
         <is>
-          <t>Nick Gonzales</t>
+          <t>Gabriel Rincones Jr.</t>
         </is>
       </c>
       <c r="O302" t="n">
-        <v>693304</v>
+        <v>687282</v>
       </c>
       <c r="P302" t="inlineStr">
         <is>
-          <t>3B</t>
+          <t>RF</t>
         </is>
       </c>
       <c r="Q302" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>8</t>
         </is>
       </c>
       <c r="R302" t="n">
@@ -35338,13 +35347,13 @@
         <v>0</v>
       </c>
       <c r="AD302" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AE302" s="4" t="n">
         <v>0</v>
       </c>
       <c r="AF302" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="AG302" t="n">
         <v>7</v>
@@ -35358,7 +35367,7 @@
       </c>
       <c r="B303" t="inlineStr">
         <is>
-          <t>2026-07-11 08:37:52 PM PT</t>
+          <t>2026-07-11 08:39:53 PM PT</t>
         </is>
       </c>
       <c r="C303" t="n">
@@ -35399,27 +35408,27 @@
       </c>
       <c r="N303" t="inlineStr">
         <is>
-          <t>Jake Mangum</t>
+          <t>Nick Gonzales</t>
         </is>
       </c>
       <c r="O303" t="n">
-        <v>663968</v>
+        <v>693304</v>
       </c>
       <c r="P303" t="inlineStr">
         <is>
-          <t>LF</t>
+          <t>3B</t>
         </is>
       </c>
       <c r="Q303" t="inlineStr">
         <is>
-          <t>4 (Sub)</t>
+          <t>1</t>
         </is>
       </c>
       <c r="R303" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="S303" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="T303" t="n">
         <v>0</v>
@@ -35472,7 +35481,7 @@
       </c>
       <c r="B304" t="inlineStr">
         <is>
-          <t>2026-07-11 08:37:52 PM PT</t>
+          <t>2026-07-11 08:39:53 PM PT</t>
         </is>
       </c>
       <c r="C304" t="n">
@@ -35513,27 +35522,27 @@
       </c>
       <c r="N304" t="inlineStr">
         <is>
-          <t>Marcell Ozuna</t>
+          <t>Jake Mangum</t>
         </is>
       </c>
       <c r="O304" t="n">
-        <v>542303</v>
+        <v>663968</v>
       </c>
       <c r="P304" t="inlineStr">
         <is>
-          <t>DH</t>
+          <t>LF</t>
         </is>
       </c>
       <c r="Q304" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>4 (Sub)</t>
         </is>
       </c>
       <c r="R304" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="S304" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="T304" t="n">
         <v>0</v>
@@ -35566,7 +35575,7 @@
         <v>0</v>
       </c>
       <c r="AD304" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AE304" s="4" t="n">
         <v>0</v>
@@ -35586,15 +35595,15 @@
       </c>
       <c r="B305" t="inlineStr">
         <is>
-          <t>2026-07-11 08:37:52 PM PT</t>
+          <t>2026-07-11 08:39:53 PM PT</t>
         </is>
       </c>
       <c r="C305" t="n">
-        <v>823357</v>
+        <v>823356</v>
       </c>
       <c r="D305" t="inlineStr">
         <is>
-          <t>9:05 AM PT</t>
+          <t>1:05 PM PT</t>
         </is>
       </c>
       <c r="E305" t="inlineStr">
@@ -35627,27 +35636,27 @@
       </c>
       <c r="N305" t="inlineStr">
         <is>
-          <t>Billy Cook</t>
+          <t>Marcell Ozuna</t>
         </is>
       </c>
       <c r="O305" t="n">
-        <v>695257</v>
+        <v>542303</v>
       </c>
       <c r="P305" t="inlineStr">
         <is>
-          <t>CF</t>
+          <t>DH</t>
         </is>
       </c>
       <c r="Q305" t="inlineStr">
         <is>
-          <t>7 (Sub)</t>
+          <t>6</t>
         </is>
       </c>
       <c r="R305" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="S305" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="T305" t="n">
         <v>0</v>
@@ -35680,13 +35689,13 @@
         <v>0</v>
       </c>
       <c r="AD305" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AE305" s="4" t="n">
         <v>0</v>
       </c>
       <c r="AF305" t="n">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="AG305" t="n">
         <v>7</v>
@@ -35700,15 +35709,15 @@
       </c>
       <c r="B306" t="inlineStr">
         <is>
-          <t>2026-07-11 08:37:52 PM PT</t>
+          <t>2026-07-11 08:39:52 PM PT</t>
         </is>
       </c>
       <c r="C306" t="n">
-        <v>823356</v>
+        <v>823357</v>
       </c>
       <c r="D306" t="inlineStr">
         <is>
-          <t>1:05 PM PT</t>
+          <t>9:05 AM PT</t>
         </is>
       </c>
       <c r="E306" t="inlineStr">
@@ -35741,15 +35750,15 @@
       </c>
       <c r="N306" t="inlineStr">
         <is>
-          <t>Henry Davis</t>
+          <t>Billy Cook</t>
         </is>
       </c>
       <c r="O306" t="n">
-        <v>680779</v>
+        <v>695257</v>
       </c>
       <c r="P306" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>CF</t>
         </is>
       </c>
       <c r="Q306" t="inlineStr">
@@ -35800,7 +35809,7 @@
         <v>0</v>
       </c>
       <c r="AF306" t="n">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="AG306" t="n">
         <v>7</v>
@@ -35814,15 +35823,15 @@
       </c>
       <c r="B307" t="inlineStr">
         <is>
-          <t>2026-07-11 08:37:52 PM PT</t>
+          <t>2026-07-11 08:39:53 PM PT</t>
         </is>
       </c>
       <c r="C307" t="n">
-        <v>823357</v>
+        <v>823356</v>
       </c>
       <c r="D307" t="inlineStr">
         <is>
-          <t>9:05 AM PT</t>
+          <t>1:05 PM PT</t>
         </is>
       </c>
       <c r="E307" t="inlineStr">
@@ -35855,27 +35864,27 @@
       </c>
       <c r="N307" t="inlineStr">
         <is>
-          <t>Tyler Callihan</t>
+          <t>Henry Davis</t>
         </is>
       </c>
       <c r="O307" t="n">
-        <v>682997</v>
+        <v>680779</v>
       </c>
       <c r="P307" t="inlineStr">
         <is>
-          <t>LF</t>
+          <t>C</t>
         </is>
       </c>
       <c r="Q307" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>7 (Sub)</t>
         </is>
       </c>
       <c r="R307" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="S307" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="T307" t="n">
         <v>0</v>
@@ -35914,7 +35923,7 @@
         <v>0</v>
       </c>
       <c r="AF307" t="n">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="AG307" t="n">
         <v>7</v>
@@ -35928,7 +35937,7 @@
       </c>
       <c r="B308" t="inlineStr">
         <is>
-          <t>2026-07-11 08:37:52 PM PT</t>
+          <t>2026-07-11 08:39:52 PM PT</t>
         </is>
       </c>
       <c r="C308" t="n">
@@ -35969,20 +35978,20 @@
       </c>
       <c r="N308" t="inlineStr">
         <is>
-          <t>Jared Triolo</t>
+          <t>Tyler Callihan</t>
         </is>
       </c>
       <c r="O308" t="n">
-        <v>669707</v>
+        <v>682997</v>
       </c>
       <c r="P308" t="inlineStr">
         <is>
-          <t>SS</t>
+          <t>LF</t>
         </is>
       </c>
       <c r="Q308" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>7</t>
         </is>
       </c>
       <c r="R308" t="n">
@@ -36022,7 +36031,7 @@
         <v>0</v>
       </c>
       <c r="AD308" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AE308" s="4" t="n">
         <v>0</v>
@@ -36042,15 +36051,15 @@
       </c>
       <c r="B309" t="inlineStr">
         <is>
-          <t>2026-07-11 08:37:52 PM PT</t>
+          <t>2026-07-11 08:39:52 PM PT</t>
         </is>
       </c>
       <c r="C309" t="n">
-        <v>823356</v>
+        <v>823357</v>
       </c>
       <c r="D309" t="inlineStr">
         <is>
-          <t>1:05 PM PT</t>
+          <t>9:05 AM PT</t>
         </is>
       </c>
       <c r="E309" t="inlineStr">
@@ -36100,10 +36109,10 @@
         </is>
       </c>
       <c r="R309" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="S309" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="T309" t="n">
         <v>0</v>
@@ -36136,13 +36145,13 @@
         <v>0</v>
       </c>
       <c r="AD309" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AE309" s="4" t="n">
         <v>0</v>
       </c>
       <c r="AF309" t="n">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="AG309" t="n">
         <v>7</v>
@@ -36156,38 +36165,29 @@
       </c>
       <c r="B310" t="inlineStr">
         <is>
-          <t>2026-07-11 08:37:54 PM PT</t>
+          <t>2026-07-11 08:39:53 PM PT</t>
         </is>
       </c>
       <c r="C310" t="n">
-        <v>823276</v>
+        <v>823356</v>
       </c>
       <c r="D310" t="inlineStr">
         <is>
-          <t>5:40 PM PT</t>
+          <t>1:05 PM PT</t>
         </is>
       </c>
       <c r="E310" t="inlineStr">
         <is>
-          <t>Bottom 8 | 1 out</t>
+          <t>Final</t>
         </is>
       </c>
       <c r="F310" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="G310" t="inlineStr">
         <is>
-          <t>Bottom</t>
-        </is>
-      </c>
-      <c r="H310" t="n">
-        <v>1</v>
-      </c>
-      <c r="I310" t="n">
-        <v>0</v>
-      </c>
-      <c r="J310" t="n">
-        <v>0</v>
+          <t>Top</t>
+        </is>
       </c>
       <c r="K310" t="inlineStr">
         <is>
@@ -36196,25 +36196,25 @@
       </c>
       <c r="L310" t="inlineStr">
         <is>
-          <t>SD</t>
+          <t>PIT</t>
         </is>
       </c>
       <c r="M310" t="inlineStr">
         <is>
-          <t>TOR</t>
+          <t>MIL</t>
         </is>
       </c>
       <c r="N310" t="inlineStr">
         <is>
-          <t>Luis Campusano</t>
+          <t>Jared Triolo</t>
         </is>
       </c>
       <c r="O310" t="n">
-        <v>669134</v>
+        <v>669707</v>
       </c>
       <c r="P310" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>SS</t>
         </is>
       </c>
       <c r="Q310" t="inlineStr">
@@ -36223,10 +36223,10 @@
         </is>
       </c>
       <c r="R310" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="S310" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="T310" t="n">
         <v>0</v>
@@ -36259,16 +36259,16 @@
         <v>0</v>
       </c>
       <c r="AD310" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE310" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF310" t="n">
         <v>3</v>
       </c>
-      <c r="AE310" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="AF310" t="n">
-        <v>8</v>
-      </c>
       <c r="AG310" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
     </row>
     <row r="311">
@@ -36279,61 +36279,70 @@
       </c>
       <c r="B311" t="inlineStr">
         <is>
-          <t>2026-07-11 08:37:53 PM PT</t>
+          <t>2026-07-11 08:39:54 PM PT</t>
         </is>
       </c>
       <c r="C311" t="n">
-        <v>822953</v>
+        <v>823276</v>
       </c>
       <c r="D311" t="inlineStr">
         <is>
-          <t>1:10 PM PT</t>
+          <t>5:40 PM PT</t>
         </is>
       </c>
       <c r="E311" t="inlineStr">
         <is>
-          <t>Final</t>
+          <t>Bottom 8 | 2 out</t>
         </is>
       </c>
       <c r="F311" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="G311" t="inlineStr">
         <is>
-          <t>Top</t>
-        </is>
+          <t>Bottom</t>
+        </is>
+      </c>
+      <c r="H311" t="n">
+        <v>2</v>
+      </c>
+      <c r="I311" t="n">
+        <v>4</v>
+      </c>
+      <c r="J311" t="n">
+        <v>0</v>
       </c>
       <c r="K311" t="inlineStr">
         <is>
-          <t>Away</t>
+          <t>Home</t>
         </is>
       </c>
       <c r="L311" t="inlineStr">
         <is>
-          <t>SEA</t>
+          <t>SD</t>
         </is>
       </c>
       <c r="M311" t="inlineStr">
         <is>
-          <t>TB</t>
+          <t>TOR</t>
         </is>
       </c>
       <c r="N311" t="inlineStr">
         <is>
-          <t>J.P. Crawford</t>
+          <t>Luis Campusano</t>
         </is>
       </c>
       <c r="O311" t="n">
-        <v>641487</v>
+        <v>669134</v>
       </c>
       <c r="P311" t="inlineStr">
         <is>
-          <t>3B</t>
+          <t>C</t>
         </is>
       </c>
       <c r="Q311" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>8</t>
         </is>
       </c>
       <c r="R311" t="n">
@@ -36373,16 +36382,16 @@
         <v>0</v>
       </c>
       <c r="AD311" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="AE311" s="4" t="n">
         <v>0</v>
       </c>
       <c r="AF311" t="n">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="AG311" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
     </row>
     <row r="312">
@@ -36393,7 +36402,7 @@
       </c>
       <c r="B312" t="inlineStr">
         <is>
-          <t>2026-07-11 08:37:53 PM PT</t>
+          <t>2026-07-11 08:39:53 PM PT</t>
         </is>
       </c>
       <c r="C312" t="n">
@@ -36434,27 +36443,27 @@
       </c>
       <c r="N312" t="inlineStr">
         <is>
-          <t>Luke Raley</t>
+          <t>J.P. Crawford</t>
         </is>
       </c>
       <c r="O312" t="n">
-        <v>670042</v>
+        <v>641487</v>
       </c>
       <c r="P312" t="inlineStr">
         <is>
-          <t>RF</t>
+          <t>3B</t>
         </is>
       </c>
       <c r="Q312" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>1</t>
         </is>
       </c>
       <c r="R312" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="S312" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="T312" t="n">
         <v>0</v>
@@ -36507,7 +36516,7 @@
       </c>
       <c r="B313" t="inlineStr">
         <is>
-          <t>2026-07-11 08:37:53 PM PT</t>
+          <t>2026-07-11 08:39:53 PM PT</t>
         </is>
       </c>
       <c r="C313" t="n">
@@ -36548,27 +36557,27 @@
       </c>
       <c r="N313" t="inlineStr">
         <is>
-          <t>Mitch Garver</t>
+          <t>Luke Raley</t>
         </is>
       </c>
       <c r="O313" t="n">
-        <v>641598</v>
+        <v>670042</v>
       </c>
       <c r="P313" t="inlineStr">
         <is>
-          <t>PH</t>
+          <t>RF</t>
         </is>
       </c>
       <c r="Q313" t="inlineStr">
         <is>
-          <t>6 (Sub)</t>
+          <t>6</t>
         </is>
       </c>
       <c r="R313" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="S313" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="T313" t="n">
         <v>0</v>
@@ -36621,7 +36630,7 @@
       </c>
       <c r="B314" t="inlineStr">
         <is>
-          <t>2026-07-11 08:37:53 PM PT</t>
+          <t>2026-07-11 08:39:53 PM PT</t>
         </is>
       </c>
       <c r="C314" t="n">
@@ -36662,15 +36671,15 @@
       </c>
       <c r="N314" t="inlineStr">
         <is>
-          <t>Weston Wilson</t>
+          <t>Mitch Garver</t>
         </is>
       </c>
       <c r="O314" t="n">
-        <v>642215</v>
+        <v>641598</v>
       </c>
       <c r="P314" t="inlineStr">
         <is>
-          <t>RF</t>
+          <t>PH</t>
         </is>
       </c>
       <c r="Q314" t="inlineStr">
@@ -36679,10 +36688,10 @@
         </is>
       </c>
       <c r="R314" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S314" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T314" t="n">
         <v>0</v>
@@ -36715,7 +36724,7 @@
         <v>0</v>
       </c>
       <c r="AD314" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AE314" s="4" t="n">
         <v>0</v>
@@ -36735,7 +36744,7 @@
       </c>
       <c r="B315" t="inlineStr">
         <is>
-          <t>2026-07-11 08:37:53 PM PT</t>
+          <t>2026-07-11 08:39:53 PM PT</t>
         </is>
       </c>
       <c r="C315" t="n">
@@ -36776,27 +36785,27 @@
       </c>
       <c r="N315" t="inlineStr">
         <is>
-          <t>Miles Mastrobuoni</t>
+          <t>Weston Wilson</t>
         </is>
       </c>
       <c r="O315" t="n">
-        <v>670156</v>
+        <v>642215</v>
       </c>
       <c r="P315" t="inlineStr">
         <is>
-          <t>PH</t>
+          <t>RF</t>
         </is>
       </c>
       <c r="Q315" t="inlineStr">
         <is>
-          <t>8 (Sub)</t>
+          <t>6 (Sub)</t>
         </is>
       </c>
       <c r="R315" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S315" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="T315" t="n">
         <v>0</v>
@@ -36849,15 +36858,15 @@
       </c>
       <c r="B316" t="inlineStr">
         <is>
-          <t>2026-07-11 08:37:53 PM PT</t>
+          <t>2026-07-11 08:39:53 PM PT</t>
         </is>
       </c>
       <c r="C316" t="n">
-        <v>823198</v>
+        <v>822953</v>
       </c>
       <c r="D316" t="inlineStr">
         <is>
-          <t>1:05 PM PT</t>
+          <t>1:10 PM PT</t>
         </is>
       </c>
       <c r="E316" t="inlineStr">
@@ -36875,42 +36884,42 @@
       </c>
       <c r="K316" t="inlineStr">
         <is>
-          <t>Home</t>
+          <t>Away</t>
         </is>
       </c>
       <c r="L316" t="inlineStr">
         <is>
-          <t>SF</t>
+          <t>SEA</t>
         </is>
       </c>
       <c r="M316" t="inlineStr">
         <is>
-          <t>COL</t>
+          <t>TB</t>
         </is>
       </c>
       <c r="N316" t="inlineStr">
         <is>
-          <t>Willy Adames</t>
+          <t>Miles Mastrobuoni</t>
         </is>
       </c>
       <c r="O316" t="n">
-        <v>642715</v>
+        <v>670156</v>
       </c>
       <c r="P316" t="inlineStr">
         <is>
-          <t>SS</t>
+          <t>PH</t>
         </is>
       </c>
       <c r="Q316" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>8 (Sub)</t>
         </is>
       </c>
       <c r="R316" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="S316" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="T316" t="n">
         <v>0</v>
@@ -36943,16 +36952,16 @@
         <v>0</v>
       </c>
       <c r="AD316" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AE316" s="4" t="n">
         <v>0</v>
       </c>
       <c r="AF316" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="AG316" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
     </row>
     <row r="317">
@@ -36963,7 +36972,7 @@
       </c>
       <c r="B317" t="inlineStr">
         <is>
-          <t>2026-07-11 08:37:53 PM PT</t>
+          <t>2026-07-11 08:39:53 PM PT</t>
         </is>
       </c>
       <c r="C317" t="n">
@@ -37004,27 +37013,27 @@
       </c>
       <c r="N317" t="inlineStr">
         <is>
-          <t>Jung Hoo Lee</t>
+          <t>Willy Adames</t>
         </is>
       </c>
       <c r="O317" t="n">
-        <v>808982</v>
+        <v>642715</v>
       </c>
       <c r="P317" t="inlineStr">
         <is>
-          <t>RF</t>
+          <t>SS</t>
         </is>
       </c>
       <c r="Q317" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>5</t>
         </is>
       </c>
       <c r="R317" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="S317" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="T317" t="n">
         <v>0</v>
@@ -37077,15 +37086,15 @@
       </c>
       <c r="B318" t="inlineStr">
         <is>
-          <t>2026-07-11 08:37:54 PM PT</t>
+          <t>2026-07-11 08:39:53 PM PT</t>
         </is>
       </c>
       <c r="C318" t="n">
-        <v>823030</v>
+        <v>823198</v>
       </c>
       <c r="D318" t="inlineStr">
         <is>
-          <t>4:15 PM PT</t>
+          <t>1:05 PM PT</t>
         </is>
       </c>
       <c r="E318" t="inlineStr">
@@ -37108,37 +37117,37 @@
       </c>
       <c r="L318" t="inlineStr">
         <is>
-          <t>STL</t>
+          <t>SF</t>
         </is>
       </c>
       <c r="M318" t="inlineStr">
         <is>
-          <t>ATL</t>
+          <t>COL</t>
         </is>
       </c>
       <c r="N318" t="inlineStr">
         <is>
-          <t>JJ Wetherholt</t>
+          <t>Jung Hoo Lee</t>
         </is>
       </c>
       <c r="O318" t="n">
-        <v>802139</v>
+        <v>808982</v>
       </c>
       <c r="P318" t="inlineStr">
         <is>
-          <t>2B</t>
+          <t>RF</t>
         </is>
       </c>
       <c r="Q318" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>7</t>
         </is>
       </c>
       <c r="R318" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="S318" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="T318" t="n">
         <v>0</v>
@@ -37180,7 +37189,7 @@
         <v>4</v>
       </c>
       <c r="AG318" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
     </row>
     <row r="319">
@@ -37191,7 +37200,7 @@
       </c>
       <c r="B319" t="inlineStr">
         <is>
-          <t>2026-07-11 08:37:54 PM PT</t>
+          <t>2026-07-11 08:39:54 PM PT</t>
         </is>
       </c>
       <c r="C319" t="n">
@@ -37232,20 +37241,20 @@
       </c>
       <c r="N319" t="inlineStr">
         <is>
-          <t>Alec Burleson</t>
+          <t>JJ Wetherholt</t>
         </is>
       </c>
       <c r="O319" t="n">
-        <v>676475</v>
+        <v>802139</v>
       </c>
       <c r="P319" t="inlineStr">
         <is>
-          <t>1B</t>
+          <t>2B</t>
         </is>
       </c>
       <c r="Q319" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>1</t>
         </is>
       </c>
       <c r="R319" t="n">
@@ -37285,7 +37294,7 @@
         <v>0</v>
       </c>
       <c r="AD319" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AE319" s="4" t="n">
         <v>0</v>
@@ -37305,7 +37314,7 @@
       </c>
       <c r="B320" t="inlineStr">
         <is>
-          <t>2026-07-11 08:37:54 PM PT</t>
+          <t>2026-07-11 08:39:54 PM PT</t>
         </is>
       </c>
       <c r="C320" t="n">
@@ -37346,27 +37355,27 @@
       </c>
       <c r="N320" t="inlineStr">
         <is>
-          <t>Masyn Winn</t>
+          <t>Alec Burleson</t>
         </is>
       </c>
       <c r="O320" t="n">
-        <v>691026</v>
+        <v>676475</v>
       </c>
       <c r="P320" t="inlineStr">
         <is>
-          <t>SS</t>
+          <t>1B</t>
         </is>
       </c>
       <c r="Q320" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>3</t>
         </is>
       </c>
       <c r="R320" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="S320" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="T320" t="n">
         <v>0</v>
@@ -37399,7 +37408,7 @@
         <v>0</v>
       </c>
       <c r="AD320" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AE320" s="4" t="n">
         <v>0</v>
@@ -37419,7 +37428,7 @@
       </c>
       <c r="B321" t="inlineStr">
         <is>
-          <t>2026-07-11 08:37:54 PM PT</t>
+          <t>2026-07-11 08:39:54 PM PT</t>
         </is>
       </c>
       <c r="C321" t="n">
@@ -37460,20 +37469,20 @@
       </c>
       <c r="N321" t="inlineStr">
         <is>
-          <t>Nathan Church</t>
+          <t>Masyn Winn</t>
         </is>
       </c>
       <c r="O321" t="n">
-        <v>701675</v>
+        <v>691026</v>
       </c>
       <c r="P321" t="inlineStr">
         <is>
-          <t>CF</t>
+          <t>SS</t>
         </is>
       </c>
       <c r="Q321" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>6</t>
         </is>
       </c>
       <c r="R321" t="n">
@@ -37533,15 +37542,15 @@
       </c>
       <c r="B322" t="inlineStr">
         <is>
-          <t>2026-07-11 08:37:53 PM PT</t>
+          <t>2026-07-11 08:39:54 PM PT</t>
         </is>
       </c>
       <c r="C322" t="n">
-        <v>822953</v>
+        <v>823030</v>
       </c>
       <c r="D322" t="inlineStr">
         <is>
-          <t>1:10 PM PT</t>
+          <t>4:15 PM PT</t>
         </is>
       </c>
       <c r="E322" t="inlineStr">
@@ -37564,21 +37573,21 @@
       </c>
       <c r="L322" t="inlineStr">
         <is>
-          <t>TB</t>
+          <t>STL</t>
         </is>
       </c>
       <c r="M322" t="inlineStr">
         <is>
-          <t>SEA</t>
+          <t>ATL</t>
         </is>
       </c>
       <c r="N322" t="inlineStr">
         <is>
-          <t>Cedric Mullins</t>
+          <t>Nathan Church</t>
         </is>
       </c>
       <c r="O322" t="n">
-        <v>656775</v>
+        <v>701675</v>
       </c>
       <c r="P322" t="inlineStr">
         <is>
@@ -37587,7 +37596,7 @@
       </c>
       <c r="Q322" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>9</t>
         </is>
       </c>
       <c r="R322" t="n">
@@ -37627,16 +37636,16 @@
         <v>0</v>
       </c>
       <c r="AD322" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AE322" s="4" t="n">
         <v>0</v>
       </c>
       <c r="AF322" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="AG322" t="n">
-        <v>12</v>
+        <v>5</v>
       </c>
     </row>
     <row r="323">
@@ -37647,7 +37656,7 @@
       </c>
       <c r="B323" t="inlineStr">
         <is>
-          <t>2026-07-11 08:37:53 PM PT</t>
+          <t>2026-07-11 08:39:53 PM PT</t>
         </is>
       </c>
       <c r="C323" t="n">
@@ -37688,27 +37697,27 @@
       </c>
       <c r="N323" t="inlineStr">
         <is>
-          <t>Victor Mesa Jr.</t>
+          <t>Cedric Mullins</t>
         </is>
       </c>
       <c r="O323" t="n">
-        <v>683748</v>
+        <v>656775</v>
       </c>
       <c r="P323" t="inlineStr">
         <is>
-          <t>RF</t>
+          <t>CF</t>
         </is>
       </c>
       <c r="Q323" t="inlineStr">
         <is>
-          <t>4 (Sub)</t>
+          <t>4</t>
         </is>
       </c>
       <c r="R323" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="S323" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="T323" t="n">
         <v>0</v>
@@ -37761,7 +37770,7 @@
       </c>
       <c r="B324" t="inlineStr">
         <is>
-          <t>2026-07-11 08:37:53 PM PT</t>
+          <t>2026-07-11 08:39:53 PM PT</t>
         </is>
       </c>
       <c r="C324" t="n">
@@ -37802,27 +37811,27 @@
       </c>
       <c r="N324" t="inlineStr">
         <is>
-          <t>Jonny DeLuca</t>
+          <t>Victor Mesa Jr.</t>
         </is>
       </c>
       <c r="O324" t="n">
-        <v>676356</v>
+        <v>683748</v>
       </c>
       <c r="P324" t="inlineStr">
         <is>
-          <t>CF</t>
+          <t>RF</t>
         </is>
       </c>
       <c r="Q324" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>4 (Sub)</t>
         </is>
       </c>
       <c r="R324" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="S324" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="T324" t="n">
         <v>0</v>
@@ -37855,7 +37864,7 @@
         <v>0</v>
       </c>
       <c r="AD324" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AE324" s="4" t="n">
         <v>0</v>
@@ -37875,7 +37884,7 @@
       </c>
       <c r="B325" t="inlineStr">
         <is>
-          <t>2026-07-11 08:37:53 PM PT</t>
+          <t>2026-07-11 08:39:53 PM PT</t>
         </is>
       </c>
       <c r="C325" t="n">
@@ -37916,20 +37925,20 @@
       </c>
       <c r="N325" t="inlineStr">
         <is>
-          <t>Richie Palacios</t>
+          <t>Jonny DeLuca</t>
         </is>
       </c>
       <c r="O325" t="n">
-        <v>680700</v>
+        <v>676356</v>
       </c>
       <c r="P325" t="inlineStr">
         <is>
-          <t>2B</t>
+          <t>CF</t>
         </is>
       </c>
       <c r="Q325" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>5</t>
         </is>
       </c>
       <c r="R325" t="n">
@@ -37969,7 +37978,7 @@
         <v>0</v>
       </c>
       <c r="AD325" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AE325" s="4" t="n">
         <v>0</v>
@@ -37989,15 +37998,15 @@
       </c>
       <c r="B326" t="inlineStr">
         <is>
-          <t>2026-07-11 08:37:54 PM PT</t>
+          <t>2026-07-11 08:39:53 PM PT</t>
         </is>
       </c>
       <c r="C326" t="n">
-        <v>822875</v>
+        <v>822953</v>
       </c>
       <c r="D326" t="inlineStr">
         <is>
-          <t>4:05 PM PT</t>
+          <t>1:10 PM PT</t>
         </is>
       </c>
       <c r="E326" t="inlineStr">
@@ -38010,7 +38019,7 @@
       </c>
       <c r="G326" t="inlineStr">
         <is>
-          <t>Bottom</t>
+          <t>Top</t>
         </is>
       </c>
       <c r="K326" t="inlineStr">
@@ -38020,37 +38029,37 @@
       </c>
       <c r="L326" t="inlineStr">
         <is>
-          <t>TEX</t>
+          <t>TB</t>
         </is>
       </c>
       <c r="M326" t="inlineStr">
         <is>
-          <t>HOU</t>
+          <t>SEA</t>
         </is>
       </c>
       <c r="N326" t="inlineStr">
         <is>
-          <t>Alejandro Osuna</t>
+          <t>Richie Palacios</t>
         </is>
       </c>
       <c r="O326" t="n">
-        <v>696030</v>
+        <v>680700</v>
       </c>
       <c r="P326" t="inlineStr">
         <is>
-          <t>LF</t>
+          <t>2B</t>
         </is>
       </c>
       <c r="Q326" t="inlineStr">
         <is>
-          <t>2 (Sub)</t>
+          <t>8</t>
         </is>
       </c>
       <c r="R326" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="S326" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="T326" t="n">
         <v>0</v>
@@ -38089,10 +38098,10 @@
         <v>0</v>
       </c>
       <c r="AF326" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="AG326" t="n">
-        <v>7</v>
+        <v>12</v>
       </c>
     </row>
     <row r="327">
@@ -38103,7 +38112,7 @@
       </c>
       <c r="B327" t="inlineStr">
         <is>
-          <t>2026-07-11 08:37:54 PM PT</t>
+          <t>2026-07-11 08:39:53 PM PT</t>
         </is>
       </c>
       <c r="C327" t="n">
@@ -38144,27 +38153,27 @@
       </c>
       <c r="N327" t="inlineStr">
         <is>
-          <t>Brandon Nimmo</t>
+          <t>Alejandro Osuna</t>
         </is>
       </c>
       <c r="O327" t="n">
-        <v>607043</v>
+        <v>696030</v>
       </c>
       <c r="P327" t="inlineStr">
         <is>
-          <t>RF</t>
+          <t>LF</t>
         </is>
       </c>
       <c r="Q327" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>2 (Sub)</t>
         </is>
       </c>
       <c r="R327" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="S327" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="T327" t="n">
         <v>0</v>
@@ -38197,7 +38206,7 @@
         <v>0</v>
       </c>
       <c r="AD327" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="AE327" s="4" t="n">
         <v>0</v>
@@ -38217,7 +38226,7 @@
       </c>
       <c r="B328" t="inlineStr">
         <is>
-          <t>2026-07-11 08:37:54 PM PT</t>
+          <t>2026-07-11 08:39:53 PM PT</t>
         </is>
       </c>
       <c r="C328" t="n">
@@ -38258,20 +38267,20 @@
       </c>
       <c r="N328" t="inlineStr">
         <is>
-          <t>Jake Burger</t>
+          <t>Brandon Nimmo</t>
         </is>
       </c>
       <c r="O328" t="n">
-        <v>669394</v>
+        <v>607043</v>
       </c>
       <c r="P328" t="inlineStr">
         <is>
-          <t>1B</t>
+          <t>RF</t>
         </is>
       </c>
       <c r="Q328" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>4</t>
         </is>
       </c>
       <c r="R328" t="n">
@@ -38311,7 +38320,7 @@
         <v>0</v>
       </c>
       <c r="AD328" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="AE328" s="4" t="n">
         <v>0</v>
@@ -38331,7 +38340,7 @@
       </c>
       <c r="B329" t="inlineStr">
         <is>
-          <t>2026-07-11 08:37:54 PM PT</t>
+          <t>2026-07-11 08:39:53 PM PT</t>
         </is>
       </c>
       <c r="C329" t="n">
@@ -38372,27 +38381,27 @@
       </c>
       <c r="N329" t="inlineStr">
         <is>
-          <t>Justin Foscue</t>
+          <t>Jake Burger</t>
         </is>
       </c>
       <c r="O329" t="n">
-        <v>679822</v>
+        <v>669394</v>
       </c>
       <c r="P329" t="inlineStr">
         <is>
-          <t>PH</t>
+          <t>1B</t>
         </is>
       </c>
       <c r="Q329" t="inlineStr">
         <is>
-          <t>5 (Sub)</t>
+          <t>5</t>
         </is>
       </c>
       <c r="R329" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="S329" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="T329" t="n">
         <v>0</v>
@@ -38445,7 +38454,7 @@
       </c>
       <c r="B330" t="inlineStr">
         <is>
-          <t>2026-07-11 08:37:54 PM PT</t>
+          <t>2026-07-11 08:39:53 PM PT</t>
         </is>
       </c>
       <c r="C330" t="n">
@@ -38486,27 +38495,27 @@
       </c>
       <c r="N330" t="inlineStr">
         <is>
-          <t>Nicky Lopez</t>
+          <t>Justin Foscue</t>
         </is>
       </c>
       <c r="O330" t="n">
-        <v>670032</v>
+        <v>679822</v>
       </c>
       <c r="P330" t="inlineStr">
         <is>
-          <t>2B</t>
+          <t>PH</t>
         </is>
       </c>
       <c r="Q330" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>5 (Sub)</t>
         </is>
       </c>
       <c r="R330" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="S330" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="T330" t="n">
         <v>0</v>
@@ -38559,70 +38568,61 @@
       </c>
       <c r="B331" t="inlineStr">
         <is>
-          <t>2026-07-11 08:37:54 PM PT</t>
+          <t>2026-07-11 08:39:53 PM PT</t>
         </is>
       </c>
       <c r="C331" t="n">
-        <v>823276</v>
+        <v>822875</v>
       </c>
       <c r="D331" t="inlineStr">
         <is>
-          <t>5:40 PM PT</t>
+          <t>4:05 PM PT</t>
         </is>
       </c>
       <c r="E331" t="inlineStr">
         <is>
-          <t>Bottom 8 | 1 out</t>
+          <t>Final</t>
         </is>
       </c>
       <c r="F331" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="G331" t="inlineStr">
         <is>
           <t>Bottom</t>
         </is>
       </c>
-      <c r="H331" t="n">
-        <v>1</v>
-      </c>
-      <c r="I331" t="n">
-        <v>0</v>
-      </c>
-      <c r="J331" t="n">
-        <v>0</v>
-      </c>
       <c r="K331" t="inlineStr">
         <is>
-          <t>Away</t>
+          <t>Home</t>
         </is>
       </c>
       <c r="L331" t="inlineStr">
         <is>
-          <t>TOR</t>
+          <t>TEX</t>
         </is>
       </c>
       <c r="M331" t="inlineStr">
         <is>
-          <t>SD</t>
+          <t>HOU</t>
         </is>
       </c>
       <c r="N331" t="inlineStr">
         <is>
-          <t>George Springer</t>
+          <t>Nicky Lopez</t>
         </is>
       </c>
       <c r="O331" t="n">
-        <v>543807</v>
+        <v>670032</v>
       </c>
       <c r="P331" t="inlineStr">
         <is>
-          <t>DH</t>
+          <t>2B</t>
         </is>
       </c>
       <c r="Q331" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>8</t>
         </is>
       </c>
       <c r="R331" t="n">
@@ -38668,7 +38668,7 @@
         <v>0</v>
       </c>
       <c r="AF331" t="n">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="AG331" t="n">
         <v>7</v>
@@ -38682,61 +38682,70 @@
       </c>
       <c r="B332" t="inlineStr">
         <is>
-          <t>2026-07-11 08:37:53 PM PT</t>
+          <t>2026-07-11 08:39:54 PM PT</t>
         </is>
       </c>
       <c r="C332" t="n">
-        <v>822711</v>
+        <v>823276</v>
       </c>
       <c r="D332" t="inlineStr">
         <is>
-          <t>1:05 PM PT</t>
+          <t>5:40 PM PT</t>
         </is>
       </c>
       <c r="E332" t="inlineStr">
         <is>
-          <t>Final</t>
+          <t>Bottom 8 | 2 out</t>
         </is>
       </c>
       <c r="F332" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="G332" t="inlineStr">
         <is>
           <t>Bottom</t>
         </is>
       </c>
+      <c r="H332" t="n">
+        <v>2</v>
+      </c>
+      <c r="I332" t="n">
+        <v>4</v>
+      </c>
+      <c r="J332" t="n">
+        <v>0</v>
+      </c>
       <c r="K332" t="inlineStr">
         <is>
-          <t>Home</t>
+          <t>Away</t>
         </is>
       </c>
       <c r="L332" t="inlineStr">
         <is>
-          <t>WSH</t>
+          <t>TOR</t>
         </is>
       </c>
       <c r="M332" t="inlineStr">
         <is>
-          <t>NYY</t>
+          <t>SD</t>
         </is>
       </c>
       <c r="N332" t="inlineStr">
         <is>
-          <t>Daylen Lile</t>
+          <t>George Springer</t>
         </is>
       </c>
       <c r="O332" t="n">
-        <v>695734</v>
+        <v>543807</v>
       </c>
       <c r="P332" t="inlineStr">
         <is>
-          <t>LF</t>
+          <t>DH</t>
         </is>
       </c>
       <c r="Q332" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>4</t>
         </is>
       </c>
       <c r="R332" t="n">
@@ -38776,13 +38785,13 @@
         <v>0</v>
       </c>
       <c r="AD332" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AE332" s="4" t="n">
         <v>0</v>
       </c>
       <c r="AF332" t="n">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="AG332" t="n">
         <v>7</v>
@@ -38796,7 +38805,7 @@
       </c>
       <c r="B333" t="inlineStr">
         <is>
-          <t>2026-07-11 08:37:53 PM PT</t>
+          <t>2026-07-11 08:39:53 PM PT</t>
         </is>
       </c>
       <c r="C333" t="n">
@@ -38837,27 +38846,27 @@
       </c>
       <c r="N333" t="inlineStr">
         <is>
-          <t>José Tena</t>
+          <t>Daylen Lile</t>
         </is>
       </c>
       <c r="O333" t="n">
-        <v>677588</v>
+        <v>695734</v>
       </c>
       <c r="P333" t="inlineStr">
         <is>
-          <t>PH</t>
+          <t>LF</t>
         </is>
       </c>
       <c r="Q333" t="inlineStr">
         <is>
-          <t>8 (Sub)</t>
+          <t>5</t>
         </is>
       </c>
       <c r="R333" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="S333" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="T333" t="n">
         <v>0</v>
@@ -38890,7 +38899,7 @@
         <v>0</v>
       </c>
       <c r="AD333" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AE333" s="4" t="n">
         <v>0</v>
@@ -38902,9 +38911,123 @@
         <v>7</v>
       </c>
     </row>
+    <row r="334">
+      <c r="A334" t="inlineStr">
+        <is>
+          <t>2026-07-11</t>
+        </is>
+      </c>
+      <c r="B334" t="inlineStr">
+        <is>
+          <t>2026-07-11 08:39:53 PM PT</t>
+        </is>
+      </c>
+      <c r="C334" t="n">
+        <v>822711</v>
+      </c>
+      <c r="D334" t="inlineStr">
+        <is>
+          <t>1:05 PM PT</t>
+        </is>
+      </c>
+      <c r="E334" t="inlineStr">
+        <is>
+          <t>Final</t>
+        </is>
+      </c>
+      <c r="F334" t="n">
+        <v>9</v>
+      </c>
+      <c r="G334" t="inlineStr">
+        <is>
+          <t>Bottom</t>
+        </is>
+      </c>
+      <c r="K334" t="inlineStr">
+        <is>
+          <t>Home</t>
+        </is>
+      </c>
+      <c r="L334" t="inlineStr">
+        <is>
+          <t>WSH</t>
+        </is>
+      </c>
+      <c r="M334" t="inlineStr">
+        <is>
+          <t>NYY</t>
+        </is>
+      </c>
+      <c r="N334" t="inlineStr">
+        <is>
+          <t>José Tena</t>
+        </is>
+      </c>
+      <c r="O334" t="n">
+        <v>677588</v>
+      </c>
+      <c r="P334" t="inlineStr">
+        <is>
+          <t>PH</t>
+        </is>
+      </c>
+      <c r="Q334" t="inlineStr">
+        <is>
+          <t>8 (Sub)</t>
+        </is>
+      </c>
+      <c r="R334" t="n">
+        <v>1</v>
+      </c>
+      <c r="S334" t="n">
+        <v>1</v>
+      </c>
+      <c r="T334" t="n">
+        <v>0</v>
+      </c>
+      <c r="U334" t="n">
+        <v>0</v>
+      </c>
+      <c r="V334" t="n">
+        <v>0</v>
+      </c>
+      <c r="W334" t="n">
+        <v>0</v>
+      </c>
+      <c r="X334" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y334" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z334" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA334" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB334" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC334" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD334" t="n">
+        <v>1</v>
+      </c>
+      <c r="AE334" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF334" t="n">
+        <v>2</v>
+      </c>
+      <c r="AG334" t="n">
+        <v>7</v>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:AG333"/>
-  <conditionalFormatting sqref="AE2:AE333">
+  <autoFilter ref="A1:AG334"/>
+  <conditionalFormatting sqref="AE2:AE334">
     <cfRule type="colorScale" priority="1">
       <colorScale>
         <cfvo type="num" val="0"/>

--- a/live_mlb_hitter_fantasy_scores_2026_07_11.xlsx
+++ b/live_mlb_hitter_fantasy_scores_2026_07_11.xlsx
@@ -11,7 +11,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Scoring" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Live Fantasy Scores'!$A$1:$AG$334</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Live Fantasy Scores'!$A$1:$AG$335</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -480,7 +480,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AG334"/>
+  <dimension ref="A1:AG335"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -693,7 +693,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-07-11 08:39:52 PM PT</t>
+          <t>2026-07-11 08:41:52 PM PT</t>
         </is>
       </c>
       <c r="C2" t="n">
@@ -807,7 +807,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>2026-07-11 08:39:54 PM PT</t>
+          <t>2026-07-11 08:41:54 PM PT</t>
         </is>
       </c>
       <c r="C3" t="n">
@@ -820,7 +820,7 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Bottom 8 | 1 out</t>
+          <t>Bottom 8 | 2 out</t>
         </is>
       </c>
       <c r="F3" t="n">
@@ -832,13 +832,13 @@
         </is>
       </c>
       <c r="H3" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J3" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K3" t="inlineStr">
         <is>
@@ -930,7 +930,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-07-11 08:39:53 PM PT</t>
+          <t>2026-07-11 08:41:53 PM PT</t>
         </is>
       </c>
       <c r="C4" t="n">
@@ -1044,7 +1044,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>2026-07-11 08:39:54 PM PT</t>
+          <t>2026-07-11 08:41:54 PM PT</t>
         </is>
       </c>
       <c r="C5" t="n">
@@ -1057,7 +1057,7 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Bottom 8 | 2 out</t>
+          <t>Bottom 8 | 3 out</t>
         </is>
       </c>
       <c r="F5" t="n">
@@ -1069,13 +1069,13 @@
         </is>
       </c>
       <c r="H5" t="n">
+        <v>3</v>
+      </c>
+      <c r="I5" t="n">
+        <v>1</v>
+      </c>
+      <c r="J5" t="n">
         <v>2</v>
-      </c>
-      <c r="I5" t="n">
-        <v>4</v>
-      </c>
-      <c r="J5" t="n">
-        <v>0</v>
       </c>
       <c r="K5" t="inlineStr">
         <is>
@@ -1167,7 +1167,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>2026-07-11 08:39:53 PM PT</t>
+          <t>2026-07-11 08:41:53 PM PT</t>
         </is>
       </c>
       <c r="C6" t="n">
@@ -1281,7 +1281,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>2026-07-11 08:39:54 PM PT</t>
+          <t>2026-07-11 08:41:54 PM PT</t>
         </is>
       </c>
       <c r="C7" t="n">
@@ -1395,7 +1395,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>2026-07-11 08:39:53 PM PT</t>
+          <t>2026-07-11 08:41:53 PM PT</t>
         </is>
       </c>
       <c r="C8" t="n">
@@ -1509,7 +1509,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>2026-07-11 08:39:53 PM PT</t>
+          <t>2026-07-11 08:41:53 PM PT</t>
         </is>
       </c>
       <c r="C9" t="n">
@@ -1623,7 +1623,7 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>2026-07-11 08:39:53 PM PT</t>
+          <t>2026-07-11 08:41:53 PM PT</t>
         </is>
       </c>
       <c r="C10" t="n">
@@ -1737,7 +1737,7 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>2026-07-11 08:39:54 PM PT</t>
+          <t>2026-07-11 08:41:54 PM PT</t>
         </is>
       </c>
       <c r="C11" t="n">
@@ -1750,7 +1750,7 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Bottom 8 | 2 out</t>
+          <t>Bottom 8 | 3 out</t>
         </is>
       </c>
       <c r="F11" t="n">
@@ -1762,13 +1762,13 @@
         </is>
       </c>
       <c r="H11" t="n">
+        <v>3</v>
+      </c>
+      <c r="I11" t="n">
+        <v>1</v>
+      </c>
+      <c r="J11" t="n">
         <v>2</v>
-      </c>
-      <c r="I11" t="n">
-        <v>4</v>
-      </c>
-      <c r="J11" t="n">
-        <v>0</v>
       </c>
       <c r="K11" t="inlineStr">
         <is>
@@ -1804,10 +1804,10 @@
         </is>
       </c>
       <c r="R11" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="S11" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="T11" t="n">
         <v>2</v>
@@ -1860,7 +1860,7 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>2026-07-11 08:39:53 PM PT</t>
+          <t>2026-07-11 08:41:53 PM PT</t>
         </is>
       </c>
       <c r="C12" t="n">
@@ -1974,7 +1974,7 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>2026-07-11 08:39:53 PM PT</t>
+          <t>2026-07-11 08:41:53 PM PT</t>
         </is>
       </c>
       <c r="C13" t="n">
@@ -2088,7 +2088,7 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>2026-07-11 08:39:54 PM PT</t>
+          <t>2026-07-11 08:41:54 PM PT</t>
         </is>
       </c>
       <c r="C14" t="n">
@@ -2101,7 +2101,7 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Bottom 8 | 2 out</t>
+          <t>Bottom 8 | 3 out</t>
         </is>
       </c>
       <c r="F14" t="n">
@@ -2113,13 +2113,13 @@
         </is>
       </c>
       <c r="H14" t="n">
+        <v>3</v>
+      </c>
+      <c r="I14" t="n">
+        <v>1</v>
+      </c>
+      <c r="J14" t="n">
         <v>2</v>
-      </c>
-      <c r="I14" t="n">
-        <v>4</v>
-      </c>
-      <c r="J14" t="n">
-        <v>0</v>
       </c>
       <c r="K14" t="inlineStr">
         <is>
@@ -2211,7 +2211,7 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>2026-07-11 08:39:53 PM PT</t>
+          <t>2026-07-11 08:41:53 PM PT</t>
         </is>
       </c>
       <c r="C15" t="n">
@@ -2325,7 +2325,7 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>2026-07-11 08:39:53 PM PT</t>
+          <t>2026-07-11 08:41:53 PM PT</t>
         </is>
       </c>
       <c r="C16" t="n">
@@ -2439,7 +2439,7 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>2026-07-11 08:39:53 PM PT</t>
+          <t>2026-07-11 08:41:53 PM PT</t>
         </is>
       </c>
       <c r="C17" t="n">
@@ -2553,7 +2553,7 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>2026-07-11 08:39:54 PM PT</t>
+          <t>2026-07-11 08:41:54 PM PT</t>
         </is>
       </c>
       <c r="C18" t="n">
@@ -2566,7 +2566,7 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Bottom 8 | 2 out</t>
+          <t>Bottom 8 | 3 out</t>
         </is>
       </c>
       <c r="F18" t="n">
@@ -2578,13 +2578,13 @@
         </is>
       </c>
       <c r="H18" t="n">
+        <v>3</v>
+      </c>
+      <c r="I18" t="n">
+        <v>1</v>
+      </c>
+      <c r="J18" t="n">
         <v>2</v>
-      </c>
-      <c r="I18" t="n">
-        <v>4</v>
-      </c>
-      <c r="J18" t="n">
-        <v>0</v>
       </c>
       <c r="K18" t="inlineStr">
         <is>
@@ -2676,7 +2676,7 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>2026-07-11 08:39:53 PM PT</t>
+          <t>2026-07-11 08:41:53 PM PT</t>
         </is>
       </c>
       <c r="C19" t="n">
@@ -2790,7 +2790,7 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>2026-07-11 08:39:54 PM PT</t>
+          <t>2026-07-11 08:41:54 PM PT</t>
         </is>
       </c>
       <c r="C20" t="n">
@@ -2904,7 +2904,7 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>2026-07-11 08:39:53 PM PT</t>
+          <t>2026-07-11 08:41:53 PM PT</t>
         </is>
       </c>
       <c r="C21" t="n">
@@ -3018,7 +3018,7 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>2026-07-11 08:39:53 PM PT</t>
+          <t>2026-07-11 08:41:53 PM PT</t>
         </is>
       </c>
       <c r="C22" t="n">
@@ -3132,7 +3132,7 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>2026-07-11 08:39:54 PM PT</t>
+          <t>2026-07-11 08:41:54 PM PT</t>
         </is>
       </c>
       <c r="C23" t="n">
@@ -3145,7 +3145,7 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Bottom 8 | 1 out</t>
+          <t>Bottom 8 | 2 out</t>
         </is>
       </c>
       <c r="F23" t="n">
@@ -3157,13 +3157,13 @@
         </is>
       </c>
       <c r="H23" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I23" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J23" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K23" t="inlineStr">
         <is>
@@ -3255,7 +3255,7 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>2026-07-11 08:39:53 PM PT</t>
+          <t>2026-07-11 08:41:53 PM PT</t>
         </is>
       </c>
       <c r="C24" t="n">
@@ -3369,7 +3369,7 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>2026-07-11 08:39:53 PM PT</t>
+          <t>2026-07-11 08:41:53 PM PT</t>
         </is>
       </c>
       <c r="C25" t="n">
@@ -3483,7 +3483,7 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>2026-07-11 08:39:54 PM PT</t>
+          <t>2026-07-11 08:41:54 PM PT</t>
         </is>
       </c>
       <c r="C26" t="n">
@@ -3597,7 +3597,7 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>2026-07-11 08:39:52 PM PT</t>
+          <t>2026-07-11 08:41:52 PM PT</t>
         </is>
       </c>
       <c r="C27" t="n">
@@ -3711,7 +3711,7 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>2026-07-11 08:39:53 PM PT</t>
+          <t>2026-07-11 08:41:53 PM PT</t>
         </is>
       </c>
       <c r="C28" t="n">
@@ -3825,7 +3825,7 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>2026-07-11 08:39:53 PM PT</t>
+          <t>2026-07-11 08:41:53 PM PT</t>
         </is>
       </c>
       <c r="C29" t="n">
@@ -3939,7 +3939,7 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>2026-07-11 08:39:54 PM PT</t>
+          <t>2026-07-11 08:41:54 PM PT</t>
         </is>
       </c>
       <c r="C30" t="n">
@@ -4053,7 +4053,7 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>2026-07-11 08:39:54 PM PT</t>
+          <t>2026-07-11 08:41:54 PM PT</t>
         </is>
       </c>
       <c r="C31" t="n">
@@ -4167,7 +4167,7 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>2026-07-11 08:39:53 PM PT</t>
+          <t>2026-07-11 08:41:53 PM PT</t>
         </is>
       </c>
       <c r="C32" t="n">
@@ -4281,7 +4281,7 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>2026-07-11 08:39:53 PM PT</t>
+          <t>2026-07-11 08:41:53 PM PT</t>
         </is>
       </c>
       <c r="C33" t="n">
@@ -4395,7 +4395,7 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>2026-07-11 08:39:53 PM PT</t>
+          <t>2026-07-11 08:41:53 PM PT</t>
         </is>
       </c>
       <c r="C34" t="n">
@@ -4509,7 +4509,7 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>2026-07-11 08:39:52 PM PT</t>
+          <t>2026-07-11 08:41:52 PM PT</t>
         </is>
       </c>
       <c r="C35" t="n">
@@ -4623,7 +4623,7 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>2026-07-11 08:39:53 PM PT</t>
+          <t>2026-07-11 08:41:52 PM PT</t>
         </is>
       </c>
       <c r="C36" t="n">
@@ -4737,7 +4737,7 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>2026-07-11 08:39:54 PM PT</t>
+          <t>2026-07-11 08:41:54 PM PT</t>
         </is>
       </c>
       <c r="C37" t="n">
@@ -4750,7 +4750,7 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Bottom 8 | 2 out</t>
+          <t>Bottom 8 | 3 out</t>
         </is>
       </c>
       <c r="F37" t="n">
@@ -4762,13 +4762,13 @@
         </is>
       </c>
       <c r="H37" t="n">
+        <v>3</v>
+      </c>
+      <c r="I37" t="n">
+        <v>1</v>
+      </c>
+      <c r="J37" t="n">
         <v>2</v>
-      </c>
-      <c r="I37" t="n">
-        <v>4</v>
-      </c>
-      <c r="J37" t="n">
-        <v>0</v>
       </c>
       <c r="K37" t="inlineStr">
         <is>
@@ -4860,7 +4860,7 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>2026-07-11 08:39:53 PM PT</t>
+          <t>2026-07-11 08:41:53 PM PT</t>
         </is>
       </c>
       <c r="C38" t="n">
@@ -4974,7 +4974,7 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>2026-07-11 08:39:53 PM PT</t>
+          <t>2026-07-11 08:41:53 PM PT</t>
         </is>
       </c>
       <c r="C39" t="n">
@@ -5088,7 +5088,7 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>2026-07-11 08:39:53 PM PT</t>
+          <t>2026-07-11 08:41:53 PM PT</t>
         </is>
       </c>
       <c r="C40" t="n">
@@ -5202,7 +5202,7 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>2026-07-11 08:39:53 PM PT</t>
+          <t>2026-07-11 08:41:52 PM PT</t>
         </is>
       </c>
       <c r="C41" t="n">
@@ -5316,7 +5316,7 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>2026-07-11 08:39:54 PM PT</t>
+          <t>2026-07-11 08:41:54 PM PT</t>
         </is>
       </c>
       <c r="C42" t="n">
@@ -5329,7 +5329,7 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>Bottom 8 | 1 out</t>
+          <t>Bottom 8 | 2 out</t>
         </is>
       </c>
       <c r="F42" t="n">
@@ -5341,13 +5341,13 @@
         </is>
       </c>
       <c r="H42" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I42" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J42" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K42" t="inlineStr">
         <is>
@@ -5439,7 +5439,7 @@
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>2026-07-11 08:39:54 PM PT</t>
+          <t>2026-07-11 08:41:54 PM PT</t>
         </is>
       </c>
       <c r="C43" t="n">
@@ -5553,7 +5553,7 @@
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>2026-07-11 08:39:53 PM PT</t>
+          <t>2026-07-11 08:41:53 PM PT</t>
         </is>
       </c>
       <c r="C44" t="n">
@@ -5667,7 +5667,7 @@
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>2026-07-11 08:39:53 PM PT</t>
+          <t>2026-07-11 08:41:53 PM PT</t>
         </is>
       </c>
       <c r="C45" t="n">
@@ -5781,7 +5781,7 @@
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>2026-07-11 08:39:54 PM PT</t>
+          <t>2026-07-11 08:41:54 PM PT</t>
         </is>
       </c>
       <c r="C46" t="n">
@@ -5895,7 +5895,7 @@
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>2026-07-11 08:39:53 PM PT</t>
+          <t>2026-07-11 08:41:53 PM PT</t>
         </is>
       </c>
       <c r="C47" t="n">
@@ -6009,7 +6009,7 @@
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>2026-07-11 08:39:53 PM PT</t>
+          <t>2026-07-11 08:41:53 PM PT</t>
         </is>
       </c>
       <c r="C48" t="n">
@@ -6123,7 +6123,7 @@
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>2026-07-11 08:39:53 PM PT</t>
+          <t>2026-07-11 08:41:53 PM PT</t>
         </is>
       </c>
       <c r="C49" t="n">
@@ -6237,7 +6237,7 @@
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>2026-07-11 08:39:53 PM PT</t>
+          <t>2026-07-11 08:41:53 PM PT</t>
         </is>
       </c>
       <c r="C50" t="n">
@@ -6351,7 +6351,7 @@
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>2026-07-11 08:39:53 PM PT</t>
+          <t>2026-07-11 08:41:52 PM PT</t>
         </is>
       </c>
       <c r="C51" t="n">
@@ -6465,7 +6465,7 @@
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>2026-07-11 08:39:54 PM PT</t>
+          <t>2026-07-11 08:41:54 PM PT</t>
         </is>
       </c>
       <c r="C52" t="n">
@@ -6478,7 +6478,7 @@
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>Bottom 8 | 2 out</t>
+          <t>Bottom 8 | 3 out</t>
         </is>
       </c>
       <c r="F52" t="n">
@@ -6490,13 +6490,13 @@
         </is>
       </c>
       <c r="H52" t="n">
+        <v>3</v>
+      </c>
+      <c r="I52" t="n">
+        <v>1</v>
+      </c>
+      <c r="J52" t="n">
         <v>2</v>
-      </c>
-      <c r="I52" t="n">
-        <v>4</v>
-      </c>
-      <c r="J52" t="n">
-        <v>0</v>
       </c>
       <c r="K52" t="inlineStr">
         <is>
@@ -6588,7 +6588,7 @@
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>2026-07-11 08:39:54 PM PT</t>
+          <t>2026-07-11 08:41:54 PM PT</t>
         </is>
       </c>
       <c r="C53" t="n">
@@ -6601,7 +6601,7 @@
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>Bottom 8 | 1 out</t>
+          <t>Bottom 8 | 2 out</t>
         </is>
       </c>
       <c r="F53" t="n">
@@ -6613,13 +6613,13 @@
         </is>
       </c>
       <c r="H53" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I53" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J53" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K53" t="inlineStr">
         <is>
@@ -6711,7 +6711,7 @@
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>2026-07-11 08:39:54 PM PT</t>
+          <t>2026-07-11 08:41:54 PM PT</t>
         </is>
       </c>
       <c r="C54" t="n">
@@ -6825,7 +6825,7 @@
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>2026-07-11 08:39:54 PM PT</t>
+          <t>2026-07-11 08:41:54 PM PT</t>
         </is>
       </c>
       <c r="C55" t="n">
@@ -6939,7 +6939,7 @@
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>2026-07-11 08:39:53 PM PT</t>
+          <t>2026-07-11 08:41:53 PM PT</t>
         </is>
       </c>
       <c r="C56" t="n">
@@ -7053,7 +7053,7 @@
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>2026-07-11 08:39:53 PM PT</t>
+          <t>2026-07-11 08:41:53 PM PT</t>
         </is>
       </c>
       <c r="C57" t="n">
@@ -7167,7 +7167,7 @@
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>2026-07-11 08:39:53 PM PT</t>
+          <t>2026-07-11 08:41:53 PM PT</t>
         </is>
       </c>
       <c r="C58" t="n">
@@ -7281,7 +7281,7 @@
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>2026-07-11 08:39:53 PM PT</t>
+          <t>2026-07-11 08:41:53 PM PT</t>
         </is>
       </c>
       <c r="C59" t="n">
@@ -7395,7 +7395,7 @@
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>2026-07-11 08:39:53 PM PT</t>
+          <t>2026-07-11 08:41:53 PM PT</t>
         </is>
       </c>
       <c r="C60" t="n">
@@ -7509,7 +7509,7 @@
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>2026-07-11 08:39:53 PM PT</t>
+          <t>2026-07-11 08:41:53 PM PT</t>
         </is>
       </c>
       <c r="C61" t="n">
@@ -7623,7 +7623,7 @@
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>2026-07-11 08:39:53 PM PT</t>
+          <t>2026-07-11 08:41:53 PM PT</t>
         </is>
       </c>
       <c r="C62" t="n">
@@ -7737,7 +7737,7 @@
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>2026-07-11 08:39:52 PM PT</t>
+          <t>2026-07-11 08:41:52 PM PT</t>
         </is>
       </c>
       <c r="C63" t="n">
@@ -7851,7 +7851,7 @@
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>2026-07-11 08:39:52 PM PT</t>
+          <t>2026-07-11 08:41:52 PM PT</t>
         </is>
       </c>
       <c r="C64" t="n">
@@ -7965,7 +7965,7 @@
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>2026-07-11 08:39:54 PM PT</t>
+          <t>2026-07-11 08:41:54 PM PT</t>
         </is>
       </c>
       <c r="C65" t="n">
@@ -7978,7 +7978,7 @@
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>Bottom 8 | 2 out</t>
+          <t>Bottom 8 | 3 out</t>
         </is>
       </c>
       <c r="F65" t="n">
@@ -7990,13 +7990,13 @@
         </is>
       </c>
       <c r="H65" t="n">
+        <v>3</v>
+      </c>
+      <c r="I65" t="n">
+        <v>1</v>
+      </c>
+      <c r="J65" t="n">
         <v>2</v>
-      </c>
-      <c r="I65" t="n">
-        <v>4</v>
-      </c>
-      <c r="J65" t="n">
-        <v>0</v>
       </c>
       <c r="K65" t="inlineStr">
         <is>
@@ -8088,7 +8088,7 @@
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>2026-07-11 08:39:54 PM PT</t>
+          <t>2026-07-11 08:41:54 PM PT</t>
         </is>
       </c>
       <c r="C66" t="n">
@@ -8101,7 +8101,7 @@
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>Bottom 8 | 1 out</t>
+          <t>Bottom 8 | 2 out</t>
         </is>
       </c>
       <c r="F66" t="n">
@@ -8113,13 +8113,13 @@
         </is>
       </c>
       <c r="H66" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I66" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J66" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K66" t="inlineStr">
         <is>
@@ -8211,7 +8211,7 @@
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>2026-07-11 08:39:53 PM PT</t>
+          <t>2026-07-11 08:41:53 PM PT</t>
         </is>
       </c>
       <c r="C67" t="n">
@@ -8325,7 +8325,7 @@
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>2026-07-11 08:39:53 PM PT</t>
+          <t>2026-07-11 08:41:53 PM PT</t>
         </is>
       </c>
       <c r="C68" t="n">
@@ -8439,7 +8439,7 @@
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>2026-07-11 08:39:53 PM PT</t>
+          <t>2026-07-11 08:41:53 PM PT</t>
         </is>
       </c>
       <c r="C69" t="n">
@@ -8553,7 +8553,7 @@
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>2026-07-11 08:39:53 PM PT</t>
+          <t>2026-07-11 08:41:53 PM PT</t>
         </is>
       </c>
       <c r="C70" t="n">
@@ -8667,7 +8667,7 @@
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>2026-07-11 08:39:53 PM PT</t>
+          <t>2026-07-11 08:41:53 PM PT</t>
         </is>
       </c>
       <c r="C71" t="n">
@@ -8781,7 +8781,7 @@
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>2026-07-11 08:39:54 PM PT</t>
+          <t>2026-07-11 08:41:54 PM PT</t>
         </is>
       </c>
       <c r="C72" t="n">
@@ -8794,7 +8794,7 @@
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>Bottom 8 | 1 out</t>
+          <t>Bottom 8 | 2 out</t>
         </is>
       </c>
       <c r="F72" t="n">
@@ -8806,13 +8806,13 @@
         </is>
       </c>
       <c r="H72" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I72" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J72" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K72" t="inlineStr">
         <is>
@@ -8848,10 +8848,10 @@
         </is>
       </c>
       <c r="R72" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="S72" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="T72" t="n">
         <v>2</v>
@@ -8884,7 +8884,7 @@
         <v>0</v>
       </c>
       <c r="AD72" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AE72" s="4" t="n">
         <v>10</v>
@@ -8904,7 +8904,7 @@
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>2026-07-11 08:39:53 PM PT</t>
+          <t>2026-07-11 08:41:52 PM PT</t>
         </is>
       </c>
       <c r="C73" t="n">
@@ -9018,7 +9018,7 @@
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>2026-07-11 08:39:53 PM PT</t>
+          <t>2026-07-11 08:41:53 PM PT</t>
         </is>
       </c>
       <c r="C74" t="n">
@@ -9132,7 +9132,7 @@
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>2026-07-11 08:39:53 PM PT</t>
+          <t>2026-07-11 08:41:52 PM PT</t>
         </is>
       </c>
       <c r="C75" t="n">
@@ -9246,7 +9246,7 @@
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>2026-07-11 08:39:54 PM PT</t>
+          <t>2026-07-11 08:41:54 PM PT</t>
         </is>
       </c>
       <c r="C76" t="n">
@@ -9259,7 +9259,7 @@
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>Bottom 8 | 2 out</t>
+          <t>Bottom 8 | 3 out</t>
         </is>
       </c>
       <c r="F76" t="n">
@@ -9271,13 +9271,13 @@
         </is>
       </c>
       <c r="H76" t="n">
+        <v>3</v>
+      </c>
+      <c r="I76" t="n">
+        <v>1</v>
+      </c>
+      <c r="J76" t="n">
         <v>2</v>
-      </c>
-      <c r="I76" t="n">
-        <v>4</v>
-      </c>
-      <c r="J76" t="n">
-        <v>0</v>
       </c>
       <c r="K76" t="inlineStr">
         <is>
@@ -9369,7 +9369,7 @@
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>2026-07-11 08:39:54 PM PT</t>
+          <t>2026-07-11 08:41:54 PM PT</t>
         </is>
       </c>
       <c r="C77" t="n">
@@ -9382,7 +9382,7 @@
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>Bottom 8 | 2 out</t>
+          <t>Bottom 8 | 3 out</t>
         </is>
       </c>
       <c r="F77" t="n">
@@ -9394,13 +9394,13 @@
         </is>
       </c>
       <c r="H77" t="n">
+        <v>3</v>
+      </c>
+      <c r="I77" t="n">
+        <v>1</v>
+      </c>
+      <c r="J77" t="n">
         <v>2</v>
-      </c>
-      <c r="I77" t="n">
-        <v>4</v>
-      </c>
-      <c r="J77" t="n">
-        <v>0</v>
       </c>
       <c r="K77" t="inlineStr">
         <is>
@@ -9492,7 +9492,7 @@
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>2026-07-11 08:39:54 PM PT</t>
+          <t>2026-07-11 08:41:54 PM PT</t>
         </is>
       </c>
       <c r="C78" t="n">
@@ -9606,7 +9606,7 @@
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>2026-07-11 08:39:54 PM PT</t>
+          <t>2026-07-11 08:41:54 PM PT</t>
         </is>
       </c>
       <c r="C79" t="n">
@@ -9720,7 +9720,7 @@
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>2026-07-11 08:39:53 PM PT</t>
+          <t>2026-07-11 08:41:53 PM PT</t>
         </is>
       </c>
       <c r="C80" t="n">
@@ -9834,7 +9834,7 @@
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>2026-07-11 08:39:52 PM PT</t>
+          <t>2026-07-11 08:41:52 PM PT</t>
         </is>
       </c>
       <c r="C81" t="n">
@@ -9948,7 +9948,7 @@
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>2026-07-11 08:39:53 PM PT</t>
+          <t>2026-07-11 08:41:52 PM PT</t>
         </is>
       </c>
       <c r="C82" t="n">
@@ -10062,7 +10062,7 @@
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>2026-07-11 08:39:53 PM PT</t>
+          <t>2026-07-11 08:41:52 PM PT</t>
         </is>
       </c>
       <c r="C83" t="n">
@@ -10176,7 +10176,7 @@
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>2026-07-11 08:39:52 PM PT</t>
+          <t>2026-07-11 08:41:52 PM PT</t>
         </is>
       </c>
       <c r="C84" t="n">
@@ -10290,7 +10290,7 @@
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>2026-07-11 08:39:52 PM PT</t>
+          <t>2026-07-11 08:41:52 PM PT</t>
         </is>
       </c>
       <c r="C85" t="n">
@@ -10404,7 +10404,7 @@
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>2026-07-11 08:39:52 PM PT</t>
+          <t>2026-07-11 08:41:52 PM PT</t>
         </is>
       </c>
       <c r="C86" t="n">
@@ -10518,7 +10518,7 @@
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>2026-07-11 08:39:53 PM PT</t>
+          <t>2026-07-11 08:41:53 PM PT</t>
         </is>
       </c>
       <c r="C87" t="n">
@@ -10632,7 +10632,7 @@
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>2026-07-11 08:39:53 PM PT</t>
+          <t>2026-07-11 08:41:53 PM PT</t>
         </is>
       </c>
       <c r="C88" t="n">
@@ -10746,7 +10746,7 @@
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>2026-07-11 08:39:53 PM PT</t>
+          <t>2026-07-11 08:41:53 PM PT</t>
         </is>
       </c>
       <c r="C89" t="n">
@@ -10860,7 +10860,7 @@
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>2026-07-11 08:39:53 PM PT</t>
+          <t>2026-07-11 08:41:53 PM PT</t>
         </is>
       </c>
       <c r="C90" t="n">
@@ -10974,7 +10974,7 @@
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>2026-07-11 08:39:53 PM PT</t>
+          <t>2026-07-11 08:41:53 PM PT</t>
         </is>
       </c>
       <c r="C91" t="n">
@@ -11088,7 +11088,7 @@
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>2026-07-11 08:39:54 PM PT</t>
+          <t>2026-07-11 08:41:54 PM PT</t>
         </is>
       </c>
       <c r="C92" t="n">
@@ -11202,7 +11202,7 @@
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>2026-07-11 08:39:54 PM PT</t>
+          <t>2026-07-11 08:41:54 PM PT</t>
         </is>
       </c>
       <c r="C93" t="n">
@@ -11215,7 +11215,7 @@
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>Bottom 8 | 1 out</t>
+          <t>Bottom 8 | 2 out</t>
         </is>
       </c>
       <c r="F93" t="n">
@@ -11227,13 +11227,13 @@
         </is>
       </c>
       <c r="H93" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I93" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J93" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K93" t="inlineStr">
         <is>
@@ -11325,7 +11325,7 @@
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>2026-07-11 08:39:53 PM PT</t>
+          <t>2026-07-11 08:41:53 PM PT</t>
         </is>
       </c>
       <c r="C94" t="n">
@@ -11439,7 +11439,7 @@
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>2026-07-11 08:39:53 PM PT</t>
+          <t>2026-07-11 08:41:53 PM PT</t>
         </is>
       </c>
       <c r="C95" t="n">
@@ -11553,7 +11553,7 @@
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>2026-07-11 08:39:53 PM PT</t>
+          <t>2026-07-11 08:41:53 PM PT</t>
         </is>
       </c>
       <c r="C96" t="n">
@@ -11667,7 +11667,7 @@
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>2026-07-11 08:39:53 PM PT</t>
+          <t>2026-07-11 08:41:53 PM PT</t>
         </is>
       </c>
       <c r="C97" t="n">
@@ -11781,7 +11781,7 @@
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>2026-07-11 08:39:53 PM PT</t>
+          <t>2026-07-11 08:41:53 PM PT</t>
         </is>
       </c>
       <c r="C98" t="n">
@@ -11895,7 +11895,7 @@
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>2026-07-11 08:39:54 PM PT</t>
+          <t>2026-07-11 08:41:54 PM PT</t>
         </is>
       </c>
       <c r="C99" t="n">
@@ -11908,7 +11908,7 @@
       </c>
       <c r="E99" t="inlineStr">
         <is>
-          <t>Bottom 8 | 1 out</t>
+          <t>Bottom 8 | 2 out</t>
         </is>
       </c>
       <c r="F99" t="n">
@@ -11920,13 +11920,13 @@
         </is>
       </c>
       <c r="H99" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I99" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J99" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K99" t="inlineStr">
         <is>
@@ -12018,7 +12018,7 @@
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>2026-07-11 08:39:53 PM PT</t>
+          <t>2026-07-11 08:41:53 PM PT</t>
         </is>
       </c>
       <c r="C100" t="n">
@@ -12132,7 +12132,7 @@
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>2026-07-11 08:39:53 PM PT</t>
+          <t>2026-07-11 08:41:52 PM PT</t>
         </is>
       </c>
       <c r="C101" t="n">
@@ -12246,7 +12246,7 @@
       </c>
       <c r="B102" t="inlineStr">
         <is>
-          <t>2026-07-11 08:39:53 PM PT</t>
+          <t>2026-07-11 08:41:53 PM PT</t>
         </is>
       </c>
       <c r="C102" t="n">
@@ -12360,7 +12360,7 @@
       </c>
       <c r="B103" t="inlineStr">
         <is>
-          <t>2026-07-11 08:39:53 PM PT</t>
+          <t>2026-07-11 08:41:53 PM PT</t>
         </is>
       </c>
       <c r="C103" t="n">
@@ -12474,7 +12474,7 @@
       </c>
       <c r="B104" t="inlineStr">
         <is>
-          <t>2026-07-11 08:39:54 PM PT</t>
+          <t>2026-07-11 08:41:54 PM PT</t>
         </is>
       </c>
       <c r="C104" t="n">
@@ -12487,7 +12487,7 @@
       </c>
       <c r="E104" t="inlineStr">
         <is>
-          <t>Bottom 8 | 2 out</t>
+          <t>Bottom 8 | 3 out</t>
         </is>
       </c>
       <c r="F104" t="n">
@@ -12499,13 +12499,13 @@
         </is>
       </c>
       <c r="H104" t="n">
+        <v>3</v>
+      </c>
+      <c r="I104" t="n">
+        <v>1</v>
+      </c>
+      <c r="J104" t="n">
         <v>2</v>
-      </c>
-      <c r="I104" t="n">
-        <v>4</v>
-      </c>
-      <c r="J104" t="n">
-        <v>0</v>
       </c>
       <c r="K104" t="inlineStr">
         <is>
@@ -12597,7 +12597,7 @@
       </c>
       <c r="B105" t="inlineStr">
         <is>
-          <t>2026-07-11 08:39:53 PM PT</t>
+          <t>2026-07-11 08:41:53 PM PT</t>
         </is>
       </c>
       <c r="C105" t="n">
@@ -12711,7 +12711,7 @@
       </c>
       <c r="B106" t="inlineStr">
         <is>
-          <t>2026-07-11 08:39:53 PM PT</t>
+          <t>2026-07-11 08:41:53 PM PT</t>
         </is>
       </c>
       <c r="C106" t="n">
@@ -12825,7 +12825,7 @@
       </c>
       <c r="B107" t="inlineStr">
         <is>
-          <t>2026-07-11 08:39:53 PM PT</t>
+          <t>2026-07-11 08:41:53 PM PT</t>
         </is>
       </c>
       <c r="C107" t="n">
@@ -12939,7 +12939,7 @@
       </c>
       <c r="B108" t="inlineStr">
         <is>
-          <t>2026-07-11 08:39:53 PM PT</t>
+          <t>2026-07-11 08:41:53 PM PT</t>
         </is>
       </c>
       <c r="C108" t="n">
@@ -13053,7 +13053,7 @@
       </c>
       <c r="B109" t="inlineStr">
         <is>
-          <t>2026-07-11 08:39:53 PM PT</t>
+          <t>2026-07-11 08:41:53 PM PT</t>
         </is>
       </c>
       <c r="C109" t="n">
@@ -13167,7 +13167,7 @@
       </c>
       <c r="B110" t="inlineStr">
         <is>
-          <t>2026-07-11 08:39:53 PM PT</t>
+          <t>2026-07-11 08:41:53 PM PT</t>
         </is>
       </c>
       <c r="C110" t="n">
@@ -13281,7 +13281,7 @@
       </c>
       <c r="B111" t="inlineStr">
         <is>
-          <t>2026-07-11 08:39:53 PM PT</t>
+          <t>2026-07-11 08:41:53 PM PT</t>
         </is>
       </c>
       <c r="C111" t="n">
@@ -13395,7 +13395,7 @@
       </c>
       <c r="B112" t="inlineStr">
         <is>
-          <t>2026-07-11 08:39:54 PM PT</t>
+          <t>2026-07-11 08:41:54 PM PT</t>
         </is>
       </c>
       <c r="C112" t="n">
@@ -13509,7 +13509,7 @@
       </c>
       <c r="B113" t="inlineStr">
         <is>
-          <t>2026-07-11 08:39:53 PM PT</t>
+          <t>2026-07-11 08:41:53 PM PT</t>
         </is>
       </c>
       <c r="C113" t="n">
@@ -13623,7 +13623,7 @@
       </c>
       <c r="B114" t="inlineStr">
         <is>
-          <t>2026-07-11 08:39:53 PM PT</t>
+          <t>2026-07-11 08:41:53 PM PT</t>
         </is>
       </c>
       <c r="C114" t="n">
@@ -13737,7 +13737,7 @@
       </c>
       <c r="B115" t="inlineStr">
         <is>
-          <t>2026-07-11 08:39:53 PM PT</t>
+          <t>2026-07-11 08:41:53 PM PT</t>
         </is>
       </c>
       <c r="C115" t="n">
@@ -13851,7 +13851,7 @@
       </c>
       <c r="B116" t="inlineStr">
         <is>
-          <t>2026-07-11 08:39:54 PM PT</t>
+          <t>2026-07-11 08:41:54 PM PT</t>
         </is>
       </c>
       <c r="C116" t="n">
@@ -13864,7 +13864,7 @@
       </c>
       <c r="E116" t="inlineStr">
         <is>
-          <t>Bottom 8 | 2 out</t>
+          <t>Bottom 8 | 3 out</t>
         </is>
       </c>
       <c r="F116" t="n">
@@ -13876,13 +13876,13 @@
         </is>
       </c>
       <c r="H116" t="n">
+        <v>3</v>
+      </c>
+      <c r="I116" t="n">
+        <v>1</v>
+      </c>
+      <c r="J116" t="n">
         <v>2</v>
-      </c>
-      <c r="I116" t="n">
-        <v>4</v>
-      </c>
-      <c r="J116" t="n">
-        <v>0</v>
       </c>
       <c r="K116" t="inlineStr">
         <is>
@@ -13974,7 +13974,7 @@
       </c>
       <c r="B117" t="inlineStr">
         <is>
-          <t>2026-07-11 08:39:54 PM PT</t>
+          <t>2026-07-11 08:41:54 PM PT</t>
         </is>
       </c>
       <c r="C117" t="n">
@@ -13987,7 +13987,7 @@
       </c>
       <c r="E117" t="inlineStr">
         <is>
-          <t>Bottom 8 | 2 out</t>
+          <t>Bottom 8 | 3 out</t>
         </is>
       </c>
       <c r="F117" t="n">
@@ -13999,13 +13999,13 @@
         </is>
       </c>
       <c r="H117" t="n">
+        <v>3</v>
+      </c>
+      <c r="I117" t="n">
+        <v>1</v>
+      </c>
+      <c r="J117" t="n">
         <v>2</v>
-      </c>
-      <c r="I117" t="n">
-        <v>4</v>
-      </c>
-      <c r="J117" t="n">
-        <v>0</v>
       </c>
       <c r="K117" t="inlineStr">
         <is>
@@ -14097,7 +14097,7 @@
       </c>
       <c r="B118" t="inlineStr">
         <is>
-          <t>2026-07-11 08:39:53 PM PT</t>
+          <t>2026-07-11 08:41:53 PM PT</t>
         </is>
       </c>
       <c r="C118" t="n">
@@ -14211,7 +14211,7 @@
       </c>
       <c r="B119" t="inlineStr">
         <is>
-          <t>2026-07-11 08:39:54 PM PT</t>
+          <t>2026-07-11 08:41:54 PM PT</t>
         </is>
       </c>
       <c r="C119" t="n">
@@ -14325,7 +14325,7 @@
       </c>
       <c r="B120" t="inlineStr">
         <is>
-          <t>2026-07-11 08:39:54 PM PT</t>
+          <t>2026-07-11 08:41:54 PM PT</t>
         </is>
       </c>
       <c r="C120" t="n">
@@ -14439,7 +14439,7 @@
       </c>
       <c r="B121" t="inlineStr">
         <is>
-          <t>2026-07-11 08:39:53 PM PT</t>
+          <t>2026-07-11 08:41:53 PM PT</t>
         </is>
       </c>
       <c r="C121" t="n">
@@ -14553,7 +14553,7 @@
       </c>
       <c r="B122" t="inlineStr">
         <is>
-          <t>2026-07-11 08:39:53 PM PT</t>
+          <t>2026-07-11 08:41:53 PM PT</t>
         </is>
       </c>
       <c r="C122" t="n">
@@ -14667,7 +14667,7 @@
       </c>
       <c r="B123" t="inlineStr">
         <is>
-          <t>2026-07-11 08:39:54 PM PT</t>
+          <t>2026-07-11 08:41:54 PM PT</t>
         </is>
       </c>
       <c r="C123" t="n">
@@ -14781,7 +14781,7 @@
       </c>
       <c r="B124" t="inlineStr">
         <is>
-          <t>2026-07-11 08:39:53 PM PT</t>
+          <t>2026-07-11 08:41:53 PM PT</t>
         </is>
       </c>
       <c r="C124" t="n">
@@ -14895,7 +14895,7 @@
       </c>
       <c r="B125" t="inlineStr">
         <is>
-          <t>2026-07-11 08:39:53 PM PT</t>
+          <t>2026-07-11 08:41:53 PM PT</t>
         </is>
       </c>
       <c r="C125" t="n">
@@ -15009,7 +15009,7 @@
       </c>
       <c r="B126" t="inlineStr">
         <is>
-          <t>2026-07-11 08:39:53 PM PT</t>
+          <t>2026-07-11 08:41:53 PM PT</t>
         </is>
       </c>
       <c r="C126" t="n">
@@ -15123,7 +15123,7 @@
       </c>
       <c r="B127" t="inlineStr">
         <is>
-          <t>2026-07-11 08:39:53 PM PT</t>
+          <t>2026-07-11 08:41:53 PM PT</t>
         </is>
       </c>
       <c r="C127" t="n">
@@ -15237,7 +15237,7 @@
       </c>
       <c r="B128" t="inlineStr">
         <is>
-          <t>2026-07-11 08:39:53 PM PT</t>
+          <t>2026-07-11 08:41:53 PM PT</t>
         </is>
       </c>
       <c r="C128" t="n">
@@ -15351,7 +15351,7 @@
       </c>
       <c r="B129" t="inlineStr">
         <is>
-          <t>2026-07-11 08:39:53 PM PT</t>
+          <t>2026-07-11 08:41:53 PM PT</t>
         </is>
       </c>
       <c r="C129" t="n">
@@ -15465,7 +15465,7 @@
       </c>
       <c r="B130" t="inlineStr">
         <is>
-          <t>2026-07-11 08:39:54 PM PT</t>
+          <t>2026-07-11 08:41:54 PM PT</t>
         </is>
       </c>
       <c r="C130" t="n">
@@ -15478,7 +15478,7 @@
       </c>
       <c r="E130" t="inlineStr">
         <is>
-          <t>Bottom 8 | 1 out</t>
+          <t>Bottom 8 | 2 out</t>
         </is>
       </c>
       <c r="F130" t="n">
@@ -15490,13 +15490,13 @@
         </is>
       </c>
       <c r="H130" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I130" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J130" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K130" t="inlineStr">
         <is>
@@ -15588,7 +15588,7 @@
       </c>
       <c r="B131" t="inlineStr">
         <is>
-          <t>2026-07-11 08:39:53 PM PT</t>
+          <t>2026-07-11 08:41:53 PM PT</t>
         </is>
       </c>
       <c r="C131" t="n">
@@ -15702,7 +15702,7 @@
       </c>
       <c r="B132" t="inlineStr">
         <is>
-          <t>2026-07-11 08:39:53 PM PT</t>
+          <t>2026-07-11 08:41:53 PM PT</t>
         </is>
       </c>
       <c r="C132" t="n">
@@ -15816,7 +15816,7 @@
       </c>
       <c r="B133" t="inlineStr">
         <is>
-          <t>2026-07-11 08:39:53 PM PT</t>
+          <t>2026-07-11 08:41:52 PM PT</t>
         </is>
       </c>
       <c r="C133" t="n">
@@ -15930,7 +15930,7 @@
       </c>
       <c r="B134" t="inlineStr">
         <is>
-          <t>2026-07-11 08:39:53 PM PT</t>
+          <t>2026-07-11 08:41:53 PM PT</t>
         </is>
       </c>
       <c r="C134" t="n">
@@ -16044,7 +16044,7 @@
       </c>
       <c r="B135" t="inlineStr">
         <is>
-          <t>2026-07-11 08:39:53 PM PT</t>
+          <t>2026-07-11 08:41:53 PM PT</t>
         </is>
       </c>
       <c r="C135" t="n">
@@ -16158,7 +16158,7 @@
       </c>
       <c r="B136" t="inlineStr">
         <is>
-          <t>2026-07-11 08:39:53 PM PT</t>
+          <t>2026-07-11 08:41:53 PM PT</t>
         </is>
       </c>
       <c r="C136" t="n">
@@ -16272,7 +16272,7 @@
       </c>
       <c r="B137" t="inlineStr">
         <is>
-          <t>2026-07-11 08:39:52 PM PT</t>
+          <t>2026-07-11 08:41:52 PM PT</t>
         </is>
       </c>
       <c r="C137" t="n">
@@ -16386,7 +16386,7 @@
       </c>
       <c r="B138" t="inlineStr">
         <is>
-          <t>2026-07-11 08:39:52 PM PT</t>
+          <t>2026-07-11 08:41:52 PM PT</t>
         </is>
       </c>
       <c r="C138" t="n">
@@ -16500,7 +16500,7 @@
       </c>
       <c r="B139" t="inlineStr">
         <is>
-          <t>2026-07-11 08:39:53 PM PT</t>
+          <t>2026-07-11 08:41:53 PM PT</t>
         </is>
       </c>
       <c r="C139" t="n">
@@ -16614,7 +16614,7 @@
       </c>
       <c r="B140" t="inlineStr">
         <is>
-          <t>2026-07-11 08:39:53 PM PT</t>
+          <t>2026-07-11 08:41:53 PM PT</t>
         </is>
       </c>
       <c r="C140" t="n">
@@ -16728,7 +16728,7 @@
       </c>
       <c r="B141" t="inlineStr">
         <is>
-          <t>2026-07-11 08:39:53 PM PT</t>
+          <t>2026-07-11 08:41:53 PM PT</t>
         </is>
       </c>
       <c r="C141" t="n">
@@ -16842,7 +16842,7 @@
       </c>
       <c r="B142" t="inlineStr">
         <is>
-          <t>2026-07-11 08:39:54 PM PT</t>
+          <t>2026-07-11 08:41:54 PM PT</t>
         </is>
       </c>
       <c r="C142" t="n">
@@ -16956,7 +16956,7 @@
       </c>
       <c r="B143" t="inlineStr">
         <is>
-          <t>2026-07-11 08:39:54 PM PT</t>
+          <t>2026-07-11 08:41:54 PM PT</t>
         </is>
       </c>
       <c r="C143" t="n">
@@ -17070,7 +17070,7 @@
       </c>
       <c r="B144" t="inlineStr">
         <is>
-          <t>2026-07-11 08:39:54 PM PT</t>
+          <t>2026-07-11 08:41:54 PM PT</t>
         </is>
       </c>
       <c r="C144" t="n">
@@ -17184,7 +17184,7 @@
       </c>
       <c r="B145" t="inlineStr">
         <is>
-          <t>2026-07-11 08:39:53 PM PT</t>
+          <t>2026-07-11 08:41:53 PM PT</t>
         </is>
       </c>
       <c r="C145" t="n">
@@ -17298,7 +17298,7 @@
       </c>
       <c r="B146" t="inlineStr">
         <is>
-          <t>2026-07-11 08:39:53 PM PT</t>
+          <t>2026-07-11 08:41:53 PM PT</t>
         </is>
       </c>
       <c r="C146" t="n">
@@ -17412,7 +17412,7 @@
       </c>
       <c r="B147" t="inlineStr">
         <is>
-          <t>2026-07-11 08:39:53 PM PT</t>
+          <t>2026-07-11 08:41:53 PM PT</t>
         </is>
       </c>
       <c r="C147" t="n">
@@ -17526,7 +17526,7 @@
       </c>
       <c r="B148" t="inlineStr">
         <is>
-          <t>2026-07-11 08:39:54 PM PT</t>
+          <t>2026-07-11 08:41:54 PM PT</t>
         </is>
       </c>
       <c r="C148" t="n">
@@ -17640,7 +17640,7 @@
       </c>
       <c r="B149" t="inlineStr">
         <is>
-          <t>2026-07-11 08:39:53 PM PT</t>
+          <t>2026-07-11 08:41:53 PM PT</t>
         </is>
       </c>
       <c r="C149" t="n">
@@ -17754,7 +17754,7 @@
       </c>
       <c r="B150" t="inlineStr">
         <is>
-          <t>2026-07-11 08:39:53 PM PT</t>
+          <t>2026-07-11 08:41:53 PM PT</t>
         </is>
       </c>
       <c r="C150" t="n">
@@ -17868,7 +17868,7 @@
       </c>
       <c r="B151" t="inlineStr">
         <is>
-          <t>2026-07-11 08:39:52 PM PT</t>
+          <t>2026-07-11 08:41:52 PM PT</t>
         </is>
       </c>
       <c r="C151" t="n">
@@ -17982,7 +17982,7 @@
       </c>
       <c r="B152" t="inlineStr">
         <is>
-          <t>2026-07-11 08:39:53 PM PT</t>
+          <t>2026-07-11 08:41:52 PM PT</t>
         </is>
       </c>
       <c r="C152" t="n">
@@ -18096,7 +18096,7 @@
       </c>
       <c r="B153" t="inlineStr">
         <is>
-          <t>2026-07-11 08:39:53 PM PT</t>
+          <t>2026-07-11 08:41:53 PM PT</t>
         </is>
       </c>
       <c r="C153" t="n">
@@ -18210,7 +18210,7 @@
       </c>
       <c r="B154" t="inlineStr">
         <is>
-          <t>2026-07-11 08:39:53 PM PT</t>
+          <t>2026-07-11 08:41:53 PM PT</t>
         </is>
       </c>
       <c r="C154" t="n">
@@ -18324,7 +18324,7 @@
       </c>
       <c r="B155" t="inlineStr">
         <is>
-          <t>2026-07-11 08:39:53 PM PT</t>
+          <t>2026-07-11 08:41:53 PM PT</t>
         </is>
       </c>
       <c r="C155" t="n">
@@ -18438,7 +18438,7 @@
       </c>
       <c r="B156" t="inlineStr">
         <is>
-          <t>2026-07-11 08:39:52 PM PT</t>
+          <t>2026-07-11 08:41:52 PM PT</t>
         </is>
       </c>
       <c r="C156" t="n">
@@ -18552,7 +18552,7 @@
       </c>
       <c r="B157" t="inlineStr">
         <is>
-          <t>2026-07-11 08:39:54 PM PT</t>
+          <t>2026-07-11 08:41:54 PM PT</t>
         </is>
       </c>
       <c r="C157" t="n">
@@ -18565,7 +18565,7 @@
       </c>
       <c r="E157" t="inlineStr">
         <is>
-          <t>Bottom 8 | 2 out</t>
+          <t>Bottom 8 | 3 out</t>
         </is>
       </c>
       <c r="F157" t="n">
@@ -18577,13 +18577,13 @@
         </is>
       </c>
       <c r="H157" t="n">
+        <v>3</v>
+      </c>
+      <c r="I157" t="n">
+        <v>1</v>
+      </c>
+      <c r="J157" t="n">
         <v>2</v>
-      </c>
-      <c r="I157" t="n">
-        <v>4</v>
-      </c>
-      <c r="J157" t="n">
-        <v>0</v>
       </c>
       <c r="K157" t="inlineStr">
         <is>
@@ -18675,7 +18675,7 @@
       </c>
       <c r="B158" t="inlineStr">
         <is>
-          <t>2026-07-11 08:39:54 PM PT</t>
+          <t>2026-07-11 08:41:54 PM PT</t>
         </is>
       </c>
       <c r="C158" t="n">
@@ -18688,7 +18688,7 @@
       </c>
       <c r="E158" t="inlineStr">
         <is>
-          <t>Bottom 8 | 2 out</t>
+          <t>Bottom 8 | 3 out</t>
         </is>
       </c>
       <c r="F158" t="n">
@@ -18700,13 +18700,13 @@
         </is>
       </c>
       <c r="H158" t="n">
+        <v>3</v>
+      </c>
+      <c r="I158" t="n">
+        <v>1</v>
+      </c>
+      <c r="J158" t="n">
         <v>2</v>
-      </c>
-      <c r="I158" t="n">
-        <v>4</v>
-      </c>
-      <c r="J158" t="n">
-        <v>0</v>
       </c>
       <c r="K158" t="inlineStr">
         <is>
@@ -18798,7 +18798,7 @@
       </c>
       <c r="B159" t="inlineStr">
         <is>
-          <t>2026-07-11 08:39:54 PM PT</t>
+          <t>2026-07-11 08:41:54 PM PT</t>
         </is>
       </c>
       <c r="C159" t="n">
@@ -18811,7 +18811,7 @@
       </c>
       <c r="E159" t="inlineStr">
         <is>
-          <t>Bottom 8 | 2 out</t>
+          <t>Bottom 8 | 3 out</t>
         </is>
       </c>
       <c r="F159" t="n">
@@ -18823,13 +18823,13 @@
         </is>
       </c>
       <c r="H159" t="n">
+        <v>3</v>
+      </c>
+      <c r="I159" t="n">
+        <v>1</v>
+      </c>
+      <c r="J159" t="n">
         <v>2</v>
-      </c>
-      <c r="I159" t="n">
-        <v>4</v>
-      </c>
-      <c r="J159" t="n">
-        <v>0</v>
       </c>
       <c r="K159" t="inlineStr">
         <is>
@@ -18921,7 +18921,7 @@
       </c>
       <c r="B160" t="inlineStr">
         <is>
-          <t>2026-07-11 08:39:54 PM PT</t>
+          <t>2026-07-11 08:41:54 PM PT</t>
         </is>
       </c>
       <c r="C160" t="n">
@@ -19035,7 +19035,7 @@
       </c>
       <c r="B161" t="inlineStr">
         <is>
-          <t>2026-07-11 08:39:54 PM PT</t>
+          <t>2026-07-11 08:41:54 PM PT</t>
         </is>
       </c>
       <c r="C161" t="n">
@@ -19149,7 +19149,7 @@
       </c>
       <c r="B162" t="inlineStr">
         <is>
-          <t>2026-07-11 08:39:54 PM PT</t>
+          <t>2026-07-11 08:41:54 PM PT</t>
         </is>
       </c>
       <c r="C162" t="n">
@@ -19263,7 +19263,7 @@
       </c>
       <c r="B163" t="inlineStr">
         <is>
-          <t>2026-07-11 08:39:54 PM PT</t>
+          <t>2026-07-11 08:41:54 PM PT</t>
         </is>
       </c>
       <c r="C163" t="n">
@@ -19377,7 +19377,7 @@
       </c>
       <c r="B164" t="inlineStr">
         <is>
-          <t>2026-07-11 08:39:54 PM PT</t>
+          <t>2026-07-11 08:41:54 PM PT</t>
         </is>
       </c>
       <c r="C164" t="n">
@@ -19491,7 +19491,7 @@
       </c>
       <c r="B165" t="inlineStr">
         <is>
-          <t>2026-07-11 08:39:53 PM PT</t>
+          <t>2026-07-11 08:41:53 PM PT</t>
         </is>
       </c>
       <c r="C165" t="n">
@@ -19605,7 +19605,7 @@
       </c>
       <c r="B166" t="inlineStr">
         <is>
-          <t>2026-07-11 08:39:53 PM PT</t>
+          <t>2026-07-11 08:41:53 PM PT</t>
         </is>
       </c>
       <c r="C166" t="n">
@@ -19719,7 +19719,7 @@
       </c>
       <c r="B167" t="inlineStr">
         <is>
-          <t>2026-07-11 08:39:53 PM PT</t>
+          <t>2026-07-11 08:41:53 PM PT</t>
         </is>
       </c>
       <c r="C167" t="n">
@@ -19833,7 +19833,7 @@
       </c>
       <c r="B168" t="inlineStr">
         <is>
-          <t>2026-07-11 08:39:53 PM PT</t>
+          <t>2026-07-11 08:41:53 PM PT</t>
         </is>
       </c>
       <c r="C168" t="n">
@@ -19947,7 +19947,7 @@
       </c>
       <c r="B169" t="inlineStr">
         <is>
-          <t>2026-07-11 08:39:53 PM PT</t>
+          <t>2026-07-11 08:41:53 PM PT</t>
         </is>
       </c>
       <c r="C169" t="n">
@@ -20061,7 +20061,7 @@
       </c>
       <c r="B170" t="inlineStr">
         <is>
-          <t>2026-07-11 08:39:53 PM PT</t>
+          <t>2026-07-11 08:41:53 PM PT</t>
         </is>
       </c>
       <c r="C170" t="n">
@@ -20175,7 +20175,7 @@
       </c>
       <c r="B171" t="inlineStr">
         <is>
-          <t>2026-07-11 08:39:54 PM PT</t>
+          <t>2026-07-11 08:41:54 PM PT</t>
         </is>
       </c>
       <c r="C171" t="n">
@@ -20188,7 +20188,7 @@
       </c>
       <c r="E171" t="inlineStr">
         <is>
-          <t>Bottom 8 | 1 out</t>
+          <t>Bottom 8 | 2 out</t>
         </is>
       </c>
       <c r="F171" t="n">
@@ -20200,13 +20200,13 @@
         </is>
       </c>
       <c r="H171" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I171" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J171" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K171" t="inlineStr">
         <is>
@@ -20298,7 +20298,7 @@
       </c>
       <c r="B172" t="inlineStr">
         <is>
-          <t>2026-07-11 08:39:54 PM PT</t>
+          <t>2026-07-11 08:41:54 PM PT</t>
         </is>
       </c>
       <c r="C172" t="n">
@@ -20311,7 +20311,7 @@
       </c>
       <c r="E172" t="inlineStr">
         <is>
-          <t>Bottom 8 | 1 out</t>
+          <t>Bottom 8 | 2 out</t>
         </is>
       </c>
       <c r="F172" t="n">
@@ -20323,13 +20323,13 @@
         </is>
       </c>
       <c r="H172" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I172" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J172" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K172" t="inlineStr">
         <is>
@@ -20421,7 +20421,7 @@
       </c>
       <c r="B173" t="inlineStr">
         <is>
-          <t>2026-07-11 08:39:53 PM PT</t>
+          <t>2026-07-11 08:41:53 PM PT</t>
         </is>
       </c>
       <c r="C173" t="n">
@@ -20535,7 +20535,7 @@
       </c>
       <c r="B174" t="inlineStr">
         <is>
-          <t>2026-07-11 08:39:53 PM PT</t>
+          <t>2026-07-11 08:41:53 PM PT</t>
         </is>
       </c>
       <c r="C174" t="n">
@@ -20649,7 +20649,7 @@
       </c>
       <c r="B175" t="inlineStr">
         <is>
-          <t>2026-07-11 08:39:52 PM PT</t>
+          <t>2026-07-11 08:41:52 PM PT</t>
         </is>
       </c>
       <c r="C175" t="n">
@@ -20763,7 +20763,7 @@
       </c>
       <c r="B176" t="inlineStr">
         <is>
-          <t>2026-07-11 08:39:53 PM PT</t>
+          <t>2026-07-11 08:41:52 PM PT</t>
         </is>
       </c>
       <c r="C176" t="n">
@@ -20877,7 +20877,7 @@
       </c>
       <c r="B177" t="inlineStr">
         <is>
-          <t>2026-07-11 08:39:53 PM PT</t>
+          <t>2026-07-11 08:41:53 PM PT</t>
         </is>
       </c>
       <c r="C177" t="n">
@@ -20991,7 +20991,7 @@
       </c>
       <c r="B178" t="inlineStr">
         <is>
-          <t>2026-07-11 08:39:53 PM PT</t>
+          <t>2026-07-11 08:41:53 PM PT</t>
         </is>
       </c>
       <c r="C178" t="n">
@@ -21105,7 +21105,7 @@
       </c>
       <c r="B179" t="inlineStr">
         <is>
-          <t>2026-07-11 08:39:53 PM PT</t>
+          <t>2026-07-11 08:41:53 PM PT</t>
         </is>
       </c>
       <c r="C179" t="n">
@@ -21219,7 +21219,7 @@
       </c>
       <c r="B180" t="inlineStr">
         <is>
-          <t>2026-07-11 08:39:53 PM PT</t>
+          <t>2026-07-11 08:41:53 PM PT</t>
         </is>
       </c>
       <c r="C180" t="n">
@@ -21333,7 +21333,7 @@
       </c>
       <c r="B181" t="inlineStr">
         <is>
-          <t>2026-07-11 08:39:53 PM PT</t>
+          <t>2026-07-11 08:41:53 PM PT</t>
         </is>
       </c>
       <c r="C181" t="n">
@@ -21447,7 +21447,7 @@
       </c>
       <c r="B182" t="inlineStr">
         <is>
-          <t>2026-07-11 08:39:53 PM PT</t>
+          <t>2026-07-11 08:41:53 PM PT</t>
         </is>
       </c>
       <c r="C182" t="n">
@@ -21561,7 +21561,7 @@
       </c>
       <c r="B183" t="inlineStr">
         <is>
-          <t>2026-07-11 08:39:53 PM PT</t>
+          <t>2026-07-11 08:41:53 PM PT</t>
         </is>
       </c>
       <c r="C183" t="n">
@@ -21675,7 +21675,7 @@
       </c>
       <c r="B184" t="inlineStr">
         <is>
-          <t>2026-07-11 08:39:53 PM PT</t>
+          <t>2026-07-11 08:41:52 PM PT</t>
         </is>
       </c>
       <c r="C184" t="n">
@@ -21789,7 +21789,7 @@
       </c>
       <c r="B185" t="inlineStr">
         <is>
-          <t>2026-07-11 08:39:53 PM PT</t>
+          <t>2026-07-11 08:41:52 PM PT</t>
         </is>
       </c>
       <c r="C185" t="n">
@@ -21903,7 +21903,7 @@
       </c>
       <c r="B186" t="inlineStr">
         <is>
-          <t>2026-07-11 08:39:53 PM PT</t>
+          <t>2026-07-11 08:41:53 PM PT</t>
         </is>
       </c>
       <c r="C186" t="n">
@@ -22017,7 +22017,7 @@
       </c>
       <c r="B187" t="inlineStr">
         <is>
-          <t>2026-07-11 08:39:53 PM PT</t>
+          <t>2026-07-11 08:41:53 PM PT</t>
         </is>
       </c>
       <c r="C187" t="n">
@@ -22131,7 +22131,7 @@
       </c>
       <c r="B188" t="inlineStr">
         <is>
-          <t>2026-07-11 08:39:53 PM PT</t>
+          <t>2026-07-11 08:41:53 PM PT</t>
         </is>
       </c>
       <c r="C188" t="n">
@@ -22245,7 +22245,7 @@
       </c>
       <c r="B189" t="inlineStr">
         <is>
-          <t>2026-07-11 08:39:53 PM PT</t>
+          <t>2026-07-11 08:41:53 PM PT</t>
         </is>
       </c>
       <c r="C189" t="n">
@@ -22359,7 +22359,7 @@
       </c>
       <c r="B190" t="inlineStr">
         <is>
-          <t>2026-07-11 08:39:54 PM PT</t>
+          <t>2026-07-11 08:41:54 PM PT</t>
         </is>
       </c>
       <c r="C190" t="n">
@@ -22372,7 +22372,7 @@
       </c>
       <c r="E190" t="inlineStr">
         <is>
-          <t>Bottom 8 | 2 out</t>
+          <t>Bottom 8 | 3 out</t>
         </is>
       </c>
       <c r="F190" t="n">
@@ -22384,13 +22384,13 @@
         </is>
       </c>
       <c r="H190" t="n">
+        <v>3</v>
+      </c>
+      <c r="I190" t="n">
+        <v>1</v>
+      </c>
+      <c r="J190" t="n">
         <v>2</v>
-      </c>
-      <c r="I190" t="n">
-        <v>4</v>
-      </c>
-      <c r="J190" t="n">
-        <v>0</v>
       </c>
       <c r="K190" t="inlineStr">
         <is>
@@ -22482,7 +22482,7 @@
       </c>
       <c r="B191" t="inlineStr">
         <is>
-          <t>2026-07-11 08:39:53 PM PT</t>
+          <t>2026-07-11 08:41:53 PM PT</t>
         </is>
       </c>
       <c r="C191" t="n">
@@ -22596,7 +22596,7 @@
       </c>
       <c r="B192" t="inlineStr">
         <is>
-          <t>2026-07-11 08:39:53 PM PT</t>
+          <t>2026-07-11 08:41:53 PM PT</t>
         </is>
       </c>
       <c r="C192" t="n">
@@ -22710,7 +22710,7 @@
       </c>
       <c r="B193" t="inlineStr">
         <is>
-          <t>2026-07-11 08:39:54 PM PT</t>
+          <t>2026-07-11 08:41:54 PM PT</t>
         </is>
       </c>
       <c r="C193" t="n">
@@ -22723,7 +22723,7 @@
       </c>
       <c r="E193" t="inlineStr">
         <is>
-          <t>Bottom 8 | 1 out</t>
+          <t>Bottom 8 | 2 out</t>
         </is>
       </c>
       <c r="F193" t="n">
@@ -22735,13 +22735,13 @@
         </is>
       </c>
       <c r="H193" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I193" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J193" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K193" t="inlineStr">
         <is>
@@ -22833,7 +22833,7 @@
       </c>
       <c r="B194" t="inlineStr">
         <is>
-          <t>2026-07-11 08:39:54 PM PT</t>
+          <t>2026-07-11 08:41:54 PM PT</t>
         </is>
       </c>
       <c r="C194" t="n">
@@ -22846,7 +22846,7 @@
       </c>
       <c r="E194" t="inlineStr">
         <is>
-          <t>Bottom 8 | 1 out</t>
+          <t>Bottom 8 | 2 out</t>
         </is>
       </c>
       <c r="F194" t="n">
@@ -22858,13 +22858,13 @@
         </is>
       </c>
       <c r="H194" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I194" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J194" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K194" t="inlineStr">
         <is>
@@ -22956,7 +22956,7 @@
       </c>
       <c r="B195" t="inlineStr">
         <is>
-          <t>2026-07-11 08:39:53 PM PT</t>
+          <t>2026-07-11 08:41:53 PM PT</t>
         </is>
       </c>
       <c r="C195" t="n">
@@ -23070,7 +23070,7 @@
       </c>
       <c r="B196" t="inlineStr">
         <is>
-          <t>2026-07-11 08:39:54 PM PT</t>
+          <t>2026-07-11 08:41:54 PM PT</t>
         </is>
       </c>
       <c r="C196" t="n">
@@ -23184,7 +23184,7 @@
       </c>
       <c r="B197" t="inlineStr">
         <is>
-          <t>2026-07-11 08:39:54 PM PT</t>
+          <t>2026-07-11 08:41:54 PM PT</t>
         </is>
       </c>
       <c r="C197" t="n">
@@ -23298,7 +23298,7 @@
       </c>
       <c r="B198" t="inlineStr">
         <is>
-          <t>2026-07-11 08:39:53 PM PT</t>
+          <t>2026-07-11 08:41:53 PM PT</t>
         </is>
       </c>
       <c r="C198" t="n">
@@ -23412,7 +23412,7 @@
       </c>
       <c r="B199" t="inlineStr">
         <is>
-          <t>2026-07-11 08:39:53 PM PT</t>
+          <t>2026-07-11 08:41:53 PM PT</t>
         </is>
       </c>
       <c r="C199" t="n">
@@ -23526,7 +23526,7 @@
       </c>
       <c r="B200" t="inlineStr">
         <is>
-          <t>2026-07-11 08:39:53 PM PT</t>
+          <t>2026-07-11 08:41:53 PM PT</t>
         </is>
       </c>
       <c r="C200" t="n">
@@ -23640,7 +23640,7 @@
       </c>
       <c r="B201" t="inlineStr">
         <is>
-          <t>2026-07-11 08:39:53 PM PT</t>
+          <t>2026-07-11 08:41:53 PM PT</t>
         </is>
       </c>
       <c r="C201" t="n">
@@ -23754,7 +23754,7 @@
       </c>
       <c r="B202" t="inlineStr">
         <is>
-          <t>2026-07-11 08:39:54 PM PT</t>
+          <t>2026-07-11 08:41:54 PM PT</t>
         </is>
       </c>
       <c r="C202" t="n">
@@ -23868,7 +23868,7 @@
       </c>
       <c r="B203" t="inlineStr">
         <is>
-          <t>2026-07-11 08:39:53 PM PT</t>
+          <t>2026-07-11 08:41:53 PM PT</t>
         </is>
       </c>
       <c r="C203" t="n">
@@ -23982,7 +23982,7 @@
       </c>
       <c r="B204" t="inlineStr">
         <is>
-          <t>2026-07-11 08:39:53 PM PT</t>
+          <t>2026-07-11 08:41:53 PM PT</t>
         </is>
       </c>
       <c r="C204" t="n">
@@ -24096,7 +24096,7 @@
       </c>
       <c r="B205" t="inlineStr">
         <is>
-          <t>2026-07-11 08:39:53 PM PT</t>
+          <t>2026-07-11 08:41:53 PM PT</t>
         </is>
       </c>
       <c r="C205" t="n">
@@ -24210,7 +24210,7 @@
       </c>
       <c r="B206" t="inlineStr">
         <is>
-          <t>2026-07-11 08:39:53 PM PT</t>
+          <t>2026-07-11 08:41:53 PM PT</t>
         </is>
       </c>
       <c r="C206" t="n">
@@ -24324,7 +24324,7 @@
       </c>
       <c r="B207" t="inlineStr">
         <is>
-          <t>2026-07-11 08:39:53 PM PT</t>
+          <t>2026-07-11 08:41:53 PM PT</t>
         </is>
       </c>
       <c r="C207" t="n">
@@ -24438,7 +24438,7 @@
       </c>
       <c r="B208" t="inlineStr">
         <is>
-          <t>2026-07-11 08:39:53 PM PT</t>
+          <t>2026-07-11 08:41:53 PM PT</t>
         </is>
       </c>
       <c r="C208" t="n">
@@ -24552,7 +24552,7 @@
       </c>
       <c r="B209" t="inlineStr">
         <is>
-          <t>2026-07-11 08:39:53 PM PT</t>
+          <t>2026-07-11 08:41:53 PM PT</t>
         </is>
       </c>
       <c r="C209" t="n">
@@ -24666,7 +24666,7 @@
       </c>
       <c r="B210" t="inlineStr">
         <is>
-          <t>2026-07-11 08:39:53 PM PT</t>
+          <t>2026-07-11 08:41:53 PM PT</t>
         </is>
       </c>
       <c r="C210" t="n">
@@ -24780,7 +24780,7 @@
       </c>
       <c r="B211" t="inlineStr">
         <is>
-          <t>2026-07-11 08:39:53 PM PT</t>
+          <t>2026-07-11 08:41:53 PM PT</t>
         </is>
       </c>
       <c r="C211" t="n">
@@ -24894,7 +24894,7 @@
       </c>
       <c r="B212" t="inlineStr">
         <is>
-          <t>2026-07-11 08:39:53 PM PT</t>
+          <t>2026-07-11 08:41:53 PM PT</t>
         </is>
       </c>
       <c r="C212" t="n">
@@ -25008,7 +25008,7 @@
       </c>
       <c r="B213" t="inlineStr">
         <is>
-          <t>2026-07-11 08:39:53 PM PT</t>
+          <t>2026-07-11 08:41:53 PM PT</t>
         </is>
       </c>
       <c r="C213" t="n">
@@ -25122,7 +25122,7 @@
       </c>
       <c r="B214" t="inlineStr">
         <is>
-          <t>2026-07-11 08:39:53 PM PT</t>
+          <t>2026-07-11 08:41:53 PM PT</t>
         </is>
       </c>
       <c r="C214" t="n">
@@ -25236,7 +25236,7 @@
       </c>
       <c r="B215" t="inlineStr">
         <is>
-          <t>2026-07-11 08:39:53 PM PT</t>
+          <t>2026-07-11 08:41:53 PM PT</t>
         </is>
       </c>
       <c r="C215" t="n">
@@ -25350,7 +25350,7 @@
       </c>
       <c r="B216" t="inlineStr">
         <is>
-          <t>2026-07-11 08:39:53 PM PT</t>
+          <t>2026-07-11 08:41:53 PM PT</t>
         </is>
       </c>
       <c r="C216" t="n">
@@ -25464,7 +25464,7 @@
       </c>
       <c r="B217" t="inlineStr">
         <is>
-          <t>2026-07-11 08:39:53 PM PT</t>
+          <t>2026-07-11 08:41:53 PM PT</t>
         </is>
       </c>
       <c r="C217" t="n">
@@ -25578,7 +25578,7 @@
       </c>
       <c r="B218" t="inlineStr">
         <is>
-          <t>2026-07-11 08:39:53 PM PT</t>
+          <t>2026-07-11 08:41:53 PM PT</t>
         </is>
       </c>
       <c r="C218" t="n">
@@ -25692,7 +25692,7 @@
       </c>
       <c r="B219" t="inlineStr">
         <is>
-          <t>2026-07-11 08:39:53 PM PT</t>
+          <t>2026-07-11 08:41:53 PM PT</t>
         </is>
       </c>
       <c r="C219" t="n">
@@ -25806,7 +25806,7 @@
       </c>
       <c r="B220" t="inlineStr">
         <is>
-          <t>2026-07-11 08:39:53 PM PT</t>
+          <t>2026-07-11 08:41:53 PM PT</t>
         </is>
       </c>
       <c r="C220" t="n">
@@ -25920,7 +25920,7 @@
       </c>
       <c r="B221" t="inlineStr">
         <is>
-          <t>2026-07-11 08:39:53 PM PT</t>
+          <t>2026-07-11 08:41:53 PM PT</t>
         </is>
       </c>
       <c r="C221" t="n">
@@ -26034,7 +26034,7 @@
       </c>
       <c r="B222" t="inlineStr">
         <is>
-          <t>2026-07-11 08:39:53 PM PT</t>
+          <t>2026-07-11 08:41:53 PM PT</t>
         </is>
       </c>
       <c r="C222" t="n">
@@ -26148,7 +26148,7 @@
       </c>
       <c r="B223" t="inlineStr">
         <is>
-          <t>2026-07-11 08:39:53 PM PT</t>
+          <t>2026-07-11 08:41:53 PM PT</t>
         </is>
       </c>
       <c r="C223" t="n">
@@ -26262,7 +26262,7 @@
       </c>
       <c r="B224" t="inlineStr">
         <is>
-          <t>2026-07-11 08:39:52 PM PT</t>
+          <t>2026-07-11 08:41:52 PM PT</t>
         </is>
       </c>
       <c r="C224" t="n">
@@ -26376,7 +26376,7 @@
       </c>
       <c r="B225" t="inlineStr">
         <is>
-          <t>2026-07-11 08:39:53 PM PT</t>
+          <t>2026-07-11 08:41:52 PM PT</t>
         </is>
       </c>
       <c r="C225" t="n">
@@ -26490,7 +26490,7 @@
       </c>
       <c r="B226" t="inlineStr">
         <is>
-          <t>2026-07-11 08:39:53 PM PT</t>
+          <t>2026-07-11 08:41:53 PM PT</t>
         </is>
       </c>
       <c r="C226" t="n">
@@ -26604,7 +26604,7 @@
       </c>
       <c r="B227" t="inlineStr">
         <is>
-          <t>2026-07-11 08:39:53 PM PT</t>
+          <t>2026-07-11 08:41:53 PM PT</t>
         </is>
       </c>
       <c r="C227" t="n">
@@ -26718,7 +26718,7 @@
       </c>
       <c r="B228" t="inlineStr">
         <is>
-          <t>2026-07-11 08:39:53 PM PT</t>
+          <t>2026-07-11 08:41:53 PM PT</t>
         </is>
       </c>
       <c r="C228" t="n">
@@ -26832,7 +26832,7 @@
       </c>
       <c r="B229" t="inlineStr">
         <is>
-          <t>2026-07-11 08:39:53 PM PT</t>
+          <t>2026-07-11 08:41:53 PM PT</t>
         </is>
       </c>
       <c r="C229" t="n">
@@ -26946,7 +26946,7 @@
       </c>
       <c r="B230" t="inlineStr">
         <is>
-          <t>2026-07-11 08:39:54 PM PT</t>
+          <t>2026-07-11 08:41:54 PM PT</t>
         </is>
       </c>
       <c r="C230" t="n">
@@ -26959,7 +26959,7 @@
       </c>
       <c r="E230" t="inlineStr">
         <is>
-          <t>Bottom 8 | 2 out</t>
+          <t>Bottom 8 | 3 out</t>
         </is>
       </c>
       <c r="F230" t="n">
@@ -26971,13 +26971,13 @@
         </is>
       </c>
       <c r="H230" t="n">
+        <v>3</v>
+      </c>
+      <c r="I230" t="n">
+        <v>1</v>
+      </c>
+      <c r="J230" t="n">
         <v>2</v>
-      </c>
-      <c r="I230" t="n">
-        <v>4</v>
-      </c>
-      <c r="J230" t="n">
-        <v>0</v>
       </c>
       <c r="K230" t="inlineStr">
         <is>
@@ -27069,7 +27069,7 @@
       </c>
       <c r="B231" t="inlineStr">
         <is>
-          <t>2026-07-11 08:39:53 PM PT</t>
+          <t>2026-07-11 08:41:53 PM PT</t>
         </is>
       </c>
       <c r="C231" t="n">
@@ -27183,7 +27183,7 @@
       </c>
       <c r="B232" t="inlineStr">
         <is>
-          <t>2026-07-11 08:39:53 PM PT</t>
+          <t>2026-07-11 08:41:53 PM PT</t>
         </is>
       </c>
       <c r="C232" t="n">
@@ -27297,7 +27297,7 @@
       </c>
       <c r="B233" t="inlineStr">
         <is>
-          <t>2026-07-11 08:39:53 PM PT</t>
+          <t>2026-07-11 08:41:53 PM PT</t>
         </is>
       </c>
       <c r="C233" t="n">
@@ -27411,7 +27411,7 @@
       </c>
       <c r="B234" t="inlineStr">
         <is>
-          <t>2026-07-11 08:39:53 PM PT</t>
+          <t>2026-07-11 08:41:53 PM PT</t>
         </is>
       </c>
       <c r="C234" t="n">
@@ -27525,7 +27525,7 @@
       </c>
       <c r="B235" t="inlineStr">
         <is>
-          <t>2026-07-11 08:39:54 PM PT</t>
+          <t>2026-07-11 08:41:54 PM PT</t>
         </is>
       </c>
       <c r="C235" t="n">
@@ -27538,7 +27538,7 @@
       </c>
       <c r="E235" t="inlineStr">
         <is>
-          <t>Bottom 8 | 1 out</t>
+          <t>Bottom 8 | 2 out</t>
         </is>
       </c>
       <c r="F235" t="n">
@@ -27550,13 +27550,13 @@
         </is>
       </c>
       <c r="H235" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I235" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J235" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K235" t="inlineStr">
         <is>
@@ -27648,7 +27648,7 @@
       </c>
       <c r="B236" t="inlineStr">
         <is>
-          <t>2026-07-11 08:39:54 PM PT</t>
+          <t>2026-07-11 08:41:54 PM PT</t>
         </is>
       </c>
       <c r="C236" t="n">
@@ -27661,7 +27661,7 @@
       </c>
       <c r="E236" t="inlineStr">
         <is>
-          <t>Bottom 8 | 1 out</t>
+          <t>Bottom 8 | 2 out</t>
         </is>
       </c>
       <c r="F236" t="n">
@@ -27673,13 +27673,13 @@
         </is>
       </c>
       <c r="H236" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I236" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J236" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K236" t="inlineStr">
         <is>
@@ -27771,7 +27771,7 @@
       </c>
       <c r="B237" t="inlineStr">
         <is>
-          <t>2026-07-11 08:39:53 PM PT</t>
+          <t>2026-07-11 08:41:53 PM PT</t>
         </is>
       </c>
       <c r="C237" t="n">
@@ -27885,7 +27885,7 @@
       </c>
       <c r="B238" t="inlineStr">
         <is>
-          <t>2026-07-11 08:39:53 PM PT</t>
+          <t>2026-07-11 08:41:53 PM PT</t>
         </is>
       </c>
       <c r="C238" t="n">
@@ -27999,7 +27999,7 @@
       </c>
       <c r="B239" t="inlineStr">
         <is>
-          <t>2026-07-11 08:39:53 PM PT</t>
+          <t>2026-07-11 08:41:53 PM PT</t>
         </is>
       </c>
       <c r="C239" t="n">
@@ -28113,7 +28113,7 @@
       </c>
       <c r="B240" t="inlineStr">
         <is>
-          <t>2026-07-11 08:39:53 PM PT</t>
+          <t>2026-07-11 08:41:53 PM PT</t>
         </is>
       </c>
       <c r="C240" t="n">
@@ -28227,7 +28227,7 @@
       </c>
       <c r="B241" t="inlineStr">
         <is>
-          <t>2026-07-11 08:39:53 PM PT</t>
+          <t>2026-07-11 08:41:53 PM PT</t>
         </is>
       </c>
       <c r="C241" t="n">
@@ -28341,7 +28341,7 @@
       </c>
       <c r="B242" t="inlineStr">
         <is>
-          <t>2026-07-11 08:39:53 PM PT</t>
+          <t>2026-07-11 08:41:53 PM PT</t>
         </is>
       </c>
       <c r="C242" t="n">
@@ -28455,7 +28455,7 @@
       </c>
       <c r="B243" t="inlineStr">
         <is>
-          <t>2026-07-11 08:39:53 PM PT</t>
+          <t>2026-07-11 08:41:53 PM PT</t>
         </is>
       </c>
       <c r="C243" t="n">
@@ -28569,7 +28569,7 @@
       </c>
       <c r="B244" t="inlineStr">
         <is>
-          <t>2026-07-11 08:39:54 PM PT</t>
+          <t>2026-07-11 08:41:54 PM PT</t>
         </is>
       </c>
       <c r="C244" t="n">
@@ -28683,7 +28683,7 @@
       </c>
       <c r="B245" t="inlineStr">
         <is>
-          <t>2026-07-11 08:39:54 PM PT</t>
+          <t>2026-07-11 08:41:54 PM PT</t>
         </is>
       </c>
       <c r="C245" t="n">
@@ -28797,7 +28797,7 @@
       </c>
       <c r="B246" t="inlineStr">
         <is>
-          <t>2026-07-11 08:39:54 PM PT</t>
+          <t>2026-07-11 08:41:54 PM PT</t>
         </is>
       </c>
       <c r="C246" t="n">
@@ -28911,7 +28911,7 @@
       </c>
       <c r="B247" t="inlineStr">
         <is>
-          <t>2026-07-11 08:39:53 PM PT</t>
+          <t>2026-07-11 08:41:53 PM PT</t>
         </is>
       </c>
       <c r="C247" t="n">
@@ -29025,7 +29025,7 @@
       </c>
       <c r="B248" t="inlineStr">
         <is>
-          <t>2026-07-11 08:39:53 PM PT</t>
+          <t>2026-07-11 08:41:53 PM PT</t>
         </is>
       </c>
       <c r="C248" t="n">
@@ -29139,7 +29139,7 @@
       </c>
       <c r="B249" t="inlineStr">
         <is>
-          <t>2026-07-11 08:39:53 PM PT</t>
+          <t>2026-07-11 08:41:53 PM PT</t>
         </is>
       </c>
       <c r="C249" t="n">
@@ -29253,7 +29253,7 @@
       </c>
       <c r="B250" t="inlineStr">
         <is>
-          <t>2026-07-11 08:39:53 PM PT</t>
+          <t>2026-07-11 08:41:53 PM PT</t>
         </is>
       </c>
       <c r="C250" t="n">
@@ -29367,7 +29367,7 @@
       </c>
       <c r="B251" t="inlineStr">
         <is>
-          <t>2026-07-11 08:39:53 PM PT</t>
+          <t>2026-07-11 08:41:53 PM PT</t>
         </is>
       </c>
       <c r="C251" t="n">
@@ -29481,7 +29481,7 @@
       </c>
       <c r="B252" t="inlineStr">
         <is>
-          <t>2026-07-11 08:39:53 PM PT</t>
+          <t>2026-07-11 08:41:53 PM PT</t>
         </is>
       </c>
       <c r="C252" t="n">
@@ -29595,7 +29595,7 @@
       </c>
       <c r="B253" t="inlineStr">
         <is>
-          <t>2026-07-11 08:39:54 PM PT</t>
+          <t>2026-07-11 08:41:54 PM PT</t>
         </is>
       </c>
       <c r="C253" t="n">
@@ -29709,7 +29709,7 @@
       </c>
       <c r="B254" t="inlineStr">
         <is>
-          <t>2026-07-11 08:39:54 PM PT</t>
+          <t>2026-07-11 08:41:54 PM PT</t>
         </is>
       </c>
       <c r="C254" t="n">
@@ -29823,7 +29823,7 @@
       </c>
       <c r="B255" t="inlineStr">
         <is>
-          <t>2026-07-11 08:39:54 PM PT</t>
+          <t>2026-07-11 08:41:54 PM PT</t>
         </is>
       </c>
       <c r="C255" t="n">
@@ -29937,7 +29937,7 @@
       </c>
       <c r="B256" t="inlineStr">
         <is>
-          <t>2026-07-11 08:39:54 PM PT</t>
+          <t>2026-07-11 08:41:54 PM PT</t>
         </is>
       </c>
       <c r="C256" t="n">
@@ -30051,7 +30051,7 @@
       </c>
       <c r="B257" t="inlineStr">
         <is>
-          <t>2026-07-11 08:39:54 PM PT</t>
+          <t>2026-07-11 08:41:54 PM PT</t>
         </is>
       </c>
       <c r="C257" t="n">
@@ -30165,7 +30165,7 @@
       </c>
       <c r="B258" t="inlineStr">
         <is>
-          <t>2026-07-11 08:39:53 PM PT</t>
+          <t>2026-07-11 08:41:53 PM PT</t>
         </is>
       </c>
       <c r="C258" t="n">
@@ -30279,7 +30279,7 @@
       </c>
       <c r="B259" t="inlineStr">
         <is>
-          <t>2026-07-11 08:39:53 PM PT</t>
+          <t>2026-07-11 08:41:53 PM PT</t>
         </is>
       </c>
       <c r="C259" t="n">
@@ -30393,7 +30393,7 @@
       </c>
       <c r="B260" t="inlineStr">
         <is>
-          <t>2026-07-11 08:39:53 PM PT</t>
+          <t>2026-07-11 08:41:53 PM PT</t>
         </is>
       </c>
       <c r="C260" t="n">
@@ -30507,7 +30507,7 @@
       </c>
       <c r="B261" t="inlineStr">
         <is>
-          <t>2026-07-11 08:39:53 PM PT</t>
+          <t>2026-07-11 08:41:53 PM PT</t>
         </is>
       </c>
       <c r="C261" t="n">
@@ -30621,7 +30621,7 @@
       </c>
       <c r="B262" t="inlineStr">
         <is>
-          <t>2026-07-11 08:39:53 PM PT</t>
+          <t>2026-07-11 08:41:53 PM PT</t>
         </is>
       </c>
       <c r="C262" t="n">
@@ -30735,7 +30735,7 @@
       </c>
       <c r="B263" t="inlineStr">
         <is>
-          <t>2026-07-11 08:39:53 PM PT</t>
+          <t>2026-07-11 08:41:53 PM PT</t>
         </is>
       </c>
       <c r="C263" t="n">
@@ -30849,7 +30849,7 @@
       </c>
       <c r="B264" t="inlineStr">
         <is>
-          <t>2026-07-11 08:39:53 PM PT</t>
+          <t>2026-07-11 08:41:53 PM PT</t>
         </is>
       </c>
       <c r="C264" t="n">
@@ -30963,7 +30963,7 @@
       </c>
       <c r="B265" t="inlineStr">
         <is>
-          <t>2026-07-11 08:39:53 PM PT</t>
+          <t>2026-07-11 08:41:53 PM PT</t>
         </is>
       </c>
       <c r="C265" t="n">
@@ -31077,7 +31077,7 @@
       </c>
       <c r="B266" t="inlineStr">
         <is>
-          <t>2026-07-11 08:39:53 PM PT</t>
+          <t>2026-07-11 08:41:53 PM PT</t>
         </is>
       </c>
       <c r="C266" t="n">
@@ -31191,7 +31191,7 @@
       </c>
       <c r="B267" t="inlineStr">
         <is>
-          <t>2026-07-11 08:39:53 PM PT</t>
+          <t>2026-07-11 08:41:53 PM PT</t>
         </is>
       </c>
       <c r="C267" t="n">
@@ -31305,7 +31305,7 @@
       </c>
       <c r="B268" t="inlineStr">
         <is>
-          <t>2026-07-11 08:39:53 PM PT</t>
+          <t>2026-07-11 08:41:53 PM PT</t>
         </is>
       </c>
       <c r="C268" t="n">
@@ -31419,7 +31419,7 @@
       </c>
       <c r="B269" t="inlineStr">
         <is>
-          <t>2026-07-11 08:39:53 PM PT</t>
+          <t>2026-07-11 08:41:53 PM PT</t>
         </is>
       </c>
       <c r="C269" t="n">
@@ -31533,7 +31533,7 @@
       </c>
       <c r="B270" t="inlineStr">
         <is>
-          <t>2026-07-11 08:39:53 PM PT</t>
+          <t>2026-07-11 08:41:53 PM PT</t>
         </is>
       </c>
       <c r="C270" t="n">
@@ -31647,7 +31647,7 @@
       </c>
       <c r="B271" t="inlineStr">
         <is>
-          <t>2026-07-11 08:39:53 PM PT</t>
+          <t>2026-07-11 08:41:53 PM PT</t>
         </is>
       </c>
       <c r="C271" t="n">
@@ -31761,7 +31761,7 @@
       </c>
       <c r="B272" t="inlineStr">
         <is>
-          <t>2026-07-11 08:39:53 PM PT</t>
+          <t>2026-07-11 08:41:53 PM PT</t>
         </is>
       </c>
       <c r="C272" t="n">
@@ -31875,7 +31875,7 @@
       </c>
       <c r="B273" t="inlineStr">
         <is>
-          <t>2026-07-11 08:39:53 PM PT</t>
+          <t>2026-07-11 08:41:53 PM PT</t>
         </is>
       </c>
       <c r="C273" t="n">
@@ -31989,7 +31989,7 @@
       </c>
       <c r="B274" t="inlineStr">
         <is>
-          <t>2026-07-11 08:39:53 PM PT</t>
+          <t>2026-07-11 08:41:53 PM PT</t>
         </is>
       </c>
       <c r="C274" t="n">
@@ -32103,7 +32103,7 @@
       </c>
       <c r="B275" t="inlineStr">
         <is>
-          <t>2026-07-11 08:39:53 PM PT</t>
+          <t>2026-07-11 08:41:53 PM PT</t>
         </is>
       </c>
       <c r="C275" t="n">
@@ -32217,7 +32217,7 @@
       </c>
       <c r="B276" t="inlineStr">
         <is>
-          <t>2026-07-11 08:39:53 PM PT</t>
+          <t>2026-07-11 08:41:53 PM PT</t>
         </is>
       </c>
       <c r="C276" t="n">
@@ -32331,7 +32331,7 @@
       </c>
       <c r="B277" t="inlineStr">
         <is>
-          <t>2026-07-11 08:39:53 PM PT</t>
+          <t>2026-07-11 08:41:53 PM PT</t>
         </is>
       </c>
       <c r="C277" t="n">
@@ -32445,7 +32445,7 @@
       </c>
       <c r="B278" t="inlineStr">
         <is>
-          <t>2026-07-11 08:39:53 PM PT</t>
+          <t>2026-07-11 08:41:53 PM PT</t>
         </is>
       </c>
       <c r="C278" t="n">
@@ -32559,7 +32559,7 @@
       </c>
       <c r="B279" t="inlineStr">
         <is>
-          <t>2026-07-11 08:39:54 PM PT</t>
+          <t>2026-07-11 08:41:54 PM PT</t>
         </is>
       </c>
       <c r="C279" t="n">
@@ -32572,7 +32572,7 @@
       </c>
       <c r="E279" t="inlineStr">
         <is>
-          <t>Bottom 8 | 1 out</t>
+          <t>Bottom 8 | 2 out</t>
         </is>
       </c>
       <c r="F279" t="n">
@@ -32584,13 +32584,13 @@
         </is>
       </c>
       <c r="H279" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I279" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J279" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K279" t="inlineStr">
         <is>
@@ -32682,7 +32682,7 @@
       </c>
       <c r="B280" t="inlineStr">
         <is>
-          <t>2026-07-11 08:39:54 PM PT</t>
+          <t>2026-07-11 08:41:54 PM PT</t>
         </is>
       </c>
       <c r="C280" t="n">
@@ -32695,7 +32695,7 @@
       </c>
       <c r="E280" t="inlineStr">
         <is>
-          <t>Bottom 8 | 1 out</t>
+          <t>Bottom 8 | 2 out</t>
         </is>
       </c>
       <c r="F280" t="n">
@@ -32707,13 +32707,13 @@
         </is>
       </c>
       <c r="H280" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I280" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J280" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K280" t="inlineStr">
         <is>
@@ -32805,7 +32805,7 @@
       </c>
       <c r="B281" t="inlineStr">
         <is>
-          <t>2026-07-11 08:39:54 PM PT</t>
+          <t>2026-07-11 08:41:54 PM PT</t>
         </is>
       </c>
       <c r="C281" t="n">
@@ -32818,7 +32818,7 @@
       </c>
       <c r="E281" t="inlineStr">
         <is>
-          <t>Bottom 8 | 1 out</t>
+          <t>Bottom 8 | 2 out</t>
         </is>
       </c>
       <c r="F281" t="n">
@@ -32830,13 +32830,13 @@
         </is>
       </c>
       <c r="H281" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I281" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J281" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K281" t="inlineStr">
         <is>
@@ -32928,7 +32928,7 @@
       </c>
       <c r="B282" t="inlineStr">
         <is>
-          <t>2026-07-11 08:39:54 PM PT</t>
+          <t>2026-07-11 08:41:54 PM PT</t>
         </is>
       </c>
       <c r="C282" t="n">
@@ -32941,7 +32941,7 @@
       </c>
       <c r="E282" t="inlineStr">
         <is>
-          <t>Bottom 8 | 1 out</t>
+          <t>Bottom 8 | 2 out</t>
         </is>
       </c>
       <c r="F282" t="n">
@@ -32953,13 +32953,13 @@
         </is>
       </c>
       <c r="H282" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I282" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J282" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K282" t="inlineStr">
         <is>
@@ -33051,7 +33051,7 @@
       </c>
       <c r="B283" t="inlineStr">
         <is>
-          <t>2026-07-11 08:39:54 PM PT</t>
+          <t>2026-07-11 08:41:54 PM PT</t>
         </is>
       </c>
       <c r="C283" t="n">
@@ -33064,7 +33064,7 @@
       </c>
       <c r="E283" t="inlineStr">
         <is>
-          <t>Bottom 8 | 1 out</t>
+          <t>Bottom 8 | 2 out</t>
         </is>
       </c>
       <c r="F283" t="n">
@@ -33076,13 +33076,13 @@
         </is>
       </c>
       <c r="H283" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I283" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J283" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K283" t="inlineStr">
         <is>
@@ -33174,7 +33174,7 @@
       </c>
       <c r="B284" t="inlineStr">
         <is>
-          <t>2026-07-11 08:39:54 PM PT</t>
+          <t>2026-07-11 08:41:54 PM PT</t>
         </is>
       </c>
       <c r="C284" t="n">
@@ -33187,7 +33187,7 @@
       </c>
       <c r="E284" t="inlineStr">
         <is>
-          <t>Bottom 8 | 1 out</t>
+          <t>Bottom 8 | 2 out</t>
         </is>
       </c>
       <c r="F284" t="n">
@@ -33199,13 +33199,13 @@
         </is>
       </c>
       <c r="H284" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I284" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J284" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K284" t="inlineStr">
         <is>
@@ -33297,7 +33297,7 @@
       </c>
       <c r="B285" t="inlineStr">
         <is>
-          <t>2026-07-11 08:39:54 PM PT</t>
+          <t>2026-07-11 08:41:54 PM PT</t>
         </is>
       </c>
       <c r="C285" t="n">
@@ -33310,7 +33310,7 @@
       </c>
       <c r="E285" t="inlineStr">
         <is>
-          <t>Bottom 8 | 1 out</t>
+          <t>Bottom 8 | 2 out</t>
         </is>
       </c>
       <c r="F285" t="n">
@@ -33322,13 +33322,13 @@
         </is>
       </c>
       <c r="H285" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I285" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J285" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K285" t="inlineStr">
         <is>
@@ -33420,7 +33420,7 @@
       </c>
       <c r="B286" t="inlineStr">
         <is>
-          <t>2026-07-11 08:39:54 PM PT</t>
+          <t>2026-07-11 08:41:54 PM PT</t>
         </is>
       </c>
       <c r="C286" t="n">
@@ -33433,7 +33433,7 @@
       </c>
       <c r="E286" t="inlineStr">
         <is>
-          <t>Bottom 8 | 1 out</t>
+          <t>Bottom 8 | 2 out</t>
         </is>
       </c>
       <c r="F286" t="n">
@@ -33445,13 +33445,13 @@
         </is>
       </c>
       <c r="H286" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I286" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J286" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K286" t="inlineStr">
         <is>
@@ -33543,7 +33543,7 @@
       </c>
       <c r="B287" t="inlineStr">
         <is>
-          <t>2026-07-11 08:39:53 PM PT</t>
+          <t>2026-07-11 08:41:53 PM PT</t>
         </is>
       </c>
       <c r="C287" t="n">
@@ -33657,7 +33657,7 @@
       </c>
       <c r="B288" t="inlineStr">
         <is>
-          <t>2026-07-11 08:39:52 PM PT</t>
+          <t>2026-07-11 08:41:52 PM PT</t>
         </is>
       </c>
       <c r="C288" t="n">
@@ -33771,7 +33771,7 @@
       </c>
       <c r="B289" t="inlineStr">
         <is>
-          <t>2026-07-11 08:39:53 PM PT</t>
+          <t>2026-07-11 08:41:52 PM PT</t>
         </is>
       </c>
       <c r="C289" t="n">
@@ -33885,7 +33885,7 @@
       </c>
       <c r="B290" t="inlineStr">
         <is>
-          <t>2026-07-11 08:39:52 PM PT</t>
+          <t>2026-07-11 08:41:52 PM PT</t>
         </is>
       </c>
       <c r="C290" t="n">
@@ -33999,7 +33999,7 @@
       </c>
       <c r="B291" t="inlineStr">
         <is>
-          <t>2026-07-11 08:39:53 PM PT</t>
+          <t>2026-07-11 08:41:52 PM PT</t>
         </is>
       </c>
       <c r="C291" t="n">
@@ -34113,7 +34113,7 @@
       </c>
       <c r="B292" t="inlineStr">
         <is>
-          <t>2026-07-11 08:39:53 PM PT</t>
+          <t>2026-07-11 08:41:52 PM PT</t>
         </is>
       </c>
       <c r="C292" t="n">
@@ -34227,7 +34227,7 @@
       </c>
       <c r="B293" t="inlineStr">
         <is>
-          <t>2026-07-11 08:39:52 PM PT</t>
+          <t>2026-07-11 08:41:52 PM PT</t>
         </is>
       </c>
       <c r="C293" t="n">
@@ -34341,7 +34341,7 @@
       </c>
       <c r="B294" t="inlineStr">
         <is>
-          <t>2026-07-11 08:39:53 PM PT</t>
+          <t>2026-07-11 08:41:53 PM PT</t>
         </is>
       </c>
       <c r="C294" t="n">
@@ -34455,7 +34455,7 @@
       </c>
       <c r="B295" t="inlineStr">
         <is>
-          <t>2026-07-11 08:39:53 PM PT</t>
+          <t>2026-07-11 08:41:53 PM PT</t>
         </is>
       </c>
       <c r="C295" t="n">
@@ -34569,7 +34569,7 @@
       </c>
       <c r="B296" t="inlineStr">
         <is>
-          <t>2026-07-11 08:39:53 PM PT</t>
+          <t>2026-07-11 08:41:53 PM PT</t>
         </is>
       </c>
       <c r="C296" t="n">
@@ -34683,7 +34683,7 @@
       </c>
       <c r="B297" t="inlineStr">
         <is>
-          <t>2026-07-11 08:39:53 PM PT</t>
+          <t>2026-07-11 08:41:53 PM PT</t>
         </is>
       </c>
       <c r="C297" t="n">
@@ -34797,7 +34797,7 @@
       </c>
       <c r="B298" t="inlineStr">
         <is>
-          <t>2026-07-11 08:39:53 PM PT</t>
+          <t>2026-07-11 08:41:53 PM PT</t>
         </is>
       </c>
       <c r="C298" t="n">
@@ -34911,7 +34911,7 @@
       </c>
       <c r="B299" t="inlineStr">
         <is>
-          <t>2026-07-11 08:39:53 PM PT</t>
+          <t>2026-07-11 08:41:53 PM PT</t>
         </is>
       </c>
       <c r="C299" t="n">
@@ -35025,7 +35025,7 @@
       </c>
       <c r="B300" t="inlineStr">
         <is>
-          <t>2026-07-11 08:39:53 PM PT</t>
+          <t>2026-07-11 08:41:53 PM PT</t>
         </is>
       </c>
       <c r="C300" t="n">
@@ -35139,7 +35139,7 @@
       </c>
       <c r="B301" t="inlineStr">
         <is>
-          <t>2026-07-11 08:39:53 PM PT</t>
+          <t>2026-07-11 08:41:53 PM PT</t>
         </is>
       </c>
       <c r="C301" t="n">
@@ -35253,7 +35253,7 @@
       </c>
       <c r="B302" t="inlineStr">
         <is>
-          <t>2026-07-11 08:39:53 PM PT</t>
+          <t>2026-07-11 08:41:53 PM PT</t>
         </is>
       </c>
       <c r="C302" t="n">
@@ -35367,7 +35367,7 @@
       </c>
       <c r="B303" t="inlineStr">
         <is>
-          <t>2026-07-11 08:39:53 PM PT</t>
+          <t>2026-07-11 08:41:52 PM PT</t>
         </is>
       </c>
       <c r="C303" t="n">
@@ -35481,7 +35481,7 @@
       </c>
       <c r="B304" t="inlineStr">
         <is>
-          <t>2026-07-11 08:39:53 PM PT</t>
+          <t>2026-07-11 08:41:52 PM PT</t>
         </is>
       </c>
       <c r="C304" t="n">
@@ -35595,7 +35595,7 @@
       </c>
       <c r="B305" t="inlineStr">
         <is>
-          <t>2026-07-11 08:39:53 PM PT</t>
+          <t>2026-07-11 08:41:52 PM PT</t>
         </is>
       </c>
       <c r="C305" t="n">
@@ -35709,7 +35709,7 @@
       </c>
       <c r="B306" t="inlineStr">
         <is>
-          <t>2026-07-11 08:39:52 PM PT</t>
+          <t>2026-07-11 08:41:52 PM PT</t>
         </is>
       </c>
       <c r="C306" t="n">
@@ -35823,7 +35823,7 @@
       </c>
       <c r="B307" t="inlineStr">
         <is>
-          <t>2026-07-11 08:39:53 PM PT</t>
+          <t>2026-07-11 08:41:52 PM PT</t>
         </is>
       </c>
       <c r="C307" t="n">
@@ -35937,7 +35937,7 @@
       </c>
       <c r="B308" t="inlineStr">
         <is>
-          <t>2026-07-11 08:39:52 PM PT</t>
+          <t>2026-07-11 08:41:52 PM PT</t>
         </is>
       </c>
       <c r="C308" t="n">
@@ -36051,7 +36051,7 @@
       </c>
       <c r="B309" t="inlineStr">
         <is>
-          <t>2026-07-11 08:39:52 PM PT</t>
+          <t>2026-07-11 08:41:52 PM PT</t>
         </is>
       </c>
       <c r="C309" t="n">
@@ -36165,7 +36165,7 @@
       </c>
       <c r="B310" t="inlineStr">
         <is>
-          <t>2026-07-11 08:39:53 PM PT</t>
+          <t>2026-07-11 08:41:52 PM PT</t>
         </is>
       </c>
       <c r="C310" t="n">
@@ -36279,7 +36279,7 @@
       </c>
       <c r="B311" t="inlineStr">
         <is>
-          <t>2026-07-11 08:39:54 PM PT</t>
+          <t>2026-07-11 08:41:54 PM PT</t>
         </is>
       </c>
       <c r="C311" t="n">
@@ -36292,7 +36292,7 @@
       </c>
       <c r="E311" t="inlineStr">
         <is>
-          <t>Bottom 8 | 2 out</t>
+          <t>Bottom 8 | 3 out</t>
         </is>
       </c>
       <c r="F311" t="n">
@@ -36304,14 +36304,14 @@
         </is>
       </c>
       <c r="H311" t="n">
+        <v>3</v>
+      </c>
+      <c r="I311" t="n">
+        <v>1</v>
+      </c>
+      <c r="J311" t="n">
         <v>2</v>
       </c>
-      <c r="I311" t="n">
-        <v>4</v>
-      </c>
-      <c r="J311" t="n">
-        <v>0</v>
-      </c>
       <c r="K311" t="inlineStr">
         <is>
           <t>Home</t>
@@ -36329,27 +36329,27 @@
       </c>
       <c r="N311" t="inlineStr">
         <is>
-          <t>Luis Campusano</t>
+          <t>Jase Bowen</t>
         </is>
       </c>
       <c r="O311" t="n">
-        <v>669134</v>
+        <v>687749</v>
       </c>
       <c r="P311" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>PR</t>
         </is>
       </c>
       <c r="Q311" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>5 (Sub)</t>
         </is>
       </c>
       <c r="R311" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="S311" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="T311" t="n">
         <v>0</v>
@@ -36382,7 +36382,7 @@
         <v>0</v>
       </c>
       <c r="AD311" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="AE311" s="4" t="n">
         <v>0</v>
@@ -36402,61 +36402,70 @@
       </c>
       <c r="B312" t="inlineStr">
         <is>
-          <t>2026-07-11 08:39:53 PM PT</t>
+          <t>2026-07-11 08:41:54 PM PT</t>
         </is>
       </c>
       <c r="C312" t="n">
-        <v>822953</v>
+        <v>823276</v>
       </c>
       <c r="D312" t="inlineStr">
         <is>
-          <t>1:10 PM PT</t>
+          <t>5:40 PM PT</t>
         </is>
       </c>
       <c r="E312" t="inlineStr">
         <is>
-          <t>Final</t>
+          <t>Bottom 8 | 3 out</t>
         </is>
       </c>
       <c r="F312" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="G312" t="inlineStr">
         <is>
-          <t>Top</t>
-        </is>
+          <t>Bottom</t>
+        </is>
+      </c>
+      <c r="H312" t="n">
+        <v>3</v>
+      </c>
+      <c r="I312" t="n">
+        <v>1</v>
+      </c>
+      <c r="J312" t="n">
+        <v>2</v>
       </c>
       <c r="K312" t="inlineStr">
         <is>
-          <t>Away</t>
+          <t>Home</t>
         </is>
       </c>
       <c r="L312" t="inlineStr">
         <is>
-          <t>SEA</t>
+          <t>SD</t>
         </is>
       </c>
       <c r="M312" t="inlineStr">
         <is>
-          <t>TB</t>
+          <t>TOR</t>
         </is>
       </c>
       <c r="N312" t="inlineStr">
         <is>
-          <t>J.P. Crawford</t>
+          <t>Luis Campusano</t>
         </is>
       </c>
       <c r="O312" t="n">
-        <v>641487</v>
+        <v>669134</v>
       </c>
       <c r="P312" t="inlineStr">
         <is>
-          <t>3B</t>
+          <t>C</t>
         </is>
       </c>
       <c r="Q312" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>8</t>
         </is>
       </c>
       <c r="R312" t="n">
@@ -36496,16 +36505,16 @@
         <v>0</v>
       </c>
       <c r="AD312" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="AE312" s="4" t="n">
         <v>0</v>
       </c>
       <c r="AF312" t="n">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="AG312" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
     </row>
     <row r="313">
@@ -36516,7 +36525,7 @@
       </c>
       <c r="B313" t="inlineStr">
         <is>
-          <t>2026-07-11 08:39:53 PM PT</t>
+          <t>2026-07-11 08:41:53 PM PT</t>
         </is>
       </c>
       <c r="C313" t="n">
@@ -36557,27 +36566,27 @@
       </c>
       <c r="N313" t="inlineStr">
         <is>
-          <t>Luke Raley</t>
+          <t>J.P. Crawford</t>
         </is>
       </c>
       <c r="O313" t="n">
-        <v>670042</v>
+        <v>641487</v>
       </c>
       <c r="P313" t="inlineStr">
         <is>
-          <t>RF</t>
+          <t>3B</t>
         </is>
       </c>
       <c r="Q313" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>1</t>
         </is>
       </c>
       <c r="R313" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="S313" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="T313" t="n">
         <v>0</v>
@@ -36630,7 +36639,7 @@
       </c>
       <c r="B314" t="inlineStr">
         <is>
-          <t>2026-07-11 08:39:53 PM PT</t>
+          <t>2026-07-11 08:41:53 PM PT</t>
         </is>
       </c>
       <c r="C314" t="n">
@@ -36671,27 +36680,27 @@
       </c>
       <c r="N314" t="inlineStr">
         <is>
-          <t>Mitch Garver</t>
+          <t>Luke Raley</t>
         </is>
       </c>
       <c r="O314" t="n">
-        <v>641598</v>
+        <v>670042</v>
       </c>
       <c r="P314" t="inlineStr">
         <is>
-          <t>PH</t>
+          <t>RF</t>
         </is>
       </c>
       <c r="Q314" t="inlineStr">
         <is>
-          <t>6 (Sub)</t>
+          <t>6</t>
         </is>
       </c>
       <c r="R314" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="S314" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="T314" t="n">
         <v>0</v>
@@ -36744,7 +36753,7 @@
       </c>
       <c r="B315" t="inlineStr">
         <is>
-          <t>2026-07-11 08:39:53 PM PT</t>
+          <t>2026-07-11 08:41:53 PM PT</t>
         </is>
       </c>
       <c r="C315" t="n">
@@ -36785,15 +36794,15 @@
       </c>
       <c r="N315" t="inlineStr">
         <is>
-          <t>Weston Wilson</t>
+          <t>Mitch Garver</t>
         </is>
       </c>
       <c r="O315" t="n">
-        <v>642215</v>
+        <v>641598</v>
       </c>
       <c r="P315" t="inlineStr">
         <is>
-          <t>RF</t>
+          <t>PH</t>
         </is>
       </c>
       <c r="Q315" t="inlineStr">
@@ -36802,10 +36811,10 @@
         </is>
       </c>
       <c r="R315" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S315" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T315" t="n">
         <v>0</v>
@@ -36838,7 +36847,7 @@
         <v>0</v>
       </c>
       <c r="AD315" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AE315" s="4" t="n">
         <v>0</v>
@@ -36858,7 +36867,7 @@
       </c>
       <c r="B316" t="inlineStr">
         <is>
-          <t>2026-07-11 08:39:53 PM PT</t>
+          <t>2026-07-11 08:41:53 PM PT</t>
         </is>
       </c>
       <c r="C316" t="n">
@@ -36899,27 +36908,27 @@
       </c>
       <c r="N316" t="inlineStr">
         <is>
-          <t>Miles Mastrobuoni</t>
+          <t>Weston Wilson</t>
         </is>
       </c>
       <c r="O316" t="n">
-        <v>670156</v>
+        <v>642215</v>
       </c>
       <c r="P316" t="inlineStr">
         <is>
-          <t>PH</t>
+          <t>RF</t>
         </is>
       </c>
       <c r="Q316" t="inlineStr">
         <is>
-          <t>8 (Sub)</t>
+          <t>6 (Sub)</t>
         </is>
       </c>
       <c r="R316" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S316" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="T316" t="n">
         <v>0</v>
@@ -36972,15 +36981,15 @@
       </c>
       <c r="B317" t="inlineStr">
         <is>
-          <t>2026-07-11 08:39:53 PM PT</t>
+          <t>2026-07-11 08:41:53 PM PT</t>
         </is>
       </c>
       <c r="C317" t="n">
-        <v>823198</v>
+        <v>822953</v>
       </c>
       <c r="D317" t="inlineStr">
         <is>
-          <t>1:05 PM PT</t>
+          <t>1:10 PM PT</t>
         </is>
       </c>
       <c r="E317" t="inlineStr">
@@ -36998,42 +37007,42 @@
       </c>
       <c r="K317" t="inlineStr">
         <is>
-          <t>Home</t>
+          <t>Away</t>
         </is>
       </c>
       <c r="L317" t="inlineStr">
         <is>
-          <t>SF</t>
+          <t>SEA</t>
         </is>
       </c>
       <c r="M317" t="inlineStr">
         <is>
-          <t>COL</t>
+          <t>TB</t>
         </is>
       </c>
       <c r="N317" t="inlineStr">
         <is>
-          <t>Willy Adames</t>
+          <t>Miles Mastrobuoni</t>
         </is>
       </c>
       <c r="O317" t="n">
-        <v>642715</v>
+        <v>670156</v>
       </c>
       <c r="P317" t="inlineStr">
         <is>
-          <t>SS</t>
+          <t>PH</t>
         </is>
       </c>
       <c r="Q317" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>8 (Sub)</t>
         </is>
       </c>
       <c r="R317" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="S317" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="T317" t="n">
         <v>0</v>
@@ -37066,16 +37075,16 @@
         <v>0</v>
       </c>
       <c r="AD317" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AE317" s="4" t="n">
         <v>0</v>
       </c>
       <c r="AF317" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="AG317" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
     </row>
     <row r="318">
@@ -37086,7 +37095,7 @@
       </c>
       <c r="B318" t="inlineStr">
         <is>
-          <t>2026-07-11 08:39:53 PM PT</t>
+          <t>2026-07-11 08:41:53 PM PT</t>
         </is>
       </c>
       <c r="C318" t="n">
@@ -37127,27 +37136,27 @@
       </c>
       <c r="N318" t="inlineStr">
         <is>
-          <t>Jung Hoo Lee</t>
+          <t>Willy Adames</t>
         </is>
       </c>
       <c r="O318" t="n">
-        <v>808982</v>
+        <v>642715</v>
       </c>
       <c r="P318" t="inlineStr">
         <is>
-          <t>RF</t>
+          <t>SS</t>
         </is>
       </c>
       <c r="Q318" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>5</t>
         </is>
       </c>
       <c r="R318" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="S318" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="T318" t="n">
         <v>0</v>
@@ -37200,15 +37209,15 @@
       </c>
       <c r="B319" t="inlineStr">
         <is>
-          <t>2026-07-11 08:39:54 PM PT</t>
+          <t>2026-07-11 08:41:53 PM PT</t>
         </is>
       </c>
       <c r="C319" t="n">
-        <v>823030</v>
+        <v>823198</v>
       </c>
       <c r="D319" t="inlineStr">
         <is>
-          <t>4:15 PM PT</t>
+          <t>1:05 PM PT</t>
         </is>
       </c>
       <c r="E319" t="inlineStr">
@@ -37231,37 +37240,37 @@
       </c>
       <c r="L319" t="inlineStr">
         <is>
-          <t>STL</t>
+          <t>SF</t>
         </is>
       </c>
       <c r="M319" t="inlineStr">
         <is>
-          <t>ATL</t>
+          <t>COL</t>
         </is>
       </c>
       <c r="N319" t="inlineStr">
         <is>
-          <t>JJ Wetherholt</t>
+          <t>Jung Hoo Lee</t>
         </is>
       </c>
       <c r="O319" t="n">
-        <v>802139</v>
+        <v>808982</v>
       </c>
       <c r="P319" t="inlineStr">
         <is>
-          <t>2B</t>
+          <t>RF</t>
         </is>
       </c>
       <c r="Q319" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>7</t>
         </is>
       </c>
       <c r="R319" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="S319" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="T319" t="n">
         <v>0</v>
@@ -37303,7 +37312,7 @@
         <v>4</v>
       </c>
       <c r="AG319" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
     </row>
     <row r="320">
@@ -37314,7 +37323,7 @@
       </c>
       <c r="B320" t="inlineStr">
         <is>
-          <t>2026-07-11 08:39:54 PM PT</t>
+          <t>2026-07-11 08:41:54 PM PT</t>
         </is>
       </c>
       <c r="C320" t="n">
@@ -37355,20 +37364,20 @@
       </c>
       <c r="N320" t="inlineStr">
         <is>
-          <t>Alec Burleson</t>
+          <t>JJ Wetherholt</t>
         </is>
       </c>
       <c r="O320" t="n">
-        <v>676475</v>
+        <v>802139</v>
       </c>
       <c r="P320" t="inlineStr">
         <is>
-          <t>1B</t>
+          <t>2B</t>
         </is>
       </c>
       <c r="Q320" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>1</t>
         </is>
       </c>
       <c r="R320" t="n">
@@ -37408,7 +37417,7 @@
         <v>0</v>
       </c>
       <c r="AD320" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AE320" s="4" t="n">
         <v>0</v>
@@ -37428,7 +37437,7 @@
       </c>
       <c r="B321" t="inlineStr">
         <is>
-          <t>2026-07-11 08:39:54 PM PT</t>
+          <t>2026-07-11 08:41:54 PM PT</t>
         </is>
       </c>
       <c r="C321" t="n">
@@ -37469,27 +37478,27 @@
       </c>
       <c r="N321" t="inlineStr">
         <is>
-          <t>Masyn Winn</t>
+          <t>Alec Burleson</t>
         </is>
       </c>
       <c r="O321" t="n">
-        <v>691026</v>
+        <v>676475</v>
       </c>
       <c r="P321" t="inlineStr">
         <is>
-          <t>SS</t>
+          <t>1B</t>
         </is>
       </c>
       <c r="Q321" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>3</t>
         </is>
       </c>
       <c r="R321" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="S321" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="T321" t="n">
         <v>0</v>
@@ -37522,7 +37531,7 @@
         <v>0</v>
       </c>
       <c r="AD321" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AE321" s="4" t="n">
         <v>0</v>
@@ -37542,7 +37551,7 @@
       </c>
       <c r="B322" t="inlineStr">
         <is>
-          <t>2026-07-11 08:39:54 PM PT</t>
+          <t>2026-07-11 08:41:54 PM PT</t>
         </is>
       </c>
       <c r="C322" t="n">
@@ -37583,20 +37592,20 @@
       </c>
       <c r="N322" t="inlineStr">
         <is>
-          <t>Nathan Church</t>
+          <t>Masyn Winn</t>
         </is>
       </c>
       <c r="O322" t="n">
-        <v>701675</v>
+        <v>691026</v>
       </c>
       <c r="P322" t="inlineStr">
         <is>
-          <t>CF</t>
+          <t>SS</t>
         </is>
       </c>
       <c r="Q322" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>6</t>
         </is>
       </c>
       <c r="R322" t="n">
@@ -37656,15 +37665,15 @@
       </c>
       <c r="B323" t="inlineStr">
         <is>
-          <t>2026-07-11 08:39:53 PM PT</t>
+          <t>2026-07-11 08:41:54 PM PT</t>
         </is>
       </c>
       <c r="C323" t="n">
-        <v>822953</v>
+        <v>823030</v>
       </c>
       <c r="D323" t="inlineStr">
         <is>
-          <t>1:10 PM PT</t>
+          <t>4:15 PM PT</t>
         </is>
       </c>
       <c r="E323" t="inlineStr">
@@ -37687,21 +37696,21 @@
       </c>
       <c r="L323" t="inlineStr">
         <is>
-          <t>TB</t>
+          <t>STL</t>
         </is>
       </c>
       <c r="M323" t="inlineStr">
         <is>
-          <t>SEA</t>
+          <t>ATL</t>
         </is>
       </c>
       <c r="N323" t="inlineStr">
         <is>
-          <t>Cedric Mullins</t>
+          <t>Nathan Church</t>
         </is>
       </c>
       <c r="O323" t="n">
-        <v>656775</v>
+        <v>701675</v>
       </c>
       <c r="P323" t="inlineStr">
         <is>
@@ -37710,7 +37719,7 @@
       </c>
       <c r="Q323" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>9</t>
         </is>
       </c>
       <c r="R323" t="n">
@@ -37750,16 +37759,16 @@
         <v>0</v>
       </c>
       <c r="AD323" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AE323" s="4" t="n">
         <v>0</v>
       </c>
       <c r="AF323" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="AG323" t="n">
-        <v>12</v>
+        <v>5</v>
       </c>
     </row>
     <row r="324">
@@ -37770,7 +37779,7 @@
       </c>
       <c r="B324" t="inlineStr">
         <is>
-          <t>2026-07-11 08:39:53 PM PT</t>
+          <t>2026-07-11 08:41:53 PM PT</t>
         </is>
       </c>
       <c r="C324" t="n">
@@ -37811,27 +37820,27 @@
       </c>
       <c r="N324" t="inlineStr">
         <is>
-          <t>Victor Mesa Jr.</t>
+          <t>Cedric Mullins</t>
         </is>
       </c>
       <c r="O324" t="n">
-        <v>683748</v>
+        <v>656775</v>
       </c>
       <c r="P324" t="inlineStr">
         <is>
-          <t>RF</t>
+          <t>CF</t>
         </is>
       </c>
       <c r="Q324" t="inlineStr">
         <is>
-          <t>4 (Sub)</t>
+          <t>4</t>
         </is>
       </c>
       <c r="R324" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="S324" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="T324" t="n">
         <v>0</v>
@@ -37884,7 +37893,7 @@
       </c>
       <c r="B325" t="inlineStr">
         <is>
-          <t>2026-07-11 08:39:53 PM PT</t>
+          <t>2026-07-11 08:41:53 PM PT</t>
         </is>
       </c>
       <c r="C325" t="n">
@@ -37925,27 +37934,27 @@
       </c>
       <c r="N325" t="inlineStr">
         <is>
-          <t>Jonny DeLuca</t>
+          <t>Victor Mesa Jr.</t>
         </is>
       </c>
       <c r="O325" t="n">
-        <v>676356</v>
+        <v>683748</v>
       </c>
       <c r="P325" t="inlineStr">
         <is>
-          <t>CF</t>
+          <t>RF</t>
         </is>
       </c>
       <c r="Q325" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>4 (Sub)</t>
         </is>
       </c>
       <c r="R325" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="S325" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="T325" t="n">
         <v>0</v>
@@ -37978,7 +37987,7 @@
         <v>0</v>
       </c>
       <c r="AD325" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AE325" s="4" t="n">
         <v>0</v>
@@ -37998,7 +38007,7 @@
       </c>
       <c r="B326" t="inlineStr">
         <is>
-          <t>2026-07-11 08:39:53 PM PT</t>
+          <t>2026-07-11 08:41:53 PM PT</t>
         </is>
       </c>
       <c r="C326" t="n">
@@ -38039,20 +38048,20 @@
       </c>
       <c r="N326" t="inlineStr">
         <is>
-          <t>Richie Palacios</t>
+          <t>Jonny DeLuca</t>
         </is>
       </c>
       <c r="O326" t="n">
-        <v>680700</v>
+        <v>676356</v>
       </c>
       <c r="P326" t="inlineStr">
         <is>
-          <t>2B</t>
+          <t>CF</t>
         </is>
       </c>
       <c r="Q326" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>5</t>
         </is>
       </c>
       <c r="R326" t="n">
@@ -38092,7 +38101,7 @@
         <v>0</v>
       </c>
       <c r="AD326" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AE326" s="4" t="n">
         <v>0</v>
@@ -38112,15 +38121,15 @@
       </c>
       <c r="B327" t="inlineStr">
         <is>
-          <t>2026-07-11 08:39:53 PM PT</t>
+          <t>2026-07-11 08:41:53 PM PT</t>
         </is>
       </c>
       <c r="C327" t="n">
-        <v>822875</v>
+        <v>822953</v>
       </c>
       <c r="D327" t="inlineStr">
         <is>
-          <t>4:05 PM PT</t>
+          <t>1:10 PM PT</t>
         </is>
       </c>
       <c r="E327" t="inlineStr">
@@ -38133,7 +38142,7 @@
       </c>
       <c r="G327" t="inlineStr">
         <is>
-          <t>Bottom</t>
+          <t>Top</t>
         </is>
       </c>
       <c r="K327" t="inlineStr">
@@ -38143,37 +38152,37 @@
       </c>
       <c r="L327" t="inlineStr">
         <is>
-          <t>TEX</t>
+          <t>TB</t>
         </is>
       </c>
       <c r="M327" t="inlineStr">
         <is>
-          <t>HOU</t>
+          <t>SEA</t>
         </is>
       </c>
       <c r="N327" t="inlineStr">
         <is>
-          <t>Alejandro Osuna</t>
+          <t>Richie Palacios</t>
         </is>
       </c>
       <c r="O327" t="n">
-        <v>696030</v>
+        <v>680700</v>
       </c>
       <c r="P327" t="inlineStr">
         <is>
-          <t>LF</t>
+          <t>2B</t>
         </is>
       </c>
       <c r="Q327" t="inlineStr">
         <is>
-          <t>2 (Sub)</t>
+          <t>8</t>
         </is>
       </c>
       <c r="R327" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="S327" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="T327" t="n">
         <v>0</v>
@@ -38212,10 +38221,10 @@
         <v>0</v>
       </c>
       <c r="AF327" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="AG327" t="n">
-        <v>7</v>
+        <v>12</v>
       </c>
     </row>
     <row r="328">
@@ -38226,7 +38235,7 @@
       </c>
       <c r="B328" t="inlineStr">
         <is>
-          <t>2026-07-11 08:39:53 PM PT</t>
+          <t>2026-07-11 08:41:53 PM PT</t>
         </is>
       </c>
       <c r="C328" t="n">
@@ -38267,27 +38276,27 @@
       </c>
       <c r="N328" t="inlineStr">
         <is>
-          <t>Brandon Nimmo</t>
+          <t>Alejandro Osuna</t>
         </is>
       </c>
       <c r="O328" t="n">
-        <v>607043</v>
+        <v>696030</v>
       </c>
       <c r="P328" t="inlineStr">
         <is>
-          <t>RF</t>
+          <t>LF</t>
         </is>
       </c>
       <c r="Q328" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>2 (Sub)</t>
         </is>
       </c>
       <c r="R328" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="S328" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="T328" t="n">
         <v>0</v>
@@ -38320,7 +38329,7 @@
         <v>0</v>
       </c>
       <c r="AD328" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="AE328" s="4" t="n">
         <v>0</v>
@@ -38340,7 +38349,7 @@
       </c>
       <c r="B329" t="inlineStr">
         <is>
-          <t>2026-07-11 08:39:53 PM PT</t>
+          <t>2026-07-11 08:41:53 PM PT</t>
         </is>
       </c>
       <c r="C329" t="n">
@@ -38381,20 +38390,20 @@
       </c>
       <c r="N329" t="inlineStr">
         <is>
-          <t>Jake Burger</t>
+          <t>Brandon Nimmo</t>
         </is>
       </c>
       <c r="O329" t="n">
-        <v>669394</v>
+        <v>607043</v>
       </c>
       <c r="P329" t="inlineStr">
         <is>
-          <t>1B</t>
+          <t>RF</t>
         </is>
       </c>
       <c r="Q329" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>4</t>
         </is>
       </c>
       <c r="R329" t="n">
@@ -38434,7 +38443,7 @@
         <v>0</v>
       </c>
       <c r="AD329" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="AE329" s="4" t="n">
         <v>0</v>
@@ -38454,7 +38463,7 @@
       </c>
       <c r="B330" t="inlineStr">
         <is>
-          <t>2026-07-11 08:39:53 PM PT</t>
+          <t>2026-07-11 08:41:53 PM PT</t>
         </is>
       </c>
       <c r="C330" t="n">
@@ -38495,27 +38504,27 @@
       </c>
       <c r="N330" t="inlineStr">
         <is>
-          <t>Justin Foscue</t>
+          <t>Jake Burger</t>
         </is>
       </c>
       <c r="O330" t="n">
-        <v>679822</v>
+        <v>669394</v>
       </c>
       <c r="P330" t="inlineStr">
         <is>
-          <t>PH</t>
+          <t>1B</t>
         </is>
       </c>
       <c r="Q330" t="inlineStr">
         <is>
-          <t>5 (Sub)</t>
+          <t>5</t>
         </is>
       </c>
       <c r="R330" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="S330" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="T330" t="n">
         <v>0</v>
@@ -38568,7 +38577,7 @@
       </c>
       <c r="B331" t="inlineStr">
         <is>
-          <t>2026-07-11 08:39:53 PM PT</t>
+          <t>2026-07-11 08:41:53 PM PT</t>
         </is>
       </c>
       <c r="C331" t="n">
@@ -38609,27 +38618,27 @@
       </c>
       <c r="N331" t="inlineStr">
         <is>
-          <t>Nicky Lopez</t>
+          <t>Justin Foscue</t>
         </is>
       </c>
       <c r="O331" t="n">
-        <v>670032</v>
+        <v>679822</v>
       </c>
       <c r="P331" t="inlineStr">
         <is>
-          <t>2B</t>
+          <t>PH</t>
         </is>
       </c>
       <c r="Q331" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>5 (Sub)</t>
         </is>
       </c>
       <c r="R331" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="S331" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="T331" t="n">
         <v>0</v>
@@ -38682,70 +38691,61 @@
       </c>
       <c r="B332" t="inlineStr">
         <is>
-          <t>2026-07-11 08:39:54 PM PT</t>
+          <t>2026-07-11 08:41:53 PM PT</t>
         </is>
       </c>
       <c r="C332" t="n">
-        <v>823276</v>
+        <v>822875</v>
       </c>
       <c r="D332" t="inlineStr">
         <is>
-          <t>5:40 PM PT</t>
+          <t>4:05 PM PT</t>
         </is>
       </c>
       <c r="E332" t="inlineStr">
         <is>
-          <t>Bottom 8 | 2 out</t>
+          <t>Final</t>
         </is>
       </c>
       <c r="F332" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="G332" t="inlineStr">
         <is>
           <t>Bottom</t>
         </is>
       </c>
-      <c r="H332" t="n">
-        <v>2</v>
-      </c>
-      <c r="I332" t="n">
-        <v>4</v>
-      </c>
-      <c r="J332" t="n">
-        <v>0</v>
-      </c>
       <c r="K332" t="inlineStr">
         <is>
-          <t>Away</t>
+          <t>Home</t>
         </is>
       </c>
       <c r="L332" t="inlineStr">
         <is>
-          <t>TOR</t>
+          <t>TEX</t>
         </is>
       </c>
       <c r="M332" t="inlineStr">
         <is>
-          <t>SD</t>
+          <t>HOU</t>
         </is>
       </c>
       <c r="N332" t="inlineStr">
         <is>
-          <t>George Springer</t>
+          <t>Nicky Lopez</t>
         </is>
       </c>
       <c r="O332" t="n">
-        <v>543807</v>
+        <v>670032</v>
       </c>
       <c r="P332" t="inlineStr">
         <is>
-          <t>DH</t>
+          <t>2B</t>
         </is>
       </c>
       <c r="Q332" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>8</t>
         </is>
       </c>
       <c r="R332" t="n">
@@ -38791,7 +38791,7 @@
         <v>0</v>
       </c>
       <c r="AF332" t="n">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="AG332" t="n">
         <v>7</v>
@@ -38805,61 +38805,70 @@
       </c>
       <c r="B333" t="inlineStr">
         <is>
-          <t>2026-07-11 08:39:53 PM PT</t>
+          <t>2026-07-11 08:41:54 PM PT</t>
         </is>
       </c>
       <c r="C333" t="n">
-        <v>822711</v>
+        <v>823276</v>
       </c>
       <c r="D333" t="inlineStr">
         <is>
-          <t>1:05 PM PT</t>
+          <t>5:40 PM PT</t>
         </is>
       </c>
       <c r="E333" t="inlineStr">
         <is>
-          <t>Final</t>
+          <t>Bottom 8 | 3 out</t>
         </is>
       </c>
       <c r="F333" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="G333" t="inlineStr">
         <is>
           <t>Bottom</t>
         </is>
       </c>
+      <c r="H333" t="n">
+        <v>3</v>
+      </c>
+      <c r="I333" t="n">
+        <v>1</v>
+      </c>
+      <c r="J333" t="n">
+        <v>2</v>
+      </c>
       <c r="K333" t="inlineStr">
         <is>
-          <t>Home</t>
+          <t>Away</t>
         </is>
       </c>
       <c r="L333" t="inlineStr">
         <is>
-          <t>WSH</t>
+          <t>TOR</t>
         </is>
       </c>
       <c r="M333" t="inlineStr">
         <is>
-          <t>NYY</t>
+          <t>SD</t>
         </is>
       </c>
       <c r="N333" t="inlineStr">
         <is>
-          <t>Daylen Lile</t>
+          <t>George Springer</t>
         </is>
       </c>
       <c r="O333" t="n">
-        <v>695734</v>
+        <v>543807</v>
       </c>
       <c r="P333" t="inlineStr">
         <is>
-          <t>LF</t>
+          <t>DH</t>
         </is>
       </c>
       <c r="Q333" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>4</t>
         </is>
       </c>
       <c r="R333" t="n">
@@ -38899,13 +38908,13 @@
         <v>0</v>
       </c>
       <c r="AD333" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AE333" s="4" t="n">
         <v>0</v>
       </c>
       <c r="AF333" t="n">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="AG333" t="n">
         <v>7</v>
@@ -38919,7 +38928,7 @@
       </c>
       <c r="B334" t="inlineStr">
         <is>
-          <t>2026-07-11 08:39:53 PM PT</t>
+          <t>2026-07-11 08:41:53 PM PT</t>
         </is>
       </c>
       <c r="C334" t="n">
@@ -38960,27 +38969,27 @@
       </c>
       <c r="N334" t="inlineStr">
         <is>
-          <t>José Tena</t>
+          <t>Daylen Lile</t>
         </is>
       </c>
       <c r="O334" t="n">
-        <v>677588</v>
+        <v>695734</v>
       </c>
       <c r="P334" t="inlineStr">
         <is>
-          <t>PH</t>
+          <t>LF</t>
         </is>
       </c>
       <c r="Q334" t="inlineStr">
         <is>
-          <t>8 (Sub)</t>
+          <t>5</t>
         </is>
       </c>
       <c r="R334" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="S334" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="T334" t="n">
         <v>0</v>
@@ -39013,7 +39022,7 @@
         <v>0</v>
       </c>
       <c r="AD334" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AE334" s="4" t="n">
         <v>0</v>
@@ -39025,9 +39034,123 @@
         <v>7</v>
       </c>
     </row>
+    <row r="335">
+      <c r="A335" t="inlineStr">
+        <is>
+          <t>2026-07-11</t>
+        </is>
+      </c>
+      <c r="B335" t="inlineStr">
+        <is>
+          <t>2026-07-11 08:41:53 PM PT</t>
+        </is>
+      </c>
+      <c r="C335" t="n">
+        <v>822711</v>
+      </c>
+      <c r="D335" t="inlineStr">
+        <is>
+          <t>1:05 PM PT</t>
+        </is>
+      </c>
+      <c r="E335" t="inlineStr">
+        <is>
+          <t>Final</t>
+        </is>
+      </c>
+      <c r="F335" t="n">
+        <v>9</v>
+      </c>
+      <c r="G335" t="inlineStr">
+        <is>
+          <t>Bottom</t>
+        </is>
+      </c>
+      <c r="K335" t="inlineStr">
+        <is>
+          <t>Home</t>
+        </is>
+      </c>
+      <c r="L335" t="inlineStr">
+        <is>
+          <t>WSH</t>
+        </is>
+      </c>
+      <c r="M335" t="inlineStr">
+        <is>
+          <t>NYY</t>
+        </is>
+      </c>
+      <c r="N335" t="inlineStr">
+        <is>
+          <t>José Tena</t>
+        </is>
+      </c>
+      <c r="O335" t="n">
+        <v>677588</v>
+      </c>
+      <c r="P335" t="inlineStr">
+        <is>
+          <t>PH</t>
+        </is>
+      </c>
+      <c r="Q335" t="inlineStr">
+        <is>
+          <t>8 (Sub)</t>
+        </is>
+      </c>
+      <c r="R335" t="n">
+        <v>1</v>
+      </c>
+      <c r="S335" t="n">
+        <v>1</v>
+      </c>
+      <c r="T335" t="n">
+        <v>0</v>
+      </c>
+      <c r="U335" t="n">
+        <v>0</v>
+      </c>
+      <c r="V335" t="n">
+        <v>0</v>
+      </c>
+      <c r="W335" t="n">
+        <v>0</v>
+      </c>
+      <c r="X335" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y335" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z335" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA335" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB335" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC335" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD335" t="n">
+        <v>1</v>
+      </c>
+      <c r="AE335" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF335" t="n">
+        <v>2</v>
+      </c>
+      <c r="AG335" t="n">
+        <v>7</v>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:AG334"/>
-  <conditionalFormatting sqref="AE2:AE334">
+  <autoFilter ref="A1:AG335"/>
+  <conditionalFormatting sqref="AE2:AE335">
     <cfRule type="colorScale" priority="1">
       <colorScale>
         <cfvo type="num" val="0"/>

--- a/live_mlb_hitter_fantasy_scores_2026_07_11.xlsx
+++ b/live_mlb_hitter_fantasy_scores_2026_07_11.xlsx
@@ -487,7 +487,7 @@
     <col width="27" customWidth="1" min="2" max="2"/>
     <col width="10" customWidth="1" min="3" max="3"/>
     <col width="14" customWidth="1" min="4" max="4"/>
-    <col width="18" customWidth="1" min="5" max="5"/>
+    <col width="15" customWidth="1" min="5" max="5"/>
     <col width="10" customWidth="1" min="6" max="6"/>
     <col width="13" customWidth="1" min="7" max="7"/>
     <col width="10" customWidth="1" min="8" max="8"/>
@@ -693,7 +693,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-07-11 08:41:52 PM PT</t>
+          <t>2026-07-11 08:43:52 PM PT</t>
         </is>
       </c>
       <c r="C2" t="n">
@@ -807,7 +807,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>2026-07-11 08:41:54 PM PT</t>
+          <t>2026-07-11 08:43:54 PM PT</t>
         </is>
       </c>
       <c r="C3" t="n">
@@ -820,25 +820,25 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Bottom 8 | 2 out</t>
+          <t>Top 9 | 0 out</t>
         </is>
       </c>
       <c r="F3" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Bottom</t>
+          <t>Top</t>
         </is>
       </c>
       <c r="H3" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="I3" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J3" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="K3" t="inlineStr">
         <is>
@@ -930,7 +930,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-07-11 08:41:53 PM PT</t>
+          <t>2026-07-11 08:43:53 PM PT</t>
         </is>
       </c>
       <c r="C4" t="n">
@@ -1044,7 +1044,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>2026-07-11 08:41:54 PM PT</t>
+          <t>2026-07-11 08:43:54 PM PT</t>
         </is>
       </c>
       <c r="C5" t="n">
@@ -1057,25 +1057,25 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Bottom 8 | 3 out</t>
+          <t>Top 9 | 0 out</t>
         </is>
       </c>
       <c r="F5" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Bottom</t>
+          <t>Top</t>
         </is>
       </c>
       <c r="H5" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="I5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J5" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="K5" t="inlineStr">
         <is>
@@ -1167,7 +1167,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>2026-07-11 08:41:53 PM PT</t>
+          <t>2026-07-11 08:43:53 PM PT</t>
         </is>
       </c>
       <c r="C6" t="n">
@@ -1281,7 +1281,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>2026-07-11 08:41:54 PM PT</t>
+          <t>2026-07-11 08:43:54 PM PT</t>
         </is>
       </c>
       <c r="C7" t="n">
@@ -1395,7 +1395,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>2026-07-11 08:41:53 PM PT</t>
+          <t>2026-07-11 08:43:53 PM PT</t>
         </is>
       </c>
       <c r="C8" t="n">
@@ -1509,7 +1509,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>2026-07-11 08:41:53 PM PT</t>
+          <t>2026-07-11 08:43:53 PM PT</t>
         </is>
       </c>
       <c r="C9" t="n">
@@ -1623,7 +1623,7 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>2026-07-11 08:41:53 PM PT</t>
+          <t>2026-07-11 08:43:53 PM PT</t>
         </is>
       </c>
       <c r="C10" t="n">
@@ -1737,7 +1737,7 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>2026-07-11 08:41:54 PM PT</t>
+          <t>2026-07-11 08:43:54 PM PT</t>
         </is>
       </c>
       <c r="C11" t="n">
@@ -1750,25 +1750,25 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Bottom 8 | 3 out</t>
+          <t>Top 9 | 0 out</t>
         </is>
       </c>
       <c r="F11" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Bottom</t>
+          <t>Top</t>
         </is>
       </c>
       <c r="H11" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="I11" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J11" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="K11" t="inlineStr">
         <is>
@@ -1860,7 +1860,7 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>2026-07-11 08:41:53 PM PT</t>
+          <t>2026-07-11 08:43:53 PM PT</t>
         </is>
       </c>
       <c r="C12" t="n">
@@ -1974,7 +1974,7 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>2026-07-11 08:41:53 PM PT</t>
+          <t>2026-07-11 08:43:53 PM PT</t>
         </is>
       </c>
       <c r="C13" t="n">
@@ -2088,7 +2088,7 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>2026-07-11 08:41:54 PM PT</t>
+          <t>2026-07-11 08:43:54 PM PT</t>
         </is>
       </c>
       <c r="C14" t="n">
@@ -2101,25 +2101,25 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Bottom 8 | 3 out</t>
+          <t>Top 9 | 0 out</t>
         </is>
       </c>
       <c r="F14" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Bottom</t>
+          <t>Top</t>
         </is>
       </c>
       <c r="H14" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="I14" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J14" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="K14" t="inlineStr">
         <is>
@@ -2211,7 +2211,7 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>2026-07-11 08:41:53 PM PT</t>
+          <t>2026-07-11 08:43:53 PM PT</t>
         </is>
       </c>
       <c r="C15" t="n">
@@ -2325,7 +2325,7 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>2026-07-11 08:41:53 PM PT</t>
+          <t>2026-07-11 08:43:53 PM PT</t>
         </is>
       </c>
       <c r="C16" t="n">
@@ -2439,7 +2439,7 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>2026-07-11 08:41:53 PM PT</t>
+          <t>2026-07-11 08:43:53 PM PT</t>
         </is>
       </c>
       <c r="C17" t="n">
@@ -2553,7 +2553,7 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>2026-07-11 08:41:54 PM PT</t>
+          <t>2026-07-11 08:43:54 PM PT</t>
         </is>
       </c>
       <c r="C18" t="n">
@@ -2566,25 +2566,25 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Bottom 8 | 3 out</t>
+          <t>Top 9 | 0 out</t>
         </is>
       </c>
       <c r="F18" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Bottom</t>
+          <t>Top</t>
         </is>
       </c>
       <c r="H18" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="I18" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J18" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="K18" t="inlineStr">
         <is>
@@ -2676,7 +2676,7 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>2026-07-11 08:41:53 PM PT</t>
+          <t>2026-07-11 08:43:53 PM PT</t>
         </is>
       </c>
       <c r="C19" t="n">
@@ -2790,7 +2790,7 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>2026-07-11 08:41:54 PM PT</t>
+          <t>2026-07-11 08:43:54 PM PT</t>
         </is>
       </c>
       <c r="C20" t="n">
@@ -2904,7 +2904,7 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>2026-07-11 08:41:53 PM PT</t>
+          <t>2026-07-11 08:43:53 PM PT</t>
         </is>
       </c>
       <c r="C21" t="n">
@@ -3018,7 +3018,7 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>2026-07-11 08:41:53 PM PT</t>
+          <t>2026-07-11 08:43:53 PM PT</t>
         </is>
       </c>
       <c r="C22" t="n">
@@ -3132,7 +3132,7 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>2026-07-11 08:41:54 PM PT</t>
+          <t>2026-07-11 08:43:54 PM PT</t>
         </is>
       </c>
       <c r="C23" t="n">
@@ -3145,25 +3145,25 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Bottom 8 | 2 out</t>
+          <t>Top 9 | 0 out</t>
         </is>
       </c>
       <c r="F23" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Bottom</t>
+          <t>Top</t>
         </is>
       </c>
       <c r="H23" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="I23" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J23" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="K23" t="inlineStr">
         <is>
@@ -3255,7 +3255,7 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>2026-07-11 08:41:53 PM PT</t>
+          <t>2026-07-11 08:43:53 PM PT</t>
         </is>
       </c>
       <c r="C24" t="n">
@@ -3369,7 +3369,7 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>2026-07-11 08:41:53 PM PT</t>
+          <t>2026-07-11 08:43:53 PM PT</t>
         </is>
       </c>
       <c r="C25" t="n">
@@ -3483,7 +3483,7 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>2026-07-11 08:41:54 PM PT</t>
+          <t>2026-07-11 08:43:54 PM PT</t>
         </is>
       </c>
       <c r="C26" t="n">
@@ -3597,7 +3597,7 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>2026-07-11 08:41:52 PM PT</t>
+          <t>2026-07-11 08:43:52 PM PT</t>
         </is>
       </c>
       <c r="C27" t="n">
@@ -3711,7 +3711,7 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>2026-07-11 08:41:53 PM PT</t>
+          <t>2026-07-11 08:43:53 PM PT</t>
         </is>
       </c>
       <c r="C28" t="n">
@@ -3825,7 +3825,7 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>2026-07-11 08:41:53 PM PT</t>
+          <t>2026-07-11 08:43:53 PM PT</t>
         </is>
       </c>
       <c r="C29" t="n">
@@ -3939,7 +3939,7 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>2026-07-11 08:41:54 PM PT</t>
+          <t>2026-07-11 08:43:54 PM PT</t>
         </is>
       </c>
       <c r="C30" t="n">
@@ -4053,7 +4053,7 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>2026-07-11 08:41:54 PM PT</t>
+          <t>2026-07-11 08:43:54 PM PT</t>
         </is>
       </c>
       <c r="C31" t="n">
@@ -4167,7 +4167,7 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>2026-07-11 08:41:53 PM PT</t>
+          <t>2026-07-11 08:43:53 PM PT</t>
         </is>
       </c>
       <c r="C32" t="n">
@@ -4281,7 +4281,7 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>2026-07-11 08:41:53 PM PT</t>
+          <t>2026-07-11 08:43:53 PM PT</t>
         </is>
       </c>
       <c r="C33" t="n">
@@ -4395,7 +4395,7 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>2026-07-11 08:41:53 PM PT</t>
+          <t>2026-07-11 08:43:53 PM PT</t>
         </is>
       </c>
       <c r="C34" t="n">
@@ -4509,7 +4509,7 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>2026-07-11 08:41:52 PM PT</t>
+          <t>2026-07-11 08:43:52 PM PT</t>
         </is>
       </c>
       <c r="C35" t="n">
@@ -4623,7 +4623,7 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>2026-07-11 08:41:52 PM PT</t>
+          <t>2026-07-11 08:43:53 PM PT</t>
         </is>
       </c>
       <c r="C36" t="n">
@@ -4737,7 +4737,7 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>2026-07-11 08:41:54 PM PT</t>
+          <t>2026-07-11 08:43:54 PM PT</t>
         </is>
       </c>
       <c r="C37" t="n">
@@ -4750,25 +4750,25 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Bottom 8 | 3 out</t>
+          <t>Top 9 | 0 out</t>
         </is>
       </c>
       <c r="F37" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Bottom</t>
+          <t>Top</t>
         </is>
       </c>
       <c r="H37" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="I37" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J37" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="K37" t="inlineStr">
         <is>
@@ -4860,7 +4860,7 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>2026-07-11 08:41:53 PM PT</t>
+          <t>2026-07-11 08:43:53 PM PT</t>
         </is>
       </c>
       <c r="C38" t="n">
@@ -4974,7 +4974,7 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>2026-07-11 08:41:53 PM PT</t>
+          <t>2026-07-11 08:43:53 PM PT</t>
         </is>
       </c>
       <c r="C39" t="n">
@@ -5088,7 +5088,7 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>2026-07-11 08:41:53 PM PT</t>
+          <t>2026-07-11 08:43:53 PM PT</t>
         </is>
       </c>
       <c r="C40" t="n">
@@ -5202,7 +5202,7 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>2026-07-11 08:41:52 PM PT</t>
+          <t>2026-07-11 08:43:53 PM PT</t>
         </is>
       </c>
       <c r="C41" t="n">
@@ -5316,7 +5316,7 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>2026-07-11 08:41:54 PM PT</t>
+          <t>2026-07-11 08:43:54 PM PT</t>
         </is>
       </c>
       <c r="C42" t="n">
@@ -5329,25 +5329,25 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>Bottom 8 | 2 out</t>
+          <t>Top 9 | 0 out</t>
         </is>
       </c>
       <c r="F42" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Bottom</t>
+          <t>Top</t>
         </is>
       </c>
       <c r="H42" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="I42" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J42" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="K42" t="inlineStr">
         <is>
@@ -5439,7 +5439,7 @@
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>2026-07-11 08:41:54 PM PT</t>
+          <t>2026-07-11 08:43:54 PM PT</t>
         </is>
       </c>
       <c r="C43" t="n">
@@ -5553,7 +5553,7 @@
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>2026-07-11 08:41:53 PM PT</t>
+          <t>2026-07-11 08:43:53 PM PT</t>
         </is>
       </c>
       <c r="C44" t="n">
@@ -5667,7 +5667,7 @@
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>2026-07-11 08:41:53 PM PT</t>
+          <t>2026-07-11 08:43:53 PM PT</t>
         </is>
       </c>
       <c r="C45" t="n">
@@ -5781,7 +5781,7 @@
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>2026-07-11 08:41:54 PM PT</t>
+          <t>2026-07-11 08:43:54 PM PT</t>
         </is>
       </c>
       <c r="C46" t="n">
@@ -5895,7 +5895,7 @@
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>2026-07-11 08:41:53 PM PT</t>
+          <t>2026-07-11 08:43:53 PM PT</t>
         </is>
       </c>
       <c r="C47" t="n">
@@ -6009,7 +6009,7 @@
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>2026-07-11 08:41:53 PM PT</t>
+          <t>2026-07-11 08:43:53 PM PT</t>
         </is>
       </c>
       <c r="C48" t="n">
@@ -6123,7 +6123,7 @@
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>2026-07-11 08:41:53 PM PT</t>
+          <t>2026-07-11 08:43:53 PM PT</t>
         </is>
       </c>
       <c r="C49" t="n">
@@ -6237,7 +6237,7 @@
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>2026-07-11 08:41:53 PM PT</t>
+          <t>2026-07-11 08:43:53 PM PT</t>
         </is>
       </c>
       <c r="C50" t="n">
@@ -6351,7 +6351,7 @@
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>2026-07-11 08:41:52 PM PT</t>
+          <t>2026-07-11 08:43:53 PM PT</t>
         </is>
       </c>
       <c r="C51" t="n">
@@ -6465,7 +6465,7 @@
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>2026-07-11 08:41:54 PM PT</t>
+          <t>2026-07-11 08:43:54 PM PT</t>
         </is>
       </c>
       <c r="C52" t="n">
@@ -6478,25 +6478,25 @@
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>Bottom 8 | 3 out</t>
+          <t>Top 9 | 0 out</t>
         </is>
       </c>
       <c r="F52" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Bottom</t>
+          <t>Top</t>
         </is>
       </c>
       <c r="H52" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="I52" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J52" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="K52" t="inlineStr">
         <is>
@@ -6588,7 +6588,7 @@
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>2026-07-11 08:41:54 PM PT</t>
+          <t>2026-07-11 08:43:54 PM PT</t>
         </is>
       </c>
       <c r="C53" t="n">
@@ -6601,25 +6601,25 @@
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>Bottom 8 | 2 out</t>
+          <t>Top 9 | 0 out</t>
         </is>
       </c>
       <c r="F53" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Bottom</t>
+          <t>Top</t>
         </is>
       </c>
       <c r="H53" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="I53" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J53" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="K53" t="inlineStr">
         <is>
@@ -6711,7 +6711,7 @@
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>2026-07-11 08:41:54 PM PT</t>
+          <t>2026-07-11 08:43:54 PM PT</t>
         </is>
       </c>
       <c r="C54" t="n">
@@ -6825,7 +6825,7 @@
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>2026-07-11 08:41:54 PM PT</t>
+          <t>2026-07-11 08:43:54 PM PT</t>
         </is>
       </c>
       <c r="C55" t="n">
@@ -6939,7 +6939,7 @@
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>2026-07-11 08:41:53 PM PT</t>
+          <t>2026-07-11 08:43:53 PM PT</t>
         </is>
       </c>
       <c r="C56" t="n">
@@ -7053,7 +7053,7 @@
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>2026-07-11 08:41:53 PM PT</t>
+          <t>2026-07-11 08:43:53 PM PT</t>
         </is>
       </c>
       <c r="C57" t="n">
@@ -7167,7 +7167,7 @@
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>2026-07-11 08:41:53 PM PT</t>
+          <t>2026-07-11 08:43:53 PM PT</t>
         </is>
       </c>
       <c r="C58" t="n">
@@ -7281,7 +7281,7 @@
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>2026-07-11 08:41:53 PM PT</t>
+          <t>2026-07-11 08:43:53 PM PT</t>
         </is>
       </c>
       <c r="C59" t="n">
@@ -7395,7 +7395,7 @@
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>2026-07-11 08:41:53 PM PT</t>
+          <t>2026-07-11 08:43:53 PM PT</t>
         </is>
       </c>
       <c r="C60" t="n">
@@ -7509,7 +7509,7 @@
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>2026-07-11 08:41:53 PM PT</t>
+          <t>2026-07-11 08:43:53 PM PT</t>
         </is>
       </c>
       <c r="C61" t="n">
@@ -7623,7 +7623,7 @@
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>2026-07-11 08:41:53 PM PT</t>
+          <t>2026-07-11 08:43:53 PM PT</t>
         </is>
       </c>
       <c r="C62" t="n">
@@ -7737,7 +7737,7 @@
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>2026-07-11 08:41:52 PM PT</t>
+          <t>2026-07-11 08:43:52 PM PT</t>
         </is>
       </c>
       <c r="C63" t="n">
@@ -7851,7 +7851,7 @@
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>2026-07-11 08:41:52 PM PT</t>
+          <t>2026-07-11 08:43:52 PM PT</t>
         </is>
       </c>
       <c r="C64" t="n">
@@ -7965,7 +7965,7 @@
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>2026-07-11 08:41:54 PM PT</t>
+          <t>2026-07-11 08:43:54 PM PT</t>
         </is>
       </c>
       <c r="C65" t="n">
@@ -7978,25 +7978,25 @@
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>Bottom 8 | 3 out</t>
+          <t>Top 9 | 0 out</t>
         </is>
       </c>
       <c r="F65" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>Bottom</t>
+          <t>Top</t>
         </is>
       </c>
       <c r="H65" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="I65" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J65" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="K65" t="inlineStr">
         <is>
@@ -8088,7 +8088,7 @@
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>2026-07-11 08:41:54 PM PT</t>
+          <t>2026-07-11 08:43:54 PM PT</t>
         </is>
       </c>
       <c r="C66" t="n">
@@ -8101,25 +8101,25 @@
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>Bottom 8 | 2 out</t>
+          <t>Top 9 | 0 out</t>
         </is>
       </c>
       <c r="F66" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>Bottom</t>
+          <t>Top</t>
         </is>
       </c>
       <c r="H66" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="I66" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J66" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="K66" t="inlineStr">
         <is>
@@ -8211,7 +8211,7 @@
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>2026-07-11 08:41:53 PM PT</t>
+          <t>2026-07-11 08:43:53 PM PT</t>
         </is>
       </c>
       <c r="C67" t="n">
@@ -8325,7 +8325,7 @@
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>2026-07-11 08:41:53 PM PT</t>
+          <t>2026-07-11 08:43:53 PM PT</t>
         </is>
       </c>
       <c r="C68" t="n">
@@ -8439,7 +8439,7 @@
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>2026-07-11 08:41:53 PM PT</t>
+          <t>2026-07-11 08:43:53 PM PT</t>
         </is>
       </c>
       <c r="C69" t="n">
@@ -8553,7 +8553,7 @@
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>2026-07-11 08:41:53 PM PT</t>
+          <t>2026-07-11 08:43:53 PM PT</t>
         </is>
       </c>
       <c r="C70" t="n">
@@ -8667,7 +8667,7 @@
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>2026-07-11 08:41:53 PM PT</t>
+          <t>2026-07-11 08:43:53 PM PT</t>
         </is>
       </c>
       <c r="C71" t="n">
@@ -8781,7 +8781,7 @@
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>2026-07-11 08:41:54 PM PT</t>
+          <t>2026-07-11 08:43:54 PM PT</t>
         </is>
       </c>
       <c r="C72" t="n">
@@ -8794,25 +8794,25 @@
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>Bottom 8 | 2 out</t>
+          <t>Top 9 | 0 out</t>
         </is>
       </c>
       <c r="F72" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>Bottom</t>
+          <t>Top</t>
         </is>
       </c>
       <c r="H72" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="I72" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J72" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="K72" t="inlineStr">
         <is>
@@ -8904,7 +8904,7 @@
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>2026-07-11 08:41:52 PM PT</t>
+          <t>2026-07-11 08:43:53 PM PT</t>
         </is>
       </c>
       <c r="C73" t="n">
@@ -9018,7 +9018,7 @@
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>2026-07-11 08:41:53 PM PT</t>
+          <t>2026-07-11 08:43:53 PM PT</t>
         </is>
       </c>
       <c r="C74" t="n">
@@ -9132,7 +9132,7 @@
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>2026-07-11 08:41:52 PM PT</t>
+          <t>2026-07-11 08:43:53 PM PT</t>
         </is>
       </c>
       <c r="C75" t="n">
@@ -9246,7 +9246,7 @@
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>2026-07-11 08:41:54 PM PT</t>
+          <t>2026-07-11 08:43:54 PM PT</t>
         </is>
       </c>
       <c r="C76" t="n">
@@ -9259,25 +9259,25 @@
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>Bottom 8 | 3 out</t>
+          <t>Top 9 | 0 out</t>
         </is>
       </c>
       <c r="F76" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>Bottom</t>
+          <t>Top</t>
         </is>
       </c>
       <c r="H76" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="I76" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J76" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="K76" t="inlineStr">
         <is>
@@ -9369,7 +9369,7 @@
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>2026-07-11 08:41:54 PM PT</t>
+          <t>2026-07-11 08:43:54 PM PT</t>
         </is>
       </c>
       <c r="C77" t="n">
@@ -9382,25 +9382,25 @@
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>Bottom 8 | 3 out</t>
+          <t>Top 9 | 0 out</t>
         </is>
       </c>
       <c r="F77" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>Bottom</t>
+          <t>Top</t>
         </is>
       </c>
       <c r="H77" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="I77" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J77" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="K77" t="inlineStr">
         <is>
@@ -9492,7 +9492,7 @@
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>2026-07-11 08:41:54 PM PT</t>
+          <t>2026-07-11 08:43:54 PM PT</t>
         </is>
       </c>
       <c r="C78" t="n">
@@ -9606,7 +9606,7 @@
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>2026-07-11 08:41:54 PM PT</t>
+          <t>2026-07-11 08:43:54 PM PT</t>
         </is>
       </c>
       <c r="C79" t="n">
@@ -9720,7 +9720,7 @@
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>2026-07-11 08:41:53 PM PT</t>
+          <t>2026-07-11 08:43:53 PM PT</t>
         </is>
       </c>
       <c r="C80" t="n">
@@ -9834,7 +9834,7 @@
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>2026-07-11 08:41:52 PM PT</t>
+          <t>2026-07-11 08:43:52 PM PT</t>
         </is>
       </c>
       <c r="C81" t="n">
@@ -9948,7 +9948,7 @@
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>2026-07-11 08:41:52 PM PT</t>
+          <t>2026-07-11 08:43:53 PM PT</t>
         </is>
       </c>
       <c r="C82" t="n">
@@ -10062,7 +10062,7 @@
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>2026-07-11 08:41:52 PM PT</t>
+          <t>2026-07-11 08:43:53 PM PT</t>
         </is>
       </c>
       <c r="C83" t="n">
@@ -10176,7 +10176,7 @@
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>2026-07-11 08:41:52 PM PT</t>
+          <t>2026-07-11 08:43:52 PM PT</t>
         </is>
       </c>
       <c r="C84" t="n">
@@ -10290,7 +10290,7 @@
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>2026-07-11 08:41:52 PM PT</t>
+          <t>2026-07-11 08:43:52 PM PT</t>
         </is>
       </c>
       <c r="C85" t="n">
@@ -10404,7 +10404,7 @@
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>2026-07-11 08:41:52 PM PT</t>
+          <t>2026-07-11 08:43:52 PM PT</t>
         </is>
       </c>
       <c r="C86" t="n">
@@ -10518,7 +10518,7 @@
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>2026-07-11 08:41:53 PM PT</t>
+          <t>2026-07-11 08:43:53 PM PT</t>
         </is>
       </c>
       <c r="C87" t="n">
@@ -10632,7 +10632,7 @@
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>2026-07-11 08:41:53 PM PT</t>
+          <t>2026-07-11 08:43:53 PM PT</t>
         </is>
       </c>
       <c r="C88" t="n">
@@ -10746,7 +10746,7 @@
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>2026-07-11 08:41:53 PM PT</t>
+          <t>2026-07-11 08:43:53 PM PT</t>
         </is>
       </c>
       <c r="C89" t="n">
@@ -10860,7 +10860,7 @@
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>2026-07-11 08:41:53 PM PT</t>
+          <t>2026-07-11 08:43:53 PM PT</t>
         </is>
       </c>
       <c r="C90" t="n">
@@ -10974,7 +10974,7 @@
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>2026-07-11 08:41:53 PM PT</t>
+          <t>2026-07-11 08:43:53 PM PT</t>
         </is>
       </c>
       <c r="C91" t="n">
@@ -11088,7 +11088,7 @@
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>2026-07-11 08:41:54 PM PT</t>
+          <t>2026-07-11 08:43:54 PM PT</t>
         </is>
       </c>
       <c r="C92" t="n">
@@ -11202,7 +11202,7 @@
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>2026-07-11 08:41:54 PM PT</t>
+          <t>2026-07-11 08:43:54 PM PT</t>
         </is>
       </c>
       <c r="C93" t="n">
@@ -11215,25 +11215,25 @@
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>Bottom 8 | 2 out</t>
+          <t>Top 9 | 0 out</t>
         </is>
       </c>
       <c r="F93" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>Bottom</t>
+          <t>Top</t>
         </is>
       </c>
       <c r="H93" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="I93" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J93" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="K93" t="inlineStr">
         <is>
@@ -11325,7 +11325,7 @@
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>2026-07-11 08:41:53 PM PT</t>
+          <t>2026-07-11 08:43:53 PM PT</t>
         </is>
       </c>
       <c r="C94" t="n">
@@ -11439,7 +11439,7 @@
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>2026-07-11 08:41:53 PM PT</t>
+          <t>2026-07-11 08:43:53 PM PT</t>
         </is>
       </c>
       <c r="C95" t="n">
@@ -11553,7 +11553,7 @@
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>2026-07-11 08:41:53 PM PT</t>
+          <t>2026-07-11 08:43:53 PM PT</t>
         </is>
       </c>
       <c r="C96" t="n">
@@ -11667,7 +11667,7 @@
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>2026-07-11 08:41:53 PM PT</t>
+          <t>2026-07-11 08:43:53 PM PT</t>
         </is>
       </c>
       <c r="C97" t="n">
@@ -11781,7 +11781,7 @@
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>2026-07-11 08:41:53 PM PT</t>
+          <t>2026-07-11 08:43:53 PM PT</t>
         </is>
       </c>
       <c r="C98" t="n">
@@ -11895,7 +11895,7 @@
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>2026-07-11 08:41:54 PM PT</t>
+          <t>2026-07-11 08:43:54 PM PT</t>
         </is>
       </c>
       <c r="C99" t="n">
@@ -11908,25 +11908,25 @@
       </c>
       <c r="E99" t="inlineStr">
         <is>
-          <t>Bottom 8 | 2 out</t>
+          <t>Top 9 | 0 out</t>
         </is>
       </c>
       <c r="F99" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>Bottom</t>
+          <t>Top</t>
         </is>
       </c>
       <c r="H99" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="I99" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J99" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="K99" t="inlineStr">
         <is>
@@ -12018,7 +12018,7 @@
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>2026-07-11 08:41:53 PM PT</t>
+          <t>2026-07-11 08:43:53 PM PT</t>
         </is>
       </c>
       <c r="C100" t="n">
@@ -12132,7 +12132,7 @@
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>2026-07-11 08:41:52 PM PT</t>
+          <t>2026-07-11 08:43:53 PM PT</t>
         </is>
       </c>
       <c r="C101" t="n">
@@ -12246,7 +12246,7 @@
       </c>
       <c r="B102" t="inlineStr">
         <is>
-          <t>2026-07-11 08:41:53 PM PT</t>
+          <t>2026-07-11 08:43:53 PM PT</t>
         </is>
       </c>
       <c r="C102" t="n">
@@ -12360,7 +12360,7 @@
       </c>
       <c r="B103" t="inlineStr">
         <is>
-          <t>2026-07-11 08:41:53 PM PT</t>
+          <t>2026-07-11 08:43:53 PM PT</t>
         </is>
       </c>
       <c r="C103" t="n">
@@ -12474,7 +12474,7 @@
       </c>
       <c r="B104" t="inlineStr">
         <is>
-          <t>2026-07-11 08:41:54 PM PT</t>
+          <t>2026-07-11 08:43:54 PM PT</t>
         </is>
       </c>
       <c r="C104" t="n">
@@ -12487,25 +12487,25 @@
       </c>
       <c r="E104" t="inlineStr">
         <is>
-          <t>Bottom 8 | 3 out</t>
+          <t>Top 9 | 0 out</t>
         </is>
       </c>
       <c r="F104" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="G104" t="inlineStr">
         <is>
-          <t>Bottom</t>
+          <t>Top</t>
         </is>
       </c>
       <c r="H104" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="I104" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J104" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="K104" t="inlineStr">
         <is>
@@ -12597,7 +12597,7 @@
       </c>
       <c r="B105" t="inlineStr">
         <is>
-          <t>2026-07-11 08:41:53 PM PT</t>
+          <t>2026-07-11 08:43:53 PM PT</t>
         </is>
       </c>
       <c r="C105" t="n">
@@ -12711,7 +12711,7 @@
       </c>
       <c r="B106" t="inlineStr">
         <is>
-          <t>2026-07-11 08:41:53 PM PT</t>
+          <t>2026-07-11 08:43:53 PM PT</t>
         </is>
       </c>
       <c r="C106" t="n">
@@ -12825,7 +12825,7 @@
       </c>
       <c r="B107" t="inlineStr">
         <is>
-          <t>2026-07-11 08:41:53 PM PT</t>
+          <t>2026-07-11 08:43:53 PM PT</t>
         </is>
       </c>
       <c r="C107" t="n">
@@ -12939,7 +12939,7 @@
       </c>
       <c r="B108" t="inlineStr">
         <is>
-          <t>2026-07-11 08:41:53 PM PT</t>
+          <t>2026-07-11 08:43:53 PM PT</t>
         </is>
       </c>
       <c r="C108" t="n">
@@ -13053,7 +13053,7 @@
       </c>
       <c r="B109" t="inlineStr">
         <is>
-          <t>2026-07-11 08:41:53 PM PT</t>
+          <t>2026-07-11 08:43:53 PM PT</t>
         </is>
       </c>
       <c r="C109" t="n">
@@ -13167,7 +13167,7 @@
       </c>
       <c r="B110" t="inlineStr">
         <is>
-          <t>2026-07-11 08:41:53 PM PT</t>
+          <t>2026-07-11 08:43:53 PM PT</t>
         </is>
       </c>
       <c r="C110" t="n">
@@ -13281,7 +13281,7 @@
       </c>
       <c r="B111" t="inlineStr">
         <is>
-          <t>2026-07-11 08:41:53 PM PT</t>
+          <t>2026-07-11 08:43:53 PM PT</t>
         </is>
       </c>
       <c r="C111" t="n">
@@ -13395,7 +13395,7 @@
       </c>
       <c r="B112" t="inlineStr">
         <is>
-          <t>2026-07-11 08:41:54 PM PT</t>
+          <t>2026-07-11 08:43:54 PM PT</t>
         </is>
       </c>
       <c r="C112" t="n">
@@ -13509,7 +13509,7 @@
       </c>
       <c r="B113" t="inlineStr">
         <is>
-          <t>2026-07-11 08:41:53 PM PT</t>
+          <t>2026-07-11 08:43:53 PM PT</t>
         </is>
       </c>
       <c r="C113" t="n">
@@ -13623,7 +13623,7 @@
       </c>
       <c r="B114" t="inlineStr">
         <is>
-          <t>2026-07-11 08:41:53 PM PT</t>
+          <t>2026-07-11 08:43:53 PM PT</t>
         </is>
       </c>
       <c r="C114" t="n">
@@ -13737,7 +13737,7 @@
       </c>
       <c r="B115" t="inlineStr">
         <is>
-          <t>2026-07-11 08:41:53 PM PT</t>
+          <t>2026-07-11 08:43:53 PM PT</t>
         </is>
       </c>
       <c r="C115" t="n">
@@ -13851,7 +13851,7 @@
       </c>
       <c r="B116" t="inlineStr">
         <is>
-          <t>2026-07-11 08:41:54 PM PT</t>
+          <t>2026-07-11 08:43:54 PM PT</t>
         </is>
       </c>
       <c r="C116" t="n">
@@ -13864,25 +13864,25 @@
       </c>
       <c r="E116" t="inlineStr">
         <is>
-          <t>Bottom 8 | 3 out</t>
+          <t>Top 9 | 0 out</t>
         </is>
       </c>
       <c r="F116" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="G116" t="inlineStr">
         <is>
-          <t>Bottom</t>
+          <t>Top</t>
         </is>
       </c>
       <c r="H116" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="I116" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J116" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="K116" t="inlineStr">
         <is>
@@ -13974,7 +13974,7 @@
       </c>
       <c r="B117" t="inlineStr">
         <is>
-          <t>2026-07-11 08:41:54 PM PT</t>
+          <t>2026-07-11 08:43:54 PM PT</t>
         </is>
       </c>
       <c r="C117" t="n">
@@ -13987,25 +13987,25 @@
       </c>
       <c r="E117" t="inlineStr">
         <is>
-          <t>Bottom 8 | 3 out</t>
+          <t>Top 9 | 0 out</t>
         </is>
       </c>
       <c r="F117" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="G117" t="inlineStr">
         <is>
-          <t>Bottom</t>
+          <t>Top</t>
         </is>
       </c>
       <c r="H117" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="I117" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J117" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="K117" t="inlineStr">
         <is>
@@ -14097,7 +14097,7 @@
       </c>
       <c r="B118" t="inlineStr">
         <is>
-          <t>2026-07-11 08:41:53 PM PT</t>
+          <t>2026-07-11 08:43:53 PM PT</t>
         </is>
       </c>
       <c r="C118" t="n">
@@ -14211,7 +14211,7 @@
       </c>
       <c r="B119" t="inlineStr">
         <is>
-          <t>2026-07-11 08:41:54 PM PT</t>
+          <t>2026-07-11 08:43:54 PM PT</t>
         </is>
       </c>
       <c r="C119" t="n">
@@ -14325,7 +14325,7 @@
       </c>
       <c r="B120" t="inlineStr">
         <is>
-          <t>2026-07-11 08:41:54 PM PT</t>
+          <t>2026-07-11 08:43:54 PM PT</t>
         </is>
       </c>
       <c r="C120" t="n">
@@ -14439,7 +14439,7 @@
       </c>
       <c r="B121" t="inlineStr">
         <is>
-          <t>2026-07-11 08:41:53 PM PT</t>
+          <t>2026-07-11 08:43:53 PM PT</t>
         </is>
       </c>
       <c r="C121" t="n">
@@ -14553,7 +14553,7 @@
       </c>
       <c r="B122" t="inlineStr">
         <is>
-          <t>2026-07-11 08:41:53 PM PT</t>
+          <t>2026-07-11 08:43:53 PM PT</t>
         </is>
       </c>
       <c r="C122" t="n">
@@ -14667,7 +14667,7 @@
       </c>
       <c r="B123" t="inlineStr">
         <is>
-          <t>2026-07-11 08:41:54 PM PT</t>
+          <t>2026-07-11 08:43:54 PM PT</t>
         </is>
       </c>
       <c r="C123" t="n">
@@ -14781,7 +14781,7 @@
       </c>
       <c r="B124" t="inlineStr">
         <is>
-          <t>2026-07-11 08:41:53 PM PT</t>
+          <t>2026-07-11 08:43:53 PM PT</t>
         </is>
       </c>
       <c r="C124" t="n">
@@ -14895,7 +14895,7 @@
       </c>
       <c r="B125" t="inlineStr">
         <is>
-          <t>2026-07-11 08:41:53 PM PT</t>
+          <t>2026-07-11 08:43:53 PM PT</t>
         </is>
       </c>
       <c r="C125" t="n">
@@ -15009,7 +15009,7 @@
       </c>
       <c r="B126" t="inlineStr">
         <is>
-          <t>2026-07-11 08:41:53 PM PT</t>
+          <t>2026-07-11 08:43:53 PM PT</t>
         </is>
       </c>
       <c r="C126" t="n">
@@ -15123,7 +15123,7 @@
       </c>
       <c r="B127" t="inlineStr">
         <is>
-          <t>2026-07-11 08:41:53 PM PT</t>
+          <t>2026-07-11 08:43:53 PM PT</t>
         </is>
       </c>
       <c r="C127" t="n">
@@ -15237,7 +15237,7 @@
       </c>
       <c r="B128" t="inlineStr">
         <is>
-          <t>2026-07-11 08:41:53 PM PT</t>
+          <t>2026-07-11 08:43:53 PM PT</t>
         </is>
       </c>
       <c r="C128" t="n">
@@ -15351,7 +15351,7 @@
       </c>
       <c r="B129" t="inlineStr">
         <is>
-          <t>2026-07-11 08:41:53 PM PT</t>
+          <t>2026-07-11 08:43:53 PM PT</t>
         </is>
       </c>
       <c r="C129" t="n">
@@ -15465,7 +15465,7 @@
       </c>
       <c r="B130" t="inlineStr">
         <is>
-          <t>2026-07-11 08:41:54 PM PT</t>
+          <t>2026-07-11 08:43:54 PM PT</t>
         </is>
       </c>
       <c r="C130" t="n">
@@ -15478,25 +15478,25 @@
       </c>
       <c r="E130" t="inlineStr">
         <is>
-          <t>Bottom 8 | 2 out</t>
+          <t>Top 9 | 0 out</t>
         </is>
       </c>
       <c r="F130" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="G130" t="inlineStr">
         <is>
-          <t>Bottom</t>
+          <t>Top</t>
         </is>
       </c>
       <c r="H130" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="I130" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J130" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="K130" t="inlineStr">
         <is>
@@ -15588,7 +15588,7 @@
       </c>
       <c r="B131" t="inlineStr">
         <is>
-          <t>2026-07-11 08:41:53 PM PT</t>
+          <t>2026-07-11 08:43:53 PM PT</t>
         </is>
       </c>
       <c r="C131" t="n">
@@ -15702,7 +15702,7 @@
       </c>
       <c r="B132" t="inlineStr">
         <is>
-          <t>2026-07-11 08:41:53 PM PT</t>
+          <t>2026-07-11 08:43:53 PM PT</t>
         </is>
       </c>
       <c r="C132" t="n">
@@ -15816,7 +15816,7 @@
       </c>
       <c r="B133" t="inlineStr">
         <is>
-          <t>2026-07-11 08:41:52 PM PT</t>
+          <t>2026-07-11 08:43:53 PM PT</t>
         </is>
       </c>
       <c r="C133" t="n">
@@ -15930,7 +15930,7 @@
       </c>
       <c r="B134" t="inlineStr">
         <is>
-          <t>2026-07-11 08:41:53 PM PT</t>
+          <t>2026-07-11 08:43:53 PM PT</t>
         </is>
       </c>
       <c r="C134" t="n">
@@ -16044,7 +16044,7 @@
       </c>
       <c r="B135" t="inlineStr">
         <is>
-          <t>2026-07-11 08:41:53 PM PT</t>
+          <t>2026-07-11 08:43:53 PM PT</t>
         </is>
       </c>
       <c r="C135" t="n">
@@ -16158,7 +16158,7 @@
       </c>
       <c r="B136" t="inlineStr">
         <is>
-          <t>2026-07-11 08:41:53 PM PT</t>
+          <t>2026-07-11 08:43:53 PM PT</t>
         </is>
       </c>
       <c r="C136" t="n">
@@ -16272,7 +16272,7 @@
       </c>
       <c r="B137" t="inlineStr">
         <is>
-          <t>2026-07-11 08:41:52 PM PT</t>
+          <t>2026-07-11 08:43:52 PM PT</t>
         </is>
       </c>
       <c r="C137" t="n">
@@ -16386,7 +16386,7 @@
       </c>
       <c r="B138" t="inlineStr">
         <is>
-          <t>2026-07-11 08:41:52 PM PT</t>
+          <t>2026-07-11 08:43:52 PM PT</t>
         </is>
       </c>
       <c r="C138" t="n">
@@ -16500,7 +16500,7 @@
       </c>
       <c r="B139" t="inlineStr">
         <is>
-          <t>2026-07-11 08:41:53 PM PT</t>
+          <t>2026-07-11 08:43:53 PM PT</t>
         </is>
       </c>
       <c r="C139" t="n">
@@ -16614,7 +16614,7 @@
       </c>
       <c r="B140" t="inlineStr">
         <is>
-          <t>2026-07-11 08:41:53 PM PT</t>
+          <t>2026-07-11 08:43:53 PM PT</t>
         </is>
       </c>
       <c r="C140" t="n">
@@ -16728,7 +16728,7 @@
       </c>
       <c r="B141" t="inlineStr">
         <is>
-          <t>2026-07-11 08:41:53 PM PT</t>
+          <t>2026-07-11 08:43:53 PM PT</t>
         </is>
       </c>
       <c r="C141" t="n">
@@ -16842,7 +16842,7 @@
       </c>
       <c r="B142" t="inlineStr">
         <is>
-          <t>2026-07-11 08:41:54 PM PT</t>
+          <t>2026-07-11 08:43:54 PM PT</t>
         </is>
       </c>
       <c r="C142" t="n">
@@ -16956,7 +16956,7 @@
       </c>
       <c r="B143" t="inlineStr">
         <is>
-          <t>2026-07-11 08:41:54 PM PT</t>
+          <t>2026-07-11 08:43:54 PM PT</t>
         </is>
       </c>
       <c r="C143" t="n">
@@ -17070,7 +17070,7 @@
       </c>
       <c r="B144" t="inlineStr">
         <is>
-          <t>2026-07-11 08:41:54 PM PT</t>
+          <t>2026-07-11 08:43:54 PM PT</t>
         </is>
       </c>
       <c r="C144" t="n">
@@ -17184,7 +17184,7 @@
       </c>
       <c r="B145" t="inlineStr">
         <is>
-          <t>2026-07-11 08:41:53 PM PT</t>
+          <t>2026-07-11 08:43:53 PM PT</t>
         </is>
       </c>
       <c r="C145" t="n">
@@ -17298,7 +17298,7 @@
       </c>
       <c r="B146" t="inlineStr">
         <is>
-          <t>2026-07-11 08:41:53 PM PT</t>
+          <t>2026-07-11 08:43:53 PM PT</t>
         </is>
       </c>
       <c r="C146" t="n">
@@ -17412,7 +17412,7 @@
       </c>
       <c r="B147" t="inlineStr">
         <is>
-          <t>2026-07-11 08:41:53 PM PT</t>
+          <t>2026-07-11 08:43:53 PM PT</t>
         </is>
       </c>
       <c r="C147" t="n">
@@ -17526,7 +17526,7 @@
       </c>
       <c r="B148" t="inlineStr">
         <is>
-          <t>2026-07-11 08:41:54 PM PT</t>
+          <t>2026-07-11 08:43:54 PM PT</t>
         </is>
       </c>
       <c r="C148" t="n">
@@ -17640,7 +17640,7 @@
       </c>
       <c r="B149" t="inlineStr">
         <is>
-          <t>2026-07-11 08:41:53 PM PT</t>
+          <t>2026-07-11 08:43:53 PM PT</t>
         </is>
       </c>
       <c r="C149" t="n">
@@ -17754,7 +17754,7 @@
       </c>
       <c r="B150" t="inlineStr">
         <is>
-          <t>2026-07-11 08:41:53 PM PT</t>
+          <t>2026-07-11 08:43:53 PM PT</t>
         </is>
       </c>
       <c r="C150" t="n">
@@ -17868,7 +17868,7 @@
       </c>
       <c r="B151" t="inlineStr">
         <is>
-          <t>2026-07-11 08:41:52 PM PT</t>
+          <t>2026-07-11 08:43:52 PM PT</t>
         </is>
       </c>
       <c r="C151" t="n">
@@ -17982,7 +17982,7 @@
       </c>
       <c r="B152" t="inlineStr">
         <is>
-          <t>2026-07-11 08:41:52 PM PT</t>
+          <t>2026-07-11 08:43:53 PM PT</t>
         </is>
       </c>
       <c r="C152" t="n">
@@ -18096,7 +18096,7 @@
       </c>
       <c r="B153" t="inlineStr">
         <is>
-          <t>2026-07-11 08:41:53 PM PT</t>
+          <t>2026-07-11 08:43:53 PM PT</t>
         </is>
       </c>
       <c r="C153" t="n">
@@ -18210,7 +18210,7 @@
       </c>
       <c r="B154" t="inlineStr">
         <is>
-          <t>2026-07-11 08:41:53 PM PT</t>
+          <t>2026-07-11 08:43:53 PM PT</t>
         </is>
       </c>
       <c r="C154" t="n">
@@ -18324,7 +18324,7 @@
       </c>
       <c r="B155" t="inlineStr">
         <is>
-          <t>2026-07-11 08:41:53 PM PT</t>
+          <t>2026-07-11 08:43:53 PM PT</t>
         </is>
       </c>
       <c r="C155" t="n">
@@ -18438,7 +18438,7 @@
       </c>
       <c r="B156" t="inlineStr">
         <is>
-          <t>2026-07-11 08:41:52 PM PT</t>
+          <t>2026-07-11 08:43:52 PM PT</t>
         </is>
       </c>
       <c r="C156" t="n">
@@ -18552,7 +18552,7 @@
       </c>
       <c r="B157" t="inlineStr">
         <is>
-          <t>2026-07-11 08:41:54 PM PT</t>
+          <t>2026-07-11 08:43:54 PM PT</t>
         </is>
       </c>
       <c r="C157" t="n">
@@ -18565,25 +18565,25 @@
       </c>
       <c r="E157" t="inlineStr">
         <is>
-          <t>Bottom 8 | 3 out</t>
+          <t>Top 9 | 0 out</t>
         </is>
       </c>
       <c r="F157" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="G157" t="inlineStr">
         <is>
-          <t>Bottom</t>
+          <t>Top</t>
         </is>
       </c>
       <c r="H157" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="I157" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J157" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="K157" t="inlineStr">
         <is>
@@ -18675,7 +18675,7 @@
       </c>
       <c r="B158" t="inlineStr">
         <is>
-          <t>2026-07-11 08:41:54 PM PT</t>
+          <t>2026-07-11 08:43:54 PM PT</t>
         </is>
       </c>
       <c r="C158" t="n">
@@ -18688,25 +18688,25 @@
       </c>
       <c r="E158" t="inlineStr">
         <is>
-          <t>Bottom 8 | 3 out</t>
+          <t>Top 9 | 0 out</t>
         </is>
       </c>
       <c r="F158" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="G158" t="inlineStr">
         <is>
-          <t>Bottom</t>
+          <t>Top</t>
         </is>
       </c>
       <c r="H158" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="I158" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J158" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="K158" t="inlineStr">
         <is>
@@ -18798,7 +18798,7 @@
       </c>
       <c r="B159" t="inlineStr">
         <is>
-          <t>2026-07-11 08:41:54 PM PT</t>
+          <t>2026-07-11 08:43:54 PM PT</t>
         </is>
       </c>
       <c r="C159" t="n">
@@ -18811,25 +18811,25 @@
       </c>
       <c r="E159" t="inlineStr">
         <is>
-          <t>Bottom 8 | 3 out</t>
+          <t>Top 9 | 0 out</t>
         </is>
       </c>
       <c r="F159" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="G159" t="inlineStr">
         <is>
-          <t>Bottom</t>
+          <t>Top</t>
         </is>
       </c>
       <c r="H159" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="I159" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J159" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="K159" t="inlineStr">
         <is>
@@ -18921,7 +18921,7 @@
       </c>
       <c r="B160" t="inlineStr">
         <is>
-          <t>2026-07-11 08:41:54 PM PT</t>
+          <t>2026-07-11 08:43:54 PM PT</t>
         </is>
       </c>
       <c r="C160" t="n">
@@ -19035,7 +19035,7 @@
       </c>
       <c r="B161" t="inlineStr">
         <is>
-          <t>2026-07-11 08:41:54 PM PT</t>
+          <t>2026-07-11 08:43:54 PM PT</t>
         </is>
       </c>
       <c r="C161" t="n">
@@ -19149,7 +19149,7 @@
       </c>
       <c r="B162" t="inlineStr">
         <is>
-          <t>2026-07-11 08:41:54 PM PT</t>
+          <t>2026-07-11 08:43:54 PM PT</t>
         </is>
       </c>
       <c r="C162" t="n">
@@ -19263,7 +19263,7 @@
       </c>
       <c r="B163" t="inlineStr">
         <is>
-          <t>2026-07-11 08:41:54 PM PT</t>
+          <t>2026-07-11 08:43:54 PM PT</t>
         </is>
       </c>
       <c r="C163" t="n">
@@ -19377,7 +19377,7 @@
       </c>
       <c r="B164" t="inlineStr">
         <is>
-          <t>2026-07-11 08:41:54 PM PT</t>
+          <t>2026-07-11 08:43:54 PM PT</t>
         </is>
       </c>
       <c r="C164" t="n">
@@ -19491,7 +19491,7 @@
       </c>
       <c r="B165" t="inlineStr">
         <is>
-          <t>2026-07-11 08:41:53 PM PT</t>
+          <t>2026-07-11 08:43:53 PM PT</t>
         </is>
       </c>
       <c r="C165" t="n">
@@ -19605,7 +19605,7 @@
       </c>
       <c r="B166" t="inlineStr">
         <is>
-          <t>2026-07-11 08:41:53 PM PT</t>
+          <t>2026-07-11 08:43:53 PM PT</t>
         </is>
       </c>
       <c r="C166" t="n">
@@ -19719,7 +19719,7 @@
       </c>
       <c r="B167" t="inlineStr">
         <is>
-          <t>2026-07-11 08:41:53 PM PT</t>
+          <t>2026-07-11 08:43:53 PM PT</t>
         </is>
       </c>
       <c r="C167" t="n">
@@ -19833,7 +19833,7 @@
       </c>
       <c r="B168" t="inlineStr">
         <is>
-          <t>2026-07-11 08:41:53 PM PT</t>
+          <t>2026-07-11 08:43:53 PM PT</t>
         </is>
       </c>
       <c r="C168" t="n">
@@ -19947,7 +19947,7 @@
       </c>
       <c r="B169" t="inlineStr">
         <is>
-          <t>2026-07-11 08:41:53 PM PT</t>
+          <t>2026-07-11 08:43:53 PM PT</t>
         </is>
       </c>
       <c r="C169" t="n">
@@ -20061,7 +20061,7 @@
       </c>
       <c r="B170" t="inlineStr">
         <is>
-          <t>2026-07-11 08:41:53 PM PT</t>
+          <t>2026-07-11 08:43:53 PM PT</t>
         </is>
       </c>
       <c r="C170" t="n">
@@ -20175,7 +20175,7 @@
       </c>
       <c r="B171" t="inlineStr">
         <is>
-          <t>2026-07-11 08:41:54 PM PT</t>
+          <t>2026-07-11 08:43:54 PM PT</t>
         </is>
       </c>
       <c r="C171" t="n">
@@ -20188,25 +20188,25 @@
       </c>
       <c r="E171" t="inlineStr">
         <is>
-          <t>Bottom 8 | 2 out</t>
+          <t>Top 9 | 0 out</t>
         </is>
       </c>
       <c r="F171" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="G171" t="inlineStr">
         <is>
-          <t>Bottom</t>
+          <t>Top</t>
         </is>
       </c>
       <c r="H171" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="I171" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J171" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="K171" t="inlineStr">
         <is>
@@ -20298,7 +20298,7 @@
       </c>
       <c r="B172" t="inlineStr">
         <is>
-          <t>2026-07-11 08:41:54 PM PT</t>
+          <t>2026-07-11 08:43:54 PM PT</t>
         </is>
       </c>
       <c r="C172" t="n">
@@ -20311,25 +20311,25 @@
       </c>
       <c r="E172" t="inlineStr">
         <is>
-          <t>Bottom 8 | 2 out</t>
+          <t>Top 9 | 0 out</t>
         </is>
       </c>
       <c r="F172" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="G172" t="inlineStr">
         <is>
-          <t>Bottom</t>
+          <t>Top</t>
         </is>
       </c>
       <c r="H172" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="I172" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J172" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="K172" t="inlineStr">
         <is>
@@ -20421,7 +20421,7 @@
       </c>
       <c r="B173" t="inlineStr">
         <is>
-          <t>2026-07-11 08:41:53 PM PT</t>
+          <t>2026-07-11 08:43:53 PM PT</t>
         </is>
       </c>
       <c r="C173" t="n">
@@ -20535,7 +20535,7 @@
       </c>
       <c r="B174" t="inlineStr">
         <is>
-          <t>2026-07-11 08:41:53 PM PT</t>
+          <t>2026-07-11 08:43:53 PM PT</t>
         </is>
       </c>
       <c r="C174" t="n">
@@ -20649,7 +20649,7 @@
       </c>
       <c r="B175" t="inlineStr">
         <is>
-          <t>2026-07-11 08:41:52 PM PT</t>
+          <t>2026-07-11 08:43:52 PM PT</t>
         </is>
       </c>
       <c r="C175" t="n">
@@ -20763,7 +20763,7 @@
       </c>
       <c r="B176" t="inlineStr">
         <is>
-          <t>2026-07-11 08:41:52 PM PT</t>
+          <t>2026-07-11 08:43:53 PM PT</t>
         </is>
       </c>
       <c r="C176" t="n">
@@ -20877,7 +20877,7 @@
       </c>
       <c r="B177" t="inlineStr">
         <is>
-          <t>2026-07-11 08:41:53 PM PT</t>
+          <t>2026-07-11 08:43:53 PM PT</t>
         </is>
       </c>
       <c r="C177" t="n">
@@ -20991,7 +20991,7 @@
       </c>
       <c r="B178" t="inlineStr">
         <is>
-          <t>2026-07-11 08:41:53 PM PT</t>
+          <t>2026-07-11 08:43:53 PM PT</t>
         </is>
       </c>
       <c r="C178" t="n">
@@ -21105,7 +21105,7 @@
       </c>
       <c r="B179" t="inlineStr">
         <is>
-          <t>2026-07-11 08:41:53 PM PT</t>
+          <t>2026-07-11 08:43:53 PM PT</t>
         </is>
       </c>
       <c r="C179" t="n">
@@ -21219,7 +21219,7 @@
       </c>
       <c r="B180" t="inlineStr">
         <is>
-          <t>2026-07-11 08:41:53 PM PT</t>
+          <t>2026-07-11 08:43:53 PM PT</t>
         </is>
       </c>
       <c r="C180" t="n">
@@ -21333,7 +21333,7 @@
       </c>
       <c r="B181" t="inlineStr">
         <is>
-          <t>2026-07-11 08:41:53 PM PT</t>
+          <t>2026-07-11 08:43:53 PM PT</t>
         </is>
       </c>
       <c r="C181" t="n">
@@ -21447,7 +21447,7 @@
       </c>
       <c r="B182" t="inlineStr">
         <is>
-          <t>2026-07-11 08:41:53 PM PT</t>
+          <t>2026-07-11 08:43:53 PM PT</t>
         </is>
       </c>
       <c r="C182" t="n">
@@ -21561,7 +21561,7 @@
       </c>
       <c r="B183" t="inlineStr">
         <is>
-          <t>2026-07-11 08:41:53 PM PT</t>
+          <t>2026-07-11 08:43:53 PM PT</t>
         </is>
       </c>
       <c r="C183" t="n">
@@ -21675,7 +21675,7 @@
       </c>
       <c r="B184" t="inlineStr">
         <is>
-          <t>2026-07-11 08:41:52 PM PT</t>
+          <t>2026-07-11 08:43:53 PM PT</t>
         </is>
       </c>
       <c r="C184" t="n">
@@ -21789,7 +21789,7 @@
       </c>
       <c r="B185" t="inlineStr">
         <is>
-          <t>2026-07-11 08:41:52 PM PT</t>
+          <t>2026-07-11 08:43:53 PM PT</t>
         </is>
       </c>
       <c r="C185" t="n">
@@ -21903,7 +21903,7 @@
       </c>
       <c r="B186" t="inlineStr">
         <is>
-          <t>2026-07-11 08:41:53 PM PT</t>
+          <t>2026-07-11 08:43:53 PM PT</t>
         </is>
       </c>
       <c r="C186" t="n">
@@ -22017,7 +22017,7 @@
       </c>
       <c r="B187" t="inlineStr">
         <is>
-          <t>2026-07-11 08:41:53 PM PT</t>
+          <t>2026-07-11 08:43:53 PM PT</t>
         </is>
       </c>
       <c r="C187" t="n">
@@ -22131,7 +22131,7 @@
       </c>
       <c r="B188" t="inlineStr">
         <is>
-          <t>2026-07-11 08:41:53 PM PT</t>
+          <t>2026-07-11 08:43:53 PM PT</t>
         </is>
       </c>
       <c r="C188" t="n">
@@ -22245,7 +22245,7 @@
       </c>
       <c r="B189" t="inlineStr">
         <is>
-          <t>2026-07-11 08:41:53 PM PT</t>
+          <t>2026-07-11 08:43:53 PM PT</t>
         </is>
       </c>
       <c r="C189" t="n">
@@ -22359,7 +22359,7 @@
       </c>
       <c r="B190" t="inlineStr">
         <is>
-          <t>2026-07-11 08:41:54 PM PT</t>
+          <t>2026-07-11 08:43:54 PM PT</t>
         </is>
       </c>
       <c r="C190" t="n">
@@ -22372,25 +22372,25 @@
       </c>
       <c r="E190" t="inlineStr">
         <is>
-          <t>Bottom 8 | 3 out</t>
+          <t>Top 9 | 0 out</t>
         </is>
       </c>
       <c r="F190" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="G190" t="inlineStr">
         <is>
-          <t>Bottom</t>
+          <t>Top</t>
         </is>
       </c>
       <c r="H190" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="I190" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J190" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="K190" t="inlineStr">
         <is>
@@ -22482,7 +22482,7 @@
       </c>
       <c r="B191" t="inlineStr">
         <is>
-          <t>2026-07-11 08:41:53 PM PT</t>
+          <t>2026-07-11 08:43:53 PM PT</t>
         </is>
       </c>
       <c r="C191" t="n">
@@ -22596,7 +22596,7 @@
       </c>
       <c r="B192" t="inlineStr">
         <is>
-          <t>2026-07-11 08:41:53 PM PT</t>
+          <t>2026-07-11 08:43:53 PM PT</t>
         </is>
       </c>
       <c r="C192" t="n">
@@ -22710,7 +22710,7 @@
       </c>
       <c r="B193" t="inlineStr">
         <is>
-          <t>2026-07-11 08:41:54 PM PT</t>
+          <t>2026-07-11 08:43:54 PM PT</t>
         </is>
       </c>
       <c r="C193" t="n">
@@ -22723,25 +22723,25 @@
       </c>
       <c r="E193" t="inlineStr">
         <is>
-          <t>Bottom 8 | 2 out</t>
+          <t>Top 9 | 0 out</t>
         </is>
       </c>
       <c r="F193" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="G193" t="inlineStr">
         <is>
-          <t>Bottom</t>
+          <t>Top</t>
         </is>
       </c>
       <c r="H193" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="I193" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J193" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="K193" t="inlineStr">
         <is>
@@ -22833,7 +22833,7 @@
       </c>
       <c r="B194" t="inlineStr">
         <is>
-          <t>2026-07-11 08:41:54 PM PT</t>
+          <t>2026-07-11 08:43:54 PM PT</t>
         </is>
       </c>
       <c r="C194" t="n">
@@ -22846,25 +22846,25 @@
       </c>
       <c r="E194" t="inlineStr">
         <is>
-          <t>Bottom 8 | 2 out</t>
+          <t>Top 9 | 0 out</t>
         </is>
       </c>
       <c r="F194" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="G194" t="inlineStr">
         <is>
-          <t>Bottom</t>
+          <t>Top</t>
         </is>
       </c>
       <c r="H194" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="I194" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J194" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="K194" t="inlineStr">
         <is>
@@ -22956,7 +22956,7 @@
       </c>
       <c r="B195" t="inlineStr">
         <is>
-          <t>2026-07-11 08:41:53 PM PT</t>
+          <t>2026-07-11 08:43:53 PM PT</t>
         </is>
       </c>
       <c r="C195" t="n">
@@ -23070,7 +23070,7 @@
       </c>
       <c r="B196" t="inlineStr">
         <is>
-          <t>2026-07-11 08:41:54 PM PT</t>
+          <t>2026-07-11 08:43:54 PM PT</t>
         </is>
       </c>
       <c r="C196" t="n">
@@ -23184,7 +23184,7 @@
       </c>
       <c r="B197" t="inlineStr">
         <is>
-          <t>2026-07-11 08:41:54 PM PT</t>
+          <t>2026-07-11 08:43:54 PM PT</t>
         </is>
       </c>
       <c r="C197" t="n">
@@ -23298,7 +23298,7 @@
       </c>
       <c r="B198" t="inlineStr">
         <is>
-          <t>2026-07-11 08:41:53 PM PT</t>
+          <t>2026-07-11 08:43:53 PM PT</t>
         </is>
       </c>
       <c r="C198" t="n">
@@ -23412,7 +23412,7 @@
       </c>
       <c r="B199" t="inlineStr">
         <is>
-          <t>2026-07-11 08:41:53 PM PT</t>
+          <t>2026-07-11 08:43:53 PM PT</t>
         </is>
       </c>
       <c r="C199" t="n">
@@ -23526,7 +23526,7 @@
       </c>
       <c r="B200" t="inlineStr">
         <is>
-          <t>2026-07-11 08:41:53 PM PT</t>
+          <t>2026-07-11 08:43:53 PM PT</t>
         </is>
       </c>
       <c r="C200" t="n">
@@ -23640,7 +23640,7 @@
       </c>
       <c r="B201" t="inlineStr">
         <is>
-          <t>2026-07-11 08:41:53 PM PT</t>
+          <t>2026-07-11 08:43:53 PM PT</t>
         </is>
       </c>
       <c r="C201" t="n">
@@ -23754,7 +23754,7 @@
       </c>
       <c r="B202" t="inlineStr">
         <is>
-          <t>2026-07-11 08:41:54 PM PT</t>
+          <t>2026-07-11 08:43:54 PM PT</t>
         </is>
       </c>
       <c r="C202" t="n">
@@ -23868,7 +23868,7 @@
       </c>
       <c r="B203" t="inlineStr">
         <is>
-          <t>2026-07-11 08:41:53 PM PT</t>
+          <t>2026-07-11 08:43:53 PM PT</t>
         </is>
       </c>
       <c r="C203" t="n">
@@ -23982,7 +23982,7 @@
       </c>
       <c r="B204" t="inlineStr">
         <is>
-          <t>2026-07-11 08:41:53 PM PT</t>
+          <t>2026-07-11 08:43:53 PM PT</t>
         </is>
       </c>
       <c r="C204" t="n">
@@ -24096,7 +24096,7 @@
       </c>
       <c r="B205" t="inlineStr">
         <is>
-          <t>2026-07-11 08:41:53 PM PT</t>
+          <t>2026-07-11 08:43:53 PM PT</t>
         </is>
       </c>
       <c r="C205" t="n">
@@ -24210,7 +24210,7 @@
       </c>
       <c r="B206" t="inlineStr">
         <is>
-          <t>2026-07-11 08:41:53 PM PT</t>
+          <t>2026-07-11 08:43:53 PM PT</t>
         </is>
       </c>
       <c r="C206" t="n">
@@ -24324,7 +24324,7 @@
       </c>
       <c r="B207" t="inlineStr">
         <is>
-          <t>2026-07-11 08:41:53 PM PT</t>
+          <t>2026-07-11 08:43:53 PM PT</t>
         </is>
       </c>
       <c r="C207" t="n">
@@ -24438,7 +24438,7 @@
       </c>
       <c r="B208" t="inlineStr">
         <is>
-          <t>2026-07-11 08:41:53 PM PT</t>
+          <t>2026-07-11 08:43:53 PM PT</t>
         </is>
       </c>
       <c r="C208" t="n">
@@ -24552,7 +24552,7 @@
       </c>
       <c r="B209" t="inlineStr">
         <is>
-          <t>2026-07-11 08:41:53 PM PT</t>
+          <t>2026-07-11 08:43:53 PM PT</t>
         </is>
       </c>
       <c r="C209" t="n">
@@ -24666,7 +24666,7 @@
       </c>
       <c r="B210" t="inlineStr">
         <is>
-          <t>2026-07-11 08:41:53 PM PT</t>
+          <t>2026-07-11 08:43:53 PM PT</t>
         </is>
       </c>
       <c r="C210" t="n">
@@ -24780,7 +24780,7 @@
       </c>
       <c r="B211" t="inlineStr">
         <is>
-          <t>2026-07-11 08:41:53 PM PT</t>
+          <t>2026-07-11 08:43:53 PM PT</t>
         </is>
       </c>
       <c r="C211" t="n">
@@ -24894,7 +24894,7 @@
       </c>
       <c r="B212" t="inlineStr">
         <is>
-          <t>2026-07-11 08:41:53 PM PT</t>
+          <t>2026-07-11 08:43:53 PM PT</t>
         </is>
       </c>
       <c r="C212" t="n">
@@ -25008,7 +25008,7 @@
       </c>
       <c r="B213" t="inlineStr">
         <is>
-          <t>2026-07-11 08:41:53 PM PT</t>
+          <t>2026-07-11 08:43:53 PM PT</t>
         </is>
       </c>
       <c r="C213" t="n">
@@ -25122,7 +25122,7 @@
       </c>
       <c r="B214" t="inlineStr">
         <is>
-          <t>2026-07-11 08:41:53 PM PT</t>
+          <t>2026-07-11 08:43:53 PM PT</t>
         </is>
       </c>
       <c r="C214" t="n">
@@ -25236,7 +25236,7 @@
       </c>
       <c r="B215" t="inlineStr">
         <is>
-          <t>2026-07-11 08:41:53 PM PT</t>
+          <t>2026-07-11 08:43:53 PM PT</t>
         </is>
       </c>
       <c r="C215" t="n">
@@ -25350,7 +25350,7 @@
       </c>
       <c r="B216" t="inlineStr">
         <is>
-          <t>2026-07-11 08:41:53 PM PT</t>
+          <t>2026-07-11 08:43:53 PM PT</t>
         </is>
       </c>
       <c r="C216" t="n">
@@ -25464,7 +25464,7 @@
       </c>
       <c r="B217" t="inlineStr">
         <is>
-          <t>2026-07-11 08:41:53 PM PT</t>
+          <t>2026-07-11 08:43:53 PM PT</t>
         </is>
       </c>
       <c r="C217" t="n">
@@ -25578,7 +25578,7 @@
       </c>
       <c r="B218" t="inlineStr">
         <is>
-          <t>2026-07-11 08:41:53 PM PT</t>
+          <t>2026-07-11 08:43:53 PM PT</t>
         </is>
       </c>
       <c r="C218" t="n">
@@ -25692,7 +25692,7 @@
       </c>
       <c r="B219" t="inlineStr">
         <is>
-          <t>2026-07-11 08:41:53 PM PT</t>
+          <t>2026-07-11 08:43:53 PM PT</t>
         </is>
       </c>
       <c r="C219" t="n">
@@ -25806,7 +25806,7 @@
       </c>
       <c r="B220" t="inlineStr">
         <is>
-          <t>2026-07-11 08:41:53 PM PT</t>
+          <t>2026-07-11 08:43:53 PM PT</t>
         </is>
       </c>
       <c r="C220" t="n">
@@ -25920,7 +25920,7 @@
       </c>
       <c r="B221" t="inlineStr">
         <is>
-          <t>2026-07-11 08:41:53 PM PT</t>
+          <t>2026-07-11 08:43:53 PM PT</t>
         </is>
       </c>
       <c r="C221" t="n">
@@ -26034,7 +26034,7 @@
       </c>
       <c r="B222" t="inlineStr">
         <is>
-          <t>2026-07-11 08:41:53 PM PT</t>
+          <t>2026-07-11 08:43:53 PM PT</t>
         </is>
       </c>
       <c r="C222" t="n">
@@ -26148,7 +26148,7 @@
       </c>
       <c r="B223" t="inlineStr">
         <is>
-          <t>2026-07-11 08:41:53 PM PT</t>
+          <t>2026-07-11 08:43:53 PM PT</t>
         </is>
       </c>
       <c r="C223" t="n">
@@ -26262,7 +26262,7 @@
       </c>
       <c r="B224" t="inlineStr">
         <is>
-          <t>2026-07-11 08:41:52 PM PT</t>
+          <t>2026-07-11 08:43:52 PM PT</t>
         </is>
       </c>
       <c r="C224" t="n">
@@ -26376,7 +26376,7 @@
       </c>
       <c r="B225" t="inlineStr">
         <is>
-          <t>2026-07-11 08:41:52 PM PT</t>
+          <t>2026-07-11 08:43:53 PM PT</t>
         </is>
       </c>
       <c r="C225" t="n">
@@ -26490,7 +26490,7 @@
       </c>
       <c r="B226" t="inlineStr">
         <is>
-          <t>2026-07-11 08:41:53 PM PT</t>
+          <t>2026-07-11 08:43:53 PM PT</t>
         </is>
       </c>
       <c r="C226" t="n">
@@ -26604,7 +26604,7 @@
       </c>
       <c r="B227" t="inlineStr">
         <is>
-          <t>2026-07-11 08:41:53 PM PT</t>
+          <t>2026-07-11 08:43:53 PM PT</t>
         </is>
       </c>
       <c r="C227" t="n">
@@ -26718,7 +26718,7 @@
       </c>
       <c r="B228" t="inlineStr">
         <is>
-          <t>2026-07-11 08:41:53 PM PT</t>
+          <t>2026-07-11 08:43:53 PM PT</t>
         </is>
       </c>
       <c r="C228" t="n">
@@ -26832,7 +26832,7 @@
       </c>
       <c r="B229" t="inlineStr">
         <is>
-          <t>2026-07-11 08:41:53 PM PT</t>
+          <t>2026-07-11 08:43:53 PM PT</t>
         </is>
       </c>
       <c r="C229" t="n">
@@ -26946,7 +26946,7 @@
       </c>
       <c r="B230" t="inlineStr">
         <is>
-          <t>2026-07-11 08:41:54 PM PT</t>
+          <t>2026-07-11 08:43:54 PM PT</t>
         </is>
       </c>
       <c r="C230" t="n">
@@ -26959,25 +26959,25 @@
       </c>
       <c r="E230" t="inlineStr">
         <is>
-          <t>Bottom 8 | 3 out</t>
+          <t>Top 9 | 0 out</t>
         </is>
       </c>
       <c r="F230" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="G230" t="inlineStr">
         <is>
-          <t>Bottom</t>
+          <t>Top</t>
         </is>
       </c>
       <c r="H230" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="I230" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J230" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="K230" t="inlineStr">
         <is>
@@ -27069,7 +27069,7 @@
       </c>
       <c r="B231" t="inlineStr">
         <is>
-          <t>2026-07-11 08:41:53 PM PT</t>
+          <t>2026-07-11 08:43:53 PM PT</t>
         </is>
       </c>
       <c r="C231" t="n">
@@ -27183,7 +27183,7 @@
       </c>
       <c r="B232" t="inlineStr">
         <is>
-          <t>2026-07-11 08:41:53 PM PT</t>
+          <t>2026-07-11 08:43:53 PM PT</t>
         </is>
       </c>
       <c r="C232" t="n">
@@ -27297,7 +27297,7 @@
       </c>
       <c r="B233" t="inlineStr">
         <is>
-          <t>2026-07-11 08:41:53 PM PT</t>
+          <t>2026-07-11 08:43:53 PM PT</t>
         </is>
       </c>
       <c r="C233" t="n">
@@ -27411,7 +27411,7 @@
       </c>
       <c r="B234" t="inlineStr">
         <is>
-          <t>2026-07-11 08:41:53 PM PT</t>
+          <t>2026-07-11 08:43:53 PM PT</t>
         </is>
       </c>
       <c r="C234" t="n">
@@ -27525,7 +27525,7 @@
       </c>
       <c r="B235" t="inlineStr">
         <is>
-          <t>2026-07-11 08:41:54 PM PT</t>
+          <t>2026-07-11 08:43:54 PM PT</t>
         </is>
       </c>
       <c r="C235" t="n">
@@ -27538,25 +27538,25 @@
       </c>
       <c r="E235" t="inlineStr">
         <is>
-          <t>Bottom 8 | 2 out</t>
+          <t>Top 9 | 0 out</t>
         </is>
       </c>
       <c r="F235" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="G235" t="inlineStr">
         <is>
-          <t>Bottom</t>
+          <t>Top</t>
         </is>
       </c>
       <c r="H235" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="I235" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J235" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="K235" t="inlineStr">
         <is>
@@ -27648,7 +27648,7 @@
       </c>
       <c r="B236" t="inlineStr">
         <is>
-          <t>2026-07-11 08:41:54 PM PT</t>
+          <t>2026-07-11 08:43:54 PM PT</t>
         </is>
       </c>
       <c r="C236" t="n">
@@ -27661,25 +27661,25 @@
       </c>
       <c r="E236" t="inlineStr">
         <is>
-          <t>Bottom 8 | 2 out</t>
+          <t>Top 9 | 0 out</t>
         </is>
       </c>
       <c r="F236" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="G236" t="inlineStr">
         <is>
-          <t>Bottom</t>
+          <t>Top</t>
         </is>
       </c>
       <c r="H236" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="I236" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J236" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="K236" t="inlineStr">
         <is>
@@ -27771,7 +27771,7 @@
       </c>
       <c r="B237" t="inlineStr">
         <is>
-          <t>2026-07-11 08:41:53 PM PT</t>
+          <t>2026-07-11 08:43:53 PM PT</t>
         </is>
       </c>
       <c r="C237" t="n">
@@ -27885,7 +27885,7 @@
       </c>
       <c r="B238" t="inlineStr">
         <is>
-          <t>2026-07-11 08:41:53 PM PT</t>
+          <t>2026-07-11 08:43:53 PM PT</t>
         </is>
       </c>
       <c r="C238" t="n">
@@ -27999,7 +27999,7 @@
       </c>
       <c r="B239" t="inlineStr">
         <is>
-          <t>2026-07-11 08:41:53 PM PT</t>
+          <t>2026-07-11 08:43:53 PM PT</t>
         </is>
       </c>
       <c r="C239" t="n">
@@ -28113,7 +28113,7 @@
       </c>
       <c r="B240" t="inlineStr">
         <is>
-          <t>2026-07-11 08:41:53 PM PT</t>
+          <t>2026-07-11 08:43:53 PM PT</t>
         </is>
       </c>
       <c r="C240" t="n">
@@ -28227,7 +28227,7 @@
       </c>
       <c r="B241" t="inlineStr">
         <is>
-          <t>2026-07-11 08:41:53 PM PT</t>
+          <t>2026-07-11 08:43:53 PM PT</t>
         </is>
       </c>
       <c r="C241" t="n">
@@ -28341,7 +28341,7 @@
       </c>
       <c r="B242" t="inlineStr">
         <is>
-          <t>2026-07-11 08:41:53 PM PT</t>
+          <t>2026-07-11 08:43:53 PM PT</t>
         </is>
       </c>
       <c r="C242" t="n">
@@ -28455,7 +28455,7 @@
       </c>
       <c r="B243" t="inlineStr">
         <is>
-          <t>2026-07-11 08:41:53 PM PT</t>
+          <t>2026-07-11 08:43:53 PM PT</t>
         </is>
       </c>
       <c r="C243" t="n">
@@ -28569,7 +28569,7 @@
       </c>
       <c r="B244" t="inlineStr">
         <is>
-          <t>2026-07-11 08:41:54 PM PT</t>
+          <t>2026-07-11 08:43:54 PM PT</t>
         </is>
       </c>
       <c r="C244" t="n">
@@ -28683,7 +28683,7 @@
       </c>
       <c r="B245" t="inlineStr">
         <is>
-          <t>2026-07-11 08:41:54 PM PT</t>
+          <t>2026-07-11 08:43:54 PM PT</t>
         </is>
       </c>
       <c r="C245" t="n">
@@ -28797,7 +28797,7 @@
       </c>
       <c r="B246" t="inlineStr">
         <is>
-          <t>2026-07-11 08:41:54 PM PT</t>
+          <t>2026-07-11 08:43:54 PM PT</t>
         </is>
       </c>
       <c r="C246" t="n">
@@ -28911,7 +28911,7 @@
       </c>
       <c r="B247" t="inlineStr">
         <is>
-          <t>2026-07-11 08:41:53 PM PT</t>
+          <t>2026-07-11 08:43:53 PM PT</t>
         </is>
       </c>
       <c r="C247" t="n">
@@ -29025,7 +29025,7 @@
       </c>
       <c r="B248" t="inlineStr">
         <is>
-          <t>2026-07-11 08:41:53 PM PT</t>
+          <t>2026-07-11 08:43:53 PM PT</t>
         </is>
       </c>
       <c r="C248" t="n">
@@ -29139,7 +29139,7 @@
       </c>
       <c r="B249" t="inlineStr">
         <is>
-          <t>2026-07-11 08:41:53 PM PT</t>
+          <t>2026-07-11 08:43:53 PM PT</t>
         </is>
       </c>
       <c r="C249" t="n">
@@ -29253,7 +29253,7 @@
       </c>
       <c r="B250" t="inlineStr">
         <is>
-          <t>2026-07-11 08:41:53 PM PT</t>
+          <t>2026-07-11 08:43:53 PM PT</t>
         </is>
       </c>
       <c r="C250" t="n">
@@ -29367,7 +29367,7 @@
       </c>
       <c r="B251" t="inlineStr">
         <is>
-          <t>2026-07-11 08:41:53 PM PT</t>
+          <t>2026-07-11 08:43:53 PM PT</t>
         </is>
       </c>
       <c r="C251" t="n">
@@ -29481,7 +29481,7 @@
       </c>
       <c r="B252" t="inlineStr">
         <is>
-          <t>2026-07-11 08:41:53 PM PT</t>
+          <t>2026-07-11 08:43:53 PM PT</t>
         </is>
       </c>
       <c r="C252" t="n">
@@ -29595,7 +29595,7 @@
       </c>
       <c r="B253" t="inlineStr">
         <is>
-          <t>2026-07-11 08:41:54 PM PT</t>
+          <t>2026-07-11 08:43:54 PM PT</t>
         </is>
       </c>
       <c r="C253" t="n">
@@ -29709,7 +29709,7 @@
       </c>
       <c r="B254" t="inlineStr">
         <is>
-          <t>2026-07-11 08:41:54 PM PT</t>
+          <t>2026-07-11 08:43:54 PM PT</t>
         </is>
       </c>
       <c r="C254" t="n">
@@ -29823,7 +29823,7 @@
       </c>
       <c r="B255" t="inlineStr">
         <is>
-          <t>2026-07-11 08:41:54 PM PT</t>
+          <t>2026-07-11 08:43:54 PM PT</t>
         </is>
       </c>
       <c r="C255" t="n">
@@ -29937,7 +29937,7 @@
       </c>
       <c r="B256" t="inlineStr">
         <is>
-          <t>2026-07-11 08:41:54 PM PT</t>
+          <t>2026-07-11 08:43:54 PM PT</t>
         </is>
       </c>
       <c r="C256" t="n">
@@ -30051,7 +30051,7 @@
       </c>
       <c r="B257" t="inlineStr">
         <is>
-          <t>2026-07-11 08:41:54 PM PT</t>
+          <t>2026-07-11 08:43:54 PM PT</t>
         </is>
       </c>
       <c r="C257" t="n">
@@ -30165,7 +30165,7 @@
       </c>
       <c r="B258" t="inlineStr">
         <is>
-          <t>2026-07-11 08:41:53 PM PT</t>
+          <t>2026-07-11 08:43:53 PM PT</t>
         </is>
       </c>
       <c r="C258" t="n">
@@ -30279,7 +30279,7 @@
       </c>
       <c r="B259" t="inlineStr">
         <is>
-          <t>2026-07-11 08:41:53 PM PT</t>
+          <t>2026-07-11 08:43:53 PM PT</t>
         </is>
       </c>
       <c r="C259" t="n">
@@ -30393,7 +30393,7 @@
       </c>
       <c r="B260" t="inlineStr">
         <is>
-          <t>2026-07-11 08:41:53 PM PT</t>
+          <t>2026-07-11 08:43:53 PM PT</t>
         </is>
       </c>
       <c r="C260" t="n">
@@ -30507,7 +30507,7 @@
       </c>
       <c r="B261" t="inlineStr">
         <is>
-          <t>2026-07-11 08:41:53 PM PT</t>
+          <t>2026-07-11 08:43:53 PM PT</t>
         </is>
       </c>
       <c r="C261" t="n">
@@ -30621,7 +30621,7 @@
       </c>
       <c r="B262" t="inlineStr">
         <is>
-          <t>2026-07-11 08:41:53 PM PT</t>
+          <t>2026-07-11 08:43:53 PM PT</t>
         </is>
       </c>
       <c r="C262" t="n">
@@ -30735,7 +30735,7 @@
       </c>
       <c r="B263" t="inlineStr">
         <is>
-          <t>2026-07-11 08:41:53 PM PT</t>
+          <t>2026-07-11 08:43:53 PM PT</t>
         </is>
       </c>
       <c r="C263" t="n">
@@ -30849,7 +30849,7 @@
       </c>
       <c r="B264" t="inlineStr">
         <is>
-          <t>2026-07-11 08:41:53 PM PT</t>
+          <t>2026-07-11 08:43:53 PM PT</t>
         </is>
       </c>
       <c r="C264" t="n">
@@ -30963,7 +30963,7 @@
       </c>
       <c r="B265" t="inlineStr">
         <is>
-          <t>2026-07-11 08:41:53 PM PT</t>
+          <t>2026-07-11 08:43:53 PM PT</t>
         </is>
       </c>
       <c r="C265" t="n">
@@ -31077,7 +31077,7 @@
       </c>
       <c r="B266" t="inlineStr">
         <is>
-          <t>2026-07-11 08:41:53 PM PT</t>
+          <t>2026-07-11 08:43:53 PM PT</t>
         </is>
       </c>
       <c r="C266" t="n">
@@ -31191,7 +31191,7 @@
       </c>
       <c r="B267" t="inlineStr">
         <is>
-          <t>2026-07-11 08:41:53 PM PT</t>
+          <t>2026-07-11 08:43:53 PM PT</t>
         </is>
       </c>
       <c r="C267" t="n">
@@ -31305,7 +31305,7 @@
       </c>
       <c r="B268" t="inlineStr">
         <is>
-          <t>2026-07-11 08:41:53 PM PT</t>
+          <t>2026-07-11 08:43:53 PM PT</t>
         </is>
       </c>
       <c r="C268" t="n">
@@ -31419,7 +31419,7 @@
       </c>
       <c r="B269" t="inlineStr">
         <is>
-          <t>2026-07-11 08:41:53 PM PT</t>
+          <t>2026-07-11 08:43:53 PM PT</t>
         </is>
       </c>
       <c r="C269" t="n">
@@ -31533,7 +31533,7 @@
       </c>
       <c r="B270" t="inlineStr">
         <is>
-          <t>2026-07-11 08:41:53 PM PT</t>
+          <t>2026-07-11 08:43:53 PM PT</t>
         </is>
       </c>
       <c r="C270" t="n">
@@ -31647,7 +31647,7 @@
       </c>
       <c r="B271" t="inlineStr">
         <is>
-          <t>2026-07-11 08:41:53 PM PT</t>
+          <t>2026-07-11 08:43:53 PM PT</t>
         </is>
       </c>
       <c r="C271" t="n">
@@ -31761,7 +31761,7 @@
       </c>
       <c r="B272" t="inlineStr">
         <is>
-          <t>2026-07-11 08:41:53 PM PT</t>
+          <t>2026-07-11 08:43:53 PM PT</t>
         </is>
       </c>
       <c r="C272" t="n">
@@ -31875,7 +31875,7 @@
       </c>
       <c r="B273" t="inlineStr">
         <is>
-          <t>2026-07-11 08:41:53 PM PT</t>
+          <t>2026-07-11 08:43:53 PM PT</t>
         </is>
       </c>
       <c r="C273" t="n">
@@ -31989,7 +31989,7 @@
       </c>
       <c r="B274" t="inlineStr">
         <is>
-          <t>2026-07-11 08:41:53 PM PT</t>
+          <t>2026-07-11 08:43:53 PM PT</t>
         </is>
       </c>
       <c r="C274" t="n">
@@ -32103,7 +32103,7 @@
       </c>
       <c r="B275" t="inlineStr">
         <is>
-          <t>2026-07-11 08:41:53 PM PT</t>
+          <t>2026-07-11 08:43:53 PM PT</t>
         </is>
       </c>
       <c r="C275" t="n">
@@ -32217,7 +32217,7 @@
       </c>
       <c r="B276" t="inlineStr">
         <is>
-          <t>2026-07-11 08:41:53 PM PT</t>
+          <t>2026-07-11 08:43:53 PM PT</t>
         </is>
       </c>
       <c r="C276" t="n">
@@ -32331,7 +32331,7 @@
       </c>
       <c r="B277" t="inlineStr">
         <is>
-          <t>2026-07-11 08:41:53 PM PT</t>
+          <t>2026-07-11 08:43:53 PM PT</t>
         </is>
       </c>
       <c r="C277" t="n">
@@ -32445,7 +32445,7 @@
       </c>
       <c r="B278" t="inlineStr">
         <is>
-          <t>2026-07-11 08:41:53 PM PT</t>
+          <t>2026-07-11 08:43:53 PM PT</t>
         </is>
       </c>
       <c r="C278" t="n">
@@ -32559,7 +32559,7 @@
       </c>
       <c r="B279" t="inlineStr">
         <is>
-          <t>2026-07-11 08:41:54 PM PT</t>
+          <t>2026-07-11 08:43:54 PM PT</t>
         </is>
       </c>
       <c r="C279" t="n">
@@ -32572,25 +32572,25 @@
       </c>
       <c r="E279" t="inlineStr">
         <is>
-          <t>Bottom 8 | 2 out</t>
+          <t>Top 9 | 0 out</t>
         </is>
       </c>
       <c r="F279" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="G279" t="inlineStr">
         <is>
-          <t>Bottom</t>
+          <t>Top</t>
         </is>
       </c>
       <c r="H279" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="I279" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J279" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="K279" t="inlineStr">
         <is>
@@ -32617,7 +32617,7 @@
       </c>
       <c r="P279" t="inlineStr">
         <is>
-          <t>PH</t>
+          <t>DH</t>
         </is>
       </c>
       <c r="Q279" t="inlineStr">
@@ -32682,7 +32682,7 @@
       </c>
       <c r="B280" t="inlineStr">
         <is>
-          <t>2026-07-11 08:41:54 PM PT</t>
+          <t>2026-07-11 08:43:54 PM PT</t>
         </is>
       </c>
       <c r="C280" t="n">
@@ -32695,25 +32695,25 @@
       </c>
       <c r="E280" t="inlineStr">
         <is>
-          <t>Bottom 8 | 2 out</t>
+          <t>Top 9 | 0 out</t>
         </is>
       </c>
       <c r="F280" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="G280" t="inlineStr">
         <is>
-          <t>Bottom</t>
+          <t>Top</t>
         </is>
       </c>
       <c r="H280" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="I280" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J280" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="K280" t="inlineStr">
         <is>
@@ -32749,10 +32749,10 @@
         </is>
       </c>
       <c r="R280" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S280" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T280" t="n">
         <v>0</v>
@@ -32785,7 +32785,7 @@
         <v>0</v>
       </c>
       <c r="AD280" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AE280" s="4" t="n">
         <v>0</v>
@@ -32805,7 +32805,7 @@
       </c>
       <c r="B281" t="inlineStr">
         <is>
-          <t>2026-07-11 08:41:54 PM PT</t>
+          <t>2026-07-11 08:43:54 PM PT</t>
         </is>
       </c>
       <c r="C281" t="n">
@@ -32818,25 +32818,25 @@
       </c>
       <c r="E281" t="inlineStr">
         <is>
-          <t>Bottom 8 | 2 out</t>
+          <t>Top 9 | 0 out</t>
         </is>
       </c>
       <c r="F281" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="G281" t="inlineStr">
         <is>
-          <t>Bottom</t>
+          <t>Top</t>
         </is>
       </c>
       <c r="H281" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="I281" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J281" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="K281" t="inlineStr">
         <is>
@@ -32928,7 +32928,7 @@
       </c>
       <c r="B282" t="inlineStr">
         <is>
-          <t>2026-07-11 08:41:54 PM PT</t>
+          <t>2026-07-11 08:43:54 PM PT</t>
         </is>
       </c>
       <c r="C282" t="n">
@@ -32941,25 +32941,25 @@
       </c>
       <c r="E282" t="inlineStr">
         <is>
-          <t>Bottom 8 | 2 out</t>
+          <t>Top 9 | 0 out</t>
         </is>
       </c>
       <c r="F282" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="G282" t="inlineStr">
         <is>
-          <t>Bottom</t>
+          <t>Top</t>
         </is>
       </c>
       <c r="H282" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="I282" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J282" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="K282" t="inlineStr">
         <is>
@@ -33051,7 +33051,7 @@
       </c>
       <c r="B283" t="inlineStr">
         <is>
-          <t>2026-07-11 08:41:54 PM PT</t>
+          <t>2026-07-11 08:43:54 PM PT</t>
         </is>
       </c>
       <c r="C283" t="n">
@@ -33064,25 +33064,25 @@
       </c>
       <c r="E283" t="inlineStr">
         <is>
-          <t>Bottom 8 | 2 out</t>
+          <t>Top 9 | 0 out</t>
         </is>
       </c>
       <c r="F283" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="G283" t="inlineStr">
         <is>
-          <t>Bottom</t>
+          <t>Top</t>
         </is>
       </c>
       <c r="H283" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="I283" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J283" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="K283" t="inlineStr">
         <is>
@@ -33174,7 +33174,7 @@
       </c>
       <c r="B284" t="inlineStr">
         <is>
-          <t>2026-07-11 08:41:54 PM PT</t>
+          <t>2026-07-11 08:43:54 PM PT</t>
         </is>
       </c>
       <c r="C284" t="n">
@@ -33187,25 +33187,25 @@
       </c>
       <c r="E284" t="inlineStr">
         <is>
-          <t>Bottom 8 | 2 out</t>
+          <t>Top 9 | 0 out</t>
         </is>
       </c>
       <c r="F284" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="G284" t="inlineStr">
         <is>
-          <t>Bottom</t>
+          <t>Top</t>
         </is>
       </c>
       <c r="H284" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="I284" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J284" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="K284" t="inlineStr">
         <is>
@@ -33297,7 +33297,7 @@
       </c>
       <c r="B285" t="inlineStr">
         <is>
-          <t>2026-07-11 08:41:54 PM PT</t>
+          <t>2026-07-11 08:43:54 PM PT</t>
         </is>
       </c>
       <c r="C285" t="n">
@@ -33310,25 +33310,25 @@
       </c>
       <c r="E285" t="inlineStr">
         <is>
-          <t>Bottom 8 | 2 out</t>
+          <t>Top 9 | 0 out</t>
         </is>
       </c>
       <c r="F285" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="G285" t="inlineStr">
         <is>
-          <t>Bottom</t>
+          <t>Top</t>
         </is>
       </c>
       <c r="H285" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="I285" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J285" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="K285" t="inlineStr">
         <is>
@@ -33420,7 +33420,7 @@
       </c>
       <c r="B286" t="inlineStr">
         <is>
-          <t>2026-07-11 08:41:54 PM PT</t>
+          <t>2026-07-11 08:43:54 PM PT</t>
         </is>
       </c>
       <c r="C286" t="n">
@@ -33433,25 +33433,25 @@
       </c>
       <c r="E286" t="inlineStr">
         <is>
-          <t>Bottom 8 | 2 out</t>
+          <t>Top 9 | 0 out</t>
         </is>
       </c>
       <c r="F286" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="G286" t="inlineStr">
         <is>
-          <t>Bottom</t>
+          <t>Top</t>
         </is>
       </c>
       <c r="H286" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="I286" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J286" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="K286" t="inlineStr">
         <is>
@@ -33543,7 +33543,7 @@
       </c>
       <c r="B287" t="inlineStr">
         <is>
-          <t>2026-07-11 08:41:53 PM PT</t>
+          <t>2026-07-11 08:43:53 PM PT</t>
         </is>
       </c>
       <c r="C287" t="n">
@@ -33657,7 +33657,7 @@
       </c>
       <c r="B288" t="inlineStr">
         <is>
-          <t>2026-07-11 08:41:52 PM PT</t>
+          <t>2026-07-11 08:43:52 PM PT</t>
         </is>
       </c>
       <c r="C288" t="n">
@@ -33771,7 +33771,7 @@
       </c>
       <c r="B289" t="inlineStr">
         <is>
-          <t>2026-07-11 08:41:52 PM PT</t>
+          <t>2026-07-11 08:43:53 PM PT</t>
         </is>
       </c>
       <c r="C289" t="n">
@@ -33885,7 +33885,7 @@
       </c>
       <c r="B290" t="inlineStr">
         <is>
-          <t>2026-07-11 08:41:52 PM PT</t>
+          <t>2026-07-11 08:43:52 PM PT</t>
         </is>
       </c>
       <c r="C290" t="n">
@@ -33999,7 +33999,7 @@
       </c>
       <c r="B291" t="inlineStr">
         <is>
-          <t>2026-07-11 08:41:52 PM PT</t>
+          <t>2026-07-11 08:43:53 PM PT</t>
         </is>
       </c>
       <c r="C291" t="n">
@@ -34113,7 +34113,7 @@
       </c>
       <c r="B292" t="inlineStr">
         <is>
-          <t>2026-07-11 08:41:52 PM PT</t>
+          <t>2026-07-11 08:43:53 PM PT</t>
         </is>
       </c>
       <c r="C292" t="n">
@@ -34227,7 +34227,7 @@
       </c>
       <c r="B293" t="inlineStr">
         <is>
-          <t>2026-07-11 08:41:52 PM PT</t>
+          <t>2026-07-11 08:43:52 PM PT</t>
         </is>
       </c>
       <c r="C293" t="n">
@@ -34341,7 +34341,7 @@
       </c>
       <c r="B294" t="inlineStr">
         <is>
-          <t>2026-07-11 08:41:53 PM PT</t>
+          <t>2026-07-11 08:43:53 PM PT</t>
         </is>
       </c>
       <c r="C294" t="n">
@@ -34455,7 +34455,7 @@
       </c>
       <c r="B295" t="inlineStr">
         <is>
-          <t>2026-07-11 08:41:53 PM PT</t>
+          <t>2026-07-11 08:43:53 PM PT</t>
         </is>
       </c>
       <c r="C295" t="n">
@@ -34569,7 +34569,7 @@
       </c>
       <c r="B296" t="inlineStr">
         <is>
-          <t>2026-07-11 08:41:53 PM PT</t>
+          <t>2026-07-11 08:43:53 PM PT</t>
         </is>
       </c>
       <c r="C296" t="n">
@@ -34683,7 +34683,7 @@
       </c>
       <c r="B297" t="inlineStr">
         <is>
-          <t>2026-07-11 08:41:53 PM PT</t>
+          <t>2026-07-11 08:43:53 PM PT</t>
         </is>
       </c>
       <c r="C297" t="n">
@@ -34797,7 +34797,7 @@
       </c>
       <c r="B298" t="inlineStr">
         <is>
-          <t>2026-07-11 08:41:53 PM PT</t>
+          <t>2026-07-11 08:43:53 PM PT</t>
         </is>
       </c>
       <c r="C298" t="n">
@@ -34911,7 +34911,7 @@
       </c>
       <c r="B299" t="inlineStr">
         <is>
-          <t>2026-07-11 08:41:53 PM PT</t>
+          <t>2026-07-11 08:43:53 PM PT</t>
         </is>
       </c>
       <c r="C299" t="n">
@@ -35025,7 +35025,7 @@
       </c>
       <c r="B300" t="inlineStr">
         <is>
-          <t>2026-07-11 08:41:53 PM PT</t>
+          <t>2026-07-11 08:43:53 PM PT</t>
         </is>
       </c>
       <c r="C300" t="n">
@@ -35139,7 +35139,7 @@
       </c>
       <c r="B301" t="inlineStr">
         <is>
-          <t>2026-07-11 08:41:53 PM PT</t>
+          <t>2026-07-11 08:43:53 PM PT</t>
         </is>
       </c>
       <c r="C301" t="n">
@@ -35253,7 +35253,7 @@
       </c>
       <c r="B302" t="inlineStr">
         <is>
-          <t>2026-07-11 08:41:53 PM PT</t>
+          <t>2026-07-11 08:43:53 PM PT</t>
         </is>
       </c>
       <c r="C302" t="n">
@@ -35367,7 +35367,7 @@
       </c>
       <c r="B303" t="inlineStr">
         <is>
-          <t>2026-07-11 08:41:52 PM PT</t>
+          <t>2026-07-11 08:43:53 PM PT</t>
         </is>
       </c>
       <c r="C303" t="n">
@@ -35481,7 +35481,7 @@
       </c>
       <c r="B304" t="inlineStr">
         <is>
-          <t>2026-07-11 08:41:52 PM PT</t>
+          <t>2026-07-11 08:43:53 PM PT</t>
         </is>
       </c>
       <c r="C304" t="n">
@@ -35595,7 +35595,7 @@
       </c>
       <c r="B305" t="inlineStr">
         <is>
-          <t>2026-07-11 08:41:52 PM PT</t>
+          <t>2026-07-11 08:43:53 PM PT</t>
         </is>
       </c>
       <c r="C305" t="n">
@@ -35709,7 +35709,7 @@
       </c>
       <c r="B306" t="inlineStr">
         <is>
-          <t>2026-07-11 08:41:52 PM PT</t>
+          <t>2026-07-11 08:43:52 PM PT</t>
         </is>
       </c>
       <c r="C306" t="n">
@@ -35823,7 +35823,7 @@
       </c>
       <c r="B307" t="inlineStr">
         <is>
-          <t>2026-07-11 08:41:52 PM PT</t>
+          <t>2026-07-11 08:43:53 PM PT</t>
         </is>
       </c>
       <c r="C307" t="n">
@@ -35937,7 +35937,7 @@
       </c>
       <c r="B308" t="inlineStr">
         <is>
-          <t>2026-07-11 08:41:52 PM PT</t>
+          <t>2026-07-11 08:43:52 PM PT</t>
         </is>
       </c>
       <c r="C308" t="n">
@@ -36051,7 +36051,7 @@
       </c>
       <c r="B309" t="inlineStr">
         <is>
-          <t>2026-07-11 08:41:52 PM PT</t>
+          <t>2026-07-11 08:43:52 PM PT</t>
         </is>
       </c>
       <c r="C309" t="n">
@@ -36165,7 +36165,7 @@
       </c>
       <c r="B310" t="inlineStr">
         <is>
-          <t>2026-07-11 08:41:52 PM PT</t>
+          <t>2026-07-11 08:43:53 PM PT</t>
         </is>
       </c>
       <c r="C310" t="n">
@@ -36279,7 +36279,7 @@
       </c>
       <c r="B311" t="inlineStr">
         <is>
-          <t>2026-07-11 08:41:54 PM PT</t>
+          <t>2026-07-11 08:43:54 PM PT</t>
         </is>
       </c>
       <c r="C311" t="n">
@@ -36292,25 +36292,25 @@
       </c>
       <c r="E311" t="inlineStr">
         <is>
-          <t>Bottom 8 | 3 out</t>
+          <t>Top 9 | 0 out</t>
         </is>
       </c>
       <c r="F311" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="G311" t="inlineStr">
         <is>
-          <t>Bottom</t>
+          <t>Top</t>
         </is>
       </c>
       <c r="H311" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="I311" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J311" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="K311" t="inlineStr">
         <is>
@@ -36337,7 +36337,7 @@
       </c>
       <c r="P311" t="inlineStr">
         <is>
-          <t>PR</t>
+          <t>LF</t>
         </is>
       </c>
       <c r="Q311" t="inlineStr">
@@ -36402,7 +36402,7 @@
       </c>
       <c r="B312" t="inlineStr">
         <is>
-          <t>2026-07-11 08:41:54 PM PT</t>
+          <t>2026-07-11 08:43:54 PM PT</t>
         </is>
       </c>
       <c r="C312" t="n">
@@ -36415,25 +36415,25 @@
       </c>
       <c r="E312" t="inlineStr">
         <is>
-          <t>Bottom 8 | 3 out</t>
+          <t>Top 9 | 0 out</t>
         </is>
       </c>
       <c r="F312" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="G312" t="inlineStr">
         <is>
-          <t>Bottom</t>
+          <t>Top</t>
         </is>
       </c>
       <c r="H312" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="I312" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J312" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="K312" t="inlineStr">
         <is>
@@ -36525,7 +36525,7 @@
       </c>
       <c r="B313" t="inlineStr">
         <is>
-          <t>2026-07-11 08:41:53 PM PT</t>
+          <t>2026-07-11 08:43:53 PM PT</t>
         </is>
       </c>
       <c r="C313" t="n">
@@ -36639,7 +36639,7 @@
       </c>
       <c r="B314" t="inlineStr">
         <is>
-          <t>2026-07-11 08:41:53 PM PT</t>
+          <t>2026-07-11 08:43:53 PM PT</t>
         </is>
       </c>
       <c r="C314" t="n">
@@ -36753,7 +36753,7 @@
       </c>
       <c r="B315" t="inlineStr">
         <is>
-          <t>2026-07-11 08:41:53 PM PT</t>
+          <t>2026-07-11 08:43:53 PM PT</t>
         </is>
       </c>
       <c r="C315" t="n">
@@ -36867,7 +36867,7 @@
       </c>
       <c r="B316" t="inlineStr">
         <is>
-          <t>2026-07-11 08:41:53 PM PT</t>
+          <t>2026-07-11 08:43:53 PM PT</t>
         </is>
       </c>
       <c r="C316" t="n">
@@ -36981,7 +36981,7 @@
       </c>
       <c r="B317" t="inlineStr">
         <is>
-          <t>2026-07-11 08:41:53 PM PT</t>
+          <t>2026-07-11 08:43:53 PM PT</t>
         </is>
       </c>
       <c r="C317" t="n">
@@ -37095,7 +37095,7 @@
       </c>
       <c r="B318" t="inlineStr">
         <is>
-          <t>2026-07-11 08:41:53 PM PT</t>
+          <t>2026-07-11 08:43:53 PM PT</t>
         </is>
       </c>
       <c r="C318" t="n">
@@ -37209,7 +37209,7 @@
       </c>
       <c r="B319" t="inlineStr">
         <is>
-          <t>2026-07-11 08:41:53 PM PT</t>
+          <t>2026-07-11 08:43:53 PM PT</t>
         </is>
       </c>
       <c r="C319" t="n">
@@ -37323,7 +37323,7 @@
       </c>
       <c r="B320" t="inlineStr">
         <is>
-          <t>2026-07-11 08:41:54 PM PT</t>
+          <t>2026-07-11 08:43:54 PM PT</t>
         </is>
       </c>
       <c r="C320" t="n">
@@ -37437,7 +37437,7 @@
       </c>
       <c r="B321" t="inlineStr">
         <is>
-          <t>2026-07-11 08:41:54 PM PT</t>
+          <t>2026-07-11 08:43:54 PM PT</t>
         </is>
       </c>
       <c r="C321" t="n">
@@ -37551,7 +37551,7 @@
       </c>
       <c r="B322" t="inlineStr">
         <is>
-          <t>2026-07-11 08:41:54 PM PT</t>
+          <t>2026-07-11 08:43:54 PM PT</t>
         </is>
       </c>
       <c r="C322" t="n">
@@ -37665,7 +37665,7 @@
       </c>
       <c r="B323" t="inlineStr">
         <is>
-          <t>2026-07-11 08:41:54 PM PT</t>
+          <t>2026-07-11 08:43:54 PM PT</t>
         </is>
       </c>
       <c r="C323" t="n">
@@ -37779,7 +37779,7 @@
       </c>
       <c r="B324" t="inlineStr">
         <is>
-          <t>2026-07-11 08:41:53 PM PT</t>
+          <t>2026-07-11 08:43:53 PM PT</t>
         </is>
       </c>
       <c r="C324" t="n">
@@ -37893,7 +37893,7 @@
       </c>
       <c r="B325" t="inlineStr">
         <is>
-          <t>2026-07-11 08:41:53 PM PT</t>
+          <t>2026-07-11 08:43:53 PM PT</t>
         </is>
       </c>
       <c r="C325" t="n">
@@ -38007,7 +38007,7 @@
       </c>
       <c r="B326" t="inlineStr">
         <is>
-          <t>2026-07-11 08:41:53 PM PT</t>
+          <t>2026-07-11 08:43:53 PM PT</t>
         </is>
       </c>
       <c r="C326" t="n">
@@ -38121,7 +38121,7 @@
       </c>
       <c r="B327" t="inlineStr">
         <is>
-          <t>2026-07-11 08:41:53 PM PT</t>
+          <t>2026-07-11 08:43:53 PM PT</t>
         </is>
       </c>
       <c r="C327" t="n">
@@ -38235,7 +38235,7 @@
       </c>
       <c r="B328" t="inlineStr">
         <is>
-          <t>2026-07-11 08:41:53 PM PT</t>
+          <t>2026-07-11 08:43:53 PM PT</t>
         </is>
       </c>
       <c r="C328" t="n">
@@ -38349,7 +38349,7 @@
       </c>
       <c r="B329" t="inlineStr">
         <is>
-          <t>2026-07-11 08:41:53 PM PT</t>
+          <t>2026-07-11 08:43:53 PM PT</t>
         </is>
       </c>
       <c r="C329" t="n">
@@ -38463,7 +38463,7 @@
       </c>
       <c r="B330" t="inlineStr">
         <is>
-          <t>2026-07-11 08:41:53 PM PT</t>
+          <t>2026-07-11 08:43:53 PM PT</t>
         </is>
       </c>
       <c r="C330" t="n">
@@ -38577,7 +38577,7 @@
       </c>
       <c r="B331" t="inlineStr">
         <is>
-          <t>2026-07-11 08:41:53 PM PT</t>
+          <t>2026-07-11 08:43:53 PM PT</t>
         </is>
       </c>
       <c r="C331" t="n">
@@ -38691,7 +38691,7 @@
       </c>
       <c r="B332" t="inlineStr">
         <is>
-          <t>2026-07-11 08:41:53 PM PT</t>
+          <t>2026-07-11 08:43:53 PM PT</t>
         </is>
       </c>
       <c r="C332" t="n">
@@ -38805,7 +38805,7 @@
       </c>
       <c r="B333" t="inlineStr">
         <is>
-          <t>2026-07-11 08:41:54 PM PT</t>
+          <t>2026-07-11 08:43:54 PM PT</t>
         </is>
       </c>
       <c r="C333" t="n">
@@ -38818,25 +38818,25 @@
       </c>
       <c r="E333" t="inlineStr">
         <is>
-          <t>Bottom 8 | 3 out</t>
+          <t>Top 9 | 0 out</t>
         </is>
       </c>
       <c r="F333" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="G333" t="inlineStr">
         <is>
-          <t>Bottom</t>
+          <t>Top</t>
         </is>
       </c>
       <c r="H333" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="I333" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J333" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="K333" t="inlineStr">
         <is>
@@ -38928,7 +38928,7 @@
       </c>
       <c r="B334" t="inlineStr">
         <is>
-          <t>2026-07-11 08:41:53 PM PT</t>
+          <t>2026-07-11 08:43:53 PM PT</t>
         </is>
       </c>
       <c r="C334" t="n">
@@ -39042,7 +39042,7 @@
       </c>
       <c r="B335" t="inlineStr">
         <is>
-          <t>2026-07-11 08:41:53 PM PT</t>
+          <t>2026-07-11 08:43:53 PM PT</t>
         </is>
       </c>
       <c r="C335" t="n">

--- a/live_mlb_hitter_fantasy_scores_2026_07_11.xlsx
+++ b/live_mlb_hitter_fantasy_scores_2026_07_11.xlsx
@@ -693,7 +693,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-07-11 08:49:52 PM PT</t>
+          <t>2026-07-11 08:51:52 PM PT</t>
         </is>
       </c>
       <c r="C2" t="n">
@@ -807,7 +807,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>2026-07-11 08:49:54 PM PT</t>
+          <t>2026-07-11 08:51:54 PM PT</t>
         </is>
       </c>
       <c r="C3" t="n">
@@ -820,7 +820,7 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Top 9 | 2 out</t>
+          <t>Top 9 | 3 out</t>
         </is>
       </c>
       <c r="F3" t="n">
@@ -832,7 +832,7 @@
         </is>
       </c>
       <c r="H3" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="I3" t="n">
         <v>1</v>
@@ -930,7 +930,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-07-11 08:49:53 PM PT</t>
+          <t>2026-07-11 08:51:54 PM PT</t>
         </is>
       </c>
       <c r="C4" t="n">
@@ -1044,7 +1044,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>2026-07-11 08:49:54 PM PT</t>
+          <t>2026-07-11 08:51:54 PM PT</t>
         </is>
       </c>
       <c r="C5" t="n">
@@ -1057,7 +1057,7 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Top 9 | 3 out</t>
+          <t>Game Over</t>
         </is>
       </c>
       <c r="F5" t="n">
@@ -1067,15 +1067,6 @@
         <is>
           <t>Top</t>
         </is>
-      </c>
-      <c r="H5" t="n">
-        <v>3</v>
-      </c>
-      <c r="I5" t="n">
-        <v>0</v>
-      </c>
-      <c r="J5" t="n">
-        <v>3</v>
       </c>
       <c r="K5" t="inlineStr">
         <is>
@@ -1167,7 +1158,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>2026-07-11 08:49:53 PM PT</t>
+          <t>2026-07-11 08:51:54 PM PT</t>
         </is>
       </c>
       <c r="C6" t="n">
@@ -1281,7 +1272,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>2026-07-11 08:49:53 PM PT</t>
+          <t>2026-07-11 08:51:54 PM PT</t>
         </is>
       </c>
       <c r="C7" t="n">
@@ -1395,7 +1386,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>2026-07-11 08:49:53 PM PT</t>
+          <t>2026-07-11 08:51:53 PM PT</t>
         </is>
       </c>
       <c r="C8" t="n">
@@ -1509,7 +1500,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>2026-07-11 08:49:53 PM PT</t>
+          <t>2026-07-11 08:51:54 PM PT</t>
         </is>
       </c>
       <c r="C9" t="n">
@@ -1623,7 +1614,7 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>2026-07-11 08:49:53 PM PT</t>
+          <t>2026-07-11 08:51:53 PM PT</t>
         </is>
       </c>
       <c r="C10" t="n">
@@ -1737,7 +1728,7 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>2026-07-11 08:49:54 PM PT</t>
+          <t>2026-07-11 08:51:54 PM PT</t>
         </is>
       </c>
       <c r="C11" t="n">
@@ -1750,7 +1741,7 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Top 9 | 3 out</t>
+          <t>Game Over</t>
         </is>
       </c>
       <c r="F11" t="n">
@@ -1760,15 +1751,6 @@
         <is>
           <t>Top</t>
         </is>
-      </c>
-      <c r="H11" t="n">
-        <v>3</v>
-      </c>
-      <c r="I11" t="n">
-        <v>0</v>
-      </c>
-      <c r="J11" t="n">
-        <v>3</v>
       </c>
       <c r="K11" t="inlineStr">
         <is>
@@ -1860,7 +1842,7 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>2026-07-11 08:49:53 PM PT</t>
+          <t>2026-07-11 08:51:53 PM PT</t>
         </is>
       </c>
       <c r="C12" t="n">
@@ -1974,7 +1956,7 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>2026-07-11 08:49:53 PM PT</t>
+          <t>2026-07-11 08:51:53 PM PT</t>
         </is>
       </c>
       <c r="C13" t="n">
@@ -2088,7 +2070,7 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>2026-07-11 08:49:54 PM PT</t>
+          <t>2026-07-11 08:51:54 PM PT</t>
         </is>
       </c>
       <c r="C14" t="n">
@@ -2101,7 +2083,7 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Top 9 | 3 out</t>
+          <t>Game Over</t>
         </is>
       </c>
       <c r="F14" t="n">
@@ -2111,15 +2093,6 @@
         <is>
           <t>Top</t>
         </is>
-      </c>
-      <c r="H14" t="n">
-        <v>3</v>
-      </c>
-      <c r="I14" t="n">
-        <v>0</v>
-      </c>
-      <c r="J14" t="n">
-        <v>3</v>
       </c>
       <c r="K14" t="inlineStr">
         <is>
@@ -2211,7 +2184,7 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>2026-07-11 08:49:53 PM PT</t>
+          <t>2026-07-11 08:51:53 PM PT</t>
         </is>
       </c>
       <c r="C15" t="n">
@@ -2325,7 +2298,7 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>2026-07-11 08:49:53 PM PT</t>
+          <t>2026-07-11 08:51:53 PM PT</t>
         </is>
       </c>
       <c r="C16" t="n">
@@ -2439,7 +2412,7 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>2026-07-11 08:49:53 PM PT</t>
+          <t>2026-07-11 08:51:54 PM PT</t>
         </is>
       </c>
       <c r="C17" t="n">
@@ -2553,7 +2526,7 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>2026-07-11 08:49:54 PM PT</t>
+          <t>2026-07-11 08:51:54 PM PT</t>
         </is>
       </c>
       <c r="C18" t="n">
@@ -2566,7 +2539,7 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Top 9 | 3 out</t>
+          <t>Game Over</t>
         </is>
       </c>
       <c r="F18" t="n">
@@ -2576,15 +2549,6 @@
         <is>
           <t>Top</t>
         </is>
-      </c>
-      <c r="H18" t="n">
-        <v>3</v>
-      </c>
-      <c r="I18" t="n">
-        <v>0</v>
-      </c>
-      <c r="J18" t="n">
-        <v>3</v>
       </c>
       <c r="K18" t="inlineStr">
         <is>
@@ -2676,7 +2640,7 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>2026-07-11 08:49:53 PM PT</t>
+          <t>2026-07-11 08:51:53 PM PT</t>
         </is>
       </c>
       <c r="C19" t="n">
@@ -2790,7 +2754,7 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>2026-07-11 08:49:54 PM PT</t>
+          <t>2026-07-11 08:51:54 PM PT</t>
         </is>
       </c>
       <c r="C20" t="n">
@@ -2803,7 +2767,7 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Top 9 | 2 out</t>
+          <t>Top 9 | 3 out</t>
         </is>
       </c>
       <c r="F20" t="n">
@@ -2815,7 +2779,7 @@
         </is>
       </c>
       <c r="H20" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="I20" t="n">
         <v>1</v>
@@ -2913,7 +2877,7 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>2026-07-11 08:49:53 PM PT</t>
+          <t>2026-07-11 08:51:54 PM PT</t>
         </is>
       </c>
       <c r="C21" t="n">
@@ -3027,7 +2991,7 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>2026-07-11 08:49:53 PM PT</t>
+          <t>2026-07-11 08:51:53 PM PT</t>
         </is>
       </c>
       <c r="C22" t="n">
@@ -3141,7 +3105,7 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>2026-07-11 08:49:53 PM PT</t>
+          <t>2026-07-11 08:51:53 PM PT</t>
         </is>
       </c>
       <c r="C23" t="n">
@@ -3255,7 +3219,7 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>2026-07-11 08:49:54 PM PT</t>
+          <t>2026-07-11 08:51:54 PM PT</t>
         </is>
       </c>
       <c r="C24" t="n">
@@ -3268,7 +3232,7 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Top 9 | 2 out</t>
+          <t>Top 9 | 3 out</t>
         </is>
       </c>
       <c r="F24" t="n">
@@ -3280,7 +3244,7 @@
         </is>
       </c>
       <c r="H24" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="I24" t="n">
         <v>1</v>
@@ -3378,7 +3342,7 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>2026-07-11 08:49:53 PM PT</t>
+          <t>2026-07-11 08:51:54 PM PT</t>
         </is>
       </c>
       <c r="C25" t="n">
@@ -3492,7 +3456,7 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>2026-07-11 08:49:53 PM PT</t>
+          <t>2026-07-11 08:51:53 PM PT</t>
         </is>
       </c>
       <c r="C26" t="n">
@@ -3606,7 +3570,7 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>2026-07-11 08:49:53 PM PT</t>
+          <t>2026-07-11 08:51:54 PM PT</t>
         </is>
       </c>
       <c r="C27" t="n">
@@ -3720,7 +3684,7 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>2026-07-11 08:49:52 PM PT</t>
+          <t>2026-07-11 08:51:52 PM PT</t>
         </is>
       </c>
       <c r="C28" t="n">
@@ -3834,7 +3798,7 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>2026-07-11 08:49:53 PM PT</t>
+          <t>2026-07-11 08:51:53 PM PT</t>
         </is>
       </c>
       <c r="C29" t="n">
@@ -3948,7 +3912,7 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>2026-07-11 08:49:53 PM PT</t>
+          <t>2026-07-11 08:51:53 PM PT</t>
         </is>
       </c>
       <c r="C30" t="n">
@@ -4062,7 +4026,7 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>2026-07-11 08:49:53 PM PT</t>
+          <t>2026-07-11 08:51:54 PM PT</t>
         </is>
       </c>
       <c r="C31" t="n">
@@ -4176,7 +4140,7 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>2026-07-11 08:49:53 PM PT</t>
+          <t>2026-07-11 08:51:54 PM PT</t>
         </is>
       </c>
       <c r="C32" t="n">
@@ -4290,7 +4254,7 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>2026-07-11 08:49:53 PM PT</t>
+          <t>2026-07-11 08:51:53 PM PT</t>
         </is>
       </c>
       <c r="C33" t="n">
@@ -4404,7 +4368,7 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>2026-07-11 08:49:53 PM PT</t>
+          <t>2026-07-11 08:51:53 PM PT</t>
         </is>
       </c>
       <c r="C34" t="n">
@@ -4518,7 +4482,7 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>2026-07-11 08:49:53 PM PT</t>
+          <t>2026-07-11 08:51:54 PM PT</t>
         </is>
       </c>
       <c r="C35" t="n">
@@ -4632,7 +4596,7 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>2026-07-11 08:49:52 PM PT</t>
+          <t>2026-07-11 08:51:52 PM PT</t>
         </is>
       </c>
       <c r="C36" t="n">
@@ -4746,7 +4710,7 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>2026-07-11 08:49:52 PM PT</t>
+          <t>2026-07-11 08:51:52 PM PT</t>
         </is>
       </c>
       <c r="C37" t="n">
@@ -4860,7 +4824,7 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>2026-07-11 08:49:54 PM PT</t>
+          <t>2026-07-11 08:51:54 PM PT</t>
         </is>
       </c>
       <c r="C38" t="n">
@@ -4873,7 +4837,7 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>Top 9 | 3 out</t>
+          <t>Game Over</t>
         </is>
       </c>
       <c r="F38" t="n">
@@ -4883,15 +4847,6 @@
         <is>
           <t>Top</t>
         </is>
-      </c>
-      <c r="H38" t="n">
-        <v>3</v>
-      </c>
-      <c r="I38" t="n">
-        <v>0</v>
-      </c>
-      <c r="J38" t="n">
-        <v>3</v>
       </c>
       <c r="K38" t="inlineStr">
         <is>
@@ -4983,7 +4938,7 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>2026-07-11 08:49:53 PM PT</t>
+          <t>2026-07-11 08:51:53 PM PT</t>
         </is>
       </c>
       <c r="C39" t="n">
@@ -5097,7 +5052,7 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>2026-07-11 08:49:53 PM PT</t>
+          <t>2026-07-11 08:51:53 PM PT</t>
         </is>
       </c>
       <c r="C40" t="n">
@@ -5211,7 +5166,7 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>2026-07-11 08:49:53 PM PT</t>
+          <t>2026-07-11 08:51:53 PM PT</t>
         </is>
       </c>
       <c r="C41" t="n">
@@ -5325,7 +5280,7 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>2026-07-11 08:49:52 PM PT</t>
+          <t>2026-07-11 08:51:52 PM PT</t>
         </is>
       </c>
       <c r="C42" t="n">
@@ -5439,7 +5394,7 @@
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>2026-07-11 08:49:54 PM PT</t>
+          <t>2026-07-11 08:51:54 PM PT</t>
         </is>
       </c>
       <c r="C43" t="n">
@@ -5452,7 +5407,7 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>Top 9 | 2 out</t>
+          <t>Top 9 | 3 out</t>
         </is>
       </c>
       <c r="F43" t="n">
@@ -5464,7 +5419,7 @@
         </is>
       </c>
       <c r="H43" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="I43" t="n">
         <v>1</v>
@@ -5562,7 +5517,7 @@
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>2026-07-11 08:49:53 PM PT</t>
+          <t>2026-07-11 08:51:54 PM PT</t>
         </is>
       </c>
       <c r="C44" t="n">
@@ -5676,7 +5631,7 @@
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>2026-07-11 08:49:53 PM PT</t>
+          <t>2026-07-11 08:51:54 PM PT</t>
         </is>
       </c>
       <c r="C45" t="n">
@@ -5790,7 +5745,7 @@
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>2026-07-11 08:49:53 PM PT</t>
+          <t>2026-07-11 08:51:54 PM PT</t>
         </is>
       </c>
       <c r="C46" t="n">
@@ -5904,7 +5859,7 @@
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>2026-07-11 08:49:53 PM PT</t>
+          <t>2026-07-11 08:51:54 PM PT</t>
         </is>
       </c>
       <c r="C47" t="n">
@@ -6018,7 +5973,7 @@
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>2026-07-11 08:49:53 PM PT</t>
+          <t>2026-07-11 08:51:53 PM PT</t>
         </is>
       </c>
       <c r="C48" t="n">
@@ -6132,7 +6087,7 @@
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>2026-07-11 08:49:53 PM PT</t>
+          <t>2026-07-11 08:51:53 PM PT</t>
         </is>
       </c>
       <c r="C49" t="n">
@@ -6246,7 +6201,7 @@
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>2026-07-11 08:49:53 PM PT</t>
+          <t>2026-07-11 08:51:54 PM PT</t>
         </is>
       </c>
       <c r="C50" t="n">
@@ -6360,7 +6315,7 @@
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>2026-07-11 08:49:53 PM PT</t>
+          <t>2026-07-11 08:51:53 PM PT</t>
         </is>
       </c>
       <c r="C51" t="n">
@@ -6474,7 +6429,7 @@
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>2026-07-11 08:49:52 PM PT</t>
+          <t>2026-07-11 08:51:52 PM PT</t>
         </is>
       </c>
       <c r="C52" t="n">
@@ -6588,7 +6543,7 @@
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>2026-07-11 08:49:54 PM PT</t>
+          <t>2026-07-11 08:51:54 PM PT</t>
         </is>
       </c>
       <c r="C53" t="n">
@@ -6601,7 +6556,7 @@
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>Top 9 | 3 out</t>
+          <t>Game Over</t>
         </is>
       </c>
       <c r="F53" t="n">
@@ -6611,15 +6566,6 @@
         <is>
           <t>Top</t>
         </is>
-      </c>
-      <c r="H53" t="n">
-        <v>3</v>
-      </c>
-      <c r="I53" t="n">
-        <v>0</v>
-      </c>
-      <c r="J53" t="n">
-        <v>3</v>
       </c>
       <c r="K53" t="inlineStr">
         <is>
@@ -6711,7 +6657,7 @@
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>2026-07-11 08:49:54 PM PT</t>
+          <t>2026-07-11 08:51:54 PM PT</t>
         </is>
       </c>
       <c r="C54" t="n">
@@ -6724,7 +6670,7 @@
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>Top 9 | 2 out</t>
+          <t>Top 9 | 3 out</t>
         </is>
       </c>
       <c r="F54" t="n">
@@ -6736,7 +6682,7 @@
         </is>
       </c>
       <c r="H54" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="I54" t="n">
         <v>1</v>
@@ -6834,7 +6780,7 @@
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>2026-07-11 08:49:53 PM PT</t>
+          <t>2026-07-11 08:51:54 PM PT</t>
         </is>
       </c>
       <c r="C55" t="n">
@@ -6948,7 +6894,7 @@
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>2026-07-11 08:49:53 PM PT</t>
+          <t>2026-07-11 08:51:54 PM PT</t>
         </is>
       </c>
       <c r="C56" t="n">
@@ -7062,7 +7008,7 @@
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>2026-07-11 08:49:53 PM PT</t>
+          <t>2026-07-11 08:51:53 PM PT</t>
         </is>
       </c>
       <c r="C57" t="n">
@@ -7176,7 +7122,7 @@
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>2026-07-11 08:49:53 PM PT</t>
+          <t>2026-07-11 08:51:53 PM PT</t>
         </is>
       </c>
       <c r="C58" t="n">
@@ -7290,7 +7236,7 @@
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>2026-07-11 08:49:53 PM PT</t>
+          <t>2026-07-11 08:51:53 PM PT</t>
         </is>
       </c>
       <c r="C59" t="n">
@@ -7404,7 +7350,7 @@
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>2026-07-11 08:49:53 PM PT</t>
+          <t>2026-07-11 08:51:53 PM PT</t>
         </is>
       </c>
       <c r="C60" t="n">
@@ -7518,7 +7464,7 @@
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>2026-07-11 08:49:53 PM PT</t>
+          <t>2026-07-11 08:51:53 PM PT</t>
         </is>
       </c>
       <c r="C61" t="n">
@@ -7632,7 +7578,7 @@
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>2026-07-11 08:49:53 PM PT</t>
+          <t>2026-07-11 08:51:53 PM PT</t>
         </is>
       </c>
       <c r="C62" t="n">
@@ -7746,7 +7692,7 @@
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>2026-07-11 08:49:53 PM PT</t>
+          <t>2026-07-11 08:51:53 PM PT</t>
         </is>
       </c>
       <c r="C63" t="n">
@@ -7860,7 +7806,7 @@
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>2026-07-11 08:49:52 PM PT</t>
+          <t>2026-07-11 08:51:52 PM PT</t>
         </is>
       </c>
       <c r="C64" t="n">
@@ -7974,7 +7920,7 @@
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>2026-07-11 08:49:52 PM PT</t>
+          <t>2026-07-11 08:51:52 PM PT</t>
         </is>
       </c>
       <c r="C65" t="n">
@@ -8088,7 +8034,7 @@
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>2026-07-11 08:49:54 PM PT</t>
+          <t>2026-07-11 08:51:54 PM PT</t>
         </is>
       </c>
       <c r="C66" t="n">
@@ -8101,7 +8047,7 @@
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>Top 9 | 3 out</t>
+          <t>Game Over</t>
         </is>
       </c>
       <c r="F66" t="n">
@@ -8111,15 +8057,6 @@
         <is>
           <t>Top</t>
         </is>
-      </c>
-      <c r="H66" t="n">
-        <v>3</v>
-      </c>
-      <c r="I66" t="n">
-        <v>0</v>
-      </c>
-      <c r="J66" t="n">
-        <v>3</v>
       </c>
       <c r="K66" t="inlineStr">
         <is>
@@ -8211,7 +8148,7 @@
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>2026-07-11 08:49:53 PM PT</t>
+          <t>2026-07-11 08:51:53 PM PT</t>
         </is>
       </c>
       <c r="C67" t="n">
@@ -8325,7 +8262,7 @@
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>2026-07-11 08:49:53 PM PT</t>
+          <t>2026-07-11 08:51:53 PM PT</t>
         </is>
       </c>
       <c r="C68" t="n">
@@ -8439,7 +8376,7 @@
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>2026-07-11 08:49:53 PM PT</t>
+          <t>2026-07-11 08:51:53 PM PT</t>
         </is>
       </c>
       <c r="C69" t="n">
@@ -8553,7 +8490,7 @@
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>2026-07-11 08:49:53 PM PT</t>
+          <t>2026-07-11 08:51:53 PM PT</t>
         </is>
       </c>
       <c r="C70" t="n">
@@ -8667,7 +8604,7 @@
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>2026-07-11 08:49:53 PM PT</t>
+          <t>2026-07-11 08:51:53 PM PT</t>
         </is>
       </c>
       <c r="C71" t="n">
@@ -8781,7 +8718,7 @@
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>2026-07-11 08:49:54 PM PT</t>
+          <t>2026-07-11 08:51:54 PM PT</t>
         </is>
       </c>
       <c r="C72" t="n">
@@ -8794,7 +8731,7 @@
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>Top 9 | 2 out</t>
+          <t>Top 9 | 3 out</t>
         </is>
       </c>
       <c r="F72" t="n">
@@ -8806,7 +8743,7 @@
         </is>
       </c>
       <c r="H72" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="I72" t="n">
         <v>1</v>
@@ -8904,7 +8841,7 @@
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>2026-07-11 08:49:52 PM PT</t>
+          <t>2026-07-11 08:51:52 PM PT</t>
         </is>
       </c>
       <c r="C73" t="n">
@@ -9018,7 +8955,7 @@
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>2026-07-11 08:49:53 PM PT</t>
+          <t>2026-07-11 08:51:53 PM PT</t>
         </is>
       </c>
       <c r="C74" t="n">
@@ -9132,7 +9069,7 @@
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>2026-07-11 08:49:52 PM PT</t>
+          <t>2026-07-11 08:51:52 PM PT</t>
         </is>
       </c>
       <c r="C75" t="n">
@@ -9246,7 +9183,7 @@
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>2026-07-11 08:49:54 PM PT</t>
+          <t>2026-07-11 08:51:54 PM PT</t>
         </is>
       </c>
       <c r="C76" t="n">
@@ -9259,7 +9196,7 @@
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>Top 9 | 3 out</t>
+          <t>Game Over</t>
         </is>
       </c>
       <c r="F76" t="n">
@@ -9269,15 +9206,6 @@
         <is>
           <t>Top</t>
         </is>
-      </c>
-      <c r="H76" t="n">
-        <v>3</v>
-      </c>
-      <c r="I76" t="n">
-        <v>0</v>
-      </c>
-      <c r="J76" t="n">
-        <v>3</v>
       </c>
       <c r="K76" t="inlineStr">
         <is>
@@ -9369,7 +9297,7 @@
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>2026-07-11 08:49:54 PM PT</t>
+          <t>2026-07-11 08:51:54 PM PT</t>
         </is>
       </c>
       <c r="C77" t="n">
@@ -9382,7 +9310,7 @@
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>Top 9 | 3 out</t>
+          <t>Game Over</t>
         </is>
       </c>
       <c r="F77" t="n">
@@ -9392,15 +9320,6 @@
         <is>
           <t>Top</t>
         </is>
-      </c>
-      <c r="H77" t="n">
-        <v>3</v>
-      </c>
-      <c r="I77" t="n">
-        <v>0</v>
-      </c>
-      <c r="J77" t="n">
-        <v>3</v>
       </c>
       <c r="K77" t="inlineStr">
         <is>
@@ -9492,7 +9411,7 @@
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>2026-07-11 08:49:53 PM PT</t>
+          <t>2026-07-11 08:51:54 PM PT</t>
         </is>
       </c>
       <c r="C78" t="n">
@@ -9606,7 +9525,7 @@
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>2026-07-11 08:49:53 PM PT</t>
+          <t>2026-07-11 08:51:54 PM PT</t>
         </is>
       </c>
       <c r="C79" t="n">
@@ -9720,7 +9639,7 @@
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>2026-07-11 08:49:53 PM PT</t>
+          <t>2026-07-11 08:51:53 PM PT</t>
         </is>
       </c>
       <c r="C80" t="n">
@@ -9834,7 +9753,7 @@
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>2026-07-11 08:49:52 PM PT</t>
+          <t>2026-07-11 08:51:52 PM PT</t>
         </is>
       </c>
       <c r="C81" t="n">
@@ -9948,7 +9867,7 @@
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>2026-07-11 08:49:52 PM PT</t>
+          <t>2026-07-11 08:51:52 PM PT</t>
         </is>
       </c>
       <c r="C82" t="n">
@@ -10062,7 +9981,7 @@
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>2026-07-11 08:49:52 PM PT</t>
+          <t>2026-07-11 08:51:52 PM PT</t>
         </is>
       </c>
       <c r="C83" t="n">
@@ -10176,7 +10095,7 @@
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>2026-07-11 08:49:52 PM PT</t>
+          <t>2026-07-11 08:51:52 PM PT</t>
         </is>
       </c>
       <c r="C84" t="n">
@@ -10290,7 +10209,7 @@
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>2026-07-11 08:49:52 PM PT</t>
+          <t>2026-07-11 08:51:52 PM PT</t>
         </is>
       </c>
       <c r="C85" t="n">
@@ -10404,7 +10323,7 @@
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>2026-07-11 08:49:52 PM PT</t>
+          <t>2026-07-11 08:51:52 PM PT</t>
         </is>
       </c>
       <c r="C86" t="n">
@@ -10518,7 +10437,7 @@
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>2026-07-11 08:49:53 PM PT</t>
+          <t>2026-07-11 08:51:53 PM PT</t>
         </is>
       </c>
       <c r="C87" t="n">
@@ -10632,7 +10551,7 @@
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>2026-07-11 08:49:53 PM PT</t>
+          <t>2026-07-11 08:51:53 PM PT</t>
         </is>
       </c>
       <c r="C88" t="n">
@@ -10746,7 +10665,7 @@
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>2026-07-11 08:49:53 PM PT</t>
+          <t>2026-07-11 08:51:53 PM PT</t>
         </is>
       </c>
       <c r="C89" t="n">
@@ -10860,7 +10779,7 @@
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>2026-07-11 08:49:53 PM PT</t>
+          <t>2026-07-11 08:51:53 PM PT</t>
         </is>
       </c>
       <c r="C90" t="n">
@@ -10974,7 +10893,7 @@
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>2026-07-11 08:49:53 PM PT</t>
+          <t>2026-07-11 08:51:53 PM PT</t>
         </is>
       </c>
       <c r="C91" t="n">
@@ -11088,7 +11007,7 @@
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>2026-07-11 08:49:53 PM PT</t>
+          <t>2026-07-11 08:51:54 PM PT</t>
         </is>
       </c>
       <c r="C92" t="n">
@@ -11202,7 +11121,7 @@
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>2026-07-11 08:49:54 PM PT</t>
+          <t>2026-07-11 08:51:54 PM PT</t>
         </is>
       </c>
       <c r="C93" t="n">
@@ -11215,7 +11134,7 @@
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>Top 9 | 2 out</t>
+          <t>Top 9 | 3 out</t>
         </is>
       </c>
       <c r="F93" t="n">
@@ -11227,7 +11146,7 @@
         </is>
       </c>
       <c r="H93" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="I93" t="n">
         <v>1</v>
@@ -11325,7 +11244,7 @@
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>2026-07-11 08:49:53 PM PT</t>
+          <t>2026-07-11 08:51:53 PM PT</t>
         </is>
       </c>
       <c r="C94" t="n">
@@ -11439,7 +11358,7 @@
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>2026-07-11 08:49:53 PM PT</t>
+          <t>2026-07-11 08:51:53 PM PT</t>
         </is>
       </c>
       <c r="C95" t="n">
@@ -11553,7 +11472,7 @@
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>2026-07-11 08:49:53 PM PT</t>
+          <t>2026-07-11 08:51:53 PM PT</t>
         </is>
       </c>
       <c r="C96" t="n">
@@ -11667,7 +11586,7 @@
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>2026-07-11 08:49:53 PM PT</t>
+          <t>2026-07-11 08:51:54 PM PT</t>
         </is>
       </c>
       <c r="C97" t="n">
@@ -11781,7 +11700,7 @@
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>2026-07-11 08:49:53 PM PT</t>
+          <t>2026-07-11 08:51:54 PM PT</t>
         </is>
       </c>
       <c r="C98" t="n">
@@ -11895,7 +11814,7 @@
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>2026-07-11 08:49:54 PM PT</t>
+          <t>2026-07-11 08:51:54 PM PT</t>
         </is>
       </c>
       <c r="C99" t="n">
@@ -11908,7 +11827,7 @@
       </c>
       <c r="E99" t="inlineStr">
         <is>
-          <t>Top 9 | 2 out</t>
+          <t>Top 9 | 3 out</t>
         </is>
       </c>
       <c r="F99" t="n">
@@ -11920,7 +11839,7 @@
         </is>
       </c>
       <c r="H99" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="I99" t="n">
         <v>1</v>
@@ -12018,7 +11937,7 @@
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>2026-07-11 08:49:53 PM PT</t>
+          <t>2026-07-11 08:51:53 PM PT</t>
         </is>
       </c>
       <c r="C100" t="n">
@@ -12132,7 +12051,7 @@
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>2026-07-11 08:49:52 PM PT</t>
+          <t>2026-07-11 08:51:52 PM PT</t>
         </is>
       </c>
       <c r="C101" t="n">
@@ -12246,7 +12165,7 @@
       </c>
       <c r="B102" t="inlineStr">
         <is>
-          <t>2026-07-11 08:49:53 PM PT</t>
+          <t>2026-07-11 08:51:53 PM PT</t>
         </is>
       </c>
       <